--- a/data/teams/leagues/Averages_Belgium_Pro_League_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Belgium_Pro_League_2025-2026.xlsx
@@ -137,7 +137,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="AveragesTable" displayName="AveragesTable" ref="A1:EC17" headerRowCount="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="AveragesTable_Belgium_Pr" displayName="AveragesTable_Belgium_Pr" ref="A1:EC17" headerRowCount="1">
   <autoFilter ref="A1:EC17"/>
   <tableColumns count="133">
     <tableColumn id="1" name="team_name"/>

--- a/data/teams/leagues/Averages_Belgium_Pro_League_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Belgium_Pro_League_2025-2026.xlsx
@@ -6614,94 +6614,94 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C15" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D15" t="n">
         <v>7</v>
       </c>
       <c r="E15" t="n">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="F15" t="n">
-        <v>1.71</v>
+        <v>1.75</v>
       </c>
       <c r="G15" t="n">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="H15" t="n">
-        <v>86</v>
+        <v>85.5</v>
       </c>
       <c r="I15" t="n">
         <v>0</v>
       </c>
       <c r="J15" t="n">
-        <v>3.29</v>
+        <v>3.38</v>
       </c>
       <c r="K15" t="n">
-        <v>5.43</v>
+        <v>5.38</v>
       </c>
       <c r="L15" t="n">
-        <v>0.43</v>
+        <v>0.5</v>
       </c>
       <c r="M15" t="n">
-        <v>42</v>
+        <v>56.25</v>
       </c>
       <c r="N15" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="O15" t="n">
-        <v>3.29</v>
+        <v>3.25</v>
       </c>
       <c r="P15" t="n">
-        <v>11.14</v>
+        <v>11.38</v>
       </c>
       <c r="Q15" t="n">
-        <v>12.43</v>
+        <v>12.38</v>
       </c>
       <c r="R15" t="n">
-        <v>8.859999999999999</v>
+        <v>8.380000000000001</v>
       </c>
       <c r="S15" t="n">
-        <v>1.29</v>
+        <v>1.12</v>
       </c>
       <c r="T15" t="n">
-        <v>1.29</v>
+        <v>1.12</v>
       </c>
       <c r="U15" t="n">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="V15" t="n">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="W15" t="n">
         <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>41</v>
+        <v>45.12</v>
       </c>
       <c r="Y15" t="n">
-        <v>0.29</v>
+        <v>0.38</v>
       </c>
       <c r="Z15" t="n">
-        <v>11.29</v>
+        <v>12.5</v>
       </c>
       <c r="AA15" t="n">
-        <v>6.86</v>
+        <v>7.62</v>
       </c>
       <c r="AB15" t="n">
-        <v>4.43</v>
+        <v>4.88</v>
       </c>
       <c r="AC15" t="n">
-        <v>17.86</v>
+        <v>18.38</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.33</v>
+        <v>1.54</v>
       </c>
       <c r="AE15" t="n">
-        <v>2.71</v>
+        <v>2.62</v>
       </c>
       <c r="AF15" t="n">
         <v>0.14</v>
@@ -6785,49 +6785,49 @@
         <v>2.14</v>
       </c>
       <c r="BG15" t="n">
-        <v>2.29</v>
+        <v>2.13</v>
       </c>
       <c r="BH15" t="n">
-        <v>9.640000000000001</v>
+        <v>9.529999999999999</v>
       </c>
       <c r="BI15" t="n">
-        <v>2.29</v>
+        <v>2.13</v>
       </c>
       <c r="BJ15" t="n">
-        <v>0.57</v>
+        <v>0.53</v>
       </c>
       <c r="BK15" t="n">
-        <v>0.64</v>
+        <v>0.6</v>
       </c>
       <c r="BL15" t="n">
-        <v>0.79</v>
+        <v>0.73</v>
       </c>
       <c r="BM15" t="n">
-        <v>0.29</v>
+        <v>0.27</v>
       </c>
       <c r="BN15" t="n">
-        <v>1.07</v>
+        <v>1</v>
       </c>
       <c r="BO15" t="n">
-        <v>1.21</v>
+        <v>1.13</v>
       </c>
       <c r="BP15" t="n">
-        <v>4.64</v>
+        <v>4.53</v>
       </c>
       <c r="BQ15" t="n">
         <v>5</v>
       </c>
       <c r="BR15" t="n">
-        <v>100</v>
+        <v>93.33</v>
       </c>
       <c r="BS15" t="n">
-        <v>71.43000000000001</v>
+        <v>66.67</v>
       </c>
       <c r="BT15" t="n">
-        <v>42.86</v>
+        <v>40</v>
       </c>
       <c r="BU15" t="n">
-        <v>14.29</v>
+        <v>13.33</v>
       </c>
       <c r="BV15" t="n">
         <v>0</v>
@@ -6836,19 +6836,19 @@
         <v>0</v>
       </c>
       <c r="BX15" t="n">
-        <v>35.71</v>
+        <v>33.33</v>
       </c>
       <c r="BY15" t="n">
-        <v>2.97</v>
+        <v>2.9</v>
       </c>
       <c r="BZ15" t="n">
-        <v>3.2</v>
+        <v>3.11</v>
       </c>
       <c r="CA15" t="n">
-        <v>3.54</v>
+        <v>3.53</v>
       </c>
       <c r="CB15" t="n">
-        <v>3.6</v>
+        <v>3.59</v>
       </c>
       <c r="CC15" t="n">
         <v>4.34</v>
@@ -6857,7 +6857,7 @@
         <v>4.99</v>
       </c>
       <c r="CE15" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="CF15" t="n">
         <v>2.78</v>
@@ -6869,22 +6869,22 @@
         <v>1.41</v>
       </c>
       <c r="CI15" t="n">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="CJ15" t="n">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="CK15" t="n">
         <v>1.47</v>
       </c>
       <c r="CL15" t="n">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="CM15" t="n">
-        <v>2.58</v>
+        <v>2.6</v>
       </c>
       <c r="CN15" t="n">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="CO15" t="n">
         <v>1.3</v>
@@ -6893,121 +6893,121 @@
         <v>1.92</v>
       </c>
       <c r="CQ15" t="n">
-        <v>3.44</v>
+        <v>3.41</v>
       </c>
       <c r="CR15" t="n">
         <v>1.4</v>
       </c>
       <c r="CS15" t="n">
-        <v>2.9</v>
+        <v>2.88</v>
       </c>
       <c r="CT15" t="n">
-        <v>3.04</v>
+        <v>3.05</v>
       </c>
       <c r="CU15" t="n">
         <v>1.45</v>
       </c>
       <c r="CV15" t="n">
-        <v>2.07</v>
+        <v>2.09</v>
       </c>
       <c r="CW15" t="n">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="CX15" t="n">
         <v>1.56</v>
       </c>
       <c r="CY15" t="n">
-        <v>1.92</v>
+        <v>1.9</v>
       </c>
       <c r="CZ15" t="n">
         <v>2.39</v>
       </c>
       <c r="DA15" t="n">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="DB15" t="n">
         <v>1.32</v>
       </c>
       <c r="DC15" t="n">
-        <v>2.01</v>
+        <v>2</v>
       </c>
       <c r="DD15" t="n">
-        <v>3.44</v>
+        <v>3.41</v>
       </c>
       <c r="DE15" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="DF15" t="n">
-        <v>1.64</v>
+        <v>1.67</v>
       </c>
       <c r="DG15" t="n">
-        <v>1.64</v>
+        <v>1.66</v>
       </c>
       <c r="DH15" t="n">
-        <v>84.28</v>
+        <v>84.13</v>
       </c>
       <c r="DI15" t="n">
         <v>0</v>
       </c>
       <c r="DJ15" t="n">
-        <v>2.86</v>
+        <v>2.94</v>
       </c>
       <c r="DK15" t="n">
-        <v>3.86</v>
+        <v>3.94</v>
       </c>
       <c r="DL15" t="n">
-        <v>0.28</v>
+        <v>0.33</v>
       </c>
       <c r="DM15" t="n">
-        <v>36.71</v>
+        <v>44.67</v>
       </c>
       <c r="DN15" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="DO15" t="n">
-        <v>2.22</v>
+        <v>2.27</v>
       </c>
       <c r="DP15" t="n">
-        <v>11</v>
+        <v>11.14</v>
       </c>
       <c r="DQ15" t="n">
         <v>12.14</v>
       </c>
       <c r="DR15" t="n">
-        <v>9.279999999999999</v>
+        <v>9</v>
       </c>
       <c r="DS15" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="DT15" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="DU15" t="n">
         <v>0</v>
       </c>
       <c r="DV15" t="n">
-        <v>43.22</v>
+        <v>45.26</v>
       </c>
       <c r="DW15" t="n">
-        <v>0.29</v>
+        <v>0.34</v>
       </c>
       <c r="DX15" t="n">
-        <v>9.289999999999999</v>
+        <v>10.07</v>
       </c>
       <c r="DY15" t="n">
-        <v>6</v>
+        <v>6.46</v>
       </c>
       <c r="DZ15" t="n">
-        <v>3.28</v>
+        <v>3.6</v>
       </c>
       <c r="EA15" t="n">
-        <v>17.86</v>
+        <v>18.14</v>
       </c>
       <c r="EB15" t="n">
-        <v>1.09</v>
+        <v>1.22</v>
       </c>
       <c r="EC15" t="n">
-        <v>2.43</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="16">
@@ -7420,13 +7420,13 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C17" t="n">
         <v>7</v>
       </c>
       <c r="D17" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
@@ -7510,139 +7510,139 @@
         <v>1.43</v>
       </c>
       <c r="AF17" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.43</v>
+        <v>1.38</v>
       </c>
       <c r="AH17" t="n">
-        <v>2.29</v>
+        <v>2.38</v>
       </c>
       <c r="AI17" t="n">
-        <v>92.29000000000001</v>
+        <v>88.38</v>
       </c>
       <c r="AJ17" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="AK17" t="n">
-        <v>1.71</v>
+        <v>1.88</v>
       </c>
       <c r="AL17" t="n">
-        <v>4.86</v>
+        <v>4.62</v>
       </c>
       <c r="AM17" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="AN17" t="n">
-        <v>46.86</v>
+        <v>48.75</v>
       </c>
       <c r="AO17" t="n">
-        <v>0.29</v>
+        <v>0.38</v>
       </c>
       <c r="AP17" t="n">
-        <v>1.57</v>
+        <v>1.38</v>
       </c>
       <c r="AQ17" t="n">
-        <v>13.71</v>
+        <v>13.5</v>
       </c>
       <c r="AR17" t="n">
-        <v>8.57</v>
+        <v>9.119999999999999</v>
       </c>
       <c r="AS17" t="n">
-        <v>9.43</v>
+        <v>9.880000000000001</v>
       </c>
       <c r="AT17" t="n">
-        <v>1.71</v>
+        <v>1.5</v>
       </c>
       <c r="AU17" t="n">
-        <v>1.57</v>
+        <v>1.38</v>
       </c>
       <c r="AV17" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="AW17" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="AX17" t="n">
         <v>0</v>
       </c>
       <c r="AY17" t="n">
-        <v>50.14</v>
+        <v>47.12</v>
       </c>
       <c r="AZ17" t="n">
-        <v>0</v>
+        <v>0.12</v>
       </c>
       <c r="BA17" t="n">
-        <v>12.29</v>
+        <v>11.5</v>
       </c>
       <c r="BB17" t="n">
-        <v>8</v>
+        <v>7.5</v>
       </c>
       <c r="BC17" t="n">
-        <v>4.29</v>
+        <v>4</v>
       </c>
       <c r="BD17" t="n">
-        <v>20.57</v>
+        <v>19.62</v>
       </c>
       <c r="BE17" t="n">
-        <v>1.42</v>
+        <v>1.36</v>
       </c>
       <c r="BF17" t="n">
-        <v>1.71</v>
+        <v>1.62</v>
       </c>
       <c r="BG17" t="n">
-        <v>3</v>
+        <v>2.8</v>
       </c>
       <c r="BH17" t="n">
-        <v>10.71</v>
+        <v>10.53</v>
       </c>
       <c r="BI17" t="n">
-        <v>3</v>
+        <v>2.8</v>
       </c>
       <c r="BJ17" t="n">
-        <v>0.79</v>
+        <v>0.73</v>
       </c>
       <c r="BK17" t="n">
-        <v>0.57</v>
+        <v>0.53</v>
       </c>
       <c r="BL17" t="n">
-        <v>0.79</v>
+        <v>0.73</v>
       </c>
       <c r="BM17" t="n">
-        <v>0.86</v>
+        <v>0.8</v>
       </c>
       <c r="BN17" t="n">
-        <v>1.64</v>
+        <v>1.53</v>
       </c>
       <c r="BO17" t="n">
-        <v>1.36</v>
+        <v>1.27</v>
       </c>
       <c r="BP17" t="n">
-        <v>3.86</v>
+        <v>3.8</v>
       </c>
       <c r="BQ17" t="n">
-        <v>5.93</v>
+        <v>5.87</v>
       </c>
       <c r="BR17" t="n">
-        <v>92.86</v>
+        <v>86.67</v>
       </c>
       <c r="BS17" t="n">
-        <v>85.70999999999999</v>
+        <v>80</v>
       </c>
       <c r="BT17" t="n">
-        <v>50</v>
+        <v>46.67</v>
       </c>
       <c r="BU17" t="n">
-        <v>42.86</v>
+        <v>40</v>
       </c>
       <c r="BV17" t="n">
-        <v>28.57</v>
+        <v>26.67</v>
       </c>
       <c r="BW17" t="n">
         <v>0</v>
       </c>
       <c r="BX17" t="n">
-        <v>64.29000000000001</v>
+        <v>60</v>
       </c>
       <c r="BY17" t="n">
         <v>3.17</v>
@@ -7651,40 +7651,40 @@
         <v>3.44</v>
       </c>
       <c r="CA17" t="n">
-        <v>3.77</v>
+        <v>3.75</v>
       </c>
       <c r="CB17" t="n">
-        <v>3.77</v>
+        <v>3.74</v>
       </c>
       <c r="CC17" t="n">
-        <v>3.94</v>
+        <v>3.81</v>
       </c>
       <c r="CD17" t="n">
-        <v>4.34</v>
+        <v>4.17</v>
       </c>
       <c r="CE17" t="n">
         <v>1.3</v>
       </c>
       <c r="CF17" t="n">
-        <v>2.41</v>
+        <v>2.43</v>
       </c>
       <c r="CG17" t="n">
-        <v>3.37</v>
+        <v>3.34</v>
       </c>
       <c r="CH17" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="CI17" t="n">
-        <v>2.22</v>
+        <v>2.21</v>
       </c>
       <c r="CJ17" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="CK17" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="CL17" t="n">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="CM17" t="n">
         <v>2.7</v>
@@ -7696,28 +7696,28 @@
         <v>1.2</v>
       </c>
       <c r="CP17" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="CQ17" t="n">
-        <v>2.68</v>
+        <v>2.71</v>
       </c>
       <c r="CR17" t="n">
         <v>1.36</v>
       </c>
       <c r="CS17" t="n">
-        <v>2.56</v>
+        <v>2.58</v>
       </c>
       <c r="CT17" t="n">
         <v>3.23</v>
       </c>
       <c r="CU17" t="n">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="CV17" t="n">
-        <v>2.35</v>
+        <v>2.36</v>
       </c>
       <c r="CW17" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="CX17" t="n">
         <v>1.53</v>
@@ -7729,7 +7729,7 @@
         <v>2.45</v>
       </c>
       <c r="DA17" t="n">
-        <v>2.06</v>
+        <v>2.07</v>
       </c>
       <c r="DB17" t="n">
         <v>1.23</v>
@@ -7738,82 +7738,82 @@
         <v>1.75</v>
       </c>
       <c r="DD17" t="n">
-        <v>2.79</v>
+        <v>2.81</v>
       </c>
       <c r="DE17" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="DF17" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="DG17" t="n">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="DH17" t="n">
-        <v>93.58</v>
+        <v>91.40000000000001</v>
       </c>
       <c r="DI17" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="DJ17" t="n">
-        <v>1.71</v>
+        <v>1.8</v>
       </c>
       <c r="DK17" t="n">
-        <v>4.22</v>
+        <v>4.13</v>
       </c>
       <c r="DL17" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DM17" t="n">
-        <v>43.08</v>
+        <v>44.34</v>
       </c>
       <c r="DN17" t="n">
-        <v>0.36</v>
+        <v>0.4</v>
       </c>
       <c r="DO17" t="n">
-        <v>1.57</v>
+        <v>1.47</v>
       </c>
       <c r="DP17" t="n">
-        <v>11.78</v>
+        <v>11.8</v>
       </c>
       <c r="DQ17" t="n">
-        <v>10.93</v>
+        <v>11.07</v>
       </c>
       <c r="DR17" t="n">
-        <v>10.36</v>
+        <v>10.54</v>
       </c>
       <c r="DS17" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="DT17" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="DU17" t="n">
         <v>0</v>
       </c>
       <c r="DV17" t="n">
-        <v>46.36</v>
+        <v>45</v>
       </c>
       <c r="DW17" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.13</v>
       </c>
       <c r="DX17" t="n">
-        <v>12.29</v>
+        <v>11.87</v>
       </c>
       <c r="DY17" t="n">
-        <v>7.86</v>
+        <v>7.6</v>
       </c>
       <c r="DZ17" t="n">
-        <v>4.43</v>
+        <v>4.27</v>
       </c>
       <c r="EA17" t="n">
-        <v>20.43</v>
+        <v>19.93</v>
       </c>
       <c r="EB17" t="n">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
       <c r="EC17" t="n">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
     </row>
   </sheetData>

--- a/data/teams/leagues/Averages_Belgium_Pro_League_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Belgium_Pro_League_2025-2026.xlsx
@@ -1379,13 +1379,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C2" t="n">
         <v>8</v>
       </c>
       <c r="D2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
@@ -1475,46 +1475,46 @@
         <v>1</v>
       </c>
       <c r="AH2" t="n">
-        <v>2.33</v>
+        <v>2.29</v>
       </c>
       <c r="AI2" t="n">
-        <v>108.33</v>
+        <v>109.14</v>
       </c>
       <c r="AJ2" t="n">
-        <v>0</v>
+        <v>0.14</v>
       </c>
       <c r="AK2" t="n">
-        <v>2.5</v>
+        <v>2.71</v>
       </c>
       <c r="AL2" t="n">
-        <v>4.33</v>
+        <v>4.29</v>
       </c>
       <c r="AM2" t="n">
-        <v>0.83</v>
+        <v>0.71</v>
       </c>
       <c r="AN2" t="n">
-        <v>52</v>
+        <v>52.57</v>
       </c>
       <c r="AO2" t="n">
-        <v>1.33</v>
+        <v>1.57</v>
       </c>
       <c r="AP2" t="n">
         <v>2</v>
       </c>
       <c r="AQ2" t="n">
-        <v>12.83</v>
+        <v>12.43</v>
       </c>
       <c r="AR2" t="n">
-        <v>10.17</v>
+        <v>11.14</v>
       </c>
       <c r="AS2" t="n">
-        <v>7.83</v>
+        <v>7.57</v>
       </c>
       <c r="AT2" t="n">
-        <v>0.83</v>
+        <v>1</v>
       </c>
       <c r="AU2" t="n">
-        <v>0.83</v>
+        <v>0.71</v>
       </c>
       <c r="AV2" t="n">
         <v>0</v>
@@ -1526,82 +1526,82 @@
         <v>0</v>
       </c>
       <c r="AY2" t="n">
-        <v>49.83</v>
+        <v>49.29</v>
       </c>
       <c r="AZ2" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="BA2" t="n">
-        <v>13.5</v>
+        <v>12.71</v>
       </c>
       <c r="BB2" t="n">
-        <v>9.33</v>
+        <v>9</v>
       </c>
       <c r="BC2" t="n">
-        <v>4.17</v>
+        <v>3.71</v>
       </c>
       <c r="BD2" t="n">
-        <v>23.33</v>
+        <v>24.14</v>
       </c>
       <c r="BE2" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="BF2" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="BG2" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="BH2" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="BI2" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="BJ2" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="BK2" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="BL2" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="BM2" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="BN2" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="BO2" t="n">
         <v>1.53</v>
       </c>
-      <c r="BF2" t="n">
-        <v>2.17</v>
-      </c>
-      <c r="BG2" t="n">
-        <v>2.79</v>
-      </c>
-      <c r="BH2" t="n">
-        <v>9.289999999999999</v>
-      </c>
-      <c r="BI2" t="n">
-        <v>2.79</v>
-      </c>
-      <c r="BJ2" t="n">
-        <v>0.71</v>
-      </c>
-      <c r="BK2" t="n">
-        <v>0.86</v>
-      </c>
-      <c r="BL2" t="n">
-        <v>0.57</v>
-      </c>
-      <c r="BM2" t="n">
-        <v>0.64</v>
-      </c>
-      <c r="BN2" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="BO2" t="n">
-        <v>1.57</v>
-      </c>
       <c r="BP2" t="n">
-        <v>4</v>
+        <v>4.13</v>
       </c>
       <c r="BQ2" t="n">
-        <v>5.29</v>
+        <v>5.27</v>
       </c>
       <c r="BR2" t="n">
-        <v>85.70999999999999</v>
+        <v>86.67</v>
       </c>
       <c r="BS2" t="n">
-        <v>85.70999999999999</v>
+        <v>86.67</v>
       </c>
       <c r="BT2" t="n">
-        <v>50</v>
+        <v>46.67</v>
       </c>
       <c r="BU2" t="n">
-        <v>28.57</v>
+        <v>26.67</v>
       </c>
       <c r="BV2" t="n">
-        <v>21.43</v>
+        <v>20</v>
       </c>
       <c r="BW2" t="n">
-        <v>7.14</v>
+        <v>6.67</v>
       </c>
       <c r="BX2" t="n">
-        <v>64.29000000000001</v>
+        <v>60</v>
       </c>
       <c r="BY2" t="n">
         <v>2.36</v>
@@ -1610,73 +1610,73 @@
         <v>2.42</v>
       </c>
       <c r="CA2" t="n">
-        <v>3.46</v>
+        <v>3.54</v>
       </c>
       <c r="CB2" t="n">
-        <v>3.62</v>
+        <v>3.7</v>
       </c>
       <c r="CC2" t="n">
-        <v>3.05</v>
+        <v>3.65</v>
       </c>
       <c r="CD2" t="n">
-        <v>3.32</v>
+        <v>3.9</v>
       </c>
       <c r="CE2" t="n">
         <v>1.32</v>
       </c>
       <c r="CF2" t="n">
-        <v>2.55</v>
+        <v>2.52</v>
       </c>
       <c r="CG2" t="n">
-        <v>3.12</v>
+        <v>3.16</v>
       </c>
       <c r="CH2" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="CI2" t="n">
-        <v>2.19</v>
+        <v>2.18</v>
       </c>
       <c r="CJ2" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="CK2" t="n">
         <v>1.45</v>
       </c>
       <c r="CL2" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="CM2" t="n">
-        <v>2.57</v>
+        <v>2.58</v>
       </c>
       <c r="CN2" t="n">
-        <v>2</v>
+        <v>2.01</v>
       </c>
       <c r="CO2" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="CP2" t="n">
-        <v>1.77</v>
+        <v>1.75</v>
       </c>
       <c r="CQ2" t="n">
-        <v>2.95</v>
+        <v>2.92</v>
       </c>
       <c r="CR2" t="n">
         <v>1.36</v>
       </c>
       <c r="CS2" t="n">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="CT2" t="n">
         <v>3.23</v>
       </c>
       <c r="CU2" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="CV2" t="n">
-        <v>2.33</v>
+        <v>2.31</v>
       </c>
       <c r="CW2" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="CX2" t="n">
         <v>1.5</v>
@@ -1694,85 +1694,85 @@
         <v>1.24</v>
       </c>
       <c r="DC2" t="n">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="DD2" t="n">
-        <v>2.88</v>
+        <v>2.86</v>
       </c>
       <c r="DE2" t="n">
         <v>0</v>
       </c>
       <c r="DF2" t="n">
-        <v>0.93</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="DG2" t="n">
-        <v>2.5</v>
+        <v>2.47</v>
       </c>
       <c r="DH2" t="n">
-        <v>108</v>
+        <v>108.4</v>
       </c>
       <c r="DI2" t="n">
-        <v>0</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="DJ2" t="n">
-        <v>1.86</v>
+        <v>2</v>
       </c>
       <c r="DK2" t="n">
-        <v>4.36</v>
+        <v>4.34</v>
       </c>
       <c r="DL2" t="n">
-        <v>0.5</v>
+        <v>0.46</v>
       </c>
       <c r="DM2" t="n">
-        <v>49.57</v>
+        <v>50</v>
       </c>
       <c r="DN2" t="n">
-        <v>0.86</v>
+        <v>1</v>
       </c>
       <c r="DO2" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="DP2" t="n">
-        <v>10.42</v>
+        <v>10.4</v>
       </c>
       <c r="DQ2" t="n">
-        <v>11.93</v>
+        <v>12.27</v>
       </c>
       <c r="DR2" t="n">
-        <v>7.5</v>
+        <v>7.4</v>
       </c>
       <c r="DS2" t="n">
-        <v>0.29</v>
+        <v>0.27</v>
       </c>
       <c r="DT2" t="n">
-        <v>0.29</v>
+        <v>0.27</v>
       </c>
       <c r="DU2" t="n">
         <v>0</v>
       </c>
       <c r="DV2" t="n">
-        <v>50.85</v>
+        <v>50.53</v>
       </c>
       <c r="DW2" t="n">
         <v>0.07000000000000001</v>
       </c>
       <c r="DX2" t="n">
-        <v>14.43</v>
+        <v>14</v>
       </c>
       <c r="DY2" t="n">
-        <v>9.93</v>
+        <v>9.74</v>
       </c>
       <c r="DZ2" t="n">
-        <v>4.5</v>
+        <v>4.26</v>
       </c>
       <c r="EA2" t="n">
-        <v>23.5</v>
+        <v>23.86</v>
       </c>
       <c r="EB2" t="n">
-        <v>1.59</v>
+        <v>1.55</v>
       </c>
       <c r="EC2" t="n">
-        <v>1.72</v>
+        <v>1.87</v>
       </c>
     </row>
     <row r="3">
@@ -1782,10 +1782,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C3" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D3" t="n">
         <v>8</v>
@@ -1794,49 +1794,49 @@
         <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>1.33</v>
+        <v>1.43</v>
       </c>
       <c r="G3" t="n">
-        <v>4.33</v>
+        <v>3.71</v>
       </c>
       <c r="H3" t="n">
-        <v>122.17</v>
+        <v>113.14</v>
       </c>
       <c r="I3" t="n">
         <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>1.67</v>
+        <v>1.71</v>
       </c>
       <c r="K3" t="n">
-        <v>6.83</v>
+        <v>6.71</v>
       </c>
       <c r="L3" t="n">
-        <v>0.83</v>
+        <v>1</v>
       </c>
       <c r="M3" t="n">
-        <v>67.5</v>
+        <v>64.29000000000001</v>
       </c>
       <c r="N3" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="O3" t="n">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="P3" t="n">
-        <v>10.17</v>
+        <v>9.43</v>
       </c>
       <c r="Q3" t="n">
-        <v>12.17</v>
+        <v>11.71</v>
       </c>
       <c r="R3" t="n">
-        <v>6.83</v>
+        <v>7.29</v>
       </c>
       <c r="S3" t="n">
-        <v>1.17</v>
+        <v>1</v>
       </c>
       <c r="T3" t="n">
-        <v>2.33</v>
+        <v>2.14</v>
       </c>
       <c r="U3" t="n">
         <v>0</v>
@@ -1848,28 +1848,28 @@
         <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>63.67</v>
+        <v>63.29</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="Z3" t="n">
-        <v>16.33</v>
+        <v>16.43</v>
       </c>
       <c r="AA3" t="n">
-        <v>11.33</v>
+        <v>11.43</v>
       </c>
       <c r="AB3" t="n">
         <v>5</v>
       </c>
       <c r="AC3" t="n">
-        <v>22.67</v>
+        <v>22.14</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.87</v>
+        <v>1.85</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.33</v>
+        <v>1.43</v>
       </c>
       <c r="AF3" t="n">
         <v>0.12</v>
@@ -1953,70 +1953,70 @@
         <v>1.62</v>
       </c>
       <c r="BG3" t="n">
-        <v>2.43</v>
+        <v>2.33</v>
       </c>
       <c r="BH3" t="n">
-        <v>10.79</v>
+        <v>11.2</v>
       </c>
       <c r="BI3" t="n">
-        <v>2.43</v>
+        <v>2.33</v>
       </c>
       <c r="BJ3" t="n">
-        <v>0.57</v>
+        <v>0.53</v>
       </c>
       <c r="BK3" t="n">
-        <v>0.36</v>
+        <v>0.33</v>
       </c>
       <c r="BL3" t="n">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="BM3" t="n">
-        <v>0.64</v>
+        <v>0.6</v>
       </c>
       <c r="BN3" t="n">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="BO3" t="n">
-        <v>0.93</v>
+        <v>0.87</v>
       </c>
       <c r="BP3" t="n">
-        <v>4.93</v>
+        <v>5.27</v>
       </c>
       <c r="BQ3" t="n">
-        <v>5.86</v>
+        <v>5.93</v>
       </c>
       <c r="BR3" t="n">
         <v>100</v>
       </c>
       <c r="BS3" t="n">
-        <v>57.14</v>
+        <v>53.33</v>
       </c>
       <c r="BT3" t="n">
-        <v>35.71</v>
+        <v>33.33</v>
       </c>
       <c r="BU3" t="n">
-        <v>7.14</v>
+        <v>6.67</v>
       </c>
       <c r="BV3" t="n">
-        <v>7.14</v>
+        <v>6.67</v>
       </c>
       <c r="BW3" t="n">
-        <v>7.14</v>
+        <v>6.67</v>
       </c>
       <c r="BX3" t="n">
-        <v>42.86</v>
+        <v>40</v>
       </c>
       <c r="BY3" t="n">
         <v>1.55</v>
       </c>
       <c r="BZ3" t="n">
-        <v>1.54</v>
+        <v>1.56</v>
       </c>
       <c r="CA3" t="n">
-        <v>4.42</v>
+        <v>4.43</v>
       </c>
       <c r="CB3" t="n">
-        <v>4.71</v>
+        <v>4.69</v>
       </c>
       <c r="CC3" t="n">
         <v>1.64</v>
@@ -2028,10 +2028,10 @@
         <v>1.26</v>
       </c>
       <c r="CF3" t="n">
-        <v>2.24</v>
+        <v>2.25</v>
       </c>
       <c r="CG3" t="n">
-        <v>3.52</v>
+        <v>3.53</v>
       </c>
       <c r="CH3" t="n">
         <v>1.6</v>
@@ -2046,16 +2046,16 @@
         <v>1.46</v>
       </c>
       <c r="CL3" t="n">
-        <v>1.87</v>
+        <v>1.89</v>
       </c>
       <c r="CM3" t="n">
-        <v>2.56</v>
+        <v>2.55</v>
       </c>
       <c r="CN3" t="n">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="CO3" t="n">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="CP3" t="n">
         <v>1.58</v>
@@ -2067,82 +2067,82 @@
         <v>1.33</v>
       </c>
       <c r="CS3" t="n">
-        <v>2.3</v>
+        <v>2.31</v>
       </c>
       <c r="CT3" t="n">
         <v>3.28</v>
       </c>
       <c r="CU3" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="CV3" t="n">
-        <v>2.32</v>
+        <v>2.31</v>
       </c>
       <c r="CW3" t="n">
         <v>1.66</v>
       </c>
       <c r="CX3" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="CY3" t="n">
         <v>1.8</v>
       </c>
       <c r="CZ3" t="n">
-        <v>2.49</v>
+        <v>2.48</v>
       </c>
       <c r="DA3" t="n">
-        <v>2.03</v>
+        <v>2.02</v>
       </c>
       <c r="DB3" t="n">
         <v>1.18</v>
       </c>
       <c r="DC3" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="DD3" t="n">
-        <v>2.44</v>
+        <v>2.45</v>
       </c>
       <c r="DE3" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="DF3" t="n">
-        <v>1.21</v>
+        <v>1.26</v>
       </c>
       <c r="DG3" t="n">
-        <v>4.21</v>
+        <v>3.93</v>
       </c>
       <c r="DH3" t="n">
-        <v>113.57</v>
+        <v>109.93</v>
       </c>
       <c r="DI3" t="n">
         <v>0</v>
       </c>
       <c r="DJ3" t="n">
-        <v>1.64</v>
+        <v>1.66</v>
       </c>
       <c r="DK3" t="n">
-        <v>6.78</v>
+        <v>6.73</v>
       </c>
       <c r="DL3" t="n">
-        <v>0.42</v>
+        <v>0.53</v>
       </c>
       <c r="DM3" t="n">
-        <v>62</v>
+        <v>60.87</v>
       </c>
       <c r="DN3" t="n">
-        <v>0.36</v>
+        <v>0.33</v>
       </c>
       <c r="DO3" t="n">
-        <v>2.57</v>
+        <v>2.8</v>
       </c>
       <c r="DP3" t="n">
-        <v>9.789999999999999</v>
+        <v>9.470000000000001</v>
       </c>
       <c r="DQ3" t="n">
-        <v>12.36</v>
+        <v>12.13</v>
       </c>
       <c r="DR3" t="n">
-        <v>7.21</v>
+        <v>7.4</v>
       </c>
       <c r="DS3" t="n">
         <v>0</v>
@@ -2154,28 +2154,28 @@
         <v>0</v>
       </c>
       <c r="DV3" t="n">
-        <v>62</v>
+        <v>61.94</v>
       </c>
       <c r="DW3" t="n">
         <v>0.07000000000000001</v>
       </c>
       <c r="DX3" t="n">
-        <v>15.57</v>
+        <v>15.67</v>
       </c>
       <c r="DY3" t="n">
-        <v>10.71</v>
+        <v>10.8</v>
       </c>
       <c r="DZ3" t="n">
-        <v>4.86</v>
+        <v>4.87</v>
       </c>
       <c r="EA3" t="n">
-        <v>20.29</v>
+        <v>20.2</v>
       </c>
       <c r="EB3" t="n">
         <v>1.77</v>
       </c>
       <c r="EC3" t="n">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
     </row>
     <row r="4">
@@ -2185,13 +2185,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C4" t="n">
         <v>7</v>
       </c>
       <c r="D4" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
@@ -2275,52 +2275,52 @@
         <v>1</v>
       </c>
       <c r="AF4" t="n">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.43</v>
+        <v>1.62</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.43</v>
+        <v>1.38</v>
       </c>
       <c r="AI4" t="n">
-        <v>89.29000000000001</v>
+        <v>90.38</v>
       </c>
       <c r="AJ4" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="AK4" t="n">
-        <v>2.29</v>
+        <v>2.5</v>
       </c>
       <c r="AL4" t="n">
-        <v>3.14</v>
+        <v>3.12</v>
       </c>
       <c r="AM4" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="AN4" t="n">
-        <v>36.86</v>
+        <v>36.88</v>
       </c>
       <c r="AO4" t="n">
-        <v>0.57</v>
+        <v>0.62</v>
       </c>
       <c r="AP4" t="n">
-        <v>1.71</v>
+        <v>1.75</v>
       </c>
       <c r="AQ4" t="n">
-        <v>12</v>
+        <v>12.25</v>
       </c>
       <c r="AR4" t="n">
-        <v>11.71</v>
+        <v>12.12</v>
       </c>
       <c r="AS4" t="n">
-        <v>10</v>
+        <v>10.12</v>
       </c>
       <c r="AT4" t="n">
-        <v>2</v>
+        <v>1.88</v>
       </c>
       <c r="AU4" t="n">
-        <v>0.71</v>
+        <v>0.88</v>
       </c>
       <c r="AV4" t="n">
         <v>0</v>
@@ -2332,73 +2332,73 @@
         <v>0</v>
       </c>
       <c r="AY4" t="n">
-        <v>41.86</v>
+        <v>42.5</v>
       </c>
       <c r="AZ4" t="n">
-        <v>0.43</v>
+        <v>0.38</v>
       </c>
       <c r="BA4" t="n">
-        <v>10.57</v>
+        <v>10.38</v>
       </c>
       <c r="BB4" t="n">
-        <v>6.43</v>
+        <v>6.5</v>
       </c>
       <c r="BC4" t="n">
-        <v>4.14</v>
+        <v>3.88</v>
       </c>
       <c r="BD4" t="n">
-        <v>17.57</v>
+        <v>17.5</v>
       </c>
       <c r="BE4" t="n">
-        <v>1.23</v>
+        <v>1.2</v>
       </c>
       <c r="BF4" t="n">
-        <v>1.57</v>
+        <v>1.88</v>
       </c>
       <c r="BG4" t="n">
-        <v>2.21</v>
+        <v>2.27</v>
       </c>
       <c r="BH4" t="n">
-        <v>8.640000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="BI4" t="n">
-        <v>2.21</v>
+        <v>2.27</v>
       </c>
       <c r="BJ4" t="n">
-        <v>0.5</v>
+        <v>0.47</v>
       </c>
       <c r="BK4" t="n">
-        <v>0.21</v>
+        <v>0.2</v>
       </c>
       <c r="BL4" t="n">
-        <v>0.71</v>
+        <v>0.73</v>
       </c>
       <c r="BM4" t="n">
-        <v>0.79</v>
+        <v>0.87</v>
       </c>
       <c r="BN4" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="BO4" t="n">
-        <v>0.71</v>
+        <v>0.67</v>
       </c>
       <c r="BP4" t="n">
-        <v>3.5</v>
+        <v>3.53</v>
       </c>
       <c r="BQ4" t="n">
-        <v>4.21</v>
+        <v>4.2</v>
       </c>
       <c r="BR4" t="n">
-        <v>85.70999999999999</v>
+        <v>86.67</v>
       </c>
       <c r="BS4" t="n">
-        <v>71.43000000000001</v>
+        <v>73.33</v>
       </c>
       <c r="BT4" t="n">
-        <v>42.86</v>
+        <v>46.67</v>
       </c>
       <c r="BU4" t="n">
-        <v>21.43</v>
+        <v>20</v>
       </c>
       <c r="BV4" t="n">
         <v>0</v>
@@ -2407,7 +2407,7 @@
         <v>0</v>
       </c>
       <c r="BX4" t="n">
-        <v>50</v>
+        <v>53.33</v>
       </c>
       <c r="BY4" t="n">
         <v>3.4</v>
@@ -2416,31 +2416,31 @@
         <v>3.49</v>
       </c>
       <c r="CA4" t="n">
-        <v>3.75</v>
+        <v>3.72</v>
       </c>
       <c r="CB4" t="n">
-        <v>3.98</v>
+        <v>3.94</v>
       </c>
       <c r="CC4" t="n">
-        <v>5.06</v>
+        <v>4.87</v>
       </c>
       <c r="CD4" t="n">
-        <v>5.57</v>
+        <v>5.33</v>
       </c>
       <c r="CE4" t="n">
         <v>1.34</v>
       </c>
       <c r="CF4" t="n">
-        <v>2.53</v>
+        <v>2.55</v>
       </c>
       <c r="CG4" t="n">
-        <v>3.14</v>
+        <v>3.1</v>
       </c>
       <c r="CH4" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="CI4" t="n">
-        <v>2.03</v>
+        <v>2.04</v>
       </c>
       <c r="CJ4" t="n">
         <v>1.74</v>
@@ -2449,22 +2449,22 @@
         <v>1.53</v>
       </c>
       <c r="CL4" t="n">
-        <v>2.05</v>
+        <v>2.04</v>
       </c>
       <c r="CM4" t="n">
-        <v>2.37</v>
+        <v>2.36</v>
       </c>
       <c r="CN4" t="n">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="CO4" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="CP4" t="n">
         <v>1.83</v>
       </c>
       <c r="CQ4" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="CR4" t="n">
         <v>1.38</v>
@@ -2488,64 +2488,64 @@
         <v>1.57</v>
       </c>
       <c r="CY4" t="n">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="CZ4" t="n">
-        <v>2.4</v>
+        <v>2.39</v>
       </c>
       <c r="DA4" t="n">
         <v>1.88</v>
       </c>
       <c r="DB4" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="DC4" t="n">
         <v>1.86</v>
       </c>
       <c r="DD4" t="n">
-        <v>3.05</v>
+        <v>3.07</v>
       </c>
       <c r="DE4" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DF4" t="n">
-        <v>1.07</v>
+        <v>1.2</v>
       </c>
       <c r="DG4" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="DH4" t="n">
-        <v>92.08</v>
+        <v>92.47</v>
       </c>
       <c r="DI4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DJ4" t="n">
-        <v>1.64</v>
+        <v>1.8</v>
       </c>
       <c r="DK4" t="n">
-        <v>3.28</v>
+        <v>3.26</v>
       </c>
       <c r="DL4" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="DM4" t="n">
-        <v>40.07</v>
+        <v>39.87</v>
       </c>
       <c r="DN4" t="n">
-        <v>0.43</v>
+        <v>0.47</v>
       </c>
       <c r="DO4" t="n">
-        <v>1.42</v>
+        <v>1.47</v>
       </c>
       <c r="DP4" t="n">
-        <v>10.43</v>
+        <v>10.67</v>
       </c>
       <c r="DQ4" t="n">
-        <v>11.92</v>
+        <v>12.13</v>
       </c>
       <c r="DR4" t="n">
-        <v>9.859999999999999</v>
+        <v>9.93</v>
       </c>
       <c r="DS4" t="n">
         <v>0.07000000000000001</v>
@@ -2557,28 +2557,28 @@
         <v>0</v>
       </c>
       <c r="DV4" t="n">
-        <v>46.58</v>
+        <v>46.6</v>
       </c>
       <c r="DW4" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="DX4" t="n">
-        <v>10.36</v>
+        <v>10.27</v>
       </c>
       <c r="DY4" t="n">
-        <v>6.64</v>
+        <v>6.67</v>
       </c>
       <c r="DZ4" t="n">
-        <v>3.72</v>
+        <v>3.6</v>
       </c>
       <c r="EA4" t="n">
-        <v>20.64</v>
+        <v>20.4</v>
       </c>
       <c r="EB4" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="EC4" t="n">
-        <v>1.28</v>
+        <v>1.47</v>
       </c>
     </row>
     <row r="5">
@@ -2588,13 +2588,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C5" t="n">
         <v>7</v>
       </c>
       <c r="D5" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E5" t="n">
         <v>0.43</v>
@@ -2681,136 +2681,136 @@
         <v>0</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AH5" t="n">
-        <v>3.71</v>
+        <v>3.38</v>
       </c>
       <c r="AI5" t="n">
-        <v>99.86</v>
+        <v>96.5</v>
       </c>
       <c r="AJ5" t="n">
         <v>0</v>
       </c>
       <c r="AK5" t="n">
-        <v>2.57</v>
+        <v>2.5</v>
       </c>
       <c r="AL5" t="n">
-        <v>6.14</v>
+        <v>5.62</v>
       </c>
       <c r="AM5" t="n">
-        <v>1</v>
+        <v>0.88</v>
       </c>
       <c r="AN5" t="n">
-        <v>45.43</v>
+        <v>44.38</v>
       </c>
       <c r="AO5" t="n">
         <v>1</v>
       </c>
       <c r="AP5" t="n">
-        <v>2.43</v>
+        <v>2.25</v>
       </c>
       <c r="AQ5" t="n">
-        <v>11.43</v>
+        <v>11.38</v>
       </c>
       <c r="AR5" t="n">
-        <v>11</v>
+        <v>10.88</v>
       </c>
       <c r="AS5" t="n">
-        <v>9.289999999999999</v>
+        <v>10.12</v>
       </c>
       <c r="AT5" t="n">
-        <v>2.29</v>
+        <v>2</v>
       </c>
       <c r="AU5" t="n">
-        <v>1.29</v>
+        <v>1.12</v>
       </c>
       <c r="AV5" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="AW5" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="AX5" t="n">
         <v>0</v>
       </c>
       <c r="AY5" t="n">
-        <v>53</v>
+        <v>52.62</v>
       </c>
       <c r="AZ5" t="n">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="BA5" t="n">
-        <v>13</v>
+        <v>12.62</v>
       </c>
       <c r="BB5" t="n">
-        <v>7.57</v>
+        <v>7.5</v>
       </c>
       <c r="BC5" t="n">
-        <v>5.43</v>
+        <v>5.12</v>
       </c>
       <c r="BD5" t="n">
-        <v>19.29</v>
+        <v>18</v>
       </c>
       <c r="BE5" t="n">
-        <v>1.53</v>
+        <v>1.48</v>
       </c>
       <c r="BF5" t="n">
         <v>2</v>
       </c>
       <c r="BG5" t="n">
-        <v>3.21</v>
+        <v>3</v>
       </c>
       <c r="BH5" t="n">
-        <v>9.93</v>
+        <v>10</v>
       </c>
       <c r="BI5" t="n">
-        <v>3.21</v>
+        <v>3</v>
       </c>
       <c r="BJ5" t="n">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="BK5" t="n">
-        <v>0.43</v>
+        <v>0.4</v>
       </c>
       <c r="BL5" t="n">
-        <v>1.14</v>
+        <v>1.07</v>
       </c>
       <c r="BM5" t="n">
-        <v>0.64</v>
+        <v>0.6</v>
       </c>
       <c r="BN5" t="n">
-        <v>1.79</v>
+        <v>1.67</v>
       </c>
       <c r="BO5" t="n">
-        <v>1.43</v>
+        <v>1.33</v>
       </c>
       <c r="BP5" t="n">
-        <v>4.14</v>
+        <v>4</v>
       </c>
       <c r="BQ5" t="n">
-        <v>5.79</v>
+        <v>6</v>
       </c>
       <c r="BR5" t="n">
-        <v>100</v>
+        <v>93.33</v>
       </c>
       <c r="BS5" t="n">
-        <v>85.70999999999999</v>
+        <v>80</v>
       </c>
       <c r="BT5" t="n">
-        <v>64.29000000000001</v>
+        <v>60</v>
       </c>
       <c r="BU5" t="n">
-        <v>42.86</v>
+        <v>40</v>
       </c>
       <c r="BV5" t="n">
-        <v>21.43</v>
+        <v>20</v>
       </c>
       <c r="BW5" t="n">
-        <v>7.14</v>
+        <v>6.67</v>
       </c>
       <c r="BX5" t="n">
-        <v>64.29000000000001</v>
+        <v>60</v>
       </c>
       <c r="BY5" t="n">
         <v>2.88</v>
@@ -2825,100 +2825,100 @@
         <v>3.72</v>
       </c>
       <c r="CC5" t="n">
-        <v>3.07</v>
+        <v>3.04</v>
       </c>
       <c r="CD5" t="n">
-        <v>3.26</v>
+        <v>3.22</v>
       </c>
       <c r="CE5" t="n">
         <v>1.31</v>
       </c>
       <c r="CF5" t="n">
-        <v>2.47</v>
+        <v>2.45</v>
       </c>
       <c r="CG5" t="n">
-        <v>3.2</v>
+        <v>3.23</v>
       </c>
       <c r="CH5" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="CI5" t="n">
-        <v>2.23</v>
+        <v>2.27</v>
       </c>
       <c r="CJ5" t="n">
-        <v>1.64</v>
+        <v>1.62</v>
       </c>
       <c r="CK5" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="CL5" t="n">
         <v>1.85</v>
       </c>
       <c r="CM5" t="n">
-        <v>2.56</v>
+        <v>2.59</v>
       </c>
       <c r="CN5" t="n">
-        <v>1.99</v>
+        <v>2.01</v>
       </c>
       <c r="CO5" t="n">
         <v>1.21</v>
       </c>
       <c r="CP5" t="n">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="CQ5" t="n">
-        <v>2.74</v>
+        <v>2.73</v>
       </c>
       <c r="CR5" t="n">
         <v>1.35</v>
       </c>
       <c r="CS5" t="n">
-        <v>2.56</v>
+        <v>2.54</v>
       </c>
       <c r="CT5" t="n">
         <v>3.27</v>
       </c>
       <c r="CU5" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="CV5" t="n">
-        <v>2.33</v>
+        <v>2.36</v>
       </c>
       <c r="CW5" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="CX5" t="n">
         <v>1.54</v>
       </c>
       <c r="CY5" t="n">
-        <v>1.79</v>
+        <v>1.77</v>
       </c>
       <c r="CZ5" t="n">
         <v>2.46</v>
       </c>
       <c r="DA5" t="n">
-        <v>2.03</v>
+        <v>2.06</v>
       </c>
       <c r="DB5" t="n">
         <v>1.23</v>
       </c>
       <c r="DC5" t="n">
-        <v>1.77</v>
+        <v>1.75</v>
       </c>
       <c r="DD5" t="n">
-        <v>2.85</v>
+        <v>2.81</v>
       </c>
       <c r="DE5" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="DF5" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="DG5" t="n">
-        <v>3.21</v>
+        <v>3.07</v>
       </c>
       <c r="DH5" t="n">
-        <v>105.78</v>
+        <v>103.6</v>
       </c>
       <c r="DI5" t="n">
         <v>0</v>
@@ -2927,61 +2927,61 @@
         <v>2</v>
       </c>
       <c r="DK5" t="n">
-        <v>5.36</v>
+        <v>5.13</v>
       </c>
       <c r="DL5" t="n">
-        <v>0.78</v>
+        <v>0.74</v>
       </c>
       <c r="DM5" t="n">
-        <v>47.64</v>
+        <v>46.94</v>
       </c>
       <c r="DN5" t="n">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="DO5" t="n">
-        <v>2.14</v>
+        <v>2.07</v>
       </c>
       <c r="DP5" t="n">
         <v>11</v>
       </c>
       <c r="DQ5" t="n">
-        <v>10.36</v>
+        <v>10.33</v>
       </c>
       <c r="DR5" t="n">
-        <v>8.720000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="DS5" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="DT5" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="DU5" t="n">
         <v>0</v>
       </c>
       <c r="DV5" t="n">
-        <v>54.43</v>
+        <v>54.13</v>
       </c>
       <c r="DW5" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DX5" t="n">
-        <v>13.86</v>
+        <v>13.6</v>
       </c>
       <c r="DY5" t="n">
-        <v>9</v>
+        <v>8.869999999999999</v>
       </c>
       <c r="DZ5" t="n">
-        <v>4.86</v>
+        <v>4.73</v>
       </c>
       <c r="EA5" t="n">
-        <v>18.43</v>
+        <v>17.8</v>
       </c>
       <c r="EB5" t="n">
-        <v>1.57</v>
+        <v>1.54</v>
       </c>
       <c r="EC5" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
     </row>
     <row r="6">
@@ -2991,10 +2991,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C6" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D6" t="n">
         <v>8</v>
@@ -3003,49 +3003,49 @@
         <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>0.67</v>
+        <v>0.57</v>
       </c>
       <c r="G6" t="n">
-        <v>3.83</v>
+        <v>3.71</v>
       </c>
       <c r="H6" t="n">
-        <v>137.33</v>
+        <v>140</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>1.5</v>
+        <v>1.29</v>
       </c>
       <c r="K6" t="n">
-        <v>6.33</v>
+        <v>6.29</v>
       </c>
       <c r="L6" t="n">
-        <v>0.33</v>
+        <v>0.57</v>
       </c>
       <c r="M6" t="n">
-        <v>66</v>
+        <v>67.14</v>
       </c>
       <c r="N6" t="n">
-        <v>0.67</v>
+        <v>0.57</v>
       </c>
       <c r="O6" t="n">
-        <v>2.5</v>
+        <v>2.57</v>
       </c>
       <c r="P6" t="n">
-        <v>11</v>
+        <v>10.14</v>
       </c>
       <c r="Q6" t="n">
-        <v>14.5</v>
+        <v>14.29</v>
       </c>
       <c r="R6" t="n">
-        <v>5.33</v>
+        <v>5.43</v>
       </c>
       <c r="S6" t="n">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="T6" t="n">
-        <v>1.33</v>
+        <v>1.14</v>
       </c>
       <c r="U6" t="n">
         <v>0</v>
@@ -3057,28 +3057,28 @@
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>66.67</v>
+        <v>66.56999999999999</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="Z6" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AA6" t="n">
-        <v>11.17</v>
+        <v>11.57</v>
       </c>
       <c r="AB6" t="n">
-        <v>5.33</v>
+        <v>5.43</v>
       </c>
       <c r="AC6" t="n">
-        <v>23.67</v>
+        <v>22.43</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.9</v>
+        <v>1.94</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.17</v>
+        <v>1</v>
       </c>
       <c r="AF6" t="n">
         <v>0.12</v>
@@ -3162,70 +3162,70 @@
         <v>2</v>
       </c>
       <c r="BG6" t="n">
-        <v>2.64</v>
+        <v>2.53</v>
       </c>
       <c r="BH6" t="n">
-        <v>9.640000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="BI6" t="n">
-        <v>2.64</v>
+        <v>2.53</v>
       </c>
       <c r="BJ6" t="n">
-        <v>0.64</v>
+        <v>0.6</v>
       </c>
       <c r="BK6" t="n">
         <v>0.93</v>
       </c>
       <c r="BL6" t="n">
-        <v>0.64</v>
+        <v>0.6</v>
       </c>
       <c r="BM6" t="n">
-        <v>0.43</v>
+        <v>0.4</v>
       </c>
       <c r="BN6" t="n">
-        <v>1.07</v>
+        <v>1</v>
       </c>
       <c r="BO6" t="n">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="BP6" t="n">
-        <v>4.43</v>
+        <v>4.4</v>
       </c>
       <c r="BQ6" t="n">
-        <v>5.21</v>
+        <v>5.2</v>
       </c>
       <c r="BR6" t="n">
         <v>100</v>
       </c>
       <c r="BS6" t="n">
-        <v>85.70999999999999</v>
+        <v>80</v>
       </c>
       <c r="BT6" t="n">
-        <v>57.14</v>
+        <v>53.33</v>
       </c>
       <c r="BU6" t="n">
-        <v>14.29</v>
+        <v>13.33</v>
       </c>
       <c r="BV6" t="n">
-        <v>7.14</v>
+        <v>6.67</v>
       </c>
       <c r="BW6" t="n">
         <v>0</v>
       </c>
       <c r="BX6" t="n">
-        <v>85.70999999999999</v>
+        <v>80</v>
       </c>
       <c r="BY6" t="n">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="BZ6" t="n">
-        <v>1.82</v>
+        <v>1.77</v>
       </c>
       <c r="CA6" t="n">
-        <v>3.87</v>
+        <v>3.91</v>
       </c>
       <c r="CB6" t="n">
-        <v>4.01</v>
+        <v>4.08</v>
       </c>
       <c r="CC6" t="n">
         <v>2.52</v>
@@ -3234,13 +3234,13 @@
         <v>2.54</v>
       </c>
       <c r="CE6" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="CF6" t="n">
-        <v>2.38</v>
+        <v>2.36</v>
       </c>
       <c r="CG6" t="n">
-        <v>3.34</v>
+        <v>3.35</v>
       </c>
       <c r="CH6" t="n">
         <v>1.54</v>
@@ -3252,106 +3252,106 @@
         <v>1.63</v>
       </c>
       <c r="CK6" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="CL6" t="n">
-        <v>2.04</v>
+        <v>2.03</v>
       </c>
       <c r="CM6" t="n">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="CN6" t="n">
-        <v>1.84</v>
+        <v>1.86</v>
       </c>
       <c r="CO6" t="n">
         <v>1.18</v>
       </c>
       <c r="CP6" t="n">
-        <v>1.68</v>
+        <v>1.66</v>
       </c>
       <c r="CQ6" t="n">
-        <v>2.63</v>
+        <v>2.6</v>
       </c>
       <c r="CR6" t="n">
         <v>1.4</v>
       </c>
       <c r="CS6" t="n">
-        <v>2.54</v>
+        <v>2.5</v>
       </c>
       <c r="CT6" t="n">
         <v>3.04</v>
       </c>
       <c r="CU6" t="n">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="CV6" t="n">
-        <v>2.32</v>
+        <v>2.33</v>
       </c>
       <c r="CW6" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="CX6" t="n">
         <v>1.6</v>
       </c>
       <c r="CY6" t="n">
-        <v>1.99</v>
+        <v>1.96</v>
       </c>
       <c r="CZ6" t="n">
         <v>2.31</v>
       </c>
       <c r="DA6" t="n">
-        <v>1.83</v>
+        <v>1.86</v>
       </c>
       <c r="DB6" t="n">
         <v>1.22</v>
       </c>
       <c r="DC6" t="n">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="DD6" t="n">
-        <v>2.74</v>
+        <v>2.7</v>
       </c>
       <c r="DE6" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="DF6" t="n">
-        <v>1.14</v>
+        <v>1.07</v>
       </c>
       <c r="DG6" t="n">
-        <v>3.14</v>
+        <v>3.13</v>
       </c>
       <c r="DH6" t="n">
-        <v>115.71</v>
+        <v>118.4</v>
       </c>
       <c r="DI6" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="DJ6" t="n">
-        <v>1.79</v>
+        <v>1.67</v>
       </c>
       <c r="DK6" t="n">
-        <v>5.64</v>
+        <v>5.67</v>
       </c>
       <c r="DL6" t="n">
-        <v>0.64</v>
+        <v>0.74</v>
       </c>
       <c r="DM6" t="n">
-        <v>56.14</v>
+        <v>57.33</v>
       </c>
       <c r="DN6" t="n">
-        <v>0.57</v>
+        <v>0.53</v>
       </c>
       <c r="DO6" t="n">
-        <v>2.5</v>
+        <v>2.53</v>
       </c>
       <c r="DP6" t="n">
-        <v>10.07</v>
+        <v>9.73</v>
       </c>
       <c r="DQ6" t="n">
-        <v>13.14</v>
+        <v>13.13</v>
       </c>
       <c r="DR6" t="n">
-        <v>6.22</v>
+        <v>6.2</v>
       </c>
       <c r="DS6" t="n">
         <v>0</v>
@@ -3363,28 +3363,28 @@
         <v>0</v>
       </c>
       <c r="DV6" t="n">
-        <v>63.36</v>
+        <v>63.54</v>
       </c>
       <c r="DW6" t="n">
         <v>0.07000000000000001</v>
       </c>
       <c r="DX6" t="n">
-        <v>15.79</v>
+        <v>16.07</v>
       </c>
       <c r="DY6" t="n">
-        <v>10.43</v>
+        <v>10.67</v>
       </c>
       <c r="DZ6" t="n">
-        <v>5.36</v>
+        <v>5.4</v>
       </c>
       <c r="EA6" t="n">
-        <v>20.93</v>
+        <v>20.54</v>
       </c>
       <c r="EB6" t="n">
-        <v>1.78</v>
+        <v>1.81</v>
       </c>
       <c r="EC6" t="n">
-        <v>1.64</v>
+        <v>1.53</v>
       </c>
     </row>
     <row r="7">
@@ -3394,13 +3394,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C7" t="n">
         <v>7</v>
       </c>
       <c r="D7" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E7" t="n">
         <v>0.14</v>
@@ -3484,52 +3484,52 @@
         <v>2.43</v>
       </c>
       <c r="AF7" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.43</v>
+        <v>1.62</v>
       </c>
       <c r="AH7" t="n">
-        <v>3</v>
+        <v>2.88</v>
       </c>
       <c r="AI7" t="n">
-        <v>82.70999999999999</v>
+        <v>79.88</v>
       </c>
       <c r="AJ7" t="n">
-        <v>0</v>
+        <v>0.12</v>
       </c>
       <c r="AK7" t="n">
-        <v>2</v>
+        <v>2.38</v>
       </c>
       <c r="AL7" t="n">
-        <v>5.43</v>
+        <v>5.12</v>
       </c>
       <c r="AM7" t="n">
-        <v>0.29</v>
+        <v>0.38</v>
       </c>
       <c r="AN7" t="n">
-        <v>42.14</v>
+        <v>40.75</v>
       </c>
       <c r="AO7" t="n">
-        <v>0.57</v>
+        <v>0.75</v>
       </c>
       <c r="AP7" t="n">
-        <v>2.43</v>
+        <v>2.25</v>
       </c>
       <c r="AQ7" t="n">
-        <v>8.57</v>
+        <v>9.119999999999999</v>
       </c>
       <c r="AR7" t="n">
-        <v>10.86</v>
+        <v>10.12</v>
       </c>
       <c r="AS7" t="n">
-        <v>8.57</v>
+        <v>9</v>
       </c>
       <c r="AT7" t="n">
-        <v>1.14</v>
+        <v>1</v>
       </c>
       <c r="AU7" t="n">
-        <v>1.43</v>
+        <v>1.38</v>
       </c>
       <c r="AV7" t="n">
         <v>0</v>
@@ -3541,82 +3541,82 @@
         <v>0</v>
       </c>
       <c r="AY7" t="n">
-        <v>49</v>
+        <v>47.12</v>
       </c>
       <c r="AZ7" t="n">
         <v>0</v>
       </c>
       <c r="BA7" t="n">
-        <v>10.57</v>
+        <v>10.62</v>
       </c>
       <c r="BB7" t="n">
-        <v>6.43</v>
+        <v>6.25</v>
       </c>
       <c r="BC7" t="n">
-        <v>4.14</v>
+        <v>4.38</v>
       </c>
       <c r="BD7" t="n">
-        <v>21</v>
+        <v>20.38</v>
       </c>
       <c r="BE7" t="n">
         <v>1.27</v>
       </c>
       <c r="BF7" t="n">
-        <v>2</v>
+        <v>2.38</v>
       </c>
       <c r="BG7" t="n">
-        <v>2.57</v>
+        <v>2.47</v>
       </c>
       <c r="BH7" t="n">
-        <v>12.07</v>
+        <v>11.87</v>
       </c>
       <c r="BI7" t="n">
-        <v>2.57</v>
+        <v>2.47</v>
       </c>
       <c r="BJ7" t="n">
-        <v>0.5</v>
+        <v>0.47</v>
       </c>
       <c r="BK7" t="n">
-        <v>0.43</v>
+        <v>0.47</v>
       </c>
       <c r="BL7" t="n">
-        <v>0.71</v>
+        <v>0.67</v>
       </c>
       <c r="BM7" t="n">
-        <v>0.93</v>
+        <v>0.87</v>
       </c>
       <c r="BN7" t="n">
-        <v>1.64</v>
+        <v>1.53</v>
       </c>
       <c r="BO7" t="n">
         <v>0.93</v>
       </c>
       <c r="BP7" t="n">
-        <v>5.86</v>
+        <v>5.73</v>
       </c>
       <c r="BQ7" t="n">
-        <v>6.21</v>
+        <v>6.13</v>
       </c>
       <c r="BR7" t="n">
-        <v>92.86</v>
+        <v>93.33</v>
       </c>
       <c r="BS7" t="n">
-        <v>85.70999999999999</v>
+        <v>80</v>
       </c>
       <c r="BT7" t="n">
-        <v>42.86</v>
+        <v>40</v>
       </c>
       <c r="BU7" t="n">
-        <v>28.57</v>
+        <v>26.67</v>
       </c>
       <c r="BV7" t="n">
-        <v>7.14</v>
+        <v>6.67</v>
       </c>
       <c r="BW7" t="n">
         <v>0</v>
       </c>
       <c r="BX7" t="n">
-        <v>78.56999999999999</v>
+        <v>73.33</v>
       </c>
       <c r="BY7" t="n">
         <v>2.95</v>
@@ -3625,25 +3625,25 @@
         <v>3.17</v>
       </c>
       <c r="CA7" t="n">
-        <v>3.63</v>
+        <v>3.7</v>
       </c>
       <c r="CB7" t="n">
-        <v>3.75</v>
+        <v>3.84</v>
       </c>
       <c r="CC7" t="n">
-        <v>3.14</v>
+        <v>3.47</v>
       </c>
       <c r="CD7" t="n">
-        <v>3.58</v>
+        <v>3.9</v>
       </c>
       <c r="CE7" t="n">
         <v>1.3</v>
       </c>
       <c r="CF7" t="n">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="CG7" t="n">
-        <v>3.26</v>
+        <v>3.28</v>
       </c>
       <c r="CH7" t="n">
         <v>1.53</v>
@@ -3658,103 +3658,103 @@
         <v>1.39</v>
       </c>
       <c r="CL7" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="CM7" t="n">
-        <v>2.81</v>
+        <v>2.8</v>
       </c>
       <c r="CN7" t="n">
         <v>2.13</v>
       </c>
       <c r="CO7" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="CP7" t="n">
-        <v>1.69</v>
+        <v>1.67</v>
       </c>
       <c r="CQ7" t="n">
-        <v>2.69</v>
+        <v>2.66</v>
       </c>
       <c r="CR7" t="n">
         <v>1.36</v>
       </c>
       <c r="CS7" t="n">
-        <v>2.56</v>
+        <v>2.53</v>
       </c>
       <c r="CT7" t="n">
         <v>3.22</v>
       </c>
       <c r="CU7" t="n">
-        <v>1.54</v>
+        <v>1.56</v>
       </c>
       <c r="CV7" t="n">
         <v>2.41</v>
       </c>
       <c r="CW7" t="n">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="CX7" t="n">
         <v>1.52</v>
       </c>
       <c r="CY7" t="n">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="CZ7" t="n">
         <v>2.46</v>
       </c>
       <c r="DA7" t="n">
-        <v>2.14</v>
+        <v>2.15</v>
       </c>
       <c r="DB7" t="n">
         <v>1.22</v>
       </c>
       <c r="DC7" t="n">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="DD7" t="n">
-        <v>2.79</v>
+        <v>2.75</v>
       </c>
       <c r="DE7" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DF7" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="DG7" t="n">
-        <v>2.57</v>
+        <v>2.53</v>
       </c>
       <c r="DH7" t="n">
-        <v>83.34999999999999</v>
+        <v>81.8</v>
       </c>
       <c r="DI7" t="n">
-        <v>0.22</v>
+        <v>0.26</v>
       </c>
       <c r="DJ7" t="n">
-        <v>2.22</v>
+        <v>2.4</v>
       </c>
       <c r="DK7" t="n">
-        <v>4.86</v>
+        <v>4.73</v>
       </c>
       <c r="DL7" t="n">
-        <v>0.22</v>
+        <v>0.27</v>
       </c>
       <c r="DM7" t="n">
-        <v>44.92</v>
+        <v>44</v>
       </c>
       <c r="DN7" t="n">
-        <v>0.72</v>
+        <v>0.8</v>
       </c>
       <c r="DO7" t="n">
-        <v>2.28</v>
+        <v>2.2</v>
       </c>
       <c r="DP7" t="n">
-        <v>9.5</v>
+        <v>9.73</v>
       </c>
       <c r="DQ7" t="n">
-        <v>11.28</v>
+        <v>10.86</v>
       </c>
       <c r="DR7" t="n">
-        <v>9.859999999999999</v>
+        <v>10</v>
       </c>
       <c r="DS7" t="n">
         <v>0.14</v>
@@ -3766,28 +3766,28 @@
         <v>0</v>
       </c>
       <c r="DV7" t="n">
-        <v>48.72</v>
+        <v>47.73</v>
       </c>
       <c r="DW7" t="n">
         <v>0</v>
       </c>
       <c r="DX7" t="n">
-        <v>10.43</v>
+        <v>10.47</v>
       </c>
       <c r="DY7" t="n">
-        <v>6.43</v>
+        <v>6.33</v>
       </c>
       <c r="DZ7" t="n">
-        <v>4</v>
+        <v>4.14</v>
       </c>
       <c r="EA7" t="n">
-        <v>20.72</v>
+        <v>20.4</v>
       </c>
       <c r="EB7" t="n">
         <v>1.27</v>
       </c>
       <c r="EC7" t="n">
-        <v>2.22</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="8">
@@ -3797,61 +3797,61 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C8" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D8" t="n">
         <v>7</v>
       </c>
       <c r="E8" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="F8" t="n">
         <v>1</v>
       </c>
       <c r="G8" t="n">
-        <v>2.71</v>
+        <v>3.38</v>
       </c>
       <c r="H8" t="n">
-        <v>97.70999999999999</v>
+        <v>98.12</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>1.14</v>
+        <v>1.25</v>
       </c>
       <c r="K8" t="n">
-        <v>6.29</v>
+        <v>6.62</v>
       </c>
       <c r="L8" t="n">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="M8" t="n">
-        <v>56.14</v>
+        <v>58.62</v>
       </c>
       <c r="N8" t="n">
-        <v>0.14</v>
+        <v>0.25</v>
       </c>
       <c r="O8" t="n">
-        <v>3.57</v>
+        <v>3.25</v>
       </c>
       <c r="P8" t="n">
-        <v>10.57</v>
+        <v>10.5</v>
       </c>
       <c r="Q8" t="n">
-        <v>13.14</v>
+        <v>12.88</v>
       </c>
       <c r="R8" t="n">
-        <v>8.289999999999999</v>
+        <v>7.62</v>
       </c>
       <c r="S8" t="n">
-        <v>0.86</v>
+        <v>0.75</v>
       </c>
       <c r="T8" t="n">
-        <v>1.14</v>
+        <v>1</v>
       </c>
       <c r="U8" t="n">
         <v>0</v>
@@ -3863,28 +3863,28 @@
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>51.14</v>
+        <v>51</v>
       </c>
       <c r="Y8" t="n">
         <v>0</v>
       </c>
       <c r="Z8" t="n">
-        <v>17.29</v>
+        <v>17.62</v>
       </c>
       <c r="AA8" t="n">
-        <v>12.43</v>
+        <v>12.75</v>
       </c>
       <c r="AB8" t="n">
-        <v>4.86</v>
+        <v>4.88</v>
       </c>
       <c r="AC8" t="n">
-        <v>20.71</v>
+        <v>19.38</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.83</v>
+        <v>1.87</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.14</v>
+        <v>1.25</v>
       </c>
       <c r="AF8" t="n">
         <v>0.14</v>
@@ -3968,70 +3968,70 @@
         <v>1.71</v>
       </c>
       <c r="BG8" t="n">
-        <v>3.07</v>
+        <v>2.87</v>
       </c>
       <c r="BH8" t="n">
-        <v>10.14</v>
+        <v>10.2</v>
       </c>
       <c r="BI8" t="n">
-        <v>3.07</v>
+        <v>2.87</v>
       </c>
       <c r="BJ8" t="n">
-        <v>0.79</v>
+        <v>0.73</v>
       </c>
       <c r="BK8" t="n">
-        <v>0.57</v>
+        <v>0.53</v>
       </c>
       <c r="BL8" t="n">
-        <v>1.07</v>
+        <v>1</v>
       </c>
       <c r="BM8" t="n">
-        <v>0.64</v>
+        <v>0.6</v>
       </c>
       <c r="BN8" t="n">
-        <v>1.71</v>
+        <v>1.6</v>
       </c>
       <c r="BO8" t="n">
-        <v>1.36</v>
+        <v>1.27</v>
       </c>
       <c r="BP8" t="n">
-        <v>4.93</v>
+        <v>4.73</v>
       </c>
       <c r="BQ8" t="n">
-        <v>5.21</v>
+        <v>5.47</v>
       </c>
       <c r="BR8" t="n">
-        <v>92.86</v>
+        <v>86.67</v>
       </c>
       <c r="BS8" t="n">
-        <v>78.56999999999999</v>
+        <v>73.33</v>
       </c>
       <c r="BT8" t="n">
-        <v>35.71</v>
+        <v>33.33</v>
       </c>
       <c r="BU8" t="n">
-        <v>28.57</v>
+        <v>26.67</v>
       </c>
       <c r="BV8" t="n">
-        <v>21.43</v>
+        <v>20</v>
       </c>
       <c r="BW8" t="n">
-        <v>14.29</v>
+        <v>13.33</v>
       </c>
       <c r="BX8" t="n">
-        <v>35.71</v>
+        <v>33.33</v>
       </c>
       <c r="BY8" t="n">
-        <v>2.15</v>
+        <v>2.17</v>
       </c>
       <c r="BZ8" t="n">
-        <v>2.27</v>
+        <v>2.28</v>
       </c>
       <c r="CA8" t="n">
-        <v>3.92</v>
+        <v>3.9</v>
       </c>
       <c r="CB8" t="n">
-        <v>4.04</v>
+        <v>4.01</v>
       </c>
       <c r="CC8" t="n">
         <v>4.78</v>
@@ -4049,19 +4049,19 @@
         <v>3.57</v>
       </c>
       <c r="CH8" t="n">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="CI8" t="n">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="CJ8" t="n">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="CK8" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="CL8" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="CM8" t="n">
         <v>2.9</v>
@@ -4070,13 +4070,13 @@
         <v>2.25</v>
       </c>
       <c r="CO8" t="n">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="CP8" t="n">
         <v>1.58</v>
       </c>
       <c r="CQ8" t="n">
-        <v>2.4</v>
+        <v>2.41</v>
       </c>
       <c r="CR8" t="n">
         <v>1.34</v>
@@ -4091,10 +4091,10 @@
         <v>1.66</v>
       </c>
       <c r="CV8" t="n">
-        <v>2.58</v>
+        <v>2.59</v>
       </c>
       <c r="CW8" t="n">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="CX8" t="inlineStr"/>
       <c r="CY8" t="n">
@@ -4114,46 +4114,46 @@
         <v>2.45</v>
       </c>
       <c r="DE8" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DF8" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="DG8" t="n">
-        <v>2.36</v>
+        <v>2.74</v>
       </c>
       <c r="DH8" t="n">
-        <v>89.42</v>
+        <v>90.2</v>
       </c>
       <c r="DI8" t="n">
         <v>0</v>
       </c>
       <c r="DJ8" t="n">
-        <v>1.42</v>
+        <v>1.46</v>
       </c>
       <c r="DK8" t="n">
-        <v>5.29</v>
+        <v>5.53</v>
       </c>
       <c r="DL8" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="DM8" t="n">
-        <v>46.07</v>
+        <v>48.06</v>
       </c>
       <c r="DN8" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.13</v>
       </c>
       <c r="DO8" t="n">
-        <v>2.93</v>
+        <v>2.8</v>
       </c>
       <c r="DP8" t="n">
-        <v>12.14</v>
+        <v>12</v>
       </c>
       <c r="DQ8" t="n">
-        <v>12.07</v>
+        <v>12</v>
       </c>
       <c r="DR8" t="n">
-        <v>8.359999999999999</v>
+        <v>8</v>
       </c>
       <c r="DS8" t="n">
         <v>0.07000000000000001</v>
@@ -4165,28 +4165,28 @@
         <v>0</v>
       </c>
       <c r="DV8" t="n">
-        <v>49.78</v>
+        <v>49.8</v>
       </c>
       <c r="DW8" t="n">
         <v>0</v>
       </c>
       <c r="DX8" t="n">
-        <v>15.5</v>
+        <v>15.8</v>
       </c>
       <c r="DY8" t="n">
-        <v>10.86</v>
+        <v>11.14</v>
       </c>
       <c r="DZ8" t="n">
-        <v>4.65</v>
+        <v>4.67</v>
       </c>
       <c r="EA8" t="n">
-        <v>21.71</v>
+        <v>20.93</v>
       </c>
       <c r="EB8" t="n">
-        <v>1.6</v>
+        <v>1.64</v>
       </c>
       <c r="EC8" t="n">
-        <v>1.42</v>
+        <v>1.46</v>
       </c>
     </row>
     <row r="9">
@@ -4196,25 +4196,25 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C9" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D9" t="n">
         <v>7</v>
       </c>
       <c r="E9" t="n">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="F9" t="n">
-        <v>2.57</v>
+        <v>2.5</v>
       </c>
       <c r="G9" t="n">
-        <v>1.43</v>
+        <v>2.12</v>
       </c>
       <c r="H9" t="n">
-        <v>72.56999999999999</v>
+        <v>77.25</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
@@ -4223,34 +4223,34 @@
         <v>3</v>
       </c>
       <c r="K9" t="n">
-        <v>3.14</v>
+        <v>4</v>
       </c>
       <c r="L9" t="n">
-        <v>0.71</v>
+        <v>0.62</v>
       </c>
       <c r="M9" t="n">
-        <v>35.14</v>
+        <v>37</v>
       </c>
       <c r="N9" t="n">
-        <v>0.43</v>
+        <v>0.5</v>
       </c>
       <c r="O9" t="n">
-        <v>1.71</v>
+        <v>1.88</v>
       </c>
       <c r="P9" t="n">
-        <v>16</v>
+        <v>15.88</v>
       </c>
       <c r="Q9" t="n">
-        <v>11.71</v>
+        <v>11.88</v>
       </c>
       <c r="R9" t="n">
-        <v>8.710000000000001</v>
+        <v>8.380000000000001</v>
       </c>
       <c r="S9" t="n">
-        <v>1.14</v>
+        <v>1.25</v>
       </c>
       <c r="T9" t="n">
-        <v>1.43</v>
+        <v>1.38</v>
       </c>
       <c r="U9" t="n">
         <v>0</v>
@@ -4262,25 +4262,25 @@
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>43.29</v>
+        <v>44.25</v>
       </c>
       <c r="Y9" t="n">
         <v>0</v>
       </c>
       <c r="Z9" t="n">
-        <v>12.86</v>
+        <v>13.62</v>
       </c>
       <c r="AA9" t="n">
-        <v>8.43</v>
+        <v>9</v>
       </c>
       <c r="AB9" t="n">
-        <v>4.43</v>
+        <v>4.62</v>
       </c>
       <c r="AC9" t="n">
-        <v>17.86</v>
+        <v>18.5</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.37</v>
+        <v>1.45</v>
       </c>
       <c r="AE9" t="n">
         <v>3</v>
@@ -4367,70 +4367,70 @@
         <v>3.14</v>
       </c>
       <c r="BG9" t="n">
-        <v>2.64</v>
+        <v>2.67</v>
       </c>
       <c r="BH9" t="n">
-        <v>9.57</v>
+        <v>9.67</v>
       </c>
       <c r="BI9" t="n">
-        <v>2.64</v>
+        <v>2.67</v>
       </c>
       <c r="BJ9" t="n">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="BK9" t="n">
-        <v>0.29</v>
+        <v>0.4</v>
       </c>
       <c r="BL9" t="n">
-        <v>0.86</v>
+        <v>0.8</v>
       </c>
       <c r="BM9" t="n">
-        <v>0.64</v>
+        <v>0.6</v>
       </c>
       <c r="BN9" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="BO9" t="n">
-        <v>1.14</v>
+        <v>1.27</v>
       </c>
       <c r="BP9" t="n">
-        <v>5.07</v>
+        <v>4.93</v>
       </c>
       <c r="BQ9" t="n">
-        <v>4.5</v>
+        <v>4.73</v>
       </c>
       <c r="BR9" t="n">
         <v>100</v>
       </c>
       <c r="BS9" t="n">
-        <v>78.56999999999999</v>
+        <v>80</v>
       </c>
       <c r="BT9" t="n">
-        <v>50</v>
+        <v>53.33</v>
       </c>
       <c r="BU9" t="n">
-        <v>28.57</v>
+        <v>26.67</v>
       </c>
       <c r="BV9" t="n">
-        <v>7.14</v>
+        <v>6.67</v>
       </c>
       <c r="BW9" t="n">
         <v>0</v>
       </c>
       <c r="BX9" t="n">
-        <v>50</v>
+        <v>53.33</v>
       </c>
       <c r="BY9" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="BZ9" t="n">
         <v>3.15</v>
       </c>
-      <c r="BZ9" t="n">
-        <v>3.2</v>
-      </c>
       <c r="CA9" t="n">
-        <v>3.57</v>
+        <v>3.55</v>
       </c>
       <c r="CB9" t="n">
-        <v>3.6</v>
+        <v>3.58</v>
       </c>
       <c r="CC9" t="n">
         <v>4.22</v>
@@ -4439,34 +4439,34 @@
         <v>4.46</v>
       </c>
       <c r="CE9" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="CF9" t="n">
-        <v>2.64</v>
+        <v>2.66</v>
       </c>
       <c r="CG9" t="n">
-        <v>3.05</v>
+        <v>3.03</v>
       </c>
       <c r="CH9" t="n">
         <v>1.44</v>
       </c>
       <c r="CI9" t="n">
-        <v>2</v>
+        <v>2.01</v>
       </c>
       <c r="CJ9" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="CK9" t="n">
         <v>1.43</v>
       </c>
       <c r="CL9" t="n">
-        <v>1.74</v>
+        <v>1.76</v>
       </c>
       <c r="CM9" t="n">
-        <v>2.6</v>
+        <v>2.59</v>
       </c>
       <c r="CN9" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="CO9" t="n">
         <v>1.27</v>
@@ -4475,13 +4475,13 @@
         <v>1.87</v>
       </c>
       <c r="CQ9" t="n">
-        <v>3.14</v>
+        <v>3.15</v>
       </c>
       <c r="CR9" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="CS9" t="n">
-        <v>2.82</v>
+        <v>2.83</v>
       </c>
       <c r="CT9" t="n">
         <v>3.08</v>
@@ -4490,22 +4490,22 @@
         <v>1.45</v>
       </c>
       <c r="CV9" t="n">
-        <v>2.1</v>
+        <v>2.11</v>
       </c>
       <c r="CW9" t="n">
         <v>1.79</v>
       </c>
       <c r="CX9" t="n">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="CY9" t="n">
-        <v>1.76</v>
+        <v>1.78</v>
       </c>
       <c r="CZ9" t="n">
-        <v>2.52</v>
+        <v>2.49</v>
       </c>
       <c r="DA9" t="n">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="DB9" t="n">
         <v>1.29</v>
@@ -4517,16 +4517,16 @@
         <v>3.26</v>
       </c>
       <c r="DE9" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DF9" t="n">
-        <v>2.36</v>
+        <v>2.33</v>
       </c>
       <c r="DG9" t="n">
-        <v>2.07</v>
+        <v>2.4</v>
       </c>
       <c r="DH9" t="n">
-        <v>76.86</v>
+        <v>79.06999999999999</v>
       </c>
       <c r="DI9" t="n">
         <v>0</v>
@@ -4535,28 +4535,28 @@
         <v>3.14</v>
       </c>
       <c r="DK9" t="n">
-        <v>3.92</v>
+        <v>4.33</v>
       </c>
       <c r="DL9" t="n">
-        <v>0.5</v>
+        <v>0.47</v>
       </c>
       <c r="DM9" t="n">
-        <v>40</v>
+        <v>40.67</v>
       </c>
       <c r="DN9" t="n">
-        <v>0.78</v>
+        <v>0.8</v>
       </c>
       <c r="DO9" t="n">
-        <v>1.86</v>
+        <v>1.94</v>
       </c>
       <c r="DP9" t="n">
-        <v>16.78</v>
+        <v>16.67</v>
       </c>
       <c r="DQ9" t="n">
-        <v>11</v>
+        <v>11.14</v>
       </c>
       <c r="DR9" t="n">
-        <v>8.5</v>
+        <v>8.34</v>
       </c>
       <c r="DS9" t="n">
         <v>0</v>
@@ -4568,25 +4568,25 @@
         <v>0</v>
       </c>
       <c r="DV9" t="n">
-        <v>44.29</v>
+        <v>44.74</v>
       </c>
       <c r="DW9" t="n">
         <v>0.07000000000000001</v>
       </c>
       <c r="DX9" t="n">
-        <v>11.93</v>
+        <v>12.4</v>
       </c>
       <c r="DY9" t="n">
-        <v>8.07</v>
+        <v>8.4</v>
       </c>
       <c r="DZ9" t="n">
-        <v>3.86</v>
+        <v>4</v>
       </c>
       <c r="EA9" t="n">
-        <v>18.93</v>
+        <v>19.2</v>
       </c>
       <c r="EB9" t="n">
-        <v>1.31</v>
+        <v>1.36</v>
       </c>
       <c r="EC9" t="n">
         <v>3.07</v>
@@ -4599,10 +4599,10 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C10" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D10" t="n">
         <v>7</v>
@@ -4614,46 +4614,46 @@
         <v>1</v>
       </c>
       <c r="G10" t="n">
-        <v>2.71</v>
+        <v>2.75</v>
       </c>
       <c r="H10" t="n">
-        <v>72.29000000000001</v>
+        <v>74.12</v>
       </c>
       <c r="I10" t="n">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="J10" t="n">
-        <v>1.71</v>
+        <v>1.75</v>
       </c>
       <c r="K10" t="n">
         <v>5</v>
       </c>
       <c r="L10" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="M10" t="n">
-        <v>39.43</v>
+        <v>40.38</v>
       </c>
       <c r="N10" t="n">
-        <v>0.71</v>
+        <v>0.75</v>
       </c>
       <c r="O10" t="n">
-        <v>2.29</v>
+        <v>2.25</v>
       </c>
       <c r="P10" t="n">
-        <v>11.43</v>
+        <v>11.75</v>
       </c>
       <c r="Q10" t="n">
-        <v>11.86</v>
+        <v>11.75</v>
       </c>
       <c r="R10" t="n">
-        <v>8.289999999999999</v>
+        <v>9.119999999999999</v>
       </c>
       <c r="S10" t="n">
-        <v>0.43</v>
+        <v>0.5</v>
       </c>
       <c r="T10" t="n">
-        <v>0.57</v>
+        <v>0.5</v>
       </c>
       <c r="U10" t="n">
         <v>0</v>
@@ -4665,7 +4665,7 @@
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>34.86</v>
+        <v>35.12</v>
       </c>
       <c r="Y10" t="n">
         <v>0</v>
@@ -4674,19 +4674,19 @@
         <v>10</v>
       </c>
       <c r="AA10" t="n">
-        <v>7.57</v>
+        <v>7.38</v>
       </c>
       <c r="AB10" t="n">
-        <v>2.43</v>
+        <v>2.62</v>
       </c>
       <c r="AC10" t="n">
-        <v>20.86</v>
+        <v>20.12</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.71</v>
+        <v>1.75</v>
       </c>
       <c r="AF10" t="n">
         <v>0.14</v>
@@ -4770,61 +4770,61 @@
         <v>2</v>
       </c>
       <c r="BG10" t="n">
-        <v>1.79</v>
+        <v>1.73</v>
       </c>
       <c r="BH10" t="n">
-        <v>8.07</v>
+        <v>8.33</v>
       </c>
       <c r="BI10" t="n">
-        <v>1.79</v>
+        <v>1.73</v>
       </c>
       <c r="BJ10" t="n">
-        <v>0.5</v>
+        <v>0.47</v>
       </c>
       <c r="BK10" t="n">
-        <v>0.36</v>
+        <v>0.33</v>
       </c>
       <c r="BL10" t="n">
-        <v>0.57</v>
+        <v>0.53</v>
       </c>
       <c r="BM10" t="n">
-        <v>0.36</v>
+        <v>0.4</v>
       </c>
       <c r="BN10" t="n">
         <v>0.93</v>
       </c>
       <c r="BO10" t="n">
-        <v>0.86</v>
+        <v>0.8</v>
       </c>
       <c r="BP10" t="n">
-        <v>2.93</v>
+        <v>3.07</v>
       </c>
       <c r="BQ10" t="n">
-        <v>5.14</v>
+        <v>5.27</v>
       </c>
       <c r="BR10" t="n">
-        <v>71.43000000000001</v>
+        <v>73.33</v>
       </c>
       <c r="BS10" t="n">
-        <v>50</v>
+        <v>46.67</v>
       </c>
       <c r="BT10" t="n">
-        <v>35.71</v>
+        <v>33.33</v>
       </c>
       <c r="BU10" t="n">
-        <v>14.29</v>
+        <v>13.33</v>
       </c>
       <c r="BV10" t="n">
-        <v>7.14</v>
+        <v>6.67</v>
       </c>
       <c r="BW10" t="n">
         <v>0</v>
       </c>
       <c r="BX10" t="n">
-        <v>42.86</v>
+        <v>40</v>
       </c>
       <c r="BY10" t="n">
-        <v>3.8</v>
+        <v>3.82</v>
       </c>
       <c r="BZ10" t="n">
         <v>4.01</v>
@@ -4845,13 +4845,13 @@
         <v>1.38</v>
       </c>
       <c r="CF10" t="n">
-        <v>2.77</v>
+        <v>2.78</v>
       </c>
       <c r="CG10" t="n">
-        <v>2.88</v>
+        <v>2.87</v>
       </c>
       <c r="CH10" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="CI10" t="n">
         <v>1.91</v>
@@ -4863,7 +4863,7 @@
         <v>1.58</v>
       </c>
       <c r="CL10" t="n">
-        <v>2.01</v>
+        <v>2</v>
       </c>
       <c r="CM10" t="n">
         <v>2.31</v>
@@ -4878,7 +4878,7 @@
         <v>1.97</v>
       </c>
       <c r="CQ10" t="n">
-        <v>3.46</v>
+        <v>3.48</v>
       </c>
       <c r="CR10" t="n">
         <v>1.4</v>
@@ -4917,49 +4917,49 @@
         <v>2.06</v>
       </c>
       <c r="DD10" t="n">
-        <v>3.55</v>
+        <v>3.56</v>
       </c>
       <c r="DE10" t="n">
         <v>0.07000000000000001</v>
       </c>
       <c r="DF10" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="DG10" t="n">
-        <v>2.5</v>
+        <v>2.54</v>
       </c>
       <c r="DH10" t="n">
-        <v>76.08</v>
+        <v>76.8</v>
       </c>
       <c r="DI10" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DJ10" t="n">
         <v>2</v>
       </c>
       <c r="DK10" t="n">
-        <v>4.15</v>
+        <v>4.2</v>
       </c>
       <c r="DL10" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="DM10" t="n">
-        <v>36.43</v>
+        <v>37.14</v>
       </c>
       <c r="DN10" t="n">
-        <v>0.71</v>
+        <v>0.73</v>
       </c>
       <c r="DO10" t="n">
-        <v>1.64</v>
+        <v>1.67</v>
       </c>
       <c r="DP10" t="n">
-        <v>12.28</v>
+        <v>12.4</v>
       </c>
       <c r="DQ10" t="n">
-        <v>12.72</v>
+        <v>12.6</v>
       </c>
       <c r="DR10" t="n">
-        <v>8.93</v>
+        <v>9.33</v>
       </c>
       <c r="DS10" t="n">
         <v>0</v>
@@ -4971,28 +4971,28 @@
         <v>0</v>
       </c>
       <c r="DV10" t="n">
-        <v>32.79</v>
+        <v>33.06</v>
       </c>
       <c r="DW10" t="n">
         <v>0.07000000000000001</v>
       </c>
       <c r="DX10" t="n">
-        <v>9.140000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="DY10" t="n">
-        <v>6.72</v>
+        <v>6.67</v>
       </c>
       <c r="DZ10" t="n">
-        <v>2.43</v>
+        <v>2.53</v>
       </c>
       <c r="EA10" t="n">
-        <v>21.72</v>
+        <v>21.26</v>
       </c>
       <c r="EB10" t="n">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="EC10" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
     </row>
     <row r="11">
@@ -5002,13 +5002,13 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C11" t="n">
         <v>8</v>
       </c>
       <c r="D11" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E11" t="n">
         <v>0.12</v>
@@ -5092,139 +5092,139 @@
         <v>2.62</v>
       </c>
       <c r="AF11" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.67</v>
+        <v>1.71</v>
       </c>
       <c r="AH11" t="n">
-        <v>2.67</v>
+        <v>2.86</v>
       </c>
       <c r="AI11" t="n">
-        <v>94</v>
+        <v>93.43000000000001</v>
       </c>
       <c r="AJ11" t="n">
         <v>0</v>
       </c>
       <c r="AK11" t="n">
-        <v>2.67</v>
+        <v>2.71</v>
       </c>
       <c r="AL11" t="n">
-        <v>5.83</v>
+        <v>6</v>
       </c>
       <c r="AM11" t="n">
-        <v>0.17</v>
+        <v>0.29</v>
       </c>
       <c r="AN11" t="n">
-        <v>54.83</v>
+        <v>57</v>
       </c>
       <c r="AO11" t="n">
         <v>1</v>
       </c>
       <c r="AP11" t="n">
-        <v>3.17</v>
+        <v>3.14</v>
       </c>
       <c r="AQ11" t="n">
-        <v>14.33</v>
+        <v>13.86</v>
       </c>
       <c r="AR11" t="n">
-        <v>8.33</v>
+        <v>9.140000000000001</v>
       </c>
       <c r="AS11" t="n">
-        <v>7</v>
+        <v>7.86</v>
       </c>
       <c r="AT11" t="n">
-        <v>1</v>
+        <v>0.86</v>
       </c>
       <c r="AU11" t="n">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="AV11" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="AW11" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="AX11" t="n">
         <v>0</v>
       </c>
       <c r="AY11" t="n">
-        <v>54.67</v>
+        <v>55.86</v>
       </c>
       <c r="AZ11" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="BA11" t="n">
+        <v>13</v>
+      </c>
+      <c r="BB11" t="n">
+        <v>8.859999999999999</v>
+      </c>
+      <c r="BC11" t="n">
+        <v>4.14</v>
+      </c>
+      <c r="BD11" t="n">
+        <v>22.86</v>
+      </c>
+      <c r="BE11" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="BF11" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="BG11" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="BH11" t="n">
+        <v>10.33</v>
+      </c>
+      <c r="BI11" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="BJ11" t="n">
+        <v>0.47</v>
+      </c>
+      <c r="BK11" t="n">
         <v>0.33</v>
       </c>
-      <c r="BA11" t="n">
-        <v>11.83</v>
-      </c>
-      <c r="BB11" t="n">
-        <v>8.17</v>
-      </c>
-      <c r="BC11" t="n">
-        <v>3.67</v>
-      </c>
-      <c r="BD11" t="n">
-        <v>22.5</v>
-      </c>
-      <c r="BE11" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="BF11" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="BG11" t="n">
-        <v>2.43</v>
-      </c>
-      <c r="BH11" t="n">
-        <v>10.21</v>
-      </c>
-      <c r="BI11" t="n">
-        <v>2.43</v>
-      </c>
-      <c r="BJ11" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="BK11" t="n">
-        <v>0.36</v>
-      </c>
       <c r="BL11" t="n">
-        <v>0.93</v>
+        <v>0.87</v>
       </c>
       <c r="BM11" t="n">
-        <v>0.64</v>
+        <v>0.67</v>
       </c>
       <c r="BN11" t="n">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="BO11" t="n">
-        <v>0.86</v>
+        <v>0.8</v>
       </c>
       <c r="BP11" t="n">
         <v>5.07</v>
       </c>
       <c r="BQ11" t="n">
-        <v>5.14</v>
+        <v>5.27</v>
       </c>
       <c r="BR11" t="n">
-        <v>92.86</v>
+        <v>93.33</v>
       </c>
       <c r="BS11" t="n">
-        <v>64.29000000000001</v>
+        <v>60</v>
       </c>
       <c r="BT11" t="n">
-        <v>28.57</v>
+        <v>26.67</v>
       </c>
       <c r="BU11" t="n">
-        <v>28.57</v>
+        <v>26.67</v>
       </c>
       <c r="BV11" t="n">
-        <v>14.29</v>
+        <v>13.33</v>
       </c>
       <c r="BW11" t="n">
-        <v>7.14</v>
+        <v>6.67</v>
       </c>
       <c r="BX11" t="n">
-        <v>42.86</v>
+        <v>40</v>
       </c>
       <c r="BY11" t="n">
         <v>1.85</v>
@@ -5233,55 +5233,55 @@
         <v>1.97</v>
       </c>
       <c r="CA11" t="n">
-        <v>3.67</v>
+        <v>3.66</v>
       </c>
       <c r="CB11" t="n">
-        <v>3.81</v>
+        <v>3.79</v>
       </c>
       <c r="CC11" t="n">
-        <v>2.62</v>
+        <v>2.5</v>
       </c>
       <c r="CD11" t="n">
-        <v>2.77</v>
+        <v>2.66</v>
       </c>
       <c r="CE11" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="CF11" t="n">
-        <v>2.49</v>
+        <v>2.52</v>
       </c>
       <c r="CG11" t="n">
-        <v>3.14</v>
+        <v>3.11</v>
       </c>
       <c r="CH11" t="n">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="CI11" t="n">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="CJ11" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="CK11" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="CL11" t="n">
         <v>1.89</v>
       </c>
       <c r="CM11" t="n">
-        <v>2.56</v>
+        <v>2.54</v>
       </c>
       <c r="CN11" t="n">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="CO11" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="CP11" t="n">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="CQ11" t="n">
-        <v>2.81</v>
+        <v>2.88</v>
       </c>
       <c r="CR11" t="n">
         <v>1.35</v>
@@ -5296,10 +5296,10 @@
         <v>1.52</v>
       </c>
       <c r="CV11" t="n">
-        <v>2.26</v>
+        <v>2.24</v>
       </c>
       <c r="CW11" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="CX11" t="n">
         <v>1.52</v>
@@ -5314,88 +5314,88 @@
         <v>2</v>
       </c>
       <c r="DB11" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="DC11" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="DD11" t="n">
-        <v>2.91</v>
+        <v>2.96</v>
       </c>
       <c r="DE11" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DF11" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="DG11" t="n">
-        <v>3.21</v>
+        <v>3.27</v>
       </c>
       <c r="DH11" t="n">
-        <v>100.79</v>
+        <v>100.07</v>
       </c>
       <c r="DI11" t="n">
         <v>0</v>
       </c>
       <c r="DJ11" t="n">
-        <v>2.79</v>
+        <v>2.8</v>
       </c>
       <c r="DK11" t="n">
-        <v>6.36</v>
+        <v>6.4</v>
       </c>
       <c r="DL11" t="n">
-        <v>0.29</v>
+        <v>0.34</v>
       </c>
       <c r="DM11" t="n">
-        <v>58.21</v>
+        <v>59</v>
       </c>
       <c r="DN11" t="n">
-        <v>0.93</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="DO11" t="n">
-        <v>3.14</v>
+        <v>3.13</v>
       </c>
       <c r="DP11" t="n">
-        <v>14.36</v>
+        <v>14.14</v>
       </c>
       <c r="DQ11" t="n">
-        <v>9.57</v>
+        <v>9.869999999999999</v>
       </c>
       <c r="DR11" t="n">
-        <v>7.22</v>
+        <v>7.6</v>
       </c>
       <c r="DS11" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DT11" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DU11" t="n">
         <v>0</v>
       </c>
       <c r="DV11" t="n">
-        <v>52.5</v>
+        <v>53.2</v>
       </c>
       <c r="DW11" t="n">
-        <v>0.21</v>
+        <v>0.2</v>
       </c>
       <c r="DX11" t="n">
-        <v>15.14</v>
+        <v>15.46</v>
       </c>
       <c r="DY11" t="n">
-        <v>10.22</v>
+        <v>10.4</v>
       </c>
       <c r="DZ11" t="n">
-        <v>4.93</v>
+        <v>5.07</v>
       </c>
       <c r="EA11" t="n">
-        <v>19.64</v>
+        <v>20</v>
       </c>
       <c r="EB11" t="n">
-        <v>1.72</v>
+        <v>1.75</v>
       </c>
       <c r="EC11" t="n">
-        <v>2.5</v>
+        <v>2.53</v>
       </c>
     </row>
     <row r="12">
@@ -5405,10 +5405,10 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C12" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D12" t="n">
         <v>7</v>
@@ -5417,82 +5417,82 @@
         <v>0</v>
       </c>
       <c r="F12" t="n">
-        <v>1.71</v>
+        <v>1.5</v>
       </c>
       <c r="G12" t="n">
-        <v>2.14</v>
+        <v>2.25</v>
       </c>
       <c r="H12" t="n">
-        <v>97</v>
+        <v>100.12</v>
       </c>
       <c r="I12" t="n">
         <v>0</v>
       </c>
       <c r="J12" t="n">
-        <v>2.71</v>
+        <v>2.5</v>
       </c>
       <c r="K12" t="n">
-        <v>4.86</v>
+        <v>4.88</v>
       </c>
       <c r="L12" t="n">
-        <v>0.71</v>
+        <v>0.75</v>
       </c>
       <c r="M12" t="n">
-        <v>43.71</v>
+        <v>45</v>
       </c>
       <c r="N12" t="n">
-        <v>0.86</v>
+        <v>0.88</v>
       </c>
       <c r="O12" t="n">
-        <v>2.71</v>
+        <v>2.62</v>
       </c>
       <c r="P12" t="n">
-        <v>10.57</v>
+        <v>11.12</v>
       </c>
       <c r="Q12" t="n">
-        <v>13</v>
+        <v>13.12</v>
       </c>
       <c r="R12" t="n">
-        <v>6.71</v>
+        <v>6.75</v>
       </c>
       <c r="S12" t="n">
-        <v>1.14</v>
+        <v>1.25</v>
       </c>
       <c r="T12" t="n">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="U12" t="n">
-        <v>0.43</v>
+        <v>0.38</v>
       </c>
       <c r="V12" t="n">
-        <v>0.43</v>
+        <v>0.38</v>
       </c>
       <c r="W12" t="n">
         <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>53.57</v>
+        <v>53.5</v>
       </c>
       <c r="Y12" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="Z12" t="n">
-        <v>13</v>
+        <v>13.25</v>
       </c>
       <c r="AA12" t="n">
-        <v>7.86</v>
+        <v>8</v>
       </c>
       <c r="AB12" t="n">
-        <v>5.14</v>
+        <v>5.25</v>
       </c>
       <c r="AC12" t="n">
         <v>21</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="AE12" t="n">
-        <v>2.43</v>
+        <v>2.25</v>
       </c>
       <c r="AF12" t="n">
         <v>0</v>
@@ -5576,49 +5576,49 @@
         <v>2.29</v>
       </c>
       <c r="BG12" t="n">
-        <v>2.07</v>
+        <v>2.13</v>
       </c>
       <c r="BH12" t="n">
-        <v>8.93</v>
+        <v>8.869999999999999</v>
       </c>
       <c r="BI12" t="n">
-        <v>2.07</v>
+        <v>2.13</v>
       </c>
       <c r="BJ12" t="n">
-        <v>0.71</v>
+        <v>0.67</v>
       </c>
       <c r="BK12" t="n">
-        <v>0.43</v>
+        <v>0.4</v>
       </c>
       <c r="BL12" t="n">
-        <v>0.64</v>
+        <v>0.67</v>
       </c>
       <c r="BM12" t="n">
-        <v>0.29</v>
+        <v>0.4</v>
       </c>
       <c r="BN12" t="n">
-        <v>0.93</v>
+        <v>1.07</v>
       </c>
       <c r="BO12" t="n">
-        <v>1.14</v>
+        <v>1.07</v>
       </c>
       <c r="BP12" t="n">
-        <v>3.86</v>
+        <v>3.87</v>
       </c>
       <c r="BQ12" t="n">
-        <v>5.07</v>
+        <v>5</v>
       </c>
       <c r="BR12" t="n">
-        <v>92.86</v>
+        <v>93.33</v>
       </c>
       <c r="BS12" t="n">
-        <v>71.43000000000001</v>
+        <v>73.33</v>
       </c>
       <c r="BT12" t="n">
-        <v>28.57</v>
+        <v>33.33</v>
       </c>
       <c r="BU12" t="n">
-        <v>14.29</v>
+        <v>13.33</v>
       </c>
       <c r="BV12" t="n">
         <v>0</v>
@@ -5627,19 +5627,19 @@
         <v>0</v>
       </c>
       <c r="BX12" t="n">
-        <v>57.14</v>
+        <v>60</v>
       </c>
       <c r="BY12" t="n">
-        <v>2.73</v>
+        <v>2.66</v>
       </c>
       <c r="BZ12" t="n">
-        <v>2.97</v>
+        <v>2.87</v>
       </c>
       <c r="CA12" t="n">
-        <v>3.49</v>
+        <v>3.47</v>
       </c>
       <c r="CB12" t="n">
-        <v>3.62</v>
+        <v>3.6</v>
       </c>
       <c r="CC12" t="n">
         <v>3.64</v>
@@ -5651,16 +5651,16 @@
         <v>1.34</v>
       </c>
       <c r="CF12" t="n">
-        <v>2.59</v>
+        <v>2.6</v>
       </c>
       <c r="CG12" t="n">
-        <v>3.07</v>
+        <v>3.04</v>
       </c>
       <c r="CH12" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="CI12" t="n">
-        <v>2.1</v>
+        <v>2.11</v>
       </c>
       <c r="CJ12" t="n">
         <v>1.68</v>
@@ -5672,19 +5672,19 @@
         <v>1.93</v>
       </c>
       <c r="CM12" t="n">
-        <v>2.48</v>
+        <v>2.47</v>
       </c>
       <c r="CN12" t="n">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="CO12" t="n">
         <v>1.26</v>
       </c>
       <c r="CP12" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="CQ12" t="n">
-        <v>3.03</v>
+        <v>3.08</v>
       </c>
       <c r="CR12" t="n">
         <v>1.36</v>
@@ -5708,7 +5708,7 @@
         <v>1.59</v>
       </c>
       <c r="CY12" t="n">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="CZ12" t="n">
         <v>2.34</v>
@@ -5723,82 +5723,82 @@
         <v>1.88</v>
       </c>
       <c r="DD12" t="n">
-        <v>3.09</v>
+        <v>3.11</v>
       </c>
       <c r="DE12" t="n">
         <v>0</v>
       </c>
       <c r="DF12" t="n">
-        <v>1.71</v>
+        <v>1.6</v>
       </c>
       <c r="DG12" t="n">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="DH12" t="n">
-        <v>91.5</v>
+        <v>93.53</v>
       </c>
       <c r="DI12" t="n">
         <v>0</v>
       </c>
       <c r="DJ12" t="n">
-        <v>2.64</v>
+        <v>2.53</v>
       </c>
       <c r="DK12" t="n">
-        <v>4</v>
+        <v>4.07</v>
       </c>
       <c r="DL12" t="n">
-        <v>0.57</v>
+        <v>0.6</v>
       </c>
       <c r="DM12" t="n">
-        <v>38.79</v>
+        <v>39.8</v>
       </c>
       <c r="DN12" t="n">
-        <v>0.78</v>
+        <v>0.8</v>
       </c>
       <c r="DO12" t="n">
         <v>1.86</v>
       </c>
       <c r="DP12" t="n">
-        <v>12.28</v>
+        <v>12.46</v>
       </c>
       <c r="DQ12" t="n">
-        <v>13.14</v>
+        <v>13.2</v>
       </c>
       <c r="DR12" t="n">
-        <v>7.5</v>
+        <v>7.47</v>
       </c>
       <c r="DS12" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="DT12" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="DU12" t="n">
         <v>0</v>
       </c>
       <c r="DV12" t="n">
-        <v>50</v>
+        <v>50.2</v>
       </c>
       <c r="DW12" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DX12" t="n">
-        <v>11.07</v>
+        <v>11.33</v>
       </c>
       <c r="DY12" t="n">
-        <v>7.14</v>
+        <v>7.27</v>
       </c>
       <c r="DZ12" t="n">
-        <v>3.92</v>
+        <v>4.06</v>
       </c>
       <c r="EA12" t="n">
-        <v>20.43</v>
+        <v>20.47</v>
       </c>
       <c r="EB12" t="n">
-        <v>1.26</v>
+        <v>1.29</v>
       </c>
       <c r="EC12" t="n">
-        <v>2.36</v>
+        <v>2.27</v>
       </c>
     </row>
     <row r="13">
@@ -5808,13 +5808,13 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C13" t="n">
         <v>8</v>
       </c>
       <c r="D13" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E13" t="n">
         <v>0.12</v>
@@ -5901,127 +5901,127 @@
         <v>0</v>
       </c>
       <c r="AG13" t="n">
-        <v>0.83</v>
+        <v>1</v>
       </c>
       <c r="AH13" t="n">
-        <v>4</v>
+        <v>3.57</v>
       </c>
       <c r="AI13" t="n">
-        <v>98.67</v>
+        <v>95.70999999999999</v>
       </c>
       <c r="AJ13" t="n">
         <v>0</v>
       </c>
       <c r="AK13" t="n">
-        <v>1.33</v>
+        <v>1.43</v>
       </c>
       <c r="AL13" t="n">
-        <v>6.83</v>
+        <v>6</v>
       </c>
       <c r="AM13" t="n">
-        <v>0.33</v>
+        <v>0.29</v>
       </c>
       <c r="AN13" t="n">
-        <v>53.67</v>
+        <v>50.29</v>
       </c>
       <c r="AO13" t="n">
-        <v>0.5</v>
+        <v>0.43</v>
       </c>
       <c r="AP13" t="n">
-        <v>2.83</v>
+        <v>2.43</v>
       </c>
       <c r="AQ13" t="n">
-        <v>12.17</v>
+        <v>12.29</v>
       </c>
       <c r="AR13" t="n">
-        <v>11.33</v>
+        <v>11.71</v>
       </c>
       <c r="AS13" t="n">
-        <v>6.83</v>
+        <v>7.71</v>
       </c>
       <c r="AT13" t="n">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="AU13" t="n">
-        <v>1.17</v>
+        <v>1.29</v>
       </c>
       <c r="AV13" t="n">
-        <v>0.33</v>
+        <v>0.43</v>
       </c>
       <c r="AW13" t="n">
-        <v>0.33</v>
+        <v>0.43</v>
       </c>
       <c r="AX13" t="n">
         <v>0</v>
       </c>
       <c r="AY13" t="n">
-        <v>53</v>
+        <v>52.43</v>
       </c>
       <c r="AZ13" t="n">
         <v>0</v>
       </c>
       <c r="BA13" t="n">
-        <v>14.33</v>
+        <v>13.43</v>
       </c>
       <c r="BB13" t="n">
-        <v>9.83</v>
+        <v>9</v>
       </c>
       <c r="BC13" t="n">
-        <v>4.5</v>
+        <v>4.43</v>
       </c>
       <c r="BD13" t="n">
-        <v>25</v>
+        <v>23.86</v>
       </c>
       <c r="BE13" t="n">
-        <v>1.61</v>
+        <v>1.52</v>
       </c>
       <c r="BF13" t="n">
-        <v>1.33</v>
+        <v>1.43</v>
       </c>
       <c r="BG13" t="n">
-        <v>2.5</v>
+        <v>2.53</v>
       </c>
       <c r="BH13" t="n">
-        <v>9.859999999999999</v>
+        <v>9.93</v>
       </c>
       <c r="BI13" t="n">
-        <v>2.5</v>
+        <v>2.53</v>
       </c>
       <c r="BJ13" t="n">
-        <v>0.64</v>
+        <v>0.67</v>
       </c>
       <c r="BK13" t="n">
-        <v>0.36</v>
+        <v>0.47</v>
       </c>
       <c r="BL13" t="n">
-        <v>0.71</v>
+        <v>0.67</v>
       </c>
       <c r="BM13" t="n">
-        <v>0.79</v>
+        <v>0.73</v>
       </c>
       <c r="BN13" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="BO13" t="n">
-        <v>1</v>
+        <v>1.13</v>
       </c>
       <c r="BP13" t="n">
-        <v>4.36</v>
+        <v>4.27</v>
       </c>
       <c r="BQ13" t="n">
-        <v>5.5</v>
+        <v>5.67</v>
       </c>
       <c r="BR13" t="n">
         <v>100</v>
       </c>
       <c r="BS13" t="n">
-        <v>85.70999999999999</v>
+        <v>86.67</v>
       </c>
       <c r="BT13" t="n">
-        <v>42.86</v>
+        <v>46.67</v>
       </c>
       <c r="BU13" t="n">
-        <v>21.43</v>
+        <v>20</v>
       </c>
       <c r="BV13" t="n">
         <v>0</v>
@@ -6030,7 +6030,7 @@
         <v>0</v>
       </c>
       <c r="BX13" t="n">
-        <v>50</v>
+        <v>53.33</v>
       </c>
       <c r="BY13" t="n">
         <v>2.21</v>
@@ -6039,70 +6039,70 @@
         <v>2.4</v>
       </c>
       <c r="CA13" t="n">
-        <v>3.78</v>
+        <v>3.74</v>
       </c>
       <c r="CB13" t="n">
-        <v>3.88</v>
+        <v>3.85</v>
       </c>
       <c r="CC13" t="n">
-        <v>4.61</v>
+        <v>4.35</v>
       </c>
       <c r="CD13" t="n">
-        <v>4.94</v>
+        <v>4.62</v>
       </c>
       <c r="CE13" t="n">
         <v>1.3</v>
       </c>
       <c r="CF13" t="n">
-        <v>2.41</v>
+        <v>2.45</v>
       </c>
       <c r="CG13" t="n">
-        <v>3.23</v>
+        <v>3.2</v>
       </c>
       <c r="CH13" t="n">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="CI13" t="n">
-        <v>2.18</v>
+        <v>2.19</v>
       </c>
       <c r="CJ13" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="CK13" t="n">
         <v>1.45</v>
       </c>
       <c r="CL13" t="n">
-        <v>1.86</v>
+        <v>1.88</v>
       </c>
       <c r="CM13" t="n">
-        <v>2.56</v>
+        <v>2.55</v>
       </c>
       <c r="CN13" t="n">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="CO13" t="n">
         <v>1.21</v>
       </c>
       <c r="CP13" t="n">
-        <v>1.71</v>
+        <v>1.73</v>
       </c>
       <c r="CQ13" t="n">
-        <v>2.77</v>
+        <v>2.8</v>
       </c>
       <c r="CR13" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="CS13" t="n">
-        <v>2.59</v>
+        <v>2.61</v>
       </c>
       <c r="CT13" t="n">
-        <v>3.29</v>
+        <v>3.27</v>
       </c>
       <c r="CU13" t="n">
         <v>1.52</v>
       </c>
       <c r="CV13" t="n">
-        <v>2.3</v>
+        <v>2.29</v>
       </c>
       <c r="CW13" t="n">
         <v>1.66</v>
@@ -6111,97 +6111,97 @@
         <v>1.54</v>
       </c>
       <c r="CY13" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="CZ13" t="n">
         <v>2.44</v>
       </c>
       <c r="DA13" t="n">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="DB13" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="DC13" t="n">
-        <v>1.76</v>
+        <v>1.78</v>
       </c>
       <c r="DD13" t="n">
-        <v>2.84</v>
+        <v>2.87</v>
       </c>
       <c r="DE13" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="DF13" t="n">
-        <v>1.21</v>
+        <v>1.27</v>
       </c>
       <c r="DG13" t="n">
-        <v>3.86</v>
+        <v>3.67</v>
       </c>
       <c r="DH13" t="n">
-        <v>104.72</v>
+        <v>102.93</v>
       </c>
       <c r="DI13" t="n">
         <v>0</v>
       </c>
       <c r="DJ13" t="n">
-        <v>1.71</v>
+        <v>1.73</v>
       </c>
       <c r="DK13" t="n">
-        <v>6</v>
+        <v>5.67</v>
       </c>
       <c r="DL13" t="n">
-        <v>0.28</v>
+        <v>0.27</v>
       </c>
       <c r="DM13" t="n">
-        <v>56.72</v>
+        <v>54.94</v>
       </c>
       <c r="DN13" t="n">
-        <v>0.43</v>
+        <v>0.4</v>
       </c>
       <c r="DO13" t="n">
-        <v>2.14</v>
+        <v>2</v>
       </c>
       <c r="DP13" t="n">
-        <v>11.93</v>
+        <v>12</v>
       </c>
       <c r="DQ13" t="n">
-        <v>11.36</v>
+        <v>11.53</v>
       </c>
       <c r="DR13" t="n">
-        <v>6</v>
+        <v>6.47</v>
       </c>
       <c r="DS13" t="n">
-        <v>0.21</v>
+        <v>0.26</v>
       </c>
       <c r="DT13" t="n">
-        <v>0.21</v>
+        <v>0.26</v>
       </c>
       <c r="DU13" t="n">
         <v>0</v>
       </c>
       <c r="DV13" t="n">
-        <v>54.71</v>
+        <v>54.33</v>
       </c>
       <c r="DW13" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="DX13" t="n">
-        <v>15.22</v>
+        <v>14.74</v>
       </c>
       <c r="DY13" t="n">
-        <v>10.72</v>
+        <v>10.27</v>
       </c>
       <c r="DZ13" t="n">
-        <v>4.5</v>
+        <v>4.47</v>
       </c>
       <c r="EA13" t="n">
-        <v>24.5</v>
+        <v>24</v>
       </c>
       <c r="EB13" t="n">
-        <v>1.68</v>
+        <v>1.64</v>
       </c>
       <c r="EC13" t="n">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
     </row>
     <row r="14">
@@ -6211,13 +6211,13 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C14" t="n">
         <v>7</v>
       </c>
       <c r="D14" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E14" t="n">
         <v>0.14</v>
@@ -6301,52 +6301,52 @@
         <v>2.14</v>
       </c>
       <c r="AF14" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.86</v>
+        <v>1.75</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.14</v>
+        <v>1.88</v>
       </c>
       <c r="AI14" t="n">
-        <v>99.56999999999999</v>
+        <v>92.75</v>
       </c>
       <c r="AJ14" t="n">
         <v>0</v>
       </c>
       <c r="AK14" t="n">
-        <v>2.29</v>
+        <v>2.12</v>
       </c>
       <c r="AL14" t="n">
-        <v>3.71</v>
+        <v>4.62</v>
       </c>
       <c r="AM14" t="n">
-        <v>0.71</v>
+        <v>0.62</v>
       </c>
       <c r="AN14" t="n">
-        <v>49.29</v>
+        <v>48.25</v>
       </c>
       <c r="AO14" t="n">
-        <v>0.43</v>
+        <v>0.38</v>
       </c>
       <c r="AP14" t="n">
-        <v>2.57</v>
+        <v>2.75</v>
       </c>
       <c r="AQ14" t="n">
-        <v>11.14</v>
+        <v>10.88</v>
       </c>
       <c r="AR14" t="n">
-        <v>10.57</v>
+        <v>9.880000000000001</v>
       </c>
       <c r="AS14" t="n">
-        <v>6.71</v>
+        <v>6.88</v>
       </c>
       <c r="AT14" t="n">
-        <v>1.86</v>
+        <v>1.75</v>
       </c>
       <c r="AU14" t="n">
-        <v>1.29</v>
+        <v>1.12</v>
       </c>
       <c r="AV14" t="n">
         <v>0</v>
@@ -6358,82 +6358,82 @@
         <v>0</v>
       </c>
       <c r="AY14" t="n">
-        <v>49.14</v>
+        <v>47.88</v>
       </c>
       <c r="AZ14" t="n">
         <v>0</v>
       </c>
       <c r="BA14" t="n">
-        <v>11.29</v>
+        <v>11.12</v>
       </c>
       <c r="BB14" t="n">
-        <v>6.57</v>
+        <v>7</v>
       </c>
       <c r="BC14" t="n">
-        <v>4.71</v>
+        <v>4.12</v>
       </c>
       <c r="BD14" t="n">
-        <v>22.71</v>
+        <v>21.75</v>
       </c>
       <c r="BE14" t="n">
-        <v>1.4</v>
+        <v>1.34</v>
       </c>
       <c r="BF14" t="n">
-        <v>2.29</v>
+        <v>2.12</v>
       </c>
       <c r="BG14" t="n">
-        <v>2.71</v>
+        <v>2.6</v>
       </c>
       <c r="BH14" t="n">
-        <v>8.859999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="BI14" t="n">
-        <v>2.71</v>
+        <v>2.6</v>
       </c>
       <c r="BJ14" t="n">
-        <v>0.71</v>
+        <v>0.67</v>
       </c>
       <c r="BK14" t="n">
-        <v>0.71</v>
+        <v>0.67</v>
       </c>
       <c r="BL14" t="n">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="BM14" t="n">
-        <v>0.43</v>
+        <v>0.4</v>
       </c>
       <c r="BN14" t="n">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="BO14" t="n">
-        <v>1.43</v>
+        <v>1.33</v>
       </c>
       <c r="BP14" t="n">
-        <v>4.64</v>
+        <v>5</v>
       </c>
       <c r="BQ14" t="n">
-        <v>4.21</v>
+        <v>4.4</v>
       </c>
       <c r="BR14" t="n">
         <v>100</v>
       </c>
       <c r="BS14" t="n">
-        <v>78.56999999999999</v>
+        <v>73.33</v>
       </c>
       <c r="BT14" t="n">
-        <v>50</v>
+        <v>46.67</v>
       </c>
       <c r="BU14" t="n">
-        <v>35.71</v>
+        <v>33.33</v>
       </c>
       <c r="BV14" t="n">
-        <v>7.14</v>
+        <v>6.67</v>
       </c>
       <c r="BW14" t="n">
         <v>0</v>
       </c>
       <c r="BX14" t="n">
-        <v>64.29000000000001</v>
+        <v>60</v>
       </c>
       <c r="BY14" t="n">
         <v>2.06</v>
@@ -6442,28 +6442,28 @@
         <v>2.17</v>
       </c>
       <c r="CA14" t="n">
-        <v>3.51</v>
+        <v>3.59</v>
       </c>
       <c r="CB14" t="n">
-        <v>3.54</v>
+        <v>3.59</v>
       </c>
       <c r="CC14" t="n">
-        <v>3.77</v>
+        <v>4.05</v>
       </c>
       <c r="CD14" t="n">
-        <v>3.96</v>
+        <v>4.12</v>
       </c>
       <c r="CE14" t="n">
         <v>1.33</v>
       </c>
       <c r="CF14" t="n">
-        <v>2.62</v>
+        <v>2.61</v>
       </c>
       <c r="CG14" t="n">
-        <v>3.06</v>
+        <v>3.1</v>
       </c>
       <c r="CH14" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="CI14" t="n">
         <v>2.09</v>
@@ -6475,40 +6475,40 @@
         <v>1.47</v>
       </c>
       <c r="CL14" t="n">
-        <v>1.87</v>
+        <v>1.89</v>
       </c>
       <c r="CM14" t="n">
-        <v>2.58</v>
+        <v>2.57</v>
       </c>
       <c r="CN14" t="n">
         <v>1.95</v>
       </c>
       <c r="CO14" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="CP14" t="n">
-        <v>1.82</v>
+        <v>1.8</v>
       </c>
       <c r="CQ14" t="n">
-        <v>3.06</v>
+        <v>3.02</v>
       </c>
       <c r="CR14" t="n">
         <v>1.37</v>
       </c>
       <c r="CS14" t="n">
-        <v>2.8</v>
+        <v>2.77</v>
       </c>
       <c r="CT14" t="n">
         <v>3.15</v>
       </c>
       <c r="CU14" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="CV14" t="n">
         <v>2.18</v>
       </c>
       <c r="CW14" t="n">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="CX14" t="n">
         <v>1.54</v>
@@ -6523,55 +6523,55 @@
         <v>1.95</v>
       </c>
       <c r="DB14" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="DC14" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="DD14" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="DE14" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="DF14" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="DG14" t="n">
         <v>1.94</v>
       </c>
-      <c r="DD14" t="n">
-        <v>3.22</v>
-      </c>
-      <c r="DE14" t="n">
-        <v>0.14</v>
-      </c>
-      <c r="DF14" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="DG14" t="n">
-        <v>1.57</v>
-      </c>
       <c r="DH14" t="n">
-        <v>92.93000000000001</v>
+        <v>89.73999999999999</v>
       </c>
       <c r="DI14" t="n">
         <v>0</v>
       </c>
       <c r="DJ14" t="n">
-        <v>2.43</v>
+        <v>2.33</v>
       </c>
       <c r="DK14" t="n">
-        <v>4.21</v>
+        <v>4.66</v>
       </c>
       <c r="DL14" t="n">
-        <v>0.36</v>
+        <v>0.33</v>
       </c>
       <c r="DM14" t="n">
-        <v>48.5</v>
+        <v>48</v>
       </c>
       <c r="DN14" t="n">
-        <v>0.43</v>
+        <v>0.4</v>
       </c>
       <c r="DO14" t="n">
-        <v>2.64</v>
+        <v>2.73</v>
       </c>
       <c r="DP14" t="n">
-        <v>11.42</v>
+        <v>11.27</v>
       </c>
       <c r="DQ14" t="n">
-        <v>12.36</v>
+        <v>11.87</v>
       </c>
       <c r="DR14" t="n">
-        <v>6.92</v>
+        <v>7</v>
       </c>
       <c r="DS14" t="n">
         <v>0.07000000000000001</v>
@@ -6583,28 +6583,28 @@
         <v>0</v>
       </c>
       <c r="DV14" t="n">
-        <v>47.22</v>
+        <v>46.67</v>
       </c>
       <c r="DW14" t="n">
         <v>0.14</v>
       </c>
       <c r="DX14" t="n">
-        <v>10.72</v>
+        <v>10.66</v>
       </c>
       <c r="DY14" t="n">
-        <v>6.22</v>
+        <v>6.47</v>
       </c>
       <c r="DZ14" t="n">
-        <v>4.5</v>
+        <v>4.2</v>
       </c>
       <c r="EA14" t="n">
-        <v>20</v>
+        <v>19.67</v>
       </c>
       <c r="EB14" t="n">
-        <v>1.34</v>
+        <v>1.32</v>
       </c>
       <c r="EC14" t="n">
-        <v>2.22</v>
+        <v>2.13</v>
       </c>
     </row>
     <row r="15">
@@ -7017,94 +7017,94 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C16" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D16" t="n">
         <v>8</v>
       </c>
       <c r="E16" t="n">
-        <v>0.5</v>
+        <v>0.43</v>
       </c>
       <c r="F16" t="n">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="G16" t="n">
-        <v>3.17</v>
+        <v>3.14</v>
       </c>
       <c r="H16" t="n">
-        <v>97.83</v>
+        <v>97.56999999999999</v>
       </c>
       <c r="I16" t="n">
         <v>0</v>
       </c>
       <c r="J16" t="n">
-        <v>1.17</v>
+        <v>1.29</v>
       </c>
       <c r="K16" t="n">
-        <v>6</v>
+        <v>6.14</v>
       </c>
       <c r="L16" t="n">
-        <v>0.67</v>
+        <v>0.71</v>
       </c>
       <c r="M16" t="n">
-        <v>57.5</v>
+        <v>56.43</v>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>0.14</v>
       </c>
       <c r="O16" t="n">
-        <v>2.83</v>
+        <v>3</v>
       </c>
       <c r="P16" t="n">
-        <v>11.17</v>
+        <v>12</v>
       </c>
       <c r="Q16" t="n">
         <v>10</v>
       </c>
       <c r="R16" t="n">
-        <v>5.17</v>
+        <v>5.71</v>
       </c>
       <c r="S16" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="T16" t="n">
-        <v>2.83</v>
+        <v>2.71</v>
       </c>
       <c r="U16" t="n">
-        <v>0.33</v>
+        <v>0.29</v>
       </c>
       <c r="V16" t="n">
-        <v>0.33</v>
+        <v>0.29</v>
       </c>
       <c r="W16" t="n">
         <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>53.67</v>
+        <v>53.71</v>
       </c>
       <c r="Y16" t="n">
         <v>0</v>
       </c>
       <c r="Z16" t="n">
-        <v>18.17</v>
+        <v>18</v>
       </c>
       <c r="AA16" t="n">
-        <v>11.5</v>
+        <v>11.43</v>
       </c>
       <c r="AB16" t="n">
-        <v>6.67</v>
+        <v>6.57</v>
       </c>
       <c r="AC16" t="n">
-        <v>20.67</v>
+        <v>19.43</v>
       </c>
       <c r="AD16" t="n">
-        <v>2.03</v>
+        <v>2</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.17</v>
+        <v>1.29</v>
       </c>
       <c r="AF16" t="n">
         <v>0.12</v>
@@ -7188,70 +7188,70 @@
         <v>2.88</v>
       </c>
       <c r="BG16" t="n">
-        <v>2.64</v>
+        <v>2.6</v>
       </c>
       <c r="BH16" t="n">
-        <v>9.93</v>
+        <v>10</v>
       </c>
       <c r="BI16" t="n">
-        <v>2.64</v>
+        <v>2.6</v>
       </c>
       <c r="BJ16" t="n">
-        <v>0.43</v>
+        <v>0.47</v>
       </c>
       <c r="BK16" t="n">
-        <v>0.36</v>
+        <v>0.33</v>
       </c>
       <c r="BL16" t="n">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="BM16" t="n">
-        <v>0.57</v>
+        <v>0.53</v>
       </c>
       <c r="BN16" t="n">
-        <v>1.86</v>
+        <v>1.8</v>
       </c>
       <c r="BO16" t="n">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="BP16" t="n">
-        <v>5.21</v>
+        <v>5.27</v>
       </c>
       <c r="BQ16" t="n">
-        <v>4.71</v>
+        <v>4.73</v>
       </c>
       <c r="BR16" t="n">
-        <v>92.86</v>
+        <v>93.33</v>
       </c>
       <c r="BS16" t="n">
-        <v>78.56999999999999</v>
+        <v>80</v>
       </c>
       <c r="BT16" t="n">
-        <v>42.86</v>
+        <v>40</v>
       </c>
       <c r="BU16" t="n">
-        <v>28.57</v>
+        <v>26.67</v>
       </c>
       <c r="BV16" t="n">
-        <v>21.43</v>
+        <v>20</v>
       </c>
       <c r="BW16" t="n">
         <v>0</v>
       </c>
       <c r="BX16" t="n">
-        <v>42.86</v>
+        <v>40</v>
       </c>
       <c r="BY16" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="BZ16" t="n">
         <v>1.45</v>
       </c>
       <c r="CA16" t="n">
-        <v>4.27</v>
+        <v>4.29</v>
       </c>
       <c r="CB16" t="n">
-        <v>4.39</v>
+        <v>4.42</v>
       </c>
       <c r="CC16" t="n">
         <v>1.82</v>
@@ -7260,55 +7260,55 @@
         <v>1.86</v>
       </c>
       <c r="CE16" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="CF16" t="n">
-        <v>2.47</v>
+        <v>2.46</v>
       </c>
       <c r="CG16" t="n">
-        <v>3.22</v>
+        <v>3.25</v>
       </c>
       <c r="CH16" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="CI16" t="n">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="CJ16" t="n">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="CK16" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="CL16" t="n">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="CM16" t="n">
-        <v>2.49</v>
+        <v>2.5</v>
       </c>
       <c r="CN16" t="n">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="CO16" t="n">
         <v>1.22</v>
       </c>
       <c r="CP16" t="n">
-        <v>1.78</v>
+        <v>1.76</v>
       </c>
       <c r="CQ16" t="n">
-        <v>2.75</v>
+        <v>2.72</v>
       </c>
       <c r="CR16" t="n">
         <v>1.35</v>
       </c>
       <c r="CS16" t="n">
-        <v>2.63</v>
+        <v>2.61</v>
       </c>
       <c r="CT16" t="n">
         <v>3.25</v>
       </c>
       <c r="CU16" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="CV16" t="n">
         <v>2.05</v>
@@ -7320,64 +7320,64 @@
         <v>1.58</v>
       </c>
       <c r="CY16" t="n">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="CZ16" t="n">
         <v>2.36</v>
       </c>
       <c r="DA16" t="n">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="DB16" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="DC16" t="n">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="DD16" t="n">
-        <v>2.89</v>
+        <v>2.88</v>
       </c>
       <c r="DE16" t="n">
-        <v>0.28</v>
+        <v>0.26</v>
       </c>
       <c r="DF16" t="n">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="DG16" t="n">
         <v>3</v>
       </c>
       <c r="DH16" t="n">
-        <v>103.71</v>
+        <v>103.2</v>
       </c>
       <c r="DI16" t="n">
         <v>0</v>
       </c>
       <c r="DJ16" t="n">
-        <v>2.15</v>
+        <v>2.14</v>
       </c>
       <c r="DK16" t="n">
+        <v>5.93</v>
+      </c>
+      <c r="DL16" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="DM16" t="n">
+        <v>51.07</v>
+      </c>
+      <c r="DN16" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="DO16" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="DP16" t="n">
+        <v>13</v>
+      </c>
+      <c r="DQ16" t="n">
+        <v>9.33</v>
+      </c>
+      <c r="DR16" t="n">
         <v>5.86</v>
-      </c>
-      <c r="DL16" t="n">
-        <v>0.64</v>
-      </c>
-      <c r="DM16" t="n">
-        <v>51.15</v>
-      </c>
-      <c r="DN16" t="n">
-        <v>0.64</v>
-      </c>
-      <c r="DO16" t="n">
-        <v>2.86</v>
-      </c>
-      <c r="DP16" t="n">
-        <v>12.72</v>
-      </c>
-      <c r="DQ16" t="n">
-        <v>9.289999999999999</v>
-      </c>
-      <c r="DR16" t="n">
-        <v>5.64</v>
       </c>
       <c r="DS16" t="n">
         <v>0.14</v>
@@ -7389,28 +7389,28 @@
         <v>0</v>
       </c>
       <c r="DV16" t="n">
-        <v>53.22</v>
+        <v>53.27</v>
       </c>
       <c r="DW16" t="n">
         <v>0</v>
       </c>
       <c r="DX16" t="n">
-        <v>15.93</v>
+        <v>16</v>
       </c>
       <c r="DY16" t="n">
-        <v>9.85</v>
+        <v>9.93</v>
       </c>
       <c r="DZ16" t="n">
-        <v>6.07</v>
+        <v>6.06</v>
       </c>
       <c r="EA16" t="n">
-        <v>19.57</v>
+        <v>19.07</v>
       </c>
       <c r="EB16" t="n">
         <v>1.8</v>
       </c>
       <c r="EC16" t="n">
-        <v>2.15</v>
+        <v>2.14</v>
       </c>
     </row>
     <row r="17">

--- a/data/teams/leagues/Averages_Belgium_Pro_League_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Belgium_Pro_League_2025-2026.xlsx
@@ -5480,16 +5480,16 @@
         <v>13.25</v>
       </c>
       <c r="AA12" t="n">
-        <v>8</v>
+        <v>7.88</v>
       </c>
       <c r="AB12" t="n">
-        <v>5.25</v>
+        <v>5.38</v>
       </c>
       <c r="AC12" t="n">
         <v>21</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="AE12" t="n">
         <v>2.25</v>
@@ -5786,16 +5786,16 @@
         <v>11.33</v>
       </c>
       <c r="DY12" t="n">
-        <v>7.27</v>
+        <v>7.2</v>
       </c>
       <c r="DZ12" t="n">
-        <v>4.06</v>
+        <v>4.13</v>
       </c>
       <c r="EA12" t="n">
         <v>20.47</v>
       </c>
       <c r="EB12" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="EC12" t="n">
         <v>2.27</v>

--- a/data/teams/leagues/Averages_Belgium_Pro_League_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Belgium_Pro_League_2025-2026.xlsx
@@ -3394,94 +3394,94 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C7" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D7" t="n">
         <v>8</v>
       </c>
       <c r="E7" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="F7" t="n">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="G7" t="n">
-        <v>2.14</v>
+        <v>2.38</v>
       </c>
       <c r="H7" t="n">
-        <v>84</v>
+        <v>88.5</v>
       </c>
       <c r="I7" t="n">
-        <v>0.43</v>
+        <v>0.38</v>
       </c>
       <c r="J7" t="n">
-        <v>2.43</v>
+        <v>2.25</v>
       </c>
       <c r="K7" t="n">
-        <v>4.29</v>
+        <v>4.25</v>
       </c>
       <c r="L7" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="M7" t="n">
-        <v>47.71</v>
+        <v>49.12</v>
       </c>
       <c r="N7" t="n">
-        <v>0.86</v>
+        <v>0.75</v>
       </c>
       <c r="O7" t="n">
-        <v>2.14</v>
+        <v>1.88</v>
       </c>
       <c r="P7" t="n">
-        <v>10.43</v>
+        <v>10.5</v>
       </c>
       <c r="Q7" t="n">
-        <v>11.71</v>
+        <v>11.5</v>
       </c>
       <c r="R7" t="n">
-        <v>11.14</v>
+        <v>10.5</v>
       </c>
       <c r="S7" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="T7" t="n">
-        <v>1.29</v>
+        <v>1.12</v>
       </c>
       <c r="U7" t="n">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="V7" t="n">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>48.43</v>
+        <v>49.38</v>
       </c>
       <c r="Y7" t="n">
         <v>0</v>
       </c>
       <c r="Z7" t="n">
-        <v>10.29</v>
+        <v>10.12</v>
       </c>
       <c r="AA7" t="n">
-        <v>6.43</v>
+        <v>6.62</v>
       </c>
       <c r="AB7" t="n">
-        <v>3.86</v>
+        <v>3.5</v>
       </c>
       <c r="AC7" t="n">
-        <v>20.43</v>
+        <v>21.62</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.27</v>
+        <v>1.24</v>
       </c>
       <c r="AE7" t="n">
-        <v>2.43</v>
+        <v>2.25</v>
       </c>
       <c r="AF7" t="n">
         <v>0.12</v>
@@ -3565,70 +3565,70 @@
         <v>2.38</v>
       </c>
       <c r="BG7" t="n">
-        <v>2.47</v>
+        <v>2.38</v>
       </c>
       <c r="BH7" t="n">
-        <v>11.87</v>
+        <v>11.62</v>
       </c>
       <c r="BI7" t="n">
-        <v>2.47</v>
+        <v>2.38</v>
       </c>
       <c r="BJ7" t="n">
-        <v>0.47</v>
+        <v>0.44</v>
       </c>
       <c r="BK7" t="n">
-        <v>0.47</v>
+        <v>0.44</v>
       </c>
       <c r="BL7" t="n">
-        <v>0.67</v>
+        <v>0.62</v>
       </c>
       <c r="BM7" t="n">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="BN7" t="n">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="BO7" t="n">
-        <v>0.93</v>
+        <v>0.88</v>
       </c>
       <c r="BP7" t="n">
-        <v>5.73</v>
+        <v>5.44</v>
       </c>
       <c r="BQ7" t="n">
-        <v>6.13</v>
+        <v>6.19</v>
       </c>
       <c r="BR7" t="n">
-        <v>93.33</v>
+        <v>93.75</v>
       </c>
       <c r="BS7" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="BT7" t="n">
-        <v>40</v>
+        <v>37.5</v>
       </c>
       <c r="BU7" t="n">
-        <v>26.67</v>
+        <v>25</v>
       </c>
       <c r="BV7" t="n">
-        <v>6.67</v>
+        <v>6.25</v>
       </c>
       <c r="BW7" t="n">
         <v>0</v>
       </c>
       <c r="BX7" t="n">
-        <v>73.33</v>
+        <v>68.75</v>
       </c>
       <c r="BY7" t="n">
-        <v>2.95</v>
+        <v>2.88</v>
       </c>
       <c r="BZ7" t="n">
-        <v>3.17</v>
+        <v>3.09</v>
       </c>
       <c r="CA7" t="n">
-        <v>3.7</v>
+        <v>3.67</v>
       </c>
       <c r="CB7" t="n">
-        <v>3.84</v>
+        <v>3.81</v>
       </c>
       <c r="CC7" t="n">
         <v>3.47</v>
@@ -3640,10 +3640,10 @@
         <v>1.3</v>
       </c>
       <c r="CF7" t="n">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="CG7" t="n">
-        <v>3.28</v>
+        <v>3.26</v>
       </c>
       <c r="CH7" t="n">
         <v>1.53</v>
@@ -3652,142 +3652,142 @@
         <v>2.27</v>
       </c>
       <c r="CJ7" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="CK7" t="n">
         <v>1.39</v>
       </c>
       <c r="CL7" t="n">
-        <v>1.74</v>
+        <v>1.76</v>
       </c>
       <c r="CM7" t="n">
-        <v>2.8</v>
+        <v>2.79</v>
       </c>
       <c r="CN7" t="n">
-        <v>2.13</v>
+        <v>2.12</v>
       </c>
       <c r="CO7" t="n">
         <v>1.2</v>
       </c>
       <c r="CP7" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="CQ7" t="n">
-        <v>2.66</v>
+        <v>2.68</v>
       </c>
       <c r="CR7" t="n">
         <v>1.36</v>
       </c>
       <c r="CS7" t="n">
-        <v>2.53</v>
+        <v>2.54</v>
       </c>
       <c r="CT7" t="n">
-        <v>3.22</v>
+        <v>3.21</v>
       </c>
       <c r="CU7" t="n">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="CV7" t="n">
-        <v>2.41</v>
+        <v>2.4</v>
       </c>
       <c r="CW7" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="CX7" t="n">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="CY7" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="CZ7" t="n">
-        <v>2.46</v>
+        <v>2.52</v>
       </c>
       <c r="DA7" t="n">
-        <v>2.15</v>
+        <v>2.13</v>
       </c>
       <c r="DB7" t="n">
         <v>1.22</v>
       </c>
       <c r="DC7" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="DD7" t="n">
-        <v>2.75</v>
+        <v>2.77</v>
       </c>
       <c r="DE7" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="DF7" t="n">
-        <v>1.6</v>
+        <v>1.56</v>
       </c>
       <c r="DG7" t="n">
-        <v>2.53</v>
+        <v>2.63</v>
       </c>
       <c r="DH7" t="n">
-        <v>81.8</v>
+        <v>84.19</v>
       </c>
       <c r="DI7" t="n">
-        <v>0.26</v>
+        <v>0.25</v>
       </c>
       <c r="DJ7" t="n">
-        <v>2.4</v>
+        <v>2.32</v>
       </c>
       <c r="DK7" t="n">
-        <v>4.73</v>
+        <v>4.69</v>
       </c>
       <c r="DL7" t="n">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="DM7" t="n">
-        <v>44</v>
+        <v>44.94</v>
       </c>
       <c r="DN7" t="n">
-        <v>0.8</v>
+        <v>0.75</v>
       </c>
       <c r="DO7" t="n">
-        <v>2.2</v>
+        <v>2.06</v>
       </c>
       <c r="DP7" t="n">
-        <v>9.73</v>
+        <v>9.81</v>
       </c>
       <c r="DQ7" t="n">
-        <v>10.86</v>
+        <v>10.81</v>
       </c>
       <c r="DR7" t="n">
-        <v>10</v>
+        <v>9.75</v>
       </c>
       <c r="DS7" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="DT7" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="DU7" t="n">
         <v>0</v>
       </c>
       <c r="DV7" t="n">
-        <v>47.73</v>
+        <v>48.25</v>
       </c>
       <c r="DW7" t="n">
         <v>0</v>
       </c>
       <c r="DX7" t="n">
-        <v>10.47</v>
+        <v>10.37</v>
       </c>
       <c r="DY7" t="n">
-        <v>6.33</v>
+        <v>6.44</v>
       </c>
       <c r="DZ7" t="n">
-        <v>4.14</v>
+        <v>3.94</v>
       </c>
       <c r="EA7" t="n">
-        <v>20.4</v>
+        <v>21</v>
       </c>
       <c r="EB7" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="EC7" t="n">
-        <v>2.4</v>
+        <v>2.32</v>
       </c>
     </row>
     <row r="8">
@@ -6614,13 +6614,13 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C15" t="n">
         <v>8</v>
       </c>
       <c r="D15" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E15" t="n">
         <v>0.25</v>
@@ -6704,130 +6704,130 @@
         <v>2.62</v>
       </c>
       <c r="AF15" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.14</v>
+        <v>1.38</v>
       </c>
       <c r="AI15" t="n">
-        <v>82.56999999999999</v>
+        <v>84.75</v>
       </c>
       <c r="AJ15" t="n">
         <v>0</v>
       </c>
       <c r="AK15" t="n">
-        <v>2.43</v>
+        <v>2.25</v>
       </c>
       <c r="AL15" t="n">
-        <v>2.29</v>
+        <v>2.5</v>
       </c>
       <c r="AM15" t="n">
-        <v>0.14</v>
+        <v>0.25</v>
       </c>
       <c r="AN15" t="n">
-        <v>31.43</v>
+        <v>31</v>
       </c>
       <c r="AO15" t="n">
-        <v>0.86</v>
+        <v>0.75</v>
       </c>
       <c r="AP15" t="n">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="AQ15" t="n">
-        <v>10.86</v>
+        <v>10.75</v>
       </c>
       <c r="AR15" t="n">
-        <v>11.86</v>
+        <v>11.75</v>
       </c>
       <c r="AS15" t="n">
-        <v>9.710000000000001</v>
+        <v>9.25</v>
       </c>
       <c r="AT15" t="n">
-        <v>1.43</v>
+        <v>1.25</v>
       </c>
       <c r="AU15" t="n">
-        <v>0.57</v>
+        <v>0.62</v>
       </c>
       <c r="AV15" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="AW15" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="AX15" t="n">
         <v>0</v>
       </c>
       <c r="AY15" t="n">
-        <v>45.43</v>
+        <v>45.25</v>
       </c>
       <c r="AZ15" t="n">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="BA15" t="n">
-        <v>7.29</v>
+        <v>7.12</v>
       </c>
       <c r="BB15" t="n">
-        <v>5.14</v>
+        <v>5</v>
       </c>
       <c r="BC15" t="n">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="BD15" t="n">
-        <v>17.86</v>
+        <v>17</v>
       </c>
       <c r="BE15" t="n">
-        <v>0.85</v>
+        <v>0.83</v>
       </c>
       <c r="BF15" t="n">
-        <v>2.14</v>
+        <v>2</v>
       </c>
       <c r="BG15" t="n">
-        <v>2.13</v>
+        <v>2.06</v>
       </c>
       <c r="BH15" t="n">
-        <v>9.529999999999999</v>
+        <v>9.44</v>
       </c>
       <c r="BI15" t="n">
-        <v>2.13</v>
+        <v>2.06</v>
       </c>
       <c r="BJ15" t="n">
-        <v>0.53</v>
+        <v>0.5</v>
       </c>
       <c r="BK15" t="n">
-        <v>0.6</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="BL15" t="n">
-        <v>0.73</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="BM15" t="n">
-        <v>0.27</v>
+        <v>0.31</v>
       </c>
       <c r="BN15" t="n">
         <v>1</v>
       </c>
       <c r="BO15" t="n">
-        <v>1.13</v>
+        <v>1.06</v>
       </c>
       <c r="BP15" t="n">
-        <v>4.53</v>
+        <v>4.31</v>
       </c>
       <c r="BQ15" t="n">
-        <v>5</v>
+        <v>5.12</v>
       </c>
       <c r="BR15" t="n">
-        <v>93.33</v>
+        <v>93.75</v>
       </c>
       <c r="BS15" t="n">
-        <v>66.67</v>
+        <v>62.5</v>
       </c>
       <c r="BT15" t="n">
-        <v>40</v>
+        <v>37.5</v>
       </c>
       <c r="BU15" t="n">
-        <v>13.33</v>
+        <v>12.5</v>
       </c>
       <c r="BV15" t="n">
         <v>0</v>
@@ -6836,7 +6836,7 @@
         <v>0</v>
       </c>
       <c r="BX15" t="n">
-        <v>33.33</v>
+        <v>31.25</v>
       </c>
       <c r="BY15" t="n">
         <v>2.9</v>
@@ -6845,43 +6845,43 @@
         <v>3.11</v>
       </c>
       <c r="CA15" t="n">
-        <v>3.53</v>
+        <v>3.51</v>
       </c>
       <c r="CB15" t="n">
-        <v>3.59</v>
+        <v>3.57</v>
       </c>
       <c r="CC15" t="n">
-        <v>4.34</v>
+        <v>4.18</v>
       </c>
       <c r="CD15" t="n">
-        <v>4.99</v>
+        <v>4.74</v>
       </c>
       <c r="CE15" t="n">
         <v>1.37</v>
       </c>
       <c r="CF15" t="n">
-        <v>2.78</v>
+        <v>2.77</v>
       </c>
       <c r="CG15" t="n">
-        <v>2.96</v>
+        <v>2.95</v>
       </c>
       <c r="CH15" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="CI15" t="n">
-        <v>1.94</v>
+        <v>1.97</v>
       </c>
       <c r="CJ15" t="n">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="CK15" t="n">
         <v>1.47</v>
       </c>
       <c r="CL15" t="n">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="CM15" t="n">
-        <v>2.6</v>
+        <v>2.59</v>
       </c>
       <c r="CN15" t="n">
         <v>1.96</v>
@@ -6890,124 +6890,124 @@
         <v>1.3</v>
       </c>
       <c r="CP15" t="n">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="CQ15" t="n">
-        <v>3.41</v>
+        <v>3.39</v>
       </c>
       <c r="CR15" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="CS15" t="n">
-        <v>2.88</v>
+        <v>2.87</v>
       </c>
       <c r="CT15" t="n">
-        <v>3.05</v>
+        <v>3.06</v>
       </c>
       <c r="CU15" t="n">
         <v>1.45</v>
       </c>
       <c r="CV15" t="n">
-        <v>2.09</v>
+        <v>2.1</v>
       </c>
       <c r="CW15" t="n">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="CX15" t="n">
         <v>1.56</v>
       </c>
       <c r="CY15" t="n">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="CZ15" t="n">
-        <v>2.39</v>
+        <v>2.42</v>
       </c>
       <c r="DA15" t="n">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="DB15" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="DC15" t="n">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="DD15" t="n">
-        <v>3.41</v>
+        <v>3.4</v>
       </c>
       <c r="DE15" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="DF15" t="n">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="DG15" t="n">
-        <v>1.66</v>
+        <v>1.75</v>
       </c>
       <c r="DH15" t="n">
-        <v>84.13</v>
+        <v>85.12</v>
       </c>
       <c r="DI15" t="n">
         <v>0</v>
       </c>
       <c r="DJ15" t="n">
-        <v>2.94</v>
+        <v>2.82</v>
       </c>
       <c r="DK15" t="n">
         <v>3.94</v>
       </c>
       <c r="DL15" t="n">
-        <v>0.33</v>
+        <v>0.38</v>
       </c>
       <c r="DM15" t="n">
-        <v>44.67</v>
+        <v>43.62</v>
       </c>
       <c r="DN15" t="n">
-        <v>1.07</v>
+        <v>1</v>
       </c>
       <c r="DO15" t="n">
-        <v>2.27</v>
+        <v>2.18</v>
       </c>
       <c r="DP15" t="n">
-        <v>11.14</v>
+        <v>11.07</v>
       </c>
       <c r="DQ15" t="n">
-        <v>12.14</v>
+        <v>12.07</v>
       </c>
       <c r="DR15" t="n">
-        <v>9</v>
+        <v>8.82</v>
       </c>
       <c r="DS15" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="DT15" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="DU15" t="n">
         <v>0</v>
       </c>
       <c r="DV15" t="n">
-        <v>45.26</v>
+        <v>45.18</v>
       </c>
       <c r="DW15" t="n">
-        <v>0.34</v>
+        <v>0.32</v>
       </c>
       <c r="DX15" t="n">
-        <v>10.07</v>
+        <v>9.81</v>
       </c>
       <c r="DY15" t="n">
-        <v>6.46</v>
+        <v>6.31</v>
       </c>
       <c r="DZ15" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="EA15" t="n">
-        <v>18.14</v>
+        <v>17.69</v>
       </c>
       <c r="EB15" t="n">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="EC15" t="n">
-        <v>2.4</v>
+        <v>2.31</v>
       </c>
     </row>
     <row r="16">

--- a/data/teams/leagues/Averages_Belgium_Pro_League_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Belgium_Pro_League_2025-2026.xlsx
@@ -1379,13 +1379,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C2" t="n">
         <v>8</v>
       </c>
       <c r="D2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
@@ -1475,46 +1475,46 @@
         <v>1</v>
       </c>
       <c r="AH2" t="n">
-        <v>2.29</v>
+        <v>2.5</v>
       </c>
       <c r="AI2" t="n">
-        <v>109.14</v>
+        <v>108.88</v>
       </c>
       <c r="AJ2" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="AK2" t="n">
-        <v>2.71</v>
+        <v>2.62</v>
       </c>
       <c r="AL2" t="n">
-        <v>4.29</v>
+        <v>4.62</v>
       </c>
       <c r="AM2" t="n">
-        <v>0.71</v>
+        <v>0.62</v>
       </c>
       <c r="AN2" t="n">
-        <v>52.57</v>
+        <v>53.38</v>
       </c>
       <c r="AO2" t="n">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="AP2" t="n">
-        <v>2</v>
+        <v>2.12</v>
       </c>
       <c r="AQ2" t="n">
-        <v>12.43</v>
+        <v>12.5</v>
       </c>
       <c r="AR2" t="n">
-        <v>11.14</v>
+        <v>11.38</v>
       </c>
       <c r="AS2" t="n">
-        <v>7.57</v>
+        <v>7.12</v>
       </c>
       <c r="AT2" t="n">
         <v>1</v>
       </c>
       <c r="AU2" t="n">
-        <v>0.71</v>
+        <v>0.75</v>
       </c>
       <c r="AV2" t="n">
         <v>0</v>
@@ -1526,82 +1526,82 @@
         <v>0</v>
       </c>
       <c r="AY2" t="n">
-        <v>49.29</v>
+        <v>49.88</v>
       </c>
       <c r="AZ2" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="BA2" t="n">
-        <v>12.71</v>
+        <v>12.75</v>
       </c>
       <c r="BB2" t="n">
         <v>9</v>
       </c>
       <c r="BC2" t="n">
-        <v>3.71</v>
+        <v>3.75</v>
       </c>
       <c r="BD2" t="n">
-        <v>24.14</v>
+        <v>23.12</v>
       </c>
       <c r="BE2" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="BF2" t="n">
-        <v>2.43</v>
+        <v>2.38</v>
       </c>
       <c r="BG2" t="n">
-        <v>2.73</v>
+        <v>2.69</v>
       </c>
       <c r="BH2" t="n">
-        <v>9.4</v>
+        <v>9.619999999999999</v>
       </c>
       <c r="BI2" t="n">
-        <v>2.73</v>
+        <v>2.69</v>
       </c>
       <c r="BJ2" t="n">
-        <v>0.73</v>
+        <v>0.75</v>
       </c>
       <c r="BK2" t="n">
-        <v>0.8</v>
+        <v>0.75</v>
       </c>
       <c r="BL2" t="n">
-        <v>0.6</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="BM2" t="n">
-        <v>0.6</v>
+        <v>0.62</v>
       </c>
       <c r="BN2" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="BO2" t="n">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="BP2" t="n">
-        <v>4.13</v>
+        <v>4.19</v>
       </c>
       <c r="BQ2" t="n">
-        <v>5.27</v>
+        <v>5.44</v>
       </c>
       <c r="BR2" t="n">
-        <v>86.67</v>
+        <v>87.5</v>
       </c>
       <c r="BS2" t="n">
-        <v>86.67</v>
+        <v>87.5</v>
       </c>
       <c r="BT2" t="n">
-        <v>46.67</v>
+        <v>43.75</v>
       </c>
       <c r="BU2" t="n">
-        <v>26.67</v>
+        <v>25</v>
       </c>
       <c r="BV2" t="n">
-        <v>20</v>
+        <v>18.75</v>
       </c>
       <c r="BW2" t="n">
-        <v>6.67</v>
+        <v>6.25</v>
       </c>
       <c r="BX2" t="n">
-        <v>60</v>
+        <v>62.5</v>
       </c>
       <c r="BY2" t="n">
         <v>2.36</v>
@@ -1610,43 +1610,43 @@
         <v>2.42</v>
       </c>
       <c r="CA2" t="n">
-        <v>3.54</v>
+        <v>3.52</v>
       </c>
       <c r="CB2" t="n">
-        <v>3.7</v>
+        <v>3.71</v>
       </c>
       <c r="CC2" t="n">
-        <v>3.65</v>
+        <v>3.51</v>
       </c>
       <c r="CD2" t="n">
-        <v>3.9</v>
+        <v>3.69</v>
       </c>
       <c r="CE2" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="CF2" t="n">
-        <v>2.52</v>
+        <v>2.51</v>
       </c>
       <c r="CG2" t="n">
-        <v>3.16</v>
+        <v>3.17</v>
       </c>
       <c r="CH2" t="n">
         <v>1.48</v>
       </c>
       <c r="CI2" t="n">
-        <v>2.18</v>
+        <v>2.19</v>
       </c>
       <c r="CJ2" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="CK2" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="CL2" t="n">
         <v>1.75</v>
       </c>
       <c r="CM2" t="n">
-        <v>2.58</v>
+        <v>2.6</v>
       </c>
       <c r="CN2" t="n">
         <v>2.01</v>
@@ -1655,10 +1655,10 @@
         <v>1.22</v>
       </c>
       <c r="CP2" t="n">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="CQ2" t="n">
-        <v>2.92</v>
+        <v>2.89</v>
       </c>
       <c r="CR2" t="n">
         <v>1.36</v>
@@ -1673,31 +1673,31 @@
         <v>1.52</v>
       </c>
       <c r="CV2" t="n">
-        <v>2.31</v>
+        <v>2.33</v>
       </c>
       <c r="CW2" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="CX2" t="n">
         <v>1.5</v>
       </c>
       <c r="CY2" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="CZ2" t="n">
         <v>2.55</v>
       </c>
       <c r="DA2" t="n">
-        <v>2.07</v>
+        <v>2.08</v>
       </c>
       <c r="DB2" t="n">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="DC2" t="n">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="DD2" t="n">
-        <v>2.86</v>
+        <v>2.84</v>
       </c>
       <c r="DE2" t="n">
         <v>0</v>
@@ -1706,73 +1706,73 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="DG2" t="n">
-        <v>2.47</v>
+        <v>2.56</v>
       </c>
       <c r="DH2" t="n">
-        <v>108.4</v>
+        <v>108.32</v>
       </c>
       <c r="DI2" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="DJ2" t="n">
         <v>2</v>
       </c>
       <c r="DK2" t="n">
-        <v>4.34</v>
+        <v>4.5</v>
       </c>
       <c r="DL2" t="n">
-        <v>0.46</v>
+        <v>0.44</v>
       </c>
       <c r="DM2" t="n">
-        <v>50</v>
+        <v>50.56</v>
       </c>
       <c r="DN2" t="n">
         <v>1</v>
       </c>
       <c r="DO2" t="n">
-        <v>1.87</v>
+        <v>1.94</v>
       </c>
       <c r="DP2" t="n">
-        <v>10.4</v>
+        <v>10.56</v>
       </c>
       <c r="DQ2" t="n">
-        <v>12.27</v>
+        <v>12.32</v>
       </c>
       <c r="DR2" t="n">
-        <v>7.4</v>
+        <v>7.18</v>
       </c>
       <c r="DS2" t="n">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="DT2" t="n">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="DU2" t="n">
         <v>0</v>
       </c>
       <c r="DV2" t="n">
-        <v>50.53</v>
+        <v>50.75</v>
       </c>
       <c r="DW2" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="DX2" t="n">
-        <v>14</v>
+        <v>13.93</v>
       </c>
       <c r="DY2" t="n">
-        <v>9.74</v>
+        <v>9.69</v>
       </c>
       <c r="DZ2" t="n">
-        <v>4.26</v>
+        <v>4.25</v>
       </c>
       <c r="EA2" t="n">
-        <v>23.86</v>
+        <v>23.37</v>
       </c>
       <c r="EB2" t="n">
         <v>1.55</v>
       </c>
       <c r="EC2" t="n">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
     </row>
     <row r="3">
@@ -1782,10 +1782,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C3" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D3" t="n">
         <v>8</v>
@@ -1794,49 +1794,49 @@
         <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>1.43</v>
+        <v>1.25</v>
       </c>
       <c r="G3" t="n">
-        <v>3.71</v>
+        <v>4</v>
       </c>
       <c r="H3" t="n">
-        <v>113.14</v>
+        <v>116</v>
       </c>
       <c r="I3" t="n">
         <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>1.71</v>
+        <v>1.5</v>
       </c>
       <c r="K3" t="n">
-        <v>6.71</v>
+        <v>7</v>
       </c>
       <c r="L3" t="n">
         <v>1</v>
       </c>
       <c r="M3" t="n">
-        <v>64.29000000000001</v>
+        <v>67.88</v>
       </c>
       <c r="N3" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="O3" t="n">
         <v>3</v>
       </c>
       <c r="P3" t="n">
-        <v>9.43</v>
+        <v>9.619999999999999</v>
       </c>
       <c r="Q3" t="n">
-        <v>11.71</v>
+        <v>12.12</v>
       </c>
       <c r="R3" t="n">
-        <v>7.29</v>
+        <v>7.25</v>
       </c>
       <c r="S3" t="n">
         <v>1</v>
       </c>
       <c r="T3" t="n">
-        <v>2.14</v>
+        <v>1.88</v>
       </c>
       <c r="U3" t="n">
         <v>0</v>
@@ -1848,28 +1848,28 @@
         <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>63.29</v>
+        <v>64.75</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="Z3" t="n">
-        <v>16.43</v>
+        <v>17.75</v>
       </c>
       <c r="AA3" t="n">
-        <v>11.43</v>
+        <v>12.62</v>
       </c>
       <c r="AB3" t="n">
-        <v>5</v>
+        <v>5.12</v>
       </c>
       <c r="AC3" t="n">
-        <v>22.14</v>
+        <v>22.25</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.85</v>
+        <v>1.97</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.43</v>
+        <v>1.25</v>
       </c>
       <c r="AF3" t="n">
         <v>0.12</v>
@@ -1953,70 +1953,70 @@
         <v>1.62</v>
       </c>
       <c r="BG3" t="n">
-        <v>2.33</v>
+        <v>2.25</v>
       </c>
       <c r="BH3" t="n">
-        <v>11.2</v>
+        <v>11.31</v>
       </c>
       <c r="BI3" t="n">
-        <v>2.33</v>
+        <v>2.25</v>
       </c>
       <c r="BJ3" t="n">
-        <v>0.53</v>
+        <v>0.5</v>
       </c>
       <c r="BK3" t="n">
-        <v>0.33</v>
+        <v>0.31</v>
       </c>
       <c r="BL3" t="n">
-        <v>0.87</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="BM3" t="n">
-        <v>0.6</v>
+        <v>0.62</v>
       </c>
       <c r="BN3" t="n">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="BO3" t="n">
-        <v>0.87</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="BP3" t="n">
-        <v>5.27</v>
+        <v>5.25</v>
       </c>
       <c r="BQ3" t="n">
-        <v>5.93</v>
+        <v>6.06</v>
       </c>
       <c r="BR3" t="n">
         <v>100</v>
       </c>
       <c r="BS3" t="n">
-        <v>53.33</v>
+        <v>50</v>
       </c>
       <c r="BT3" t="n">
-        <v>33.33</v>
+        <v>31.25</v>
       </c>
       <c r="BU3" t="n">
-        <v>6.67</v>
+        <v>6.25</v>
       </c>
       <c r="BV3" t="n">
-        <v>6.67</v>
+        <v>6.25</v>
       </c>
       <c r="BW3" t="n">
-        <v>6.67</v>
+        <v>6.25</v>
       </c>
       <c r="BX3" t="n">
-        <v>40</v>
+        <v>37.5</v>
       </c>
       <c r="BY3" t="n">
-        <v>1.55</v>
+        <v>1.52</v>
       </c>
       <c r="BZ3" t="n">
-        <v>1.56</v>
+        <v>1.53</v>
       </c>
       <c r="CA3" t="n">
-        <v>4.43</v>
+        <v>4.48</v>
       </c>
       <c r="CB3" t="n">
-        <v>4.69</v>
+        <v>4.75</v>
       </c>
       <c r="CC3" t="n">
         <v>1.64</v>
@@ -2037,28 +2037,28 @@
         <v>1.6</v>
       </c>
       <c r="CI3" t="n">
-        <v>2.13</v>
+        <v>2.12</v>
       </c>
       <c r="CJ3" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="CK3" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="CL3" t="n">
-        <v>1.89</v>
+        <v>1.93</v>
       </c>
       <c r="CM3" t="n">
-        <v>2.55</v>
+        <v>2.53</v>
       </c>
       <c r="CN3" t="n">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="CO3" t="n">
         <v>1.16</v>
       </c>
       <c r="CP3" t="n">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="CQ3" t="n">
         <v>2.42</v>
@@ -2076,10 +2076,10 @@
         <v>1.65</v>
       </c>
       <c r="CV3" t="n">
-        <v>2.31</v>
+        <v>2.28</v>
       </c>
       <c r="CW3" t="n">
-        <v>1.66</v>
+        <v>1.68</v>
       </c>
       <c r="CX3" t="n">
         <v>1.53</v>
@@ -2094,55 +2094,55 @@
         <v>2.02</v>
       </c>
       <c r="DB3" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="DC3" t="n">
         <v>1.59</v>
       </c>
       <c r="DD3" t="n">
-        <v>2.45</v>
+        <v>2.46</v>
       </c>
       <c r="DE3" t="n">
         <v>0.06</v>
       </c>
       <c r="DF3" t="n">
-        <v>1.26</v>
+        <v>1.18</v>
       </c>
       <c r="DG3" t="n">
-        <v>3.93</v>
+        <v>4.06</v>
       </c>
       <c r="DH3" t="n">
-        <v>109.93</v>
+        <v>111.56</v>
       </c>
       <c r="DI3" t="n">
         <v>0</v>
       </c>
       <c r="DJ3" t="n">
-        <v>1.66</v>
+        <v>1.56</v>
       </c>
       <c r="DK3" t="n">
-        <v>6.73</v>
+        <v>6.88</v>
       </c>
       <c r="DL3" t="n">
-        <v>0.53</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="DM3" t="n">
-        <v>60.87</v>
+        <v>62.88</v>
       </c>
       <c r="DN3" t="n">
-        <v>0.33</v>
+        <v>0.31</v>
       </c>
       <c r="DO3" t="n">
-        <v>2.8</v>
+        <v>2.81</v>
       </c>
       <c r="DP3" t="n">
-        <v>9.470000000000001</v>
+        <v>9.56</v>
       </c>
       <c r="DQ3" t="n">
-        <v>12.13</v>
+        <v>12.31</v>
       </c>
       <c r="DR3" t="n">
-        <v>7.4</v>
+        <v>7.38</v>
       </c>
       <c r="DS3" t="n">
         <v>0</v>
@@ -2154,28 +2154,28 @@
         <v>0</v>
       </c>
       <c r="DV3" t="n">
-        <v>61.94</v>
+        <v>62.75</v>
       </c>
       <c r="DW3" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="DX3" t="n">
-        <v>15.67</v>
+        <v>16.38</v>
       </c>
       <c r="DY3" t="n">
-        <v>10.8</v>
+        <v>11.43</v>
       </c>
       <c r="DZ3" t="n">
-        <v>4.87</v>
+        <v>4.94</v>
       </c>
       <c r="EA3" t="n">
-        <v>20.2</v>
+        <v>20.38</v>
       </c>
       <c r="EB3" t="n">
-        <v>1.77</v>
+        <v>1.84</v>
       </c>
       <c r="EC3" t="n">
-        <v>1.53</v>
+        <v>1.44</v>
       </c>
     </row>
     <row r="4">
@@ -2185,10 +2185,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C4" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D4" t="n">
         <v>8</v>
@@ -2197,82 +2197,82 @@
         <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>0.71</v>
+        <v>1</v>
       </c>
       <c r="G4" t="n">
-        <v>1.14</v>
+        <v>1</v>
       </c>
       <c r="H4" t="n">
-        <v>94.86</v>
+        <v>93.25</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.14</v>
+        <v>-0.12</v>
       </c>
       <c r="J4" t="n">
-        <v>1</v>
+        <v>1.38</v>
       </c>
       <c r="K4" t="n">
-        <v>3.43</v>
+        <v>3.25</v>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>0.12</v>
       </c>
       <c r="M4" t="n">
-        <v>43.29</v>
+        <v>43.25</v>
       </c>
       <c r="N4" t="n">
-        <v>0.29</v>
+        <v>0.38</v>
       </c>
       <c r="O4" t="n">
-        <v>1.14</v>
+        <v>1.25</v>
       </c>
       <c r="P4" t="n">
-        <v>8.859999999999999</v>
+        <v>9.75</v>
       </c>
       <c r="Q4" t="n">
-        <v>12.14</v>
+        <v>12.25</v>
       </c>
       <c r="R4" t="n">
-        <v>9.710000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="S4" t="n">
-        <v>1.29</v>
+        <v>1.38</v>
       </c>
       <c r="T4" t="n">
-        <v>0.43</v>
+        <v>0.62</v>
       </c>
       <c r="U4" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="V4" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="W4" t="n">
         <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>51.29</v>
+        <v>50.5</v>
       </c>
       <c r="Y4" t="n">
         <v>0</v>
       </c>
       <c r="Z4" t="n">
-        <v>10.14</v>
+        <v>9.880000000000001</v>
       </c>
       <c r="AA4" t="n">
-        <v>6.86</v>
+        <v>6.5</v>
       </c>
       <c r="AB4" t="n">
-        <v>3.29</v>
+        <v>3.38</v>
       </c>
       <c r="AC4" t="n">
-        <v>23.71</v>
+        <v>23.88</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="AE4" t="n">
-        <v>1</v>
+        <v>1.38</v>
       </c>
       <c r="AF4" t="n">
         <v>0.25</v>
@@ -2356,49 +2356,49 @@
         <v>1.88</v>
       </c>
       <c r="BG4" t="n">
-        <v>2.27</v>
+        <v>2.38</v>
       </c>
       <c r="BH4" t="n">
-        <v>8.6</v>
+        <v>8.44</v>
       </c>
       <c r="BI4" t="n">
-        <v>2.27</v>
+        <v>2.38</v>
       </c>
       <c r="BJ4" t="n">
-        <v>0.47</v>
+        <v>0.5</v>
       </c>
       <c r="BK4" t="n">
-        <v>0.2</v>
+        <v>0.19</v>
       </c>
       <c r="BL4" t="n">
-        <v>0.73</v>
+        <v>0.75</v>
       </c>
       <c r="BM4" t="n">
-        <v>0.87</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="BN4" t="n">
-        <v>1.6</v>
+        <v>1.69</v>
       </c>
       <c r="BO4" t="n">
-        <v>0.67</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="BP4" t="n">
-        <v>3.53</v>
+        <v>3.5</v>
       </c>
       <c r="BQ4" t="n">
-        <v>4.2</v>
+        <v>4.12</v>
       </c>
       <c r="BR4" t="n">
-        <v>86.67</v>
+        <v>87.5</v>
       </c>
       <c r="BS4" t="n">
-        <v>73.33</v>
+        <v>75</v>
       </c>
       <c r="BT4" t="n">
-        <v>46.67</v>
+        <v>50</v>
       </c>
       <c r="BU4" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="BV4" t="n">
         <v>0</v>
@@ -2407,19 +2407,19 @@
         <v>0</v>
       </c>
       <c r="BX4" t="n">
-        <v>53.33</v>
+        <v>56.25</v>
       </c>
       <c r="BY4" t="n">
-        <v>3.4</v>
+        <v>3.33</v>
       </c>
       <c r="BZ4" t="n">
-        <v>3.49</v>
+        <v>3.41</v>
       </c>
       <c r="CA4" t="n">
         <v>3.72</v>
       </c>
       <c r="CB4" t="n">
-        <v>3.94</v>
+        <v>3.93</v>
       </c>
       <c r="CC4" t="n">
         <v>4.87</v>
@@ -2431,154 +2431,154 @@
         <v>1.34</v>
       </c>
       <c r="CF4" t="n">
-        <v>2.55</v>
+        <v>2.54</v>
       </c>
       <c r="CG4" t="n">
-        <v>3.1</v>
+        <v>3.13</v>
       </c>
       <c r="CH4" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="CI4" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="CJ4" t="n">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="CK4" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="CL4" t="n">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="CM4" t="n">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="CN4" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="CO4" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="CP4" t="n">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="CQ4" t="n">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="CR4" t="n">
         <v>1.38</v>
       </c>
       <c r="CS4" t="n">
-        <v>2.74</v>
+        <v>2.71</v>
       </c>
       <c r="CT4" t="n">
         <v>3.13</v>
       </c>
       <c r="CU4" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="CV4" t="n">
-        <v>2.14</v>
+        <v>2.17</v>
       </c>
       <c r="CW4" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="CX4" t="n">
         <v>1.57</v>
       </c>
       <c r="CY4" t="n">
-        <v>1.95</v>
+        <v>1.93</v>
       </c>
       <c r="CZ4" t="n">
         <v>2.39</v>
       </c>
       <c r="DA4" t="n">
-        <v>1.88</v>
+        <v>1.9</v>
       </c>
       <c r="DB4" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="DC4" t="n">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="DD4" t="n">
-        <v>3.07</v>
+        <v>3.03</v>
       </c>
       <c r="DE4" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="DF4" t="n">
-        <v>1.2</v>
+        <v>1.31</v>
       </c>
       <c r="DG4" t="n">
-        <v>1.27</v>
+        <v>1.19</v>
       </c>
       <c r="DH4" t="n">
-        <v>92.47</v>
+        <v>91.81999999999999</v>
       </c>
       <c r="DI4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DJ4" t="n">
-        <v>1.8</v>
+        <v>1.94</v>
       </c>
       <c r="DK4" t="n">
-        <v>3.26</v>
+        <v>3.18</v>
       </c>
       <c r="DL4" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="DM4" t="n">
+        <v>40.06</v>
+      </c>
+      <c r="DN4" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="DO4" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="DP4" t="n">
+        <v>11</v>
+      </c>
+      <c r="DQ4" t="n">
+        <v>12.18</v>
+      </c>
+      <c r="DR4" t="n">
+        <v>10.31</v>
+      </c>
+      <c r="DS4" t="n">
         <v>0.06</v>
       </c>
-      <c r="DM4" t="n">
-        <v>39.87</v>
-      </c>
-      <c r="DN4" t="n">
-        <v>0.47</v>
-      </c>
-      <c r="DO4" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="DP4" t="n">
-        <v>10.67</v>
-      </c>
-      <c r="DQ4" t="n">
-        <v>12.13</v>
-      </c>
-      <c r="DR4" t="n">
-        <v>9.93</v>
-      </c>
-      <c r="DS4" t="n">
-        <v>0.07000000000000001</v>
-      </c>
       <c r="DT4" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="DU4" t="n">
         <v>0</v>
       </c>
       <c r="DV4" t="n">
-        <v>46.6</v>
+        <v>46.5</v>
       </c>
       <c r="DW4" t="n">
-        <v>0.2</v>
+        <v>0.19</v>
       </c>
       <c r="DX4" t="n">
-        <v>10.27</v>
+        <v>10.13</v>
       </c>
       <c r="DY4" t="n">
-        <v>6.67</v>
+        <v>6.5</v>
       </c>
       <c r="DZ4" t="n">
-        <v>3.6</v>
+        <v>3.63</v>
       </c>
       <c r="EA4" t="n">
-        <v>20.4</v>
+        <v>20.69</v>
       </c>
       <c r="EB4" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="EC4" t="n">
-        <v>1.47</v>
+        <v>1.63</v>
       </c>
     </row>
     <row r="5">
@@ -2588,61 +2588,61 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C5" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D5" t="n">
         <v>8</v>
       </c>
       <c r="E5" t="n">
-        <v>0.43</v>
+        <v>0.38</v>
       </c>
       <c r="F5" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="G5" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="H5" t="n">
+        <v>109.25</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="K5" t="n">
+        <v>4.62</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="M5" t="n">
+        <v>49</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="O5" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="P5" t="n">
+        <v>10.38</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>9.75</v>
+      </c>
+      <c r="R5" t="n">
+        <v>8.380000000000001</v>
+      </c>
+      <c r="S5" t="n">
         <v>1</v>
       </c>
-      <c r="G5" t="n">
-        <v>2.71</v>
-      </c>
-      <c r="H5" t="n">
-        <v>111.71</v>
-      </c>
-      <c r="I5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J5" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="K5" t="n">
-        <v>4.57</v>
-      </c>
-      <c r="L5" t="n">
-        <v>0.57</v>
-      </c>
-      <c r="M5" t="n">
-        <v>49.86</v>
-      </c>
-      <c r="N5" t="n">
-        <v>0.43</v>
-      </c>
-      <c r="O5" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="P5" t="n">
-        <v>10.57</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>9.710000000000001</v>
-      </c>
-      <c r="R5" t="n">
-        <v>8.140000000000001</v>
-      </c>
-      <c r="S5" t="n">
-        <v>0.86</v>
-      </c>
       <c r="T5" t="n">
-        <v>2</v>
+        <v>1.88</v>
       </c>
       <c r="U5" t="n">
         <v>0</v>
@@ -2654,28 +2654,28 @@
         <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>55.86</v>
+        <v>55</v>
       </c>
       <c r="Y5" t="n">
         <v>0</v>
       </c>
       <c r="Z5" t="n">
-        <v>14.71</v>
+        <v>15.25</v>
       </c>
       <c r="AA5" t="n">
-        <v>10.43</v>
+        <v>11</v>
       </c>
       <c r="AB5" t="n">
-        <v>4.29</v>
+        <v>4.25</v>
       </c>
       <c r="AC5" t="n">
-        <v>17.57</v>
+        <v>18.5</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.43</v>
+        <v>1.5</v>
       </c>
       <c r="AF5" t="n">
         <v>0</v>
@@ -2762,67 +2762,67 @@
         <v>3</v>
       </c>
       <c r="BH5" t="n">
-        <v>10</v>
+        <v>10.06</v>
       </c>
       <c r="BI5" t="n">
         <v>3</v>
       </c>
       <c r="BJ5" t="n">
-        <v>0.93</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="BK5" t="n">
-        <v>0.4</v>
+        <v>0.38</v>
       </c>
       <c r="BL5" t="n">
-        <v>1.07</v>
+        <v>1</v>
       </c>
       <c r="BM5" t="n">
-        <v>0.6</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="BN5" t="n">
-        <v>1.67</v>
+        <v>1.69</v>
       </c>
       <c r="BO5" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="BP5" t="n">
         <v>4</v>
       </c>
       <c r="BQ5" t="n">
-        <v>6</v>
+        <v>6.06</v>
       </c>
       <c r="BR5" t="n">
-        <v>93.33</v>
+        <v>93.75</v>
       </c>
       <c r="BS5" t="n">
-        <v>80</v>
+        <v>81.25</v>
       </c>
       <c r="BT5" t="n">
-        <v>60</v>
+        <v>62.5</v>
       </c>
       <c r="BU5" t="n">
-        <v>40</v>
+        <v>37.5</v>
       </c>
       <c r="BV5" t="n">
-        <v>20</v>
+        <v>18.75</v>
       </c>
       <c r="BW5" t="n">
-        <v>6.67</v>
+        <v>6.25</v>
       </c>
       <c r="BX5" t="n">
-        <v>60</v>
+        <v>62.5</v>
       </c>
       <c r="BY5" t="n">
-        <v>2.88</v>
+        <v>2.8</v>
       </c>
       <c r="BZ5" t="n">
-        <v>3.03</v>
+        <v>2.94</v>
       </c>
       <c r="CA5" t="n">
-        <v>3.59</v>
+        <v>3.58</v>
       </c>
       <c r="CB5" t="n">
-        <v>3.72</v>
+        <v>3.7</v>
       </c>
       <c r="CC5" t="n">
         <v>3.04</v>
@@ -2834,16 +2834,16 @@
         <v>1.31</v>
       </c>
       <c r="CF5" t="n">
-        <v>2.45</v>
+        <v>2.46</v>
       </c>
       <c r="CG5" t="n">
-        <v>3.23</v>
+        <v>3.21</v>
       </c>
       <c r="CH5" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="CI5" t="n">
-        <v>2.27</v>
+        <v>2.26</v>
       </c>
       <c r="CJ5" t="n">
         <v>1.62</v>
@@ -2855,10 +2855,10 @@
         <v>1.85</v>
       </c>
       <c r="CM5" t="n">
-        <v>2.59</v>
+        <v>2.58</v>
       </c>
       <c r="CN5" t="n">
-        <v>2.01</v>
+        <v>2</v>
       </c>
       <c r="CO5" t="n">
         <v>1.21</v>
@@ -2882,22 +2882,22 @@
         <v>1.54</v>
       </c>
       <c r="CV5" t="n">
-        <v>2.36</v>
+        <v>2.37</v>
       </c>
       <c r="CW5" t="n">
         <v>1.64</v>
       </c>
       <c r="CX5" t="n">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="CY5" t="n">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="CZ5" t="n">
-        <v>2.46</v>
+        <v>2.47</v>
       </c>
       <c r="DA5" t="n">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="DB5" t="n">
         <v>1.23</v>
@@ -2909,16 +2909,16 @@
         <v>2.81</v>
       </c>
       <c r="DE5" t="n">
-        <v>0.2</v>
+        <v>0.19</v>
       </c>
       <c r="DF5" t="n">
-        <v>1.13</v>
+        <v>1.18</v>
       </c>
       <c r="DG5" t="n">
-        <v>3.07</v>
+        <v>3.06</v>
       </c>
       <c r="DH5" t="n">
-        <v>103.6</v>
+        <v>102.88</v>
       </c>
       <c r="DI5" t="n">
         <v>0</v>
@@ -2927,28 +2927,28 @@
         <v>2</v>
       </c>
       <c r="DK5" t="n">
-        <v>5.13</v>
+        <v>5.12</v>
       </c>
       <c r="DL5" t="n">
-        <v>0.74</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="DM5" t="n">
-        <v>46.94</v>
+        <v>46.69</v>
       </c>
       <c r="DN5" t="n">
-        <v>0.73</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="DO5" t="n">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="DP5" t="n">
-        <v>11</v>
+        <v>10.88</v>
       </c>
       <c r="DQ5" t="n">
-        <v>10.33</v>
+        <v>10.32</v>
       </c>
       <c r="DR5" t="n">
-        <v>9.199999999999999</v>
+        <v>9.25</v>
       </c>
       <c r="DS5" t="n">
         <v>0.06</v>
@@ -2960,28 +2960,28 @@
         <v>0</v>
       </c>
       <c r="DV5" t="n">
-        <v>54.13</v>
+        <v>53.81</v>
       </c>
       <c r="DW5" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="DX5" t="n">
-        <v>13.6</v>
+        <v>13.93</v>
       </c>
       <c r="DY5" t="n">
-        <v>8.869999999999999</v>
+        <v>9.25</v>
       </c>
       <c r="DZ5" t="n">
-        <v>4.73</v>
+        <v>4.69</v>
       </c>
       <c r="EA5" t="n">
-        <v>17.8</v>
+        <v>18.25</v>
       </c>
       <c r="EB5" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="EC5" t="n">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
     </row>
     <row r="6">
@@ -2991,10 +2991,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C6" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D6" t="n">
         <v>8</v>
@@ -3003,49 +3003,49 @@
         <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>0.57</v>
+        <v>0.5</v>
       </c>
       <c r="G6" t="n">
-        <v>3.71</v>
+        <v>3.75</v>
       </c>
       <c r="H6" t="n">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>1.29</v>
+        <v>1.12</v>
       </c>
       <c r="K6" t="n">
-        <v>6.29</v>
+        <v>6.75</v>
       </c>
       <c r="L6" t="n">
-        <v>0.57</v>
+        <v>0.75</v>
       </c>
       <c r="M6" t="n">
-        <v>67.14</v>
+        <v>66.12</v>
       </c>
       <c r="N6" t="n">
-        <v>0.57</v>
+        <v>0.5</v>
       </c>
       <c r="O6" t="n">
-        <v>2.57</v>
+        <v>3</v>
       </c>
       <c r="P6" t="n">
-        <v>10.14</v>
+        <v>10.5</v>
       </c>
       <c r="Q6" t="n">
-        <v>14.29</v>
+        <v>14.5</v>
       </c>
       <c r="R6" t="n">
-        <v>5.43</v>
+        <v>5</v>
       </c>
       <c r="S6" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="T6" t="n">
-        <v>1.14</v>
+        <v>1.25</v>
       </c>
       <c r="U6" t="n">
         <v>0</v>
@@ -3057,28 +3057,28 @@
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>66.56999999999999</v>
+        <v>66.5</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="Z6" t="n">
-        <v>17</v>
+        <v>17.75</v>
       </c>
       <c r="AA6" t="n">
-        <v>11.57</v>
+        <v>12</v>
       </c>
       <c r="AB6" t="n">
-        <v>5.43</v>
+        <v>5.75</v>
       </c>
       <c r="AC6" t="n">
-        <v>22.43</v>
+        <v>20.62</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.94</v>
+        <v>2.01</v>
       </c>
       <c r="AE6" t="n">
-        <v>1</v>
+        <v>0.88</v>
       </c>
       <c r="AF6" t="n">
         <v>0.12</v>
@@ -3162,70 +3162,70 @@
         <v>2</v>
       </c>
       <c r="BG6" t="n">
-        <v>2.53</v>
+        <v>2.56</v>
       </c>
       <c r="BH6" t="n">
-        <v>9.6</v>
+        <v>9.75</v>
       </c>
       <c r="BI6" t="n">
-        <v>2.53</v>
+        <v>2.56</v>
       </c>
       <c r="BJ6" t="n">
-        <v>0.6</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="BK6" t="n">
-        <v>0.93</v>
+        <v>0.88</v>
       </c>
       <c r="BL6" t="n">
-        <v>0.6</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="BM6" t="n">
-        <v>0.4</v>
+        <v>0.44</v>
       </c>
       <c r="BN6" t="n">
-        <v>1</v>
+        <v>1.12</v>
       </c>
       <c r="BO6" t="n">
-        <v>1.53</v>
+        <v>1.44</v>
       </c>
       <c r="BP6" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="BQ6" t="n">
-        <v>5.2</v>
+        <v>5.25</v>
       </c>
       <c r="BR6" t="n">
         <v>100</v>
       </c>
       <c r="BS6" t="n">
-        <v>80</v>
+        <v>81.25</v>
       </c>
       <c r="BT6" t="n">
-        <v>53.33</v>
+        <v>56.25</v>
       </c>
       <c r="BU6" t="n">
-        <v>13.33</v>
+        <v>12.5</v>
       </c>
       <c r="BV6" t="n">
-        <v>6.67</v>
+        <v>6.25</v>
       </c>
       <c r="BW6" t="n">
         <v>0</v>
       </c>
       <c r="BX6" t="n">
-        <v>80</v>
+        <v>81.25</v>
       </c>
       <c r="BY6" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="BZ6" t="n">
-        <v>1.77</v>
+        <v>1.74</v>
       </c>
       <c r="CA6" t="n">
-        <v>3.91</v>
+        <v>3.92</v>
       </c>
       <c r="CB6" t="n">
-        <v>4.08</v>
+        <v>4.09</v>
       </c>
       <c r="CC6" t="n">
         <v>2.52</v>
@@ -3234,124 +3234,124 @@
         <v>2.54</v>
       </c>
       <c r="CE6" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="CF6" t="n">
-        <v>2.36</v>
+        <v>2.39</v>
       </c>
       <c r="CG6" t="n">
-        <v>3.35</v>
+        <v>3.33</v>
       </c>
       <c r="CH6" t="n">
         <v>1.54</v>
       </c>
       <c r="CI6" t="n">
-        <v>2.27</v>
+        <v>2.25</v>
       </c>
       <c r="CJ6" t="n">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
       <c r="CK6" t="n">
         <v>1.52</v>
       </c>
       <c r="CL6" t="n">
-        <v>2.03</v>
+        <v>2.02</v>
       </c>
       <c r="CM6" t="n">
-        <v>2.4</v>
+        <v>2.41</v>
       </c>
       <c r="CN6" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="CO6" t="n">
         <v>1.18</v>
       </c>
       <c r="CP6" t="n">
-        <v>1.66</v>
+        <v>1.68</v>
       </c>
       <c r="CQ6" t="n">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="CR6" t="n">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="CS6" t="n">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="CT6" t="n">
-        <v>3.04</v>
+        <v>3.1</v>
       </c>
       <c r="CU6" t="n">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="CV6" t="n">
-        <v>2.33</v>
+        <v>2.31</v>
       </c>
       <c r="CW6" t="n">
-        <v>1.66</v>
+        <v>1.68</v>
       </c>
       <c r="CX6" t="n">
         <v>1.6</v>
       </c>
       <c r="CY6" t="n">
-        <v>1.96</v>
+        <v>1.94</v>
       </c>
       <c r="CZ6" t="n">
         <v>2.31</v>
       </c>
       <c r="DA6" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="DB6" t="n">
         <v>1.22</v>
       </c>
       <c r="DC6" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="DD6" t="n">
-        <v>2.7</v>
+        <v>2.73</v>
       </c>
       <c r="DE6" t="n">
         <v>0.06</v>
       </c>
       <c r="DF6" t="n">
-        <v>1.07</v>
+        <v>1</v>
       </c>
       <c r="DG6" t="n">
-        <v>3.13</v>
+        <v>3.18</v>
       </c>
       <c r="DH6" t="n">
-        <v>118.4</v>
+        <v>118.75</v>
       </c>
       <c r="DI6" t="n">
         <v>0.06</v>
       </c>
       <c r="DJ6" t="n">
-        <v>1.67</v>
+        <v>1.56</v>
       </c>
       <c r="DK6" t="n">
-        <v>5.67</v>
+        <v>5.94</v>
       </c>
       <c r="DL6" t="n">
-        <v>0.74</v>
+        <v>0.82</v>
       </c>
       <c r="DM6" t="n">
-        <v>57.33</v>
+        <v>57.44</v>
       </c>
       <c r="DN6" t="n">
-        <v>0.53</v>
+        <v>0.5</v>
       </c>
       <c r="DO6" t="n">
-        <v>2.53</v>
+        <v>2.75</v>
       </c>
       <c r="DP6" t="n">
-        <v>9.73</v>
+        <v>9.94</v>
       </c>
       <c r="DQ6" t="n">
-        <v>13.13</v>
+        <v>13.31</v>
       </c>
       <c r="DR6" t="n">
-        <v>6.2</v>
+        <v>5.94</v>
       </c>
       <c r="DS6" t="n">
         <v>0</v>
@@ -3363,28 +3363,28 @@
         <v>0</v>
       </c>
       <c r="DV6" t="n">
-        <v>63.54</v>
+        <v>63.69</v>
       </c>
       <c r="DW6" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="DX6" t="n">
-        <v>16.07</v>
+        <v>16.5</v>
       </c>
       <c r="DY6" t="n">
-        <v>10.67</v>
+        <v>10.94</v>
       </c>
       <c r="DZ6" t="n">
-        <v>5.4</v>
+        <v>5.56</v>
       </c>
       <c r="EA6" t="n">
-        <v>20.54</v>
+        <v>19.75</v>
       </c>
       <c r="EB6" t="n">
-        <v>1.81</v>
+        <v>1.85</v>
       </c>
       <c r="EC6" t="n">
-        <v>1.53</v>
+        <v>1.44</v>
       </c>
     </row>
     <row r="7">
@@ -3797,13 +3797,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C8" t="n">
         <v>8</v>
       </c>
       <c r="D8" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E8" t="n">
         <v>0.12</v>
@@ -3887,139 +3887,139 @@
         <v>1.25</v>
       </c>
       <c r="AF8" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.71</v>
+        <v>1.62</v>
       </c>
       <c r="AH8" t="n">
-        <v>2</v>
+        <v>2.12</v>
       </c>
       <c r="AI8" t="n">
-        <v>81.14</v>
+        <v>83.38</v>
       </c>
       <c r="AJ8" t="n">
         <v>0</v>
       </c>
       <c r="AK8" t="n">
-        <v>1.71</v>
+        <v>1.62</v>
       </c>
       <c r="AL8" t="n">
-        <v>4.29</v>
+        <v>4.25</v>
       </c>
       <c r="AM8" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="AN8" t="n">
-        <v>36</v>
+        <v>39.25</v>
       </c>
       <c r="AO8" t="n">
         <v>0</v>
       </c>
       <c r="AP8" t="n">
-        <v>2.29</v>
+        <v>2.12</v>
       </c>
       <c r="AQ8" t="n">
-        <v>13.71</v>
+        <v>13.62</v>
       </c>
       <c r="AR8" t="n">
-        <v>11</v>
+        <v>11.38</v>
       </c>
       <c r="AS8" t="n">
-        <v>8.43</v>
+        <v>8.5</v>
       </c>
       <c r="AT8" t="n">
-        <v>2.57</v>
+        <v>2.5</v>
       </c>
       <c r="AU8" t="n">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="AV8" t="n">
-        <v>0.14</v>
+        <v>0.25</v>
       </c>
       <c r="AW8" t="n">
-        <v>0.14</v>
+        <v>0.25</v>
       </c>
       <c r="AX8" t="n">
         <v>0</v>
       </c>
       <c r="AY8" t="n">
-        <v>48.43</v>
+        <v>49.25</v>
       </c>
       <c r="AZ8" t="n">
         <v>0</v>
       </c>
       <c r="BA8" t="n">
-        <v>13.71</v>
+        <v>14.38</v>
       </c>
       <c r="BB8" t="n">
-        <v>9.289999999999999</v>
+        <v>9.880000000000001</v>
       </c>
       <c r="BC8" t="n">
-        <v>4.43</v>
+        <v>4.5</v>
       </c>
       <c r="BD8" t="n">
-        <v>22.71</v>
+        <v>22.62</v>
       </c>
       <c r="BE8" t="n">
-        <v>1.37</v>
+        <v>1.45</v>
       </c>
       <c r="BF8" t="n">
-        <v>1.71</v>
+        <v>1.62</v>
       </c>
       <c r="BG8" t="n">
-        <v>2.87</v>
+        <v>2.94</v>
       </c>
       <c r="BH8" t="n">
-        <v>10.2</v>
+        <v>9.94</v>
       </c>
       <c r="BI8" t="n">
-        <v>2.87</v>
+        <v>2.94</v>
       </c>
       <c r="BJ8" t="n">
-        <v>0.73</v>
+        <v>0.75</v>
       </c>
       <c r="BK8" t="n">
-        <v>0.53</v>
+        <v>0.5</v>
       </c>
       <c r="BL8" t="n">
         <v>1</v>
       </c>
       <c r="BM8" t="n">
-        <v>0.6</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="BN8" t="n">
-        <v>1.6</v>
+        <v>1.69</v>
       </c>
       <c r="BO8" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="BP8" t="n">
-        <v>4.73</v>
+        <v>4.62</v>
       </c>
       <c r="BQ8" t="n">
-        <v>5.47</v>
+        <v>5.31</v>
       </c>
       <c r="BR8" t="n">
-        <v>86.67</v>
+        <v>87.5</v>
       </c>
       <c r="BS8" t="n">
-        <v>73.33</v>
+        <v>75</v>
       </c>
       <c r="BT8" t="n">
-        <v>33.33</v>
+        <v>37.5</v>
       </c>
       <c r="BU8" t="n">
-        <v>26.67</v>
+        <v>31.25</v>
       </c>
       <c r="BV8" t="n">
-        <v>20</v>
+        <v>18.75</v>
       </c>
       <c r="BW8" t="n">
-        <v>13.33</v>
+        <v>12.5</v>
       </c>
       <c r="BX8" t="n">
-        <v>33.33</v>
+        <v>37.5</v>
       </c>
       <c r="BY8" t="n">
         <v>2.17</v>
@@ -4028,22 +4028,22 @@
         <v>2.28</v>
       </c>
       <c r="CA8" t="n">
-        <v>3.9</v>
+        <v>3.89</v>
       </c>
       <c r="CB8" t="n">
-        <v>4.01</v>
+        <v>3.99</v>
       </c>
       <c r="CC8" t="n">
-        <v>4.78</v>
+        <v>4.48</v>
       </c>
       <c r="CD8" t="n">
-        <v>4.67</v>
+        <v>4.38</v>
       </c>
       <c r="CE8" t="n">
         <v>1.26</v>
       </c>
       <c r="CF8" t="n">
-        <v>2.24</v>
+        <v>2.25</v>
       </c>
       <c r="CG8" t="n">
         <v>3.57</v>
@@ -4058,19 +4058,19 @@
         <v>1.56</v>
       </c>
       <c r="CK8" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="CL8" t="n">
         <v>1.67</v>
       </c>
       <c r="CM8" t="n">
-        <v>2.9</v>
+        <v>2.89</v>
       </c>
       <c r="CN8" t="n">
-        <v>2.25</v>
+        <v>2.24</v>
       </c>
       <c r="CO8" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="CP8" t="n">
         <v>1.58</v>
@@ -4082,7 +4082,7 @@
         <v>1.34</v>
       </c>
       <c r="CS8" t="n">
-        <v>2.3</v>
+        <v>2.31</v>
       </c>
       <c r="CT8" t="n">
         <v>3.3</v>
@@ -4098,11 +4098,11 @@
       </c>
       <c r="CX8" t="inlineStr"/>
       <c r="CY8" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="CZ8" t="inlineStr"/>
       <c r="DA8" t="n">
-        <v>2.31</v>
+        <v>2.29</v>
       </c>
       <c r="DB8" t="n">
         <v>1.18</v>
@@ -4114,79 +4114,79 @@
         <v>2.45</v>
       </c>
       <c r="DE8" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="DF8" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="DG8" t="n">
-        <v>2.74</v>
+        <v>2.75</v>
       </c>
       <c r="DH8" t="n">
-        <v>90.2</v>
+        <v>90.75</v>
       </c>
       <c r="DI8" t="n">
         <v>0</v>
       </c>
       <c r="DJ8" t="n">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="DK8" t="n">
-        <v>5.53</v>
+        <v>5.44</v>
       </c>
       <c r="DL8" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="DM8" t="n">
-        <v>48.06</v>
+        <v>48.94</v>
       </c>
       <c r="DN8" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="DO8" t="n">
-        <v>2.8</v>
+        <v>2.68</v>
       </c>
       <c r="DP8" t="n">
-        <v>12</v>
+        <v>12.06</v>
       </c>
       <c r="DQ8" t="n">
-        <v>12</v>
+        <v>12.13</v>
       </c>
       <c r="DR8" t="n">
-        <v>8</v>
+        <v>8.06</v>
       </c>
       <c r="DS8" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.12</v>
       </c>
       <c r="DT8" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.12</v>
       </c>
       <c r="DU8" t="n">
         <v>0</v>
       </c>
       <c r="DV8" t="n">
-        <v>49.8</v>
+        <v>50.12</v>
       </c>
       <c r="DW8" t="n">
         <v>0</v>
       </c>
       <c r="DX8" t="n">
-        <v>15.8</v>
+        <v>16</v>
       </c>
       <c r="DY8" t="n">
-        <v>11.14</v>
+        <v>11.32</v>
       </c>
       <c r="DZ8" t="n">
-        <v>4.67</v>
+        <v>4.69</v>
       </c>
       <c r="EA8" t="n">
-        <v>20.93</v>
+        <v>21</v>
       </c>
       <c r="EB8" t="n">
-        <v>1.64</v>
+        <v>1.66</v>
       </c>
       <c r="EC8" t="n">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
     </row>
     <row r="9">
@@ -4196,13 +4196,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C9" t="n">
         <v>8</v>
       </c>
       <c r="D9" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E9" t="n">
         <v>0.25</v>
@@ -4289,49 +4289,49 @@
         <v>0</v>
       </c>
       <c r="AG9" t="n">
-        <v>2.14</v>
+        <v>2</v>
       </c>
       <c r="AH9" t="n">
-        <v>2.71</v>
+        <v>2.62</v>
       </c>
       <c r="AI9" t="n">
-        <v>81.14</v>
+        <v>79</v>
       </c>
       <c r="AJ9" t="n">
         <v>0</v>
       </c>
       <c r="AK9" t="n">
-        <v>3.29</v>
+        <v>3.25</v>
       </c>
       <c r="AL9" t="n">
-        <v>4.71</v>
+        <v>4.38</v>
       </c>
       <c r="AM9" t="n">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="AN9" t="n">
-        <v>44.86</v>
+        <v>43.88</v>
       </c>
       <c r="AO9" t="n">
-        <v>1.14</v>
+        <v>1.25</v>
       </c>
       <c r="AP9" t="n">
-        <v>2</v>
+        <v>1.75</v>
       </c>
       <c r="AQ9" t="n">
-        <v>17.57</v>
+        <v>17.38</v>
       </c>
       <c r="AR9" t="n">
-        <v>10.29</v>
+        <v>10.62</v>
       </c>
       <c r="AS9" t="n">
-        <v>8.289999999999999</v>
+        <v>8.619999999999999</v>
       </c>
       <c r="AT9" t="n">
         <v>2</v>
       </c>
       <c r="AU9" t="n">
-        <v>0.71</v>
+        <v>0.75</v>
       </c>
       <c r="AV9" t="n">
         <v>0</v>
@@ -4343,82 +4343,82 @@
         <v>0</v>
       </c>
       <c r="AY9" t="n">
-        <v>45.29</v>
+        <v>43.88</v>
       </c>
       <c r="AZ9" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="BA9" t="n">
         <v>11</v>
       </c>
       <c r="BB9" t="n">
-        <v>7.71</v>
+        <v>7.38</v>
       </c>
       <c r="BC9" t="n">
-        <v>3.29</v>
+        <v>3.62</v>
       </c>
       <c r="BD9" t="n">
-        <v>20</v>
+        <v>19.88</v>
       </c>
       <c r="BE9" t="n">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="BF9" t="n">
-        <v>3.14</v>
+        <v>3.12</v>
       </c>
       <c r="BG9" t="n">
-        <v>2.67</v>
+        <v>2.69</v>
       </c>
       <c r="BH9" t="n">
-        <v>9.67</v>
+        <v>9.81</v>
       </c>
       <c r="BI9" t="n">
-        <v>2.67</v>
+        <v>2.69</v>
       </c>
       <c r="BJ9" t="n">
-        <v>0.87</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="BK9" t="n">
-        <v>0.4</v>
+        <v>0.38</v>
       </c>
       <c r="BL9" t="n">
-        <v>0.8</v>
+        <v>0.88</v>
       </c>
       <c r="BM9" t="n">
-        <v>0.6</v>
+        <v>0.62</v>
       </c>
       <c r="BN9" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="BO9" t="n">
-        <v>1.27</v>
+        <v>1.19</v>
       </c>
       <c r="BP9" t="n">
-        <v>4.93</v>
+        <v>5</v>
       </c>
       <c r="BQ9" t="n">
-        <v>4.73</v>
+        <v>4.81</v>
       </c>
       <c r="BR9" t="n">
         <v>100</v>
       </c>
       <c r="BS9" t="n">
-        <v>80</v>
+        <v>81.25</v>
       </c>
       <c r="BT9" t="n">
-        <v>53.33</v>
+        <v>56.25</v>
       </c>
       <c r="BU9" t="n">
-        <v>26.67</v>
+        <v>25</v>
       </c>
       <c r="BV9" t="n">
-        <v>6.67</v>
+        <v>6.25</v>
       </c>
       <c r="BW9" t="n">
         <v>0</v>
       </c>
       <c r="BX9" t="n">
-        <v>53.33</v>
+        <v>56.25</v>
       </c>
       <c r="BY9" t="n">
         <v>3.08</v>
@@ -4427,22 +4427,22 @@
         <v>3.15</v>
       </c>
       <c r="CA9" t="n">
-        <v>3.55</v>
+        <v>3.58</v>
       </c>
       <c r="CB9" t="n">
-        <v>3.58</v>
+        <v>3.62</v>
       </c>
       <c r="CC9" t="n">
-        <v>4.22</v>
+        <v>4.37</v>
       </c>
       <c r="CD9" t="n">
-        <v>4.46</v>
+        <v>4.63</v>
       </c>
       <c r="CE9" t="n">
         <v>1.35</v>
       </c>
       <c r="CF9" t="n">
-        <v>2.66</v>
+        <v>2.67</v>
       </c>
       <c r="CG9" t="n">
         <v>3.03</v>
@@ -4454,13 +4454,13 @@
         <v>2.01</v>
       </c>
       <c r="CJ9" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="CK9" t="n">
         <v>1.43</v>
       </c>
       <c r="CL9" t="n">
-        <v>1.76</v>
+        <v>1.78</v>
       </c>
       <c r="CM9" t="n">
         <v>2.59</v>
@@ -4469,22 +4469,22 @@
         <v>2</v>
       </c>
       <c r="CO9" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="CP9" t="n">
         <v>1.87</v>
       </c>
       <c r="CQ9" t="n">
-        <v>3.15</v>
+        <v>3.14</v>
       </c>
       <c r="CR9" t="n">
         <v>1.38</v>
       </c>
       <c r="CS9" t="n">
-        <v>2.83</v>
+        <v>2.82</v>
       </c>
       <c r="CT9" t="n">
-        <v>3.08</v>
+        <v>3.09</v>
       </c>
       <c r="CU9" t="n">
         <v>1.45</v>
@@ -4511,52 +4511,52 @@
         <v>1.29</v>
       </c>
       <c r="DC9" t="n">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="DD9" t="n">
-        <v>3.26</v>
+        <v>3.25</v>
       </c>
       <c r="DE9" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="DF9" t="n">
-        <v>2.33</v>
+        <v>2.25</v>
       </c>
       <c r="DG9" t="n">
-        <v>2.4</v>
+        <v>2.37</v>
       </c>
       <c r="DH9" t="n">
-        <v>79.06999999999999</v>
+        <v>78.12</v>
       </c>
       <c r="DI9" t="n">
         <v>0</v>
       </c>
       <c r="DJ9" t="n">
-        <v>3.14</v>
+        <v>3.12</v>
       </c>
       <c r="DK9" t="n">
-        <v>4.33</v>
+        <v>4.19</v>
       </c>
       <c r="DL9" t="n">
-        <v>0.47</v>
+        <v>0.44</v>
       </c>
       <c r="DM9" t="n">
-        <v>40.67</v>
+        <v>40.44</v>
       </c>
       <c r="DN9" t="n">
-        <v>0.8</v>
+        <v>0.88</v>
       </c>
       <c r="DO9" t="n">
-        <v>1.94</v>
+        <v>1.82</v>
       </c>
       <c r="DP9" t="n">
-        <v>16.67</v>
+        <v>16.63</v>
       </c>
       <c r="DQ9" t="n">
-        <v>11.14</v>
+        <v>11.25</v>
       </c>
       <c r="DR9" t="n">
-        <v>8.34</v>
+        <v>8.5</v>
       </c>
       <c r="DS9" t="n">
         <v>0</v>
@@ -4568,28 +4568,28 @@
         <v>0</v>
       </c>
       <c r="DV9" t="n">
-        <v>44.74</v>
+        <v>44.06</v>
       </c>
       <c r="DW9" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="DX9" t="n">
-        <v>12.4</v>
+        <v>12.31</v>
       </c>
       <c r="DY9" t="n">
-        <v>8.4</v>
+        <v>8.19</v>
       </c>
       <c r="DZ9" t="n">
-        <v>4</v>
+        <v>4.12</v>
       </c>
       <c r="EA9" t="n">
-        <v>19.2</v>
+        <v>19.19</v>
       </c>
       <c r="EB9" t="n">
         <v>1.36</v>
       </c>
       <c r="EC9" t="n">
-        <v>3.07</v>
+        <v>3.06</v>
       </c>
     </row>
     <row r="10">
@@ -4599,13 +4599,13 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C10" t="n">
         <v>8</v>
       </c>
       <c r="D10" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
@@ -4689,52 +4689,52 @@
         <v>1.75</v>
       </c>
       <c r="AF10" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.43</v>
+        <v>1.25</v>
       </c>
       <c r="AH10" t="n">
-        <v>2.29</v>
+        <v>2.12</v>
       </c>
       <c r="AI10" t="n">
-        <v>79.86</v>
+        <v>81.38</v>
       </c>
       <c r="AJ10" t="n">
         <v>0</v>
       </c>
       <c r="AK10" t="n">
-        <v>2.29</v>
+        <v>2.12</v>
       </c>
       <c r="AL10" t="n">
-        <v>3.29</v>
+        <v>3.5</v>
       </c>
       <c r="AM10" t="n">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="AN10" t="n">
-        <v>33.43</v>
+        <v>34</v>
       </c>
       <c r="AO10" t="n">
-        <v>0.71</v>
+        <v>0.75</v>
       </c>
       <c r="AP10" t="n">
-        <v>1</v>
+        <v>1.38</v>
       </c>
       <c r="AQ10" t="n">
-        <v>13.14</v>
+        <v>13.12</v>
       </c>
       <c r="AR10" t="n">
-        <v>13.57</v>
+        <v>13.38</v>
       </c>
       <c r="AS10" t="n">
-        <v>9.57</v>
+        <v>9.5</v>
       </c>
       <c r="AT10" t="n">
-        <v>1.57</v>
+        <v>1.38</v>
       </c>
       <c r="AU10" t="n">
-        <v>1</v>
+        <v>0.88</v>
       </c>
       <c r="AV10" t="n">
         <v>0</v>
@@ -4746,82 +4746,82 @@
         <v>0</v>
       </c>
       <c r="AY10" t="n">
-        <v>30.71</v>
+        <v>31.38</v>
       </c>
       <c r="AZ10" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="BA10" t="n">
-        <v>8.289999999999999</v>
+        <v>8</v>
       </c>
       <c r="BB10" t="n">
-        <v>5.86</v>
+        <v>5.88</v>
       </c>
       <c r="BC10" t="n">
-        <v>2.43</v>
+        <v>2.12</v>
       </c>
       <c r="BD10" t="n">
-        <v>22.57</v>
+        <v>22</v>
       </c>
       <c r="BE10" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.91</v>
       </c>
       <c r="BF10" t="n">
-        <v>2</v>
+        <v>1.88</v>
       </c>
       <c r="BG10" t="n">
-        <v>1.73</v>
+        <v>1.62</v>
       </c>
       <c r="BH10" t="n">
-        <v>8.33</v>
+        <v>8.5</v>
       </c>
       <c r="BI10" t="n">
-        <v>1.73</v>
+        <v>1.62</v>
       </c>
       <c r="BJ10" t="n">
-        <v>0.47</v>
+        <v>0.44</v>
       </c>
       <c r="BK10" t="n">
-        <v>0.33</v>
+        <v>0.31</v>
       </c>
       <c r="BL10" t="n">
-        <v>0.53</v>
+        <v>0.5</v>
       </c>
       <c r="BM10" t="n">
-        <v>0.4</v>
+        <v>0.38</v>
       </c>
       <c r="BN10" t="n">
-        <v>0.93</v>
+        <v>0.88</v>
       </c>
       <c r="BO10" t="n">
-        <v>0.8</v>
+        <v>0.75</v>
       </c>
       <c r="BP10" t="n">
-        <v>3.07</v>
+        <v>3.38</v>
       </c>
       <c r="BQ10" t="n">
-        <v>5.27</v>
+        <v>5.12</v>
       </c>
       <c r="BR10" t="n">
-        <v>73.33</v>
+        <v>68.75</v>
       </c>
       <c r="BS10" t="n">
-        <v>46.67</v>
+        <v>43.75</v>
       </c>
       <c r="BT10" t="n">
-        <v>33.33</v>
+        <v>31.25</v>
       </c>
       <c r="BU10" t="n">
-        <v>13.33</v>
+        <v>12.5</v>
       </c>
       <c r="BV10" t="n">
-        <v>6.67</v>
+        <v>6.25</v>
       </c>
       <c r="BW10" t="n">
         <v>0</v>
       </c>
       <c r="BX10" t="n">
-        <v>40</v>
+        <v>37.5</v>
       </c>
       <c r="BY10" t="n">
         <v>3.82</v>
@@ -4830,34 +4830,34 @@
         <v>4.01</v>
       </c>
       <c r="CA10" t="n">
-        <v>3.53</v>
+        <v>3.51</v>
       </c>
       <c r="CB10" t="n">
-        <v>3.6</v>
+        <v>3.57</v>
       </c>
       <c r="CC10" t="n">
-        <v>4.08</v>
+        <v>4.16</v>
       </c>
       <c r="CD10" t="n">
-        <v>4.35</v>
+        <v>4.31</v>
       </c>
       <c r="CE10" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="CF10" t="n">
-        <v>2.78</v>
+        <v>2.79</v>
       </c>
       <c r="CG10" t="n">
-        <v>2.87</v>
+        <v>2.85</v>
       </c>
       <c r="CH10" t="n">
         <v>1.39</v>
       </c>
       <c r="CI10" t="n">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="CJ10" t="n">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="CK10" t="n">
         <v>1.58</v>
@@ -4866,7 +4866,7 @@
         <v>2</v>
       </c>
       <c r="CM10" t="n">
-        <v>2.31</v>
+        <v>2.32</v>
       </c>
       <c r="CN10" t="n">
         <v>1.81</v>
@@ -4875,19 +4875,19 @@
         <v>1.31</v>
       </c>
       <c r="CP10" t="n">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="CQ10" t="n">
-        <v>3.48</v>
+        <v>3.5</v>
       </c>
       <c r="CR10" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="CS10" t="n">
-        <v>2.94</v>
+        <v>2.96</v>
       </c>
       <c r="CT10" t="n">
-        <v>3.02</v>
+        <v>3</v>
       </c>
       <c r="CU10" t="n">
         <v>1.42</v>
@@ -4899,67 +4899,67 @@
         <v>1.87</v>
       </c>
       <c r="CX10" t="n">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="CY10" t="n">
-        <v>2.04</v>
+        <v>2.03</v>
       </c>
       <c r="CZ10" t="n">
-        <v>2.27</v>
+        <v>2.29</v>
       </c>
       <c r="DA10" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="DB10" t="n">
         <v>1.33</v>
       </c>
       <c r="DC10" t="n">
-        <v>2.06</v>
+        <v>2.07</v>
       </c>
       <c r="DD10" t="n">
-        <v>3.56</v>
+        <v>3.59</v>
       </c>
       <c r="DE10" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="DF10" t="n">
-        <v>1.2</v>
+        <v>1.12</v>
       </c>
       <c r="DG10" t="n">
-        <v>2.54</v>
+        <v>2.44</v>
       </c>
       <c r="DH10" t="n">
-        <v>76.8</v>
+        <v>77.75</v>
       </c>
       <c r="DI10" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="DJ10" t="n">
-        <v>2</v>
+        <v>1.94</v>
       </c>
       <c r="DK10" t="n">
-        <v>4.2</v>
+        <v>4.25</v>
       </c>
       <c r="DL10" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="DM10" t="n">
-        <v>37.14</v>
+        <v>37.19</v>
       </c>
       <c r="DN10" t="n">
-        <v>0.73</v>
+        <v>0.75</v>
       </c>
       <c r="DO10" t="n">
-        <v>1.67</v>
+        <v>1.82</v>
       </c>
       <c r="DP10" t="n">
-        <v>12.4</v>
+        <v>12.43</v>
       </c>
       <c r="DQ10" t="n">
-        <v>12.6</v>
+        <v>12.57</v>
       </c>
       <c r="DR10" t="n">
-        <v>9.33</v>
+        <v>9.31</v>
       </c>
       <c r="DS10" t="n">
         <v>0</v>
@@ -4971,28 +4971,28 @@
         <v>0</v>
       </c>
       <c r="DV10" t="n">
-        <v>33.06</v>
+        <v>33.25</v>
       </c>
       <c r="DW10" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="DX10" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="DY10" t="n">
-        <v>6.67</v>
+        <v>6.63</v>
       </c>
       <c r="DZ10" t="n">
-        <v>2.53</v>
+        <v>2.37</v>
       </c>
       <c r="EA10" t="n">
-        <v>21.26</v>
+        <v>21.06</v>
       </c>
       <c r="EB10" t="n">
-        <v>0.99</v>
+        <v>0.98</v>
       </c>
       <c r="EC10" t="n">
-        <v>1.87</v>
+        <v>1.82</v>
       </c>
     </row>
     <row r="11">
@@ -5002,94 +5002,94 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C11" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D11" t="n">
         <v>7</v>
       </c>
       <c r="E11" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="F11" t="n">
-        <v>1.88</v>
+        <v>1.78</v>
       </c>
       <c r="G11" t="n">
-        <v>3.62</v>
+        <v>3.44</v>
       </c>
       <c r="H11" t="n">
-        <v>105.88</v>
+        <v>103.22</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
       </c>
       <c r="J11" t="n">
-        <v>2.88</v>
+        <v>2.78</v>
       </c>
       <c r="K11" t="n">
-        <v>6.75</v>
+        <v>6.44</v>
       </c>
       <c r="L11" t="n">
-        <v>0.38</v>
+        <v>0.44</v>
       </c>
       <c r="M11" t="n">
-        <v>60.75</v>
+        <v>58.78</v>
       </c>
       <c r="N11" t="n">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="O11" t="n">
-        <v>3.12</v>
+        <v>3</v>
       </c>
       <c r="P11" t="n">
-        <v>14.38</v>
+        <v>13.67</v>
       </c>
       <c r="Q11" t="n">
-        <v>10.5</v>
+        <v>10.56</v>
       </c>
       <c r="R11" t="n">
-        <v>7.38</v>
+        <v>7.67</v>
       </c>
       <c r="S11" t="n">
-        <v>0.88</v>
+        <v>0.78</v>
       </c>
       <c r="T11" t="n">
-        <v>1.75</v>
+        <v>1.67</v>
       </c>
       <c r="U11" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="V11" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="W11" t="n">
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>50.88</v>
+        <v>49.67</v>
       </c>
       <c r="Y11" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="Z11" t="n">
-        <v>17.62</v>
+        <v>16.33</v>
       </c>
       <c r="AA11" t="n">
-        <v>11.75</v>
+        <v>10.89</v>
       </c>
       <c r="AB11" t="n">
-        <v>5.88</v>
+        <v>5.44</v>
       </c>
       <c r="AC11" t="n">
-        <v>17.5</v>
+        <v>19.56</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.96</v>
+        <v>1.84</v>
       </c>
       <c r="AE11" t="n">
-        <v>2.62</v>
+        <v>2.56</v>
       </c>
       <c r="AF11" t="n">
         <v>0.14</v>
@@ -5173,70 +5173,70 @@
         <v>2.43</v>
       </c>
       <c r="BG11" t="n">
-        <v>2.33</v>
+        <v>2.25</v>
       </c>
       <c r="BH11" t="n">
-        <v>10.33</v>
+        <v>10.06</v>
       </c>
       <c r="BI11" t="n">
-        <v>2.33</v>
+        <v>2.25</v>
       </c>
       <c r="BJ11" t="n">
-        <v>0.47</v>
+        <v>0.5</v>
       </c>
       <c r="BK11" t="n">
-        <v>0.33</v>
+        <v>0.31</v>
       </c>
       <c r="BL11" t="n">
-        <v>0.87</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="BM11" t="n">
-        <v>0.67</v>
+        <v>0.62</v>
       </c>
       <c r="BN11" t="n">
-        <v>1.53</v>
+        <v>1.44</v>
       </c>
       <c r="BO11" t="n">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="BP11" t="n">
-        <v>5.07</v>
+        <v>4.88</v>
       </c>
       <c r="BQ11" t="n">
-        <v>5.27</v>
+        <v>5.19</v>
       </c>
       <c r="BR11" t="n">
-        <v>93.33</v>
+        <v>93.75</v>
       </c>
       <c r="BS11" t="n">
-        <v>60</v>
+        <v>56.25</v>
       </c>
       <c r="BT11" t="n">
-        <v>26.67</v>
+        <v>25</v>
       </c>
       <c r="BU11" t="n">
-        <v>26.67</v>
+        <v>25</v>
       </c>
       <c r="BV11" t="n">
-        <v>13.33</v>
+        <v>12.5</v>
       </c>
       <c r="BW11" t="n">
-        <v>6.67</v>
+        <v>6.25</v>
       </c>
       <c r="BX11" t="n">
-        <v>40</v>
+        <v>37.5</v>
       </c>
       <c r="BY11" t="n">
-        <v>1.85</v>
+        <v>1.99</v>
       </c>
       <c r="BZ11" t="n">
-        <v>1.97</v>
+        <v>2.11</v>
       </c>
       <c r="CA11" t="n">
-        <v>3.66</v>
+        <v>3.64</v>
       </c>
       <c r="CB11" t="n">
-        <v>3.79</v>
+        <v>3.77</v>
       </c>
       <c r="CC11" t="n">
         <v>2.5</v>
@@ -5248,52 +5248,52 @@
         <v>1.32</v>
       </c>
       <c r="CF11" t="n">
-        <v>2.52</v>
+        <v>2.53</v>
       </c>
       <c r="CG11" t="n">
-        <v>3.11</v>
+        <v>3.09</v>
       </c>
       <c r="CH11" t="n">
         <v>1.48</v>
       </c>
       <c r="CI11" t="n">
-        <v>2.12</v>
+        <v>2.13</v>
       </c>
       <c r="CJ11" t="n">
         <v>1.69</v>
       </c>
       <c r="CK11" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="CL11" t="n">
-        <v>1.89</v>
+        <v>1.91</v>
       </c>
       <c r="CM11" t="n">
-        <v>2.54</v>
+        <v>2.53</v>
       </c>
       <c r="CN11" t="n">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="CO11" t="n">
         <v>1.23</v>
       </c>
       <c r="CP11" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="CQ11" t="n">
-        <v>2.88</v>
+        <v>2.89</v>
       </c>
       <c r="CR11" t="n">
         <v>1.35</v>
       </c>
       <c r="CS11" t="n">
-        <v>2.6</v>
+        <v>2.61</v>
       </c>
       <c r="CT11" t="n">
-        <v>3.27</v>
+        <v>3.26</v>
       </c>
       <c r="CU11" t="n">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="CV11" t="n">
         <v>2.24</v>
@@ -5305,97 +5305,97 @@
         <v>1.52</v>
       </c>
       <c r="CY11" t="n">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="CZ11" t="n">
-        <v>2.51</v>
+        <v>2.49</v>
       </c>
       <c r="DA11" t="n">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="DB11" t="n">
         <v>1.25</v>
       </c>
       <c r="DC11" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="DD11" t="n">
-        <v>2.96</v>
+        <v>2.98</v>
       </c>
       <c r="DE11" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="DF11" t="n">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="DG11" t="n">
-        <v>3.27</v>
+        <v>3.19</v>
       </c>
       <c r="DH11" t="n">
-        <v>100.07</v>
+        <v>98.94</v>
       </c>
       <c r="DI11" t="n">
         <v>0</v>
       </c>
       <c r="DJ11" t="n">
-        <v>2.8</v>
+        <v>2.75</v>
       </c>
       <c r="DK11" t="n">
-        <v>6.4</v>
+        <v>6.25</v>
       </c>
       <c r="DL11" t="n">
-        <v>0.34</v>
+        <v>0.37</v>
       </c>
       <c r="DM11" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="DN11" t="n">
         <v>0.9399999999999999</v>
       </c>
       <c r="DO11" t="n">
-        <v>3.13</v>
+        <v>3.06</v>
       </c>
       <c r="DP11" t="n">
-        <v>14.14</v>
+        <v>13.75</v>
       </c>
       <c r="DQ11" t="n">
-        <v>9.869999999999999</v>
+        <v>9.94</v>
       </c>
       <c r="DR11" t="n">
-        <v>7.6</v>
+        <v>7.75</v>
       </c>
       <c r="DS11" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="DT11" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="DU11" t="n">
         <v>0</v>
       </c>
       <c r="DV11" t="n">
-        <v>53.2</v>
+        <v>52.38</v>
       </c>
       <c r="DW11" t="n">
-        <v>0.2</v>
+        <v>0.19</v>
       </c>
       <c r="DX11" t="n">
-        <v>15.46</v>
+        <v>14.87</v>
       </c>
       <c r="DY11" t="n">
-        <v>10.4</v>
+        <v>10</v>
       </c>
       <c r="DZ11" t="n">
-        <v>5.07</v>
+        <v>4.87</v>
       </c>
       <c r="EA11" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="EB11" t="n">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="EC11" t="n">
-        <v>2.53</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="12">
@@ -5405,13 +5405,13 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C12" t="n">
         <v>8</v>
       </c>
       <c r="D12" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E12" t="n">
         <v>0</v>
@@ -5498,49 +5498,49 @@
         <v>0</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.71</v>
+        <v>1.88</v>
       </c>
       <c r="AH12" t="n">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="AI12" t="n">
-        <v>86</v>
+        <v>83.75</v>
       </c>
       <c r="AJ12" t="n">
         <v>0</v>
       </c>
       <c r="AK12" t="n">
-        <v>2.57</v>
+        <v>2.62</v>
       </c>
       <c r="AL12" t="n">
-        <v>3.14</v>
+        <v>3.25</v>
       </c>
       <c r="AM12" t="n">
-        <v>0.43</v>
+        <v>0.38</v>
       </c>
       <c r="AN12" t="n">
-        <v>33.86</v>
+        <v>32.12</v>
       </c>
       <c r="AO12" t="n">
-        <v>0.71</v>
+        <v>0.62</v>
       </c>
       <c r="AP12" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AQ12" t="n">
+        <v>14.12</v>
+      </c>
+      <c r="AR12" t="n">
+        <v>12.88</v>
+      </c>
+      <c r="AS12" t="n">
+        <v>9.119999999999999</v>
+      </c>
+      <c r="AT12" t="n">
         <v>1</v>
       </c>
-      <c r="AQ12" t="n">
-        <v>14</v>
-      </c>
-      <c r="AR12" t="n">
-        <v>13.29</v>
-      </c>
-      <c r="AS12" t="n">
-        <v>8.289999999999999</v>
-      </c>
-      <c r="AT12" t="n">
-        <v>1.14</v>
-      </c>
       <c r="AU12" t="n">
-        <v>0.29</v>
+        <v>0.38</v>
       </c>
       <c r="AV12" t="n">
         <v>0</v>
@@ -5552,73 +5552,73 @@
         <v>0</v>
       </c>
       <c r="AY12" t="n">
-        <v>46.43</v>
+        <v>43.75</v>
       </c>
       <c r="AZ12" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="BA12" t="n">
-        <v>9.140000000000001</v>
+        <v>9.5</v>
       </c>
       <c r="BB12" t="n">
-        <v>6.43</v>
+        <v>6.5</v>
       </c>
       <c r="BC12" t="n">
-        <v>2.71</v>
+        <v>3</v>
       </c>
       <c r="BD12" t="n">
-        <v>19.86</v>
+        <v>18.75</v>
       </c>
       <c r="BE12" t="n">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="BF12" t="n">
-        <v>2.29</v>
+        <v>2.38</v>
       </c>
       <c r="BG12" t="n">
-        <v>2.13</v>
+        <v>2.06</v>
       </c>
       <c r="BH12" t="n">
-        <v>8.869999999999999</v>
+        <v>9.119999999999999</v>
       </c>
       <c r="BI12" t="n">
-        <v>2.13</v>
+        <v>2.06</v>
       </c>
       <c r="BJ12" t="n">
-        <v>0.67</v>
+        <v>0.62</v>
       </c>
       <c r="BK12" t="n">
-        <v>0.4</v>
+        <v>0.38</v>
       </c>
       <c r="BL12" t="n">
-        <v>0.67</v>
+        <v>0.62</v>
       </c>
       <c r="BM12" t="n">
-        <v>0.4</v>
+        <v>0.44</v>
       </c>
       <c r="BN12" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="BO12" t="n">
-        <v>1.07</v>
+        <v>1</v>
       </c>
       <c r="BP12" t="n">
-        <v>3.87</v>
+        <v>3.94</v>
       </c>
       <c r="BQ12" t="n">
-        <v>5</v>
+        <v>5.19</v>
       </c>
       <c r="BR12" t="n">
-        <v>93.33</v>
+        <v>93.75</v>
       </c>
       <c r="BS12" t="n">
-        <v>73.33</v>
+        <v>68.75</v>
       </c>
       <c r="BT12" t="n">
-        <v>33.33</v>
+        <v>31.25</v>
       </c>
       <c r="BU12" t="n">
-        <v>13.33</v>
+        <v>12.5</v>
       </c>
       <c r="BV12" t="n">
         <v>0</v>
@@ -5627,7 +5627,7 @@
         <v>0</v>
       </c>
       <c r="BX12" t="n">
-        <v>60</v>
+        <v>56.25</v>
       </c>
       <c r="BY12" t="n">
         <v>2.66</v>
@@ -5636,61 +5636,61 @@
         <v>2.87</v>
       </c>
       <c r="CA12" t="n">
-        <v>3.47</v>
+        <v>3.58</v>
       </c>
       <c r="CB12" t="n">
-        <v>3.6</v>
+        <v>3.73</v>
       </c>
       <c r="CC12" t="n">
-        <v>3.64</v>
+        <v>4.22</v>
       </c>
       <c r="CD12" t="n">
-        <v>4.06</v>
+        <v>4.74</v>
       </c>
       <c r="CE12" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="CF12" t="n">
-        <v>2.6</v>
+        <v>2.58</v>
       </c>
       <c r="CG12" t="n">
-        <v>3.04</v>
+        <v>3.07</v>
       </c>
       <c r="CH12" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="CI12" t="n">
-        <v>2.11</v>
+        <v>2.1</v>
       </c>
       <c r="CJ12" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="CK12" t="n">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="CL12" t="n">
-        <v>1.93</v>
+        <v>1.96</v>
       </c>
       <c r="CM12" t="n">
-        <v>2.47</v>
+        <v>2.45</v>
       </c>
       <c r="CN12" t="n">
         <v>1.9</v>
       </c>
       <c r="CO12" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="CP12" t="n">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="CQ12" t="n">
-        <v>3.08</v>
+        <v>3.03</v>
       </c>
       <c r="CR12" t="n">
         <v>1.36</v>
       </c>
       <c r="CS12" t="n">
-        <v>2.7</v>
+        <v>2.68</v>
       </c>
       <c r="CT12" t="n">
         <v>3.19</v>
@@ -5699,10 +5699,10 @@
         <v>1.49</v>
       </c>
       <c r="CV12" t="n">
-        <v>2.19</v>
+        <v>2.17</v>
       </c>
       <c r="CW12" t="n">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="CX12" t="n">
         <v>1.59</v>
@@ -5720,85 +5720,85 @@
         <v>1.27</v>
       </c>
       <c r="DC12" t="n">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="DD12" t="n">
-        <v>3.11</v>
+        <v>3.07</v>
       </c>
       <c r="DE12" t="n">
         <v>0</v>
       </c>
       <c r="DF12" t="n">
-        <v>1.6</v>
+        <v>1.69</v>
       </c>
       <c r="DG12" t="n">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="DH12" t="n">
-        <v>93.53</v>
+        <v>91.94</v>
       </c>
       <c r="DI12" t="n">
         <v>0</v>
       </c>
       <c r="DJ12" t="n">
-        <v>2.53</v>
+        <v>2.56</v>
       </c>
       <c r="DK12" t="n">
-        <v>4.07</v>
+        <v>4.06</v>
       </c>
       <c r="DL12" t="n">
-        <v>0.6</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="DM12" t="n">
-        <v>39.8</v>
+        <v>38.56</v>
       </c>
       <c r="DN12" t="n">
-        <v>0.8</v>
+        <v>0.75</v>
       </c>
       <c r="DO12" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="DP12" t="n">
-        <v>12.46</v>
+        <v>12.62</v>
       </c>
       <c r="DQ12" t="n">
-        <v>13.2</v>
+        <v>13</v>
       </c>
       <c r="DR12" t="n">
-        <v>7.47</v>
+        <v>7.94</v>
       </c>
       <c r="DS12" t="n">
-        <v>0.2</v>
+        <v>0.19</v>
       </c>
       <c r="DT12" t="n">
-        <v>0.2</v>
+        <v>0.19</v>
       </c>
       <c r="DU12" t="n">
         <v>0</v>
       </c>
       <c r="DV12" t="n">
-        <v>50.2</v>
+        <v>48.62</v>
       </c>
       <c r="DW12" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="DX12" t="n">
-        <v>11.33</v>
+        <v>11.38</v>
       </c>
       <c r="DY12" t="n">
-        <v>7.2</v>
+        <v>7.19</v>
       </c>
       <c r="DZ12" t="n">
-        <v>4.13</v>
+        <v>4.19</v>
       </c>
       <c r="EA12" t="n">
-        <v>20.47</v>
+        <v>19.88</v>
       </c>
       <c r="EB12" t="n">
         <v>1.3</v>
       </c>
       <c r="EC12" t="n">
-        <v>2.27</v>
+        <v>2.32</v>
       </c>
     </row>
     <row r="13">
@@ -5808,13 +5808,13 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C13" t="n">
         <v>8</v>
       </c>
       <c r="D13" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E13" t="n">
         <v>0.12</v>
@@ -5904,124 +5904,124 @@
         <v>1</v>
       </c>
       <c r="AH13" t="n">
-        <v>3.57</v>
+        <v>3.62</v>
       </c>
       <c r="AI13" t="n">
-        <v>95.70999999999999</v>
+        <v>99.62</v>
       </c>
       <c r="AJ13" t="n">
-        <v>0</v>
+        <v>0.12</v>
       </c>
       <c r="AK13" t="n">
-        <v>1.43</v>
+        <v>1.5</v>
       </c>
       <c r="AL13" t="n">
         <v>6</v>
       </c>
       <c r="AM13" t="n">
-        <v>0.29</v>
+        <v>0.38</v>
       </c>
       <c r="AN13" t="n">
-        <v>50.29</v>
+        <v>52.75</v>
       </c>
       <c r="AO13" t="n">
-        <v>0.43</v>
+        <v>0.5</v>
       </c>
       <c r="AP13" t="n">
-        <v>2.43</v>
+        <v>2.38</v>
       </c>
       <c r="AQ13" t="n">
-        <v>12.29</v>
+        <v>12</v>
       </c>
       <c r="AR13" t="n">
-        <v>11.71</v>
+        <v>11.38</v>
       </c>
       <c r="AS13" t="n">
-        <v>7.71</v>
+        <v>8.5</v>
       </c>
       <c r="AT13" t="n">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="AU13" t="n">
-        <v>1.29</v>
+        <v>1.38</v>
       </c>
       <c r="AV13" t="n">
-        <v>0.43</v>
+        <v>0.38</v>
       </c>
       <c r="AW13" t="n">
-        <v>0.43</v>
+        <v>0.38</v>
       </c>
       <c r="AX13" t="n">
         <v>0</v>
       </c>
       <c r="AY13" t="n">
-        <v>52.43</v>
+        <v>52.25</v>
       </c>
       <c r="AZ13" t="n">
         <v>0</v>
       </c>
       <c r="BA13" t="n">
-        <v>13.43</v>
+        <v>13.5</v>
       </c>
       <c r="BB13" t="n">
-        <v>9</v>
+        <v>9.119999999999999</v>
       </c>
       <c r="BC13" t="n">
-        <v>4.43</v>
+        <v>4.38</v>
       </c>
       <c r="BD13" t="n">
-        <v>23.86</v>
+        <v>22.88</v>
       </c>
       <c r="BE13" t="n">
-        <v>1.52</v>
+        <v>1.54</v>
       </c>
       <c r="BF13" t="n">
-        <v>1.43</v>
+        <v>1.5</v>
       </c>
       <c r="BG13" t="n">
-        <v>2.53</v>
+        <v>2.56</v>
       </c>
       <c r="BH13" t="n">
-        <v>9.93</v>
+        <v>10</v>
       </c>
       <c r="BI13" t="n">
-        <v>2.53</v>
+        <v>2.56</v>
       </c>
       <c r="BJ13" t="n">
-        <v>0.67</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="BK13" t="n">
-        <v>0.47</v>
+        <v>0.44</v>
       </c>
       <c r="BL13" t="n">
-        <v>0.67</v>
+        <v>0.62</v>
       </c>
       <c r="BM13" t="n">
-        <v>0.73</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="BN13" t="n">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="BO13" t="n">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="BP13" t="n">
-        <v>4.27</v>
+        <v>4.25</v>
       </c>
       <c r="BQ13" t="n">
-        <v>5.67</v>
+        <v>5.75</v>
       </c>
       <c r="BR13" t="n">
         <v>100</v>
       </c>
       <c r="BS13" t="n">
-        <v>86.67</v>
+        <v>87.5</v>
       </c>
       <c r="BT13" t="n">
-        <v>46.67</v>
+        <v>50</v>
       </c>
       <c r="BU13" t="n">
-        <v>20</v>
+        <v>18.75</v>
       </c>
       <c r="BV13" t="n">
         <v>0</v>
@@ -6030,7 +6030,7 @@
         <v>0</v>
       </c>
       <c r="BX13" t="n">
-        <v>53.33</v>
+        <v>56.25</v>
       </c>
       <c r="BY13" t="n">
         <v>2.21</v>
@@ -6039,25 +6039,25 @@
         <v>2.4</v>
       </c>
       <c r="CA13" t="n">
-        <v>3.74</v>
+        <v>3.72</v>
       </c>
       <c r="CB13" t="n">
-        <v>3.85</v>
+        <v>3.82</v>
       </c>
       <c r="CC13" t="n">
-        <v>4.35</v>
+        <v>4.19</v>
       </c>
       <c r="CD13" t="n">
-        <v>4.62</v>
+        <v>4.45</v>
       </c>
       <c r="CE13" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="CF13" t="n">
         <v>2.45</v>
       </c>
       <c r="CG13" t="n">
-        <v>3.2</v>
+        <v>3.18</v>
       </c>
       <c r="CH13" t="n">
         <v>1.51</v>
@@ -6066,7 +6066,7 @@
         <v>2.19</v>
       </c>
       <c r="CJ13" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="CK13" t="n">
         <v>1.45</v>
@@ -6075,13 +6075,13 @@
         <v>1.88</v>
       </c>
       <c r="CM13" t="n">
-        <v>2.55</v>
+        <v>2.54</v>
       </c>
       <c r="CN13" t="n">
         <v>1.96</v>
       </c>
       <c r="CO13" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="CP13" t="n">
         <v>1.73</v>
@@ -6102,7 +6102,7 @@
         <v>1.52</v>
       </c>
       <c r="CV13" t="n">
-        <v>2.29</v>
+        <v>2.3</v>
       </c>
       <c r="CW13" t="n">
         <v>1.66</v>
@@ -6117,7 +6117,7 @@
         <v>2.44</v>
       </c>
       <c r="DA13" t="n">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="DB13" t="n">
         <v>1.24</v>
@@ -6126,82 +6126,82 @@
         <v>1.78</v>
       </c>
       <c r="DD13" t="n">
-        <v>2.87</v>
+        <v>2.86</v>
       </c>
       <c r="DE13" t="n">
         <v>0.06</v>
       </c>
       <c r="DF13" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="DG13" t="n">
-        <v>3.67</v>
+        <v>3.68</v>
       </c>
       <c r="DH13" t="n">
-        <v>102.93</v>
+        <v>104.44</v>
       </c>
       <c r="DI13" t="n">
-        <v>0</v>
+        <v>0.06</v>
       </c>
       <c r="DJ13" t="n">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="DK13" t="n">
-        <v>5.67</v>
+        <v>5.69</v>
       </c>
       <c r="DL13" t="n">
-        <v>0.27</v>
+        <v>0.32</v>
       </c>
       <c r="DM13" t="n">
-        <v>54.94</v>
+        <v>55.88</v>
       </c>
       <c r="DN13" t="n">
-        <v>0.4</v>
+        <v>0.44</v>
       </c>
       <c r="DO13" t="n">
         <v>2</v>
       </c>
       <c r="DP13" t="n">
-        <v>12</v>
+        <v>11.88</v>
       </c>
       <c r="DQ13" t="n">
-        <v>11.53</v>
+        <v>11.38</v>
       </c>
       <c r="DR13" t="n">
-        <v>6.47</v>
+        <v>6.94</v>
       </c>
       <c r="DS13" t="n">
-        <v>0.26</v>
+        <v>0.25</v>
       </c>
       <c r="DT13" t="n">
-        <v>0.26</v>
+        <v>0.25</v>
       </c>
       <c r="DU13" t="n">
         <v>0</v>
       </c>
       <c r="DV13" t="n">
-        <v>54.33</v>
+        <v>54.12</v>
       </c>
       <c r="DW13" t="n">
         <v>0.06</v>
       </c>
       <c r="DX13" t="n">
-        <v>14.74</v>
+        <v>14.69</v>
       </c>
       <c r="DY13" t="n">
-        <v>10.27</v>
+        <v>10.25</v>
       </c>
       <c r="DZ13" t="n">
-        <v>4.47</v>
+        <v>4.44</v>
       </c>
       <c r="EA13" t="n">
-        <v>24</v>
+        <v>23.5</v>
       </c>
       <c r="EB13" t="n">
         <v>1.64</v>
       </c>
       <c r="EC13" t="n">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
     </row>
     <row r="14">
@@ -6211,94 +6211,94 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C14" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D14" t="n">
         <v>8</v>
       </c>
       <c r="E14" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="F14" t="n">
-        <v>2</v>
+        <v>1.75</v>
       </c>
       <c r="G14" t="n">
         <v>2</v>
       </c>
       <c r="H14" t="n">
-        <v>86.29000000000001</v>
+        <v>88.88</v>
       </c>
       <c r="I14" t="n">
         <v>0</v>
       </c>
       <c r="J14" t="n">
-        <v>2.57</v>
+        <v>2.25</v>
       </c>
       <c r="K14" t="n">
-        <v>4.71</v>
+        <v>4.88</v>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>0.12</v>
       </c>
       <c r="M14" t="n">
-        <v>47.71</v>
+        <v>50</v>
       </c>
       <c r="N14" t="n">
-        <v>0.43</v>
+        <v>0.38</v>
       </c>
       <c r="O14" t="n">
-        <v>2.71</v>
+        <v>2.88</v>
       </c>
       <c r="P14" t="n">
-        <v>11.71</v>
+        <v>11.75</v>
       </c>
       <c r="Q14" t="n">
-        <v>14.14</v>
+        <v>14</v>
       </c>
       <c r="R14" t="n">
-        <v>7.14</v>
+        <v>7.12</v>
       </c>
       <c r="S14" t="n">
-        <v>1</v>
+        <v>0.88</v>
       </c>
       <c r="T14" t="n">
-        <v>1.29</v>
+        <v>1.12</v>
       </c>
       <c r="U14" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="V14" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="W14" t="n">
         <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>45.29</v>
+        <v>47.62</v>
       </c>
       <c r="Y14" t="n">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="Z14" t="n">
-        <v>10.14</v>
+        <v>11</v>
       </c>
       <c r="AA14" t="n">
-        <v>5.86</v>
+        <v>6.62</v>
       </c>
       <c r="AB14" t="n">
-        <v>4.29</v>
+        <v>4.38</v>
       </c>
       <c r="AC14" t="n">
-        <v>17.29</v>
+        <v>18</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.29</v>
+        <v>1.36</v>
       </c>
       <c r="AE14" t="n">
-        <v>2.14</v>
+        <v>1.88</v>
       </c>
       <c r="AF14" t="n">
         <v>0.12</v>
@@ -6382,70 +6382,70 @@
         <v>2.12</v>
       </c>
       <c r="BG14" t="n">
-        <v>2.6</v>
+        <v>2.44</v>
       </c>
       <c r="BH14" t="n">
-        <v>9.4</v>
+        <v>9.5</v>
       </c>
       <c r="BI14" t="n">
-        <v>2.6</v>
+        <v>2.44</v>
       </c>
       <c r="BJ14" t="n">
-        <v>0.67</v>
+        <v>0.62</v>
       </c>
       <c r="BK14" t="n">
-        <v>0.67</v>
+        <v>0.62</v>
       </c>
       <c r="BL14" t="n">
-        <v>0.87</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="BM14" t="n">
-        <v>0.4</v>
+        <v>0.38</v>
       </c>
       <c r="BN14" t="n">
-        <v>1.27</v>
+        <v>1.19</v>
       </c>
       <c r="BO14" t="n">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="BP14" t="n">
-        <v>5</v>
+        <v>5.19</v>
       </c>
       <c r="BQ14" t="n">
-        <v>4.4</v>
+        <v>4.31</v>
       </c>
       <c r="BR14" t="n">
-        <v>100</v>
+        <v>93.75</v>
       </c>
       <c r="BS14" t="n">
-        <v>73.33</v>
+        <v>68.75</v>
       </c>
       <c r="BT14" t="n">
-        <v>46.67</v>
+        <v>43.75</v>
       </c>
       <c r="BU14" t="n">
-        <v>33.33</v>
+        <v>31.25</v>
       </c>
       <c r="BV14" t="n">
-        <v>6.67</v>
+        <v>6.25</v>
       </c>
       <c r="BW14" t="n">
         <v>0</v>
       </c>
       <c r="BX14" t="n">
-        <v>60</v>
+        <v>56.25</v>
       </c>
       <c r="BY14" t="n">
-        <v>2.06</v>
+        <v>2.03</v>
       </c>
       <c r="BZ14" t="n">
         <v>2.17</v>
       </c>
       <c r="CA14" t="n">
-        <v>3.59</v>
+        <v>3.57</v>
       </c>
       <c r="CB14" t="n">
-        <v>3.59</v>
+        <v>3.56</v>
       </c>
       <c r="CC14" t="n">
         <v>4.05</v>
@@ -6457,58 +6457,58 @@
         <v>1.33</v>
       </c>
       <c r="CF14" t="n">
-        <v>2.61</v>
+        <v>2.63</v>
       </c>
       <c r="CG14" t="n">
-        <v>3.1</v>
+        <v>3.06</v>
       </c>
       <c r="CH14" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="CI14" t="n">
-        <v>2.09</v>
+        <v>2.07</v>
       </c>
       <c r="CJ14" t="n">
-        <v>1.72</v>
+        <v>1.74</v>
       </c>
       <c r="CK14" t="n">
         <v>1.47</v>
       </c>
       <c r="CL14" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="CM14" t="n">
         <v>2.57</v>
       </c>
       <c r="CN14" t="n">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="CO14" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="CP14" t="n">
-        <v>1.8</v>
+        <v>1.82</v>
       </c>
       <c r="CQ14" t="n">
-        <v>3.02</v>
+        <v>3.07</v>
       </c>
       <c r="CR14" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="CS14" t="n">
-        <v>2.77</v>
+        <v>2.8</v>
       </c>
       <c r="CT14" t="n">
-        <v>3.15</v>
+        <v>3.12</v>
       </c>
       <c r="CU14" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="CV14" t="n">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="CW14" t="n">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="CX14" t="n">
         <v>1.54</v>
@@ -6523,88 +6523,88 @@
         <v>1.95</v>
       </c>
       <c r="DB14" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="DC14" t="n">
-        <v>1.92</v>
+        <v>1.94</v>
       </c>
       <c r="DD14" t="n">
-        <v>3.18</v>
+        <v>3.24</v>
       </c>
       <c r="DE14" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="DF14" t="n">
-        <v>1.87</v>
+        <v>1.75</v>
       </c>
       <c r="DG14" t="n">
         <v>1.94</v>
       </c>
       <c r="DH14" t="n">
-        <v>89.73999999999999</v>
+        <v>90.81999999999999</v>
       </c>
       <c r="DI14" t="n">
         <v>0</v>
       </c>
       <c r="DJ14" t="n">
-        <v>2.33</v>
+        <v>2.18</v>
       </c>
       <c r="DK14" t="n">
-        <v>4.66</v>
+        <v>4.75</v>
       </c>
       <c r="DL14" t="n">
-        <v>0.33</v>
+        <v>0.37</v>
       </c>
       <c r="DM14" t="n">
-        <v>48</v>
+        <v>49.12</v>
       </c>
       <c r="DN14" t="n">
-        <v>0.4</v>
+        <v>0.38</v>
       </c>
       <c r="DO14" t="n">
-        <v>2.73</v>
+        <v>2.82</v>
       </c>
       <c r="DP14" t="n">
-        <v>11.27</v>
+        <v>11.32</v>
       </c>
       <c r="DQ14" t="n">
-        <v>11.87</v>
+        <v>11.94</v>
       </c>
       <c r="DR14" t="n">
         <v>7</v>
       </c>
       <c r="DS14" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="DT14" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="DU14" t="n">
         <v>0</v>
       </c>
       <c r="DV14" t="n">
-        <v>46.67</v>
+        <v>47.75</v>
       </c>
       <c r="DW14" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="DX14" t="n">
-        <v>10.66</v>
+        <v>11.06</v>
       </c>
       <c r="DY14" t="n">
-        <v>6.47</v>
+        <v>6.81</v>
       </c>
       <c r="DZ14" t="n">
-        <v>4.2</v>
+        <v>4.25</v>
       </c>
       <c r="EA14" t="n">
-        <v>19.67</v>
+        <v>19.88</v>
       </c>
       <c r="EB14" t="n">
-        <v>1.32</v>
+        <v>1.35</v>
       </c>
       <c r="EC14" t="n">
-        <v>2.13</v>
+        <v>2</v>
       </c>
     </row>
     <row r="15">
@@ -7017,13 +7017,13 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C16" t="n">
         <v>7</v>
       </c>
       <c r="D16" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E16" t="n">
         <v>0.43</v>
@@ -7107,52 +7107,52 @@
         <v>1.29</v>
       </c>
       <c r="AF16" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.75</v>
+        <v>1.67</v>
       </c>
       <c r="AH16" t="n">
-        <v>2.88</v>
+        <v>2.78</v>
       </c>
       <c r="AI16" t="n">
-        <v>108.12</v>
+        <v>112.67</v>
       </c>
       <c r="AJ16" t="n">
-        <v>0</v>
+        <v>0.11</v>
       </c>
       <c r="AK16" t="n">
-        <v>2.88</v>
+        <v>2.89</v>
       </c>
       <c r="AL16" t="n">
-        <v>5.75</v>
+        <v>5.33</v>
       </c>
       <c r="AM16" t="n">
-        <v>0.62</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AN16" t="n">
-        <v>46.38</v>
+        <v>49.67</v>
       </c>
       <c r="AO16" t="n">
-        <v>1.12</v>
+        <v>1.22</v>
       </c>
       <c r="AP16" t="n">
-        <v>2.88</v>
+        <v>2.56</v>
       </c>
       <c r="AQ16" t="n">
-        <v>13.88</v>
+        <v>13.56</v>
       </c>
       <c r="AR16" t="n">
-        <v>8.75</v>
+        <v>8.67</v>
       </c>
       <c r="AS16" t="n">
-        <v>6</v>
+        <v>6.11</v>
       </c>
       <c r="AT16" t="n">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="AU16" t="n">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="AV16" t="n">
         <v>0</v>
@@ -7164,82 +7164,82 @@
         <v>0</v>
       </c>
       <c r="AY16" t="n">
-        <v>52.88</v>
+        <v>53.67</v>
       </c>
       <c r="AZ16" t="n">
         <v>0</v>
       </c>
       <c r="BA16" t="n">
-        <v>14.25</v>
+        <v>13.78</v>
       </c>
       <c r="BB16" t="n">
-        <v>8.619999999999999</v>
+        <v>8.67</v>
       </c>
       <c r="BC16" t="n">
-        <v>5.62</v>
+        <v>5.11</v>
       </c>
       <c r="BD16" t="n">
+        <v>19.67</v>
+      </c>
+      <c r="BE16" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="BF16" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="BG16" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="BH16" t="n">
+        <v>9.75</v>
+      </c>
+      <c r="BI16" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="BJ16" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="BK16" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="BL16" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="BM16" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="BN16" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="BO16" t="n">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="BP16" t="n">
+        <v>5.06</v>
+      </c>
+      <c r="BQ16" t="n">
+        <v>4.69</v>
+      </c>
+      <c r="BR16" t="n">
+        <v>93.75</v>
+      </c>
+      <c r="BS16" t="n">
+        <v>75</v>
+      </c>
+      <c r="BT16" t="n">
+        <v>37.5</v>
+      </c>
+      <c r="BU16" t="n">
+        <v>25</v>
+      </c>
+      <c r="BV16" t="n">
         <v>18.75</v>
       </c>
-      <c r="BE16" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="BF16" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="BG16" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="BH16" t="n">
-        <v>10</v>
-      </c>
-      <c r="BI16" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="BJ16" t="n">
-        <v>0.47</v>
-      </c>
-      <c r="BK16" t="n">
-        <v>0.33</v>
-      </c>
-      <c r="BL16" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="BM16" t="n">
-        <v>0.53</v>
-      </c>
-      <c r="BN16" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="BO16" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="BP16" t="n">
-        <v>5.27</v>
-      </c>
-      <c r="BQ16" t="n">
-        <v>4.73</v>
-      </c>
-      <c r="BR16" t="n">
-        <v>93.33</v>
-      </c>
-      <c r="BS16" t="n">
-        <v>80</v>
-      </c>
-      <c r="BT16" t="n">
-        <v>40</v>
-      </c>
-      <c r="BU16" t="n">
-        <v>26.67</v>
-      </c>
-      <c r="BV16" t="n">
-        <v>20</v>
-      </c>
       <c r="BW16" t="n">
         <v>0</v>
       </c>
       <c r="BX16" t="n">
-        <v>40</v>
+        <v>37.5</v>
       </c>
       <c r="BY16" t="n">
         <v>1.35</v>
@@ -7248,43 +7248,43 @@
         <v>1.45</v>
       </c>
       <c r="CA16" t="n">
-        <v>4.29</v>
+        <v>4.24</v>
       </c>
       <c r="CB16" t="n">
-        <v>4.42</v>
+        <v>4.36</v>
       </c>
       <c r="CC16" t="n">
-        <v>1.82</v>
+        <v>1.87</v>
       </c>
       <c r="CD16" t="n">
-        <v>1.86</v>
+        <v>1.91</v>
       </c>
       <c r="CE16" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="CF16" t="n">
-        <v>2.46</v>
+        <v>2.47</v>
       </c>
       <c r="CG16" t="n">
-        <v>3.25</v>
+        <v>3.22</v>
       </c>
       <c r="CH16" t="n">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="CI16" t="n">
-        <v>1.94</v>
+        <v>1.96</v>
       </c>
       <c r="CJ16" t="n">
         <v>1.82</v>
       </c>
       <c r="CK16" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="CL16" t="n">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="CM16" t="n">
-        <v>2.5</v>
+        <v>2.49</v>
       </c>
       <c r="CN16" t="n">
         <v>1.94</v>
@@ -7293,28 +7293,28 @@
         <v>1.22</v>
       </c>
       <c r="CP16" t="n">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="CQ16" t="n">
-        <v>2.72</v>
+        <v>2.74</v>
       </c>
       <c r="CR16" t="n">
         <v>1.35</v>
       </c>
       <c r="CS16" t="n">
-        <v>2.61</v>
+        <v>2.62</v>
       </c>
       <c r="CT16" t="n">
-        <v>3.25</v>
+        <v>3.24</v>
       </c>
       <c r="CU16" t="n">
         <v>1.52</v>
       </c>
       <c r="CV16" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="CW16" t="n">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="CX16" t="n">
         <v>1.58</v>
@@ -7329,88 +7329,88 @@
         <v>1.94</v>
       </c>
       <c r="DB16" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="DC16" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="DD16" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="DE16" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="DF16" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="DG16" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="DH16" t="n">
+        <v>106.06</v>
+      </c>
+      <c r="DI16" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="DJ16" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="DK16" t="n">
+        <v>5.68</v>
+      </c>
+      <c r="DL16" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="DM16" t="n">
+        <v>52.63</v>
+      </c>
+      <c r="DN16" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="DO16" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="DP16" t="n">
+        <v>12.88</v>
+      </c>
+      <c r="DQ16" t="n">
+        <v>9.25</v>
+      </c>
+      <c r="DR16" t="n">
+        <v>5.94</v>
+      </c>
+      <c r="DS16" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="DT16" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="DU16" t="n">
+        <v>0</v>
+      </c>
+      <c r="DV16" t="n">
+        <v>53.69</v>
+      </c>
+      <c r="DW16" t="n">
+        <v>0</v>
+      </c>
+      <c r="DX16" t="n">
+        <v>15.63</v>
+      </c>
+      <c r="DY16" t="n">
+        <v>9.880000000000001</v>
+      </c>
+      <c r="DZ16" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="EA16" t="n">
+        <v>19.57</v>
+      </c>
+      <c r="EB16" t="n">
         <v>1.77</v>
       </c>
-      <c r="DD16" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="DE16" t="n">
-        <v>0.26</v>
-      </c>
-      <c r="DF16" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="DG16" t="n">
-        <v>3</v>
-      </c>
-      <c r="DH16" t="n">
-        <v>103.2</v>
-      </c>
-      <c r="DI16" t="n">
-        <v>0</v>
-      </c>
-      <c r="DJ16" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="DK16" t="n">
-        <v>5.93</v>
-      </c>
-      <c r="DL16" t="n">
-        <v>0.66</v>
-      </c>
-      <c r="DM16" t="n">
-        <v>51.07</v>
-      </c>
-      <c r="DN16" t="n">
-        <v>0.66</v>
-      </c>
-      <c r="DO16" t="n">
-        <v>2.94</v>
-      </c>
-      <c r="DP16" t="n">
-        <v>13</v>
-      </c>
-      <c r="DQ16" t="n">
-        <v>9.33</v>
-      </c>
-      <c r="DR16" t="n">
-        <v>5.86</v>
-      </c>
-      <c r="DS16" t="n">
-        <v>0.14</v>
-      </c>
-      <c r="DT16" t="n">
-        <v>0.14</v>
-      </c>
-      <c r="DU16" t="n">
-        <v>0</v>
-      </c>
-      <c r="DV16" t="n">
-        <v>53.27</v>
-      </c>
-      <c r="DW16" t="n">
-        <v>0</v>
-      </c>
-      <c r="DX16" t="n">
-        <v>16</v>
-      </c>
-      <c r="DY16" t="n">
-        <v>9.93</v>
-      </c>
-      <c r="DZ16" t="n">
-        <v>6.06</v>
-      </c>
-      <c r="EA16" t="n">
-        <v>19.07</v>
-      </c>
-      <c r="EB16" t="n">
-        <v>1.8</v>
-      </c>
       <c r="EC16" t="n">
-        <v>2.14</v>
+        <v>2.19</v>
       </c>
     </row>
     <row r="17">
@@ -7420,10 +7420,10 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C17" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D17" t="n">
         <v>8</v>
@@ -7432,82 +7432,82 @@
         <v>0</v>
       </c>
       <c r="F17" t="n">
-        <v>1.14</v>
+        <v>1</v>
       </c>
       <c r="G17" t="n">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="H17" t="n">
-        <v>94.86</v>
+        <v>92.62</v>
       </c>
       <c r="I17" t="n">
         <v>0</v>
       </c>
       <c r="J17" t="n">
-        <v>1.71</v>
+        <v>1.62</v>
       </c>
       <c r="K17" t="n">
-        <v>3.57</v>
+        <v>3.88</v>
       </c>
       <c r="L17" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="M17" t="n">
-        <v>39.29</v>
+        <v>38</v>
       </c>
       <c r="N17" t="n">
-        <v>0.43</v>
+        <v>0.5</v>
       </c>
       <c r="O17" t="n">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="P17" t="n">
-        <v>9.859999999999999</v>
+        <v>10.25</v>
       </c>
       <c r="Q17" t="n">
-        <v>13.29</v>
+        <v>13.12</v>
       </c>
       <c r="R17" t="n">
-        <v>11.29</v>
+        <v>11.5</v>
       </c>
       <c r="S17" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="T17" t="n">
-        <v>1.43</v>
+        <v>1.38</v>
       </c>
       <c r="U17" t="n">
-        <v>0.29</v>
+        <v>0.38</v>
       </c>
       <c r="V17" t="n">
-        <v>0.29</v>
+        <v>0.38</v>
       </c>
       <c r="W17" t="n">
         <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>42.57</v>
+        <v>43</v>
       </c>
       <c r="Y17" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="Z17" t="n">
-        <v>12.29</v>
+        <v>11.62</v>
       </c>
       <c r="AA17" t="n">
-        <v>7.71</v>
+        <v>7.38</v>
       </c>
       <c r="AB17" t="n">
-        <v>4.57</v>
+        <v>4.25</v>
       </c>
       <c r="AC17" t="n">
-        <v>20.29</v>
+        <v>21.62</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.39</v>
+        <v>1.31</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.43</v>
+        <v>1.38</v>
       </c>
       <c r="AF17" t="n">
         <v>0.12</v>
@@ -7591,67 +7591,67 @@
         <v>1.62</v>
       </c>
       <c r="BG17" t="n">
-        <v>2.8</v>
+        <v>2.75</v>
       </c>
       <c r="BH17" t="n">
-        <v>10.53</v>
+        <v>10.69</v>
       </c>
       <c r="BI17" t="n">
-        <v>2.8</v>
+        <v>2.75</v>
       </c>
       <c r="BJ17" t="n">
-        <v>0.73</v>
+        <v>0.75</v>
       </c>
       <c r="BK17" t="n">
-        <v>0.53</v>
+        <v>0.5</v>
       </c>
       <c r="BL17" t="n">
-        <v>0.73</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="BM17" t="n">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="BN17" t="n">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="BO17" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="BP17" t="n">
-        <v>3.8</v>
+        <v>3.88</v>
       </c>
       <c r="BQ17" t="n">
-        <v>5.87</v>
+        <v>6</v>
       </c>
       <c r="BR17" t="n">
-        <v>86.67</v>
+        <v>87.5</v>
       </c>
       <c r="BS17" t="n">
-        <v>80</v>
+        <v>81.25</v>
       </c>
       <c r="BT17" t="n">
-        <v>46.67</v>
+        <v>43.75</v>
       </c>
       <c r="BU17" t="n">
-        <v>40</v>
+        <v>37.5</v>
       </c>
       <c r="BV17" t="n">
-        <v>26.67</v>
+        <v>25</v>
       </c>
       <c r="BW17" t="n">
         <v>0</v>
       </c>
       <c r="BX17" t="n">
-        <v>60</v>
+        <v>62.5</v>
       </c>
       <c r="BY17" t="n">
-        <v>3.17</v>
+        <v>3.12</v>
       </c>
       <c r="BZ17" t="n">
-        <v>3.44</v>
+        <v>3.41</v>
       </c>
       <c r="CA17" t="n">
-        <v>3.75</v>
+        <v>3.72</v>
       </c>
       <c r="CB17" t="n">
         <v>3.74</v>
@@ -7675,31 +7675,31 @@
         <v>1.52</v>
       </c>
       <c r="CI17" t="n">
-        <v>2.21</v>
+        <v>2.23</v>
       </c>
       <c r="CJ17" t="n">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="CK17" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="CL17" t="n">
         <v>1.78</v>
       </c>
       <c r="CM17" t="n">
-        <v>2.7</v>
+        <v>2.71</v>
       </c>
       <c r="CN17" t="n">
-        <v>2.07</v>
+        <v>2.08</v>
       </c>
       <c r="CO17" t="n">
         <v>1.2</v>
       </c>
       <c r="CP17" t="n">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="CQ17" t="n">
-        <v>2.71</v>
+        <v>2.69</v>
       </c>
       <c r="CR17" t="n">
         <v>1.36</v>
@@ -7714,7 +7714,7 @@
         <v>1.53</v>
       </c>
       <c r="CV17" t="n">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="CW17" t="n">
         <v>1.64</v>
@@ -7723,7 +7723,7 @@
         <v>1.53</v>
       </c>
       <c r="CY17" t="n">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="CZ17" t="n">
         <v>2.45</v>
@@ -7735,85 +7735,85 @@
         <v>1.23</v>
       </c>
       <c r="DC17" t="n">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="DD17" t="n">
-        <v>2.81</v>
+        <v>2.79</v>
       </c>
       <c r="DE17" t="n">
         <v>0.06</v>
       </c>
       <c r="DF17" t="n">
-        <v>1.27</v>
+        <v>1.19</v>
       </c>
       <c r="DG17" t="n">
-        <v>2.2</v>
+        <v>2.32</v>
       </c>
       <c r="DH17" t="n">
-        <v>91.40000000000001</v>
+        <v>90.5</v>
       </c>
       <c r="DI17" t="n">
         <v>0.06</v>
       </c>
       <c r="DJ17" t="n">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="DK17" t="n">
-        <v>4.13</v>
+        <v>4.25</v>
       </c>
       <c r="DL17" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="DM17" t="n">
-        <v>44.34</v>
+        <v>43.38</v>
       </c>
       <c r="DN17" t="n">
-        <v>0.4</v>
+        <v>0.44</v>
       </c>
       <c r="DO17" t="n">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="DP17" t="n">
-        <v>11.8</v>
+        <v>11.88</v>
       </c>
       <c r="DQ17" t="n">
-        <v>11.07</v>
+        <v>11.12</v>
       </c>
       <c r="DR17" t="n">
-        <v>10.54</v>
+        <v>10.69</v>
       </c>
       <c r="DS17" t="n">
-        <v>0.2</v>
+        <v>0.25</v>
       </c>
       <c r="DT17" t="n">
-        <v>0.2</v>
+        <v>0.25</v>
       </c>
       <c r="DU17" t="n">
         <v>0</v>
       </c>
       <c r="DV17" t="n">
-        <v>45</v>
+        <v>45.06</v>
       </c>
       <c r="DW17" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="DX17" t="n">
-        <v>11.87</v>
+        <v>11.56</v>
       </c>
       <c r="DY17" t="n">
-        <v>7.6</v>
+        <v>7.44</v>
       </c>
       <c r="DZ17" t="n">
-        <v>4.27</v>
+        <v>4.12</v>
       </c>
       <c r="EA17" t="n">
-        <v>19.93</v>
+        <v>20.62</v>
       </c>
       <c r="EB17" t="n">
-        <v>1.37</v>
+        <v>1.34</v>
       </c>
       <c r="EC17" t="n">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
     </row>
   </sheetData>

--- a/data/teams/leagues/Averages_Belgium_Pro_League_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Belgium_Pro_League_2025-2026.xlsx
@@ -1532,19 +1532,19 @@
         <v>0.12</v>
       </c>
       <c r="BA2" t="n">
-        <v>12.75</v>
+        <v>12.62</v>
       </c>
       <c r="BB2" t="n">
         <v>9</v>
       </c>
       <c r="BC2" t="n">
-        <v>3.75</v>
+        <v>3.62</v>
       </c>
       <c r="BD2" t="n">
         <v>23.12</v>
       </c>
       <c r="BE2" t="n">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="BF2" t="n">
         <v>2.38</v>
@@ -1757,19 +1757,19 @@
         <v>0.06</v>
       </c>
       <c r="DX2" t="n">
-        <v>13.93</v>
+        <v>13.87</v>
       </c>
       <c r="DY2" t="n">
         <v>9.69</v>
       </c>
       <c r="DZ2" t="n">
-        <v>4.25</v>
+        <v>4.19</v>
       </c>
       <c r="EA2" t="n">
         <v>23.37</v>
       </c>
       <c r="EB2" t="n">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="EC2" t="n">
         <v>1.88</v>
@@ -1848,7 +1848,7 @@
         <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>64.75</v>
+        <v>64.88</v>
       </c>
       <c r="Y3" t="n">
         <v>0.12</v>
@@ -2154,7 +2154,7 @@
         <v>0</v>
       </c>
       <c r="DV3" t="n">
-        <v>62.75</v>
+        <v>62.82</v>
       </c>
       <c r="DW3" t="n">
         <v>0.06</v>
@@ -5552,7 +5552,7 @@
         <v>0</v>
       </c>
       <c r="AY12" t="n">
-        <v>43.75</v>
+        <v>43.62</v>
       </c>
       <c r="AZ12" t="n">
         <v>0.12</v>
@@ -5777,7 +5777,7 @@
         <v>0</v>
       </c>
       <c r="DV12" t="n">
-        <v>48.62</v>
+        <v>48.56</v>
       </c>
       <c r="DW12" t="n">
         <v>0.12</v>
@@ -6283,19 +6283,19 @@
         <v>0.25</v>
       </c>
       <c r="Z14" t="n">
-        <v>11</v>
+        <v>10.88</v>
       </c>
       <c r="AA14" t="n">
         <v>6.62</v>
       </c>
       <c r="AB14" t="n">
-        <v>4.38</v>
+        <v>4.25</v>
       </c>
       <c r="AC14" t="n">
         <v>18</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="AE14" t="n">
         <v>1.88</v>
@@ -6589,13 +6589,13 @@
         <v>0.12</v>
       </c>
       <c r="DX14" t="n">
-        <v>11.06</v>
+        <v>11</v>
       </c>
       <c r="DY14" t="n">
         <v>6.81</v>
       </c>
       <c r="DZ14" t="n">
-        <v>4.25</v>
+        <v>4.19</v>
       </c>
       <c r="EA14" t="n">
         <v>19.88</v>
@@ -7110,7 +7110,7 @@
         <v>0.11</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.67</v>
+        <v>1.78</v>
       </c>
       <c r="AH16" t="n">
         <v>2.78</v>
@@ -7122,7 +7122,7 @@
         <v>0.11</v>
       </c>
       <c r="AK16" t="n">
-        <v>2.89</v>
+        <v>3</v>
       </c>
       <c r="AL16" t="n">
         <v>5.33</v>
@@ -7185,7 +7185,7 @@
         <v>1.59</v>
       </c>
       <c r="BF16" t="n">
-        <v>2.89</v>
+        <v>3</v>
       </c>
       <c r="BG16" t="n">
         <v>2.5</v>
@@ -7341,7 +7341,7 @@
         <v>0.25</v>
       </c>
       <c r="DF16" t="n">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="DG16" t="n">
         <v>2.94</v>
@@ -7353,7 +7353,7 @@
         <v>0.06</v>
       </c>
       <c r="DJ16" t="n">
-        <v>2.19</v>
+        <v>2.25</v>
       </c>
       <c r="DK16" t="n">
         <v>5.68</v>
@@ -7410,7 +7410,7 @@
         <v>1.77</v>
       </c>
       <c r="EC16" t="n">
-        <v>2.19</v>
+        <v>2.25</v>
       </c>
     </row>
     <row r="17">

--- a/data/teams/leagues/Averages_Belgium_Pro_League_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Belgium_Pro_League_2025-2026.xlsx
@@ -2185,13 +2185,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C4" t="n">
         <v>8</v>
       </c>
       <c r="D4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
@@ -2275,130 +2275,130 @@
         <v>1.38</v>
       </c>
       <c r="AF4" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.62</v>
+        <v>1.56</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.38</v>
+        <v>1.22</v>
       </c>
       <c r="AI4" t="n">
-        <v>90.38</v>
+        <v>88.44</v>
       </c>
       <c r="AJ4" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="AK4" t="n">
-        <v>2.5</v>
+        <v>2.33</v>
       </c>
       <c r="AL4" t="n">
-        <v>3.12</v>
+        <v>3</v>
       </c>
       <c r="AM4" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="AN4" t="n">
-        <v>36.88</v>
+        <v>37.22</v>
       </c>
       <c r="AO4" t="n">
-        <v>0.62</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AP4" t="n">
-        <v>1.75</v>
+        <v>1.78</v>
       </c>
       <c r="AQ4" t="n">
-        <v>12.25</v>
+        <v>11.78</v>
       </c>
       <c r="AR4" t="n">
-        <v>12.12</v>
+        <v>11.67</v>
       </c>
       <c r="AS4" t="n">
-        <v>10.12</v>
+        <v>10.78</v>
       </c>
       <c r="AT4" t="n">
-        <v>1.88</v>
+        <v>1.78</v>
       </c>
       <c r="AU4" t="n">
-        <v>0.88</v>
+        <v>1</v>
       </c>
       <c r="AV4" t="n">
-        <v>0</v>
+        <v>0.11</v>
       </c>
       <c r="AW4" t="n">
-        <v>0</v>
+        <v>0.11</v>
       </c>
       <c r="AX4" t="n">
         <v>0</v>
       </c>
       <c r="AY4" t="n">
-        <v>42.5</v>
+        <v>43.33</v>
       </c>
       <c r="AZ4" t="n">
-        <v>0.38</v>
+        <v>0.33</v>
       </c>
       <c r="BA4" t="n">
-        <v>10.38</v>
+        <v>10.78</v>
       </c>
       <c r="BB4" t="n">
-        <v>6.5</v>
+        <v>6.67</v>
       </c>
       <c r="BC4" t="n">
-        <v>3.88</v>
+        <v>4.11</v>
       </c>
       <c r="BD4" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="BE4" t="n">
-        <v>1.2</v>
+        <v>1.24</v>
       </c>
       <c r="BF4" t="n">
-        <v>1.88</v>
+        <v>1.78</v>
       </c>
       <c r="BG4" t="n">
-        <v>2.38</v>
+        <v>2.41</v>
       </c>
       <c r="BH4" t="n">
-        <v>8.44</v>
+        <v>8.35</v>
       </c>
       <c r="BI4" t="n">
-        <v>2.38</v>
+        <v>2.41</v>
       </c>
       <c r="BJ4" t="n">
-        <v>0.5</v>
+        <v>0.53</v>
       </c>
       <c r="BK4" t="n">
-        <v>0.19</v>
+        <v>0.24</v>
       </c>
       <c r="BL4" t="n">
-        <v>0.75</v>
+        <v>0.71</v>
       </c>
       <c r="BM4" t="n">
         <v>0.9399999999999999</v>
       </c>
       <c r="BN4" t="n">
-        <v>1.69</v>
+        <v>1.65</v>
       </c>
       <c r="BO4" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.76</v>
       </c>
       <c r="BP4" t="n">
-        <v>3.5</v>
+        <v>3.65</v>
       </c>
       <c r="BQ4" t="n">
-        <v>4.12</v>
+        <v>3.94</v>
       </c>
       <c r="BR4" t="n">
-        <v>87.5</v>
+        <v>88.23999999999999</v>
       </c>
       <c r="BS4" t="n">
-        <v>75</v>
+        <v>76.47</v>
       </c>
       <c r="BT4" t="n">
-        <v>50</v>
+        <v>52.94</v>
       </c>
       <c r="BU4" t="n">
-        <v>25</v>
+        <v>23.53</v>
       </c>
       <c r="BV4" t="n">
         <v>0</v>
@@ -2407,7 +2407,7 @@
         <v>0</v>
       </c>
       <c r="BX4" t="n">
-        <v>56.25</v>
+        <v>58.82</v>
       </c>
       <c r="BY4" t="n">
         <v>3.33</v>
@@ -2416,169 +2416,169 @@
         <v>3.41</v>
       </c>
       <c r="CA4" t="n">
-        <v>3.72</v>
+        <v>3.69</v>
       </c>
       <c r="CB4" t="n">
-        <v>3.93</v>
+        <v>3.88</v>
       </c>
       <c r="CC4" t="n">
-        <v>4.87</v>
+        <v>4.74</v>
       </c>
       <c r="CD4" t="n">
-        <v>5.33</v>
+        <v>5.16</v>
       </c>
       <c r="CE4" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="CF4" t="n">
-        <v>2.54</v>
+        <v>2.56</v>
       </c>
       <c r="CG4" t="n">
-        <v>3.13</v>
+        <v>3.11</v>
       </c>
       <c r="CH4" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="CI4" t="n">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="CJ4" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="CK4" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="CL4" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="CM4" t="n">
-        <v>2.38</v>
+        <v>2.37</v>
       </c>
       <c r="CN4" t="n">
         <v>1.85</v>
       </c>
       <c r="CO4" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="CP4" t="n">
-        <v>1.82</v>
+        <v>1.85</v>
       </c>
       <c r="CQ4" t="n">
-        <v>3</v>
+        <v>3.08</v>
       </c>
       <c r="CR4" t="n">
         <v>1.38</v>
       </c>
       <c r="CS4" t="n">
-        <v>2.71</v>
+        <v>2.74</v>
       </c>
       <c r="CT4" t="n">
-        <v>3.13</v>
+        <v>3.1</v>
       </c>
       <c r="CU4" t="n">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="CV4" t="n">
-        <v>2.17</v>
+        <v>2.16</v>
       </c>
       <c r="CW4" t="n">
         <v>1.75</v>
       </c>
       <c r="CX4" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="CY4" t="n">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="CZ4" t="n">
-        <v>2.39</v>
+        <v>2.37</v>
       </c>
       <c r="DA4" t="n">
-        <v>1.9</v>
+        <v>1.88</v>
       </c>
       <c r="DB4" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="DC4" t="n">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="DD4" t="n">
-        <v>3.03</v>
+        <v>3.09</v>
       </c>
       <c r="DE4" t="n">
         <v>0.12</v>
       </c>
       <c r="DF4" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="DG4" t="n">
-        <v>1.19</v>
+        <v>1.12</v>
       </c>
       <c r="DH4" t="n">
-        <v>91.81999999999999</v>
+        <v>90.7</v>
       </c>
       <c r="DI4" t="n">
         <v>0</v>
       </c>
       <c r="DJ4" t="n">
-        <v>1.94</v>
+        <v>1.88</v>
       </c>
       <c r="DK4" t="n">
-        <v>3.18</v>
+        <v>3.12</v>
       </c>
       <c r="DL4" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DM4" t="n">
         <v>40.06</v>
       </c>
       <c r="DN4" t="n">
-        <v>0.5</v>
+        <v>0.48</v>
       </c>
       <c r="DO4" t="n">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="DP4" t="n">
-        <v>11</v>
+        <v>10.82</v>
       </c>
       <c r="DQ4" t="n">
-        <v>12.18</v>
+        <v>11.94</v>
       </c>
       <c r="DR4" t="n">
-        <v>10.31</v>
+        <v>10.65</v>
       </c>
       <c r="DS4" t="n">
-        <v>0.06</v>
+        <v>0.11</v>
       </c>
       <c r="DT4" t="n">
-        <v>0.06</v>
+        <v>0.11</v>
       </c>
       <c r="DU4" t="n">
         <v>0</v>
       </c>
       <c r="DV4" t="n">
-        <v>46.5</v>
+        <v>46.7</v>
       </c>
       <c r="DW4" t="n">
-        <v>0.19</v>
+        <v>0.17</v>
       </c>
       <c r="DX4" t="n">
-        <v>10.13</v>
+        <v>10.36</v>
       </c>
       <c r="DY4" t="n">
-        <v>6.5</v>
+        <v>6.59</v>
       </c>
       <c r="DZ4" t="n">
-        <v>3.63</v>
+        <v>3.77</v>
       </c>
       <c r="EA4" t="n">
-        <v>20.69</v>
+        <v>20.77</v>
       </c>
       <c r="EB4" t="n">
-        <v>1.19</v>
+        <v>1.21</v>
       </c>
       <c r="EC4" t="n">
-        <v>1.63</v>
+        <v>1.59</v>
       </c>
     </row>
     <row r="5">
@@ -4599,10 +4599,10 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C10" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D10" t="n">
         <v>8</v>
@@ -4611,49 +4611,49 @@
         <v>0</v>
       </c>
       <c r="F10" t="n">
-        <v>1</v>
+        <v>0.89</v>
       </c>
       <c r="G10" t="n">
-        <v>2.75</v>
+        <v>2.56</v>
       </c>
       <c r="H10" t="n">
-        <v>74.12</v>
+        <v>79.22</v>
       </c>
       <c r="I10" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="J10" t="n">
-        <v>1.75</v>
+        <v>1.67</v>
       </c>
       <c r="K10" t="n">
         <v>5</v>
       </c>
       <c r="L10" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="M10" t="n">
-        <v>40.38</v>
+        <v>43.33</v>
       </c>
       <c r="N10" t="n">
-        <v>0.75</v>
+        <v>0.78</v>
       </c>
       <c r="O10" t="n">
-        <v>2.25</v>
+        <v>2.44</v>
       </c>
       <c r="P10" t="n">
-        <v>11.75</v>
+        <v>11.44</v>
       </c>
       <c r="Q10" t="n">
-        <v>11.75</v>
+        <v>11.33</v>
       </c>
       <c r="R10" t="n">
-        <v>9.119999999999999</v>
+        <v>8.779999999999999</v>
       </c>
       <c r="S10" t="n">
-        <v>0.5</v>
+        <v>0.67</v>
       </c>
       <c r="T10" t="n">
-        <v>0.5</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="U10" t="n">
         <v>0</v>
@@ -4665,28 +4665,28 @@
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>35.12</v>
+        <v>36.78</v>
       </c>
       <c r="Y10" t="n">
         <v>0</v>
       </c>
       <c r="Z10" t="n">
-        <v>10</v>
+        <v>10.67</v>
       </c>
       <c r="AA10" t="n">
-        <v>7.38</v>
+        <v>7.89</v>
       </c>
       <c r="AB10" t="n">
-        <v>2.62</v>
+        <v>2.78</v>
       </c>
       <c r="AC10" t="n">
-        <v>20.12</v>
+        <v>21</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.04</v>
+        <v>1.12</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.75</v>
+        <v>1.67</v>
       </c>
       <c r="AF10" t="n">
         <v>0.12</v>
@@ -4770,70 +4770,70 @@
         <v>1.88</v>
       </c>
       <c r="BG10" t="n">
-        <v>1.62</v>
+        <v>1.71</v>
       </c>
       <c r="BH10" t="n">
-        <v>8.5</v>
+        <v>8.41</v>
       </c>
       <c r="BI10" t="n">
-        <v>1.62</v>
+        <v>1.71</v>
       </c>
       <c r="BJ10" t="n">
-        <v>0.44</v>
+        <v>0.47</v>
       </c>
       <c r="BK10" t="n">
-        <v>0.31</v>
+        <v>0.35</v>
       </c>
       <c r="BL10" t="n">
-        <v>0.5</v>
+        <v>0.47</v>
       </c>
       <c r="BM10" t="n">
-        <v>0.38</v>
+        <v>0.41</v>
       </c>
       <c r="BN10" t="n">
         <v>0.88</v>
       </c>
       <c r="BO10" t="n">
-        <v>0.75</v>
+        <v>0.82</v>
       </c>
       <c r="BP10" t="n">
-        <v>3.38</v>
+        <v>3.53</v>
       </c>
       <c r="BQ10" t="n">
-        <v>5.12</v>
+        <v>4.88</v>
       </c>
       <c r="BR10" t="n">
-        <v>68.75</v>
+        <v>70.59</v>
       </c>
       <c r="BS10" t="n">
-        <v>43.75</v>
+        <v>47.06</v>
       </c>
       <c r="BT10" t="n">
-        <v>31.25</v>
+        <v>35.29</v>
       </c>
       <c r="BU10" t="n">
-        <v>12.5</v>
+        <v>11.76</v>
       </c>
       <c r="BV10" t="n">
-        <v>6.25</v>
+        <v>5.88</v>
       </c>
       <c r="BW10" t="n">
         <v>0</v>
       </c>
       <c r="BX10" t="n">
-        <v>37.5</v>
+        <v>41.18</v>
       </c>
       <c r="BY10" t="n">
+        <v>3.64</v>
+      </c>
+      <c r="BZ10" t="n">
         <v>3.82</v>
       </c>
-      <c r="BZ10" t="n">
-        <v>4.01</v>
-      </c>
       <c r="CA10" t="n">
-        <v>3.51</v>
+        <v>3.49</v>
       </c>
       <c r="CB10" t="n">
-        <v>3.57</v>
+        <v>3.54</v>
       </c>
       <c r="CC10" t="n">
         <v>4.16</v>
@@ -4845,16 +4845,16 @@
         <v>1.39</v>
       </c>
       <c r="CF10" t="n">
-        <v>2.79</v>
+        <v>2.8</v>
       </c>
       <c r="CG10" t="n">
-        <v>2.85</v>
+        <v>2.84</v>
       </c>
       <c r="CH10" t="n">
         <v>1.39</v>
       </c>
       <c r="CI10" t="n">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="CJ10" t="n">
         <v>1.87</v>
@@ -4863,10 +4863,10 @@
         <v>1.58</v>
       </c>
       <c r="CL10" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="CM10" t="n">
-        <v>2.32</v>
+        <v>2.31</v>
       </c>
       <c r="CN10" t="n">
         <v>1.81</v>
@@ -4875,25 +4875,25 @@
         <v>1.31</v>
       </c>
       <c r="CP10" t="n">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="CQ10" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="CR10" t="n">
         <v>1.41</v>
       </c>
       <c r="CS10" t="n">
-        <v>2.96</v>
+        <v>2.98</v>
       </c>
       <c r="CT10" t="n">
-        <v>3</v>
+        <v>2.99</v>
       </c>
       <c r="CU10" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="CV10" t="n">
-        <v>2.01</v>
+        <v>2</v>
       </c>
       <c r="CW10" t="n">
         <v>1.87</v>
@@ -4902,64 +4902,64 @@
         <v>1.62</v>
       </c>
       <c r="CY10" t="n">
-        <v>2.03</v>
+        <v>2.04</v>
       </c>
       <c r="CZ10" t="n">
-        <v>2.29</v>
+        <v>2.28</v>
       </c>
       <c r="DA10" t="n">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="DB10" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="DC10" t="n">
-        <v>2.07</v>
+        <v>2.08</v>
       </c>
       <c r="DD10" t="n">
-        <v>3.59</v>
+        <v>3.62</v>
       </c>
       <c r="DE10" t="n">
         <v>0.06</v>
       </c>
       <c r="DF10" t="n">
-        <v>1.12</v>
+        <v>1.06</v>
       </c>
       <c r="DG10" t="n">
-        <v>2.44</v>
+        <v>2.35</v>
       </c>
       <c r="DH10" t="n">
-        <v>77.75</v>
+        <v>80.23999999999999</v>
       </c>
       <c r="DI10" t="n">
         <v>0.12</v>
       </c>
       <c r="DJ10" t="n">
-        <v>1.94</v>
+        <v>1.88</v>
       </c>
       <c r="DK10" t="n">
-        <v>4.25</v>
+        <v>4.29</v>
       </c>
       <c r="DL10" t="n">
         <v>0.18</v>
       </c>
       <c r="DM10" t="n">
-        <v>37.19</v>
+        <v>38.94</v>
       </c>
       <c r="DN10" t="n">
-        <v>0.75</v>
+        <v>0.77</v>
       </c>
       <c r="DO10" t="n">
-        <v>1.82</v>
+        <v>1.94</v>
       </c>
       <c r="DP10" t="n">
-        <v>12.43</v>
+        <v>12.23</v>
       </c>
       <c r="DQ10" t="n">
-        <v>12.57</v>
+        <v>12.29</v>
       </c>
       <c r="DR10" t="n">
-        <v>9.31</v>
+        <v>9.119999999999999</v>
       </c>
       <c r="DS10" t="n">
         <v>0</v>
@@ -4971,28 +4971,28 @@
         <v>0</v>
       </c>
       <c r="DV10" t="n">
-        <v>33.25</v>
+        <v>34.24</v>
       </c>
       <c r="DW10" t="n">
         <v>0.06</v>
       </c>
       <c r="DX10" t="n">
-        <v>9</v>
+        <v>9.41</v>
       </c>
       <c r="DY10" t="n">
-        <v>6.63</v>
+        <v>6.94</v>
       </c>
       <c r="DZ10" t="n">
-        <v>2.37</v>
+        <v>2.47</v>
       </c>
       <c r="EA10" t="n">
-        <v>21.06</v>
+        <v>21.47</v>
       </c>
       <c r="EB10" t="n">
-        <v>0.98</v>
+        <v>1.02</v>
       </c>
       <c r="EC10" t="n">
-        <v>1.82</v>
+        <v>1.77</v>
       </c>
     </row>
     <row r="11">

--- a/data/teams/leagues/Averages_Belgium_Pro_League_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Belgium_Pro_League_2025-2026.xlsx
@@ -1379,10 +1379,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D2" t="n">
         <v>8</v>
@@ -1391,82 +1391,82 @@
         <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>0.88</v>
+        <v>0.78</v>
       </c>
       <c r="G2" t="n">
-        <v>2.62</v>
+        <v>2.89</v>
       </c>
       <c r="H2" t="n">
-        <v>107.75</v>
+        <v>108.78</v>
       </c>
       <c r="I2" t="n">
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>1.38</v>
+        <v>1.22</v>
       </c>
       <c r="K2" t="n">
-        <v>4.38</v>
+        <v>4.89</v>
       </c>
       <c r="L2" t="n">
-        <v>0.25</v>
+        <v>0.44</v>
       </c>
       <c r="M2" t="n">
-        <v>47.75</v>
+        <v>50.11</v>
       </c>
       <c r="N2" t="n">
-        <v>0.5</v>
+        <v>0.44</v>
       </c>
       <c r="O2" t="n">
-        <v>1.75</v>
+        <v>2</v>
       </c>
       <c r="P2" t="n">
-        <v>8.619999999999999</v>
+        <v>8.44</v>
       </c>
       <c r="Q2" t="n">
-        <v>13.25</v>
+        <v>13.56</v>
       </c>
       <c r="R2" t="n">
-        <v>7.25</v>
+        <v>7</v>
       </c>
       <c r="S2" t="n">
         <v>2</v>
       </c>
       <c r="T2" t="n">
-        <v>1.62</v>
+        <v>1.56</v>
       </c>
       <c r="U2" t="n">
-        <v>0.5</v>
+        <v>0.44</v>
       </c>
       <c r="V2" t="n">
-        <v>0.5</v>
+        <v>0.44</v>
       </c>
       <c r="W2" t="n">
         <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>51.62</v>
+        <v>53.11</v>
       </c>
       <c r="Y2" t="n">
         <v>0</v>
       </c>
       <c r="Z2" t="n">
-        <v>15.12</v>
+        <v>15.11</v>
       </c>
       <c r="AA2" t="n">
-        <v>10.38</v>
+        <v>10.22</v>
       </c>
       <c r="AB2" t="n">
-        <v>4.75</v>
+        <v>4.89</v>
       </c>
       <c r="AC2" t="n">
-        <v>23.62</v>
+        <v>24.56</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.64</v>
+        <v>1.66</v>
       </c>
       <c r="AE2" t="n">
-        <v>1.38</v>
+        <v>1.22</v>
       </c>
       <c r="AF2" t="n">
         <v>0</v>
@@ -1550,70 +1550,70 @@
         <v>2.38</v>
       </c>
       <c r="BG2" t="n">
-        <v>2.69</v>
+        <v>2.71</v>
       </c>
       <c r="BH2" t="n">
-        <v>9.619999999999999</v>
+        <v>9.880000000000001</v>
       </c>
       <c r="BI2" t="n">
-        <v>2.69</v>
+        <v>2.71</v>
       </c>
       <c r="BJ2" t="n">
-        <v>0.75</v>
+        <v>0.71</v>
       </c>
       <c r="BK2" t="n">
-        <v>0.75</v>
+        <v>0.82</v>
       </c>
       <c r="BL2" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.59</v>
       </c>
       <c r="BM2" t="n">
-        <v>0.62</v>
+        <v>0.59</v>
       </c>
       <c r="BN2" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="BO2" t="n">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="BP2" t="n">
-        <v>4.19</v>
+        <v>4.41</v>
       </c>
       <c r="BQ2" t="n">
-        <v>5.44</v>
+        <v>5.47</v>
       </c>
       <c r="BR2" t="n">
-        <v>87.5</v>
+        <v>88.23999999999999</v>
       </c>
       <c r="BS2" t="n">
-        <v>87.5</v>
+        <v>88.23999999999999</v>
       </c>
       <c r="BT2" t="n">
-        <v>43.75</v>
+        <v>47.06</v>
       </c>
       <c r="BU2" t="n">
-        <v>25</v>
+        <v>23.53</v>
       </c>
       <c r="BV2" t="n">
-        <v>18.75</v>
+        <v>17.65</v>
       </c>
       <c r="BW2" t="n">
-        <v>6.25</v>
+        <v>5.88</v>
       </c>
       <c r="BX2" t="n">
-        <v>62.5</v>
+        <v>64.70999999999999</v>
       </c>
       <c r="BY2" t="n">
-        <v>2.36</v>
+        <v>2.31</v>
       </c>
       <c r="BZ2" t="n">
-        <v>2.42</v>
+        <v>2.38</v>
       </c>
       <c r="CA2" t="n">
         <v>3.52</v>
       </c>
       <c r="CB2" t="n">
-        <v>3.71</v>
+        <v>3.69</v>
       </c>
       <c r="CC2" t="n">
         <v>3.51</v>
@@ -1625,37 +1625,37 @@
         <v>1.31</v>
       </c>
       <c r="CF2" t="n">
-        <v>2.51</v>
+        <v>2.52</v>
       </c>
       <c r="CG2" t="n">
-        <v>3.17</v>
+        <v>3.15</v>
       </c>
       <c r="CH2" t="n">
         <v>1.48</v>
       </c>
       <c r="CI2" t="n">
-        <v>2.19</v>
+        <v>2.18</v>
       </c>
       <c r="CJ2" t="n">
         <v>1.66</v>
       </c>
       <c r="CK2" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="CL2" t="n">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="CM2" t="n">
-        <v>2.6</v>
+        <v>2.58</v>
       </c>
       <c r="CN2" t="n">
-        <v>2.01</v>
+        <v>2</v>
       </c>
       <c r="CO2" t="n">
         <v>1.22</v>
       </c>
       <c r="CP2" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="CQ2" t="n">
         <v>2.89</v>
@@ -1664,31 +1664,31 @@
         <v>1.36</v>
       </c>
       <c r="CS2" t="n">
-        <v>2.6</v>
+        <v>2.61</v>
       </c>
       <c r="CT2" t="n">
         <v>3.23</v>
       </c>
       <c r="CU2" t="n">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="CV2" t="n">
-        <v>2.33</v>
+        <v>2.32</v>
       </c>
       <c r="CW2" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="CX2" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="CY2" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="CZ2" t="n">
-        <v>2.55</v>
+        <v>2.52</v>
       </c>
       <c r="DA2" t="n">
-        <v>2.08</v>
+        <v>2.07</v>
       </c>
       <c r="DB2" t="n">
         <v>1.23</v>
@@ -1703,76 +1703,76 @@
         <v>0</v>
       </c>
       <c r="DF2" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.88</v>
       </c>
       <c r="DG2" t="n">
-        <v>2.56</v>
+        <v>2.71</v>
       </c>
       <c r="DH2" t="n">
-        <v>108.32</v>
+        <v>108.83</v>
       </c>
       <c r="DI2" t="n">
         <v>0.06</v>
       </c>
       <c r="DJ2" t="n">
-        <v>2</v>
+        <v>1.88</v>
       </c>
       <c r="DK2" t="n">
-        <v>4.5</v>
+        <v>4.76</v>
       </c>
       <c r="DL2" t="n">
-        <v>0.44</v>
+        <v>0.52</v>
       </c>
       <c r="DM2" t="n">
-        <v>50.56</v>
+        <v>51.65</v>
       </c>
       <c r="DN2" t="n">
-        <v>1</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="DO2" t="n">
-        <v>1.94</v>
+        <v>2.06</v>
       </c>
       <c r="DP2" t="n">
-        <v>10.56</v>
+        <v>10.35</v>
       </c>
       <c r="DQ2" t="n">
-        <v>12.32</v>
+        <v>12.53</v>
       </c>
       <c r="DR2" t="n">
-        <v>7.18</v>
+        <v>7.06</v>
       </c>
       <c r="DS2" t="n">
-        <v>0.25</v>
+        <v>0.23</v>
       </c>
       <c r="DT2" t="n">
-        <v>0.25</v>
+        <v>0.23</v>
       </c>
       <c r="DU2" t="n">
         <v>0</v>
       </c>
       <c r="DV2" t="n">
-        <v>50.75</v>
+        <v>51.59</v>
       </c>
       <c r="DW2" t="n">
         <v>0.06</v>
       </c>
       <c r="DX2" t="n">
-        <v>13.87</v>
+        <v>13.94</v>
       </c>
       <c r="DY2" t="n">
-        <v>9.69</v>
+        <v>9.65</v>
       </c>
       <c r="DZ2" t="n">
-        <v>4.19</v>
+        <v>4.29</v>
       </c>
       <c r="EA2" t="n">
-        <v>23.37</v>
+        <v>23.88</v>
       </c>
       <c r="EB2" t="n">
-        <v>1.54</v>
+        <v>1.56</v>
       </c>
       <c r="EC2" t="n">
-        <v>1.88</v>
+        <v>1.77</v>
       </c>
     </row>
     <row r="3">
@@ -1782,13 +1782,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C3" t="n">
         <v>8</v>
       </c>
       <c r="D3" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
@@ -1872,52 +1872,52 @@
         <v>1.25</v>
       </c>
       <c r="AF3" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="AH3" t="n">
-        <v>4.12</v>
+        <v>4.22</v>
       </c>
       <c r="AI3" t="n">
-        <v>107.12</v>
+        <v>107.89</v>
       </c>
       <c r="AJ3" t="n">
         <v>0</v>
       </c>
       <c r="AK3" t="n">
-        <v>1.62</v>
+        <v>1.56</v>
       </c>
       <c r="AL3" t="n">
-        <v>6.75</v>
+        <v>6.67</v>
       </c>
       <c r="AM3" t="n">
-        <v>0.12</v>
+        <v>0.22</v>
       </c>
       <c r="AN3" t="n">
-        <v>57.88</v>
+        <v>56</v>
       </c>
       <c r="AO3" t="n">
-        <v>0.5</v>
+        <v>0.44</v>
       </c>
       <c r="AP3" t="n">
-        <v>2.62</v>
+        <v>2.44</v>
       </c>
       <c r="AQ3" t="n">
-        <v>9.5</v>
+        <v>9.44</v>
       </c>
       <c r="AR3" t="n">
-        <v>12.5</v>
+        <v>11.89</v>
       </c>
       <c r="AS3" t="n">
-        <v>7.5</v>
+        <v>8</v>
       </c>
       <c r="AT3" t="n">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="AU3" t="n">
-        <v>0.88</v>
+        <v>1</v>
       </c>
       <c r="AV3" t="n">
         <v>0</v>
@@ -1929,82 +1929,82 @@
         <v>0</v>
       </c>
       <c r="AY3" t="n">
-        <v>60.75</v>
+        <v>60.33</v>
       </c>
       <c r="AZ3" t="n">
         <v>0</v>
       </c>
       <c r="BA3" t="n">
-        <v>15</v>
+        <v>15.44</v>
       </c>
       <c r="BB3" t="n">
-        <v>10.25</v>
+        <v>10.33</v>
       </c>
       <c r="BC3" t="n">
-        <v>4.75</v>
+        <v>5.11</v>
       </c>
       <c r="BD3" t="n">
-        <v>18.5</v>
+        <v>17.89</v>
       </c>
       <c r="BE3" t="n">
-        <v>1.7</v>
+        <v>1.74</v>
       </c>
       <c r="BF3" t="n">
-        <v>1.62</v>
+        <v>1.56</v>
       </c>
       <c r="BG3" t="n">
-        <v>2.25</v>
+        <v>2.41</v>
       </c>
       <c r="BH3" t="n">
-        <v>11.31</v>
+        <v>11.47</v>
       </c>
       <c r="BI3" t="n">
-        <v>2.25</v>
+        <v>2.41</v>
       </c>
       <c r="BJ3" t="n">
-        <v>0.5</v>
+        <v>0.59</v>
       </c>
       <c r="BK3" t="n">
-        <v>0.31</v>
+        <v>0.35</v>
       </c>
       <c r="BL3" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.82</v>
       </c>
       <c r="BM3" t="n">
-        <v>0.62</v>
+        <v>0.65</v>
       </c>
       <c r="BN3" t="n">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="BO3" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="BP3" t="n">
-        <v>5.25</v>
+        <v>5.18</v>
       </c>
       <c r="BQ3" t="n">
-        <v>6.06</v>
+        <v>6.29</v>
       </c>
       <c r="BR3" t="n">
         <v>100</v>
       </c>
       <c r="BS3" t="n">
-        <v>50</v>
+        <v>52.94</v>
       </c>
       <c r="BT3" t="n">
-        <v>31.25</v>
+        <v>35.29</v>
       </c>
       <c r="BU3" t="n">
-        <v>6.25</v>
+        <v>11.76</v>
       </c>
       <c r="BV3" t="n">
-        <v>6.25</v>
+        <v>11.76</v>
       </c>
       <c r="BW3" t="n">
-        <v>6.25</v>
+        <v>5.88</v>
       </c>
       <c r="BX3" t="n">
-        <v>37.5</v>
+        <v>41.18</v>
       </c>
       <c r="BY3" t="n">
         <v>1.52</v>
@@ -2013,34 +2013,34 @@
         <v>1.53</v>
       </c>
       <c r="CA3" t="n">
-        <v>4.48</v>
+        <v>4.44</v>
       </c>
       <c r="CB3" t="n">
-        <v>4.75</v>
+        <v>4.69</v>
       </c>
       <c r="CC3" t="n">
-        <v>1.64</v>
+        <v>1.7</v>
       </c>
       <c r="CD3" t="n">
-        <v>1.73</v>
+        <v>1.78</v>
       </c>
       <c r="CE3" t="n">
         <v>1.26</v>
       </c>
       <c r="CF3" t="n">
-        <v>2.25</v>
+        <v>2.24</v>
       </c>
       <c r="CG3" t="n">
-        <v>3.53</v>
+        <v>3.54</v>
       </c>
       <c r="CH3" t="n">
         <v>1.6</v>
       </c>
       <c r="CI3" t="n">
-        <v>2.12</v>
+        <v>2.13</v>
       </c>
       <c r="CJ3" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="CK3" t="n">
         <v>1.47</v>
@@ -2061,7 +2061,7 @@
         <v>1.57</v>
       </c>
       <c r="CQ3" t="n">
-        <v>2.42</v>
+        <v>2.41</v>
       </c>
       <c r="CR3" t="n">
         <v>1.33</v>
@@ -2076,19 +2076,19 @@
         <v>1.65</v>
       </c>
       <c r="CV3" t="n">
-        <v>2.28</v>
+        <v>2.31</v>
       </c>
       <c r="CW3" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="CX3" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="CY3" t="n">
         <v>1.8</v>
       </c>
       <c r="CZ3" t="n">
-        <v>2.48</v>
+        <v>2.49</v>
       </c>
       <c r="DA3" t="n">
         <v>2.02</v>
@@ -2100,7 +2100,7 @@
         <v>1.59</v>
       </c>
       <c r="DD3" t="n">
-        <v>2.46</v>
+        <v>2.45</v>
       </c>
       <c r="DE3" t="n">
         <v>0.06</v>
@@ -2109,40 +2109,40 @@
         <v>1.18</v>
       </c>
       <c r="DG3" t="n">
-        <v>4.06</v>
+        <v>4.12</v>
       </c>
       <c r="DH3" t="n">
-        <v>111.56</v>
+        <v>111.71</v>
       </c>
       <c r="DI3" t="n">
         <v>0</v>
       </c>
       <c r="DJ3" t="n">
-        <v>1.56</v>
+        <v>1.53</v>
       </c>
       <c r="DK3" t="n">
-        <v>6.88</v>
+        <v>6.83</v>
       </c>
       <c r="DL3" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.59</v>
       </c>
       <c r="DM3" t="n">
-        <v>62.88</v>
+        <v>61.59</v>
       </c>
       <c r="DN3" t="n">
-        <v>0.31</v>
+        <v>0.29</v>
       </c>
       <c r="DO3" t="n">
-        <v>2.81</v>
+        <v>2.7</v>
       </c>
       <c r="DP3" t="n">
-        <v>9.56</v>
+        <v>9.52</v>
       </c>
       <c r="DQ3" t="n">
-        <v>12.31</v>
+        <v>12</v>
       </c>
       <c r="DR3" t="n">
-        <v>7.38</v>
+        <v>7.65</v>
       </c>
       <c r="DS3" t="n">
         <v>0</v>
@@ -2154,28 +2154,28 @@
         <v>0</v>
       </c>
       <c r="DV3" t="n">
-        <v>62.82</v>
+        <v>62.47</v>
       </c>
       <c r="DW3" t="n">
         <v>0.06</v>
       </c>
       <c r="DX3" t="n">
-        <v>16.38</v>
+        <v>16.53</v>
       </c>
       <c r="DY3" t="n">
-        <v>11.43</v>
+        <v>11.41</v>
       </c>
       <c r="DZ3" t="n">
-        <v>4.94</v>
+        <v>5.11</v>
       </c>
       <c r="EA3" t="n">
-        <v>20.38</v>
+        <v>19.94</v>
       </c>
       <c r="EB3" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="EC3" t="n">
-        <v>1.44</v>
+        <v>1.41</v>
       </c>
     </row>
     <row r="4">
@@ -2308,7 +2308,7 @@
         <v>1.78</v>
       </c>
       <c r="AQ4" t="n">
-        <v>11.78</v>
+        <v>11.89</v>
       </c>
       <c r="AR4" t="n">
         <v>11.67</v>
@@ -2539,7 +2539,7 @@
         <v>1.53</v>
       </c>
       <c r="DP4" t="n">
-        <v>10.82</v>
+        <v>10.88</v>
       </c>
       <c r="DQ4" t="n">
         <v>11.94</v>
@@ -2588,13 +2588,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C5" t="n">
         <v>8</v>
       </c>
       <c r="D5" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E5" t="n">
         <v>0.38</v>
@@ -2678,139 +2678,139 @@
         <v>1.5</v>
       </c>
       <c r="AF5" t="n">
-        <v>0</v>
+        <v>0.11</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AH5" t="n">
-        <v>3.38</v>
+        <v>3</v>
       </c>
       <c r="AI5" t="n">
-        <v>96.5</v>
+        <v>92.33</v>
       </c>
       <c r="AJ5" t="n">
         <v>0</v>
       </c>
       <c r="AK5" t="n">
-        <v>2.5</v>
+        <v>2.33</v>
       </c>
       <c r="AL5" t="n">
-        <v>5.62</v>
+        <v>5</v>
       </c>
       <c r="AM5" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>41.78</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>2</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>10.78</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>11.11</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>10.89</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AV5" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="AW5" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="AX5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY5" t="n">
+        <v>50.89</v>
+      </c>
+      <c r="AZ5" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="BA5" t="n">
+        <v>11.89</v>
+      </c>
+      <c r="BB5" t="n">
+        <v>6.89</v>
+      </c>
+      <c r="BC5" t="n">
+        <v>5</v>
+      </c>
+      <c r="BD5" t="n">
+        <v>17.89</v>
+      </c>
+      <c r="BE5" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="BF5" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="BG5" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="BH5" t="n">
+        <v>9.94</v>
+      </c>
+      <c r="BI5" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="BJ5" t="n">
         <v>0.88</v>
       </c>
-      <c r="AN5" t="n">
-        <v>44.38</v>
-      </c>
-      <c r="AO5" t="n">
-        <v>1</v>
-      </c>
-      <c r="AP5" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AQ5" t="n">
-        <v>11.38</v>
-      </c>
-      <c r="AR5" t="n">
-        <v>10.88</v>
-      </c>
-      <c r="AS5" t="n">
-        <v>10.12</v>
-      </c>
-      <c r="AT5" t="n">
-        <v>2</v>
-      </c>
-      <c r="AU5" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="AV5" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="AW5" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="AX5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY5" t="n">
-        <v>52.62</v>
-      </c>
-      <c r="AZ5" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="BA5" t="n">
-        <v>12.62</v>
-      </c>
-      <c r="BB5" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="BC5" t="n">
-        <v>5.12</v>
-      </c>
-      <c r="BD5" t="n">
-        <v>18</v>
-      </c>
-      <c r="BE5" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="BF5" t="n">
-        <v>2</v>
-      </c>
-      <c r="BG5" t="n">
-        <v>3</v>
-      </c>
-      <c r="BH5" t="n">
-        <v>10.06</v>
-      </c>
-      <c r="BI5" t="n">
-        <v>3</v>
-      </c>
-      <c r="BJ5" t="n">
-        <v>0.9399999999999999</v>
-      </c>
       <c r="BK5" t="n">
-        <v>0.38</v>
+        <v>0.41</v>
       </c>
       <c r="BL5" t="n">
         <v>1</v>
       </c>
       <c r="BM5" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.65</v>
       </c>
       <c r="BN5" t="n">
-        <v>1.69</v>
+        <v>1.65</v>
       </c>
       <c r="BO5" t="n">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="BP5" t="n">
-        <v>4</v>
+        <v>3.88</v>
       </c>
       <c r="BQ5" t="n">
         <v>6.06</v>
       </c>
       <c r="BR5" t="n">
-        <v>93.75</v>
+        <v>94.12</v>
       </c>
       <c r="BS5" t="n">
-        <v>81.25</v>
+        <v>82.34999999999999</v>
       </c>
       <c r="BT5" t="n">
-        <v>62.5</v>
+        <v>58.82</v>
       </c>
       <c r="BU5" t="n">
-        <v>37.5</v>
+        <v>35.29</v>
       </c>
       <c r="BV5" t="n">
-        <v>18.75</v>
+        <v>17.65</v>
       </c>
       <c r="BW5" t="n">
-        <v>6.25</v>
+        <v>5.88</v>
       </c>
       <c r="BX5" t="n">
-        <v>62.5</v>
+        <v>64.70999999999999</v>
       </c>
       <c r="BY5" t="n">
         <v>2.8</v>
@@ -2819,46 +2819,46 @@
         <v>2.94</v>
       </c>
       <c r="CA5" t="n">
-        <v>3.58</v>
+        <v>3.64</v>
       </c>
       <c r="CB5" t="n">
-        <v>3.7</v>
+        <v>3.81</v>
       </c>
       <c r="CC5" t="n">
-        <v>3.04</v>
+        <v>3.59</v>
       </c>
       <c r="CD5" t="n">
-        <v>3.22</v>
+        <v>3.84</v>
       </c>
       <c r="CE5" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="CF5" t="n">
-        <v>2.46</v>
+        <v>2.44</v>
       </c>
       <c r="CG5" t="n">
-        <v>3.21</v>
+        <v>3.23</v>
       </c>
       <c r="CH5" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="CI5" t="n">
-        <v>2.26</v>
+        <v>2.24</v>
       </c>
       <c r="CJ5" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="CK5" t="n">
         <v>1.44</v>
       </c>
       <c r="CL5" t="n">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="CM5" t="n">
         <v>2.58</v>
       </c>
       <c r="CN5" t="n">
-        <v>2</v>
+        <v>2.01</v>
       </c>
       <c r="CO5" t="n">
         <v>1.21</v>
@@ -2867,25 +2867,25 @@
         <v>1.73</v>
       </c>
       <c r="CQ5" t="n">
-        <v>2.73</v>
+        <v>2.71</v>
       </c>
       <c r="CR5" t="n">
         <v>1.35</v>
       </c>
       <c r="CS5" t="n">
-        <v>2.54</v>
+        <v>2.52</v>
       </c>
       <c r="CT5" t="n">
         <v>3.27</v>
       </c>
       <c r="CU5" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="CV5" t="n">
-        <v>2.37</v>
+        <v>2.35</v>
       </c>
       <c r="CW5" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="CX5" t="n">
         <v>1.53</v>
@@ -2897,58 +2897,58 @@
         <v>2.47</v>
       </c>
       <c r="DA5" t="n">
-        <v>2.04</v>
+        <v>2.05</v>
       </c>
       <c r="DB5" t="n">
         <v>1.23</v>
       </c>
       <c r="DC5" t="n">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="DD5" t="n">
-        <v>2.81</v>
+        <v>2.79</v>
       </c>
       <c r="DE5" t="n">
-        <v>0.19</v>
+        <v>0.24</v>
       </c>
       <c r="DF5" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="DG5" t="n">
-        <v>3.06</v>
+        <v>2.88</v>
       </c>
       <c r="DH5" t="n">
-        <v>102.88</v>
+        <v>100.29</v>
       </c>
       <c r="DI5" t="n">
         <v>0</v>
       </c>
       <c r="DJ5" t="n">
-        <v>2</v>
+        <v>1.94</v>
       </c>
       <c r="DK5" t="n">
-        <v>5.12</v>
+        <v>4.82</v>
       </c>
       <c r="DL5" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.65</v>
       </c>
       <c r="DM5" t="n">
-        <v>46.69</v>
+        <v>45.18</v>
       </c>
       <c r="DN5" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.65</v>
       </c>
       <c r="DO5" t="n">
-        <v>2.06</v>
+        <v>1.94</v>
       </c>
       <c r="DP5" t="n">
-        <v>10.88</v>
+        <v>10.59</v>
       </c>
       <c r="DQ5" t="n">
-        <v>10.32</v>
+        <v>10.47</v>
       </c>
       <c r="DR5" t="n">
-        <v>9.25</v>
+        <v>9.710000000000001</v>
       </c>
       <c r="DS5" t="n">
         <v>0.06</v>
@@ -2960,28 +2960,28 @@
         <v>0</v>
       </c>
       <c r="DV5" t="n">
-        <v>53.81</v>
+        <v>52.82</v>
       </c>
       <c r="DW5" t="n">
         <v>0.12</v>
       </c>
       <c r="DX5" t="n">
-        <v>13.93</v>
+        <v>13.47</v>
       </c>
       <c r="DY5" t="n">
-        <v>9.25</v>
+        <v>8.82</v>
       </c>
       <c r="DZ5" t="n">
-        <v>4.69</v>
+        <v>4.65</v>
       </c>
       <c r="EA5" t="n">
-        <v>18.25</v>
+        <v>18.18</v>
       </c>
       <c r="EB5" t="n">
-        <v>1.55</v>
+        <v>1.51</v>
       </c>
       <c r="EC5" t="n">
-        <v>1.75</v>
+        <v>1.71</v>
       </c>
     </row>
     <row r="6">
@@ -2991,13 +2991,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C6" t="n">
         <v>8</v>
       </c>
       <c r="D6" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
@@ -3081,52 +3081,52 @@
         <v>0.88</v>
       </c>
       <c r="AF6" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="AH6" t="n">
-        <v>2.62</v>
+        <v>3.22</v>
       </c>
       <c r="AI6" t="n">
-        <v>99.5</v>
+        <v>102.22</v>
       </c>
       <c r="AJ6" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="AK6" t="n">
-        <v>2</v>
+        <v>1.89</v>
       </c>
       <c r="AL6" t="n">
-        <v>5.12</v>
+        <v>5.67</v>
       </c>
       <c r="AM6" t="n">
-        <v>0.88</v>
+        <v>0.78</v>
       </c>
       <c r="AN6" t="n">
-        <v>48.75</v>
+        <v>49.78</v>
       </c>
       <c r="AO6" t="n">
-        <v>0.5</v>
+        <v>0.44</v>
       </c>
       <c r="AP6" t="n">
-        <v>2.5</v>
+        <v>2.44</v>
       </c>
       <c r="AQ6" t="n">
-        <v>9.380000000000001</v>
+        <v>9.56</v>
       </c>
       <c r="AR6" t="n">
-        <v>12.12</v>
+        <v>12.11</v>
       </c>
       <c r="AS6" t="n">
-        <v>6.88</v>
+        <v>6.89</v>
       </c>
       <c r="AT6" t="n">
-        <v>1.25</v>
+        <v>1.44</v>
       </c>
       <c r="AU6" t="n">
-        <v>1.38</v>
+        <v>1.22</v>
       </c>
       <c r="AV6" t="n">
         <v>0</v>
@@ -3138,82 +3138,82 @@
         <v>0</v>
       </c>
       <c r="AY6" t="n">
-        <v>60.88</v>
+        <v>62</v>
       </c>
       <c r="AZ6" t="n">
         <v>0</v>
       </c>
       <c r="BA6" t="n">
-        <v>15.25</v>
+        <v>15.56</v>
       </c>
       <c r="BB6" t="n">
-        <v>9.880000000000001</v>
+        <v>9.890000000000001</v>
       </c>
       <c r="BC6" t="n">
-        <v>5.38</v>
+        <v>5.67</v>
       </c>
       <c r="BD6" t="n">
-        <v>18.88</v>
+        <v>19.44</v>
       </c>
       <c r="BE6" t="n">
-        <v>1.69</v>
+        <v>1.74</v>
       </c>
       <c r="BF6" t="n">
-        <v>2</v>
+        <v>1.89</v>
       </c>
       <c r="BG6" t="n">
-        <v>2.56</v>
+        <v>2.59</v>
       </c>
       <c r="BH6" t="n">
-        <v>9.75</v>
+        <v>9.94</v>
       </c>
       <c r="BI6" t="n">
-        <v>2.56</v>
+        <v>2.59</v>
       </c>
       <c r="BJ6" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.65</v>
       </c>
       <c r="BK6" t="n">
-        <v>0.88</v>
+        <v>0.82</v>
       </c>
       <c r="BL6" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.71</v>
       </c>
       <c r="BM6" t="n">
-        <v>0.44</v>
+        <v>0.41</v>
       </c>
       <c r="BN6" t="n">
         <v>1.12</v>
       </c>
       <c r="BO6" t="n">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="BP6" t="n">
-        <v>4.5</v>
+        <v>4.53</v>
       </c>
       <c r="BQ6" t="n">
-        <v>5.25</v>
+        <v>5.41</v>
       </c>
       <c r="BR6" t="n">
         <v>100</v>
       </c>
       <c r="BS6" t="n">
-        <v>81.25</v>
+        <v>82.34999999999999</v>
       </c>
       <c r="BT6" t="n">
-        <v>56.25</v>
+        <v>58.82</v>
       </c>
       <c r="BU6" t="n">
-        <v>12.5</v>
+        <v>11.76</v>
       </c>
       <c r="BV6" t="n">
-        <v>6.25</v>
+        <v>5.88</v>
       </c>
       <c r="BW6" t="n">
         <v>0</v>
       </c>
       <c r="BX6" t="n">
-        <v>81.25</v>
+        <v>76.47</v>
       </c>
       <c r="BY6" t="n">
         <v>1.66</v>
@@ -3222,46 +3222,46 @@
         <v>1.74</v>
       </c>
       <c r="CA6" t="n">
-        <v>3.92</v>
+        <v>3.91</v>
       </c>
       <c r="CB6" t="n">
-        <v>4.09</v>
+        <v>4.06</v>
       </c>
       <c r="CC6" t="n">
-        <v>2.52</v>
+        <v>2.47</v>
       </c>
       <c r="CD6" t="n">
-        <v>2.54</v>
+        <v>2.48</v>
       </c>
       <c r="CE6" t="n">
         <v>1.28</v>
       </c>
       <c r="CF6" t="n">
-        <v>2.39</v>
+        <v>2.4</v>
       </c>
       <c r="CG6" t="n">
-        <v>3.33</v>
+        <v>3.31</v>
       </c>
       <c r="CH6" t="n">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="CI6" t="n">
-        <v>2.25</v>
+        <v>2.26</v>
       </c>
       <c r="CJ6" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="CK6" t="n">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="CL6" t="n">
-        <v>2.02</v>
+        <v>2.03</v>
       </c>
       <c r="CM6" t="n">
         <v>2.41</v>
       </c>
       <c r="CN6" t="n">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="CO6" t="n">
         <v>1.18</v>
@@ -3270,22 +3270,22 @@
         <v>1.68</v>
       </c>
       <c r="CQ6" t="n">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="CR6" t="n">
         <v>1.38</v>
       </c>
       <c r="CS6" t="n">
-        <v>2.52</v>
+        <v>2.55</v>
       </c>
       <c r="CT6" t="n">
-        <v>3.1</v>
+        <v>3.12</v>
       </c>
       <c r="CU6" t="n">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="CV6" t="n">
-        <v>2.31</v>
+        <v>2.3</v>
       </c>
       <c r="CW6" t="n">
         <v>1.68</v>
@@ -3297,19 +3297,19 @@
         <v>1.94</v>
       </c>
       <c r="CZ6" t="n">
-        <v>2.31</v>
+        <v>2.32</v>
       </c>
       <c r="DA6" t="n">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="DB6" t="n">
         <v>1.22</v>
       </c>
       <c r="DC6" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="DD6" t="n">
-        <v>2.73</v>
+        <v>2.75</v>
       </c>
       <c r="DE6" t="n">
         <v>0.06</v>
@@ -3318,40 +3318,40 @@
         <v>1</v>
       </c>
       <c r="DG6" t="n">
-        <v>3.18</v>
+        <v>3.47</v>
       </c>
       <c r="DH6" t="n">
-        <v>118.75</v>
+        <v>119.06</v>
       </c>
       <c r="DI6" t="n">
         <v>0.06</v>
       </c>
       <c r="DJ6" t="n">
-        <v>1.56</v>
+        <v>1.53</v>
       </c>
       <c r="DK6" t="n">
-        <v>5.94</v>
+        <v>6.18</v>
       </c>
       <c r="DL6" t="n">
-        <v>0.82</v>
+        <v>0.77</v>
       </c>
       <c r="DM6" t="n">
-        <v>57.44</v>
+        <v>57.47</v>
       </c>
       <c r="DN6" t="n">
-        <v>0.5</v>
+        <v>0.47</v>
       </c>
       <c r="DO6" t="n">
-        <v>2.75</v>
+        <v>2.7</v>
       </c>
       <c r="DP6" t="n">
-        <v>9.94</v>
+        <v>10</v>
       </c>
       <c r="DQ6" t="n">
-        <v>13.31</v>
+        <v>13.23</v>
       </c>
       <c r="DR6" t="n">
-        <v>5.94</v>
+        <v>6</v>
       </c>
       <c r="DS6" t="n">
         <v>0</v>
@@ -3363,28 +3363,28 @@
         <v>0</v>
       </c>
       <c r="DV6" t="n">
-        <v>63.69</v>
+        <v>64.12</v>
       </c>
       <c r="DW6" t="n">
         <v>0.06</v>
       </c>
       <c r="DX6" t="n">
-        <v>16.5</v>
+        <v>16.59</v>
       </c>
       <c r="DY6" t="n">
-        <v>10.94</v>
+        <v>10.88</v>
       </c>
       <c r="DZ6" t="n">
-        <v>5.56</v>
+        <v>5.71</v>
       </c>
       <c r="EA6" t="n">
-        <v>19.75</v>
+        <v>20</v>
       </c>
       <c r="EB6" t="n">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="EC6" t="n">
-        <v>1.44</v>
+        <v>1.41</v>
       </c>
     </row>
     <row r="7">
@@ -3394,94 +3394,94 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C7" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D7" t="n">
         <v>8</v>
       </c>
       <c r="E7" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="F7" t="n">
-        <v>1.5</v>
+        <v>1.56</v>
       </c>
       <c r="G7" t="n">
-        <v>2.38</v>
+        <v>2.56</v>
       </c>
       <c r="H7" t="n">
-        <v>88.5</v>
+        <v>89.56</v>
       </c>
       <c r="I7" t="n">
-        <v>0.38</v>
+        <v>0.33</v>
       </c>
       <c r="J7" t="n">
-        <v>2.25</v>
+        <v>2.44</v>
       </c>
       <c r="K7" t="n">
-        <v>4.25</v>
+        <v>4.56</v>
       </c>
       <c r="L7" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="M7" t="n">
-        <v>49.12</v>
+        <v>50</v>
       </c>
       <c r="N7" t="n">
-        <v>0.75</v>
+        <v>0.89</v>
       </c>
       <c r="O7" t="n">
-        <v>1.88</v>
+        <v>2</v>
       </c>
       <c r="P7" t="n">
-        <v>10.5</v>
+        <v>10.56</v>
       </c>
       <c r="Q7" t="n">
-        <v>11.5</v>
+        <v>11.33</v>
       </c>
       <c r="R7" t="n">
-        <v>10.5</v>
+        <v>10.44</v>
       </c>
       <c r="S7" t="n">
-        <v>1.25</v>
+        <v>1.11</v>
       </c>
       <c r="T7" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="U7" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="V7" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>49.38</v>
+        <v>49.89</v>
       </c>
       <c r="Y7" t="n">
         <v>0</v>
       </c>
       <c r="Z7" t="n">
-        <v>10.12</v>
+        <v>10.22</v>
       </c>
       <c r="AA7" t="n">
-        <v>6.62</v>
+        <v>6.67</v>
       </c>
       <c r="AB7" t="n">
-        <v>3.5</v>
+        <v>3.56</v>
       </c>
       <c r="AC7" t="n">
-        <v>21.62</v>
+        <v>21.67</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="AE7" t="n">
-        <v>2.25</v>
+        <v>2.44</v>
       </c>
       <c r="AF7" t="n">
         <v>0.12</v>
@@ -3565,70 +3565,70 @@
         <v>2.38</v>
       </c>
       <c r="BG7" t="n">
-        <v>2.38</v>
+        <v>2.29</v>
       </c>
       <c r="BH7" t="n">
-        <v>11.62</v>
+        <v>11.53</v>
       </c>
       <c r="BI7" t="n">
-        <v>2.38</v>
+        <v>2.29</v>
       </c>
       <c r="BJ7" t="n">
-        <v>0.44</v>
+        <v>0.47</v>
       </c>
       <c r="BK7" t="n">
-        <v>0.44</v>
+        <v>0.41</v>
       </c>
       <c r="BL7" t="n">
-        <v>0.62</v>
+        <v>0.59</v>
       </c>
       <c r="BM7" t="n">
-        <v>0.88</v>
+        <v>0.82</v>
       </c>
       <c r="BN7" t="n">
-        <v>1.5</v>
+        <v>1.41</v>
       </c>
       <c r="BO7" t="n">
         <v>0.88</v>
       </c>
       <c r="BP7" t="n">
-        <v>5.44</v>
+        <v>5.29</v>
       </c>
       <c r="BQ7" t="n">
-        <v>6.19</v>
+        <v>6.24</v>
       </c>
       <c r="BR7" t="n">
-        <v>93.75</v>
+        <v>94.12</v>
       </c>
       <c r="BS7" t="n">
-        <v>75</v>
+        <v>70.59</v>
       </c>
       <c r="BT7" t="n">
-        <v>37.5</v>
+        <v>35.29</v>
       </c>
       <c r="BU7" t="n">
-        <v>25</v>
+        <v>23.53</v>
       </c>
       <c r="BV7" t="n">
-        <v>6.25</v>
+        <v>5.88</v>
       </c>
       <c r="BW7" t="n">
         <v>0</v>
       </c>
       <c r="BX7" t="n">
-        <v>68.75</v>
+        <v>64.70999999999999</v>
       </c>
       <c r="BY7" t="n">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="BZ7" t="n">
-        <v>3.09</v>
+        <v>3.11</v>
       </c>
       <c r="CA7" t="n">
-        <v>3.67</v>
+        <v>3.65</v>
       </c>
       <c r="CB7" t="n">
-        <v>3.81</v>
+        <v>3.78</v>
       </c>
       <c r="CC7" t="n">
         <v>3.47</v>
@@ -3640,16 +3640,16 @@
         <v>1.3</v>
       </c>
       <c r="CF7" t="n">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="CG7" t="n">
         <v>3.26</v>
       </c>
       <c r="CH7" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="CI7" t="n">
-        <v>2.27</v>
+        <v>2.26</v>
       </c>
       <c r="CJ7" t="n">
         <v>1.61</v>
@@ -3661,19 +3661,19 @@
         <v>1.76</v>
       </c>
       <c r="CM7" t="n">
-        <v>2.79</v>
+        <v>2.77</v>
       </c>
       <c r="CN7" t="n">
-        <v>2.12</v>
+        <v>2.11</v>
       </c>
       <c r="CO7" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="CP7" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="CQ7" t="n">
-        <v>2.68</v>
+        <v>2.7</v>
       </c>
       <c r="CR7" t="n">
         <v>1.36</v>
@@ -3688,73 +3688,73 @@
         <v>1.55</v>
       </c>
       <c r="CV7" t="n">
-        <v>2.4</v>
+        <v>2.39</v>
       </c>
       <c r="CW7" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="CX7" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="CY7" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="CZ7" t="n">
-        <v>2.52</v>
+        <v>2.54</v>
       </c>
       <c r="DA7" t="n">
-        <v>2.13</v>
+        <v>2.12</v>
       </c>
       <c r="DB7" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="DC7" t="n">
-        <v>1.74</v>
+        <v>1.76</v>
       </c>
       <c r="DD7" t="n">
-        <v>2.77</v>
+        <v>2.82</v>
       </c>
       <c r="DE7" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DF7" t="n">
-        <v>1.56</v>
+        <v>1.59</v>
       </c>
       <c r="DG7" t="n">
-        <v>2.63</v>
+        <v>2.71</v>
       </c>
       <c r="DH7" t="n">
-        <v>84.19</v>
+        <v>85</v>
       </c>
       <c r="DI7" t="n">
-        <v>0.25</v>
+        <v>0.23</v>
       </c>
       <c r="DJ7" t="n">
-        <v>2.32</v>
+        <v>2.41</v>
       </c>
       <c r="DK7" t="n">
-        <v>4.69</v>
+        <v>4.82</v>
       </c>
       <c r="DL7" t="n">
-        <v>0.25</v>
+        <v>0.24</v>
       </c>
       <c r="DM7" t="n">
-        <v>44.94</v>
+        <v>45.65</v>
       </c>
       <c r="DN7" t="n">
-        <v>0.75</v>
+        <v>0.82</v>
       </c>
       <c r="DO7" t="n">
-        <v>2.06</v>
+        <v>2.12</v>
       </c>
       <c r="DP7" t="n">
-        <v>9.81</v>
+        <v>9.880000000000001</v>
       </c>
       <c r="DQ7" t="n">
-        <v>10.81</v>
+        <v>10.76</v>
       </c>
       <c r="DR7" t="n">
-        <v>9.75</v>
+        <v>9.76</v>
       </c>
       <c r="DS7" t="n">
         <v>0.12</v>
@@ -3766,28 +3766,28 @@
         <v>0</v>
       </c>
       <c r="DV7" t="n">
-        <v>48.25</v>
+        <v>48.59</v>
       </c>
       <c r="DW7" t="n">
         <v>0</v>
       </c>
       <c r="DX7" t="n">
-        <v>10.37</v>
+        <v>10.41</v>
       </c>
       <c r="DY7" t="n">
-        <v>6.44</v>
+        <v>6.47</v>
       </c>
       <c r="DZ7" t="n">
-        <v>3.94</v>
+        <v>3.95</v>
       </c>
       <c r="EA7" t="n">
-        <v>21</v>
+        <v>21.06</v>
       </c>
       <c r="EB7" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="EC7" t="n">
-        <v>2.32</v>
+        <v>2.41</v>
       </c>
     </row>
     <row r="8">
@@ -3797,94 +3797,94 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C8" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D8" t="n">
         <v>8</v>
       </c>
       <c r="E8" t="n">
-        <v>0.12</v>
+        <v>0.22</v>
       </c>
       <c r="F8" t="n">
         <v>1</v>
       </c>
       <c r="G8" t="n">
-        <v>3.38</v>
+        <v>3.11</v>
       </c>
       <c r="H8" t="n">
-        <v>98.12</v>
+        <v>97.33</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>1.25</v>
+        <v>1.44</v>
       </c>
       <c r="K8" t="n">
-        <v>6.62</v>
+        <v>6.44</v>
       </c>
       <c r="L8" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="M8" t="n">
-        <v>58.62</v>
+        <v>57.78</v>
       </c>
       <c r="N8" t="n">
-        <v>0.25</v>
+        <v>0.44</v>
       </c>
       <c r="O8" t="n">
-        <v>3.25</v>
+        <v>3.33</v>
       </c>
       <c r="P8" t="n">
-        <v>10.5</v>
+        <v>10.56</v>
       </c>
       <c r="Q8" t="n">
-        <v>12.88</v>
+        <v>12.89</v>
       </c>
       <c r="R8" t="n">
-        <v>7.62</v>
+        <v>7.44</v>
       </c>
       <c r="S8" t="n">
-        <v>0.75</v>
+        <v>0.67</v>
       </c>
       <c r="T8" t="n">
-        <v>1</v>
+        <v>1.33</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>0.11</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>0.11</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>51</v>
+        <v>49.44</v>
       </c>
       <c r="Y8" t="n">
         <v>0</v>
       </c>
       <c r="Z8" t="n">
-        <v>17.62</v>
+        <v>17.44</v>
       </c>
       <c r="AA8" t="n">
-        <v>12.75</v>
+        <v>12.22</v>
       </c>
       <c r="AB8" t="n">
-        <v>4.88</v>
+        <v>5.22</v>
       </c>
       <c r="AC8" t="n">
-        <v>19.38</v>
+        <v>19.44</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.25</v>
+        <v>1.44</v>
       </c>
       <c r="AF8" t="n">
         <v>0.12</v>
@@ -3968,70 +3968,70 @@
         <v>1.62</v>
       </c>
       <c r="BG8" t="n">
-        <v>2.94</v>
+        <v>3</v>
       </c>
       <c r="BH8" t="n">
-        <v>9.94</v>
+        <v>10.18</v>
       </c>
       <c r="BI8" t="n">
-        <v>2.94</v>
+        <v>3</v>
       </c>
       <c r="BJ8" t="n">
-        <v>0.75</v>
+        <v>0.88</v>
       </c>
       <c r="BK8" t="n">
-        <v>0.5</v>
+        <v>0.47</v>
       </c>
       <c r="BL8" t="n">
         <v>1</v>
       </c>
       <c r="BM8" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.65</v>
       </c>
       <c r="BN8" t="n">
-        <v>1.69</v>
+        <v>1.65</v>
       </c>
       <c r="BO8" t="n">
-        <v>1.25</v>
+        <v>1.35</v>
       </c>
       <c r="BP8" t="n">
-        <v>4.62</v>
+        <v>4.82</v>
       </c>
       <c r="BQ8" t="n">
-        <v>5.31</v>
+        <v>5.35</v>
       </c>
       <c r="BR8" t="n">
-        <v>87.5</v>
+        <v>88.23999999999999</v>
       </c>
       <c r="BS8" t="n">
-        <v>75</v>
+        <v>76.47</v>
       </c>
       <c r="BT8" t="n">
-        <v>37.5</v>
+        <v>41.18</v>
       </c>
       <c r="BU8" t="n">
-        <v>31.25</v>
+        <v>35.29</v>
       </c>
       <c r="BV8" t="n">
-        <v>18.75</v>
+        <v>17.65</v>
       </c>
       <c r="BW8" t="n">
-        <v>12.5</v>
+        <v>11.76</v>
       </c>
       <c r="BX8" t="n">
-        <v>37.5</v>
+        <v>35.29</v>
       </c>
       <c r="BY8" t="n">
-        <v>2.17</v>
+        <v>2.25</v>
       </c>
       <c r="BZ8" t="n">
-        <v>2.28</v>
+        <v>2.37</v>
       </c>
       <c r="CA8" t="n">
-        <v>3.89</v>
+        <v>3.88</v>
       </c>
       <c r="CB8" t="n">
-        <v>3.99</v>
+        <v>3.97</v>
       </c>
       <c r="CC8" t="n">
         <v>4.48</v>
@@ -4043,19 +4043,19 @@
         <v>1.26</v>
       </c>
       <c r="CF8" t="n">
-        <v>2.25</v>
+        <v>2.26</v>
       </c>
       <c r="CG8" t="n">
-        <v>3.57</v>
+        <v>3.56</v>
       </c>
       <c r="CH8" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="CI8" t="n">
-        <v>2.4</v>
+        <v>2.41</v>
       </c>
       <c r="CJ8" t="n">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="CK8" t="n">
         <v>1.35</v>
@@ -4067,16 +4067,16 @@
         <v>2.89</v>
       </c>
       <c r="CN8" t="n">
-        <v>2.24</v>
+        <v>2.23</v>
       </c>
       <c r="CO8" t="n">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="CP8" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="CQ8" t="n">
-        <v>2.41</v>
+        <v>2.42</v>
       </c>
       <c r="CR8" t="n">
         <v>1.34</v>
@@ -4111,61 +4111,61 @@
         <v>1.6</v>
       </c>
       <c r="DD8" t="n">
-        <v>2.45</v>
+        <v>2.46</v>
       </c>
       <c r="DE8" t="n">
-        <v>0.12</v>
+        <v>0.17</v>
       </c>
       <c r="DF8" t="n">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="DG8" t="n">
-        <v>2.75</v>
+        <v>2.64</v>
       </c>
       <c r="DH8" t="n">
-        <v>90.75</v>
+        <v>90.77</v>
       </c>
       <c r="DI8" t="n">
         <v>0</v>
       </c>
       <c r="DJ8" t="n">
-        <v>1.44</v>
+        <v>1.52</v>
       </c>
       <c r="DK8" t="n">
-        <v>5.44</v>
+        <v>5.41</v>
       </c>
       <c r="DL8" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="DM8" t="n">
+        <v>49.06</v>
+      </c>
+      <c r="DN8" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="DO8" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="DP8" t="n">
+        <v>12</v>
+      </c>
+      <c r="DQ8" t="n">
+        <v>12.18</v>
+      </c>
+      <c r="DR8" t="n">
+        <v>7.94</v>
+      </c>
+      <c r="DS8" t="n">
         <v>0.18</v>
       </c>
-      <c r="DM8" t="n">
-        <v>48.94</v>
-      </c>
-      <c r="DN8" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="DO8" t="n">
-        <v>2.68</v>
-      </c>
-      <c r="DP8" t="n">
-        <v>12.06</v>
-      </c>
-      <c r="DQ8" t="n">
-        <v>12.13</v>
-      </c>
-      <c r="DR8" t="n">
-        <v>8.06</v>
-      </c>
-      <c r="DS8" t="n">
-        <v>0.12</v>
-      </c>
       <c r="DT8" t="n">
-        <v>0.12</v>
+        <v>0.18</v>
       </c>
       <c r="DU8" t="n">
         <v>0</v>
       </c>
       <c r="DV8" t="n">
-        <v>50.12</v>
+        <v>49.35</v>
       </c>
       <c r="DW8" t="n">
         <v>0</v>
@@ -4174,19 +4174,19 @@
         <v>16</v>
       </c>
       <c r="DY8" t="n">
-        <v>11.32</v>
+        <v>11.12</v>
       </c>
       <c r="DZ8" t="n">
-        <v>4.69</v>
+        <v>4.88</v>
       </c>
       <c r="EA8" t="n">
-        <v>21</v>
+        <v>20.94</v>
       </c>
       <c r="EB8" t="n">
-        <v>1.66</v>
+        <v>1.68</v>
       </c>
       <c r="EC8" t="n">
-        <v>1.44</v>
+        <v>1.52</v>
       </c>
     </row>
     <row r="9">
@@ -4196,61 +4196,61 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C9" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D9" t="n">
         <v>8</v>
       </c>
       <c r="E9" t="n">
-        <v>0.25</v>
+        <v>0.33</v>
       </c>
       <c r="F9" t="n">
-        <v>2.5</v>
+        <v>2.33</v>
       </c>
       <c r="G9" t="n">
-        <v>2.12</v>
+        <v>2.22</v>
       </c>
       <c r="H9" t="n">
-        <v>77.25</v>
+        <v>77.78</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>3</v>
+        <v>2.89</v>
       </c>
       <c r="K9" t="n">
         <v>4</v>
       </c>
       <c r="L9" t="n">
-        <v>0.62</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="M9" t="n">
-        <v>37</v>
+        <v>37.78</v>
       </c>
       <c r="N9" t="n">
-        <v>0.5</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="O9" t="n">
-        <v>1.88</v>
+        <v>1.78</v>
       </c>
       <c r="P9" t="n">
-        <v>15.88</v>
+        <v>16.11</v>
       </c>
       <c r="Q9" t="n">
-        <v>11.88</v>
+        <v>11.78</v>
       </c>
       <c r="R9" t="n">
-        <v>8.380000000000001</v>
+        <v>8.109999999999999</v>
       </c>
       <c r="S9" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="T9" t="n">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="U9" t="n">
         <v>0</v>
@@ -4262,28 +4262,28 @@
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>44.25</v>
+        <v>44.44</v>
       </c>
       <c r="Y9" t="n">
         <v>0</v>
       </c>
       <c r="Z9" t="n">
-        <v>13.62</v>
+        <v>14</v>
       </c>
       <c r="AA9" t="n">
-        <v>9</v>
+        <v>9.220000000000001</v>
       </c>
       <c r="AB9" t="n">
-        <v>4.62</v>
+        <v>4.78</v>
       </c>
       <c r="AC9" t="n">
-        <v>18.5</v>
+        <v>17.78</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.45</v>
+        <v>1.49</v>
       </c>
       <c r="AE9" t="n">
-        <v>3</v>
+        <v>2.89</v>
       </c>
       <c r="AF9" t="n">
         <v>0</v>
@@ -4367,70 +4367,70 @@
         <v>3.12</v>
       </c>
       <c r="BG9" t="n">
-        <v>2.69</v>
+        <v>2.65</v>
       </c>
       <c r="BH9" t="n">
-        <v>9.81</v>
+        <v>9.65</v>
       </c>
       <c r="BI9" t="n">
-        <v>2.69</v>
+        <v>2.65</v>
       </c>
       <c r="BJ9" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.82</v>
       </c>
       <c r="BK9" t="n">
-        <v>0.38</v>
+        <v>0.41</v>
       </c>
       <c r="BL9" t="n">
-        <v>0.88</v>
+        <v>0.82</v>
       </c>
       <c r="BM9" t="n">
-        <v>0.62</v>
+        <v>0.59</v>
       </c>
       <c r="BN9" t="n">
-        <v>1.5</v>
+        <v>1.41</v>
       </c>
       <c r="BO9" t="n">
-        <v>1.19</v>
+        <v>1.24</v>
       </c>
       <c r="BP9" t="n">
-        <v>5</v>
+        <v>4.82</v>
       </c>
       <c r="BQ9" t="n">
-        <v>4.81</v>
+        <v>4.82</v>
       </c>
       <c r="BR9" t="n">
         <v>100</v>
       </c>
       <c r="BS9" t="n">
-        <v>81.25</v>
+        <v>82.34999999999999</v>
       </c>
       <c r="BT9" t="n">
-        <v>56.25</v>
+        <v>52.94</v>
       </c>
       <c r="BU9" t="n">
-        <v>25</v>
+        <v>23.53</v>
       </c>
       <c r="BV9" t="n">
-        <v>6.25</v>
+        <v>5.88</v>
       </c>
       <c r="BW9" t="n">
         <v>0</v>
       </c>
       <c r="BX9" t="n">
-        <v>56.25</v>
+        <v>58.82</v>
       </c>
       <c r="BY9" t="n">
-        <v>3.08</v>
+        <v>2.97</v>
       </c>
       <c r="BZ9" t="n">
-        <v>3.15</v>
+        <v>3.03</v>
       </c>
       <c r="CA9" t="n">
-        <v>3.58</v>
+        <v>3.57</v>
       </c>
       <c r="CB9" t="n">
-        <v>3.62</v>
+        <v>3.6</v>
       </c>
       <c r="CC9" t="n">
         <v>4.37</v>
@@ -4445,7 +4445,7 @@
         <v>2.67</v>
       </c>
       <c r="CG9" t="n">
-        <v>3.03</v>
+        <v>3.04</v>
       </c>
       <c r="CH9" t="n">
         <v>1.44</v>
@@ -4454,16 +4454,16 @@
         <v>2.01</v>
       </c>
       <c r="CJ9" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="CK9" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="CL9" t="n">
         <v>1.78</v>
       </c>
       <c r="CM9" t="n">
-        <v>2.59</v>
+        <v>2.58</v>
       </c>
       <c r="CN9" t="n">
         <v>2</v>
@@ -4475,37 +4475,37 @@
         <v>1.87</v>
       </c>
       <c r="CQ9" t="n">
-        <v>3.14</v>
+        <v>3.13</v>
       </c>
       <c r="CR9" t="n">
         <v>1.38</v>
       </c>
       <c r="CS9" t="n">
-        <v>2.82</v>
+        <v>2.81</v>
       </c>
       <c r="CT9" t="n">
-        <v>3.09</v>
+        <v>3.11</v>
       </c>
       <c r="CU9" t="n">
         <v>1.45</v>
       </c>
       <c r="CV9" t="n">
-        <v>2.11</v>
+        <v>2.12</v>
       </c>
       <c r="CW9" t="n">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="CX9" t="n">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="CY9" t="n">
         <v>1.78</v>
       </c>
       <c r="CZ9" t="n">
-        <v>2.49</v>
+        <v>2.52</v>
       </c>
       <c r="DA9" t="n">
-        <v>2.04</v>
+        <v>2.03</v>
       </c>
       <c r="DB9" t="n">
         <v>1.29</v>
@@ -4514,49 +4514,49 @@
         <v>1.94</v>
       </c>
       <c r="DD9" t="n">
-        <v>3.25</v>
+        <v>3.24</v>
       </c>
       <c r="DE9" t="n">
-        <v>0.12</v>
+        <v>0.17</v>
       </c>
       <c r="DF9" t="n">
-        <v>2.25</v>
+        <v>2.17</v>
       </c>
       <c r="DG9" t="n">
-        <v>2.37</v>
+        <v>2.41</v>
       </c>
       <c r="DH9" t="n">
-        <v>78.12</v>
+        <v>78.34999999999999</v>
       </c>
       <c r="DI9" t="n">
         <v>0</v>
       </c>
       <c r="DJ9" t="n">
-        <v>3.12</v>
+        <v>3.06</v>
       </c>
       <c r="DK9" t="n">
-        <v>4.19</v>
+        <v>4.18</v>
       </c>
       <c r="DL9" t="n">
-        <v>0.44</v>
+        <v>0.41</v>
       </c>
       <c r="DM9" t="n">
-        <v>40.44</v>
+        <v>40.65</v>
       </c>
       <c r="DN9" t="n">
         <v>0.88</v>
       </c>
       <c r="DO9" t="n">
-        <v>1.82</v>
+        <v>1.77</v>
       </c>
       <c r="DP9" t="n">
-        <v>16.63</v>
+        <v>16.71</v>
       </c>
       <c r="DQ9" t="n">
-        <v>11.25</v>
+        <v>11.23</v>
       </c>
       <c r="DR9" t="n">
-        <v>8.5</v>
+        <v>8.35</v>
       </c>
       <c r="DS9" t="n">
         <v>0</v>
@@ -4568,28 +4568,28 @@
         <v>0</v>
       </c>
       <c r="DV9" t="n">
-        <v>44.06</v>
+        <v>44.18</v>
       </c>
       <c r="DW9" t="n">
         <v>0.06</v>
       </c>
       <c r="DX9" t="n">
-        <v>12.31</v>
+        <v>12.59</v>
       </c>
       <c r="DY9" t="n">
-        <v>8.19</v>
+        <v>8.35</v>
       </c>
       <c r="DZ9" t="n">
-        <v>4.12</v>
+        <v>4.23</v>
       </c>
       <c r="EA9" t="n">
-        <v>19.19</v>
+        <v>18.77</v>
       </c>
       <c r="EB9" t="n">
-        <v>1.36</v>
+        <v>1.39</v>
       </c>
       <c r="EC9" t="n">
-        <v>3.06</v>
+        <v>3</v>
       </c>
     </row>
     <row r="10">
@@ -4644,7 +4644,7 @@
         <v>11.44</v>
       </c>
       <c r="Q10" t="n">
-        <v>11.33</v>
+        <v>11.44</v>
       </c>
       <c r="R10" t="n">
         <v>8.779999999999999</v>
@@ -4671,19 +4671,19 @@
         <v>0</v>
       </c>
       <c r="Z10" t="n">
-        <v>10.67</v>
+        <v>10.56</v>
       </c>
       <c r="AA10" t="n">
-        <v>7.89</v>
+        <v>7.78</v>
       </c>
       <c r="AB10" t="n">
         <v>2.78</v>
       </c>
       <c r="AC10" t="n">
-        <v>21</v>
+        <v>20.89</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="AE10" t="n">
         <v>1.67</v>
@@ -4884,7 +4884,7 @@
         <v>1.41</v>
       </c>
       <c r="CS10" t="n">
-        <v>2.98</v>
+        <v>2.97</v>
       </c>
       <c r="CT10" t="n">
         <v>2.99</v>
@@ -4893,7 +4893,7 @@
         <v>1.41</v>
       </c>
       <c r="CV10" t="n">
-        <v>2</v>
+        <v>2.01</v>
       </c>
       <c r="CW10" t="n">
         <v>1.87</v>
@@ -4917,7 +4917,7 @@
         <v>2.08</v>
       </c>
       <c r="DD10" t="n">
-        <v>3.62</v>
+        <v>3.61</v>
       </c>
       <c r="DE10" t="n">
         <v>0.06</v>
@@ -4956,7 +4956,7 @@
         <v>12.23</v>
       </c>
       <c r="DQ10" t="n">
-        <v>12.29</v>
+        <v>12.35</v>
       </c>
       <c r="DR10" t="n">
         <v>9.119999999999999</v>
@@ -4977,16 +4977,16 @@
         <v>0.06</v>
       </c>
       <c r="DX10" t="n">
-        <v>9.41</v>
+        <v>9.359999999999999</v>
       </c>
       <c r="DY10" t="n">
-        <v>6.94</v>
+        <v>6.89</v>
       </c>
       <c r="DZ10" t="n">
         <v>2.47</v>
       </c>
       <c r="EA10" t="n">
-        <v>21.47</v>
+        <v>21.41</v>
       </c>
       <c r="EB10" t="n">
         <v>1.02</v>
@@ -5002,13 +5002,13 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C11" t="n">
         <v>9</v>
       </c>
       <c r="D11" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E11" t="n">
         <v>0.11</v>
@@ -5092,139 +5092,139 @@
         <v>2.56</v>
       </c>
       <c r="AF11" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.71</v>
+        <v>1.62</v>
       </c>
       <c r="AH11" t="n">
-        <v>2.86</v>
+        <v>3.12</v>
       </c>
       <c r="AI11" t="n">
-        <v>93.43000000000001</v>
+        <v>95.12</v>
       </c>
       <c r="AJ11" t="n">
         <v>0</v>
       </c>
       <c r="AK11" t="n">
-        <v>2.71</v>
+        <v>2.62</v>
       </c>
       <c r="AL11" t="n">
-        <v>6</v>
+        <v>6.38</v>
       </c>
       <c r="AM11" t="n">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="AN11" t="n">
-        <v>57</v>
+        <v>57.38</v>
       </c>
       <c r="AO11" t="n">
         <v>1</v>
       </c>
       <c r="AP11" t="n">
-        <v>3.14</v>
+        <v>3.25</v>
       </c>
       <c r="AQ11" t="n">
-        <v>13.86</v>
+        <v>13.88</v>
       </c>
       <c r="AR11" t="n">
-        <v>9.140000000000001</v>
+        <v>9.380000000000001</v>
       </c>
       <c r="AS11" t="n">
-        <v>7.86</v>
+        <v>8</v>
       </c>
       <c r="AT11" t="n">
-        <v>0.86</v>
+        <v>1.25</v>
       </c>
       <c r="AU11" t="n">
-        <v>1.14</v>
+        <v>1</v>
       </c>
       <c r="AV11" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="AW11" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="AX11" t="n">
         <v>0</v>
       </c>
       <c r="AY11" t="n">
-        <v>55.86</v>
+        <v>56.75</v>
       </c>
       <c r="AZ11" t="n">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="BA11" t="n">
         <v>13</v>
       </c>
       <c r="BB11" t="n">
-        <v>8.859999999999999</v>
+        <v>9</v>
       </c>
       <c r="BC11" t="n">
-        <v>4.14</v>
+        <v>4</v>
       </c>
       <c r="BD11" t="n">
-        <v>22.86</v>
+        <v>22.62</v>
       </c>
       <c r="BE11" t="n">
         <v>1.52</v>
       </c>
       <c r="BF11" t="n">
-        <v>2.43</v>
+        <v>2.38</v>
       </c>
       <c r="BG11" t="n">
-        <v>2.25</v>
+        <v>2.35</v>
       </c>
       <c r="BH11" t="n">
-        <v>10.06</v>
+        <v>10.29</v>
       </c>
       <c r="BI11" t="n">
-        <v>2.25</v>
+        <v>2.35</v>
       </c>
       <c r="BJ11" t="n">
-        <v>0.5</v>
+        <v>0.65</v>
       </c>
       <c r="BK11" t="n">
-        <v>0.31</v>
+        <v>0.29</v>
       </c>
       <c r="BL11" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.82</v>
       </c>
       <c r="BM11" t="n">
-        <v>0.62</v>
+        <v>0.59</v>
       </c>
       <c r="BN11" t="n">
-        <v>1.44</v>
+        <v>1.41</v>
       </c>
       <c r="BO11" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="BP11" t="n">
-        <v>4.88</v>
+        <v>5.06</v>
       </c>
       <c r="BQ11" t="n">
-        <v>5.19</v>
+        <v>5.24</v>
       </c>
       <c r="BR11" t="n">
-        <v>93.75</v>
+        <v>94.12</v>
       </c>
       <c r="BS11" t="n">
-        <v>56.25</v>
+        <v>58.82</v>
       </c>
       <c r="BT11" t="n">
-        <v>25</v>
+        <v>29.41</v>
       </c>
       <c r="BU11" t="n">
-        <v>25</v>
+        <v>29.41</v>
       </c>
       <c r="BV11" t="n">
-        <v>12.5</v>
+        <v>11.76</v>
       </c>
       <c r="BW11" t="n">
-        <v>6.25</v>
+        <v>5.88</v>
       </c>
       <c r="BX11" t="n">
-        <v>37.5</v>
+        <v>35.29</v>
       </c>
       <c r="BY11" t="n">
         <v>1.99</v>
@@ -5233,46 +5233,46 @@
         <v>2.11</v>
       </c>
       <c r="CA11" t="n">
-        <v>3.64</v>
+        <v>3.65</v>
       </c>
       <c r="CB11" t="n">
-        <v>3.77</v>
+        <v>3.76</v>
       </c>
       <c r="CC11" t="n">
-        <v>2.5</v>
+        <v>2.47</v>
       </c>
       <c r="CD11" t="n">
-        <v>2.66</v>
+        <v>2.62</v>
       </c>
       <c r="CE11" t="n">
         <v>1.32</v>
       </c>
       <c r="CF11" t="n">
-        <v>2.53</v>
+        <v>2.52</v>
       </c>
       <c r="CG11" t="n">
-        <v>3.09</v>
+        <v>3.1</v>
       </c>
       <c r="CH11" t="n">
         <v>1.48</v>
       </c>
       <c r="CI11" t="n">
-        <v>2.13</v>
+        <v>2.15</v>
       </c>
       <c r="CJ11" t="n">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="CK11" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="CL11" t="n">
-        <v>1.91</v>
+        <v>1.89</v>
       </c>
       <c r="CM11" t="n">
-        <v>2.53</v>
+        <v>2.56</v>
       </c>
       <c r="CN11" t="n">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="CO11" t="n">
         <v>1.23</v>
@@ -5281,7 +5281,7 @@
         <v>1.76</v>
       </c>
       <c r="CQ11" t="n">
-        <v>2.89</v>
+        <v>2.87</v>
       </c>
       <c r="CR11" t="n">
         <v>1.35</v>
@@ -5296,10 +5296,10 @@
         <v>1.51</v>
       </c>
       <c r="CV11" t="n">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="CW11" t="n">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="CX11" t="n">
         <v>1.52</v>
@@ -5317,85 +5317,85 @@
         <v>1.25</v>
       </c>
       <c r="DC11" t="n">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="DD11" t="n">
-        <v>2.98</v>
+        <v>2.96</v>
       </c>
       <c r="DE11" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DF11" t="n">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="DG11" t="n">
-        <v>3.19</v>
+        <v>3.29</v>
       </c>
       <c r="DH11" t="n">
-        <v>98.94</v>
+        <v>99.41</v>
       </c>
       <c r="DI11" t="n">
         <v>0</v>
       </c>
       <c r="DJ11" t="n">
-        <v>2.75</v>
+        <v>2.7</v>
       </c>
       <c r="DK11" t="n">
-        <v>6.25</v>
+        <v>6.41</v>
       </c>
       <c r="DL11" t="n">
-        <v>0.37</v>
+        <v>0.35</v>
       </c>
       <c r="DM11" t="n">
-        <v>58</v>
+        <v>58.12</v>
       </c>
       <c r="DN11" t="n">
         <v>0.9399999999999999</v>
       </c>
       <c r="DO11" t="n">
-        <v>3.06</v>
+        <v>3.12</v>
       </c>
       <c r="DP11" t="n">
-        <v>13.75</v>
+        <v>13.77</v>
       </c>
       <c r="DQ11" t="n">
-        <v>9.94</v>
+        <v>10</v>
       </c>
       <c r="DR11" t="n">
-        <v>7.75</v>
+        <v>7.83</v>
       </c>
       <c r="DS11" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DT11" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DU11" t="n">
         <v>0</v>
       </c>
       <c r="DV11" t="n">
-        <v>52.38</v>
+        <v>53</v>
       </c>
       <c r="DW11" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
       <c r="DX11" t="n">
-        <v>14.87</v>
+        <v>14.76</v>
       </c>
       <c r="DY11" t="n">
         <v>10</v>
       </c>
       <c r="DZ11" t="n">
-        <v>4.87</v>
+        <v>4.76</v>
       </c>
       <c r="EA11" t="n">
         <v>21</v>
       </c>
       <c r="EB11" t="n">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="EC11" t="n">
-        <v>2.5</v>
+        <v>2.48</v>
       </c>
     </row>
     <row r="12">
@@ -5405,94 +5405,94 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C12" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D12" t="n">
         <v>8</v>
       </c>
       <c r="E12" t="n">
-        <v>0</v>
+        <v>0.11</v>
       </c>
       <c r="F12" t="n">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="G12" t="n">
-        <v>2.25</v>
+        <v>2</v>
       </c>
       <c r="H12" t="n">
-        <v>100.12</v>
+        <v>98</v>
       </c>
       <c r="I12" t="n">
         <v>0</v>
       </c>
       <c r="J12" t="n">
-        <v>2.5</v>
+        <v>2.33</v>
       </c>
       <c r="K12" t="n">
-        <v>4.88</v>
+        <v>4.67</v>
       </c>
       <c r="L12" t="n">
-        <v>0.75</v>
+        <v>0.67</v>
       </c>
       <c r="M12" t="n">
-        <v>45</v>
+        <v>43.56</v>
       </c>
       <c r="N12" t="n">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="O12" t="n">
-        <v>2.62</v>
+        <v>2.67</v>
       </c>
       <c r="P12" t="n">
-        <v>11.12</v>
+        <v>11.22</v>
       </c>
       <c r="Q12" t="n">
-        <v>13.12</v>
+        <v>12.89</v>
       </c>
       <c r="R12" t="n">
-        <v>6.75</v>
+        <v>6.33</v>
       </c>
       <c r="S12" t="n">
-        <v>1.25</v>
+        <v>1.11</v>
       </c>
       <c r="T12" t="n">
-        <v>1.5</v>
+        <v>1.67</v>
       </c>
       <c r="U12" t="n">
-        <v>0.38</v>
+        <v>0.33</v>
       </c>
       <c r="V12" t="n">
-        <v>0.38</v>
+        <v>0.33</v>
       </c>
       <c r="W12" t="n">
         <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>53.5</v>
+        <v>50.78</v>
       </c>
       <c r="Y12" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="Z12" t="n">
-        <v>13.25</v>
+        <v>13</v>
       </c>
       <c r="AA12" t="n">
-        <v>7.88</v>
+        <v>7.78</v>
       </c>
       <c r="AB12" t="n">
-        <v>5.38</v>
+        <v>5.22</v>
       </c>
       <c r="AC12" t="n">
-        <v>21</v>
+        <v>20.22</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.54</v>
+        <v>1.51</v>
       </c>
       <c r="AE12" t="n">
-        <v>2.25</v>
+        <v>2.11</v>
       </c>
       <c r="AF12" t="n">
         <v>0</v>
@@ -5576,49 +5576,49 @@
         <v>2.38</v>
       </c>
       <c r="BG12" t="n">
-        <v>2.06</v>
+        <v>2.12</v>
       </c>
       <c r="BH12" t="n">
-        <v>9.119999999999999</v>
+        <v>9.35</v>
       </c>
       <c r="BI12" t="n">
-        <v>2.06</v>
+        <v>2.12</v>
       </c>
       <c r="BJ12" t="n">
-        <v>0.62</v>
+        <v>0.71</v>
       </c>
       <c r="BK12" t="n">
-        <v>0.38</v>
+        <v>0.35</v>
       </c>
       <c r="BL12" t="n">
-        <v>0.62</v>
+        <v>0.65</v>
       </c>
       <c r="BM12" t="n">
-        <v>0.44</v>
+        <v>0.41</v>
       </c>
       <c r="BN12" t="n">
         <v>1.06</v>
       </c>
       <c r="BO12" t="n">
-        <v>1</v>
+        <v>1.06</v>
       </c>
       <c r="BP12" t="n">
-        <v>3.94</v>
+        <v>4</v>
       </c>
       <c r="BQ12" t="n">
-        <v>5.19</v>
+        <v>5.35</v>
       </c>
       <c r="BR12" t="n">
-        <v>93.75</v>
+        <v>94.12</v>
       </c>
       <c r="BS12" t="n">
-        <v>68.75</v>
+        <v>70.59</v>
       </c>
       <c r="BT12" t="n">
-        <v>31.25</v>
+        <v>35.29</v>
       </c>
       <c r="BU12" t="n">
-        <v>12.5</v>
+        <v>11.76</v>
       </c>
       <c r="BV12" t="n">
         <v>0</v>
@@ -5627,13 +5627,13 @@
         <v>0</v>
       </c>
       <c r="BX12" t="n">
-        <v>56.25</v>
+        <v>52.94</v>
       </c>
       <c r="BY12" t="n">
-        <v>2.66</v>
+        <v>2.74</v>
       </c>
       <c r="BZ12" t="n">
-        <v>2.87</v>
+        <v>3</v>
       </c>
       <c r="CA12" t="n">
         <v>3.58</v>
@@ -5648,19 +5648,19 @@
         <v>4.74</v>
       </c>
       <c r="CE12" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="CF12" t="n">
         <v>2.58</v>
       </c>
       <c r="CG12" t="n">
-        <v>3.07</v>
+        <v>3.06</v>
       </c>
       <c r="CH12" t="n">
         <v>1.46</v>
       </c>
       <c r="CI12" t="n">
-        <v>2.1</v>
+        <v>2.11</v>
       </c>
       <c r="CJ12" t="n">
         <v>1.69</v>
@@ -5669,28 +5669,28 @@
         <v>1.49</v>
       </c>
       <c r="CL12" t="n">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="CM12" t="n">
         <v>2.45</v>
       </c>
       <c r="CN12" t="n">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="CO12" t="n">
         <v>1.25</v>
       </c>
       <c r="CP12" t="n">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="CQ12" t="n">
-        <v>3.03</v>
+        <v>3.02</v>
       </c>
       <c r="CR12" t="n">
         <v>1.36</v>
       </c>
       <c r="CS12" t="n">
-        <v>2.68</v>
+        <v>2.69</v>
       </c>
       <c r="CT12" t="n">
         <v>3.19</v>
@@ -5723,82 +5723,82 @@
         <v>1.87</v>
       </c>
       <c r="DD12" t="n">
-        <v>3.07</v>
+        <v>3.08</v>
       </c>
       <c r="DE12" t="n">
-        <v>0</v>
+        <v>0.06</v>
       </c>
       <c r="DF12" t="n">
-        <v>1.69</v>
+        <v>1.59</v>
       </c>
       <c r="DG12" t="n">
-        <v>2.18</v>
+        <v>2.06</v>
       </c>
       <c r="DH12" t="n">
-        <v>91.94</v>
+        <v>91.29000000000001</v>
       </c>
       <c r="DI12" t="n">
         <v>0</v>
       </c>
       <c r="DJ12" t="n">
-        <v>2.56</v>
+        <v>2.47</v>
       </c>
       <c r="DK12" t="n">
-        <v>4.06</v>
+        <v>4</v>
       </c>
       <c r="DL12" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.53</v>
       </c>
       <c r="DM12" t="n">
-        <v>38.56</v>
+        <v>38.18</v>
       </c>
       <c r="DN12" t="n">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="DO12" t="n">
-        <v>1.87</v>
+        <v>1.94</v>
       </c>
       <c r="DP12" t="n">
-        <v>12.62</v>
+        <v>12.58</v>
       </c>
       <c r="DQ12" t="n">
-        <v>13</v>
+        <v>12.89</v>
       </c>
       <c r="DR12" t="n">
-        <v>7.94</v>
+        <v>7.64</v>
       </c>
       <c r="DS12" t="n">
-        <v>0.19</v>
+        <v>0.17</v>
       </c>
       <c r="DT12" t="n">
-        <v>0.19</v>
+        <v>0.17</v>
       </c>
       <c r="DU12" t="n">
         <v>0</v>
       </c>
       <c r="DV12" t="n">
-        <v>48.56</v>
+        <v>47.41</v>
       </c>
       <c r="DW12" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DX12" t="n">
-        <v>11.38</v>
+        <v>11.35</v>
       </c>
       <c r="DY12" t="n">
-        <v>7.19</v>
+        <v>7.18</v>
       </c>
       <c r="DZ12" t="n">
-        <v>4.19</v>
+        <v>4.18</v>
       </c>
       <c r="EA12" t="n">
-        <v>19.88</v>
+        <v>19.53</v>
       </c>
       <c r="EB12" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="EC12" t="n">
-        <v>2.32</v>
+        <v>2.24</v>
       </c>
     </row>
     <row r="13">
@@ -5808,94 +5808,94 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C13" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D13" t="n">
         <v>8</v>
       </c>
       <c r="E13" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="F13" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="G13" t="n">
-        <v>3.75</v>
+        <v>3.89</v>
       </c>
       <c r="H13" t="n">
-        <v>109.25</v>
+        <v>106.78</v>
       </c>
       <c r="I13" t="n">
         <v>0</v>
       </c>
       <c r="J13" t="n">
-        <v>2</v>
+        <v>1.89</v>
       </c>
       <c r="K13" t="n">
-        <v>5.38</v>
+        <v>5.67</v>
       </c>
       <c r="L13" t="n">
-        <v>0.25</v>
+        <v>0.33</v>
       </c>
       <c r="M13" t="n">
-        <v>59</v>
+        <v>56.56</v>
       </c>
       <c r="N13" t="n">
-        <v>0.38</v>
+        <v>0.33</v>
       </c>
       <c r="O13" t="n">
-        <v>1.62</v>
+        <v>1.78</v>
       </c>
       <c r="P13" t="n">
-        <v>11.75</v>
+        <v>11.22</v>
       </c>
       <c r="Q13" t="n">
-        <v>11.38</v>
+        <v>11</v>
       </c>
       <c r="R13" t="n">
-        <v>5.38</v>
+        <v>5.78</v>
       </c>
       <c r="S13" t="n">
-        <v>1.12</v>
+        <v>1.22</v>
       </c>
       <c r="T13" t="n">
-        <v>1.5</v>
+        <v>1.67</v>
       </c>
       <c r="U13" t="n">
-        <v>0.12</v>
+        <v>0.22</v>
       </c>
       <c r="V13" t="n">
-        <v>0.12</v>
+        <v>0.22</v>
       </c>
       <c r="W13" t="n">
         <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>56</v>
+        <v>54.56</v>
       </c>
       <c r="Y13" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="Z13" t="n">
-        <v>15.88</v>
+        <v>15.67</v>
       </c>
       <c r="AA13" t="n">
-        <v>11.38</v>
+        <v>11</v>
       </c>
       <c r="AB13" t="n">
-        <v>4.5</v>
+        <v>4.67</v>
       </c>
       <c r="AC13" t="n">
-        <v>24.12</v>
+        <v>23.33</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.75</v>
+        <v>1.67</v>
       </c>
       <c r="AF13" t="n">
         <v>0</v>
@@ -5979,70 +5979,70 @@
         <v>1.5</v>
       </c>
       <c r="BG13" t="n">
-        <v>2.56</v>
+        <v>2.71</v>
       </c>
       <c r="BH13" t="n">
-        <v>10</v>
+        <v>10.24</v>
       </c>
       <c r="BI13" t="n">
-        <v>2.56</v>
+        <v>2.71</v>
       </c>
       <c r="BJ13" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.76</v>
       </c>
       <c r="BK13" t="n">
-        <v>0.44</v>
+        <v>0.47</v>
       </c>
       <c r="BL13" t="n">
-        <v>0.62</v>
+        <v>0.65</v>
       </c>
       <c r="BM13" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.82</v>
       </c>
       <c r="BN13" t="n">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="BO13" t="n">
-        <v>1.12</v>
+        <v>1.24</v>
       </c>
       <c r="BP13" t="n">
-        <v>4.25</v>
+        <v>4.24</v>
       </c>
       <c r="BQ13" t="n">
-        <v>5.75</v>
+        <v>6</v>
       </c>
       <c r="BR13" t="n">
         <v>100</v>
       </c>
       <c r="BS13" t="n">
-        <v>87.5</v>
+        <v>88.23999999999999</v>
       </c>
       <c r="BT13" t="n">
-        <v>50</v>
+        <v>52.94</v>
       </c>
       <c r="BU13" t="n">
-        <v>18.75</v>
+        <v>23.53</v>
       </c>
       <c r="BV13" t="n">
-        <v>0</v>
+        <v>5.88</v>
       </c>
       <c r="BW13" t="n">
         <v>0</v>
       </c>
       <c r="BX13" t="n">
-        <v>56.25</v>
+        <v>58.82</v>
       </c>
       <c r="BY13" t="n">
-        <v>2.21</v>
+        <v>2.38</v>
       </c>
       <c r="BZ13" t="n">
-        <v>2.4</v>
+        <v>2.49</v>
       </c>
       <c r="CA13" t="n">
         <v>3.72</v>
       </c>
       <c r="CB13" t="n">
-        <v>3.82</v>
+        <v>3.83</v>
       </c>
       <c r="CC13" t="n">
         <v>4.19</v>
@@ -6051,28 +6051,28 @@
         <v>4.45</v>
       </c>
       <c r="CE13" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="CF13" t="n">
-        <v>2.45</v>
+        <v>2.43</v>
       </c>
       <c r="CG13" t="n">
-        <v>3.18</v>
+        <v>3.21</v>
       </c>
       <c r="CH13" t="n">
         <v>1.51</v>
       </c>
       <c r="CI13" t="n">
-        <v>2.19</v>
+        <v>2.2</v>
       </c>
       <c r="CJ13" t="n">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="CK13" t="n">
         <v>1.45</v>
       </c>
       <c r="CL13" t="n">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="CM13" t="n">
         <v>2.54</v>
@@ -6081,13 +6081,13 @@
         <v>1.96</v>
       </c>
       <c r="CO13" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="CP13" t="n">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="CQ13" t="n">
-        <v>2.8</v>
+        <v>2.76</v>
       </c>
       <c r="CR13" t="n">
         <v>1.35</v>
@@ -6102,106 +6102,106 @@
         <v>1.52</v>
       </c>
       <c r="CV13" t="n">
-        <v>2.3</v>
+        <v>2.33</v>
       </c>
       <c r="CW13" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="CX13" t="n">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="CY13" t="n">
         <v>1.84</v>
       </c>
       <c r="CZ13" t="n">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="DA13" t="n">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="DB13" t="n">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="DC13" t="n">
-        <v>1.78</v>
+        <v>1.76</v>
       </c>
       <c r="DD13" t="n">
-        <v>2.86</v>
+        <v>2.83</v>
       </c>
       <c r="DE13" t="n">
         <v>0.06</v>
       </c>
       <c r="DF13" t="n">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="DG13" t="n">
-        <v>3.68</v>
+        <v>3.76</v>
       </c>
       <c r="DH13" t="n">
-        <v>104.44</v>
+        <v>103.41</v>
       </c>
       <c r="DI13" t="n">
         <v>0.06</v>
       </c>
       <c r="DJ13" t="n">
-        <v>1.75</v>
+        <v>1.71</v>
       </c>
       <c r="DK13" t="n">
-        <v>5.69</v>
+        <v>5.83</v>
       </c>
       <c r="DL13" t="n">
-        <v>0.32</v>
+        <v>0.35</v>
       </c>
       <c r="DM13" t="n">
-        <v>55.88</v>
+        <v>54.77</v>
       </c>
       <c r="DN13" t="n">
-        <v>0.44</v>
+        <v>0.41</v>
       </c>
       <c r="DO13" t="n">
-        <v>2</v>
+        <v>2.06</v>
       </c>
       <c r="DP13" t="n">
-        <v>11.88</v>
+        <v>11.59</v>
       </c>
       <c r="DQ13" t="n">
-        <v>11.38</v>
+        <v>11.18</v>
       </c>
       <c r="DR13" t="n">
-        <v>6.94</v>
+        <v>7.06</v>
       </c>
       <c r="DS13" t="n">
-        <v>0.25</v>
+        <v>0.3</v>
       </c>
       <c r="DT13" t="n">
-        <v>0.25</v>
+        <v>0.3</v>
       </c>
       <c r="DU13" t="n">
         <v>0</v>
       </c>
       <c r="DV13" t="n">
-        <v>54.12</v>
+        <v>53.47</v>
       </c>
       <c r="DW13" t="n">
         <v>0.06</v>
       </c>
       <c r="DX13" t="n">
-        <v>14.69</v>
+        <v>14.65</v>
       </c>
       <c r="DY13" t="n">
-        <v>10.25</v>
+        <v>10.12</v>
       </c>
       <c r="DZ13" t="n">
-        <v>4.44</v>
+        <v>4.53</v>
       </c>
       <c r="EA13" t="n">
-        <v>23.5</v>
+        <v>23.12</v>
       </c>
       <c r="EB13" t="n">
         <v>1.64</v>
       </c>
       <c r="EC13" t="n">
-        <v>1.62</v>
+        <v>1.59</v>
       </c>
     </row>
     <row r="14">
@@ -6211,13 +6211,13 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C14" t="n">
         <v>8</v>
       </c>
       <c r="D14" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E14" t="n">
         <v>0.12</v>
@@ -6301,52 +6301,52 @@
         <v>1.88</v>
       </c>
       <c r="AF14" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.75</v>
+        <v>1.78</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.88</v>
+        <v>2</v>
       </c>
       <c r="AI14" t="n">
-        <v>92.75</v>
+        <v>92.11</v>
       </c>
       <c r="AJ14" t="n">
         <v>0</v>
       </c>
       <c r="AK14" t="n">
-        <v>2.12</v>
+        <v>2.11</v>
       </c>
       <c r="AL14" t="n">
-        <v>4.62</v>
+        <v>4.44</v>
       </c>
       <c r="AM14" t="n">
-        <v>0.62</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AN14" t="n">
-        <v>48.25</v>
+        <v>47.78</v>
       </c>
       <c r="AO14" t="n">
-        <v>0.38</v>
+        <v>0.33</v>
       </c>
       <c r="AP14" t="n">
-        <v>2.75</v>
+        <v>2.44</v>
       </c>
       <c r="AQ14" t="n">
-        <v>10.88</v>
+        <v>10.78</v>
       </c>
       <c r="AR14" t="n">
-        <v>9.880000000000001</v>
+        <v>10</v>
       </c>
       <c r="AS14" t="n">
-        <v>6.88</v>
+        <v>6.56</v>
       </c>
       <c r="AT14" t="n">
-        <v>1.75</v>
+        <v>1.67</v>
       </c>
       <c r="AU14" t="n">
-        <v>1.12</v>
+        <v>1</v>
       </c>
       <c r="AV14" t="n">
         <v>0</v>
@@ -6358,82 +6358,82 @@
         <v>0</v>
       </c>
       <c r="AY14" t="n">
-        <v>47.88</v>
+        <v>47.67</v>
       </c>
       <c r="AZ14" t="n">
         <v>0</v>
       </c>
       <c r="BA14" t="n">
-        <v>11.12</v>
+        <v>10.67</v>
       </c>
       <c r="BB14" t="n">
         <v>7</v>
       </c>
       <c r="BC14" t="n">
-        <v>4.12</v>
+        <v>3.67</v>
       </c>
       <c r="BD14" t="n">
-        <v>21.75</v>
+        <v>21.22</v>
       </c>
       <c r="BE14" t="n">
-        <v>1.34</v>
+        <v>1.28</v>
       </c>
       <c r="BF14" t="n">
-        <v>2.12</v>
+        <v>2.11</v>
       </c>
       <c r="BG14" t="n">
-        <v>2.44</v>
+        <v>2.35</v>
       </c>
       <c r="BH14" t="n">
-        <v>9.5</v>
+        <v>9.529999999999999</v>
       </c>
       <c r="BI14" t="n">
-        <v>2.44</v>
+        <v>2.35</v>
       </c>
       <c r="BJ14" t="n">
-        <v>0.62</v>
+        <v>0.65</v>
       </c>
       <c r="BK14" t="n">
-        <v>0.62</v>
+        <v>0.59</v>
       </c>
       <c r="BL14" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.76</v>
       </c>
       <c r="BM14" t="n">
-        <v>0.38</v>
+        <v>0.35</v>
       </c>
       <c r="BN14" t="n">
-        <v>1.19</v>
+        <v>1.12</v>
       </c>
       <c r="BO14" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="BP14" t="n">
-        <v>5.19</v>
+        <v>5.06</v>
       </c>
       <c r="BQ14" t="n">
-        <v>4.31</v>
+        <v>4.47</v>
       </c>
       <c r="BR14" t="n">
-        <v>93.75</v>
+        <v>94.12</v>
       </c>
       <c r="BS14" t="n">
-        <v>68.75</v>
+        <v>64.70999999999999</v>
       </c>
       <c r="BT14" t="n">
-        <v>43.75</v>
+        <v>41.18</v>
       </c>
       <c r="BU14" t="n">
-        <v>31.25</v>
+        <v>29.41</v>
       </c>
       <c r="BV14" t="n">
-        <v>6.25</v>
+        <v>5.88</v>
       </c>
       <c r="BW14" t="n">
         <v>0</v>
       </c>
       <c r="BX14" t="n">
-        <v>56.25</v>
+        <v>52.94</v>
       </c>
       <c r="BY14" t="n">
         <v>2.03</v>
@@ -6442,16 +6442,16 @@
         <v>2.17</v>
       </c>
       <c r="CA14" t="n">
-        <v>3.57</v>
+        <v>3.56</v>
       </c>
       <c r="CB14" t="n">
-        <v>3.56</v>
+        <v>3.55</v>
       </c>
       <c r="CC14" t="n">
-        <v>4.05</v>
+        <v>3.85</v>
       </c>
       <c r="CD14" t="n">
-        <v>4.12</v>
+        <v>3.92</v>
       </c>
       <c r="CE14" t="n">
         <v>1.33</v>
@@ -6460,7 +6460,7 @@
         <v>2.63</v>
       </c>
       <c r="CG14" t="n">
-        <v>3.06</v>
+        <v>3.08</v>
       </c>
       <c r="CH14" t="n">
         <v>1.45</v>
@@ -6469,7 +6469,7 @@
         <v>2.07</v>
       </c>
       <c r="CJ14" t="n">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="CK14" t="n">
         <v>1.47</v>
@@ -6481,7 +6481,7 @@
         <v>2.57</v>
       </c>
       <c r="CN14" t="n">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="CO14" t="n">
         <v>1.26</v>
@@ -6490,7 +6490,7 @@
         <v>1.82</v>
       </c>
       <c r="CQ14" t="n">
-        <v>3.07</v>
+        <v>3.06</v>
       </c>
       <c r="CR14" t="n">
         <v>1.38</v>
@@ -6511,13 +6511,13 @@
         <v>1.75</v>
       </c>
       <c r="CX14" t="n">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="CY14" t="n">
         <v>1.86</v>
       </c>
       <c r="CZ14" t="n">
-        <v>2.45</v>
+        <v>2.46</v>
       </c>
       <c r="DA14" t="n">
         <v>1.95</v>
@@ -6526,22 +6526,22 @@
         <v>1.29</v>
       </c>
       <c r="DC14" t="n">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="DD14" t="n">
-        <v>3.24</v>
+        <v>3.25</v>
       </c>
       <c r="DE14" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DF14" t="n">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="DG14" t="n">
-        <v>1.94</v>
+        <v>2</v>
       </c>
       <c r="DH14" t="n">
-        <v>90.81999999999999</v>
+        <v>90.59</v>
       </c>
       <c r="DI14" t="n">
         <v>0</v>
@@ -6550,28 +6550,28 @@
         <v>2.18</v>
       </c>
       <c r="DK14" t="n">
-        <v>4.75</v>
+        <v>4.65</v>
       </c>
       <c r="DL14" t="n">
-        <v>0.37</v>
+        <v>0.35</v>
       </c>
       <c r="DM14" t="n">
-        <v>49.12</v>
+        <v>48.82</v>
       </c>
       <c r="DN14" t="n">
-        <v>0.38</v>
+        <v>0.35</v>
       </c>
       <c r="DO14" t="n">
-        <v>2.82</v>
+        <v>2.65</v>
       </c>
       <c r="DP14" t="n">
-        <v>11.32</v>
+        <v>11.24</v>
       </c>
       <c r="DQ14" t="n">
-        <v>11.94</v>
+        <v>11.88</v>
       </c>
       <c r="DR14" t="n">
-        <v>7</v>
+        <v>6.82</v>
       </c>
       <c r="DS14" t="n">
         <v>0.06</v>
@@ -6583,25 +6583,25 @@
         <v>0</v>
       </c>
       <c r="DV14" t="n">
-        <v>47.75</v>
+        <v>47.65</v>
       </c>
       <c r="DW14" t="n">
         <v>0.12</v>
       </c>
       <c r="DX14" t="n">
-        <v>11</v>
+        <v>10.77</v>
       </c>
       <c r="DY14" t="n">
-        <v>6.81</v>
+        <v>6.82</v>
       </c>
       <c r="DZ14" t="n">
-        <v>4.19</v>
+        <v>3.94</v>
       </c>
       <c r="EA14" t="n">
-        <v>19.88</v>
+        <v>19.7</v>
       </c>
       <c r="EB14" t="n">
-        <v>1.35</v>
+        <v>1.31</v>
       </c>
       <c r="EC14" t="n">
         <v>2</v>
@@ -6614,13 +6614,13 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C15" t="n">
         <v>8</v>
       </c>
       <c r="D15" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E15" t="n">
         <v>0.25</v>
@@ -6704,130 +6704,130 @@
         <v>2.62</v>
       </c>
       <c r="AF15" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="AI15" t="n">
-        <v>84.75</v>
+        <v>85.22</v>
       </c>
       <c r="AJ15" t="n">
         <v>0</v>
       </c>
       <c r="AK15" t="n">
-        <v>2.25</v>
+        <v>2.22</v>
       </c>
       <c r="AL15" t="n">
-        <v>2.5</v>
+        <v>2.78</v>
       </c>
       <c r="AM15" t="n">
-        <v>0.25</v>
+        <v>0.33</v>
       </c>
       <c r="AN15" t="n">
-        <v>31</v>
+        <v>32.11</v>
       </c>
       <c r="AO15" t="n">
-        <v>0.75</v>
+        <v>0.78</v>
       </c>
       <c r="AP15" t="n">
-        <v>1.12</v>
+        <v>1.44</v>
       </c>
       <c r="AQ15" t="n">
-        <v>10.75</v>
+        <v>11.33</v>
       </c>
       <c r="AR15" t="n">
-        <v>11.75</v>
+        <v>11.22</v>
       </c>
       <c r="AS15" t="n">
-        <v>9.25</v>
+        <v>9.779999999999999</v>
       </c>
       <c r="AT15" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AU15" t="n">
-        <v>0.62</v>
+        <v>0.78</v>
       </c>
       <c r="AV15" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="AW15" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="AX15" t="n">
         <v>0</v>
       </c>
       <c r="AY15" t="n">
-        <v>45.25</v>
+        <v>44.11</v>
       </c>
       <c r="AZ15" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="BA15" t="n">
-        <v>7.12</v>
+        <v>7.56</v>
       </c>
       <c r="BB15" t="n">
-        <v>5</v>
+        <v>5.44</v>
       </c>
       <c r="BC15" t="n">
-        <v>2.12</v>
+        <v>2.11</v>
       </c>
       <c r="BD15" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="BE15" t="n">
-        <v>0.83</v>
+        <v>0.87</v>
       </c>
       <c r="BF15" t="n">
         <v>2</v>
       </c>
       <c r="BG15" t="n">
-        <v>2.06</v>
+        <v>2.12</v>
       </c>
       <c r="BH15" t="n">
-        <v>9.44</v>
+        <v>9.710000000000001</v>
       </c>
       <c r="BI15" t="n">
-        <v>2.06</v>
+        <v>2.12</v>
       </c>
       <c r="BJ15" t="n">
-        <v>0.5</v>
+        <v>0.47</v>
       </c>
       <c r="BK15" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.65</v>
       </c>
       <c r="BL15" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.71</v>
       </c>
       <c r="BM15" t="n">
-        <v>0.31</v>
+        <v>0.29</v>
       </c>
       <c r="BN15" t="n">
         <v>1</v>
       </c>
       <c r="BO15" t="n">
-        <v>1.06</v>
+        <v>1.12</v>
       </c>
       <c r="BP15" t="n">
-        <v>4.31</v>
+        <v>4.53</v>
       </c>
       <c r="BQ15" t="n">
-        <v>5.12</v>
+        <v>5.18</v>
       </c>
       <c r="BR15" t="n">
-        <v>93.75</v>
+        <v>94.12</v>
       </c>
       <c r="BS15" t="n">
-        <v>62.5</v>
+        <v>64.70999999999999</v>
       </c>
       <c r="BT15" t="n">
-        <v>37.5</v>
+        <v>41.18</v>
       </c>
       <c r="BU15" t="n">
-        <v>12.5</v>
+        <v>11.76</v>
       </c>
       <c r="BV15" t="n">
         <v>0</v>
@@ -6836,7 +6836,7 @@
         <v>0</v>
       </c>
       <c r="BX15" t="n">
-        <v>31.25</v>
+        <v>35.29</v>
       </c>
       <c r="BY15" t="n">
         <v>2.9</v>
@@ -6851,10 +6851,10 @@
         <v>3.57</v>
       </c>
       <c r="CC15" t="n">
-        <v>4.18</v>
+        <v>4.11</v>
       </c>
       <c r="CD15" t="n">
-        <v>4.74</v>
+        <v>4.66</v>
       </c>
       <c r="CE15" t="n">
         <v>1.37</v>
@@ -6863,7 +6863,7 @@
         <v>2.77</v>
       </c>
       <c r="CG15" t="n">
-        <v>2.95</v>
+        <v>2.94</v>
       </c>
       <c r="CH15" t="n">
         <v>1.42</v>
@@ -6872,19 +6872,19 @@
         <v>1.97</v>
       </c>
       <c r="CJ15" t="n">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="CK15" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="CL15" t="n">
-        <v>1.82</v>
+        <v>1.84</v>
       </c>
       <c r="CM15" t="n">
-        <v>2.59</v>
+        <v>2.58</v>
       </c>
       <c r="CN15" t="n">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="CO15" t="n">
         <v>1.3</v>
@@ -6893,7 +6893,7 @@
         <v>1.91</v>
       </c>
       <c r="CQ15" t="n">
-        <v>3.39</v>
+        <v>3.37</v>
       </c>
       <c r="CR15" t="n">
         <v>1.39</v>
@@ -6902,7 +6902,7 @@
         <v>2.87</v>
       </c>
       <c r="CT15" t="n">
-        <v>3.06</v>
+        <v>3.07</v>
       </c>
       <c r="CU15" t="n">
         <v>1.45</v>
@@ -6911,7 +6911,7 @@
         <v>2.1</v>
       </c>
       <c r="CW15" t="n">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="CX15" t="n">
         <v>1.56</v>
@@ -6920,10 +6920,10 @@
         <v>1.89</v>
       </c>
       <c r="CZ15" t="n">
-        <v>2.42</v>
+        <v>2.41</v>
       </c>
       <c r="DA15" t="n">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="DB15" t="n">
         <v>1.31</v>
@@ -6938,43 +6938,43 @@
         <v>0.18</v>
       </c>
       <c r="DF15" t="n">
-        <v>1.62</v>
+        <v>1.59</v>
       </c>
       <c r="DG15" t="n">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="DH15" t="n">
-        <v>85.12</v>
+        <v>85.34999999999999</v>
       </c>
       <c r="DI15" t="n">
         <v>0</v>
       </c>
       <c r="DJ15" t="n">
-        <v>2.82</v>
+        <v>2.77</v>
       </c>
       <c r="DK15" t="n">
-        <v>3.94</v>
+        <v>4</v>
       </c>
       <c r="DL15" t="n">
-        <v>0.38</v>
+        <v>0.41</v>
       </c>
       <c r="DM15" t="n">
-        <v>43.62</v>
+        <v>43.47</v>
       </c>
       <c r="DN15" t="n">
         <v>1</v>
       </c>
       <c r="DO15" t="n">
-        <v>2.18</v>
+        <v>2.29</v>
       </c>
       <c r="DP15" t="n">
-        <v>11.07</v>
+        <v>11.35</v>
       </c>
       <c r="DQ15" t="n">
-        <v>12.07</v>
+        <v>11.77</v>
       </c>
       <c r="DR15" t="n">
-        <v>8.82</v>
+        <v>9.119999999999999</v>
       </c>
       <c r="DS15" t="n">
         <v>0.18</v>
@@ -6986,28 +6986,28 @@
         <v>0</v>
       </c>
       <c r="DV15" t="n">
-        <v>45.18</v>
+        <v>44.59</v>
       </c>
       <c r="DW15" t="n">
-        <v>0.32</v>
+        <v>0.3</v>
       </c>
       <c r="DX15" t="n">
-        <v>9.81</v>
+        <v>9.880000000000001</v>
       </c>
       <c r="DY15" t="n">
-        <v>6.31</v>
+        <v>6.47</v>
       </c>
       <c r="DZ15" t="n">
-        <v>3.5</v>
+        <v>3.41</v>
       </c>
       <c r="EA15" t="n">
-        <v>17.69</v>
+        <v>18.18</v>
       </c>
       <c r="EB15" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="EC15" t="n">
-        <v>2.31</v>
+        <v>2.29</v>
       </c>
     </row>
     <row r="16">
@@ -7017,94 +7017,94 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C16" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D16" t="n">
         <v>9</v>
       </c>
       <c r="E16" t="n">
-        <v>0.43</v>
+        <v>0.38</v>
       </c>
       <c r="F16" t="n">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="G16" t="n">
-        <v>3.14</v>
+        <v>3.5</v>
       </c>
       <c r="H16" t="n">
-        <v>97.56999999999999</v>
+        <v>103.88</v>
       </c>
       <c r="I16" t="n">
         <v>0</v>
       </c>
       <c r="J16" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="K16" t="n">
-        <v>6.14</v>
+        <v>6.38</v>
       </c>
       <c r="L16" t="n">
-        <v>0.71</v>
+        <v>0.62</v>
       </c>
       <c r="M16" t="n">
-        <v>56.43</v>
+        <v>60.12</v>
       </c>
       <c r="N16" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="O16" t="n">
-        <v>3</v>
+        <v>2.88</v>
       </c>
       <c r="P16" t="n">
-        <v>12</v>
+        <v>12.12</v>
       </c>
       <c r="Q16" t="n">
-        <v>10</v>
+        <v>9.5</v>
       </c>
       <c r="R16" t="n">
-        <v>5.71</v>
+        <v>5.62</v>
       </c>
       <c r="S16" t="n">
-        <v>0.14</v>
+        <v>0.25</v>
       </c>
       <c r="T16" t="n">
-        <v>2.71</v>
+        <v>2.5</v>
       </c>
       <c r="U16" t="n">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="V16" t="n">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="W16" t="n">
         <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>53.71</v>
+        <v>54.88</v>
       </c>
       <c r="Y16" t="n">
         <v>0</v>
       </c>
       <c r="Z16" t="n">
-        <v>18</v>
+        <v>18.25</v>
       </c>
       <c r="AA16" t="n">
-        <v>11.43</v>
+        <v>11.25</v>
       </c>
       <c r="AB16" t="n">
-        <v>6.57</v>
+        <v>7</v>
       </c>
       <c r="AC16" t="n">
-        <v>19.43</v>
+        <v>19.88</v>
       </c>
       <c r="AD16" t="n">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AF16" t="n">
         <v>0.11</v>
@@ -7188,70 +7188,70 @@
         <v>3</v>
       </c>
       <c r="BG16" t="n">
-        <v>2.5</v>
+        <v>2.47</v>
       </c>
       <c r="BH16" t="n">
-        <v>9.75</v>
+        <v>9.65</v>
       </c>
       <c r="BI16" t="n">
-        <v>2.5</v>
+        <v>2.47</v>
       </c>
       <c r="BJ16" t="n">
-        <v>0.5</v>
+        <v>0.47</v>
       </c>
       <c r="BK16" t="n">
-        <v>0.31</v>
+        <v>0.35</v>
       </c>
       <c r="BL16" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="BM16" t="n">
-        <v>0.5</v>
+        <v>0.47</v>
       </c>
       <c r="BN16" t="n">
-        <v>1.69</v>
+        <v>1.65</v>
       </c>
       <c r="BO16" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.82</v>
       </c>
       <c r="BP16" t="n">
-        <v>5.06</v>
+        <v>4.88</v>
       </c>
       <c r="BQ16" t="n">
-        <v>4.69</v>
+        <v>4.76</v>
       </c>
       <c r="BR16" t="n">
-        <v>93.75</v>
+        <v>94.12</v>
       </c>
       <c r="BS16" t="n">
-        <v>75</v>
+        <v>76.47</v>
       </c>
       <c r="BT16" t="n">
-        <v>37.5</v>
+        <v>35.29</v>
       </c>
       <c r="BU16" t="n">
-        <v>25</v>
+        <v>23.53</v>
       </c>
       <c r="BV16" t="n">
-        <v>18.75</v>
+        <v>17.65</v>
       </c>
       <c r="BW16" t="n">
         <v>0</v>
       </c>
       <c r="BX16" t="n">
-        <v>37.5</v>
+        <v>41.18</v>
       </c>
       <c r="BY16" t="n">
         <v>1.35</v>
       </c>
       <c r="BZ16" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="CA16" t="n">
-        <v>4.24</v>
+        <v>4.26</v>
       </c>
       <c r="CB16" t="n">
-        <v>4.36</v>
+        <v>4.42</v>
       </c>
       <c r="CC16" t="n">
         <v>1.87</v>
@@ -7260,19 +7260,19 @@
         <v>1.91</v>
       </c>
       <c r="CE16" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="CF16" t="n">
-        <v>2.47</v>
+        <v>2.46</v>
       </c>
       <c r="CG16" t="n">
-        <v>3.22</v>
+        <v>3.24</v>
       </c>
       <c r="CH16" t="n">
         <v>1.51</v>
       </c>
       <c r="CI16" t="n">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="CJ16" t="n">
         <v>1.82</v>
@@ -7281,34 +7281,34 @@
         <v>1.47</v>
       </c>
       <c r="CL16" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="CM16" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="CN16" t="n">
         <v>1.95</v>
-      </c>
-      <c r="CM16" t="n">
-        <v>2.49</v>
-      </c>
-      <c r="CN16" t="n">
-        <v>1.94</v>
       </c>
       <c r="CO16" t="n">
         <v>1.22</v>
       </c>
       <c r="CP16" t="n">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="CQ16" t="n">
-        <v>2.74</v>
+        <v>2.72</v>
       </c>
       <c r="CR16" t="n">
         <v>1.35</v>
       </c>
       <c r="CS16" t="n">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="CT16" t="n">
         <v>3.24</v>
       </c>
       <c r="CU16" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="CV16" t="n">
         <v>2.06</v>
@@ -7320,97 +7320,97 @@
         <v>1.58</v>
       </c>
       <c r="CY16" t="n">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="CZ16" t="n">
         <v>2.36</v>
       </c>
       <c r="DA16" t="n">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="DB16" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="DC16" t="n">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="DD16" t="n">
-        <v>2.9</v>
+        <v>2.87</v>
       </c>
       <c r="DE16" t="n">
-        <v>0.25</v>
+        <v>0.24</v>
       </c>
       <c r="DF16" t="n">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="DG16" t="n">
-        <v>2.94</v>
+        <v>3.12</v>
       </c>
       <c r="DH16" t="n">
-        <v>106.06</v>
+        <v>108.53</v>
       </c>
       <c r="DI16" t="n">
         <v>0.06</v>
       </c>
       <c r="DJ16" t="n">
-        <v>2.25</v>
+        <v>2.18</v>
       </c>
       <c r="DK16" t="n">
-        <v>5.68</v>
+        <v>5.82</v>
       </c>
       <c r="DL16" t="n">
-        <v>0.63</v>
+        <v>0.59</v>
       </c>
       <c r="DM16" t="n">
-        <v>52.63</v>
+        <v>54.59</v>
       </c>
       <c r="DN16" t="n">
-        <v>0.75</v>
+        <v>0.7</v>
       </c>
       <c r="DO16" t="n">
-        <v>2.75</v>
+        <v>2.71</v>
       </c>
       <c r="DP16" t="n">
         <v>12.88</v>
       </c>
       <c r="DQ16" t="n">
-        <v>9.25</v>
+        <v>9.06</v>
       </c>
       <c r="DR16" t="n">
-        <v>5.94</v>
+        <v>5.88</v>
       </c>
       <c r="DS16" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="DT16" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="DU16" t="n">
         <v>0</v>
       </c>
       <c r="DV16" t="n">
-        <v>53.69</v>
+        <v>54.24</v>
       </c>
       <c r="DW16" t="n">
         <v>0</v>
       </c>
       <c r="DX16" t="n">
-        <v>15.63</v>
+        <v>15.88</v>
       </c>
       <c r="DY16" t="n">
         <v>9.880000000000001</v>
       </c>
       <c r="DZ16" t="n">
-        <v>5.75</v>
+        <v>6</v>
       </c>
       <c r="EA16" t="n">
-        <v>19.57</v>
+        <v>19.77</v>
       </c>
       <c r="EB16" t="n">
-        <v>1.77</v>
+        <v>1.82</v>
       </c>
       <c r="EC16" t="n">
-        <v>2.25</v>
+        <v>2.18</v>
       </c>
     </row>
     <row r="17">
@@ -7420,13 +7420,13 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C17" t="n">
         <v>8</v>
       </c>
       <c r="D17" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
@@ -7510,139 +7510,139 @@
         <v>1.38</v>
       </c>
       <c r="AF17" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.38</v>
+        <v>1.44</v>
       </c>
       <c r="AH17" t="n">
-        <v>2.38</v>
+        <v>2.33</v>
       </c>
       <c r="AI17" t="n">
-        <v>88.38</v>
+        <v>90</v>
       </c>
       <c r="AJ17" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="AK17" t="n">
-        <v>1.88</v>
+        <v>2</v>
       </c>
       <c r="AL17" t="n">
-        <v>4.62</v>
+        <v>4.44</v>
       </c>
       <c r="AM17" t="n">
-        <v>0.12</v>
+        <v>0.22</v>
       </c>
       <c r="AN17" t="n">
-        <v>48.75</v>
+        <v>49.11</v>
       </c>
       <c r="AO17" t="n">
-        <v>0.38</v>
+        <v>0.44</v>
       </c>
       <c r="AP17" t="n">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="AQ17" t="n">
-        <v>13.5</v>
+        <v>13.22</v>
       </c>
       <c r="AR17" t="n">
-        <v>9.119999999999999</v>
+        <v>10.11</v>
       </c>
       <c r="AS17" t="n">
-        <v>9.880000000000001</v>
+        <v>10</v>
       </c>
       <c r="AT17" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="AU17" t="n">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="AV17" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="AW17" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="AX17" t="n">
         <v>0</v>
       </c>
       <c r="AY17" t="n">
-        <v>47.12</v>
+        <v>47.89</v>
       </c>
       <c r="AZ17" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="BA17" t="n">
-        <v>11.5</v>
+        <v>10.67</v>
       </c>
       <c r="BB17" t="n">
-        <v>7.5</v>
+        <v>7</v>
       </c>
       <c r="BC17" t="n">
-        <v>4</v>
+        <v>3.67</v>
       </c>
       <c r="BD17" t="n">
-        <v>19.62</v>
+        <v>19.33</v>
       </c>
       <c r="BE17" t="n">
-        <v>1.36</v>
+        <v>1.29</v>
       </c>
       <c r="BF17" t="n">
-        <v>1.62</v>
+        <v>1.78</v>
       </c>
       <c r="BG17" t="n">
-        <v>2.75</v>
+        <v>2.71</v>
       </c>
       <c r="BH17" t="n">
-        <v>10.69</v>
+        <v>10.47</v>
       </c>
       <c r="BI17" t="n">
-        <v>2.75</v>
+        <v>2.71</v>
       </c>
       <c r="BJ17" t="n">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="BK17" t="n">
-        <v>0.5</v>
+        <v>0.53</v>
       </c>
       <c r="BL17" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.65</v>
       </c>
       <c r="BM17" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.76</v>
       </c>
       <c r="BN17" t="n">
-        <v>1.5</v>
+        <v>1.41</v>
       </c>
       <c r="BO17" t="n">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="BP17" t="n">
-        <v>3.88</v>
+        <v>3.76</v>
       </c>
       <c r="BQ17" t="n">
-        <v>6</v>
+        <v>5.94</v>
       </c>
       <c r="BR17" t="n">
-        <v>87.5</v>
+        <v>88.23999999999999</v>
       </c>
       <c r="BS17" t="n">
-        <v>81.25</v>
+        <v>82.34999999999999</v>
       </c>
       <c r="BT17" t="n">
-        <v>43.75</v>
+        <v>41.18</v>
       </c>
       <c r="BU17" t="n">
-        <v>37.5</v>
+        <v>35.29</v>
       </c>
       <c r="BV17" t="n">
-        <v>25</v>
+        <v>23.53</v>
       </c>
       <c r="BW17" t="n">
         <v>0</v>
       </c>
       <c r="BX17" t="n">
-        <v>62.5</v>
+        <v>64.70999999999999</v>
       </c>
       <c r="BY17" t="n">
         <v>3.12</v>
@@ -7651,31 +7651,31 @@
         <v>3.41</v>
       </c>
       <c r="CA17" t="n">
+        <v>3.69</v>
+      </c>
+      <c r="CB17" t="n">
         <v>3.72</v>
       </c>
-      <c r="CB17" t="n">
+      <c r="CC17" t="n">
         <v>3.74</v>
       </c>
-      <c r="CC17" t="n">
-        <v>3.81</v>
-      </c>
       <c r="CD17" t="n">
-        <v>4.17</v>
+        <v>4.12</v>
       </c>
       <c r="CE17" t="n">
         <v>1.3</v>
       </c>
       <c r="CF17" t="n">
-        <v>2.43</v>
+        <v>2.44</v>
       </c>
       <c r="CG17" t="n">
-        <v>3.34</v>
+        <v>3.33</v>
       </c>
       <c r="CH17" t="n">
         <v>1.52</v>
       </c>
       <c r="CI17" t="n">
-        <v>2.23</v>
+        <v>2.22</v>
       </c>
       <c r="CJ17" t="n">
         <v>1.61</v>
@@ -7687,22 +7687,22 @@
         <v>1.78</v>
       </c>
       <c r="CM17" t="n">
-        <v>2.71</v>
+        <v>2.7</v>
       </c>
       <c r="CN17" t="n">
-        <v>2.08</v>
+        <v>2.07</v>
       </c>
       <c r="CO17" t="n">
         <v>1.2</v>
       </c>
       <c r="CP17" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="CQ17" t="n">
-        <v>2.69</v>
+        <v>2.71</v>
       </c>
       <c r="CR17" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="CS17" t="n">
         <v>2.58</v>
@@ -7714,19 +7714,19 @@
         <v>1.53</v>
       </c>
       <c r="CV17" t="n">
-        <v>2.38</v>
+        <v>2.37</v>
       </c>
       <c r="CW17" t="n">
         <v>1.64</v>
       </c>
       <c r="CX17" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="CY17" t="n">
         <v>1.76</v>
       </c>
       <c r="CZ17" t="n">
-        <v>2.45</v>
+        <v>2.48</v>
       </c>
       <c r="DA17" t="n">
         <v>2.07</v>
@@ -7735,85 +7735,85 @@
         <v>1.23</v>
       </c>
       <c r="DC17" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="DD17" t="n">
-        <v>2.79</v>
+        <v>2.8</v>
       </c>
       <c r="DE17" t="n">
         <v>0.06</v>
       </c>
       <c r="DF17" t="n">
-        <v>1.19</v>
+        <v>1.23</v>
       </c>
       <c r="DG17" t="n">
-        <v>2.32</v>
+        <v>2.29</v>
       </c>
       <c r="DH17" t="n">
-        <v>90.5</v>
+        <v>91.23</v>
       </c>
       <c r="DI17" t="n">
         <v>0.06</v>
       </c>
       <c r="DJ17" t="n">
-        <v>1.75</v>
+        <v>1.82</v>
       </c>
       <c r="DK17" t="n">
-        <v>4.25</v>
+        <v>4.18</v>
       </c>
       <c r="DL17" t="n">
-        <v>0.12</v>
+        <v>0.17</v>
       </c>
       <c r="DM17" t="n">
-        <v>43.38</v>
+        <v>43.88</v>
       </c>
       <c r="DN17" t="n">
-        <v>0.44</v>
+        <v>0.47</v>
       </c>
       <c r="DO17" t="n">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="DP17" t="n">
-        <v>11.88</v>
+        <v>11.82</v>
       </c>
       <c r="DQ17" t="n">
+        <v>11.53</v>
+      </c>
+      <c r="DR17" t="n">
+        <v>10.71</v>
+      </c>
+      <c r="DS17" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="DT17" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="DU17" t="n">
+        <v>0</v>
+      </c>
+      <c r="DV17" t="n">
+        <v>45.59</v>
+      </c>
+      <c r="DW17" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="DX17" t="n">
         <v>11.12</v>
       </c>
-      <c r="DR17" t="n">
-        <v>10.69</v>
-      </c>
-      <c r="DS17" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="DT17" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="DU17" t="n">
-        <v>0</v>
-      </c>
-      <c r="DV17" t="n">
-        <v>45.06</v>
-      </c>
-      <c r="DW17" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="DX17" t="n">
-        <v>11.56</v>
-      </c>
       <c r="DY17" t="n">
-        <v>7.44</v>
+        <v>7.18</v>
       </c>
       <c r="DZ17" t="n">
-        <v>4.12</v>
+        <v>3.94</v>
       </c>
       <c r="EA17" t="n">
-        <v>20.62</v>
+        <v>20.41</v>
       </c>
       <c r="EB17" t="n">
-        <v>1.34</v>
+        <v>1.3</v>
       </c>
       <c r="EC17" t="n">
-        <v>1.5</v>
+        <v>1.59</v>
       </c>
     </row>
   </sheetData>

--- a/data/teams/leagues/Averages_Belgium_Pro_League_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Belgium_Pro_League_2025-2026.xlsx
@@ -1445,7 +1445,7 @@
         <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>53.11</v>
+        <v>53.22</v>
       </c>
       <c r="Y2" t="n">
         <v>0</v>
@@ -1751,7 +1751,7 @@
         <v>0</v>
       </c>
       <c r="DV2" t="n">
-        <v>51.59</v>
+        <v>51.65</v>
       </c>
       <c r="DW2" t="n">
         <v>0.06</v>
@@ -1929,7 +1929,7 @@
         <v>0</v>
       </c>
       <c r="AY3" t="n">
-        <v>60.33</v>
+        <v>60.22</v>
       </c>
       <c r="AZ3" t="n">
         <v>0</v>
@@ -2154,7 +2154,7 @@
         <v>0</v>
       </c>
       <c r="DV3" t="n">
-        <v>62.47</v>
+        <v>62.41</v>
       </c>
       <c r="DW3" t="n">
         <v>0.06</v>
@@ -3138,7 +3138,7 @@
         <v>0</v>
       </c>
       <c r="AY6" t="n">
-        <v>62</v>
+        <v>62.11</v>
       </c>
       <c r="AZ6" t="n">
         <v>0</v>
@@ -3153,7 +3153,7 @@
         <v>5.67</v>
       </c>
       <c r="BD6" t="n">
-        <v>19.44</v>
+        <v>19.56</v>
       </c>
       <c r="BE6" t="n">
         <v>1.74</v>
@@ -3363,7 +3363,7 @@
         <v>0</v>
       </c>
       <c r="DV6" t="n">
-        <v>64.12</v>
+        <v>64.18000000000001</v>
       </c>
       <c r="DW6" t="n">
         <v>0.06</v>
@@ -3378,7 +3378,7 @@
         <v>5.71</v>
       </c>
       <c r="EA6" t="n">
-        <v>20</v>
+        <v>20.06</v>
       </c>
       <c r="EB6" t="n">
         <v>1.87</v>
@@ -3869,10 +3869,10 @@
         <v>0</v>
       </c>
       <c r="Z8" t="n">
-        <v>17.44</v>
+        <v>17.56</v>
       </c>
       <c r="AA8" t="n">
-        <v>12.22</v>
+        <v>12.33</v>
       </c>
       <c r="AB8" t="n">
         <v>5.22</v>
@@ -3881,7 +3881,7 @@
         <v>19.44</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="AE8" t="n">
         <v>1.44</v>
@@ -4171,10 +4171,10 @@
         <v>0</v>
       </c>
       <c r="DX8" t="n">
-        <v>16</v>
+        <v>16.06</v>
       </c>
       <c r="DY8" t="n">
-        <v>11.12</v>
+        <v>11.18</v>
       </c>
       <c r="DZ8" t="n">
         <v>4.88</v>
@@ -4268,19 +4268,19 @@
         <v>0</v>
       </c>
       <c r="Z9" t="n">
-        <v>14</v>
+        <v>13.89</v>
       </c>
       <c r="AA9" t="n">
         <v>9.220000000000001</v>
       </c>
       <c r="AB9" t="n">
-        <v>4.78</v>
+        <v>4.67</v>
       </c>
       <c r="AC9" t="n">
         <v>17.78</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.49</v>
+        <v>1.47</v>
       </c>
       <c r="AE9" t="n">
         <v>2.89</v>
@@ -4574,19 +4574,19 @@
         <v>0.06</v>
       </c>
       <c r="DX9" t="n">
-        <v>12.59</v>
+        <v>12.53</v>
       </c>
       <c r="DY9" t="n">
         <v>8.35</v>
       </c>
       <c r="DZ9" t="n">
-        <v>4.23</v>
+        <v>4.18</v>
       </c>
       <c r="EA9" t="n">
         <v>18.77</v>
       </c>
       <c r="EB9" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="EC9" t="n">
         <v>3</v>
@@ -5131,7 +5131,7 @@
         <v>9.380000000000001</v>
       </c>
       <c r="AS11" t="n">
-        <v>8</v>
+        <v>8.119999999999999</v>
       </c>
       <c r="AT11" t="n">
         <v>1.25</v>
@@ -5362,7 +5362,7 @@
         <v>10</v>
       </c>
       <c r="DR11" t="n">
-        <v>7.83</v>
+        <v>7.88</v>
       </c>
       <c r="DS11" t="n">
         <v>0.11</v>
@@ -5471,7 +5471,7 @@
         <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>50.78</v>
+        <v>50.67</v>
       </c>
       <c r="Y12" t="n">
         <v>0.11</v>
@@ -5777,7 +5777,7 @@
         <v>0</v>
       </c>
       <c r="DV12" t="n">
-        <v>47.41</v>
+        <v>47.35</v>
       </c>
       <c r="DW12" t="n">
         <v>0.11</v>
@@ -5874,7 +5874,7 @@
         <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>54.56</v>
+        <v>54.67</v>
       </c>
       <c r="Y13" t="n">
         <v>0.11</v>
@@ -6180,7 +6180,7 @@
         <v>0</v>
       </c>
       <c r="DV13" t="n">
-        <v>53.47</v>
+        <v>53.53</v>
       </c>
       <c r="DW13" t="n">
         <v>0.06</v>
@@ -6373,7 +6373,7 @@
         <v>3.67</v>
       </c>
       <c r="BD14" t="n">
-        <v>21.22</v>
+        <v>21.33</v>
       </c>
       <c r="BE14" t="n">
         <v>1.28</v>
@@ -6598,7 +6598,7 @@
         <v>3.94</v>
       </c>
       <c r="EA14" t="n">
-        <v>19.7</v>
+        <v>19.76</v>
       </c>
       <c r="EB14" t="n">
         <v>1.31</v>
@@ -6761,7 +6761,7 @@
         <v>0</v>
       </c>
       <c r="AY15" t="n">
-        <v>44.11</v>
+        <v>44</v>
       </c>
       <c r="AZ15" t="n">
         <v>0.22</v>
@@ -6986,7 +6986,7 @@
         <v>0</v>
       </c>
       <c r="DV15" t="n">
-        <v>44.59</v>
+        <v>44.53</v>
       </c>
       <c r="DW15" t="n">
         <v>0.3</v>

--- a/data/teams/leagues/Averages_Belgium_Pro_League_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Belgium_Pro_League_2025-2026.xlsx
@@ -1379,10 +1379,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D2" t="n">
         <v>8</v>
@@ -1391,82 +1391,82 @@
         <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>0.78</v>
+        <v>0.8</v>
       </c>
       <c r="G2" t="n">
-        <v>2.89</v>
+        <v>3</v>
       </c>
       <c r="H2" t="n">
-        <v>108.78</v>
+        <v>109.2</v>
       </c>
       <c r="I2" t="n">
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="K2" t="n">
-        <v>4.89</v>
+        <v>5</v>
       </c>
       <c r="L2" t="n">
-        <v>0.44</v>
+        <v>0.4</v>
       </c>
       <c r="M2" t="n">
-        <v>50.11</v>
+        <v>50.1</v>
       </c>
       <c r="N2" t="n">
-        <v>0.44</v>
+        <v>0.4</v>
       </c>
       <c r="O2" t="n">
         <v>2</v>
       </c>
       <c r="P2" t="n">
-        <v>8.44</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="Q2" t="n">
-        <v>13.56</v>
+        <v>13.6</v>
       </c>
       <c r="R2" t="n">
-        <v>7</v>
+        <v>6.7</v>
       </c>
       <c r="S2" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="T2" t="n">
-        <v>1.56</v>
+        <v>1.6</v>
       </c>
       <c r="U2" t="n">
-        <v>0.44</v>
+        <v>0.5</v>
       </c>
       <c r="V2" t="n">
-        <v>0.44</v>
+        <v>0.5</v>
       </c>
       <c r="W2" t="n">
         <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>53.22</v>
+        <v>53</v>
       </c>
       <c r="Y2" t="n">
         <v>0</v>
       </c>
       <c r="Z2" t="n">
-        <v>15.11</v>
+        <v>15.3</v>
       </c>
       <c r="AA2" t="n">
-        <v>10.22</v>
+        <v>10.2</v>
       </c>
       <c r="AB2" t="n">
-        <v>4.89</v>
+        <v>5.1</v>
       </c>
       <c r="AC2" t="n">
-        <v>24.56</v>
+        <v>24.2</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.66</v>
+        <v>1.69</v>
       </c>
       <c r="AE2" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AF2" t="n">
         <v>0</v>
@@ -1550,70 +1550,70 @@
         <v>2.38</v>
       </c>
       <c r="BG2" t="n">
-        <v>2.71</v>
+        <v>2.83</v>
       </c>
       <c r="BH2" t="n">
-        <v>9.880000000000001</v>
+        <v>10.17</v>
       </c>
       <c r="BI2" t="n">
-        <v>2.71</v>
+        <v>2.83</v>
       </c>
       <c r="BJ2" t="n">
-        <v>0.71</v>
+        <v>0.67</v>
       </c>
       <c r="BK2" t="n">
-        <v>0.82</v>
+        <v>0.89</v>
       </c>
       <c r="BL2" t="n">
-        <v>0.59</v>
+        <v>0.67</v>
       </c>
       <c r="BM2" t="n">
-        <v>0.59</v>
+        <v>0.61</v>
       </c>
       <c r="BN2" t="n">
-        <v>1.18</v>
+        <v>1.28</v>
       </c>
       <c r="BO2" t="n">
-        <v>1.53</v>
+        <v>1.56</v>
       </c>
       <c r="BP2" t="n">
-        <v>4.41</v>
+        <v>4.56</v>
       </c>
       <c r="BQ2" t="n">
-        <v>5.47</v>
+        <v>5.61</v>
       </c>
       <c r="BR2" t="n">
-        <v>88.23999999999999</v>
+        <v>88.89</v>
       </c>
       <c r="BS2" t="n">
-        <v>88.23999999999999</v>
+        <v>88.89</v>
       </c>
       <c r="BT2" t="n">
-        <v>47.06</v>
+        <v>50</v>
       </c>
       <c r="BU2" t="n">
-        <v>23.53</v>
+        <v>27.78</v>
       </c>
       <c r="BV2" t="n">
-        <v>17.65</v>
+        <v>22.22</v>
       </c>
       <c r="BW2" t="n">
-        <v>5.88</v>
+        <v>5.56</v>
       </c>
       <c r="BX2" t="n">
-        <v>64.70999999999999</v>
+        <v>66.67</v>
       </c>
       <c r="BY2" t="n">
-        <v>2.31</v>
+        <v>2.24</v>
       </c>
       <c r="BZ2" t="n">
-        <v>2.38</v>
+        <v>2.3</v>
       </c>
       <c r="CA2" t="n">
-        <v>3.52</v>
+        <v>3.56</v>
       </c>
       <c r="CB2" t="n">
-        <v>3.69</v>
+        <v>3.72</v>
       </c>
       <c r="CC2" t="n">
         <v>3.51</v>
@@ -1625,16 +1625,16 @@
         <v>1.31</v>
       </c>
       <c r="CF2" t="n">
-        <v>2.52</v>
+        <v>2.51</v>
       </c>
       <c r="CG2" t="n">
-        <v>3.15</v>
+        <v>3.16</v>
       </c>
       <c r="CH2" t="n">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="CI2" t="n">
-        <v>2.18</v>
+        <v>2.19</v>
       </c>
       <c r="CJ2" t="n">
         <v>1.66</v>
@@ -1643,13 +1643,13 @@
         <v>1.45</v>
       </c>
       <c r="CL2" t="n">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="CM2" t="n">
         <v>2.58</v>
       </c>
       <c r="CN2" t="n">
-        <v>2</v>
+        <v>2.01</v>
       </c>
       <c r="CO2" t="n">
         <v>1.22</v>
@@ -1658,19 +1658,19 @@
         <v>1.75</v>
       </c>
       <c r="CQ2" t="n">
-        <v>2.89</v>
+        <v>2.87</v>
       </c>
       <c r="CR2" t="n">
         <v>1.36</v>
       </c>
       <c r="CS2" t="n">
-        <v>2.61</v>
+        <v>2.6</v>
       </c>
       <c r="CT2" t="n">
         <v>3.23</v>
       </c>
       <c r="CU2" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="CV2" t="n">
         <v>2.32</v>
@@ -1679,13 +1679,13 @@
         <v>1.66</v>
       </c>
       <c r="CX2" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="CY2" t="n">
         <v>1.76</v>
       </c>
       <c r="CZ2" t="n">
-        <v>2.52</v>
+        <v>2.54</v>
       </c>
       <c r="DA2" t="n">
         <v>2.07</v>
@@ -1694,85 +1694,85 @@
         <v>1.23</v>
       </c>
       <c r="DC2" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="DD2" t="n">
-        <v>2.84</v>
+        <v>2.82</v>
       </c>
       <c r="DE2" t="n">
         <v>0</v>
       </c>
       <c r="DF2" t="n">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="DG2" t="n">
-        <v>2.71</v>
+        <v>2.78</v>
       </c>
       <c r="DH2" t="n">
-        <v>108.83</v>
+        <v>109.06</v>
       </c>
       <c r="DI2" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="DJ2" t="n">
-        <v>1.88</v>
+        <v>1.83</v>
       </c>
       <c r="DK2" t="n">
-        <v>4.76</v>
+        <v>4.83</v>
       </c>
       <c r="DL2" t="n">
-        <v>0.52</v>
+        <v>0.5</v>
       </c>
       <c r="DM2" t="n">
-        <v>51.65</v>
+        <v>51.56</v>
       </c>
       <c r="DN2" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.89</v>
       </c>
       <c r="DO2" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="DP2" t="n">
-        <v>10.35</v>
+        <v>10.44</v>
       </c>
       <c r="DQ2" t="n">
-        <v>12.53</v>
+        <v>12.61</v>
       </c>
       <c r="DR2" t="n">
-        <v>7.06</v>
+        <v>6.89</v>
       </c>
       <c r="DS2" t="n">
-        <v>0.23</v>
+        <v>0.28</v>
       </c>
       <c r="DT2" t="n">
-        <v>0.23</v>
+        <v>0.28</v>
       </c>
       <c r="DU2" t="n">
         <v>0</v>
       </c>
       <c r="DV2" t="n">
-        <v>51.65</v>
+        <v>51.61</v>
       </c>
       <c r="DW2" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="DX2" t="n">
-        <v>13.94</v>
+        <v>14.11</v>
       </c>
       <c r="DY2" t="n">
-        <v>9.65</v>
+        <v>9.67</v>
       </c>
       <c r="DZ2" t="n">
-        <v>4.29</v>
+        <v>4.44</v>
       </c>
       <c r="EA2" t="n">
-        <v>23.88</v>
+        <v>23.72</v>
       </c>
       <c r="EB2" t="n">
-        <v>1.56</v>
+        <v>1.58</v>
       </c>
       <c r="EC2" t="n">
-        <v>1.77</v>
+        <v>1.72</v>
       </c>
     </row>
     <row r="3">
@@ -1782,13 +1782,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C3" t="n">
         <v>8</v>
       </c>
       <c r="D3" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
@@ -1872,139 +1872,139 @@
         <v>1.25</v>
       </c>
       <c r="AF3" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.11</v>
+        <v>1</v>
       </c>
       <c r="AH3" t="n">
-        <v>4.22</v>
+        <v>4</v>
       </c>
       <c r="AI3" t="n">
-        <v>107.89</v>
+        <v>109.6</v>
       </c>
       <c r="AJ3" t="n">
-        <v>0</v>
+        <v>-0.1</v>
       </c>
       <c r="AK3" t="n">
-        <v>1.56</v>
+        <v>1.4</v>
       </c>
       <c r="AL3" t="n">
-        <v>6.67</v>
+        <v>6.3</v>
       </c>
       <c r="AM3" t="n">
-        <v>0.22</v>
+        <v>0.3</v>
       </c>
       <c r="AN3" t="n">
-        <v>56</v>
+        <v>58.9</v>
       </c>
       <c r="AO3" t="n">
-        <v>0.44</v>
+        <v>0.4</v>
       </c>
       <c r="AP3" t="n">
-        <v>2.44</v>
+        <v>2.3</v>
       </c>
       <c r="AQ3" t="n">
-        <v>9.44</v>
+        <v>9.1</v>
       </c>
       <c r="AR3" t="n">
-        <v>11.89</v>
+        <v>11.3</v>
       </c>
       <c r="AS3" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AT3" t="n">
         <v>1</v>
       </c>
       <c r="AU3" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AV3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY3" t="n">
+        <v>60.4</v>
+      </c>
+      <c r="AZ3" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA3" t="n">
+        <v>16.1</v>
+      </c>
+      <c r="BB3" t="n">
+        <v>10.6</v>
+      </c>
+      <c r="BC3" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BD3" t="n">
+        <v>17.7</v>
+      </c>
+      <c r="BE3" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="BF3" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="BG3" t="n">
+        <v>2.61</v>
+      </c>
+      <c r="BH3" t="n">
+        <v>11</v>
+      </c>
+      <c r="BI3" t="n">
+        <v>2.61</v>
+      </c>
+      <c r="BJ3" t="n">
+        <v>0.61</v>
+      </c>
+      <c r="BK3" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="BL3" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="BM3" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="BN3" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="BO3" t="n">
         <v>1</v>
       </c>
-      <c r="AV3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY3" t="n">
-        <v>60.22</v>
-      </c>
-      <c r="AZ3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA3" t="n">
-        <v>15.44</v>
-      </c>
-      <c r="BB3" t="n">
-        <v>10.33</v>
-      </c>
-      <c r="BC3" t="n">
-        <v>5.11</v>
-      </c>
-      <c r="BD3" t="n">
-        <v>17.89</v>
-      </c>
-      <c r="BE3" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="BF3" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="BG3" t="n">
-        <v>2.41</v>
-      </c>
-      <c r="BH3" t="n">
-        <v>11.47</v>
-      </c>
-      <c r="BI3" t="n">
-        <v>2.41</v>
-      </c>
-      <c r="BJ3" t="n">
-        <v>0.59</v>
-      </c>
-      <c r="BK3" t="n">
-        <v>0.35</v>
-      </c>
-      <c r="BL3" t="n">
-        <v>0.82</v>
-      </c>
-      <c r="BM3" t="n">
-        <v>0.65</v>
-      </c>
-      <c r="BN3" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="BO3" t="n">
-        <v>0.9399999999999999</v>
-      </c>
       <c r="BP3" t="n">
-        <v>5.18</v>
+        <v>4.94</v>
       </c>
       <c r="BQ3" t="n">
-        <v>6.29</v>
+        <v>6.06</v>
       </c>
       <c r="BR3" t="n">
         <v>100</v>
       </c>
       <c r="BS3" t="n">
-        <v>52.94</v>
+        <v>55.56</v>
       </c>
       <c r="BT3" t="n">
-        <v>35.29</v>
+        <v>38.89</v>
       </c>
       <c r="BU3" t="n">
-        <v>11.76</v>
+        <v>16.67</v>
       </c>
       <c r="BV3" t="n">
-        <v>11.76</v>
+        <v>16.67</v>
       </c>
       <c r="BW3" t="n">
-        <v>5.88</v>
+        <v>11.11</v>
       </c>
       <c r="BX3" t="n">
-        <v>41.18</v>
+        <v>44.44</v>
       </c>
       <c r="BY3" t="n">
         <v>1.52</v>
@@ -2016,13 +2016,13 @@
         <v>4.44</v>
       </c>
       <c r="CB3" t="n">
-        <v>4.69</v>
+        <v>4.7</v>
       </c>
       <c r="CC3" t="n">
         <v>1.7</v>
       </c>
       <c r="CD3" t="n">
-        <v>1.78</v>
+        <v>1.76</v>
       </c>
       <c r="CE3" t="n">
         <v>1.26</v>
@@ -2049,7 +2049,7 @@
         <v>1.93</v>
       </c>
       <c r="CM3" t="n">
-        <v>2.53</v>
+        <v>2.52</v>
       </c>
       <c r="CN3" t="n">
         <v>1.96</v>
@@ -2061,7 +2061,7 @@
         <v>1.57</v>
       </c>
       <c r="CQ3" t="n">
-        <v>2.41</v>
+        <v>2.4</v>
       </c>
       <c r="CR3" t="n">
         <v>1.33</v>
@@ -2085,64 +2085,64 @@
         <v>1.52</v>
       </c>
       <c r="CY3" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="CZ3" t="n">
         <v>2.49</v>
       </c>
       <c r="DA3" t="n">
-        <v>2.02</v>
+        <v>2.01</v>
       </c>
       <c r="DB3" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="DC3" t="n">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="DD3" t="n">
-        <v>2.45</v>
+        <v>2.44</v>
       </c>
       <c r="DE3" t="n">
         <v>0.06</v>
       </c>
       <c r="DF3" t="n">
-        <v>1.18</v>
+        <v>1.11</v>
       </c>
       <c r="DG3" t="n">
-        <v>4.12</v>
+        <v>4</v>
       </c>
       <c r="DH3" t="n">
-        <v>111.71</v>
+        <v>112.44</v>
       </c>
       <c r="DI3" t="n">
-        <v>0</v>
+        <v>-0.06</v>
       </c>
       <c r="DJ3" t="n">
-        <v>1.53</v>
+        <v>1.44</v>
       </c>
       <c r="DK3" t="n">
-        <v>6.83</v>
+        <v>6.61</v>
       </c>
       <c r="DL3" t="n">
-        <v>0.59</v>
+        <v>0.61</v>
       </c>
       <c r="DM3" t="n">
-        <v>61.59</v>
+        <v>62.89</v>
       </c>
       <c r="DN3" t="n">
-        <v>0.29</v>
+        <v>0.28</v>
       </c>
       <c r="DO3" t="n">
-        <v>2.7</v>
+        <v>2.61</v>
       </c>
       <c r="DP3" t="n">
-        <v>9.52</v>
+        <v>9.33</v>
       </c>
       <c r="DQ3" t="n">
-        <v>12</v>
+        <v>11.66</v>
       </c>
       <c r="DR3" t="n">
-        <v>7.65</v>
+        <v>7.56</v>
       </c>
       <c r="DS3" t="n">
         <v>0</v>
@@ -2154,28 +2154,28 @@
         <v>0</v>
       </c>
       <c r="DV3" t="n">
-        <v>62.41</v>
+        <v>62.39</v>
       </c>
       <c r="DW3" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="DX3" t="n">
-        <v>16.53</v>
+        <v>16.83</v>
       </c>
       <c r="DY3" t="n">
-        <v>11.41</v>
+        <v>11.5</v>
       </c>
       <c r="DZ3" t="n">
-        <v>5.11</v>
+        <v>5.33</v>
       </c>
       <c r="EA3" t="n">
-        <v>19.94</v>
+        <v>19.72</v>
       </c>
       <c r="EB3" t="n">
-        <v>1.85</v>
+        <v>1.89</v>
       </c>
       <c r="EC3" t="n">
-        <v>1.41</v>
+        <v>1.33</v>
       </c>
     </row>
     <row r="4">
@@ -2185,10 +2185,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D4" t="n">
         <v>9</v>
@@ -2197,82 +2197,82 @@
         <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>1</v>
+        <v>0.89</v>
       </c>
       <c r="G4" t="n">
-        <v>1</v>
+        <v>0.89</v>
       </c>
       <c r="H4" t="n">
-        <v>93.25</v>
+        <v>92.89</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.12</v>
+        <v>-0.22</v>
       </c>
       <c r="J4" t="n">
-        <v>1.38</v>
+        <v>1.22</v>
       </c>
       <c r="K4" t="n">
-        <v>3.25</v>
+        <v>2.89</v>
       </c>
       <c r="L4" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="M4" t="n">
-        <v>43.25</v>
+        <v>41.78</v>
       </c>
       <c r="N4" t="n">
-        <v>0.38</v>
+        <v>0.33</v>
       </c>
       <c r="O4" t="n">
-        <v>1.25</v>
+        <v>1.11</v>
       </c>
       <c r="P4" t="n">
-        <v>9.75</v>
+        <v>9.33</v>
       </c>
       <c r="Q4" t="n">
-        <v>12.25</v>
+        <v>11.56</v>
       </c>
       <c r="R4" t="n">
-        <v>10.5</v>
+        <v>10.78</v>
       </c>
       <c r="S4" t="n">
-        <v>1.38</v>
+        <v>1.78</v>
       </c>
       <c r="T4" t="n">
-        <v>0.62</v>
+        <v>0.67</v>
       </c>
       <c r="U4" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="V4" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="W4" t="n">
         <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>50.5</v>
+        <v>49.11</v>
       </c>
       <c r="Y4" t="n">
         <v>0</v>
       </c>
       <c r="Z4" t="n">
-        <v>9.880000000000001</v>
+        <v>9.44</v>
       </c>
       <c r="AA4" t="n">
-        <v>6.5</v>
+        <v>6.33</v>
       </c>
       <c r="AB4" t="n">
-        <v>3.38</v>
+        <v>3.11</v>
       </c>
       <c r="AC4" t="n">
-        <v>23.88</v>
+        <v>23.22</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.18</v>
+        <v>1.12</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.38</v>
+        <v>1.22</v>
       </c>
       <c r="AF4" t="n">
         <v>0.22</v>
@@ -2356,70 +2356,70 @@
         <v>1.78</v>
       </c>
       <c r="BG4" t="n">
-        <v>2.41</v>
+        <v>2.61</v>
       </c>
       <c r="BH4" t="n">
-        <v>8.35</v>
+        <v>8.06</v>
       </c>
       <c r="BI4" t="n">
-        <v>2.41</v>
+        <v>2.61</v>
       </c>
       <c r="BJ4" t="n">
-        <v>0.53</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="BK4" t="n">
-        <v>0.24</v>
+        <v>0.28</v>
       </c>
       <c r="BL4" t="n">
-        <v>0.71</v>
+        <v>0.67</v>
       </c>
       <c r="BM4" t="n">
-        <v>0.9399999999999999</v>
+        <v>1.11</v>
       </c>
       <c r="BN4" t="n">
-        <v>1.65</v>
+        <v>1.78</v>
       </c>
       <c r="BO4" t="n">
-        <v>0.76</v>
+        <v>0.83</v>
       </c>
       <c r="BP4" t="n">
-        <v>3.65</v>
+        <v>3.5</v>
       </c>
       <c r="BQ4" t="n">
-        <v>3.94</v>
+        <v>3.83</v>
       </c>
       <c r="BR4" t="n">
-        <v>88.23999999999999</v>
+        <v>88.89</v>
       </c>
       <c r="BS4" t="n">
-        <v>76.47</v>
+        <v>77.78</v>
       </c>
       <c r="BT4" t="n">
-        <v>52.94</v>
+        <v>55.56</v>
       </c>
       <c r="BU4" t="n">
-        <v>23.53</v>
+        <v>27.78</v>
       </c>
       <c r="BV4" t="n">
-        <v>0</v>
+        <v>5.56</v>
       </c>
       <c r="BW4" t="n">
-        <v>0</v>
+        <v>5.56</v>
       </c>
       <c r="BX4" t="n">
-        <v>58.82</v>
+        <v>61.11</v>
       </c>
       <c r="BY4" t="n">
-        <v>3.33</v>
+        <v>3.6</v>
       </c>
       <c r="BZ4" t="n">
-        <v>3.41</v>
+        <v>3.68</v>
       </c>
       <c r="CA4" t="n">
-        <v>3.69</v>
+        <v>3.73</v>
       </c>
       <c r="CB4" t="n">
-        <v>3.88</v>
+        <v>3.93</v>
       </c>
       <c r="CC4" t="n">
         <v>4.74</v>
@@ -2428,28 +2428,28 @@
         <v>5.16</v>
       </c>
       <c r="CE4" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="CF4" t="n">
-        <v>2.56</v>
+        <v>2.54</v>
       </c>
       <c r="CG4" t="n">
-        <v>3.11</v>
+        <v>3.13</v>
       </c>
       <c r="CH4" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="CI4" t="n">
-        <v>2.04</v>
+        <v>2.05</v>
       </c>
       <c r="CJ4" t="n">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="CK4" t="n">
         <v>1.53</v>
       </c>
       <c r="CL4" t="n">
-        <v>2.04</v>
+        <v>2.03</v>
       </c>
       <c r="CM4" t="n">
         <v>2.37</v>
@@ -2458,28 +2458,28 @@
         <v>1.85</v>
       </c>
       <c r="CO4" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="CP4" t="n">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="CQ4" t="n">
-        <v>3.08</v>
+        <v>3.04</v>
       </c>
       <c r="CR4" t="n">
         <v>1.38</v>
       </c>
       <c r="CS4" t="n">
-        <v>2.74</v>
+        <v>2.71</v>
       </c>
       <c r="CT4" t="n">
         <v>3.1</v>
       </c>
       <c r="CU4" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="CV4" t="n">
-        <v>2.16</v>
+        <v>2.17</v>
       </c>
       <c r="CW4" t="n">
         <v>1.75</v>
@@ -2491,61 +2491,61 @@
         <v>1.94</v>
       </c>
       <c r="CZ4" t="n">
-        <v>2.37</v>
+        <v>2.38</v>
       </c>
       <c r="DA4" t="n">
         <v>1.88</v>
       </c>
       <c r="DB4" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="DC4" t="n">
-        <v>1.87</v>
+        <v>1.85</v>
       </c>
       <c r="DD4" t="n">
-        <v>3.09</v>
+        <v>3.04</v>
       </c>
       <c r="DE4" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DF4" t="n">
-        <v>1.3</v>
+        <v>1.23</v>
       </c>
       <c r="DG4" t="n">
-        <v>1.12</v>
+        <v>1.06</v>
       </c>
       <c r="DH4" t="n">
-        <v>90.7</v>
+        <v>90.66</v>
       </c>
       <c r="DI4" t="n">
-        <v>0</v>
+        <v>-0.06</v>
       </c>
       <c r="DJ4" t="n">
-        <v>1.88</v>
+        <v>1.78</v>
       </c>
       <c r="DK4" t="n">
-        <v>3.12</v>
+        <v>2.94</v>
       </c>
       <c r="DL4" t="n">
         <v>0.11</v>
       </c>
       <c r="DM4" t="n">
-        <v>40.06</v>
+        <v>39.5</v>
       </c>
       <c r="DN4" t="n">
-        <v>0.48</v>
+        <v>0.45</v>
       </c>
       <c r="DO4" t="n">
-        <v>1.53</v>
+        <v>1.44</v>
       </c>
       <c r="DP4" t="n">
-        <v>10.88</v>
+        <v>10.61</v>
       </c>
       <c r="DQ4" t="n">
-        <v>11.94</v>
+        <v>11.62</v>
       </c>
       <c r="DR4" t="n">
-        <v>10.65</v>
+        <v>10.78</v>
       </c>
       <c r="DS4" t="n">
         <v>0.11</v>
@@ -2557,28 +2557,28 @@
         <v>0</v>
       </c>
       <c r="DV4" t="n">
-        <v>46.7</v>
+        <v>46.22</v>
       </c>
       <c r="DW4" t="n">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
       <c r="DX4" t="n">
-        <v>10.36</v>
+        <v>10.11</v>
       </c>
       <c r="DY4" t="n">
-        <v>6.59</v>
+        <v>6.5</v>
       </c>
       <c r="DZ4" t="n">
-        <v>3.77</v>
+        <v>3.61</v>
       </c>
       <c r="EA4" t="n">
-        <v>20.77</v>
+        <v>20.61</v>
       </c>
       <c r="EB4" t="n">
-        <v>1.21</v>
+        <v>1.18</v>
       </c>
       <c r="EC4" t="n">
-        <v>1.59</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="5">
@@ -2588,61 +2588,61 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C5" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D5" t="n">
         <v>9</v>
       </c>
       <c r="E5" t="n">
-        <v>0.38</v>
+        <v>0.33</v>
       </c>
       <c r="F5" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="G5" t="n">
-        <v>2.75</v>
+        <v>2.78</v>
       </c>
       <c r="H5" t="n">
-        <v>109.25</v>
+        <v>111</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>1.5</v>
+        <v>1.56</v>
       </c>
       <c r="K5" t="n">
-        <v>4.62</v>
+        <v>4.67</v>
       </c>
       <c r="L5" t="n">
-        <v>0.5</v>
+        <v>0.44</v>
       </c>
       <c r="M5" t="n">
-        <v>49</v>
+        <v>51.11</v>
       </c>
       <c r="N5" t="n">
-        <v>0.38</v>
+        <v>0.33</v>
       </c>
       <c r="O5" t="n">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="P5" t="n">
-        <v>10.38</v>
+        <v>10</v>
       </c>
       <c r="Q5" t="n">
-        <v>9.75</v>
+        <v>9.67</v>
       </c>
       <c r="R5" t="n">
-        <v>8.380000000000001</v>
+        <v>8.109999999999999</v>
       </c>
       <c r="S5" t="n">
-        <v>1</v>
+        <v>1.11</v>
       </c>
       <c r="T5" t="n">
-        <v>1.88</v>
+        <v>1.67</v>
       </c>
       <c r="U5" t="n">
         <v>0</v>
@@ -2654,28 +2654,28 @@
         <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>55</v>
+        <v>56.11</v>
       </c>
       <c r="Y5" t="n">
-        <v>0</v>
+        <v>0.11</v>
       </c>
       <c r="Z5" t="n">
-        <v>15.25</v>
+        <v>15.11</v>
       </c>
       <c r="AA5" t="n">
-        <v>11</v>
+        <v>11.11</v>
       </c>
       <c r="AB5" t="n">
-        <v>4.25</v>
+        <v>4</v>
       </c>
       <c r="AC5" t="n">
-        <v>18.5</v>
+        <v>19.78</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="AF5" t="n">
         <v>0.11</v>
@@ -2759,70 +2759,70 @@
         <v>1.89</v>
       </c>
       <c r="BG5" t="n">
-        <v>2.94</v>
+        <v>2.89</v>
       </c>
       <c r="BH5" t="n">
-        <v>9.94</v>
+        <v>9.720000000000001</v>
       </c>
       <c r="BI5" t="n">
-        <v>2.94</v>
+        <v>2.89</v>
       </c>
       <c r="BJ5" t="n">
-        <v>0.88</v>
+        <v>0.83</v>
       </c>
       <c r="BK5" t="n">
-        <v>0.41</v>
+        <v>0.44</v>
       </c>
       <c r="BL5" t="n">
-        <v>1</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="BM5" t="n">
-        <v>0.65</v>
+        <v>0.67</v>
       </c>
       <c r="BN5" t="n">
-        <v>1.65</v>
+        <v>1.61</v>
       </c>
       <c r="BO5" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="BP5" t="n">
-        <v>3.88</v>
+        <v>3.78</v>
       </c>
       <c r="BQ5" t="n">
-        <v>6.06</v>
+        <v>5.94</v>
       </c>
       <c r="BR5" t="n">
-        <v>94.12</v>
+        <v>94.44</v>
       </c>
       <c r="BS5" t="n">
-        <v>82.34999999999999</v>
+        <v>83.33</v>
       </c>
       <c r="BT5" t="n">
-        <v>58.82</v>
+        <v>55.56</v>
       </c>
       <c r="BU5" t="n">
-        <v>35.29</v>
+        <v>33.33</v>
       </c>
       <c r="BV5" t="n">
-        <v>17.65</v>
+        <v>16.67</v>
       </c>
       <c r="BW5" t="n">
-        <v>5.88</v>
+        <v>5.56</v>
       </c>
       <c r="BX5" t="n">
-        <v>64.70999999999999</v>
+        <v>61.11</v>
       </c>
       <c r="BY5" t="n">
-        <v>2.8</v>
+        <v>2.73</v>
       </c>
       <c r="BZ5" t="n">
-        <v>2.94</v>
+        <v>2.85</v>
       </c>
       <c r="CA5" t="n">
-        <v>3.64</v>
+        <v>3.63</v>
       </c>
       <c r="CB5" t="n">
-        <v>3.81</v>
+        <v>3.79</v>
       </c>
       <c r="CC5" t="n">
         <v>3.59</v>
@@ -2834,13 +2834,13 @@
         <v>1.3</v>
       </c>
       <c r="CF5" t="n">
-        <v>2.44</v>
+        <v>2.45</v>
       </c>
       <c r="CG5" t="n">
-        <v>3.23</v>
+        <v>3.22</v>
       </c>
       <c r="CH5" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="CI5" t="n">
         <v>2.24</v>
@@ -2852,7 +2852,7 @@
         <v>1.44</v>
       </c>
       <c r="CL5" t="n">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="CM5" t="n">
         <v>2.58</v>
@@ -2882,7 +2882,7 @@
         <v>1.55</v>
       </c>
       <c r="CV5" t="n">
-        <v>2.35</v>
+        <v>2.34</v>
       </c>
       <c r="CW5" t="n">
         <v>1.65</v>
@@ -2903,22 +2903,22 @@
         <v>1.23</v>
       </c>
       <c r="DC5" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="DD5" t="n">
-        <v>2.79</v>
+        <v>2.81</v>
       </c>
       <c r="DE5" t="n">
-        <v>0.24</v>
+        <v>0.22</v>
       </c>
       <c r="DF5" t="n">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="DG5" t="n">
-        <v>2.88</v>
+        <v>2.89</v>
       </c>
       <c r="DH5" t="n">
-        <v>100.29</v>
+        <v>101.66</v>
       </c>
       <c r="DI5" t="n">
         <v>0</v>
@@ -2927,28 +2927,28 @@
         <v>1.94</v>
       </c>
       <c r="DK5" t="n">
-        <v>4.82</v>
+        <v>4.84</v>
       </c>
       <c r="DL5" t="n">
-        <v>0.65</v>
+        <v>0.61</v>
       </c>
       <c r="DM5" t="n">
-        <v>45.18</v>
+        <v>46.44</v>
       </c>
       <c r="DN5" t="n">
-        <v>0.65</v>
+        <v>0.61</v>
       </c>
       <c r="DO5" t="n">
         <v>1.94</v>
       </c>
       <c r="DP5" t="n">
-        <v>10.59</v>
+        <v>10.39</v>
       </c>
       <c r="DQ5" t="n">
-        <v>10.47</v>
+        <v>10.39</v>
       </c>
       <c r="DR5" t="n">
-        <v>9.710000000000001</v>
+        <v>9.5</v>
       </c>
       <c r="DS5" t="n">
         <v>0.06</v>
@@ -2960,28 +2960,28 @@
         <v>0</v>
       </c>
       <c r="DV5" t="n">
-        <v>52.82</v>
+        <v>53.5</v>
       </c>
       <c r="DW5" t="n">
-        <v>0.12</v>
+        <v>0.16</v>
       </c>
       <c r="DX5" t="n">
-        <v>13.47</v>
+        <v>13.5</v>
       </c>
       <c r="DY5" t="n">
-        <v>8.82</v>
+        <v>9</v>
       </c>
       <c r="DZ5" t="n">
-        <v>4.65</v>
+        <v>4.5</v>
       </c>
       <c r="EA5" t="n">
-        <v>18.18</v>
+        <v>18.83</v>
       </c>
       <c r="EB5" t="n">
         <v>1.51</v>
       </c>
       <c r="EC5" t="n">
-        <v>1.71</v>
+        <v>1.61</v>
       </c>
     </row>
     <row r="6">
@@ -2991,10 +2991,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C6" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D6" t="n">
         <v>9</v>
@@ -3003,49 +3003,49 @@
         <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>0.5</v>
+        <v>0.44</v>
       </c>
       <c r="G6" t="n">
-        <v>3.75</v>
+        <v>4</v>
       </c>
       <c r="H6" t="n">
-        <v>138</v>
+        <v>134.56</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>1.12</v>
+        <v>1</v>
       </c>
       <c r="K6" t="n">
-        <v>6.75</v>
+        <v>7</v>
       </c>
       <c r="L6" t="n">
-        <v>0.75</v>
+        <v>0.67</v>
       </c>
       <c r="M6" t="n">
-        <v>66.12</v>
+        <v>66.22</v>
       </c>
       <c r="N6" t="n">
-        <v>0.5</v>
+        <v>0.44</v>
       </c>
       <c r="O6" t="n">
-        <v>3</v>
+        <v>2.89</v>
       </c>
       <c r="P6" t="n">
-        <v>10.5</v>
+        <v>10.78</v>
       </c>
       <c r="Q6" t="n">
-        <v>14.5</v>
+        <v>14.22</v>
       </c>
       <c r="R6" t="n">
-        <v>5</v>
+        <v>5.22</v>
       </c>
       <c r="S6" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="T6" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="U6" t="n">
         <v>0</v>
@@ -3057,28 +3057,28 @@
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>66.5</v>
+        <v>66.67</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="Z6" t="n">
-        <v>17.75</v>
+        <v>18.22</v>
       </c>
       <c r="AA6" t="n">
-        <v>12</v>
+        <v>12.44</v>
       </c>
       <c r="AB6" t="n">
-        <v>5.75</v>
+        <v>5.78</v>
       </c>
       <c r="AC6" t="n">
-        <v>20.62</v>
+        <v>20.89</v>
       </c>
       <c r="AD6" t="n">
-        <v>2.01</v>
+        <v>2.04</v>
       </c>
       <c r="AE6" t="n">
-        <v>0.88</v>
+        <v>0.78</v>
       </c>
       <c r="AF6" t="n">
         <v>0.11</v>
@@ -3162,70 +3162,70 @@
         <v>1.89</v>
       </c>
       <c r="BG6" t="n">
-        <v>2.59</v>
+        <v>2.56</v>
       </c>
       <c r="BH6" t="n">
-        <v>9.94</v>
+        <v>10.28</v>
       </c>
       <c r="BI6" t="n">
-        <v>2.59</v>
+        <v>2.56</v>
       </c>
       <c r="BJ6" t="n">
-        <v>0.65</v>
+        <v>0.61</v>
       </c>
       <c r="BK6" t="n">
-        <v>0.82</v>
+        <v>0.83</v>
       </c>
       <c r="BL6" t="n">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="BM6" t="n">
-        <v>0.41</v>
+        <v>0.39</v>
       </c>
       <c r="BN6" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="BO6" t="n">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="BP6" t="n">
-        <v>4.53</v>
+        <v>4.61</v>
       </c>
       <c r="BQ6" t="n">
-        <v>5.41</v>
+        <v>5.61</v>
       </c>
       <c r="BR6" t="n">
         <v>100</v>
       </c>
       <c r="BS6" t="n">
-        <v>82.34999999999999</v>
+        <v>83.33</v>
       </c>
       <c r="BT6" t="n">
-        <v>58.82</v>
+        <v>55.56</v>
       </c>
       <c r="BU6" t="n">
-        <v>11.76</v>
+        <v>11.11</v>
       </c>
       <c r="BV6" t="n">
-        <v>5.88</v>
+        <v>5.56</v>
       </c>
       <c r="BW6" t="n">
         <v>0</v>
       </c>
       <c r="BX6" t="n">
-        <v>76.47</v>
+        <v>77.78</v>
       </c>
       <c r="BY6" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="BZ6" t="n">
-        <v>1.74</v>
+        <v>1.78</v>
       </c>
       <c r="CA6" t="n">
-        <v>3.91</v>
+        <v>3.92</v>
       </c>
       <c r="CB6" t="n">
-        <v>4.06</v>
+        <v>4.04</v>
       </c>
       <c r="CC6" t="n">
         <v>2.47</v>
@@ -3237,13 +3237,13 @@
         <v>1.28</v>
       </c>
       <c r="CF6" t="n">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="CG6" t="n">
-        <v>3.31</v>
+        <v>3.32</v>
       </c>
       <c r="CH6" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="CI6" t="n">
         <v>2.26</v>
@@ -3255,28 +3255,28 @@
         <v>1.51</v>
       </c>
       <c r="CL6" t="n">
-        <v>2.03</v>
+        <v>2.01</v>
       </c>
       <c r="CM6" t="n">
-        <v>2.41</v>
+        <v>2.44</v>
       </c>
       <c r="CN6" t="n">
-        <v>1.86</v>
+        <v>1.88</v>
       </c>
       <c r="CO6" t="n">
         <v>1.18</v>
       </c>
       <c r="CP6" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="CQ6" t="n">
-        <v>2.64</v>
+        <v>2.62</v>
       </c>
       <c r="CR6" t="n">
         <v>1.38</v>
       </c>
       <c r="CS6" t="n">
-        <v>2.55</v>
+        <v>2.54</v>
       </c>
       <c r="CT6" t="n">
         <v>3.12</v>
@@ -3285,19 +3285,19 @@
         <v>1.55</v>
       </c>
       <c r="CV6" t="n">
-        <v>2.3</v>
+        <v>2.31</v>
       </c>
       <c r="CW6" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="CX6" t="n">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="CY6" t="n">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="CZ6" t="n">
-        <v>2.32</v>
+        <v>2.35</v>
       </c>
       <c r="DA6" t="n">
         <v>1.88</v>
@@ -3309,49 +3309,49 @@
         <v>1.72</v>
       </c>
       <c r="DD6" t="n">
-        <v>2.75</v>
+        <v>2.74</v>
       </c>
       <c r="DE6" t="n">
         <v>0.06</v>
       </c>
       <c r="DF6" t="n">
-        <v>1</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="DG6" t="n">
-        <v>3.47</v>
+        <v>3.61</v>
       </c>
       <c r="DH6" t="n">
-        <v>119.06</v>
+        <v>118.39</v>
       </c>
       <c r="DI6" t="n">
         <v>0.06</v>
       </c>
       <c r="DJ6" t="n">
-        <v>1.53</v>
+        <v>1.44</v>
       </c>
       <c r="DK6" t="n">
-        <v>6.18</v>
+        <v>6.34</v>
       </c>
       <c r="DL6" t="n">
-        <v>0.77</v>
+        <v>0.73</v>
       </c>
       <c r="DM6" t="n">
-        <v>57.47</v>
+        <v>58</v>
       </c>
       <c r="DN6" t="n">
-        <v>0.47</v>
+        <v>0.44</v>
       </c>
       <c r="DO6" t="n">
-        <v>2.7</v>
+        <v>2.66</v>
       </c>
       <c r="DP6" t="n">
-        <v>10</v>
+        <v>10.17</v>
       </c>
       <c r="DQ6" t="n">
-        <v>13.23</v>
+        <v>13.16</v>
       </c>
       <c r="DR6" t="n">
-        <v>6</v>
+        <v>6.06</v>
       </c>
       <c r="DS6" t="n">
         <v>0</v>
@@ -3363,28 +3363,28 @@
         <v>0</v>
       </c>
       <c r="DV6" t="n">
-        <v>64.18000000000001</v>
+        <v>64.39</v>
       </c>
       <c r="DW6" t="n">
         <v>0.06</v>
       </c>
       <c r="DX6" t="n">
-        <v>16.59</v>
+        <v>16.89</v>
       </c>
       <c r="DY6" t="n">
-        <v>10.88</v>
+        <v>11.16</v>
       </c>
       <c r="DZ6" t="n">
-        <v>5.71</v>
+        <v>5.72</v>
       </c>
       <c r="EA6" t="n">
-        <v>20.06</v>
+        <v>20.22</v>
       </c>
       <c r="EB6" t="n">
-        <v>1.87</v>
+        <v>1.89</v>
       </c>
       <c r="EC6" t="n">
-        <v>1.41</v>
+        <v>1.34</v>
       </c>
     </row>
     <row r="7">
@@ -3394,13 +3394,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C7" t="n">
         <v>9</v>
       </c>
       <c r="D7" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E7" t="n">
         <v>0.11</v>
@@ -3484,52 +3484,52 @@
         <v>2.44</v>
       </c>
       <c r="AF7" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.62</v>
+        <v>1.56</v>
       </c>
       <c r="AH7" t="n">
-        <v>2.88</v>
+        <v>3</v>
       </c>
       <c r="AI7" t="n">
-        <v>79.88</v>
+        <v>81.33</v>
       </c>
       <c r="AJ7" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="AK7" t="n">
-        <v>2.38</v>
+        <v>2.33</v>
       </c>
       <c r="AL7" t="n">
-        <v>5.12</v>
+        <v>5.56</v>
       </c>
       <c r="AM7" t="n">
-        <v>0.38</v>
+        <v>0.44</v>
       </c>
       <c r="AN7" t="n">
-        <v>40.75</v>
+        <v>41.56</v>
       </c>
       <c r="AO7" t="n">
-        <v>0.75</v>
+        <v>0.78</v>
       </c>
       <c r="AP7" t="n">
-        <v>2.25</v>
+        <v>2.56</v>
       </c>
       <c r="AQ7" t="n">
-        <v>9.119999999999999</v>
+        <v>9.779999999999999</v>
       </c>
       <c r="AR7" t="n">
-        <v>10.12</v>
+        <v>10.33</v>
       </c>
       <c r="AS7" t="n">
-        <v>9</v>
+        <v>8.779999999999999</v>
       </c>
       <c r="AT7" t="n">
-        <v>1</v>
+        <v>1.11</v>
       </c>
       <c r="AU7" t="n">
-        <v>1.38</v>
+        <v>1.56</v>
       </c>
       <c r="AV7" t="n">
         <v>0</v>
@@ -3541,82 +3541,82 @@
         <v>0</v>
       </c>
       <c r="AY7" t="n">
-        <v>47.12</v>
+        <v>47.33</v>
       </c>
       <c r="AZ7" t="n">
         <v>0</v>
       </c>
       <c r="BA7" t="n">
-        <v>10.62</v>
+        <v>10.78</v>
       </c>
       <c r="BB7" t="n">
-        <v>6.25</v>
+        <v>6.22</v>
       </c>
       <c r="BC7" t="n">
-        <v>4.38</v>
+        <v>4.56</v>
       </c>
       <c r="BD7" t="n">
-        <v>20.38</v>
+        <v>20.22</v>
       </c>
       <c r="BE7" t="n">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="BF7" t="n">
-        <v>2.38</v>
+        <v>2.33</v>
       </c>
       <c r="BG7" t="n">
-        <v>2.29</v>
+        <v>2.44</v>
       </c>
       <c r="BH7" t="n">
-        <v>11.53</v>
+        <v>11.72</v>
       </c>
       <c r="BI7" t="n">
-        <v>2.29</v>
+        <v>2.44</v>
       </c>
       <c r="BJ7" t="n">
-        <v>0.47</v>
+        <v>0.44</v>
       </c>
       <c r="BK7" t="n">
-        <v>0.41</v>
+        <v>0.5</v>
       </c>
       <c r="BL7" t="n">
-        <v>0.59</v>
+        <v>0.67</v>
       </c>
       <c r="BM7" t="n">
-        <v>0.82</v>
+        <v>0.83</v>
       </c>
       <c r="BN7" t="n">
-        <v>1.41</v>
+        <v>1.5</v>
       </c>
       <c r="BO7" t="n">
-        <v>0.88</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="BP7" t="n">
-        <v>5.29</v>
+        <v>5.39</v>
       </c>
       <c r="BQ7" t="n">
-        <v>6.24</v>
+        <v>6.33</v>
       </c>
       <c r="BR7" t="n">
-        <v>94.12</v>
+        <v>94.44</v>
       </c>
       <c r="BS7" t="n">
-        <v>70.59</v>
+        <v>72.22</v>
       </c>
       <c r="BT7" t="n">
-        <v>35.29</v>
+        <v>38.89</v>
       </c>
       <c r="BU7" t="n">
-        <v>23.53</v>
+        <v>27.78</v>
       </c>
       <c r="BV7" t="n">
-        <v>5.88</v>
+        <v>11.11</v>
       </c>
       <c r="BW7" t="n">
         <v>0</v>
       </c>
       <c r="BX7" t="n">
-        <v>64.70999999999999</v>
+        <v>66.67</v>
       </c>
       <c r="BY7" t="n">
         <v>2.9</v>
@@ -3625,28 +3625,28 @@
         <v>3.11</v>
       </c>
       <c r="CA7" t="n">
-        <v>3.65</v>
+        <v>3.68</v>
       </c>
       <c r="CB7" t="n">
-        <v>3.78</v>
+        <v>3.81</v>
       </c>
       <c r="CC7" t="n">
-        <v>3.47</v>
+        <v>3.5</v>
       </c>
       <c r="CD7" t="n">
-        <v>3.9</v>
+        <v>4.04</v>
       </c>
       <c r="CE7" t="n">
         <v>1.3</v>
       </c>
       <c r="CF7" t="n">
-        <v>2.42</v>
+        <v>2.41</v>
       </c>
       <c r="CG7" t="n">
-        <v>3.26</v>
+        <v>3.27</v>
       </c>
       <c r="CH7" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="CI7" t="n">
         <v>2.26</v>
@@ -3661,7 +3661,7 @@
         <v>1.76</v>
       </c>
       <c r="CM7" t="n">
-        <v>2.77</v>
+        <v>2.76</v>
       </c>
       <c r="CN7" t="n">
         <v>2.11</v>
@@ -3670,10 +3670,10 @@
         <v>1.21</v>
       </c>
       <c r="CP7" t="n">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="CQ7" t="n">
-        <v>2.7</v>
+        <v>2.69</v>
       </c>
       <c r="CR7" t="n">
         <v>1.36</v>
@@ -3688,106 +3688,106 @@
         <v>1.55</v>
       </c>
       <c r="CV7" t="n">
-        <v>2.39</v>
+        <v>2.38</v>
       </c>
       <c r="CW7" t="n">
         <v>1.63</v>
       </c>
       <c r="CX7" t="n">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="CY7" t="n">
         <v>1.72</v>
       </c>
       <c r="CZ7" t="n">
-        <v>2.54</v>
+        <v>2.56</v>
       </c>
       <c r="DA7" t="n">
-        <v>2.12</v>
+        <v>2.13</v>
       </c>
       <c r="DB7" t="n">
         <v>1.23</v>
       </c>
       <c r="DC7" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="DD7" t="n">
-        <v>2.82</v>
+        <v>2.8</v>
       </c>
       <c r="DE7" t="n">
         <v>0.11</v>
       </c>
       <c r="DF7" t="n">
-        <v>1.59</v>
+        <v>1.56</v>
       </c>
       <c r="DG7" t="n">
-        <v>2.71</v>
+        <v>2.78</v>
       </c>
       <c r="DH7" t="n">
-        <v>85</v>
+        <v>85.44</v>
       </c>
       <c r="DI7" t="n">
-        <v>0.23</v>
+        <v>0.22</v>
       </c>
       <c r="DJ7" t="n">
-        <v>2.41</v>
+        <v>2.38</v>
       </c>
       <c r="DK7" t="n">
-        <v>4.82</v>
+        <v>5.06</v>
       </c>
       <c r="DL7" t="n">
-        <v>0.24</v>
+        <v>0.28</v>
       </c>
       <c r="DM7" t="n">
-        <v>45.65</v>
+        <v>45.78</v>
       </c>
       <c r="DN7" t="n">
-        <v>0.82</v>
+        <v>0.84</v>
       </c>
       <c r="DO7" t="n">
-        <v>2.12</v>
+        <v>2.28</v>
       </c>
       <c r="DP7" t="n">
-        <v>9.880000000000001</v>
+        <v>10.17</v>
       </c>
       <c r="DQ7" t="n">
-        <v>10.76</v>
+        <v>10.83</v>
       </c>
       <c r="DR7" t="n">
-        <v>9.76</v>
+        <v>9.609999999999999</v>
       </c>
       <c r="DS7" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DT7" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DU7" t="n">
         <v>0</v>
       </c>
       <c r="DV7" t="n">
-        <v>48.59</v>
+        <v>48.61</v>
       </c>
       <c r="DW7" t="n">
         <v>0</v>
       </c>
       <c r="DX7" t="n">
-        <v>10.41</v>
+        <v>10.5</v>
       </c>
       <c r="DY7" t="n">
-        <v>6.47</v>
+        <v>6.44</v>
       </c>
       <c r="DZ7" t="n">
-        <v>3.95</v>
+        <v>4.06</v>
       </c>
       <c r="EA7" t="n">
-        <v>21.06</v>
+        <v>20.94</v>
       </c>
       <c r="EB7" t="n">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="EC7" t="n">
-        <v>2.41</v>
+        <v>2.38</v>
       </c>
     </row>
     <row r="8">
@@ -3797,13 +3797,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C8" t="n">
         <v>9</v>
       </c>
       <c r="D8" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E8" t="n">
         <v>0.22</v>
@@ -3887,139 +3887,139 @@
         <v>1.44</v>
       </c>
       <c r="AF8" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.62</v>
+        <v>1.78</v>
       </c>
       <c r="AH8" t="n">
-        <v>2.12</v>
+        <v>2.22</v>
       </c>
       <c r="AI8" t="n">
-        <v>83.38</v>
+        <v>82.78</v>
       </c>
       <c r="AJ8" t="n">
         <v>0</v>
       </c>
       <c r="AK8" t="n">
-        <v>1.62</v>
+        <v>1.89</v>
       </c>
       <c r="AL8" t="n">
-        <v>4.25</v>
+        <v>4.56</v>
       </c>
       <c r="AM8" t="n">
-        <v>0.12</v>
+        <v>0.22</v>
       </c>
       <c r="AN8" t="n">
-        <v>39.25</v>
+        <v>39.89</v>
       </c>
       <c r="AO8" t="n">
         <v>0</v>
       </c>
       <c r="AP8" t="n">
-        <v>2.12</v>
+        <v>2.33</v>
       </c>
       <c r="AQ8" t="n">
-        <v>13.62</v>
+        <v>13.44</v>
       </c>
       <c r="AR8" t="n">
-        <v>11.38</v>
+        <v>11.56</v>
       </c>
       <c r="AS8" t="n">
-        <v>8.5</v>
+        <v>9</v>
       </c>
       <c r="AT8" t="n">
-        <v>2.5</v>
+        <v>2.33</v>
       </c>
       <c r="AU8" t="n">
-        <v>1.62</v>
+        <v>1.56</v>
       </c>
       <c r="AV8" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="AW8" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="AX8" t="n">
         <v>0</v>
       </c>
       <c r="AY8" t="n">
-        <v>49.25</v>
+        <v>47.33</v>
       </c>
       <c r="AZ8" t="n">
-        <v>0</v>
+        <v>0.11</v>
       </c>
       <c r="BA8" t="n">
-        <v>14.38</v>
+        <v>13.89</v>
       </c>
       <c r="BB8" t="n">
-        <v>9.880000000000001</v>
+        <v>9.56</v>
       </c>
       <c r="BC8" t="n">
-        <v>4.5</v>
+        <v>4.33</v>
       </c>
       <c r="BD8" t="n">
-        <v>22.62</v>
+        <v>22</v>
       </c>
       <c r="BE8" t="n">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="BF8" t="n">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="BG8" t="n">
-        <v>3</v>
+        <v>2.94</v>
       </c>
       <c r="BH8" t="n">
-        <v>10.18</v>
+        <v>10.5</v>
       </c>
       <c r="BI8" t="n">
-        <v>3</v>
+        <v>2.94</v>
       </c>
       <c r="BJ8" t="n">
-        <v>0.88</v>
+        <v>0.83</v>
       </c>
       <c r="BK8" t="n">
-        <v>0.47</v>
+        <v>0.5</v>
       </c>
       <c r="BL8" t="n">
         <v>1</v>
       </c>
       <c r="BM8" t="n">
-        <v>0.65</v>
+        <v>0.61</v>
       </c>
       <c r="BN8" t="n">
-        <v>1.65</v>
+        <v>1.61</v>
       </c>
       <c r="BO8" t="n">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="BP8" t="n">
-        <v>4.82</v>
+        <v>4.89</v>
       </c>
       <c r="BQ8" t="n">
-        <v>5.35</v>
+        <v>5.56</v>
       </c>
       <c r="BR8" t="n">
-        <v>88.23999999999999</v>
+        <v>88.89</v>
       </c>
       <c r="BS8" t="n">
-        <v>76.47</v>
+        <v>77.78</v>
       </c>
       <c r="BT8" t="n">
-        <v>41.18</v>
+        <v>38.89</v>
       </c>
       <c r="BU8" t="n">
-        <v>35.29</v>
+        <v>33.33</v>
       </c>
       <c r="BV8" t="n">
-        <v>17.65</v>
+        <v>16.67</v>
       </c>
       <c r="BW8" t="n">
-        <v>11.76</v>
+        <v>11.11</v>
       </c>
       <c r="BX8" t="n">
-        <v>35.29</v>
+        <v>38.89</v>
       </c>
       <c r="BY8" t="n">
         <v>2.25</v>
@@ -4028,25 +4028,25 @@
         <v>2.37</v>
       </c>
       <c r="CA8" t="n">
-        <v>3.88</v>
+        <v>3.89</v>
       </c>
       <c r="CB8" t="n">
-        <v>3.97</v>
+        <v>3.95</v>
       </c>
       <c r="CC8" t="n">
-        <v>4.48</v>
+        <v>4.44</v>
       </c>
       <c r="CD8" t="n">
-        <v>4.38</v>
+        <v>4.3</v>
       </c>
       <c r="CE8" t="n">
         <v>1.26</v>
       </c>
       <c r="CF8" t="n">
-        <v>2.26</v>
+        <v>2.25</v>
       </c>
       <c r="CG8" t="n">
-        <v>3.56</v>
+        <v>3.55</v>
       </c>
       <c r="CH8" t="n">
         <v>1.6</v>
@@ -4067,13 +4067,13 @@
         <v>2.89</v>
       </c>
       <c r="CN8" t="n">
-        <v>2.23</v>
+        <v>2.22</v>
       </c>
       <c r="CO8" t="n">
         <v>1.15</v>
       </c>
       <c r="CP8" t="n">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="CQ8" t="n">
         <v>2.42</v>
@@ -4088,105 +4088,109 @@
         <v>3.3</v>
       </c>
       <c r="CU8" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="CV8" t="n">
-        <v>2.59</v>
+        <v>2.58</v>
       </c>
       <c r="CW8" t="n">
         <v>1.54</v>
       </c>
-      <c r="CX8" t="inlineStr"/>
+      <c r="CX8" t="n">
+        <v>1.46</v>
+      </c>
       <c r="CY8" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="CZ8" t="inlineStr"/>
+        <v>1.63</v>
+      </c>
+      <c r="CZ8" t="n">
+        <v>2.67</v>
+      </c>
       <c r="DA8" t="n">
-        <v>2.29</v>
+        <v>2.27</v>
       </c>
       <c r="DB8" t="n">
         <v>1.18</v>
       </c>
       <c r="DC8" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="DD8" t="n">
-        <v>2.46</v>
+        <v>2.47</v>
       </c>
       <c r="DE8" t="n">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
       <c r="DF8" t="n">
-        <v>1.29</v>
+        <v>1.39</v>
       </c>
       <c r="DG8" t="n">
-        <v>2.64</v>
+        <v>2.66</v>
       </c>
       <c r="DH8" t="n">
-        <v>90.77</v>
+        <v>90.06</v>
       </c>
       <c r="DI8" t="n">
         <v>0</v>
       </c>
       <c r="DJ8" t="n">
-        <v>1.52</v>
+        <v>1.66</v>
       </c>
       <c r="DK8" t="n">
-        <v>5.41</v>
+        <v>5.5</v>
       </c>
       <c r="DL8" t="n">
-        <v>0.17</v>
+        <v>0.22</v>
       </c>
       <c r="DM8" t="n">
-        <v>49.06</v>
+        <v>48.84</v>
       </c>
       <c r="DN8" t="n">
-        <v>0.23</v>
+        <v>0.22</v>
       </c>
       <c r="DO8" t="n">
-        <v>2.76</v>
+        <v>2.83</v>
       </c>
       <c r="DP8" t="n">
         <v>12</v>
       </c>
       <c r="DQ8" t="n">
-        <v>12.18</v>
+        <v>12.23</v>
       </c>
       <c r="DR8" t="n">
-        <v>7.94</v>
+        <v>8.220000000000001</v>
       </c>
       <c r="DS8" t="n">
-        <v>0.18</v>
+        <v>0.16</v>
       </c>
       <c r="DT8" t="n">
-        <v>0.18</v>
+        <v>0.16</v>
       </c>
       <c r="DU8" t="n">
         <v>0</v>
       </c>
       <c r="DV8" t="n">
-        <v>49.35</v>
+        <v>48.38</v>
       </c>
       <c r="DW8" t="n">
-        <v>0</v>
+        <v>0.06</v>
       </c>
       <c r="DX8" t="n">
-        <v>16.06</v>
+        <v>15.73</v>
       </c>
       <c r="DY8" t="n">
-        <v>11.18</v>
+        <v>10.94</v>
       </c>
       <c r="DZ8" t="n">
-        <v>4.88</v>
+        <v>4.77</v>
       </c>
       <c r="EA8" t="n">
-        <v>20.94</v>
+        <v>20.72</v>
       </c>
       <c r="EB8" t="n">
-        <v>1.68</v>
+        <v>1.66</v>
       </c>
       <c r="EC8" t="n">
-        <v>1.52</v>
+        <v>1.56</v>
       </c>
     </row>
     <row r="9">
@@ -4196,13 +4200,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C9" t="n">
         <v>9</v>
       </c>
       <c r="D9" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E9" t="n">
         <v>0.33</v>
@@ -4292,46 +4296,46 @@
         <v>2</v>
       </c>
       <c r="AH9" t="n">
-        <v>2.62</v>
+        <v>2.56</v>
       </c>
       <c r="AI9" t="n">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="AJ9" t="n">
         <v>0</v>
       </c>
       <c r="AK9" t="n">
-        <v>3.25</v>
+        <v>3.11</v>
       </c>
       <c r="AL9" t="n">
-        <v>4.38</v>
+        <v>4.33</v>
       </c>
       <c r="AM9" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="AN9" t="n">
-        <v>43.88</v>
+        <v>43.44</v>
       </c>
       <c r="AO9" t="n">
-        <v>1.25</v>
+        <v>1.11</v>
       </c>
       <c r="AP9" t="n">
-        <v>1.75</v>
+        <v>1.78</v>
       </c>
       <c r="AQ9" t="n">
-        <v>17.38</v>
+        <v>17</v>
       </c>
       <c r="AR9" t="n">
-        <v>10.62</v>
+        <v>10.89</v>
       </c>
       <c r="AS9" t="n">
-        <v>8.619999999999999</v>
+        <v>8.33</v>
       </c>
       <c r="AT9" t="n">
-        <v>2</v>
+        <v>1.78</v>
       </c>
       <c r="AU9" t="n">
-        <v>0.75</v>
+        <v>0.78</v>
       </c>
       <c r="AV9" t="n">
         <v>0</v>
@@ -4343,82 +4347,82 @@
         <v>0</v>
       </c>
       <c r="AY9" t="n">
-        <v>43.88</v>
+        <v>44.78</v>
       </c>
       <c r="AZ9" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="BA9" t="n">
-        <v>11</v>
+        <v>11.78</v>
       </c>
       <c r="BB9" t="n">
-        <v>7.38</v>
+        <v>7.56</v>
       </c>
       <c r="BC9" t="n">
-        <v>3.62</v>
+        <v>4.22</v>
       </c>
       <c r="BD9" t="n">
-        <v>19.88</v>
+        <v>20.67</v>
       </c>
       <c r="BE9" t="n">
-        <v>1.27</v>
+        <v>1.35</v>
       </c>
       <c r="BF9" t="n">
-        <v>3.12</v>
+        <v>3</v>
       </c>
       <c r="BG9" t="n">
-        <v>2.65</v>
+        <v>2.56</v>
       </c>
       <c r="BH9" t="n">
-        <v>9.65</v>
+        <v>9.609999999999999</v>
       </c>
       <c r="BI9" t="n">
-        <v>2.65</v>
+        <v>2.56</v>
       </c>
       <c r="BJ9" t="n">
-        <v>0.82</v>
+        <v>0.78</v>
       </c>
       <c r="BK9" t="n">
-        <v>0.41</v>
+        <v>0.39</v>
       </c>
       <c r="BL9" t="n">
-        <v>0.82</v>
+        <v>0.78</v>
       </c>
       <c r="BM9" t="n">
-        <v>0.59</v>
+        <v>0.61</v>
       </c>
       <c r="BN9" t="n">
-        <v>1.41</v>
+        <v>1.39</v>
       </c>
       <c r="BO9" t="n">
-        <v>1.24</v>
+        <v>1.17</v>
       </c>
       <c r="BP9" t="n">
-        <v>4.82</v>
+        <v>4.83</v>
       </c>
       <c r="BQ9" t="n">
-        <v>4.82</v>
+        <v>4.78</v>
       </c>
       <c r="BR9" t="n">
         <v>100</v>
       </c>
       <c r="BS9" t="n">
-        <v>82.34999999999999</v>
+        <v>77.78</v>
       </c>
       <c r="BT9" t="n">
-        <v>52.94</v>
+        <v>50</v>
       </c>
       <c r="BU9" t="n">
-        <v>23.53</v>
+        <v>22.22</v>
       </c>
       <c r="BV9" t="n">
-        <v>5.88</v>
+        <v>5.56</v>
       </c>
       <c r="BW9" t="n">
         <v>0</v>
       </c>
       <c r="BX9" t="n">
-        <v>58.82</v>
+        <v>55.56</v>
       </c>
       <c r="BY9" t="n">
         <v>2.97</v>
@@ -4427,34 +4431,34 @@
         <v>3.03</v>
       </c>
       <c r="CA9" t="n">
-        <v>3.57</v>
+        <v>3.55</v>
       </c>
       <c r="CB9" t="n">
-        <v>3.6</v>
+        <v>3.58</v>
       </c>
       <c r="CC9" t="n">
-        <v>4.37</v>
+        <v>4.22</v>
       </c>
       <c r="CD9" t="n">
-        <v>4.63</v>
+        <v>4.51</v>
       </c>
       <c r="CE9" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="CF9" t="n">
-        <v>2.67</v>
+        <v>2.7</v>
       </c>
       <c r="CG9" t="n">
-        <v>3.04</v>
+        <v>3.01</v>
       </c>
       <c r="CH9" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="CI9" t="n">
-        <v>2.01</v>
+        <v>2</v>
       </c>
       <c r="CJ9" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="CK9" t="n">
         <v>1.44</v>
@@ -4463,100 +4467,100 @@
         <v>1.78</v>
       </c>
       <c r="CM9" t="n">
-        <v>2.58</v>
+        <v>2.57</v>
       </c>
       <c r="CN9" t="n">
         <v>2</v>
       </c>
       <c r="CO9" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="CP9" t="n">
-        <v>1.87</v>
+        <v>1.9</v>
       </c>
       <c r="CQ9" t="n">
-        <v>3.13</v>
+        <v>3.18</v>
       </c>
       <c r="CR9" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="CS9" t="n">
-        <v>2.81</v>
+        <v>2.84</v>
       </c>
       <c r="CT9" t="n">
-        <v>3.11</v>
+        <v>3.08</v>
       </c>
       <c r="CU9" t="n">
         <v>1.45</v>
       </c>
       <c r="CV9" t="n">
-        <v>2.12</v>
+        <v>2.11</v>
       </c>
       <c r="CW9" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="CX9" t="n">
         <v>1.51</v>
       </c>
       <c r="CY9" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="CZ9" t="n">
-        <v>2.52</v>
+        <v>2.51</v>
       </c>
       <c r="DA9" t="n">
         <v>2.03</v>
       </c>
       <c r="DB9" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="DC9" t="n">
-        <v>1.94</v>
+        <v>1.96</v>
       </c>
       <c r="DD9" t="n">
-        <v>3.24</v>
+        <v>3.29</v>
       </c>
       <c r="DE9" t="n">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
       <c r="DF9" t="n">
-        <v>2.17</v>
+        <v>2.16</v>
       </c>
       <c r="DG9" t="n">
-        <v>2.41</v>
+        <v>2.39</v>
       </c>
       <c r="DH9" t="n">
-        <v>78.34999999999999</v>
+        <v>77.89</v>
       </c>
       <c r="DI9" t="n">
         <v>0</v>
       </c>
       <c r="DJ9" t="n">
-        <v>3.06</v>
+        <v>3</v>
       </c>
       <c r="DK9" t="n">
-        <v>4.18</v>
+        <v>4.16</v>
       </c>
       <c r="DL9" t="n">
-        <v>0.41</v>
+        <v>0.39</v>
       </c>
       <c r="DM9" t="n">
-        <v>40.65</v>
+        <v>40.61</v>
       </c>
       <c r="DN9" t="n">
-        <v>0.88</v>
+        <v>0.84</v>
       </c>
       <c r="DO9" t="n">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="DP9" t="n">
-        <v>16.71</v>
+        <v>16.56</v>
       </c>
       <c r="DQ9" t="n">
-        <v>11.23</v>
+        <v>11.34</v>
       </c>
       <c r="DR9" t="n">
-        <v>8.35</v>
+        <v>8.220000000000001</v>
       </c>
       <c r="DS9" t="n">
         <v>0</v>
@@ -4568,28 +4572,28 @@
         <v>0</v>
       </c>
       <c r="DV9" t="n">
-        <v>44.18</v>
+        <v>44.61</v>
       </c>
       <c r="DW9" t="n">
         <v>0.06</v>
       </c>
       <c r="DX9" t="n">
-        <v>12.53</v>
+        <v>12.84</v>
       </c>
       <c r="DY9" t="n">
-        <v>8.35</v>
+        <v>8.390000000000001</v>
       </c>
       <c r="DZ9" t="n">
-        <v>4.18</v>
+        <v>4.44</v>
       </c>
       <c r="EA9" t="n">
-        <v>18.77</v>
+        <v>19.23</v>
       </c>
       <c r="EB9" t="n">
-        <v>1.38</v>
+        <v>1.41</v>
       </c>
       <c r="EC9" t="n">
-        <v>3</v>
+        <v>2.94</v>
       </c>
     </row>
     <row r="10">
@@ -4599,13 +4603,13 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C10" t="n">
         <v>9</v>
       </c>
       <c r="D10" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
@@ -4689,52 +4693,52 @@
         <v>1.67</v>
       </c>
       <c r="AF10" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="AH10" t="n">
-        <v>2.12</v>
+        <v>2.11</v>
       </c>
       <c r="AI10" t="n">
-        <v>81.38</v>
+        <v>78.78</v>
       </c>
       <c r="AJ10" t="n">
         <v>0</v>
       </c>
       <c r="AK10" t="n">
-        <v>2.12</v>
+        <v>2.11</v>
       </c>
       <c r="AL10" t="n">
-        <v>3.5</v>
+        <v>3.33</v>
       </c>
       <c r="AM10" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="AN10" t="n">
-        <v>34</v>
+        <v>32.78</v>
       </c>
       <c r="AO10" t="n">
-        <v>0.75</v>
+        <v>0.67</v>
       </c>
       <c r="AP10" t="n">
-        <v>1.38</v>
+        <v>1.22</v>
       </c>
       <c r="AQ10" t="n">
-        <v>13.12</v>
+        <v>13.11</v>
       </c>
       <c r="AR10" t="n">
-        <v>13.38</v>
+        <v>13.22</v>
       </c>
       <c r="AS10" t="n">
-        <v>9.5</v>
+        <v>9</v>
       </c>
       <c r="AT10" t="n">
-        <v>1.38</v>
+        <v>1.44</v>
       </c>
       <c r="AU10" t="n">
-        <v>0.88</v>
+        <v>1</v>
       </c>
       <c r="AV10" t="n">
         <v>0</v>
@@ -4746,82 +4750,82 @@
         <v>0</v>
       </c>
       <c r="AY10" t="n">
-        <v>31.38</v>
+        <v>31.22</v>
       </c>
       <c r="AZ10" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="BA10" t="n">
         <v>8</v>
       </c>
       <c r="BB10" t="n">
-        <v>5.88</v>
+        <v>5.67</v>
       </c>
       <c r="BC10" t="n">
-        <v>2.12</v>
+        <v>2.33</v>
       </c>
       <c r="BD10" t="n">
-        <v>22</v>
+        <v>21.11</v>
       </c>
       <c r="BE10" t="n">
         <v>0.91</v>
       </c>
       <c r="BF10" t="n">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="BG10" t="n">
-        <v>1.71</v>
+        <v>1.83</v>
       </c>
       <c r="BH10" t="n">
-        <v>8.41</v>
+        <v>8.220000000000001</v>
       </c>
       <c r="BI10" t="n">
-        <v>1.71</v>
+        <v>1.83</v>
       </c>
       <c r="BJ10" t="n">
-        <v>0.47</v>
+        <v>0.5</v>
       </c>
       <c r="BK10" t="n">
-        <v>0.35</v>
+        <v>0.39</v>
       </c>
       <c r="BL10" t="n">
-        <v>0.47</v>
+        <v>0.5</v>
       </c>
       <c r="BM10" t="n">
-        <v>0.41</v>
+        <v>0.44</v>
       </c>
       <c r="BN10" t="n">
-        <v>0.88</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="BO10" t="n">
-        <v>0.82</v>
+        <v>0.89</v>
       </c>
       <c r="BP10" t="n">
-        <v>3.53</v>
+        <v>3.44</v>
       </c>
       <c r="BQ10" t="n">
-        <v>4.88</v>
+        <v>4.78</v>
       </c>
       <c r="BR10" t="n">
-        <v>70.59</v>
+        <v>72.22</v>
       </c>
       <c r="BS10" t="n">
-        <v>47.06</v>
+        <v>50</v>
       </c>
       <c r="BT10" t="n">
-        <v>35.29</v>
+        <v>38.89</v>
       </c>
       <c r="BU10" t="n">
-        <v>11.76</v>
+        <v>16.67</v>
       </c>
       <c r="BV10" t="n">
-        <v>5.88</v>
+        <v>5.56</v>
       </c>
       <c r="BW10" t="n">
         <v>0</v>
       </c>
       <c r="BX10" t="n">
-        <v>41.18</v>
+        <v>44.44</v>
       </c>
       <c r="BY10" t="n">
         <v>3.64</v>
@@ -4830,22 +4834,22 @@
         <v>3.82</v>
       </c>
       <c r="CA10" t="n">
-        <v>3.49</v>
+        <v>3.48</v>
       </c>
       <c r="CB10" t="n">
-        <v>3.54</v>
+        <v>3.52</v>
       </c>
       <c r="CC10" t="n">
-        <v>4.16</v>
+        <v>4.06</v>
       </c>
       <c r="CD10" t="n">
-        <v>4.31</v>
+        <v>4.23</v>
       </c>
       <c r="CE10" t="n">
         <v>1.39</v>
       </c>
       <c r="CF10" t="n">
-        <v>2.8</v>
+        <v>2.81</v>
       </c>
       <c r="CG10" t="n">
         <v>2.84</v>
@@ -4854,22 +4858,22 @@
         <v>1.39</v>
       </c>
       <c r="CI10" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="CJ10" t="n">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="CK10" t="n">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="CL10" t="n">
-        <v>2.02</v>
+        <v>2.01</v>
       </c>
       <c r="CM10" t="n">
-        <v>2.31</v>
+        <v>2.32</v>
       </c>
       <c r="CN10" t="n">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="CO10" t="n">
         <v>1.31</v>
@@ -4878,7 +4882,7 @@
         <v>2</v>
       </c>
       <c r="CQ10" t="n">
-        <v>3.55</v>
+        <v>3.54</v>
       </c>
       <c r="CR10" t="n">
         <v>1.41</v>
@@ -4902,13 +4906,13 @@
         <v>1.62</v>
       </c>
       <c r="CY10" t="n">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="CZ10" t="n">
-        <v>2.28</v>
+        <v>2.29</v>
       </c>
       <c r="DA10" t="n">
-        <v>1.79</v>
+        <v>1.81</v>
       </c>
       <c r="DB10" t="n">
         <v>1.34</v>
@@ -4923,43 +4927,43 @@
         <v>0.06</v>
       </c>
       <c r="DF10" t="n">
-        <v>1.06</v>
+        <v>1.11</v>
       </c>
       <c r="DG10" t="n">
-        <v>2.35</v>
+        <v>2.34</v>
       </c>
       <c r="DH10" t="n">
-        <v>80.23999999999999</v>
+        <v>79</v>
       </c>
       <c r="DI10" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DJ10" t="n">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="DK10" t="n">
-        <v>4.29</v>
+        <v>4.16</v>
       </c>
       <c r="DL10" t="n">
-        <v>0.18</v>
+        <v>0.16</v>
       </c>
       <c r="DM10" t="n">
-        <v>38.94</v>
+        <v>38.06</v>
       </c>
       <c r="DN10" t="n">
-        <v>0.77</v>
+        <v>0.73</v>
       </c>
       <c r="DO10" t="n">
-        <v>1.94</v>
+        <v>1.83</v>
       </c>
       <c r="DP10" t="n">
-        <v>12.23</v>
+        <v>12.27</v>
       </c>
       <c r="DQ10" t="n">
-        <v>12.35</v>
+        <v>12.33</v>
       </c>
       <c r="DR10" t="n">
-        <v>9.119999999999999</v>
+        <v>8.890000000000001</v>
       </c>
       <c r="DS10" t="n">
         <v>0</v>
@@ -4971,28 +4975,28 @@
         <v>0</v>
       </c>
       <c r="DV10" t="n">
-        <v>34.24</v>
+        <v>34</v>
       </c>
       <c r="DW10" t="n">
         <v>0.06</v>
       </c>
       <c r="DX10" t="n">
-        <v>9.359999999999999</v>
+        <v>9.279999999999999</v>
       </c>
       <c r="DY10" t="n">
-        <v>6.89</v>
+        <v>6.72</v>
       </c>
       <c r="DZ10" t="n">
-        <v>2.47</v>
+        <v>2.55</v>
       </c>
       <c r="EA10" t="n">
-        <v>21.41</v>
+        <v>21</v>
       </c>
       <c r="EB10" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="EC10" t="n">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
     </row>
     <row r="11">
@@ -5002,94 +5006,94 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C11" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D11" t="n">
         <v>8</v>
       </c>
       <c r="E11" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="F11" t="n">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="G11" t="n">
-        <v>3.44</v>
+        <v>3.3</v>
       </c>
       <c r="H11" t="n">
-        <v>103.22</v>
+        <v>104.9</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
       </c>
       <c r="J11" t="n">
-        <v>2.78</v>
+        <v>2.9</v>
       </c>
       <c r="K11" t="n">
-        <v>6.44</v>
+        <v>6.4</v>
       </c>
       <c r="L11" t="n">
-        <v>0.44</v>
+        <v>0.6</v>
       </c>
       <c r="M11" t="n">
-        <v>58.78</v>
+        <v>58.6</v>
       </c>
       <c r="N11" t="n">
-        <v>0.89</v>
+        <v>1</v>
       </c>
       <c r="O11" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="P11" t="n">
-        <v>13.67</v>
+        <v>13.4</v>
       </c>
       <c r="Q11" t="n">
-        <v>10.56</v>
+        <v>11.3</v>
       </c>
       <c r="R11" t="n">
-        <v>7.67</v>
+        <v>7.3</v>
       </c>
       <c r="S11" t="n">
-        <v>0.78</v>
+        <v>0.8</v>
       </c>
       <c r="T11" t="n">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="U11" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="V11" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="W11" t="n">
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>49.67</v>
+        <v>50.1</v>
       </c>
       <c r="Y11" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="Z11" t="n">
-        <v>16.33</v>
+        <v>16.9</v>
       </c>
       <c r="AA11" t="n">
-        <v>10.89</v>
+        <v>11.1</v>
       </c>
       <c r="AB11" t="n">
-        <v>5.44</v>
+        <v>5.8</v>
       </c>
       <c r="AC11" t="n">
-        <v>19.56</v>
+        <v>19.6</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.84</v>
+        <v>1.9</v>
       </c>
       <c r="AE11" t="n">
-        <v>2.56</v>
+        <v>2.7</v>
       </c>
       <c r="AF11" t="n">
         <v>0.12</v>
@@ -5173,64 +5177,64 @@
         <v>2.38</v>
       </c>
       <c r="BG11" t="n">
-        <v>2.35</v>
+        <v>2.39</v>
       </c>
       <c r="BH11" t="n">
-        <v>10.29</v>
+        <v>10.17</v>
       </c>
       <c r="BI11" t="n">
-        <v>2.35</v>
+        <v>2.39</v>
       </c>
       <c r="BJ11" t="n">
-        <v>0.65</v>
+        <v>0.61</v>
       </c>
       <c r="BK11" t="n">
-        <v>0.29</v>
+        <v>0.28</v>
       </c>
       <c r="BL11" t="n">
-        <v>0.82</v>
+        <v>0.89</v>
       </c>
       <c r="BM11" t="n">
-        <v>0.59</v>
+        <v>0.61</v>
       </c>
       <c r="BN11" t="n">
-        <v>1.41</v>
+        <v>1.5</v>
       </c>
       <c r="BO11" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.89</v>
       </c>
       <c r="BP11" t="n">
-        <v>5.06</v>
+        <v>5</v>
       </c>
       <c r="BQ11" t="n">
-        <v>5.24</v>
+        <v>5.17</v>
       </c>
       <c r="BR11" t="n">
-        <v>94.12</v>
+        <v>94.44</v>
       </c>
       <c r="BS11" t="n">
-        <v>58.82</v>
+        <v>61.11</v>
       </c>
       <c r="BT11" t="n">
-        <v>29.41</v>
+        <v>33.33</v>
       </c>
       <c r="BU11" t="n">
-        <v>29.41</v>
+        <v>27.78</v>
       </c>
       <c r="BV11" t="n">
-        <v>11.76</v>
+        <v>11.11</v>
       </c>
       <c r="BW11" t="n">
-        <v>5.88</v>
+        <v>5.56</v>
       </c>
       <c r="BX11" t="n">
-        <v>35.29</v>
+        <v>38.89</v>
       </c>
       <c r="BY11" t="n">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="BZ11" t="n">
-        <v>2.11</v>
+        <v>2.08</v>
       </c>
       <c r="CA11" t="n">
         <v>3.65</v>
@@ -5251,13 +5255,13 @@
         <v>2.52</v>
       </c>
       <c r="CG11" t="n">
-        <v>3.1</v>
+        <v>3.09</v>
       </c>
       <c r="CH11" t="n">
         <v>1.48</v>
       </c>
       <c r="CI11" t="n">
-        <v>2.15</v>
+        <v>2.16</v>
       </c>
       <c r="CJ11" t="n">
         <v>1.68</v>
@@ -5266,28 +5270,28 @@
         <v>1.47</v>
       </c>
       <c r="CL11" t="n">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="CM11" t="n">
         <v>2.56</v>
       </c>
       <c r="CN11" t="n">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="CO11" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="CP11" t="n">
         <v>1.76</v>
       </c>
       <c r="CQ11" t="n">
-        <v>2.87</v>
+        <v>2.86</v>
       </c>
       <c r="CR11" t="n">
         <v>1.35</v>
       </c>
       <c r="CS11" t="n">
-        <v>2.61</v>
+        <v>2.62</v>
       </c>
       <c r="CT11" t="n">
         <v>3.26</v>
@@ -5305,13 +5309,13 @@
         <v>1.52</v>
       </c>
       <c r="CY11" t="n">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="CZ11" t="n">
-        <v>2.49</v>
+        <v>2.5</v>
       </c>
       <c r="DA11" t="n">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="DB11" t="n">
         <v>1.25</v>
@@ -5320,49 +5324,49 @@
         <v>1.8</v>
       </c>
       <c r="DD11" t="n">
-        <v>2.96</v>
+        <v>2.95</v>
       </c>
       <c r="DE11" t="n">
         <v>0.11</v>
       </c>
       <c r="DF11" t="n">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="DG11" t="n">
-        <v>3.29</v>
+        <v>3.22</v>
       </c>
       <c r="DH11" t="n">
-        <v>99.41</v>
+        <v>100.55</v>
       </c>
       <c r="DI11" t="n">
         <v>0</v>
       </c>
       <c r="DJ11" t="n">
-        <v>2.7</v>
+        <v>2.78</v>
       </c>
       <c r="DK11" t="n">
-        <v>6.41</v>
+        <v>6.39</v>
       </c>
       <c r="DL11" t="n">
-        <v>0.35</v>
+        <v>0.44</v>
       </c>
       <c r="DM11" t="n">
-        <v>58.12</v>
+        <v>58.06</v>
       </c>
       <c r="DN11" t="n">
-        <v>0.9399999999999999</v>
+        <v>1</v>
       </c>
       <c r="DO11" t="n">
-        <v>3.12</v>
+        <v>3.17</v>
       </c>
       <c r="DP11" t="n">
-        <v>13.77</v>
+        <v>13.61</v>
       </c>
       <c r="DQ11" t="n">
-        <v>10</v>
+        <v>10.45</v>
       </c>
       <c r="DR11" t="n">
-        <v>7.88</v>
+        <v>7.66</v>
       </c>
       <c r="DS11" t="n">
         <v>0.11</v>
@@ -5374,28 +5378,28 @@
         <v>0</v>
       </c>
       <c r="DV11" t="n">
-        <v>53</v>
+        <v>53.06</v>
       </c>
       <c r="DW11" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="DX11" t="n">
-        <v>14.76</v>
+        <v>15.17</v>
       </c>
       <c r="DY11" t="n">
-        <v>10</v>
+        <v>10.17</v>
       </c>
       <c r="DZ11" t="n">
-        <v>4.76</v>
+        <v>5</v>
       </c>
       <c r="EA11" t="n">
-        <v>21</v>
+        <v>20.94</v>
       </c>
       <c r="EB11" t="n">
-        <v>1.69</v>
+        <v>1.73</v>
       </c>
       <c r="EC11" t="n">
-        <v>2.48</v>
+        <v>2.56</v>
       </c>
     </row>
     <row r="12">
@@ -5405,13 +5409,13 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C12" t="n">
         <v>9</v>
       </c>
       <c r="D12" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E12" t="n">
         <v>0.11</v>
@@ -5498,49 +5502,49 @@
         <v>0</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.88</v>
+        <v>1.78</v>
       </c>
       <c r="AH12" t="n">
-        <v>2.12</v>
+        <v>2</v>
       </c>
       <c r="AI12" t="n">
-        <v>83.75</v>
+        <v>84.11</v>
       </c>
       <c r="AJ12" t="n">
         <v>0</v>
       </c>
       <c r="AK12" t="n">
-        <v>2.62</v>
+        <v>2.44</v>
       </c>
       <c r="AL12" t="n">
-        <v>3.25</v>
+        <v>3</v>
       </c>
       <c r="AM12" t="n">
-        <v>0.38</v>
+        <v>0.33</v>
       </c>
       <c r="AN12" t="n">
-        <v>32.12</v>
+        <v>31.11</v>
       </c>
       <c r="AO12" t="n">
-        <v>0.62</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AP12" t="n">
-        <v>1.12</v>
+        <v>1</v>
       </c>
       <c r="AQ12" t="n">
-        <v>14.12</v>
+        <v>13.56</v>
       </c>
       <c r="AR12" t="n">
-        <v>12.88</v>
+        <v>12.22</v>
       </c>
       <c r="AS12" t="n">
-        <v>9.119999999999999</v>
+        <v>8.56</v>
       </c>
       <c r="AT12" t="n">
-        <v>1</v>
+        <v>0.89</v>
       </c>
       <c r="AU12" t="n">
-        <v>0.38</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AV12" t="n">
         <v>0</v>
@@ -5552,49 +5556,49 @@
         <v>0</v>
       </c>
       <c r="AY12" t="n">
-        <v>43.62</v>
+        <v>42.67</v>
       </c>
       <c r="AZ12" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="BA12" t="n">
-        <v>9.5</v>
+        <v>9.890000000000001</v>
       </c>
       <c r="BB12" t="n">
-        <v>6.5</v>
+        <v>6.67</v>
       </c>
       <c r="BC12" t="n">
-        <v>3</v>
+        <v>3.22</v>
       </c>
       <c r="BD12" t="n">
-        <v>18.75</v>
+        <v>18.78</v>
       </c>
       <c r="BE12" t="n">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="BF12" t="n">
-        <v>2.38</v>
+        <v>2.22</v>
       </c>
       <c r="BG12" t="n">
-        <v>2.12</v>
+        <v>2.11</v>
       </c>
       <c r="BH12" t="n">
-        <v>9.35</v>
+        <v>9.17</v>
       </c>
       <c r="BI12" t="n">
-        <v>2.12</v>
+        <v>2.11</v>
       </c>
       <c r="BJ12" t="n">
-        <v>0.71</v>
+        <v>0.67</v>
       </c>
       <c r="BK12" t="n">
-        <v>0.35</v>
+        <v>0.39</v>
       </c>
       <c r="BL12" t="n">
-        <v>0.65</v>
+        <v>0.61</v>
       </c>
       <c r="BM12" t="n">
-        <v>0.41</v>
+        <v>0.44</v>
       </c>
       <c r="BN12" t="n">
         <v>1.06</v>
@@ -5603,22 +5607,22 @@
         <v>1.06</v>
       </c>
       <c r="BP12" t="n">
-        <v>4</v>
+        <v>3.89</v>
       </c>
       <c r="BQ12" t="n">
-        <v>5.35</v>
+        <v>5.28</v>
       </c>
       <c r="BR12" t="n">
-        <v>94.12</v>
+        <v>94.44</v>
       </c>
       <c r="BS12" t="n">
-        <v>70.59</v>
+        <v>72.22</v>
       </c>
       <c r="BT12" t="n">
-        <v>35.29</v>
+        <v>33.33</v>
       </c>
       <c r="BU12" t="n">
-        <v>11.76</v>
+        <v>11.11</v>
       </c>
       <c r="BV12" t="n">
         <v>0</v>
@@ -5627,7 +5631,7 @@
         <v>0</v>
       </c>
       <c r="BX12" t="n">
-        <v>52.94</v>
+        <v>50</v>
       </c>
       <c r="BY12" t="n">
         <v>2.74</v>
@@ -5639,16 +5643,16 @@
         <v>3.58</v>
       </c>
       <c r="CB12" t="n">
-        <v>3.73</v>
+        <v>3.71</v>
       </c>
       <c r="CC12" t="n">
-        <v>4.22</v>
+        <v>4.08</v>
       </c>
       <c r="CD12" t="n">
-        <v>4.74</v>
+        <v>4.61</v>
       </c>
       <c r="CE12" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="CF12" t="n">
         <v>2.58</v>
@@ -5660,22 +5664,22 @@
         <v>1.46</v>
       </c>
       <c r="CI12" t="n">
-        <v>2.11</v>
+        <v>2.12</v>
       </c>
       <c r="CJ12" t="n">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="CK12" t="n">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="CL12" t="n">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="CM12" t="n">
-        <v>2.45</v>
+        <v>2.46</v>
       </c>
       <c r="CN12" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="CO12" t="n">
         <v>1.25</v>
@@ -5684,7 +5688,7 @@
         <v>1.82</v>
       </c>
       <c r="CQ12" t="n">
-        <v>3.02</v>
+        <v>3.01</v>
       </c>
       <c r="CR12" t="n">
         <v>1.36</v>
@@ -5723,82 +5727,82 @@
         <v>1.87</v>
       </c>
       <c r="DD12" t="n">
-        <v>3.08</v>
+        <v>3.09</v>
       </c>
       <c r="DE12" t="n">
         <v>0.06</v>
       </c>
       <c r="DF12" t="n">
-        <v>1.59</v>
+        <v>1.56</v>
       </c>
       <c r="DG12" t="n">
-        <v>2.06</v>
+        <v>2</v>
       </c>
       <c r="DH12" t="n">
-        <v>91.29000000000001</v>
+        <v>91.06</v>
       </c>
       <c r="DI12" t="n">
         <v>0</v>
       </c>
       <c r="DJ12" t="n">
-        <v>2.47</v>
+        <v>2.38</v>
       </c>
       <c r="DK12" t="n">
-        <v>4</v>
+        <v>3.84</v>
       </c>
       <c r="DL12" t="n">
-        <v>0.53</v>
+        <v>0.5</v>
       </c>
       <c r="DM12" t="n">
-        <v>38.18</v>
+        <v>37.34</v>
       </c>
       <c r="DN12" t="n">
-        <v>0.76</v>
+        <v>0.73</v>
       </c>
       <c r="DO12" t="n">
-        <v>1.94</v>
+        <v>1.84</v>
       </c>
       <c r="DP12" t="n">
-        <v>12.58</v>
+        <v>12.39</v>
       </c>
       <c r="DQ12" t="n">
-        <v>12.89</v>
+        <v>12.56</v>
       </c>
       <c r="DR12" t="n">
-        <v>7.64</v>
+        <v>7.44</v>
       </c>
       <c r="DS12" t="n">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
       <c r="DT12" t="n">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
       <c r="DU12" t="n">
         <v>0</v>
       </c>
       <c r="DV12" t="n">
-        <v>47.35</v>
+        <v>46.67</v>
       </c>
       <c r="DW12" t="n">
         <v>0.11</v>
       </c>
       <c r="DX12" t="n">
-        <v>11.35</v>
+        <v>11.44</v>
       </c>
       <c r="DY12" t="n">
-        <v>7.18</v>
+        <v>7.22</v>
       </c>
       <c r="DZ12" t="n">
-        <v>4.18</v>
+        <v>4.22</v>
       </c>
       <c r="EA12" t="n">
-        <v>19.53</v>
+        <v>19.5</v>
       </c>
       <c r="EB12" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="EC12" t="n">
-        <v>2.24</v>
+        <v>2.16</v>
       </c>
     </row>
     <row r="13">
@@ -5808,13 +5812,13 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C13" t="n">
         <v>9</v>
       </c>
       <c r="D13" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E13" t="n">
         <v>0.11</v>
@@ -5901,136 +5905,136 @@
         <v>0</v>
       </c>
       <c r="AG13" t="n">
-        <v>1</v>
+        <v>1.33</v>
       </c>
       <c r="AH13" t="n">
-        <v>3.62</v>
+        <v>3.44</v>
       </c>
       <c r="AI13" t="n">
-        <v>99.62</v>
+        <v>96.33</v>
       </c>
       <c r="AJ13" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="AK13" t="n">
-        <v>1.5</v>
+        <v>1.89</v>
       </c>
       <c r="AL13" t="n">
-        <v>6</v>
+        <v>5.56</v>
       </c>
       <c r="AM13" t="n">
-        <v>0.38</v>
+        <v>0.33</v>
       </c>
       <c r="AN13" t="n">
-        <v>52.75</v>
+        <v>52</v>
       </c>
       <c r="AO13" t="n">
-        <v>0.5</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AP13" t="n">
-        <v>2.38</v>
+        <v>2.11</v>
       </c>
       <c r="AQ13" t="n">
-        <v>12</v>
+        <v>12.67</v>
       </c>
       <c r="AR13" t="n">
-        <v>11.38</v>
+        <v>11.22</v>
       </c>
       <c r="AS13" t="n">
-        <v>8.5</v>
+        <v>8.67</v>
       </c>
       <c r="AT13" t="n">
-        <v>1.12</v>
+        <v>1.22</v>
       </c>
       <c r="AU13" t="n">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="AV13" t="n">
-        <v>0.38</v>
+        <v>0.44</v>
       </c>
       <c r="AW13" t="n">
-        <v>0.38</v>
+        <v>0.44</v>
       </c>
       <c r="AX13" t="n">
         <v>0</v>
       </c>
       <c r="AY13" t="n">
-        <v>52.25</v>
+        <v>51.56</v>
       </c>
       <c r="AZ13" t="n">
         <v>0</v>
       </c>
       <c r="BA13" t="n">
-        <v>13.5</v>
+        <v>12.89</v>
       </c>
       <c r="BB13" t="n">
-        <v>9.119999999999999</v>
+        <v>8.779999999999999</v>
       </c>
       <c r="BC13" t="n">
-        <v>4.38</v>
+        <v>4.11</v>
       </c>
       <c r="BD13" t="n">
-        <v>22.88</v>
+        <v>23.22</v>
       </c>
       <c r="BE13" t="n">
-        <v>1.54</v>
+        <v>1.48</v>
       </c>
       <c r="BF13" t="n">
-        <v>1.5</v>
+        <v>1.89</v>
       </c>
       <c r="BG13" t="n">
-        <v>2.71</v>
+        <v>2.72</v>
       </c>
       <c r="BH13" t="n">
-        <v>10.24</v>
+        <v>10.11</v>
       </c>
       <c r="BI13" t="n">
-        <v>2.71</v>
+        <v>2.72</v>
       </c>
       <c r="BJ13" t="n">
-        <v>0.76</v>
+        <v>0.72</v>
       </c>
       <c r="BK13" t="n">
-        <v>0.47</v>
+        <v>0.44</v>
       </c>
       <c r="BL13" t="n">
-        <v>0.65</v>
+        <v>0.72</v>
       </c>
       <c r="BM13" t="n">
-        <v>0.82</v>
+        <v>0.83</v>
       </c>
       <c r="BN13" t="n">
-        <v>1.47</v>
+        <v>1.56</v>
       </c>
       <c r="BO13" t="n">
-        <v>1.24</v>
+        <v>1.17</v>
       </c>
       <c r="BP13" t="n">
-        <v>4.24</v>
+        <v>4.22</v>
       </c>
       <c r="BQ13" t="n">
-        <v>6</v>
+        <v>5.89</v>
       </c>
       <c r="BR13" t="n">
         <v>100</v>
       </c>
       <c r="BS13" t="n">
-        <v>88.23999999999999</v>
+        <v>88.89</v>
       </c>
       <c r="BT13" t="n">
-        <v>52.94</v>
+        <v>55.56</v>
       </c>
       <c r="BU13" t="n">
-        <v>23.53</v>
+        <v>22.22</v>
       </c>
       <c r="BV13" t="n">
-        <v>5.88</v>
+        <v>5.56</v>
       </c>
       <c r="BW13" t="n">
         <v>0</v>
       </c>
       <c r="BX13" t="n">
-        <v>58.82</v>
+        <v>61.11</v>
       </c>
       <c r="BY13" t="n">
         <v>2.38</v>
@@ -6042,22 +6046,22 @@
         <v>3.72</v>
       </c>
       <c r="CB13" t="n">
-        <v>3.83</v>
+        <v>3.82</v>
       </c>
       <c r="CC13" t="n">
-        <v>4.19</v>
+        <v>4.17</v>
       </c>
       <c r="CD13" t="n">
-        <v>4.45</v>
+        <v>4.42</v>
       </c>
       <c r="CE13" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="CF13" t="n">
-        <v>2.43</v>
+        <v>2.44</v>
       </c>
       <c r="CG13" t="n">
-        <v>3.21</v>
+        <v>3.2</v>
       </c>
       <c r="CH13" t="n">
         <v>1.51</v>
@@ -6072,7 +6076,7 @@
         <v>1.45</v>
       </c>
       <c r="CL13" t="n">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="CM13" t="n">
         <v>2.54</v>
@@ -6096,13 +6100,13 @@
         <v>2.61</v>
       </c>
       <c r="CT13" t="n">
-        <v>3.27</v>
+        <v>3.28</v>
       </c>
       <c r="CU13" t="n">
         <v>1.52</v>
       </c>
       <c r="CV13" t="n">
-        <v>2.33</v>
+        <v>2.32</v>
       </c>
       <c r="CW13" t="n">
         <v>1.65</v>
@@ -6111,13 +6115,13 @@
         <v>1.53</v>
       </c>
       <c r="CY13" t="n">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="CZ13" t="n">
-        <v>2.46</v>
+        <v>2.47</v>
       </c>
       <c r="DA13" t="n">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="DB13" t="n">
         <v>1.23</v>
@@ -6132,76 +6136,76 @@
         <v>0.06</v>
       </c>
       <c r="DF13" t="n">
-        <v>1.23</v>
+        <v>1.38</v>
       </c>
       <c r="DG13" t="n">
-        <v>3.76</v>
+        <v>3.66</v>
       </c>
       <c r="DH13" t="n">
-        <v>103.41</v>
+        <v>101.56</v>
       </c>
       <c r="DI13" t="n">
         <v>0.06</v>
       </c>
       <c r="DJ13" t="n">
-        <v>1.71</v>
+        <v>1.89</v>
       </c>
       <c r="DK13" t="n">
-        <v>5.83</v>
+        <v>5.61</v>
       </c>
       <c r="DL13" t="n">
-        <v>0.35</v>
+        <v>0.33</v>
       </c>
       <c r="DM13" t="n">
-        <v>54.77</v>
+        <v>54.28</v>
       </c>
       <c r="DN13" t="n">
-        <v>0.41</v>
+        <v>0.45</v>
       </c>
       <c r="DO13" t="n">
-        <v>2.06</v>
+        <v>1.94</v>
       </c>
       <c r="DP13" t="n">
-        <v>11.59</v>
+        <v>11.94</v>
       </c>
       <c r="DQ13" t="n">
-        <v>11.18</v>
+        <v>11.11</v>
       </c>
       <c r="DR13" t="n">
-        <v>7.06</v>
+        <v>7.22</v>
       </c>
       <c r="DS13" t="n">
-        <v>0.3</v>
+        <v>0.33</v>
       </c>
       <c r="DT13" t="n">
-        <v>0.3</v>
+        <v>0.33</v>
       </c>
       <c r="DU13" t="n">
         <v>0</v>
       </c>
       <c r="DV13" t="n">
-        <v>53.53</v>
+        <v>53.12</v>
       </c>
       <c r="DW13" t="n">
         <v>0.06</v>
       </c>
       <c r="DX13" t="n">
-        <v>14.65</v>
+        <v>14.28</v>
       </c>
       <c r="DY13" t="n">
-        <v>10.12</v>
+        <v>9.890000000000001</v>
       </c>
       <c r="DZ13" t="n">
-        <v>4.53</v>
+        <v>4.39</v>
       </c>
       <c r="EA13" t="n">
-        <v>23.12</v>
+        <v>23.27</v>
       </c>
       <c r="EB13" t="n">
-        <v>1.64</v>
+        <v>1.6</v>
       </c>
       <c r="EC13" t="n">
-        <v>1.59</v>
+        <v>1.78</v>
       </c>
     </row>
     <row r="14">
@@ -6211,94 +6215,94 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C14" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D14" t="n">
         <v>9</v>
       </c>
       <c r="E14" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="F14" t="n">
-        <v>1.75</v>
+        <v>1.67</v>
       </c>
       <c r="G14" t="n">
-        <v>2</v>
+        <v>2.11</v>
       </c>
       <c r="H14" t="n">
-        <v>88.88</v>
+        <v>87.78</v>
       </c>
       <c r="I14" t="n">
         <v>0</v>
       </c>
       <c r="J14" t="n">
-        <v>2.25</v>
+        <v>2.11</v>
       </c>
       <c r="K14" t="n">
-        <v>4.88</v>
+        <v>4.78</v>
       </c>
       <c r="L14" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="M14" t="n">
-        <v>50</v>
+        <v>48.78</v>
       </c>
       <c r="N14" t="n">
-        <v>0.38</v>
+        <v>0.33</v>
       </c>
       <c r="O14" t="n">
-        <v>2.88</v>
+        <v>2.67</v>
       </c>
       <c r="P14" t="n">
-        <v>11.75</v>
+        <v>11.33</v>
       </c>
       <c r="Q14" t="n">
-        <v>14</v>
+        <v>13.56</v>
       </c>
       <c r="R14" t="n">
-        <v>7.12</v>
+        <v>7.56</v>
       </c>
       <c r="S14" t="n">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="T14" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="U14" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="V14" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="W14" t="n">
         <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>47.62</v>
+        <v>47.22</v>
       </c>
       <c r="Y14" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="Z14" t="n">
-        <v>10.88</v>
+        <v>10.78</v>
       </c>
       <c r="AA14" t="n">
-        <v>6.62</v>
+        <v>6.44</v>
       </c>
       <c r="AB14" t="n">
-        <v>4.25</v>
+        <v>4.33</v>
       </c>
       <c r="AC14" t="n">
-        <v>18</v>
+        <v>18.11</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.88</v>
+        <v>1.78</v>
       </c>
       <c r="AF14" t="n">
         <v>0.11</v>
@@ -6382,70 +6386,70 @@
         <v>2.11</v>
       </c>
       <c r="BG14" t="n">
-        <v>2.35</v>
+        <v>2.33</v>
       </c>
       <c r="BH14" t="n">
-        <v>9.529999999999999</v>
+        <v>9.5</v>
       </c>
       <c r="BI14" t="n">
-        <v>2.35</v>
+        <v>2.33</v>
       </c>
       <c r="BJ14" t="n">
-        <v>0.65</v>
+        <v>0.61</v>
       </c>
       <c r="BK14" t="n">
-        <v>0.59</v>
+        <v>0.61</v>
       </c>
       <c r="BL14" t="n">
-        <v>0.76</v>
+        <v>0.78</v>
       </c>
       <c r="BM14" t="n">
-        <v>0.35</v>
+        <v>0.33</v>
       </c>
       <c r="BN14" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="BO14" t="n">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="BP14" t="n">
-        <v>5.06</v>
+        <v>5</v>
       </c>
       <c r="BQ14" t="n">
-        <v>4.47</v>
+        <v>4.5</v>
       </c>
       <c r="BR14" t="n">
-        <v>94.12</v>
+        <v>94.44</v>
       </c>
       <c r="BS14" t="n">
-        <v>64.70999999999999</v>
+        <v>66.67</v>
       </c>
       <c r="BT14" t="n">
-        <v>41.18</v>
+        <v>38.89</v>
       </c>
       <c r="BU14" t="n">
-        <v>29.41</v>
+        <v>27.78</v>
       </c>
       <c r="BV14" t="n">
-        <v>5.88</v>
+        <v>5.56</v>
       </c>
       <c r="BW14" t="n">
         <v>0</v>
       </c>
       <c r="BX14" t="n">
-        <v>52.94</v>
+        <v>55.56</v>
       </c>
       <c r="BY14" t="n">
-        <v>2.03</v>
+        <v>2.27</v>
       </c>
       <c r="BZ14" t="n">
-        <v>2.17</v>
+        <v>2.41</v>
       </c>
       <c r="CA14" t="n">
-        <v>3.56</v>
+        <v>3.55</v>
       </c>
       <c r="CB14" t="n">
-        <v>3.55</v>
+        <v>3.54</v>
       </c>
       <c r="CC14" t="n">
         <v>3.85</v>
@@ -6454,124 +6458,124 @@
         <v>3.92</v>
       </c>
       <c r="CE14" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="CF14" t="n">
-        <v>2.63</v>
+        <v>2.66</v>
       </c>
       <c r="CG14" t="n">
-        <v>3.08</v>
+        <v>3.05</v>
       </c>
       <c r="CH14" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="CI14" t="n">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="CJ14" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="CK14" t="n">
         <v>1.47</v>
       </c>
       <c r="CL14" t="n">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="CM14" t="n">
-        <v>2.57</v>
+        <v>2.56</v>
       </c>
       <c r="CN14" t="n">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="CO14" t="n">
         <v>1.26</v>
       </c>
       <c r="CP14" t="n">
-        <v>1.82</v>
+        <v>1.84</v>
       </c>
       <c r="CQ14" t="n">
-        <v>3.06</v>
+        <v>3.1</v>
       </c>
       <c r="CR14" t="n">
         <v>1.38</v>
       </c>
       <c r="CS14" t="n">
-        <v>2.8</v>
+        <v>2.83</v>
       </c>
       <c r="CT14" t="n">
-        <v>3.12</v>
+        <v>3.09</v>
       </c>
       <c r="CU14" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="CV14" t="n">
-        <v>2.16</v>
+        <v>2.15</v>
       </c>
       <c r="CW14" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="CX14" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="CY14" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="CZ14" t="n">
-        <v>2.46</v>
+        <v>2.45</v>
       </c>
       <c r="DA14" t="n">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="DB14" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="DC14" t="n">
-        <v>1.95</v>
+        <v>1.97</v>
       </c>
       <c r="DD14" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="DE14" t="n">
         <v>0.11</v>
       </c>
       <c r="DF14" t="n">
-        <v>1.77</v>
+        <v>1.72</v>
       </c>
       <c r="DG14" t="n">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="DH14" t="n">
-        <v>90.59</v>
+        <v>89.94</v>
       </c>
       <c r="DI14" t="n">
         <v>0</v>
       </c>
       <c r="DJ14" t="n">
-        <v>2.18</v>
+        <v>2.11</v>
       </c>
       <c r="DK14" t="n">
-        <v>4.65</v>
+        <v>4.61</v>
       </c>
       <c r="DL14" t="n">
-        <v>0.35</v>
+        <v>0.34</v>
       </c>
       <c r="DM14" t="n">
-        <v>48.82</v>
+        <v>48.28</v>
       </c>
       <c r="DN14" t="n">
-        <v>0.35</v>
+        <v>0.33</v>
       </c>
       <c r="DO14" t="n">
-        <v>2.65</v>
+        <v>2.56</v>
       </c>
       <c r="DP14" t="n">
-        <v>11.24</v>
+        <v>11.06</v>
       </c>
       <c r="DQ14" t="n">
-        <v>11.88</v>
+        <v>11.78</v>
       </c>
       <c r="DR14" t="n">
-        <v>6.82</v>
+        <v>7.06</v>
       </c>
       <c r="DS14" t="n">
         <v>0.06</v>
@@ -6583,28 +6587,28 @@
         <v>0</v>
       </c>
       <c r="DV14" t="n">
-        <v>47.65</v>
+        <v>47.44</v>
       </c>
       <c r="DW14" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DX14" t="n">
-        <v>10.77</v>
+        <v>10.73</v>
       </c>
       <c r="DY14" t="n">
-        <v>6.82</v>
+        <v>6.72</v>
       </c>
       <c r="DZ14" t="n">
-        <v>3.94</v>
+        <v>4</v>
       </c>
       <c r="EA14" t="n">
-        <v>19.76</v>
+        <v>19.72</v>
       </c>
       <c r="EB14" t="n">
         <v>1.31</v>
       </c>
       <c r="EC14" t="n">
-        <v>2</v>
+        <v>1.94</v>
       </c>
     </row>
     <row r="15">
@@ -6614,94 +6618,94 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C15" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D15" t="n">
         <v>9</v>
       </c>
       <c r="E15" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="F15" t="n">
-        <v>1.75</v>
+        <v>1.78</v>
       </c>
       <c r="G15" t="n">
-        <v>2.12</v>
+        <v>2.11</v>
       </c>
       <c r="H15" t="n">
-        <v>85.5</v>
+        <v>84.22</v>
       </c>
       <c r="I15" t="n">
         <v>0</v>
       </c>
       <c r="J15" t="n">
-        <v>3.38</v>
+        <v>3.22</v>
       </c>
       <c r="K15" t="n">
-        <v>5.38</v>
+        <v>5.33</v>
       </c>
       <c r="L15" t="n">
-        <v>0.5</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="M15" t="n">
-        <v>56.25</v>
+        <v>53.67</v>
       </c>
       <c r="N15" t="n">
-        <v>1.25</v>
+        <v>1.11</v>
       </c>
       <c r="O15" t="n">
-        <v>3.25</v>
+        <v>3.22</v>
       </c>
       <c r="P15" t="n">
-        <v>11.38</v>
+        <v>11.56</v>
       </c>
       <c r="Q15" t="n">
-        <v>12.38</v>
+        <v>12.56</v>
       </c>
       <c r="R15" t="n">
-        <v>8.380000000000001</v>
+        <v>8.44</v>
       </c>
       <c r="S15" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="T15" t="n">
-        <v>1.12</v>
+        <v>1</v>
       </c>
       <c r="U15" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="V15" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="W15" t="n">
         <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>45.12</v>
+        <v>45.44</v>
       </c>
       <c r="Y15" t="n">
-        <v>0.38</v>
+        <v>0.33</v>
       </c>
       <c r="Z15" t="n">
-        <v>12.5</v>
+        <v>12.11</v>
       </c>
       <c r="AA15" t="n">
-        <v>7.62</v>
+        <v>7.44</v>
       </c>
       <c r="AB15" t="n">
-        <v>4.88</v>
+        <v>4.67</v>
       </c>
       <c r="AC15" t="n">
-        <v>18.38</v>
+        <v>19.56</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.54</v>
+        <v>1.48</v>
       </c>
       <c r="AE15" t="n">
-        <v>2.62</v>
+        <v>2.56</v>
       </c>
       <c r="AF15" t="n">
         <v>0.11</v>
@@ -6785,49 +6789,49 @@
         <v>2</v>
       </c>
       <c r="BG15" t="n">
-        <v>2.12</v>
+        <v>2.06</v>
       </c>
       <c r="BH15" t="n">
-        <v>9.710000000000001</v>
+        <v>9.67</v>
       </c>
       <c r="BI15" t="n">
-        <v>2.12</v>
+        <v>2.06</v>
       </c>
       <c r="BJ15" t="n">
-        <v>0.47</v>
+        <v>0.44</v>
       </c>
       <c r="BK15" t="n">
-        <v>0.65</v>
+        <v>0.61</v>
       </c>
       <c r="BL15" t="n">
-        <v>0.71</v>
+        <v>0.67</v>
       </c>
       <c r="BM15" t="n">
-        <v>0.29</v>
+        <v>0.33</v>
       </c>
       <c r="BN15" t="n">
         <v>1</v>
       </c>
       <c r="BO15" t="n">
-        <v>1.12</v>
+        <v>1.06</v>
       </c>
       <c r="BP15" t="n">
-        <v>4.53</v>
+        <v>4.56</v>
       </c>
       <c r="BQ15" t="n">
-        <v>5.18</v>
+        <v>5.11</v>
       </c>
       <c r="BR15" t="n">
-        <v>94.12</v>
+        <v>94.44</v>
       </c>
       <c r="BS15" t="n">
-        <v>64.70999999999999</v>
+        <v>61.11</v>
       </c>
       <c r="BT15" t="n">
-        <v>41.18</v>
+        <v>38.89</v>
       </c>
       <c r="BU15" t="n">
-        <v>11.76</v>
+        <v>11.11</v>
       </c>
       <c r="BV15" t="n">
         <v>0</v>
@@ -6836,19 +6840,19 @@
         <v>0</v>
       </c>
       <c r="BX15" t="n">
-        <v>35.29</v>
+        <v>33.33</v>
       </c>
       <c r="BY15" t="n">
-        <v>2.9</v>
+        <v>2.84</v>
       </c>
       <c r="BZ15" t="n">
-        <v>3.11</v>
+        <v>3.03</v>
       </c>
       <c r="CA15" t="n">
-        <v>3.51</v>
+        <v>3.49</v>
       </c>
       <c r="CB15" t="n">
-        <v>3.57</v>
+        <v>3.54</v>
       </c>
       <c r="CC15" t="n">
         <v>4.11</v>
@@ -6857,19 +6861,19 @@
         <v>4.66</v>
       </c>
       <c r="CE15" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="CF15" t="n">
-        <v>2.77</v>
+        <v>2.79</v>
       </c>
       <c r="CG15" t="n">
-        <v>2.94</v>
+        <v>2.92</v>
       </c>
       <c r="CH15" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="CI15" t="n">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="CJ15" t="n">
         <v>1.81</v>
@@ -6878,136 +6882,136 @@
         <v>1.48</v>
       </c>
       <c r="CL15" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="CM15" t="n">
-        <v>2.58</v>
+        <v>2.57</v>
       </c>
       <c r="CN15" t="n">
         <v>1.95</v>
       </c>
       <c r="CO15" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="CP15" t="n">
-        <v>1.91</v>
+        <v>1.93</v>
       </c>
       <c r="CQ15" t="n">
-        <v>3.37</v>
+        <v>3.41</v>
       </c>
       <c r="CR15" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="CS15" t="n">
-        <v>2.87</v>
+        <v>2.9</v>
       </c>
       <c r="CT15" t="n">
-        <v>3.07</v>
+        <v>3.05</v>
       </c>
       <c r="CU15" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="CV15" t="n">
-        <v>2.1</v>
+        <v>2.09</v>
       </c>
       <c r="CW15" t="n">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="CX15" t="n">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="CY15" t="n">
         <v>1.89</v>
       </c>
       <c r="CZ15" t="n">
-        <v>2.41</v>
+        <v>2.42</v>
       </c>
       <c r="DA15" t="n">
         <v>1.92</v>
       </c>
       <c r="DB15" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="DC15" t="n">
-        <v>1.99</v>
+        <v>2.01</v>
       </c>
       <c r="DD15" t="n">
-        <v>3.4</v>
+        <v>3.44</v>
       </c>
       <c r="DE15" t="n">
-        <v>0.18</v>
+        <v>0.16</v>
       </c>
       <c r="DF15" t="n">
-        <v>1.59</v>
+        <v>1.61</v>
       </c>
       <c r="DG15" t="n">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="DH15" t="n">
-        <v>85.34999999999999</v>
+        <v>84.72</v>
       </c>
       <c r="DI15" t="n">
         <v>0</v>
       </c>
       <c r="DJ15" t="n">
-        <v>2.77</v>
+        <v>2.72</v>
       </c>
       <c r="DK15" t="n">
-        <v>4</v>
+        <v>4.06</v>
       </c>
       <c r="DL15" t="n">
-        <v>0.41</v>
+        <v>0.45</v>
       </c>
       <c r="DM15" t="n">
-        <v>43.47</v>
+        <v>42.89</v>
       </c>
       <c r="DN15" t="n">
-        <v>1</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="DO15" t="n">
-        <v>2.29</v>
+        <v>2.33</v>
       </c>
       <c r="DP15" t="n">
-        <v>11.35</v>
+        <v>11.44</v>
       </c>
       <c r="DQ15" t="n">
-        <v>11.77</v>
+        <v>11.89</v>
       </c>
       <c r="DR15" t="n">
-        <v>9.119999999999999</v>
+        <v>9.109999999999999</v>
       </c>
       <c r="DS15" t="n">
-        <v>0.18</v>
+        <v>0.16</v>
       </c>
       <c r="DT15" t="n">
-        <v>0.18</v>
+        <v>0.16</v>
       </c>
       <c r="DU15" t="n">
         <v>0</v>
       </c>
       <c r="DV15" t="n">
-        <v>44.53</v>
+        <v>44.72</v>
       </c>
       <c r="DW15" t="n">
-        <v>0.3</v>
+        <v>0.28</v>
       </c>
       <c r="DX15" t="n">
-        <v>9.880000000000001</v>
+        <v>9.83</v>
       </c>
       <c r="DY15" t="n">
-        <v>6.47</v>
+        <v>6.44</v>
       </c>
       <c r="DZ15" t="n">
-        <v>3.41</v>
+        <v>3.39</v>
       </c>
       <c r="EA15" t="n">
-        <v>18.18</v>
+        <v>18.78</v>
       </c>
       <c r="EB15" t="n">
-        <v>1.19</v>
+        <v>1.17</v>
       </c>
       <c r="EC15" t="n">
-        <v>2.29</v>
+        <v>2.28</v>
       </c>
     </row>
     <row r="16">
@@ -7017,13 +7021,13 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C16" t="n">
         <v>8</v>
       </c>
       <c r="D16" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E16" t="n">
         <v>0.38</v>
@@ -7107,52 +7111,52 @@
         <v>1.25</v>
       </c>
       <c r="AF16" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="AH16" t="n">
-        <v>2.78</v>
+        <v>2.7</v>
       </c>
       <c r="AI16" t="n">
-        <v>112.67</v>
+        <v>112.3</v>
       </c>
       <c r="AJ16" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="AK16" t="n">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="AL16" t="n">
-        <v>5.33</v>
+        <v>5.3</v>
       </c>
       <c r="AM16" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.6</v>
       </c>
       <c r="AN16" t="n">
-        <v>49.67</v>
+        <v>51.5</v>
       </c>
       <c r="AO16" t="n">
-        <v>1.22</v>
+        <v>1.1</v>
       </c>
       <c r="AP16" t="n">
-        <v>2.56</v>
+        <v>2.6</v>
       </c>
       <c r="AQ16" t="n">
-        <v>13.56</v>
+        <v>13.2</v>
       </c>
       <c r="AR16" t="n">
-        <v>8.67</v>
+        <v>8.6</v>
       </c>
       <c r="AS16" t="n">
-        <v>6.11</v>
+        <v>6</v>
       </c>
       <c r="AT16" t="n">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="AU16" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AV16" t="n">
         <v>0</v>
@@ -7164,82 +7168,82 @@
         <v>0</v>
       </c>
       <c r="AY16" t="n">
-        <v>53.67</v>
+        <v>53.9</v>
       </c>
       <c r="AZ16" t="n">
         <v>0</v>
       </c>
       <c r="BA16" t="n">
-        <v>13.78</v>
+        <v>13.7</v>
       </c>
       <c r="BB16" t="n">
-        <v>8.67</v>
+        <v>9</v>
       </c>
       <c r="BC16" t="n">
-        <v>5.11</v>
+        <v>4.7</v>
       </c>
       <c r="BD16" t="n">
-        <v>19.67</v>
+        <v>20.2</v>
       </c>
       <c r="BE16" t="n">
-        <v>1.59</v>
+        <v>1.57</v>
       </c>
       <c r="BF16" t="n">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="BG16" t="n">
-        <v>2.47</v>
+        <v>2.44</v>
       </c>
       <c r="BH16" t="n">
-        <v>9.65</v>
+        <v>9.609999999999999</v>
       </c>
       <c r="BI16" t="n">
-        <v>2.47</v>
+        <v>2.44</v>
       </c>
       <c r="BJ16" t="n">
-        <v>0.47</v>
+        <v>0.44</v>
       </c>
       <c r="BK16" t="n">
-        <v>0.35</v>
+        <v>0.39</v>
       </c>
       <c r="BL16" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="BM16" t="n">
-        <v>0.47</v>
+        <v>0.44</v>
       </c>
       <c r="BN16" t="n">
-        <v>1.65</v>
+        <v>1.61</v>
       </c>
       <c r="BO16" t="n">
-        <v>0.82</v>
+        <v>0.83</v>
       </c>
       <c r="BP16" t="n">
-        <v>4.88</v>
+        <v>4.83</v>
       </c>
       <c r="BQ16" t="n">
-        <v>4.76</v>
+        <v>4.78</v>
       </c>
       <c r="BR16" t="n">
-        <v>94.12</v>
+        <v>94.44</v>
       </c>
       <c r="BS16" t="n">
-        <v>76.47</v>
+        <v>77.78</v>
       </c>
       <c r="BT16" t="n">
-        <v>35.29</v>
+        <v>33.33</v>
       </c>
       <c r="BU16" t="n">
-        <v>23.53</v>
+        <v>22.22</v>
       </c>
       <c r="BV16" t="n">
-        <v>17.65</v>
+        <v>16.67</v>
       </c>
       <c r="BW16" t="n">
         <v>0</v>
       </c>
       <c r="BX16" t="n">
-        <v>41.18</v>
+        <v>44.44</v>
       </c>
       <c r="BY16" t="n">
         <v>1.35</v>
@@ -7248,25 +7252,25 @@
         <v>1.44</v>
       </c>
       <c r="CA16" t="n">
-        <v>4.26</v>
+        <v>4.22</v>
       </c>
       <c r="CB16" t="n">
-        <v>4.42</v>
+        <v>4.37</v>
       </c>
       <c r="CC16" t="n">
         <v>1.87</v>
       </c>
       <c r="CD16" t="n">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="CE16" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="CF16" t="n">
-        <v>2.46</v>
+        <v>2.49</v>
       </c>
       <c r="CG16" t="n">
-        <v>3.24</v>
+        <v>3.2</v>
       </c>
       <c r="CH16" t="n">
         <v>1.51</v>
@@ -7281,7 +7285,7 @@
         <v>1.47</v>
       </c>
       <c r="CL16" t="n">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="CM16" t="n">
         <v>2.5</v>
@@ -7293,28 +7297,28 @@
         <v>1.22</v>
       </c>
       <c r="CP16" t="n">
-        <v>1.76</v>
+        <v>1.78</v>
       </c>
       <c r="CQ16" t="n">
-        <v>2.72</v>
+        <v>2.77</v>
       </c>
       <c r="CR16" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="CS16" t="n">
-        <v>2.6</v>
+        <v>2.64</v>
       </c>
       <c r="CT16" t="n">
-        <v>3.24</v>
+        <v>3.2</v>
       </c>
       <c r="CU16" t="n">
-        <v>1.53</v>
+        <v>1.51</v>
       </c>
       <c r="CV16" t="n">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="CW16" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="CX16" t="n">
         <v>1.58</v>
@@ -7323,94 +7327,94 @@
         <v>1.87</v>
       </c>
       <c r="CZ16" t="n">
-        <v>2.36</v>
+        <v>2.35</v>
       </c>
       <c r="DA16" t="n">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="DB16" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="DC16" t="n">
-        <v>1.77</v>
+        <v>1.8</v>
       </c>
       <c r="DD16" t="n">
-        <v>2.87</v>
+        <v>2.94</v>
       </c>
       <c r="DE16" t="n">
-        <v>0.24</v>
+        <v>0.22</v>
       </c>
       <c r="DF16" t="n">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="DG16" t="n">
-        <v>3.12</v>
+        <v>3.06</v>
       </c>
       <c r="DH16" t="n">
-        <v>108.53</v>
+        <v>108.56</v>
       </c>
       <c r="DI16" t="n">
         <v>0.06</v>
       </c>
       <c r="DJ16" t="n">
-        <v>2.18</v>
+        <v>2.17</v>
       </c>
       <c r="DK16" t="n">
-        <v>5.82</v>
+        <v>5.78</v>
       </c>
       <c r="DL16" t="n">
-        <v>0.59</v>
+        <v>0.61</v>
       </c>
       <c r="DM16" t="n">
-        <v>54.59</v>
+        <v>55.33</v>
       </c>
       <c r="DN16" t="n">
-        <v>0.7</v>
+        <v>0.66</v>
       </c>
       <c r="DO16" t="n">
-        <v>2.71</v>
+        <v>2.72</v>
       </c>
       <c r="DP16" t="n">
-        <v>12.88</v>
+        <v>12.72</v>
       </c>
       <c r="DQ16" t="n">
-        <v>9.06</v>
+        <v>9</v>
       </c>
       <c r="DR16" t="n">
-        <v>5.88</v>
+        <v>5.83</v>
       </c>
       <c r="DS16" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DT16" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DU16" t="n">
         <v>0</v>
       </c>
       <c r="DV16" t="n">
-        <v>54.24</v>
+        <v>54.34</v>
       </c>
       <c r="DW16" t="n">
         <v>0</v>
       </c>
       <c r="DX16" t="n">
-        <v>15.88</v>
+        <v>15.72</v>
       </c>
       <c r="DY16" t="n">
-        <v>9.880000000000001</v>
+        <v>10</v>
       </c>
       <c r="DZ16" t="n">
-        <v>6</v>
+        <v>5.72</v>
       </c>
       <c r="EA16" t="n">
-        <v>19.77</v>
+        <v>20.06</v>
       </c>
       <c r="EB16" t="n">
-        <v>1.82</v>
+        <v>1.8</v>
       </c>
       <c r="EC16" t="n">
-        <v>2.18</v>
+        <v>2.17</v>
       </c>
     </row>
     <row r="17">
@@ -7420,10 +7424,10 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C17" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D17" t="n">
         <v>9</v>
@@ -7432,82 +7436,82 @@
         <v>0</v>
       </c>
       <c r="F17" t="n">
-        <v>1</v>
+        <v>0.89</v>
       </c>
       <c r="G17" t="n">
-        <v>2.25</v>
+        <v>2.11</v>
       </c>
       <c r="H17" t="n">
-        <v>92.62</v>
+        <v>97.67</v>
       </c>
       <c r="I17" t="n">
         <v>0</v>
       </c>
       <c r="J17" t="n">
-        <v>1.62</v>
+        <v>1.56</v>
       </c>
       <c r="K17" t="n">
-        <v>3.88</v>
+        <v>3.78</v>
       </c>
       <c r="L17" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="M17" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="N17" t="n">
-        <v>0.5</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="O17" t="n">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="P17" t="n">
-        <v>10.25</v>
+        <v>10.44</v>
       </c>
       <c r="Q17" t="n">
-        <v>13.12</v>
+        <v>13</v>
       </c>
       <c r="R17" t="n">
-        <v>11.5</v>
+        <v>10.67</v>
       </c>
       <c r="S17" t="n">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="T17" t="n">
-        <v>1.38</v>
+        <v>1.44</v>
       </c>
       <c r="U17" t="n">
-        <v>0.38</v>
+        <v>0.44</v>
       </c>
       <c r="V17" t="n">
-        <v>0.38</v>
+        <v>0.44</v>
       </c>
       <c r="W17" t="n">
         <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="Y17" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="Z17" t="n">
-        <v>11.62</v>
+        <v>11.33</v>
       </c>
       <c r="AA17" t="n">
-        <v>7.38</v>
+        <v>7.11</v>
       </c>
       <c r="AB17" t="n">
-        <v>4.25</v>
+        <v>4.22</v>
       </c>
       <c r="AC17" t="n">
-        <v>21.62</v>
+        <v>22.11</v>
       </c>
       <c r="AD17" t="n">
         <v>1.31</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="AF17" t="n">
         <v>0.11</v>
@@ -7591,70 +7595,70 @@
         <v>1.78</v>
       </c>
       <c r="BG17" t="n">
-        <v>2.71</v>
+        <v>2.78</v>
       </c>
       <c r="BH17" t="n">
-        <v>10.47</v>
+        <v>10.17</v>
       </c>
       <c r="BI17" t="n">
-        <v>2.71</v>
+        <v>2.78</v>
       </c>
       <c r="BJ17" t="n">
-        <v>0.76</v>
+        <v>0.78</v>
       </c>
       <c r="BK17" t="n">
-        <v>0.53</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="BL17" t="n">
-        <v>0.65</v>
+        <v>0.67</v>
       </c>
       <c r="BM17" t="n">
-        <v>0.76</v>
+        <v>0.78</v>
       </c>
       <c r="BN17" t="n">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="BO17" t="n">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="BP17" t="n">
-        <v>3.76</v>
+        <v>3.67</v>
       </c>
       <c r="BQ17" t="n">
-        <v>5.94</v>
+        <v>5.78</v>
       </c>
       <c r="BR17" t="n">
-        <v>88.23999999999999</v>
+        <v>88.89</v>
       </c>
       <c r="BS17" t="n">
-        <v>82.34999999999999</v>
+        <v>83.33</v>
       </c>
       <c r="BT17" t="n">
-        <v>41.18</v>
+        <v>44.44</v>
       </c>
       <c r="BU17" t="n">
-        <v>35.29</v>
+        <v>38.89</v>
       </c>
       <c r="BV17" t="n">
-        <v>23.53</v>
+        <v>22.22</v>
       </c>
       <c r="BW17" t="n">
         <v>0</v>
       </c>
       <c r="BX17" t="n">
-        <v>64.70999999999999</v>
+        <v>66.67</v>
       </c>
       <c r="BY17" t="n">
-        <v>3.12</v>
+        <v>3.02</v>
       </c>
       <c r="BZ17" t="n">
-        <v>3.41</v>
+        <v>3.28</v>
       </c>
       <c r="CA17" t="n">
-        <v>3.69</v>
+        <v>3.67</v>
       </c>
       <c r="CB17" t="n">
-        <v>3.72</v>
+        <v>3.7</v>
       </c>
       <c r="CC17" t="n">
         <v>3.74</v>
@@ -7666,40 +7670,40 @@
         <v>1.3</v>
       </c>
       <c r="CF17" t="n">
-        <v>2.44</v>
+        <v>2.47</v>
       </c>
       <c r="CG17" t="n">
-        <v>3.33</v>
+        <v>3.31</v>
       </c>
       <c r="CH17" t="n">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="CI17" t="n">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="CJ17" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="CK17" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="CL17" t="n">
         <v>1.78</v>
       </c>
       <c r="CM17" t="n">
-        <v>2.7</v>
+        <v>2.69</v>
       </c>
       <c r="CN17" t="n">
         <v>2.07</v>
       </c>
       <c r="CO17" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="CP17" t="n">
-        <v>1.69</v>
+        <v>1.71</v>
       </c>
       <c r="CQ17" t="n">
-        <v>2.71</v>
+        <v>2.75</v>
       </c>
       <c r="CR17" t="n">
         <v>1.35</v>
@@ -7714,106 +7718,106 @@
         <v>1.53</v>
       </c>
       <c r="CV17" t="n">
-        <v>2.37</v>
+        <v>2.35</v>
       </c>
       <c r="CW17" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="CX17" t="n">
         <v>1.52</v>
       </c>
       <c r="CY17" t="n">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="CZ17" t="n">
         <v>2.48</v>
       </c>
       <c r="DA17" t="n">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="DB17" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="DC17" t="n">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="DD17" t="n">
-        <v>2.8</v>
+        <v>2.86</v>
       </c>
       <c r="DE17" t="n">
         <v>0.06</v>
       </c>
       <c r="DF17" t="n">
-        <v>1.23</v>
+        <v>1.16</v>
       </c>
       <c r="DG17" t="n">
-        <v>2.29</v>
+        <v>2.22</v>
       </c>
       <c r="DH17" t="n">
-        <v>91.23</v>
+        <v>93.84</v>
       </c>
       <c r="DI17" t="n">
         <v>0.06</v>
       </c>
       <c r="DJ17" t="n">
-        <v>1.82</v>
+        <v>1.78</v>
       </c>
       <c r="DK17" t="n">
-        <v>4.18</v>
+        <v>4.11</v>
       </c>
       <c r="DL17" t="n">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
       <c r="DM17" t="n">
-        <v>43.88</v>
+        <v>44.56</v>
       </c>
       <c r="DN17" t="n">
-        <v>0.47</v>
+        <v>0.5</v>
       </c>
       <c r="DO17" t="n">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="DP17" t="n">
-        <v>11.82</v>
+        <v>11.83</v>
       </c>
       <c r="DQ17" t="n">
-        <v>11.53</v>
+        <v>11.56</v>
       </c>
       <c r="DR17" t="n">
-        <v>10.71</v>
+        <v>10.34</v>
       </c>
       <c r="DS17" t="n">
-        <v>0.24</v>
+        <v>0.28</v>
       </c>
       <c r="DT17" t="n">
-        <v>0.24</v>
+        <v>0.28</v>
       </c>
       <c r="DU17" t="n">
         <v>0</v>
       </c>
       <c r="DV17" t="n">
-        <v>45.59</v>
+        <v>46.94</v>
       </c>
       <c r="DW17" t="n">
         <v>0.11</v>
       </c>
       <c r="DX17" t="n">
-        <v>11.12</v>
+        <v>11</v>
       </c>
       <c r="DY17" t="n">
-        <v>7.18</v>
+        <v>7.06</v>
       </c>
       <c r="DZ17" t="n">
         <v>3.94</v>
       </c>
       <c r="EA17" t="n">
-        <v>20.41</v>
+        <v>20.72</v>
       </c>
       <c r="EB17" t="n">
         <v>1.3</v>
       </c>
       <c r="EC17" t="n">
-        <v>1.59</v>
+        <v>1.56</v>
       </c>
     </row>
   </sheetData>

--- a/data/teams/leagues/Averages_Belgium_Pro_League_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Belgium_Pro_League_2025-2026.xlsx
@@ -1935,10 +1935,10 @@
         <v>0</v>
       </c>
       <c r="BA3" t="n">
-        <v>16.1</v>
+        <v>16.2</v>
       </c>
       <c r="BB3" t="n">
-        <v>10.6</v>
+        <v>10.7</v>
       </c>
       <c r="BC3" t="n">
         <v>5.5</v>
@@ -2160,10 +2160,10 @@
         <v>0.05</v>
       </c>
       <c r="DX3" t="n">
-        <v>16.83</v>
+        <v>16.89</v>
       </c>
       <c r="DY3" t="n">
-        <v>11.5</v>
+        <v>11.55</v>
       </c>
       <c r="DZ3" t="n">
         <v>5.33</v>
@@ -2233,7 +2233,7 @@
         <v>11.56</v>
       </c>
       <c r="R4" t="n">
-        <v>10.78</v>
+        <v>10.89</v>
       </c>
       <c r="S4" t="n">
         <v>1.78</v>
@@ -2266,7 +2266,7 @@
         <v>3.11</v>
       </c>
       <c r="AC4" t="n">
-        <v>23.22</v>
+        <v>23.11</v>
       </c>
       <c r="AD4" t="n">
         <v>1.12</v>
@@ -2545,7 +2545,7 @@
         <v>11.62</v>
       </c>
       <c r="DR4" t="n">
-        <v>10.78</v>
+        <v>10.84</v>
       </c>
       <c r="DS4" t="n">
         <v>0.11</v>
@@ -2572,7 +2572,7 @@
         <v>3.61</v>
       </c>
       <c r="EA4" t="n">
-        <v>20.61</v>
+        <v>20.56</v>
       </c>
       <c r="EB4" t="n">
         <v>1.18</v>
@@ -2660,19 +2660,19 @@
         <v>0.11</v>
       </c>
       <c r="Z5" t="n">
-        <v>15.11</v>
+        <v>15.22</v>
       </c>
       <c r="AA5" t="n">
         <v>11.11</v>
       </c>
       <c r="AB5" t="n">
-        <v>4</v>
+        <v>4.11</v>
       </c>
       <c r="AC5" t="n">
         <v>19.78</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="AE5" t="n">
         <v>1.33</v>
@@ -2966,19 +2966,19 @@
         <v>0.16</v>
       </c>
       <c r="DX5" t="n">
-        <v>13.5</v>
+        <v>13.56</v>
       </c>
       <c r="DY5" t="n">
         <v>9</v>
       </c>
       <c r="DZ5" t="n">
-        <v>4.5</v>
+        <v>4.56</v>
       </c>
       <c r="EA5" t="n">
         <v>18.83</v>
       </c>
       <c r="EB5" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="EC5" t="n">
         <v>1.61</v>
@@ -4750,7 +4750,7 @@
         <v>0</v>
       </c>
       <c r="AY10" t="n">
-        <v>31.22</v>
+        <v>31.11</v>
       </c>
       <c r="AZ10" t="n">
         <v>0.11</v>
@@ -4975,7 +4975,7 @@
         <v>0</v>
       </c>
       <c r="DV10" t="n">
-        <v>34</v>
+        <v>33.94</v>
       </c>
       <c r="DW10" t="n">
         <v>0.06</v>
@@ -5072,16 +5072,16 @@
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>50.1</v>
+        <v>50.2</v>
       </c>
       <c r="Y11" t="n">
         <v>0.1</v>
       </c>
       <c r="Z11" t="n">
-        <v>16.9</v>
+        <v>16.8</v>
       </c>
       <c r="AA11" t="n">
-        <v>11.1</v>
+        <v>11</v>
       </c>
       <c r="AB11" t="n">
         <v>5.8</v>
@@ -5090,7 +5090,7 @@
         <v>19.6</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="AE11" t="n">
         <v>2.7</v>
@@ -5378,16 +5378,16 @@
         <v>0</v>
       </c>
       <c r="DV11" t="n">
-        <v>53.06</v>
+        <v>53.11</v>
       </c>
       <c r="DW11" t="n">
         <v>0.17</v>
       </c>
       <c r="DX11" t="n">
-        <v>15.17</v>
+        <v>15.11</v>
       </c>
       <c r="DY11" t="n">
-        <v>10.17</v>
+        <v>10.11</v>
       </c>
       <c r="DZ11" t="n">
         <v>5</v>
@@ -5959,7 +5959,7 @@
         <v>0</v>
       </c>
       <c r="AY13" t="n">
-        <v>51.56</v>
+        <v>51.44</v>
       </c>
       <c r="AZ13" t="n">
         <v>0</v>
@@ -6184,7 +6184,7 @@
         <v>0</v>
       </c>
       <c r="DV13" t="n">
-        <v>53.12</v>
+        <v>53.06</v>
       </c>
       <c r="DW13" t="n">
         <v>0.06</v>
@@ -7490,7 +7490,7 @@
         <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>46</v>
+        <v>46.11</v>
       </c>
       <c r="Y17" t="n">
         <v>0.11</v>
@@ -7796,7 +7796,7 @@
         <v>0</v>
       </c>
       <c r="DV17" t="n">
-        <v>46.94</v>
+        <v>47</v>
       </c>
       <c r="DW17" t="n">
         <v>0.11</v>

--- a/data/teams/leagues/Averages_Belgium_Pro_League_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Belgium_Pro_League_2025-2026.xlsx
@@ -1782,10 +1782,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C3" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D3" t="n">
         <v>10</v>
@@ -1794,49 +1794,49 @@
         <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>1.25</v>
+        <v>1.11</v>
       </c>
       <c r="G3" t="n">
-        <v>4</v>
+        <v>4.22</v>
       </c>
       <c r="H3" t="n">
-        <v>116</v>
+        <v>116.44</v>
       </c>
       <c r="I3" t="n">
         <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="K3" t="n">
-        <v>7</v>
+        <v>7.33</v>
       </c>
       <c r="L3" t="n">
         <v>1</v>
       </c>
       <c r="M3" t="n">
-        <v>67.88</v>
+        <v>68.56</v>
       </c>
       <c r="N3" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="O3" t="n">
-        <v>3</v>
+        <v>3.11</v>
       </c>
       <c r="P3" t="n">
-        <v>9.619999999999999</v>
+        <v>9.56</v>
       </c>
       <c r="Q3" t="n">
-        <v>12.12</v>
+        <v>12.11</v>
       </c>
       <c r="R3" t="n">
-        <v>7.25</v>
+        <v>6.89</v>
       </c>
       <c r="S3" t="n">
         <v>1</v>
       </c>
       <c r="T3" t="n">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="U3" t="n">
         <v>0</v>
@@ -1848,28 +1848,28 @@
         <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>64.88</v>
+        <v>65.78</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="Z3" t="n">
-        <v>17.75</v>
+        <v>18.22</v>
       </c>
       <c r="AA3" t="n">
-        <v>12.62</v>
+        <v>13.33</v>
       </c>
       <c r="AB3" t="n">
-        <v>5.12</v>
+        <v>4.89</v>
       </c>
       <c r="AC3" t="n">
-        <v>22.25</v>
+        <v>23.89</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.97</v>
+        <v>1.99</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.25</v>
+        <v>1.11</v>
       </c>
       <c r="AF3" t="n">
         <v>0.1</v>
@@ -1953,70 +1953,70 @@
         <v>1.4</v>
       </c>
       <c r="BG3" t="n">
-        <v>2.61</v>
+        <v>2.63</v>
       </c>
       <c r="BH3" t="n">
-        <v>11</v>
+        <v>11.05</v>
       </c>
       <c r="BI3" t="n">
-        <v>2.61</v>
+        <v>2.63</v>
       </c>
       <c r="BJ3" t="n">
-        <v>0.61</v>
+        <v>0.63</v>
       </c>
       <c r="BK3" t="n">
-        <v>0.39</v>
+        <v>0.37</v>
       </c>
       <c r="BL3" t="n">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="BM3" t="n">
-        <v>0.83</v>
+        <v>0.84</v>
       </c>
       <c r="BN3" t="n">
-        <v>1.61</v>
+        <v>1.63</v>
       </c>
       <c r="BO3" t="n">
         <v>1</v>
       </c>
       <c r="BP3" t="n">
-        <v>4.94</v>
+        <v>4.89</v>
       </c>
       <c r="BQ3" t="n">
-        <v>6.06</v>
+        <v>6.16</v>
       </c>
       <c r="BR3" t="n">
         <v>100</v>
       </c>
       <c r="BS3" t="n">
-        <v>55.56</v>
+        <v>57.89</v>
       </c>
       <c r="BT3" t="n">
-        <v>38.89</v>
+        <v>42.11</v>
       </c>
       <c r="BU3" t="n">
-        <v>16.67</v>
+        <v>15.79</v>
       </c>
       <c r="BV3" t="n">
-        <v>16.67</v>
+        <v>15.79</v>
       </c>
       <c r="BW3" t="n">
-        <v>11.11</v>
+        <v>10.53</v>
       </c>
       <c r="BX3" t="n">
-        <v>44.44</v>
+        <v>47.37</v>
       </c>
       <c r="BY3" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="BZ3" t="n">
         <v>1.52</v>
-      </c>
-      <c r="BZ3" t="n">
-        <v>1.53</v>
       </c>
       <c r="CA3" t="n">
         <v>4.44</v>
       </c>
       <c r="CB3" t="n">
-        <v>4.7</v>
+        <v>4.72</v>
       </c>
       <c r="CC3" t="n">
         <v>1.7</v>
@@ -2025,19 +2025,19 @@
         <v>1.76</v>
       </c>
       <c r="CE3" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="CF3" t="n">
         <v>2.24</v>
       </c>
       <c r="CG3" t="n">
-        <v>3.54</v>
+        <v>3.56</v>
       </c>
       <c r="CH3" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="CI3" t="n">
-        <v>2.13</v>
+        <v>2.14</v>
       </c>
       <c r="CJ3" t="n">
         <v>1.67</v>
@@ -2046,7 +2046,7 @@
         <v>1.47</v>
       </c>
       <c r="CL3" t="n">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="CM3" t="n">
         <v>2.52</v>
@@ -2058,7 +2058,7 @@
         <v>1.16</v>
       </c>
       <c r="CP3" t="n">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="CQ3" t="n">
         <v>2.4</v>
@@ -2088,7 +2088,7 @@
         <v>1.81</v>
       </c>
       <c r="CZ3" t="n">
-        <v>2.49</v>
+        <v>2.5</v>
       </c>
       <c r="DA3" t="n">
         <v>2.01</v>
@@ -2100,49 +2100,49 @@
         <v>1.58</v>
       </c>
       <c r="DD3" t="n">
-        <v>2.44</v>
+        <v>2.43</v>
       </c>
       <c r="DE3" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="DF3" t="n">
-        <v>1.11</v>
+        <v>1.05</v>
       </c>
       <c r="DG3" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="DH3" t="n">
-        <v>112.44</v>
+        <v>112.84</v>
       </c>
       <c r="DI3" t="n">
-        <v>-0.06</v>
+        <v>-0.05</v>
       </c>
       <c r="DJ3" t="n">
-        <v>1.44</v>
+        <v>1.37</v>
       </c>
       <c r="DK3" t="n">
-        <v>6.61</v>
+        <v>6.79</v>
       </c>
       <c r="DL3" t="n">
-        <v>0.61</v>
+        <v>0.63</v>
       </c>
       <c r="DM3" t="n">
-        <v>62.89</v>
+        <v>63.48</v>
       </c>
       <c r="DN3" t="n">
-        <v>0.28</v>
+        <v>0.26</v>
       </c>
       <c r="DO3" t="n">
-        <v>2.61</v>
+        <v>2.68</v>
       </c>
       <c r="DP3" t="n">
-        <v>9.33</v>
+        <v>9.32</v>
       </c>
       <c r="DQ3" t="n">
-        <v>11.66</v>
+        <v>11.68</v>
       </c>
       <c r="DR3" t="n">
-        <v>7.56</v>
+        <v>7.37</v>
       </c>
       <c r="DS3" t="n">
         <v>0</v>
@@ -2154,28 +2154,28 @@
         <v>0</v>
       </c>
       <c r="DV3" t="n">
-        <v>62.39</v>
+        <v>62.95</v>
       </c>
       <c r="DW3" t="n">
         <v>0.05</v>
       </c>
       <c r="DX3" t="n">
-        <v>16.89</v>
+        <v>17.16</v>
       </c>
       <c r="DY3" t="n">
-        <v>11.55</v>
+        <v>11.95</v>
       </c>
       <c r="DZ3" t="n">
-        <v>5.33</v>
+        <v>5.21</v>
       </c>
       <c r="EA3" t="n">
-        <v>19.72</v>
+        <v>20.63</v>
       </c>
       <c r="EB3" t="n">
-        <v>1.89</v>
+        <v>1.91</v>
       </c>
       <c r="EC3" t="n">
-        <v>1.33</v>
+        <v>1.26</v>
       </c>
     </row>
     <row r="4">
@@ -2185,10 +2185,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D4" t="n">
         <v>9</v>
@@ -2197,82 +2197,82 @@
         <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="G4" t="n">
-        <v>0.89</v>
+        <v>1.2</v>
       </c>
       <c r="H4" t="n">
-        <v>92.89</v>
+        <v>94.5</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.22</v>
+        <v>-0.2</v>
       </c>
       <c r="J4" t="n">
-        <v>1.22</v>
+        <v>1.5</v>
       </c>
       <c r="K4" t="n">
-        <v>2.89</v>
+        <v>3.1</v>
       </c>
       <c r="L4" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="M4" t="n">
-        <v>41.78</v>
+        <v>43.6</v>
       </c>
       <c r="N4" t="n">
-        <v>0.33</v>
+        <v>0.6</v>
       </c>
       <c r="O4" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="P4" t="n">
-        <v>9.33</v>
+        <v>10.1</v>
       </c>
       <c r="Q4" t="n">
-        <v>11.56</v>
+        <v>11.5</v>
       </c>
       <c r="R4" t="n">
-        <v>10.89</v>
+        <v>10.6</v>
       </c>
       <c r="S4" t="n">
-        <v>1.78</v>
+        <v>1.7</v>
       </c>
       <c r="T4" t="n">
-        <v>0.67</v>
+        <v>0.6</v>
       </c>
       <c r="U4" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="V4" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="W4" t="n">
         <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>49.11</v>
+        <v>50.1</v>
       </c>
       <c r="Y4" t="n">
         <v>0</v>
       </c>
       <c r="Z4" t="n">
-        <v>9.44</v>
+        <v>9.5</v>
       </c>
       <c r="AA4" t="n">
-        <v>6.33</v>
+        <v>6.3</v>
       </c>
       <c r="AB4" t="n">
-        <v>3.11</v>
+        <v>3.2</v>
       </c>
       <c r="AC4" t="n">
-        <v>23.11</v>
+        <v>23.7</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.22</v>
+        <v>1.5</v>
       </c>
       <c r="AF4" t="n">
         <v>0.22</v>
@@ -2356,70 +2356,70 @@
         <v>1.78</v>
       </c>
       <c r="BG4" t="n">
-        <v>2.61</v>
+        <v>2.53</v>
       </c>
       <c r="BH4" t="n">
-        <v>8.06</v>
+        <v>8.109999999999999</v>
       </c>
       <c r="BI4" t="n">
-        <v>2.61</v>
+        <v>2.53</v>
       </c>
       <c r="BJ4" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.53</v>
       </c>
       <c r="BK4" t="n">
-        <v>0.28</v>
+        <v>0.32</v>
       </c>
       <c r="BL4" t="n">
-        <v>0.67</v>
+        <v>0.63</v>
       </c>
       <c r="BM4" t="n">
-        <v>1.11</v>
+        <v>1.05</v>
       </c>
       <c r="BN4" t="n">
-        <v>1.78</v>
+        <v>1.68</v>
       </c>
       <c r="BO4" t="n">
-        <v>0.83</v>
+        <v>0.84</v>
       </c>
       <c r="BP4" t="n">
-        <v>3.5</v>
+        <v>3.47</v>
       </c>
       <c r="BQ4" t="n">
-        <v>3.83</v>
+        <v>3.95</v>
       </c>
       <c r="BR4" t="n">
-        <v>88.89</v>
+        <v>89.47</v>
       </c>
       <c r="BS4" t="n">
-        <v>77.78</v>
+        <v>73.68000000000001</v>
       </c>
       <c r="BT4" t="n">
-        <v>55.56</v>
+        <v>52.63</v>
       </c>
       <c r="BU4" t="n">
-        <v>27.78</v>
+        <v>26.32</v>
       </c>
       <c r="BV4" t="n">
-        <v>5.56</v>
+        <v>5.26</v>
       </c>
       <c r="BW4" t="n">
-        <v>5.56</v>
+        <v>5.26</v>
       </c>
       <c r="BX4" t="n">
-        <v>61.11</v>
+        <v>57.89</v>
       </c>
       <c r="BY4" t="n">
-        <v>3.6</v>
+        <v>3.46</v>
       </c>
       <c r="BZ4" t="n">
-        <v>3.68</v>
+        <v>3.54</v>
       </c>
       <c r="CA4" t="n">
-        <v>3.73</v>
+        <v>3.7</v>
       </c>
       <c r="CB4" t="n">
-        <v>3.93</v>
+        <v>3.89</v>
       </c>
       <c r="CC4" t="n">
         <v>4.74</v>
@@ -2431,133 +2431,133 @@
         <v>1.34</v>
       </c>
       <c r="CF4" t="n">
-        <v>2.54</v>
+        <v>2.57</v>
       </c>
       <c r="CG4" t="n">
-        <v>3.13</v>
+        <v>3.1</v>
       </c>
       <c r="CH4" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="CI4" t="n">
-        <v>2.05</v>
+        <v>2.04</v>
       </c>
       <c r="CJ4" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="CK4" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="CL4" t="n">
-        <v>2.03</v>
+        <v>2.04</v>
       </c>
       <c r="CM4" t="n">
-        <v>2.37</v>
+        <v>2.35</v>
       </c>
       <c r="CN4" t="n">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="CO4" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="CP4" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="CQ4" t="n">
-        <v>3.04</v>
+        <v>3.07</v>
       </c>
       <c r="CR4" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="CS4" t="n">
-        <v>2.71</v>
+        <v>2.74</v>
       </c>
       <c r="CT4" t="n">
-        <v>3.1</v>
+        <v>3.07</v>
       </c>
       <c r="CU4" t="n">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="CV4" t="n">
-        <v>2.17</v>
+        <v>2.16</v>
       </c>
       <c r="CW4" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="CX4" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="CY4" t="n">
-        <v>1.94</v>
+        <v>1.96</v>
       </c>
       <c r="CZ4" t="n">
-        <v>2.38</v>
+        <v>2.36</v>
       </c>
       <c r="DA4" t="n">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="DB4" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="DC4" t="n">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="DD4" t="n">
-        <v>3.04</v>
+        <v>3.09</v>
       </c>
       <c r="DE4" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DF4" t="n">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="DG4" t="n">
-        <v>1.06</v>
+        <v>1.21</v>
       </c>
       <c r="DH4" t="n">
-        <v>90.66</v>
+        <v>91.63</v>
       </c>
       <c r="DI4" t="n">
-        <v>-0.06</v>
+        <v>-0.05</v>
       </c>
       <c r="DJ4" t="n">
-        <v>1.78</v>
+        <v>1.89</v>
       </c>
       <c r="DK4" t="n">
-        <v>2.94</v>
+        <v>3.05</v>
       </c>
       <c r="DL4" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DM4" t="n">
-        <v>39.5</v>
+        <v>40.58</v>
       </c>
       <c r="DN4" t="n">
-        <v>0.45</v>
+        <v>0.58</v>
       </c>
       <c r="DO4" t="n">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="DP4" t="n">
-        <v>10.61</v>
+        <v>10.95</v>
       </c>
       <c r="DQ4" t="n">
-        <v>11.62</v>
+        <v>11.58</v>
       </c>
       <c r="DR4" t="n">
-        <v>10.84</v>
+        <v>10.69</v>
       </c>
       <c r="DS4" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DT4" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DU4" t="n">
         <v>0</v>
       </c>
       <c r="DV4" t="n">
-        <v>46.22</v>
+        <v>46.89</v>
       </c>
       <c r="DW4" t="n">
         <v>0.16</v>
@@ -2566,19 +2566,19 @@
         <v>10.11</v>
       </c>
       <c r="DY4" t="n">
-        <v>6.5</v>
+        <v>6.48</v>
       </c>
       <c r="DZ4" t="n">
-        <v>3.61</v>
+        <v>3.63</v>
       </c>
       <c r="EA4" t="n">
-        <v>20.56</v>
+        <v>21</v>
       </c>
       <c r="EB4" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="EC4" t="n">
-        <v>1.5</v>
+        <v>1.63</v>
       </c>
     </row>
     <row r="5">
@@ -2588,13 +2588,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C5" t="n">
         <v>9</v>
       </c>
       <c r="D5" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E5" t="n">
         <v>0.33</v>
@@ -2678,139 +2678,139 @@
         <v>1.33</v>
       </c>
       <c r="AF5" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="AH5" t="n">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="AI5" t="n">
-        <v>92.33</v>
+        <v>89.8</v>
       </c>
       <c r="AJ5" t="n">
         <v>0</v>
       </c>
       <c r="AK5" t="n">
-        <v>2.33</v>
+        <v>2.3</v>
       </c>
       <c r="AL5" t="n">
-        <v>5</v>
+        <v>4.7</v>
       </c>
       <c r="AM5" t="n">
-        <v>0.78</v>
+        <v>0.7</v>
       </c>
       <c r="AN5" t="n">
-        <v>41.78</v>
+        <v>40.4</v>
       </c>
       <c r="AO5" t="n">
-        <v>0.89</v>
+        <v>0.8</v>
       </c>
       <c r="AP5" t="n">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="AQ5" t="n">
-        <v>10.78</v>
+        <v>10.9</v>
       </c>
       <c r="AR5" t="n">
-        <v>11.11</v>
+        <v>10.9</v>
       </c>
       <c r="AS5" t="n">
-        <v>10.89</v>
+        <v>11</v>
       </c>
       <c r="AT5" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="AU5" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="AV5" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="AW5" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="AX5" t="n">
         <v>0</v>
       </c>
       <c r="AY5" t="n">
-        <v>50.89</v>
+        <v>48.5</v>
       </c>
       <c r="AZ5" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="BA5" t="n">
-        <v>11.89</v>
+        <v>11.3</v>
       </c>
       <c r="BB5" t="n">
-        <v>6.89</v>
+        <v>6.6</v>
       </c>
       <c r="BC5" t="n">
-        <v>5</v>
+        <v>4.7</v>
       </c>
       <c r="BD5" t="n">
-        <v>17.89</v>
+        <v>18.5</v>
       </c>
       <c r="BE5" t="n">
-        <v>1.41</v>
+        <v>1.34</v>
       </c>
       <c r="BF5" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="BG5" t="n">
         <v>2.89</v>
       </c>
       <c r="BH5" t="n">
-        <v>9.720000000000001</v>
+        <v>9.84</v>
       </c>
       <c r="BI5" t="n">
         <v>2.89</v>
       </c>
       <c r="BJ5" t="n">
-        <v>0.83</v>
+        <v>0.84</v>
       </c>
       <c r="BK5" t="n">
-        <v>0.44</v>
+        <v>0.42</v>
       </c>
       <c r="BL5" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.95</v>
       </c>
       <c r="BM5" t="n">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="BN5" t="n">
-        <v>1.61</v>
+        <v>1.63</v>
       </c>
       <c r="BO5" t="n">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="BP5" t="n">
-        <v>3.78</v>
+        <v>3.79</v>
       </c>
       <c r="BQ5" t="n">
-        <v>5.94</v>
+        <v>6.05</v>
       </c>
       <c r="BR5" t="n">
-        <v>94.44</v>
+        <v>94.73999999999999</v>
       </c>
       <c r="BS5" t="n">
-        <v>83.33</v>
+        <v>84.20999999999999</v>
       </c>
       <c r="BT5" t="n">
-        <v>55.56</v>
+        <v>57.89</v>
       </c>
       <c r="BU5" t="n">
-        <v>33.33</v>
+        <v>31.58</v>
       </c>
       <c r="BV5" t="n">
-        <v>16.67</v>
+        <v>15.79</v>
       </c>
       <c r="BW5" t="n">
-        <v>5.56</v>
+        <v>5.26</v>
       </c>
       <c r="BX5" t="n">
-        <v>61.11</v>
+        <v>63.16</v>
       </c>
       <c r="BY5" t="n">
         <v>2.73</v>
@@ -2819,28 +2819,28 @@
         <v>2.85</v>
       </c>
       <c r="CA5" t="n">
-        <v>3.63</v>
+        <v>3.67</v>
       </c>
       <c r="CB5" t="n">
-        <v>3.79</v>
+        <v>3.85</v>
       </c>
       <c r="CC5" t="n">
-        <v>3.59</v>
+        <v>3.75</v>
       </c>
       <c r="CD5" t="n">
-        <v>3.84</v>
+        <v>4.07</v>
       </c>
       <c r="CE5" t="n">
         <v>1.3</v>
       </c>
       <c r="CF5" t="n">
-        <v>2.45</v>
+        <v>2.43</v>
       </c>
       <c r="CG5" t="n">
-        <v>3.22</v>
+        <v>3.26</v>
       </c>
       <c r="CH5" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="CI5" t="n">
         <v>2.24</v>
@@ -2858,130 +2858,130 @@
         <v>2.58</v>
       </c>
       <c r="CN5" t="n">
-        <v>2.01</v>
+        <v>2</v>
       </c>
       <c r="CO5" t="n">
         <v>1.21</v>
       </c>
       <c r="CP5" t="n">
-        <v>1.73</v>
+        <v>1.71</v>
       </c>
       <c r="CQ5" t="n">
-        <v>2.71</v>
+        <v>2.69</v>
       </c>
       <c r="CR5" t="n">
         <v>1.35</v>
       </c>
       <c r="CS5" t="n">
-        <v>2.52</v>
+        <v>2.5</v>
       </c>
       <c r="CT5" t="n">
         <v>3.27</v>
       </c>
       <c r="CU5" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="CV5" t="n">
-        <v>2.34</v>
+        <v>2.33</v>
       </c>
       <c r="CW5" t="n">
         <v>1.65</v>
       </c>
       <c r="CX5" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="CY5" t="n">
         <v>1.78</v>
       </c>
       <c r="CZ5" t="n">
-        <v>2.47</v>
+        <v>2.49</v>
       </c>
       <c r="DA5" t="n">
-        <v>2.05</v>
+        <v>2.04</v>
       </c>
       <c r="DB5" t="n">
         <v>1.23</v>
       </c>
       <c r="DC5" t="n">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="DD5" t="n">
-        <v>2.81</v>
+        <v>2.78</v>
       </c>
       <c r="DE5" t="n">
-        <v>0.22</v>
+        <v>0.21</v>
       </c>
       <c r="DF5" t="n">
-        <v>1.16</v>
+        <v>1.21</v>
       </c>
       <c r="DG5" t="n">
-        <v>2.89</v>
+        <v>2.84</v>
       </c>
       <c r="DH5" t="n">
-        <v>101.66</v>
+        <v>99.84</v>
       </c>
       <c r="DI5" t="n">
         <v>0</v>
       </c>
       <c r="DJ5" t="n">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="DK5" t="n">
-        <v>4.84</v>
+        <v>4.69</v>
       </c>
       <c r="DL5" t="n">
-        <v>0.61</v>
+        <v>0.58</v>
       </c>
       <c r="DM5" t="n">
-        <v>46.44</v>
+        <v>45.47</v>
       </c>
       <c r="DN5" t="n">
-        <v>0.61</v>
+        <v>0.58</v>
       </c>
       <c r="DO5" t="n">
-        <v>1.94</v>
+        <v>1.84</v>
       </c>
       <c r="DP5" t="n">
-        <v>10.39</v>
+        <v>10.47</v>
       </c>
       <c r="DQ5" t="n">
-        <v>10.39</v>
+        <v>10.32</v>
       </c>
       <c r="DR5" t="n">
-        <v>9.5</v>
+        <v>9.630000000000001</v>
       </c>
       <c r="DS5" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="DT5" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="DU5" t="n">
         <v>0</v>
       </c>
       <c r="DV5" t="n">
-        <v>53.5</v>
+        <v>52.1</v>
       </c>
       <c r="DW5" t="n">
         <v>0.16</v>
       </c>
       <c r="DX5" t="n">
-        <v>13.56</v>
+        <v>13.16</v>
       </c>
       <c r="DY5" t="n">
-        <v>9</v>
+        <v>8.74</v>
       </c>
       <c r="DZ5" t="n">
-        <v>4.56</v>
+        <v>4.42</v>
       </c>
       <c r="EA5" t="n">
-        <v>18.83</v>
+        <v>19.11</v>
       </c>
       <c r="EB5" t="n">
-        <v>1.52</v>
+        <v>1.47</v>
       </c>
       <c r="EC5" t="n">
-        <v>1.61</v>
+        <v>1.63</v>
       </c>
     </row>
     <row r="6">
@@ -2991,13 +2991,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C6" t="n">
         <v>9</v>
       </c>
       <c r="D6" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
@@ -3081,52 +3081,52 @@
         <v>0.78</v>
       </c>
       <c r="AF6" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.44</v>
+        <v>1.3</v>
       </c>
       <c r="AH6" t="n">
-        <v>3.22</v>
+        <v>2.9</v>
       </c>
       <c r="AI6" t="n">
-        <v>102.22</v>
+        <v>101.7</v>
       </c>
       <c r="AJ6" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="AK6" t="n">
-        <v>1.89</v>
+        <v>1.7</v>
       </c>
       <c r="AL6" t="n">
-        <v>5.67</v>
+        <v>5.2</v>
       </c>
       <c r="AM6" t="n">
-        <v>0.78</v>
+        <v>0.8</v>
       </c>
       <c r="AN6" t="n">
-        <v>49.78</v>
+        <v>47.4</v>
       </c>
       <c r="AO6" t="n">
-        <v>0.44</v>
+        <v>0.4</v>
       </c>
       <c r="AP6" t="n">
-        <v>2.44</v>
+        <v>2.3</v>
       </c>
       <c r="AQ6" t="n">
-        <v>9.56</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="AR6" t="n">
-        <v>12.11</v>
+        <v>12.2</v>
       </c>
       <c r="AS6" t="n">
-        <v>6.89</v>
+        <v>7.1</v>
       </c>
       <c r="AT6" t="n">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="AU6" t="n">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="AV6" t="n">
         <v>0</v>
@@ -3138,82 +3138,82 @@
         <v>0</v>
       </c>
       <c r="AY6" t="n">
-        <v>62.11</v>
+        <v>61.2</v>
       </c>
       <c r="AZ6" t="n">
         <v>0</v>
       </c>
       <c r="BA6" t="n">
-        <v>15.56</v>
+        <v>14.9</v>
       </c>
       <c r="BB6" t="n">
-        <v>9.890000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BC6" t="n">
-        <v>5.67</v>
+        <v>5.7</v>
       </c>
       <c r="BD6" t="n">
-        <v>19.56</v>
+        <v>19.7</v>
       </c>
       <c r="BE6" t="n">
-        <v>1.74</v>
+        <v>1.69</v>
       </c>
       <c r="BF6" t="n">
-        <v>1.89</v>
+        <v>1.7</v>
       </c>
       <c r="BG6" t="n">
-        <v>2.56</v>
+        <v>2.63</v>
       </c>
       <c r="BH6" t="n">
-        <v>10.28</v>
+        <v>10.21</v>
       </c>
       <c r="BI6" t="n">
-        <v>2.56</v>
+        <v>2.63</v>
       </c>
       <c r="BJ6" t="n">
-        <v>0.61</v>
+        <v>0.63</v>
       </c>
       <c r="BK6" t="n">
-        <v>0.83</v>
+        <v>0.84</v>
       </c>
       <c r="BL6" t="n">
-        <v>0.72</v>
+        <v>0.74</v>
       </c>
       <c r="BM6" t="n">
-        <v>0.39</v>
+        <v>0.42</v>
       </c>
       <c r="BN6" t="n">
-        <v>1.11</v>
+        <v>1.16</v>
       </c>
       <c r="BO6" t="n">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="BP6" t="n">
-        <v>4.61</v>
+        <v>4.63</v>
       </c>
       <c r="BQ6" t="n">
-        <v>5.61</v>
+        <v>5.53</v>
       </c>
       <c r="BR6" t="n">
         <v>100</v>
       </c>
       <c r="BS6" t="n">
-        <v>83.33</v>
+        <v>84.20999999999999</v>
       </c>
       <c r="BT6" t="n">
-        <v>55.56</v>
+        <v>57.89</v>
       </c>
       <c r="BU6" t="n">
-        <v>11.11</v>
+        <v>15.79</v>
       </c>
       <c r="BV6" t="n">
-        <v>5.56</v>
+        <v>5.26</v>
       </c>
       <c r="BW6" t="n">
         <v>0</v>
       </c>
       <c r="BX6" t="n">
-        <v>77.78</v>
+        <v>78.95</v>
       </c>
       <c r="BY6" t="n">
         <v>1.67</v>
@@ -3222,31 +3222,31 @@
         <v>1.78</v>
       </c>
       <c r="CA6" t="n">
-        <v>3.92</v>
+        <v>3.88</v>
       </c>
       <c r="CB6" t="n">
-        <v>4.04</v>
+        <v>4</v>
       </c>
       <c r="CC6" t="n">
-        <v>2.47</v>
+        <v>2.45</v>
       </c>
       <c r="CD6" t="n">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="CE6" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="CF6" t="n">
-        <v>2.38</v>
+        <v>2.42</v>
       </c>
       <c r="CG6" t="n">
-        <v>3.32</v>
+        <v>3.28</v>
       </c>
       <c r="CH6" t="n">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="CI6" t="n">
-        <v>2.26</v>
+        <v>2.24</v>
       </c>
       <c r="CJ6" t="n">
         <v>1.64</v>
@@ -3258,100 +3258,100 @@
         <v>2.01</v>
       </c>
       <c r="CM6" t="n">
-        <v>2.44</v>
+        <v>2.42</v>
       </c>
       <c r="CN6" t="n">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="CO6" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="CP6" t="n">
-        <v>1.67</v>
+        <v>1.69</v>
       </c>
       <c r="CQ6" t="n">
-        <v>2.62</v>
+        <v>2.68</v>
       </c>
       <c r="CR6" t="n">
         <v>1.38</v>
       </c>
       <c r="CS6" t="n">
-        <v>2.54</v>
+        <v>2.57</v>
       </c>
       <c r="CT6" t="n">
-        <v>3.12</v>
+        <v>3.09</v>
       </c>
       <c r="CU6" t="n">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="CV6" t="n">
-        <v>2.31</v>
+        <v>2.29</v>
       </c>
       <c r="CW6" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="CX6" t="n">
         <v>1.59</v>
       </c>
       <c r="CY6" t="n">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="CZ6" t="n">
-        <v>2.35</v>
+        <v>2.33</v>
       </c>
       <c r="DA6" t="n">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="DB6" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="DC6" t="n">
-        <v>1.72</v>
+        <v>1.74</v>
       </c>
       <c r="DD6" t="n">
-        <v>2.74</v>
+        <v>2.8</v>
       </c>
       <c r="DE6" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="DF6" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.89</v>
       </c>
       <c r="DG6" t="n">
-        <v>3.61</v>
+        <v>3.42</v>
       </c>
       <c r="DH6" t="n">
-        <v>118.39</v>
+        <v>117.27</v>
       </c>
       <c r="DI6" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="DJ6" t="n">
-        <v>1.44</v>
+        <v>1.37</v>
       </c>
       <c r="DK6" t="n">
-        <v>6.34</v>
+        <v>6.05</v>
       </c>
       <c r="DL6" t="n">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="DM6" t="n">
-        <v>58</v>
+        <v>56.31</v>
       </c>
       <c r="DN6" t="n">
-        <v>0.44</v>
+        <v>0.42</v>
       </c>
       <c r="DO6" t="n">
-        <v>2.66</v>
+        <v>2.58</v>
       </c>
       <c r="DP6" t="n">
-        <v>10.17</v>
+        <v>10</v>
       </c>
       <c r="DQ6" t="n">
         <v>13.16</v>
       </c>
       <c r="DR6" t="n">
-        <v>6.06</v>
+        <v>6.21</v>
       </c>
       <c r="DS6" t="n">
         <v>0</v>
@@ -3363,28 +3363,28 @@
         <v>0</v>
       </c>
       <c r="DV6" t="n">
-        <v>64.39</v>
+        <v>63.79</v>
       </c>
       <c r="DW6" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="DX6" t="n">
-        <v>16.89</v>
+        <v>16.47</v>
       </c>
       <c r="DY6" t="n">
-        <v>11.16</v>
+        <v>10.73</v>
       </c>
       <c r="DZ6" t="n">
-        <v>5.72</v>
+        <v>5.74</v>
       </c>
       <c r="EA6" t="n">
-        <v>20.22</v>
+        <v>20.26</v>
       </c>
       <c r="EB6" t="n">
-        <v>1.89</v>
+        <v>1.86</v>
       </c>
       <c r="EC6" t="n">
-        <v>1.34</v>
+        <v>1.26</v>
       </c>
     </row>
     <row r="7">
@@ -3797,94 +3797,94 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C8" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D8" t="n">
         <v>9</v>
       </c>
       <c r="E8" t="n">
-        <v>0.22</v>
+        <v>0.3</v>
       </c>
       <c r="F8" t="n">
         <v>1</v>
       </c>
       <c r="G8" t="n">
-        <v>3.11</v>
+        <v>2.9</v>
       </c>
       <c r="H8" t="n">
-        <v>97.33</v>
+        <v>98.5</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="K8" t="n">
-        <v>6.44</v>
+        <v>6.2</v>
       </c>
       <c r="L8" t="n">
-        <v>0.22</v>
+        <v>0.4</v>
       </c>
       <c r="M8" t="n">
-        <v>57.78</v>
+        <v>57</v>
       </c>
       <c r="N8" t="n">
-        <v>0.44</v>
+        <v>0.4</v>
       </c>
       <c r="O8" t="n">
-        <v>3.33</v>
+        <v>3.3</v>
       </c>
       <c r="P8" t="n">
-        <v>10.56</v>
+        <v>10.5</v>
       </c>
       <c r="Q8" t="n">
-        <v>12.89</v>
+        <v>12.1</v>
       </c>
       <c r="R8" t="n">
-        <v>7.44</v>
+        <v>8.1</v>
       </c>
       <c r="S8" t="n">
-        <v>0.67</v>
+        <v>0.7</v>
       </c>
       <c r="T8" t="n">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="U8" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="V8" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>49.44</v>
+        <v>50.5</v>
       </c>
       <c r="Y8" t="n">
         <v>0</v>
       </c>
       <c r="Z8" t="n">
-        <v>17.56</v>
+        <v>17.2</v>
       </c>
       <c r="AA8" t="n">
-        <v>12.33</v>
+        <v>12.1</v>
       </c>
       <c r="AB8" t="n">
-        <v>5.22</v>
+        <v>5.1</v>
       </c>
       <c r="AC8" t="n">
-        <v>19.44</v>
+        <v>20.2</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.89</v>
+        <v>1.85</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AF8" t="n">
         <v>0.11</v>
@@ -3968,67 +3968,67 @@
         <v>1.67</v>
       </c>
       <c r="BG8" t="n">
-        <v>2.94</v>
+        <v>2.95</v>
       </c>
       <c r="BH8" t="n">
-        <v>10.5</v>
+        <v>10.42</v>
       </c>
       <c r="BI8" t="n">
-        <v>2.94</v>
+        <v>2.95</v>
       </c>
       <c r="BJ8" t="n">
-        <v>0.83</v>
+        <v>0.84</v>
       </c>
       <c r="BK8" t="n">
-        <v>0.5</v>
+        <v>0.47</v>
       </c>
       <c r="BL8" t="n">
         <v>1</v>
       </c>
       <c r="BM8" t="n">
-        <v>0.61</v>
+        <v>0.63</v>
       </c>
       <c r="BN8" t="n">
-        <v>1.61</v>
+        <v>1.63</v>
       </c>
       <c r="BO8" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="BP8" t="n">
         <v>4.89</v>
       </c>
       <c r="BQ8" t="n">
-        <v>5.56</v>
+        <v>5.47</v>
       </c>
       <c r="BR8" t="n">
-        <v>88.89</v>
+        <v>89.47</v>
       </c>
       <c r="BS8" t="n">
-        <v>77.78</v>
+        <v>78.95</v>
       </c>
       <c r="BT8" t="n">
-        <v>38.89</v>
+        <v>42.11</v>
       </c>
       <c r="BU8" t="n">
-        <v>33.33</v>
+        <v>31.58</v>
       </c>
       <c r="BV8" t="n">
-        <v>16.67</v>
+        <v>15.79</v>
       </c>
       <c r="BW8" t="n">
-        <v>11.11</v>
+        <v>10.53</v>
       </c>
       <c r="BX8" t="n">
-        <v>38.89</v>
+        <v>42.11</v>
       </c>
       <c r="BY8" t="n">
-        <v>2.25</v>
+        <v>2.21</v>
       </c>
       <c r="BZ8" t="n">
-        <v>2.37</v>
+        <v>2.3</v>
       </c>
       <c r="CA8" t="n">
-        <v>3.89</v>
+        <v>3.88</v>
       </c>
       <c r="CB8" t="n">
         <v>3.95</v>
@@ -4040,22 +4040,22 @@
         <v>4.3</v>
       </c>
       <c r="CE8" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="CF8" t="n">
-        <v>2.25</v>
+        <v>2.26</v>
       </c>
       <c r="CG8" t="n">
-        <v>3.55</v>
+        <v>3.52</v>
       </c>
       <c r="CH8" t="n">
         <v>1.6</v>
       </c>
       <c r="CI8" t="n">
-        <v>2.41</v>
+        <v>2.39</v>
       </c>
       <c r="CJ8" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="CK8" t="n">
         <v>1.35</v>
@@ -4064,37 +4064,37 @@
         <v>1.67</v>
       </c>
       <c r="CM8" t="n">
-        <v>2.89</v>
+        <v>2.87</v>
       </c>
       <c r="CN8" t="n">
-        <v>2.22</v>
+        <v>2.21</v>
       </c>
       <c r="CO8" t="n">
         <v>1.15</v>
       </c>
       <c r="CP8" t="n">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
       <c r="CQ8" t="n">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="CR8" t="n">
         <v>1.34</v>
       </c>
       <c r="CS8" t="n">
-        <v>2.31</v>
+        <v>2.33</v>
       </c>
       <c r="CT8" t="n">
-        <v>3.3</v>
+        <v>3.31</v>
       </c>
       <c r="CU8" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="CV8" t="n">
-        <v>2.58</v>
+        <v>2.55</v>
       </c>
       <c r="CW8" t="n">
-        <v>1.54</v>
+        <v>1.56</v>
       </c>
       <c r="CX8" t="n">
         <v>1.46</v>
@@ -4106,58 +4106,58 @@
         <v>2.67</v>
       </c>
       <c r="DA8" t="n">
-        <v>2.27</v>
+        <v>2.26</v>
       </c>
       <c r="DB8" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="DC8" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="DD8" t="n">
-        <v>2.47</v>
+        <v>2.49</v>
       </c>
       <c r="DE8" t="n">
-        <v>0.16</v>
+        <v>0.21</v>
       </c>
       <c r="DF8" t="n">
-        <v>1.39</v>
+        <v>1.37</v>
       </c>
       <c r="DG8" t="n">
-        <v>2.66</v>
+        <v>2.58</v>
       </c>
       <c r="DH8" t="n">
-        <v>90.06</v>
+        <v>91.05</v>
       </c>
       <c r="DI8" t="n">
         <v>0</v>
       </c>
       <c r="DJ8" t="n">
-        <v>1.66</v>
+        <v>1.63</v>
       </c>
       <c r="DK8" t="n">
-        <v>5.5</v>
+        <v>5.42</v>
       </c>
       <c r="DL8" t="n">
-        <v>0.22</v>
+        <v>0.31</v>
       </c>
       <c r="DM8" t="n">
-        <v>48.84</v>
+        <v>48.9</v>
       </c>
       <c r="DN8" t="n">
-        <v>0.22</v>
+        <v>0.21</v>
       </c>
       <c r="DO8" t="n">
-        <v>2.83</v>
+        <v>2.84</v>
       </c>
       <c r="DP8" t="n">
-        <v>12</v>
+        <v>11.89</v>
       </c>
       <c r="DQ8" t="n">
-        <v>12.23</v>
+        <v>11.84</v>
       </c>
       <c r="DR8" t="n">
-        <v>8.220000000000001</v>
+        <v>8.529999999999999</v>
       </c>
       <c r="DS8" t="n">
         <v>0.16</v>
@@ -4169,28 +4169,28 @@
         <v>0</v>
       </c>
       <c r="DV8" t="n">
-        <v>48.38</v>
+        <v>49</v>
       </c>
       <c r="DW8" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="DX8" t="n">
-        <v>15.73</v>
+        <v>15.63</v>
       </c>
       <c r="DY8" t="n">
-        <v>10.94</v>
+        <v>10.9</v>
       </c>
       <c r="DZ8" t="n">
-        <v>4.77</v>
+        <v>4.74</v>
       </c>
       <c r="EA8" t="n">
-        <v>20.72</v>
+        <v>21.05</v>
       </c>
       <c r="EB8" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="EC8" t="n">
-        <v>1.56</v>
+        <v>1.53</v>
       </c>
     </row>
     <row r="9">
@@ -4603,13 +4603,13 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C10" t="n">
         <v>9</v>
       </c>
       <c r="D10" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
@@ -4693,49 +4693,49 @@
         <v>1.67</v>
       </c>
       <c r="AF10" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="AH10" t="n">
-        <v>2.11</v>
+        <v>2.2</v>
       </c>
       <c r="AI10" t="n">
-        <v>78.78</v>
+        <v>79.3</v>
       </c>
       <c r="AJ10" t="n">
         <v>0</v>
       </c>
       <c r="AK10" t="n">
-        <v>2.11</v>
+        <v>1.9</v>
       </c>
       <c r="AL10" t="n">
-        <v>3.33</v>
+        <v>3.5</v>
       </c>
       <c r="AM10" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="AN10" t="n">
-        <v>32.78</v>
+        <v>33.7</v>
       </c>
       <c r="AO10" t="n">
-        <v>0.67</v>
+        <v>0.6</v>
       </c>
       <c r="AP10" t="n">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="AQ10" t="n">
-        <v>13.11</v>
+        <v>12.3</v>
       </c>
       <c r="AR10" t="n">
-        <v>13.22</v>
+        <v>12.9</v>
       </c>
       <c r="AS10" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AT10" t="n">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="AU10" t="n">
         <v>1</v>
@@ -4750,82 +4750,82 @@
         <v>0</v>
       </c>
       <c r="AY10" t="n">
-        <v>31.11</v>
+        <v>32</v>
       </c>
       <c r="AZ10" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="BA10" t="n">
-        <v>8</v>
+        <v>8.6</v>
       </c>
       <c r="BB10" t="n">
-        <v>5.67</v>
+        <v>6.2</v>
       </c>
       <c r="BC10" t="n">
-        <v>2.33</v>
+        <v>2.4</v>
       </c>
       <c r="BD10" t="n">
-        <v>21.11</v>
+        <v>20.9</v>
       </c>
       <c r="BE10" t="n">
-        <v>0.91</v>
+        <v>0.96</v>
       </c>
       <c r="BF10" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="BG10" t="n">
         <v>1.89</v>
       </c>
-      <c r="BG10" t="n">
-        <v>1.83</v>
-      </c>
       <c r="BH10" t="n">
-        <v>8.220000000000001</v>
+        <v>8.26</v>
       </c>
       <c r="BI10" t="n">
-        <v>1.83</v>
+        <v>1.89</v>
       </c>
       <c r="BJ10" t="n">
-        <v>0.5</v>
+        <v>0.53</v>
       </c>
       <c r="BK10" t="n">
-        <v>0.39</v>
+        <v>0.37</v>
       </c>
       <c r="BL10" t="n">
-        <v>0.5</v>
+        <v>0.53</v>
       </c>
       <c r="BM10" t="n">
-        <v>0.44</v>
+        <v>0.47</v>
       </c>
       <c r="BN10" t="n">
-        <v>0.9399999999999999</v>
+        <v>1</v>
       </c>
       <c r="BO10" t="n">
         <v>0.89</v>
       </c>
       <c r="BP10" t="n">
-        <v>3.44</v>
+        <v>3.53</v>
       </c>
       <c r="BQ10" t="n">
-        <v>4.78</v>
+        <v>4.74</v>
       </c>
       <c r="BR10" t="n">
-        <v>72.22</v>
+        <v>73.68000000000001</v>
       </c>
       <c r="BS10" t="n">
-        <v>50</v>
+        <v>52.63</v>
       </c>
       <c r="BT10" t="n">
-        <v>38.89</v>
+        <v>42.11</v>
       </c>
       <c r="BU10" t="n">
-        <v>16.67</v>
+        <v>15.79</v>
       </c>
       <c r="BV10" t="n">
-        <v>5.56</v>
+        <v>5.26</v>
       </c>
       <c r="BW10" t="n">
         <v>0</v>
       </c>
       <c r="BX10" t="n">
-        <v>44.44</v>
+        <v>47.37</v>
       </c>
       <c r="BY10" t="n">
         <v>3.64</v>
@@ -4834,25 +4834,25 @@
         <v>3.82</v>
       </c>
       <c r="CA10" t="n">
-        <v>3.48</v>
+        <v>3.49</v>
       </c>
       <c r="CB10" t="n">
-        <v>3.52</v>
+        <v>3.54</v>
       </c>
       <c r="CC10" t="n">
-        <v>4.06</v>
+        <v>4.09</v>
       </c>
       <c r="CD10" t="n">
-        <v>4.23</v>
+        <v>4.35</v>
       </c>
       <c r="CE10" t="n">
         <v>1.39</v>
       </c>
       <c r="CF10" t="n">
-        <v>2.81</v>
+        <v>2.79</v>
       </c>
       <c r="CG10" t="n">
-        <v>2.84</v>
+        <v>2.85</v>
       </c>
       <c r="CH10" t="n">
         <v>1.39</v>
@@ -4861,19 +4861,19 @@
         <v>1.9</v>
       </c>
       <c r="CJ10" t="n">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="CK10" t="n">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="CL10" t="n">
-        <v>2.01</v>
+        <v>1.99</v>
       </c>
       <c r="CM10" t="n">
-        <v>2.32</v>
+        <v>2.33</v>
       </c>
       <c r="CN10" t="n">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="CO10" t="n">
         <v>1.31</v>
@@ -4882,88 +4882,88 @@
         <v>2</v>
       </c>
       <c r="CQ10" t="n">
-        <v>3.54</v>
+        <v>3.5</v>
       </c>
       <c r="CR10" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="CS10" t="n">
-        <v>2.97</v>
+        <v>2.96</v>
       </c>
       <c r="CT10" t="n">
-        <v>2.99</v>
+        <v>3.01</v>
       </c>
       <c r="CU10" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="CV10" t="n">
         <v>2.01</v>
       </c>
       <c r="CW10" t="n">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="CX10" t="n">
         <v>1.62</v>
       </c>
       <c r="CY10" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="CZ10" t="n">
         <v>2.29</v>
       </c>
       <c r="DA10" t="n">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="DB10" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="DC10" t="n">
-        <v>2.08</v>
+        <v>2.07</v>
       </c>
       <c r="DD10" t="n">
-        <v>3.61</v>
+        <v>3.58</v>
       </c>
       <c r="DE10" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="DF10" t="n">
-        <v>1.11</v>
+        <v>1.05</v>
       </c>
       <c r="DG10" t="n">
-        <v>2.34</v>
+        <v>2.37</v>
       </c>
       <c r="DH10" t="n">
-        <v>79</v>
+        <v>79.26000000000001</v>
       </c>
       <c r="DI10" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DJ10" t="n">
-        <v>1.89</v>
+        <v>1.79</v>
       </c>
       <c r="DK10" t="n">
-        <v>4.16</v>
+        <v>4.21</v>
       </c>
       <c r="DL10" t="n">
         <v>0.16</v>
       </c>
       <c r="DM10" t="n">
-        <v>38.06</v>
+        <v>38.26</v>
       </c>
       <c r="DN10" t="n">
-        <v>0.73</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="DO10" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="DP10" t="n">
-        <v>12.27</v>
+        <v>11.89</v>
       </c>
       <c r="DQ10" t="n">
-        <v>12.33</v>
+        <v>12.21</v>
       </c>
       <c r="DR10" t="n">
-        <v>8.890000000000001</v>
+        <v>8.789999999999999</v>
       </c>
       <c r="DS10" t="n">
         <v>0</v>
@@ -4975,28 +4975,28 @@
         <v>0</v>
       </c>
       <c r="DV10" t="n">
-        <v>33.94</v>
+        <v>34.26</v>
       </c>
       <c r="DW10" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="DX10" t="n">
-        <v>9.279999999999999</v>
+        <v>9.529999999999999</v>
       </c>
       <c r="DY10" t="n">
-        <v>6.72</v>
+        <v>6.95</v>
       </c>
       <c r="DZ10" t="n">
-        <v>2.55</v>
+        <v>2.58</v>
       </c>
       <c r="EA10" t="n">
-        <v>21</v>
+        <v>20.9</v>
       </c>
       <c r="EB10" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="EC10" t="n">
-        <v>1.78</v>
+        <v>1.69</v>
       </c>
     </row>
     <row r="11">
@@ -6215,94 +6215,94 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C14" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D14" t="n">
         <v>9</v>
       </c>
       <c r="E14" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="F14" t="n">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="G14" t="n">
-        <v>2.11</v>
+        <v>2.3</v>
       </c>
       <c r="H14" t="n">
-        <v>87.78</v>
+        <v>89.7</v>
       </c>
       <c r="I14" t="n">
         <v>0</v>
       </c>
       <c r="J14" t="n">
-        <v>2.11</v>
+        <v>2.1</v>
       </c>
       <c r="K14" t="n">
-        <v>4.78</v>
+        <v>5.1</v>
       </c>
       <c r="L14" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="M14" t="n">
-        <v>48.78</v>
+        <v>48.1</v>
       </c>
       <c r="N14" t="n">
-        <v>0.33</v>
+        <v>0.4</v>
       </c>
       <c r="O14" t="n">
-        <v>2.67</v>
+        <v>2.8</v>
       </c>
       <c r="P14" t="n">
-        <v>11.33</v>
+        <v>11.5</v>
       </c>
       <c r="Q14" t="n">
-        <v>13.56</v>
+        <v>12.9</v>
       </c>
       <c r="R14" t="n">
-        <v>7.56</v>
+        <v>7.3</v>
       </c>
       <c r="S14" t="n">
-        <v>0.89</v>
+        <v>1</v>
       </c>
       <c r="T14" t="n">
-        <v>1.11</v>
+        <v>1.2</v>
       </c>
       <c r="U14" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="V14" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="W14" t="n">
         <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>47.22</v>
+        <v>47.2</v>
       </c>
       <c r="Y14" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="Z14" t="n">
-        <v>10.78</v>
+        <v>11.4</v>
       </c>
       <c r="AA14" t="n">
-        <v>6.44</v>
+        <v>6.9</v>
       </c>
       <c r="AB14" t="n">
-        <v>4.33</v>
+        <v>4.5</v>
       </c>
       <c r="AC14" t="n">
-        <v>18.11</v>
+        <v>17.6</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.34</v>
+        <v>1.39</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="AF14" t="n">
         <v>0.11</v>
@@ -6386,70 +6386,70 @@
         <v>2.11</v>
       </c>
       <c r="BG14" t="n">
-        <v>2.33</v>
+        <v>2.42</v>
       </c>
       <c r="BH14" t="n">
-        <v>9.5</v>
+        <v>9.470000000000001</v>
       </c>
       <c r="BI14" t="n">
-        <v>2.33</v>
+        <v>2.42</v>
       </c>
       <c r="BJ14" t="n">
-        <v>0.61</v>
+        <v>0.63</v>
       </c>
       <c r="BK14" t="n">
-        <v>0.61</v>
+        <v>0.63</v>
       </c>
       <c r="BL14" t="n">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="BM14" t="n">
-        <v>0.33</v>
+        <v>0.37</v>
       </c>
       <c r="BN14" t="n">
-        <v>1.11</v>
+        <v>1.16</v>
       </c>
       <c r="BO14" t="n">
-        <v>1.22</v>
+        <v>1.26</v>
       </c>
       <c r="BP14" t="n">
         <v>5</v>
       </c>
       <c r="BQ14" t="n">
-        <v>4.5</v>
+        <v>4.47</v>
       </c>
       <c r="BR14" t="n">
-        <v>94.44</v>
+        <v>94.73999999999999</v>
       </c>
       <c r="BS14" t="n">
-        <v>66.67</v>
+        <v>68.42</v>
       </c>
       <c r="BT14" t="n">
-        <v>38.89</v>
+        <v>42.11</v>
       </c>
       <c r="BU14" t="n">
-        <v>27.78</v>
+        <v>31.58</v>
       </c>
       <c r="BV14" t="n">
-        <v>5.56</v>
+        <v>5.26</v>
       </c>
       <c r="BW14" t="n">
         <v>0</v>
       </c>
       <c r="BX14" t="n">
-        <v>55.56</v>
+        <v>57.89</v>
       </c>
       <c r="BY14" t="n">
-        <v>2.27</v>
+        <v>2.33</v>
       </c>
       <c r="BZ14" t="n">
-        <v>2.41</v>
+        <v>2.44</v>
       </c>
       <c r="CA14" t="n">
-        <v>3.55</v>
+        <v>3.53</v>
       </c>
       <c r="CB14" t="n">
-        <v>3.54</v>
+        <v>3.53</v>
       </c>
       <c r="CC14" t="n">
         <v>3.85</v>
@@ -6461,16 +6461,16 @@
         <v>1.34</v>
       </c>
       <c r="CF14" t="n">
-        <v>2.66</v>
+        <v>2.68</v>
       </c>
       <c r="CG14" t="n">
-        <v>3.05</v>
+        <v>3.03</v>
       </c>
       <c r="CH14" t="n">
         <v>1.44</v>
       </c>
       <c r="CI14" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="CJ14" t="n">
         <v>1.74</v>
@@ -6479,10 +6479,10 @@
         <v>1.47</v>
       </c>
       <c r="CL14" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="CM14" t="n">
-        <v>2.56</v>
+        <v>2.54</v>
       </c>
       <c r="CN14" t="n">
         <v>1.94</v>
@@ -6491,40 +6491,40 @@
         <v>1.26</v>
       </c>
       <c r="CP14" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="CQ14" t="n">
-        <v>3.1</v>
+        <v>3.13</v>
       </c>
       <c r="CR14" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="CS14" t="n">
-        <v>2.83</v>
+        <v>2.84</v>
       </c>
       <c r="CT14" t="n">
-        <v>3.09</v>
+        <v>3.08</v>
       </c>
       <c r="CU14" t="n">
         <v>1.45</v>
       </c>
       <c r="CV14" t="n">
-        <v>2.15</v>
+        <v>2.14</v>
       </c>
       <c r="CW14" t="n">
         <v>1.76</v>
       </c>
       <c r="CX14" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="CY14" t="n">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="CZ14" t="n">
-        <v>2.45</v>
+        <v>2.43</v>
       </c>
       <c r="DA14" t="n">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="DB14" t="n">
         <v>1.3</v>
@@ -6533,82 +6533,82 @@
         <v>1.97</v>
       </c>
       <c r="DD14" t="n">
-        <v>3.3</v>
+        <v>3.32</v>
       </c>
       <c r="DE14" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DF14" t="n">
-        <v>1.72</v>
+        <v>1.69</v>
       </c>
       <c r="DG14" t="n">
-        <v>2.05</v>
+        <v>2.16</v>
       </c>
       <c r="DH14" t="n">
-        <v>89.94</v>
+        <v>90.84</v>
       </c>
       <c r="DI14" t="n">
         <v>0</v>
       </c>
       <c r="DJ14" t="n">
-        <v>2.11</v>
+        <v>2.1</v>
       </c>
       <c r="DK14" t="n">
-        <v>4.61</v>
+        <v>4.79</v>
       </c>
       <c r="DL14" t="n">
-        <v>0.34</v>
+        <v>0.32</v>
       </c>
       <c r="DM14" t="n">
-        <v>48.28</v>
+        <v>47.95</v>
       </c>
       <c r="DN14" t="n">
-        <v>0.33</v>
+        <v>0.37</v>
       </c>
       <c r="DO14" t="n">
-        <v>2.56</v>
+        <v>2.63</v>
       </c>
       <c r="DP14" t="n">
-        <v>11.06</v>
+        <v>11.16</v>
       </c>
       <c r="DQ14" t="n">
-        <v>11.78</v>
+        <v>11.53</v>
       </c>
       <c r="DR14" t="n">
-        <v>7.06</v>
+        <v>6.95</v>
       </c>
       <c r="DS14" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="DT14" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="DU14" t="n">
         <v>0</v>
       </c>
       <c r="DV14" t="n">
-        <v>47.44</v>
+        <v>47.42</v>
       </c>
       <c r="DW14" t="n">
         <v>0.11</v>
       </c>
       <c r="DX14" t="n">
-        <v>10.73</v>
+        <v>11.05</v>
       </c>
       <c r="DY14" t="n">
-        <v>6.72</v>
+        <v>6.95</v>
       </c>
       <c r="DZ14" t="n">
-        <v>4</v>
+        <v>4.11</v>
       </c>
       <c r="EA14" t="n">
-        <v>19.72</v>
+        <v>19.37</v>
       </c>
       <c r="EB14" t="n">
-        <v>1.31</v>
+        <v>1.34</v>
       </c>
       <c r="EC14" t="n">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
     </row>
     <row r="15">
@@ -6618,13 +6618,13 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C15" t="n">
         <v>9</v>
       </c>
       <c r="D15" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E15" t="n">
         <v>0.22</v>
@@ -6708,130 +6708,130 @@
         <v>2.56</v>
       </c>
       <c r="AF15" t="n">
-        <v>0.11</v>
+        <v>0.2</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="AI15" t="n">
-        <v>85.22</v>
+        <v>84.59999999999999</v>
       </c>
       <c r="AJ15" t="n">
         <v>0</v>
       </c>
       <c r="AK15" t="n">
-        <v>2.22</v>
+        <v>2.1</v>
       </c>
       <c r="AL15" t="n">
-        <v>2.78</v>
+        <v>2.9</v>
       </c>
       <c r="AM15" t="n">
-        <v>0.33</v>
+        <v>0.4</v>
       </c>
       <c r="AN15" t="n">
-        <v>32.11</v>
+        <v>33.7</v>
       </c>
       <c r="AO15" t="n">
-        <v>0.78</v>
+        <v>0.7</v>
       </c>
       <c r="AP15" t="n">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="AQ15" t="n">
-        <v>11.33</v>
+        <v>11.3</v>
       </c>
       <c r="AR15" t="n">
-        <v>11.22</v>
+        <v>11.8</v>
       </c>
       <c r="AS15" t="n">
-        <v>9.779999999999999</v>
+        <v>10</v>
       </c>
       <c r="AT15" t="n">
-        <v>1.22</v>
+        <v>1.1</v>
       </c>
       <c r="AU15" t="n">
-        <v>0.78</v>
+        <v>0.8</v>
       </c>
       <c r="AV15" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="AW15" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="AX15" t="n">
         <v>0</v>
       </c>
       <c r="AY15" t="n">
-        <v>44</v>
+        <v>43.7</v>
       </c>
       <c r="AZ15" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="BA15" t="n">
-        <v>7.56</v>
+        <v>7.6</v>
       </c>
       <c r="BB15" t="n">
-        <v>5.44</v>
+        <v>5.3</v>
       </c>
       <c r="BC15" t="n">
-        <v>2.11</v>
+        <v>2.3</v>
       </c>
       <c r="BD15" t="n">
-        <v>18</v>
+        <v>18.3</v>
       </c>
       <c r="BE15" t="n">
-        <v>0.87</v>
+        <v>0.89</v>
       </c>
       <c r="BF15" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="BG15" t="n">
         <v>2</v>
       </c>
-      <c r="BG15" t="n">
-        <v>2.06</v>
-      </c>
       <c r="BH15" t="n">
-        <v>9.67</v>
+        <v>9.630000000000001</v>
       </c>
       <c r="BI15" t="n">
-        <v>2.06</v>
+        <v>2</v>
       </c>
       <c r="BJ15" t="n">
-        <v>0.44</v>
+        <v>0.42</v>
       </c>
       <c r="BK15" t="n">
-        <v>0.61</v>
+        <v>0.63</v>
       </c>
       <c r="BL15" t="n">
-        <v>0.67</v>
+        <v>0.63</v>
       </c>
       <c r="BM15" t="n">
-        <v>0.33</v>
+        <v>0.32</v>
       </c>
       <c r="BN15" t="n">
-        <v>1</v>
+        <v>0.95</v>
       </c>
       <c r="BO15" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="BP15" t="n">
-        <v>4.56</v>
+        <v>4.47</v>
       </c>
       <c r="BQ15" t="n">
-        <v>5.11</v>
+        <v>5.16</v>
       </c>
       <c r="BR15" t="n">
-        <v>94.44</v>
+        <v>94.73999999999999</v>
       </c>
       <c r="BS15" t="n">
-        <v>61.11</v>
+        <v>57.89</v>
       </c>
       <c r="BT15" t="n">
-        <v>38.89</v>
+        <v>36.84</v>
       </c>
       <c r="BU15" t="n">
-        <v>11.11</v>
+        <v>10.53</v>
       </c>
       <c r="BV15" t="n">
         <v>0</v>
@@ -6840,7 +6840,7 @@
         <v>0</v>
       </c>
       <c r="BX15" t="n">
-        <v>33.33</v>
+        <v>31.58</v>
       </c>
       <c r="BY15" t="n">
         <v>2.84</v>
@@ -6849,136 +6849,136 @@
         <v>3.03</v>
       </c>
       <c r="CA15" t="n">
-        <v>3.49</v>
+        <v>3.48</v>
       </c>
       <c r="CB15" t="n">
-        <v>3.54</v>
+        <v>3.52</v>
       </c>
       <c r="CC15" t="n">
-        <v>4.11</v>
+        <v>4.03</v>
       </c>
       <c r="CD15" t="n">
-        <v>4.66</v>
+        <v>4.56</v>
       </c>
       <c r="CE15" t="n">
         <v>1.38</v>
       </c>
       <c r="CF15" t="n">
-        <v>2.79</v>
+        <v>2.81</v>
       </c>
       <c r="CG15" t="n">
-        <v>2.92</v>
+        <v>2.9</v>
       </c>
       <c r="CH15" t="n">
         <v>1.41</v>
       </c>
       <c r="CI15" t="n">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="CJ15" t="n">
         <v>1.81</v>
       </c>
       <c r="CK15" t="n">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="CL15" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="CM15" t="n">
-        <v>2.57</v>
+        <v>2.55</v>
       </c>
       <c r="CN15" t="n">
-        <v>1.95</v>
+        <v>1.93</v>
       </c>
       <c r="CO15" t="n">
         <v>1.31</v>
       </c>
       <c r="CP15" t="n">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="CQ15" t="n">
-        <v>3.41</v>
+        <v>3.43</v>
       </c>
       <c r="CR15" t="n">
         <v>1.4</v>
       </c>
       <c r="CS15" t="n">
-        <v>2.9</v>
+        <v>2.92</v>
       </c>
       <c r="CT15" t="n">
-        <v>3.05</v>
+        <v>3.03</v>
       </c>
       <c r="CU15" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="CV15" t="n">
-        <v>2.09</v>
+        <v>2.08</v>
       </c>
       <c r="CW15" t="n">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="CX15" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="CY15" t="n">
-        <v>1.89</v>
+        <v>1.91</v>
       </c>
       <c r="CZ15" t="n">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="DA15" t="n">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="DB15" t="n">
         <v>1.32</v>
       </c>
       <c r="DC15" t="n">
-        <v>2.01</v>
+        <v>2.02</v>
       </c>
       <c r="DD15" t="n">
-        <v>3.44</v>
+        <v>3.47</v>
       </c>
       <c r="DE15" t="n">
-        <v>0.16</v>
+        <v>0.21</v>
       </c>
       <c r="DF15" t="n">
-        <v>1.61</v>
+        <v>1.58</v>
       </c>
       <c r="DG15" t="n">
-        <v>1.72</v>
+        <v>1.74</v>
       </c>
       <c r="DH15" t="n">
-        <v>84.72</v>
+        <v>84.42</v>
       </c>
       <c r="DI15" t="n">
         <v>0</v>
       </c>
       <c r="DJ15" t="n">
-        <v>2.72</v>
+        <v>2.63</v>
       </c>
       <c r="DK15" t="n">
-        <v>4.06</v>
+        <v>4.05</v>
       </c>
       <c r="DL15" t="n">
-        <v>0.45</v>
+        <v>0.48</v>
       </c>
       <c r="DM15" t="n">
-        <v>42.89</v>
+        <v>43.16</v>
       </c>
       <c r="DN15" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.89</v>
       </c>
       <c r="DO15" t="n">
-        <v>2.33</v>
+        <v>2.31</v>
       </c>
       <c r="DP15" t="n">
-        <v>11.44</v>
+        <v>11.42</v>
       </c>
       <c r="DQ15" t="n">
-        <v>11.89</v>
+        <v>12.16</v>
       </c>
       <c r="DR15" t="n">
-        <v>9.109999999999999</v>
+        <v>9.26</v>
       </c>
       <c r="DS15" t="n">
         <v>0.16</v>
@@ -6990,28 +6990,28 @@
         <v>0</v>
       </c>
       <c r="DV15" t="n">
-        <v>44.72</v>
+        <v>44.52</v>
       </c>
       <c r="DW15" t="n">
-        <v>0.28</v>
+        <v>0.26</v>
       </c>
       <c r="DX15" t="n">
-        <v>9.83</v>
+        <v>9.74</v>
       </c>
       <c r="DY15" t="n">
-        <v>6.44</v>
+        <v>6.31</v>
       </c>
       <c r="DZ15" t="n">
-        <v>3.39</v>
+        <v>3.42</v>
       </c>
       <c r="EA15" t="n">
-        <v>18.78</v>
+        <v>18.9</v>
       </c>
       <c r="EB15" t="n">
         <v>1.17</v>
       </c>
       <c r="EC15" t="n">
-        <v>2.28</v>
+        <v>2.21</v>
       </c>
     </row>
     <row r="16">
@@ -7021,94 +7021,94 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C16" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D16" t="n">
         <v>10</v>
       </c>
       <c r="E16" t="n">
-        <v>0.38</v>
+        <v>0.33</v>
       </c>
       <c r="F16" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="G16" t="n">
-        <v>3.5</v>
+        <v>3.44</v>
       </c>
       <c r="H16" t="n">
-        <v>103.88</v>
+        <v>103.11</v>
       </c>
       <c r="I16" t="n">
         <v>0</v>
       </c>
       <c r="J16" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="K16" t="n">
-        <v>6.38</v>
+        <v>6.22</v>
       </c>
       <c r="L16" t="n">
-        <v>0.62</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="M16" t="n">
-        <v>60.12</v>
+        <v>56.67</v>
       </c>
       <c r="N16" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="O16" t="n">
-        <v>2.88</v>
+        <v>2.78</v>
       </c>
       <c r="P16" t="n">
-        <v>12.12</v>
+        <v>11.89</v>
       </c>
       <c r="Q16" t="n">
-        <v>9.5</v>
+        <v>9.44</v>
       </c>
       <c r="R16" t="n">
-        <v>5.62</v>
+        <v>5.44</v>
       </c>
       <c r="S16" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="T16" t="n">
-        <v>2.5</v>
+        <v>2.44</v>
       </c>
       <c r="U16" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="V16" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="W16" t="n">
         <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>54.88</v>
+        <v>53.44</v>
       </c>
       <c r="Y16" t="n">
         <v>0</v>
       </c>
       <c r="Z16" t="n">
-        <v>18.25</v>
+        <v>17.11</v>
       </c>
       <c r="AA16" t="n">
-        <v>11.25</v>
+        <v>10.33</v>
       </c>
       <c r="AB16" t="n">
-        <v>7</v>
+        <v>6.78</v>
       </c>
       <c r="AC16" t="n">
-        <v>19.88</v>
+        <v>19.44</v>
       </c>
       <c r="AD16" t="n">
-        <v>2.08</v>
+        <v>1.96</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AF16" t="n">
         <v>0.1</v>
@@ -7192,70 +7192,70 @@
         <v>2.9</v>
       </c>
       <c r="BG16" t="n">
-        <v>2.44</v>
+        <v>2.42</v>
       </c>
       <c r="BH16" t="n">
-        <v>9.609999999999999</v>
+        <v>9.529999999999999</v>
       </c>
       <c r="BI16" t="n">
-        <v>2.44</v>
+        <v>2.42</v>
       </c>
       <c r="BJ16" t="n">
-        <v>0.44</v>
+        <v>0.47</v>
       </c>
       <c r="BK16" t="n">
-        <v>0.39</v>
+        <v>0.37</v>
       </c>
       <c r="BL16" t="n">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="BM16" t="n">
-        <v>0.44</v>
+        <v>0.42</v>
       </c>
       <c r="BN16" t="n">
-        <v>1.61</v>
+        <v>1.58</v>
       </c>
       <c r="BO16" t="n">
-        <v>0.83</v>
+        <v>0.84</v>
       </c>
       <c r="BP16" t="n">
-        <v>4.83</v>
+        <v>4.74</v>
       </c>
       <c r="BQ16" t="n">
-        <v>4.78</v>
+        <v>4.79</v>
       </c>
       <c r="BR16" t="n">
-        <v>94.44</v>
+        <v>94.73999999999999</v>
       </c>
       <c r="BS16" t="n">
-        <v>77.78</v>
+        <v>78.95</v>
       </c>
       <c r="BT16" t="n">
-        <v>33.33</v>
+        <v>31.58</v>
       </c>
       <c r="BU16" t="n">
-        <v>22.22</v>
+        <v>21.05</v>
       </c>
       <c r="BV16" t="n">
-        <v>16.67</v>
+        <v>15.79</v>
       </c>
       <c r="BW16" t="n">
         <v>0</v>
       </c>
       <c r="BX16" t="n">
-        <v>44.44</v>
+        <v>42.11</v>
       </c>
       <c r="BY16" t="n">
         <v>1.35</v>
       </c>
       <c r="BZ16" t="n">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="CA16" t="n">
-        <v>4.22</v>
+        <v>4.26</v>
       </c>
       <c r="CB16" t="n">
-        <v>4.37</v>
+        <v>4.45</v>
       </c>
       <c r="CC16" t="n">
         <v>1.87</v>
@@ -7267,10 +7267,10 @@
         <v>1.3</v>
       </c>
       <c r="CF16" t="n">
-        <v>2.49</v>
+        <v>2.48</v>
       </c>
       <c r="CG16" t="n">
-        <v>3.2</v>
+        <v>3.21</v>
       </c>
       <c r="CH16" t="n">
         <v>1.51</v>
@@ -7282,37 +7282,37 @@
         <v>1.82</v>
       </c>
       <c r="CK16" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="CL16" t="n">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="CM16" t="n">
         <v>2.5</v>
       </c>
       <c r="CN16" t="n">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="CO16" t="n">
         <v>1.22</v>
       </c>
       <c r="CP16" t="n">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="CQ16" t="n">
-        <v>2.77</v>
+        <v>2.76</v>
       </c>
       <c r="CR16" t="n">
         <v>1.36</v>
       </c>
       <c r="CS16" t="n">
-        <v>2.64</v>
+        <v>2.62</v>
       </c>
       <c r="CT16" t="n">
         <v>3.2</v>
       </c>
       <c r="CU16" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="CV16" t="n">
         <v>2.04</v>
@@ -7330,91 +7330,91 @@
         <v>2.35</v>
       </c>
       <c r="DA16" t="n">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="DB16" t="n">
         <v>1.25</v>
       </c>
       <c r="DC16" t="n">
-        <v>1.8</v>
+        <v>1.78</v>
       </c>
       <c r="DD16" t="n">
-        <v>2.94</v>
+        <v>2.91</v>
       </c>
       <c r="DE16" t="n">
-        <v>0.22</v>
+        <v>0.21</v>
       </c>
       <c r="DF16" t="n">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="DG16" t="n">
-        <v>3.06</v>
+        <v>3.05</v>
       </c>
       <c r="DH16" t="n">
-        <v>108.56</v>
+        <v>107.95</v>
       </c>
       <c r="DI16" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="DJ16" t="n">
-        <v>2.17</v>
+        <v>2.1</v>
       </c>
       <c r="DK16" t="n">
-        <v>5.78</v>
+        <v>5.74</v>
       </c>
       <c r="DL16" t="n">
-        <v>0.61</v>
+        <v>0.58</v>
       </c>
       <c r="DM16" t="n">
-        <v>55.33</v>
+        <v>53.95</v>
       </c>
       <c r="DN16" t="n">
-        <v>0.66</v>
+        <v>0.63</v>
       </c>
       <c r="DO16" t="n">
-        <v>2.72</v>
+        <v>2.69</v>
       </c>
       <c r="DP16" t="n">
-        <v>12.72</v>
+        <v>12.58</v>
       </c>
       <c r="DQ16" t="n">
         <v>9</v>
       </c>
       <c r="DR16" t="n">
-        <v>5.83</v>
+        <v>5.73</v>
       </c>
       <c r="DS16" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DT16" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DU16" t="n">
         <v>0</v>
       </c>
       <c r="DV16" t="n">
-        <v>54.34</v>
+        <v>53.68</v>
       </c>
       <c r="DW16" t="n">
         <v>0</v>
       </c>
       <c r="DX16" t="n">
-        <v>15.72</v>
+        <v>15.32</v>
       </c>
       <c r="DY16" t="n">
-        <v>10</v>
+        <v>9.630000000000001</v>
       </c>
       <c r="DZ16" t="n">
-        <v>5.72</v>
+        <v>5.69</v>
       </c>
       <c r="EA16" t="n">
-        <v>20.06</v>
+        <v>19.84</v>
       </c>
       <c r="EB16" t="n">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="EC16" t="n">
-        <v>2.17</v>
+        <v>2.1</v>
       </c>
     </row>
     <row r="17">
@@ -7424,13 +7424,13 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C17" t="n">
         <v>9</v>
       </c>
       <c r="D17" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
@@ -7514,139 +7514,139 @@
         <v>1.33</v>
       </c>
       <c r="AF17" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AH17" t="n">
-        <v>2.33</v>
+        <v>2.3</v>
       </c>
       <c r="AI17" t="n">
-        <v>90</v>
+        <v>93.3</v>
       </c>
       <c r="AJ17" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="AK17" t="n">
         <v>2</v>
       </c>
       <c r="AL17" t="n">
-        <v>4.44</v>
+        <v>4.3</v>
       </c>
       <c r="AM17" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="AN17" t="n">
-        <v>49.11</v>
+        <v>48.3</v>
       </c>
       <c r="AO17" t="n">
-        <v>0.44</v>
+        <v>0.5</v>
       </c>
       <c r="AP17" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AQ17" t="n">
-        <v>13.22</v>
+        <v>12.8</v>
       </c>
       <c r="AR17" t="n">
-        <v>10.11</v>
+        <v>10.1</v>
       </c>
       <c r="AS17" t="n">
-        <v>10</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AT17" t="n">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="AU17" t="n">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="AV17" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="AW17" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="AX17" t="n">
         <v>0</v>
       </c>
       <c r="AY17" t="n">
-        <v>47.89</v>
+        <v>48.9</v>
       </c>
       <c r="AZ17" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="BA17" t="n">
-        <v>10.67</v>
+        <v>10.5</v>
       </c>
       <c r="BB17" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BC17" t="n">
-        <v>3.67</v>
+        <v>3.3</v>
       </c>
       <c r="BD17" t="n">
-        <v>19.33</v>
+        <v>20.1</v>
       </c>
       <c r="BE17" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="BF17" t="n">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="BG17" t="n">
-        <v>2.78</v>
+        <v>2.74</v>
       </c>
       <c r="BH17" t="n">
-        <v>10.17</v>
+        <v>10.05</v>
       </c>
       <c r="BI17" t="n">
-        <v>2.78</v>
+        <v>2.74</v>
       </c>
       <c r="BJ17" t="n">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="BK17" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.53</v>
       </c>
       <c r="BL17" t="n">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="BM17" t="n">
-        <v>0.78</v>
+        <v>0.74</v>
       </c>
       <c r="BN17" t="n">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="BO17" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="BP17" t="n">
-        <v>3.67</v>
+        <v>3.63</v>
       </c>
       <c r="BQ17" t="n">
-        <v>5.78</v>
+        <v>5.74</v>
       </c>
       <c r="BR17" t="n">
-        <v>88.89</v>
+        <v>89.47</v>
       </c>
       <c r="BS17" t="n">
-        <v>83.33</v>
+        <v>84.20999999999999</v>
       </c>
       <c r="BT17" t="n">
-        <v>44.44</v>
+        <v>42.11</v>
       </c>
       <c r="BU17" t="n">
-        <v>38.89</v>
+        <v>36.84</v>
       </c>
       <c r="BV17" t="n">
-        <v>22.22</v>
+        <v>21.05</v>
       </c>
       <c r="BW17" t="n">
         <v>0</v>
       </c>
       <c r="BX17" t="n">
-        <v>66.67</v>
+        <v>63.16</v>
       </c>
       <c r="BY17" t="n">
         <v>3.02</v>
@@ -7655,34 +7655,34 @@
         <v>3.28</v>
       </c>
       <c r="CA17" t="n">
-        <v>3.67</v>
+        <v>3.74</v>
       </c>
       <c r="CB17" t="n">
-        <v>3.7</v>
+        <v>3.81</v>
       </c>
       <c r="CC17" t="n">
-        <v>3.74</v>
+        <v>4.18</v>
       </c>
       <c r="CD17" t="n">
-        <v>4.12</v>
+        <v>4.74</v>
       </c>
       <c r="CE17" t="n">
         <v>1.3</v>
       </c>
       <c r="CF17" t="n">
-        <v>2.47</v>
+        <v>2.46</v>
       </c>
       <c r="CG17" t="n">
         <v>3.31</v>
       </c>
       <c r="CH17" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="CI17" t="n">
-        <v>2.2</v>
+        <v>2.19</v>
       </c>
       <c r="CJ17" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="CK17" t="n">
         <v>1.43</v>
@@ -7691,7 +7691,7 @@
         <v>1.78</v>
       </c>
       <c r="CM17" t="n">
-        <v>2.69</v>
+        <v>2.68</v>
       </c>
       <c r="CN17" t="n">
         <v>2.07</v>
@@ -7703,13 +7703,13 @@
         <v>1.71</v>
       </c>
       <c r="CQ17" t="n">
-        <v>2.75</v>
+        <v>2.73</v>
       </c>
       <c r="CR17" t="n">
         <v>1.35</v>
       </c>
       <c r="CS17" t="n">
-        <v>2.58</v>
+        <v>2.56</v>
       </c>
       <c r="CT17" t="n">
         <v>3.23</v>
@@ -7718,10 +7718,10 @@
         <v>1.53</v>
       </c>
       <c r="CV17" t="n">
-        <v>2.35</v>
+        <v>2.33</v>
       </c>
       <c r="CW17" t="n">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="CX17" t="n">
         <v>1.52</v>
@@ -7736,88 +7736,88 @@
         <v>2.06</v>
       </c>
       <c r="DB17" t="n">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="DC17" t="n">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="DD17" t="n">
-        <v>2.86</v>
+        <v>2.83</v>
       </c>
       <c r="DE17" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="DF17" t="n">
         <v>1.16</v>
       </c>
       <c r="DG17" t="n">
-        <v>2.22</v>
+        <v>2.21</v>
       </c>
       <c r="DH17" t="n">
-        <v>93.84</v>
+        <v>95.37</v>
       </c>
       <c r="DI17" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="DJ17" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="DK17" t="n">
-        <v>4.11</v>
+        <v>4.05</v>
       </c>
       <c r="DL17" t="n">
         <v>0.16</v>
       </c>
       <c r="DM17" t="n">
-        <v>44.56</v>
+        <v>44.37</v>
       </c>
       <c r="DN17" t="n">
-        <v>0.5</v>
+        <v>0.53</v>
       </c>
       <c r="DO17" t="n">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="DP17" t="n">
-        <v>11.83</v>
+        <v>11.68</v>
       </c>
       <c r="DQ17" t="n">
-        <v>11.56</v>
+        <v>11.47</v>
       </c>
       <c r="DR17" t="n">
-        <v>10.34</v>
+        <v>9.9</v>
       </c>
       <c r="DS17" t="n">
-        <v>0.28</v>
+        <v>0.26</v>
       </c>
       <c r="DT17" t="n">
-        <v>0.28</v>
+        <v>0.26</v>
       </c>
       <c r="DU17" t="n">
         <v>0</v>
       </c>
       <c r="DV17" t="n">
-        <v>47</v>
+        <v>47.58</v>
       </c>
       <c r="DW17" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DX17" t="n">
-        <v>11</v>
+        <v>10.89</v>
       </c>
       <c r="DY17" t="n">
-        <v>7.06</v>
+        <v>7.16</v>
       </c>
       <c r="DZ17" t="n">
-        <v>3.94</v>
+        <v>3.74</v>
       </c>
       <c r="EA17" t="n">
-        <v>20.72</v>
+        <v>21.05</v>
       </c>
       <c r="EB17" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="EC17" t="n">
-        <v>1.56</v>
+        <v>1.58</v>
       </c>
     </row>
   </sheetData>

--- a/data/teams/leagues/Averages_Belgium_Pro_League_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Belgium_Pro_League_2025-2026.xlsx
@@ -1379,13 +1379,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C2" t="n">
         <v>10</v>
       </c>
       <c r="D2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
@@ -1469,52 +1469,52 @@
         <v>1.2</v>
       </c>
       <c r="AF2" t="n">
-        <v>0</v>
+        <v>0.11</v>
       </c>
       <c r="AG2" t="n">
-        <v>1</v>
+        <v>1.22</v>
       </c>
       <c r="AH2" t="n">
-        <v>2.5</v>
+        <v>2.67</v>
       </c>
       <c r="AI2" t="n">
-        <v>108.88</v>
+        <v>105.56</v>
       </c>
       <c r="AJ2" t="n">
-        <v>0.12</v>
+        <v>0.22</v>
       </c>
       <c r="AK2" t="n">
-        <v>2.62</v>
+        <v>2.89</v>
       </c>
       <c r="AL2" t="n">
-        <v>4.62</v>
+        <v>4.89</v>
       </c>
       <c r="AM2" t="n">
-        <v>0.62</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AN2" t="n">
-        <v>53.38</v>
+        <v>51.56</v>
       </c>
       <c r="AO2" t="n">
-        <v>1.5</v>
+        <v>1.56</v>
       </c>
       <c r="AP2" t="n">
-        <v>2.12</v>
+        <v>2.22</v>
       </c>
       <c r="AQ2" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AR2" t="n">
-        <v>11.38</v>
+        <v>12.44</v>
       </c>
       <c r="AS2" t="n">
-        <v>7.12</v>
+        <v>7.44</v>
       </c>
       <c r="AT2" t="n">
-        <v>1</v>
+        <v>0.89</v>
       </c>
       <c r="AU2" t="n">
-        <v>0.75</v>
+        <v>0.89</v>
       </c>
       <c r="AV2" t="n">
         <v>0</v>
@@ -1526,82 +1526,82 @@
         <v>0</v>
       </c>
       <c r="AY2" t="n">
-        <v>49.88</v>
+        <v>49</v>
       </c>
       <c r="AZ2" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="BA2" t="n">
-        <v>12.62</v>
+        <v>12.44</v>
       </c>
       <c r="BB2" t="n">
-        <v>9</v>
+        <v>8.890000000000001</v>
       </c>
       <c r="BC2" t="n">
-        <v>3.62</v>
+        <v>3.56</v>
       </c>
       <c r="BD2" t="n">
-        <v>23.12</v>
+        <v>22.33</v>
       </c>
       <c r="BE2" t="n">
-        <v>1.44</v>
+        <v>1.41</v>
       </c>
       <c r="BF2" t="n">
-        <v>2.38</v>
+        <v>2.67</v>
       </c>
       <c r="BG2" t="n">
-        <v>2.83</v>
+        <v>2.79</v>
       </c>
       <c r="BH2" t="n">
-        <v>10.17</v>
+        <v>10.42</v>
       </c>
       <c r="BI2" t="n">
-        <v>2.83</v>
+        <v>2.79</v>
       </c>
       <c r="BJ2" t="n">
-        <v>0.67</v>
+        <v>0.63</v>
       </c>
       <c r="BK2" t="n">
-        <v>0.89</v>
+        <v>0.95</v>
       </c>
       <c r="BL2" t="n">
-        <v>0.67</v>
+        <v>0.63</v>
       </c>
       <c r="BM2" t="n">
-        <v>0.61</v>
+        <v>0.58</v>
       </c>
       <c r="BN2" t="n">
-        <v>1.28</v>
+        <v>1.21</v>
       </c>
       <c r="BO2" t="n">
-        <v>1.56</v>
+        <v>1.58</v>
       </c>
       <c r="BP2" t="n">
-        <v>4.56</v>
+        <v>4.63</v>
       </c>
       <c r="BQ2" t="n">
-        <v>5.61</v>
+        <v>5.74</v>
       </c>
       <c r="BR2" t="n">
-        <v>88.89</v>
+        <v>89.47</v>
       </c>
       <c r="BS2" t="n">
-        <v>88.89</v>
+        <v>89.47</v>
       </c>
       <c r="BT2" t="n">
-        <v>50</v>
+        <v>47.37</v>
       </c>
       <c r="BU2" t="n">
-        <v>27.78</v>
+        <v>26.32</v>
       </c>
       <c r="BV2" t="n">
-        <v>22.22</v>
+        <v>21.05</v>
       </c>
       <c r="BW2" t="n">
-        <v>5.56</v>
+        <v>5.26</v>
       </c>
       <c r="BX2" t="n">
-        <v>66.67</v>
+        <v>63.16</v>
       </c>
       <c r="BY2" t="n">
         <v>2.24</v>
@@ -1610,46 +1610,46 @@
         <v>2.3</v>
       </c>
       <c r="CA2" t="n">
-        <v>3.56</v>
+        <v>3.55</v>
       </c>
       <c r="CB2" t="n">
-        <v>3.72</v>
+        <v>3.7</v>
       </c>
       <c r="CC2" t="n">
-        <v>3.51</v>
+        <v>3.41</v>
       </c>
       <c r="CD2" t="n">
-        <v>3.69</v>
+        <v>3.6</v>
       </c>
       <c r="CE2" t="n">
         <v>1.31</v>
       </c>
       <c r="CF2" t="n">
-        <v>2.51</v>
+        <v>2.52</v>
       </c>
       <c r="CG2" t="n">
-        <v>3.16</v>
+        <v>3.17</v>
       </c>
       <c r="CH2" t="n">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="CI2" t="n">
-        <v>2.19</v>
+        <v>2.18</v>
       </c>
       <c r="CJ2" t="n">
         <v>1.66</v>
       </c>
       <c r="CK2" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="CL2" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="CM2" t="n">
-        <v>2.58</v>
+        <v>2.59</v>
       </c>
       <c r="CN2" t="n">
-        <v>2.01</v>
+        <v>2.02</v>
       </c>
       <c r="CO2" t="n">
         <v>1.22</v>
@@ -1673,7 +1673,7 @@
         <v>1.52</v>
       </c>
       <c r="CV2" t="n">
-        <v>2.32</v>
+        <v>2.31</v>
       </c>
       <c r="CW2" t="n">
         <v>1.66</v>
@@ -1682,97 +1682,97 @@
         <v>1.5</v>
       </c>
       <c r="CY2" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="CZ2" t="n">
         <v>2.54</v>
       </c>
       <c r="DA2" t="n">
-        <v>2.07</v>
+        <v>2.08</v>
       </c>
       <c r="DB2" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="DC2" t="n">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="DD2" t="n">
-        <v>2.82</v>
+        <v>2.86</v>
       </c>
       <c r="DE2" t="n">
-        <v>0</v>
+        <v>0.05</v>
       </c>
       <c r="DF2" t="n">
-        <v>0.89</v>
+        <v>1</v>
       </c>
       <c r="DG2" t="n">
-        <v>2.78</v>
+        <v>2.84</v>
       </c>
       <c r="DH2" t="n">
-        <v>109.06</v>
+        <v>107.48</v>
       </c>
       <c r="DI2" t="n">
-        <v>0.05</v>
+        <v>0.1</v>
       </c>
       <c r="DJ2" t="n">
-        <v>1.83</v>
+        <v>2</v>
       </c>
       <c r="DK2" t="n">
-        <v>4.83</v>
+        <v>4.95</v>
       </c>
       <c r="DL2" t="n">
-        <v>0.5</v>
+        <v>0.48</v>
       </c>
       <c r="DM2" t="n">
-        <v>51.56</v>
+        <v>50.79</v>
       </c>
       <c r="DN2" t="n">
-        <v>0.89</v>
+        <v>0.95</v>
       </c>
       <c r="DO2" t="n">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="DP2" t="n">
-        <v>10.44</v>
+        <v>10.79</v>
       </c>
       <c r="DQ2" t="n">
-        <v>12.61</v>
+        <v>13.05</v>
       </c>
       <c r="DR2" t="n">
-        <v>6.89</v>
+        <v>7.05</v>
       </c>
       <c r="DS2" t="n">
-        <v>0.28</v>
+        <v>0.26</v>
       </c>
       <c r="DT2" t="n">
-        <v>0.28</v>
+        <v>0.26</v>
       </c>
       <c r="DU2" t="n">
         <v>0</v>
       </c>
       <c r="DV2" t="n">
-        <v>51.61</v>
+        <v>51.11</v>
       </c>
       <c r="DW2" t="n">
         <v>0.05</v>
       </c>
       <c r="DX2" t="n">
-        <v>14.11</v>
+        <v>13.95</v>
       </c>
       <c r="DY2" t="n">
-        <v>9.67</v>
+        <v>9.58</v>
       </c>
       <c r="DZ2" t="n">
-        <v>4.44</v>
+        <v>4.37</v>
       </c>
       <c r="EA2" t="n">
-        <v>23.72</v>
+        <v>23.31</v>
       </c>
       <c r="EB2" t="n">
-        <v>1.58</v>
+        <v>1.56</v>
       </c>
       <c r="EC2" t="n">
-        <v>1.72</v>
+        <v>1.9</v>
       </c>
     </row>
     <row r="3">
@@ -2016,7 +2016,7 @@
         <v>4.44</v>
       </c>
       <c r="CB3" t="n">
-        <v>4.72</v>
+        <v>4.73</v>
       </c>
       <c r="CC3" t="n">
         <v>1.7</v>
@@ -2091,7 +2091,7 @@
         <v>2.5</v>
       </c>
       <c r="DA3" t="n">
-        <v>2.01</v>
+        <v>2.02</v>
       </c>
       <c r="DB3" t="n">
         <v>1.18</v>
@@ -2822,13 +2822,13 @@
         <v>3.67</v>
       </c>
       <c r="CB5" t="n">
-        <v>3.85</v>
+        <v>3.86</v>
       </c>
       <c r="CC5" t="n">
         <v>3.75</v>
       </c>
       <c r="CD5" t="n">
-        <v>4.07</v>
+        <v>4.12</v>
       </c>
       <c r="CE5" t="n">
         <v>1.3</v>
@@ -2879,13 +2879,13 @@
         <v>3.27</v>
       </c>
       <c r="CU5" t="n">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="CV5" t="n">
         <v>2.33</v>
       </c>
       <c r="CW5" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="CX5" t="n">
         <v>1.52</v>
@@ -2897,7 +2897,7 @@
         <v>2.49</v>
       </c>
       <c r="DA5" t="n">
-        <v>2.04</v>
+        <v>2.05</v>
       </c>
       <c r="DB5" t="n">
         <v>1.23</v>
@@ -3147,16 +3147,16 @@
         <v>14.9</v>
       </c>
       <c r="BB6" t="n">
-        <v>9.199999999999999</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="BC6" t="n">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="BD6" t="n">
         <v>19.7</v>
       </c>
       <c r="BE6" t="n">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="BF6" t="n">
         <v>1.7</v>
@@ -3372,16 +3372,16 @@
         <v>16.47</v>
       </c>
       <c r="DY6" t="n">
-        <v>10.73</v>
+        <v>10.79</v>
       </c>
       <c r="DZ6" t="n">
-        <v>5.74</v>
+        <v>5.69</v>
       </c>
       <c r="EA6" t="n">
         <v>20.26</v>
       </c>
       <c r="EB6" t="n">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="EC6" t="n">
         <v>1.26</v>
@@ -3394,13 +3394,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C7" t="n">
         <v>9</v>
       </c>
       <c r="D7" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E7" t="n">
         <v>0.11</v>
@@ -3484,52 +3484,52 @@
         <v>2.44</v>
       </c>
       <c r="AF7" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.56</v>
+        <v>1.5</v>
       </c>
       <c r="AH7" t="n">
-        <v>3</v>
+        <v>3.3</v>
       </c>
       <c r="AI7" t="n">
-        <v>81.33</v>
+        <v>84</v>
       </c>
       <c r="AJ7" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="AK7" t="n">
-        <v>2.33</v>
+        <v>2.3</v>
       </c>
       <c r="AL7" t="n">
-        <v>5.56</v>
+        <v>5.6</v>
       </c>
       <c r="AM7" t="n">
-        <v>0.44</v>
+        <v>0.4</v>
       </c>
       <c r="AN7" t="n">
-        <v>41.56</v>
+        <v>42.4</v>
       </c>
       <c r="AO7" t="n">
-        <v>0.78</v>
+        <v>0.8</v>
       </c>
       <c r="AP7" t="n">
-        <v>2.56</v>
+        <v>2.3</v>
       </c>
       <c r="AQ7" t="n">
-        <v>9.779999999999999</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="AR7" t="n">
-        <v>10.33</v>
+        <v>10.5</v>
       </c>
       <c r="AS7" t="n">
-        <v>8.779999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="AT7" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="AU7" t="n">
-        <v>1.56</v>
+        <v>1.4</v>
       </c>
       <c r="AV7" t="n">
         <v>0</v>
@@ -3541,82 +3541,82 @@
         <v>0</v>
       </c>
       <c r="AY7" t="n">
-        <v>47.33</v>
+        <v>47.9</v>
       </c>
       <c r="AZ7" t="n">
         <v>0</v>
       </c>
       <c r="BA7" t="n">
-        <v>10.78</v>
+        <v>10.7</v>
       </c>
       <c r="BB7" t="n">
-        <v>6.22</v>
+        <v>6.4</v>
       </c>
       <c r="BC7" t="n">
-        <v>4.56</v>
+        <v>4.3</v>
       </c>
       <c r="BD7" t="n">
-        <v>20.22</v>
+        <v>20.3</v>
       </c>
       <c r="BE7" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="BF7" t="n">
-        <v>2.33</v>
+        <v>2.3</v>
       </c>
       <c r="BG7" t="n">
-        <v>2.44</v>
+        <v>2.37</v>
       </c>
       <c r="BH7" t="n">
-        <v>11.72</v>
+        <v>11.53</v>
       </c>
       <c r="BI7" t="n">
-        <v>2.44</v>
+        <v>2.37</v>
       </c>
       <c r="BJ7" t="n">
-        <v>0.44</v>
+        <v>0.47</v>
       </c>
       <c r="BK7" t="n">
-        <v>0.5</v>
+        <v>0.47</v>
       </c>
       <c r="BL7" t="n">
-        <v>0.67</v>
+        <v>0.63</v>
       </c>
       <c r="BM7" t="n">
-        <v>0.83</v>
+        <v>0.79</v>
       </c>
       <c r="BN7" t="n">
-        <v>1.5</v>
+        <v>1.42</v>
       </c>
       <c r="BO7" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.95</v>
       </c>
       <c r="BP7" t="n">
-        <v>5.39</v>
+        <v>5.16</v>
       </c>
       <c r="BQ7" t="n">
-        <v>6.33</v>
+        <v>6.37</v>
       </c>
       <c r="BR7" t="n">
-        <v>94.44</v>
+        <v>94.73999999999999</v>
       </c>
       <c r="BS7" t="n">
-        <v>72.22</v>
+        <v>68.42</v>
       </c>
       <c r="BT7" t="n">
-        <v>38.89</v>
+        <v>36.84</v>
       </c>
       <c r="BU7" t="n">
-        <v>27.78</v>
+        <v>26.32</v>
       </c>
       <c r="BV7" t="n">
-        <v>11.11</v>
+        <v>10.53</v>
       </c>
       <c r="BW7" t="n">
         <v>0</v>
       </c>
       <c r="BX7" t="n">
-        <v>66.67</v>
+        <v>63.16</v>
       </c>
       <c r="BY7" t="n">
         <v>2.9</v>
@@ -3625,16 +3625,16 @@
         <v>3.11</v>
       </c>
       <c r="CA7" t="n">
-        <v>3.68</v>
+        <v>3.7</v>
       </c>
       <c r="CB7" t="n">
-        <v>3.81</v>
+        <v>3.82</v>
       </c>
       <c r="CC7" t="n">
-        <v>3.5</v>
+        <v>3.59</v>
       </c>
       <c r="CD7" t="n">
-        <v>4.04</v>
+        <v>4.12</v>
       </c>
       <c r="CE7" t="n">
         <v>1.3</v>
@@ -3661,7 +3661,7 @@
         <v>1.76</v>
       </c>
       <c r="CM7" t="n">
-        <v>2.76</v>
+        <v>2.77</v>
       </c>
       <c r="CN7" t="n">
         <v>2.11</v>
@@ -3673,13 +3673,13 @@
         <v>1.68</v>
       </c>
       <c r="CQ7" t="n">
-        <v>2.69</v>
+        <v>2.68</v>
       </c>
       <c r="CR7" t="n">
         <v>1.36</v>
       </c>
       <c r="CS7" t="n">
-        <v>2.54</v>
+        <v>2.52</v>
       </c>
       <c r="CT7" t="n">
         <v>3.21</v>
@@ -3688,7 +3688,7 @@
         <v>1.55</v>
       </c>
       <c r="CV7" t="n">
-        <v>2.38</v>
+        <v>2.39</v>
       </c>
       <c r="CW7" t="n">
         <v>1.63</v>
@@ -3697,97 +3697,97 @@
         <v>1.49</v>
       </c>
       <c r="CY7" t="n">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="CZ7" t="n">
         <v>2.56</v>
       </c>
       <c r="DA7" t="n">
-        <v>2.13</v>
+        <v>2.14</v>
       </c>
       <c r="DB7" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="DC7" t="n">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="DD7" t="n">
-        <v>2.8</v>
+        <v>2.79</v>
       </c>
       <c r="DE7" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DF7" t="n">
-        <v>1.56</v>
+        <v>1.53</v>
       </c>
       <c r="DG7" t="n">
-        <v>2.78</v>
+        <v>2.95</v>
       </c>
       <c r="DH7" t="n">
-        <v>85.44</v>
+        <v>86.63</v>
       </c>
       <c r="DI7" t="n">
-        <v>0.22</v>
+        <v>0.21</v>
       </c>
       <c r="DJ7" t="n">
-        <v>2.38</v>
+        <v>2.37</v>
       </c>
       <c r="DK7" t="n">
-        <v>5.06</v>
+        <v>5.11</v>
       </c>
       <c r="DL7" t="n">
-        <v>0.28</v>
+        <v>0.26</v>
       </c>
       <c r="DM7" t="n">
-        <v>45.78</v>
+        <v>46</v>
       </c>
       <c r="DN7" t="n">
         <v>0.84</v>
       </c>
       <c r="DO7" t="n">
-        <v>2.28</v>
+        <v>2.16</v>
       </c>
       <c r="DP7" t="n">
-        <v>10.17</v>
+        <v>10.11</v>
       </c>
       <c r="DQ7" t="n">
-        <v>10.83</v>
+        <v>10.89</v>
       </c>
       <c r="DR7" t="n">
-        <v>9.609999999999999</v>
+        <v>9.470000000000001</v>
       </c>
       <c r="DS7" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DT7" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DU7" t="n">
         <v>0</v>
       </c>
       <c r="DV7" t="n">
-        <v>48.61</v>
+        <v>48.84</v>
       </c>
       <c r="DW7" t="n">
         <v>0</v>
       </c>
       <c r="DX7" t="n">
-        <v>10.5</v>
+        <v>10.47</v>
       </c>
       <c r="DY7" t="n">
-        <v>6.44</v>
+        <v>6.53</v>
       </c>
       <c r="DZ7" t="n">
-        <v>4.06</v>
+        <v>3.95</v>
       </c>
       <c r="EA7" t="n">
-        <v>20.94</v>
+        <v>20.95</v>
       </c>
       <c r="EB7" t="n">
         <v>1.28</v>
       </c>
       <c r="EC7" t="n">
-        <v>2.38</v>
+        <v>2.37</v>
       </c>
     </row>
     <row r="8">
@@ -3863,7 +3863,7 @@
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>50.5</v>
+        <v>50.4</v>
       </c>
       <c r="Y8" t="n">
         <v>0</v>
@@ -4169,7 +4169,7 @@
         <v>0</v>
       </c>
       <c r="DV8" t="n">
-        <v>49</v>
+        <v>48.95</v>
       </c>
       <c r="DW8" t="n">
         <v>0.05</v>
@@ -4200,61 +4200,61 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C9" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D9" t="n">
         <v>9</v>
       </c>
       <c r="E9" t="n">
-        <v>0.33</v>
+        <v>0.3</v>
       </c>
       <c r="F9" t="n">
-        <v>2.33</v>
+        <v>2.4</v>
       </c>
       <c r="G9" t="n">
-        <v>2.22</v>
+        <v>2.4</v>
       </c>
       <c r="H9" t="n">
-        <v>77.78</v>
+        <v>79.8</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>2.89</v>
+        <v>3.1</v>
       </c>
       <c r="K9" t="n">
-        <v>4</v>
+        <v>4.4</v>
       </c>
       <c r="L9" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.5</v>
       </c>
       <c r="M9" t="n">
-        <v>37.78</v>
+        <v>39.3</v>
       </c>
       <c r="N9" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.7</v>
       </c>
       <c r="O9" t="n">
-        <v>1.78</v>
+        <v>1.9</v>
       </c>
       <c r="P9" t="n">
-        <v>16.11</v>
+        <v>16.6</v>
       </c>
       <c r="Q9" t="n">
-        <v>11.78</v>
+        <v>12.3</v>
       </c>
       <c r="R9" t="n">
-        <v>8.109999999999999</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="S9" t="n">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="T9" t="n">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="U9" t="n">
         <v>0</v>
@@ -4266,28 +4266,28 @@
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>44.44</v>
+        <v>45.8</v>
       </c>
       <c r="Y9" t="n">
         <v>0</v>
       </c>
       <c r="Z9" t="n">
-        <v>13.89</v>
+        <v>14.3</v>
       </c>
       <c r="AA9" t="n">
-        <v>9.220000000000001</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="AB9" t="n">
-        <v>4.67</v>
+        <v>4.6</v>
       </c>
       <c r="AC9" t="n">
-        <v>17.78</v>
+        <v>18.8</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.47</v>
+        <v>1.51</v>
       </c>
       <c r="AE9" t="n">
-        <v>2.89</v>
+        <v>3.1</v>
       </c>
       <c r="AF9" t="n">
         <v>0</v>
@@ -4371,70 +4371,70 @@
         <v>3</v>
       </c>
       <c r="BG9" t="n">
-        <v>2.56</v>
+        <v>2.53</v>
       </c>
       <c r="BH9" t="n">
-        <v>9.609999999999999</v>
+        <v>9.890000000000001</v>
       </c>
       <c r="BI9" t="n">
-        <v>2.56</v>
+        <v>2.53</v>
       </c>
       <c r="BJ9" t="n">
-        <v>0.78</v>
+        <v>0.74</v>
       </c>
       <c r="BK9" t="n">
-        <v>0.39</v>
+        <v>0.47</v>
       </c>
       <c r="BL9" t="n">
-        <v>0.78</v>
+        <v>0.74</v>
       </c>
       <c r="BM9" t="n">
-        <v>0.61</v>
+        <v>0.58</v>
       </c>
       <c r="BN9" t="n">
-        <v>1.39</v>
+        <v>1.32</v>
       </c>
       <c r="BO9" t="n">
-        <v>1.17</v>
+        <v>1.21</v>
       </c>
       <c r="BP9" t="n">
-        <v>4.83</v>
+        <v>4.89</v>
       </c>
       <c r="BQ9" t="n">
-        <v>4.78</v>
+        <v>4.95</v>
       </c>
       <c r="BR9" t="n">
         <v>100</v>
       </c>
       <c r="BS9" t="n">
-        <v>77.78</v>
+        <v>78.95</v>
       </c>
       <c r="BT9" t="n">
-        <v>50</v>
+        <v>47.37</v>
       </c>
       <c r="BU9" t="n">
-        <v>22.22</v>
+        <v>21.05</v>
       </c>
       <c r="BV9" t="n">
-        <v>5.56</v>
+        <v>5.26</v>
       </c>
       <c r="BW9" t="n">
         <v>0</v>
       </c>
       <c r="BX9" t="n">
-        <v>55.56</v>
+        <v>52.63</v>
       </c>
       <c r="BY9" t="n">
-        <v>2.97</v>
+        <v>2.94</v>
       </c>
       <c r="BZ9" t="n">
-        <v>3.03</v>
+        <v>2.99</v>
       </c>
       <c r="CA9" t="n">
-        <v>3.55</v>
+        <v>3.54</v>
       </c>
       <c r="CB9" t="n">
-        <v>3.58</v>
+        <v>3.56</v>
       </c>
       <c r="CC9" t="n">
         <v>4.22</v>
@@ -4446,10 +4446,10 @@
         <v>1.36</v>
       </c>
       <c r="CF9" t="n">
-        <v>2.7</v>
+        <v>2.69</v>
       </c>
       <c r="CG9" t="n">
-        <v>3.01</v>
+        <v>3.03</v>
       </c>
       <c r="CH9" t="n">
         <v>1.43</v>
@@ -4458,16 +4458,16 @@
         <v>2</v>
       </c>
       <c r="CJ9" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="CK9" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="CL9" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="CM9" t="n">
-        <v>2.57</v>
+        <v>2.58</v>
       </c>
       <c r="CN9" t="n">
         <v>2</v>
@@ -4479,7 +4479,7 @@
         <v>1.9</v>
       </c>
       <c r="CQ9" t="n">
-        <v>3.18</v>
+        <v>3.17</v>
       </c>
       <c r="CR9" t="n">
         <v>1.39</v>
@@ -4518,49 +4518,49 @@
         <v>1.96</v>
       </c>
       <c r="DD9" t="n">
-        <v>3.29</v>
+        <v>3.3</v>
       </c>
       <c r="DE9" t="n">
         <v>0.16</v>
       </c>
       <c r="DF9" t="n">
-        <v>2.16</v>
+        <v>2.21</v>
       </c>
       <c r="DG9" t="n">
-        <v>2.39</v>
+        <v>2.48</v>
       </c>
       <c r="DH9" t="n">
-        <v>77.89</v>
+        <v>78.95</v>
       </c>
       <c r="DI9" t="n">
         <v>0</v>
       </c>
       <c r="DJ9" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="DK9" t="n">
-        <v>4.16</v>
+        <v>4.37</v>
       </c>
       <c r="DL9" t="n">
-        <v>0.39</v>
+        <v>0.37</v>
       </c>
       <c r="DM9" t="n">
-        <v>40.61</v>
+        <v>41.26</v>
       </c>
       <c r="DN9" t="n">
-        <v>0.84</v>
+        <v>0.89</v>
       </c>
       <c r="DO9" t="n">
-        <v>1.78</v>
+        <v>1.84</v>
       </c>
       <c r="DP9" t="n">
-        <v>16.56</v>
+        <v>16.79</v>
       </c>
       <c r="DQ9" t="n">
-        <v>11.34</v>
+        <v>11.63</v>
       </c>
       <c r="DR9" t="n">
-        <v>8.220000000000001</v>
+        <v>8.31</v>
       </c>
       <c r="DS9" t="n">
         <v>0</v>
@@ -4572,28 +4572,28 @@
         <v>0</v>
       </c>
       <c r="DV9" t="n">
-        <v>44.61</v>
+        <v>45.32</v>
       </c>
       <c r="DW9" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="DX9" t="n">
-        <v>12.84</v>
+        <v>13.11</v>
       </c>
       <c r="DY9" t="n">
-        <v>8.390000000000001</v>
+        <v>8.69</v>
       </c>
       <c r="DZ9" t="n">
-        <v>4.44</v>
+        <v>4.42</v>
       </c>
       <c r="EA9" t="n">
-        <v>19.23</v>
+        <v>19.69</v>
       </c>
       <c r="EB9" t="n">
-        <v>1.41</v>
+        <v>1.43</v>
       </c>
       <c r="EC9" t="n">
-        <v>2.94</v>
+        <v>3.05</v>
       </c>
     </row>
     <row r="10">
@@ -4750,7 +4750,7 @@
         <v>0</v>
       </c>
       <c r="AY10" t="n">
-        <v>32</v>
+        <v>32.1</v>
       </c>
       <c r="AZ10" t="n">
         <v>0.1</v>
@@ -4975,7 +4975,7 @@
         <v>0</v>
       </c>
       <c r="DV10" t="n">
-        <v>34.26</v>
+        <v>34.32</v>
       </c>
       <c r="DW10" t="n">
         <v>0.05</v>
@@ -5006,13 +5006,13 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C11" t="n">
         <v>10</v>
       </c>
       <c r="D11" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E11" t="n">
         <v>0.1</v>
@@ -5096,139 +5096,139 @@
         <v>2.7</v>
       </c>
       <c r="AF11" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="AH11" t="n">
-        <v>3.12</v>
+        <v>2.89</v>
       </c>
       <c r="AI11" t="n">
-        <v>95.12</v>
+        <v>94.89</v>
       </c>
       <c r="AJ11" t="n">
         <v>0</v>
       </c>
       <c r="AK11" t="n">
-        <v>2.62</v>
+        <v>2.67</v>
       </c>
       <c r="AL11" t="n">
-        <v>6.38</v>
+        <v>6.22</v>
       </c>
       <c r="AM11" t="n">
-        <v>0.25</v>
+        <v>0.33</v>
       </c>
       <c r="AN11" t="n">
-        <v>57.38</v>
+        <v>55.44</v>
       </c>
       <c r="AO11" t="n">
         <v>1</v>
       </c>
       <c r="AP11" t="n">
-        <v>3.25</v>
+        <v>3.33</v>
       </c>
       <c r="AQ11" t="n">
-        <v>13.88</v>
+        <v>13.67</v>
       </c>
       <c r="AR11" t="n">
-        <v>9.380000000000001</v>
+        <v>9.56</v>
       </c>
       <c r="AS11" t="n">
-        <v>8.119999999999999</v>
+        <v>8</v>
       </c>
       <c r="AT11" t="n">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="AU11" t="n">
-        <v>1</v>
+        <v>1.11</v>
       </c>
       <c r="AV11" t="n">
-        <v>0.12</v>
+        <v>0.22</v>
       </c>
       <c r="AW11" t="n">
-        <v>0.12</v>
+        <v>0.22</v>
       </c>
       <c r="AX11" t="n">
         <v>0</v>
       </c>
       <c r="AY11" t="n">
-        <v>56.75</v>
+        <v>55.89</v>
       </c>
       <c r="AZ11" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="BA11" t="n">
-        <v>13</v>
+        <v>12.89</v>
       </c>
       <c r="BB11" t="n">
         <v>9</v>
       </c>
       <c r="BC11" t="n">
-        <v>4</v>
+        <v>3.89</v>
       </c>
       <c r="BD11" t="n">
-        <v>22.62</v>
+        <v>24.11</v>
       </c>
       <c r="BE11" t="n">
-        <v>1.52</v>
+        <v>1.49</v>
       </c>
       <c r="BF11" t="n">
-        <v>2.38</v>
+        <v>2.44</v>
       </c>
       <c r="BG11" t="n">
-        <v>2.39</v>
+        <v>2.47</v>
       </c>
       <c r="BH11" t="n">
-        <v>10.17</v>
+        <v>10.21</v>
       </c>
       <c r="BI11" t="n">
-        <v>2.39</v>
+        <v>2.47</v>
       </c>
       <c r="BJ11" t="n">
-        <v>0.61</v>
+        <v>0.68</v>
       </c>
       <c r="BK11" t="n">
-        <v>0.28</v>
+        <v>0.26</v>
       </c>
       <c r="BL11" t="n">
-        <v>0.89</v>
+        <v>0.84</v>
       </c>
       <c r="BM11" t="n">
-        <v>0.61</v>
+        <v>0.68</v>
       </c>
       <c r="BN11" t="n">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="BO11" t="n">
-        <v>0.89</v>
+        <v>0.95</v>
       </c>
       <c r="BP11" t="n">
         <v>5</v>
       </c>
       <c r="BQ11" t="n">
-        <v>5.17</v>
+        <v>5.21</v>
       </c>
       <c r="BR11" t="n">
-        <v>94.44</v>
+        <v>94.73999999999999</v>
       </c>
       <c r="BS11" t="n">
-        <v>61.11</v>
+        <v>63.16</v>
       </c>
       <c r="BT11" t="n">
-        <v>33.33</v>
+        <v>36.84</v>
       </c>
       <c r="BU11" t="n">
-        <v>27.78</v>
+        <v>31.58</v>
       </c>
       <c r="BV11" t="n">
-        <v>11.11</v>
+        <v>10.53</v>
       </c>
       <c r="BW11" t="n">
-        <v>5.56</v>
+        <v>5.26</v>
       </c>
       <c r="BX11" t="n">
-        <v>38.89</v>
+        <v>42.11</v>
       </c>
       <c r="BY11" t="n">
         <v>1.98</v>
@@ -5237,31 +5237,31 @@
         <v>2.08</v>
       </c>
       <c r="CA11" t="n">
-        <v>3.65</v>
+        <v>3.63</v>
       </c>
       <c r="CB11" t="n">
-        <v>3.76</v>
+        <v>3.73</v>
       </c>
       <c r="CC11" t="n">
-        <v>2.47</v>
+        <v>2.46</v>
       </c>
       <c r="CD11" t="n">
-        <v>2.62</v>
+        <v>2.58</v>
       </c>
       <c r="CE11" t="n">
         <v>1.32</v>
       </c>
       <c r="CF11" t="n">
-        <v>2.52</v>
+        <v>2.54</v>
       </c>
       <c r="CG11" t="n">
-        <v>3.09</v>
+        <v>3.08</v>
       </c>
       <c r="CH11" t="n">
         <v>1.48</v>
       </c>
       <c r="CI11" t="n">
-        <v>2.16</v>
+        <v>2.15</v>
       </c>
       <c r="CJ11" t="n">
         <v>1.68</v>
@@ -5270,40 +5270,40 @@
         <v>1.47</v>
       </c>
       <c r="CL11" t="n">
-        <v>1.88</v>
+        <v>1.9</v>
       </c>
       <c r="CM11" t="n">
-        <v>2.56</v>
+        <v>2.55</v>
       </c>
       <c r="CN11" t="n">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="CO11" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="CP11" t="n">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="CQ11" t="n">
-        <v>2.86</v>
+        <v>2.9</v>
       </c>
       <c r="CR11" t="n">
         <v>1.35</v>
       </c>
       <c r="CS11" t="n">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="CT11" t="n">
-        <v>3.26</v>
+        <v>3.24</v>
       </c>
       <c r="CU11" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="CV11" t="n">
-        <v>2.26</v>
+        <v>2.24</v>
       </c>
       <c r="CW11" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="CX11" t="n">
         <v>1.52</v>
@@ -5315,91 +5315,91 @@
         <v>2.5</v>
       </c>
       <c r="DA11" t="n">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="DB11" t="n">
         <v>1.25</v>
       </c>
       <c r="DC11" t="n">
-        <v>1.8</v>
+        <v>1.82</v>
       </c>
       <c r="DD11" t="n">
-        <v>2.95</v>
+        <v>2.99</v>
       </c>
       <c r="DE11" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DF11" t="n">
-        <v>1.72</v>
+        <v>1.74</v>
       </c>
       <c r="DG11" t="n">
-        <v>3.22</v>
+        <v>3.11</v>
       </c>
       <c r="DH11" t="n">
-        <v>100.55</v>
+        <v>100.16</v>
       </c>
       <c r="DI11" t="n">
         <v>0</v>
       </c>
       <c r="DJ11" t="n">
-        <v>2.78</v>
+        <v>2.79</v>
       </c>
       <c r="DK11" t="n">
-        <v>6.39</v>
+        <v>6.31</v>
       </c>
       <c r="DL11" t="n">
-        <v>0.44</v>
+        <v>0.47</v>
       </c>
       <c r="DM11" t="n">
-        <v>58.06</v>
+        <v>57.1</v>
       </c>
       <c r="DN11" t="n">
         <v>1</v>
       </c>
       <c r="DO11" t="n">
-        <v>3.17</v>
+        <v>3.21</v>
       </c>
       <c r="DP11" t="n">
-        <v>13.61</v>
+        <v>13.53</v>
       </c>
       <c r="DQ11" t="n">
-        <v>10.45</v>
+        <v>10.48</v>
       </c>
       <c r="DR11" t="n">
-        <v>7.66</v>
+        <v>7.63</v>
       </c>
       <c r="DS11" t="n">
-        <v>0.11</v>
+        <v>0.16</v>
       </c>
       <c r="DT11" t="n">
-        <v>0.11</v>
+        <v>0.16</v>
       </c>
       <c r="DU11" t="n">
         <v>0</v>
       </c>
       <c r="DV11" t="n">
-        <v>53.11</v>
+        <v>52.9</v>
       </c>
       <c r="DW11" t="n">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
       <c r="DX11" t="n">
-        <v>15.11</v>
+        <v>14.95</v>
       </c>
       <c r="DY11" t="n">
-        <v>10.11</v>
+        <v>10.05</v>
       </c>
       <c r="DZ11" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="EA11" t="n">
-        <v>20.94</v>
+        <v>21.74</v>
       </c>
       <c r="EB11" t="n">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="EC11" t="n">
-        <v>2.56</v>
+        <v>2.58</v>
       </c>
     </row>
     <row r="12">
@@ -5409,94 +5409,94 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C12" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D12" t="n">
         <v>9</v>
       </c>
       <c r="E12" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="F12" t="n">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="G12" t="n">
-        <v>2</v>
+        <v>2.3</v>
       </c>
       <c r="H12" t="n">
-        <v>98</v>
+        <v>98.8</v>
       </c>
       <c r="I12" t="n">
         <v>0</v>
       </c>
       <c r="J12" t="n">
-        <v>2.33</v>
+        <v>2.1</v>
       </c>
       <c r="K12" t="n">
-        <v>4.67</v>
+        <v>4.8</v>
       </c>
       <c r="L12" t="n">
-        <v>0.67</v>
+        <v>0.6</v>
       </c>
       <c r="M12" t="n">
-        <v>43.56</v>
+        <v>45.3</v>
       </c>
       <c r="N12" t="n">
-        <v>0.89</v>
+        <v>0.8</v>
       </c>
       <c r="O12" t="n">
-        <v>2.67</v>
+        <v>2.5</v>
       </c>
       <c r="P12" t="n">
-        <v>11.22</v>
+        <v>11.3</v>
       </c>
       <c r="Q12" t="n">
-        <v>12.89</v>
+        <v>12.7</v>
       </c>
       <c r="R12" t="n">
-        <v>6.33</v>
+        <v>6.8</v>
       </c>
       <c r="S12" t="n">
-        <v>1.11</v>
+        <v>1.2</v>
       </c>
       <c r="T12" t="n">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="U12" t="n">
-        <v>0.33</v>
+        <v>0.4</v>
       </c>
       <c r="V12" t="n">
-        <v>0.33</v>
+        <v>0.4</v>
       </c>
       <c r="W12" t="n">
         <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>50.67</v>
+        <v>50.7</v>
       </c>
       <c r="Y12" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="Z12" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AA12" t="n">
-        <v>7.78</v>
+        <v>8.4</v>
       </c>
       <c r="AB12" t="n">
-        <v>5.22</v>
+        <v>5.6</v>
       </c>
       <c r="AC12" t="n">
-        <v>20.22</v>
+        <v>20.2</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.51</v>
+        <v>1.61</v>
       </c>
       <c r="AE12" t="n">
-        <v>2.11</v>
+        <v>1.9</v>
       </c>
       <c r="AF12" t="n">
         <v>0</v>
@@ -5580,49 +5580,49 @@
         <v>2.22</v>
       </c>
       <c r="BG12" t="n">
-        <v>2.11</v>
+        <v>2.21</v>
       </c>
       <c r="BH12" t="n">
-        <v>9.17</v>
+        <v>9.26</v>
       </c>
       <c r="BI12" t="n">
-        <v>2.11</v>
+        <v>2.21</v>
       </c>
       <c r="BJ12" t="n">
-        <v>0.67</v>
+        <v>0.74</v>
       </c>
       <c r="BK12" t="n">
-        <v>0.39</v>
+        <v>0.37</v>
       </c>
       <c r="BL12" t="n">
-        <v>0.61</v>
+        <v>0.58</v>
       </c>
       <c r="BM12" t="n">
-        <v>0.44</v>
+        <v>0.53</v>
       </c>
       <c r="BN12" t="n">
-        <v>1.06</v>
+        <v>1.11</v>
       </c>
       <c r="BO12" t="n">
-        <v>1.06</v>
+        <v>1.11</v>
       </c>
       <c r="BP12" t="n">
-        <v>3.89</v>
+        <v>3.95</v>
       </c>
       <c r="BQ12" t="n">
-        <v>5.28</v>
+        <v>5.32</v>
       </c>
       <c r="BR12" t="n">
-        <v>94.44</v>
+        <v>94.73999999999999</v>
       </c>
       <c r="BS12" t="n">
-        <v>72.22</v>
+        <v>73.68000000000001</v>
       </c>
       <c r="BT12" t="n">
-        <v>33.33</v>
+        <v>36.84</v>
       </c>
       <c r="BU12" t="n">
-        <v>11.11</v>
+        <v>15.79</v>
       </c>
       <c r="BV12" t="n">
         <v>0</v>
@@ -5631,19 +5631,19 @@
         <v>0</v>
       </c>
       <c r="BX12" t="n">
-        <v>50</v>
+        <v>52.63</v>
       </c>
       <c r="BY12" t="n">
-        <v>2.74</v>
+        <v>2.79</v>
       </c>
       <c r="BZ12" t="n">
-        <v>3</v>
+        <v>3.04</v>
       </c>
       <c r="CA12" t="n">
-        <v>3.58</v>
+        <v>3.56</v>
       </c>
       <c r="CB12" t="n">
-        <v>3.71</v>
+        <v>3.69</v>
       </c>
       <c r="CC12" t="n">
         <v>4.08</v>
@@ -5652,58 +5652,58 @@
         <v>4.61</v>
       </c>
       <c r="CE12" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="CF12" t="n">
-        <v>2.58</v>
+        <v>2.59</v>
       </c>
       <c r="CG12" t="n">
-        <v>3.06</v>
+        <v>3.05</v>
       </c>
       <c r="CH12" t="n">
         <v>1.46</v>
       </c>
       <c r="CI12" t="n">
-        <v>2.12</v>
+        <v>2.11</v>
       </c>
       <c r="CJ12" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="CK12" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="CL12" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="CM12" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="CN12" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="CO12" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="CP12" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="CQ12" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="CR12" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="CS12" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="CT12" t="n">
+        <v>3.17</v>
+      </c>
+      <c r="CU12" t="n">
         <v>1.48</v>
       </c>
-      <c r="CL12" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="CM12" t="n">
-        <v>2.46</v>
-      </c>
-      <c r="CN12" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="CO12" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="CP12" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="CQ12" t="n">
-        <v>3.01</v>
-      </c>
-      <c r="CR12" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="CS12" t="n">
-        <v>2.69</v>
-      </c>
-      <c r="CT12" t="n">
-        <v>3.19</v>
-      </c>
-      <c r="CU12" t="n">
-        <v>1.49</v>
-      </c>
       <c r="CV12" t="n">
-        <v>2.17</v>
+        <v>2.16</v>
       </c>
       <c r="CW12" t="n">
         <v>1.75</v>
@@ -5712,10 +5712,10 @@
         <v>1.59</v>
       </c>
       <c r="CY12" t="n">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="CZ12" t="n">
-        <v>2.34</v>
+        <v>2.35</v>
       </c>
       <c r="DA12" t="n">
         <v>1.89</v>
@@ -5724,85 +5724,85 @@
         <v>1.27</v>
       </c>
       <c r="DC12" t="n">
-        <v>1.87</v>
+        <v>1.89</v>
       </c>
       <c r="DD12" t="n">
-        <v>3.09</v>
+        <v>3.12</v>
       </c>
       <c r="DE12" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="DF12" t="n">
-        <v>1.56</v>
+        <v>1.47</v>
       </c>
       <c r="DG12" t="n">
-        <v>2</v>
+        <v>2.16</v>
       </c>
       <c r="DH12" t="n">
-        <v>91.06</v>
+        <v>91.84</v>
       </c>
       <c r="DI12" t="n">
         <v>0</v>
       </c>
       <c r="DJ12" t="n">
-        <v>2.38</v>
+        <v>2.26</v>
       </c>
       <c r="DK12" t="n">
-        <v>3.84</v>
+        <v>3.95</v>
       </c>
       <c r="DL12" t="n">
-        <v>0.5</v>
+        <v>0.47</v>
       </c>
       <c r="DM12" t="n">
-        <v>37.34</v>
+        <v>38.58</v>
       </c>
       <c r="DN12" t="n">
-        <v>0.73</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="DO12" t="n">
-        <v>1.84</v>
+        <v>1.79</v>
       </c>
       <c r="DP12" t="n">
-        <v>12.39</v>
+        <v>12.37</v>
       </c>
       <c r="DQ12" t="n">
-        <v>12.56</v>
+        <v>12.47</v>
       </c>
       <c r="DR12" t="n">
-        <v>7.44</v>
+        <v>7.63</v>
       </c>
       <c r="DS12" t="n">
-        <v>0.16</v>
+        <v>0.21</v>
       </c>
       <c r="DT12" t="n">
-        <v>0.16</v>
+        <v>0.21</v>
       </c>
       <c r="DU12" t="n">
         <v>0</v>
       </c>
       <c r="DV12" t="n">
-        <v>46.67</v>
+        <v>46.9</v>
       </c>
       <c r="DW12" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DX12" t="n">
-        <v>11.44</v>
+        <v>12.05</v>
       </c>
       <c r="DY12" t="n">
-        <v>7.22</v>
+        <v>7.58</v>
       </c>
       <c r="DZ12" t="n">
-        <v>4.22</v>
+        <v>4.47</v>
       </c>
       <c r="EA12" t="n">
-        <v>19.5</v>
+        <v>19.53</v>
       </c>
       <c r="EB12" t="n">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="EC12" t="n">
-        <v>2.16</v>
+        <v>2.05</v>
       </c>
     </row>
     <row r="13">
@@ -5812,94 +5812,94 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C13" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D13" t="n">
         <v>9</v>
       </c>
       <c r="E13" t="n">
-        <v>0.11</v>
+        <v>0.2</v>
       </c>
       <c r="F13" t="n">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="G13" t="n">
-        <v>3.89</v>
+        <v>3.6</v>
       </c>
       <c r="H13" t="n">
-        <v>106.78</v>
+        <v>104.9</v>
       </c>
       <c r="I13" t="n">
         <v>0</v>
       </c>
       <c r="J13" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="K13" t="n">
-        <v>5.67</v>
+        <v>5.3</v>
       </c>
       <c r="L13" t="n">
-        <v>0.33</v>
+        <v>0.3</v>
       </c>
       <c r="M13" t="n">
-        <v>56.56</v>
+        <v>55.1</v>
       </c>
       <c r="N13" t="n">
-        <v>0.33</v>
+        <v>0.3</v>
       </c>
       <c r="O13" t="n">
-        <v>1.78</v>
+        <v>1.7</v>
       </c>
       <c r="P13" t="n">
-        <v>11.22</v>
+        <v>11.3</v>
       </c>
       <c r="Q13" t="n">
-        <v>11</v>
+        <v>10.8</v>
       </c>
       <c r="R13" t="n">
-        <v>5.78</v>
+        <v>6</v>
       </c>
       <c r="S13" t="n">
-        <v>1.22</v>
+        <v>1.1</v>
       </c>
       <c r="T13" t="n">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="U13" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="V13" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="W13" t="n">
         <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>54.67</v>
+        <v>53.9</v>
       </c>
       <c r="Y13" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="Z13" t="n">
-        <v>15.67</v>
+        <v>15</v>
       </c>
       <c r="AA13" t="n">
-        <v>11</v>
+        <v>10.3</v>
       </c>
       <c r="AB13" t="n">
-        <v>4.67</v>
+        <v>4.7</v>
       </c>
       <c r="AC13" t="n">
-        <v>23.33</v>
+        <v>23.5</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.73</v>
+        <v>1.68</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="AF13" t="n">
         <v>0</v>
@@ -5983,70 +5983,70 @@
         <v>1.89</v>
       </c>
       <c r="BG13" t="n">
-        <v>2.72</v>
+        <v>2.63</v>
       </c>
       <c r="BH13" t="n">
-        <v>10.11</v>
+        <v>10</v>
       </c>
       <c r="BI13" t="n">
-        <v>2.72</v>
+        <v>2.63</v>
       </c>
       <c r="BJ13" t="n">
-        <v>0.72</v>
+        <v>0.74</v>
       </c>
       <c r="BK13" t="n">
-        <v>0.44</v>
+        <v>0.42</v>
       </c>
       <c r="BL13" t="n">
-        <v>0.72</v>
+        <v>0.68</v>
       </c>
       <c r="BM13" t="n">
-        <v>0.83</v>
+        <v>0.79</v>
       </c>
       <c r="BN13" t="n">
-        <v>1.56</v>
+        <v>1.47</v>
       </c>
       <c r="BO13" t="n">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="BP13" t="n">
-        <v>4.22</v>
+        <v>4.05</v>
       </c>
       <c r="BQ13" t="n">
-        <v>5.89</v>
+        <v>5.95</v>
       </c>
       <c r="BR13" t="n">
         <v>100</v>
       </c>
       <c r="BS13" t="n">
-        <v>88.89</v>
+        <v>84.20999999999999</v>
       </c>
       <c r="BT13" t="n">
-        <v>55.56</v>
+        <v>52.63</v>
       </c>
       <c r="BU13" t="n">
-        <v>22.22</v>
+        <v>21.05</v>
       </c>
       <c r="BV13" t="n">
-        <v>5.56</v>
+        <v>5.26</v>
       </c>
       <c r="BW13" t="n">
         <v>0</v>
       </c>
       <c r="BX13" t="n">
-        <v>61.11</v>
+        <v>57.89</v>
       </c>
       <c r="BY13" t="n">
-        <v>2.38</v>
+        <v>2.32</v>
       </c>
       <c r="BZ13" t="n">
-        <v>2.49</v>
+        <v>2.41</v>
       </c>
       <c r="CA13" t="n">
-        <v>3.72</v>
+        <v>3.73</v>
       </c>
       <c r="CB13" t="n">
-        <v>3.82</v>
+        <v>3.84</v>
       </c>
       <c r="CC13" t="n">
         <v>4.17</v>
@@ -6055,49 +6055,49 @@
         <v>4.42</v>
       </c>
       <c r="CE13" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="CF13" t="n">
-        <v>2.44</v>
+        <v>2.43</v>
       </c>
       <c r="CG13" t="n">
         <v>3.2</v>
       </c>
       <c r="CH13" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="CI13" t="n">
         <v>2.2</v>
       </c>
       <c r="CJ13" t="n">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="CK13" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="CL13" t="n">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="CM13" t="n">
-        <v>2.54</v>
+        <v>2.56</v>
       </c>
       <c r="CN13" t="n">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="CO13" t="n">
         <v>1.21</v>
       </c>
       <c r="CP13" t="n">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="CQ13" t="n">
-        <v>2.76</v>
+        <v>2.75</v>
       </c>
       <c r="CR13" t="n">
         <v>1.35</v>
       </c>
       <c r="CS13" t="n">
-        <v>2.61</v>
+        <v>2.59</v>
       </c>
       <c r="CT13" t="n">
         <v>3.28</v>
@@ -6106,7 +6106,7 @@
         <v>1.52</v>
       </c>
       <c r="CV13" t="n">
-        <v>2.32</v>
+        <v>2.33</v>
       </c>
       <c r="CW13" t="n">
         <v>1.65</v>
@@ -6115,97 +6115,97 @@
         <v>1.53</v>
       </c>
       <c r="CY13" t="n">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="CZ13" t="n">
         <v>2.47</v>
       </c>
       <c r="DA13" t="n">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="DB13" t="n">
         <v>1.23</v>
       </c>
       <c r="DC13" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="DD13" t="n">
-        <v>2.83</v>
+        <v>2.81</v>
       </c>
       <c r="DE13" t="n">
-        <v>0.06</v>
+        <v>0.11</v>
       </c>
       <c r="DF13" t="n">
-        <v>1.38</v>
+        <v>1.42</v>
       </c>
       <c r="DG13" t="n">
-        <v>3.66</v>
+        <v>3.52</v>
       </c>
       <c r="DH13" t="n">
-        <v>101.56</v>
+        <v>100.84</v>
       </c>
       <c r="DI13" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="DJ13" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="DK13" t="n">
+        <v>5.42</v>
+      </c>
+      <c r="DL13" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="DM13" t="n">
+        <v>53.63</v>
+      </c>
+      <c r="DN13" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="DO13" t="n">
         <v>1.89</v>
       </c>
-      <c r="DK13" t="n">
-        <v>5.61</v>
-      </c>
-      <c r="DL13" t="n">
-        <v>0.33</v>
-      </c>
-      <c r="DM13" t="n">
-        <v>54.28</v>
-      </c>
-      <c r="DN13" t="n">
-        <v>0.45</v>
-      </c>
-      <c r="DO13" t="n">
-        <v>1.94</v>
-      </c>
       <c r="DP13" t="n">
-        <v>11.94</v>
+        <v>11.95</v>
       </c>
       <c r="DQ13" t="n">
-        <v>11.11</v>
+        <v>11</v>
       </c>
       <c r="DR13" t="n">
-        <v>7.22</v>
+        <v>7.26</v>
       </c>
       <c r="DS13" t="n">
-        <v>0.33</v>
+        <v>0.31</v>
       </c>
       <c r="DT13" t="n">
-        <v>0.33</v>
+        <v>0.31</v>
       </c>
       <c r="DU13" t="n">
         <v>0</v>
       </c>
       <c r="DV13" t="n">
-        <v>53.06</v>
+        <v>52.73</v>
       </c>
       <c r="DW13" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="DX13" t="n">
-        <v>14.28</v>
+        <v>14</v>
       </c>
       <c r="DY13" t="n">
-        <v>9.890000000000001</v>
+        <v>9.58</v>
       </c>
       <c r="DZ13" t="n">
-        <v>4.39</v>
+        <v>4.42</v>
       </c>
       <c r="EA13" t="n">
-        <v>23.27</v>
+        <v>23.37</v>
       </c>
       <c r="EB13" t="n">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="EC13" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
     </row>
     <row r="14">

--- a/data/teams/leagues/Averages_Belgium_Pro_League_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Belgium_Pro_League_2025-2026.xlsx
@@ -1848,7 +1848,7 @@
         <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>65.78</v>
+        <v>65.67</v>
       </c>
       <c r="Y3" t="n">
         <v>0.11</v>
@@ -2154,7 +2154,7 @@
         <v>0</v>
       </c>
       <c r="DV3" t="n">
-        <v>62.95</v>
+        <v>62.9</v>
       </c>
       <c r="DW3" t="n">
         <v>0.05</v>
@@ -2735,7 +2735,7 @@
         <v>0</v>
       </c>
       <c r="AY5" t="n">
-        <v>48.5</v>
+        <v>48.6</v>
       </c>
       <c r="AZ5" t="n">
         <v>0.2</v>
@@ -2960,7 +2960,7 @@
         <v>0</v>
       </c>
       <c r="DV5" t="n">
-        <v>52.1</v>
+        <v>52.16</v>
       </c>
       <c r="DW5" t="n">
         <v>0.16</v>

--- a/data/teams/leagues/Averages_Belgium_Pro_League_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Belgium_Pro_League_2025-2026.xlsx
@@ -645,7 +645,7 @@
     <col width="9.6" customWidth="1" min="73" max="73"/>
     <col width="9.6" customWidth="1" min="74" max="74"/>
     <col width="9.6" customWidth="1" min="75" max="75"/>
-    <col width="8.4" customWidth="1" min="76" max="76"/>
+    <col width="7.199999999999999" customWidth="1" min="76" max="76"/>
     <col width="18" customWidth="1" min="77" max="77"/>
     <col width="27.6" customWidth="1" min="78" max="78"/>
     <col width="18" customWidth="1" min="79" max="79"/>
@@ -1379,10 +1379,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D2" t="n">
         <v>9</v>
@@ -1391,82 +1391,82 @@
         <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>0.8</v>
+        <v>0.91</v>
       </c>
       <c r="G2" t="n">
-        <v>3</v>
+        <v>2.91</v>
       </c>
       <c r="H2" t="n">
-        <v>109.2</v>
+        <v>109.82</v>
       </c>
       <c r="I2" t="n">
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>1.2</v>
+        <v>1.36</v>
       </c>
       <c r="K2" t="n">
-        <v>5</v>
+        <v>4.91</v>
       </c>
       <c r="L2" t="n">
-        <v>0.4</v>
+        <v>0.45</v>
       </c>
       <c r="M2" t="n">
-        <v>50.1</v>
+        <v>48.82</v>
       </c>
       <c r="N2" t="n">
-        <v>0.4</v>
+        <v>0.45</v>
       </c>
       <c r="O2" t="n">
         <v>2</v>
       </c>
       <c r="P2" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="Q2" t="n">
-        <v>13.6</v>
+        <v>13.64</v>
       </c>
       <c r="R2" t="n">
-        <v>6.7</v>
+        <v>6.91</v>
       </c>
       <c r="S2" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="T2" t="n">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="U2" t="n">
-        <v>0.5</v>
+        <v>0.55</v>
       </c>
       <c r="V2" t="n">
-        <v>0.5</v>
+        <v>0.55</v>
       </c>
       <c r="W2" t="n">
         <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>53</v>
+        <v>51.45</v>
       </c>
       <c r="Y2" t="n">
-        <v>0</v>
+        <v>0.09</v>
       </c>
       <c r="Z2" t="n">
-        <v>15.3</v>
+        <v>14.73</v>
       </c>
       <c r="AA2" t="n">
-        <v>10.2</v>
+        <v>9.640000000000001</v>
       </c>
       <c r="AB2" t="n">
-        <v>5.1</v>
+        <v>5.09</v>
       </c>
       <c r="AC2" t="n">
-        <v>24.2</v>
+        <v>23.82</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.69</v>
+        <v>1.64</v>
       </c>
       <c r="AE2" t="n">
-        <v>1.2</v>
+        <v>1.27</v>
       </c>
       <c r="AF2" t="n">
         <v>0.11</v>
@@ -1550,70 +1550,70 @@
         <v>2.67</v>
       </c>
       <c r="BG2" t="n">
-        <v>2.79</v>
+        <v>2.75</v>
       </c>
       <c r="BH2" t="n">
-        <v>10.42</v>
+        <v>10.3</v>
       </c>
       <c r="BI2" t="n">
-        <v>2.79</v>
+        <v>2.75</v>
       </c>
       <c r="BJ2" t="n">
-        <v>0.63</v>
+        <v>0.65</v>
       </c>
       <c r="BK2" t="n">
         <v>0.95</v>
       </c>
       <c r="BL2" t="n">
-        <v>0.63</v>
+        <v>0.6</v>
       </c>
       <c r="BM2" t="n">
-        <v>0.58</v>
+        <v>0.55</v>
       </c>
       <c r="BN2" t="n">
-        <v>1.21</v>
+        <v>1.15</v>
       </c>
       <c r="BO2" t="n">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
       <c r="BP2" t="n">
-        <v>4.63</v>
+        <v>4.6</v>
       </c>
       <c r="BQ2" t="n">
-        <v>5.74</v>
+        <v>5.65</v>
       </c>
       <c r="BR2" t="n">
-        <v>89.47</v>
+        <v>90</v>
       </c>
       <c r="BS2" t="n">
-        <v>89.47</v>
+        <v>90</v>
       </c>
       <c r="BT2" t="n">
-        <v>47.37</v>
+        <v>45</v>
       </c>
       <c r="BU2" t="n">
-        <v>26.32</v>
+        <v>25</v>
       </c>
       <c r="BV2" t="n">
-        <v>21.05</v>
+        <v>20</v>
       </c>
       <c r="BW2" t="n">
-        <v>5.26</v>
+        <v>5</v>
       </c>
       <c r="BX2" t="n">
-        <v>63.16</v>
+        <v>65</v>
       </c>
       <c r="BY2" t="n">
-        <v>2.24</v>
+        <v>2.37</v>
       </c>
       <c r="BZ2" t="n">
-        <v>2.3</v>
+        <v>2.45</v>
       </c>
       <c r="CA2" t="n">
         <v>3.55</v>
       </c>
       <c r="CB2" t="n">
-        <v>3.7</v>
+        <v>3.69</v>
       </c>
       <c r="CC2" t="n">
         <v>3.41</v>
@@ -1622,109 +1622,109 @@
         <v>3.6</v>
       </c>
       <c r="CE2" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="CF2" t="n">
-        <v>2.52</v>
+        <v>2.53</v>
       </c>
       <c r="CG2" t="n">
-        <v>3.17</v>
+        <v>3.15</v>
       </c>
       <c r="CH2" t="n">
         <v>1.48</v>
       </c>
       <c r="CI2" t="n">
-        <v>2.18</v>
+        <v>2.17</v>
       </c>
       <c r="CJ2" t="n">
         <v>1.66</v>
       </c>
       <c r="CK2" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="CL2" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="CM2" t="n">
-        <v>2.59</v>
+        <v>2.58</v>
       </c>
       <c r="CN2" t="n">
-        <v>2.02</v>
+        <v>2.01</v>
       </c>
       <c r="CO2" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="CP2" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="CQ2" t="n">
-        <v>2.87</v>
+        <v>2.9</v>
       </c>
       <c r="CR2" t="n">
         <v>1.36</v>
       </c>
       <c r="CS2" t="n">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="CT2" t="n">
-        <v>3.23</v>
+        <v>3.2</v>
       </c>
       <c r="CU2" t="n">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="CV2" t="n">
-        <v>2.31</v>
+        <v>2.29</v>
       </c>
       <c r="CW2" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="CX2" t="n">
         <v>1.5</v>
       </c>
       <c r="CY2" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="CZ2" t="n">
-        <v>2.54</v>
+        <v>2.53</v>
       </c>
       <c r="DA2" t="n">
-        <v>2.08</v>
+        <v>2.07</v>
       </c>
       <c r="DB2" t="n">
         <v>1.24</v>
       </c>
       <c r="DC2" t="n">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="DD2" t="n">
-        <v>2.86</v>
+        <v>2.9</v>
       </c>
       <c r="DE2" t="n">
         <v>0.05</v>
       </c>
       <c r="DF2" t="n">
-        <v>1</v>
+        <v>1.05</v>
       </c>
       <c r="DG2" t="n">
-        <v>2.84</v>
+        <v>2.8</v>
       </c>
       <c r="DH2" t="n">
-        <v>107.48</v>
+        <v>107.9</v>
       </c>
       <c r="DI2" t="n">
         <v>0.1</v>
       </c>
       <c r="DJ2" t="n">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="DK2" t="n">
-        <v>4.95</v>
+        <v>4.9</v>
       </c>
       <c r="DL2" t="n">
-        <v>0.48</v>
+        <v>0.5</v>
       </c>
       <c r="DM2" t="n">
-        <v>50.79</v>
+        <v>50.05</v>
       </c>
       <c r="DN2" t="n">
         <v>0.95</v>
@@ -1733,43 +1733,43 @@
         <v>2.1</v>
       </c>
       <c r="DP2" t="n">
-        <v>10.79</v>
+        <v>10.8</v>
       </c>
       <c r="DQ2" t="n">
-        <v>13.05</v>
+        <v>13.1</v>
       </c>
       <c r="DR2" t="n">
-        <v>7.05</v>
+        <v>7.15</v>
       </c>
       <c r="DS2" t="n">
-        <v>0.26</v>
+        <v>0.3</v>
       </c>
       <c r="DT2" t="n">
-        <v>0.26</v>
+        <v>0.3</v>
       </c>
       <c r="DU2" t="n">
         <v>0</v>
       </c>
       <c r="DV2" t="n">
-        <v>51.11</v>
+        <v>50.35</v>
       </c>
       <c r="DW2" t="n">
-        <v>0.05</v>
+        <v>0.1</v>
       </c>
       <c r="DX2" t="n">
-        <v>13.95</v>
+        <v>13.7</v>
       </c>
       <c r="DY2" t="n">
-        <v>9.58</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="DZ2" t="n">
-        <v>4.37</v>
+        <v>4.4</v>
       </c>
       <c r="EA2" t="n">
-        <v>23.31</v>
+        <v>23.15</v>
       </c>
       <c r="EB2" t="n">
-        <v>1.56</v>
+        <v>1.54</v>
       </c>
       <c r="EC2" t="n">
         <v>1.9</v>
@@ -1782,13 +1782,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C3" t="n">
         <v>9</v>
       </c>
       <c r="D3" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
@@ -1872,52 +1872,52 @@
         <v>1.11</v>
       </c>
       <c r="AF3" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="AG3" t="n">
-        <v>1</v>
+        <v>1.09</v>
       </c>
       <c r="AH3" t="n">
-        <v>4</v>
+        <v>3.64</v>
       </c>
       <c r="AI3" t="n">
-        <v>109.6</v>
+        <v>107.45</v>
       </c>
       <c r="AJ3" t="n">
-        <v>-0.1</v>
+        <v>-0.09</v>
       </c>
       <c r="AK3" t="n">
-        <v>1.4</v>
+        <v>1.55</v>
       </c>
       <c r="AL3" t="n">
-        <v>6.3</v>
+        <v>5.91</v>
       </c>
       <c r="AM3" t="n">
-        <v>0.3</v>
+        <v>0.27</v>
       </c>
       <c r="AN3" t="n">
-        <v>58.9</v>
+        <v>56.55</v>
       </c>
       <c r="AO3" t="n">
-        <v>0.4</v>
+        <v>0.45</v>
       </c>
       <c r="AP3" t="n">
-        <v>2.3</v>
+        <v>2.27</v>
       </c>
       <c r="AQ3" t="n">
-        <v>9.1</v>
+        <v>9.359999999999999</v>
       </c>
       <c r="AR3" t="n">
-        <v>11.3</v>
+        <v>11.45</v>
       </c>
       <c r="AS3" t="n">
-        <v>7.8</v>
+        <v>7.91</v>
       </c>
       <c r="AT3" t="n">
-        <v>1</v>
+        <v>1.18</v>
       </c>
       <c r="AU3" t="n">
-        <v>1.4</v>
+        <v>1.73</v>
       </c>
       <c r="AV3" t="n">
         <v>0</v>
@@ -1929,82 +1929,82 @@
         <v>0</v>
       </c>
       <c r="AY3" t="n">
-        <v>60.4</v>
+        <v>59.18</v>
       </c>
       <c r="AZ3" t="n">
         <v>0</v>
       </c>
       <c r="BA3" t="n">
-        <v>16.2</v>
+        <v>15.45</v>
       </c>
       <c r="BB3" t="n">
-        <v>10.7</v>
+        <v>9.91</v>
       </c>
       <c r="BC3" t="n">
-        <v>5.5</v>
+        <v>5.55</v>
       </c>
       <c r="BD3" t="n">
-        <v>17.7</v>
+        <v>17.91</v>
       </c>
       <c r="BE3" t="n">
-        <v>1.83</v>
+        <v>1.77</v>
       </c>
       <c r="BF3" t="n">
-        <v>1.4</v>
+        <v>1.55</v>
       </c>
       <c r="BG3" t="n">
-        <v>2.63</v>
+        <v>2.9</v>
       </c>
       <c r="BH3" t="n">
         <v>11.05</v>
       </c>
       <c r="BI3" t="n">
-        <v>2.63</v>
+        <v>2.9</v>
       </c>
       <c r="BJ3" t="n">
-        <v>0.63</v>
+        <v>0.65</v>
       </c>
       <c r="BK3" t="n">
-        <v>0.37</v>
+        <v>0.5</v>
       </c>
       <c r="BL3" t="n">
-        <v>0.79</v>
+        <v>0.85</v>
       </c>
       <c r="BM3" t="n">
-        <v>0.84</v>
+        <v>0.9</v>
       </c>
       <c r="BN3" t="n">
-        <v>1.63</v>
+        <v>1.75</v>
       </c>
       <c r="BO3" t="n">
-        <v>1</v>
+        <v>1.15</v>
       </c>
       <c r="BP3" t="n">
-        <v>4.89</v>
+        <v>4.8</v>
       </c>
       <c r="BQ3" t="n">
-        <v>6.16</v>
+        <v>6.25</v>
       </c>
       <c r="BR3" t="n">
         <v>100</v>
       </c>
       <c r="BS3" t="n">
-        <v>57.89</v>
+        <v>60</v>
       </c>
       <c r="BT3" t="n">
-        <v>42.11</v>
+        <v>45</v>
       </c>
       <c r="BU3" t="n">
-        <v>15.79</v>
+        <v>20</v>
       </c>
       <c r="BV3" t="n">
-        <v>15.79</v>
+        <v>20</v>
       </c>
       <c r="BW3" t="n">
-        <v>10.53</v>
+        <v>15</v>
       </c>
       <c r="BX3" t="n">
-        <v>47.37</v>
+        <v>50</v>
       </c>
       <c r="BY3" t="n">
         <v>1.51</v>
@@ -2013,34 +2013,34 @@
         <v>1.52</v>
       </c>
       <c r="CA3" t="n">
-        <v>4.44</v>
+        <v>4.39</v>
       </c>
       <c r="CB3" t="n">
-        <v>4.73</v>
+        <v>4.68</v>
       </c>
       <c r="CC3" t="n">
-        <v>1.7</v>
+        <v>1.74</v>
       </c>
       <c r="CD3" t="n">
-        <v>1.76</v>
+        <v>1.81</v>
       </c>
       <c r="CE3" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="CF3" t="n">
         <v>2.24</v>
       </c>
       <c r="CG3" t="n">
-        <v>3.56</v>
+        <v>3.55</v>
       </c>
       <c r="CH3" t="n">
         <v>1.61</v>
       </c>
       <c r="CI3" t="n">
-        <v>2.14</v>
+        <v>2.15</v>
       </c>
       <c r="CJ3" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="CK3" t="n">
         <v>1.47</v>
@@ -2058,7 +2058,7 @@
         <v>1.16</v>
       </c>
       <c r="CP3" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="CQ3" t="n">
         <v>2.4</v>
@@ -2076,7 +2076,7 @@
         <v>1.65</v>
       </c>
       <c r="CV3" t="n">
-        <v>2.31</v>
+        <v>2.32</v>
       </c>
       <c r="CW3" t="n">
         <v>1.67</v>
@@ -2085,7 +2085,7 @@
         <v>1.52</v>
       </c>
       <c r="CY3" t="n">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="CZ3" t="n">
         <v>2.5</v>
@@ -2100,49 +2100,49 @@
         <v>1.58</v>
       </c>
       <c r="DD3" t="n">
-        <v>2.43</v>
+        <v>2.44</v>
       </c>
       <c r="DE3" t="n">
         <v>0.05</v>
       </c>
       <c r="DF3" t="n">
-        <v>1.05</v>
+        <v>1.1</v>
       </c>
       <c r="DG3" t="n">
-        <v>4.1</v>
+        <v>3.9</v>
       </c>
       <c r="DH3" t="n">
-        <v>112.84</v>
+        <v>111.5</v>
       </c>
       <c r="DI3" t="n">
         <v>-0.05</v>
       </c>
       <c r="DJ3" t="n">
-        <v>1.37</v>
+        <v>1.45</v>
       </c>
       <c r="DK3" t="n">
-        <v>6.79</v>
+        <v>6.55</v>
       </c>
       <c r="DL3" t="n">
-        <v>0.63</v>
+        <v>0.6</v>
       </c>
       <c r="DM3" t="n">
-        <v>63.48</v>
+        <v>61.95</v>
       </c>
       <c r="DN3" t="n">
-        <v>0.26</v>
+        <v>0.3</v>
       </c>
       <c r="DO3" t="n">
-        <v>2.68</v>
+        <v>2.65</v>
       </c>
       <c r="DP3" t="n">
-        <v>9.32</v>
+        <v>9.449999999999999</v>
       </c>
       <c r="DQ3" t="n">
-        <v>11.68</v>
+        <v>11.75</v>
       </c>
       <c r="DR3" t="n">
-        <v>7.37</v>
+        <v>7.45</v>
       </c>
       <c r="DS3" t="n">
         <v>0</v>
@@ -2154,28 +2154,28 @@
         <v>0</v>
       </c>
       <c r="DV3" t="n">
-        <v>62.9</v>
+        <v>62.1</v>
       </c>
       <c r="DW3" t="n">
         <v>0.05</v>
       </c>
       <c r="DX3" t="n">
-        <v>17.16</v>
+        <v>16.7</v>
       </c>
       <c r="DY3" t="n">
-        <v>11.95</v>
+        <v>11.45</v>
       </c>
       <c r="DZ3" t="n">
-        <v>5.21</v>
+        <v>5.25</v>
       </c>
       <c r="EA3" t="n">
-        <v>20.63</v>
+        <v>20.6</v>
       </c>
       <c r="EB3" t="n">
-        <v>1.91</v>
+        <v>1.87</v>
       </c>
       <c r="EC3" t="n">
-        <v>1.26</v>
+        <v>1.35</v>
       </c>
     </row>
     <row r="4">
@@ -2185,13 +2185,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C4" t="n">
         <v>10</v>
       </c>
       <c r="D4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
@@ -2275,139 +2275,139 @@
         <v>1.5</v>
       </c>
       <c r="AF4" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.56</v>
+        <v>1.7</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.22</v>
+        <v>1.5</v>
       </c>
       <c r="AI4" t="n">
-        <v>88.44</v>
+        <v>91.09999999999999</v>
       </c>
       <c r="AJ4" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="AK4" t="n">
-        <v>2.33</v>
+        <v>2.6</v>
       </c>
       <c r="AL4" t="n">
-        <v>3</v>
+        <v>3.3</v>
       </c>
       <c r="AM4" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="AN4" t="n">
-        <v>37.22</v>
+        <v>39.4</v>
       </c>
       <c r="AO4" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.7</v>
       </c>
       <c r="AP4" t="n">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="AQ4" t="n">
-        <v>11.89</v>
+        <v>11.8</v>
       </c>
       <c r="AR4" t="n">
-        <v>11.67</v>
+        <v>11.8</v>
       </c>
       <c r="AS4" t="n">
-        <v>10.78</v>
+        <v>10.5</v>
       </c>
       <c r="AT4" t="n">
-        <v>1.78</v>
+        <v>1.7</v>
       </c>
       <c r="AU4" t="n">
         <v>1</v>
       </c>
       <c r="AV4" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="AW4" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="AX4" t="n">
         <v>0</v>
       </c>
       <c r="AY4" t="n">
-        <v>43.33</v>
+        <v>43.6</v>
       </c>
       <c r="AZ4" t="n">
-        <v>0.33</v>
+        <v>0.4</v>
       </c>
       <c r="BA4" t="n">
-        <v>10.78</v>
+        <v>11.4</v>
       </c>
       <c r="BB4" t="n">
-        <v>6.67</v>
+        <v>6.8</v>
       </c>
       <c r="BC4" t="n">
-        <v>4.11</v>
+        <v>4.6</v>
       </c>
       <c r="BD4" t="n">
-        <v>18</v>
+        <v>19.1</v>
       </c>
       <c r="BE4" t="n">
-        <v>1.24</v>
+        <v>1.33</v>
       </c>
       <c r="BF4" t="n">
-        <v>1.78</v>
+        <v>2</v>
       </c>
       <c r="BG4" t="n">
-        <v>2.53</v>
+        <v>2.5</v>
       </c>
       <c r="BH4" t="n">
-        <v>8.109999999999999</v>
+        <v>8.25</v>
       </c>
       <c r="BI4" t="n">
-        <v>2.53</v>
+        <v>2.5</v>
       </c>
       <c r="BJ4" t="n">
-        <v>0.53</v>
+        <v>0.55</v>
       </c>
       <c r="BK4" t="n">
-        <v>0.32</v>
+        <v>0.3</v>
       </c>
       <c r="BL4" t="n">
-        <v>0.63</v>
+        <v>0.6</v>
       </c>
       <c r="BM4" t="n">
         <v>1.05</v>
       </c>
       <c r="BN4" t="n">
-        <v>1.68</v>
+        <v>1.65</v>
       </c>
       <c r="BO4" t="n">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="BP4" t="n">
-        <v>3.47</v>
+        <v>3.65</v>
       </c>
       <c r="BQ4" t="n">
         <v>3.95</v>
       </c>
       <c r="BR4" t="n">
-        <v>89.47</v>
+        <v>90</v>
       </c>
       <c r="BS4" t="n">
-        <v>73.68000000000001</v>
+        <v>75</v>
       </c>
       <c r="BT4" t="n">
-        <v>52.63</v>
+        <v>50</v>
       </c>
       <c r="BU4" t="n">
-        <v>26.32</v>
+        <v>25</v>
       </c>
       <c r="BV4" t="n">
-        <v>5.26</v>
+        <v>5</v>
       </c>
       <c r="BW4" t="n">
-        <v>5.26</v>
+        <v>5</v>
       </c>
       <c r="BX4" t="n">
-        <v>57.89</v>
+        <v>60</v>
       </c>
       <c r="BY4" t="n">
         <v>3.46</v>
@@ -2416,28 +2416,28 @@
         <v>3.54</v>
       </c>
       <c r="CA4" t="n">
-        <v>3.7</v>
+        <v>3.69</v>
       </c>
       <c r="CB4" t="n">
-        <v>3.89</v>
+        <v>3.87</v>
       </c>
       <c r="CC4" t="n">
-        <v>4.74</v>
+        <v>4.63</v>
       </c>
       <c r="CD4" t="n">
-        <v>5.16</v>
+        <v>5.03</v>
       </c>
       <c r="CE4" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="CF4" t="n">
-        <v>2.57</v>
+        <v>2.59</v>
       </c>
       <c r="CG4" t="n">
-        <v>3.1</v>
+        <v>3.08</v>
       </c>
       <c r="CH4" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="CI4" t="n">
         <v>2.04</v>
@@ -2449,13 +2449,13 @@
         <v>1.54</v>
       </c>
       <c r="CL4" t="n">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="CM4" t="n">
-        <v>2.35</v>
+        <v>2.36</v>
       </c>
       <c r="CN4" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="CO4" t="n">
         <v>1.25</v>
@@ -2470,7 +2470,7 @@
         <v>1.39</v>
       </c>
       <c r="CS4" t="n">
-        <v>2.74</v>
+        <v>2.75</v>
       </c>
       <c r="CT4" t="n">
         <v>3.07</v>
@@ -2479,73 +2479,73 @@
         <v>1.49</v>
       </c>
       <c r="CV4" t="n">
-        <v>2.16</v>
+        <v>2.15</v>
       </c>
       <c r="CW4" t="n">
         <v>1.76</v>
       </c>
       <c r="CX4" t="n">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="CY4" t="n">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="CZ4" t="n">
-        <v>2.36</v>
+        <v>2.37</v>
       </c>
       <c r="DA4" t="n">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="DB4" t="n">
         <v>1.27</v>
       </c>
       <c r="DC4" t="n">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="DD4" t="n">
-        <v>3.09</v>
+        <v>3.1</v>
       </c>
       <c r="DE4" t="n">
         <v>0.1</v>
       </c>
       <c r="DF4" t="n">
-        <v>1.21</v>
+        <v>1.3</v>
       </c>
       <c r="DG4" t="n">
-        <v>1.21</v>
+        <v>1.35</v>
       </c>
       <c r="DH4" t="n">
-        <v>91.63</v>
+        <v>92.8</v>
       </c>
       <c r="DI4" t="n">
         <v>-0.05</v>
       </c>
       <c r="DJ4" t="n">
-        <v>1.89</v>
+        <v>2.05</v>
       </c>
       <c r="DK4" t="n">
-        <v>3.05</v>
+        <v>3.2</v>
       </c>
       <c r="DL4" t="n">
         <v>0.1</v>
       </c>
       <c r="DM4" t="n">
-        <v>40.58</v>
+        <v>41.5</v>
       </c>
       <c r="DN4" t="n">
-        <v>0.58</v>
+        <v>0.65</v>
       </c>
       <c r="DO4" t="n">
-        <v>1.42</v>
+        <v>1.45</v>
       </c>
       <c r="DP4" t="n">
         <v>10.95</v>
       </c>
       <c r="DQ4" t="n">
-        <v>11.58</v>
+        <v>11.65</v>
       </c>
       <c r="DR4" t="n">
-        <v>10.69</v>
+        <v>10.55</v>
       </c>
       <c r="DS4" t="n">
         <v>0.1</v>
@@ -2557,28 +2557,28 @@
         <v>0</v>
       </c>
       <c r="DV4" t="n">
-        <v>46.89</v>
+        <v>46.85</v>
       </c>
       <c r="DW4" t="n">
-        <v>0.16</v>
+        <v>0.2</v>
       </c>
       <c r="DX4" t="n">
-        <v>10.11</v>
+        <v>10.45</v>
       </c>
       <c r="DY4" t="n">
-        <v>6.48</v>
+        <v>6.55</v>
       </c>
       <c r="DZ4" t="n">
-        <v>3.63</v>
+        <v>3.9</v>
       </c>
       <c r="EA4" t="n">
-        <v>21</v>
+        <v>21.4</v>
       </c>
       <c r="EB4" t="n">
-        <v>1.19</v>
+        <v>1.23</v>
       </c>
       <c r="EC4" t="n">
-        <v>1.63</v>
+        <v>1.75</v>
       </c>
     </row>
     <row r="5">
@@ -2588,61 +2588,61 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C5" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D5" t="n">
         <v>10</v>
       </c>
       <c r="E5" t="n">
-        <v>0.33</v>
+        <v>0.3</v>
       </c>
       <c r="F5" t="n">
-        <v>1.11</v>
+        <v>1</v>
       </c>
       <c r="G5" t="n">
-        <v>2.78</v>
+        <v>2.5</v>
       </c>
       <c r="H5" t="n">
-        <v>111</v>
+        <v>106.7</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>1.56</v>
+        <v>1.5</v>
       </c>
       <c r="K5" t="n">
-        <v>4.67</v>
+        <v>4.6</v>
       </c>
       <c r="L5" t="n">
-        <v>0.44</v>
+        <v>0.4</v>
       </c>
       <c r="M5" t="n">
-        <v>51.11</v>
+        <v>48.8</v>
       </c>
       <c r="N5" t="n">
-        <v>0.33</v>
+        <v>0.4</v>
       </c>
       <c r="O5" t="n">
-        <v>1.89</v>
+        <v>2.1</v>
       </c>
       <c r="P5" t="n">
-        <v>10</v>
+        <v>10.7</v>
       </c>
       <c r="Q5" t="n">
-        <v>9.67</v>
+        <v>10.2</v>
       </c>
       <c r="R5" t="n">
-        <v>8.109999999999999</v>
+        <v>8.5</v>
       </c>
       <c r="S5" t="n">
-        <v>1.11</v>
+        <v>1</v>
       </c>
       <c r="T5" t="n">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="U5" t="n">
         <v>0</v>
@@ -2654,28 +2654,28 @@
         <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>56.11</v>
+        <v>54.8</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="Z5" t="n">
-        <v>15.22</v>
+        <v>15.5</v>
       </c>
       <c r="AA5" t="n">
-        <v>11.11</v>
+        <v>11.3</v>
       </c>
       <c r="AB5" t="n">
-        <v>4.11</v>
+        <v>4.2</v>
       </c>
       <c r="AC5" t="n">
-        <v>19.78</v>
+        <v>19.1</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AF5" t="n">
         <v>0.1</v>
@@ -2759,70 +2759,70 @@
         <v>1.9</v>
       </c>
       <c r="BG5" t="n">
-        <v>2.89</v>
+        <v>2.85</v>
       </c>
       <c r="BH5" t="n">
-        <v>9.84</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="BI5" t="n">
-        <v>2.89</v>
+        <v>2.85</v>
       </c>
       <c r="BJ5" t="n">
-        <v>0.84</v>
+        <v>0.9</v>
       </c>
       <c r="BK5" t="n">
-        <v>0.42</v>
+        <v>0.4</v>
       </c>
       <c r="BL5" t="n">
-        <v>0.95</v>
+        <v>0.9</v>
       </c>
       <c r="BM5" t="n">
-        <v>0.68</v>
+        <v>0.65</v>
       </c>
       <c r="BN5" t="n">
-        <v>1.63</v>
+        <v>1.55</v>
       </c>
       <c r="BO5" t="n">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="BP5" t="n">
-        <v>3.79</v>
+        <v>3.9</v>
       </c>
       <c r="BQ5" t="n">
-        <v>6.05</v>
+        <v>5.8</v>
       </c>
       <c r="BR5" t="n">
-        <v>94.73999999999999</v>
+        <v>95</v>
       </c>
       <c r="BS5" t="n">
-        <v>84.20999999999999</v>
+        <v>85</v>
       </c>
       <c r="BT5" t="n">
-        <v>57.89</v>
+        <v>55</v>
       </c>
       <c r="BU5" t="n">
-        <v>31.58</v>
+        <v>30</v>
       </c>
       <c r="BV5" t="n">
-        <v>15.79</v>
+        <v>15</v>
       </c>
       <c r="BW5" t="n">
-        <v>5.26</v>
+        <v>5</v>
       </c>
       <c r="BX5" t="n">
-        <v>63.16</v>
+        <v>60</v>
       </c>
       <c r="BY5" t="n">
-        <v>2.73</v>
+        <v>2.69</v>
       </c>
       <c r="BZ5" t="n">
-        <v>2.85</v>
+        <v>2.82</v>
       </c>
       <c r="CA5" t="n">
-        <v>3.67</v>
+        <v>3.66</v>
       </c>
       <c r="CB5" t="n">
-        <v>3.86</v>
+        <v>3.84</v>
       </c>
       <c r="CC5" t="n">
         <v>3.75</v>
@@ -2840,13 +2840,13 @@
         <v>3.26</v>
       </c>
       <c r="CH5" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="CI5" t="n">
-        <v>2.24</v>
+        <v>2.25</v>
       </c>
       <c r="CJ5" t="n">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="CK5" t="n">
         <v>1.44</v>
@@ -2858,7 +2858,7 @@
         <v>2.58</v>
       </c>
       <c r="CN5" t="n">
-        <v>2</v>
+        <v>2.01</v>
       </c>
       <c r="CO5" t="n">
         <v>1.21</v>
@@ -2867,88 +2867,88 @@
         <v>1.71</v>
       </c>
       <c r="CQ5" t="n">
-        <v>2.69</v>
+        <v>2.68</v>
       </c>
       <c r="CR5" t="n">
         <v>1.35</v>
       </c>
       <c r="CS5" t="n">
-        <v>2.5</v>
+        <v>2.49</v>
       </c>
       <c r="CT5" t="n">
         <v>3.27</v>
       </c>
       <c r="CU5" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="CV5" t="n">
-        <v>2.33</v>
+        <v>2.35</v>
       </c>
       <c r="CW5" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="CX5" t="n">
         <v>1.52</v>
       </c>
       <c r="CY5" t="n">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="CZ5" t="n">
         <v>2.49</v>
       </c>
       <c r="DA5" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="DB5" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="DC5" t="n">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="DD5" t="n">
-        <v>2.78</v>
+        <v>2.77</v>
       </c>
       <c r="DE5" t="n">
-        <v>0.21</v>
+        <v>0.2</v>
       </c>
       <c r="DF5" t="n">
-        <v>1.21</v>
+        <v>1.15</v>
       </c>
       <c r="DG5" t="n">
-        <v>2.84</v>
+        <v>2.7</v>
       </c>
       <c r="DH5" t="n">
-        <v>99.84</v>
+        <v>98.25</v>
       </c>
       <c r="DI5" t="n">
         <v>0</v>
       </c>
       <c r="DJ5" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="DK5" t="n">
+        <v>4.65</v>
+      </c>
+      <c r="DL5" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="DM5" t="n">
+        <v>44.6</v>
+      </c>
+      <c r="DN5" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="DO5" t="n">
         <v>1.95</v>
       </c>
-      <c r="DK5" t="n">
-        <v>4.69</v>
-      </c>
-      <c r="DL5" t="n">
-        <v>0.58</v>
-      </c>
-      <c r="DM5" t="n">
-        <v>45.47</v>
-      </c>
-      <c r="DN5" t="n">
-        <v>0.58</v>
-      </c>
-      <c r="DO5" t="n">
-        <v>1.84</v>
-      </c>
       <c r="DP5" t="n">
-        <v>10.47</v>
+        <v>10.8</v>
       </c>
       <c r="DQ5" t="n">
-        <v>10.32</v>
+        <v>10.55</v>
       </c>
       <c r="DR5" t="n">
-        <v>9.630000000000001</v>
+        <v>9.75</v>
       </c>
       <c r="DS5" t="n">
         <v>0.05</v>
@@ -2960,28 +2960,28 @@
         <v>0</v>
       </c>
       <c r="DV5" t="n">
-        <v>52.16</v>
+        <v>51.7</v>
       </c>
       <c r="DW5" t="n">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
       <c r="DX5" t="n">
-        <v>13.16</v>
+        <v>13.4</v>
       </c>
       <c r="DY5" t="n">
-        <v>8.74</v>
+        <v>8.949999999999999</v>
       </c>
       <c r="DZ5" t="n">
-        <v>4.42</v>
+        <v>4.45</v>
       </c>
       <c r="EA5" t="n">
-        <v>19.11</v>
+        <v>18.8</v>
       </c>
       <c r="EB5" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="EC5" t="n">
-        <v>1.63</v>
+        <v>1.6</v>
       </c>
     </row>
     <row r="6">
@@ -2991,10 +2991,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C6" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D6" t="n">
         <v>10</v>
@@ -3003,82 +3003,82 @@
         <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>0.44</v>
+        <v>0.5</v>
       </c>
       <c r="G6" t="n">
-        <v>4</v>
+        <v>4.4</v>
       </c>
       <c r="H6" t="n">
-        <v>134.56</v>
+        <v>131.7</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
       </c>
       <c r="J6" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="K6" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="M6" t="n">
+        <v>64.59999999999999</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="O6" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="P6" t="n">
+        <v>11</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>14</v>
+      </c>
+      <c r="R6" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="S6" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="T6" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="U6" t="n">
+        <v>0</v>
+      </c>
+      <c r="V6" t="n">
+        <v>0</v>
+      </c>
+      <c r="W6" t="n">
+        <v>0</v>
+      </c>
+      <c r="X6" t="n">
+        <v>65.3</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>18.6</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>12.7</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>20.8</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="AE6" t="n">
         <v>1</v>
-      </c>
-      <c r="K6" t="n">
-        <v>7</v>
-      </c>
-      <c r="L6" t="n">
-        <v>0.67</v>
-      </c>
-      <c r="M6" t="n">
-        <v>66.22</v>
-      </c>
-      <c r="N6" t="n">
-        <v>0.44</v>
-      </c>
-      <c r="O6" t="n">
-        <v>2.89</v>
-      </c>
-      <c r="P6" t="n">
-        <v>10.78</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>14.22</v>
-      </c>
-      <c r="R6" t="n">
-        <v>5.22</v>
-      </c>
-      <c r="S6" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="T6" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="U6" t="n">
-        <v>0</v>
-      </c>
-      <c r="V6" t="n">
-        <v>0</v>
-      </c>
-      <c r="W6" t="n">
-        <v>0</v>
-      </c>
-      <c r="X6" t="n">
-        <v>66.67</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>18.22</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>12.44</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>5.78</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>20.89</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="AE6" t="n">
-        <v>0.78</v>
       </c>
       <c r="AF6" t="n">
         <v>0.1</v>
@@ -3162,70 +3162,70 @@
         <v>1.7</v>
       </c>
       <c r="BG6" t="n">
-        <v>2.63</v>
+        <v>2.9</v>
       </c>
       <c r="BH6" t="n">
-        <v>10.21</v>
+        <v>10.25</v>
       </c>
       <c r="BI6" t="n">
-        <v>2.63</v>
+        <v>2.9</v>
       </c>
       <c r="BJ6" t="n">
-        <v>0.63</v>
+        <v>0.65</v>
       </c>
       <c r="BK6" t="n">
-        <v>0.84</v>
+        <v>0.95</v>
       </c>
       <c r="BL6" t="n">
-        <v>0.74</v>
+        <v>0.8</v>
       </c>
       <c r="BM6" t="n">
-        <v>0.42</v>
+        <v>0.5</v>
       </c>
       <c r="BN6" t="n">
-        <v>1.16</v>
+        <v>1.3</v>
       </c>
       <c r="BO6" t="n">
-        <v>1.47</v>
+        <v>1.6</v>
       </c>
       <c r="BP6" t="n">
-        <v>4.63</v>
+        <v>4.55</v>
       </c>
       <c r="BQ6" t="n">
-        <v>5.53</v>
+        <v>5.65</v>
       </c>
       <c r="BR6" t="n">
         <v>100</v>
       </c>
       <c r="BS6" t="n">
-        <v>84.20999999999999</v>
+        <v>85</v>
       </c>
       <c r="BT6" t="n">
-        <v>57.89</v>
+        <v>60</v>
       </c>
       <c r="BU6" t="n">
-        <v>15.79</v>
+        <v>20</v>
       </c>
       <c r="BV6" t="n">
-        <v>5.26</v>
+        <v>10</v>
       </c>
       <c r="BW6" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="BX6" t="n">
-        <v>78.95</v>
+        <v>80</v>
       </c>
       <c r="BY6" t="n">
-        <v>1.67</v>
+        <v>1.81</v>
       </c>
       <c r="BZ6" t="n">
-        <v>1.78</v>
+        <v>1.9</v>
       </c>
       <c r="CA6" t="n">
-        <v>3.88</v>
+        <v>3.86</v>
       </c>
       <c r="CB6" t="n">
-        <v>4</v>
+        <v>3.99</v>
       </c>
       <c r="CC6" t="n">
         <v>2.45</v>
@@ -3246,7 +3246,7 @@
         <v>1.53</v>
       </c>
       <c r="CI6" t="n">
-        <v>2.24</v>
+        <v>2.25</v>
       </c>
       <c r="CJ6" t="n">
         <v>1.64</v>
@@ -3255,13 +3255,13 @@
         <v>1.51</v>
       </c>
       <c r="CL6" t="n">
-        <v>2.01</v>
+        <v>2</v>
       </c>
       <c r="CM6" t="n">
-        <v>2.42</v>
+        <v>2.43</v>
       </c>
       <c r="CN6" t="n">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="CO6" t="n">
         <v>1.19</v>
@@ -3270,88 +3270,88 @@
         <v>1.69</v>
       </c>
       <c r="CQ6" t="n">
-        <v>2.68</v>
+        <v>2.67</v>
       </c>
       <c r="CR6" t="n">
         <v>1.38</v>
       </c>
       <c r="CS6" t="n">
-        <v>2.57</v>
+        <v>2.55</v>
       </c>
       <c r="CT6" t="n">
         <v>3.09</v>
       </c>
       <c r="CU6" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="CV6" t="n">
-        <v>2.29</v>
+        <v>2.31</v>
       </c>
       <c r="CW6" t="n">
         <v>1.68</v>
       </c>
       <c r="CX6" t="n">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="CY6" t="n">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="CZ6" t="n">
-        <v>2.33</v>
+        <v>2.35</v>
       </c>
       <c r="DA6" t="n">
-        <v>1.87</v>
+        <v>1.89</v>
       </c>
       <c r="DB6" t="n">
         <v>1.23</v>
       </c>
       <c r="DC6" t="n">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="DD6" t="n">
-        <v>2.8</v>
+        <v>2.78</v>
       </c>
       <c r="DE6" t="n">
         <v>0.05</v>
       </c>
       <c r="DF6" t="n">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="DG6" t="n">
-        <v>3.42</v>
+        <v>3.65</v>
       </c>
       <c r="DH6" t="n">
-        <v>117.27</v>
+        <v>116.7</v>
       </c>
       <c r="DI6" t="n">
         <v>0.05</v>
       </c>
       <c r="DJ6" t="n">
-        <v>1.37</v>
+        <v>1.45</v>
       </c>
       <c r="DK6" t="n">
-        <v>6.05</v>
+        <v>6.2</v>
       </c>
       <c r="DL6" t="n">
-        <v>0.74</v>
+        <v>0.7</v>
       </c>
       <c r="DM6" t="n">
-        <v>56.31</v>
+        <v>56</v>
       </c>
       <c r="DN6" t="n">
-        <v>0.42</v>
+        <v>0.5</v>
       </c>
       <c r="DO6" t="n">
-        <v>2.58</v>
+        <v>2.5</v>
       </c>
       <c r="DP6" t="n">
-        <v>10</v>
+        <v>10.15</v>
       </c>
       <c r="DQ6" t="n">
-        <v>13.16</v>
+        <v>13.1</v>
       </c>
       <c r="DR6" t="n">
-        <v>6.21</v>
+        <v>6</v>
       </c>
       <c r="DS6" t="n">
         <v>0</v>
@@ -3363,28 +3363,28 @@
         <v>0</v>
       </c>
       <c r="DV6" t="n">
-        <v>63.79</v>
+        <v>63.25</v>
       </c>
       <c r="DW6" t="n">
         <v>0.05</v>
       </c>
       <c r="DX6" t="n">
-        <v>16.47</v>
+        <v>16.75</v>
       </c>
       <c r="DY6" t="n">
-        <v>10.79</v>
+        <v>11</v>
       </c>
       <c r="DZ6" t="n">
-        <v>5.69</v>
+        <v>5.75</v>
       </c>
       <c r="EA6" t="n">
-        <v>20.26</v>
+        <v>20.25</v>
       </c>
       <c r="EB6" t="n">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="EC6" t="n">
-        <v>1.26</v>
+        <v>1.35</v>
       </c>
     </row>
     <row r="7">
@@ -3394,94 +3394,94 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C7" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D7" t="n">
         <v>10</v>
       </c>
       <c r="E7" t="n">
-        <v>0.11</v>
+        <v>0.2</v>
       </c>
       <c r="F7" t="n">
-        <v>1.56</v>
+        <v>1.6</v>
       </c>
       <c r="G7" t="n">
-        <v>2.56</v>
+        <v>2.3</v>
       </c>
       <c r="H7" t="n">
-        <v>89.56</v>
+        <v>89.59999999999999</v>
       </c>
       <c r="I7" t="n">
-        <v>0.33</v>
+        <v>0.3</v>
       </c>
       <c r="J7" t="n">
-        <v>2.44</v>
+        <v>2.4</v>
       </c>
       <c r="K7" t="n">
-        <v>4.56</v>
+        <v>4.6</v>
       </c>
       <c r="L7" t="n">
-        <v>0.11</v>
+        <v>0.2</v>
       </c>
       <c r="M7" t="n">
-        <v>50</v>
+        <v>50.5</v>
       </c>
       <c r="N7" t="n">
-        <v>0.89</v>
+        <v>0.8</v>
       </c>
       <c r="O7" t="n">
-        <v>2</v>
+        <v>2.3</v>
       </c>
       <c r="P7" t="n">
-        <v>10.56</v>
+        <v>10.8</v>
       </c>
       <c r="Q7" t="n">
-        <v>11.33</v>
+        <v>11.3</v>
       </c>
       <c r="R7" t="n">
-        <v>10.44</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="S7" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="T7" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="U7" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="V7" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>49.89</v>
+        <v>50.3</v>
       </c>
       <c r="Y7" t="n">
         <v>0</v>
       </c>
       <c r="Z7" t="n">
-        <v>10.22</v>
+        <v>10.6</v>
       </c>
       <c r="AA7" t="n">
-        <v>6.67</v>
+        <v>6.8</v>
       </c>
       <c r="AB7" t="n">
-        <v>3.56</v>
+        <v>3.8</v>
       </c>
       <c r="AC7" t="n">
-        <v>21.67</v>
+        <v>21.8</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="AE7" t="n">
-        <v>2.44</v>
+        <v>2.4</v>
       </c>
       <c r="AF7" t="n">
         <v>0.1</v>
@@ -3565,70 +3565,70 @@
         <v>2.3</v>
       </c>
       <c r="BG7" t="n">
-        <v>2.37</v>
+        <v>2.35</v>
       </c>
       <c r="BH7" t="n">
-        <v>11.53</v>
+        <v>11.5</v>
       </c>
       <c r="BI7" t="n">
-        <v>2.37</v>
+        <v>2.35</v>
       </c>
       <c r="BJ7" t="n">
-        <v>0.47</v>
+        <v>0.5</v>
       </c>
       <c r="BK7" t="n">
-        <v>0.47</v>
+        <v>0.45</v>
       </c>
       <c r="BL7" t="n">
-        <v>0.63</v>
+        <v>0.6</v>
       </c>
       <c r="BM7" t="n">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="BN7" t="n">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="BO7" t="n">
         <v>0.95</v>
       </c>
       <c r="BP7" t="n">
-        <v>5.16</v>
+        <v>5.25</v>
       </c>
       <c r="BQ7" t="n">
-        <v>6.37</v>
+        <v>6.25</v>
       </c>
       <c r="BR7" t="n">
-        <v>94.73999999999999</v>
+        <v>95</v>
       </c>
       <c r="BS7" t="n">
-        <v>68.42</v>
+        <v>70</v>
       </c>
       <c r="BT7" t="n">
-        <v>36.84</v>
+        <v>35</v>
       </c>
       <c r="BU7" t="n">
-        <v>26.32</v>
+        <v>25</v>
       </c>
       <c r="BV7" t="n">
-        <v>10.53</v>
+        <v>10</v>
       </c>
       <c r="BW7" t="n">
         <v>0</v>
       </c>
       <c r="BX7" t="n">
-        <v>63.16</v>
+        <v>65</v>
       </c>
       <c r="BY7" t="n">
-        <v>2.9</v>
+        <v>2.81</v>
       </c>
       <c r="BZ7" t="n">
-        <v>3.11</v>
+        <v>3</v>
       </c>
       <c r="CA7" t="n">
-        <v>3.7</v>
+        <v>3.68</v>
       </c>
       <c r="CB7" t="n">
-        <v>3.82</v>
+        <v>3.8</v>
       </c>
       <c r="CC7" t="n">
         <v>3.59</v>
@@ -3640,16 +3640,16 @@
         <v>1.3</v>
       </c>
       <c r="CF7" t="n">
-        <v>2.41</v>
+        <v>2.43</v>
       </c>
       <c r="CG7" t="n">
-        <v>3.27</v>
+        <v>3.24</v>
       </c>
       <c r="CH7" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="CI7" t="n">
-        <v>2.26</v>
+        <v>2.24</v>
       </c>
       <c r="CJ7" t="n">
         <v>1.61</v>
@@ -3661,7 +3661,7 @@
         <v>1.76</v>
       </c>
       <c r="CM7" t="n">
-        <v>2.77</v>
+        <v>2.76</v>
       </c>
       <c r="CN7" t="n">
         <v>2.11</v>
@@ -3670,25 +3670,25 @@
         <v>1.21</v>
       </c>
       <c r="CP7" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="CQ7" t="n">
-        <v>2.68</v>
+        <v>2.7</v>
       </c>
       <c r="CR7" t="n">
         <v>1.36</v>
       </c>
       <c r="CS7" t="n">
-        <v>2.52</v>
+        <v>2.54</v>
       </c>
       <c r="CT7" t="n">
-        <v>3.21</v>
+        <v>3.2</v>
       </c>
       <c r="CU7" t="n">
         <v>1.55</v>
       </c>
       <c r="CV7" t="n">
-        <v>2.39</v>
+        <v>2.37</v>
       </c>
       <c r="CW7" t="n">
         <v>1.63</v>
@@ -3697,64 +3697,64 @@
         <v>1.49</v>
       </c>
       <c r="CY7" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="CZ7" t="n">
         <v>2.56</v>
       </c>
       <c r="DA7" t="n">
-        <v>2.14</v>
+        <v>2.13</v>
       </c>
       <c r="DB7" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="DC7" t="n">
-        <v>1.74</v>
+        <v>1.76</v>
       </c>
       <c r="DD7" t="n">
-        <v>2.79</v>
+        <v>2.81</v>
       </c>
       <c r="DE7" t="n">
-        <v>0.1</v>
+        <v>0.15</v>
       </c>
       <c r="DF7" t="n">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="DG7" t="n">
-        <v>2.95</v>
+        <v>2.8</v>
       </c>
       <c r="DH7" t="n">
-        <v>86.63</v>
+        <v>86.8</v>
       </c>
       <c r="DI7" t="n">
-        <v>0.21</v>
+        <v>0.2</v>
       </c>
       <c r="DJ7" t="n">
-        <v>2.37</v>
+        <v>2.35</v>
       </c>
       <c r="DK7" t="n">
-        <v>5.11</v>
+        <v>5.1</v>
       </c>
       <c r="DL7" t="n">
-        <v>0.26</v>
+        <v>0.3</v>
       </c>
       <c r="DM7" t="n">
-        <v>46</v>
+        <v>46.45</v>
       </c>
       <c r="DN7" t="n">
-        <v>0.84</v>
+        <v>0.8</v>
       </c>
       <c r="DO7" t="n">
-        <v>2.16</v>
+        <v>2.3</v>
       </c>
       <c r="DP7" t="n">
-        <v>10.11</v>
+        <v>10.25</v>
       </c>
       <c r="DQ7" t="n">
-        <v>10.89</v>
+        <v>10.9</v>
       </c>
       <c r="DR7" t="n">
-        <v>9.470000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="DS7" t="n">
         <v>0.1</v>
@@ -3766,28 +3766,28 @@
         <v>0</v>
       </c>
       <c r="DV7" t="n">
-        <v>48.84</v>
+        <v>49.1</v>
       </c>
       <c r="DW7" t="n">
         <v>0</v>
       </c>
       <c r="DX7" t="n">
-        <v>10.47</v>
+        <v>10.65</v>
       </c>
       <c r="DY7" t="n">
-        <v>6.53</v>
+        <v>6.6</v>
       </c>
       <c r="DZ7" t="n">
-        <v>3.95</v>
+        <v>4.05</v>
       </c>
       <c r="EA7" t="n">
-        <v>20.95</v>
+        <v>21.05</v>
       </c>
       <c r="EB7" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="EC7" t="n">
-        <v>2.37</v>
+        <v>2.35</v>
       </c>
     </row>
     <row r="8">
@@ -3797,13 +3797,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C8" t="n">
         <v>10</v>
       </c>
       <c r="D8" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E8" t="n">
         <v>0.3</v>
@@ -3887,139 +3887,139 @@
         <v>1.4</v>
       </c>
       <c r="AF8" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.78</v>
+        <v>1.6</v>
       </c>
       <c r="AH8" t="n">
-        <v>2.22</v>
+        <v>2.1</v>
       </c>
       <c r="AI8" t="n">
-        <v>82.78</v>
+        <v>88</v>
       </c>
       <c r="AJ8" t="n">
         <v>0</v>
       </c>
       <c r="AK8" t="n">
-        <v>1.89</v>
+        <v>1.8</v>
       </c>
       <c r="AL8" t="n">
-        <v>4.56</v>
+        <v>4.4</v>
       </c>
       <c r="AM8" t="n">
-        <v>0.22</v>
+        <v>0.3</v>
       </c>
       <c r="AN8" t="n">
-        <v>39.89</v>
+        <v>44.1</v>
       </c>
       <c r="AO8" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="AP8" t="n">
-        <v>2.33</v>
+        <v>2.3</v>
       </c>
       <c r="AQ8" t="n">
-        <v>13.44</v>
+        <v>13.6</v>
       </c>
       <c r="AR8" t="n">
-        <v>11.56</v>
+        <v>12.1</v>
       </c>
       <c r="AS8" t="n">
-        <v>9</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="AT8" t="n">
-        <v>2.33</v>
+        <v>2.3</v>
       </c>
       <c r="AU8" t="n">
-        <v>1.56</v>
+        <v>1.4</v>
       </c>
       <c r="AV8" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="AW8" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="AX8" t="n">
         <v>0</v>
       </c>
       <c r="AY8" t="n">
-        <v>47.33</v>
+        <v>48.3</v>
       </c>
       <c r="AZ8" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="BA8" t="n">
-        <v>13.89</v>
+        <v>13.9</v>
       </c>
       <c r="BB8" t="n">
-        <v>9.56</v>
+        <v>9.5</v>
       </c>
       <c r="BC8" t="n">
-        <v>4.33</v>
+        <v>4.4</v>
       </c>
       <c r="BD8" t="n">
-        <v>22</v>
+        <v>22.7</v>
       </c>
       <c r="BE8" t="n">
-        <v>1.42</v>
+        <v>1.46</v>
       </c>
       <c r="BF8" t="n">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="BG8" t="n">
-        <v>2.95</v>
+        <v>2.9</v>
       </c>
       <c r="BH8" t="n">
-        <v>10.42</v>
+        <v>10.25</v>
       </c>
       <c r="BI8" t="n">
-        <v>2.95</v>
+        <v>2.9</v>
       </c>
       <c r="BJ8" t="n">
-        <v>0.84</v>
+        <v>0.9</v>
       </c>
       <c r="BK8" t="n">
-        <v>0.47</v>
+        <v>0.45</v>
       </c>
       <c r="BL8" t="n">
-        <v>1</v>
+        <v>0.95</v>
       </c>
       <c r="BM8" t="n">
-        <v>0.63</v>
+        <v>0.6</v>
       </c>
       <c r="BN8" t="n">
-        <v>1.63</v>
+        <v>1.55</v>
       </c>
       <c r="BO8" t="n">
-        <v>1.32</v>
+        <v>1.35</v>
       </c>
       <c r="BP8" t="n">
-        <v>4.89</v>
+        <v>4.95</v>
       </c>
       <c r="BQ8" t="n">
-        <v>5.47</v>
+        <v>5.25</v>
       </c>
       <c r="BR8" t="n">
-        <v>89.47</v>
+        <v>90</v>
       </c>
       <c r="BS8" t="n">
-        <v>78.95</v>
+        <v>80</v>
       </c>
       <c r="BT8" t="n">
-        <v>42.11</v>
+        <v>40</v>
       </c>
       <c r="BU8" t="n">
-        <v>31.58</v>
+        <v>30</v>
       </c>
       <c r="BV8" t="n">
-        <v>15.79</v>
+        <v>15</v>
       </c>
       <c r="BW8" t="n">
-        <v>10.53</v>
+        <v>10</v>
       </c>
       <c r="BX8" t="n">
-        <v>42.11</v>
+        <v>40</v>
       </c>
       <c r="BY8" t="n">
         <v>2.21</v>
@@ -4028,25 +4028,25 @@
         <v>2.3</v>
       </c>
       <c r="CA8" t="n">
-        <v>3.88</v>
+        <v>3.86</v>
       </c>
       <c r="CB8" t="n">
-        <v>3.95</v>
+        <v>3.93</v>
       </c>
       <c r="CC8" t="n">
-        <v>4.44</v>
+        <v>4.24</v>
       </c>
       <c r="CD8" t="n">
-        <v>4.3</v>
+        <v>4.14</v>
       </c>
       <c r="CE8" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="CF8" t="n">
         <v>2.26</v>
       </c>
       <c r="CG8" t="n">
-        <v>3.52</v>
+        <v>3.5</v>
       </c>
       <c r="CH8" t="n">
         <v>1.6</v>
@@ -4058,13 +4058,13 @@
         <v>1.56</v>
       </c>
       <c r="CK8" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="CL8" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="CM8" t="n">
-        <v>2.87</v>
+        <v>2.86</v>
       </c>
       <c r="CN8" t="n">
         <v>2.21</v>
@@ -4091,22 +4091,22 @@
         <v>1.64</v>
       </c>
       <c r="CV8" t="n">
-        <v>2.55</v>
+        <v>2.56</v>
       </c>
       <c r="CW8" t="n">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="CX8" t="n">
         <v>1.46</v>
       </c>
       <c r="CY8" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="CZ8" t="n">
         <v>2.67</v>
       </c>
       <c r="DA8" t="n">
-        <v>2.26</v>
+        <v>2.25</v>
       </c>
       <c r="DB8" t="n">
         <v>1.19</v>
@@ -4118,79 +4118,79 @@
         <v>2.49</v>
       </c>
       <c r="DE8" t="n">
-        <v>0.21</v>
+        <v>0.2</v>
       </c>
       <c r="DF8" t="n">
-        <v>1.37</v>
+        <v>1.3</v>
       </c>
       <c r="DG8" t="n">
-        <v>2.58</v>
+        <v>2.5</v>
       </c>
       <c r="DH8" t="n">
-        <v>91.05</v>
+        <v>93.25</v>
       </c>
       <c r="DI8" t="n">
         <v>0</v>
       </c>
       <c r="DJ8" t="n">
-        <v>1.63</v>
+        <v>1.6</v>
       </c>
       <c r="DK8" t="n">
-        <v>5.42</v>
+        <v>5.3</v>
       </c>
       <c r="DL8" t="n">
-        <v>0.31</v>
+        <v>0.35</v>
       </c>
       <c r="DM8" t="n">
-        <v>48.9</v>
+        <v>50.55</v>
       </c>
       <c r="DN8" t="n">
-        <v>0.21</v>
+        <v>0.25</v>
       </c>
       <c r="DO8" t="n">
-        <v>2.84</v>
+        <v>2.8</v>
       </c>
       <c r="DP8" t="n">
-        <v>11.89</v>
+        <v>12.05</v>
       </c>
       <c r="DQ8" t="n">
-        <v>11.84</v>
+        <v>12.1</v>
       </c>
       <c r="DR8" t="n">
-        <v>8.529999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="DS8" t="n">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
       <c r="DT8" t="n">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
       <c r="DU8" t="n">
         <v>0</v>
       </c>
       <c r="DV8" t="n">
-        <v>48.95</v>
+        <v>49.35</v>
       </c>
       <c r="DW8" t="n">
         <v>0.05</v>
       </c>
       <c r="DX8" t="n">
-        <v>15.63</v>
+        <v>15.55</v>
       </c>
       <c r="DY8" t="n">
-        <v>10.9</v>
+        <v>10.8</v>
       </c>
       <c r="DZ8" t="n">
-        <v>4.74</v>
+        <v>4.75</v>
       </c>
       <c r="EA8" t="n">
-        <v>21.05</v>
+        <v>21.45</v>
       </c>
       <c r="EB8" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="EC8" t="n">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="9">
@@ -4200,13 +4200,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C9" t="n">
         <v>10</v>
       </c>
       <c r="D9" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E9" t="n">
         <v>0.3</v>
@@ -4296,46 +4296,46 @@
         <v>2</v>
       </c>
       <c r="AH9" t="n">
-        <v>2.56</v>
+        <v>2.6</v>
       </c>
       <c r="AI9" t="n">
-        <v>78</v>
+        <v>77.8</v>
       </c>
       <c r="AJ9" t="n">
         <v>0</v>
       </c>
       <c r="AK9" t="n">
-        <v>3.11</v>
+        <v>3.1</v>
       </c>
       <c r="AL9" t="n">
-        <v>4.33</v>
+        <v>4.4</v>
       </c>
       <c r="AM9" t="n">
-        <v>0.22</v>
+        <v>0.4</v>
       </c>
       <c r="AN9" t="n">
-        <v>43.44</v>
+        <v>43.2</v>
       </c>
       <c r="AO9" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="AP9" t="n">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="AQ9" t="n">
-        <v>17</v>
+        <v>16.6</v>
       </c>
       <c r="AR9" t="n">
-        <v>10.89</v>
+        <v>10.5</v>
       </c>
       <c r="AS9" t="n">
-        <v>8.33</v>
+        <v>8.5</v>
       </c>
       <c r="AT9" t="n">
-        <v>1.78</v>
+        <v>1.6</v>
       </c>
       <c r="AU9" t="n">
-        <v>0.78</v>
+        <v>0.7</v>
       </c>
       <c r="AV9" t="n">
         <v>0</v>
@@ -4347,82 +4347,82 @@
         <v>0</v>
       </c>
       <c r="AY9" t="n">
-        <v>44.78</v>
+        <v>45.1</v>
       </c>
       <c r="AZ9" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="BA9" t="n">
-        <v>11.78</v>
+        <v>11.7</v>
       </c>
       <c r="BB9" t="n">
-        <v>7.56</v>
+        <v>7.6</v>
       </c>
       <c r="BC9" t="n">
-        <v>4.22</v>
+        <v>4.1</v>
       </c>
       <c r="BD9" t="n">
-        <v>20.67</v>
+        <v>19.5</v>
       </c>
       <c r="BE9" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="BF9" t="n">
         <v>3</v>
       </c>
       <c r="BG9" t="n">
-        <v>2.53</v>
+        <v>2.4</v>
       </c>
       <c r="BH9" t="n">
-        <v>9.890000000000001</v>
+        <v>10.3</v>
       </c>
       <c r="BI9" t="n">
-        <v>2.53</v>
+        <v>2.4</v>
       </c>
       <c r="BJ9" t="n">
-        <v>0.74</v>
+        <v>0.7</v>
       </c>
       <c r="BK9" t="n">
-        <v>0.47</v>
+        <v>0.45</v>
       </c>
       <c r="BL9" t="n">
-        <v>0.74</v>
+        <v>0.7</v>
       </c>
       <c r="BM9" t="n">
-        <v>0.58</v>
+        <v>0.55</v>
       </c>
       <c r="BN9" t="n">
-        <v>1.32</v>
+        <v>1.25</v>
       </c>
       <c r="BO9" t="n">
-        <v>1.21</v>
+        <v>1.15</v>
       </c>
       <c r="BP9" t="n">
-        <v>4.89</v>
+        <v>5</v>
       </c>
       <c r="BQ9" t="n">
-        <v>4.95</v>
+        <v>5.25</v>
       </c>
       <c r="BR9" t="n">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="BS9" t="n">
-        <v>78.95</v>
+        <v>75</v>
       </c>
       <c r="BT9" t="n">
-        <v>47.37</v>
+        <v>45</v>
       </c>
       <c r="BU9" t="n">
-        <v>21.05</v>
+        <v>20</v>
       </c>
       <c r="BV9" t="n">
-        <v>5.26</v>
+        <v>5</v>
       </c>
       <c r="BW9" t="n">
         <v>0</v>
       </c>
       <c r="BX9" t="n">
-        <v>52.63</v>
+        <v>50</v>
       </c>
       <c r="BY9" t="n">
         <v>2.94</v>
@@ -4431,55 +4431,55 @@
         <v>2.99</v>
       </c>
       <c r="CA9" t="n">
-        <v>3.54</v>
+        <v>3.5</v>
       </c>
       <c r="CB9" t="n">
-        <v>3.56</v>
+        <v>3.53</v>
       </c>
       <c r="CC9" t="n">
-        <v>4.22</v>
+        <v>4.12</v>
       </c>
       <c r="CD9" t="n">
-        <v>4.51</v>
+        <v>4.39</v>
       </c>
       <c r="CE9" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="CF9" t="n">
-        <v>2.69</v>
+        <v>2.72</v>
       </c>
       <c r="CG9" t="n">
-        <v>3.03</v>
+        <v>3</v>
       </c>
       <c r="CH9" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="CI9" t="n">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="CJ9" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="CK9" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="CL9" t="n">
-        <v>1.79</v>
+        <v>1.82</v>
       </c>
       <c r="CM9" t="n">
-        <v>2.58</v>
+        <v>2.56</v>
       </c>
       <c r="CN9" t="n">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="CO9" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="CP9" t="n">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="CQ9" t="n">
-        <v>3.17</v>
+        <v>3.27</v>
       </c>
       <c r="CR9" t="n">
         <v>1.39</v>
@@ -4494,43 +4494,43 @@
         <v>1.45</v>
       </c>
       <c r="CV9" t="n">
-        <v>2.11</v>
+        <v>2.09</v>
       </c>
       <c r="CW9" t="n">
-        <v>1.79</v>
+        <v>1.81</v>
       </c>
       <c r="CX9" t="n">
-        <v>1.51</v>
+        <v>1.53</v>
       </c>
       <c r="CY9" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="CZ9" t="n">
-        <v>2.51</v>
+        <v>2.47</v>
       </c>
       <c r="DA9" t="n">
-        <v>2.03</v>
+        <v>2.02</v>
       </c>
       <c r="DB9" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="DC9" t="n">
-        <v>1.96</v>
+        <v>2</v>
       </c>
       <c r="DD9" t="n">
-        <v>3.3</v>
+        <v>3.39</v>
       </c>
       <c r="DE9" t="n">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
       <c r="DF9" t="n">
-        <v>2.21</v>
+        <v>2.2</v>
       </c>
       <c r="DG9" t="n">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="DH9" t="n">
-        <v>78.95</v>
+        <v>78.8</v>
       </c>
       <c r="DI9" t="n">
         <v>0</v>
@@ -4539,28 +4539,28 @@
         <v>3.1</v>
       </c>
       <c r="DK9" t="n">
-        <v>4.37</v>
+        <v>4.4</v>
       </c>
       <c r="DL9" t="n">
-        <v>0.37</v>
+        <v>0.45</v>
       </c>
       <c r="DM9" t="n">
-        <v>41.26</v>
+        <v>41.25</v>
       </c>
       <c r="DN9" t="n">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="DO9" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="DP9" t="n">
-        <v>16.79</v>
+        <v>16.6</v>
       </c>
       <c r="DQ9" t="n">
-        <v>11.63</v>
+        <v>11.4</v>
       </c>
       <c r="DR9" t="n">
-        <v>8.31</v>
+        <v>8.4</v>
       </c>
       <c r="DS9" t="n">
         <v>0</v>
@@ -4572,25 +4572,25 @@
         <v>0</v>
       </c>
       <c r="DV9" t="n">
-        <v>45.32</v>
+        <v>45.45</v>
       </c>
       <c r="DW9" t="n">
         <v>0.05</v>
       </c>
       <c r="DX9" t="n">
-        <v>13.11</v>
+        <v>13</v>
       </c>
       <c r="DY9" t="n">
-        <v>8.69</v>
+        <v>8.65</v>
       </c>
       <c r="DZ9" t="n">
-        <v>4.42</v>
+        <v>4.35</v>
       </c>
       <c r="EA9" t="n">
-        <v>19.69</v>
+        <v>19.15</v>
       </c>
       <c r="EB9" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="EC9" t="n">
         <v>3.05</v>
@@ -4603,10 +4603,10 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C10" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D10" t="n">
         <v>10</v>
@@ -4615,49 +4615,49 @@
         <v>0</v>
       </c>
       <c r="F10" t="n">
-        <v>0.89</v>
+        <v>0.8</v>
       </c>
       <c r="G10" t="n">
-        <v>2.56</v>
+        <v>3.1</v>
       </c>
       <c r="H10" t="n">
-        <v>79.22</v>
+        <v>82.09999999999999</v>
       </c>
       <c r="I10" t="n">
-        <v>0.22</v>
+        <v>0.3</v>
       </c>
       <c r="J10" t="n">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="K10" t="n">
-        <v>5</v>
+        <v>5.8</v>
       </c>
       <c r="L10" t="n">
-        <v>0.11</v>
+        <v>0.2</v>
       </c>
       <c r="M10" t="n">
-        <v>43.33</v>
+        <v>46.8</v>
       </c>
       <c r="N10" t="n">
-        <v>0.78</v>
+        <v>0.8</v>
       </c>
       <c r="O10" t="n">
-        <v>2.44</v>
+        <v>2.7</v>
       </c>
       <c r="P10" t="n">
-        <v>11.44</v>
+        <v>11</v>
       </c>
       <c r="Q10" t="n">
-        <v>11.44</v>
+        <v>11.6</v>
       </c>
       <c r="R10" t="n">
-        <v>8.779999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="S10" t="n">
-        <v>0.67</v>
+        <v>0.6</v>
       </c>
       <c r="T10" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.5</v>
       </c>
       <c r="U10" t="n">
         <v>0</v>
@@ -4669,28 +4669,28 @@
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>36.78</v>
+        <v>38.3</v>
       </c>
       <c r="Y10" t="n">
         <v>0</v>
       </c>
       <c r="Z10" t="n">
-        <v>10.56</v>
+        <v>11</v>
       </c>
       <c r="AA10" t="n">
-        <v>7.78</v>
+        <v>7.8</v>
       </c>
       <c r="AB10" t="n">
-        <v>2.78</v>
+        <v>3.2</v>
       </c>
       <c r="AC10" t="n">
-        <v>20.89</v>
+        <v>21.5</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.11</v>
+        <v>1.2</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="AF10" t="n">
         <v>0.1</v>
@@ -4774,70 +4774,70 @@
         <v>1.7</v>
       </c>
       <c r="BG10" t="n">
-        <v>1.89</v>
+        <v>1.8</v>
       </c>
       <c r="BH10" t="n">
-        <v>8.26</v>
+        <v>8.75</v>
       </c>
       <c r="BI10" t="n">
-        <v>1.89</v>
+        <v>1.8</v>
       </c>
       <c r="BJ10" t="n">
-        <v>0.53</v>
+        <v>0.5</v>
       </c>
       <c r="BK10" t="n">
-        <v>0.37</v>
+        <v>0.35</v>
       </c>
       <c r="BL10" t="n">
-        <v>0.53</v>
+        <v>0.5</v>
       </c>
       <c r="BM10" t="n">
-        <v>0.47</v>
+        <v>0.45</v>
       </c>
       <c r="BN10" t="n">
-        <v>1</v>
+        <v>0.95</v>
       </c>
       <c r="BO10" t="n">
-        <v>0.89</v>
+        <v>0.85</v>
       </c>
       <c r="BP10" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="BQ10" t="n">
+        <v>5.05</v>
+      </c>
+      <c r="BR10" t="n">
+        <v>70</v>
+      </c>
+      <c r="BS10" t="n">
+        <v>50</v>
+      </c>
+      <c r="BT10" t="n">
+        <v>40</v>
+      </c>
+      <c r="BU10" t="n">
+        <v>15</v>
+      </c>
+      <c r="BV10" t="n">
+        <v>5</v>
+      </c>
+      <c r="BW10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX10" t="n">
+        <v>45</v>
+      </c>
+      <c r="BY10" t="n">
         <v>3.53</v>
       </c>
-      <c r="BQ10" t="n">
-        <v>4.74</v>
-      </c>
-      <c r="BR10" t="n">
-        <v>73.68000000000001</v>
-      </c>
-      <c r="BS10" t="n">
-        <v>52.63</v>
-      </c>
-      <c r="BT10" t="n">
-        <v>42.11</v>
-      </c>
-      <c r="BU10" t="n">
-        <v>15.79</v>
-      </c>
-      <c r="BV10" t="n">
-        <v>5.26</v>
-      </c>
-      <c r="BW10" t="n">
-        <v>0</v>
-      </c>
-      <c r="BX10" t="n">
-        <v>47.37</v>
-      </c>
-      <c r="BY10" t="n">
-        <v>3.64</v>
-      </c>
       <c r="BZ10" t="n">
-        <v>3.82</v>
+        <v>3.69</v>
       </c>
       <c r="CA10" t="n">
-        <v>3.49</v>
+        <v>3.46</v>
       </c>
       <c r="CB10" t="n">
-        <v>3.54</v>
+        <v>3.51</v>
       </c>
       <c r="CC10" t="n">
         <v>4.09</v>
@@ -4846,43 +4846,43 @@
         <v>4.35</v>
       </c>
       <c r="CE10" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="CF10" t="n">
-        <v>2.79</v>
+        <v>2.82</v>
       </c>
       <c r="CG10" t="n">
-        <v>2.85</v>
+        <v>2.83</v>
       </c>
       <c r="CH10" t="n">
         <v>1.39</v>
       </c>
       <c r="CI10" t="n">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="CJ10" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="CK10" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="CL10" t="n">
-        <v>1.99</v>
+        <v>2.01</v>
       </c>
       <c r="CM10" t="n">
-        <v>2.33</v>
+        <v>2.32</v>
       </c>
       <c r="CN10" t="n">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="CO10" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="CP10" t="n">
-        <v>2</v>
+        <v>2.01</v>
       </c>
       <c r="CQ10" t="n">
-        <v>3.5</v>
+        <v>3.59</v>
       </c>
       <c r="CR10" t="n">
         <v>1.4</v>
@@ -4897,10 +4897,10 @@
         <v>1.42</v>
       </c>
       <c r="CV10" t="n">
-        <v>2.01</v>
+        <v>2</v>
       </c>
       <c r="CW10" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="CX10" t="n">
         <v>1.62</v>
@@ -4912,58 +4912,58 @@
         <v>2.29</v>
       </c>
       <c r="DA10" t="n">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="DB10" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="DC10" t="n">
-        <v>2.07</v>
+        <v>2.1</v>
       </c>
       <c r="DD10" t="n">
-        <v>3.58</v>
+        <v>3.65</v>
       </c>
       <c r="DE10" t="n">
         <v>0.05</v>
       </c>
       <c r="DF10" t="n">
-        <v>1.05</v>
+        <v>1</v>
       </c>
       <c r="DG10" t="n">
-        <v>2.37</v>
+        <v>2.65</v>
       </c>
       <c r="DH10" t="n">
-        <v>79.26000000000001</v>
+        <v>80.7</v>
       </c>
       <c r="DI10" t="n">
-        <v>0.1</v>
+        <v>0.15</v>
       </c>
       <c r="DJ10" t="n">
-        <v>1.79</v>
+        <v>1.75</v>
       </c>
       <c r="DK10" t="n">
-        <v>4.21</v>
+        <v>4.65</v>
       </c>
       <c r="DL10" t="n">
-        <v>0.16</v>
+        <v>0.2</v>
       </c>
       <c r="DM10" t="n">
-        <v>38.26</v>
+        <v>40.25</v>
       </c>
       <c r="DN10" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.7</v>
       </c>
       <c r="DO10" t="n">
-        <v>1.84</v>
+        <v>2</v>
       </c>
       <c r="DP10" t="n">
-        <v>11.89</v>
+        <v>11.65</v>
       </c>
       <c r="DQ10" t="n">
-        <v>12.21</v>
+        <v>12.25</v>
       </c>
       <c r="DR10" t="n">
-        <v>8.789999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="DS10" t="n">
         <v>0</v>
@@ -4975,28 +4975,28 @@
         <v>0</v>
       </c>
       <c r="DV10" t="n">
-        <v>34.32</v>
+        <v>35.2</v>
       </c>
       <c r="DW10" t="n">
         <v>0.05</v>
       </c>
       <c r="DX10" t="n">
-        <v>9.529999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="DY10" t="n">
-        <v>6.95</v>
+        <v>7</v>
       </c>
       <c r="DZ10" t="n">
-        <v>2.58</v>
+        <v>2.8</v>
       </c>
       <c r="EA10" t="n">
-        <v>20.9</v>
+        <v>21.2</v>
       </c>
       <c r="EB10" t="n">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="EC10" t="n">
-        <v>1.69</v>
+        <v>1.65</v>
       </c>
     </row>
     <row r="11">
@@ -5006,94 +5006,94 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C11" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D11" t="n">
         <v>9</v>
       </c>
       <c r="E11" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="F11" t="n">
-        <v>1.8</v>
+        <v>1.64</v>
       </c>
       <c r="G11" t="n">
-        <v>3.3</v>
+        <v>3.45</v>
       </c>
       <c r="H11" t="n">
-        <v>104.9</v>
+        <v>107.73</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
       </c>
       <c r="J11" t="n">
-        <v>2.9</v>
+        <v>2.73</v>
       </c>
       <c r="K11" t="n">
-        <v>6.4</v>
+        <v>6.55</v>
       </c>
       <c r="L11" t="n">
-        <v>0.6</v>
+        <v>0.73</v>
       </c>
       <c r="M11" t="n">
-        <v>58.6</v>
+        <v>57.64</v>
       </c>
       <c r="N11" t="n">
         <v>1</v>
       </c>
       <c r="O11" t="n">
-        <v>3.1</v>
+        <v>3.09</v>
       </c>
       <c r="P11" t="n">
-        <v>13.4</v>
+        <v>12.82</v>
       </c>
       <c r="Q11" t="n">
-        <v>11.3</v>
+        <v>11.64</v>
       </c>
       <c r="R11" t="n">
-        <v>7.3</v>
+        <v>7.36</v>
       </c>
       <c r="S11" t="n">
-        <v>0.8</v>
+        <v>0.91</v>
       </c>
       <c r="T11" t="n">
-        <v>1.7</v>
+        <v>1.64</v>
       </c>
       <c r="U11" t="n">
-        <v>0.1</v>
+        <v>0.18</v>
       </c>
       <c r="V11" t="n">
-        <v>0.1</v>
+        <v>0.18</v>
       </c>
       <c r="W11" t="n">
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>50.2</v>
+        <v>51.18</v>
       </c>
       <c r="Y11" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="Z11" t="n">
-        <v>16.8</v>
+        <v>16.82</v>
       </c>
       <c r="AA11" t="n">
-        <v>11</v>
+        <v>11.18</v>
       </c>
       <c r="AB11" t="n">
-        <v>5.8</v>
+        <v>5.64</v>
       </c>
       <c r="AC11" t="n">
-        <v>19.6</v>
+        <v>20.09</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.89</v>
+        <v>1.87</v>
       </c>
       <c r="AE11" t="n">
-        <v>2.7</v>
+        <v>2.55</v>
       </c>
       <c r="AF11" t="n">
         <v>0.11</v>
@@ -5177,67 +5177,67 @@
         <v>2.44</v>
       </c>
       <c r="BG11" t="n">
-        <v>2.47</v>
+        <v>2.5</v>
       </c>
       <c r="BH11" t="n">
-        <v>10.21</v>
+        <v>10.25</v>
       </c>
       <c r="BI11" t="n">
-        <v>2.47</v>
+        <v>2.5</v>
       </c>
       <c r="BJ11" t="n">
-        <v>0.68</v>
+        <v>0.7</v>
       </c>
       <c r="BK11" t="n">
-        <v>0.26</v>
+        <v>0.35</v>
       </c>
       <c r="BL11" t="n">
-        <v>0.84</v>
+        <v>0.8</v>
       </c>
       <c r="BM11" t="n">
-        <v>0.68</v>
+        <v>0.65</v>
       </c>
       <c r="BN11" t="n">
-        <v>1.53</v>
+        <v>1.45</v>
       </c>
       <c r="BO11" t="n">
-        <v>0.95</v>
+        <v>1.05</v>
       </c>
       <c r="BP11" t="n">
+        <v>4.95</v>
+      </c>
+      <c r="BQ11" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BR11" t="n">
+        <v>95</v>
+      </c>
+      <c r="BS11" t="n">
+        <v>65</v>
+      </c>
+      <c r="BT11" t="n">
+        <v>40</v>
+      </c>
+      <c r="BU11" t="n">
+        <v>30</v>
+      </c>
+      <c r="BV11" t="n">
+        <v>10</v>
+      </c>
+      <c r="BW11" t="n">
         <v>5</v>
       </c>
-      <c r="BQ11" t="n">
-        <v>5.21</v>
-      </c>
-      <c r="BR11" t="n">
-        <v>94.73999999999999</v>
-      </c>
-      <c r="BS11" t="n">
-        <v>63.16</v>
-      </c>
-      <c r="BT11" t="n">
-        <v>36.84</v>
-      </c>
-      <c r="BU11" t="n">
-        <v>31.58</v>
-      </c>
-      <c r="BV11" t="n">
-        <v>10.53</v>
-      </c>
-      <c r="BW11" t="n">
-        <v>5.26</v>
-      </c>
       <c r="BX11" t="n">
-        <v>42.11</v>
+        <v>45</v>
       </c>
       <c r="BY11" t="n">
-        <v>1.98</v>
+        <v>1.96</v>
       </c>
       <c r="BZ11" t="n">
-        <v>2.08</v>
+        <v>2.05</v>
       </c>
       <c r="CA11" t="n">
-        <v>3.63</v>
+        <v>3.62</v>
       </c>
       <c r="CB11" t="n">
         <v>3.73</v>
@@ -5249,22 +5249,22 @@
         <v>2.58</v>
       </c>
       <c r="CE11" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="CF11" t="n">
-        <v>2.54</v>
+        <v>2.55</v>
       </c>
       <c r="CG11" t="n">
-        <v>3.08</v>
+        <v>3.09</v>
       </c>
       <c r="CH11" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="CI11" t="n">
-        <v>2.15</v>
+        <v>2.14</v>
       </c>
       <c r="CJ11" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="CK11" t="n">
         <v>1.47</v>
@@ -5282,37 +5282,37 @@
         <v>1.23</v>
       </c>
       <c r="CP11" t="n">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="CQ11" t="n">
-        <v>2.9</v>
+        <v>2.92</v>
       </c>
       <c r="CR11" t="n">
         <v>1.35</v>
       </c>
       <c r="CS11" t="n">
-        <v>2.64</v>
+        <v>2.65</v>
       </c>
       <c r="CT11" t="n">
-        <v>3.24</v>
+        <v>3.23</v>
       </c>
       <c r="CU11" t="n">
         <v>1.5</v>
       </c>
       <c r="CV11" t="n">
-        <v>2.24</v>
+        <v>2.23</v>
       </c>
       <c r="CW11" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="CX11" t="n">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="CY11" t="n">
         <v>1.82</v>
       </c>
       <c r="CZ11" t="n">
-        <v>2.5</v>
+        <v>2.51</v>
       </c>
       <c r="DA11" t="n">
         <v>1.99</v>
@@ -5324,82 +5324,82 @@
         <v>1.82</v>
       </c>
       <c r="DD11" t="n">
-        <v>2.99</v>
+        <v>3</v>
       </c>
       <c r="DE11" t="n">
         <v>0.1</v>
       </c>
       <c r="DF11" t="n">
-        <v>1.74</v>
+        <v>1.65</v>
       </c>
       <c r="DG11" t="n">
-        <v>3.11</v>
+        <v>3.2</v>
       </c>
       <c r="DH11" t="n">
-        <v>100.16</v>
+        <v>101.95</v>
       </c>
       <c r="DI11" t="n">
         <v>0</v>
       </c>
       <c r="DJ11" t="n">
-        <v>2.79</v>
+        <v>2.7</v>
       </c>
       <c r="DK11" t="n">
-        <v>6.31</v>
+        <v>6.4</v>
       </c>
       <c r="DL11" t="n">
-        <v>0.47</v>
+        <v>0.55</v>
       </c>
       <c r="DM11" t="n">
-        <v>57.1</v>
+        <v>56.65</v>
       </c>
       <c r="DN11" t="n">
         <v>1</v>
       </c>
       <c r="DO11" t="n">
-        <v>3.21</v>
+        <v>3.2</v>
       </c>
       <c r="DP11" t="n">
-        <v>13.53</v>
+        <v>13.2</v>
       </c>
       <c r="DQ11" t="n">
-        <v>10.48</v>
+        <v>10.7</v>
       </c>
       <c r="DR11" t="n">
-        <v>7.63</v>
+        <v>7.65</v>
       </c>
       <c r="DS11" t="n">
-        <v>0.16</v>
+        <v>0.2</v>
       </c>
       <c r="DT11" t="n">
-        <v>0.16</v>
+        <v>0.2</v>
       </c>
       <c r="DU11" t="n">
         <v>0</v>
       </c>
       <c r="DV11" t="n">
-        <v>52.9</v>
+        <v>53.3</v>
       </c>
       <c r="DW11" t="n">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
       <c r="DX11" t="n">
-        <v>14.95</v>
+        <v>15.05</v>
       </c>
       <c r="DY11" t="n">
-        <v>10.05</v>
+        <v>10.2</v>
       </c>
       <c r="DZ11" t="n">
-        <v>4.9</v>
+        <v>4.85</v>
       </c>
       <c r="EA11" t="n">
-        <v>21.74</v>
+        <v>21.9</v>
       </c>
       <c r="EB11" t="n">
         <v>1.7</v>
       </c>
       <c r="EC11" t="n">
-        <v>2.58</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="12">
@@ -5409,94 +5409,94 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C12" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D12" t="n">
         <v>9</v>
       </c>
       <c r="E12" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="F12" t="n">
-        <v>1.2</v>
+        <v>1.36</v>
       </c>
       <c r="G12" t="n">
-        <v>2.3</v>
+        <v>2.36</v>
       </c>
       <c r="H12" t="n">
-        <v>98.8</v>
+        <v>96.73</v>
       </c>
       <c r="I12" t="n">
         <v>0</v>
       </c>
       <c r="J12" t="n">
-        <v>2.1</v>
+        <v>2.18</v>
       </c>
       <c r="K12" t="n">
-        <v>4.8</v>
+        <v>4.82</v>
       </c>
       <c r="L12" t="n">
-        <v>0.6</v>
+        <v>0.64</v>
       </c>
       <c r="M12" t="n">
-        <v>45.3</v>
+        <v>44.27</v>
       </c>
       <c r="N12" t="n">
-        <v>0.8</v>
+        <v>0.73</v>
       </c>
       <c r="O12" t="n">
-        <v>2.5</v>
+        <v>2.36</v>
       </c>
       <c r="P12" t="n">
-        <v>11.3</v>
+        <v>12</v>
       </c>
       <c r="Q12" t="n">
-        <v>12.7</v>
+        <v>12</v>
       </c>
       <c r="R12" t="n">
-        <v>6.8</v>
+        <v>7.09</v>
       </c>
       <c r="S12" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="T12" t="n">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="U12" t="n">
-        <v>0.4</v>
+        <v>0.36</v>
       </c>
       <c r="V12" t="n">
-        <v>0.4</v>
+        <v>0.36</v>
       </c>
       <c r="W12" t="n">
         <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>50.7</v>
+        <v>49.91</v>
       </c>
       <c r="Y12" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="Z12" t="n">
-        <v>14</v>
+        <v>13.36</v>
       </c>
       <c r="AA12" t="n">
-        <v>8.4</v>
+        <v>8</v>
       </c>
       <c r="AB12" t="n">
-        <v>5.6</v>
+        <v>5.36</v>
       </c>
       <c r="AC12" t="n">
-        <v>20.2</v>
+        <v>20.55</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.61</v>
+        <v>1.54</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="AF12" t="n">
         <v>0</v>
@@ -5580,49 +5580,49 @@
         <v>2.22</v>
       </c>
       <c r="BG12" t="n">
-        <v>2.21</v>
+        <v>2.25</v>
       </c>
       <c r="BH12" t="n">
-        <v>9.26</v>
+        <v>9.4</v>
       </c>
       <c r="BI12" t="n">
-        <v>2.21</v>
+        <v>2.25</v>
       </c>
       <c r="BJ12" t="n">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="BK12" t="n">
-        <v>0.37</v>
+        <v>0.4</v>
       </c>
       <c r="BL12" t="n">
-        <v>0.58</v>
+        <v>0.6</v>
       </c>
       <c r="BM12" t="n">
-        <v>0.53</v>
+        <v>0.5</v>
       </c>
       <c r="BN12" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="BO12" t="n">
-        <v>1.11</v>
+        <v>1.15</v>
       </c>
       <c r="BP12" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="BQ12" t="n">
-        <v>5.32</v>
+        <v>5.35</v>
       </c>
       <c r="BR12" t="n">
-        <v>94.73999999999999</v>
+        <v>95</v>
       </c>
       <c r="BS12" t="n">
-        <v>73.68000000000001</v>
+        <v>75</v>
       </c>
       <c r="BT12" t="n">
-        <v>36.84</v>
+        <v>40</v>
       </c>
       <c r="BU12" t="n">
-        <v>15.79</v>
+        <v>15</v>
       </c>
       <c r="BV12" t="n">
         <v>0</v>
@@ -5631,13 +5631,13 @@
         <v>0</v>
       </c>
       <c r="BX12" t="n">
-        <v>52.63</v>
+        <v>55</v>
       </c>
       <c r="BY12" t="n">
-        <v>2.79</v>
+        <v>2.71</v>
       </c>
       <c r="BZ12" t="n">
-        <v>3.04</v>
+        <v>2.93</v>
       </c>
       <c r="CA12" t="n">
         <v>3.56</v>
@@ -5655,16 +5655,16 @@
         <v>1.34</v>
       </c>
       <c r="CF12" t="n">
-        <v>2.59</v>
+        <v>2.6</v>
       </c>
       <c r="CG12" t="n">
         <v>3.05</v>
       </c>
       <c r="CH12" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="CI12" t="n">
-        <v>2.11</v>
+        <v>2.1</v>
       </c>
       <c r="CJ12" t="n">
         <v>1.69</v>
@@ -5673,7 +5673,7 @@
         <v>1.49</v>
       </c>
       <c r="CL12" t="n">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="CM12" t="n">
         <v>2.45</v>
@@ -5682,13 +5682,13 @@
         <v>1.89</v>
       </c>
       <c r="CO12" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="CP12" t="n">
         <v>1.83</v>
       </c>
       <c r="CQ12" t="n">
-        <v>3.04</v>
+        <v>3.03</v>
       </c>
       <c r="CR12" t="n">
         <v>1.37</v>
@@ -5709,13 +5709,13 @@
         <v>1.75</v>
       </c>
       <c r="CX12" t="n">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="CY12" t="n">
         <v>1.93</v>
       </c>
       <c r="CZ12" t="n">
-        <v>2.35</v>
+        <v>2.36</v>
       </c>
       <c r="DA12" t="n">
         <v>1.89</v>
@@ -5733,76 +5733,76 @@
         <v>0.05</v>
       </c>
       <c r="DF12" t="n">
-        <v>1.47</v>
+        <v>1.55</v>
       </c>
       <c r="DG12" t="n">
-        <v>2.16</v>
+        <v>2.2</v>
       </c>
       <c r="DH12" t="n">
-        <v>91.84</v>
+        <v>91.05</v>
       </c>
       <c r="DI12" t="n">
         <v>0</v>
       </c>
       <c r="DJ12" t="n">
-        <v>2.26</v>
+        <v>2.3</v>
       </c>
       <c r="DK12" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="DL12" t="n">
-        <v>0.47</v>
+        <v>0.5</v>
       </c>
       <c r="DM12" t="n">
-        <v>38.58</v>
+        <v>38.35</v>
       </c>
       <c r="DN12" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.65</v>
       </c>
       <c r="DO12" t="n">
-        <v>1.79</v>
+        <v>1.75</v>
       </c>
       <c r="DP12" t="n">
-        <v>12.37</v>
+        <v>12.7</v>
       </c>
       <c r="DQ12" t="n">
-        <v>12.47</v>
+        <v>12.1</v>
       </c>
       <c r="DR12" t="n">
-        <v>7.63</v>
+        <v>7.75</v>
       </c>
       <c r="DS12" t="n">
-        <v>0.21</v>
+        <v>0.2</v>
       </c>
       <c r="DT12" t="n">
-        <v>0.21</v>
+        <v>0.2</v>
       </c>
       <c r="DU12" t="n">
         <v>0</v>
       </c>
       <c r="DV12" t="n">
-        <v>46.9</v>
+        <v>46.65</v>
       </c>
       <c r="DW12" t="n">
         <v>0.1</v>
       </c>
       <c r="DX12" t="n">
-        <v>12.05</v>
+        <v>11.8</v>
       </c>
       <c r="DY12" t="n">
-        <v>7.58</v>
+        <v>7.4</v>
       </c>
       <c r="DZ12" t="n">
-        <v>4.47</v>
+        <v>4.4</v>
       </c>
       <c r="EA12" t="n">
-        <v>19.53</v>
+        <v>19.75</v>
       </c>
       <c r="EB12" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="EC12" t="n">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
     </row>
     <row r="13">
@@ -5812,13 +5812,13 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C13" t="n">
         <v>10</v>
       </c>
       <c r="D13" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E13" t="n">
         <v>0.2</v>
@@ -5905,136 +5905,136 @@
         <v>0</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="AH13" t="n">
-        <v>3.44</v>
+        <v>3.3</v>
       </c>
       <c r="AI13" t="n">
-        <v>96.33</v>
+        <v>99.59999999999999</v>
       </c>
       <c r="AJ13" t="n">
-        <v>0.11</v>
+        <v>0.2</v>
       </c>
       <c r="AK13" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="AL13" t="n">
-        <v>5.56</v>
+        <v>5.5</v>
       </c>
       <c r="AM13" t="n">
-        <v>0.33</v>
+        <v>0.4</v>
       </c>
       <c r="AN13" t="n">
-        <v>52</v>
+        <v>52.7</v>
       </c>
       <c r="AO13" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.7</v>
       </c>
       <c r="AP13" t="n">
-        <v>2.11</v>
+        <v>2.2</v>
       </c>
       <c r="AQ13" t="n">
-        <v>12.67</v>
+        <v>12.5</v>
       </c>
       <c r="AR13" t="n">
-        <v>11.22</v>
+        <v>10.8</v>
       </c>
       <c r="AS13" t="n">
-        <v>8.67</v>
+        <v>8.6</v>
       </c>
       <c r="AT13" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AU13" t="n">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="AV13" t="n">
-        <v>0.44</v>
+        <v>0.4</v>
       </c>
       <c r="AW13" t="n">
-        <v>0.44</v>
+        <v>0.4</v>
       </c>
       <c r="AX13" t="n">
         <v>0</v>
       </c>
       <c r="AY13" t="n">
-        <v>51.44</v>
+        <v>53.2</v>
       </c>
       <c r="AZ13" t="n">
         <v>0</v>
       </c>
       <c r="BA13" t="n">
-        <v>12.89</v>
+        <v>13.2</v>
       </c>
       <c r="BB13" t="n">
-        <v>8.779999999999999</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BC13" t="n">
-        <v>4.11</v>
+        <v>4</v>
       </c>
       <c r="BD13" t="n">
-        <v>23.22</v>
+        <v>22.3</v>
       </c>
       <c r="BE13" t="n">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="BF13" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="BG13" t="n">
-        <v>2.63</v>
+        <v>2.65</v>
       </c>
       <c r="BH13" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BI13" t="n">
-        <v>2.63</v>
+        <v>2.65</v>
       </c>
       <c r="BJ13" t="n">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="BK13" t="n">
-        <v>0.42</v>
+        <v>0.45</v>
       </c>
       <c r="BL13" t="n">
-        <v>0.68</v>
+        <v>0.65</v>
       </c>
       <c r="BM13" t="n">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="BN13" t="n">
-        <v>1.47</v>
+        <v>1.45</v>
       </c>
       <c r="BO13" t="n">
-        <v>1.16</v>
+        <v>1.2</v>
       </c>
       <c r="BP13" t="n">
-        <v>4.05</v>
+        <v>4</v>
       </c>
       <c r="BQ13" t="n">
-        <v>5.95</v>
+        <v>5.8</v>
       </c>
       <c r="BR13" t="n">
         <v>100</v>
       </c>
       <c r="BS13" t="n">
-        <v>84.20999999999999</v>
+        <v>85</v>
       </c>
       <c r="BT13" t="n">
-        <v>52.63</v>
+        <v>55</v>
       </c>
       <c r="BU13" t="n">
-        <v>21.05</v>
+        <v>20</v>
       </c>
       <c r="BV13" t="n">
-        <v>5.26</v>
+        <v>5</v>
       </c>
       <c r="BW13" t="n">
         <v>0</v>
       </c>
       <c r="BX13" t="n">
-        <v>57.89</v>
+        <v>60</v>
       </c>
       <c r="BY13" t="n">
         <v>2.32</v>
@@ -6043,169 +6043,169 @@
         <v>2.41</v>
       </c>
       <c r="CA13" t="n">
-        <v>3.73</v>
+        <v>3.7</v>
       </c>
       <c r="CB13" t="n">
-        <v>3.84</v>
+        <v>3.81</v>
       </c>
       <c r="CC13" t="n">
-        <v>4.17</v>
+        <v>3.99</v>
       </c>
       <c r="CD13" t="n">
-        <v>4.42</v>
+        <v>4.2</v>
       </c>
       <c r="CE13" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="CF13" t="n">
-        <v>2.43</v>
+        <v>2.45</v>
       </c>
       <c r="CG13" t="n">
-        <v>3.2</v>
+        <v>3.17</v>
       </c>
       <c r="CH13" t="n">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="CI13" t="n">
-        <v>2.2</v>
+        <v>2.19</v>
       </c>
       <c r="CJ13" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="CK13" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="CL13" t="n">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="CM13" t="n">
-        <v>2.56</v>
+        <v>2.54</v>
       </c>
       <c r="CN13" t="n">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="CO13" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="CP13" t="n">
-        <v>1.71</v>
+        <v>1.74</v>
       </c>
       <c r="CQ13" t="n">
-        <v>2.75</v>
+        <v>2.79</v>
       </c>
       <c r="CR13" t="n">
         <v>1.35</v>
       </c>
       <c r="CS13" t="n">
-        <v>2.59</v>
+        <v>2.62</v>
       </c>
       <c r="CT13" t="n">
-        <v>3.28</v>
+        <v>3.24</v>
       </c>
       <c r="CU13" t="n">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="CV13" t="n">
-        <v>2.33</v>
+        <v>2.31</v>
       </c>
       <c r="CW13" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="CX13" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="CY13" t="n">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="CZ13" t="n">
-        <v>2.47</v>
+        <v>2.45</v>
       </c>
       <c r="DA13" t="n">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="DB13" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="DC13" t="n">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="DD13" t="n">
-        <v>2.81</v>
+        <v>2.86</v>
       </c>
       <c r="DE13" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DF13" t="n">
-        <v>1.42</v>
+        <v>1.35</v>
       </c>
       <c r="DG13" t="n">
-        <v>3.52</v>
+        <v>3.45</v>
       </c>
       <c r="DH13" t="n">
-        <v>100.84</v>
+        <v>102.25</v>
       </c>
       <c r="DI13" t="n">
-        <v>0.05</v>
+        <v>0.1</v>
       </c>
       <c r="DJ13" t="n">
         <v>1.9</v>
       </c>
       <c r="DK13" t="n">
-        <v>5.42</v>
+        <v>5.4</v>
       </c>
       <c r="DL13" t="n">
-        <v>0.31</v>
+        <v>0.35</v>
       </c>
       <c r="DM13" t="n">
-        <v>53.63</v>
+        <v>53.9</v>
       </c>
       <c r="DN13" t="n">
-        <v>0.42</v>
+        <v>0.5</v>
       </c>
       <c r="DO13" t="n">
-        <v>1.89</v>
+        <v>1.95</v>
       </c>
       <c r="DP13" t="n">
-        <v>11.95</v>
+        <v>11.9</v>
       </c>
       <c r="DQ13" t="n">
-        <v>11</v>
+        <v>10.8</v>
       </c>
       <c r="DR13" t="n">
-        <v>7.26</v>
+        <v>7.3</v>
       </c>
       <c r="DS13" t="n">
-        <v>0.31</v>
+        <v>0.3</v>
       </c>
       <c r="DT13" t="n">
-        <v>0.31</v>
+        <v>0.3</v>
       </c>
       <c r="DU13" t="n">
         <v>0</v>
       </c>
       <c r="DV13" t="n">
-        <v>52.73</v>
+        <v>53.55</v>
       </c>
       <c r="DW13" t="n">
         <v>0.05</v>
       </c>
       <c r="DX13" t="n">
-        <v>14</v>
+        <v>14.1</v>
       </c>
       <c r="DY13" t="n">
-        <v>9.58</v>
+        <v>9.75</v>
       </c>
       <c r="DZ13" t="n">
-        <v>4.42</v>
+        <v>4.35</v>
       </c>
       <c r="EA13" t="n">
-        <v>23.37</v>
+        <v>22.9</v>
       </c>
       <c r="EB13" t="n">
         <v>1.59</v>
       </c>
       <c r="EC13" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
     </row>
     <row r="14">
@@ -6215,13 +6215,13 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C14" t="n">
         <v>10</v>
       </c>
       <c r="D14" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E14" t="n">
         <v>0.1</v>
@@ -6305,52 +6305,52 @@
         <v>1.8</v>
       </c>
       <c r="AF14" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="AH14" t="n">
         <v>2</v>
       </c>
       <c r="AI14" t="n">
-        <v>92.11</v>
+        <v>90</v>
       </c>
       <c r="AJ14" t="n">
         <v>0</v>
       </c>
       <c r="AK14" t="n">
-        <v>2.11</v>
+        <v>2.3</v>
       </c>
       <c r="AL14" t="n">
-        <v>4.44</v>
+        <v>4.3</v>
       </c>
       <c r="AM14" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.6</v>
       </c>
       <c r="AN14" t="n">
-        <v>47.78</v>
+        <v>46.2</v>
       </c>
       <c r="AO14" t="n">
-        <v>0.33</v>
+        <v>0.5</v>
       </c>
       <c r="AP14" t="n">
-        <v>2.44</v>
+        <v>2.3</v>
       </c>
       <c r="AQ14" t="n">
-        <v>10.78</v>
+        <v>11.3</v>
       </c>
       <c r="AR14" t="n">
-        <v>10</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="AS14" t="n">
-        <v>6.56</v>
+        <v>7.2</v>
       </c>
       <c r="AT14" t="n">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="AU14" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="AV14" t="n">
         <v>0</v>
@@ -6362,82 +6362,82 @@
         <v>0</v>
       </c>
       <c r="AY14" t="n">
-        <v>47.67</v>
+        <v>46.8</v>
       </c>
       <c r="AZ14" t="n">
         <v>0</v>
       </c>
       <c r="BA14" t="n">
-        <v>10.67</v>
+        <v>10.9</v>
       </c>
       <c r="BB14" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="BC14" t="n">
-        <v>3.67</v>
+        <v>3.8</v>
       </c>
       <c r="BD14" t="n">
-        <v>21.33</v>
+        <v>21.3</v>
       </c>
       <c r="BE14" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="BF14" t="n">
-        <v>2.11</v>
+        <v>2.3</v>
       </c>
       <c r="BG14" t="n">
-        <v>2.42</v>
+        <v>2.45</v>
       </c>
       <c r="BH14" t="n">
-        <v>9.470000000000001</v>
+        <v>9.550000000000001</v>
       </c>
       <c r="BI14" t="n">
-        <v>2.42</v>
+        <v>2.45</v>
       </c>
       <c r="BJ14" t="n">
-        <v>0.63</v>
+        <v>0.65</v>
       </c>
       <c r="BK14" t="n">
-        <v>0.63</v>
+        <v>0.7</v>
       </c>
       <c r="BL14" t="n">
-        <v>0.79</v>
+        <v>0.75</v>
       </c>
       <c r="BM14" t="n">
-        <v>0.37</v>
+        <v>0.35</v>
       </c>
       <c r="BN14" t="n">
-        <v>1.16</v>
+        <v>1.1</v>
       </c>
       <c r="BO14" t="n">
-        <v>1.26</v>
+        <v>1.35</v>
       </c>
       <c r="BP14" t="n">
+        <v>4.95</v>
+      </c>
+      <c r="BQ14" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BR14" t="n">
+        <v>95</v>
+      </c>
+      <c r="BS14" t="n">
+        <v>70</v>
+      </c>
+      <c r="BT14" t="n">
+        <v>45</v>
+      </c>
+      <c r="BU14" t="n">
+        <v>30</v>
+      </c>
+      <c r="BV14" t="n">
         <v>5</v>
       </c>
-      <c r="BQ14" t="n">
-        <v>4.47</v>
-      </c>
-      <c r="BR14" t="n">
-        <v>94.73999999999999</v>
-      </c>
-      <c r="BS14" t="n">
-        <v>68.42</v>
-      </c>
-      <c r="BT14" t="n">
-        <v>42.11</v>
-      </c>
-      <c r="BU14" t="n">
-        <v>31.58</v>
-      </c>
-      <c r="BV14" t="n">
-        <v>5.26</v>
-      </c>
       <c r="BW14" t="n">
         <v>0</v>
       </c>
       <c r="BX14" t="n">
-        <v>57.89</v>
+        <v>60</v>
       </c>
       <c r="BY14" t="n">
         <v>2.33</v>
@@ -6449,16 +6449,16 @@
         <v>3.53</v>
       </c>
       <c r="CB14" t="n">
-        <v>3.53</v>
+        <v>3.54</v>
       </c>
       <c r="CC14" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="CD14" t="n">
-        <v>3.92</v>
+        <v>4.04</v>
       </c>
       <c r="CE14" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="CF14" t="n">
         <v>2.68</v>
@@ -6467,13 +6467,13 @@
         <v>3.03</v>
       </c>
       <c r="CH14" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="CI14" t="n">
         <v>2.05</v>
       </c>
       <c r="CJ14" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="CK14" t="n">
         <v>1.47</v>
@@ -6491,37 +6491,37 @@
         <v>1.26</v>
       </c>
       <c r="CP14" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="CQ14" t="n">
-        <v>3.13</v>
+        <v>3.14</v>
       </c>
       <c r="CR14" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="CS14" t="n">
         <v>2.84</v>
       </c>
       <c r="CT14" t="n">
-        <v>3.08</v>
+        <v>3.09</v>
       </c>
       <c r="CU14" t="n">
         <v>1.45</v>
       </c>
       <c r="CV14" t="n">
-        <v>2.14</v>
+        <v>2.13</v>
       </c>
       <c r="CW14" t="n">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="CX14" t="n">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="CY14" t="n">
         <v>1.88</v>
       </c>
       <c r="CZ14" t="n">
-        <v>2.43</v>
+        <v>2.44</v>
       </c>
       <c r="DA14" t="n">
         <v>1.93</v>
@@ -6539,43 +6539,43 @@
         <v>0.1</v>
       </c>
       <c r="DF14" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="DG14" t="n">
-        <v>2.16</v>
+        <v>2.15</v>
       </c>
       <c r="DH14" t="n">
-        <v>90.84</v>
+        <v>89.84999999999999</v>
       </c>
       <c r="DI14" t="n">
         <v>0</v>
       </c>
       <c r="DJ14" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="DK14" t="n">
-        <v>4.79</v>
+        <v>4.7</v>
       </c>
       <c r="DL14" t="n">
-        <v>0.32</v>
+        <v>0.35</v>
       </c>
       <c r="DM14" t="n">
-        <v>47.95</v>
+        <v>47.15</v>
       </c>
       <c r="DN14" t="n">
-        <v>0.37</v>
+        <v>0.45</v>
       </c>
       <c r="DO14" t="n">
-        <v>2.63</v>
+        <v>2.55</v>
       </c>
       <c r="DP14" t="n">
-        <v>11.16</v>
+        <v>11.4</v>
       </c>
       <c r="DQ14" t="n">
-        <v>11.53</v>
+        <v>11.3</v>
       </c>
       <c r="DR14" t="n">
-        <v>6.95</v>
+        <v>7.25</v>
       </c>
       <c r="DS14" t="n">
         <v>0.05</v>
@@ -6587,28 +6587,28 @@
         <v>0</v>
       </c>
       <c r="DV14" t="n">
-        <v>47.42</v>
+        <v>47</v>
       </c>
       <c r="DW14" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DX14" t="n">
-        <v>11.05</v>
+        <v>11.15</v>
       </c>
       <c r="DY14" t="n">
-        <v>6.95</v>
+        <v>7</v>
       </c>
       <c r="DZ14" t="n">
-        <v>4.11</v>
+        <v>4.15</v>
       </c>
       <c r="EA14" t="n">
-        <v>19.37</v>
+        <v>19.45</v>
       </c>
       <c r="EB14" t="n">
         <v>1.34</v>
       </c>
       <c r="EC14" t="n">
-        <v>1.95</v>
+        <v>2.05</v>
       </c>
     </row>
     <row r="15">
@@ -6618,94 +6618,94 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C15" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D15" t="n">
         <v>10</v>
       </c>
       <c r="E15" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="F15" t="n">
-        <v>1.78</v>
+        <v>1.7</v>
       </c>
       <c r="G15" t="n">
-        <v>2.11</v>
+        <v>2</v>
       </c>
       <c r="H15" t="n">
-        <v>84.22</v>
+        <v>85</v>
       </c>
       <c r="I15" t="n">
         <v>0</v>
       </c>
       <c r="J15" t="n">
-        <v>3.22</v>
+        <v>3.2</v>
       </c>
       <c r="K15" t="n">
-        <v>5.33</v>
+        <v>4.9</v>
       </c>
       <c r="L15" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.5</v>
       </c>
       <c r="M15" t="n">
-        <v>53.67</v>
+        <v>51.4</v>
       </c>
       <c r="N15" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="O15" t="n">
-        <v>3.22</v>
+        <v>2.9</v>
       </c>
       <c r="P15" t="n">
-        <v>11.56</v>
+        <v>11.1</v>
       </c>
       <c r="Q15" t="n">
-        <v>12.56</v>
+        <v>12.4</v>
       </c>
       <c r="R15" t="n">
-        <v>8.44</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="S15" t="n">
-        <v>1.11</v>
+        <v>1.2</v>
       </c>
       <c r="T15" t="n">
         <v>1</v>
       </c>
       <c r="U15" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="V15" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="W15" t="n">
         <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>45.44</v>
+        <v>44</v>
       </c>
       <c r="Y15" t="n">
-        <v>0.33</v>
+        <v>0.4</v>
       </c>
       <c r="Z15" t="n">
-        <v>12.11</v>
+        <v>11.4</v>
       </c>
       <c r="AA15" t="n">
-        <v>7.44</v>
+        <v>7</v>
       </c>
       <c r="AB15" t="n">
-        <v>4.67</v>
+        <v>4.4</v>
       </c>
       <c r="AC15" t="n">
-        <v>19.56</v>
+        <v>20.7</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.48</v>
+        <v>1.4</v>
       </c>
       <c r="AE15" t="n">
-        <v>2.56</v>
+        <v>2.4</v>
       </c>
       <c r="AF15" t="n">
         <v>0.2</v>
@@ -6789,49 +6789,49 @@
         <v>1.9</v>
       </c>
       <c r="BG15" t="n">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="BH15" t="n">
-        <v>9.630000000000001</v>
+        <v>9.449999999999999</v>
       </c>
       <c r="BI15" t="n">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="BJ15" t="n">
-        <v>0.42</v>
+        <v>0.45</v>
       </c>
       <c r="BK15" t="n">
-        <v>0.63</v>
+        <v>0.65</v>
       </c>
       <c r="BL15" t="n">
-        <v>0.63</v>
+        <v>0.6</v>
       </c>
       <c r="BM15" t="n">
-        <v>0.32</v>
+        <v>0.35</v>
       </c>
       <c r="BN15" t="n">
         <v>0.95</v>
       </c>
       <c r="BO15" t="n">
-        <v>1.05</v>
+        <v>1.1</v>
       </c>
       <c r="BP15" t="n">
-        <v>4.47</v>
+        <v>4.4</v>
       </c>
       <c r="BQ15" t="n">
-        <v>5.16</v>
+        <v>5.05</v>
       </c>
       <c r="BR15" t="n">
-        <v>94.73999999999999</v>
+        <v>95</v>
       </c>
       <c r="BS15" t="n">
-        <v>57.89</v>
+        <v>60</v>
       </c>
       <c r="BT15" t="n">
-        <v>36.84</v>
+        <v>40</v>
       </c>
       <c r="BU15" t="n">
-        <v>10.53</v>
+        <v>10</v>
       </c>
       <c r="BV15" t="n">
         <v>0</v>
@@ -6840,19 +6840,19 @@
         <v>0</v>
       </c>
       <c r="BX15" t="n">
-        <v>31.58</v>
+        <v>35</v>
       </c>
       <c r="BY15" t="n">
-        <v>2.84</v>
+        <v>2.86</v>
       </c>
       <c r="BZ15" t="n">
-        <v>3.03</v>
+        <v>3.09</v>
       </c>
       <c r="CA15" t="n">
-        <v>3.48</v>
+        <v>3.46</v>
       </c>
       <c r="CB15" t="n">
-        <v>3.52</v>
+        <v>3.51</v>
       </c>
       <c r="CC15" t="n">
         <v>4.03</v>
@@ -6867,10 +6867,10 @@
         <v>2.81</v>
       </c>
       <c r="CG15" t="n">
-        <v>2.9</v>
+        <v>2.89</v>
       </c>
       <c r="CH15" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="CI15" t="n">
         <v>1.95</v>
@@ -6879,22 +6879,22 @@
         <v>1.81</v>
       </c>
       <c r="CK15" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="CL15" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="CM15" t="n">
-        <v>2.55</v>
+        <v>2.53</v>
       </c>
       <c r="CN15" t="n">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="CO15" t="n">
         <v>1.31</v>
       </c>
       <c r="CP15" t="n">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="CQ15" t="n">
         <v>3.43</v>
@@ -6903,10 +6903,10 @@
         <v>1.4</v>
       </c>
       <c r="CS15" t="n">
-        <v>2.92</v>
+        <v>2.93</v>
       </c>
       <c r="CT15" t="n">
-        <v>3.03</v>
+        <v>3.02</v>
       </c>
       <c r="CU15" t="n">
         <v>1.43</v>
@@ -6918,100 +6918,100 @@
         <v>1.83</v>
       </c>
       <c r="CX15" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="CY15" t="n">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="CZ15" t="n">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="DA15" t="n">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="DB15" t="n">
         <v>1.32</v>
       </c>
       <c r="DC15" t="n">
-        <v>2.02</v>
+        <v>2.03</v>
       </c>
       <c r="DD15" t="n">
-        <v>3.47</v>
+        <v>3.48</v>
       </c>
       <c r="DE15" t="n">
-        <v>0.21</v>
+        <v>0.2</v>
       </c>
       <c r="DF15" t="n">
-        <v>1.58</v>
+        <v>1.55</v>
       </c>
       <c r="DG15" t="n">
-        <v>1.74</v>
+        <v>1.7</v>
       </c>
       <c r="DH15" t="n">
-        <v>84.42</v>
+        <v>84.8</v>
       </c>
       <c r="DI15" t="n">
         <v>0</v>
       </c>
       <c r="DJ15" t="n">
-        <v>2.63</v>
+        <v>2.65</v>
       </c>
       <c r="DK15" t="n">
-        <v>4.05</v>
+        <v>3.9</v>
       </c>
       <c r="DL15" t="n">
-        <v>0.48</v>
+        <v>0.45</v>
       </c>
       <c r="DM15" t="n">
-        <v>43.16</v>
+        <v>42.55</v>
       </c>
       <c r="DN15" t="n">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="DO15" t="n">
-        <v>2.31</v>
+        <v>2.2</v>
       </c>
       <c r="DP15" t="n">
-        <v>11.42</v>
+        <v>11.2</v>
       </c>
       <c r="DQ15" t="n">
-        <v>12.16</v>
+        <v>12.1</v>
       </c>
       <c r="DR15" t="n">
-        <v>9.26</v>
+        <v>9.4</v>
       </c>
       <c r="DS15" t="n">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
       <c r="DT15" t="n">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
       <c r="DU15" t="n">
         <v>0</v>
       </c>
       <c r="DV15" t="n">
-        <v>44.52</v>
+        <v>43.85</v>
       </c>
       <c r="DW15" t="n">
-        <v>0.26</v>
+        <v>0.3</v>
       </c>
       <c r="DX15" t="n">
-        <v>9.74</v>
+        <v>9.5</v>
       </c>
       <c r="DY15" t="n">
-        <v>6.31</v>
+        <v>6.15</v>
       </c>
       <c r="DZ15" t="n">
-        <v>3.42</v>
+        <v>3.35</v>
       </c>
       <c r="EA15" t="n">
-        <v>18.9</v>
+        <v>19.5</v>
       </c>
       <c r="EB15" t="n">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="EC15" t="n">
-        <v>2.21</v>
+        <v>2.15</v>
       </c>
     </row>
     <row r="16">
@@ -7021,13 +7021,13 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C16" t="n">
         <v>9</v>
       </c>
       <c r="D16" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E16" t="n">
         <v>0.33</v>
@@ -7111,139 +7111,139 @@
         <v>1.22</v>
       </c>
       <c r="AF16" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.8</v>
+        <v>1.82</v>
       </c>
       <c r="AH16" t="n">
-        <v>2.7</v>
+        <v>2.64</v>
       </c>
       <c r="AI16" t="n">
-        <v>112.3</v>
+        <v>112.18</v>
       </c>
       <c r="AJ16" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="AK16" t="n">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="AL16" t="n">
-        <v>5.3</v>
+        <v>5.18</v>
       </c>
       <c r="AM16" t="n">
-        <v>0.6</v>
+        <v>0.55</v>
       </c>
       <c r="AN16" t="n">
-        <v>51.5</v>
+        <v>51.64</v>
       </c>
       <c r="AO16" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AP16" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="AQ16" t="n">
+        <v>13.36</v>
+      </c>
+      <c r="AR16" t="n">
+        <v>8.82</v>
+      </c>
+      <c r="AS16" t="n">
+        <v>6.09</v>
+      </c>
+      <c r="AT16" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="AU16" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AV16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY16" t="n">
+        <v>54.82</v>
+      </c>
+      <c r="AZ16" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="BA16" t="n">
+        <v>14.36</v>
+      </c>
+      <c r="BB16" t="n">
+        <v>9.359999999999999</v>
+      </c>
+      <c r="BC16" t="n">
+        <v>5</v>
+      </c>
+      <c r="BD16" t="n">
+        <v>20.36</v>
+      </c>
+      <c r="BE16" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="BF16" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="BG16" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="BH16" t="n">
+        <v>9.449999999999999</v>
+      </c>
+      <c r="BI16" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="BJ16" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="BK16" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="BL16" t="n">
         <v>1.1</v>
       </c>
-      <c r="AP16" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AQ16" t="n">
-        <v>13.2</v>
-      </c>
-      <c r="AR16" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AS16" t="n">
-        <v>6</v>
-      </c>
-      <c r="AT16" t="n">
+      <c r="BM16" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="BN16" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="BO16" t="n">
         <v>0.9</v>
       </c>
-      <c r="AU16" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AV16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY16" t="n">
-        <v>53.9</v>
-      </c>
-      <c r="AZ16" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA16" t="n">
-        <v>13.7</v>
-      </c>
-      <c r="BB16" t="n">
-        <v>9</v>
-      </c>
-      <c r="BC16" t="n">
+      <c r="BP16" t="n">
         <v>4.7</v>
       </c>
-      <c r="BD16" t="n">
-        <v>20.2</v>
-      </c>
-      <c r="BE16" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="BF16" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="BG16" t="n">
-        <v>2.42</v>
-      </c>
-      <c r="BH16" t="n">
-        <v>9.529999999999999</v>
-      </c>
-      <c r="BI16" t="n">
-        <v>2.42</v>
-      </c>
-      <c r="BJ16" t="n">
-        <v>0.47</v>
-      </c>
-      <c r="BK16" t="n">
-        <v>0.37</v>
-      </c>
-      <c r="BL16" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="BM16" t="n">
-        <v>0.42</v>
-      </c>
-      <c r="BN16" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="BO16" t="n">
-        <v>0.84</v>
-      </c>
-      <c r="BP16" t="n">
-        <v>4.74</v>
-      </c>
       <c r="BQ16" t="n">
-        <v>4.79</v>
+        <v>4.75</v>
       </c>
       <c r="BR16" t="n">
-        <v>94.73999999999999</v>
+        <v>95</v>
       </c>
       <c r="BS16" t="n">
-        <v>78.95</v>
+        <v>80</v>
       </c>
       <c r="BT16" t="n">
-        <v>31.58</v>
+        <v>30</v>
       </c>
       <c r="BU16" t="n">
-        <v>21.05</v>
+        <v>20</v>
       </c>
       <c r="BV16" t="n">
-        <v>15.79</v>
+        <v>15</v>
       </c>
       <c r="BW16" t="n">
         <v>0</v>
       </c>
       <c r="BX16" t="n">
-        <v>42.11</v>
+        <v>45</v>
       </c>
       <c r="BY16" t="n">
         <v>1.35</v>
@@ -7252,28 +7252,28 @@
         <v>1.42</v>
       </c>
       <c r="CA16" t="n">
-        <v>4.26</v>
+        <v>4.22</v>
       </c>
       <c r="CB16" t="n">
-        <v>4.45</v>
+        <v>4.4</v>
       </c>
       <c r="CC16" t="n">
-        <v>1.87</v>
+        <v>1.89</v>
       </c>
       <c r="CD16" t="n">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="CE16" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="CF16" t="n">
-        <v>2.48</v>
+        <v>2.49</v>
       </c>
       <c r="CG16" t="n">
-        <v>3.21</v>
+        <v>3.19</v>
       </c>
       <c r="CH16" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="CI16" t="n">
         <v>1.95</v>
@@ -7285,37 +7285,37 @@
         <v>1.46</v>
       </c>
       <c r="CL16" t="n">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="CM16" t="n">
         <v>2.5</v>
       </c>
       <c r="CN16" t="n">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="CO16" t="n">
         <v>1.22</v>
       </c>
       <c r="CP16" t="n">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="CQ16" t="n">
-        <v>2.76</v>
+        <v>2.79</v>
       </c>
       <c r="CR16" t="n">
         <v>1.36</v>
       </c>
       <c r="CS16" t="n">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="CT16" t="n">
-        <v>3.2</v>
+        <v>3.17</v>
       </c>
       <c r="CU16" t="n">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="CV16" t="n">
-        <v>2.04</v>
+        <v>2.03</v>
       </c>
       <c r="CW16" t="n">
         <v>1.86</v>
@@ -7327,7 +7327,7 @@
         <v>1.87</v>
       </c>
       <c r="CZ16" t="n">
-        <v>2.35</v>
+        <v>2.37</v>
       </c>
       <c r="DA16" t="n">
         <v>1.95</v>
@@ -7336,52 +7336,52 @@
         <v>1.25</v>
       </c>
       <c r="DC16" t="n">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="DD16" t="n">
-        <v>2.91</v>
+        <v>2.94</v>
       </c>
       <c r="DE16" t="n">
-        <v>0.21</v>
+        <v>0.2</v>
       </c>
       <c r="DF16" t="n">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="DG16" t="n">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="DH16" t="n">
-        <v>107.95</v>
+        <v>108.1</v>
       </c>
       <c r="DI16" t="n">
         <v>0.05</v>
       </c>
       <c r="DJ16" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="DK16" t="n">
-        <v>5.74</v>
+        <v>5.65</v>
       </c>
       <c r="DL16" t="n">
-        <v>0.58</v>
+        <v>0.55</v>
       </c>
       <c r="DM16" t="n">
-        <v>53.95</v>
+        <v>53.9</v>
       </c>
       <c r="DN16" t="n">
-        <v>0.63</v>
+        <v>0.7</v>
       </c>
       <c r="DO16" t="n">
-        <v>2.69</v>
+        <v>2.65</v>
       </c>
       <c r="DP16" t="n">
-        <v>12.58</v>
+        <v>12.7</v>
       </c>
       <c r="DQ16" t="n">
-        <v>9</v>
+        <v>9.1</v>
       </c>
       <c r="DR16" t="n">
-        <v>5.73</v>
+        <v>5.8</v>
       </c>
       <c r="DS16" t="n">
         <v>0.1</v>
@@ -7393,28 +7393,28 @@
         <v>0</v>
       </c>
       <c r="DV16" t="n">
-        <v>53.68</v>
+        <v>54.2</v>
       </c>
       <c r="DW16" t="n">
-        <v>0</v>
+        <v>0.05</v>
       </c>
       <c r="DX16" t="n">
-        <v>15.32</v>
+        <v>15.6</v>
       </c>
       <c r="DY16" t="n">
-        <v>9.630000000000001</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="DZ16" t="n">
-        <v>5.69</v>
+        <v>5.8</v>
       </c>
       <c r="EA16" t="n">
-        <v>19.84</v>
+        <v>19.95</v>
       </c>
       <c r="EB16" t="n">
-        <v>1.75</v>
+        <v>1.78</v>
       </c>
       <c r="EC16" t="n">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
     </row>
     <row r="17">
@@ -7424,13 +7424,13 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C17" t="n">
         <v>9</v>
       </c>
       <c r="D17" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
@@ -7514,139 +7514,139 @@
         <v>1.33</v>
       </c>
       <c r="AF17" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="AG17" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AH17" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="AI17" t="n">
+        <v>95.64</v>
+      </c>
+      <c r="AJ17" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="AK17" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AL17" t="n">
+        <v>4.55</v>
+      </c>
+      <c r="AM17" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>48.45</v>
+      </c>
+      <c r="AO17" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="AP17" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AQ17" t="n">
+        <v>12.09</v>
+      </c>
+      <c r="AR17" t="n">
+        <v>10.91</v>
+      </c>
+      <c r="AS17" t="n">
+        <v>8.91</v>
+      </c>
+      <c r="AT17" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AU17" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AV17" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="AW17" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="AX17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY17" t="n">
+        <v>49.73</v>
+      </c>
+      <c r="AZ17" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="BA17" t="n">
+        <v>11</v>
+      </c>
+      <c r="BB17" t="n">
+        <v>7.45</v>
+      </c>
+      <c r="BC17" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="BD17" t="n">
+        <v>20.18</v>
+      </c>
+      <c r="BE17" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="BF17" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="BG17" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="BH17" t="n">
+        <v>10.15</v>
+      </c>
+      <c r="BI17" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="BJ17" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="BK17" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="BL17" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="BM17" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="BN17" t="n">
         <v>1.4</v>
       </c>
-      <c r="AH17" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AI17" t="n">
-        <v>93.3</v>
-      </c>
-      <c r="AJ17" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="AK17" t="n">
-        <v>2</v>
-      </c>
-      <c r="AL17" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AM17" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="AN17" t="n">
-        <v>48.3</v>
-      </c>
-      <c r="AO17" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AP17" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AQ17" t="n">
-        <v>12.8</v>
-      </c>
-      <c r="AR17" t="n">
-        <v>10.1</v>
-      </c>
-      <c r="AS17" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AT17" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AU17" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AV17" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="AW17" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="AX17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY17" t="n">
-        <v>48.9</v>
-      </c>
-      <c r="AZ17" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="BA17" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="BB17" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="BC17" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="BD17" t="n">
-        <v>20.1</v>
-      </c>
-      <c r="BE17" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="BF17" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="BG17" t="n">
-        <v>2.74</v>
-      </c>
-      <c r="BH17" t="n">
-        <v>10.05</v>
-      </c>
-      <c r="BI17" t="n">
-        <v>2.74</v>
-      </c>
-      <c r="BJ17" t="n">
-        <v>0.79</v>
-      </c>
-      <c r="BK17" t="n">
-        <v>0.53</v>
-      </c>
-      <c r="BL17" t="n">
-        <v>0.68</v>
-      </c>
-      <c r="BM17" t="n">
-        <v>0.74</v>
-      </c>
-      <c r="BN17" t="n">
-        <v>1.42</v>
-      </c>
       <c r="BO17" t="n">
-        <v>1.32</v>
+        <v>1.35</v>
       </c>
       <c r="BP17" t="n">
-        <v>3.63</v>
+        <v>3.7</v>
       </c>
       <c r="BQ17" t="n">
-        <v>5.74</v>
+        <v>5.75</v>
       </c>
       <c r="BR17" t="n">
-        <v>89.47</v>
+        <v>90</v>
       </c>
       <c r="BS17" t="n">
-        <v>84.20999999999999</v>
+        <v>85</v>
       </c>
       <c r="BT17" t="n">
-        <v>42.11</v>
+        <v>45</v>
       </c>
       <c r="BU17" t="n">
-        <v>36.84</v>
+        <v>35</v>
       </c>
       <c r="BV17" t="n">
-        <v>21.05</v>
+        <v>20</v>
       </c>
       <c r="BW17" t="n">
         <v>0</v>
       </c>
       <c r="BX17" t="n">
-        <v>63.16</v>
+        <v>65</v>
       </c>
       <c r="BY17" t="n">
         <v>3.02</v>
@@ -7655,31 +7655,31 @@
         <v>3.28</v>
       </c>
       <c r="CA17" t="n">
-        <v>3.74</v>
+        <v>3.73</v>
       </c>
       <c r="CB17" t="n">
-        <v>3.81</v>
+        <v>3.82</v>
       </c>
       <c r="CC17" t="n">
-        <v>4.18</v>
+        <v>4.19</v>
       </c>
       <c r="CD17" t="n">
-        <v>4.74</v>
+        <v>4.73</v>
       </c>
       <c r="CE17" t="n">
         <v>1.3</v>
       </c>
       <c r="CF17" t="n">
-        <v>2.46</v>
+        <v>2.47</v>
       </c>
       <c r="CG17" t="n">
-        <v>3.31</v>
+        <v>3.29</v>
       </c>
       <c r="CH17" t="n">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="CI17" t="n">
-        <v>2.19</v>
+        <v>2.18</v>
       </c>
       <c r="CJ17" t="n">
         <v>1.63</v>
@@ -7688,13 +7688,13 @@
         <v>1.43</v>
       </c>
       <c r="CL17" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="CM17" t="n">
-        <v>2.68</v>
+        <v>2.67</v>
       </c>
       <c r="CN17" t="n">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="CO17" t="n">
         <v>1.21</v>
@@ -7703,7 +7703,7 @@
         <v>1.71</v>
       </c>
       <c r="CQ17" t="n">
-        <v>2.73</v>
+        <v>2.74</v>
       </c>
       <c r="CR17" t="n">
         <v>1.35</v>
@@ -7718,7 +7718,7 @@
         <v>1.53</v>
       </c>
       <c r="CV17" t="n">
-        <v>2.33</v>
+        <v>2.32</v>
       </c>
       <c r="CW17" t="n">
         <v>1.67</v>
@@ -7733,91 +7733,91 @@
         <v>2.48</v>
       </c>
       <c r="DA17" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="DB17" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="DC17" t="n">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="DD17" t="n">
-        <v>2.83</v>
+        <v>2.84</v>
       </c>
       <c r="DE17" t="n">
         <v>0.05</v>
       </c>
       <c r="DF17" t="n">
-        <v>1.16</v>
+        <v>1.1</v>
       </c>
       <c r="DG17" t="n">
-        <v>2.21</v>
+        <v>2.25</v>
       </c>
       <c r="DH17" t="n">
-        <v>95.37</v>
+        <v>96.55</v>
       </c>
       <c r="DI17" t="n">
         <v>0.05</v>
       </c>
       <c r="DJ17" t="n">
-        <v>1.79</v>
+        <v>1.7</v>
       </c>
       <c r="DK17" t="n">
-        <v>4.05</v>
+        <v>4.2</v>
       </c>
       <c r="DL17" t="n">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
       <c r="DM17" t="n">
-        <v>44.37</v>
+        <v>44.65</v>
       </c>
       <c r="DN17" t="n">
-        <v>0.53</v>
+        <v>0.5</v>
       </c>
       <c r="DO17" t="n">
-        <v>1.48</v>
+        <v>1.6</v>
       </c>
       <c r="DP17" t="n">
-        <v>11.68</v>
+        <v>11.35</v>
       </c>
       <c r="DQ17" t="n">
-        <v>11.47</v>
+        <v>11.85</v>
       </c>
       <c r="DR17" t="n">
-        <v>9.9</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="DS17" t="n">
-        <v>0.26</v>
+        <v>0.25</v>
       </c>
       <c r="DT17" t="n">
-        <v>0.26</v>
+        <v>0.25</v>
       </c>
       <c r="DU17" t="n">
         <v>0</v>
       </c>
       <c r="DV17" t="n">
-        <v>47.58</v>
+        <v>48.1</v>
       </c>
       <c r="DW17" t="n">
         <v>0.1</v>
       </c>
       <c r="DX17" t="n">
-        <v>10.89</v>
+        <v>11.15</v>
       </c>
       <c r="DY17" t="n">
-        <v>7.16</v>
+        <v>7.3</v>
       </c>
       <c r="DZ17" t="n">
-        <v>3.74</v>
+        <v>3.85</v>
       </c>
       <c r="EA17" t="n">
         <v>21.05</v>
       </c>
       <c r="EB17" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="EC17" t="n">
-        <v>1.58</v>
+        <v>1.5</v>
       </c>
     </row>
   </sheetData>

--- a/data/teams/leagues/Averages_Belgium_Pro_League_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Belgium_Pro_League_2025-2026.xlsx
@@ -1445,7 +1445,7 @@
         <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>51.45</v>
+        <v>51.36</v>
       </c>
       <c r="Y2" t="n">
         <v>0.09</v>
@@ -1751,7 +1751,7 @@
         <v>0</v>
       </c>
       <c r="DV2" t="n">
-        <v>50.35</v>
+        <v>50.3</v>
       </c>
       <c r="DW2" t="n">
         <v>0.1</v>
@@ -2660,10 +2660,10 @@
         <v>0.1</v>
       </c>
       <c r="Z5" t="n">
-        <v>15.5</v>
+        <v>15.4</v>
       </c>
       <c r="AA5" t="n">
-        <v>11.3</v>
+        <v>11.2</v>
       </c>
       <c r="AB5" t="n">
         <v>4.2</v>
@@ -2672,7 +2672,7 @@
         <v>19.1</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="AE5" t="n">
         <v>1.3</v>
@@ -2966,10 +2966,10 @@
         <v>0.15</v>
       </c>
       <c r="DX5" t="n">
-        <v>13.4</v>
+        <v>13.35</v>
       </c>
       <c r="DY5" t="n">
-        <v>8.949999999999999</v>
+        <v>8.9</v>
       </c>
       <c r="DZ5" t="n">
         <v>4.45</v>
@@ -3926,7 +3926,7 @@
         <v>12.1</v>
       </c>
       <c r="AS8" t="n">
-        <v>8.699999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="AT8" t="n">
         <v>2.3</v>
@@ -4157,7 +4157,7 @@
         <v>12.1</v>
       </c>
       <c r="DR8" t="n">
-        <v>8.4</v>
+        <v>8.35</v>
       </c>
       <c r="DS8" t="n">
         <v>0.15</v>
@@ -7168,7 +7168,7 @@
         <v>0</v>
       </c>
       <c r="AY16" t="n">
-        <v>54.82</v>
+        <v>54.91</v>
       </c>
       <c r="AZ16" t="n">
         <v>0.09</v>
@@ -7393,7 +7393,7 @@
         <v>0</v>
       </c>
       <c r="DV16" t="n">
-        <v>54.2</v>
+        <v>54.25</v>
       </c>
       <c r="DW16" t="n">
         <v>0.05</v>

--- a/data/teams/leagues/Averages_Belgium_Pro_League_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Belgium_Pro_League_2025-2026.xlsx
@@ -3436,7 +3436,7 @@
         <v>2.3</v>
       </c>
       <c r="P7" t="n">
-        <v>10.8</v>
+        <v>10.6</v>
       </c>
       <c r="Q7" t="n">
         <v>11.3</v>
@@ -3748,7 +3748,7 @@
         <v>2.3</v>
       </c>
       <c r="DP7" t="n">
-        <v>10.25</v>
+        <v>10.15</v>
       </c>
       <c r="DQ7" t="n">
         <v>10.9</v>
@@ -4708,7 +4708,7 @@
         <v>0</v>
       </c>
       <c r="AK10" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="AL10" t="n">
         <v>3.5</v>
@@ -4720,7 +4720,7 @@
         <v>33.7</v>
       </c>
       <c r="AO10" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="AP10" t="n">
         <v>1.3</v>
@@ -4771,7 +4771,7 @@
         <v>0.96</v>
       </c>
       <c r="BF10" t="n">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="BG10" t="n">
         <v>1.8</v>
@@ -4939,7 +4939,7 @@
         <v>0.15</v>
       </c>
       <c r="DJ10" t="n">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="DK10" t="n">
         <v>4.65</v>
@@ -4951,7 +4951,7 @@
         <v>40.25</v>
       </c>
       <c r="DN10" t="n">
-        <v>0.7</v>
+        <v>0.75</v>
       </c>
       <c r="DO10" t="n">
         <v>2</v>
@@ -4996,7 +4996,7 @@
         <v>1.08</v>
       </c>
       <c r="EC10" t="n">
-        <v>1.65</v>
+        <v>1.7</v>
       </c>
     </row>
     <row r="11">
@@ -5421,7 +5421,7 @@
         <v>0.09</v>
       </c>
       <c r="F12" t="n">
-        <v>1.36</v>
+        <v>1.27</v>
       </c>
       <c r="G12" t="n">
         <v>2.36</v>
@@ -5430,7 +5430,7 @@
         <v>96.73</v>
       </c>
       <c r="I12" t="n">
-        <v>0</v>
+        <v>0.09</v>
       </c>
       <c r="J12" t="n">
         <v>2.18</v>
@@ -5445,7 +5445,7 @@
         <v>44.27</v>
       </c>
       <c r="N12" t="n">
-        <v>0.73</v>
+        <v>0.82</v>
       </c>
       <c r="O12" t="n">
         <v>2.36</v>
@@ -5502,7 +5502,7 @@
         <v>0</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.78</v>
+        <v>1.67</v>
       </c>
       <c r="AH12" t="n">
         <v>2</v>
@@ -5514,7 +5514,7 @@
         <v>0</v>
       </c>
       <c r="AK12" t="n">
-        <v>2.44</v>
+        <v>2.33</v>
       </c>
       <c r="AL12" t="n">
         <v>3</v>
@@ -5562,10 +5562,10 @@
         <v>0.11</v>
       </c>
       <c r="BA12" t="n">
-        <v>9.890000000000001</v>
+        <v>10</v>
       </c>
       <c r="BB12" t="n">
-        <v>6.67</v>
+        <v>6.78</v>
       </c>
       <c r="BC12" t="n">
         <v>3.22</v>
@@ -5574,10 +5574,10 @@
         <v>18.78</v>
       </c>
       <c r="BE12" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="BF12" t="n">
-        <v>2.22</v>
+        <v>2.11</v>
       </c>
       <c r="BG12" t="n">
         <v>2.25</v>
@@ -5733,7 +5733,7 @@
         <v>0.05</v>
       </c>
       <c r="DF12" t="n">
-        <v>1.55</v>
+        <v>1.45</v>
       </c>
       <c r="DG12" t="n">
         <v>2.2</v>
@@ -5742,10 +5742,10 @@
         <v>91.05</v>
       </c>
       <c r="DI12" t="n">
-        <v>0</v>
+        <v>0.05</v>
       </c>
       <c r="DJ12" t="n">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="DK12" t="n">
         <v>4</v>
@@ -5757,7 +5757,7 @@
         <v>38.35</v>
       </c>
       <c r="DN12" t="n">
-        <v>0.65</v>
+        <v>0.7</v>
       </c>
       <c r="DO12" t="n">
         <v>1.75</v>
@@ -5787,10 +5787,10 @@
         <v>0.1</v>
       </c>
       <c r="DX12" t="n">
-        <v>11.8</v>
+        <v>11.85</v>
       </c>
       <c r="DY12" t="n">
-        <v>7.4</v>
+        <v>7.45</v>
       </c>
       <c r="DZ12" t="n">
         <v>4.4</v>
@@ -5799,10 +5799,10 @@
         <v>19.75</v>
       </c>
       <c r="EB12" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="EC12" t="n">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
     </row>
     <row r="13">
@@ -5836,7 +5836,7 @@
         <v>0</v>
       </c>
       <c r="J13" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="K13" t="n">
         <v>5.3</v>
@@ -5848,7 +5848,7 @@
         <v>55.1</v>
       </c>
       <c r="N13" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="O13" t="n">
         <v>1.7</v>
@@ -5899,7 +5899,7 @@
         <v>1.68</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="AF13" t="n">
         <v>0</v>
@@ -6148,7 +6148,7 @@
         <v>0.1</v>
       </c>
       <c r="DJ13" t="n">
-        <v>1.9</v>
+        <v>1.95</v>
       </c>
       <c r="DK13" t="n">
         <v>5.4</v>
@@ -6160,7 +6160,7 @@
         <v>53.9</v>
       </c>
       <c r="DN13" t="n">
-        <v>0.5</v>
+        <v>0.55</v>
       </c>
       <c r="DO13" t="n">
         <v>1.95</v>
@@ -6205,7 +6205,7 @@
         <v>1.59</v>
       </c>
       <c r="EC13" t="n">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
     </row>
     <row r="14">
@@ -7174,10 +7174,10 @@
         <v>0.09</v>
       </c>
       <c r="BA16" t="n">
-        <v>14.36</v>
+        <v>14.27</v>
       </c>
       <c r="BB16" t="n">
-        <v>9.359999999999999</v>
+        <v>9.27</v>
       </c>
       <c r="BC16" t="n">
         <v>5</v>
@@ -7186,7 +7186,7 @@
         <v>20.36</v>
       </c>
       <c r="BE16" t="n">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="BF16" t="n">
         <v>2.91</v>
@@ -7399,10 +7399,10 @@
         <v>0.05</v>
       </c>
       <c r="DX16" t="n">
-        <v>15.6</v>
+        <v>15.55</v>
       </c>
       <c r="DY16" t="n">
-        <v>9.800000000000001</v>
+        <v>9.75</v>
       </c>
       <c r="DZ16" t="n">
         <v>5.8</v>

--- a/data/teams/leagues/Averages_Belgium_Pro_League_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Belgium_Pro_League_2025-2026.xlsx
@@ -645,7 +645,7 @@
     <col width="9.6" customWidth="1" min="73" max="73"/>
     <col width="9.6" customWidth="1" min="74" max="74"/>
     <col width="9.6" customWidth="1" min="75" max="75"/>
-    <col width="7.199999999999999" customWidth="1" min="76" max="76"/>
+    <col width="8.4" customWidth="1" min="76" max="76"/>
     <col width="18" customWidth="1" min="77" max="77"/>
     <col width="27.6" customWidth="1" min="78" max="78"/>
     <col width="18" customWidth="1" min="79" max="79"/>
@@ -1782,10 +1782,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C3" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D3" t="n">
         <v>11</v>
@@ -1794,82 +1794,82 @@
         <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>1.11</v>
+        <v>1</v>
       </c>
       <c r="G3" t="n">
-        <v>4.22</v>
+        <v>3.8</v>
       </c>
       <c r="H3" t="n">
-        <v>116.44</v>
+        <v>112.7</v>
       </c>
       <c r="I3" t="n">
         <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="K3" t="n">
-        <v>7.33</v>
+        <v>6.8</v>
       </c>
       <c r="L3" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="M3" t="n">
+        <v>66.59999999999999</v>
+      </c>
+      <c r="N3" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="O3" t="n">
+        <v>3</v>
+      </c>
+      <c r="P3" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>12</v>
+      </c>
+      <c r="R3" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="S3" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="T3" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="U3" t="n">
+        <v>0</v>
+      </c>
+      <c r="V3" t="n">
+        <v>0</v>
+      </c>
+      <c r="W3" t="n">
+        <v>0</v>
+      </c>
+      <c r="X3" t="n">
+        <v>64.59999999999999</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>5</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>23.1</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AE3" t="n">
         <v>1</v>
-      </c>
-      <c r="M3" t="n">
-        <v>68.56</v>
-      </c>
-      <c r="N3" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="O3" t="n">
-        <v>3.11</v>
-      </c>
-      <c r="P3" t="n">
-        <v>9.56</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>12.11</v>
-      </c>
-      <c r="R3" t="n">
-        <v>6.89</v>
-      </c>
-      <c r="S3" t="n">
-        <v>1</v>
-      </c>
-      <c r="T3" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="U3" t="n">
-        <v>0</v>
-      </c>
-      <c r="V3" t="n">
-        <v>0</v>
-      </c>
-      <c r="W3" t="n">
-        <v>0</v>
-      </c>
-      <c r="X3" t="n">
-        <v>65.67</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>18.22</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>13.33</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>4.89</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>23.89</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>1.99</v>
-      </c>
-      <c r="AE3" t="n">
-        <v>1.11</v>
       </c>
       <c r="AF3" t="n">
         <v>0.09</v>
@@ -1953,70 +1953,70 @@
         <v>1.55</v>
       </c>
       <c r="BG3" t="n">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="BH3" t="n">
-        <v>11.05</v>
+        <v>10.95</v>
       </c>
       <c r="BI3" t="n">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="BJ3" t="n">
-        <v>0.65</v>
+        <v>0.71</v>
       </c>
       <c r="BK3" t="n">
-        <v>0.5</v>
+        <v>0.48</v>
       </c>
       <c r="BL3" t="n">
-        <v>0.85</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="BM3" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="BN3" t="n">
-        <v>1.75</v>
+        <v>1.81</v>
       </c>
       <c r="BO3" t="n">
-        <v>1.15</v>
+        <v>1.19</v>
       </c>
       <c r="BP3" t="n">
-        <v>4.8</v>
+        <v>4.67</v>
       </c>
       <c r="BQ3" t="n">
-        <v>6.25</v>
+        <v>6.29</v>
       </c>
       <c r="BR3" t="n">
         <v>100</v>
       </c>
       <c r="BS3" t="n">
-        <v>60</v>
+        <v>61.9</v>
       </c>
       <c r="BT3" t="n">
-        <v>45</v>
+        <v>47.62</v>
       </c>
       <c r="BU3" t="n">
-        <v>20</v>
+        <v>23.81</v>
       </c>
       <c r="BV3" t="n">
-        <v>20</v>
+        <v>23.81</v>
       </c>
       <c r="BW3" t="n">
-        <v>15</v>
+        <v>14.29</v>
       </c>
       <c r="BX3" t="n">
-        <v>50</v>
+        <v>52.38</v>
       </c>
       <c r="BY3" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="BZ3" t="n">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="CA3" t="n">
-        <v>4.39</v>
+        <v>4.44</v>
       </c>
       <c r="CB3" t="n">
-        <v>4.68</v>
+        <v>4.74</v>
       </c>
       <c r="CC3" t="n">
         <v>1.74</v>
@@ -2037,7 +2037,7 @@
         <v>1.61</v>
       </c>
       <c r="CI3" t="n">
-        <v>2.15</v>
+        <v>2.13</v>
       </c>
       <c r="CJ3" t="n">
         <v>1.66</v>
@@ -2046,7 +2046,7 @@
         <v>1.47</v>
       </c>
       <c r="CL3" t="n">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="CM3" t="n">
         <v>2.52</v>
@@ -2058,7 +2058,7 @@
         <v>1.16</v>
       </c>
       <c r="CP3" t="n">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="CQ3" t="n">
         <v>2.4</v>
@@ -2067,7 +2067,7 @@
         <v>1.33</v>
       </c>
       <c r="CS3" t="n">
-        <v>2.31</v>
+        <v>2.3</v>
       </c>
       <c r="CT3" t="n">
         <v>3.28</v>
@@ -2076,22 +2076,22 @@
         <v>1.65</v>
       </c>
       <c r="CV3" t="n">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="CW3" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="CX3" t="n">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="CY3" t="n">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="CZ3" t="n">
-        <v>2.5</v>
+        <v>2.51</v>
       </c>
       <c r="DA3" t="n">
-        <v>2.02</v>
+        <v>2.03</v>
       </c>
       <c r="DB3" t="n">
         <v>1.18</v>
@@ -2106,43 +2106,43 @@
         <v>0.05</v>
       </c>
       <c r="DF3" t="n">
-        <v>1.1</v>
+        <v>1.05</v>
       </c>
       <c r="DG3" t="n">
-        <v>3.9</v>
+        <v>3.72</v>
       </c>
       <c r="DH3" t="n">
-        <v>111.5</v>
+        <v>109.95</v>
       </c>
       <c r="DI3" t="n">
         <v>-0.05</v>
       </c>
       <c r="DJ3" t="n">
-        <v>1.45</v>
+        <v>1.48</v>
       </c>
       <c r="DK3" t="n">
-        <v>6.55</v>
+        <v>6.33</v>
       </c>
       <c r="DL3" t="n">
-        <v>0.6</v>
+        <v>0.57</v>
       </c>
       <c r="DM3" t="n">
-        <v>61.95</v>
+        <v>61.34</v>
       </c>
       <c r="DN3" t="n">
-        <v>0.3</v>
+        <v>0.33</v>
       </c>
       <c r="DO3" t="n">
-        <v>2.65</v>
+        <v>2.62</v>
       </c>
       <c r="DP3" t="n">
-        <v>9.449999999999999</v>
+        <v>9.43</v>
       </c>
       <c r="DQ3" t="n">
-        <v>11.75</v>
+        <v>11.71</v>
       </c>
       <c r="DR3" t="n">
-        <v>7.45</v>
+        <v>7.62</v>
       </c>
       <c r="DS3" t="n">
         <v>0</v>
@@ -2154,28 +2154,28 @@
         <v>0</v>
       </c>
       <c r="DV3" t="n">
-        <v>62.1</v>
+        <v>61.76</v>
       </c>
       <c r="DW3" t="n">
-        <v>0.05</v>
+        <v>0.1</v>
       </c>
       <c r="DX3" t="n">
-        <v>16.7</v>
+        <v>16.43</v>
       </c>
       <c r="DY3" t="n">
-        <v>11.45</v>
+        <v>11.14</v>
       </c>
       <c r="DZ3" t="n">
-        <v>5.25</v>
+        <v>5.29</v>
       </c>
       <c r="EA3" t="n">
-        <v>20.6</v>
+        <v>20.38</v>
       </c>
       <c r="EB3" t="n">
-        <v>1.87</v>
+        <v>1.85</v>
       </c>
       <c r="EC3" t="n">
-        <v>1.35</v>
+        <v>1.29</v>
       </c>
     </row>
     <row r="4">
@@ -4603,13 +4603,13 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C10" t="n">
         <v>10</v>
       </c>
       <c r="D10" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
@@ -4693,52 +4693,52 @@
         <v>1.6</v>
       </c>
       <c r="AF10" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AH10" t="n">
-        <v>2.2</v>
+        <v>2.64</v>
       </c>
       <c r="AI10" t="n">
-        <v>79.3</v>
+        <v>82.09</v>
       </c>
       <c r="AJ10" t="n">
         <v>0</v>
       </c>
       <c r="AK10" t="n">
-        <v>2</v>
+        <v>2.09</v>
       </c>
       <c r="AL10" t="n">
-        <v>3.5</v>
+        <v>3.82</v>
       </c>
       <c r="AM10" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="AN10" t="n">
-        <v>33.7</v>
+        <v>37.36</v>
       </c>
       <c r="AO10" t="n">
-        <v>0.7</v>
+        <v>0.82</v>
       </c>
       <c r="AP10" t="n">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="AQ10" t="n">
-        <v>12.3</v>
+        <v>12.18</v>
       </c>
       <c r="AR10" t="n">
-        <v>12.9</v>
+        <v>12.55</v>
       </c>
       <c r="AS10" t="n">
-        <v>8.800000000000001</v>
+        <v>8.449999999999999</v>
       </c>
       <c r="AT10" t="n">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="AU10" t="n">
-        <v>1</v>
+        <v>1.18</v>
       </c>
       <c r="AV10" t="n">
         <v>0</v>
@@ -4750,82 +4750,82 @@
         <v>0</v>
       </c>
       <c r="AY10" t="n">
-        <v>32.1</v>
+        <v>33.27</v>
       </c>
       <c r="AZ10" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="BA10" t="n">
-        <v>8.6</v>
+        <v>9.09</v>
       </c>
       <c r="BB10" t="n">
-        <v>6.2</v>
+        <v>6.45</v>
       </c>
       <c r="BC10" t="n">
-        <v>2.4</v>
+        <v>2.64</v>
       </c>
       <c r="BD10" t="n">
-        <v>20.9</v>
+        <v>20.45</v>
       </c>
       <c r="BE10" t="n">
-        <v>0.96</v>
+        <v>1.03</v>
       </c>
       <c r="BF10" t="n">
-        <v>1.8</v>
+        <v>1.91</v>
       </c>
       <c r="BG10" t="n">
-        <v>1.8</v>
+        <v>1.95</v>
       </c>
       <c r="BH10" t="n">
-        <v>8.75</v>
+        <v>8.76</v>
       </c>
       <c r="BI10" t="n">
-        <v>1.8</v>
+        <v>1.95</v>
       </c>
       <c r="BJ10" t="n">
-        <v>0.5</v>
+        <v>0.57</v>
       </c>
       <c r="BK10" t="n">
-        <v>0.35</v>
+        <v>0.33</v>
       </c>
       <c r="BL10" t="n">
-        <v>0.5</v>
+        <v>0.48</v>
       </c>
       <c r="BM10" t="n">
-        <v>0.45</v>
+        <v>0.57</v>
       </c>
       <c r="BN10" t="n">
-        <v>0.95</v>
+        <v>1.05</v>
       </c>
       <c r="BO10" t="n">
-        <v>0.85</v>
+        <v>0.9</v>
       </c>
       <c r="BP10" t="n">
-        <v>3.7</v>
+        <v>3.62</v>
       </c>
       <c r="BQ10" t="n">
-        <v>5.05</v>
+        <v>5.14</v>
       </c>
       <c r="BR10" t="n">
-        <v>70</v>
+        <v>71.43000000000001</v>
       </c>
       <c r="BS10" t="n">
-        <v>50</v>
+        <v>52.38</v>
       </c>
       <c r="BT10" t="n">
-        <v>40</v>
+        <v>42.86</v>
       </c>
       <c r="BU10" t="n">
-        <v>15</v>
+        <v>19.05</v>
       </c>
       <c r="BV10" t="n">
-        <v>5</v>
+        <v>9.52</v>
       </c>
       <c r="BW10" t="n">
         <v>0</v>
       </c>
       <c r="BX10" t="n">
-        <v>45</v>
+        <v>47.62</v>
       </c>
       <c r="BY10" t="n">
         <v>3.53</v>
@@ -4834,28 +4834,28 @@
         <v>3.69</v>
       </c>
       <c r="CA10" t="n">
-        <v>3.46</v>
+        <v>3.56</v>
       </c>
       <c r="CB10" t="n">
-        <v>3.51</v>
+        <v>3.63</v>
       </c>
       <c r="CC10" t="n">
-        <v>4.09</v>
+        <v>4.49</v>
       </c>
       <c r="CD10" t="n">
-        <v>4.35</v>
+        <v>4.83</v>
       </c>
       <c r="CE10" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="CF10" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="CG10" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="CH10" t="n">
         <v>1.4</v>
-      </c>
-      <c r="CF10" t="n">
-        <v>2.82</v>
-      </c>
-      <c r="CG10" t="n">
-        <v>2.83</v>
-      </c>
-      <c r="CH10" t="n">
-        <v>1.39</v>
       </c>
       <c r="CI10" t="n">
         <v>1.89</v>
@@ -4864,37 +4864,37 @@
         <v>1.86</v>
       </c>
       <c r="CK10" t="n">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="CL10" t="n">
-        <v>2.01</v>
+        <v>2</v>
       </c>
       <c r="CM10" t="n">
-        <v>2.32</v>
+        <v>2.33</v>
       </c>
       <c r="CN10" t="n">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="CO10" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="CP10" t="n">
-        <v>2.01</v>
+        <v>1.99</v>
       </c>
       <c r="CQ10" t="n">
-        <v>3.59</v>
+        <v>3.52</v>
       </c>
       <c r="CR10" t="n">
         <v>1.4</v>
       </c>
       <c r="CS10" t="n">
-        <v>2.96</v>
+        <v>2.92</v>
       </c>
       <c r="CT10" t="n">
         <v>3.01</v>
       </c>
       <c r="CU10" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="CV10" t="n">
         <v>2</v>
@@ -4903,25 +4903,25 @@
         <v>1.87</v>
       </c>
       <c r="CX10" t="n">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="CY10" t="n">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="CZ10" t="n">
-        <v>2.29</v>
+        <v>2.3</v>
       </c>
       <c r="DA10" t="n">
-        <v>1.82</v>
+        <v>1.85</v>
       </c>
       <c r="DB10" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="DC10" t="n">
-        <v>2.1</v>
+        <v>2.07</v>
       </c>
       <c r="DD10" t="n">
-        <v>3.65</v>
+        <v>3.59</v>
       </c>
       <c r="DE10" t="n">
         <v>0.05</v>
@@ -4930,40 +4930,40 @@
         <v>1</v>
       </c>
       <c r="DG10" t="n">
-        <v>2.65</v>
+        <v>2.86</v>
       </c>
       <c r="DH10" t="n">
-        <v>80.7</v>
+        <v>82.09</v>
       </c>
       <c r="DI10" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="DJ10" t="n">
-        <v>1.8</v>
+        <v>1.86</v>
       </c>
       <c r="DK10" t="n">
-        <v>4.65</v>
+        <v>4.76</v>
       </c>
       <c r="DL10" t="n">
-        <v>0.2</v>
+        <v>0.19</v>
       </c>
       <c r="DM10" t="n">
-        <v>40.25</v>
+        <v>41.86</v>
       </c>
       <c r="DN10" t="n">
-        <v>0.75</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="DO10" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="DP10" t="n">
-        <v>11.65</v>
+        <v>11.62</v>
       </c>
       <c r="DQ10" t="n">
-        <v>12.25</v>
+        <v>12.1</v>
       </c>
       <c r="DR10" t="n">
-        <v>8.6</v>
+        <v>8.43</v>
       </c>
       <c r="DS10" t="n">
         <v>0</v>
@@ -4975,28 +4975,28 @@
         <v>0</v>
       </c>
       <c r="DV10" t="n">
-        <v>35.2</v>
+        <v>35.67</v>
       </c>
       <c r="DW10" t="n">
         <v>0.05</v>
       </c>
       <c r="DX10" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="DY10" t="n">
-        <v>7</v>
+        <v>7.09</v>
       </c>
       <c r="DZ10" t="n">
-        <v>2.8</v>
+        <v>2.91</v>
       </c>
       <c r="EA10" t="n">
-        <v>21.2</v>
+        <v>20.95</v>
       </c>
       <c r="EB10" t="n">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="EC10" t="n">
-        <v>1.7</v>
+        <v>1.76</v>
       </c>
     </row>
     <row r="11">

--- a/data/teams/leagues/Averages_Belgium_Pro_League_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Belgium_Pro_League_2025-2026.xlsx
@@ -1379,13 +1379,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C2" t="n">
         <v>11</v>
       </c>
       <c r="D2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
@@ -1469,52 +1469,52 @@
         <v>1.27</v>
       </c>
       <c r="AF2" t="n">
-        <v>0.11</v>
+        <v>0.2</v>
       </c>
       <c r="AG2" t="n">
-        <v>1.22</v>
+        <v>1.4</v>
       </c>
       <c r="AH2" t="n">
-        <v>2.67</v>
+        <v>2.5</v>
       </c>
       <c r="AI2" t="n">
-        <v>105.56</v>
+        <v>103.5</v>
       </c>
       <c r="AJ2" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="AK2" t="n">
-        <v>2.89</v>
+        <v>3</v>
       </c>
       <c r="AL2" t="n">
-        <v>4.89</v>
+        <v>4.8</v>
       </c>
       <c r="AM2" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.7</v>
       </c>
       <c r="AN2" t="n">
-        <v>51.56</v>
+        <v>51.3</v>
       </c>
       <c r="AO2" t="n">
-        <v>1.56</v>
+        <v>1.5</v>
       </c>
       <c r="AP2" t="n">
-        <v>2.22</v>
+        <v>2.3</v>
       </c>
       <c r="AQ2" t="n">
-        <v>13</v>
+        <v>12.8</v>
       </c>
       <c r="AR2" t="n">
-        <v>12.44</v>
+        <v>12.3</v>
       </c>
       <c r="AS2" t="n">
-        <v>7.44</v>
+        <v>7.6</v>
       </c>
       <c r="AT2" t="n">
-        <v>0.89</v>
+        <v>0.8</v>
       </c>
       <c r="AU2" t="n">
-        <v>0.89</v>
+        <v>1</v>
       </c>
       <c r="AV2" t="n">
         <v>0</v>
@@ -1526,82 +1526,82 @@
         <v>0</v>
       </c>
       <c r="AY2" t="n">
-        <v>49</v>
+        <v>47.2</v>
       </c>
       <c r="AZ2" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="BA2" t="n">
-        <v>12.44</v>
+        <v>12</v>
       </c>
       <c r="BB2" t="n">
-        <v>8.890000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="BC2" t="n">
-        <v>3.56</v>
+        <v>3.4</v>
       </c>
       <c r="BD2" t="n">
-        <v>22.33</v>
+        <v>22.5</v>
       </c>
       <c r="BE2" t="n">
-        <v>1.41</v>
+        <v>1.37</v>
       </c>
       <c r="BF2" t="n">
-        <v>2.67</v>
+        <v>2.8</v>
       </c>
       <c r="BG2" t="n">
-        <v>2.75</v>
+        <v>2.71</v>
       </c>
       <c r="BH2" t="n">
-        <v>10.3</v>
+        <v>10.33</v>
       </c>
       <c r="BI2" t="n">
-        <v>2.75</v>
+        <v>2.71</v>
       </c>
       <c r="BJ2" t="n">
-        <v>0.65</v>
+        <v>0.62</v>
       </c>
       <c r="BK2" t="n">
-        <v>0.95</v>
+        <v>1</v>
       </c>
       <c r="BL2" t="n">
-        <v>0.6</v>
+        <v>0.57</v>
       </c>
       <c r="BM2" t="n">
-        <v>0.55</v>
+        <v>0.52</v>
       </c>
       <c r="BN2" t="n">
-        <v>1.15</v>
+        <v>1.1</v>
       </c>
       <c r="BO2" t="n">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="BP2" t="n">
-        <v>4.6</v>
+        <v>4.62</v>
       </c>
       <c r="BQ2" t="n">
-        <v>5.65</v>
+        <v>5.67</v>
       </c>
       <c r="BR2" t="n">
-        <v>90</v>
+        <v>90.48</v>
       </c>
       <c r="BS2" t="n">
-        <v>90</v>
+        <v>90.48</v>
       </c>
       <c r="BT2" t="n">
-        <v>45</v>
+        <v>42.86</v>
       </c>
       <c r="BU2" t="n">
-        <v>25</v>
+        <v>23.81</v>
       </c>
       <c r="BV2" t="n">
-        <v>20</v>
+        <v>19.05</v>
       </c>
       <c r="BW2" t="n">
-        <v>5</v>
+        <v>4.76</v>
       </c>
       <c r="BX2" t="n">
-        <v>65</v>
+        <v>61.9</v>
       </c>
       <c r="BY2" t="n">
         <v>2.37</v>
@@ -1616,16 +1616,16 @@
         <v>3.69</v>
       </c>
       <c r="CC2" t="n">
-        <v>3.41</v>
+        <v>3.37</v>
       </c>
       <c r="CD2" t="n">
-        <v>3.6</v>
+        <v>3.53</v>
       </c>
       <c r="CE2" t="n">
         <v>1.32</v>
       </c>
       <c r="CF2" t="n">
-        <v>2.53</v>
+        <v>2.52</v>
       </c>
       <c r="CG2" t="n">
         <v>3.15</v>
@@ -1634,31 +1634,31 @@
         <v>1.48</v>
       </c>
       <c r="CI2" t="n">
-        <v>2.17</v>
+        <v>2.19</v>
       </c>
       <c r="CJ2" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="CK2" t="n">
-        <v>1.45</v>
+        <v>1.43</v>
       </c>
       <c r="CL2" t="n">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="CM2" t="n">
-        <v>2.58</v>
+        <v>2.62</v>
       </c>
       <c r="CN2" t="n">
-        <v>2.01</v>
+        <v>2.04</v>
       </c>
       <c r="CO2" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="CP2" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="CQ2" t="n">
-        <v>2.9</v>
+        <v>2.88</v>
       </c>
       <c r="CR2" t="n">
         <v>1.36</v>
@@ -1673,106 +1673,106 @@
         <v>1.51</v>
       </c>
       <c r="CV2" t="n">
-        <v>2.29</v>
+        <v>2.31</v>
       </c>
       <c r="CW2" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="CX2" t="n">
         <v>1.5</v>
       </c>
       <c r="CY2" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="CZ2" t="n">
         <v>2.53</v>
       </c>
       <c r="DA2" t="n">
-        <v>2.07</v>
+        <v>2.08</v>
       </c>
       <c r="DB2" t="n">
         <v>1.24</v>
       </c>
       <c r="DC2" t="n">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="DD2" t="n">
-        <v>2.9</v>
+        <v>2.88</v>
       </c>
       <c r="DE2" t="n">
-        <v>0.05</v>
+        <v>0.1</v>
       </c>
       <c r="DF2" t="n">
-        <v>1.05</v>
+        <v>1.14</v>
       </c>
       <c r="DG2" t="n">
-        <v>2.8</v>
+        <v>2.71</v>
       </c>
       <c r="DH2" t="n">
-        <v>107.9</v>
+        <v>106.81</v>
       </c>
       <c r="DI2" t="n">
         <v>0.1</v>
       </c>
       <c r="DJ2" t="n">
-        <v>2.05</v>
+        <v>2.14</v>
       </c>
       <c r="DK2" t="n">
-        <v>4.9</v>
+        <v>4.86</v>
       </c>
       <c r="DL2" t="n">
-        <v>0.5</v>
+        <v>0.57</v>
       </c>
       <c r="DM2" t="n">
-        <v>50.05</v>
+        <v>50</v>
       </c>
       <c r="DN2" t="n">
         <v>0.95</v>
       </c>
       <c r="DO2" t="n">
-        <v>2.1</v>
+        <v>2.14</v>
       </c>
       <c r="DP2" t="n">
-        <v>10.8</v>
+        <v>10.81</v>
       </c>
       <c r="DQ2" t="n">
-        <v>13.1</v>
+        <v>13</v>
       </c>
       <c r="DR2" t="n">
-        <v>7.15</v>
+        <v>7.24</v>
       </c>
       <c r="DS2" t="n">
-        <v>0.3</v>
+        <v>0.29</v>
       </c>
       <c r="DT2" t="n">
-        <v>0.3</v>
+        <v>0.29</v>
       </c>
       <c r="DU2" t="n">
         <v>0</v>
       </c>
       <c r="DV2" t="n">
-        <v>50.3</v>
+        <v>49.38</v>
       </c>
       <c r="DW2" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="DX2" t="n">
-        <v>13.7</v>
+        <v>13.43</v>
       </c>
       <c r="DY2" t="n">
-        <v>9.300000000000001</v>
+        <v>9.140000000000001</v>
       </c>
       <c r="DZ2" t="n">
-        <v>4.4</v>
+        <v>4.29</v>
       </c>
       <c r="EA2" t="n">
-        <v>23.15</v>
+        <v>23.19</v>
       </c>
       <c r="EB2" t="n">
-        <v>1.54</v>
+        <v>1.51</v>
       </c>
       <c r="EC2" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3">
@@ -2185,10 +2185,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C4" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D4" t="n">
         <v>10</v>
@@ -2197,82 +2197,82 @@
         <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="G4" t="n">
-        <v>1.2</v>
+        <v>1.09</v>
       </c>
       <c r="H4" t="n">
-        <v>94.5</v>
+        <v>95.64</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.2</v>
+        <v>-0.18</v>
       </c>
       <c r="J4" t="n">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="K4" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="M4" t="n">
-        <v>43.6</v>
+        <v>44.64</v>
       </c>
       <c r="N4" t="n">
-        <v>0.6</v>
+        <v>0.55</v>
       </c>
       <c r="O4" t="n">
-        <v>1.1</v>
+        <v>1.18</v>
       </c>
       <c r="P4" t="n">
-        <v>10.1</v>
+        <v>10.45</v>
       </c>
       <c r="Q4" t="n">
-        <v>11.5</v>
+        <v>11.27</v>
       </c>
       <c r="R4" t="n">
-        <v>10.6</v>
+        <v>10.91</v>
       </c>
       <c r="S4" t="n">
-        <v>1.7</v>
+        <v>1.55</v>
       </c>
       <c r="T4" t="n">
-        <v>0.6</v>
+        <v>0.64</v>
       </c>
       <c r="U4" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="V4" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="W4" t="n">
         <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>50.1</v>
+        <v>49.91</v>
       </c>
       <c r="Y4" t="n">
         <v>0</v>
       </c>
       <c r="Z4" t="n">
-        <v>9.5</v>
+        <v>9.550000000000001</v>
       </c>
       <c r="AA4" t="n">
-        <v>6.3</v>
+        <v>6.55</v>
       </c>
       <c r="AB4" t="n">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="AC4" t="n">
-        <v>23.7</v>
+        <v>23.27</v>
       </c>
       <c r="AD4" t="n">
         <v>1.14</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="AF4" t="n">
         <v>0.2</v>
@@ -2356,70 +2356,70 @@
         <v>2</v>
       </c>
       <c r="BG4" t="n">
-        <v>2.5</v>
+        <v>2.43</v>
       </c>
       <c r="BH4" t="n">
-        <v>8.25</v>
+        <v>8.19</v>
       </c>
       <c r="BI4" t="n">
-        <v>2.5</v>
+        <v>2.43</v>
       </c>
       <c r="BJ4" t="n">
-        <v>0.55</v>
+        <v>0.57</v>
       </c>
       <c r="BK4" t="n">
-        <v>0.3</v>
+        <v>0.29</v>
       </c>
       <c r="BL4" t="n">
-        <v>0.6</v>
+        <v>0.57</v>
       </c>
       <c r="BM4" t="n">
-        <v>1.05</v>
+        <v>1</v>
       </c>
       <c r="BN4" t="n">
-        <v>1.65</v>
+        <v>1.57</v>
       </c>
       <c r="BO4" t="n">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="BP4" t="n">
-        <v>3.65</v>
+        <v>3.62</v>
       </c>
       <c r="BQ4" t="n">
         <v>3.95</v>
       </c>
       <c r="BR4" t="n">
-        <v>90</v>
+        <v>90.48</v>
       </c>
       <c r="BS4" t="n">
-        <v>75</v>
+        <v>71.43000000000001</v>
       </c>
       <c r="BT4" t="n">
-        <v>50</v>
+        <v>47.62</v>
       </c>
       <c r="BU4" t="n">
-        <v>25</v>
+        <v>23.81</v>
       </c>
       <c r="BV4" t="n">
-        <v>5</v>
+        <v>4.76</v>
       </c>
       <c r="BW4" t="n">
-        <v>5</v>
+        <v>4.76</v>
       </c>
       <c r="BX4" t="n">
-        <v>60</v>
+        <v>57.14</v>
       </c>
       <c r="BY4" t="n">
-        <v>3.46</v>
+        <v>3.41</v>
       </c>
       <c r="BZ4" t="n">
-        <v>3.54</v>
+        <v>3.51</v>
       </c>
       <c r="CA4" t="n">
-        <v>3.69</v>
+        <v>3.66</v>
       </c>
       <c r="CB4" t="n">
-        <v>3.87</v>
+        <v>3.83</v>
       </c>
       <c r="CC4" t="n">
         <v>4.63</v>
@@ -2431,16 +2431,16 @@
         <v>1.35</v>
       </c>
       <c r="CF4" t="n">
-        <v>2.59</v>
+        <v>2.6</v>
       </c>
       <c r="CG4" t="n">
-        <v>3.08</v>
+        <v>3.06</v>
       </c>
       <c r="CH4" t="n">
         <v>1.46</v>
       </c>
       <c r="CI4" t="n">
-        <v>2.04</v>
+        <v>2.03</v>
       </c>
       <c r="CJ4" t="n">
         <v>1.74</v>
@@ -2452,19 +2452,19 @@
         <v>2.02</v>
       </c>
       <c r="CM4" t="n">
-        <v>2.36</v>
+        <v>2.35</v>
       </c>
       <c r="CN4" t="n">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="CO4" t="n">
         <v>1.25</v>
       </c>
       <c r="CP4" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="CQ4" t="n">
-        <v>3.07</v>
+        <v>3.09</v>
       </c>
       <c r="CR4" t="n">
         <v>1.39</v>
@@ -2479,43 +2479,43 @@
         <v>1.49</v>
       </c>
       <c r="CV4" t="n">
-        <v>2.15</v>
+        <v>2.14</v>
       </c>
       <c r="CW4" t="n">
         <v>1.76</v>
       </c>
       <c r="CX4" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="CY4" t="n">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="CZ4" t="n">
-        <v>2.37</v>
+        <v>2.36</v>
       </c>
       <c r="DA4" t="n">
-        <v>1.88</v>
+        <v>1.86</v>
       </c>
       <c r="DB4" t="n">
         <v>1.27</v>
       </c>
       <c r="DC4" t="n">
-        <v>1.88</v>
+        <v>1.9</v>
       </c>
       <c r="DD4" t="n">
-        <v>3.1</v>
+        <v>3.14</v>
       </c>
       <c r="DE4" t="n">
         <v>0.1</v>
       </c>
       <c r="DF4" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="DG4" t="n">
-        <v>1.35</v>
+        <v>1.29</v>
       </c>
       <c r="DH4" t="n">
-        <v>92.8</v>
+        <v>93.48</v>
       </c>
       <c r="DI4" t="n">
         <v>-0.05</v>
@@ -2524,61 +2524,61 @@
         <v>2.05</v>
       </c>
       <c r="DK4" t="n">
-        <v>3.2</v>
+        <v>3.14</v>
       </c>
       <c r="DL4" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="DM4" t="n">
-        <v>41.5</v>
+        <v>42.14</v>
       </c>
       <c r="DN4" t="n">
-        <v>0.65</v>
+        <v>0.62</v>
       </c>
       <c r="DO4" t="n">
-        <v>1.45</v>
+        <v>1.48</v>
       </c>
       <c r="DP4" t="n">
-        <v>10.95</v>
+        <v>11.09</v>
       </c>
       <c r="DQ4" t="n">
-        <v>11.65</v>
+        <v>11.52</v>
       </c>
       <c r="DR4" t="n">
-        <v>10.55</v>
+        <v>10.71</v>
       </c>
       <c r="DS4" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="DT4" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="DU4" t="n">
         <v>0</v>
       </c>
       <c r="DV4" t="n">
-        <v>46.85</v>
+        <v>46.91</v>
       </c>
       <c r="DW4" t="n">
-        <v>0.2</v>
+        <v>0.19</v>
       </c>
       <c r="DX4" t="n">
-        <v>10.45</v>
+        <v>10.43</v>
       </c>
       <c r="DY4" t="n">
-        <v>6.55</v>
+        <v>6.67</v>
       </c>
       <c r="DZ4" t="n">
-        <v>3.9</v>
+        <v>3.76</v>
       </c>
       <c r="EA4" t="n">
-        <v>21.4</v>
+        <v>21.28</v>
       </c>
       <c r="EB4" t="n">
         <v>1.23</v>
       </c>
       <c r="EC4" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
     </row>
     <row r="5">
@@ -2588,94 +2588,94 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C5" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D5" t="n">
         <v>10</v>
       </c>
       <c r="E5" t="n">
-        <v>0.3</v>
+        <v>0.27</v>
       </c>
       <c r="F5" t="n">
-        <v>1</v>
+        <v>1.18</v>
       </c>
       <c r="G5" t="n">
-        <v>2.5</v>
+        <v>2.73</v>
       </c>
       <c r="H5" t="n">
-        <v>106.7</v>
+        <v>105.73</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>1.5</v>
+        <v>1.73</v>
       </c>
       <c r="K5" t="n">
-        <v>4.6</v>
+        <v>5</v>
       </c>
       <c r="L5" t="n">
-        <v>0.4</v>
+        <v>0.36</v>
       </c>
       <c r="M5" t="n">
-        <v>48.8</v>
+        <v>48.36</v>
       </c>
       <c r="N5" t="n">
-        <v>0.4</v>
+        <v>0.45</v>
       </c>
       <c r="O5" t="n">
-        <v>2.1</v>
+        <v>2.27</v>
       </c>
       <c r="P5" t="n">
-        <v>10.7</v>
+        <v>10.82</v>
       </c>
       <c r="Q5" t="n">
-        <v>10.2</v>
+        <v>10.82</v>
       </c>
       <c r="R5" t="n">
-        <v>8.5</v>
+        <v>8.09</v>
       </c>
       <c r="S5" t="n">
-        <v>1</v>
+        <v>1.09</v>
       </c>
       <c r="T5" t="n">
-        <v>1.7</v>
+        <v>1.91</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>0.09</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>0.09</v>
       </c>
       <c r="W5" t="n">
         <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>54.8</v>
+        <v>54.55</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="Z5" t="n">
-        <v>15.4</v>
+        <v>15.64</v>
       </c>
       <c r="AA5" t="n">
-        <v>11.2</v>
+        <v>11.27</v>
       </c>
       <c r="AB5" t="n">
-        <v>4.2</v>
+        <v>4.36</v>
       </c>
       <c r="AC5" t="n">
-        <v>19.1</v>
+        <v>19.09</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.3</v>
+        <v>1.55</v>
       </c>
       <c r="AF5" t="n">
         <v>0.1</v>
@@ -2759,70 +2759,70 @@
         <v>1.9</v>
       </c>
       <c r="BG5" t="n">
-        <v>2.85</v>
+        <v>3</v>
       </c>
       <c r="BH5" t="n">
-        <v>9.699999999999999</v>
+        <v>10.05</v>
       </c>
       <c r="BI5" t="n">
-        <v>2.85</v>
+        <v>3</v>
       </c>
       <c r="BJ5" t="n">
         <v>0.9</v>
       </c>
       <c r="BK5" t="n">
-        <v>0.4</v>
+        <v>0.48</v>
       </c>
       <c r="BL5" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="BM5" t="n">
-        <v>0.65</v>
+        <v>0.62</v>
       </c>
       <c r="BN5" t="n">
-        <v>1.55</v>
+        <v>1.62</v>
       </c>
       <c r="BO5" t="n">
-        <v>1.3</v>
+        <v>1.38</v>
       </c>
       <c r="BP5" t="n">
-        <v>3.9</v>
+        <v>4.05</v>
       </c>
       <c r="BQ5" t="n">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="BR5" t="n">
-        <v>95</v>
+        <v>95.23999999999999</v>
       </c>
       <c r="BS5" t="n">
-        <v>85</v>
+        <v>85.70999999999999</v>
       </c>
       <c r="BT5" t="n">
-        <v>55</v>
+        <v>57.14</v>
       </c>
       <c r="BU5" t="n">
-        <v>30</v>
+        <v>33.33</v>
       </c>
       <c r="BV5" t="n">
-        <v>15</v>
+        <v>19.05</v>
       </c>
       <c r="BW5" t="n">
-        <v>5</v>
+        <v>9.52</v>
       </c>
       <c r="BX5" t="n">
-        <v>60</v>
+        <v>61.9</v>
       </c>
       <c r="BY5" t="n">
-        <v>2.69</v>
+        <v>2.71</v>
       </c>
       <c r="BZ5" t="n">
-        <v>2.82</v>
+        <v>2.83</v>
       </c>
       <c r="CA5" t="n">
-        <v>3.66</v>
+        <v>3.64</v>
       </c>
       <c r="CB5" t="n">
-        <v>3.84</v>
+        <v>3.82</v>
       </c>
       <c r="CC5" t="n">
         <v>3.75</v>
@@ -2837,10 +2837,10 @@
         <v>2.43</v>
       </c>
       <c r="CG5" t="n">
-        <v>3.26</v>
+        <v>3.25</v>
       </c>
       <c r="CH5" t="n">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="CI5" t="n">
         <v>2.25</v>
@@ -2852,136 +2852,136 @@
         <v>1.44</v>
       </c>
       <c r="CL5" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="CM5" t="n">
-        <v>2.58</v>
+        <v>2.57</v>
       </c>
       <c r="CN5" t="n">
-        <v>2.01</v>
+        <v>2</v>
       </c>
       <c r="CO5" t="n">
         <v>1.21</v>
       </c>
       <c r="CP5" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="CQ5" t="n">
-        <v>2.68</v>
+        <v>2.7</v>
       </c>
       <c r="CR5" t="n">
         <v>1.35</v>
       </c>
       <c r="CS5" t="n">
-        <v>2.49</v>
+        <v>2.51</v>
       </c>
       <c r="CT5" t="n">
-        <v>3.27</v>
+        <v>3.24</v>
       </c>
       <c r="CU5" t="n">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="CV5" t="n">
-        <v>2.35</v>
+        <v>2.34</v>
       </c>
       <c r="CW5" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="CX5" t="n">
         <v>1.52</v>
       </c>
       <c r="CY5" t="n">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="CZ5" t="n">
         <v>2.49</v>
       </c>
       <c r="DA5" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="DB5" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="DC5" t="n">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="DD5" t="n">
-        <v>2.77</v>
+        <v>2.81</v>
       </c>
       <c r="DE5" t="n">
-        <v>0.2</v>
+        <v>0.19</v>
       </c>
       <c r="DF5" t="n">
-        <v>1.15</v>
+        <v>1.24</v>
       </c>
       <c r="DG5" t="n">
-        <v>2.7</v>
+        <v>2.81</v>
       </c>
       <c r="DH5" t="n">
-        <v>98.25</v>
+        <v>98.14</v>
       </c>
       <c r="DI5" t="n">
         <v>0</v>
       </c>
       <c r="DJ5" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="DK5" t="n">
-        <v>4.65</v>
+        <v>4.86</v>
       </c>
       <c r="DL5" t="n">
-        <v>0.55</v>
+        <v>0.52</v>
       </c>
       <c r="DM5" t="n">
-        <v>44.6</v>
+        <v>44.57</v>
       </c>
       <c r="DN5" t="n">
-        <v>0.6</v>
+        <v>0.62</v>
       </c>
       <c r="DO5" t="n">
-        <v>1.95</v>
+        <v>2.05</v>
       </c>
       <c r="DP5" t="n">
-        <v>10.8</v>
+        <v>10.86</v>
       </c>
       <c r="DQ5" t="n">
-        <v>10.55</v>
+        <v>10.86</v>
       </c>
       <c r="DR5" t="n">
-        <v>9.75</v>
+        <v>9.48</v>
       </c>
       <c r="DS5" t="n">
-        <v>0.05</v>
+        <v>0.09</v>
       </c>
       <c r="DT5" t="n">
-        <v>0.05</v>
+        <v>0.09</v>
       </c>
       <c r="DU5" t="n">
         <v>0</v>
       </c>
       <c r="DV5" t="n">
-        <v>51.7</v>
+        <v>51.72</v>
       </c>
       <c r="DW5" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="DX5" t="n">
-        <v>13.35</v>
+        <v>13.57</v>
       </c>
       <c r="DY5" t="n">
-        <v>8.9</v>
+        <v>9.050000000000001</v>
       </c>
       <c r="DZ5" t="n">
-        <v>4.45</v>
+        <v>4.52</v>
       </c>
       <c r="EA5" t="n">
-        <v>18.8</v>
+        <v>18.81</v>
       </c>
       <c r="EB5" t="n">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="EC5" t="n">
-        <v>1.6</v>
+        <v>1.72</v>
       </c>
     </row>
     <row r="6">
@@ -2991,13 +2991,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C6" t="n">
         <v>10</v>
       </c>
       <c r="D6" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
@@ -3081,52 +3081,52 @@
         <v>1</v>
       </c>
       <c r="AF6" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AH6" t="n">
-        <v>2.9</v>
+        <v>2.64</v>
       </c>
       <c r="AI6" t="n">
-        <v>101.7</v>
+        <v>103.45</v>
       </c>
       <c r="AJ6" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="AK6" t="n">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="AL6" t="n">
-        <v>5.2</v>
+        <v>4.73</v>
       </c>
       <c r="AM6" t="n">
-        <v>0.8</v>
+        <v>0.73</v>
       </c>
       <c r="AN6" t="n">
-        <v>47.4</v>
+        <v>47.27</v>
       </c>
       <c r="AO6" t="n">
-        <v>0.4</v>
+        <v>0.45</v>
       </c>
       <c r="AP6" t="n">
-        <v>2.3</v>
+        <v>2.09</v>
       </c>
       <c r="AQ6" t="n">
-        <v>9.300000000000001</v>
+        <v>9.73</v>
       </c>
       <c r="AR6" t="n">
-        <v>12.2</v>
+        <v>11.91</v>
       </c>
       <c r="AS6" t="n">
-        <v>7.1</v>
+        <v>7.45</v>
       </c>
       <c r="AT6" t="n">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="AU6" t="n">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AV6" t="n">
         <v>0</v>
@@ -3138,82 +3138,82 @@
         <v>0</v>
       </c>
       <c r="AY6" t="n">
-        <v>61.2</v>
+        <v>61.18</v>
       </c>
       <c r="AZ6" t="n">
         <v>0</v>
       </c>
       <c r="BA6" t="n">
-        <v>14.9</v>
+        <v>14.18</v>
       </c>
       <c r="BB6" t="n">
-        <v>9.300000000000001</v>
+        <v>8.640000000000001</v>
       </c>
       <c r="BC6" t="n">
-        <v>5.6</v>
+        <v>5.55</v>
       </c>
       <c r="BD6" t="n">
-        <v>19.7</v>
+        <v>19.27</v>
       </c>
       <c r="BE6" t="n">
-        <v>1.68</v>
+        <v>1.63</v>
       </c>
       <c r="BF6" t="n">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="BG6" t="n">
         <v>2.9</v>
       </c>
       <c r="BH6" t="n">
-        <v>10.25</v>
+        <v>9.949999999999999</v>
       </c>
       <c r="BI6" t="n">
         <v>2.9</v>
       </c>
       <c r="BJ6" t="n">
-        <v>0.65</v>
+        <v>0.62</v>
       </c>
       <c r="BK6" t="n">
-        <v>0.95</v>
+        <v>0.9</v>
       </c>
       <c r="BL6" t="n">
-        <v>0.8</v>
+        <v>0.86</v>
       </c>
       <c r="BM6" t="n">
-        <v>0.5</v>
+        <v>0.52</v>
       </c>
       <c r="BN6" t="n">
-        <v>1.3</v>
+        <v>1.38</v>
       </c>
       <c r="BO6" t="n">
-        <v>1.6</v>
+        <v>1.52</v>
       </c>
       <c r="BP6" t="n">
-        <v>4.55</v>
+        <v>4.48</v>
       </c>
       <c r="BQ6" t="n">
-        <v>5.65</v>
+        <v>5.43</v>
       </c>
       <c r="BR6" t="n">
         <v>100</v>
       </c>
       <c r="BS6" t="n">
-        <v>85</v>
+        <v>85.70999999999999</v>
       </c>
       <c r="BT6" t="n">
-        <v>60</v>
+        <v>61.9</v>
       </c>
       <c r="BU6" t="n">
-        <v>20</v>
+        <v>19.05</v>
       </c>
       <c r="BV6" t="n">
-        <v>10</v>
+        <v>9.52</v>
       </c>
       <c r="BW6" t="n">
-        <v>5</v>
+        <v>4.76</v>
       </c>
       <c r="BX6" t="n">
-        <v>80</v>
+        <v>80.95</v>
       </c>
       <c r="BY6" t="n">
         <v>1.81</v>
@@ -3222,16 +3222,16 @@
         <v>1.9</v>
       </c>
       <c r="CA6" t="n">
-        <v>3.86</v>
+        <v>3.85</v>
       </c>
       <c r="CB6" t="n">
-        <v>3.99</v>
+        <v>3.97</v>
       </c>
       <c r="CC6" t="n">
-        <v>2.45</v>
+        <v>2.41</v>
       </c>
       <c r="CD6" t="n">
-        <v>2.5</v>
+        <v>2.46</v>
       </c>
       <c r="CE6" t="n">
         <v>1.29</v>
@@ -3249,19 +3249,19 @@
         <v>2.25</v>
       </c>
       <c r="CJ6" t="n">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="CK6" t="n">
         <v>1.51</v>
       </c>
       <c r="CL6" t="n">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="CM6" t="n">
         <v>2.43</v>
       </c>
       <c r="CN6" t="n">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="CO6" t="n">
         <v>1.19</v>
@@ -3270,22 +3270,22 @@
         <v>1.69</v>
       </c>
       <c r="CQ6" t="n">
-        <v>2.67</v>
+        <v>2.68</v>
       </c>
       <c r="CR6" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="CS6" t="n">
-        <v>2.55</v>
+        <v>2.56</v>
       </c>
       <c r="CT6" t="n">
-        <v>3.09</v>
+        <v>3.12</v>
       </c>
       <c r="CU6" t="n">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="CV6" t="n">
-        <v>2.31</v>
+        <v>2.3</v>
       </c>
       <c r="CW6" t="n">
         <v>1.68</v>
@@ -3306,10 +3306,10 @@
         <v>1.23</v>
       </c>
       <c r="DC6" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="DD6" t="n">
-        <v>2.78</v>
+        <v>2.79</v>
       </c>
       <c r="DE6" t="n">
         <v>0.05</v>
@@ -3318,40 +3318,40 @@
         <v>0.9</v>
       </c>
       <c r="DG6" t="n">
-        <v>3.65</v>
+        <v>3.48</v>
       </c>
       <c r="DH6" t="n">
-        <v>116.7</v>
+        <v>116.9</v>
       </c>
       <c r="DI6" t="n">
         <v>0.05</v>
       </c>
       <c r="DJ6" t="n">
-        <v>1.45</v>
+        <v>1.48</v>
       </c>
       <c r="DK6" t="n">
-        <v>6.2</v>
+        <v>5.91</v>
       </c>
       <c r="DL6" t="n">
-        <v>0.7</v>
+        <v>0.67</v>
       </c>
       <c r="DM6" t="n">
-        <v>56</v>
+        <v>55.52</v>
       </c>
       <c r="DN6" t="n">
-        <v>0.5</v>
+        <v>0.52</v>
       </c>
       <c r="DO6" t="n">
-        <v>2.5</v>
+        <v>2.38</v>
       </c>
       <c r="DP6" t="n">
-        <v>10.15</v>
+        <v>10.33</v>
       </c>
       <c r="DQ6" t="n">
-        <v>13.1</v>
+        <v>12.91</v>
       </c>
       <c r="DR6" t="n">
-        <v>6</v>
+        <v>6.24</v>
       </c>
       <c r="DS6" t="n">
         <v>0</v>
@@ -3363,28 +3363,28 @@
         <v>0</v>
       </c>
       <c r="DV6" t="n">
-        <v>63.25</v>
+        <v>63.14</v>
       </c>
       <c r="DW6" t="n">
         <v>0.05</v>
       </c>
       <c r="DX6" t="n">
-        <v>16.75</v>
+        <v>16.28</v>
       </c>
       <c r="DY6" t="n">
-        <v>11</v>
+        <v>10.57</v>
       </c>
       <c r="DZ6" t="n">
-        <v>5.75</v>
+        <v>5.72</v>
       </c>
       <c r="EA6" t="n">
-        <v>20.25</v>
+        <v>20</v>
       </c>
       <c r="EB6" t="n">
-        <v>1.87</v>
+        <v>1.83</v>
       </c>
       <c r="EC6" t="n">
-        <v>1.35</v>
+        <v>1.38</v>
       </c>
     </row>
     <row r="7">
@@ -3394,13 +3394,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C7" t="n">
         <v>10</v>
       </c>
       <c r="D7" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E7" t="n">
         <v>0.2</v>
@@ -3484,52 +3484,52 @@
         <v>2.4</v>
       </c>
       <c r="AF7" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="AH7" t="n">
-        <v>3.3</v>
+        <v>3</v>
       </c>
       <c r="AI7" t="n">
-        <v>84</v>
+        <v>85.64</v>
       </c>
       <c r="AJ7" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="AK7" t="n">
-        <v>2.3</v>
+        <v>2.27</v>
       </c>
       <c r="AL7" t="n">
-        <v>5.6</v>
+        <v>5.09</v>
       </c>
       <c r="AM7" t="n">
-        <v>0.4</v>
+        <v>0.36</v>
       </c>
       <c r="AN7" t="n">
-        <v>42.4</v>
+        <v>41.82</v>
       </c>
       <c r="AO7" t="n">
-        <v>0.8</v>
+        <v>0.82</v>
       </c>
       <c r="AP7" t="n">
-        <v>2.3</v>
+        <v>2.09</v>
       </c>
       <c r="AQ7" t="n">
-        <v>9.699999999999999</v>
+        <v>10</v>
       </c>
       <c r="AR7" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AS7" t="n">
-        <v>8.6</v>
+        <v>8.91</v>
       </c>
       <c r="AT7" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="AU7" t="n">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="AV7" t="n">
         <v>0</v>
@@ -3541,82 +3541,82 @@
         <v>0</v>
       </c>
       <c r="AY7" t="n">
-        <v>47.9</v>
+        <v>48.82</v>
       </c>
       <c r="AZ7" t="n">
         <v>0</v>
       </c>
       <c r="BA7" t="n">
-        <v>10.7</v>
+        <v>10.09</v>
       </c>
       <c r="BB7" t="n">
-        <v>6.4</v>
+        <v>6.09</v>
       </c>
       <c r="BC7" t="n">
-        <v>4.3</v>
+        <v>4</v>
       </c>
       <c r="BD7" t="n">
-        <v>20.3</v>
+        <v>21.91</v>
       </c>
       <c r="BE7" t="n">
-        <v>1.29</v>
+        <v>1.22</v>
       </c>
       <c r="BF7" t="n">
-        <v>2.3</v>
+        <v>2.27</v>
       </c>
       <c r="BG7" t="n">
-        <v>2.35</v>
+        <v>2.29</v>
       </c>
       <c r="BH7" t="n">
-        <v>11.5</v>
+        <v>11.29</v>
       </c>
       <c r="BI7" t="n">
-        <v>2.35</v>
+        <v>2.29</v>
       </c>
       <c r="BJ7" t="n">
-        <v>0.5</v>
+        <v>0.52</v>
       </c>
       <c r="BK7" t="n">
-        <v>0.45</v>
+        <v>0.43</v>
       </c>
       <c r="BL7" t="n">
-        <v>0.6</v>
+        <v>0.57</v>
       </c>
       <c r="BM7" t="n">
-        <v>0.8</v>
+        <v>0.76</v>
       </c>
       <c r="BN7" t="n">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="BO7" t="n">
         <v>0.95</v>
       </c>
       <c r="BP7" t="n">
-        <v>5.25</v>
+        <v>5.14</v>
       </c>
       <c r="BQ7" t="n">
-        <v>6.25</v>
+        <v>6.14</v>
       </c>
       <c r="BR7" t="n">
-        <v>95</v>
+        <v>95.23999999999999</v>
       </c>
       <c r="BS7" t="n">
-        <v>70</v>
+        <v>66.67</v>
       </c>
       <c r="BT7" t="n">
-        <v>35</v>
+        <v>33.33</v>
       </c>
       <c r="BU7" t="n">
-        <v>25</v>
+        <v>23.81</v>
       </c>
       <c r="BV7" t="n">
-        <v>10</v>
+        <v>9.52</v>
       </c>
       <c r="BW7" t="n">
         <v>0</v>
       </c>
       <c r="BX7" t="n">
-        <v>65</v>
+        <v>61.9</v>
       </c>
       <c r="BY7" t="n">
         <v>2.81</v>
@@ -3625,16 +3625,16 @@
         <v>3</v>
       </c>
       <c r="CA7" t="n">
-        <v>3.68</v>
+        <v>3.73</v>
       </c>
       <c r="CB7" t="n">
-        <v>3.8</v>
+        <v>3.87</v>
       </c>
       <c r="CC7" t="n">
-        <v>3.59</v>
+        <v>3.98</v>
       </c>
       <c r="CD7" t="n">
-        <v>4.12</v>
+        <v>4.51</v>
       </c>
       <c r="CE7" t="n">
         <v>1.3</v>
@@ -3643,55 +3643,55 @@
         <v>2.43</v>
       </c>
       <c r="CG7" t="n">
-        <v>3.24</v>
+        <v>3.25</v>
       </c>
       <c r="CH7" t="n">
         <v>1.52</v>
       </c>
       <c r="CI7" t="n">
-        <v>2.24</v>
+        <v>2.22</v>
       </c>
       <c r="CJ7" t="n">
-        <v>1.61</v>
+        <v>1.63</v>
       </c>
       <c r="CK7" t="n">
         <v>1.39</v>
       </c>
       <c r="CL7" t="n">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="CM7" t="n">
-        <v>2.76</v>
+        <v>2.75</v>
       </c>
       <c r="CN7" t="n">
-        <v>2.11</v>
+        <v>2.1</v>
       </c>
       <c r="CO7" t="n">
         <v>1.21</v>
       </c>
       <c r="CP7" t="n">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="CQ7" t="n">
-        <v>2.7</v>
+        <v>2.68</v>
       </c>
       <c r="CR7" t="n">
         <v>1.36</v>
       </c>
       <c r="CS7" t="n">
-        <v>2.54</v>
+        <v>2.55</v>
       </c>
       <c r="CT7" t="n">
         <v>3.2</v>
       </c>
       <c r="CU7" t="n">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="CV7" t="n">
-        <v>2.37</v>
+        <v>2.34</v>
       </c>
       <c r="CW7" t="n">
-        <v>1.63</v>
+        <v>1.66</v>
       </c>
       <c r="CX7" t="n">
         <v>1.49</v>
@@ -3700,10 +3700,10 @@
         <v>1.72</v>
       </c>
       <c r="CZ7" t="n">
-        <v>2.56</v>
+        <v>2.57</v>
       </c>
       <c r="DA7" t="n">
-        <v>2.13</v>
+        <v>2.12</v>
       </c>
       <c r="DB7" t="n">
         <v>1.23</v>
@@ -3712,49 +3712,49 @@
         <v>1.76</v>
       </c>
       <c r="DD7" t="n">
-        <v>2.81</v>
+        <v>2.82</v>
       </c>
       <c r="DE7" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="DF7" t="n">
-        <v>1.55</v>
+        <v>1.52</v>
       </c>
       <c r="DG7" t="n">
-        <v>2.8</v>
+        <v>2.67</v>
       </c>
       <c r="DH7" t="n">
-        <v>86.8</v>
+        <v>87.53</v>
       </c>
       <c r="DI7" t="n">
-        <v>0.2</v>
+        <v>0.19</v>
       </c>
       <c r="DJ7" t="n">
-        <v>2.35</v>
+        <v>2.33</v>
       </c>
       <c r="DK7" t="n">
-        <v>5.1</v>
+        <v>4.86</v>
       </c>
       <c r="DL7" t="n">
-        <v>0.3</v>
+        <v>0.28</v>
       </c>
       <c r="DM7" t="n">
-        <v>46.45</v>
+        <v>45.95</v>
       </c>
       <c r="DN7" t="n">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="DO7" t="n">
-        <v>2.3</v>
+        <v>2.19</v>
       </c>
       <c r="DP7" t="n">
-        <v>10.15</v>
+        <v>10.29</v>
       </c>
       <c r="DQ7" t="n">
-        <v>10.9</v>
+        <v>11.14</v>
       </c>
       <c r="DR7" t="n">
-        <v>9.199999999999999</v>
+        <v>9.33</v>
       </c>
       <c r="DS7" t="n">
         <v>0.1</v>
@@ -3766,28 +3766,28 @@
         <v>0</v>
       </c>
       <c r="DV7" t="n">
-        <v>49.1</v>
+        <v>49.52</v>
       </c>
       <c r="DW7" t="n">
         <v>0</v>
       </c>
       <c r="DX7" t="n">
-        <v>10.65</v>
+        <v>10.33</v>
       </c>
       <c r="DY7" t="n">
-        <v>6.6</v>
+        <v>6.43</v>
       </c>
       <c r="DZ7" t="n">
-        <v>4.05</v>
+        <v>3.9</v>
       </c>
       <c r="EA7" t="n">
-        <v>21.05</v>
+        <v>21.86</v>
       </c>
       <c r="EB7" t="n">
-        <v>1.3</v>
+        <v>1.26</v>
       </c>
       <c r="EC7" t="n">
-        <v>2.35</v>
+        <v>2.33</v>
       </c>
     </row>
     <row r="8">
@@ -3797,94 +3797,94 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C8" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D8" t="n">
         <v>10</v>
       </c>
       <c r="E8" t="n">
-        <v>0.3</v>
+        <v>0.27</v>
       </c>
       <c r="F8" t="n">
-        <v>1</v>
+        <v>0.91</v>
       </c>
       <c r="G8" t="n">
-        <v>2.9</v>
+        <v>3.09</v>
       </c>
       <c r="H8" t="n">
-        <v>98.5</v>
+        <v>100.73</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="K8" t="n">
-        <v>6.2</v>
+        <v>6.27</v>
       </c>
       <c r="L8" t="n">
-        <v>0.4</v>
+        <v>0.36</v>
       </c>
       <c r="M8" t="n">
-        <v>57</v>
+        <v>57.73</v>
       </c>
       <c r="N8" t="n">
-        <v>0.4</v>
+        <v>0.36</v>
       </c>
       <c r="O8" t="n">
-        <v>3.3</v>
+        <v>3.18</v>
       </c>
       <c r="P8" t="n">
-        <v>10.5</v>
+        <v>10.55</v>
       </c>
       <c r="Q8" t="n">
-        <v>12.1</v>
+        <v>12</v>
       </c>
       <c r="R8" t="n">
-        <v>8.1</v>
+        <v>7.82</v>
       </c>
       <c r="S8" t="n">
-        <v>0.7</v>
+        <v>0.82</v>
       </c>
       <c r="T8" t="n">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="U8" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="V8" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>50.4</v>
+        <v>52.09</v>
       </c>
       <c r="Y8" t="n">
         <v>0</v>
       </c>
       <c r="Z8" t="n">
-        <v>17.2</v>
+        <v>17.18</v>
       </c>
       <c r="AA8" t="n">
-        <v>12.1</v>
+        <v>12</v>
       </c>
       <c r="AB8" t="n">
-        <v>5.1</v>
+        <v>5.18</v>
       </c>
       <c r="AC8" t="n">
-        <v>20.2</v>
+        <v>20.64</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="AF8" t="n">
         <v>0.1</v>
@@ -3968,70 +3968,70 @@
         <v>1.6</v>
       </c>
       <c r="BG8" t="n">
-        <v>2.9</v>
+        <v>2.86</v>
       </c>
       <c r="BH8" t="n">
-        <v>10.25</v>
+        <v>10.29</v>
       </c>
       <c r="BI8" t="n">
-        <v>2.9</v>
+        <v>2.86</v>
       </c>
       <c r="BJ8" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="BK8" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="BL8" t="n">
         <v>0.9</v>
       </c>
-      <c r="BK8" t="n">
-        <v>0.45</v>
-      </c>
-      <c r="BL8" t="n">
-        <v>0.95</v>
-      </c>
       <c r="BM8" t="n">
-        <v>0.6</v>
+        <v>0.57</v>
       </c>
       <c r="BN8" t="n">
-        <v>1.55</v>
+        <v>1.48</v>
       </c>
       <c r="BO8" t="n">
-        <v>1.35</v>
+        <v>1.38</v>
       </c>
       <c r="BP8" t="n">
         <v>4.95</v>
       </c>
       <c r="BQ8" t="n">
-        <v>5.25</v>
+        <v>5.29</v>
       </c>
       <c r="BR8" t="n">
-        <v>90</v>
+        <v>90.48</v>
       </c>
       <c r="BS8" t="n">
-        <v>80</v>
+        <v>80.95</v>
       </c>
       <c r="BT8" t="n">
-        <v>40</v>
+        <v>38.1</v>
       </c>
       <c r="BU8" t="n">
-        <v>30</v>
+        <v>28.57</v>
       </c>
       <c r="BV8" t="n">
-        <v>15</v>
+        <v>14.29</v>
       </c>
       <c r="BW8" t="n">
-        <v>10</v>
+        <v>9.52</v>
       </c>
       <c r="BX8" t="n">
-        <v>40</v>
+        <v>38.1</v>
       </c>
       <c r="BY8" t="n">
-        <v>2.21</v>
+        <v>2.19</v>
       </c>
       <c r="BZ8" t="n">
-        <v>2.3</v>
+        <v>2.31</v>
       </c>
       <c r="CA8" t="n">
-        <v>3.86</v>
+        <v>3.85</v>
       </c>
       <c r="CB8" t="n">
-        <v>3.93</v>
+        <v>3.92</v>
       </c>
       <c r="CC8" t="n">
         <v>4.24</v>
@@ -4043,31 +4043,31 @@
         <v>1.26</v>
       </c>
       <c r="CF8" t="n">
-        <v>2.26</v>
+        <v>2.27</v>
       </c>
       <c r="CG8" t="n">
-        <v>3.5</v>
+        <v>3.49</v>
       </c>
       <c r="CH8" t="n">
         <v>1.6</v>
       </c>
       <c r="CI8" t="n">
-        <v>2.39</v>
+        <v>2.4</v>
       </c>
       <c r="CJ8" t="n">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="CK8" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="CL8" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="CM8" t="n">
-        <v>2.86</v>
+        <v>2.88</v>
       </c>
       <c r="CN8" t="n">
-        <v>2.21</v>
+        <v>2.23</v>
       </c>
       <c r="CO8" t="n">
         <v>1.15</v>
@@ -4091,7 +4091,7 @@
         <v>1.64</v>
       </c>
       <c r="CV8" t="n">
-        <v>2.56</v>
+        <v>2.57</v>
       </c>
       <c r="CW8" t="n">
         <v>1.55</v>
@@ -4118,79 +4118,79 @@
         <v>2.49</v>
       </c>
       <c r="DE8" t="n">
-        <v>0.2</v>
+        <v>0.19</v>
       </c>
       <c r="DF8" t="n">
-        <v>1.3</v>
+        <v>1.24</v>
       </c>
       <c r="DG8" t="n">
-        <v>2.5</v>
+        <v>2.62</v>
       </c>
       <c r="DH8" t="n">
-        <v>93.25</v>
+        <v>94.67</v>
       </c>
       <c r="DI8" t="n">
         <v>0</v>
       </c>
       <c r="DJ8" t="n">
-        <v>1.6</v>
+        <v>1.52</v>
       </c>
       <c r="DK8" t="n">
-        <v>5.3</v>
+        <v>5.38</v>
       </c>
       <c r="DL8" t="n">
-        <v>0.35</v>
+        <v>0.33</v>
       </c>
       <c r="DM8" t="n">
-        <v>50.55</v>
+        <v>51.24</v>
       </c>
       <c r="DN8" t="n">
-        <v>0.25</v>
+        <v>0.24</v>
       </c>
       <c r="DO8" t="n">
-        <v>2.8</v>
+        <v>2.76</v>
       </c>
       <c r="DP8" t="n">
+        <v>12</v>
+      </c>
+      <c r="DQ8" t="n">
         <v>12.05</v>
       </c>
-      <c r="DQ8" t="n">
-        <v>12.1</v>
-      </c>
       <c r="DR8" t="n">
-        <v>8.35</v>
+        <v>8.19</v>
       </c>
       <c r="DS8" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="DT8" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="DU8" t="n">
         <v>0</v>
       </c>
       <c r="DV8" t="n">
-        <v>49.35</v>
+        <v>50.29</v>
       </c>
       <c r="DW8" t="n">
         <v>0.05</v>
       </c>
       <c r="DX8" t="n">
-        <v>15.55</v>
+        <v>15.62</v>
       </c>
       <c r="DY8" t="n">
-        <v>10.8</v>
+        <v>10.81</v>
       </c>
       <c r="DZ8" t="n">
-        <v>4.75</v>
+        <v>4.81</v>
       </c>
       <c r="EA8" t="n">
-        <v>21.45</v>
+        <v>21.62</v>
       </c>
       <c r="EB8" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="EC8" t="n">
-        <v>1.5</v>
+        <v>1.43</v>
       </c>
     </row>
     <row r="9">
@@ -4200,13 +4200,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C9" t="n">
         <v>10</v>
       </c>
       <c r="D9" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E9" t="n">
         <v>0.3</v>
@@ -4293,49 +4293,49 @@
         <v>0</v>
       </c>
       <c r="AG9" t="n">
-        <v>2</v>
+        <v>2.09</v>
       </c>
       <c r="AH9" t="n">
-        <v>2.6</v>
+        <v>2.55</v>
       </c>
       <c r="AI9" t="n">
-        <v>77.8</v>
+        <v>79.91</v>
       </c>
       <c r="AJ9" t="n">
         <v>0</v>
       </c>
       <c r="AK9" t="n">
-        <v>3.1</v>
+        <v>3.27</v>
       </c>
       <c r="AL9" t="n">
-        <v>4.4</v>
+        <v>4.27</v>
       </c>
       <c r="AM9" t="n">
-        <v>0.4</v>
+        <v>0.45</v>
       </c>
       <c r="AN9" t="n">
-        <v>43.2</v>
+        <v>43.09</v>
       </c>
       <c r="AO9" t="n">
-        <v>1.1</v>
+        <v>1.18</v>
       </c>
       <c r="AP9" t="n">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="AQ9" t="n">
-        <v>16.6</v>
+        <v>16.73</v>
       </c>
       <c r="AR9" t="n">
-        <v>10.5</v>
+        <v>10.45</v>
       </c>
       <c r="AS9" t="n">
-        <v>8.5</v>
+        <v>8.91</v>
       </c>
       <c r="AT9" t="n">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="AU9" t="n">
-        <v>0.7</v>
+        <v>0.64</v>
       </c>
       <c r="AV9" t="n">
         <v>0</v>
@@ -4347,82 +4347,82 @@
         <v>0</v>
       </c>
       <c r="AY9" t="n">
-        <v>45.1</v>
+        <v>45.64</v>
       </c>
       <c r="AZ9" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="BA9" t="n">
-        <v>11.7</v>
+        <v>12.45</v>
       </c>
       <c r="BB9" t="n">
-        <v>7.6</v>
+        <v>8.449999999999999</v>
       </c>
       <c r="BC9" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="BD9" t="n">
-        <v>19.5</v>
+        <v>19.55</v>
       </c>
       <c r="BE9" t="n">
-        <v>1.34</v>
+        <v>1.38</v>
       </c>
       <c r="BF9" t="n">
-        <v>3</v>
+        <v>3.18</v>
       </c>
       <c r="BG9" t="n">
-        <v>2.4</v>
+        <v>2.33</v>
       </c>
       <c r="BH9" t="n">
-        <v>10.3</v>
+        <v>10.05</v>
       </c>
       <c r="BI9" t="n">
-        <v>2.4</v>
+        <v>2.33</v>
       </c>
       <c r="BJ9" t="n">
-        <v>0.7</v>
+        <v>0.71</v>
       </c>
       <c r="BK9" t="n">
-        <v>0.45</v>
+        <v>0.43</v>
       </c>
       <c r="BL9" t="n">
-        <v>0.7</v>
+        <v>0.67</v>
       </c>
       <c r="BM9" t="n">
-        <v>0.55</v>
+        <v>0.52</v>
       </c>
       <c r="BN9" t="n">
-        <v>1.25</v>
+        <v>1.19</v>
       </c>
       <c r="BO9" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="BP9" t="n">
-        <v>5</v>
+        <v>4.86</v>
       </c>
       <c r="BQ9" t="n">
-        <v>5.25</v>
+        <v>5.14</v>
       </c>
       <c r="BR9" t="n">
-        <v>95</v>
+        <v>95.23999999999999</v>
       </c>
       <c r="BS9" t="n">
-        <v>75</v>
+        <v>71.43000000000001</v>
       </c>
       <c r="BT9" t="n">
-        <v>45</v>
+        <v>42.86</v>
       </c>
       <c r="BU9" t="n">
-        <v>20</v>
+        <v>19.05</v>
       </c>
       <c r="BV9" t="n">
-        <v>5</v>
+        <v>4.76</v>
       </c>
       <c r="BW9" t="n">
         <v>0</v>
       </c>
       <c r="BX9" t="n">
-        <v>50</v>
+        <v>47.62</v>
       </c>
       <c r="BY9" t="n">
         <v>2.94</v>
@@ -4434,37 +4434,37 @@
         <v>3.5</v>
       </c>
       <c r="CB9" t="n">
-        <v>3.53</v>
+        <v>3.54</v>
       </c>
       <c r="CC9" t="n">
-        <v>4.12</v>
+        <v>4.18</v>
       </c>
       <c r="CD9" t="n">
-        <v>4.39</v>
+        <v>4.43</v>
       </c>
       <c r="CE9" t="n">
         <v>1.37</v>
       </c>
       <c r="CF9" t="n">
-        <v>2.72</v>
+        <v>2.73</v>
       </c>
       <c r="CG9" t="n">
-        <v>3</v>
+        <v>2.99</v>
       </c>
       <c r="CH9" t="n">
         <v>1.42</v>
       </c>
       <c r="CI9" t="n">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="CJ9" t="n">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="CK9" t="n">
         <v>1.44</v>
       </c>
       <c r="CL9" t="n">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="CM9" t="n">
         <v>2.56</v>
@@ -4482,13 +4482,13 @@
         <v>3.27</v>
       </c>
       <c r="CR9" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="CS9" t="n">
-        <v>2.84</v>
+        <v>2.83</v>
       </c>
       <c r="CT9" t="n">
-        <v>3.08</v>
+        <v>3.09</v>
       </c>
       <c r="CU9" t="n">
         <v>1.45</v>
@@ -4500,13 +4500,13 @@
         <v>1.81</v>
       </c>
       <c r="CX9" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="CY9" t="n">
         <v>1.8</v>
       </c>
       <c r="CZ9" t="n">
-        <v>2.47</v>
+        <v>2.49</v>
       </c>
       <c r="DA9" t="n">
         <v>2.02</v>
@@ -4515,52 +4515,52 @@
         <v>1.31</v>
       </c>
       <c r="DC9" t="n">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="DD9" t="n">
-        <v>3.39</v>
+        <v>3.37</v>
       </c>
       <c r="DE9" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="DF9" t="n">
-        <v>2.2</v>
+        <v>2.24</v>
       </c>
       <c r="DG9" t="n">
-        <v>2.5</v>
+        <v>2.48</v>
       </c>
       <c r="DH9" t="n">
-        <v>78.8</v>
+        <v>79.86</v>
       </c>
       <c r="DI9" t="n">
         <v>0</v>
       </c>
       <c r="DJ9" t="n">
-        <v>3.1</v>
+        <v>3.19</v>
       </c>
       <c r="DK9" t="n">
-        <v>4.4</v>
+        <v>4.33</v>
       </c>
       <c r="DL9" t="n">
-        <v>0.45</v>
+        <v>0.47</v>
       </c>
       <c r="DM9" t="n">
-        <v>41.25</v>
+        <v>41.29</v>
       </c>
       <c r="DN9" t="n">
-        <v>0.9</v>
+        <v>0.95</v>
       </c>
       <c r="DO9" t="n">
-        <v>1.85</v>
+        <v>1.81</v>
       </c>
       <c r="DP9" t="n">
-        <v>16.6</v>
+        <v>16.67</v>
       </c>
       <c r="DQ9" t="n">
-        <v>11.4</v>
+        <v>11.33</v>
       </c>
       <c r="DR9" t="n">
-        <v>8.4</v>
+        <v>8.619999999999999</v>
       </c>
       <c r="DS9" t="n">
         <v>0</v>
@@ -4572,28 +4572,28 @@
         <v>0</v>
       </c>
       <c r="DV9" t="n">
-        <v>45.45</v>
+        <v>45.72</v>
       </c>
       <c r="DW9" t="n">
         <v>0.05</v>
       </c>
       <c r="DX9" t="n">
-        <v>13</v>
+        <v>13.33</v>
       </c>
       <c r="DY9" t="n">
-        <v>8.65</v>
+        <v>9.050000000000001</v>
       </c>
       <c r="DZ9" t="n">
-        <v>4.35</v>
+        <v>4.29</v>
       </c>
       <c r="EA9" t="n">
-        <v>19.15</v>
+        <v>19.19</v>
       </c>
       <c r="EB9" t="n">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="EC9" t="n">
-        <v>3.05</v>
+        <v>3.14</v>
       </c>
     </row>
     <row r="10">
@@ -5006,13 +5006,13 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C11" t="n">
         <v>11</v>
       </c>
       <c r="D11" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E11" t="n">
         <v>0.09</v>
@@ -5096,139 +5096,139 @@
         <v>2.55</v>
       </c>
       <c r="AF11" t="n">
-        <v>0.11</v>
+        <v>0.2</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="AH11" t="n">
-        <v>2.89</v>
+        <v>3.1</v>
       </c>
       <c r="AI11" t="n">
-        <v>94.89</v>
+        <v>94.7</v>
       </c>
       <c r="AJ11" t="n">
         <v>0</v>
       </c>
       <c r="AK11" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AL11" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AM11" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>54.3</v>
+      </c>
+      <c r="AO11" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AP11" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AQ11" t="n">
+        <v>14.1</v>
+      </c>
+      <c r="AR11" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AS11" t="n">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="AT11" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AU11" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AV11" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="AW11" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="AX11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY11" t="n">
+        <v>55.1</v>
+      </c>
+      <c r="AZ11" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="BA11" t="n">
+        <v>12.6</v>
+      </c>
+      <c r="BB11" t="n">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="BC11" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="BD11" t="n">
+        <v>23.2</v>
+      </c>
+      <c r="BE11" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="BF11" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="BG11" t="n">
         <v>2.67</v>
       </c>
-      <c r="AL11" t="n">
-        <v>6.22</v>
-      </c>
-      <c r="AM11" t="n">
-        <v>0.33</v>
-      </c>
-      <c r="AN11" t="n">
-        <v>55.44</v>
-      </c>
-      <c r="AO11" t="n">
-        <v>1</v>
-      </c>
-      <c r="AP11" t="n">
-        <v>3.33</v>
-      </c>
-      <c r="AQ11" t="n">
-        <v>13.67</v>
-      </c>
-      <c r="AR11" t="n">
-        <v>9.56</v>
-      </c>
-      <c r="AS11" t="n">
-        <v>8</v>
-      </c>
-      <c r="AT11" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AU11" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AV11" t="n">
-        <v>0.22</v>
-      </c>
-      <c r="AW11" t="n">
-        <v>0.22</v>
-      </c>
-      <c r="AX11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY11" t="n">
-        <v>55.89</v>
-      </c>
-      <c r="AZ11" t="n">
-        <v>0.22</v>
-      </c>
-      <c r="BA11" t="n">
-        <v>12.89</v>
-      </c>
-      <c r="BB11" t="n">
-        <v>9</v>
-      </c>
-      <c r="BC11" t="n">
-        <v>3.89</v>
-      </c>
-      <c r="BD11" t="n">
-        <v>24.11</v>
-      </c>
-      <c r="BE11" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="BF11" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="BG11" t="n">
-        <v>2.5</v>
-      </c>
       <c r="BH11" t="n">
-        <v>10.25</v>
+        <v>10.57</v>
       </c>
       <c r="BI11" t="n">
-        <v>2.5</v>
+        <v>2.67</v>
       </c>
       <c r="BJ11" t="n">
-        <v>0.7</v>
+        <v>0.71</v>
       </c>
       <c r="BK11" t="n">
-        <v>0.35</v>
+        <v>0.43</v>
       </c>
       <c r="BL11" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="BM11" t="n">
-        <v>0.65</v>
+        <v>0.62</v>
       </c>
       <c r="BN11" t="n">
-        <v>1.45</v>
+        <v>1.52</v>
       </c>
       <c r="BO11" t="n">
-        <v>1.05</v>
+        <v>1.14</v>
       </c>
       <c r="BP11" t="n">
-        <v>4.95</v>
+        <v>5.05</v>
       </c>
       <c r="BQ11" t="n">
-        <v>5.3</v>
+        <v>5.52</v>
       </c>
       <c r="BR11" t="n">
-        <v>95</v>
+        <v>95.23999999999999</v>
       </c>
       <c r="BS11" t="n">
-        <v>65</v>
+        <v>66.67</v>
       </c>
       <c r="BT11" t="n">
-        <v>40</v>
+        <v>42.86</v>
       </c>
       <c r="BU11" t="n">
-        <v>30</v>
+        <v>33.33</v>
       </c>
       <c r="BV11" t="n">
-        <v>10</v>
+        <v>14.29</v>
       </c>
       <c r="BW11" t="n">
-        <v>5</v>
+        <v>9.52</v>
       </c>
       <c r="BX11" t="n">
-        <v>45</v>
+        <v>47.62</v>
       </c>
       <c r="BY11" t="n">
         <v>1.96</v>
@@ -5237,31 +5237,31 @@
         <v>2.05</v>
       </c>
       <c r="CA11" t="n">
-        <v>3.62</v>
+        <v>3.61</v>
       </c>
       <c r="CB11" t="n">
-        <v>3.73</v>
+        <v>3.71</v>
       </c>
       <c r="CC11" t="n">
-        <v>2.46</v>
+        <v>2.45</v>
       </c>
       <c r="CD11" t="n">
-        <v>2.58</v>
+        <v>2.59</v>
       </c>
       <c r="CE11" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="CF11" t="n">
-        <v>2.55</v>
+        <v>2.56</v>
       </c>
       <c r="CG11" t="n">
-        <v>3.09</v>
+        <v>3.08</v>
       </c>
       <c r="CH11" t="n">
         <v>1.47</v>
       </c>
       <c r="CI11" t="n">
-        <v>2.14</v>
+        <v>2.13</v>
       </c>
       <c r="CJ11" t="n">
         <v>1.69</v>
@@ -5270,16 +5270,16 @@
         <v>1.47</v>
       </c>
       <c r="CL11" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="CM11" t="n">
-        <v>2.55</v>
+        <v>2.54</v>
       </c>
       <c r="CN11" t="n">
         <v>1.95</v>
       </c>
       <c r="CO11" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="CP11" t="n">
         <v>1.78</v>
@@ -5288,118 +5288,118 @@
         <v>2.92</v>
       </c>
       <c r="CR11" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="CS11" t="n">
-        <v>2.65</v>
+        <v>2.66</v>
       </c>
       <c r="CT11" t="n">
-        <v>3.23</v>
+        <v>3.22</v>
       </c>
       <c r="CU11" t="n">
         <v>1.5</v>
       </c>
       <c r="CV11" t="n">
-        <v>2.23</v>
+        <v>2.22</v>
       </c>
       <c r="CW11" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="CX11" t="n">
         <v>1.51</v>
       </c>
       <c r="CY11" t="n">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="CZ11" t="n">
-        <v>2.51</v>
+        <v>2.5</v>
       </c>
       <c r="DA11" t="n">
         <v>1.99</v>
       </c>
       <c r="DB11" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="DC11" t="n">
-        <v>1.82</v>
+        <v>1.84</v>
       </c>
       <c r="DD11" t="n">
-        <v>3</v>
+        <v>3.04</v>
       </c>
       <c r="DE11" t="n">
-        <v>0.1</v>
+        <v>0.14</v>
       </c>
       <c r="DF11" t="n">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="DG11" t="n">
-        <v>3.2</v>
+        <v>3.28</v>
       </c>
       <c r="DH11" t="n">
-        <v>101.95</v>
+        <v>101.53</v>
       </c>
       <c r="DI11" t="n">
         <v>0</v>
       </c>
       <c r="DJ11" t="n">
-        <v>2.7</v>
+        <v>2.72</v>
       </c>
       <c r="DK11" t="n">
-        <v>6.4</v>
+        <v>6.48</v>
       </c>
       <c r="DL11" t="n">
-        <v>0.55</v>
+        <v>0.57</v>
       </c>
       <c r="DM11" t="n">
-        <v>56.65</v>
+        <v>56.05</v>
       </c>
       <c r="DN11" t="n">
-        <v>1</v>
+        <v>1.05</v>
       </c>
       <c r="DO11" t="n">
-        <v>3.2</v>
+        <v>3.19</v>
       </c>
       <c r="DP11" t="n">
-        <v>13.2</v>
+        <v>13.43</v>
       </c>
       <c r="DQ11" t="n">
-        <v>10.7</v>
+        <v>10.76</v>
       </c>
       <c r="DR11" t="n">
-        <v>7.65</v>
+        <v>7.81</v>
       </c>
       <c r="DS11" t="n">
-        <v>0.2</v>
+        <v>0.19</v>
       </c>
       <c r="DT11" t="n">
-        <v>0.2</v>
+        <v>0.19</v>
       </c>
       <c r="DU11" t="n">
         <v>0</v>
       </c>
       <c r="DV11" t="n">
-        <v>53.3</v>
+        <v>53.05</v>
       </c>
       <c r="DW11" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="DX11" t="n">
-        <v>15.05</v>
+        <v>14.81</v>
       </c>
       <c r="DY11" t="n">
-        <v>10.2</v>
+        <v>10</v>
       </c>
       <c r="DZ11" t="n">
-        <v>4.85</v>
+        <v>4.81</v>
       </c>
       <c r="EA11" t="n">
-        <v>21.9</v>
+        <v>21.57</v>
       </c>
       <c r="EB11" t="n">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="EC11" t="n">
-        <v>2.5</v>
+        <v>2.53</v>
       </c>
     </row>
     <row r="12">
@@ -5409,13 +5409,13 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C12" t="n">
         <v>11</v>
       </c>
       <c r="D12" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E12" t="n">
         <v>0.09</v>
@@ -5502,49 +5502,49 @@
         <v>0</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.67</v>
+        <v>1.5</v>
       </c>
       <c r="AH12" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="AI12" t="n">
-        <v>84.11</v>
+        <v>87.40000000000001</v>
       </c>
       <c r="AJ12" t="n">
         <v>0</v>
       </c>
       <c r="AK12" t="n">
-        <v>2.33</v>
+        <v>2.1</v>
       </c>
       <c r="AL12" t="n">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="AM12" t="n">
-        <v>0.33</v>
+        <v>0.3</v>
       </c>
       <c r="AN12" t="n">
-        <v>31.11</v>
+        <v>33.8</v>
       </c>
       <c r="AO12" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.5</v>
       </c>
       <c r="AP12" t="n">
         <v>1</v>
       </c>
       <c r="AQ12" t="n">
-        <v>13.56</v>
+        <v>13.1</v>
       </c>
       <c r="AR12" t="n">
-        <v>12.22</v>
+        <v>12.4</v>
       </c>
       <c r="AS12" t="n">
-        <v>8.56</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="AT12" t="n">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="AU12" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.5</v>
       </c>
       <c r="AV12" t="n">
         <v>0</v>
@@ -5556,73 +5556,73 @@
         <v>0</v>
       </c>
       <c r="AY12" t="n">
-        <v>42.67</v>
+        <v>43.6</v>
       </c>
       <c r="AZ12" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="BA12" t="n">
-        <v>10</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="BB12" t="n">
-        <v>6.78</v>
+        <v>6.8</v>
       </c>
       <c r="BC12" t="n">
-        <v>3.22</v>
+        <v>2.9</v>
       </c>
       <c r="BD12" t="n">
-        <v>18.78</v>
+        <v>21</v>
       </c>
       <c r="BE12" t="n">
-        <v>1.09</v>
+        <v>1.07</v>
       </c>
       <c r="BF12" t="n">
-        <v>2.11</v>
+        <v>1.9</v>
       </c>
       <c r="BG12" t="n">
-        <v>2.25</v>
+        <v>2.19</v>
       </c>
       <c r="BH12" t="n">
-        <v>9.4</v>
+        <v>9.289999999999999</v>
       </c>
       <c r="BI12" t="n">
-        <v>2.25</v>
+        <v>2.19</v>
       </c>
       <c r="BJ12" t="n">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="BK12" t="n">
-        <v>0.4</v>
+        <v>0.38</v>
       </c>
       <c r="BL12" t="n">
-        <v>0.6</v>
+        <v>0.57</v>
       </c>
       <c r="BM12" t="n">
-        <v>0.5</v>
+        <v>0.48</v>
       </c>
       <c r="BN12" t="n">
-        <v>1.1</v>
+        <v>1.05</v>
       </c>
       <c r="BO12" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="BP12" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="BQ12" t="n">
-        <v>5.35</v>
+        <v>5.29</v>
       </c>
       <c r="BR12" t="n">
-        <v>95</v>
+        <v>95.23999999999999</v>
       </c>
       <c r="BS12" t="n">
-        <v>75</v>
+        <v>71.43000000000001</v>
       </c>
       <c r="BT12" t="n">
-        <v>40</v>
+        <v>38.1</v>
       </c>
       <c r="BU12" t="n">
-        <v>15</v>
+        <v>14.29</v>
       </c>
       <c r="BV12" t="n">
         <v>0</v>
@@ -5631,7 +5631,7 @@
         <v>0</v>
       </c>
       <c r="BX12" t="n">
-        <v>55</v>
+        <v>52.38</v>
       </c>
       <c r="BY12" t="n">
         <v>2.71</v>
@@ -5640,25 +5640,25 @@
         <v>2.93</v>
       </c>
       <c r="CA12" t="n">
-        <v>3.56</v>
+        <v>3.54</v>
       </c>
       <c r="CB12" t="n">
-        <v>3.69</v>
+        <v>3.67</v>
       </c>
       <c r="CC12" t="n">
-        <v>4.08</v>
+        <v>3.9</v>
       </c>
       <c r="CD12" t="n">
-        <v>4.61</v>
+        <v>4.39</v>
       </c>
       <c r="CE12" t="n">
         <v>1.34</v>
       </c>
       <c r="CF12" t="n">
-        <v>2.6</v>
+        <v>2.61</v>
       </c>
       <c r="CG12" t="n">
-        <v>3.05</v>
+        <v>3.03</v>
       </c>
       <c r="CH12" t="n">
         <v>1.45</v>
@@ -5670,25 +5670,25 @@
         <v>1.69</v>
       </c>
       <c r="CK12" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="CL12" t="n">
         <v>1.98</v>
       </c>
       <c r="CM12" t="n">
-        <v>2.45</v>
+        <v>2.43</v>
       </c>
       <c r="CN12" t="n">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="CO12" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="CP12" t="n">
         <v>1.83</v>
       </c>
       <c r="CQ12" t="n">
-        <v>3.03</v>
+        <v>3.05</v>
       </c>
       <c r="CR12" t="n">
         <v>1.37</v>
@@ -5703,106 +5703,106 @@
         <v>1.48</v>
       </c>
       <c r="CV12" t="n">
-        <v>2.16</v>
+        <v>2.15</v>
       </c>
       <c r="CW12" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="CX12" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="CY12" t="n">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="CZ12" t="n">
-        <v>2.36</v>
+        <v>2.35</v>
       </c>
       <c r="DA12" t="n">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="DB12" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="DC12" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="DD12" t="n">
-        <v>3.12</v>
+        <v>3.16</v>
       </c>
       <c r="DE12" t="n">
         <v>0.05</v>
       </c>
       <c r="DF12" t="n">
-        <v>1.45</v>
+        <v>1.38</v>
       </c>
       <c r="DG12" t="n">
-        <v>2.2</v>
+        <v>2.28</v>
       </c>
       <c r="DH12" t="n">
-        <v>91.05</v>
+        <v>92.29000000000001</v>
       </c>
       <c r="DI12" t="n">
         <v>0.05</v>
       </c>
       <c r="DJ12" t="n">
-        <v>2.25</v>
+        <v>2.14</v>
       </c>
       <c r="DK12" t="n">
-        <v>4</v>
+        <v>4.05</v>
       </c>
       <c r="DL12" t="n">
-        <v>0.5</v>
+        <v>0.48</v>
       </c>
       <c r="DM12" t="n">
-        <v>38.35</v>
+        <v>39.28</v>
       </c>
       <c r="DN12" t="n">
-        <v>0.7</v>
+        <v>0.67</v>
       </c>
       <c r="DO12" t="n">
-        <v>1.75</v>
+        <v>1.71</v>
       </c>
       <c r="DP12" t="n">
-        <v>12.7</v>
+        <v>12.52</v>
       </c>
       <c r="DQ12" t="n">
-        <v>12.1</v>
+        <v>12.19</v>
       </c>
       <c r="DR12" t="n">
-        <v>7.75</v>
+        <v>7.67</v>
       </c>
       <c r="DS12" t="n">
-        <v>0.2</v>
+        <v>0.19</v>
       </c>
       <c r="DT12" t="n">
-        <v>0.2</v>
+        <v>0.19</v>
       </c>
       <c r="DU12" t="n">
         <v>0</v>
       </c>
       <c r="DV12" t="n">
-        <v>46.65</v>
+        <v>46.91</v>
       </c>
       <c r="DW12" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="DX12" t="n">
-        <v>11.85</v>
+        <v>11.62</v>
       </c>
       <c r="DY12" t="n">
-        <v>7.45</v>
+        <v>7.43</v>
       </c>
       <c r="DZ12" t="n">
-        <v>4.4</v>
+        <v>4.19</v>
       </c>
       <c r="EA12" t="n">
-        <v>19.75</v>
+        <v>20.76</v>
       </c>
       <c r="EB12" t="n">
-        <v>1.34</v>
+        <v>1.32</v>
       </c>
       <c r="EC12" t="n">
-        <v>2.05</v>
+        <v>1.95</v>
       </c>
     </row>
     <row r="13">
@@ -5812,94 +5812,94 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C13" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D13" t="n">
         <v>10</v>
       </c>
       <c r="E13" t="n">
-        <v>0.2</v>
+        <v>0.27</v>
       </c>
       <c r="F13" t="n">
-        <v>1.5</v>
+        <v>1.64</v>
       </c>
       <c r="G13" t="n">
-        <v>3.6</v>
+        <v>3.36</v>
       </c>
       <c r="H13" t="n">
-        <v>104.9</v>
+        <v>102.45</v>
       </c>
       <c r="I13" t="n">
         <v>0</v>
       </c>
       <c r="J13" t="n">
-        <v>2</v>
+        <v>2.09</v>
       </c>
       <c r="K13" t="n">
-        <v>5.3</v>
+        <v>5</v>
       </c>
       <c r="L13" t="n">
-        <v>0.3</v>
+        <v>0.27</v>
       </c>
       <c r="M13" t="n">
-        <v>55.1</v>
+        <v>54.45</v>
       </c>
       <c r="N13" t="n">
-        <v>0.4</v>
+        <v>0.36</v>
       </c>
       <c r="O13" t="n">
-        <v>1.7</v>
+        <v>1.64</v>
       </c>
       <c r="P13" t="n">
-        <v>11.3</v>
+        <v>11.18</v>
       </c>
       <c r="Q13" t="n">
-        <v>10.8</v>
+        <v>11.45</v>
       </c>
       <c r="R13" t="n">
-        <v>6</v>
+        <v>6.36</v>
       </c>
       <c r="S13" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="T13" t="n">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="U13" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="V13" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="W13" t="n">
         <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>53.9</v>
+        <v>53.45</v>
       </c>
       <c r="Y13" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="Z13" t="n">
-        <v>15</v>
+        <v>15.55</v>
       </c>
       <c r="AA13" t="n">
-        <v>10.3</v>
+        <v>10.64</v>
       </c>
       <c r="AB13" t="n">
-        <v>4.7</v>
+        <v>4.91</v>
       </c>
       <c r="AC13" t="n">
-        <v>23.5</v>
+        <v>22.45</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.68</v>
+        <v>1.72</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.8</v>
+        <v>1.91</v>
       </c>
       <c r="AF13" t="n">
         <v>0</v>
@@ -5983,70 +5983,70 @@
         <v>1.9</v>
       </c>
       <c r="BG13" t="n">
-        <v>2.65</v>
+        <v>2.57</v>
       </c>
       <c r="BH13" t="n">
-        <v>9.800000000000001</v>
+        <v>9.57</v>
       </c>
       <c r="BI13" t="n">
-        <v>2.65</v>
+        <v>2.57</v>
       </c>
       <c r="BJ13" t="n">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="BK13" t="n">
-        <v>0.45</v>
+        <v>0.43</v>
       </c>
       <c r="BL13" t="n">
-        <v>0.65</v>
+        <v>0.62</v>
       </c>
       <c r="BM13" t="n">
-        <v>0.8</v>
+        <v>0.76</v>
       </c>
       <c r="BN13" t="n">
-        <v>1.45</v>
+        <v>1.38</v>
       </c>
       <c r="BO13" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="BP13" t="n">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="BQ13" t="n">
-        <v>5.8</v>
+        <v>5.67</v>
       </c>
       <c r="BR13" t="n">
         <v>100</v>
       </c>
       <c r="BS13" t="n">
-        <v>85</v>
+        <v>80.95</v>
       </c>
       <c r="BT13" t="n">
-        <v>55</v>
+        <v>52.38</v>
       </c>
       <c r="BU13" t="n">
-        <v>20</v>
+        <v>19.05</v>
       </c>
       <c r="BV13" t="n">
-        <v>5</v>
+        <v>4.76</v>
       </c>
       <c r="BW13" t="n">
         <v>0</v>
       </c>
       <c r="BX13" t="n">
-        <v>60</v>
+        <v>57.14</v>
       </c>
       <c r="BY13" t="n">
-        <v>2.32</v>
+        <v>2.27</v>
       </c>
       <c r="BZ13" t="n">
-        <v>2.41</v>
+        <v>2.36</v>
       </c>
       <c r="CA13" t="n">
-        <v>3.7</v>
+        <v>3.69</v>
       </c>
       <c r="CB13" t="n">
-        <v>3.81</v>
+        <v>3.8</v>
       </c>
       <c r="CC13" t="n">
         <v>3.99</v>
@@ -6058,19 +6058,19 @@
         <v>1.31</v>
       </c>
       <c r="CF13" t="n">
-        <v>2.45</v>
+        <v>2.47</v>
       </c>
       <c r="CG13" t="n">
-        <v>3.17</v>
+        <v>3.15</v>
       </c>
       <c r="CH13" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="CI13" t="n">
-        <v>2.19</v>
+        <v>2.17</v>
       </c>
       <c r="CJ13" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="CK13" t="n">
         <v>1.45</v>
@@ -6088,10 +6088,10 @@
         <v>1.22</v>
       </c>
       <c r="CP13" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="CQ13" t="n">
-        <v>2.79</v>
+        <v>2.81</v>
       </c>
       <c r="CR13" t="n">
         <v>1.35</v>
@@ -6100,25 +6100,25 @@
         <v>2.62</v>
       </c>
       <c r="CT13" t="n">
-        <v>3.24</v>
+        <v>3.25</v>
       </c>
       <c r="CU13" t="n">
         <v>1.51</v>
       </c>
       <c r="CV13" t="n">
-        <v>2.31</v>
+        <v>2.3</v>
       </c>
       <c r="CW13" t="n">
         <v>1.66</v>
       </c>
       <c r="CX13" t="n">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="CY13" t="n">
         <v>1.83</v>
       </c>
       <c r="CZ13" t="n">
-        <v>2.45</v>
+        <v>2.46</v>
       </c>
       <c r="DA13" t="n">
         <v>1.99</v>
@@ -6127,85 +6127,85 @@
         <v>1.24</v>
       </c>
       <c r="DC13" t="n">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="DD13" t="n">
-        <v>2.86</v>
+        <v>2.87</v>
       </c>
       <c r="DE13" t="n">
-        <v>0.1</v>
+        <v>0.14</v>
       </c>
       <c r="DF13" t="n">
-        <v>1.35</v>
+        <v>1.43</v>
       </c>
       <c r="DG13" t="n">
-        <v>3.45</v>
+        <v>3.33</v>
       </c>
       <c r="DH13" t="n">
-        <v>102.25</v>
+        <v>101.09</v>
       </c>
       <c r="DI13" t="n">
         <v>0.1</v>
       </c>
       <c r="DJ13" t="n">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="DK13" t="n">
-        <v>5.4</v>
+        <v>5.24</v>
       </c>
       <c r="DL13" t="n">
-        <v>0.35</v>
+        <v>0.33</v>
       </c>
       <c r="DM13" t="n">
-        <v>53.9</v>
+        <v>53.62</v>
       </c>
       <c r="DN13" t="n">
-        <v>0.55</v>
+        <v>0.52</v>
       </c>
       <c r="DO13" t="n">
-        <v>1.95</v>
+        <v>1.91</v>
       </c>
       <c r="DP13" t="n">
-        <v>11.9</v>
+        <v>11.81</v>
       </c>
       <c r="DQ13" t="n">
-        <v>10.8</v>
+        <v>11.14</v>
       </c>
       <c r="DR13" t="n">
-        <v>7.3</v>
+        <v>7.43</v>
       </c>
       <c r="DS13" t="n">
-        <v>0.3</v>
+        <v>0.28</v>
       </c>
       <c r="DT13" t="n">
-        <v>0.3</v>
+        <v>0.28</v>
       </c>
       <c r="DU13" t="n">
         <v>0</v>
       </c>
       <c r="DV13" t="n">
-        <v>53.55</v>
+        <v>53.33</v>
       </c>
       <c r="DW13" t="n">
         <v>0.05</v>
       </c>
       <c r="DX13" t="n">
-        <v>14.1</v>
+        <v>14.43</v>
       </c>
       <c r="DY13" t="n">
-        <v>9.75</v>
+        <v>9.949999999999999</v>
       </c>
       <c r="DZ13" t="n">
-        <v>4.35</v>
+        <v>4.48</v>
       </c>
       <c r="EA13" t="n">
-        <v>22.9</v>
+        <v>22.38</v>
       </c>
       <c r="EB13" t="n">
-        <v>1.59</v>
+        <v>1.62</v>
       </c>
       <c r="EC13" t="n">
-        <v>1.85</v>
+        <v>1.91</v>
       </c>
     </row>
     <row r="14">
@@ -6215,94 +6215,94 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C14" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D14" t="n">
         <v>10</v>
       </c>
       <c r="E14" t="n">
-        <v>0.1</v>
+        <v>0.18</v>
       </c>
       <c r="F14" t="n">
-        <v>1.6</v>
+        <v>1.64</v>
       </c>
       <c r="G14" t="n">
-        <v>2.3</v>
+        <v>2.45</v>
       </c>
       <c r="H14" t="n">
-        <v>89.7</v>
+        <v>90.27</v>
       </c>
       <c r="I14" t="n">
         <v>0</v>
       </c>
       <c r="J14" t="n">
-        <v>2.1</v>
+        <v>2.09</v>
       </c>
       <c r="K14" t="n">
-        <v>5.1</v>
+        <v>5.27</v>
       </c>
       <c r="L14" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="M14" t="n">
-        <v>48.1</v>
+        <v>47.73</v>
       </c>
       <c r="N14" t="n">
-        <v>0.4</v>
+        <v>0.36</v>
       </c>
       <c r="O14" t="n">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="P14" t="n">
-        <v>11.5</v>
+        <v>11.73</v>
       </c>
       <c r="Q14" t="n">
-        <v>12.9</v>
+        <v>12.64</v>
       </c>
       <c r="R14" t="n">
-        <v>7.3</v>
+        <v>7.27</v>
       </c>
       <c r="S14" t="n">
-        <v>1</v>
+        <v>0.91</v>
       </c>
       <c r="T14" t="n">
-        <v>1.2</v>
+        <v>1.27</v>
       </c>
       <c r="U14" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="V14" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="W14" t="n">
         <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>47.2</v>
+        <v>46.64</v>
       </c>
       <c r="Y14" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="Z14" t="n">
-        <v>11.4</v>
+        <v>11.82</v>
       </c>
       <c r="AA14" t="n">
-        <v>6.9</v>
+        <v>7.27</v>
       </c>
       <c r="AB14" t="n">
-        <v>4.5</v>
+        <v>4.55</v>
       </c>
       <c r="AC14" t="n">
-        <v>17.6</v>
+        <v>17.82</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.39</v>
+        <v>1.41</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.8</v>
+        <v>1.82</v>
       </c>
       <c r="AF14" t="n">
         <v>0.1</v>
@@ -6386,70 +6386,70 @@
         <v>2.3</v>
       </c>
       <c r="BG14" t="n">
-        <v>2.45</v>
+        <v>2.43</v>
       </c>
       <c r="BH14" t="n">
-        <v>9.550000000000001</v>
+        <v>9.859999999999999</v>
       </c>
       <c r="BI14" t="n">
-        <v>2.45</v>
+        <v>2.43</v>
       </c>
       <c r="BJ14" t="n">
-        <v>0.65</v>
+        <v>0.71</v>
       </c>
       <c r="BK14" t="n">
-        <v>0.7</v>
+        <v>0.67</v>
       </c>
       <c r="BL14" t="n">
-        <v>0.75</v>
+        <v>0.71</v>
       </c>
       <c r="BM14" t="n">
-        <v>0.35</v>
+        <v>0.33</v>
       </c>
       <c r="BN14" t="n">
-        <v>1.1</v>
+        <v>1.05</v>
       </c>
       <c r="BO14" t="n">
-        <v>1.35</v>
+        <v>1.38</v>
       </c>
       <c r="BP14" t="n">
-        <v>4.95</v>
+        <v>5.05</v>
       </c>
       <c r="BQ14" t="n">
-        <v>4.6</v>
+        <v>4.81</v>
       </c>
       <c r="BR14" t="n">
-        <v>95</v>
+        <v>95.23999999999999</v>
       </c>
       <c r="BS14" t="n">
-        <v>70</v>
+        <v>71.43000000000001</v>
       </c>
       <c r="BT14" t="n">
-        <v>45</v>
+        <v>42.86</v>
       </c>
       <c r="BU14" t="n">
-        <v>30</v>
+        <v>28.57</v>
       </c>
       <c r="BV14" t="n">
-        <v>5</v>
+        <v>4.76</v>
       </c>
       <c r="BW14" t="n">
         <v>0</v>
       </c>
       <c r="BX14" t="n">
-        <v>60</v>
+        <v>57.14</v>
       </c>
       <c r="BY14" t="n">
-        <v>2.33</v>
+        <v>2.31</v>
       </c>
       <c r="BZ14" t="n">
-        <v>2.44</v>
+        <v>2.4</v>
       </c>
       <c r="CA14" t="n">
+        <v>3.51</v>
+      </c>
+      <c r="CB14" t="n">
         <v>3.53</v>
-      </c>
-      <c r="CB14" t="n">
-        <v>3.54</v>
       </c>
       <c r="CC14" t="n">
         <v>3.9</v>
@@ -6461,19 +6461,19 @@
         <v>1.35</v>
       </c>
       <c r="CF14" t="n">
-        <v>2.68</v>
+        <v>2.71</v>
       </c>
       <c r="CG14" t="n">
-        <v>3.03</v>
+        <v>3</v>
       </c>
       <c r="CH14" t="n">
         <v>1.43</v>
       </c>
       <c r="CI14" t="n">
-        <v>2.05</v>
+        <v>2.03</v>
       </c>
       <c r="CJ14" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="CK14" t="n">
         <v>1.47</v>
@@ -6482,37 +6482,37 @@
         <v>1.9</v>
       </c>
       <c r="CM14" t="n">
-        <v>2.54</v>
+        <v>2.53</v>
       </c>
       <c r="CN14" t="n">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="CO14" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="CP14" t="n">
-        <v>1.86</v>
+        <v>1.88</v>
       </c>
       <c r="CQ14" t="n">
-        <v>3.14</v>
+        <v>3.18</v>
       </c>
       <c r="CR14" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="CS14" t="n">
-        <v>2.84</v>
+        <v>2.86</v>
       </c>
       <c r="CT14" t="n">
-        <v>3.09</v>
+        <v>3.07</v>
       </c>
       <c r="CU14" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="CV14" t="n">
-        <v>2.13</v>
+        <v>2.12</v>
       </c>
       <c r="CW14" t="n">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="CX14" t="n">
         <v>1.54</v>
@@ -6530,52 +6530,52 @@
         <v>1.3</v>
       </c>
       <c r="DC14" t="n">
-        <v>1.97</v>
+        <v>1.99</v>
       </c>
       <c r="DD14" t="n">
-        <v>3.32</v>
+        <v>3.37</v>
       </c>
       <c r="DE14" t="n">
-        <v>0.1</v>
+        <v>0.14</v>
       </c>
       <c r="DF14" t="n">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="DG14" t="n">
-        <v>2.15</v>
+        <v>2.24</v>
       </c>
       <c r="DH14" t="n">
-        <v>89.84999999999999</v>
+        <v>90.14</v>
       </c>
       <c r="DI14" t="n">
         <v>0</v>
       </c>
       <c r="DJ14" t="n">
-        <v>2.2</v>
+        <v>2.19</v>
       </c>
       <c r="DK14" t="n">
-        <v>4.7</v>
+        <v>4.81</v>
       </c>
       <c r="DL14" t="n">
-        <v>0.35</v>
+        <v>0.33</v>
       </c>
       <c r="DM14" t="n">
-        <v>47.15</v>
+        <v>47</v>
       </c>
       <c r="DN14" t="n">
-        <v>0.45</v>
+        <v>0.43</v>
       </c>
       <c r="DO14" t="n">
-        <v>2.55</v>
+        <v>2.57</v>
       </c>
       <c r="DP14" t="n">
-        <v>11.4</v>
+        <v>11.53</v>
       </c>
       <c r="DQ14" t="n">
-        <v>11.3</v>
+        <v>11.24</v>
       </c>
       <c r="DR14" t="n">
-        <v>7.25</v>
+        <v>7.24</v>
       </c>
       <c r="DS14" t="n">
         <v>0.05</v>
@@ -6587,25 +6587,25 @@
         <v>0</v>
       </c>
       <c r="DV14" t="n">
-        <v>47</v>
+        <v>46.72</v>
       </c>
       <c r="DW14" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="DX14" t="n">
-        <v>11.15</v>
+        <v>11.38</v>
       </c>
       <c r="DY14" t="n">
-        <v>7</v>
+        <v>7.19</v>
       </c>
       <c r="DZ14" t="n">
-        <v>4.15</v>
+        <v>4.19</v>
       </c>
       <c r="EA14" t="n">
-        <v>19.45</v>
+        <v>19.48</v>
       </c>
       <c r="EB14" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="EC14" t="n">
         <v>2.05</v>
@@ -6618,13 +6618,13 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C15" t="n">
         <v>10</v>
       </c>
       <c r="D15" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E15" t="n">
         <v>0.2</v>
@@ -6708,130 +6708,130 @@
         <v>2.4</v>
       </c>
       <c r="AF15" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.4</v>
+        <v>1.73</v>
       </c>
       <c r="AI15" t="n">
-        <v>84.59999999999999</v>
+        <v>85.36</v>
       </c>
       <c r="AJ15" t="n">
         <v>0</v>
       </c>
       <c r="AK15" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AL15" t="n">
-        <v>2.9</v>
+        <v>3.45</v>
       </c>
       <c r="AM15" t="n">
-        <v>0.4</v>
+        <v>0.36</v>
       </c>
       <c r="AN15" t="n">
-        <v>33.7</v>
+        <v>36</v>
       </c>
       <c r="AO15" t="n">
-        <v>0.7</v>
+        <v>0.64</v>
       </c>
       <c r="AP15" t="n">
-        <v>1.5</v>
+        <v>1.73</v>
       </c>
       <c r="AQ15" t="n">
-        <v>11.3</v>
+        <v>11.18</v>
       </c>
       <c r="AR15" t="n">
-        <v>11.8</v>
+        <v>12</v>
       </c>
       <c r="AS15" t="n">
-        <v>10</v>
+        <v>10.09</v>
       </c>
       <c r="AT15" t="n">
-        <v>1.1</v>
+        <v>1.18</v>
       </c>
       <c r="AU15" t="n">
-        <v>0.8</v>
+        <v>0.73</v>
       </c>
       <c r="AV15" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="AW15" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="AX15" t="n">
         <v>0</v>
       </c>
       <c r="AY15" t="n">
-        <v>43.7</v>
+        <v>45.09</v>
       </c>
       <c r="AZ15" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="BA15" t="n">
-        <v>7.6</v>
+        <v>8.09</v>
       </c>
       <c r="BB15" t="n">
-        <v>5.3</v>
+        <v>5.64</v>
       </c>
       <c r="BC15" t="n">
-        <v>2.3</v>
+        <v>2.45</v>
       </c>
       <c r="BD15" t="n">
-        <v>18.3</v>
+        <v>18.09</v>
       </c>
       <c r="BE15" t="n">
-        <v>0.89</v>
+        <v>0.95</v>
       </c>
       <c r="BF15" t="n">
-        <v>1.9</v>
+        <v>1.82</v>
       </c>
       <c r="BG15" t="n">
         <v>2.05</v>
       </c>
       <c r="BH15" t="n">
-        <v>9.449999999999999</v>
+        <v>9.76</v>
       </c>
       <c r="BI15" t="n">
         <v>2.05</v>
       </c>
       <c r="BJ15" t="n">
-        <v>0.45</v>
+        <v>0.52</v>
       </c>
       <c r="BK15" t="n">
-        <v>0.65</v>
+        <v>0.62</v>
       </c>
       <c r="BL15" t="n">
-        <v>0.6</v>
+        <v>0.57</v>
       </c>
       <c r="BM15" t="n">
-        <v>0.35</v>
+        <v>0.33</v>
       </c>
       <c r="BN15" t="n">
-        <v>0.95</v>
+        <v>0.9</v>
       </c>
       <c r="BO15" t="n">
-        <v>1.1</v>
+        <v>1.14</v>
       </c>
       <c r="BP15" t="n">
-        <v>4.4</v>
+        <v>4.52</v>
       </c>
       <c r="BQ15" t="n">
-        <v>5.05</v>
+        <v>5.24</v>
       </c>
       <c r="BR15" t="n">
-        <v>95</v>
+        <v>95.23999999999999</v>
       </c>
       <c r="BS15" t="n">
-        <v>60</v>
+        <v>61.9</v>
       </c>
       <c r="BT15" t="n">
-        <v>40</v>
+        <v>38.1</v>
       </c>
       <c r="BU15" t="n">
-        <v>10</v>
+        <v>9.52</v>
       </c>
       <c r="BV15" t="n">
         <v>0</v>
@@ -6840,7 +6840,7 @@
         <v>0</v>
       </c>
       <c r="BX15" t="n">
-        <v>35</v>
+        <v>33.33</v>
       </c>
       <c r="BY15" t="n">
         <v>2.86</v>
@@ -6849,34 +6849,34 @@
         <v>3.09</v>
       </c>
       <c r="CA15" t="n">
-        <v>3.46</v>
+        <v>3.45</v>
       </c>
       <c r="CB15" t="n">
         <v>3.51</v>
       </c>
       <c r="CC15" t="n">
-        <v>4.03</v>
+        <v>4.01</v>
       </c>
       <c r="CD15" t="n">
-        <v>4.56</v>
+        <v>4.54</v>
       </c>
       <c r="CE15" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="CF15" t="n">
-        <v>2.81</v>
+        <v>2.83</v>
       </c>
       <c r="CG15" t="n">
-        <v>2.89</v>
+        <v>2.86</v>
       </c>
       <c r="CH15" t="n">
         <v>1.4</v>
       </c>
       <c r="CI15" t="n">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="CJ15" t="n">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="CK15" t="n">
         <v>1.5</v>
@@ -6885,7 +6885,7 @@
         <v>1.87</v>
       </c>
       <c r="CM15" t="n">
-        <v>2.53</v>
+        <v>2.52</v>
       </c>
       <c r="CN15" t="n">
         <v>1.92</v>
@@ -6894,124 +6894,124 @@
         <v>1.31</v>
       </c>
       <c r="CP15" t="n">
-        <v>1.95</v>
+        <v>1.97</v>
       </c>
       <c r="CQ15" t="n">
-        <v>3.43</v>
+        <v>3.47</v>
       </c>
       <c r="CR15" t="n">
         <v>1.4</v>
       </c>
       <c r="CS15" t="n">
-        <v>2.93</v>
+        <v>2.95</v>
       </c>
       <c r="CT15" t="n">
-        <v>3.02</v>
+        <v>3.01</v>
       </c>
       <c r="CU15" t="n">
         <v>1.43</v>
       </c>
       <c r="CV15" t="n">
-        <v>2.08</v>
+        <v>2.07</v>
       </c>
       <c r="CW15" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="CX15" t="n">
         <v>1.57</v>
       </c>
       <c r="CY15" t="n">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="CZ15" t="n">
         <v>2.38</v>
       </c>
       <c r="DA15" t="n">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="DB15" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="DC15" t="n">
-        <v>2.03</v>
+        <v>2.04</v>
       </c>
       <c r="DD15" t="n">
-        <v>3.48</v>
+        <v>3.52</v>
       </c>
       <c r="DE15" t="n">
-        <v>0.2</v>
+        <v>0.19</v>
       </c>
       <c r="DF15" t="n">
-        <v>1.55</v>
+        <v>1.52</v>
       </c>
       <c r="DG15" t="n">
-        <v>1.7</v>
+        <v>1.86</v>
       </c>
       <c r="DH15" t="n">
-        <v>84.8</v>
+        <v>85.19</v>
       </c>
       <c r="DI15" t="n">
         <v>0</v>
       </c>
       <c r="DJ15" t="n">
-        <v>2.65</v>
+        <v>2.57</v>
       </c>
       <c r="DK15" t="n">
-        <v>3.9</v>
+        <v>4.14</v>
       </c>
       <c r="DL15" t="n">
-        <v>0.45</v>
+        <v>0.43</v>
       </c>
       <c r="DM15" t="n">
-        <v>42.55</v>
+        <v>43.33</v>
       </c>
       <c r="DN15" t="n">
-        <v>0.9</v>
+        <v>0.86</v>
       </c>
       <c r="DO15" t="n">
-        <v>2.2</v>
+        <v>2.29</v>
       </c>
       <c r="DP15" t="n">
-        <v>11.2</v>
+        <v>11.14</v>
       </c>
       <c r="DQ15" t="n">
-        <v>12.1</v>
+        <v>12.19</v>
       </c>
       <c r="DR15" t="n">
-        <v>9.4</v>
+        <v>9.48</v>
       </c>
       <c r="DS15" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="DT15" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="DU15" t="n">
         <v>0</v>
       </c>
       <c r="DV15" t="n">
-        <v>43.85</v>
+        <v>44.57</v>
       </c>
       <c r="DW15" t="n">
-        <v>0.3</v>
+        <v>0.28</v>
       </c>
       <c r="DX15" t="n">
-        <v>9.5</v>
+        <v>9.67</v>
       </c>
       <c r="DY15" t="n">
-        <v>6.15</v>
+        <v>6.29</v>
       </c>
       <c r="DZ15" t="n">
-        <v>3.35</v>
+        <v>3.38</v>
       </c>
       <c r="EA15" t="n">
-        <v>19.5</v>
+        <v>19.33</v>
       </c>
       <c r="EB15" t="n">
-        <v>1.14</v>
+        <v>1.16</v>
       </c>
       <c r="EC15" t="n">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
     </row>
     <row r="16">
@@ -7021,94 +7021,94 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C16" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D16" t="n">
         <v>11</v>
       </c>
       <c r="E16" t="n">
-        <v>0.33</v>
+        <v>0.3</v>
       </c>
       <c r="F16" t="n">
-        <v>1.11</v>
+        <v>1.3</v>
       </c>
       <c r="G16" t="n">
-        <v>3.44</v>
+        <v>3.5</v>
       </c>
       <c r="H16" t="n">
-        <v>103.11</v>
+        <v>103.4</v>
       </c>
       <c r="I16" t="n">
         <v>0</v>
       </c>
       <c r="J16" t="n">
-        <v>1.22</v>
+        <v>1.5</v>
       </c>
       <c r="K16" t="n">
-        <v>6.22</v>
+        <v>6.3</v>
       </c>
       <c r="L16" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.5</v>
       </c>
       <c r="M16" t="n">
-        <v>56.67</v>
+        <v>56.1</v>
       </c>
       <c r="N16" t="n">
-        <v>0.11</v>
+        <v>0.2</v>
       </c>
       <c r="O16" t="n">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="P16" t="n">
-        <v>11.89</v>
+        <v>12.3</v>
       </c>
       <c r="Q16" t="n">
-        <v>9.44</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="R16" t="n">
-        <v>5.44</v>
+        <v>5.3</v>
       </c>
       <c r="S16" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="T16" t="n">
-        <v>2.44</v>
+        <v>2.3</v>
       </c>
       <c r="U16" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="V16" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="W16" t="n">
         <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>53.44</v>
+        <v>52.3</v>
       </c>
       <c r="Y16" t="n">
         <v>0</v>
       </c>
       <c r="Z16" t="n">
-        <v>17.11</v>
+        <v>16.9</v>
       </c>
       <c r="AA16" t="n">
-        <v>10.33</v>
+        <v>10.2</v>
       </c>
       <c r="AB16" t="n">
-        <v>6.78</v>
+        <v>6.7</v>
       </c>
       <c r="AC16" t="n">
-        <v>19.44</v>
+        <v>20.1</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.96</v>
+        <v>1.94</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.22</v>
+        <v>1.5</v>
       </c>
       <c r="AF16" t="n">
         <v>0.09</v>
@@ -7192,58 +7192,58 @@
         <v>2.91</v>
       </c>
       <c r="BG16" t="n">
-        <v>2.4</v>
+        <v>2.33</v>
       </c>
       <c r="BH16" t="n">
-        <v>9.449999999999999</v>
+        <v>9.33</v>
       </c>
       <c r="BI16" t="n">
-        <v>2.4</v>
+        <v>2.33</v>
       </c>
       <c r="BJ16" t="n">
-        <v>0.5</v>
+        <v>0.52</v>
       </c>
       <c r="BK16" t="n">
-        <v>0.4</v>
+        <v>0.38</v>
       </c>
       <c r="BL16" t="n">
-        <v>1.1</v>
+        <v>1.05</v>
       </c>
       <c r="BM16" t="n">
-        <v>0.4</v>
+        <v>0.38</v>
       </c>
       <c r="BN16" t="n">
-        <v>1.5</v>
+        <v>1.43</v>
       </c>
       <c r="BO16" t="n">
         <v>0.9</v>
       </c>
       <c r="BP16" t="n">
-        <v>4.7</v>
+        <v>4.62</v>
       </c>
       <c r="BQ16" t="n">
-        <v>4.75</v>
+        <v>4.71</v>
       </c>
       <c r="BR16" t="n">
-        <v>95</v>
+        <v>95.23999999999999</v>
       </c>
       <c r="BS16" t="n">
-        <v>80</v>
+        <v>76.19</v>
       </c>
       <c r="BT16" t="n">
-        <v>30</v>
+        <v>28.57</v>
       </c>
       <c r="BU16" t="n">
-        <v>20</v>
+        <v>19.05</v>
       </c>
       <c r="BV16" t="n">
-        <v>15</v>
+        <v>14.29</v>
       </c>
       <c r="BW16" t="n">
         <v>0</v>
       </c>
       <c r="BX16" t="n">
-        <v>45</v>
+        <v>42.86</v>
       </c>
       <c r="BY16" t="n">
         <v>1.35</v>
@@ -7252,10 +7252,10 @@
         <v>1.42</v>
       </c>
       <c r="CA16" t="n">
-        <v>4.22</v>
+        <v>4.24</v>
       </c>
       <c r="CB16" t="n">
-        <v>4.4</v>
+        <v>4.44</v>
       </c>
       <c r="CC16" t="n">
         <v>1.89</v>
@@ -7264,19 +7264,19 @@
         <v>1.93</v>
       </c>
       <c r="CE16" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="CF16" t="n">
-        <v>2.49</v>
+        <v>2.5</v>
       </c>
       <c r="CG16" t="n">
-        <v>3.19</v>
+        <v>3.2</v>
       </c>
       <c r="CH16" t="n">
         <v>1.5</v>
       </c>
       <c r="CI16" t="n">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="CJ16" t="n">
         <v>1.82</v>
@@ -7297,10 +7297,10 @@
         <v>1.22</v>
       </c>
       <c r="CP16" t="n">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="CQ16" t="n">
-        <v>2.79</v>
+        <v>2.77</v>
       </c>
       <c r="CR16" t="n">
         <v>1.36</v>
@@ -7315,19 +7315,19 @@
         <v>1.51</v>
       </c>
       <c r="CV16" t="n">
-        <v>2.03</v>
+        <v>2.02</v>
       </c>
       <c r="CW16" t="n">
-        <v>1.86</v>
+        <v>1.88</v>
       </c>
       <c r="CX16" t="n">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="CY16" t="n">
         <v>1.87</v>
       </c>
       <c r="CZ16" t="n">
-        <v>2.37</v>
+        <v>2.39</v>
       </c>
       <c r="DA16" t="n">
         <v>1.95</v>
@@ -7342,46 +7342,46 @@
         <v>2.94</v>
       </c>
       <c r="DE16" t="n">
-        <v>0.2</v>
+        <v>0.19</v>
       </c>
       <c r="DF16" t="n">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="DG16" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="DH16" t="n">
-        <v>108.1</v>
+        <v>108</v>
       </c>
       <c r="DI16" t="n">
         <v>0.05</v>
       </c>
       <c r="DJ16" t="n">
-        <v>2.2</v>
+        <v>2.29</v>
       </c>
       <c r="DK16" t="n">
-        <v>5.65</v>
+        <v>5.71</v>
       </c>
       <c r="DL16" t="n">
-        <v>0.55</v>
+        <v>0.53</v>
       </c>
       <c r="DM16" t="n">
-        <v>53.9</v>
+        <v>53.76</v>
       </c>
       <c r="DN16" t="n">
-        <v>0.7</v>
+        <v>0.71</v>
       </c>
       <c r="DO16" t="n">
-        <v>2.65</v>
+        <v>2.67</v>
       </c>
       <c r="DP16" t="n">
-        <v>12.7</v>
+        <v>12.86</v>
       </c>
       <c r="DQ16" t="n">
-        <v>9.1</v>
+        <v>9.289999999999999</v>
       </c>
       <c r="DR16" t="n">
-        <v>5.8</v>
+        <v>5.71</v>
       </c>
       <c r="DS16" t="n">
         <v>0.1</v>
@@ -7393,28 +7393,28 @@
         <v>0</v>
       </c>
       <c r="DV16" t="n">
-        <v>54.25</v>
+        <v>53.67</v>
       </c>
       <c r="DW16" t="n">
         <v>0.05</v>
       </c>
       <c r="DX16" t="n">
-        <v>15.55</v>
+        <v>15.52</v>
       </c>
       <c r="DY16" t="n">
-        <v>9.75</v>
+        <v>9.710000000000001</v>
       </c>
       <c r="DZ16" t="n">
-        <v>5.8</v>
+        <v>5.81</v>
       </c>
       <c r="EA16" t="n">
-        <v>19.95</v>
+        <v>20.24</v>
       </c>
       <c r="EB16" t="n">
         <v>1.78</v>
       </c>
       <c r="EC16" t="n">
-        <v>2.15</v>
+        <v>2.24</v>
       </c>
     </row>
     <row r="17">
@@ -7424,10 +7424,10 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C17" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D17" t="n">
         <v>11</v>
@@ -7436,82 +7436,82 @@
         <v>0</v>
       </c>
       <c r="F17" t="n">
-        <v>0.89</v>
+        <v>1</v>
       </c>
       <c r="G17" t="n">
-        <v>2.11</v>
+        <v>2</v>
       </c>
       <c r="H17" t="n">
-        <v>97.67</v>
+        <v>94.59999999999999</v>
       </c>
       <c r="I17" t="n">
         <v>0</v>
       </c>
       <c r="J17" t="n">
-        <v>1.56</v>
+        <v>1.6</v>
       </c>
       <c r="K17" t="n">
-        <v>3.78</v>
+        <v>3.8</v>
       </c>
       <c r="L17" t="n">
-        <v>0.11</v>
+        <v>0.2</v>
       </c>
       <c r="M17" t="n">
-        <v>40</v>
+        <v>41.7</v>
       </c>
       <c r="N17" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.5</v>
       </c>
       <c r="O17" t="n">
-        <v>1.67</v>
+        <v>1.8</v>
       </c>
       <c r="P17" t="n">
-        <v>10.44</v>
+        <v>10.3</v>
       </c>
       <c r="Q17" t="n">
-        <v>13</v>
+        <v>13.1</v>
       </c>
       <c r="R17" t="n">
-        <v>10.67</v>
+        <v>10.1</v>
       </c>
       <c r="S17" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="T17" t="n">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="U17" t="n">
-        <v>0.44</v>
+        <v>0.4</v>
       </c>
       <c r="V17" t="n">
-        <v>0.44</v>
+        <v>0.4</v>
       </c>
       <c r="W17" t="n">
         <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>46.11</v>
+        <v>45.4</v>
       </c>
       <c r="Y17" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="Z17" t="n">
-        <v>11.33</v>
+        <v>12.4</v>
       </c>
       <c r="AA17" t="n">
-        <v>7.11</v>
+        <v>7.6</v>
       </c>
       <c r="AB17" t="n">
-        <v>4.22</v>
+        <v>4.8</v>
       </c>
       <c r="AC17" t="n">
-        <v>22.11</v>
+        <v>21.4</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.31</v>
+        <v>1.42</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="AF17" t="n">
         <v>0.09</v>
@@ -7595,70 +7595,70 @@
         <v>1.64</v>
       </c>
       <c r="BG17" t="n">
-        <v>2.75</v>
+        <v>2.76</v>
       </c>
       <c r="BH17" t="n">
-        <v>10.15</v>
+        <v>9.859999999999999</v>
       </c>
       <c r="BI17" t="n">
-        <v>2.75</v>
+        <v>2.76</v>
       </c>
       <c r="BJ17" t="n">
-        <v>0.8</v>
+        <v>0.76</v>
       </c>
       <c r="BK17" t="n">
-        <v>0.55</v>
+        <v>0.52</v>
       </c>
       <c r="BL17" t="n">
-        <v>0.7</v>
+        <v>0.76</v>
       </c>
       <c r="BM17" t="n">
-        <v>0.7</v>
+        <v>0.71</v>
       </c>
       <c r="BN17" t="n">
-        <v>1.4</v>
+        <v>1.48</v>
       </c>
       <c r="BO17" t="n">
-        <v>1.35</v>
+        <v>1.29</v>
       </c>
       <c r="BP17" t="n">
-        <v>3.7</v>
+        <v>3.67</v>
       </c>
       <c r="BQ17" t="n">
-        <v>5.75</v>
+        <v>5.52</v>
       </c>
       <c r="BR17" t="n">
-        <v>90</v>
+        <v>90.48</v>
       </c>
       <c r="BS17" t="n">
-        <v>85</v>
+        <v>85.70999999999999</v>
       </c>
       <c r="BT17" t="n">
-        <v>45</v>
+        <v>47.62</v>
       </c>
       <c r="BU17" t="n">
-        <v>35</v>
+        <v>33.33</v>
       </c>
       <c r="BV17" t="n">
-        <v>20</v>
+        <v>19.05</v>
       </c>
       <c r="BW17" t="n">
         <v>0</v>
       </c>
       <c r="BX17" t="n">
-        <v>65</v>
+        <v>66.67</v>
       </c>
       <c r="BY17" t="n">
-        <v>3.02</v>
+        <v>3.07</v>
       </c>
       <c r="BZ17" t="n">
-        <v>3.28</v>
+        <v>3.32</v>
       </c>
       <c r="CA17" t="n">
         <v>3.73</v>
       </c>
       <c r="CB17" t="n">
-        <v>3.82</v>
+        <v>3.81</v>
       </c>
       <c r="CC17" t="n">
         <v>4.19</v>
@@ -7691,7 +7691,7 @@
         <v>1.79</v>
       </c>
       <c r="CM17" t="n">
-        <v>2.67</v>
+        <v>2.66</v>
       </c>
       <c r="CN17" t="n">
         <v>2.06</v>
@@ -7709,16 +7709,16 @@
         <v>1.35</v>
       </c>
       <c r="CS17" t="n">
-        <v>2.56</v>
+        <v>2.57</v>
       </c>
       <c r="CT17" t="n">
-        <v>3.23</v>
+        <v>3.24</v>
       </c>
       <c r="CU17" t="n">
         <v>1.53</v>
       </c>
       <c r="CV17" t="n">
-        <v>2.32</v>
+        <v>2.31</v>
       </c>
       <c r="CW17" t="n">
         <v>1.67</v>
@@ -7742,82 +7742,82 @@
         <v>1.77</v>
       </c>
       <c r="DD17" t="n">
-        <v>2.84</v>
+        <v>2.85</v>
       </c>
       <c r="DE17" t="n">
         <v>0.05</v>
       </c>
       <c r="DF17" t="n">
-        <v>1.1</v>
+        <v>1.14</v>
       </c>
       <c r="DG17" t="n">
-        <v>2.25</v>
+        <v>2.19</v>
       </c>
       <c r="DH17" t="n">
-        <v>96.55</v>
+        <v>95.14</v>
       </c>
       <c r="DI17" t="n">
         <v>0.05</v>
       </c>
       <c r="DJ17" t="n">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="DK17" t="n">
-        <v>4.2</v>
+        <v>4.19</v>
       </c>
       <c r="DL17" t="n">
-        <v>0.15</v>
+        <v>0.19</v>
       </c>
       <c r="DM17" t="n">
-        <v>44.65</v>
+        <v>45.24</v>
       </c>
       <c r="DN17" t="n">
-        <v>0.5</v>
+        <v>0.47</v>
       </c>
       <c r="DO17" t="n">
-        <v>1.6</v>
+        <v>1.67</v>
       </c>
       <c r="DP17" t="n">
-        <v>11.35</v>
+        <v>11.24</v>
       </c>
       <c r="DQ17" t="n">
-        <v>11.85</v>
+        <v>11.95</v>
       </c>
       <c r="DR17" t="n">
-        <v>9.699999999999999</v>
+        <v>9.48</v>
       </c>
       <c r="DS17" t="n">
-        <v>0.25</v>
+        <v>0.24</v>
       </c>
       <c r="DT17" t="n">
-        <v>0.25</v>
+        <v>0.24</v>
       </c>
       <c r="DU17" t="n">
         <v>0</v>
       </c>
       <c r="DV17" t="n">
-        <v>48.1</v>
+        <v>47.67</v>
       </c>
       <c r="DW17" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="DX17" t="n">
-        <v>11.15</v>
+        <v>11.67</v>
       </c>
       <c r="DY17" t="n">
-        <v>7.3</v>
+        <v>7.52</v>
       </c>
       <c r="DZ17" t="n">
-        <v>3.85</v>
+        <v>4.15</v>
       </c>
       <c r="EA17" t="n">
-        <v>21.05</v>
+        <v>20.76</v>
       </c>
       <c r="EB17" t="n">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="EC17" t="n">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
     </row>
   </sheetData>

--- a/data/teams/leagues/Averages_Belgium_Pro_League_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Belgium_Pro_League_2025-2026.xlsx
@@ -1830,7 +1830,7 @@
         <v>12</v>
       </c>
       <c r="R3" t="n">
-        <v>7.3</v>
+        <v>7.2</v>
       </c>
       <c r="S3" t="n">
         <v>1.2</v>
@@ -2142,7 +2142,7 @@
         <v>11.71</v>
       </c>
       <c r="DR3" t="n">
-        <v>7.62</v>
+        <v>7.57</v>
       </c>
       <c r="DS3" t="n">
         <v>0</v>
@@ -3541,7 +3541,7 @@
         <v>0</v>
       </c>
       <c r="AY7" t="n">
-        <v>48.82</v>
+        <v>48.91</v>
       </c>
       <c r="AZ7" t="n">
         <v>0</v>
@@ -3766,7 +3766,7 @@
         <v>0</v>
       </c>
       <c r="DV7" t="n">
-        <v>49.52</v>
+        <v>49.57</v>
       </c>
       <c r="DW7" t="n">
         <v>0</v>
@@ -4293,7 +4293,7 @@
         <v>0</v>
       </c>
       <c r="AG9" t="n">
-        <v>2.09</v>
+        <v>2.18</v>
       </c>
       <c r="AH9" t="n">
         <v>2.55</v>
@@ -4305,7 +4305,7 @@
         <v>0</v>
       </c>
       <c r="AK9" t="n">
-        <v>3.27</v>
+        <v>3.36</v>
       </c>
       <c r="AL9" t="n">
         <v>4.27</v>
@@ -4326,7 +4326,7 @@
         <v>16.73</v>
       </c>
       <c r="AR9" t="n">
-        <v>10.45</v>
+        <v>10.36</v>
       </c>
       <c r="AS9" t="n">
         <v>8.91</v>
@@ -4368,7 +4368,7 @@
         <v>1.38</v>
       </c>
       <c r="BF9" t="n">
-        <v>3.18</v>
+        <v>3.27</v>
       </c>
       <c r="BG9" t="n">
         <v>2.33</v>
@@ -4482,13 +4482,13 @@
         <v>3.27</v>
       </c>
       <c r="CR9" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="CS9" t="n">
-        <v>2.83</v>
+        <v>2.84</v>
       </c>
       <c r="CT9" t="n">
-        <v>3.09</v>
+        <v>3.08</v>
       </c>
       <c r="CU9" t="n">
         <v>1.45</v>
@@ -4500,13 +4500,13 @@
         <v>1.81</v>
       </c>
       <c r="CX9" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="CY9" t="n">
         <v>1.8</v>
       </c>
       <c r="CZ9" t="n">
-        <v>2.49</v>
+        <v>2.47</v>
       </c>
       <c r="DA9" t="n">
         <v>2.02</v>
@@ -4524,7 +4524,7 @@
         <v>0.14</v>
       </c>
       <c r="DF9" t="n">
-        <v>2.24</v>
+        <v>2.28</v>
       </c>
       <c r="DG9" t="n">
         <v>2.48</v>
@@ -4536,7 +4536,7 @@
         <v>0</v>
       </c>
       <c r="DJ9" t="n">
-        <v>3.19</v>
+        <v>3.24</v>
       </c>
       <c r="DK9" t="n">
         <v>4.33</v>
@@ -4557,7 +4557,7 @@
         <v>16.67</v>
       </c>
       <c r="DQ9" t="n">
-        <v>11.33</v>
+        <v>11.28</v>
       </c>
       <c r="DR9" t="n">
         <v>8.619999999999999</v>
@@ -4593,7 +4593,7 @@
         <v>1.44</v>
       </c>
       <c r="EC9" t="n">
-        <v>3.14</v>
+        <v>3.19</v>
       </c>
     </row>
     <row r="10">
@@ -5854,7 +5854,7 @@
         <v>1.64</v>
       </c>
       <c r="P13" t="n">
-        <v>11.18</v>
+        <v>11.09</v>
       </c>
       <c r="Q13" t="n">
         <v>11.45</v>
@@ -6100,7 +6100,7 @@
         <v>2.62</v>
       </c>
       <c r="CT13" t="n">
-        <v>3.25</v>
+        <v>3.24</v>
       </c>
       <c r="CU13" t="n">
         <v>1.51</v>
@@ -6112,13 +6112,13 @@
         <v>1.66</v>
       </c>
       <c r="CX13" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="CY13" t="n">
         <v>1.83</v>
       </c>
       <c r="CZ13" t="n">
-        <v>2.46</v>
+        <v>2.45</v>
       </c>
       <c r="DA13" t="n">
         <v>1.99</v>
@@ -6166,7 +6166,7 @@
         <v>1.91</v>
       </c>
       <c r="DP13" t="n">
-        <v>11.81</v>
+        <v>11.76</v>
       </c>
       <c r="DQ13" t="n">
         <v>11.14</v>
@@ -6281,16 +6281,16 @@
         <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>46.64</v>
+        <v>46.55</v>
       </c>
       <c r="Y14" t="n">
         <v>0.18</v>
       </c>
       <c r="Z14" t="n">
-        <v>11.82</v>
+        <v>11.73</v>
       </c>
       <c r="AA14" t="n">
-        <v>7.27</v>
+        <v>7.18</v>
       </c>
       <c r="AB14" t="n">
         <v>4.55</v>
@@ -6587,16 +6587,16 @@
         <v>0</v>
       </c>
       <c r="DV14" t="n">
-        <v>46.72</v>
+        <v>46.67</v>
       </c>
       <c r="DW14" t="n">
         <v>0.09</v>
       </c>
       <c r="DX14" t="n">
-        <v>11.38</v>
+        <v>11.33</v>
       </c>
       <c r="DY14" t="n">
-        <v>7.19</v>
+        <v>7.14</v>
       </c>
       <c r="DZ14" t="n">
         <v>4.19</v>
@@ -6765,7 +6765,7 @@
         <v>0</v>
       </c>
       <c r="AY15" t="n">
-        <v>45.09</v>
+        <v>45.18</v>
       </c>
       <c r="AZ15" t="n">
         <v>0.18</v>
@@ -6990,7 +6990,7 @@
         <v>0</v>
       </c>
       <c r="DV15" t="n">
-        <v>44.57</v>
+        <v>44.62</v>
       </c>
       <c r="DW15" t="n">
         <v>0.28</v>
@@ -7087,7 +7087,7 @@
         <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>52.3</v>
+        <v>52.2</v>
       </c>
       <c r="Y16" t="n">
         <v>0</v>
@@ -7393,7 +7393,7 @@
         <v>0</v>
       </c>
       <c r="DV16" t="n">
-        <v>53.67</v>
+        <v>53.62</v>
       </c>
       <c r="DW16" t="n">
         <v>0.05</v>

--- a/data/teams/leagues/Averages_Belgium_Pro_League_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Belgium_Pro_League_2025-2026.xlsx
@@ -2588,13 +2588,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C5" t="n">
         <v>11</v>
       </c>
       <c r="D5" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E5" t="n">
         <v>0.27</v>
@@ -2678,139 +2678,139 @@
         <v>1.55</v>
       </c>
       <c r="AF5" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="AH5" t="n">
-        <v>2.9</v>
+        <v>2.91</v>
       </c>
       <c r="AI5" t="n">
-        <v>89.8</v>
+        <v>88.45</v>
       </c>
       <c r="AJ5" t="n">
         <v>0</v>
       </c>
       <c r="AK5" t="n">
-        <v>2.3</v>
+        <v>2.09</v>
       </c>
       <c r="AL5" t="n">
-        <v>4.7</v>
+        <v>4.64</v>
       </c>
       <c r="AM5" t="n">
-        <v>0.7</v>
+        <v>0.64</v>
       </c>
       <c r="AN5" t="n">
-        <v>40.4</v>
+        <v>40.64</v>
       </c>
       <c r="AO5" t="n">
-        <v>0.8</v>
+        <v>0.73</v>
       </c>
       <c r="AP5" t="n">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="AQ5" t="n">
-        <v>10.9</v>
+        <v>10.91</v>
       </c>
       <c r="AR5" t="n">
-        <v>10.9</v>
+        <v>11.09</v>
       </c>
       <c r="AS5" t="n">
-        <v>11</v>
+        <v>11.09</v>
       </c>
       <c r="AT5" t="n">
-        <v>1.9</v>
+        <v>1.73</v>
       </c>
       <c r="AU5" t="n">
-        <v>1.1</v>
+        <v>1.36</v>
       </c>
       <c r="AV5" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="AW5" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="AX5" t="n">
         <v>0</v>
       </c>
       <c r="AY5" t="n">
-        <v>48.6</v>
+        <v>47.91</v>
       </c>
       <c r="AZ5" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="BA5" t="n">
-        <v>11.3</v>
+        <v>11.64</v>
       </c>
       <c r="BB5" t="n">
-        <v>6.6</v>
+        <v>6.73</v>
       </c>
       <c r="BC5" t="n">
-        <v>4.7</v>
+        <v>4.91</v>
       </c>
       <c r="BD5" t="n">
-        <v>18.5</v>
+        <v>17.82</v>
       </c>
       <c r="BE5" t="n">
-        <v>1.34</v>
+        <v>1.38</v>
       </c>
       <c r="BF5" t="n">
-        <v>1.9</v>
+        <v>1.73</v>
       </c>
       <c r="BG5" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="BH5" t="n">
-        <v>10.05</v>
+        <v>10.14</v>
       </c>
       <c r="BI5" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="BJ5" t="n">
-        <v>0.9</v>
+        <v>0.86</v>
       </c>
       <c r="BK5" t="n">
-        <v>0.48</v>
+        <v>0.55</v>
       </c>
       <c r="BL5" t="n">
-        <v>1</v>
+        <v>0.95</v>
       </c>
       <c r="BM5" t="n">
-        <v>0.62</v>
+        <v>0.68</v>
       </c>
       <c r="BN5" t="n">
-        <v>1.62</v>
+        <v>1.64</v>
       </c>
       <c r="BO5" t="n">
-        <v>1.38</v>
+        <v>1.41</v>
       </c>
       <c r="BP5" t="n">
         <v>4.05</v>
       </c>
       <c r="BQ5" t="n">
-        <v>6</v>
+        <v>6.09</v>
       </c>
       <c r="BR5" t="n">
-        <v>95.23999999999999</v>
+        <v>95.45</v>
       </c>
       <c r="BS5" t="n">
-        <v>85.70999999999999</v>
+        <v>86.36</v>
       </c>
       <c r="BT5" t="n">
-        <v>57.14</v>
+        <v>59.09</v>
       </c>
       <c r="BU5" t="n">
-        <v>33.33</v>
+        <v>36.36</v>
       </c>
       <c r="BV5" t="n">
-        <v>19.05</v>
+        <v>18.18</v>
       </c>
       <c r="BW5" t="n">
-        <v>9.52</v>
+        <v>9.09</v>
       </c>
       <c r="BX5" t="n">
-        <v>61.9</v>
+        <v>59.09</v>
       </c>
       <c r="BY5" t="n">
         <v>2.71</v>
@@ -2819,37 +2819,37 @@
         <v>2.83</v>
       </c>
       <c r="CA5" t="n">
-        <v>3.64</v>
+        <v>3.61</v>
       </c>
       <c r="CB5" t="n">
-        <v>3.82</v>
+        <v>3.78</v>
       </c>
       <c r="CC5" t="n">
-        <v>3.75</v>
+        <v>3.65</v>
       </c>
       <c r="CD5" t="n">
-        <v>4.12</v>
+        <v>3.99</v>
       </c>
       <c r="CE5" t="n">
         <v>1.3</v>
       </c>
       <c r="CF5" t="n">
-        <v>2.43</v>
+        <v>2.46</v>
       </c>
       <c r="CG5" t="n">
-        <v>3.25</v>
+        <v>3.22</v>
       </c>
       <c r="CH5" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="CI5" t="n">
-        <v>2.25</v>
+        <v>2.23</v>
       </c>
       <c r="CJ5" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="CK5" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="CL5" t="n">
         <v>1.84</v>
@@ -2861,28 +2861,28 @@
         <v>2</v>
       </c>
       <c r="CO5" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="CP5" t="n">
-        <v>1.72</v>
+        <v>1.74</v>
       </c>
       <c r="CQ5" t="n">
-        <v>2.7</v>
+        <v>2.75</v>
       </c>
       <c r="CR5" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="CS5" t="n">
-        <v>2.51</v>
+        <v>2.55</v>
       </c>
       <c r="CT5" t="n">
-        <v>3.24</v>
+        <v>3.18</v>
       </c>
       <c r="CU5" t="n">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="CV5" t="n">
-        <v>2.34</v>
+        <v>2.32</v>
       </c>
       <c r="CW5" t="n">
         <v>1.66</v>
@@ -2897,58 +2897,58 @@
         <v>2.49</v>
       </c>
       <c r="DA5" t="n">
-        <v>2.05</v>
+        <v>2.04</v>
       </c>
       <c r="DB5" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="DC5" t="n">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="DD5" t="n">
-        <v>2.81</v>
+        <v>2.86</v>
       </c>
       <c r="DE5" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
       <c r="DF5" t="n">
-        <v>1.24</v>
+        <v>1.18</v>
       </c>
       <c r="DG5" t="n">
-        <v>2.81</v>
+        <v>2.82</v>
       </c>
       <c r="DH5" t="n">
-        <v>98.14</v>
+        <v>97.09</v>
       </c>
       <c r="DI5" t="n">
         <v>0</v>
       </c>
       <c r="DJ5" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="DK5" t="n">
+        <v>4.82</v>
+      </c>
+      <c r="DL5" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="DM5" t="n">
+        <v>44.5</v>
+      </c>
+      <c r="DN5" t="n">
+        <v>0.59</v>
+      </c>
+      <c r="DO5" t="n">
         <v>2</v>
       </c>
-      <c r="DK5" t="n">
-        <v>4.86</v>
-      </c>
-      <c r="DL5" t="n">
-        <v>0.52</v>
-      </c>
-      <c r="DM5" t="n">
-        <v>44.57</v>
-      </c>
-      <c r="DN5" t="n">
-        <v>0.62</v>
-      </c>
-      <c r="DO5" t="n">
-        <v>2.05</v>
-      </c>
       <c r="DP5" t="n">
-        <v>10.86</v>
+        <v>10.87</v>
       </c>
       <c r="DQ5" t="n">
-        <v>10.86</v>
+        <v>10.96</v>
       </c>
       <c r="DR5" t="n">
-        <v>9.48</v>
+        <v>9.59</v>
       </c>
       <c r="DS5" t="n">
         <v>0.09</v>
@@ -2960,28 +2960,28 @@
         <v>0</v>
       </c>
       <c r="DV5" t="n">
-        <v>51.72</v>
+        <v>51.23</v>
       </c>
       <c r="DW5" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DX5" t="n">
-        <v>13.57</v>
+        <v>13.64</v>
       </c>
       <c r="DY5" t="n">
-        <v>9.050000000000001</v>
+        <v>9</v>
       </c>
       <c r="DZ5" t="n">
-        <v>4.52</v>
+        <v>4.64</v>
       </c>
       <c r="EA5" t="n">
-        <v>18.81</v>
+        <v>18.45</v>
       </c>
       <c r="EB5" t="n">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="EC5" t="n">
-        <v>1.72</v>
+        <v>1.64</v>
       </c>
     </row>
     <row r="6">
@@ -6618,94 +6618,94 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C15" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D15" t="n">
         <v>11</v>
       </c>
       <c r="E15" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="F15" t="n">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="G15" t="n">
-        <v>2</v>
+        <v>2.27</v>
       </c>
       <c r="H15" t="n">
-        <v>85</v>
+        <v>88.91</v>
       </c>
       <c r="I15" t="n">
         <v>0</v>
       </c>
       <c r="J15" t="n">
-        <v>3.2</v>
+        <v>3.09</v>
       </c>
       <c r="K15" t="n">
-        <v>4.9</v>
+        <v>5.18</v>
       </c>
       <c r="L15" t="n">
-        <v>0.5</v>
+        <v>0.45</v>
       </c>
       <c r="M15" t="n">
-        <v>51.4</v>
+        <v>53.27</v>
       </c>
       <c r="N15" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="O15" t="n">
-        <v>2.9</v>
+        <v>2.91</v>
       </c>
       <c r="P15" t="n">
-        <v>11.1</v>
+        <v>11.27</v>
       </c>
       <c r="Q15" t="n">
-        <v>12.4</v>
+        <v>12.27</v>
       </c>
       <c r="R15" t="n">
-        <v>8.800000000000001</v>
+        <v>8.550000000000001</v>
       </c>
       <c r="S15" t="n">
-        <v>1.2</v>
+        <v>1.45</v>
       </c>
       <c r="T15" t="n">
-        <v>1</v>
+        <v>0.91</v>
       </c>
       <c r="U15" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="V15" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="W15" t="n">
         <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>44</v>
+        <v>45.36</v>
       </c>
       <c r="Y15" t="n">
-        <v>0.4</v>
+        <v>0.36</v>
       </c>
       <c r="Z15" t="n">
-        <v>11.4</v>
+        <v>11.55</v>
       </c>
       <c r="AA15" t="n">
-        <v>7</v>
+        <v>7.45</v>
       </c>
       <c r="AB15" t="n">
-        <v>4.4</v>
+        <v>4.09</v>
       </c>
       <c r="AC15" t="n">
-        <v>20.7</v>
+        <v>20.91</v>
       </c>
       <c r="AD15" t="n">
         <v>1.4</v>
       </c>
       <c r="AE15" t="n">
-        <v>2.4</v>
+        <v>2.36</v>
       </c>
       <c r="AF15" t="n">
         <v>0.18</v>
@@ -6789,49 +6789,49 @@
         <v>1.82</v>
       </c>
       <c r="BG15" t="n">
-        <v>2.05</v>
+        <v>2.14</v>
       </c>
       <c r="BH15" t="n">
-        <v>9.76</v>
+        <v>9.859999999999999</v>
       </c>
       <c r="BI15" t="n">
-        <v>2.05</v>
+        <v>2.14</v>
       </c>
       <c r="BJ15" t="n">
-        <v>0.52</v>
+        <v>0.5</v>
       </c>
       <c r="BK15" t="n">
-        <v>0.62</v>
+        <v>0.68</v>
       </c>
       <c r="BL15" t="n">
-        <v>0.57</v>
+        <v>0.55</v>
       </c>
       <c r="BM15" t="n">
-        <v>0.33</v>
+        <v>0.41</v>
       </c>
       <c r="BN15" t="n">
-        <v>0.9</v>
+        <v>0.95</v>
       </c>
       <c r="BO15" t="n">
-        <v>1.14</v>
+        <v>1.18</v>
       </c>
       <c r="BP15" t="n">
-        <v>4.52</v>
+        <v>4.5</v>
       </c>
       <c r="BQ15" t="n">
-        <v>5.24</v>
+        <v>5.36</v>
       </c>
       <c r="BR15" t="n">
-        <v>95.23999999999999</v>
+        <v>95.45</v>
       </c>
       <c r="BS15" t="n">
-        <v>61.9</v>
+        <v>63.64</v>
       </c>
       <c r="BT15" t="n">
-        <v>38.1</v>
+        <v>40.91</v>
       </c>
       <c r="BU15" t="n">
-        <v>9.52</v>
+        <v>13.64</v>
       </c>
       <c r="BV15" t="n">
         <v>0</v>
@@ -6840,19 +6840,19 @@
         <v>0</v>
       </c>
       <c r="BX15" t="n">
-        <v>33.33</v>
+        <v>31.82</v>
       </c>
       <c r="BY15" t="n">
         <v>2.86</v>
       </c>
       <c r="BZ15" t="n">
-        <v>3.09</v>
+        <v>3.08</v>
       </c>
       <c r="CA15" t="n">
-        <v>3.45</v>
+        <v>3.43</v>
       </c>
       <c r="CB15" t="n">
-        <v>3.51</v>
+        <v>3.49</v>
       </c>
       <c r="CC15" t="n">
         <v>4.01</v>
@@ -6864,13 +6864,13 @@
         <v>1.39</v>
       </c>
       <c r="CF15" t="n">
-        <v>2.83</v>
+        <v>2.84</v>
       </c>
       <c r="CG15" t="n">
         <v>2.86</v>
       </c>
       <c r="CH15" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="CI15" t="n">
         <v>1.94</v>
@@ -6891,25 +6891,25 @@
         <v>1.92</v>
       </c>
       <c r="CO15" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="CP15" t="n">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="CQ15" t="n">
-        <v>3.47</v>
+        <v>3.48</v>
       </c>
       <c r="CR15" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="CS15" t="n">
-        <v>2.95</v>
+        <v>2.96</v>
       </c>
       <c r="CT15" t="n">
-        <v>3.01</v>
+        <v>3</v>
       </c>
       <c r="CU15" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="CV15" t="n">
         <v>2.07</v>
@@ -6921,97 +6921,97 @@
         <v>1.57</v>
       </c>
       <c r="CY15" t="n">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="CZ15" t="n">
-        <v>2.38</v>
+        <v>2.39</v>
       </c>
       <c r="DA15" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="DB15" t="n">
         <v>1.33</v>
       </c>
       <c r="DC15" t="n">
-        <v>2.04</v>
+        <v>2.05</v>
       </c>
       <c r="DD15" t="n">
-        <v>3.52</v>
+        <v>3.54</v>
       </c>
       <c r="DE15" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
       <c r="DF15" t="n">
-        <v>1.52</v>
+        <v>1.55</v>
       </c>
       <c r="DG15" t="n">
-        <v>1.86</v>
+        <v>2</v>
       </c>
       <c r="DH15" t="n">
-        <v>85.19</v>
+        <v>87.14</v>
       </c>
       <c r="DI15" t="n">
         <v>0</v>
       </c>
       <c r="DJ15" t="n">
-        <v>2.57</v>
+        <v>2.54</v>
       </c>
       <c r="DK15" t="n">
-        <v>4.14</v>
+        <v>4.32</v>
       </c>
       <c r="DL15" t="n">
-        <v>0.43</v>
+        <v>0.4</v>
       </c>
       <c r="DM15" t="n">
-        <v>43.33</v>
+        <v>44.64</v>
       </c>
       <c r="DN15" t="n">
-        <v>0.86</v>
+        <v>0.82</v>
       </c>
       <c r="DO15" t="n">
-        <v>2.29</v>
+        <v>2.32</v>
       </c>
       <c r="DP15" t="n">
-        <v>11.14</v>
+        <v>11.22</v>
       </c>
       <c r="DQ15" t="n">
-        <v>12.19</v>
+        <v>12.14</v>
       </c>
       <c r="DR15" t="n">
-        <v>9.48</v>
+        <v>9.32</v>
       </c>
       <c r="DS15" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DT15" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DU15" t="n">
         <v>0</v>
       </c>
       <c r="DV15" t="n">
-        <v>44.62</v>
+        <v>45.27</v>
       </c>
       <c r="DW15" t="n">
-        <v>0.28</v>
+        <v>0.27</v>
       </c>
       <c r="DX15" t="n">
-        <v>9.67</v>
+        <v>9.82</v>
       </c>
       <c r="DY15" t="n">
-        <v>6.29</v>
+        <v>6.55</v>
       </c>
       <c r="DZ15" t="n">
-        <v>3.38</v>
+        <v>3.27</v>
       </c>
       <c r="EA15" t="n">
-        <v>19.33</v>
+        <v>19.5</v>
       </c>
       <c r="EB15" t="n">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="EC15" t="n">
-        <v>2.1</v>
+        <v>2.09</v>
       </c>
     </row>
     <row r="16">

--- a/data/teams/leagues/Averages_Belgium_Pro_League_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Belgium_Pro_League_2025-2026.xlsx
@@ -1379,13 +1379,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C2" t="n">
         <v>11</v>
       </c>
       <c r="D2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
@@ -1469,49 +1469,49 @@
         <v>1.27</v>
       </c>
       <c r="AF2" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="AG2" t="n">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="AH2" t="n">
-        <v>2.5</v>
+        <v>2.27</v>
       </c>
       <c r="AI2" t="n">
-        <v>103.5</v>
+        <v>104.27</v>
       </c>
       <c r="AJ2" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="AK2" t="n">
-        <v>3</v>
+        <v>2.73</v>
       </c>
       <c r="AL2" t="n">
-        <v>4.8</v>
+        <v>4.55</v>
       </c>
       <c r="AM2" t="n">
-        <v>0.7</v>
+        <v>0.64</v>
       </c>
       <c r="AN2" t="n">
-        <v>51.3</v>
+        <v>50.73</v>
       </c>
       <c r="AO2" t="n">
-        <v>1.5</v>
+        <v>1.36</v>
       </c>
       <c r="AP2" t="n">
-        <v>2.3</v>
+        <v>2.27</v>
       </c>
       <c r="AQ2" t="n">
-        <v>12.8</v>
+        <v>12.45</v>
       </c>
       <c r="AR2" t="n">
-        <v>12.3</v>
+        <v>12</v>
       </c>
       <c r="AS2" t="n">
-        <v>7.6</v>
+        <v>7.55</v>
       </c>
       <c r="AT2" t="n">
-        <v>0.8</v>
+        <v>0.82</v>
       </c>
       <c r="AU2" t="n">
         <v>1</v>
@@ -1526,82 +1526,82 @@
         <v>0</v>
       </c>
       <c r="AY2" t="n">
-        <v>47.2</v>
+        <v>46.91</v>
       </c>
       <c r="AZ2" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="BA2" t="n">
-        <v>12</v>
+        <v>11.91</v>
       </c>
       <c r="BB2" t="n">
-        <v>8.6</v>
+        <v>8.640000000000001</v>
       </c>
       <c r="BC2" t="n">
-        <v>3.4</v>
+        <v>3.27</v>
       </c>
       <c r="BD2" t="n">
-        <v>22.5</v>
+        <v>22</v>
       </c>
       <c r="BE2" t="n">
-        <v>1.37</v>
+        <v>1.35</v>
       </c>
       <c r="BF2" t="n">
-        <v>2.8</v>
+        <v>2.55</v>
       </c>
       <c r="BG2" t="n">
-        <v>2.71</v>
+        <v>2.68</v>
       </c>
       <c r="BH2" t="n">
-        <v>10.33</v>
+        <v>10.14</v>
       </c>
       <c r="BI2" t="n">
-        <v>2.71</v>
+        <v>2.68</v>
       </c>
       <c r="BJ2" t="n">
-        <v>0.62</v>
+        <v>0.64</v>
       </c>
       <c r="BK2" t="n">
-        <v>1</v>
+        <v>0.95</v>
       </c>
       <c r="BL2" t="n">
-        <v>0.57</v>
+        <v>0.55</v>
       </c>
       <c r="BM2" t="n">
-        <v>0.52</v>
+        <v>0.55</v>
       </c>
       <c r="BN2" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="BO2" t="n">
-        <v>1.62</v>
+        <v>1.59</v>
       </c>
       <c r="BP2" t="n">
-        <v>4.62</v>
+        <v>4.55</v>
       </c>
       <c r="BQ2" t="n">
-        <v>5.67</v>
+        <v>5.55</v>
       </c>
       <c r="BR2" t="n">
-        <v>90.48</v>
+        <v>90.91</v>
       </c>
       <c r="BS2" t="n">
-        <v>90.48</v>
+        <v>90.91</v>
       </c>
       <c r="BT2" t="n">
-        <v>42.86</v>
+        <v>40.91</v>
       </c>
       <c r="BU2" t="n">
-        <v>23.81</v>
+        <v>22.73</v>
       </c>
       <c r="BV2" t="n">
-        <v>19.05</v>
+        <v>18.18</v>
       </c>
       <c r="BW2" t="n">
-        <v>4.76</v>
+        <v>4.55</v>
       </c>
       <c r="BX2" t="n">
-        <v>61.9</v>
+        <v>63.64</v>
       </c>
       <c r="BY2" t="n">
         <v>2.37</v>
@@ -1610,16 +1610,16 @@
         <v>2.45</v>
       </c>
       <c r="CA2" t="n">
-        <v>3.55</v>
+        <v>3.54</v>
       </c>
       <c r="CB2" t="n">
-        <v>3.69</v>
+        <v>3.68</v>
       </c>
       <c r="CC2" t="n">
-        <v>3.37</v>
+        <v>3.43</v>
       </c>
       <c r="CD2" t="n">
-        <v>3.53</v>
+        <v>3.58</v>
       </c>
       <c r="CE2" t="n">
         <v>1.32</v>
@@ -1643,7 +1643,7 @@
         <v>1.43</v>
       </c>
       <c r="CL2" t="n">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="CM2" t="n">
         <v>2.62</v>
@@ -1658,16 +1658,16 @@
         <v>1.75</v>
       </c>
       <c r="CQ2" t="n">
-        <v>2.88</v>
+        <v>2.87</v>
       </c>
       <c r="CR2" t="n">
         <v>1.36</v>
       </c>
       <c r="CS2" t="n">
-        <v>2.62</v>
+        <v>2.63</v>
       </c>
       <c r="CT2" t="n">
-        <v>3.2</v>
+        <v>3.21</v>
       </c>
       <c r="CU2" t="n">
         <v>1.51</v>
@@ -1676,7 +1676,7 @@
         <v>2.31</v>
       </c>
       <c r="CW2" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="CX2" t="n">
         <v>1.5</v>
@@ -1694,85 +1694,85 @@
         <v>1.24</v>
       </c>
       <c r="DC2" t="n">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="DD2" t="n">
         <v>2.88</v>
       </c>
       <c r="DE2" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="DF2" t="n">
-        <v>1.14</v>
+        <v>1.09</v>
       </c>
       <c r="DG2" t="n">
-        <v>2.71</v>
+        <v>2.59</v>
       </c>
       <c r="DH2" t="n">
-        <v>106.81</v>
+        <v>107.04</v>
       </c>
       <c r="DI2" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="DJ2" t="n">
-        <v>2.14</v>
+        <v>2.04</v>
       </c>
       <c r="DK2" t="n">
-        <v>4.86</v>
+        <v>4.73</v>
       </c>
       <c r="DL2" t="n">
-        <v>0.57</v>
+        <v>0.55</v>
       </c>
       <c r="DM2" t="n">
-        <v>50</v>
+        <v>49.78</v>
       </c>
       <c r="DN2" t="n">
-        <v>0.95</v>
+        <v>0.9</v>
       </c>
       <c r="DO2" t="n">
-        <v>2.14</v>
+        <v>2.13</v>
       </c>
       <c r="DP2" t="n">
-        <v>10.81</v>
+        <v>10.72</v>
       </c>
       <c r="DQ2" t="n">
-        <v>13</v>
+        <v>12.82</v>
       </c>
       <c r="DR2" t="n">
-        <v>7.24</v>
+        <v>7.23</v>
       </c>
       <c r="DS2" t="n">
-        <v>0.29</v>
+        <v>0.28</v>
       </c>
       <c r="DT2" t="n">
-        <v>0.29</v>
+        <v>0.28</v>
       </c>
       <c r="DU2" t="n">
         <v>0</v>
       </c>
       <c r="DV2" t="n">
-        <v>49.38</v>
+        <v>49.14</v>
       </c>
       <c r="DW2" t="n">
         <v>0.09</v>
       </c>
       <c r="DX2" t="n">
-        <v>13.43</v>
+        <v>13.32</v>
       </c>
       <c r="DY2" t="n">
         <v>9.140000000000001</v>
       </c>
       <c r="DZ2" t="n">
-        <v>4.29</v>
+        <v>4.18</v>
       </c>
       <c r="EA2" t="n">
-        <v>23.19</v>
+        <v>22.91</v>
       </c>
       <c r="EB2" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="EC2" t="n">
-        <v>2</v>
+        <v>1.91</v>
       </c>
     </row>
     <row r="3">
@@ -1782,61 +1782,61 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C3" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D3" t="n">
         <v>11</v>
       </c>
       <c r="E3" t="n">
-        <v>0</v>
+        <v>0.09</v>
       </c>
       <c r="F3" t="n">
-        <v>1</v>
+        <v>1.09</v>
       </c>
       <c r="G3" t="n">
-        <v>3.8</v>
+        <v>3.82</v>
       </c>
       <c r="H3" t="n">
-        <v>112.7</v>
+        <v>114.18</v>
       </c>
       <c r="I3" t="n">
         <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>1.4</v>
+        <v>1.55</v>
       </c>
       <c r="K3" t="n">
-        <v>6.8</v>
+        <v>6.82</v>
       </c>
       <c r="L3" t="n">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="M3" t="n">
-        <v>66.59999999999999</v>
+        <v>65.81999999999999</v>
       </c>
       <c r="N3" t="n">
-        <v>0.2</v>
+        <v>0.27</v>
       </c>
       <c r="O3" t="n">
         <v>3</v>
       </c>
       <c r="P3" t="n">
-        <v>9.5</v>
+        <v>9.640000000000001</v>
       </c>
       <c r="Q3" t="n">
-        <v>12</v>
+        <v>12.09</v>
       </c>
       <c r="R3" t="n">
-        <v>7.2</v>
+        <v>6.55</v>
       </c>
       <c r="S3" t="n">
-        <v>1.2</v>
+        <v>1.36</v>
       </c>
       <c r="T3" t="n">
-        <v>1.9</v>
+        <v>2.09</v>
       </c>
       <c r="U3" t="n">
         <v>0</v>
@@ -1848,28 +1848,28 @@
         <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>64.59999999999999</v>
+        <v>65.27</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="Z3" t="n">
-        <v>17.5</v>
+        <v>17.45</v>
       </c>
       <c r="AA3" t="n">
-        <v>12.5</v>
+        <v>12.27</v>
       </c>
       <c r="AB3" t="n">
-        <v>5</v>
+        <v>5.18</v>
       </c>
       <c r="AC3" t="n">
-        <v>23.1</v>
+        <v>23</v>
       </c>
       <c r="AD3" t="n">
         <v>1.94</v>
       </c>
       <c r="AE3" t="n">
-        <v>1</v>
+        <v>1.18</v>
       </c>
       <c r="AF3" t="n">
         <v>0.09</v>
@@ -1953,70 +1953,70 @@
         <v>1.55</v>
       </c>
       <c r="BG3" t="n">
-        <v>3</v>
+        <v>3.18</v>
       </c>
       <c r="BH3" t="n">
-        <v>10.95</v>
+        <v>10.77</v>
       </c>
       <c r="BI3" t="n">
-        <v>3</v>
+        <v>3.18</v>
       </c>
       <c r="BJ3" t="n">
-        <v>0.71</v>
+        <v>0.73</v>
       </c>
       <c r="BK3" t="n">
-        <v>0.48</v>
+        <v>0.55</v>
       </c>
       <c r="BL3" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.91</v>
       </c>
       <c r="BM3" t="n">
         <v>1</v>
       </c>
       <c r="BN3" t="n">
-        <v>1.81</v>
+        <v>1.91</v>
       </c>
       <c r="BO3" t="n">
-        <v>1.19</v>
+        <v>1.27</v>
       </c>
       <c r="BP3" t="n">
-        <v>4.67</v>
+        <v>4.59</v>
       </c>
       <c r="BQ3" t="n">
-        <v>6.29</v>
+        <v>6.18</v>
       </c>
       <c r="BR3" t="n">
         <v>100</v>
       </c>
       <c r="BS3" t="n">
-        <v>61.9</v>
+        <v>63.64</v>
       </c>
       <c r="BT3" t="n">
-        <v>47.62</v>
+        <v>50</v>
       </c>
       <c r="BU3" t="n">
-        <v>23.81</v>
+        <v>27.27</v>
       </c>
       <c r="BV3" t="n">
-        <v>23.81</v>
+        <v>27.27</v>
       </c>
       <c r="BW3" t="n">
-        <v>14.29</v>
+        <v>18.18</v>
       </c>
       <c r="BX3" t="n">
-        <v>52.38</v>
+        <v>54.55</v>
       </c>
       <c r="BY3" t="n">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="BZ3" t="n">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="CA3" t="n">
-        <v>4.44</v>
+        <v>4.47</v>
       </c>
       <c r="CB3" t="n">
-        <v>4.74</v>
+        <v>4.76</v>
       </c>
       <c r="CC3" t="n">
         <v>1.74</v>
@@ -2025,22 +2025,22 @@
         <v>1.81</v>
       </c>
       <c r="CE3" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="CF3" t="n">
-        <v>2.24</v>
+        <v>2.23</v>
       </c>
       <c r="CG3" t="n">
         <v>3.55</v>
       </c>
       <c r="CH3" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="CI3" t="n">
         <v>2.13</v>
       </c>
       <c r="CJ3" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="CK3" t="n">
         <v>1.47</v>
@@ -2049,10 +2049,10 @@
         <v>1.91</v>
       </c>
       <c r="CM3" t="n">
-        <v>2.52</v>
+        <v>2.53</v>
       </c>
       <c r="CN3" t="n">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="CO3" t="n">
         <v>1.16</v>
@@ -2061,22 +2061,22 @@
         <v>1.56</v>
       </c>
       <c r="CQ3" t="n">
-        <v>2.4</v>
+        <v>2.37</v>
       </c>
       <c r="CR3" t="n">
         <v>1.33</v>
       </c>
       <c r="CS3" t="n">
-        <v>2.3</v>
+        <v>2.31</v>
       </c>
       <c r="CT3" t="n">
         <v>3.28</v>
       </c>
       <c r="CU3" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="CV3" t="n">
-        <v>2.3</v>
+        <v>2.29</v>
       </c>
       <c r="CW3" t="n">
         <v>1.68</v>
@@ -2094,55 +2094,55 @@
         <v>2.03</v>
       </c>
       <c r="DB3" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="DC3" t="n">
         <v>1.58</v>
       </c>
       <c r="DD3" t="n">
-        <v>2.44</v>
+        <v>2.45</v>
       </c>
       <c r="DE3" t="n">
-        <v>0.05</v>
+        <v>0.09</v>
       </c>
       <c r="DF3" t="n">
-        <v>1.05</v>
+        <v>1.09</v>
       </c>
       <c r="DG3" t="n">
-        <v>3.72</v>
+        <v>3.73</v>
       </c>
       <c r="DH3" t="n">
-        <v>109.95</v>
+        <v>110.82</v>
       </c>
       <c r="DI3" t="n">
-        <v>-0.05</v>
+        <v>-0.04</v>
       </c>
       <c r="DJ3" t="n">
-        <v>1.48</v>
+        <v>1.55</v>
       </c>
       <c r="DK3" t="n">
-        <v>6.33</v>
+        <v>6.37</v>
       </c>
       <c r="DL3" t="n">
-        <v>0.57</v>
+        <v>0.59</v>
       </c>
       <c r="DM3" t="n">
-        <v>61.34</v>
+        <v>61.18</v>
       </c>
       <c r="DN3" t="n">
-        <v>0.33</v>
+        <v>0.36</v>
       </c>
       <c r="DO3" t="n">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="DP3" t="n">
-        <v>9.43</v>
+        <v>9.5</v>
       </c>
       <c r="DQ3" t="n">
-        <v>11.71</v>
+        <v>11.77</v>
       </c>
       <c r="DR3" t="n">
-        <v>7.57</v>
+        <v>7.23</v>
       </c>
       <c r="DS3" t="n">
         <v>0</v>
@@ -2154,28 +2154,28 @@
         <v>0</v>
       </c>
       <c r="DV3" t="n">
-        <v>61.76</v>
+        <v>62.22</v>
       </c>
       <c r="DW3" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="DX3" t="n">
-        <v>16.43</v>
+        <v>16.45</v>
       </c>
       <c r="DY3" t="n">
-        <v>11.14</v>
+        <v>11.09</v>
       </c>
       <c r="DZ3" t="n">
-        <v>5.29</v>
+        <v>5.36</v>
       </c>
       <c r="EA3" t="n">
-        <v>20.38</v>
+        <v>20.45</v>
       </c>
       <c r="EB3" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="EC3" t="n">
-        <v>1.29</v>
+        <v>1.36</v>
       </c>
     </row>
     <row r="4">
@@ -2185,13 +2185,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C4" t="n">
         <v>11</v>
       </c>
       <c r="D4" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
@@ -2275,139 +2275,139 @@
         <v>1.55</v>
       </c>
       <c r="AF4" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.7</v>
+        <v>1.82</v>
       </c>
       <c r="AH4" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>89.81999999999999</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>39.18</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="AP4" t="n">
+        <v>2</v>
+      </c>
+      <c r="AQ4" t="n">
+        <v>12.18</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>11.91</v>
+      </c>
+      <c r="AS4" t="n">
+        <v>11.09</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AU4" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="AV4" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="AW4" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="AX4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY4" t="n">
+        <v>43.18</v>
+      </c>
+      <c r="AZ4" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="BA4" t="n">
+        <v>11.18</v>
+      </c>
+      <c r="BB4" t="n">
+        <v>6.82</v>
+      </c>
+      <c r="BC4" t="n">
+        <v>4.36</v>
+      </c>
+      <c r="BD4" t="n">
+        <v>19.18</v>
+      </c>
+      <c r="BE4" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="BF4" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="BG4" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="BH4" t="n">
+        <v>8.359999999999999</v>
+      </c>
+      <c r="BI4" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="BJ4" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="BK4" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="BL4" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="BM4" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="BN4" t="n">
         <v>1.5</v>
       </c>
-      <c r="AI4" t="n">
-        <v>91.09999999999999</v>
-      </c>
-      <c r="AJ4" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="AK4" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AL4" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AM4" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="AN4" t="n">
-        <v>39.4</v>
-      </c>
-      <c r="AO4" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="AP4" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AQ4" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="AR4" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="AS4" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AT4" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AU4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AV4" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="AW4" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="AX4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY4" t="n">
-        <v>43.6</v>
-      </c>
-      <c r="AZ4" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="BA4" t="n">
-        <v>11.4</v>
-      </c>
-      <c r="BB4" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="BC4" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BD4" t="n">
-        <v>19.1</v>
-      </c>
-      <c r="BE4" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="BF4" t="n">
-        <v>2</v>
-      </c>
-      <c r="BG4" t="n">
-        <v>2.43</v>
-      </c>
-      <c r="BH4" t="n">
-        <v>8.19</v>
-      </c>
-      <c r="BI4" t="n">
-        <v>2.43</v>
-      </c>
-      <c r="BJ4" t="n">
-        <v>0.57</v>
-      </c>
-      <c r="BK4" t="n">
-        <v>0.29</v>
-      </c>
-      <c r="BL4" t="n">
-        <v>0.57</v>
-      </c>
-      <c r="BM4" t="n">
-        <v>1</v>
-      </c>
-      <c r="BN4" t="n">
-        <v>1.57</v>
-      </c>
       <c r="BO4" t="n">
-        <v>0.86</v>
+        <v>0.82</v>
       </c>
       <c r="BP4" t="n">
-        <v>3.62</v>
+        <v>3.73</v>
       </c>
       <c r="BQ4" t="n">
-        <v>3.95</v>
+        <v>4.05</v>
       </c>
       <c r="BR4" t="n">
-        <v>90.48</v>
+        <v>86.36</v>
       </c>
       <c r="BS4" t="n">
-        <v>71.43000000000001</v>
+        <v>68.18000000000001</v>
       </c>
       <c r="BT4" t="n">
-        <v>47.62</v>
+        <v>45.45</v>
       </c>
       <c r="BU4" t="n">
-        <v>23.81</v>
+        <v>22.73</v>
       </c>
       <c r="BV4" t="n">
-        <v>4.76</v>
+        <v>4.55</v>
       </c>
       <c r="BW4" t="n">
-        <v>4.76</v>
+        <v>4.55</v>
       </c>
       <c r="BX4" t="n">
-        <v>57.14</v>
+        <v>54.55</v>
       </c>
       <c r="BY4" t="n">
         <v>3.41</v>
@@ -2416,16 +2416,16 @@
         <v>3.51</v>
       </c>
       <c r="CA4" t="n">
-        <v>3.66</v>
+        <v>3.69</v>
       </c>
       <c r="CB4" t="n">
-        <v>3.83</v>
+        <v>3.85</v>
       </c>
       <c r="CC4" t="n">
-        <v>4.63</v>
+        <v>4.8</v>
       </c>
       <c r="CD4" t="n">
-        <v>5.03</v>
+        <v>5.08</v>
       </c>
       <c r="CE4" t="n">
         <v>1.35</v>
@@ -2461,10 +2461,10 @@
         <v>1.25</v>
       </c>
       <c r="CP4" t="n">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="CQ4" t="n">
-        <v>3.09</v>
+        <v>3.08</v>
       </c>
       <c r="CR4" t="n">
         <v>1.39</v>
@@ -2473,79 +2473,79 @@
         <v>2.75</v>
       </c>
       <c r="CT4" t="n">
-        <v>3.07</v>
+        <v>3.08</v>
       </c>
       <c r="CU4" t="n">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="CV4" t="n">
         <v>2.14</v>
       </c>
       <c r="CW4" t="n">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="CX4" t="n">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="CY4" t="n">
         <v>1.96</v>
       </c>
       <c r="CZ4" t="n">
-        <v>2.36</v>
+        <v>2.37</v>
       </c>
       <c r="DA4" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="DB4" t="n">
         <v>1.27</v>
       </c>
       <c r="DC4" t="n">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="DD4" t="n">
         <v>3.14</v>
       </c>
       <c r="DE4" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="DF4" t="n">
-        <v>1.33</v>
+        <v>1.41</v>
       </c>
       <c r="DG4" t="n">
-        <v>1.29</v>
+        <v>1.32</v>
       </c>
       <c r="DH4" t="n">
-        <v>93.48</v>
+        <v>92.73</v>
       </c>
       <c r="DI4" t="n">
-        <v>-0.05</v>
+        <v>-0.04</v>
       </c>
       <c r="DJ4" t="n">
-        <v>2.05</v>
+        <v>2.14</v>
       </c>
       <c r="DK4" t="n">
-        <v>3.14</v>
+        <v>3.28</v>
       </c>
       <c r="DL4" t="n">
         <v>0.09</v>
       </c>
       <c r="DM4" t="n">
-        <v>42.14</v>
+        <v>41.91</v>
       </c>
       <c r="DN4" t="n">
-        <v>0.62</v>
+        <v>0.64</v>
       </c>
       <c r="DO4" t="n">
-        <v>1.48</v>
+        <v>1.59</v>
       </c>
       <c r="DP4" t="n">
-        <v>11.09</v>
+        <v>11.32</v>
       </c>
       <c r="DQ4" t="n">
-        <v>11.52</v>
+        <v>11.59</v>
       </c>
       <c r="DR4" t="n">
-        <v>10.71</v>
+        <v>11</v>
       </c>
       <c r="DS4" t="n">
         <v>0.09</v>
@@ -2557,28 +2557,28 @@
         <v>0</v>
       </c>
       <c r="DV4" t="n">
-        <v>46.91</v>
+        <v>46.54</v>
       </c>
       <c r="DW4" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
       <c r="DX4" t="n">
-        <v>10.43</v>
+        <v>10.36</v>
       </c>
       <c r="DY4" t="n">
-        <v>6.67</v>
+        <v>6.68</v>
       </c>
       <c r="DZ4" t="n">
-        <v>3.76</v>
+        <v>3.68</v>
       </c>
       <c r="EA4" t="n">
-        <v>21.28</v>
+        <v>21.22</v>
       </c>
       <c r="EB4" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="EC4" t="n">
-        <v>1.76</v>
+        <v>1.86</v>
       </c>
     </row>
     <row r="5">
@@ -2870,16 +2870,16 @@
         <v>2.75</v>
       </c>
       <c r="CR5" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="CS5" t="n">
-        <v>2.55</v>
+        <v>2.51</v>
       </c>
       <c r="CT5" t="n">
-        <v>3.18</v>
+        <v>3.24</v>
       </c>
       <c r="CU5" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="CV5" t="n">
         <v>2.32</v>
@@ -2991,10 +2991,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C6" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D6" t="n">
         <v>11</v>
@@ -3003,49 +3003,49 @@
         <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>0.5</v>
+        <v>0.55</v>
       </c>
       <c r="G6" t="n">
-        <v>4.4</v>
+        <v>4.27</v>
       </c>
       <c r="H6" t="n">
-        <v>131.7</v>
+        <v>130.18</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="K6" t="n">
-        <v>7.2</v>
+        <v>6.91</v>
       </c>
       <c r="L6" t="n">
-        <v>0.6</v>
+        <v>0.55</v>
       </c>
       <c r="M6" t="n">
-        <v>64.59999999999999</v>
+        <v>62.45</v>
       </c>
       <c r="N6" t="n">
-        <v>0.6</v>
+        <v>0.55</v>
       </c>
       <c r="O6" t="n">
-        <v>2.7</v>
+        <v>2.55</v>
       </c>
       <c r="P6" t="n">
-        <v>11</v>
+        <v>10.82</v>
       </c>
       <c r="Q6" t="n">
-        <v>14</v>
+        <v>13.55</v>
       </c>
       <c r="R6" t="n">
-        <v>4.9</v>
+        <v>5.64</v>
       </c>
       <c r="S6" t="n">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="T6" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="U6" t="n">
         <v>0</v>
@@ -3057,25 +3057,25 @@
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>65.3</v>
+        <v>64.45</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="Z6" t="n">
-        <v>18.6</v>
+        <v>18.18</v>
       </c>
       <c r="AA6" t="n">
-        <v>12.7</v>
+        <v>12.27</v>
       </c>
       <c r="AB6" t="n">
-        <v>5.9</v>
+        <v>5.91</v>
       </c>
       <c r="AC6" t="n">
-        <v>20.8</v>
+        <v>21.45</v>
       </c>
       <c r="AD6" t="n">
-        <v>2.06</v>
+        <v>2.02</v>
       </c>
       <c r="AE6" t="n">
         <v>1</v>
@@ -3162,70 +3162,70 @@
         <v>1.73</v>
       </c>
       <c r="BG6" t="n">
-        <v>2.9</v>
+        <v>2.86</v>
       </c>
       <c r="BH6" t="n">
-        <v>9.949999999999999</v>
+        <v>9.77</v>
       </c>
       <c r="BI6" t="n">
-        <v>2.9</v>
+        <v>2.86</v>
       </c>
       <c r="BJ6" t="n">
-        <v>0.62</v>
+        <v>0.64</v>
       </c>
       <c r="BK6" t="n">
-        <v>0.9</v>
+        <v>0.86</v>
       </c>
       <c r="BL6" t="n">
-        <v>0.86</v>
+        <v>0.82</v>
       </c>
       <c r="BM6" t="n">
-        <v>0.52</v>
+        <v>0.55</v>
       </c>
       <c r="BN6" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="BO6" t="n">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="BP6" t="n">
-        <v>4.48</v>
+        <v>4.41</v>
       </c>
       <c r="BQ6" t="n">
-        <v>5.43</v>
+        <v>5.32</v>
       </c>
       <c r="BR6" t="n">
         <v>100</v>
       </c>
       <c r="BS6" t="n">
-        <v>85.70999999999999</v>
+        <v>86.36</v>
       </c>
       <c r="BT6" t="n">
-        <v>61.9</v>
+        <v>59.09</v>
       </c>
       <c r="BU6" t="n">
-        <v>19.05</v>
+        <v>18.18</v>
       </c>
       <c r="BV6" t="n">
-        <v>9.52</v>
+        <v>9.09</v>
       </c>
       <c r="BW6" t="n">
-        <v>4.76</v>
+        <v>4.55</v>
       </c>
       <c r="BX6" t="n">
-        <v>80.95</v>
+        <v>81.81999999999999</v>
       </c>
       <c r="BY6" t="n">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="BZ6" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="CA6" t="n">
-        <v>3.85</v>
+        <v>3.83</v>
       </c>
       <c r="CB6" t="n">
-        <v>3.97</v>
+        <v>3.96</v>
       </c>
       <c r="CC6" t="n">
         <v>2.41</v>
@@ -3240,25 +3240,25 @@
         <v>2.42</v>
       </c>
       <c r="CG6" t="n">
-        <v>3.28</v>
+        <v>3.27</v>
       </c>
       <c r="CH6" t="n">
         <v>1.53</v>
       </c>
       <c r="CI6" t="n">
-        <v>2.25</v>
+        <v>2.24</v>
       </c>
       <c r="CJ6" t="n">
         <v>1.63</v>
       </c>
       <c r="CK6" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="CL6" t="n">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="CM6" t="n">
-        <v>2.43</v>
+        <v>2.44</v>
       </c>
       <c r="CN6" t="n">
         <v>1.89</v>
@@ -3276,10 +3276,10 @@
         <v>1.37</v>
       </c>
       <c r="CS6" t="n">
-        <v>2.56</v>
+        <v>2.57</v>
       </c>
       <c r="CT6" t="n">
-        <v>3.12</v>
+        <v>3.15</v>
       </c>
       <c r="CU6" t="n">
         <v>1.54</v>
@@ -3294,13 +3294,13 @@
         <v>1.58</v>
       </c>
       <c r="CY6" t="n">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="CZ6" t="n">
         <v>2.35</v>
       </c>
       <c r="DA6" t="n">
-        <v>1.89</v>
+        <v>1.91</v>
       </c>
       <c r="DB6" t="n">
         <v>1.23</v>
@@ -3309,49 +3309,49 @@
         <v>1.74</v>
       </c>
       <c r="DD6" t="n">
-        <v>2.79</v>
+        <v>2.8</v>
       </c>
       <c r="DE6" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="DF6" t="n">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="DG6" t="n">
-        <v>3.48</v>
+        <v>3.46</v>
       </c>
       <c r="DH6" t="n">
-        <v>116.9</v>
+        <v>116.82</v>
       </c>
       <c r="DI6" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="DJ6" t="n">
-        <v>1.48</v>
+        <v>1.45</v>
       </c>
       <c r="DK6" t="n">
-        <v>5.91</v>
+        <v>5.82</v>
       </c>
       <c r="DL6" t="n">
-        <v>0.67</v>
+        <v>0.64</v>
       </c>
       <c r="DM6" t="n">
-        <v>55.52</v>
+        <v>54.86</v>
       </c>
       <c r="DN6" t="n">
-        <v>0.52</v>
+        <v>0.5</v>
       </c>
       <c r="DO6" t="n">
-        <v>2.38</v>
+        <v>2.32</v>
       </c>
       <c r="DP6" t="n">
-        <v>10.33</v>
+        <v>10.28</v>
       </c>
       <c r="DQ6" t="n">
-        <v>12.91</v>
+        <v>12.73</v>
       </c>
       <c r="DR6" t="n">
-        <v>6.24</v>
+        <v>6.55</v>
       </c>
       <c r="DS6" t="n">
         <v>0</v>
@@ -3363,28 +3363,28 @@
         <v>0</v>
       </c>
       <c r="DV6" t="n">
-        <v>63.14</v>
+        <v>62.82</v>
       </c>
       <c r="DW6" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="DX6" t="n">
-        <v>16.28</v>
+        <v>16.18</v>
       </c>
       <c r="DY6" t="n">
-        <v>10.57</v>
+        <v>10.46</v>
       </c>
       <c r="DZ6" t="n">
-        <v>5.72</v>
+        <v>5.73</v>
       </c>
       <c r="EA6" t="n">
-        <v>20</v>
+        <v>20.36</v>
       </c>
       <c r="EB6" t="n">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="EC6" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
     </row>
     <row r="7">
@@ -3394,94 +3394,94 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C7" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D7" t="n">
         <v>11</v>
       </c>
       <c r="E7" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="F7" t="n">
-        <v>1.6</v>
+        <v>1.73</v>
       </c>
       <c r="G7" t="n">
-        <v>2.3</v>
+        <v>2.73</v>
       </c>
       <c r="H7" t="n">
-        <v>89.59999999999999</v>
+        <v>92.45</v>
       </c>
       <c r="I7" t="n">
-        <v>0.3</v>
+        <v>0.27</v>
       </c>
       <c r="J7" t="n">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="K7" t="n">
-        <v>4.6</v>
+        <v>5</v>
       </c>
       <c r="L7" t="n">
-        <v>0.2</v>
+        <v>0.27</v>
       </c>
       <c r="M7" t="n">
-        <v>50.5</v>
+        <v>52.82</v>
       </c>
       <c r="N7" t="n">
-        <v>0.8</v>
+        <v>0.73</v>
       </c>
       <c r="O7" t="n">
-        <v>2.3</v>
+        <v>2.27</v>
       </c>
       <c r="P7" t="n">
-        <v>10.6</v>
+        <v>10.55</v>
       </c>
       <c r="Q7" t="n">
-        <v>11.3</v>
+        <v>11.18</v>
       </c>
       <c r="R7" t="n">
-        <v>9.800000000000001</v>
+        <v>9.449999999999999</v>
       </c>
       <c r="S7" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="T7" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="U7" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="V7" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>50.3</v>
+        <v>51.45</v>
       </c>
       <c r="Y7" t="n">
         <v>0</v>
       </c>
       <c r="Z7" t="n">
-        <v>10.6</v>
+        <v>10.91</v>
       </c>
       <c r="AA7" t="n">
-        <v>6.8</v>
+        <v>7.27</v>
       </c>
       <c r="AB7" t="n">
-        <v>3.8</v>
+        <v>3.64</v>
       </c>
       <c r="AC7" t="n">
-        <v>21.8</v>
+        <v>21.55</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AE7" t="n">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="AF7" t="n">
         <v>0.09</v>
@@ -3565,70 +3565,70 @@
         <v>2.27</v>
       </c>
       <c r="BG7" t="n">
-        <v>2.29</v>
+        <v>2.27</v>
       </c>
       <c r="BH7" t="n">
-        <v>11.29</v>
+        <v>11.41</v>
       </c>
       <c r="BI7" t="n">
-        <v>2.29</v>
+        <v>2.27</v>
       </c>
       <c r="BJ7" t="n">
-        <v>0.52</v>
+        <v>0.5</v>
       </c>
       <c r="BK7" t="n">
-        <v>0.43</v>
+        <v>0.45</v>
       </c>
       <c r="BL7" t="n">
-        <v>0.57</v>
+        <v>0.59</v>
       </c>
       <c r="BM7" t="n">
-        <v>0.76</v>
+        <v>0.73</v>
       </c>
       <c r="BN7" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="BO7" t="n">
         <v>0.95</v>
       </c>
       <c r="BP7" t="n">
-        <v>5.14</v>
+        <v>5.09</v>
       </c>
       <c r="BQ7" t="n">
-        <v>6.14</v>
+        <v>6.32</v>
       </c>
       <c r="BR7" t="n">
-        <v>95.23999999999999</v>
+        <v>95.45</v>
       </c>
       <c r="BS7" t="n">
-        <v>66.67</v>
+        <v>68.18000000000001</v>
       </c>
       <c r="BT7" t="n">
-        <v>33.33</v>
+        <v>31.82</v>
       </c>
       <c r="BU7" t="n">
-        <v>23.81</v>
+        <v>22.73</v>
       </c>
       <c r="BV7" t="n">
-        <v>9.52</v>
+        <v>9.09</v>
       </c>
       <c r="BW7" t="n">
         <v>0</v>
       </c>
       <c r="BX7" t="n">
-        <v>61.9</v>
+        <v>63.64</v>
       </c>
       <c r="BY7" t="n">
         <v>2.81</v>
       </c>
       <c r="BZ7" t="n">
-        <v>3</v>
+        <v>2.99</v>
       </c>
       <c r="CA7" t="n">
-        <v>3.73</v>
+        <v>3.71</v>
       </c>
       <c r="CB7" t="n">
-        <v>3.87</v>
+        <v>3.85</v>
       </c>
       <c r="CC7" t="n">
         <v>3.98</v>
@@ -3658,10 +3658,10 @@
         <v>1.39</v>
       </c>
       <c r="CL7" t="n">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="CM7" t="n">
-        <v>2.75</v>
+        <v>2.76</v>
       </c>
       <c r="CN7" t="n">
         <v>2.1</v>
@@ -3673,7 +3673,7 @@
         <v>1.68</v>
       </c>
       <c r="CQ7" t="n">
-        <v>2.68</v>
+        <v>2.69</v>
       </c>
       <c r="CR7" t="n">
         <v>1.36</v>
@@ -3682,7 +3682,7 @@
         <v>2.55</v>
       </c>
       <c r="CT7" t="n">
-        <v>3.2</v>
+        <v>3.21</v>
       </c>
       <c r="CU7" t="n">
         <v>1.54</v>
@@ -3703,7 +3703,7 @@
         <v>2.57</v>
       </c>
       <c r="DA7" t="n">
-        <v>2.12</v>
+        <v>2.13</v>
       </c>
       <c r="DB7" t="n">
         <v>1.23</v>
@@ -3715,79 +3715,79 @@
         <v>2.82</v>
       </c>
       <c r="DE7" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DF7" t="n">
-        <v>1.52</v>
+        <v>1.59</v>
       </c>
       <c r="DG7" t="n">
-        <v>2.67</v>
+        <v>2.86</v>
       </c>
       <c r="DH7" t="n">
-        <v>87.53</v>
+        <v>89.04000000000001</v>
       </c>
       <c r="DI7" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
       <c r="DJ7" t="n">
-        <v>2.33</v>
+        <v>2.36</v>
       </c>
       <c r="DK7" t="n">
-        <v>4.86</v>
+        <v>5.04</v>
       </c>
       <c r="DL7" t="n">
-        <v>0.28</v>
+        <v>0.32</v>
       </c>
       <c r="DM7" t="n">
-        <v>45.95</v>
+        <v>47.32</v>
       </c>
       <c r="DN7" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.77</v>
       </c>
       <c r="DO7" t="n">
-        <v>2.19</v>
+        <v>2.18</v>
       </c>
       <c r="DP7" t="n">
-        <v>10.29</v>
+        <v>10.28</v>
       </c>
       <c r="DQ7" t="n">
-        <v>11.14</v>
+        <v>11.09</v>
       </c>
       <c r="DR7" t="n">
-        <v>9.33</v>
+        <v>9.18</v>
       </c>
       <c r="DS7" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="DT7" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="DU7" t="n">
         <v>0</v>
       </c>
       <c r="DV7" t="n">
-        <v>49.57</v>
+        <v>50.18</v>
       </c>
       <c r="DW7" t="n">
         <v>0</v>
       </c>
       <c r="DX7" t="n">
-        <v>10.33</v>
+        <v>10.5</v>
       </c>
       <c r="DY7" t="n">
-        <v>6.43</v>
+        <v>6.68</v>
       </c>
       <c r="DZ7" t="n">
-        <v>3.9</v>
+        <v>3.82</v>
       </c>
       <c r="EA7" t="n">
-        <v>21.86</v>
+        <v>21.73</v>
       </c>
       <c r="EB7" t="n">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="EC7" t="n">
-        <v>2.33</v>
+        <v>2.36</v>
       </c>
     </row>
     <row r="8">
@@ -3797,13 +3797,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C8" t="n">
         <v>11</v>
       </c>
       <c r="D8" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E8" t="n">
         <v>0.27</v>
@@ -3887,139 +3887,139 @@
         <v>1.27</v>
       </c>
       <c r="AF8" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="AH8" t="n">
-        <v>2.1</v>
+        <v>2.18</v>
       </c>
       <c r="AI8" t="n">
-        <v>88</v>
+        <v>87.64</v>
       </c>
       <c r="AJ8" t="n">
         <v>0</v>
       </c>
       <c r="AK8" t="n">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="AL8" t="n">
-        <v>4.4</v>
+        <v>4.45</v>
       </c>
       <c r="AM8" t="n">
-        <v>0.3</v>
+        <v>0.27</v>
       </c>
       <c r="AN8" t="n">
-        <v>44.1</v>
+        <v>42.91</v>
       </c>
       <c r="AO8" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="AP8" t="n">
-        <v>2.3</v>
+        <v>2.27</v>
       </c>
       <c r="AQ8" t="n">
-        <v>13.6</v>
+        <v>13.27</v>
       </c>
       <c r="AR8" t="n">
-        <v>12.1</v>
+        <v>11.91</v>
       </c>
       <c r="AS8" t="n">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="AT8" t="n">
-        <v>2.3</v>
+        <v>2.18</v>
       </c>
       <c r="AU8" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AV8" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="AW8" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="AX8" t="n">
         <v>0</v>
       </c>
       <c r="AY8" t="n">
-        <v>48.3</v>
+        <v>47.27</v>
       </c>
       <c r="AZ8" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="BA8" t="n">
-        <v>13.9</v>
+        <v>13.73</v>
       </c>
       <c r="BB8" t="n">
-        <v>9.5</v>
+        <v>9.359999999999999</v>
       </c>
       <c r="BC8" t="n">
-        <v>4.4</v>
+        <v>4.36</v>
       </c>
       <c r="BD8" t="n">
-        <v>22.7</v>
+        <v>22.55</v>
       </c>
       <c r="BE8" t="n">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="BF8" t="n">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="BG8" t="n">
-        <v>2.86</v>
+        <v>2.82</v>
       </c>
       <c r="BH8" t="n">
-        <v>10.29</v>
+        <v>10.45</v>
       </c>
       <c r="BI8" t="n">
-        <v>2.86</v>
+        <v>2.82</v>
       </c>
       <c r="BJ8" t="n">
-        <v>0.86</v>
+        <v>0.82</v>
       </c>
       <c r="BK8" t="n">
-        <v>0.52</v>
+        <v>0.55</v>
       </c>
       <c r="BL8" t="n">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="BM8" t="n">
-        <v>0.57</v>
+        <v>0.55</v>
       </c>
       <c r="BN8" t="n">
-        <v>1.48</v>
+        <v>1.45</v>
       </c>
       <c r="BO8" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="BP8" t="n">
-        <v>4.95</v>
+        <v>4.91</v>
       </c>
       <c r="BQ8" t="n">
-        <v>5.29</v>
+        <v>5.5</v>
       </c>
       <c r="BR8" t="n">
-        <v>90.48</v>
+        <v>90.91</v>
       </c>
       <c r="BS8" t="n">
-        <v>80.95</v>
+        <v>81.81999999999999</v>
       </c>
       <c r="BT8" t="n">
-        <v>38.1</v>
+        <v>36.36</v>
       </c>
       <c r="BU8" t="n">
-        <v>28.57</v>
+        <v>27.27</v>
       </c>
       <c r="BV8" t="n">
-        <v>14.29</v>
+        <v>13.64</v>
       </c>
       <c r="BW8" t="n">
-        <v>9.52</v>
+        <v>9.09</v>
       </c>
       <c r="BX8" t="n">
-        <v>38.1</v>
+        <v>40.91</v>
       </c>
       <c r="BY8" t="n">
         <v>2.19</v>
@@ -4028,19 +4028,19 @@
         <v>2.31</v>
       </c>
       <c r="CA8" t="n">
-        <v>3.85</v>
+        <v>3.82</v>
       </c>
       <c r="CB8" t="n">
-        <v>3.92</v>
+        <v>3.89</v>
       </c>
       <c r="CC8" t="n">
-        <v>4.24</v>
+        <v>4.09</v>
       </c>
       <c r="CD8" t="n">
-        <v>4.14</v>
+        <v>4</v>
       </c>
       <c r="CE8" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="CF8" t="n">
         <v>2.27</v>
@@ -4049,10 +4049,10 @@
         <v>3.49</v>
       </c>
       <c r="CH8" t="n">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="CI8" t="n">
-        <v>2.4</v>
+        <v>2.39</v>
       </c>
       <c r="CJ8" t="n">
         <v>1.55</v>
@@ -4064,34 +4064,34 @@
         <v>1.67</v>
       </c>
       <c r="CM8" t="n">
-        <v>2.88</v>
+        <v>2.89</v>
       </c>
       <c r="CN8" t="n">
-        <v>2.23</v>
+        <v>2.22</v>
       </c>
       <c r="CO8" t="n">
         <v>1.15</v>
       </c>
       <c r="CP8" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="CQ8" t="n">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="CR8" t="n">
         <v>1.34</v>
       </c>
       <c r="CS8" t="n">
-        <v>2.33</v>
+        <v>2.35</v>
       </c>
       <c r="CT8" t="n">
         <v>3.31</v>
       </c>
       <c r="CU8" t="n">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="CV8" t="n">
-        <v>2.57</v>
+        <v>2.56</v>
       </c>
       <c r="CW8" t="n">
         <v>1.55</v>
@@ -4100,7 +4100,7 @@
         <v>1.46</v>
       </c>
       <c r="CY8" t="n">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="CZ8" t="n">
         <v>2.67</v>
@@ -4115,82 +4115,82 @@
         <v>1.62</v>
       </c>
       <c r="DD8" t="n">
-        <v>2.49</v>
+        <v>2.5</v>
       </c>
       <c r="DE8" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
       <c r="DF8" t="n">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="DG8" t="n">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="DH8" t="n">
-        <v>94.67</v>
+        <v>94.18000000000001</v>
       </c>
       <c r="DI8" t="n">
         <v>0</v>
       </c>
       <c r="DJ8" t="n">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="DK8" t="n">
-        <v>5.38</v>
+        <v>5.36</v>
       </c>
       <c r="DL8" t="n">
-        <v>0.33</v>
+        <v>0.32</v>
       </c>
       <c r="DM8" t="n">
-        <v>51.24</v>
+        <v>50.32</v>
       </c>
       <c r="DN8" t="n">
-        <v>0.24</v>
+        <v>0.22</v>
       </c>
       <c r="DO8" t="n">
-        <v>2.76</v>
+        <v>2.72</v>
       </c>
       <c r="DP8" t="n">
-        <v>12</v>
+        <v>11.91</v>
       </c>
       <c r="DQ8" t="n">
-        <v>12.05</v>
+        <v>11.96</v>
       </c>
       <c r="DR8" t="n">
-        <v>8.19</v>
+        <v>8.41</v>
       </c>
       <c r="DS8" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DT8" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DU8" t="n">
         <v>0</v>
       </c>
       <c r="DV8" t="n">
-        <v>50.29</v>
+        <v>49.68</v>
       </c>
       <c r="DW8" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="DX8" t="n">
-        <v>15.62</v>
+        <v>15.46</v>
       </c>
       <c r="DY8" t="n">
-        <v>10.81</v>
+        <v>10.68</v>
       </c>
       <c r="DZ8" t="n">
-        <v>4.81</v>
+        <v>4.77</v>
       </c>
       <c r="EA8" t="n">
-        <v>21.62</v>
+        <v>21.6</v>
       </c>
       <c r="EB8" t="n">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="EC8" t="n">
-        <v>1.43</v>
+        <v>1.41</v>
       </c>
     </row>
     <row r="9">
@@ -4200,61 +4200,61 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C9" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D9" t="n">
         <v>11</v>
       </c>
       <c r="E9" t="n">
-        <v>0.3</v>
+        <v>0.27</v>
       </c>
       <c r="F9" t="n">
-        <v>2.4</v>
+        <v>2.36</v>
       </c>
       <c r="G9" t="n">
-        <v>2.4</v>
+        <v>2.36</v>
       </c>
       <c r="H9" t="n">
-        <v>79.8</v>
+        <v>79.91</v>
       </c>
       <c r="I9" t="n">
-        <v>0</v>
+        <v>0.09</v>
       </c>
       <c r="J9" t="n">
-        <v>3.1</v>
+        <v>3.09</v>
       </c>
       <c r="K9" t="n">
-        <v>4.4</v>
+        <v>4.36</v>
       </c>
       <c r="L9" t="n">
-        <v>0.5</v>
+        <v>0.45</v>
       </c>
       <c r="M9" t="n">
-        <v>39.3</v>
+        <v>40.45</v>
       </c>
       <c r="N9" t="n">
-        <v>0.7</v>
+        <v>0.73</v>
       </c>
       <c r="O9" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="P9" t="n">
-        <v>16.6</v>
+        <v>16.55</v>
       </c>
       <c r="Q9" t="n">
-        <v>12.3</v>
+        <v>12.55</v>
       </c>
       <c r="R9" t="n">
-        <v>8.300000000000001</v>
+        <v>8.640000000000001</v>
       </c>
       <c r="S9" t="n">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="T9" t="n">
-        <v>1.2</v>
+        <v>1.09</v>
       </c>
       <c r="U9" t="n">
         <v>0</v>
@@ -4266,28 +4266,28 @@
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>45.8</v>
+        <v>45.64</v>
       </c>
       <c r="Y9" t="n">
         <v>0</v>
       </c>
       <c r="Z9" t="n">
-        <v>14.3</v>
+        <v>14.55</v>
       </c>
       <c r="AA9" t="n">
-        <v>9.699999999999999</v>
+        <v>9.91</v>
       </c>
       <c r="AB9" t="n">
-        <v>4.6</v>
+        <v>4.64</v>
       </c>
       <c r="AC9" t="n">
-        <v>18.8</v>
+        <v>19.27</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.51</v>
+        <v>1.53</v>
       </c>
       <c r="AE9" t="n">
-        <v>3.1</v>
+        <v>3.09</v>
       </c>
       <c r="AF9" t="n">
         <v>0</v>
@@ -4371,70 +4371,70 @@
         <v>3.27</v>
       </c>
       <c r="BG9" t="n">
-        <v>2.33</v>
+        <v>2.23</v>
       </c>
       <c r="BH9" t="n">
-        <v>10.05</v>
+        <v>10.18</v>
       </c>
       <c r="BI9" t="n">
-        <v>2.33</v>
+        <v>2.23</v>
       </c>
       <c r="BJ9" t="n">
-        <v>0.71</v>
+        <v>0.68</v>
       </c>
       <c r="BK9" t="n">
-        <v>0.43</v>
+        <v>0.41</v>
       </c>
       <c r="BL9" t="n">
-        <v>0.67</v>
+        <v>0.64</v>
       </c>
       <c r="BM9" t="n">
-        <v>0.52</v>
+        <v>0.5</v>
       </c>
       <c r="BN9" t="n">
-        <v>1.19</v>
+        <v>1.14</v>
       </c>
       <c r="BO9" t="n">
-        <v>1.14</v>
+        <v>1.09</v>
       </c>
       <c r="BP9" t="n">
-        <v>4.86</v>
+        <v>4.91</v>
       </c>
       <c r="BQ9" t="n">
-        <v>5.14</v>
+        <v>5.23</v>
       </c>
       <c r="BR9" t="n">
-        <v>95.23999999999999</v>
+        <v>90.91</v>
       </c>
       <c r="BS9" t="n">
-        <v>71.43000000000001</v>
+        <v>68.18000000000001</v>
       </c>
       <c r="BT9" t="n">
-        <v>42.86</v>
+        <v>40.91</v>
       </c>
       <c r="BU9" t="n">
-        <v>19.05</v>
+        <v>18.18</v>
       </c>
       <c r="BV9" t="n">
-        <v>4.76</v>
+        <v>4.55</v>
       </c>
       <c r="BW9" t="n">
         <v>0</v>
       </c>
       <c r="BX9" t="n">
-        <v>47.62</v>
+        <v>45.45</v>
       </c>
       <c r="BY9" t="n">
-        <v>2.94</v>
+        <v>3.04</v>
       </c>
       <c r="BZ9" t="n">
-        <v>2.99</v>
+        <v>3.08</v>
       </c>
       <c r="CA9" t="n">
         <v>3.5</v>
       </c>
       <c r="CB9" t="n">
-        <v>3.54</v>
+        <v>3.53</v>
       </c>
       <c r="CC9" t="n">
         <v>4.18</v>
@@ -4446,10 +4446,10 @@
         <v>1.37</v>
       </c>
       <c r="CF9" t="n">
-        <v>2.73</v>
+        <v>2.74</v>
       </c>
       <c r="CG9" t="n">
-        <v>2.99</v>
+        <v>2.97</v>
       </c>
       <c r="CH9" t="n">
         <v>1.42</v>
@@ -4461,25 +4461,25 @@
         <v>1.77</v>
       </c>
       <c r="CK9" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="CL9" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="CM9" t="n">
-        <v>2.56</v>
+        <v>2.55</v>
       </c>
       <c r="CN9" t="n">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="CO9" t="n">
         <v>1.28</v>
       </c>
       <c r="CP9" t="n">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="CQ9" t="n">
-        <v>3.27</v>
+        <v>3.28</v>
       </c>
       <c r="CR9" t="n">
         <v>1.39</v>
@@ -4494,7 +4494,7 @@
         <v>1.45</v>
       </c>
       <c r="CV9" t="n">
-        <v>2.09</v>
+        <v>2.08</v>
       </c>
       <c r="CW9" t="n">
         <v>1.81</v>
@@ -4503,64 +4503,64 @@
         <v>1.53</v>
       </c>
       <c r="CY9" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="CZ9" t="n">
-        <v>2.47</v>
+        <v>2.46</v>
       </c>
       <c r="DA9" t="n">
-        <v>2.02</v>
+        <v>2.01</v>
       </c>
       <c r="DB9" t="n">
         <v>1.31</v>
       </c>
       <c r="DC9" t="n">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="DD9" t="n">
-        <v>3.37</v>
+        <v>3.39</v>
       </c>
       <c r="DE9" t="n">
         <v>0.14</v>
       </c>
       <c r="DF9" t="n">
-        <v>2.28</v>
+        <v>2.27</v>
       </c>
       <c r="DG9" t="n">
-        <v>2.48</v>
+        <v>2.45</v>
       </c>
       <c r="DH9" t="n">
-        <v>79.86</v>
+        <v>79.91</v>
       </c>
       <c r="DI9" t="n">
-        <v>0</v>
+        <v>0.04</v>
       </c>
       <c r="DJ9" t="n">
-        <v>3.24</v>
+        <v>3.22</v>
       </c>
       <c r="DK9" t="n">
-        <v>4.33</v>
+        <v>4.32</v>
       </c>
       <c r="DL9" t="n">
-        <v>0.47</v>
+        <v>0.45</v>
       </c>
       <c r="DM9" t="n">
-        <v>41.29</v>
+        <v>41.77</v>
       </c>
       <c r="DN9" t="n">
-        <v>0.95</v>
+        <v>0.96</v>
       </c>
       <c r="DO9" t="n">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="DP9" t="n">
-        <v>16.67</v>
+        <v>16.64</v>
       </c>
       <c r="DQ9" t="n">
-        <v>11.28</v>
+        <v>11.46</v>
       </c>
       <c r="DR9" t="n">
-        <v>8.619999999999999</v>
+        <v>8.779999999999999</v>
       </c>
       <c r="DS9" t="n">
         <v>0</v>
@@ -4572,28 +4572,28 @@
         <v>0</v>
       </c>
       <c r="DV9" t="n">
-        <v>45.72</v>
+        <v>45.64</v>
       </c>
       <c r="DW9" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="DX9" t="n">
-        <v>13.33</v>
+        <v>13.5</v>
       </c>
       <c r="DY9" t="n">
-        <v>9.050000000000001</v>
+        <v>9.18</v>
       </c>
       <c r="DZ9" t="n">
-        <v>4.29</v>
+        <v>4.32</v>
       </c>
       <c r="EA9" t="n">
-        <v>19.19</v>
+        <v>19.41</v>
       </c>
       <c r="EB9" t="n">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="EC9" t="n">
-        <v>3.19</v>
+        <v>3.18</v>
       </c>
     </row>
     <row r="10">
@@ -4603,10 +4603,10 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C10" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D10" t="n">
         <v>11</v>
@@ -4615,49 +4615,49 @@
         <v>0</v>
       </c>
       <c r="F10" t="n">
-        <v>0.8</v>
+        <v>0.82</v>
       </c>
       <c r="G10" t="n">
-        <v>3.1</v>
+        <v>3.18</v>
       </c>
       <c r="H10" t="n">
-        <v>82.09999999999999</v>
+        <v>83.91</v>
       </c>
       <c r="I10" t="n">
-        <v>0.3</v>
+        <v>0.27</v>
       </c>
       <c r="J10" t="n">
-        <v>1.6</v>
+        <v>1.64</v>
       </c>
       <c r="K10" t="n">
-        <v>5.8</v>
+        <v>5.82</v>
       </c>
       <c r="L10" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="M10" t="n">
-        <v>46.8</v>
+        <v>46.64</v>
       </c>
       <c r="N10" t="n">
-        <v>0.8</v>
+        <v>0.82</v>
       </c>
       <c r="O10" t="n">
-        <v>2.7</v>
+        <v>2.64</v>
       </c>
       <c r="P10" t="n">
-        <v>11</v>
+        <v>10.91</v>
       </c>
       <c r="Q10" t="n">
-        <v>11.6</v>
+        <v>11.64</v>
       </c>
       <c r="R10" t="n">
-        <v>8.4</v>
+        <v>8.359999999999999</v>
       </c>
       <c r="S10" t="n">
-        <v>0.6</v>
+        <v>0.73</v>
       </c>
       <c r="T10" t="n">
-        <v>0.5</v>
+        <v>0.55</v>
       </c>
       <c r="U10" t="n">
         <v>0</v>
@@ -4669,28 +4669,28 @@
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>38.3</v>
+        <v>38.45</v>
       </c>
       <c r="Y10" t="n">
         <v>0</v>
       </c>
       <c r="Z10" t="n">
-        <v>11</v>
+        <v>10.55</v>
       </c>
       <c r="AA10" t="n">
-        <v>7.8</v>
+        <v>7.55</v>
       </c>
       <c r="AB10" t="n">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="AC10" t="n">
-        <v>21.5</v>
+        <v>21.36</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.2</v>
+        <v>1.16</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.6</v>
+        <v>1.64</v>
       </c>
       <c r="AF10" t="n">
         <v>0.09</v>
@@ -4774,70 +4774,70 @@
         <v>1.91</v>
       </c>
       <c r="BG10" t="n">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="BH10" t="n">
-        <v>8.76</v>
+        <v>8.859999999999999</v>
       </c>
       <c r="BI10" t="n">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="BJ10" t="n">
-        <v>0.57</v>
+        <v>0.55</v>
       </c>
       <c r="BK10" t="n">
-        <v>0.33</v>
+        <v>0.32</v>
       </c>
       <c r="BL10" t="n">
-        <v>0.48</v>
+        <v>0.5</v>
       </c>
       <c r="BM10" t="n">
-        <v>0.57</v>
+        <v>0.64</v>
       </c>
       <c r="BN10" t="n">
-        <v>1.05</v>
+        <v>1.14</v>
       </c>
       <c r="BO10" t="n">
-        <v>0.9</v>
+        <v>0.86</v>
       </c>
       <c r="BP10" t="n">
+        <v>3.59</v>
+      </c>
+      <c r="BQ10" t="n">
+        <v>5.27</v>
+      </c>
+      <c r="BR10" t="n">
+        <v>72.73</v>
+      </c>
+      <c r="BS10" t="n">
+        <v>54.55</v>
+      </c>
+      <c r="BT10" t="n">
+        <v>45.45</v>
+      </c>
+      <c r="BU10" t="n">
+        <v>18.18</v>
+      </c>
+      <c r="BV10" t="n">
+        <v>9.09</v>
+      </c>
+      <c r="BW10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX10" t="n">
+        <v>50</v>
+      </c>
+      <c r="BY10" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="BZ10" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="CA10" t="n">
+        <v>3.54</v>
+      </c>
+      <c r="CB10" t="n">
         <v>3.62</v>
-      </c>
-      <c r="BQ10" t="n">
-        <v>5.14</v>
-      </c>
-      <c r="BR10" t="n">
-        <v>71.43000000000001</v>
-      </c>
-      <c r="BS10" t="n">
-        <v>52.38</v>
-      </c>
-      <c r="BT10" t="n">
-        <v>42.86</v>
-      </c>
-      <c r="BU10" t="n">
-        <v>19.05</v>
-      </c>
-      <c r="BV10" t="n">
-        <v>9.52</v>
-      </c>
-      <c r="BW10" t="n">
-        <v>0</v>
-      </c>
-      <c r="BX10" t="n">
-        <v>47.62</v>
-      </c>
-      <c r="BY10" t="n">
-        <v>3.53</v>
-      </c>
-      <c r="BZ10" t="n">
-        <v>3.69</v>
-      </c>
-      <c r="CA10" t="n">
-        <v>3.56</v>
-      </c>
-      <c r="CB10" t="n">
-        <v>3.63</v>
       </c>
       <c r="CC10" t="n">
         <v>4.49</v>
@@ -4852,7 +4852,7 @@
         <v>2.79</v>
       </c>
       <c r="CG10" t="n">
-        <v>2.86</v>
+        <v>2.87</v>
       </c>
       <c r="CH10" t="n">
         <v>1.4</v>
@@ -4861,28 +4861,28 @@
         <v>1.89</v>
       </c>
       <c r="CJ10" t="n">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="CK10" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="CL10" t="n">
         <v>2</v>
       </c>
       <c r="CM10" t="n">
-        <v>2.33</v>
+        <v>2.31</v>
       </c>
       <c r="CN10" t="n">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="CO10" t="n">
         <v>1.31</v>
       </c>
       <c r="CP10" t="n">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="CQ10" t="n">
-        <v>3.52</v>
+        <v>3.51</v>
       </c>
       <c r="CR10" t="n">
         <v>1.4</v>
@@ -4897,7 +4897,7 @@
         <v>1.43</v>
       </c>
       <c r="CV10" t="n">
-        <v>2</v>
+        <v>2.01</v>
       </c>
       <c r="CW10" t="n">
         <v>1.87</v>
@@ -4912,28 +4912,28 @@
         <v>2.3</v>
       </c>
       <c r="DA10" t="n">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="DB10" t="n">
         <v>1.33</v>
       </c>
       <c r="DC10" t="n">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="DD10" t="n">
-        <v>3.59</v>
+        <v>3.57</v>
       </c>
       <c r="DE10" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="DF10" t="n">
         <v>1</v>
       </c>
       <c r="DG10" t="n">
-        <v>2.86</v>
+        <v>2.91</v>
       </c>
       <c r="DH10" t="n">
-        <v>82.09</v>
+        <v>83</v>
       </c>
       <c r="DI10" t="n">
         <v>0.14</v>
@@ -4942,28 +4942,28 @@
         <v>1.86</v>
       </c>
       <c r="DK10" t="n">
-        <v>4.76</v>
+        <v>4.82</v>
       </c>
       <c r="DL10" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
       <c r="DM10" t="n">
-        <v>41.86</v>
+        <v>42</v>
       </c>
       <c r="DN10" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.82</v>
       </c>
       <c r="DO10" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="DP10" t="n">
-        <v>11.62</v>
+        <v>11.54</v>
       </c>
       <c r="DQ10" t="n">
         <v>12.1</v>
       </c>
       <c r="DR10" t="n">
-        <v>8.43</v>
+        <v>8.4</v>
       </c>
       <c r="DS10" t="n">
         <v>0</v>
@@ -4975,28 +4975,28 @@
         <v>0</v>
       </c>
       <c r="DV10" t="n">
-        <v>35.67</v>
+        <v>35.86</v>
       </c>
       <c r="DW10" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="DX10" t="n">
-        <v>10</v>
+        <v>9.82</v>
       </c>
       <c r="DY10" t="n">
-        <v>7.09</v>
+        <v>7</v>
       </c>
       <c r="DZ10" t="n">
-        <v>2.91</v>
+        <v>2.82</v>
       </c>
       <c r="EA10" t="n">
-        <v>20.95</v>
+        <v>20.9</v>
       </c>
       <c r="EB10" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="EC10" t="n">
-        <v>1.76</v>
+        <v>1.78</v>
       </c>
     </row>
     <row r="11">
@@ -5006,94 +5006,94 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C11" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D11" t="n">
         <v>10</v>
       </c>
       <c r="E11" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="F11" t="n">
-        <v>1.64</v>
+        <v>1.58</v>
       </c>
       <c r="G11" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="H11" t="n">
-        <v>107.73</v>
+        <v>108.42</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
       </c>
       <c r="J11" t="n">
-        <v>2.73</v>
+        <v>2.67</v>
       </c>
       <c r="K11" t="n">
-        <v>6.55</v>
+        <v>6.5</v>
       </c>
       <c r="L11" t="n">
-        <v>0.73</v>
+        <v>0.67</v>
       </c>
       <c r="M11" t="n">
-        <v>57.64</v>
+        <v>59.92</v>
       </c>
       <c r="N11" t="n">
         <v>1</v>
       </c>
       <c r="O11" t="n">
-        <v>3.09</v>
+        <v>3</v>
       </c>
       <c r="P11" t="n">
-        <v>12.82</v>
+        <v>12.83</v>
       </c>
       <c r="Q11" t="n">
-        <v>11.64</v>
+        <v>12</v>
       </c>
       <c r="R11" t="n">
-        <v>7.36</v>
+        <v>7.33</v>
       </c>
       <c r="S11" t="n">
-        <v>0.91</v>
+        <v>0.83</v>
       </c>
       <c r="T11" t="n">
-        <v>1.64</v>
+        <v>1.5</v>
       </c>
       <c r="U11" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="V11" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="W11" t="n">
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>51.18</v>
+        <v>52</v>
       </c>
       <c r="Y11" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="Z11" t="n">
-        <v>16.82</v>
+        <v>17.08</v>
       </c>
       <c r="AA11" t="n">
-        <v>11.18</v>
+        <v>11.67</v>
       </c>
       <c r="AB11" t="n">
-        <v>5.64</v>
+        <v>5.42</v>
       </c>
       <c r="AC11" t="n">
-        <v>20.09</v>
+        <v>20.25</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.87</v>
+        <v>1.89</v>
       </c>
       <c r="AE11" t="n">
-        <v>2.55</v>
+        <v>2.5</v>
       </c>
       <c r="AF11" t="n">
         <v>0.2</v>
@@ -5177,70 +5177,70 @@
         <v>2.5</v>
       </c>
       <c r="BG11" t="n">
-        <v>2.67</v>
+        <v>2.55</v>
       </c>
       <c r="BH11" t="n">
-        <v>10.57</v>
+        <v>10.64</v>
       </c>
       <c r="BI11" t="n">
-        <v>2.67</v>
+        <v>2.55</v>
       </c>
       <c r="BJ11" t="n">
-        <v>0.71</v>
+        <v>0.68</v>
       </c>
       <c r="BK11" t="n">
-        <v>0.43</v>
+        <v>0.41</v>
       </c>
       <c r="BL11" t="n">
-        <v>0.9</v>
+        <v>0.86</v>
       </c>
       <c r="BM11" t="n">
-        <v>0.62</v>
+        <v>0.59</v>
       </c>
       <c r="BN11" t="n">
-        <v>1.52</v>
+        <v>1.45</v>
       </c>
       <c r="BO11" t="n">
-        <v>1.14</v>
+        <v>1.09</v>
       </c>
       <c r="BP11" t="n">
-        <v>5.05</v>
+        <v>5.09</v>
       </c>
       <c r="BQ11" t="n">
-        <v>5.52</v>
+        <v>5.55</v>
       </c>
       <c r="BR11" t="n">
-        <v>95.23999999999999</v>
+        <v>90.91</v>
       </c>
       <c r="BS11" t="n">
-        <v>66.67</v>
+        <v>63.64</v>
       </c>
       <c r="BT11" t="n">
-        <v>42.86</v>
+        <v>40.91</v>
       </c>
       <c r="BU11" t="n">
-        <v>33.33</v>
+        <v>31.82</v>
       </c>
       <c r="BV11" t="n">
-        <v>14.29</v>
+        <v>13.64</v>
       </c>
       <c r="BW11" t="n">
-        <v>9.52</v>
+        <v>9.09</v>
       </c>
       <c r="BX11" t="n">
-        <v>47.62</v>
+        <v>45.45</v>
       </c>
       <c r="BY11" t="n">
-        <v>1.96</v>
+        <v>1.93</v>
       </c>
       <c r="BZ11" t="n">
-        <v>2.05</v>
+        <v>2.02</v>
       </c>
       <c r="CA11" t="n">
-        <v>3.61</v>
+        <v>3.64</v>
       </c>
       <c r="CB11" t="n">
-        <v>3.71</v>
+        <v>3.73</v>
       </c>
       <c r="CC11" t="n">
         <v>2.45</v>
@@ -5252,7 +5252,7 @@
         <v>1.32</v>
       </c>
       <c r="CF11" t="n">
-        <v>2.56</v>
+        <v>2.55</v>
       </c>
       <c r="CG11" t="n">
         <v>3.08</v>
@@ -5261,25 +5261,25 @@
         <v>1.47</v>
       </c>
       <c r="CI11" t="n">
-        <v>2.13</v>
+        <v>2.12</v>
       </c>
       <c r="CJ11" t="n">
         <v>1.69</v>
       </c>
       <c r="CK11" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="CL11" t="n">
         <v>1.91</v>
       </c>
       <c r="CM11" t="n">
-        <v>2.54</v>
+        <v>2.53</v>
       </c>
       <c r="CN11" t="n">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="CO11" t="n">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="CP11" t="n">
         <v>1.78</v>
@@ -5297,16 +5297,16 @@
         <v>3.22</v>
       </c>
       <c r="CU11" t="n">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="CV11" t="n">
-        <v>2.22</v>
+        <v>2.21</v>
       </c>
       <c r="CW11" t="n">
         <v>1.71</v>
       </c>
       <c r="CX11" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="CY11" t="n">
         <v>1.83</v>
@@ -5315,7 +5315,7 @@
         <v>2.5</v>
       </c>
       <c r="DA11" t="n">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="DB11" t="n">
         <v>1.26</v>
@@ -5327,79 +5327,79 @@
         <v>3.04</v>
       </c>
       <c r="DE11" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DF11" t="n">
-        <v>1.62</v>
+        <v>1.59</v>
       </c>
       <c r="DG11" t="n">
-        <v>3.28</v>
+        <v>3.32</v>
       </c>
       <c r="DH11" t="n">
-        <v>101.53</v>
+        <v>102.18</v>
       </c>
       <c r="DI11" t="n">
         <v>0</v>
       </c>
       <c r="DJ11" t="n">
-        <v>2.72</v>
+        <v>2.68</v>
       </c>
       <c r="DK11" t="n">
-        <v>6.48</v>
+        <v>6.45</v>
       </c>
       <c r="DL11" t="n">
-        <v>0.57</v>
+        <v>0.55</v>
       </c>
       <c r="DM11" t="n">
-        <v>56.05</v>
+        <v>57.37</v>
       </c>
       <c r="DN11" t="n">
         <v>1.05</v>
       </c>
       <c r="DO11" t="n">
-        <v>3.19</v>
+        <v>3.14</v>
       </c>
       <c r="DP11" t="n">
-        <v>13.43</v>
+        <v>13.41</v>
       </c>
       <c r="DQ11" t="n">
-        <v>10.76</v>
+        <v>11</v>
       </c>
       <c r="DR11" t="n">
-        <v>7.81</v>
+        <v>7.77</v>
       </c>
       <c r="DS11" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
       <c r="DT11" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
       <c r="DU11" t="n">
         <v>0</v>
       </c>
       <c r="DV11" t="n">
-        <v>53.05</v>
+        <v>53.41</v>
       </c>
       <c r="DW11" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DX11" t="n">
-        <v>14.81</v>
+        <v>15.04</v>
       </c>
       <c r="DY11" t="n">
-        <v>10</v>
+        <v>10.32</v>
       </c>
       <c r="DZ11" t="n">
-        <v>4.81</v>
+        <v>4.73</v>
       </c>
       <c r="EA11" t="n">
-        <v>21.57</v>
+        <v>21.59</v>
       </c>
       <c r="EB11" t="n">
-        <v>1.67</v>
+        <v>1.69</v>
       </c>
       <c r="EC11" t="n">
-        <v>2.53</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="12">
@@ -5409,91 +5409,91 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C12" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D12" t="n">
         <v>10</v>
       </c>
       <c r="E12" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="F12" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="G12" t="n">
-        <v>2.36</v>
+        <v>2.33</v>
       </c>
       <c r="H12" t="n">
-        <v>96.73</v>
+        <v>97.25</v>
       </c>
       <c r="I12" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="J12" t="n">
-        <v>2.18</v>
+        <v>2.17</v>
       </c>
       <c r="K12" t="n">
-        <v>4.82</v>
+        <v>4.75</v>
       </c>
       <c r="L12" t="n">
-        <v>0.64</v>
+        <v>0.58</v>
       </c>
       <c r="M12" t="n">
-        <v>44.27</v>
+        <v>44.83</v>
       </c>
       <c r="N12" t="n">
-        <v>0.82</v>
+        <v>0.83</v>
       </c>
       <c r="O12" t="n">
-        <v>2.36</v>
+        <v>2.33</v>
       </c>
       <c r="P12" t="n">
-        <v>12</v>
+        <v>12.08</v>
       </c>
       <c r="Q12" t="n">
-        <v>12</v>
+        <v>12.25</v>
       </c>
       <c r="R12" t="n">
-        <v>7.09</v>
+        <v>7.08</v>
       </c>
       <c r="S12" t="n">
-        <v>1.18</v>
+        <v>1.25</v>
       </c>
       <c r="T12" t="n">
-        <v>1.73</v>
+        <v>1.58</v>
       </c>
       <c r="U12" t="n">
-        <v>0.36</v>
+        <v>0.33</v>
       </c>
       <c r="V12" t="n">
-        <v>0.36</v>
+        <v>0.33</v>
       </c>
       <c r="W12" t="n">
         <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>49.91</v>
+        <v>50.17</v>
       </c>
       <c r="Y12" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="Z12" t="n">
-        <v>13.36</v>
+        <v>13.17</v>
       </c>
       <c r="AA12" t="n">
-        <v>8</v>
+        <v>7.92</v>
       </c>
       <c r="AB12" t="n">
-        <v>5.36</v>
+        <v>5.25</v>
       </c>
       <c r="AC12" t="n">
-        <v>20.55</v>
+        <v>20.83</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="AE12" t="n">
         <v>2</v>
@@ -5580,25 +5580,25 @@
         <v>1.9</v>
       </c>
       <c r="BG12" t="n">
-        <v>2.19</v>
+        <v>2.18</v>
       </c>
       <c r="BH12" t="n">
-        <v>9.289999999999999</v>
+        <v>9.32</v>
       </c>
       <c r="BI12" t="n">
-        <v>2.19</v>
+        <v>2.18</v>
       </c>
       <c r="BJ12" t="n">
-        <v>0.76</v>
+        <v>0.73</v>
       </c>
       <c r="BK12" t="n">
-        <v>0.38</v>
+        <v>0.41</v>
       </c>
       <c r="BL12" t="n">
-        <v>0.57</v>
+        <v>0.55</v>
       </c>
       <c r="BM12" t="n">
-        <v>0.48</v>
+        <v>0.5</v>
       </c>
       <c r="BN12" t="n">
         <v>1.05</v>
@@ -5607,22 +5607,22 @@
         <v>1.14</v>
       </c>
       <c r="BP12" t="n">
-        <v>3.95</v>
+        <v>4.05</v>
       </c>
       <c r="BQ12" t="n">
-        <v>5.29</v>
+        <v>5.23</v>
       </c>
       <c r="BR12" t="n">
-        <v>95.23999999999999</v>
+        <v>95.45</v>
       </c>
       <c r="BS12" t="n">
-        <v>71.43000000000001</v>
+        <v>72.73</v>
       </c>
       <c r="BT12" t="n">
-        <v>38.1</v>
+        <v>36.36</v>
       </c>
       <c r="BU12" t="n">
-        <v>14.29</v>
+        <v>13.64</v>
       </c>
       <c r="BV12" t="n">
         <v>0</v>
@@ -5631,19 +5631,19 @@
         <v>0</v>
       </c>
       <c r="BX12" t="n">
-        <v>52.38</v>
+        <v>50</v>
       </c>
       <c r="BY12" t="n">
-        <v>2.71</v>
+        <v>2.72</v>
       </c>
       <c r="BZ12" t="n">
         <v>2.93</v>
       </c>
       <c r="CA12" t="n">
-        <v>3.54</v>
+        <v>3.52</v>
       </c>
       <c r="CB12" t="n">
-        <v>3.67</v>
+        <v>3.65</v>
       </c>
       <c r="CC12" t="n">
         <v>3.9</v>
@@ -5658,13 +5658,13 @@
         <v>2.61</v>
       </c>
       <c r="CG12" t="n">
-        <v>3.03</v>
+        <v>3.01</v>
       </c>
       <c r="CH12" t="n">
         <v>1.45</v>
       </c>
       <c r="CI12" t="n">
-        <v>2.1</v>
+        <v>2.09</v>
       </c>
       <c r="CJ12" t="n">
         <v>1.69</v>
@@ -5673,10 +5673,10 @@
         <v>1.5</v>
       </c>
       <c r="CL12" t="n">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="CM12" t="n">
-        <v>2.43</v>
+        <v>2.42</v>
       </c>
       <c r="CN12" t="n">
         <v>1.88</v>
@@ -5685,19 +5685,19 @@
         <v>1.26</v>
       </c>
       <c r="CP12" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="CQ12" t="n">
-        <v>3.05</v>
+        <v>3.07</v>
       </c>
       <c r="CR12" t="n">
         <v>1.37</v>
       </c>
       <c r="CS12" t="n">
-        <v>2.71</v>
+        <v>2.73</v>
       </c>
       <c r="CT12" t="n">
-        <v>3.17</v>
+        <v>3.15</v>
       </c>
       <c r="CU12" t="n">
         <v>1.48</v>
@@ -5715,7 +5715,7 @@
         <v>1.94</v>
       </c>
       <c r="CZ12" t="n">
-        <v>2.35</v>
+        <v>2.36</v>
       </c>
       <c r="DA12" t="n">
         <v>1.88</v>
@@ -5724,25 +5724,25 @@
         <v>1.28</v>
       </c>
       <c r="DC12" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="DD12" t="n">
-        <v>3.16</v>
+        <v>3.18</v>
       </c>
       <c r="DE12" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="DF12" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="DG12" t="n">
-        <v>2.28</v>
+        <v>2.27</v>
       </c>
       <c r="DH12" t="n">
-        <v>92.29000000000001</v>
+        <v>92.77</v>
       </c>
       <c r="DI12" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="DJ12" t="n">
         <v>2.14</v>
@@ -5751,52 +5751,52 @@
         <v>4.05</v>
       </c>
       <c r="DL12" t="n">
-        <v>0.48</v>
+        <v>0.45</v>
       </c>
       <c r="DM12" t="n">
-        <v>39.28</v>
+        <v>39.82</v>
       </c>
       <c r="DN12" t="n">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="DO12" t="n">
-        <v>1.71</v>
+        <v>1.73</v>
       </c>
       <c r="DP12" t="n">
-        <v>12.52</v>
+        <v>12.54</v>
       </c>
       <c r="DQ12" t="n">
-        <v>12.19</v>
+        <v>12.32</v>
       </c>
       <c r="DR12" t="n">
-        <v>7.67</v>
+        <v>7.63</v>
       </c>
       <c r="DS12" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
       <c r="DT12" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
       <c r="DU12" t="n">
         <v>0</v>
       </c>
       <c r="DV12" t="n">
-        <v>46.91</v>
+        <v>47.18</v>
       </c>
       <c r="DW12" t="n">
         <v>0.09</v>
       </c>
       <c r="DX12" t="n">
-        <v>11.62</v>
+        <v>11.59</v>
       </c>
       <c r="DY12" t="n">
-        <v>7.43</v>
+        <v>7.41</v>
       </c>
       <c r="DZ12" t="n">
-        <v>4.19</v>
+        <v>4.18</v>
       </c>
       <c r="EA12" t="n">
-        <v>20.76</v>
+        <v>20.91</v>
       </c>
       <c r="EB12" t="n">
         <v>1.32</v>
@@ -5812,13 +5812,13 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C13" t="n">
         <v>11</v>
       </c>
       <c r="D13" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E13" t="n">
         <v>0.27</v>
@@ -5905,136 +5905,136 @@
         <v>0</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AH13" t="n">
-        <v>3.3</v>
+        <v>3.36</v>
       </c>
       <c r="AI13" t="n">
-        <v>99.59999999999999</v>
+        <v>98.27</v>
       </c>
       <c r="AJ13" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="AK13" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="AL13" t="n">
-        <v>5.5</v>
+        <v>5.45</v>
       </c>
       <c r="AM13" t="n">
-        <v>0.4</v>
+        <v>0.36</v>
       </c>
       <c r="AN13" t="n">
-        <v>52.7</v>
+        <v>51.55</v>
       </c>
       <c r="AO13" t="n">
-        <v>0.7</v>
+        <v>0.73</v>
       </c>
       <c r="AP13" t="n">
-        <v>2.2</v>
+        <v>2.09</v>
       </c>
       <c r="AQ13" t="n">
-        <v>12.5</v>
+        <v>12.45</v>
       </c>
       <c r="AR13" t="n">
-        <v>10.8</v>
+        <v>10.73</v>
       </c>
       <c r="AS13" t="n">
-        <v>8.6</v>
+        <v>8.73</v>
       </c>
       <c r="AT13" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AU13" t="n">
-        <v>1.4</v>
+        <v>1.45</v>
       </c>
       <c r="AV13" t="n">
-        <v>0.4</v>
+        <v>0.36</v>
       </c>
       <c r="AW13" t="n">
-        <v>0.4</v>
+        <v>0.36</v>
       </c>
       <c r="AX13" t="n">
         <v>0</v>
       </c>
       <c r="AY13" t="n">
-        <v>53.2</v>
+        <v>53.82</v>
       </c>
       <c r="AZ13" t="n">
         <v>0</v>
       </c>
       <c r="BA13" t="n">
-        <v>13.2</v>
+        <v>13.36</v>
       </c>
       <c r="BB13" t="n">
-        <v>9.199999999999999</v>
+        <v>9.18</v>
       </c>
       <c r="BC13" t="n">
-        <v>4</v>
+        <v>4.18</v>
       </c>
       <c r="BD13" t="n">
-        <v>22.3</v>
+        <v>21.82</v>
       </c>
       <c r="BE13" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="BF13" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="BG13" t="n">
-        <v>2.57</v>
+        <v>2.59</v>
       </c>
       <c r="BH13" t="n">
-        <v>9.57</v>
+        <v>9.640000000000001</v>
       </c>
       <c r="BI13" t="n">
-        <v>2.57</v>
+        <v>2.59</v>
       </c>
       <c r="BJ13" t="n">
-        <v>0.76</v>
+        <v>0.73</v>
       </c>
       <c r="BK13" t="n">
-        <v>0.43</v>
+        <v>0.41</v>
       </c>
       <c r="BL13" t="n">
-        <v>0.62</v>
+        <v>0.64</v>
       </c>
       <c r="BM13" t="n">
-        <v>0.76</v>
+        <v>0.82</v>
       </c>
       <c r="BN13" t="n">
-        <v>1.38</v>
+        <v>1.45</v>
       </c>
       <c r="BO13" t="n">
-        <v>1.19</v>
+        <v>1.14</v>
       </c>
       <c r="BP13" t="n">
-        <v>3.9</v>
+        <v>3.86</v>
       </c>
       <c r="BQ13" t="n">
-        <v>5.67</v>
+        <v>5.77</v>
       </c>
       <c r="BR13" t="n">
         <v>100</v>
       </c>
       <c r="BS13" t="n">
-        <v>80.95</v>
+        <v>81.81999999999999</v>
       </c>
       <c r="BT13" t="n">
-        <v>52.38</v>
+        <v>54.55</v>
       </c>
       <c r="BU13" t="n">
-        <v>19.05</v>
+        <v>18.18</v>
       </c>
       <c r="BV13" t="n">
-        <v>4.76</v>
+        <v>4.55</v>
       </c>
       <c r="BW13" t="n">
         <v>0</v>
       </c>
       <c r="BX13" t="n">
-        <v>57.14</v>
+        <v>59.09</v>
       </c>
       <c r="BY13" t="n">
         <v>2.27</v>
@@ -6043,22 +6043,22 @@
         <v>2.36</v>
       </c>
       <c r="CA13" t="n">
-        <v>3.69</v>
+        <v>3.67</v>
       </c>
       <c r="CB13" t="n">
-        <v>3.8</v>
+        <v>3.79</v>
       </c>
       <c r="CC13" t="n">
-        <v>3.99</v>
+        <v>3.82</v>
       </c>
       <c r="CD13" t="n">
-        <v>4.2</v>
+        <v>4.06</v>
       </c>
       <c r="CE13" t="n">
         <v>1.31</v>
       </c>
       <c r="CF13" t="n">
-        <v>2.47</v>
+        <v>2.49</v>
       </c>
       <c r="CG13" t="n">
         <v>3.15</v>
@@ -6073,16 +6073,16 @@
         <v>1.64</v>
       </c>
       <c r="CK13" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="CL13" t="n">
         <v>1.88</v>
       </c>
       <c r="CM13" t="n">
-        <v>2.54</v>
+        <v>2.52</v>
       </c>
       <c r="CN13" t="n">
-        <v>1.96</v>
+        <v>1.94</v>
       </c>
       <c r="CO13" t="n">
         <v>1.22</v>
@@ -6091,7 +6091,7 @@
         <v>1.75</v>
       </c>
       <c r="CQ13" t="n">
-        <v>2.81</v>
+        <v>2.83</v>
       </c>
       <c r="CR13" t="n">
         <v>1.35</v>
@@ -6115,13 +6115,13 @@
         <v>1.54</v>
       </c>
       <c r="CY13" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="CZ13" t="n">
-        <v>2.45</v>
+        <v>2.43</v>
       </c>
       <c r="DA13" t="n">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="DB13" t="n">
         <v>1.24</v>
@@ -6130,76 +6130,76 @@
         <v>1.78</v>
       </c>
       <c r="DD13" t="n">
-        <v>2.87</v>
+        <v>2.89</v>
       </c>
       <c r="DE13" t="n">
         <v>0.14</v>
       </c>
       <c r="DF13" t="n">
-        <v>1.43</v>
+        <v>1.41</v>
       </c>
       <c r="DG13" t="n">
-        <v>3.33</v>
+        <v>3.36</v>
       </c>
       <c r="DH13" t="n">
-        <v>101.09</v>
+        <v>100.36</v>
       </c>
       <c r="DI13" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="DJ13" t="n">
         <v>2</v>
       </c>
       <c r="DK13" t="n">
-        <v>5.24</v>
+        <v>5.22</v>
       </c>
       <c r="DL13" t="n">
-        <v>0.33</v>
+        <v>0.32</v>
       </c>
       <c r="DM13" t="n">
-        <v>53.62</v>
+        <v>53</v>
       </c>
       <c r="DN13" t="n">
-        <v>0.52</v>
+        <v>0.54</v>
       </c>
       <c r="DO13" t="n">
-        <v>1.91</v>
+        <v>1.86</v>
       </c>
       <c r="DP13" t="n">
-        <v>11.76</v>
+        <v>11.77</v>
       </c>
       <c r="DQ13" t="n">
-        <v>11.14</v>
+        <v>11.09</v>
       </c>
       <c r="DR13" t="n">
-        <v>7.43</v>
+        <v>7.55</v>
       </c>
       <c r="DS13" t="n">
-        <v>0.28</v>
+        <v>0.27</v>
       </c>
       <c r="DT13" t="n">
-        <v>0.28</v>
+        <v>0.27</v>
       </c>
       <c r="DU13" t="n">
         <v>0</v>
       </c>
       <c r="DV13" t="n">
-        <v>53.33</v>
+        <v>53.64</v>
       </c>
       <c r="DW13" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="DX13" t="n">
-        <v>14.43</v>
+        <v>14.46</v>
       </c>
       <c r="DY13" t="n">
-        <v>9.949999999999999</v>
+        <v>9.91</v>
       </c>
       <c r="DZ13" t="n">
-        <v>4.48</v>
+        <v>4.55</v>
       </c>
       <c r="EA13" t="n">
-        <v>22.38</v>
+        <v>22.14</v>
       </c>
       <c r="EB13" t="n">
         <v>1.62</v>
@@ -6215,13 +6215,13 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C14" t="n">
         <v>11</v>
       </c>
       <c r="D14" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E14" t="n">
         <v>0.18</v>
@@ -6305,139 +6305,139 @@
         <v>1.82</v>
       </c>
       <c r="AF14" t="n">
-        <v>0.1</v>
+        <v>0.18</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="AH14" t="n">
         <v>2</v>
       </c>
       <c r="AI14" t="n">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="AJ14" t="n">
         <v>0</v>
       </c>
       <c r="AK14" t="n">
-        <v>2.3</v>
+        <v>2.27</v>
       </c>
       <c r="AL14" t="n">
-        <v>4.3</v>
+        <v>4.45</v>
       </c>
       <c r="AM14" t="n">
-        <v>0.6</v>
+        <v>0.64</v>
       </c>
       <c r="AN14" t="n">
-        <v>46.2</v>
+        <v>45.64</v>
       </c>
       <c r="AO14" t="n">
-        <v>0.5</v>
+        <v>0.55</v>
       </c>
       <c r="AP14" t="n">
-        <v>2.3</v>
+        <v>2.45</v>
       </c>
       <c r="AQ14" t="n">
-        <v>11.3</v>
+        <v>11.64</v>
       </c>
       <c r="AR14" t="n">
-        <v>9.699999999999999</v>
+        <v>9.91</v>
       </c>
       <c r="AS14" t="n">
-        <v>7.2</v>
+        <v>7.55</v>
       </c>
       <c r="AT14" t="n">
-        <v>1.6</v>
+        <v>1.45</v>
       </c>
       <c r="AU14" t="n">
-        <v>1.1</v>
+        <v>1.18</v>
       </c>
       <c r="AV14" t="n">
-        <v>0</v>
+        <v>0.09</v>
       </c>
       <c r="AW14" t="n">
-        <v>0</v>
+        <v>0.09</v>
       </c>
       <c r="AX14" t="n">
         <v>0</v>
       </c>
       <c r="AY14" t="n">
-        <v>46.8</v>
+        <v>46.82</v>
       </c>
       <c r="AZ14" t="n">
         <v>0</v>
       </c>
       <c r="BA14" t="n">
-        <v>10.9</v>
+        <v>11</v>
       </c>
       <c r="BB14" t="n">
-        <v>7.1</v>
+        <v>7.27</v>
       </c>
       <c r="BC14" t="n">
-        <v>3.8</v>
+        <v>3.73</v>
       </c>
       <c r="BD14" t="n">
-        <v>21.3</v>
+        <v>21.91</v>
       </c>
       <c r="BE14" t="n">
         <v>1.29</v>
       </c>
       <c r="BF14" t="n">
-        <v>2.3</v>
+        <v>2.27</v>
       </c>
       <c r="BG14" t="n">
-        <v>2.43</v>
+        <v>2.41</v>
       </c>
       <c r="BH14" t="n">
         <v>9.859999999999999</v>
       </c>
       <c r="BI14" t="n">
-        <v>2.43</v>
+        <v>2.41</v>
       </c>
       <c r="BJ14" t="n">
-        <v>0.71</v>
+        <v>0.68</v>
       </c>
       <c r="BK14" t="n">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="BL14" t="n">
-        <v>0.71</v>
+        <v>0.68</v>
       </c>
       <c r="BM14" t="n">
-        <v>0.33</v>
+        <v>0.36</v>
       </c>
       <c r="BN14" t="n">
         <v>1.05</v>
       </c>
       <c r="BO14" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="BP14" t="n">
-        <v>5.05</v>
+        <v>5.09</v>
       </c>
       <c r="BQ14" t="n">
-        <v>4.81</v>
+        <v>4.77</v>
       </c>
       <c r="BR14" t="n">
-        <v>95.23999999999999</v>
+        <v>95.45</v>
       </c>
       <c r="BS14" t="n">
-        <v>71.43000000000001</v>
+        <v>72.73</v>
       </c>
       <c r="BT14" t="n">
-        <v>42.86</v>
+        <v>40.91</v>
       </c>
       <c r="BU14" t="n">
-        <v>28.57</v>
+        <v>27.27</v>
       </c>
       <c r="BV14" t="n">
-        <v>4.76</v>
+        <v>4.55</v>
       </c>
       <c r="BW14" t="n">
         <v>0</v>
       </c>
       <c r="BX14" t="n">
-        <v>57.14</v>
+        <v>54.55</v>
       </c>
       <c r="BY14" t="n">
         <v>2.31</v>
@@ -6446,25 +6446,25 @@
         <v>2.4</v>
       </c>
       <c r="CA14" t="n">
-        <v>3.51</v>
+        <v>3.49</v>
       </c>
       <c r="CB14" t="n">
-        <v>3.53</v>
+        <v>3.52</v>
       </c>
       <c r="CC14" t="n">
-        <v>3.9</v>
+        <v>3.77</v>
       </c>
       <c r="CD14" t="n">
-        <v>4.04</v>
+        <v>3.91</v>
       </c>
       <c r="CE14" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="CF14" t="n">
         <v>2.71</v>
       </c>
       <c r="CG14" t="n">
-        <v>3</v>
+        <v>2.98</v>
       </c>
       <c r="CH14" t="n">
         <v>1.43</v>
@@ -6482,25 +6482,25 @@
         <v>1.9</v>
       </c>
       <c r="CM14" t="n">
-        <v>2.53</v>
+        <v>2.52</v>
       </c>
       <c r="CN14" t="n">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="CO14" t="n">
         <v>1.27</v>
       </c>
       <c r="CP14" t="n">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="CQ14" t="n">
-        <v>3.18</v>
+        <v>3.19</v>
       </c>
       <c r="CR14" t="n">
         <v>1.39</v>
       </c>
       <c r="CS14" t="n">
-        <v>2.86</v>
+        <v>2.87</v>
       </c>
       <c r="CT14" t="n">
         <v>3.07</v>
@@ -6527,88 +6527,88 @@
         <v>1.93</v>
       </c>
       <c r="DB14" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="DC14" t="n">
         <v>1.99</v>
       </c>
       <c r="DD14" t="n">
-        <v>3.37</v>
+        <v>3.38</v>
       </c>
       <c r="DE14" t="n">
-        <v>0.14</v>
+        <v>0.18</v>
       </c>
       <c r="DF14" t="n">
-        <v>1.72</v>
+        <v>1.68</v>
       </c>
       <c r="DG14" t="n">
-        <v>2.24</v>
+        <v>2.22</v>
       </c>
       <c r="DH14" t="n">
-        <v>90.14</v>
+        <v>90.64</v>
       </c>
       <c r="DI14" t="n">
         <v>0</v>
       </c>
       <c r="DJ14" t="n">
-        <v>2.19</v>
+        <v>2.18</v>
       </c>
       <c r="DK14" t="n">
-        <v>4.81</v>
+        <v>4.86</v>
       </c>
       <c r="DL14" t="n">
-        <v>0.33</v>
+        <v>0.36</v>
       </c>
       <c r="DM14" t="n">
-        <v>47</v>
+        <v>46.68</v>
       </c>
       <c r="DN14" t="n">
-        <v>0.43</v>
+        <v>0.46</v>
       </c>
       <c r="DO14" t="n">
-        <v>2.57</v>
+        <v>2.64</v>
       </c>
       <c r="DP14" t="n">
-        <v>11.53</v>
+        <v>11.69</v>
       </c>
       <c r="DQ14" t="n">
-        <v>11.24</v>
+        <v>11.28</v>
       </c>
       <c r="DR14" t="n">
-        <v>7.24</v>
+        <v>7.41</v>
       </c>
       <c r="DS14" t="n">
-        <v>0.05</v>
+        <v>0.09</v>
       </c>
       <c r="DT14" t="n">
-        <v>0.05</v>
+        <v>0.09</v>
       </c>
       <c r="DU14" t="n">
         <v>0</v>
       </c>
       <c r="DV14" t="n">
-        <v>46.67</v>
+        <v>46.68</v>
       </c>
       <c r="DW14" t="n">
         <v>0.09</v>
       </c>
       <c r="DX14" t="n">
-        <v>11.33</v>
+        <v>11.36</v>
       </c>
       <c r="DY14" t="n">
-        <v>7.14</v>
+        <v>7.22</v>
       </c>
       <c r="DZ14" t="n">
-        <v>4.19</v>
+        <v>4.14</v>
       </c>
       <c r="EA14" t="n">
-        <v>19.48</v>
+        <v>19.86</v>
       </c>
       <c r="EB14" t="n">
         <v>1.35</v>
       </c>
       <c r="EC14" t="n">
-        <v>2.05</v>
+        <v>2.04</v>
       </c>
     </row>
     <row r="15">
@@ -6846,7 +6846,7 @@
         <v>2.86</v>
       </c>
       <c r="BZ15" t="n">
-        <v>3.08</v>
+        <v>3.07</v>
       </c>
       <c r="CA15" t="n">
         <v>3.43</v>
@@ -6900,16 +6900,16 @@
         <v>3.48</v>
       </c>
       <c r="CR15" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="CS15" t="n">
-        <v>2.96</v>
+        <v>2.95</v>
       </c>
       <c r="CT15" t="n">
-        <v>3</v>
+        <v>3.01</v>
       </c>
       <c r="CU15" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="CV15" t="n">
         <v>2.07</v>
@@ -7021,13 +7021,13 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C16" t="n">
         <v>10</v>
       </c>
       <c r="D16" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E16" t="n">
         <v>0.3</v>
@@ -7111,52 +7111,52 @@
         <v>1.5</v>
       </c>
       <c r="AF16" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="AH16" t="n">
-        <v>2.64</v>
+        <v>2.83</v>
       </c>
       <c r="AI16" t="n">
-        <v>112.18</v>
+        <v>110.5</v>
       </c>
       <c r="AJ16" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="AK16" t="n">
-        <v>3</v>
+        <v>2.92</v>
       </c>
       <c r="AL16" t="n">
-        <v>5.18</v>
+        <v>5.5</v>
       </c>
       <c r="AM16" t="n">
-        <v>0.55</v>
+        <v>0.5</v>
       </c>
       <c r="AN16" t="n">
-        <v>51.64</v>
+        <v>51.67</v>
       </c>
       <c r="AO16" t="n">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="AP16" t="n">
-        <v>2.55</v>
+        <v>2.67</v>
       </c>
       <c r="AQ16" t="n">
-        <v>13.36</v>
+        <v>13.5</v>
       </c>
       <c r="AR16" t="n">
-        <v>8.82</v>
+        <v>9.42</v>
       </c>
       <c r="AS16" t="n">
-        <v>6.09</v>
+        <v>6.33</v>
       </c>
       <c r="AT16" t="n">
-        <v>0.91</v>
+        <v>0.83</v>
       </c>
       <c r="AU16" t="n">
-        <v>1.27</v>
+        <v>1.17</v>
       </c>
       <c r="AV16" t="n">
         <v>0</v>
@@ -7168,82 +7168,82 @@
         <v>0</v>
       </c>
       <c r="AY16" t="n">
-        <v>54.91</v>
+        <v>55</v>
       </c>
       <c r="AZ16" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="BA16" t="n">
-        <v>14.27</v>
+        <v>14.17</v>
       </c>
       <c r="BB16" t="n">
-        <v>9.27</v>
+        <v>9.42</v>
       </c>
       <c r="BC16" t="n">
-        <v>5</v>
+        <v>4.75</v>
       </c>
       <c r="BD16" t="n">
-        <v>20.36</v>
+        <v>19.58</v>
       </c>
       <c r="BE16" t="n">
-        <v>1.63</v>
+        <v>1.6</v>
       </c>
       <c r="BF16" t="n">
-        <v>2.91</v>
+        <v>2.83</v>
       </c>
       <c r="BG16" t="n">
-        <v>2.33</v>
+        <v>2.23</v>
       </c>
       <c r="BH16" t="n">
-        <v>9.33</v>
+        <v>9.5</v>
       </c>
       <c r="BI16" t="n">
-        <v>2.33</v>
+        <v>2.23</v>
       </c>
       <c r="BJ16" t="n">
-        <v>0.52</v>
+        <v>0.5</v>
       </c>
       <c r="BK16" t="n">
-        <v>0.38</v>
+        <v>0.36</v>
       </c>
       <c r="BL16" t="n">
-        <v>1.05</v>
+        <v>1</v>
       </c>
       <c r="BM16" t="n">
-        <v>0.38</v>
+        <v>0.36</v>
       </c>
       <c r="BN16" t="n">
-        <v>1.43</v>
+        <v>1.36</v>
       </c>
       <c r="BO16" t="n">
-        <v>0.9</v>
+        <v>0.86</v>
       </c>
       <c r="BP16" t="n">
-        <v>4.62</v>
+        <v>4.68</v>
       </c>
       <c r="BQ16" t="n">
-        <v>4.71</v>
+        <v>4.82</v>
       </c>
       <c r="BR16" t="n">
-        <v>95.23999999999999</v>
+        <v>90.91</v>
       </c>
       <c r="BS16" t="n">
-        <v>76.19</v>
+        <v>72.73</v>
       </c>
       <c r="BT16" t="n">
-        <v>28.57</v>
+        <v>27.27</v>
       </c>
       <c r="BU16" t="n">
-        <v>19.05</v>
+        <v>18.18</v>
       </c>
       <c r="BV16" t="n">
-        <v>14.29</v>
+        <v>13.64</v>
       </c>
       <c r="BW16" t="n">
         <v>0</v>
       </c>
       <c r="BX16" t="n">
-        <v>42.86</v>
+        <v>40.91</v>
       </c>
       <c r="BY16" t="n">
         <v>1.35</v>
@@ -7252,55 +7252,55 @@
         <v>1.42</v>
       </c>
       <c r="CA16" t="n">
-        <v>4.24</v>
+        <v>4.2</v>
       </c>
       <c r="CB16" t="n">
-        <v>4.44</v>
+        <v>4.4</v>
       </c>
       <c r="CC16" t="n">
         <v>1.89</v>
       </c>
       <c r="CD16" t="n">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="CE16" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="CF16" t="n">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="CG16" t="n">
-        <v>3.2</v>
+        <v>3.17</v>
       </c>
       <c r="CH16" t="n">
         <v>1.5</v>
       </c>
       <c r="CI16" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="CJ16" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="CK16" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="CL16" t="n">
         <v>1.94</v>
       </c>
-      <c r="CJ16" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="CK16" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="CL16" t="n">
-        <v>1.93</v>
-      </c>
       <c r="CM16" t="n">
-        <v>2.5</v>
+        <v>2.49</v>
       </c>
       <c r="CN16" t="n">
         <v>1.95</v>
       </c>
       <c r="CO16" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="CP16" t="n">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="CQ16" t="n">
-        <v>2.77</v>
+        <v>2.81</v>
       </c>
       <c r="CR16" t="n">
         <v>1.36</v>
@@ -7333,88 +7333,88 @@
         <v>1.95</v>
       </c>
       <c r="DB16" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="DC16" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="DD16" t="n">
-        <v>2.94</v>
+        <v>2.98</v>
       </c>
       <c r="DE16" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
       <c r="DF16" t="n">
-        <v>1.57</v>
+        <v>1.59</v>
       </c>
       <c r="DG16" t="n">
-        <v>3.05</v>
+        <v>3.13</v>
       </c>
       <c r="DH16" t="n">
-        <v>108</v>
+        <v>107.27</v>
       </c>
       <c r="DI16" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="DJ16" t="n">
-        <v>2.29</v>
+        <v>2.27</v>
       </c>
       <c r="DK16" t="n">
-        <v>5.71</v>
+        <v>5.86</v>
       </c>
       <c r="DL16" t="n">
-        <v>0.53</v>
+        <v>0.5</v>
       </c>
       <c r="DM16" t="n">
-        <v>53.76</v>
+        <v>53.68</v>
       </c>
       <c r="DN16" t="n">
-        <v>0.71</v>
+        <v>0.68</v>
       </c>
       <c r="DO16" t="n">
-        <v>2.67</v>
+        <v>2.73</v>
       </c>
       <c r="DP16" t="n">
-        <v>12.86</v>
+        <v>12.95</v>
       </c>
       <c r="DQ16" t="n">
-        <v>9.289999999999999</v>
+        <v>9.59</v>
       </c>
       <c r="DR16" t="n">
-        <v>5.71</v>
+        <v>5.86</v>
       </c>
       <c r="DS16" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="DT16" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="DU16" t="n">
         <v>0</v>
       </c>
       <c r="DV16" t="n">
-        <v>53.62</v>
+        <v>53.73</v>
       </c>
       <c r="DW16" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="DX16" t="n">
-        <v>15.52</v>
+        <v>15.41</v>
       </c>
       <c r="DY16" t="n">
-        <v>9.710000000000001</v>
+        <v>9.77</v>
       </c>
       <c r="DZ16" t="n">
-        <v>5.81</v>
+        <v>5.64</v>
       </c>
       <c r="EA16" t="n">
-        <v>20.24</v>
+        <v>19.82</v>
       </c>
       <c r="EB16" t="n">
-        <v>1.78</v>
+        <v>1.75</v>
       </c>
       <c r="EC16" t="n">
-        <v>2.24</v>
+        <v>2.23</v>
       </c>
     </row>
     <row r="17">
@@ -7424,13 +7424,13 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C17" t="n">
         <v>10</v>
       </c>
       <c r="D17" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
@@ -7514,139 +7514,139 @@
         <v>1.4</v>
       </c>
       <c r="AF17" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AH17" t="n">
-        <v>2.36</v>
+        <v>2.17</v>
       </c>
       <c r="AI17" t="n">
-        <v>95.64</v>
+        <v>93.5</v>
       </c>
       <c r="AJ17" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="AK17" t="n">
-        <v>1.82</v>
+        <v>1.92</v>
       </c>
       <c r="AL17" t="n">
+        <v>4.17</v>
+      </c>
+      <c r="AM17" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>47</v>
+      </c>
+      <c r="AO17" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="AP17" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AQ17" t="n">
+        <v>12.17</v>
+      </c>
+      <c r="AR17" t="n">
+        <v>10.92</v>
+      </c>
+      <c r="AS17" t="n">
+        <v>8.83</v>
+      </c>
+      <c r="AT17" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AU17" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AV17" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="AW17" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="AX17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY17" t="n">
+        <v>47.92</v>
+      </c>
+      <c r="AZ17" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="BA17" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BB17" t="n">
+        <v>6.92</v>
+      </c>
+      <c r="BC17" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="BD17" t="n">
+        <v>19.17</v>
+      </c>
+      <c r="BE17" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="BF17" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="BG17" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="BH17" t="n">
+        <v>9.73</v>
+      </c>
+      <c r="BI17" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="BJ17" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="BK17" t="n">
+        <v>0.59</v>
+      </c>
+      <c r="BL17" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="BM17" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="BN17" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="BO17" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="BP17" t="n">
+        <v>3.64</v>
+      </c>
+      <c r="BQ17" t="n">
+        <v>5.45</v>
+      </c>
+      <c r="BR17" t="n">
+        <v>90.91</v>
+      </c>
+      <c r="BS17" t="n">
+        <v>86.36</v>
+      </c>
+      <c r="BT17" t="n">
+        <v>50</v>
+      </c>
+      <c r="BU17" t="n">
+        <v>36.36</v>
+      </c>
+      <c r="BV17" t="n">
+        <v>22.73</v>
+      </c>
+      <c r="BW17" t="n">
         <v>4.55</v>
       </c>
-      <c r="AM17" t="n">
-        <v>0.18</v>
-      </c>
-      <c r="AN17" t="n">
-        <v>48.45</v>
-      </c>
-      <c r="AO17" t="n">
-        <v>0.45</v>
-      </c>
-      <c r="AP17" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AQ17" t="n">
-        <v>12.09</v>
-      </c>
-      <c r="AR17" t="n">
-        <v>10.91</v>
-      </c>
-      <c r="AS17" t="n">
-        <v>8.91</v>
-      </c>
-      <c r="AT17" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AU17" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AV17" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="AW17" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="AX17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY17" t="n">
-        <v>49.73</v>
-      </c>
-      <c r="AZ17" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="BA17" t="n">
-        <v>11</v>
-      </c>
-      <c r="BB17" t="n">
-        <v>7.45</v>
-      </c>
-      <c r="BC17" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="BD17" t="n">
-        <v>20.18</v>
-      </c>
-      <c r="BE17" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="BF17" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="BG17" t="n">
-        <v>2.76</v>
-      </c>
-      <c r="BH17" t="n">
-        <v>9.859999999999999</v>
-      </c>
-      <c r="BI17" t="n">
-        <v>2.76</v>
-      </c>
-      <c r="BJ17" t="n">
-        <v>0.76</v>
-      </c>
-      <c r="BK17" t="n">
-        <v>0.52</v>
-      </c>
-      <c r="BL17" t="n">
-        <v>0.76</v>
-      </c>
-      <c r="BM17" t="n">
-        <v>0.71</v>
-      </c>
-      <c r="BN17" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="BO17" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="BP17" t="n">
-        <v>3.67</v>
-      </c>
-      <c r="BQ17" t="n">
-        <v>5.52</v>
-      </c>
-      <c r="BR17" t="n">
-        <v>90.48</v>
-      </c>
-      <c r="BS17" t="n">
-        <v>85.70999999999999</v>
-      </c>
-      <c r="BT17" t="n">
-        <v>47.62</v>
-      </c>
-      <c r="BU17" t="n">
-        <v>33.33</v>
-      </c>
-      <c r="BV17" t="n">
-        <v>19.05</v>
-      </c>
-      <c r="BW17" t="n">
-        <v>0</v>
-      </c>
       <c r="BX17" t="n">
-        <v>66.67</v>
+        <v>68.18000000000001</v>
       </c>
       <c r="BY17" t="n">
         <v>3.07</v>
@@ -7655,34 +7655,34 @@
         <v>3.32</v>
       </c>
       <c r="CA17" t="n">
-        <v>3.73</v>
+        <v>3.79</v>
       </c>
       <c r="CB17" t="n">
-        <v>3.81</v>
+        <v>3.87</v>
       </c>
       <c r="CC17" t="n">
-        <v>4.19</v>
+        <v>4.42</v>
       </c>
       <c r="CD17" t="n">
-        <v>4.73</v>
+        <v>4.93</v>
       </c>
       <c r="CE17" t="n">
         <v>1.3</v>
       </c>
       <c r="CF17" t="n">
-        <v>2.47</v>
+        <v>2.46</v>
       </c>
       <c r="CG17" t="n">
-        <v>3.29</v>
+        <v>3.3</v>
       </c>
       <c r="CH17" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="CI17" t="n">
-        <v>2.18</v>
+        <v>2.17</v>
       </c>
       <c r="CJ17" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="CK17" t="n">
         <v>1.43</v>
@@ -7691,25 +7691,25 @@
         <v>1.79</v>
       </c>
       <c r="CM17" t="n">
-        <v>2.66</v>
+        <v>2.67</v>
       </c>
       <c r="CN17" t="n">
         <v>2.06</v>
       </c>
       <c r="CO17" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="CP17" t="n">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="CQ17" t="n">
-        <v>2.74</v>
+        <v>2.71</v>
       </c>
       <c r="CR17" t="n">
         <v>1.35</v>
       </c>
       <c r="CS17" t="n">
-        <v>2.57</v>
+        <v>2.56</v>
       </c>
       <c r="CT17" t="n">
         <v>3.24</v>
@@ -7718,10 +7718,10 @@
         <v>1.53</v>
       </c>
       <c r="CV17" t="n">
-        <v>2.31</v>
+        <v>2.3</v>
       </c>
       <c r="CW17" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="CX17" t="n">
         <v>1.52</v>
@@ -7736,88 +7736,88 @@
         <v>2.05</v>
       </c>
       <c r="DB17" t="n">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="DC17" t="n">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="DD17" t="n">
-        <v>2.85</v>
+        <v>2.84</v>
       </c>
       <c r="DE17" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="DF17" t="n">
         <v>1.14</v>
       </c>
       <c r="DG17" t="n">
-        <v>2.19</v>
+        <v>2.09</v>
       </c>
       <c r="DH17" t="n">
-        <v>95.14</v>
+        <v>94</v>
       </c>
       <c r="DI17" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="DJ17" t="n">
-        <v>1.72</v>
+        <v>1.77</v>
       </c>
       <c r="DK17" t="n">
-        <v>4.19</v>
+        <v>4</v>
       </c>
       <c r="DL17" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
       <c r="DM17" t="n">
-        <v>45.24</v>
+        <v>44.59</v>
       </c>
       <c r="DN17" t="n">
-        <v>0.47</v>
+        <v>0.54</v>
       </c>
       <c r="DO17" t="n">
-        <v>1.67</v>
+        <v>1.59</v>
       </c>
       <c r="DP17" t="n">
-        <v>11.24</v>
+        <v>11.32</v>
       </c>
       <c r="DQ17" t="n">
-        <v>11.95</v>
+        <v>11.91</v>
       </c>
       <c r="DR17" t="n">
-        <v>9.48</v>
+        <v>9.41</v>
       </c>
       <c r="DS17" t="n">
-        <v>0.24</v>
+        <v>0.23</v>
       </c>
       <c r="DT17" t="n">
-        <v>0.24</v>
+        <v>0.23</v>
       </c>
       <c r="DU17" t="n">
         <v>0</v>
       </c>
       <c r="DV17" t="n">
-        <v>47.67</v>
+        <v>46.77</v>
       </c>
       <c r="DW17" t="n">
         <v>0.09</v>
       </c>
       <c r="DX17" t="n">
-        <v>11.67</v>
+        <v>11.36</v>
       </c>
       <c r="DY17" t="n">
-        <v>7.52</v>
+        <v>7.23</v>
       </c>
       <c r="DZ17" t="n">
-        <v>4.15</v>
+        <v>4.13</v>
       </c>
       <c r="EA17" t="n">
-        <v>20.76</v>
+        <v>20.18</v>
       </c>
       <c r="EB17" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="EC17" t="n">
-        <v>1.53</v>
+        <v>1.59</v>
       </c>
     </row>
   </sheetData>

--- a/data/teams/leagues/Averages_Belgium_Pro_League_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Belgium_Pro_League_2025-2026.xlsx
@@ -1848,7 +1848,7 @@
         <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>65.27</v>
+        <v>65.18000000000001</v>
       </c>
       <c r="Y3" t="n">
         <v>0.18</v>
@@ -2154,7 +2154,7 @@
         <v>0</v>
       </c>
       <c r="DV3" t="n">
-        <v>62.22</v>
+        <v>62.18</v>
       </c>
       <c r="DW3" t="n">
         <v>0.09</v>
@@ -2332,7 +2332,7 @@
         <v>0</v>
       </c>
       <c r="AY4" t="n">
-        <v>43.18</v>
+        <v>43.09</v>
       </c>
       <c r="AZ4" t="n">
         <v>0.36</v>
@@ -2557,7 +2557,7 @@
         <v>0</v>
       </c>
       <c r="DV4" t="n">
-        <v>46.54</v>
+        <v>46.5</v>
       </c>
       <c r="DW4" t="n">
         <v>0.18</v>
@@ -5072,7 +5072,7 @@
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>52</v>
+        <v>52.08</v>
       </c>
       <c r="Y11" t="n">
         <v>0.08</v>
@@ -5378,7 +5378,7 @@
         <v>0</v>
       </c>
       <c r="DV11" t="n">
-        <v>53.41</v>
+        <v>53.45</v>
       </c>
       <c r="DW11" t="n">
         <v>0.13</v>
@@ -7571,7 +7571,7 @@
         <v>0</v>
       </c>
       <c r="AY17" t="n">
-        <v>47.92</v>
+        <v>48</v>
       </c>
       <c r="AZ17" t="n">
         <v>0.08</v>
@@ -7796,7 +7796,7 @@
         <v>0</v>
       </c>
       <c r="DV17" t="n">
-        <v>46.77</v>
+        <v>46.82</v>
       </c>
       <c r="DW17" t="n">
         <v>0.09</v>

--- a/data/teams/leagues/Averages_Belgium_Pro_League_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Belgium_Pro_League_2025-2026.xlsx
@@ -1379,10 +1379,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D2" t="n">
         <v>11</v>
@@ -1391,82 +1391,82 @@
         <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="G2" t="n">
-        <v>2.91</v>
+        <v>2.67</v>
       </c>
       <c r="H2" t="n">
-        <v>109.82</v>
+        <v>107.33</v>
       </c>
       <c r="I2" t="n">
-        <v>0</v>
+        <v>0.08</v>
       </c>
       <c r="J2" t="n">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="K2" t="n">
-        <v>4.91</v>
+        <v>4.67</v>
       </c>
       <c r="L2" t="n">
-        <v>0.45</v>
+        <v>0.42</v>
       </c>
       <c r="M2" t="n">
-        <v>48.82</v>
+        <v>47.92</v>
       </c>
       <c r="N2" t="n">
-        <v>0.45</v>
+        <v>0.5</v>
       </c>
       <c r="O2" t="n">
         <v>2</v>
       </c>
       <c r="P2" t="n">
-        <v>9</v>
+        <v>9.08</v>
       </c>
       <c r="Q2" t="n">
-        <v>13.64</v>
+        <v>13.58</v>
       </c>
       <c r="R2" t="n">
-        <v>6.91</v>
+        <v>6.92</v>
       </c>
       <c r="S2" t="n">
-        <v>2</v>
+        <v>2.17</v>
       </c>
       <c r="T2" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="U2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="V2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="W2" t="n">
+        <v>0</v>
+      </c>
+      <c r="X2" t="n">
+        <v>49.58</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>13.75</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>9.08</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>4.67</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>23.42</v>
+      </c>
+      <c r="AD2" t="n">
         <v>1.55</v>
       </c>
-      <c r="U2" t="n">
-        <v>0.55</v>
-      </c>
-      <c r="V2" t="n">
-        <v>0.55</v>
-      </c>
-      <c r="W2" t="n">
-        <v>0</v>
-      </c>
-      <c r="X2" t="n">
-        <v>51.36</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>14.73</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>9.640000000000001</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>5.09</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>23.82</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>1.64</v>
-      </c>
       <c r="AE2" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AF2" t="n">
         <v>0.18</v>
@@ -1550,70 +1550,70 @@
         <v>2.55</v>
       </c>
       <c r="BG2" t="n">
-        <v>2.68</v>
+        <v>2.74</v>
       </c>
       <c r="BH2" t="n">
-        <v>10.14</v>
+        <v>10</v>
       </c>
       <c r="BI2" t="n">
-        <v>2.68</v>
+        <v>2.74</v>
       </c>
       <c r="BJ2" t="n">
-        <v>0.64</v>
+        <v>0.61</v>
       </c>
       <c r="BK2" t="n">
-        <v>0.95</v>
+        <v>1</v>
       </c>
       <c r="BL2" t="n">
-        <v>0.55</v>
+        <v>0.52</v>
       </c>
       <c r="BM2" t="n">
-        <v>0.55</v>
+        <v>0.61</v>
       </c>
       <c r="BN2" t="n">
-        <v>1.09</v>
+        <v>1.13</v>
       </c>
       <c r="BO2" t="n">
-        <v>1.59</v>
+        <v>1.61</v>
       </c>
       <c r="BP2" t="n">
-        <v>4.55</v>
+        <v>4.52</v>
       </c>
       <c r="BQ2" t="n">
-        <v>5.55</v>
+        <v>5.43</v>
       </c>
       <c r="BR2" t="n">
-        <v>90.91</v>
+        <v>91.3</v>
       </c>
       <c r="BS2" t="n">
-        <v>90.91</v>
+        <v>91.3</v>
       </c>
       <c r="BT2" t="n">
-        <v>40.91</v>
+        <v>43.48</v>
       </c>
       <c r="BU2" t="n">
-        <v>22.73</v>
+        <v>26.09</v>
       </c>
       <c r="BV2" t="n">
-        <v>18.18</v>
+        <v>17.39</v>
       </c>
       <c r="BW2" t="n">
-        <v>4.55</v>
+        <v>4.35</v>
       </c>
       <c r="BX2" t="n">
-        <v>63.64</v>
+        <v>60.87</v>
       </c>
       <c r="BY2" t="n">
-        <v>2.37</v>
+        <v>2.33</v>
       </c>
       <c r="BZ2" t="n">
-        <v>2.45</v>
+        <v>2.42</v>
       </c>
       <c r="CA2" t="n">
         <v>3.54</v>
       </c>
       <c r="CB2" t="n">
-        <v>3.68</v>
+        <v>3.67</v>
       </c>
       <c r="CC2" t="n">
         <v>3.43</v>
@@ -1634,7 +1634,7 @@
         <v>1.48</v>
       </c>
       <c r="CI2" t="n">
-        <v>2.19</v>
+        <v>2.18</v>
       </c>
       <c r="CJ2" t="n">
         <v>1.65</v>
@@ -1643,7 +1643,7 @@
         <v>1.43</v>
       </c>
       <c r="CL2" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="CM2" t="n">
         <v>2.62</v>
@@ -1664,16 +1664,16 @@
         <v>1.36</v>
       </c>
       <c r="CS2" t="n">
-        <v>2.63</v>
+        <v>2.65</v>
       </c>
       <c r="CT2" t="n">
-        <v>3.21</v>
+        <v>3.19</v>
       </c>
       <c r="CU2" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="CV2" t="n">
-        <v>2.31</v>
+        <v>2.3</v>
       </c>
       <c r="CW2" t="n">
         <v>1.67</v>
@@ -1694,10 +1694,10 @@
         <v>1.24</v>
       </c>
       <c r="DC2" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="DD2" t="n">
-        <v>2.88</v>
+        <v>2.91</v>
       </c>
       <c r="DE2" t="n">
         <v>0.09</v>
@@ -1706,73 +1706,73 @@
         <v>1.09</v>
       </c>
       <c r="DG2" t="n">
-        <v>2.59</v>
+        <v>2.48</v>
       </c>
       <c r="DH2" t="n">
-        <v>107.04</v>
+        <v>105.87</v>
       </c>
       <c r="DI2" t="n">
-        <v>0.09</v>
+        <v>0.13</v>
       </c>
       <c r="DJ2" t="n">
-        <v>2.04</v>
+        <v>2.09</v>
       </c>
       <c r="DK2" t="n">
-        <v>4.73</v>
+        <v>4.61</v>
       </c>
       <c r="DL2" t="n">
-        <v>0.55</v>
+        <v>0.53</v>
       </c>
       <c r="DM2" t="n">
-        <v>49.78</v>
+        <v>49.26</v>
       </c>
       <c r="DN2" t="n">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="DO2" t="n">
         <v>2.13</v>
       </c>
       <c r="DP2" t="n">
-        <v>10.72</v>
+        <v>10.69</v>
       </c>
       <c r="DQ2" t="n">
         <v>12.82</v>
       </c>
       <c r="DR2" t="n">
-        <v>7.23</v>
+        <v>7.22</v>
       </c>
       <c r="DS2" t="n">
-        <v>0.28</v>
+        <v>0.26</v>
       </c>
       <c r="DT2" t="n">
-        <v>0.28</v>
+        <v>0.26</v>
       </c>
       <c r="DU2" t="n">
         <v>0</v>
       </c>
       <c r="DV2" t="n">
-        <v>49.14</v>
+        <v>48.3</v>
       </c>
       <c r="DW2" t="n">
-        <v>0.09</v>
+        <v>0.13</v>
       </c>
       <c r="DX2" t="n">
-        <v>13.32</v>
+        <v>12.87</v>
       </c>
       <c r="DY2" t="n">
-        <v>9.140000000000001</v>
+        <v>8.869999999999999</v>
       </c>
       <c r="DZ2" t="n">
-        <v>4.18</v>
+        <v>4</v>
       </c>
       <c r="EA2" t="n">
-        <v>22.91</v>
+        <v>22.74</v>
       </c>
       <c r="EB2" t="n">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="EC2" t="n">
-        <v>1.91</v>
+        <v>1.87</v>
       </c>
     </row>
     <row r="3">
@@ -1782,13 +1782,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C3" t="n">
         <v>11</v>
       </c>
       <c r="D3" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E3" t="n">
         <v>0.09</v>
@@ -1872,52 +1872,52 @@
         <v>1.18</v>
       </c>
       <c r="AF3" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="AH3" t="n">
-        <v>3.64</v>
+        <v>3.5</v>
       </c>
       <c r="AI3" t="n">
-        <v>107.45</v>
+        <v>107.08</v>
       </c>
       <c r="AJ3" t="n">
-        <v>-0.09</v>
+        <v>0</v>
       </c>
       <c r="AK3" t="n">
-        <v>1.55</v>
+        <v>1.58</v>
       </c>
       <c r="AL3" t="n">
-        <v>5.91</v>
+        <v>5.83</v>
       </c>
       <c r="AM3" t="n">
-        <v>0.27</v>
+        <v>0.33</v>
       </c>
       <c r="AN3" t="n">
-        <v>56.55</v>
+        <v>56.67</v>
       </c>
       <c r="AO3" t="n">
-        <v>0.45</v>
+        <v>0.5</v>
       </c>
       <c r="AP3" t="n">
-        <v>2.27</v>
+        <v>2.33</v>
       </c>
       <c r="AQ3" t="n">
-        <v>9.359999999999999</v>
+        <v>9.5</v>
       </c>
       <c r="AR3" t="n">
-        <v>11.45</v>
+        <v>11.5</v>
       </c>
       <c r="AS3" t="n">
-        <v>7.91</v>
+        <v>7.92</v>
       </c>
       <c r="AT3" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AU3" t="n">
-        <v>1.73</v>
+        <v>1.58</v>
       </c>
       <c r="AV3" t="n">
         <v>0</v>
@@ -1929,82 +1929,82 @@
         <v>0</v>
       </c>
       <c r="AY3" t="n">
-        <v>59.18</v>
+        <v>60.08</v>
       </c>
       <c r="AZ3" t="n">
         <v>0</v>
       </c>
       <c r="BA3" t="n">
-        <v>15.45</v>
+        <v>14.83</v>
       </c>
       <c r="BB3" t="n">
-        <v>9.91</v>
+        <v>9.58</v>
       </c>
       <c r="BC3" t="n">
-        <v>5.55</v>
+        <v>5.25</v>
       </c>
       <c r="BD3" t="n">
-        <v>17.91</v>
+        <v>18.5</v>
       </c>
       <c r="BE3" t="n">
-        <v>1.77</v>
+        <v>1.72</v>
       </c>
       <c r="BF3" t="n">
-        <v>1.55</v>
+        <v>1.58</v>
       </c>
       <c r="BG3" t="n">
-        <v>3.18</v>
+        <v>3.09</v>
       </c>
       <c r="BH3" t="n">
-        <v>10.77</v>
+        <v>10.74</v>
       </c>
       <c r="BI3" t="n">
-        <v>3.18</v>
+        <v>3.09</v>
       </c>
       <c r="BJ3" t="n">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="BK3" t="n">
-        <v>0.55</v>
+        <v>0.52</v>
       </c>
       <c r="BL3" t="n">
-        <v>0.91</v>
+        <v>0.87</v>
       </c>
       <c r="BM3" t="n">
-        <v>1</v>
+        <v>0.96</v>
       </c>
       <c r="BN3" t="n">
-        <v>1.91</v>
+        <v>1.83</v>
       </c>
       <c r="BO3" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="BP3" t="n">
-        <v>4.59</v>
+        <v>4.74</v>
       </c>
       <c r="BQ3" t="n">
-        <v>6.18</v>
+        <v>6</v>
       </c>
       <c r="BR3" t="n">
         <v>100</v>
       </c>
       <c r="BS3" t="n">
-        <v>63.64</v>
+        <v>60.87</v>
       </c>
       <c r="BT3" t="n">
-        <v>50</v>
+        <v>47.83</v>
       </c>
       <c r="BU3" t="n">
-        <v>27.27</v>
+        <v>26.09</v>
       </c>
       <c r="BV3" t="n">
-        <v>27.27</v>
+        <v>26.09</v>
       </c>
       <c r="BW3" t="n">
-        <v>18.18</v>
+        <v>17.39</v>
       </c>
       <c r="BX3" t="n">
-        <v>54.55</v>
+        <v>52.17</v>
       </c>
       <c r="BY3" t="n">
         <v>1.48</v>
@@ -2013,31 +2013,31 @@
         <v>1.49</v>
       </c>
       <c r="CA3" t="n">
-        <v>4.47</v>
+        <v>4.42</v>
       </c>
       <c r="CB3" t="n">
-        <v>4.76</v>
+        <v>4.7</v>
       </c>
       <c r="CC3" t="n">
-        <v>1.74</v>
+        <v>1.87</v>
       </c>
       <c r="CD3" t="n">
-        <v>1.81</v>
+        <v>1.92</v>
       </c>
       <c r="CE3" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="CF3" t="n">
-        <v>2.23</v>
+        <v>2.25</v>
       </c>
       <c r="CG3" t="n">
-        <v>3.55</v>
+        <v>3.53</v>
       </c>
       <c r="CH3" t="n">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="CI3" t="n">
-        <v>2.13</v>
+        <v>2.12</v>
       </c>
       <c r="CJ3" t="n">
         <v>1.67</v>
@@ -2046,103 +2046,103 @@
         <v>1.47</v>
       </c>
       <c r="CL3" t="n">
-        <v>1.91</v>
+        <v>1.93</v>
       </c>
       <c r="CM3" t="n">
-        <v>2.53</v>
+        <v>2.51</v>
       </c>
       <c r="CN3" t="n">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="CO3" t="n">
         <v>1.16</v>
       </c>
       <c r="CP3" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="CQ3" t="n">
-        <v>2.37</v>
+        <v>2.41</v>
       </c>
       <c r="CR3" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="CS3" t="n">
-        <v>2.31</v>
+        <v>2.33</v>
       </c>
       <c r="CT3" t="n">
-        <v>3.28</v>
+        <v>3.24</v>
       </c>
       <c r="CU3" t="n">
         <v>1.64</v>
       </c>
       <c r="CV3" t="n">
-        <v>2.29</v>
+        <v>2.28</v>
       </c>
       <c r="CW3" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="CX3" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="CY3" t="n">
-        <v>1.79</v>
+        <v>1.81</v>
       </c>
       <c r="CZ3" t="n">
-        <v>2.51</v>
+        <v>2.49</v>
       </c>
       <c r="DA3" t="n">
-        <v>2.03</v>
+        <v>2.02</v>
       </c>
       <c r="DB3" t="n">
         <v>1.19</v>
       </c>
       <c r="DC3" t="n">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
       <c r="DD3" t="n">
-        <v>2.45</v>
+        <v>2.48</v>
       </c>
       <c r="DE3" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DF3" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="DG3" t="n">
-        <v>3.73</v>
+        <v>3.65</v>
       </c>
       <c r="DH3" t="n">
-        <v>110.82</v>
+        <v>110.48</v>
       </c>
       <c r="DI3" t="n">
-        <v>-0.04</v>
+        <v>0</v>
       </c>
       <c r="DJ3" t="n">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="DK3" t="n">
-        <v>6.37</v>
+        <v>6.3</v>
       </c>
       <c r="DL3" t="n">
-        <v>0.59</v>
+        <v>0.61</v>
       </c>
       <c r="DM3" t="n">
-        <v>61.18</v>
+        <v>61.05</v>
       </c>
       <c r="DN3" t="n">
-        <v>0.36</v>
+        <v>0.39</v>
       </c>
       <c r="DO3" t="n">
-        <v>2.64</v>
+        <v>2.65</v>
       </c>
       <c r="DP3" t="n">
-        <v>9.5</v>
+        <v>9.57</v>
       </c>
       <c r="DQ3" t="n">
-        <v>11.77</v>
+        <v>11.78</v>
       </c>
       <c r="DR3" t="n">
-        <v>7.23</v>
+        <v>7.26</v>
       </c>
       <c r="DS3" t="n">
         <v>0</v>
@@ -2154,28 +2154,28 @@
         <v>0</v>
       </c>
       <c r="DV3" t="n">
-        <v>62.18</v>
+        <v>62.52</v>
       </c>
       <c r="DW3" t="n">
         <v>0.09</v>
       </c>
       <c r="DX3" t="n">
-        <v>16.45</v>
+        <v>16.08</v>
       </c>
       <c r="DY3" t="n">
-        <v>11.09</v>
+        <v>10.87</v>
       </c>
       <c r="DZ3" t="n">
-        <v>5.36</v>
+        <v>5.22</v>
       </c>
       <c r="EA3" t="n">
-        <v>20.45</v>
+        <v>20.65</v>
       </c>
       <c r="EB3" t="n">
-        <v>1.86</v>
+        <v>1.83</v>
       </c>
       <c r="EC3" t="n">
-        <v>1.36</v>
+        <v>1.39</v>
       </c>
     </row>
     <row r="4">
@@ -2185,10 +2185,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C4" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D4" t="n">
         <v>11</v>
@@ -2197,82 +2197,82 @@
         <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>1</v>
+        <v>1.33</v>
       </c>
       <c r="G4" t="n">
-        <v>1.09</v>
+        <v>1.42</v>
       </c>
       <c r="H4" t="n">
-        <v>95.64</v>
+        <v>89.33</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.18</v>
+        <v>-0.17</v>
       </c>
       <c r="J4" t="n">
-        <v>1.55</v>
+        <v>1.83</v>
       </c>
       <c r="K4" t="n">
-        <v>3</v>
+        <v>3.42</v>
       </c>
       <c r="L4" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="M4" t="n">
-        <v>44.64</v>
+        <v>47.83</v>
       </c>
       <c r="N4" t="n">
-        <v>0.55</v>
+        <v>0.5</v>
       </c>
       <c r="O4" t="n">
-        <v>1.18</v>
+        <v>1.33</v>
       </c>
       <c r="P4" t="n">
-        <v>10.45</v>
+        <v>10.58</v>
       </c>
       <c r="Q4" t="n">
-        <v>11.27</v>
+        <v>11.17</v>
       </c>
       <c r="R4" t="n">
-        <v>10.91</v>
+        <v>10.33</v>
       </c>
       <c r="S4" t="n">
-        <v>1.55</v>
+        <v>1.58</v>
       </c>
       <c r="T4" t="n">
-        <v>0.64</v>
+        <v>0.67</v>
       </c>
       <c r="U4" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="V4" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="W4" t="n">
         <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>49.91</v>
+        <v>50</v>
       </c>
       <c r="Y4" t="n">
         <v>0</v>
       </c>
       <c r="Z4" t="n">
-        <v>9.550000000000001</v>
+        <v>10.58</v>
       </c>
       <c r="AA4" t="n">
-        <v>6.55</v>
+        <v>7.25</v>
       </c>
       <c r="AB4" t="n">
-        <v>3</v>
+        <v>3.33</v>
       </c>
       <c r="AC4" t="n">
-        <v>23.27</v>
+        <v>22.83</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.14</v>
+        <v>1.25</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.55</v>
+        <v>1.83</v>
       </c>
       <c r="AF4" t="n">
         <v>0.18</v>
@@ -2356,70 +2356,70 @@
         <v>2.18</v>
       </c>
       <c r="BG4" t="n">
-        <v>2.32</v>
+        <v>2.35</v>
       </c>
       <c r="BH4" t="n">
-        <v>8.359999999999999</v>
+        <v>8.43</v>
       </c>
       <c r="BI4" t="n">
-        <v>2.32</v>
+        <v>2.35</v>
       </c>
       <c r="BJ4" t="n">
-        <v>0.55</v>
+        <v>0.52</v>
       </c>
       <c r="BK4" t="n">
-        <v>0.27</v>
+        <v>0.35</v>
       </c>
       <c r="BL4" t="n">
-        <v>0.55</v>
+        <v>0.57</v>
       </c>
       <c r="BM4" t="n">
-        <v>0.95</v>
+        <v>0.91</v>
       </c>
       <c r="BN4" t="n">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="BO4" t="n">
-        <v>0.82</v>
+        <v>0.87</v>
       </c>
       <c r="BP4" t="n">
-        <v>3.73</v>
+        <v>3.74</v>
       </c>
       <c r="BQ4" t="n">
-        <v>4.05</v>
+        <v>4.13</v>
       </c>
       <c r="BR4" t="n">
-        <v>86.36</v>
+        <v>86.95999999999999</v>
       </c>
       <c r="BS4" t="n">
-        <v>68.18000000000001</v>
+        <v>69.56999999999999</v>
       </c>
       <c r="BT4" t="n">
-        <v>45.45</v>
+        <v>47.83</v>
       </c>
       <c r="BU4" t="n">
-        <v>22.73</v>
+        <v>21.74</v>
       </c>
       <c r="BV4" t="n">
-        <v>4.55</v>
+        <v>4.35</v>
       </c>
       <c r="BW4" t="n">
-        <v>4.55</v>
+        <v>4.35</v>
       </c>
       <c r="BX4" t="n">
-        <v>54.55</v>
+        <v>56.52</v>
       </c>
       <c r="BY4" t="n">
         <v>3.41</v>
       </c>
       <c r="BZ4" t="n">
-        <v>3.51</v>
+        <v>3.57</v>
       </c>
       <c r="CA4" t="n">
-        <v>3.69</v>
+        <v>3.68</v>
       </c>
       <c r="CB4" t="n">
-        <v>3.85</v>
+        <v>3.84</v>
       </c>
       <c r="CC4" t="n">
         <v>4.8</v>
@@ -2446,10 +2446,10 @@
         <v>1.74</v>
       </c>
       <c r="CK4" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="CL4" t="n">
-        <v>2.02</v>
+        <v>2.01</v>
       </c>
       <c r="CM4" t="n">
         <v>2.35</v>
@@ -2470,7 +2470,7 @@
         <v>1.39</v>
       </c>
       <c r="CS4" t="n">
-        <v>2.75</v>
+        <v>2.76</v>
       </c>
       <c r="CT4" t="n">
         <v>3.08</v>
@@ -2479,106 +2479,106 @@
         <v>1.48</v>
       </c>
       <c r="CV4" t="n">
-        <v>2.14</v>
+        <v>2.13</v>
       </c>
       <c r="CW4" t="n">
         <v>1.77</v>
       </c>
       <c r="CX4" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="CY4" t="n">
         <v>1.96</v>
       </c>
       <c r="CZ4" t="n">
-        <v>2.37</v>
+        <v>2.36</v>
       </c>
       <c r="DA4" t="n">
         <v>1.87</v>
       </c>
       <c r="DB4" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="DC4" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="DD4" t="n">
-        <v>3.14</v>
+        <v>3.15</v>
       </c>
       <c r="DE4" t="n">
         <v>0.09</v>
       </c>
       <c r="DF4" t="n">
-        <v>1.41</v>
+        <v>1.56</v>
       </c>
       <c r="DG4" t="n">
-        <v>1.32</v>
+        <v>1.48</v>
       </c>
       <c r="DH4" t="n">
-        <v>92.73</v>
+        <v>89.56</v>
       </c>
       <c r="DI4" t="n">
-        <v>-0.04</v>
+        <v>-0.05</v>
       </c>
       <c r="DJ4" t="n">
-        <v>2.14</v>
+        <v>2.26</v>
       </c>
       <c r="DK4" t="n">
-        <v>3.28</v>
+        <v>3.48</v>
       </c>
       <c r="DL4" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DM4" t="n">
-        <v>41.91</v>
+        <v>43.69</v>
       </c>
       <c r="DN4" t="n">
-        <v>0.64</v>
+        <v>0.61</v>
       </c>
       <c r="DO4" t="n">
-        <v>1.59</v>
+        <v>1.65</v>
       </c>
       <c r="DP4" t="n">
-        <v>11.32</v>
+        <v>11.35</v>
       </c>
       <c r="DQ4" t="n">
-        <v>11.59</v>
+        <v>11.52</v>
       </c>
       <c r="DR4" t="n">
-        <v>11</v>
+        <v>10.69</v>
       </c>
       <c r="DS4" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DT4" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DU4" t="n">
         <v>0</v>
       </c>
       <c r="DV4" t="n">
-        <v>46.5</v>
+        <v>46.7</v>
       </c>
       <c r="DW4" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="DX4" t="n">
-        <v>10.36</v>
+        <v>10.87</v>
       </c>
       <c r="DY4" t="n">
-        <v>6.68</v>
+        <v>7.04</v>
       </c>
       <c r="DZ4" t="n">
-        <v>3.68</v>
+        <v>3.82</v>
       </c>
       <c r="EA4" t="n">
-        <v>21.22</v>
+        <v>21.08</v>
       </c>
       <c r="EB4" t="n">
-        <v>1.22</v>
+        <v>1.27</v>
       </c>
       <c r="EC4" t="n">
-        <v>1.86</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5">
@@ -2588,13 +2588,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C5" t="n">
         <v>11</v>
       </c>
       <c r="D5" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E5" t="n">
         <v>0.27</v>
@@ -2678,139 +2678,139 @@
         <v>1.55</v>
       </c>
       <c r="AF5" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="AH5" t="n">
-        <v>2.91</v>
+        <v>2.83</v>
       </c>
       <c r="AI5" t="n">
-        <v>88.45</v>
+        <v>88.08</v>
       </c>
       <c r="AJ5" t="n">
-        <v>0</v>
+        <v>-0.08</v>
       </c>
       <c r="AK5" t="n">
-        <v>2.09</v>
+        <v>1.92</v>
       </c>
       <c r="AL5" t="n">
-        <v>4.64</v>
+        <v>4.67</v>
       </c>
       <c r="AM5" t="n">
-        <v>0.64</v>
+        <v>0.75</v>
       </c>
       <c r="AN5" t="n">
-        <v>40.64</v>
+        <v>40</v>
       </c>
       <c r="AO5" t="n">
-        <v>0.73</v>
+        <v>0.67</v>
       </c>
       <c r="AP5" t="n">
-        <v>1.73</v>
+        <v>1.83</v>
       </c>
       <c r="AQ5" t="n">
-        <v>10.91</v>
+        <v>11</v>
       </c>
       <c r="AR5" t="n">
-        <v>11.09</v>
+        <v>11.25</v>
       </c>
       <c r="AS5" t="n">
-        <v>11.09</v>
+        <v>10.92</v>
       </c>
       <c r="AT5" t="n">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="AU5" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AV5" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="AW5" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="AX5" t="n">
         <v>0</v>
       </c>
       <c r="AY5" t="n">
-        <v>47.91</v>
+        <v>48.67</v>
       </c>
       <c r="AZ5" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="BA5" t="n">
-        <v>11.64</v>
+        <v>11.33</v>
       </c>
       <c r="BB5" t="n">
-        <v>6.73</v>
+        <v>6.58</v>
       </c>
       <c r="BC5" t="n">
-        <v>4.91</v>
+        <v>4.75</v>
       </c>
       <c r="BD5" t="n">
-        <v>17.82</v>
+        <v>17.75</v>
       </c>
       <c r="BE5" t="n">
-        <v>1.38</v>
+        <v>1.34</v>
       </c>
       <c r="BF5" t="n">
-        <v>1.73</v>
+        <v>1.58</v>
       </c>
       <c r="BG5" t="n">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="BH5" t="n">
-        <v>10.14</v>
+        <v>10.17</v>
       </c>
       <c r="BI5" t="n">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="BJ5" t="n">
-        <v>0.86</v>
+        <v>0.83</v>
       </c>
       <c r="BK5" t="n">
-        <v>0.55</v>
+        <v>0.52</v>
       </c>
       <c r="BL5" t="n">
-        <v>0.95</v>
+        <v>0.96</v>
       </c>
       <c r="BM5" t="n">
-        <v>0.68</v>
+        <v>0.7</v>
       </c>
       <c r="BN5" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="BO5" t="n">
-        <v>1.41</v>
+        <v>1.35</v>
       </c>
       <c r="BP5" t="n">
-        <v>4.05</v>
+        <v>4.04</v>
       </c>
       <c r="BQ5" t="n">
-        <v>6.09</v>
+        <v>6.13</v>
       </c>
       <c r="BR5" t="n">
-        <v>95.45</v>
+        <v>95.65000000000001</v>
       </c>
       <c r="BS5" t="n">
-        <v>86.36</v>
+        <v>86.95999999999999</v>
       </c>
       <c r="BT5" t="n">
-        <v>59.09</v>
+        <v>56.52</v>
       </c>
       <c r="BU5" t="n">
-        <v>36.36</v>
+        <v>34.78</v>
       </c>
       <c r="BV5" t="n">
-        <v>18.18</v>
+        <v>17.39</v>
       </c>
       <c r="BW5" t="n">
-        <v>9.09</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="BX5" t="n">
-        <v>59.09</v>
+        <v>60.87</v>
       </c>
       <c r="BY5" t="n">
         <v>2.71</v>
@@ -2819,22 +2819,22 @@
         <v>2.83</v>
       </c>
       <c r="CA5" t="n">
-        <v>3.61</v>
+        <v>3.59</v>
       </c>
       <c r="CB5" t="n">
-        <v>3.78</v>
+        <v>3.77</v>
       </c>
       <c r="CC5" t="n">
-        <v>3.65</v>
+        <v>3.58</v>
       </c>
       <c r="CD5" t="n">
-        <v>3.99</v>
+        <v>3.9</v>
       </c>
       <c r="CE5" t="n">
         <v>1.3</v>
       </c>
       <c r="CF5" t="n">
-        <v>2.46</v>
+        <v>2.48</v>
       </c>
       <c r="CG5" t="n">
         <v>3.22</v>
@@ -2843,7 +2843,7 @@
         <v>1.5</v>
       </c>
       <c r="CI5" t="n">
-        <v>2.23</v>
+        <v>2.22</v>
       </c>
       <c r="CJ5" t="n">
         <v>1.63</v>
@@ -2852,13 +2852,13 @@
         <v>1.45</v>
       </c>
       <c r="CL5" t="n">
-        <v>1.84</v>
+        <v>1.86</v>
       </c>
       <c r="CM5" t="n">
-        <v>2.57</v>
+        <v>2.56</v>
       </c>
       <c r="CN5" t="n">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="CO5" t="n">
         <v>1.22</v>
@@ -2867,31 +2867,31 @@
         <v>1.74</v>
       </c>
       <c r="CQ5" t="n">
-        <v>2.75</v>
+        <v>2.76</v>
       </c>
       <c r="CR5" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="CS5" t="n">
-        <v>2.51</v>
+        <v>2.53</v>
       </c>
       <c r="CT5" t="n">
-        <v>3.24</v>
+        <v>3.22</v>
       </c>
       <c r="CU5" t="n">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="CV5" t="n">
-        <v>2.32</v>
+        <v>2.31</v>
       </c>
       <c r="CW5" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="CX5" t="n">
         <v>1.52</v>
       </c>
       <c r="CY5" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="CZ5" t="n">
         <v>2.49</v>
@@ -2903,85 +2903,85 @@
         <v>1.24</v>
       </c>
       <c r="DC5" t="n">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="DD5" t="n">
-        <v>2.86</v>
+        <v>2.88</v>
       </c>
       <c r="DE5" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="DF5" t="n">
-        <v>1.18</v>
+        <v>1.13</v>
       </c>
       <c r="DG5" t="n">
-        <v>2.82</v>
+        <v>2.78</v>
       </c>
       <c r="DH5" t="n">
-        <v>97.09</v>
+        <v>96.52</v>
       </c>
       <c r="DI5" t="n">
-        <v>0</v>
+        <v>-0.04</v>
       </c>
       <c r="DJ5" t="n">
-        <v>1.91</v>
+        <v>1.83</v>
       </c>
       <c r="DK5" t="n">
-        <v>4.82</v>
+        <v>4.83</v>
       </c>
       <c r="DL5" t="n">
-        <v>0.5</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="DM5" t="n">
-        <v>44.5</v>
+        <v>44</v>
       </c>
       <c r="DN5" t="n">
-        <v>0.59</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="DO5" t="n">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="DP5" t="n">
-        <v>10.87</v>
+        <v>10.91</v>
       </c>
       <c r="DQ5" t="n">
-        <v>10.96</v>
+        <v>11.04</v>
       </c>
       <c r="DR5" t="n">
-        <v>9.59</v>
+        <v>9.57</v>
       </c>
       <c r="DS5" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DT5" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DU5" t="n">
         <v>0</v>
       </c>
       <c r="DV5" t="n">
-        <v>51.23</v>
+        <v>51.48</v>
       </c>
       <c r="DW5" t="n">
         <v>0.13</v>
       </c>
       <c r="DX5" t="n">
-        <v>13.64</v>
+        <v>13.39</v>
       </c>
       <c r="DY5" t="n">
-        <v>9</v>
+        <v>8.82</v>
       </c>
       <c r="DZ5" t="n">
-        <v>4.64</v>
+        <v>4.56</v>
       </c>
       <c r="EA5" t="n">
-        <v>18.45</v>
+        <v>18.39</v>
       </c>
       <c r="EB5" t="n">
-        <v>1.52</v>
+        <v>1.49</v>
       </c>
       <c r="EC5" t="n">
-        <v>1.64</v>
+        <v>1.57</v>
       </c>
     </row>
     <row r="6">
@@ -2991,13 +2991,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C6" t="n">
         <v>11</v>
       </c>
       <c r="D6" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
@@ -3081,52 +3081,52 @@
         <v>1</v>
       </c>
       <c r="AF6" t="n">
-        <v>0.09</v>
+        <v>0.25</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AH6" t="n">
-        <v>2.64</v>
+        <v>2.5</v>
       </c>
       <c r="AI6" t="n">
-        <v>103.45</v>
+        <v>97.25</v>
       </c>
       <c r="AJ6" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="AK6" t="n">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="AL6" t="n">
-        <v>4.73</v>
+        <v>4.5</v>
       </c>
       <c r="AM6" t="n">
-        <v>0.73</v>
+        <v>0.75</v>
       </c>
       <c r="AN6" t="n">
-        <v>47.27</v>
+        <v>46.25</v>
       </c>
       <c r="AO6" t="n">
-        <v>0.45</v>
+        <v>0.42</v>
       </c>
       <c r="AP6" t="n">
-        <v>2.09</v>
+        <v>2</v>
       </c>
       <c r="AQ6" t="n">
-        <v>9.73</v>
+        <v>9.75</v>
       </c>
       <c r="AR6" t="n">
-        <v>11.91</v>
+        <v>11.92</v>
       </c>
       <c r="AS6" t="n">
-        <v>7.45</v>
+        <v>8.08</v>
       </c>
       <c r="AT6" t="n">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="AU6" t="n">
-        <v>1.27</v>
+        <v>1.33</v>
       </c>
       <c r="AV6" t="n">
         <v>0</v>
@@ -3138,82 +3138,82 @@
         <v>0</v>
       </c>
       <c r="AY6" t="n">
-        <v>61.18</v>
+        <v>60.17</v>
       </c>
       <c r="AZ6" t="n">
         <v>0</v>
       </c>
       <c r="BA6" t="n">
-        <v>14.18</v>
+        <v>13.67</v>
       </c>
       <c r="BB6" t="n">
-        <v>8.640000000000001</v>
+        <v>8.25</v>
       </c>
       <c r="BC6" t="n">
-        <v>5.55</v>
+        <v>5.42</v>
       </c>
       <c r="BD6" t="n">
-        <v>19.27</v>
+        <v>18.75</v>
       </c>
       <c r="BE6" t="n">
-        <v>1.63</v>
+        <v>1.58</v>
       </c>
       <c r="BF6" t="n">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="BG6" t="n">
-        <v>2.86</v>
+        <v>2.87</v>
       </c>
       <c r="BH6" t="n">
-        <v>9.77</v>
+        <v>9.779999999999999</v>
       </c>
       <c r="BI6" t="n">
-        <v>2.86</v>
+        <v>2.87</v>
       </c>
       <c r="BJ6" t="n">
-        <v>0.64</v>
+        <v>0.61</v>
       </c>
       <c r="BK6" t="n">
-        <v>0.86</v>
+        <v>0.91</v>
       </c>
       <c r="BL6" t="n">
-        <v>0.82</v>
+        <v>0.83</v>
       </c>
       <c r="BM6" t="n">
-        <v>0.55</v>
+        <v>0.52</v>
       </c>
       <c r="BN6" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="BO6" t="n">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="BP6" t="n">
-        <v>4.41</v>
+        <v>4.39</v>
       </c>
       <c r="BQ6" t="n">
-        <v>5.32</v>
+        <v>5.35</v>
       </c>
       <c r="BR6" t="n">
         <v>100</v>
       </c>
       <c r="BS6" t="n">
-        <v>86.36</v>
+        <v>86.95999999999999</v>
       </c>
       <c r="BT6" t="n">
-        <v>59.09</v>
+        <v>60.87</v>
       </c>
       <c r="BU6" t="n">
-        <v>18.18</v>
+        <v>17.39</v>
       </c>
       <c r="BV6" t="n">
-        <v>9.09</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="BW6" t="n">
-        <v>4.55</v>
+        <v>4.35</v>
       </c>
       <c r="BX6" t="n">
-        <v>81.81999999999999</v>
+        <v>82.61</v>
       </c>
       <c r="BY6" t="n">
         <v>1.82</v>
@@ -3222,28 +3222,28 @@
         <v>1.91</v>
       </c>
       <c r="CA6" t="n">
-        <v>3.83</v>
+        <v>3.82</v>
       </c>
       <c r="CB6" t="n">
-        <v>3.96</v>
+        <v>3.94</v>
       </c>
       <c r="CC6" t="n">
-        <v>2.41</v>
+        <v>2.38</v>
       </c>
       <c r="CD6" t="n">
-        <v>2.46</v>
+        <v>2.42</v>
       </c>
       <c r="CE6" t="n">
         <v>1.29</v>
       </c>
       <c r="CF6" t="n">
-        <v>2.42</v>
+        <v>2.43</v>
       </c>
       <c r="CG6" t="n">
-        <v>3.27</v>
+        <v>3.26</v>
       </c>
       <c r="CH6" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="CI6" t="n">
         <v>2.24</v>
@@ -3252,40 +3252,40 @@
         <v>1.63</v>
       </c>
       <c r="CK6" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="CL6" t="n">
         <v>1.97</v>
       </c>
       <c r="CM6" t="n">
-        <v>2.44</v>
+        <v>2.43</v>
       </c>
       <c r="CN6" t="n">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="CO6" t="n">
         <v>1.19</v>
       </c>
       <c r="CP6" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="CQ6" t="n">
-        <v>2.68</v>
+        <v>2.7</v>
       </c>
       <c r="CR6" t="n">
         <v>1.37</v>
       </c>
       <c r="CS6" t="n">
-        <v>2.57</v>
+        <v>2.59</v>
       </c>
       <c r="CT6" t="n">
-        <v>3.15</v>
+        <v>3.14</v>
       </c>
       <c r="CU6" t="n">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="CV6" t="n">
-        <v>2.3</v>
+        <v>2.29</v>
       </c>
       <c r="CW6" t="n">
         <v>1.68</v>
@@ -3300,58 +3300,58 @@
         <v>2.35</v>
       </c>
       <c r="DA6" t="n">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="DB6" t="n">
         <v>1.23</v>
       </c>
       <c r="DC6" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="DD6" t="n">
-        <v>2.8</v>
+        <v>2.83</v>
       </c>
       <c r="DE6" t="n">
-        <v>0.04</v>
+        <v>0.13</v>
       </c>
       <c r="DF6" t="n">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="DG6" t="n">
-        <v>3.46</v>
+        <v>3.35</v>
       </c>
       <c r="DH6" t="n">
-        <v>116.82</v>
+        <v>113</v>
       </c>
       <c r="DI6" t="n">
         <v>0.04</v>
       </c>
       <c r="DJ6" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="DK6" t="n">
-        <v>5.82</v>
+        <v>5.65</v>
       </c>
       <c r="DL6" t="n">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="DM6" t="n">
-        <v>54.86</v>
+        <v>54</v>
       </c>
       <c r="DN6" t="n">
-        <v>0.5</v>
+        <v>0.48</v>
       </c>
       <c r="DO6" t="n">
-        <v>2.32</v>
+        <v>2.26</v>
       </c>
       <c r="DP6" t="n">
-        <v>10.28</v>
+        <v>10.26</v>
       </c>
       <c r="DQ6" t="n">
-        <v>12.73</v>
+        <v>12.7</v>
       </c>
       <c r="DR6" t="n">
-        <v>6.55</v>
+        <v>6.91</v>
       </c>
       <c r="DS6" t="n">
         <v>0</v>
@@ -3363,28 +3363,28 @@
         <v>0</v>
       </c>
       <c r="DV6" t="n">
-        <v>62.82</v>
+        <v>62.22</v>
       </c>
       <c r="DW6" t="n">
         <v>0.04</v>
       </c>
       <c r="DX6" t="n">
-        <v>16.18</v>
+        <v>15.83</v>
       </c>
       <c r="DY6" t="n">
-        <v>10.46</v>
+        <v>10.17</v>
       </c>
       <c r="DZ6" t="n">
-        <v>5.73</v>
+        <v>5.65</v>
       </c>
       <c r="EA6" t="n">
-        <v>20.36</v>
+        <v>20.04</v>
       </c>
       <c r="EB6" t="n">
-        <v>1.82</v>
+        <v>1.79</v>
       </c>
       <c r="EC6" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
     </row>
     <row r="7">
@@ -3394,13 +3394,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C7" t="n">
         <v>11</v>
       </c>
       <c r="D7" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E7" t="n">
         <v>0.18</v>
@@ -3484,52 +3484,52 @@
         <v>2.45</v>
       </c>
       <c r="AF7" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.45</v>
+        <v>1.75</v>
       </c>
       <c r="AH7" t="n">
         <v>3</v>
       </c>
       <c r="AI7" t="n">
-        <v>85.64</v>
+        <v>86.25</v>
       </c>
       <c r="AJ7" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="AK7" t="n">
-        <v>2.27</v>
+        <v>2.58</v>
       </c>
       <c r="AL7" t="n">
-        <v>5.09</v>
+        <v>5.08</v>
       </c>
       <c r="AM7" t="n">
-        <v>0.36</v>
+        <v>0.33</v>
       </c>
       <c r="AN7" t="n">
-        <v>41.82</v>
+        <v>42.5</v>
       </c>
       <c r="AO7" t="n">
-        <v>0.82</v>
+        <v>0.83</v>
       </c>
       <c r="AP7" t="n">
-        <v>2.09</v>
+        <v>2.08</v>
       </c>
       <c r="AQ7" t="n">
-        <v>10</v>
+        <v>10.33</v>
       </c>
       <c r="AR7" t="n">
-        <v>11</v>
+        <v>11.67</v>
       </c>
       <c r="AS7" t="n">
-        <v>8.91</v>
+        <v>8.83</v>
       </c>
       <c r="AT7" t="n">
-        <v>1.09</v>
+        <v>1.17</v>
       </c>
       <c r="AU7" t="n">
-        <v>1.27</v>
+        <v>1.33</v>
       </c>
       <c r="AV7" t="n">
         <v>0</v>
@@ -3541,82 +3541,82 @@
         <v>0</v>
       </c>
       <c r="AY7" t="n">
-        <v>48.91</v>
+        <v>49.25</v>
       </c>
       <c r="AZ7" t="n">
         <v>0</v>
       </c>
       <c r="BA7" t="n">
-        <v>10.09</v>
+        <v>10.33</v>
       </c>
       <c r="BB7" t="n">
-        <v>6.09</v>
+        <v>6.08</v>
       </c>
       <c r="BC7" t="n">
-        <v>4</v>
+        <v>4.25</v>
       </c>
       <c r="BD7" t="n">
-        <v>21.91</v>
+        <v>21.67</v>
       </c>
       <c r="BE7" t="n">
-        <v>1.22</v>
+        <v>1.26</v>
       </c>
       <c r="BF7" t="n">
-        <v>2.27</v>
+        <v>2.58</v>
       </c>
       <c r="BG7" t="n">
-        <v>2.27</v>
+        <v>2.35</v>
       </c>
       <c r="BH7" t="n">
-        <v>11.41</v>
+        <v>11.43</v>
       </c>
       <c r="BI7" t="n">
-        <v>2.27</v>
+        <v>2.35</v>
       </c>
       <c r="BJ7" t="n">
-        <v>0.5</v>
+        <v>0.52</v>
       </c>
       <c r="BK7" t="n">
-        <v>0.45</v>
+        <v>0.43</v>
       </c>
       <c r="BL7" t="n">
-        <v>0.59</v>
+        <v>0.61</v>
       </c>
       <c r="BM7" t="n">
-        <v>0.73</v>
+        <v>0.78</v>
       </c>
       <c r="BN7" t="n">
-        <v>1.32</v>
+        <v>1.39</v>
       </c>
       <c r="BO7" t="n">
-        <v>0.95</v>
+        <v>0.96</v>
       </c>
       <c r="BP7" t="n">
-        <v>5.09</v>
+        <v>5.17</v>
       </c>
       <c r="BQ7" t="n">
-        <v>6.32</v>
+        <v>6.26</v>
       </c>
       <c r="BR7" t="n">
-        <v>95.45</v>
+        <v>95.65000000000001</v>
       </c>
       <c r="BS7" t="n">
-        <v>68.18000000000001</v>
+        <v>69.56999999999999</v>
       </c>
       <c r="BT7" t="n">
-        <v>31.82</v>
+        <v>34.78</v>
       </c>
       <c r="BU7" t="n">
-        <v>22.73</v>
+        <v>26.09</v>
       </c>
       <c r="BV7" t="n">
-        <v>9.09</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="BW7" t="n">
         <v>0</v>
       </c>
       <c r="BX7" t="n">
-        <v>63.64</v>
+        <v>65.22</v>
       </c>
       <c r="BY7" t="n">
         <v>2.81</v>
@@ -3625,40 +3625,40 @@
         <v>2.99</v>
       </c>
       <c r="CA7" t="n">
-        <v>3.71</v>
+        <v>3.69</v>
       </c>
       <c r="CB7" t="n">
-        <v>3.85</v>
+        <v>3.82</v>
       </c>
       <c r="CC7" t="n">
-        <v>3.98</v>
+        <v>3.93</v>
       </c>
       <c r="CD7" t="n">
-        <v>4.51</v>
+        <v>4.43</v>
       </c>
       <c r="CE7" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="CF7" t="n">
-        <v>2.43</v>
+        <v>2.45</v>
       </c>
       <c r="CG7" t="n">
-        <v>3.25</v>
+        <v>3.23</v>
       </c>
       <c r="CH7" t="n">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="CI7" t="n">
-        <v>2.22</v>
+        <v>2.21</v>
       </c>
       <c r="CJ7" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="CK7" t="n">
         <v>1.39</v>
       </c>
       <c r="CL7" t="n">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="CM7" t="n">
         <v>2.76</v>
@@ -3670,19 +3670,19 @@
         <v>1.21</v>
       </c>
       <c r="CP7" t="n">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="CQ7" t="n">
-        <v>2.69</v>
+        <v>2.72</v>
       </c>
       <c r="CR7" t="n">
         <v>1.36</v>
       </c>
       <c r="CS7" t="n">
-        <v>2.55</v>
+        <v>2.57</v>
       </c>
       <c r="CT7" t="n">
-        <v>3.21</v>
+        <v>3.2</v>
       </c>
       <c r="CU7" t="n">
         <v>1.54</v>
@@ -3694,13 +3694,13 @@
         <v>1.66</v>
       </c>
       <c r="CX7" t="n">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="CY7" t="n">
         <v>1.72</v>
       </c>
       <c r="CZ7" t="n">
-        <v>2.57</v>
+        <v>2.58</v>
       </c>
       <c r="DA7" t="n">
         <v>2.13</v>
@@ -3709,52 +3709,52 @@
         <v>1.23</v>
       </c>
       <c r="DC7" t="n">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="DD7" t="n">
-        <v>2.82</v>
+        <v>2.85</v>
       </c>
       <c r="DE7" t="n">
         <v>0.13</v>
       </c>
       <c r="DF7" t="n">
-        <v>1.59</v>
+        <v>1.74</v>
       </c>
       <c r="DG7" t="n">
-        <v>2.86</v>
+        <v>2.87</v>
       </c>
       <c r="DH7" t="n">
-        <v>89.04000000000001</v>
+        <v>89.22</v>
       </c>
       <c r="DI7" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="DJ7" t="n">
-        <v>2.36</v>
+        <v>2.52</v>
       </c>
       <c r="DK7" t="n">
         <v>5.04</v>
       </c>
       <c r="DL7" t="n">
-        <v>0.32</v>
+        <v>0.3</v>
       </c>
       <c r="DM7" t="n">
-        <v>47.32</v>
+        <v>47.44</v>
       </c>
       <c r="DN7" t="n">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="DO7" t="n">
-        <v>2.18</v>
+        <v>2.17</v>
       </c>
       <c r="DP7" t="n">
-        <v>10.28</v>
+        <v>10.44</v>
       </c>
       <c r="DQ7" t="n">
-        <v>11.09</v>
+        <v>11.44</v>
       </c>
       <c r="DR7" t="n">
-        <v>9.18</v>
+        <v>9.130000000000001</v>
       </c>
       <c r="DS7" t="n">
         <v>0.09</v>
@@ -3766,28 +3766,28 @@
         <v>0</v>
       </c>
       <c r="DV7" t="n">
-        <v>50.18</v>
+        <v>50.3</v>
       </c>
       <c r="DW7" t="n">
         <v>0</v>
       </c>
       <c r="DX7" t="n">
-        <v>10.5</v>
+        <v>10.61</v>
       </c>
       <c r="DY7" t="n">
-        <v>6.68</v>
+        <v>6.65</v>
       </c>
       <c r="DZ7" t="n">
-        <v>3.82</v>
+        <v>3.96</v>
       </c>
       <c r="EA7" t="n">
-        <v>21.73</v>
+        <v>21.61</v>
       </c>
       <c r="EB7" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="EC7" t="n">
-        <v>2.36</v>
+        <v>2.52</v>
       </c>
     </row>
     <row r="8">
@@ -3797,13 +3797,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C8" t="n">
         <v>11</v>
       </c>
       <c r="D8" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E8" t="n">
         <v>0.27</v>
@@ -3887,139 +3887,139 @@
         <v>1.27</v>
       </c>
       <c r="AF8" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.55</v>
+        <v>1.58</v>
       </c>
       <c r="AH8" t="n">
-        <v>2.18</v>
+        <v>2.08</v>
       </c>
       <c r="AI8" t="n">
-        <v>87.64</v>
+        <v>87.25</v>
       </c>
       <c r="AJ8" t="n">
         <v>0</v>
       </c>
       <c r="AK8" t="n">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="AL8" t="n">
-        <v>4.45</v>
+        <v>4.33</v>
       </c>
       <c r="AM8" t="n">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="AN8" t="n">
-        <v>42.91</v>
+        <v>42.67</v>
       </c>
       <c r="AO8" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="AP8" t="n">
-        <v>2.27</v>
+        <v>2.25</v>
       </c>
       <c r="AQ8" t="n">
-        <v>13.27</v>
+        <v>13.08</v>
       </c>
       <c r="AR8" t="n">
-        <v>11.91</v>
+        <v>11.58</v>
       </c>
       <c r="AS8" t="n">
         <v>9</v>
       </c>
       <c r="AT8" t="n">
-        <v>2.18</v>
+        <v>2</v>
       </c>
       <c r="AU8" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AV8" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="AW8" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="AX8" t="n">
         <v>0</v>
       </c>
       <c r="AY8" t="n">
-        <v>47.27</v>
+        <v>46.92</v>
       </c>
       <c r="AZ8" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="BA8" t="n">
-        <v>13.73</v>
+        <v>13.17</v>
       </c>
       <c r="BB8" t="n">
-        <v>9.359999999999999</v>
+        <v>8.83</v>
       </c>
       <c r="BC8" t="n">
-        <v>4.36</v>
+        <v>4.33</v>
       </c>
       <c r="BD8" t="n">
-        <v>22.55</v>
+        <v>22.08</v>
       </c>
       <c r="BE8" t="n">
-        <v>1.44</v>
+        <v>1.41</v>
       </c>
       <c r="BF8" t="n">
-        <v>1.55</v>
+        <v>1.58</v>
       </c>
       <c r="BG8" t="n">
-        <v>2.82</v>
+        <v>2.74</v>
       </c>
       <c r="BH8" t="n">
-        <v>10.45</v>
+        <v>10.43</v>
       </c>
       <c r="BI8" t="n">
-        <v>2.82</v>
+        <v>2.74</v>
       </c>
       <c r="BJ8" t="n">
-        <v>0.82</v>
+        <v>0.78</v>
       </c>
       <c r="BK8" t="n">
-        <v>0.55</v>
+        <v>0.57</v>
       </c>
       <c r="BL8" t="n">
-        <v>0.91</v>
+        <v>0.87</v>
       </c>
       <c r="BM8" t="n">
-        <v>0.55</v>
+        <v>0.52</v>
       </c>
       <c r="BN8" t="n">
-        <v>1.45</v>
+        <v>1.39</v>
       </c>
       <c r="BO8" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="BP8" t="n">
-        <v>4.91</v>
+        <v>4.83</v>
       </c>
       <c r="BQ8" t="n">
-        <v>5.5</v>
+        <v>5.57</v>
       </c>
       <c r="BR8" t="n">
-        <v>90.91</v>
+        <v>91.3</v>
       </c>
       <c r="BS8" t="n">
-        <v>81.81999999999999</v>
+        <v>78.26000000000001</v>
       </c>
       <c r="BT8" t="n">
-        <v>36.36</v>
+        <v>34.78</v>
       </c>
       <c r="BU8" t="n">
-        <v>27.27</v>
+        <v>26.09</v>
       </c>
       <c r="BV8" t="n">
-        <v>13.64</v>
+        <v>13.04</v>
       </c>
       <c r="BW8" t="n">
-        <v>9.09</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="BX8" t="n">
-        <v>40.91</v>
+        <v>39.13</v>
       </c>
       <c r="BY8" t="n">
         <v>2.19</v>
@@ -4028,31 +4028,31 @@
         <v>2.31</v>
       </c>
       <c r="CA8" t="n">
-        <v>3.82</v>
+        <v>3.8</v>
       </c>
       <c r="CB8" t="n">
-        <v>3.89</v>
+        <v>3.88</v>
       </c>
       <c r="CC8" t="n">
-        <v>4.09</v>
+        <v>3.99</v>
       </c>
       <c r="CD8" t="n">
-        <v>4</v>
+        <v>3.93</v>
       </c>
       <c r="CE8" t="n">
         <v>1.27</v>
       </c>
       <c r="CF8" t="n">
-        <v>2.27</v>
+        <v>2.28</v>
       </c>
       <c r="CG8" t="n">
-        <v>3.49</v>
+        <v>3.47</v>
       </c>
       <c r="CH8" t="n">
         <v>1.59</v>
       </c>
       <c r="CI8" t="n">
-        <v>2.39</v>
+        <v>2.4</v>
       </c>
       <c r="CJ8" t="n">
         <v>1.55</v>
@@ -4061,7 +4061,7 @@
         <v>1.35</v>
       </c>
       <c r="CL8" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="CM8" t="n">
         <v>2.89</v>
@@ -4070,13 +4070,13 @@
         <v>2.22</v>
       </c>
       <c r="CO8" t="n">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="CP8" t="n">
         <v>1.61</v>
       </c>
       <c r="CQ8" t="n">
-        <v>2.46</v>
+        <v>2.47</v>
       </c>
       <c r="CR8" t="n">
         <v>1.34</v>
@@ -4100,7 +4100,7 @@
         <v>1.46</v>
       </c>
       <c r="CY8" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="CZ8" t="n">
         <v>2.67</v>
@@ -4112,52 +4112,52 @@
         <v>1.19</v>
       </c>
       <c r="DC8" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="DD8" t="n">
-        <v>2.5</v>
+        <v>2.51</v>
       </c>
       <c r="DE8" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="DF8" t="n">
-        <v>1.23</v>
+        <v>1.26</v>
       </c>
       <c r="DG8" t="n">
-        <v>2.64</v>
+        <v>2.56</v>
       </c>
       <c r="DH8" t="n">
-        <v>94.18000000000001</v>
+        <v>93.7</v>
       </c>
       <c r="DI8" t="n">
         <v>0</v>
       </c>
       <c r="DJ8" t="n">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="DK8" t="n">
-        <v>5.36</v>
+        <v>5.26</v>
       </c>
       <c r="DL8" t="n">
-        <v>0.32</v>
+        <v>0.3</v>
       </c>
       <c r="DM8" t="n">
-        <v>50.32</v>
+        <v>49.87</v>
       </c>
       <c r="DN8" t="n">
-        <v>0.22</v>
+        <v>0.21</v>
       </c>
       <c r="DO8" t="n">
-        <v>2.72</v>
+        <v>2.69</v>
       </c>
       <c r="DP8" t="n">
-        <v>11.91</v>
+        <v>11.87</v>
       </c>
       <c r="DQ8" t="n">
-        <v>11.96</v>
+        <v>11.78</v>
       </c>
       <c r="DR8" t="n">
-        <v>8.41</v>
+        <v>8.44</v>
       </c>
       <c r="DS8" t="n">
         <v>0.13</v>
@@ -4169,28 +4169,28 @@
         <v>0</v>
       </c>
       <c r="DV8" t="n">
-        <v>49.68</v>
+        <v>49.39</v>
       </c>
       <c r="DW8" t="n">
         <v>0.04</v>
       </c>
       <c r="DX8" t="n">
-        <v>15.46</v>
+        <v>15.09</v>
       </c>
       <c r="DY8" t="n">
-        <v>10.68</v>
+        <v>10.35</v>
       </c>
       <c r="DZ8" t="n">
-        <v>4.77</v>
+        <v>4.74</v>
       </c>
       <c r="EA8" t="n">
-        <v>21.6</v>
+        <v>21.39</v>
       </c>
       <c r="EB8" t="n">
-        <v>1.65</v>
+        <v>1.63</v>
       </c>
       <c r="EC8" t="n">
-        <v>1.41</v>
+        <v>1.43</v>
       </c>
     </row>
     <row r="9">
@@ -4200,94 +4200,94 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C9" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D9" t="n">
         <v>11</v>
       </c>
       <c r="E9" t="n">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="F9" t="n">
-        <v>2.36</v>
+        <v>2.25</v>
       </c>
       <c r="G9" t="n">
-        <v>2.36</v>
+        <v>2.33</v>
       </c>
       <c r="H9" t="n">
-        <v>79.91</v>
+        <v>81.58</v>
       </c>
       <c r="I9" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="J9" t="n">
-        <v>3.09</v>
+        <v>3.08</v>
       </c>
       <c r="K9" t="n">
-        <v>4.36</v>
+        <v>4.58</v>
       </c>
       <c r="L9" t="n">
-        <v>0.45</v>
+        <v>0.42</v>
       </c>
       <c r="M9" t="n">
-        <v>40.45</v>
+        <v>40.58</v>
       </c>
       <c r="N9" t="n">
-        <v>0.73</v>
+        <v>0.83</v>
       </c>
       <c r="O9" t="n">
-        <v>1.91</v>
+        <v>2.17</v>
       </c>
       <c r="P9" t="n">
-        <v>16.55</v>
+        <v>16.75</v>
       </c>
       <c r="Q9" t="n">
-        <v>12.55</v>
+        <v>12.58</v>
       </c>
       <c r="R9" t="n">
-        <v>8.640000000000001</v>
+        <v>8.25</v>
       </c>
       <c r="S9" t="n">
-        <v>1.18</v>
+        <v>1.25</v>
       </c>
       <c r="T9" t="n">
-        <v>1.09</v>
+        <v>1.17</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>0.08</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>0.08</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>45.64</v>
+        <v>45.75</v>
       </c>
       <c r="Y9" t="n">
         <v>0</v>
       </c>
       <c r="Z9" t="n">
-        <v>14.55</v>
+        <v>14.67</v>
       </c>
       <c r="AA9" t="n">
-        <v>9.91</v>
+        <v>10</v>
       </c>
       <c r="AB9" t="n">
-        <v>4.64</v>
+        <v>4.67</v>
       </c>
       <c r="AC9" t="n">
-        <v>19.27</v>
+        <v>19.58</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="AE9" t="n">
-        <v>3.09</v>
+        <v>3.08</v>
       </c>
       <c r="AF9" t="n">
         <v>0</v>
@@ -4371,70 +4371,70 @@
         <v>3.27</v>
       </c>
       <c r="BG9" t="n">
-        <v>2.23</v>
+        <v>2.3</v>
       </c>
       <c r="BH9" t="n">
-        <v>10.18</v>
+        <v>10.26</v>
       </c>
       <c r="BI9" t="n">
-        <v>2.23</v>
+        <v>2.3</v>
       </c>
       <c r="BJ9" t="n">
-        <v>0.68</v>
+        <v>0.7</v>
       </c>
       <c r="BK9" t="n">
-        <v>0.41</v>
+        <v>0.39</v>
       </c>
       <c r="BL9" t="n">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="BM9" t="n">
-        <v>0.5</v>
+        <v>0.57</v>
       </c>
       <c r="BN9" t="n">
-        <v>1.14</v>
+        <v>1.22</v>
       </c>
       <c r="BO9" t="n">
         <v>1.09</v>
       </c>
       <c r="BP9" t="n">
-        <v>4.91</v>
+        <v>5</v>
       </c>
       <c r="BQ9" t="n">
-        <v>5.23</v>
+        <v>5.22</v>
       </c>
       <c r="BR9" t="n">
-        <v>90.91</v>
+        <v>91.3</v>
       </c>
       <c r="BS9" t="n">
-        <v>68.18000000000001</v>
+        <v>69.56999999999999</v>
       </c>
       <c r="BT9" t="n">
-        <v>40.91</v>
+        <v>43.48</v>
       </c>
       <c r="BU9" t="n">
-        <v>18.18</v>
+        <v>21.74</v>
       </c>
       <c r="BV9" t="n">
-        <v>4.55</v>
+        <v>4.35</v>
       </c>
       <c r="BW9" t="n">
         <v>0</v>
       </c>
       <c r="BX9" t="n">
-        <v>45.45</v>
+        <v>47.83</v>
       </c>
       <c r="BY9" t="n">
-        <v>3.04</v>
+        <v>2.98</v>
       </c>
       <c r="BZ9" t="n">
-        <v>3.08</v>
+        <v>3.01</v>
       </c>
       <c r="CA9" t="n">
-        <v>3.5</v>
+        <v>3.49</v>
       </c>
       <c r="CB9" t="n">
-        <v>3.53</v>
+        <v>3.52</v>
       </c>
       <c r="CC9" t="n">
         <v>4.18</v>
@@ -4449,13 +4449,13 @@
         <v>2.74</v>
       </c>
       <c r="CG9" t="n">
-        <v>2.97</v>
+        <v>2.96</v>
       </c>
       <c r="CH9" t="n">
         <v>1.42</v>
       </c>
       <c r="CI9" t="n">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="CJ9" t="n">
         <v>1.77</v>
@@ -4467,10 +4467,10 @@
         <v>1.84</v>
       </c>
       <c r="CM9" t="n">
-        <v>2.55</v>
+        <v>2.56</v>
       </c>
       <c r="CN9" t="n">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="CO9" t="n">
         <v>1.28</v>
@@ -4479,19 +4479,19 @@
         <v>1.93</v>
       </c>
       <c r="CQ9" t="n">
-        <v>3.28</v>
+        <v>3.29</v>
       </c>
       <c r="CR9" t="n">
         <v>1.39</v>
       </c>
       <c r="CS9" t="n">
-        <v>2.84</v>
+        <v>2.85</v>
       </c>
       <c r="CT9" t="n">
         <v>3.08</v>
       </c>
       <c r="CU9" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="CV9" t="n">
         <v>2.08</v>
@@ -4500,16 +4500,16 @@
         <v>1.81</v>
       </c>
       <c r="CX9" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="CY9" t="n">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="CZ9" t="n">
-        <v>2.46</v>
+        <v>2.48</v>
       </c>
       <c r="DA9" t="n">
-        <v>2.01</v>
+        <v>2.02</v>
       </c>
       <c r="DB9" t="n">
         <v>1.31</v>
@@ -4521,79 +4521,79 @@
         <v>3.39</v>
       </c>
       <c r="DE9" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DF9" t="n">
-        <v>2.27</v>
+        <v>2.22</v>
       </c>
       <c r="DG9" t="n">
-        <v>2.45</v>
+        <v>2.44</v>
       </c>
       <c r="DH9" t="n">
-        <v>79.91</v>
+        <v>80.78</v>
       </c>
       <c r="DI9" t="n">
         <v>0.04</v>
       </c>
       <c r="DJ9" t="n">
-        <v>3.22</v>
+        <v>3.21</v>
       </c>
       <c r="DK9" t="n">
-        <v>4.32</v>
+        <v>4.43</v>
       </c>
       <c r="DL9" t="n">
-        <v>0.45</v>
+        <v>0.43</v>
       </c>
       <c r="DM9" t="n">
-        <v>41.77</v>
+        <v>41.78</v>
       </c>
       <c r="DN9" t="n">
-        <v>0.96</v>
+        <v>1</v>
       </c>
       <c r="DO9" t="n">
-        <v>1.82</v>
+        <v>1.96</v>
       </c>
       <c r="DP9" t="n">
-        <v>16.64</v>
+        <v>16.74</v>
       </c>
       <c r="DQ9" t="n">
-        <v>11.46</v>
+        <v>11.52</v>
       </c>
       <c r="DR9" t="n">
-        <v>8.779999999999999</v>
+        <v>8.57</v>
       </c>
       <c r="DS9" t="n">
-        <v>0</v>
+        <v>0.04</v>
       </c>
       <c r="DT9" t="n">
-        <v>0</v>
+        <v>0.04</v>
       </c>
       <c r="DU9" t="n">
         <v>0</v>
       </c>
       <c r="DV9" t="n">
-        <v>45.64</v>
+        <v>45.7</v>
       </c>
       <c r="DW9" t="n">
         <v>0.04</v>
       </c>
       <c r="DX9" t="n">
-        <v>13.5</v>
+        <v>13.61</v>
       </c>
       <c r="DY9" t="n">
-        <v>9.18</v>
+        <v>9.26</v>
       </c>
       <c r="DZ9" t="n">
-        <v>4.32</v>
+        <v>4.35</v>
       </c>
       <c r="EA9" t="n">
-        <v>19.41</v>
+        <v>19.57</v>
       </c>
       <c r="EB9" t="n">
         <v>1.46</v>
       </c>
       <c r="EC9" t="n">
-        <v>3.18</v>
+        <v>3.17</v>
       </c>
     </row>
     <row r="10">
@@ -4603,10 +4603,10 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C10" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D10" t="n">
         <v>11</v>
@@ -4615,49 +4615,49 @@
         <v>0</v>
       </c>
       <c r="F10" t="n">
-        <v>0.82</v>
+        <v>0.75</v>
       </c>
       <c r="G10" t="n">
-        <v>3.18</v>
+        <v>3.33</v>
       </c>
       <c r="H10" t="n">
-        <v>83.91</v>
+        <v>84.75</v>
       </c>
       <c r="I10" t="n">
-        <v>0.27</v>
+        <v>0.17</v>
       </c>
       <c r="J10" t="n">
-        <v>1.64</v>
+        <v>1.5</v>
       </c>
       <c r="K10" t="n">
-        <v>5.82</v>
+        <v>5.83</v>
       </c>
       <c r="L10" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="M10" t="n">
-        <v>46.64</v>
+        <v>46</v>
       </c>
       <c r="N10" t="n">
-        <v>0.82</v>
+        <v>0.75</v>
       </c>
       <c r="O10" t="n">
-        <v>2.64</v>
+        <v>2.5</v>
       </c>
       <c r="P10" t="n">
-        <v>10.91</v>
+        <v>11.08</v>
       </c>
       <c r="Q10" t="n">
-        <v>11.64</v>
+        <v>11.67</v>
       </c>
       <c r="R10" t="n">
-        <v>8.359999999999999</v>
+        <v>8.58</v>
       </c>
       <c r="S10" t="n">
-        <v>0.73</v>
+        <v>0.75</v>
       </c>
       <c r="T10" t="n">
-        <v>0.55</v>
+        <v>0.58</v>
       </c>
       <c r="U10" t="n">
         <v>0</v>
@@ -4669,28 +4669,28 @@
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>38.45</v>
+        <v>38.83</v>
       </c>
       <c r="Y10" t="n">
         <v>0</v>
       </c>
       <c r="Z10" t="n">
-        <v>10.55</v>
+        <v>10.17</v>
       </c>
       <c r="AA10" t="n">
-        <v>7.55</v>
+        <v>7.25</v>
       </c>
       <c r="AB10" t="n">
-        <v>3</v>
+        <v>2.92</v>
       </c>
       <c r="AC10" t="n">
-        <v>21.36</v>
+        <v>21.42</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.16</v>
+        <v>1.14</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.64</v>
+        <v>1.5</v>
       </c>
       <c r="AF10" t="n">
         <v>0.09</v>
@@ -4777,67 +4777,67 @@
         <v>2</v>
       </c>
       <c r="BH10" t="n">
-        <v>8.859999999999999</v>
+        <v>8.960000000000001</v>
       </c>
       <c r="BI10" t="n">
         <v>2</v>
       </c>
       <c r="BJ10" t="n">
-        <v>0.55</v>
+        <v>0.52</v>
       </c>
       <c r="BK10" t="n">
-        <v>0.32</v>
+        <v>0.3</v>
       </c>
       <c r="BL10" t="n">
-        <v>0.5</v>
+        <v>0.52</v>
       </c>
       <c r="BM10" t="n">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="BN10" t="n">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="BO10" t="n">
-        <v>0.86</v>
+        <v>0.83</v>
       </c>
       <c r="BP10" t="n">
-        <v>3.59</v>
+        <v>3.61</v>
       </c>
       <c r="BQ10" t="n">
-        <v>5.27</v>
+        <v>5.35</v>
       </c>
       <c r="BR10" t="n">
-        <v>72.73</v>
+        <v>73.91</v>
       </c>
       <c r="BS10" t="n">
-        <v>54.55</v>
+        <v>56.52</v>
       </c>
       <c r="BT10" t="n">
-        <v>45.45</v>
+        <v>43.48</v>
       </c>
       <c r="BU10" t="n">
-        <v>18.18</v>
+        <v>17.39</v>
       </c>
       <c r="BV10" t="n">
-        <v>9.09</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="BW10" t="n">
         <v>0</v>
       </c>
       <c r="BX10" t="n">
-        <v>50</v>
+        <v>52.17</v>
       </c>
       <c r="BY10" t="n">
-        <v>3.5</v>
+        <v>3.41</v>
       </c>
       <c r="BZ10" t="n">
-        <v>3.6</v>
+        <v>3.51</v>
       </c>
       <c r="CA10" t="n">
-        <v>3.54</v>
+        <v>3.52</v>
       </c>
       <c r="CB10" t="n">
-        <v>3.62</v>
+        <v>3.61</v>
       </c>
       <c r="CC10" t="n">
         <v>4.49</v>
@@ -4852,22 +4852,22 @@
         <v>2.79</v>
       </c>
       <c r="CG10" t="n">
-        <v>2.87</v>
+        <v>2.88</v>
       </c>
       <c r="CH10" t="n">
         <v>1.4</v>
       </c>
       <c r="CI10" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="CJ10" t="n">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="CK10" t="n">
         <v>1.57</v>
       </c>
       <c r="CL10" t="n">
-        <v>2</v>
+        <v>2.01</v>
       </c>
       <c r="CM10" t="n">
         <v>2.31</v>
@@ -4882,25 +4882,25 @@
         <v>1.98</v>
       </c>
       <c r="CQ10" t="n">
-        <v>3.51</v>
+        <v>3.49</v>
       </c>
       <c r="CR10" t="n">
         <v>1.4</v>
       </c>
       <c r="CS10" t="n">
-        <v>2.92</v>
+        <v>2.91</v>
       </c>
       <c r="CT10" t="n">
-        <v>3.01</v>
+        <v>3.02</v>
       </c>
       <c r="CU10" t="n">
         <v>1.43</v>
       </c>
       <c r="CV10" t="n">
-        <v>2.01</v>
+        <v>2.02</v>
       </c>
       <c r="CW10" t="n">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="CX10" t="n">
         <v>1.61</v>
@@ -4909,10 +4909,10 @@
         <v>1.98</v>
       </c>
       <c r="CZ10" t="n">
-        <v>2.3</v>
+        <v>2.31</v>
       </c>
       <c r="DA10" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="DB10" t="n">
         <v>1.33</v>
@@ -4921,49 +4921,49 @@
         <v>2.06</v>
       </c>
       <c r="DD10" t="n">
-        <v>3.57</v>
+        <v>3.56</v>
       </c>
       <c r="DE10" t="n">
         <v>0.04</v>
       </c>
       <c r="DF10" t="n">
-        <v>1</v>
+        <v>0.96</v>
       </c>
       <c r="DG10" t="n">
-        <v>2.91</v>
+        <v>3</v>
       </c>
       <c r="DH10" t="n">
-        <v>83</v>
+        <v>83.48</v>
       </c>
       <c r="DI10" t="n">
-        <v>0.14</v>
+        <v>0.09</v>
       </c>
       <c r="DJ10" t="n">
-        <v>1.86</v>
+        <v>1.78</v>
       </c>
       <c r="DK10" t="n">
-        <v>4.82</v>
+        <v>4.87</v>
       </c>
       <c r="DL10" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="DM10" t="n">
-        <v>42</v>
+        <v>41.87</v>
       </c>
       <c r="DN10" t="n">
-        <v>0.82</v>
+        <v>0.78</v>
       </c>
       <c r="DO10" t="n">
-        <v>1.91</v>
+        <v>1.87</v>
       </c>
       <c r="DP10" t="n">
-        <v>11.54</v>
+        <v>11.61</v>
       </c>
       <c r="DQ10" t="n">
-        <v>12.1</v>
+        <v>12.09</v>
       </c>
       <c r="DR10" t="n">
-        <v>8.4</v>
+        <v>8.52</v>
       </c>
       <c r="DS10" t="n">
         <v>0</v>
@@ -4975,28 +4975,28 @@
         <v>0</v>
       </c>
       <c r="DV10" t="n">
-        <v>35.86</v>
+        <v>36.17</v>
       </c>
       <c r="DW10" t="n">
         <v>0.04</v>
       </c>
       <c r="DX10" t="n">
-        <v>9.82</v>
+        <v>9.65</v>
       </c>
       <c r="DY10" t="n">
-        <v>7</v>
+        <v>6.87</v>
       </c>
       <c r="DZ10" t="n">
-        <v>2.82</v>
+        <v>2.79</v>
       </c>
       <c r="EA10" t="n">
-        <v>20.9</v>
+        <v>20.96</v>
       </c>
       <c r="EB10" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="EC10" t="n">
-        <v>1.78</v>
+        <v>1.7</v>
       </c>
     </row>
     <row r="11">
@@ -5006,13 +5006,13 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C11" t="n">
         <v>12</v>
       </c>
       <c r="D11" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E11" t="n">
         <v>0.08</v>
@@ -5096,139 +5096,139 @@
         <v>2.5</v>
       </c>
       <c r="AF11" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="AH11" t="n">
-        <v>3.1</v>
+        <v>3.09</v>
       </c>
       <c r="AI11" t="n">
-        <v>94.7</v>
+        <v>98.91</v>
       </c>
       <c r="AJ11" t="n">
         <v>0</v>
       </c>
       <c r="AK11" t="n">
-        <v>2.7</v>
+        <v>2.82</v>
       </c>
       <c r="AL11" t="n">
-        <v>6.4</v>
+        <v>6.18</v>
       </c>
       <c r="AM11" t="n">
-        <v>0.4</v>
+        <v>0.36</v>
       </c>
       <c r="AN11" t="n">
-        <v>54.3</v>
+        <v>55</v>
       </c>
       <c r="AO11" t="n">
-        <v>1.1</v>
+        <v>1.27</v>
       </c>
       <c r="AP11" t="n">
-        <v>3.3</v>
+        <v>3.09</v>
       </c>
       <c r="AQ11" t="n">
-        <v>14.1</v>
+        <v>14.55</v>
       </c>
       <c r="AR11" t="n">
-        <v>9.800000000000001</v>
+        <v>9.82</v>
       </c>
       <c r="AS11" t="n">
-        <v>8.300000000000001</v>
+        <v>8.18</v>
       </c>
       <c r="AT11" t="n">
-        <v>1.6</v>
+        <v>1.64</v>
       </c>
       <c r="AU11" t="n">
-        <v>1.2</v>
+        <v>1.09</v>
       </c>
       <c r="AV11" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="AW11" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="AX11" t="n">
         <v>0</v>
       </c>
       <c r="AY11" t="n">
-        <v>55.1</v>
+        <v>55.91</v>
       </c>
       <c r="AZ11" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="BA11" t="n">
-        <v>12.6</v>
+        <v>12.82</v>
       </c>
       <c r="BB11" t="n">
-        <v>8.699999999999999</v>
+        <v>8.91</v>
       </c>
       <c r="BC11" t="n">
-        <v>3.9</v>
+        <v>3.91</v>
       </c>
       <c r="BD11" t="n">
-        <v>23.2</v>
+        <v>23.27</v>
       </c>
       <c r="BE11" t="n">
-        <v>1.46</v>
+        <v>1.48</v>
       </c>
       <c r="BF11" t="n">
-        <v>2.5</v>
+        <v>2.64</v>
       </c>
       <c r="BG11" t="n">
-        <v>2.55</v>
+        <v>2.52</v>
       </c>
       <c r="BH11" t="n">
-        <v>10.64</v>
+        <v>10.74</v>
       </c>
       <c r="BI11" t="n">
-        <v>2.55</v>
+        <v>2.52</v>
       </c>
       <c r="BJ11" t="n">
-        <v>0.68</v>
+        <v>0.7</v>
       </c>
       <c r="BK11" t="n">
-        <v>0.41</v>
+        <v>0.39</v>
       </c>
       <c r="BL11" t="n">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="BM11" t="n">
-        <v>0.59</v>
+        <v>0.57</v>
       </c>
       <c r="BN11" t="n">
-        <v>1.45</v>
+        <v>1.43</v>
       </c>
       <c r="BO11" t="n">
         <v>1.09</v>
       </c>
       <c r="BP11" t="n">
-        <v>5.09</v>
+        <v>5.17</v>
       </c>
       <c r="BQ11" t="n">
-        <v>5.55</v>
+        <v>5.57</v>
       </c>
       <c r="BR11" t="n">
-        <v>90.91</v>
+        <v>91.3</v>
       </c>
       <c r="BS11" t="n">
-        <v>63.64</v>
+        <v>65.22</v>
       </c>
       <c r="BT11" t="n">
-        <v>40.91</v>
+        <v>39.13</v>
       </c>
       <c r="BU11" t="n">
-        <v>31.82</v>
+        <v>30.43</v>
       </c>
       <c r="BV11" t="n">
-        <v>13.64</v>
+        <v>13.04</v>
       </c>
       <c r="BW11" t="n">
-        <v>9.09</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="BX11" t="n">
-        <v>45.45</v>
+        <v>43.48</v>
       </c>
       <c r="BY11" t="n">
         <v>1.93</v>
@@ -5237,25 +5237,25 @@
         <v>2.02</v>
       </c>
       <c r="CA11" t="n">
-        <v>3.64</v>
+        <v>3.62</v>
       </c>
       <c r="CB11" t="n">
-        <v>3.73</v>
+        <v>3.7</v>
       </c>
       <c r="CC11" t="n">
-        <v>2.45</v>
+        <v>2.41</v>
       </c>
       <c r="CD11" t="n">
-        <v>2.59</v>
+        <v>2.56</v>
       </c>
       <c r="CE11" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="CF11" t="n">
-        <v>2.55</v>
+        <v>2.57</v>
       </c>
       <c r="CG11" t="n">
-        <v>3.08</v>
+        <v>3.06</v>
       </c>
       <c r="CH11" t="n">
         <v>1.47</v>
@@ -5279,31 +5279,31 @@
         <v>1.94</v>
       </c>
       <c r="CO11" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="CP11" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="CQ11" t="n">
-        <v>2.92</v>
+        <v>2.94</v>
       </c>
       <c r="CR11" t="n">
         <v>1.36</v>
       </c>
       <c r="CS11" t="n">
-        <v>2.66</v>
+        <v>2.7</v>
       </c>
       <c r="CT11" t="n">
-        <v>3.22</v>
+        <v>3.19</v>
       </c>
       <c r="CU11" t="n">
         <v>1.49</v>
       </c>
       <c r="CV11" t="n">
-        <v>2.21</v>
+        <v>2.2</v>
       </c>
       <c r="CW11" t="n">
-        <v>1.71</v>
+        <v>1.73</v>
       </c>
       <c r="CX11" t="n">
         <v>1.52</v>
@@ -5315,70 +5315,70 @@
         <v>2.5</v>
       </c>
       <c r="DA11" t="n">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="DB11" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="DC11" t="n">
-        <v>1.84</v>
+        <v>1.86</v>
       </c>
       <c r="DD11" t="n">
-        <v>3.04</v>
+        <v>3.1</v>
       </c>
       <c r="DE11" t="n">
         <v>0.13</v>
       </c>
       <c r="DF11" t="n">
-        <v>1.59</v>
+        <v>1.57</v>
       </c>
       <c r="DG11" t="n">
-        <v>3.32</v>
+        <v>3.3</v>
       </c>
       <c r="DH11" t="n">
-        <v>102.18</v>
+        <v>103.87</v>
       </c>
       <c r="DI11" t="n">
         <v>0</v>
       </c>
       <c r="DJ11" t="n">
-        <v>2.68</v>
+        <v>2.74</v>
       </c>
       <c r="DK11" t="n">
-        <v>6.45</v>
+        <v>6.35</v>
       </c>
       <c r="DL11" t="n">
-        <v>0.55</v>
+        <v>0.52</v>
       </c>
       <c r="DM11" t="n">
-        <v>57.37</v>
+        <v>57.57</v>
       </c>
       <c r="DN11" t="n">
-        <v>1.05</v>
+        <v>1.13</v>
       </c>
       <c r="DO11" t="n">
-        <v>3.14</v>
+        <v>3.04</v>
       </c>
       <c r="DP11" t="n">
-        <v>13.41</v>
+        <v>13.65</v>
       </c>
       <c r="DQ11" t="n">
-        <v>11</v>
+        <v>10.96</v>
       </c>
       <c r="DR11" t="n">
-        <v>7.77</v>
+        <v>7.74</v>
       </c>
       <c r="DS11" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="DT11" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="DU11" t="n">
         <v>0</v>
       </c>
       <c r="DV11" t="n">
-        <v>53.45</v>
+        <v>53.91</v>
       </c>
       <c r="DW11" t="n">
         <v>0.13</v>
@@ -5387,19 +5387,19 @@
         <v>15.04</v>
       </c>
       <c r="DY11" t="n">
-        <v>10.32</v>
+        <v>10.35</v>
       </c>
       <c r="DZ11" t="n">
-        <v>4.73</v>
+        <v>4.7</v>
       </c>
       <c r="EA11" t="n">
-        <v>21.59</v>
+        <v>21.69</v>
       </c>
       <c r="EB11" t="n">
         <v>1.69</v>
       </c>
       <c r="EC11" t="n">
-        <v>2.5</v>
+        <v>2.57</v>
       </c>
     </row>
     <row r="12">
@@ -5409,13 +5409,13 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C12" t="n">
         <v>12</v>
       </c>
       <c r="D12" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E12" t="n">
         <v>0.08</v>
@@ -5502,127 +5502,127 @@
         <v>0</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="AH12" t="n">
-        <v>2.2</v>
+        <v>2.27</v>
       </c>
       <c r="AI12" t="n">
-        <v>87.40000000000001</v>
+        <v>91.36</v>
       </c>
       <c r="AJ12" t="n">
         <v>0</v>
       </c>
       <c r="AK12" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AL12" t="n">
-        <v>3.2</v>
+        <v>3.36</v>
       </c>
       <c r="AM12" t="n">
-        <v>0.3</v>
+        <v>0.27</v>
       </c>
       <c r="AN12" t="n">
-        <v>33.8</v>
+        <v>35.82</v>
       </c>
       <c r="AO12" t="n">
-        <v>0.5</v>
+        <v>0.45</v>
       </c>
       <c r="AP12" t="n">
-        <v>1</v>
+        <v>1.09</v>
       </c>
       <c r="AQ12" t="n">
-        <v>13.1</v>
+        <v>13.09</v>
       </c>
       <c r="AR12" t="n">
-        <v>12.4</v>
+        <v>12.09</v>
       </c>
       <c r="AS12" t="n">
-        <v>8.300000000000001</v>
+        <v>7.82</v>
       </c>
       <c r="AT12" t="n">
-        <v>0.9</v>
+        <v>0.82</v>
       </c>
       <c r="AU12" t="n">
-        <v>0.5</v>
+        <v>0.82</v>
       </c>
       <c r="AV12" t="n">
-        <v>0</v>
+        <v>0.09</v>
       </c>
       <c r="AW12" t="n">
-        <v>0</v>
+        <v>0.09</v>
       </c>
       <c r="AX12" t="n">
         <v>0</v>
       </c>
       <c r="AY12" t="n">
-        <v>43.6</v>
+        <v>46</v>
       </c>
       <c r="AZ12" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="BA12" t="n">
-        <v>9.699999999999999</v>
+        <v>10.18</v>
       </c>
       <c r="BB12" t="n">
-        <v>6.8</v>
+        <v>6.73</v>
       </c>
       <c r="BC12" t="n">
-        <v>2.9</v>
+        <v>3.45</v>
       </c>
       <c r="BD12" t="n">
-        <v>21</v>
+        <v>21.27</v>
       </c>
       <c r="BE12" t="n">
-        <v>1.07</v>
+        <v>1.15</v>
       </c>
       <c r="BF12" t="n">
-        <v>1.9</v>
+        <v>1.82</v>
       </c>
       <c r="BG12" t="n">
-        <v>2.18</v>
+        <v>2.26</v>
       </c>
       <c r="BH12" t="n">
-        <v>9.32</v>
+        <v>9.220000000000001</v>
       </c>
       <c r="BI12" t="n">
-        <v>2.18</v>
+        <v>2.26</v>
       </c>
       <c r="BJ12" t="n">
-        <v>0.73</v>
+        <v>0.7</v>
       </c>
       <c r="BK12" t="n">
-        <v>0.41</v>
+        <v>0.48</v>
       </c>
       <c r="BL12" t="n">
-        <v>0.55</v>
+        <v>0.52</v>
       </c>
       <c r="BM12" t="n">
-        <v>0.5</v>
+        <v>0.57</v>
       </c>
       <c r="BN12" t="n">
-        <v>1.05</v>
+        <v>1.09</v>
       </c>
       <c r="BO12" t="n">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="BP12" t="n">
-        <v>4.05</v>
+        <v>4.04</v>
       </c>
       <c r="BQ12" t="n">
-        <v>5.23</v>
+        <v>5.13</v>
       </c>
       <c r="BR12" t="n">
-        <v>95.45</v>
+        <v>95.65000000000001</v>
       </c>
       <c r="BS12" t="n">
-        <v>72.73</v>
+        <v>73.91</v>
       </c>
       <c r="BT12" t="n">
-        <v>36.36</v>
+        <v>39.13</v>
       </c>
       <c r="BU12" t="n">
-        <v>13.64</v>
+        <v>17.39</v>
       </c>
       <c r="BV12" t="n">
         <v>0</v>
@@ -5631,7 +5631,7 @@
         <v>0</v>
       </c>
       <c r="BX12" t="n">
-        <v>50</v>
+        <v>47.83</v>
       </c>
       <c r="BY12" t="n">
         <v>2.72</v>
@@ -5640,16 +5640,16 @@
         <v>2.93</v>
       </c>
       <c r="CA12" t="n">
-        <v>3.52</v>
+        <v>3.51</v>
       </c>
       <c r="CB12" t="n">
-        <v>3.65</v>
+        <v>3.64</v>
       </c>
       <c r="CC12" t="n">
-        <v>3.9</v>
+        <v>3.92</v>
       </c>
       <c r="CD12" t="n">
-        <v>4.39</v>
+        <v>4.35</v>
       </c>
       <c r="CE12" t="n">
         <v>1.34</v>
@@ -5667,43 +5667,43 @@
         <v>2.09</v>
       </c>
       <c r="CJ12" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="CK12" t="n">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="CL12" t="n">
         <v>1.97</v>
       </c>
       <c r="CM12" t="n">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="CN12" t="n">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="CO12" t="n">
         <v>1.26</v>
       </c>
       <c r="CP12" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="CQ12" t="n">
-        <v>3.07</v>
+        <v>3.06</v>
       </c>
       <c r="CR12" t="n">
         <v>1.37</v>
       </c>
       <c r="CS12" t="n">
-        <v>2.73</v>
+        <v>2.74</v>
       </c>
       <c r="CT12" t="n">
-        <v>3.15</v>
+        <v>3.14</v>
       </c>
       <c r="CU12" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="CV12" t="n">
-        <v>2.15</v>
+        <v>2.14</v>
       </c>
       <c r="CW12" t="n">
         <v>1.76</v>
@@ -5712,97 +5712,97 @@
         <v>1.59</v>
       </c>
       <c r="CY12" t="n">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="CZ12" t="n">
         <v>2.36</v>
       </c>
       <c r="DA12" t="n">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="DB12" t="n">
         <v>1.28</v>
       </c>
       <c r="DC12" t="n">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="DD12" t="n">
-        <v>3.18</v>
+        <v>3.2</v>
       </c>
       <c r="DE12" t="n">
         <v>0.04</v>
       </c>
       <c r="DF12" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="DG12" t="n">
-        <v>2.27</v>
+        <v>2.3</v>
       </c>
       <c r="DH12" t="n">
-        <v>92.77</v>
+        <v>94.43000000000001</v>
       </c>
       <c r="DI12" t="n">
         <v>0.04</v>
       </c>
       <c r="DJ12" t="n">
-        <v>2.14</v>
+        <v>2.09</v>
       </c>
       <c r="DK12" t="n">
-        <v>4.05</v>
+        <v>4.09</v>
       </c>
       <c r="DL12" t="n">
-        <v>0.45</v>
+        <v>0.43</v>
       </c>
       <c r="DM12" t="n">
-        <v>39.82</v>
+        <v>40.52</v>
       </c>
       <c r="DN12" t="n">
-        <v>0.68</v>
+        <v>0.65</v>
       </c>
       <c r="DO12" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="DP12" t="n">
-        <v>12.54</v>
+        <v>12.56</v>
       </c>
       <c r="DQ12" t="n">
-        <v>12.32</v>
+        <v>12.17</v>
       </c>
       <c r="DR12" t="n">
-        <v>7.63</v>
+        <v>7.43</v>
       </c>
       <c r="DS12" t="n">
-        <v>0.18</v>
+        <v>0.22</v>
       </c>
       <c r="DT12" t="n">
-        <v>0.18</v>
+        <v>0.22</v>
       </c>
       <c r="DU12" t="n">
         <v>0</v>
       </c>
       <c r="DV12" t="n">
-        <v>47.18</v>
+        <v>48.18</v>
       </c>
       <c r="DW12" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DX12" t="n">
-        <v>11.59</v>
+        <v>11.74</v>
       </c>
       <c r="DY12" t="n">
-        <v>7.41</v>
+        <v>7.35</v>
       </c>
       <c r="DZ12" t="n">
-        <v>4.18</v>
+        <v>4.39</v>
       </c>
       <c r="EA12" t="n">
-        <v>20.91</v>
+        <v>21.04</v>
       </c>
       <c r="EB12" t="n">
-        <v>1.32</v>
+        <v>1.35</v>
       </c>
       <c r="EC12" t="n">
-        <v>1.95</v>
+        <v>1.91</v>
       </c>
     </row>
     <row r="13">
@@ -5812,94 +5812,94 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C13" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D13" t="n">
         <v>11</v>
       </c>
       <c r="E13" t="n">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="F13" t="n">
-        <v>1.64</v>
+        <v>1.58</v>
       </c>
       <c r="G13" t="n">
-        <v>3.36</v>
+        <v>3.33</v>
       </c>
       <c r="H13" t="n">
-        <v>102.45</v>
+        <v>101.67</v>
       </c>
       <c r="I13" t="n">
         <v>0</v>
       </c>
       <c r="J13" t="n">
-        <v>2.09</v>
+        <v>2.25</v>
       </c>
       <c r="K13" t="n">
-        <v>5</v>
+        <v>5.08</v>
       </c>
       <c r="L13" t="n">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="M13" t="n">
-        <v>54.45</v>
+        <v>53.08</v>
       </c>
       <c r="N13" t="n">
-        <v>0.36</v>
+        <v>0.5</v>
       </c>
       <c r="O13" t="n">
-        <v>1.64</v>
+        <v>1.75</v>
       </c>
       <c r="P13" t="n">
-        <v>11.09</v>
+        <v>10.67</v>
       </c>
       <c r="Q13" t="n">
-        <v>11.45</v>
+        <v>11.83</v>
       </c>
       <c r="R13" t="n">
-        <v>6.36</v>
+        <v>6.75</v>
       </c>
       <c r="S13" t="n">
-        <v>1</v>
+        <v>1.08</v>
       </c>
       <c r="T13" t="n">
-        <v>1.55</v>
+        <v>1.42</v>
       </c>
       <c r="U13" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="V13" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="W13" t="n">
         <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>53.45</v>
+        <v>53</v>
       </c>
       <c r="Y13" t="n">
-        <v>0.09</v>
+        <v>0.17</v>
       </c>
       <c r="Z13" t="n">
-        <v>15.55</v>
+        <v>15.33</v>
       </c>
       <c r="AA13" t="n">
-        <v>10.64</v>
+        <v>10.67</v>
       </c>
       <c r="AB13" t="n">
-        <v>4.91</v>
+        <v>4.67</v>
       </c>
       <c r="AC13" t="n">
-        <v>22.45</v>
+        <v>21.67</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.72</v>
+        <v>1.68</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="AF13" t="n">
         <v>0</v>
@@ -5983,70 +5983,70 @@
         <v>1.91</v>
       </c>
       <c r="BG13" t="n">
-        <v>2.59</v>
+        <v>2.57</v>
       </c>
       <c r="BH13" t="n">
-        <v>9.640000000000001</v>
+        <v>9.74</v>
       </c>
       <c r="BI13" t="n">
-        <v>2.59</v>
+        <v>2.57</v>
       </c>
       <c r="BJ13" t="n">
-        <v>0.73</v>
+        <v>0.7</v>
       </c>
       <c r="BK13" t="n">
-        <v>0.41</v>
+        <v>0.39</v>
       </c>
       <c r="BL13" t="n">
-        <v>0.64</v>
+        <v>0.61</v>
       </c>
       <c r="BM13" t="n">
-        <v>0.82</v>
+        <v>0.87</v>
       </c>
       <c r="BN13" t="n">
-        <v>1.45</v>
+        <v>1.48</v>
       </c>
       <c r="BO13" t="n">
-        <v>1.14</v>
+        <v>1.09</v>
       </c>
       <c r="BP13" t="n">
-        <v>3.86</v>
+        <v>3.91</v>
       </c>
       <c r="BQ13" t="n">
-        <v>5.77</v>
+        <v>5.83</v>
       </c>
       <c r="BR13" t="n">
         <v>100</v>
       </c>
       <c r="BS13" t="n">
-        <v>81.81999999999999</v>
+        <v>82.61</v>
       </c>
       <c r="BT13" t="n">
-        <v>54.55</v>
+        <v>52.17</v>
       </c>
       <c r="BU13" t="n">
-        <v>18.18</v>
+        <v>17.39</v>
       </c>
       <c r="BV13" t="n">
-        <v>4.55</v>
+        <v>4.35</v>
       </c>
       <c r="BW13" t="n">
         <v>0</v>
       </c>
       <c r="BX13" t="n">
-        <v>59.09</v>
+        <v>56.52</v>
       </c>
       <c r="BY13" t="n">
         <v>2.27</v>
       </c>
       <c r="BZ13" t="n">
-        <v>2.36</v>
+        <v>2.35</v>
       </c>
       <c r="CA13" t="n">
-        <v>3.67</v>
+        <v>3.66</v>
       </c>
       <c r="CB13" t="n">
-        <v>3.79</v>
+        <v>3.77</v>
       </c>
       <c r="CC13" t="n">
         <v>3.82</v>
@@ -6055,19 +6055,19 @@
         <v>4.06</v>
       </c>
       <c r="CE13" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="CF13" t="n">
         <v>2.49</v>
       </c>
       <c r="CG13" t="n">
-        <v>3.15</v>
+        <v>3.14</v>
       </c>
       <c r="CH13" t="n">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="CI13" t="n">
-        <v>2.17</v>
+        <v>2.16</v>
       </c>
       <c r="CJ13" t="n">
         <v>1.64</v>
@@ -6082,13 +6082,13 @@
         <v>2.52</v>
       </c>
       <c r="CN13" t="n">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="CO13" t="n">
         <v>1.22</v>
       </c>
       <c r="CP13" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="CQ13" t="n">
         <v>2.83</v>
@@ -6097,7 +6097,7 @@
         <v>1.35</v>
       </c>
       <c r="CS13" t="n">
-        <v>2.62</v>
+        <v>2.63</v>
       </c>
       <c r="CT13" t="n">
         <v>3.24</v>
@@ -6109,7 +6109,7 @@
         <v>2.3</v>
       </c>
       <c r="CW13" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="CX13" t="n">
         <v>1.54</v>
@@ -6118,7 +6118,7 @@
         <v>1.84</v>
       </c>
       <c r="CZ13" t="n">
-        <v>2.43</v>
+        <v>2.45</v>
       </c>
       <c r="DA13" t="n">
         <v>1.98</v>
@@ -6127,85 +6127,85 @@
         <v>1.24</v>
       </c>
       <c r="DC13" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="DD13" t="n">
-        <v>2.89</v>
+        <v>2.9</v>
       </c>
       <c r="DE13" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DF13" t="n">
-        <v>1.41</v>
+        <v>1.39</v>
       </c>
       <c r="DG13" t="n">
-        <v>3.36</v>
+        <v>3.34</v>
       </c>
       <c r="DH13" t="n">
-        <v>100.36</v>
+        <v>100.04</v>
       </c>
       <c r="DI13" t="n">
         <v>0.09</v>
       </c>
       <c r="DJ13" t="n">
-        <v>2</v>
+        <v>2.09</v>
       </c>
       <c r="DK13" t="n">
-        <v>5.22</v>
+        <v>5.26</v>
       </c>
       <c r="DL13" t="n">
-        <v>0.32</v>
+        <v>0.3</v>
       </c>
       <c r="DM13" t="n">
-        <v>53</v>
+        <v>52.35</v>
       </c>
       <c r="DN13" t="n">
-        <v>0.54</v>
+        <v>0.61</v>
       </c>
       <c r="DO13" t="n">
-        <v>1.86</v>
+        <v>1.91</v>
       </c>
       <c r="DP13" t="n">
-        <v>11.77</v>
+        <v>11.52</v>
       </c>
       <c r="DQ13" t="n">
-        <v>11.09</v>
+        <v>11.3</v>
       </c>
       <c r="DR13" t="n">
-        <v>7.55</v>
+        <v>7.7</v>
       </c>
       <c r="DS13" t="n">
-        <v>0.27</v>
+        <v>0.26</v>
       </c>
       <c r="DT13" t="n">
-        <v>0.27</v>
+        <v>0.26</v>
       </c>
       <c r="DU13" t="n">
         <v>0</v>
       </c>
       <c r="DV13" t="n">
-        <v>53.64</v>
+        <v>53.39</v>
       </c>
       <c r="DW13" t="n">
-        <v>0.04</v>
+        <v>0.09</v>
       </c>
       <c r="DX13" t="n">
-        <v>14.46</v>
+        <v>14.39</v>
       </c>
       <c r="DY13" t="n">
-        <v>9.91</v>
+        <v>9.960000000000001</v>
       </c>
       <c r="DZ13" t="n">
-        <v>4.55</v>
+        <v>4.44</v>
       </c>
       <c r="EA13" t="n">
-        <v>22.14</v>
+        <v>21.74</v>
       </c>
       <c r="EB13" t="n">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="EC13" t="n">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
     </row>
     <row r="14">
@@ -6215,13 +6215,13 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C14" t="n">
         <v>11</v>
       </c>
       <c r="D14" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E14" t="n">
         <v>0.18</v>
@@ -6305,139 +6305,139 @@
         <v>1.82</v>
       </c>
       <c r="AF14" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="AH14" t="n">
-        <v>2</v>
+        <v>2.17</v>
       </c>
       <c r="AI14" t="n">
-        <v>91</v>
+        <v>92.33</v>
       </c>
       <c r="AJ14" t="n">
         <v>0</v>
       </c>
       <c r="AK14" t="n">
-        <v>2.27</v>
+        <v>2.33</v>
       </c>
       <c r="AL14" t="n">
-        <v>4.45</v>
+        <v>4.58</v>
       </c>
       <c r="AM14" t="n">
-        <v>0.64</v>
+        <v>0.67</v>
       </c>
       <c r="AN14" t="n">
-        <v>45.64</v>
+        <v>44.67</v>
       </c>
       <c r="AO14" t="n">
-        <v>0.55</v>
+        <v>0.67</v>
       </c>
       <c r="AP14" t="n">
-        <v>2.45</v>
+        <v>2.42</v>
       </c>
       <c r="AQ14" t="n">
-        <v>11.64</v>
+        <v>12</v>
       </c>
       <c r="AR14" t="n">
-        <v>9.91</v>
+        <v>9.58</v>
       </c>
       <c r="AS14" t="n">
-        <v>7.55</v>
+        <v>7.67</v>
       </c>
       <c r="AT14" t="n">
-        <v>1.45</v>
+        <v>1.33</v>
       </c>
       <c r="AU14" t="n">
-        <v>1.18</v>
+        <v>1.25</v>
       </c>
       <c r="AV14" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="AW14" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="AX14" t="n">
         <v>0</v>
       </c>
       <c r="AY14" t="n">
-        <v>46.82</v>
+        <v>47.25</v>
       </c>
       <c r="AZ14" t="n">
         <v>0</v>
       </c>
       <c r="BA14" t="n">
-        <v>11</v>
+        <v>11.33</v>
       </c>
       <c r="BB14" t="n">
-        <v>7.27</v>
+        <v>7.5</v>
       </c>
       <c r="BC14" t="n">
-        <v>3.73</v>
+        <v>3.83</v>
       </c>
       <c r="BD14" t="n">
-        <v>21.91</v>
+        <v>21.08</v>
       </c>
       <c r="BE14" t="n">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="BF14" t="n">
-        <v>2.27</v>
+        <v>2.33</v>
       </c>
       <c r="BG14" t="n">
-        <v>2.41</v>
+        <v>2.39</v>
       </c>
       <c r="BH14" t="n">
-        <v>9.859999999999999</v>
+        <v>9.960000000000001</v>
       </c>
       <c r="BI14" t="n">
-        <v>2.41</v>
+        <v>2.39</v>
       </c>
       <c r="BJ14" t="n">
-        <v>0.68</v>
+        <v>0.65</v>
       </c>
       <c r="BK14" t="n">
-        <v>0.68</v>
+        <v>0.65</v>
       </c>
       <c r="BL14" t="n">
-        <v>0.68</v>
+        <v>0.65</v>
       </c>
       <c r="BM14" t="n">
-        <v>0.36</v>
+        <v>0.43</v>
       </c>
       <c r="BN14" t="n">
-        <v>1.05</v>
+        <v>1.09</v>
       </c>
       <c r="BO14" t="n">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="BP14" t="n">
         <v>5.09</v>
       </c>
       <c r="BQ14" t="n">
-        <v>4.77</v>
+        <v>4.87</v>
       </c>
       <c r="BR14" t="n">
-        <v>95.45</v>
+        <v>95.65000000000001</v>
       </c>
       <c r="BS14" t="n">
-        <v>72.73</v>
+        <v>73.91</v>
       </c>
       <c r="BT14" t="n">
-        <v>40.91</v>
+        <v>39.13</v>
       </c>
       <c r="BU14" t="n">
-        <v>27.27</v>
+        <v>26.09</v>
       </c>
       <c r="BV14" t="n">
-        <v>4.55</v>
+        <v>4.35</v>
       </c>
       <c r="BW14" t="n">
         <v>0</v>
       </c>
       <c r="BX14" t="n">
-        <v>54.55</v>
+        <v>52.17</v>
       </c>
       <c r="BY14" t="n">
         <v>2.31</v>
@@ -6452,16 +6452,16 @@
         <v>3.52</v>
       </c>
       <c r="CC14" t="n">
-        <v>3.77</v>
+        <v>3.71</v>
       </c>
       <c r="CD14" t="n">
-        <v>3.91</v>
+        <v>3.85</v>
       </c>
       <c r="CE14" t="n">
         <v>1.36</v>
       </c>
       <c r="CF14" t="n">
-        <v>2.71</v>
+        <v>2.7</v>
       </c>
       <c r="CG14" t="n">
         <v>2.98</v>
@@ -6473,19 +6473,19 @@
         <v>2.03</v>
       </c>
       <c r="CJ14" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="CK14" t="n">
         <v>1.47</v>
       </c>
       <c r="CL14" t="n">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="CM14" t="n">
         <v>2.52</v>
       </c>
       <c r="CN14" t="n">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="CO14" t="n">
         <v>1.27</v>
@@ -6494,16 +6494,16 @@
         <v>1.89</v>
       </c>
       <c r="CQ14" t="n">
-        <v>3.19</v>
+        <v>3.18</v>
       </c>
       <c r="CR14" t="n">
         <v>1.39</v>
       </c>
       <c r="CS14" t="n">
-        <v>2.87</v>
+        <v>2.86</v>
       </c>
       <c r="CT14" t="n">
-        <v>3.07</v>
+        <v>3.08</v>
       </c>
       <c r="CU14" t="n">
         <v>1.44</v>
@@ -6521,94 +6521,94 @@
         <v>1.88</v>
       </c>
       <c r="CZ14" t="n">
-        <v>2.44</v>
+        <v>2.45</v>
       </c>
       <c r="DA14" t="n">
         <v>1.93</v>
       </c>
       <c r="DB14" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="DC14" t="n">
         <v>1.99</v>
       </c>
       <c r="DD14" t="n">
-        <v>3.38</v>
+        <v>3.37</v>
       </c>
       <c r="DE14" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="DF14" t="n">
-        <v>1.68</v>
+        <v>1.66</v>
       </c>
       <c r="DG14" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="DH14" t="n">
+        <v>91.34</v>
+      </c>
+      <c r="DI14" t="n">
+        <v>0</v>
+      </c>
+      <c r="DJ14" t="n">
         <v>2.22</v>
       </c>
-      <c r="DH14" t="n">
-        <v>90.64</v>
-      </c>
-      <c r="DI14" t="n">
-        <v>0</v>
-      </c>
-      <c r="DJ14" t="n">
-        <v>2.18</v>
-      </c>
       <c r="DK14" t="n">
-        <v>4.86</v>
+        <v>4.91</v>
       </c>
       <c r="DL14" t="n">
-        <v>0.36</v>
+        <v>0.39</v>
       </c>
       <c r="DM14" t="n">
-        <v>46.68</v>
+        <v>46.13</v>
       </c>
       <c r="DN14" t="n">
-        <v>0.46</v>
+        <v>0.52</v>
       </c>
       <c r="DO14" t="n">
-        <v>2.64</v>
+        <v>2.61</v>
       </c>
       <c r="DP14" t="n">
-        <v>11.69</v>
+        <v>11.87</v>
       </c>
       <c r="DQ14" t="n">
-        <v>11.28</v>
+        <v>11.04</v>
       </c>
       <c r="DR14" t="n">
-        <v>7.41</v>
+        <v>7.48</v>
       </c>
       <c r="DS14" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DT14" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DU14" t="n">
         <v>0</v>
       </c>
       <c r="DV14" t="n">
-        <v>46.68</v>
+        <v>46.92</v>
       </c>
       <c r="DW14" t="n">
         <v>0.09</v>
       </c>
       <c r="DX14" t="n">
-        <v>11.36</v>
+        <v>11.52</v>
       </c>
       <c r="DY14" t="n">
-        <v>7.22</v>
+        <v>7.35</v>
       </c>
       <c r="DZ14" t="n">
-        <v>4.14</v>
+        <v>4.17</v>
       </c>
       <c r="EA14" t="n">
-        <v>19.86</v>
+        <v>19.52</v>
       </c>
       <c r="EB14" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="EC14" t="n">
-        <v>2.04</v>
+        <v>2.09</v>
       </c>
     </row>
     <row r="15">
@@ -6618,94 +6618,94 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C15" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D15" t="n">
         <v>11</v>
       </c>
       <c r="E15" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="F15" t="n">
-        <v>1.73</v>
+        <v>1.58</v>
       </c>
       <c r="G15" t="n">
-        <v>2.27</v>
+        <v>2.33</v>
       </c>
       <c r="H15" t="n">
-        <v>88.91</v>
+        <v>88.25</v>
       </c>
       <c r="I15" t="n">
         <v>0</v>
       </c>
       <c r="J15" t="n">
-        <v>3.09</v>
+        <v>3</v>
       </c>
       <c r="K15" t="n">
-        <v>5.18</v>
+        <v>5.5</v>
       </c>
       <c r="L15" t="n">
-        <v>0.45</v>
+        <v>0.83</v>
       </c>
       <c r="M15" t="n">
-        <v>53.27</v>
+        <v>51.83</v>
       </c>
       <c r="N15" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="O15" t="n">
+        <v>3.17</v>
+      </c>
+      <c r="P15" t="n">
+        <v>11.17</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>12.83</v>
+      </c>
+      <c r="R15" t="n">
+        <v>8.58</v>
+      </c>
+      <c r="S15" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="T15" t="n">
         <v>1</v>
       </c>
-      <c r="O15" t="n">
-        <v>2.91</v>
-      </c>
-      <c r="P15" t="n">
-        <v>11.27</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>12.27</v>
-      </c>
-      <c r="R15" t="n">
-        <v>8.550000000000001</v>
-      </c>
-      <c r="S15" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="T15" t="n">
-        <v>0.91</v>
-      </c>
       <c r="U15" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="V15" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="W15" t="n">
         <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>45.36</v>
+        <v>44.58</v>
       </c>
       <c r="Y15" t="n">
-        <v>0.36</v>
+        <v>0.33</v>
       </c>
       <c r="Z15" t="n">
-        <v>11.55</v>
+        <v>11.33</v>
       </c>
       <c r="AA15" t="n">
-        <v>7.45</v>
+        <v>7.33</v>
       </c>
       <c r="AB15" t="n">
-        <v>4.09</v>
+        <v>4</v>
       </c>
       <c r="AC15" t="n">
-        <v>20.91</v>
+        <v>20.58</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
       <c r="AE15" t="n">
-        <v>2.36</v>
+        <v>2.33</v>
       </c>
       <c r="AF15" t="n">
         <v>0.18</v>
@@ -6789,49 +6789,49 @@
         <v>1.82</v>
       </c>
       <c r="BG15" t="n">
-        <v>2.14</v>
+        <v>2.13</v>
       </c>
       <c r="BH15" t="n">
-        <v>9.859999999999999</v>
+        <v>10</v>
       </c>
       <c r="BI15" t="n">
-        <v>2.14</v>
+        <v>2.13</v>
       </c>
       <c r="BJ15" t="n">
-        <v>0.5</v>
+        <v>0.52</v>
       </c>
       <c r="BK15" t="n">
-        <v>0.68</v>
+        <v>0.65</v>
       </c>
       <c r="BL15" t="n">
-        <v>0.55</v>
+        <v>0.57</v>
       </c>
       <c r="BM15" t="n">
-        <v>0.41</v>
+        <v>0.39</v>
       </c>
       <c r="BN15" t="n">
-        <v>0.95</v>
+        <v>0.96</v>
       </c>
       <c r="BO15" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="BP15" t="n">
-        <v>4.5</v>
+        <v>4.61</v>
       </c>
       <c r="BQ15" t="n">
-        <v>5.36</v>
+        <v>5.39</v>
       </c>
       <c r="BR15" t="n">
-        <v>95.45</v>
+        <v>95.65000000000001</v>
       </c>
       <c r="BS15" t="n">
-        <v>63.64</v>
+        <v>65.22</v>
       </c>
       <c r="BT15" t="n">
-        <v>40.91</v>
+        <v>39.13</v>
       </c>
       <c r="BU15" t="n">
-        <v>13.64</v>
+        <v>13.04</v>
       </c>
       <c r="BV15" t="n">
         <v>0</v>
@@ -6840,19 +6840,19 @@
         <v>0</v>
       </c>
       <c r="BX15" t="n">
-        <v>31.82</v>
+        <v>30.43</v>
       </c>
       <c r="BY15" t="n">
-        <v>2.86</v>
+        <v>2.88</v>
       </c>
       <c r="BZ15" t="n">
-        <v>3.07</v>
+        <v>3.12</v>
       </c>
       <c r="CA15" t="n">
-        <v>3.43</v>
+        <v>3.42</v>
       </c>
       <c r="CB15" t="n">
-        <v>3.49</v>
+        <v>3.47</v>
       </c>
       <c r="CC15" t="n">
         <v>4.01</v>
@@ -6867,7 +6867,7 @@
         <v>2.84</v>
       </c>
       <c r="CG15" t="n">
-        <v>2.86</v>
+        <v>2.85</v>
       </c>
       <c r="CH15" t="n">
         <v>1.39</v>
@@ -6885,100 +6885,100 @@
         <v>1.87</v>
       </c>
       <c r="CM15" t="n">
-        <v>2.52</v>
+        <v>2.51</v>
       </c>
       <c r="CN15" t="n">
         <v>1.92</v>
       </c>
       <c r="CO15" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="CP15" t="n">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="CQ15" t="n">
-        <v>3.48</v>
+        <v>3.47</v>
       </c>
       <c r="CR15" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="CS15" t="n">
-        <v>2.95</v>
+        <v>2.97</v>
       </c>
       <c r="CT15" t="n">
-        <v>3.01</v>
+        <v>2.99</v>
       </c>
       <c r="CU15" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="CV15" t="n">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="CW15" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="CX15" t="n">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="CY15" t="n">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="CZ15" t="n">
-        <v>2.39</v>
+        <v>2.4</v>
       </c>
       <c r="DA15" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="DB15" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="DC15" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="DD15" t="n">
-        <v>3.54</v>
+        <v>3.58</v>
       </c>
       <c r="DE15" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="DF15" t="n">
-        <v>1.55</v>
+        <v>1.47</v>
       </c>
       <c r="DG15" t="n">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="DH15" t="n">
-        <v>87.14</v>
+        <v>86.87</v>
       </c>
       <c r="DI15" t="n">
         <v>0</v>
       </c>
       <c r="DJ15" t="n">
-        <v>2.54</v>
+        <v>2.52</v>
       </c>
       <c r="DK15" t="n">
-        <v>4.32</v>
+        <v>4.52</v>
       </c>
       <c r="DL15" t="n">
-        <v>0.4</v>
+        <v>0.61</v>
       </c>
       <c r="DM15" t="n">
-        <v>44.64</v>
+        <v>44.26</v>
       </c>
       <c r="DN15" t="n">
-        <v>0.82</v>
+        <v>0.87</v>
       </c>
       <c r="DO15" t="n">
-        <v>2.32</v>
+        <v>2.48</v>
       </c>
       <c r="DP15" t="n">
-        <v>11.22</v>
+        <v>11.17</v>
       </c>
       <c r="DQ15" t="n">
-        <v>12.14</v>
+        <v>12.43</v>
       </c>
       <c r="DR15" t="n">
-        <v>9.32</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="DS15" t="n">
         <v>0.13</v>
@@ -6990,22 +6990,22 @@
         <v>0</v>
       </c>
       <c r="DV15" t="n">
-        <v>45.27</v>
+        <v>44.87</v>
       </c>
       <c r="DW15" t="n">
-        <v>0.27</v>
+        <v>0.26</v>
       </c>
       <c r="DX15" t="n">
-        <v>9.82</v>
+        <v>9.779999999999999</v>
       </c>
       <c r="DY15" t="n">
-        <v>6.55</v>
+        <v>6.52</v>
       </c>
       <c r="DZ15" t="n">
-        <v>3.27</v>
+        <v>3.26</v>
       </c>
       <c r="EA15" t="n">
-        <v>19.5</v>
+        <v>19.39</v>
       </c>
       <c r="EB15" t="n">
         <v>1.17</v>
@@ -7021,94 +7021,94 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C16" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D16" t="n">
         <v>12</v>
       </c>
       <c r="E16" t="n">
-        <v>0.3</v>
+        <v>0.27</v>
       </c>
       <c r="F16" t="n">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="G16" t="n">
-        <v>3.5</v>
+        <v>3.18</v>
       </c>
       <c r="H16" t="n">
-        <v>103.4</v>
+        <v>98.45</v>
       </c>
       <c r="I16" t="n">
         <v>0</v>
       </c>
       <c r="J16" t="n">
-        <v>1.5</v>
+        <v>1.64</v>
       </c>
       <c r="K16" t="n">
-        <v>6.3</v>
+        <v>6.18</v>
       </c>
       <c r="L16" t="n">
-        <v>0.5</v>
+        <v>0.45</v>
       </c>
       <c r="M16" t="n">
-        <v>56.1</v>
+        <v>54.91</v>
       </c>
       <c r="N16" t="n">
-        <v>0.2</v>
+        <v>0.27</v>
       </c>
       <c r="O16" t="n">
-        <v>2.8</v>
+        <v>3</v>
       </c>
       <c r="P16" t="n">
-        <v>12.3</v>
+        <v>12.27</v>
       </c>
       <c r="Q16" t="n">
-        <v>9.800000000000001</v>
+        <v>9.91</v>
       </c>
       <c r="R16" t="n">
-        <v>5.3</v>
+        <v>5.36</v>
       </c>
       <c r="S16" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="T16" t="n">
-        <v>2.3</v>
+        <v>2.18</v>
       </c>
       <c r="U16" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="V16" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="W16" t="n">
         <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>52.2</v>
+        <v>50.18</v>
       </c>
       <c r="Y16" t="n">
         <v>0</v>
       </c>
       <c r="Z16" t="n">
-        <v>16.9</v>
+        <v>16.55</v>
       </c>
       <c r="AA16" t="n">
-        <v>10.2</v>
+        <v>10</v>
       </c>
       <c r="AB16" t="n">
-        <v>6.7</v>
+        <v>6.55</v>
       </c>
       <c r="AC16" t="n">
-        <v>20.1</v>
+        <v>20</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.94</v>
+        <v>1.9</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.5</v>
+        <v>1.64</v>
       </c>
       <c r="AF16" t="n">
         <v>0.08</v>
@@ -7192,70 +7192,70 @@
         <v>2.83</v>
       </c>
       <c r="BG16" t="n">
-        <v>2.23</v>
+        <v>2.17</v>
       </c>
       <c r="BH16" t="n">
-        <v>9.5</v>
+        <v>9.52</v>
       </c>
       <c r="BI16" t="n">
-        <v>2.23</v>
+        <v>2.17</v>
       </c>
       <c r="BJ16" t="n">
-        <v>0.5</v>
+        <v>0.52</v>
       </c>
       <c r="BK16" t="n">
-        <v>0.36</v>
+        <v>0.35</v>
       </c>
       <c r="BL16" t="n">
-        <v>1</v>
+        <v>0.96</v>
       </c>
       <c r="BM16" t="n">
-        <v>0.36</v>
+        <v>0.35</v>
       </c>
       <c r="BN16" t="n">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="BO16" t="n">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="BP16" t="n">
-        <v>4.68</v>
+        <v>4.83</v>
       </c>
       <c r="BQ16" t="n">
-        <v>4.82</v>
+        <v>4.7</v>
       </c>
       <c r="BR16" t="n">
-        <v>90.91</v>
+        <v>91.3</v>
       </c>
       <c r="BS16" t="n">
-        <v>72.73</v>
+        <v>69.56999999999999</v>
       </c>
       <c r="BT16" t="n">
-        <v>27.27</v>
+        <v>26.09</v>
       </c>
       <c r="BU16" t="n">
-        <v>18.18</v>
+        <v>17.39</v>
       </c>
       <c r="BV16" t="n">
-        <v>13.64</v>
+        <v>13.04</v>
       </c>
       <c r="BW16" t="n">
         <v>0</v>
       </c>
       <c r="BX16" t="n">
-        <v>40.91</v>
+        <v>39.13</v>
       </c>
       <c r="BY16" t="n">
-        <v>1.35</v>
+        <v>1.42</v>
       </c>
       <c r="BZ16" t="n">
-        <v>1.42</v>
+        <v>1.5</v>
       </c>
       <c r="CA16" t="n">
-        <v>4.2</v>
+        <v>4.16</v>
       </c>
       <c r="CB16" t="n">
-        <v>4.4</v>
+        <v>4.35</v>
       </c>
       <c r="CC16" t="n">
         <v>1.89</v>
@@ -7267,31 +7267,31 @@
         <v>1.31</v>
       </c>
       <c r="CF16" t="n">
-        <v>2.52</v>
+        <v>2.53</v>
       </c>
       <c r="CG16" t="n">
         <v>3.17</v>
       </c>
       <c r="CH16" t="n">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="CI16" t="n">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="CJ16" t="n">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="CK16" t="n">
         <v>1.47</v>
       </c>
       <c r="CL16" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="CM16" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="CN16" t="n">
         <v>1.94</v>
-      </c>
-      <c r="CM16" t="n">
-        <v>2.49</v>
-      </c>
-      <c r="CN16" t="n">
-        <v>1.95</v>
       </c>
       <c r="CO16" t="n">
         <v>1.23</v>
@@ -7300,13 +7300,13 @@
         <v>1.78</v>
       </c>
       <c r="CQ16" t="n">
-        <v>2.81</v>
+        <v>2.82</v>
       </c>
       <c r="CR16" t="n">
         <v>1.36</v>
       </c>
       <c r="CS16" t="n">
-        <v>2.64</v>
+        <v>2.65</v>
       </c>
       <c r="CT16" t="n">
         <v>3.17</v>
@@ -7315,73 +7315,73 @@
         <v>1.51</v>
       </c>
       <c r="CV16" t="n">
-        <v>2.02</v>
+        <v>2.03</v>
       </c>
       <c r="CW16" t="n">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="CX16" t="n">
         <v>1.57</v>
       </c>
       <c r="CY16" t="n">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="CZ16" t="n">
-        <v>2.39</v>
+        <v>2.37</v>
       </c>
       <c r="DA16" t="n">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="DB16" t="n">
         <v>1.26</v>
       </c>
       <c r="DC16" t="n">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="DD16" t="n">
-        <v>2.98</v>
+        <v>2.99</v>
       </c>
       <c r="DE16" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="DF16" t="n">
-        <v>1.59</v>
+        <v>1.61</v>
       </c>
       <c r="DG16" t="n">
-        <v>3.13</v>
+        <v>3</v>
       </c>
       <c r="DH16" t="n">
-        <v>107.27</v>
+        <v>104.74</v>
       </c>
       <c r="DI16" t="n">
         <v>0.04</v>
       </c>
       <c r="DJ16" t="n">
-        <v>2.27</v>
+        <v>2.31</v>
       </c>
       <c r="DK16" t="n">
-        <v>5.86</v>
+        <v>5.83</v>
       </c>
       <c r="DL16" t="n">
-        <v>0.5</v>
+        <v>0.48</v>
       </c>
       <c r="DM16" t="n">
-        <v>53.68</v>
+        <v>53.22</v>
       </c>
       <c r="DN16" t="n">
-        <v>0.68</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="DO16" t="n">
-        <v>2.73</v>
+        <v>2.83</v>
       </c>
       <c r="DP16" t="n">
-        <v>12.95</v>
+        <v>12.91</v>
       </c>
       <c r="DQ16" t="n">
-        <v>9.59</v>
+        <v>9.65</v>
       </c>
       <c r="DR16" t="n">
-        <v>5.86</v>
+        <v>5.87</v>
       </c>
       <c r="DS16" t="n">
         <v>0.09</v>
@@ -7393,28 +7393,28 @@
         <v>0</v>
       </c>
       <c r="DV16" t="n">
-        <v>53.73</v>
+        <v>52.69</v>
       </c>
       <c r="DW16" t="n">
         <v>0.04</v>
       </c>
       <c r="DX16" t="n">
-        <v>15.41</v>
+        <v>15.31</v>
       </c>
       <c r="DY16" t="n">
-        <v>9.77</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="DZ16" t="n">
-        <v>5.64</v>
+        <v>5.61</v>
       </c>
       <c r="EA16" t="n">
-        <v>19.82</v>
+        <v>19.78</v>
       </c>
       <c r="EB16" t="n">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="EC16" t="n">
-        <v>2.23</v>
+        <v>2.26</v>
       </c>
     </row>
     <row r="17">
@@ -7424,10 +7424,10 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C17" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D17" t="n">
         <v>12</v>
@@ -7439,79 +7439,79 @@
         <v>1</v>
       </c>
       <c r="G17" t="n">
-        <v>2</v>
+        <v>2.36</v>
       </c>
       <c r="H17" t="n">
-        <v>94.59999999999999</v>
+        <v>95.64</v>
       </c>
       <c r="I17" t="n">
         <v>0</v>
       </c>
       <c r="J17" t="n">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="K17" t="n">
-        <v>3.8</v>
+        <v>4.09</v>
       </c>
       <c r="L17" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="M17" t="n">
-        <v>41.7</v>
+        <v>44.55</v>
       </c>
       <c r="N17" t="n">
-        <v>0.5</v>
+        <v>0.45</v>
       </c>
       <c r="O17" t="n">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="P17" t="n">
-        <v>10.3</v>
+        <v>10.09</v>
       </c>
       <c r="Q17" t="n">
-        <v>13.1</v>
+        <v>12.91</v>
       </c>
       <c r="R17" t="n">
-        <v>10.1</v>
+        <v>10</v>
       </c>
       <c r="S17" t="n">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="T17" t="n">
-        <v>1.5</v>
+        <v>1.36</v>
       </c>
       <c r="U17" t="n">
-        <v>0.4</v>
+        <v>0.36</v>
       </c>
       <c r="V17" t="n">
-        <v>0.4</v>
+        <v>0.36</v>
       </c>
       <c r="W17" t="n">
         <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>45.4</v>
+        <v>46.45</v>
       </c>
       <c r="Y17" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="Z17" t="n">
-        <v>12.4</v>
+        <v>13</v>
       </c>
       <c r="AA17" t="n">
-        <v>7.6</v>
+        <v>8.18</v>
       </c>
       <c r="AB17" t="n">
-        <v>4.8</v>
+        <v>4.82</v>
       </c>
       <c r="AC17" t="n">
-        <v>21.4</v>
+        <v>21.55</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.42</v>
+        <v>1.48</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AF17" t="n">
         <v>0.08</v>
@@ -7595,70 +7595,70 @@
         <v>1.75</v>
       </c>
       <c r="BG17" t="n">
-        <v>2.95</v>
+        <v>2.87</v>
       </c>
       <c r="BH17" t="n">
-        <v>9.73</v>
+        <v>9.74</v>
       </c>
       <c r="BI17" t="n">
-        <v>2.95</v>
+        <v>2.87</v>
       </c>
       <c r="BJ17" t="n">
-        <v>0.77</v>
+        <v>0.74</v>
       </c>
       <c r="BK17" t="n">
-        <v>0.59</v>
+        <v>0.61</v>
       </c>
       <c r="BL17" t="n">
-        <v>0.86</v>
+        <v>0.83</v>
       </c>
       <c r="BM17" t="n">
-        <v>0.73</v>
+        <v>0.7</v>
       </c>
       <c r="BN17" t="n">
-        <v>1.59</v>
+        <v>1.52</v>
       </c>
       <c r="BO17" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="BP17" t="n">
-        <v>3.64</v>
+        <v>3.61</v>
       </c>
       <c r="BQ17" t="n">
-        <v>5.45</v>
+        <v>5.52</v>
       </c>
       <c r="BR17" t="n">
-        <v>90.91</v>
+        <v>91.3</v>
       </c>
       <c r="BS17" t="n">
-        <v>86.36</v>
+        <v>82.61</v>
       </c>
       <c r="BT17" t="n">
-        <v>50</v>
+        <v>47.83</v>
       </c>
       <c r="BU17" t="n">
-        <v>36.36</v>
+        <v>34.78</v>
       </c>
       <c r="BV17" t="n">
-        <v>22.73</v>
+        <v>21.74</v>
       </c>
       <c r="BW17" t="n">
-        <v>4.55</v>
+        <v>4.35</v>
       </c>
       <c r="BX17" t="n">
-        <v>68.18000000000001</v>
+        <v>65.22</v>
       </c>
       <c r="BY17" t="n">
-        <v>3.07</v>
+        <v>3.01</v>
       </c>
       <c r="BZ17" t="n">
-        <v>3.32</v>
+        <v>3.23</v>
       </c>
       <c r="CA17" t="n">
-        <v>3.79</v>
+        <v>3.77</v>
       </c>
       <c r="CB17" t="n">
-        <v>3.87</v>
+        <v>3.86</v>
       </c>
       <c r="CC17" t="n">
         <v>4.42</v>
@@ -7670,7 +7670,7 @@
         <v>1.3</v>
       </c>
       <c r="CF17" t="n">
-        <v>2.46</v>
+        <v>2.45</v>
       </c>
       <c r="CG17" t="n">
         <v>3.3</v>
@@ -7679,10 +7679,10 @@
         <v>1.52</v>
       </c>
       <c r="CI17" t="n">
-        <v>2.17</v>
+        <v>2.19</v>
       </c>
       <c r="CJ17" t="n">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="CK17" t="n">
         <v>1.43</v>
@@ -7691,10 +7691,10 @@
         <v>1.79</v>
       </c>
       <c r="CM17" t="n">
-        <v>2.67</v>
+        <v>2.68</v>
       </c>
       <c r="CN17" t="n">
-        <v>2.06</v>
+        <v>2.07</v>
       </c>
       <c r="CO17" t="n">
         <v>1.2</v>
@@ -7718,7 +7718,7 @@
         <v>1.53</v>
       </c>
       <c r="CV17" t="n">
-        <v>2.3</v>
+        <v>2.31</v>
       </c>
       <c r="CW17" t="n">
         <v>1.68</v>
@@ -7733,7 +7733,7 @@
         <v>2.48</v>
       </c>
       <c r="DA17" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="DB17" t="n">
         <v>1.23</v>
@@ -7742,82 +7742,82 @@
         <v>1.76</v>
       </c>
       <c r="DD17" t="n">
-        <v>2.84</v>
+        <v>2.83</v>
       </c>
       <c r="DE17" t="n">
         <v>0.04</v>
       </c>
       <c r="DF17" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="DG17" t="n">
-        <v>2.09</v>
+        <v>2.26</v>
       </c>
       <c r="DH17" t="n">
-        <v>94</v>
+        <v>94.52</v>
       </c>
       <c r="DI17" t="n">
         <v>0.04</v>
       </c>
       <c r="DJ17" t="n">
-        <v>1.77</v>
+        <v>1.74</v>
       </c>
       <c r="DK17" t="n">
-        <v>4</v>
+        <v>4.13</v>
       </c>
       <c r="DL17" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="DM17" t="n">
-        <v>44.59</v>
+        <v>45.83</v>
       </c>
       <c r="DN17" t="n">
-        <v>0.54</v>
+        <v>0.52</v>
       </c>
       <c r="DO17" t="n">
-        <v>1.59</v>
+        <v>1.57</v>
       </c>
       <c r="DP17" t="n">
-        <v>11.32</v>
+        <v>11.18</v>
       </c>
       <c r="DQ17" t="n">
-        <v>11.91</v>
+        <v>11.87</v>
       </c>
       <c r="DR17" t="n">
-        <v>9.41</v>
+        <v>9.390000000000001</v>
       </c>
       <c r="DS17" t="n">
-        <v>0.23</v>
+        <v>0.21</v>
       </c>
       <c r="DT17" t="n">
-        <v>0.23</v>
+        <v>0.21</v>
       </c>
       <c r="DU17" t="n">
         <v>0</v>
       </c>
       <c r="DV17" t="n">
-        <v>46.82</v>
+        <v>47.26</v>
       </c>
       <c r="DW17" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DX17" t="n">
-        <v>11.36</v>
+        <v>11.7</v>
       </c>
       <c r="DY17" t="n">
-        <v>7.23</v>
+        <v>7.52</v>
       </c>
       <c r="DZ17" t="n">
-        <v>4.13</v>
+        <v>4.17</v>
       </c>
       <c r="EA17" t="n">
-        <v>20.18</v>
+        <v>20.31</v>
       </c>
       <c r="EB17" t="n">
-        <v>1.33</v>
+        <v>1.37</v>
       </c>
       <c r="EC17" t="n">
-        <v>1.59</v>
+        <v>1.56</v>
       </c>
     </row>
   </sheetData>

--- a/data/teams/leagues/Averages_Belgium_Pro_League_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Belgium_Pro_League_2025-2026.xlsx
@@ -5162,16 +5162,16 @@
         <v>12.82</v>
       </c>
       <c r="BB11" t="n">
-        <v>8.91</v>
+        <v>8.82</v>
       </c>
       <c r="BC11" t="n">
-        <v>3.91</v>
+        <v>4</v>
       </c>
       <c r="BD11" t="n">
         <v>23.27</v>
       </c>
       <c r="BE11" t="n">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="BF11" t="n">
         <v>2.64</v>
@@ -5387,16 +5387,16 @@
         <v>15.04</v>
       </c>
       <c r="DY11" t="n">
-        <v>10.35</v>
+        <v>10.31</v>
       </c>
       <c r="DZ11" t="n">
-        <v>4.7</v>
+        <v>4.74</v>
       </c>
       <c r="EA11" t="n">
         <v>21.69</v>
       </c>
       <c r="EB11" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="EC11" t="n">
         <v>2.57</v>

--- a/data/teams/leagues/Averages_Belgium_Pro_League_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Belgium_Pro_League_2025-2026.xlsx
@@ -1379,13 +1379,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C2" t="n">
         <v>12</v>
       </c>
       <c r="D2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
@@ -1469,139 +1469,139 @@
         <v>1.25</v>
       </c>
       <c r="AF2" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="AG2" t="n">
-        <v>1.27</v>
+        <v>1.42</v>
       </c>
       <c r="AH2" t="n">
-        <v>2.27</v>
+        <v>2.17</v>
       </c>
       <c r="AI2" t="n">
-        <v>104.27</v>
+        <v>100.25</v>
       </c>
       <c r="AJ2" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="AK2" t="n">
-        <v>2.73</v>
+        <v>2.92</v>
       </c>
       <c r="AL2" t="n">
-        <v>4.55</v>
+        <v>4.42</v>
       </c>
       <c r="AM2" t="n">
-        <v>0.64</v>
+        <v>0.58</v>
       </c>
       <c r="AN2" t="n">
-        <v>50.73</v>
+        <v>48.08</v>
       </c>
       <c r="AO2" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AP2" t="n">
-        <v>2.27</v>
+        <v>2.25</v>
       </c>
       <c r="AQ2" t="n">
-        <v>12.45</v>
+        <v>12.42</v>
       </c>
       <c r="AR2" t="n">
-        <v>12</v>
+        <v>11.83</v>
       </c>
       <c r="AS2" t="n">
-        <v>7.55</v>
+        <v>7.83</v>
       </c>
       <c r="AT2" t="n">
-        <v>0.82</v>
+        <v>1</v>
       </c>
       <c r="AU2" t="n">
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="AV2" t="n">
-        <v>0</v>
+        <v>0.17</v>
       </c>
       <c r="AW2" t="n">
-        <v>0</v>
+        <v>0.17</v>
       </c>
       <c r="AX2" t="n">
         <v>0</v>
       </c>
       <c r="AY2" t="n">
-        <v>46.91</v>
+        <v>45.25</v>
       </c>
       <c r="AZ2" t="n">
-        <v>0.09</v>
+        <v>0.17</v>
       </c>
       <c r="BA2" t="n">
-        <v>11.91</v>
+        <v>11.83</v>
       </c>
       <c r="BB2" t="n">
-        <v>8.640000000000001</v>
+        <v>8.25</v>
       </c>
       <c r="BC2" t="n">
-        <v>3.27</v>
+        <v>3.58</v>
       </c>
       <c r="BD2" t="n">
-        <v>22</v>
+        <v>21.25</v>
       </c>
       <c r="BE2" t="n">
         <v>1.35</v>
       </c>
       <c r="BF2" t="n">
-        <v>2.55</v>
+        <v>2.58</v>
       </c>
       <c r="BG2" t="n">
-        <v>2.74</v>
+        <v>2.92</v>
       </c>
       <c r="BH2" t="n">
-        <v>10</v>
+        <v>9.960000000000001</v>
       </c>
       <c r="BI2" t="n">
-        <v>2.74</v>
+        <v>2.92</v>
       </c>
       <c r="BJ2" t="n">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="BK2" t="n">
-        <v>1</v>
+        <v>1.08</v>
       </c>
       <c r="BL2" t="n">
-        <v>0.52</v>
+        <v>0.58</v>
       </c>
       <c r="BM2" t="n">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="BN2" t="n">
-        <v>1.13</v>
+        <v>1.21</v>
       </c>
       <c r="BO2" t="n">
-        <v>1.61</v>
+        <v>1.71</v>
       </c>
       <c r="BP2" t="n">
-        <v>4.52</v>
+        <v>4.42</v>
       </c>
       <c r="BQ2" t="n">
-        <v>5.43</v>
+        <v>5.5</v>
       </c>
       <c r="BR2" t="n">
-        <v>91.3</v>
+        <v>91.67</v>
       </c>
       <c r="BS2" t="n">
-        <v>91.3</v>
+        <v>91.67</v>
       </c>
       <c r="BT2" t="n">
-        <v>43.48</v>
+        <v>45.83</v>
       </c>
       <c r="BU2" t="n">
-        <v>26.09</v>
+        <v>29.17</v>
       </c>
       <c r="BV2" t="n">
-        <v>17.39</v>
+        <v>20.83</v>
       </c>
       <c r="BW2" t="n">
-        <v>4.35</v>
+        <v>8.33</v>
       </c>
       <c r="BX2" t="n">
-        <v>60.87</v>
+        <v>62.5</v>
       </c>
       <c r="BY2" t="n">
         <v>2.33</v>
@@ -1613,52 +1613,52 @@
         <v>3.54</v>
       </c>
       <c r="CB2" t="n">
-        <v>3.67</v>
+        <v>3.65</v>
       </c>
       <c r="CC2" t="n">
-        <v>3.43</v>
+        <v>3.44</v>
       </c>
       <c r="CD2" t="n">
-        <v>3.58</v>
+        <v>3.54</v>
       </c>
       <c r="CE2" t="n">
         <v>1.32</v>
       </c>
       <c r="CF2" t="n">
-        <v>2.52</v>
+        <v>2.53</v>
       </c>
       <c r="CG2" t="n">
-        <v>3.15</v>
+        <v>3.14</v>
       </c>
       <c r="CH2" t="n">
         <v>1.48</v>
       </c>
       <c r="CI2" t="n">
-        <v>2.18</v>
+        <v>2.17</v>
       </c>
       <c r="CJ2" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="CK2" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="CL2" t="n">
-        <v>1.79</v>
+        <v>1.81</v>
       </c>
       <c r="CM2" t="n">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="CN2" t="n">
-        <v>2.04</v>
+        <v>2.03</v>
       </c>
       <c r="CO2" t="n">
         <v>1.22</v>
       </c>
       <c r="CP2" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="CQ2" t="n">
-        <v>2.87</v>
+        <v>2.9</v>
       </c>
       <c r="CR2" t="n">
         <v>1.36</v>
@@ -1673,10 +1673,10 @@
         <v>1.5</v>
       </c>
       <c r="CV2" t="n">
-        <v>2.3</v>
+        <v>2.29</v>
       </c>
       <c r="CW2" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="CX2" t="n">
         <v>1.5</v>
@@ -1685,94 +1685,94 @@
         <v>1.75</v>
       </c>
       <c r="CZ2" t="n">
-        <v>2.53</v>
+        <v>2.54</v>
       </c>
       <c r="DA2" t="n">
         <v>2.08</v>
       </c>
       <c r="DB2" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="DC2" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="DD2" t="n">
-        <v>2.91</v>
+        <v>2.94</v>
       </c>
       <c r="DE2" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DF2" t="n">
-        <v>1.09</v>
+        <v>1.17</v>
       </c>
       <c r="DG2" t="n">
-        <v>2.48</v>
+        <v>2.42</v>
       </c>
       <c r="DH2" t="n">
-        <v>105.87</v>
+        <v>103.79</v>
       </c>
       <c r="DI2" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="DJ2" t="n">
-        <v>2.09</v>
+        <v>2.21</v>
       </c>
       <c r="DK2" t="n">
-        <v>4.61</v>
+        <v>4.54</v>
       </c>
       <c r="DL2" t="n">
-        <v>0.53</v>
+        <v>0.5</v>
       </c>
       <c r="DM2" t="n">
-        <v>49.26</v>
+        <v>48</v>
       </c>
       <c r="DN2" t="n">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="DO2" t="n">
-        <v>2.13</v>
+        <v>2.12</v>
       </c>
       <c r="DP2" t="n">
-        <v>10.69</v>
+        <v>10.75</v>
       </c>
       <c r="DQ2" t="n">
-        <v>12.82</v>
+        <v>12.7</v>
       </c>
       <c r="DR2" t="n">
-        <v>7.22</v>
+        <v>7.38</v>
       </c>
       <c r="DS2" t="n">
-        <v>0.26</v>
+        <v>0.34</v>
       </c>
       <c r="DT2" t="n">
-        <v>0.26</v>
+        <v>0.34</v>
       </c>
       <c r="DU2" t="n">
         <v>0</v>
       </c>
       <c r="DV2" t="n">
-        <v>48.3</v>
+        <v>47.42</v>
       </c>
       <c r="DW2" t="n">
-        <v>0.13</v>
+        <v>0.17</v>
       </c>
       <c r="DX2" t="n">
-        <v>12.87</v>
+        <v>12.79</v>
       </c>
       <c r="DY2" t="n">
-        <v>8.869999999999999</v>
+        <v>8.67</v>
       </c>
       <c r="DZ2" t="n">
-        <v>4</v>
+        <v>4.12</v>
       </c>
       <c r="EA2" t="n">
-        <v>22.74</v>
+        <v>22.33</v>
       </c>
       <c r="EB2" t="n">
         <v>1.45</v>
       </c>
       <c r="EC2" t="n">
-        <v>1.87</v>
+        <v>1.92</v>
       </c>
     </row>
     <row r="3">
@@ -2185,13 +2185,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C4" t="n">
         <v>12</v>
       </c>
       <c r="D4" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
@@ -2275,139 +2275,139 @@
         <v>1.83</v>
       </c>
       <c r="AF4" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.82</v>
+        <v>1.75</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.55</v>
+        <v>1.42</v>
       </c>
       <c r="AI4" t="n">
-        <v>89.81999999999999</v>
+        <v>88.92</v>
       </c>
       <c r="AJ4" t="n">
-        <v>0.09</v>
+        <v>0.17</v>
       </c>
       <c r="AK4" t="n">
-        <v>2.73</v>
+        <v>2.83</v>
       </c>
       <c r="AL4" t="n">
-        <v>3.55</v>
+        <v>3.33</v>
       </c>
       <c r="AM4" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="AN4" t="n">
-        <v>39.18</v>
+        <v>38.92</v>
       </c>
       <c r="AO4" t="n">
-        <v>0.73</v>
+        <v>0.92</v>
       </c>
       <c r="AP4" t="n">
-        <v>2</v>
+        <v>1.92</v>
       </c>
       <c r="AQ4" t="n">
-        <v>12.18</v>
+        <v>11.83</v>
       </c>
       <c r="AR4" t="n">
-        <v>11.91</v>
+        <v>11.83</v>
       </c>
       <c r="AS4" t="n">
-        <v>11.09</v>
+        <v>10.83</v>
       </c>
       <c r="AT4" t="n">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="AU4" t="n">
-        <v>0.91</v>
+        <v>0.83</v>
       </c>
       <c r="AV4" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="AW4" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="AX4" t="n">
         <v>0</v>
       </c>
       <c r="AY4" t="n">
-        <v>43.09</v>
+        <v>43.67</v>
       </c>
       <c r="AZ4" t="n">
-        <v>0.36</v>
+        <v>0.33</v>
       </c>
       <c r="BA4" t="n">
-        <v>11.18</v>
+        <v>10.83</v>
       </c>
       <c r="BB4" t="n">
-        <v>6.82</v>
+        <v>6.5</v>
       </c>
       <c r="BC4" t="n">
-        <v>4.36</v>
+        <v>4.33</v>
       </c>
       <c r="BD4" t="n">
-        <v>19.18</v>
+        <v>20.17</v>
       </c>
       <c r="BE4" t="n">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="BF4" t="n">
-        <v>2.18</v>
+        <v>2.33</v>
       </c>
       <c r="BG4" t="n">
-        <v>2.35</v>
+        <v>2.29</v>
       </c>
       <c r="BH4" t="n">
-        <v>8.43</v>
+        <v>8.380000000000001</v>
       </c>
       <c r="BI4" t="n">
-        <v>2.35</v>
+        <v>2.29</v>
       </c>
       <c r="BJ4" t="n">
-        <v>0.52</v>
+        <v>0.5</v>
       </c>
       <c r="BK4" t="n">
-        <v>0.35</v>
+        <v>0.33</v>
       </c>
       <c r="BL4" t="n">
-        <v>0.57</v>
+        <v>0.58</v>
       </c>
       <c r="BM4" t="n">
-        <v>0.91</v>
+        <v>0.88</v>
       </c>
       <c r="BN4" t="n">
-        <v>1.48</v>
+        <v>1.46</v>
       </c>
       <c r="BO4" t="n">
-        <v>0.87</v>
+        <v>0.83</v>
       </c>
       <c r="BP4" t="n">
-        <v>3.74</v>
+        <v>3.71</v>
       </c>
       <c r="BQ4" t="n">
-        <v>4.13</v>
+        <v>4.12</v>
       </c>
       <c r="BR4" t="n">
-        <v>86.95999999999999</v>
+        <v>87.5</v>
       </c>
       <c r="BS4" t="n">
-        <v>69.56999999999999</v>
+        <v>66.67</v>
       </c>
       <c r="BT4" t="n">
-        <v>47.83</v>
+        <v>45.83</v>
       </c>
       <c r="BU4" t="n">
-        <v>21.74</v>
+        <v>20.83</v>
       </c>
       <c r="BV4" t="n">
-        <v>4.35</v>
+        <v>4.17</v>
       </c>
       <c r="BW4" t="n">
-        <v>4.35</v>
+        <v>4.17</v>
       </c>
       <c r="BX4" t="n">
-        <v>56.52</v>
+        <v>54.17</v>
       </c>
       <c r="BY4" t="n">
         <v>3.41</v>
@@ -2416,25 +2416,25 @@
         <v>3.57</v>
       </c>
       <c r="CA4" t="n">
-        <v>3.68</v>
+        <v>3.66</v>
       </c>
       <c r="CB4" t="n">
-        <v>3.84</v>
+        <v>3.81</v>
       </c>
       <c r="CC4" t="n">
-        <v>4.8</v>
+        <v>4.65</v>
       </c>
       <c r="CD4" t="n">
-        <v>5.08</v>
+        <v>4.93</v>
       </c>
       <c r="CE4" t="n">
         <v>1.35</v>
       </c>
       <c r="CF4" t="n">
-        <v>2.6</v>
+        <v>2.61</v>
       </c>
       <c r="CG4" t="n">
-        <v>3.06</v>
+        <v>3.07</v>
       </c>
       <c r="CH4" t="n">
         <v>1.46</v>
@@ -2449,7 +2449,7 @@
         <v>1.55</v>
       </c>
       <c r="CL4" t="n">
-        <v>2.01</v>
+        <v>2.02</v>
       </c>
       <c r="CM4" t="n">
         <v>2.35</v>
@@ -2464,7 +2464,7 @@
         <v>1.84</v>
       </c>
       <c r="CQ4" t="n">
-        <v>3.08</v>
+        <v>3.07</v>
       </c>
       <c r="CR4" t="n">
         <v>1.39</v>
@@ -2500,52 +2500,52 @@
         <v>1.28</v>
       </c>
       <c r="DC4" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="DD4" t="n">
-        <v>3.15</v>
+        <v>3.17</v>
       </c>
       <c r="DE4" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DF4" t="n">
-        <v>1.56</v>
+        <v>1.54</v>
       </c>
       <c r="DG4" t="n">
-        <v>1.48</v>
+        <v>1.42</v>
       </c>
       <c r="DH4" t="n">
-        <v>89.56</v>
+        <v>89.12</v>
       </c>
       <c r="DI4" t="n">
-        <v>-0.05</v>
+        <v>0</v>
       </c>
       <c r="DJ4" t="n">
-        <v>2.26</v>
+        <v>2.33</v>
       </c>
       <c r="DK4" t="n">
-        <v>3.48</v>
+        <v>3.38</v>
       </c>
       <c r="DL4" t="n">
         <v>0.08</v>
       </c>
       <c r="DM4" t="n">
-        <v>43.69</v>
+        <v>43.38</v>
       </c>
       <c r="DN4" t="n">
-        <v>0.61</v>
+        <v>0.71</v>
       </c>
       <c r="DO4" t="n">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="DP4" t="n">
-        <v>11.35</v>
+        <v>11.2</v>
       </c>
       <c r="DQ4" t="n">
-        <v>11.52</v>
+        <v>11.5</v>
       </c>
       <c r="DR4" t="n">
-        <v>10.69</v>
+        <v>10.58</v>
       </c>
       <c r="DS4" t="n">
         <v>0.08</v>
@@ -2557,28 +2557,28 @@
         <v>0</v>
       </c>
       <c r="DV4" t="n">
-        <v>46.7</v>
+        <v>46.84</v>
       </c>
       <c r="DW4" t="n">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
       <c r="DX4" t="n">
-        <v>10.87</v>
+        <v>10.7</v>
       </c>
       <c r="DY4" t="n">
-        <v>7.04</v>
+        <v>6.88</v>
       </c>
       <c r="DZ4" t="n">
-        <v>3.82</v>
+        <v>3.83</v>
       </c>
       <c r="EA4" t="n">
-        <v>21.08</v>
+        <v>21.5</v>
       </c>
       <c r="EB4" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="EC4" t="n">
-        <v>2</v>
+        <v>2.08</v>
       </c>
     </row>
     <row r="5">
@@ -2588,94 +2588,94 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C5" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D5" t="n">
         <v>12</v>
       </c>
       <c r="E5" t="n">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="F5" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="G5" t="n">
-        <v>2.73</v>
+        <v>2.75</v>
       </c>
       <c r="H5" t="n">
-        <v>105.73</v>
+        <v>106.17</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="K5" t="n">
-        <v>5</v>
+        <v>5.08</v>
       </c>
       <c r="L5" t="n">
-        <v>0.36</v>
+        <v>0.42</v>
       </c>
       <c r="M5" t="n">
-        <v>48.36</v>
+        <v>54</v>
       </c>
       <c r="N5" t="n">
-        <v>0.45</v>
+        <v>0.5</v>
       </c>
       <c r="O5" t="n">
-        <v>2.27</v>
+        <v>2.33</v>
       </c>
       <c r="P5" t="n">
-        <v>10.82</v>
+        <v>11.08</v>
       </c>
       <c r="Q5" t="n">
-        <v>10.82</v>
+        <v>10.92</v>
       </c>
       <c r="R5" t="n">
-        <v>8.09</v>
+        <v>8.08</v>
       </c>
       <c r="S5" t="n">
-        <v>1.09</v>
+        <v>1.25</v>
       </c>
       <c r="T5" t="n">
-        <v>1.91</v>
+        <v>1.83</v>
       </c>
       <c r="U5" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="V5" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="W5" t="n">
         <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>54.55</v>
+        <v>55.33</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="Z5" t="n">
-        <v>15.64</v>
+        <v>16.17</v>
       </c>
       <c r="AA5" t="n">
-        <v>11.27</v>
+        <v>11.92</v>
       </c>
       <c r="AB5" t="n">
-        <v>4.36</v>
+        <v>4.25</v>
       </c>
       <c r="AC5" t="n">
-        <v>19.09</v>
+        <v>19.67</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.65</v>
+        <v>1.71</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.55</v>
+        <v>1.58</v>
       </c>
       <c r="AF5" t="n">
         <v>0.08</v>
@@ -2759,70 +2759,70 @@
         <v>1.58</v>
       </c>
       <c r="BG5" t="n">
-        <v>3</v>
+        <v>3.04</v>
       </c>
       <c r="BH5" t="n">
-        <v>10.17</v>
+        <v>10.21</v>
       </c>
       <c r="BI5" t="n">
-        <v>3</v>
+        <v>3.04</v>
       </c>
       <c r="BJ5" t="n">
-        <v>0.83</v>
+        <v>0.79</v>
       </c>
       <c r="BK5" t="n">
-        <v>0.52</v>
+        <v>0.58</v>
       </c>
       <c r="BL5" t="n">
         <v>0.96</v>
       </c>
       <c r="BM5" t="n">
-        <v>0.7</v>
+        <v>0.71</v>
       </c>
       <c r="BN5" t="n">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="BO5" t="n">
-        <v>1.35</v>
+        <v>1.38</v>
       </c>
       <c r="BP5" t="n">
-        <v>4.04</v>
+        <v>4.12</v>
       </c>
       <c r="BQ5" t="n">
-        <v>6.13</v>
+        <v>6.08</v>
       </c>
       <c r="BR5" t="n">
-        <v>95.65000000000001</v>
+        <v>95.83</v>
       </c>
       <c r="BS5" t="n">
-        <v>86.95999999999999</v>
+        <v>87.5</v>
       </c>
       <c r="BT5" t="n">
-        <v>56.52</v>
+        <v>58.33</v>
       </c>
       <c r="BU5" t="n">
-        <v>34.78</v>
+        <v>37.5</v>
       </c>
       <c r="BV5" t="n">
-        <v>17.39</v>
+        <v>16.67</v>
       </c>
       <c r="BW5" t="n">
-        <v>8.699999999999999</v>
+        <v>8.33</v>
       </c>
       <c r="BX5" t="n">
-        <v>60.87</v>
+        <v>62.5</v>
       </c>
       <c r="BY5" t="n">
-        <v>2.71</v>
+        <v>2.65</v>
       </c>
       <c r="BZ5" t="n">
-        <v>2.83</v>
+        <v>2.76</v>
       </c>
       <c r="CA5" t="n">
         <v>3.59</v>
       </c>
       <c r="CB5" t="n">
-        <v>3.77</v>
+        <v>3.76</v>
       </c>
       <c r="CC5" t="n">
         <v>3.58</v>
@@ -2831,49 +2831,49 @@
         <v>3.9</v>
       </c>
       <c r="CE5" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="CF5" t="n">
         <v>2.48</v>
       </c>
       <c r="CG5" t="n">
-        <v>3.22</v>
+        <v>3.21</v>
       </c>
       <c r="CH5" t="n">
         <v>1.5</v>
       </c>
       <c r="CI5" t="n">
-        <v>2.22</v>
+        <v>2.21</v>
       </c>
       <c r="CJ5" t="n">
         <v>1.63</v>
       </c>
       <c r="CK5" t="n">
-        <v>1.45</v>
+        <v>1.47</v>
       </c>
       <c r="CL5" t="n">
-        <v>1.86</v>
+        <v>1.88</v>
       </c>
       <c r="CM5" t="n">
-        <v>2.56</v>
+        <v>2.53</v>
       </c>
       <c r="CN5" t="n">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="CO5" t="n">
         <v>1.22</v>
       </c>
       <c r="CP5" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="CQ5" t="n">
-        <v>2.76</v>
+        <v>2.78</v>
       </c>
       <c r="CR5" t="n">
         <v>1.36</v>
       </c>
       <c r="CS5" t="n">
-        <v>2.53</v>
+        <v>2.54</v>
       </c>
       <c r="CT5" t="n">
         <v>3.22</v>
@@ -2888,16 +2888,16 @@
         <v>1.67</v>
       </c>
       <c r="CX5" t="n">
-        <v>1.52</v>
+        <v>1.55</v>
       </c>
       <c r="CY5" t="n">
-        <v>1.79</v>
+        <v>1.81</v>
       </c>
       <c r="CZ5" t="n">
-        <v>2.49</v>
+        <v>2.44</v>
       </c>
       <c r="DA5" t="n">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="DB5" t="n">
         <v>1.24</v>
@@ -2906,49 +2906,49 @@
         <v>1.78</v>
       </c>
       <c r="DD5" t="n">
-        <v>2.88</v>
+        <v>2.89</v>
       </c>
       <c r="DE5" t="n">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
       <c r="DF5" t="n">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="DG5" t="n">
-        <v>2.78</v>
+        <v>2.79</v>
       </c>
       <c r="DH5" t="n">
-        <v>96.52</v>
+        <v>97.12</v>
       </c>
       <c r="DI5" t="n">
         <v>-0.04</v>
       </c>
       <c r="DJ5" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="DK5" t="n">
-        <v>4.83</v>
+        <v>4.88</v>
       </c>
       <c r="DL5" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.58</v>
       </c>
       <c r="DM5" t="n">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="DN5" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.59</v>
       </c>
       <c r="DO5" t="n">
-        <v>2.04</v>
+        <v>2.08</v>
       </c>
       <c r="DP5" t="n">
-        <v>10.91</v>
+        <v>11.04</v>
       </c>
       <c r="DQ5" t="n">
-        <v>11.04</v>
+        <v>11.08</v>
       </c>
       <c r="DR5" t="n">
-        <v>9.57</v>
+        <v>9.5</v>
       </c>
       <c r="DS5" t="n">
         <v>0.08</v>
@@ -2960,28 +2960,28 @@
         <v>0</v>
       </c>
       <c r="DV5" t="n">
-        <v>51.48</v>
+        <v>52</v>
       </c>
       <c r="DW5" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="DX5" t="n">
-        <v>13.39</v>
+        <v>13.75</v>
       </c>
       <c r="DY5" t="n">
-        <v>8.82</v>
+        <v>9.25</v>
       </c>
       <c r="DZ5" t="n">
-        <v>4.56</v>
+        <v>4.5</v>
       </c>
       <c r="EA5" t="n">
-        <v>18.39</v>
+        <v>18.71</v>
       </c>
       <c r="EB5" t="n">
-        <v>1.49</v>
+        <v>1.52</v>
       </c>
       <c r="EC5" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
     </row>
     <row r="6">
@@ -3797,94 +3797,94 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C8" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D8" t="n">
         <v>12</v>
       </c>
       <c r="E8" t="n">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="F8" t="n">
-        <v>0.91</v>
+        <v>1.08</v>
       </c>
       <c r="G8" t="n">
-        <v>3.09</v>
+        <v>3</v>
       </c>
       <c r="H8" t="n">
-        <v>100.73</v>
+        <v>99.33</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>1.27</v>
+        <v>1.42</v>
       </c>
       <c r="K8" t="n">
-        <v>6.27</v>
+        <v>6.25</v>
       </c>
       <c r="L8" t="n">
-        <v>0.36</v>
+        <v>0.33</v>
       </c>
       <c r="M8" t="n">
-        <v>57.73</v>
+        <v>57.58</v>
       </c>
       <c r="N8" t="n">
-        <v>0.36</v>
+        <v>0.33</v>
       </c>
       <c r="O8" t="n">
-        <v>3.18</v>
+        <v>3.25</v>
       </c>
       <c r="P8" t="n">
-        <v>10.55</v>
+        <v>10.75</v>
       </c>
       <c r="Q8" t="n">
         <v>12</v>
       </c>
       <c r="R8" t="n">
-        <v>7.82</v>
+        <v>7.75</v>
       </c>
       <c r="S8" t="n">
-        <v>0.82</v>
+        <v>1.08</v>
       </c>
       <c r="T8" t="n">
-        <v>1.27</v>
+        <v>1.17</v>
       </c>
       <c r="U8" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="V8" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>52.09</v>
+        <v>51.92</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>0.08</v>
       </c>
       <c r="Z8" t="n">
-        <v>17.18</v>
+        <v>16.42</v>
       </c>
       <c r="AA8" t="n">
-        <v>12</v>
+        <v>11.58</v>
       </c>
       <c r="AB8" t="n">
-        <v>5.18</v>
+        <v>4.83</v>
       </c>
       <c r="AC8" t="n">
-        <v>20.64</v>
+        <v>20.25</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.86</v>
+        <v>1.79</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.27</v>
+        <v>1.33</v>
       </c>
       <c r="AF8" t="n">
         <v>0.08</v>
@@ -3968,70 +3968,70 @@
         <v>1.58</v>
       </c>
       <c r="BG8" t="n">
-        <v>2.74</v>
+        <v>2.79</v>
       </c>
       <c r="BH8" t="n">
-        <v>10.43</v>
+        <v>10.46</v>
       </c>
       <c r="BI8" t="n">
-        <v>2.74</v>
+        <v>2.79</v>
       </c>
       <c r="BJ8" t="n">
-        <v>0.78</v>
+        <v>0.75</v>
       </c>
       <c r="BK8" t="n">
-        <v>0.57</v>
+        <v>0.67</v>
       </c>
       <c r="BL8" t="n">
-        <v>0.87</v>
+        <v>0.83</v>
       </c>
       <c r="BM8" t="n">
-        <v>0.52</v>
+        <v>0.54</v>
       </c>
       <c r="BN8" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="BO8" t="n">
-        <v>1.35</v>
+        <v>1.42</v>
       </c>
       <c r="BP8" t="n">
-        <v>4.83</v>
+        <v>4.92</v>
       </c>
       <c r="BQ8" t="n">
-        <v>5.57</v>
+        <v>5.5</v>
       </c>
       <c r="BR8" t="n">
-        <v>91.3</v>
+        <v>91.67</v>
       </c>
       <c r="BS8" t="n">
-        <v>78.26000000000001</v>
+        <v>79.17</v>
       </c>
       <c r="BT8" t="n">
-        <v>34.78</v>
+        <v>37.5</v>
       </c>
       <c r="BU8" t="n">
-        <v>26.09</v>
+        <v>29.17</v>
       </c>
       <c r="BV8" t="n">
-        <v>13.04</v>
+        <v>12.5</v>
       </c>
       <c r="BW8" t="n">
-        <v>8.699999999999999</v>
+        <v>8.33</v>
       </c>
       <c r="BX8" t="n">
-        <v>39.13</v>
+        <v>37.5</v>
       </c>
       <c r="BY8" t="n">
-        <v>2.19</v>
+        <v>2.2</v>
       </c>
       <c r="BZ8" t="n">
-        <v>2.31</v>
+        <v>2.32</v>
       </c>
       <c r="CA8" t="n">
-        <v>3.8</v>
+        <v>3.79</v>
       </c>
       <c r="CB8" t="n">
-        <v>3.88</v>
+        <v>3.87</v>
       </c>
       <c r="CC8" t="n">
         <v>3.99</v>
@@ -4061,13 +4061,13 @@
         <v>1.35</v>
       </c>
       <c r="CL8" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="CM8" t="n">
-        <v>2.89</v>
+        <v>2.88</v>
       </c>
       <c r="CN8" t="n">
-        <v>2.22</v>
+        <v>2.21</v>
       </c>
       <c r="CO8" t="n">
         <v>1.16</v>
@@ -4076,7 +4076,7 @@
         <v>1.61</v>
       </c>
       <c r="CQ8" t="n">
-        <v>2.47</v>
+        <v>2.46</v>
       </c>
       <c r="CR8" t="n">
         <v>1.34</v>
@@ -4091,106 +4091,106 @@
         <v>1.63</v>
       </c>
       <c r="CV8" t="n">
-        <v>2.56</v>
+        <v>2.57</v>
       </c>
       <c r="CW8" t="n">
         <v>1.55</v>
       </c>
       <c r="CX8" t="n">
-        <v>1.46</v>
+        <v>1.5</v>
       </c>
       <c r="CY8" t="n">
         <v>1.64</v>
       </c>
       <c r="CZ8" t="n">
-        <v>2.67</v>
+        <v>2.54</v>
       </c>
       <c r="DA8" t="n">
-        <v>2.25</v>
+        <v>2.24</v>
       </c>
       <c r="DB8" t="n">
         <v>1.19</v>
       </c>
       <c r="DC8" t="n">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="DD8" t="n">
-        <v>2.51</v>
+        <v>2.5</v>
       </c>
       <c r="DE8" t="n">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
       <c r="DF8" t="n">
-        <v>1.26</v>
+        <v>1.33</v>
       </c>
       <c r="DG8" t="n">
-        <v>2.56</v>
+        <v>2.54</v>
       </c>
       <c r="DH8" t="n">
-        <v>93.7</v>
+        <v>93.29000000000001</v>
       </c>
       <c r="DI8" t="n">
         <v>0</v>
       </c>
       <c r="DJ8" t="n">
-        <v>1.52</v>
+        <v>1.58</v>
       </c>
       <c r="DK8" t="n">
-        <v>5.26</v>
+        <v>5.29</v>
       </c>
       <c r="DL8" t="n">
-        <v>0.3</v>
+        <v>0.29</v>
       </c>
       <c r="DM8" t="n">
-        <v>49.87</v>
+        <v>50.12</v>
       </c>
       <c r="DN8" t="n">
-        <v>0.21</v>
+        <v>0.2</v>
       </c>
       <c r="DO8" t="n">
-        <v>2.69</v>
+        <v>2.75</v>
       </c>
       <c r="DP8" t="n">
-        <v>11.87</v>
+        <v>11.92</v>
       </c>
       <c r="DQ8" t="n">
-        <v>11.78</v>
+        <v>11.79</v>
       </c>
       <c r="DR8" t="n">
-        <v>8.44</v>
+        <v>8.380000000000001</v>
       </c>
       <c r="DS8" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="DT8" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="DU8" t="n">
         <v>0</v>
       </c>
       <c r="DV8" t="n">
-        <v>49.39</v>
+        <v>49.42</v>
       </c>
       <c r="DW8" t="n">
-        <v>0.04</v>
+        <v>0.08</v>
       </c>
       <c r="DX8" t="n">
-        <v>15.09</v>
+        <v>14.8</v>
       </c>
       <c r="DY8" t="n">
-        <v>10.35</v>
+        <v>10.2</v>
       </c>
       <c r="DZ8" t="n">
-        <v>4.74</v>
+        <v>4.58</v>
       </c>
       <c r="EA8" t="n">
-        <v>21.39</v>
+        <v>21.16</v>
       </c>
       <c r="EB8" t="n">
-        <v>1.63</v>
+        <v>1.6</v>
       </c>
       <c r="EC8" t="n">
-        <v>1.43</v>
+        <v>1.46</v>
       </c>
     </row>
     <row r="9">
@@ -4200,13 +4200,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C9" t="n">
         <v>12</v>
       </c>
       <c r="D9" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E9" t="n">
         <v>0.25</v>
@@ -4293,136 +4293,136 @@
         <v>0</v>
       </c>
       <c r="AG9" t="n">
-        <v>2.18</v>
+        <v>2.33</v>
       </c>
       <c r="AH9" t="n">
-        <v>2.55</v>
+        <v>2.5</v>
       </c>
       <c r="AI9" t="n">
-        <v>79.91</v>
+        <v>78.33</v>
       </c>
       <c r="AJ9" t="n">
         <v>0</v>
       </c>
       <c r="AK9" t="n">
-        <v>3.36</v>
+        <v>3.5</v>
       </c>
       <c r="AL9" t="n">
-        <v>4.27</v>
+        <v>4.33</v>
       </c>
       <c r="AM9" t="n">
-        <v>0.45</v>
+        <v>0.5</v>
       </c>
       <c r="AN9" t="n">
-        <v>43.09</v>
+        <v>45.75</v>
       </c>
       <c r="AO9" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AP9" t="n">
-        <v>1.73</v>
+        <v>1.83</v>
       </c>
       <c r="AQ9" t="n">
-        <v>16.73</v>
+        <v>16.17</v>
       </c>
       <c r="AR9" t="n">
-        <v>10.36</v>
+        <v>10.67</v>
       </c>
       <c r="AS9" t="n">
-        <v>8.91</v>
+        <v>9</v>
       </c>
       <c r="AT9" t="n">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="AU9" t="n">
-        <v>0.64</v>
+        <v>0.83</v>
       </c>
       <c r="AV9" t="n">
-        <v>0</v>
+        <v>0.08</v>
       </c>
       <c r="AW9" t="n">
-        <v>0</v>
+        <v>0.08</v>
       </c>
       <c r="AX9" t="n">
         <v>0</v>
       </c>
       <c r="AY9" t="n">
-        <v>45.64</v>
+        <v>44.83</v>
       </c>
       <c r="AZ9" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="BA9" t="n">
-        <v>12.45</v>
+        <v>12.5</v>
       </c>
       <c r="BB9" t="n">
-        <v>8.449999999999999</v>
+        <v>8.5</v>
       </c>
       <c r="BC9" t="n">
         <v>4</v>
       </c>
       <c r="BD9" t="n">
-        <v>19.55</v>
+        <v>19.33</v>
       </c>
       <c r="BE9" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="BF9" t="n">
-        <v>3.27</v>
+        <v>3.42</v>
       </c>
       <c r="BG9" t="n">
-        <v>2.3</v>
+        <v>2.38</v>
       </c>
       <c r="BH9" t="n">
-        <v>10.26</v>
+        <v>10.29</v>
       </c>
       <c r="BI9" t="n">
-        <v>2.3</v>
+        <v>2.38</v>
       </c>
       <c r="BJ9" t="n">
-        <v>0.7</v>
+        <v>0.67</v>
       </c>
       <c r="BK9" t="n">
-        <v>0.39</v>
+        <v>0.46</v>
       </c>
       <c r="BL9" t="n">
-        <v>0.65</v>
+        <v>0.67</v>
       </c>
       <c r="BM9" t="n">
-        <v>0.57</v>
+        <v>0.58</v>
       </c>
       <c r="BN9" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="BO9" t="n">
-        <v>1.09</v>
+        <v>1.12</v>
       </c>
       <c r="BP9" t="n">
-        <v>5</v>
+        <v>5.04</v>
       </c>
       <c r="BQ9" t="n">
-        <v>5.22</v>
+        <v>5.21</v>
       </c>
       <c r="BR9" t="n">
-        <v>91.3</v>
+        <v>91.67</v>
       </c>
       <c r="BS9" t="n">
-        <v>69.56999999999999</v>
+        <v>70.83</v>
       </c>
       <c r="BT9" t="n">
-        <v>43.48</v>
+        <v>45.83</v>
       </c>
       <c r="BU9" t="n">
-        <v>21.74</v>
+        <v>25</v>
       </c>
       <c r="BV9" t="n">
-        <v>4.35</v>
+        <v>4.17</v>
       </c>
       <c r="BW9" t="n">
         <v>0</v>
       </c>
       <c r="BX9" t="n">
-        <v>47.83</v>
+        <v>50</v>
       </c>
       <c r="BY9" t="n">
         <v>2.98</v>
@@ -4437,40 +4437,40 @@
         <v>3.52</v>
       </c>
       <c r="CC9" t="n">
-        <v>4.18</v>
+        <v>4.14</v>
       </c>
       <c r="CD9" t="n">
-        <v>4.43</v>
+        <v>4.39</v>
       </c>
       <c r="CE9" t="n">
         <v>1.37</v>
       </c>
       <c r="CF9" t="n">
-        <v>2.74</v>
+        <v>2.73</v>
       </c>
       <c r="CG9" t="n">
-        <v>2.96</v>
+        <v>2.97</v>
       </c>
       <c r="CH9" t="n">
         <v>1.42</v>
       </c>
       <c r="CI9" t="n">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="CJ9" t="n">
         <v>1.77</v>
       </c>
       <c r="CK9" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="CL9" t="n">
-        <v>1.84</v>
+        <v>1.86</v>
       </c>
       <c r="CM9" t="n">
-        <v>2.56</v>
+        <v>2.53</v>
       </c>
       <c r="CN9" t="n">
-        <v>1.99</v>
+        <v>1.97</v>
       </c>
       <c r="CO9" t="n">
         <v>1.28</v>
@@ -4479,13 +4479,13 @@
         <v>1.93</v>
       </c>
       <c r="CQ9" t="n">
-        <v>3.29</v>
+        <v>3.28</v>
       </c>
       <c r="CR9" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="CS9" t="n">
-        <v>2.85</v>
+        <v>2.84</v>
       </c>
       <c r="CT9" t="n">
         <v>3.08</v>
@@ -4494,106 +4494,106 @@
         <v>1.44</v>
       </c>
       <c r="CV9" t="n">
-        <v>2.08</v>
+        <v>2.09</v>
       </c>
       <c r="CW9" t="n">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="CX9" t="n">
-        <v>1.52</v>
+        <v>1.55</v>
       </c>
       <c r="CY9" t="n">
-        <v>1.8</v>
+        <v>1.82</v>
       </c>
       <c r="CZ9" t="n">
-        <v>2.48</v>
+        <v>2.44</v>
       </c>
       <c r="DA9" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="DB9" t="n">
         <v>1.31</v>
       </c>
       <c r="DC9" t="n">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="DD9" t="n">
-        <v>3.39</v>
+        <v>3.38</v>
       </c>
       <c r="DE9" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="DF9" t="n">
-        <v>2.22</v>
+        <v>2.29</v>
       </c>
       <c r="DG9" t="n">
-        <v>2.44</v>
+        <v>2.42</v>
       </c>
       <c r="DH9" t="n">
-        <v>80.78</v>
+        <v>79.95999999999999</v>
       </c>
       <c r="DI9" t="n">
         <v>0.04</v>
       </c>
       <c r="DJ9" t="n">
-        <v>3.21</v>
+        <v>3.29</v>
       </c>
       <c r="DK9" t="n">
-        <v>4.43</v>
+        <v>4.46</v>
       </c>
       <c r="DL9" t="n">
-        <v>0.43</v>
+        <v>0.46</v>
       </c>
       <c r="DM9" t="n">
-        <v>41.78</v>
+        <v>43.16</v>
       </c>
       <c r="DN9" t="n">
         <v>1</v>
       </c>
       <c r="DO9" t="n">
-        <v>1.96</v>
+        <v>2</v>
       </c>
       <c r="DP9" t="n">
-        <v>16.74</v>
+        <v>16.46</v>
       </c>
       <c r="DQ9" t="n">
-        <v>11.52</v>
+        <v>11.62</v>
       </c>
       <c r="DR9" t="n">
-        <v>8.57</v>
+        <v>8.619999999999999</v>
       </c>
       <c r="DS9" t="n">
-        <v>0.04</v>
+        <v>0.08</v>
       </c>
       <c r="DT9" t="n">
-        <v>0.04</v>
+        <v>0.08</v>
       </c>
       <c r="DU9" t="n">
         <v>0</v>
       </c>
       <c r="DV9" t="n">
-        <v>45.7</v>
+        <v>45.29</v>
       </c>
       <c r="DW9" t="n">
         <v>0.04</v>
       </c>
       <c r="DX9" t="n">
-        <v>13.61</v>
+        <v>13.58</v>
       </c>
       <c r="DY9" t="n">
-        <v>9.26</v>
+        <v>9.25</v>
       </c>
       <c r="DZ9" t="n">
-        <v>4.35</v>
+        <v>4.34</v>
       </c>
       <c r="EA9" t="n">
-        <v>19.57</v>
+        <v>19.45</v>
       </c>
       <c r="EB9" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="EC9" t="n">
-        <v>3.17</v>
+        <v>3.25</v>
       </c>
     </row>
     <row r="10">
@@ -5812,13 +5812,13 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C13" t="n">
         <v>12</v>
       </c>
       <c r="D13" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E13" t="n">
         <v>0.25</v>
@@ -5902,139 +5902,139 @@
         <v>1.92</v>
       </c>
       <c r="AF13" t="n">
-        <v>0</v>
+        <v>0.08</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="AH13" t="n">
-        <v>3.36</v>
+        <v>3.25</v>
       </c>
       <c r="AI13" t="n">
-        <v>98.27</v>
+        <v>96.17</v>
       </c>
       <c r="AJ13" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="AK13" t="n">
-        <v>1.91</v>
+        <v>1.83</v>
       </c>
       <c r="AL13" t="n">
-        <v>5.45</v>
+        <v>5.42</v>
       </c>
       <c r="AM13" t="n">
-        <v>0.36</v>
+        <v>0.42</v>
       </c>
       <c r="AN13" t="n">
-        <v>51.55</v>
+        <v>50.33</v>
       </c>
       <c r="AO13" t="n">
-        <v>0.73</v>
+        <v>0.75</v>
       </c>
       <c r="AP13" t="n">
-        <v>2.09</v>
+        <v>2.17</v>
       </c>
       <c r="AQ13" t="n">
-        <v>12.45</v>
+        <v>12.42</v>
       </c>
       <c r="AR13" t="n">
-        <v>10.73</v>
+        <v>10.92</v>
       </c>
       <c r="AS13" t="n">
-        <v>8.73</v>
+        <v>8.67</v>
       </c>
       <c r="AT13" t="n">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="AU13" t="n">
-        <v>1.45</v>
+        <v>1.67</v>
       </c>
       <c r="AV13" t="n">
-        <v>0.36</v>
+        <v>0.33</v>
       </c>
       <c r="AW13" t="n">
-        <v>0.36</v>
+        <v>0.33</v>
       </c>
       <c r="AX13" t="n">
         <v>0</v>
       </c>
       <c r="AY13" t="n">
-        <v>53.82</v>
+        <v>53.5</v>
       </c>
       <c r="AZ13" t="n">
         <v>0</v>
       </c>
       <c r="BA13" t="n">
-        <v>13.36</v>
+        <v>13.67</v>
       </c>
       <c r="BB13" t="n">
-        <v>9.18</v>
+        <v>9.33</v>
       </c>
       <c r="BC13" t="n">
-        <v>4.18</v>
+        <v>4.33</v>
       </c>
       <c r="BD13" t="n">
-        <v>21.82</v>
+        <v>21.58</v>
       </c>
       <c r="BE13" t="n">
-        <v>1.51</v>
+        <v>1.53</v>
       </c>
       <c r="BF13" t="n">
-        <v>1.91</v>
+        <v>1.83</v>
       </c>
       <c r="BG13" t="n">
-        <v>2.57</v>
+        <v>2.62</v>
       </c>
       <c r="BH13" t="n">
-        <v>9.74</v>
+        <v>9.789999999999999</v>
       </c>
       <c r="BI13" t="n">
-        <v>2.57</v>
+        <v>2.62</v>
       </c>
       <c r="BJ13" t="n">
-        <v>0.7</v>
+        <v>0.67</v>
       </c>
       <c r="BK13" t="n">
-        <v>0.39</v>
+        <v>0.5</v>
       </c>
       <c r="BL13" t="n">
-        <v>0.61</v>
+        <v>0.58</v>
       </c>
       <c r="BM13" t="n">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="BN13" t="n">
-        <v>1.48</v>
+        <v>1.46</v>
       </c>
       <c r="BO13" t="n">
-        <v>1.09</v>
+        <v>1.17</v>
       </c>
       <c r="BP13" t="n">
-        <v>3.91</v>
+        <v>4.04</v>
       </c>
       <c r="BQ13" t="n">
-        <v>5.83</v>
+        <v>5.75</v>
       </c>
       <c r="BR13" t="n">
         <v>100</v>
       </c>
       <c r="BS13" t="n">
-        <v>82.61</v>
+        <v>83.33</v>
       </c>
       <c r="BT13" t="n">
-        <v>52.17</v>
+        <v>54.17</v>
       </c>
       <c r="BU13" t="n">
-        <v>17.39</v>
+        <v>20.83</v>
       </c>
       <c r="BV13" t="n">
-        <v>4.35</v>
+        <v>4.17</v>
       </c>
       <c r="BW13" t="n">
         <v>0</v>
       </c>
       <c r="BX13" t="n">
-        <v>56.52</v>
+        <v>54.17</v>
       </c>
       <c r="BY13" t="n">
         <v>2.27</v>
@@ -6043,34 +6043,34 @@
         <v>2.35</v>
       </c>
       <c r="CA13" t="n">
-        <v>3.66</v>
+        <v>3.65</v>
       </c>
       <c r="CB13" t="n">
         <v>3.77</v>
       </c>
       <c r="CC13" t="n">
-        <v>3.82</v>
+        <v>3.71</v>
       </c>
       <c r="CD13" t="n">
-        <v>4.06</v>
+        <v>3.96</v>
       </c>
       <c r="CE13" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="CF13" t="n">
-        <v>2.49</v>
+        <v>2.48</v>
       </c>
       <c r="CG13" t="n">
-        <v>3.14</v>
+        <v>3.15</v>
       </c>
       <c r="CH13" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="CI13" t="n">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="CJ13" t="n">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="CK13" t="n">
         <v>1.46</v>
@@ -6079,7 +6079,7 @@
         <v>1.88</v>
       </c>
       <c r="CM13" t="n">
-        <v>2.52</v>
+        <v>2.53</v>
       </c>
       <c r="CN13" t="n">
         <v>1.95</v>
@@ -6088,10 +6088,10 @@
         <v>1.22</v>
       </c>
       <c r="CP13" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="CQ13" t="n">
-        <v>2.83</v>
+        <v>2.81</v>
       </c>
       <c r="CR13" t="n">
         <v>1.35</v>
@@ -6106,106 +6106,106 @@
         <v>1.51</v>
       </c>
       <c r="CV13" t="n">
-        <v>2.3</v>
+        <v>2.31</v>
       </c>
       <c r="CW13" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="CX13" t="n">
         <v>1.54</v>
       </c>
       <c r="CY13" t="n">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="CZ13" t="n">
-        <v>2.45</v>
+        <v>2.44</v>
       </c>
       <c r="DA13" t="n">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="DB13" t="n">
         <v>1.24</v>
       </c>
       <c r="DC13" t="n">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="DD13" t="n">
-        <v>2.9</v>
+        <v>2.87</v>
       </c>
       <c r="DE13" t="n">
-        <v>0.13</v>
+        <v>0.16</v>
       </c>
       <c r="DF13" t="n">
-        <v>1.39</v>
+        <v>1.33</v>
       </c>
       <c r="DG13" t="n">
-        <v>3.34</v>
+        <v>3.29</v>
       </c>
       <c r="DH13" t="n">
-        <v>100.04</v>
+        <v>98.92</v>
       </c>
       <c r="DI13" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DJ13" t="n">
-        <v>2.09</v>
+        <v>2.04</v>
       </c>
       <c r="DK13" t="n">
-        <v>5.26</v>
+        <v>5.25</v>
       </c>
       <c r="DL13" t="n">
-        <v>0.3</v>
+        <v>0.34</v>
       </c>
       <c r="DM13" t="n">
-        <v>52.35</v>
+        <v>51.71</v>
       </c>
       <c r="DN13" t="n">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="DO13" t="n">
-        <v>1.91</v>
+        <v>1.96</v>
       </c>
       <c r="DP13" t="n">
-        <v>11.52</v>
+        <v>11.54</v>
       </c>
       <c r="DQ13" t="n">
-        <v>11.3</v>
+        <v>11.38</v>
       </c>
       <c r="DR13" t="n">
-        <v>7.7</v>
+        <v>7.71</v>
       </c>
       <c r="DS13" t="n">
-        <v>0.26</v>
+        <v>0.25</v>
       </c>
       <c r="DT13" t="n">
-        <v>0.26</v>
+        <v>0.25</v>
       </c>
       <c r="DU13" t="n">
         <v>0</v>
       </c>
       <c r="DV13" t="n">
-        <v>53.39</v>
+        <v>53.25</v>
       </c>
       <c r="DW13" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DX13" t="n">
-        <v>14.39</v>
+        <v>14.5</v>
       </c>
       <c r="DY13" t="n">
-        <v>9.960000000000001</v>
+        <v>10</v>
       </c>
       <c r="DZ13" t="n">
-        <v>4.44</v>
+        <v>4.5</v>
       </c>
       <c r="EA13" t="n">
-        <v>21.74</v>
+        <v>21.62</v>
       </c>
       <c r="EB13" t="n">
         <v>1.6</v>
       </c>
       <c r="EC13" t="n">
-        <v>1.92</v>
+        <v>1.88</v>
       </c>
     </row>
     <row r="14">
@@ -6215,94 +6215,94 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C14" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D14" t="n">
         <v>12</v>
       </c>
       <c r="E14" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="F14" t="n">
-        <v>1.64</v>
+        <v>1.83</v>
       </c>
       <c r="G14" t="n">
-        <v>2.45</v>
+        <v>2.75</v>
       </c>
       <c r="H14" t="n">
-        <v>90.27</v>
+        <v>94.75</v>
       </c>
       <c r="I14" t="n">
         <v>0</v>
       </c>
       <c r="J14" t="n">
-        <v>2.09</v>
+        <v>2.33</v>
       </c>
       <c r="K14" t="n">
-        <v>5.27</v>
+        <v>5.33</v>
       </c>
       <c r="L14" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="M14" t="n">
-        <v>47.73</v>
+        <v>50.67</v>
       </c>
       <c r="N14" t="n">
-        <v>0.36</v>
+        <v>0.33</v>
       </c>
       <c r="O14" t="n">
-        <v>2.82</v>
+        <v>2.58</v>
       </c>
       <c r="P14" t="n">
-        <v>11.73</v>
+        <v>11.75</v>
       </c>
       <c r="Q14" t="n">
-        <v>12.64</v>
+        <v>12.5</v>
       </c>
       <c r="R14" t="n">
-        <v>7.27</v>
+        <v>7.33</v>
       </c>
       <c r="S14" t="n">
-        <v>0.91</v>
+        <v>1.17</v>
       </c>
       <c r="T14" t="n">
-        <v>1.27</v>
+        <v>1.42</v>
       </c>
       <c r="U14" t="n">
-        <v>0.09</v>
+        <v>0.17</v>
       </c>
       <c r="V14" t="n">
-        <v>0.09</v>
+        <v>0.17</v>
       </c>
       <c r="W14" t="n">
         <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>46.55</v>
+        <v>48.75</v>
       </c>
       <c r="Y14" t="n">
-        <v>0.18</v>
+        <v>0.25</v>
       </c>
       <c r="Z14" t="n">
-        <v>11.73</v>
+        <v>13.08</v>
       </c>
       <c r="AA14" t="n">
-        <v>7.18</v>
+        <v>8.17</v>
       </c>
       <c r="AB14" t="n">
-        <v>4.55</v>
+        <v>4.92</v>
       </c>
       <c r="AC14" t="n">
-        <v>17.82</v>
+        <v>17.92</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.41</v>
+        <v>1.54</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.82</v>
+        <v>1.92</v>
       </c>
       <c r="AF14" t="n">
         <v>0.17</v>
@@ -6386,61 +6386,61 @@
         <v>2.33</v>
       </c>
       <c r="BG14" t="n">
-        <v>2.39</v>
+        <v>2.58</v>
       </c>
       <c r="BH14" t="n">
-        <v>9.960000000000001</v>
+        <v>9.92</v>
       </c>
       <c r="BI14" t="n">
-        <v>2.39</v>
+        <v>2.58</v>
       </c>
       <c r="BJ14" t="n">
-        <v>0.65</v>
+        <v>0.67</v>
       </c>
       <c r="BK14" t="n">
-        <v>0.65</v>
+        <v>0.75</v>
       </c>
       <c r="BL14" t="n">
-        <v>0.65</v>
+        <v>0.71</v>
       </c>
       <c r="BM14" t="n">
-        <v>0.43</v>
+        <v>0.46</v>
       </c>
       <c r="BN14" t="n">
-        <v>1.09</v>
+        <v>1.17</v>
       </c>
       <c r="BO14" t="n">
-        <v>1.3</v>
+        <v>1.42</v>
       </c>
       <c r="BP14" t="n">
-        <v>5.09</v>
+        <v>4.96</v>
       </c>
       <c r="BQ14" t="n">
-        <v>4.87</v>
+        <v>4.96</v>
       </c>
       <c r="BR14" t="n">
-        <v>95.65000000000001</v>
+        <v>95.83</v>
       </c>
       <c r="BS14" t="n">
-        <v>73.91</v>
+        <v>75</v>
       </c>
       <c r="BT14" t="n">
-        <v>39.13</v>
+        <v>41.67</v>
       </c>
       <c r="BU14" t="n">
-        <v>26.09</v>
+        <v>29.17</v>
       </c>
       <c r="BV14" t="n">
-        <v>4.35</v>
+        <v>8.33</v>
       </c>
       <c r="BW14" t="n">
-        <v>0</v>
+        <v>4.17</v>
       </c>
       <c r="BX14" t="n">
-        <v>52.17</v>
+        <v>54.17</v>
       </c>
       <c r="BY14" t="n">
-        <v>2.31</v>
+        <v>2.28</v>
       </c>
       <c r="BZ14" t="n">
         <v>2.4</v>
@@ -6449,7 +6449,7 @@
         <v>3.49</v>
       </c>
       <c r="CB14" t="n">
-        <v>3.52</v>
+        <v>3.51</v>
       </c>
       <c r="CC14" t="n">
         <v>3.71</v>
@@ -6476,16 +6476,16 @@
         <v>1.75</v>
       </c>
       <c r="CK14" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="CL14" t="n">
-        <v>1.89</v>
+        <v>1.91</v>
       </c>
       <c r="CM14" t="n">
-        <v>2.52</v>
+        <v>2.51</v>
       </c>
       <c r="CN14" t="n">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="CO14" t="n">
         <v>1.27</v>
@@ -6494,7 +6494,7 @@
         <v>1.89</v>
       </c>
       <c r="CQ14" t="n">
-        <v>3.18</v>
+        <v>3.19</v>
       </c>
       <c r="CR14" t="n">
         <v>1.39</v>
@@ -6533,82 +6533,82 @@
         <v>1.99</v>
       </c>
       <c r="DD14" t="n">
-        <v>3.37</v>
+        <v>3.38</v>
       </c>
       <c r="DE14" t="n">
         <v>0.17</v>
       </c>
       <c r="DF14" t="n">
-        <v>1.66</v>
+        <v>1.75</v>
       </c>
       <c r="DG14" t="n">
-        <v>2.3</v>
+        <v>2.46</v>
       </c>
       <c r="DH14" t="n">
-        <v>91.34</v>
+        <v>93.54000000000001</v>
       </c>
       <c r="DI14" t="n">
         <v>0</v>
       </c>
       <c r="DJ14" t="n">
-        <v>2.22</v>
+        <v>2.33</v>
       </c>
       <c r="DK14" t="n">
-        <v>4.91</v>
+        <v>4.96</v>
       </c>
       <c r="DL14" t="n">
-        <v>0.39</v>
+        <v>0.38</v>
       </c>
       <c r="DM14" t="n">
-        <v>46.13</v>
+        <v>47.67</v>
       </c>
       <c r="DN14" t="n">
-        <v>0.52</v>
+        <v>0.5</v>
       </c>
       <c r="DO14" t="n">
-        <v>2.61</v>
+        <v>2.5</v>
       </c>
       <c r="DP14" t="n">
-        <v>11.87</v>
+        <v>11.88</v>
       </c>
       <c r="DQ14" t="n">
         <v>11.04</v>
       </c>
       <c r="DR14" t="n">
-        <v>7.48</v>
+        <v>7.5</v>
       </c>
       <c r="DS14" t="n">
-        <v>0.08</v>
+        <v>0.12</v>
       </c>
       <c r="DT14" t="n">
-        <v>0.08</v>
+        <v>0.12</v>
       </c>
       <c r="DU14" t="n">
         <v>0</v>
       </c>
       <c r="DV14" t="n">
-        <v>46.92</v>
+        <v>48</v>
       </c>
       <c r="DW14" t="n">
-        <v>0.09</v>
+        <v>0.12</v>
       </c>
       <c r="DX14" t="n">
-        <v>11.52</v>
+        <v>12.2</v>
       </c>
       <c r="DY14" t="n">
-        <v>7.35</v>
+        <v>7.84</v>
       </c>
       <c r="DZ14" t="n">
-        <v>4.17</v>
+        <v>4.38</v>
       </c>
       <c r="EA14" t="n">
-        <v>19.52</v>
+        <v>19.5</v>
       </c>
       <c r="EB14" t="n">
-        <v>1.36</v>
+        <v>1.42</v>
       </c>
       <c r="EC14" t="n">
-        <v>2.09</v>
+        <v>2.12</v>
       </c>
     </row>
     <row r="15">
@@ -7424,10 +7424,10 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C17" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D17" t="n">
         <v>12</v>
@@ -7436,82 +7436,82 @@
         <v>0</v>
       </c>
       <c r="F17" t="n">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="G17" t="n">
-        <v>2.36</v>
+        <v>2.5</v>
       </c>
       <c r="H17" t="n">
-        <v>95.64</v>
+        <v>94.17</v>
       </c>
       <c r="I17" t="n">
-        <v>0</v>
+        <v>0.08</v>
       </c>
       <c r="J17" t="n">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="K17" t="n">
-        <v>4.09</v>
+        <v>4.25</v>
       </c>
       <c r="L17" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="M17" t="n">
-        <v>44.55</v>
+        <v>44.58</v>
       </c>
       <c r="N17" t="n">
-        <v>0.45</v>
+        <v>0.5</v>
       </c>
       <c r="O17" t="n">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="P17" t="n">
-        <v>10.09</v>
+        <v>9.92</v>
       </c>
       <c r="Q17" t="n">
-        <v>12.91</v>
+        <v>12.83</v>
       </c>
       <c r="R17" t="n">
-        <v>10</v>
+        <v>9.58</v>
       </c>
       <c r="S17" t="n">
-        <v>1.27</v>
+        <v>1.17</v>
       </c>
       <c r="T17" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="U17" t="n">
-        <v>0.36</v>
+        <v>0.33</v>
       </c>
       <c r="V17" t="n">
-        <v>0.36</v>
+        <v>0.33</v>
       </c>
       <c r="W17" t="n">
         <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>46.45</v>
+        <v>46.75</v>
       </c>
       <c r="Y17" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="Z17" t="n">
-        <v>13</v>
+        <v>12.92</v>
       </c>
       <c r="AA17" t="n">
-        <v>8.18</v>
+        <v>8.25</v>
       </c>
       <c r="AB17" t="n">
-        <v>4.82</v>
+        <v>4.67</v>
       </c>
       <c r="AC17" t="n">
-        <v>21.55</v>
+        <v>20.83</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AF17" t="n">
         <v>0.08</v>
@@ -7595,70 +7595,70 @@
         <v>1.75</v>
       </c>
       <c r="BG17" t="n">
-        <v>2.87</v>
+        <v>2.79</v>
       </c>
       <c r="BH17" t="n">
-        <v>9.74</v>
+        <v>9.619999999999999</v>
       </c>
       <c r="BI17" t="n">
-        <v>2.87</v>
+        <v>2.79</v>
       </c>
       <c r="BJ17" t="n">
-        <v>0.74</v>
+        <v>0.71</v>
       </c>
       <c r="BK17" t="n">
-        <v>0.61</v>
+        <v>0.58</v>
       </c>
       <c r="BL17" t="n">
         <v>0.83</v>
       </c>
       <c r="BM17" t="n">
-        <v>0.7</v>
+        <v>0.67</v>
       </c>
       <c r="BN17" t="n">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="BO17" t="n">
-        <v>1.35</v>
+        <v>1.29</v>
       </c>
       <c r="BP17" t="n">
-        <v>3.61</v>
+        <v>3.58</v>
       </c>
       <c r="BQ17" t="n">
-        <v>5.52</v>
+        <v>5.46</v>
       </c>
       <c r="BR17" t="n">
-        <v>91.3</v>
+        <v>91.67</v>
       </c>
       <c r="BS17" t="n">
-        <v>82.61</v>
+        <v>79.17</v>
       </c>
       <c r="BT17" t="n">
-        <v>47.83</v>
+        <v>45.83</v>
       </c>
       <c r="BU17" t="n">
-        <v>34.78</v>
+        <v>33.33</v>
       </c>
       <c r="BV17" t="n">
-        <v>21.74</v>
+        <v>20.83</v>
       </c>
       <c r="BW17" t="n">
-        <v>4.35</v>
+        <v>4.17</v>
       </c>
       <c r="BX17" t="n">
-        <v>65.22</v>
+        <v>62.5</v>
       </c>
       <c r="BY17" t="n">
-        <v>3.01</v>
+        <v>2.94</v>
       </c>
       <c r="BZ17" t="n">
-        <v>3.23</v>
+        <v>3.15</v>
       </c>
       <c r="CA17" t="n">
-        <v>3.77</v>
+        <v>3.75</v>
       </c>
       <c r="CB17" t="n">
-        <v>3.86</v>
+        <v>3.83</v>
       </c>
       <c r="CC17" t="n">
         <v>4.42</v>
@@ -7670,7 +7670,7 @@
         <v>1.3</v>
       </c>
       <c r="CF17" t="n">
-        <v>2.45</v>
+        <v>2.47</v>
       </c>
       <c r="CG17" t="n">
         <v>3.3</v>
@@ -7679,28 +7679,28 @@
         <v>1.52</v>
       </c>
       <c r="CI17" t="n">
-        <v>2.19</v>
+        <v>2.18</v>
       </c>
       <c r="CJ17" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="CK17" t="n">
         <v>1.43</v>
       </c>
       <c r="CL17" t="n">
-        <v>1.79</v>
+        <v>1.81</v>
       </c>
       <c r="CM17" t="n">
-        <v>2.68</v>
+        <v>2.66</v>
       </c>
       <c r="CN17" t="n">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="CO17" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="CP17" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="CQ17" t="n">
         <v>2.71</v>
@@ -7718,106 +7718,106 @@
         <v>1.53</v>
       </c>
       <c r="CV17" t="n">
-        <v>2.31</v>
+        <v>2.3</v>
       </c>
       <c r="CW17" t="n">
         <v>1.68</v>
       </c>
       <c r="CX17" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="CY17" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="CZ17" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="DA17" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="DB17" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="DC17" t="n">
         <v>1.77</v>
       </c>
-      <c r="CZ17" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="DA17" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="DB17" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="DC17" t="n">
-        <v>1.76</v>
-      </c>
       <c r="DD17" t="n">
-        <v>2.83</v>
+        <v>2.86</v>
       </c>
       <c r="DE17" t="n">
         <v>0.04</v>
       </c>
       <c r="DF17" t="n">
-        <v>1.13</v>
+        <v>1.08</v>
       </c>
       <c r="DG17" t="n">
-        <v>2.26</v>
+        <v>2.34</v>
       </c>
       <c r="DH17" t="n">
-        <v>94.52</v>
+        <v>93.84</v>
       </c>
       <c r="DI17" t="n">
-        <v>0.04</v>
+        <v>0.08</v>
       </c>
       <c r="DJ17" t="n">
-        <v>1.74</v>
+        <v>1.71</v>
       </c>
       <c r="DK17" t="n">
-        <v>4.13</v>
+        <v>4.21</v>
       </c>
       <c r="DL17" t="n">
         <v>0.17</v>
       </c>
       <c r="DM17" t="n">
-        <v>45.83</v>
+        <v>45.79</v>
       </c>
       <c r="DN17" t="n">
-        <v>0.52</v>
+        <v>0.54</v>
       </c>
       <c r="DO17" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="DP17" t="n">
-        <v>11.18</v>
+        <v>11.04</v>
       </c>
       <c r="DQ17" t="n">
-        <v>11.87</v>
+        <v>11.88</v>
       </c>
       <c r="DR17" t="n">
-        <v>9.390000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="DS17" t="n">
-        <v>0.21</v>
+        <v>0.2</v>
       </c>
       <c r="DT17" t="n">
-        <v>0.21</v>
+        <v>0.2</v>
       </c>
       <c r="DU17" t="n">
         <v>0</v>
       </c>
       <c r="DV17" t="n">
-        <v>47.26</v>
+        <v>47.38</v>
       </c>
       <c r="DW17" t="n">
         <v>0.08</v>
       </c>
       <c r="DX17" t="n">
-        <v>11.7</v>
+        <v>11.71</v>
       </c>
       <c r="DY17" t="n">
-        <v>7.52</v>
+        <v>7.58</v>
       </c>
       <c r="DZ17" t="n">
-        <v>4.17</v>
+        <v>4.12</v>
       </c>
       <c r="EA17" t="n">
-        <v>20.31</v>
+        <v>20</v>
       </c>
       <c r="EB17" t="n">
         <v>1.37</v>
       </c>
       <c r="EC17" t="n">
-        <v>1.56</v>
+        <v>1.54</v>
       </c>
     </row>
   </sheetData>

--- a/data/teams/leagues/Averages_Belgium_Pro_League_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Belgium_Pro_League_2025-2026.xlsx
@@ -1782,61 +1782,61 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C3" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D3" t="n">
         <v>12</v>
       </c>
       <c r="E3" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="F3" t="n">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="G3" t="n">
-        <v>3.82</v>
+        <v>3.75</v>
       </c>
       <c r="H3" t="n">
-        <v>114.18</v>
+        <v>115.58</v>
       </c>
       <c r="I3" t="n">
         <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>1.55</v>
+        <v>1.42</v>
       </c>
       <c r="K3" t="n">
-        <v>6.82</v>
+        <v>6.83</v>
       </c>
       <c r="L3" t="n">
-        <v>0.91</v>
+        <v>0.83</v>
       </c>
       <c r="M3" t="n">
-        <v>65.81999999999999</v>
+        <v>65.17</v>
       </c>
       <c r="N3" t="n">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="O3" t="n">
-        <v>3</v>
+        <v>3.08</v>
       </c>
       <c r="P3" t="n">
-        <v>9.640000000000001</v>
+        <v>9.5</v>
       </c>
       <c r="Q3" t="n">
-        <v>12.09</v>
+        <v>11.92</v>
       </c>
       <c r="R3" t="n">
-        <v>6.55</v>
+        <v>6.33</v>
       </c>
       <c r="S3" t="n">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="T3" t="n">
-        <v>2.09</v>
+        <v>2.17</v>
       </c>
       <c r="U3" t="n">
         <v>0</v>
@@ -1848,28 +1848,28 @@
         <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>65.18000000000001</v>
+        <v>65.67</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="Z3" t="n">
-        <v>17.45</v>
+        <v>17.83</v>
       </c>
       <c r="AA3" t="n">
-        <v>12.27</v>
+        <v>12.17</v>
       </c>
       <c r="AB3" t="n">
-        <v>5.18</v>
+        <v>5.67</v>
       </c>
       <c r="AC3" t="n">
-        <v>23</v>
+        <v>22.83</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.94</v>
+        <v>1.99</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="AF3" t="n">
         <v>0.08</v>
@@ -1953,70 +1953,70 @@
         <v>1.58</v>
       </c>
       <c r="BG3" t="n">
-        <v>3.09</v>
+        <v>3.08</v>
       </c>
       <c r="BH3" t="n">
-        <v>10.74</v>
+        <v>10.58</v>
       </c>
       <c r="BI3" t="n">
-        <v>3.09</v>
+        <v>3.08</v>
       </c>
       <c r="BJ3" t="n">
-        <v>0.74</v>
+        <v>0.83</v>
       </c>
       <c r="BK3" t="n">
-        <v>0.52</v>
+        <v>0.5</v>
       </c>
       <c r="BL3" t="n">
-        <v>0.87</v>
+        <v>0.83</v>
       </c>
       <c r="BM3" t="n">
-        <v>0.96</v>
+        <v>0.92</v>
       </c>
       <c r="BN3" t="n">
-        <v>1.83</v>
+        <v>1.75</v>
       </c>
       <c r="BO3" t="n">
-        <v>1.26</v>
+        <v>1.33</v>
       </c>
       <c r="BP3" t="n">
-        <v>4.74</v>
+        <v>4.71</v>
       </c>
       <c r="BQ3" t="n">
-        <v>6</v>
+        <v>5.88</v>
       </c>
       <c r="BR3" t="n">
         <v>100</v>
       </c>
       <c r="BS3" t="n">
-        <v>60.87</v>
+        <v>62.5</v>
       </c>
       <c r="BT3" t="n">
-        <v>47.83</v>
+        <v>50</v>
       </c>
       <c r="BU3" t="n">
-        <v>26.09</v>
+        <v>25</v>
       </c>
       <c r="BV3" t="n">
-        <v>26.09</v>
+        <v>25</v>
       </c>
       <c r="BW3" t="n">
-        <v>17.39</v>
+        <v>16.67</v>
       </c>
       <c r="BX3" t="n">
-        <v>52.17</v>
+        <v>50</v>
       </c>
       <c r="BY3" t="n">
-        <v>1.48</v>
+        <v>1.45</v>
       </c>
       <c r="BZ3" t="n">
-        <v>1.49</v>
+        <v>1.47</v>
       </c>
       <c r="CA3" t="n">
-        <v>4.42</v>
+        <v>4.47</v>
       </c>
       <c r="CB3" t="n">
-        <v>4.7</v>
+        <v>4.75</v>
       </c>
       <c r="CC3" t="n">
         <v>1.87</v>
@@ -2031,28 +2031,28 @@
         <v>2.25</v>
       </c>
       <c r="CG3" t="n">
-        <v>3.53</v>
+        <v>3.52</v>
       </c>
       <c r="CH3" t="n">
         <v>1.61</v>
       </c>
       <c r="CI3" t="n">
-        <v>2.12</v>
+        <v>2.11</v>
       </c>
       <c r="CJ3" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="CK3" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="CL3" t="n">
-        <v>1.93</v>
+        <v>1.95</v>
       </c>
       <c r="CM3" t="n">
         <v>2.51</v>
       </c>
       <c r="CN3" t="n">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="CO3" t="n">
         <v>1.16</v>
@@ -2073,25 +2073,25 @@
         <v>3.24</v>
       </c>
       <c r="CU3" t="n">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="CV3" t="n">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="CW3" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="CX3" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="CY3" t="n">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="CZ3" t="n">
-        <v>2.49</v>
+        <v>2.47</v>
       </c>
       <c r="DA3" t="n">
-        <v>2.02</v>
+        <v>2.01</v>
       </c>
       <c r="DB3" t="n">
         <v>1.19</v>
@@ -2106,43 +2106,43 @@
         <v>0.08</v>
       </c>
       <c r="DF3" t="n">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="DG3" t="n">
-        <v>3.65</v>
+        <v>3.62</v>
       </c>
       <c r="DH3" t="n">
-        <v>110.48</v>
+        <v>111.33</v>
       </c>
       <c r="DI3" t="n">
         <v>0</v>
       </c>
       <c r="DJ3" t="n">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="DK3" t="n">
-        <v>6.3</v>
+        <v>6.33</v>
       </c>
       <c r="DL3" t="n">
-        <v>0.61</v>
+        <v>0.58</v>
       </c>
       <c r="DM3" t="n">
-        <v>61.05</v>
+        <v>60.92</v>
       </c>
       <c r="DN3" t="n">
-        <v>0.39</v>
+        <v>0.38</v>
       </c>
       <c r="DO3" t="n">
-        <v>2.65</v>
+        <v>2.7</v>
       </c>
       <c r="DP3" t="n">
-        <v>9.57</v>
+        <v>9.5</v>
       </c>
       <c r="DQ3" t="n">
-        <v>11.78</v>
+        <v>11.71</v>
       </c>
       <c r="DR3" t="n">
-        <v>7.26</v>
+        <v>7.12</v>
       </c>
       <c r="DS3" t="n">
         <v>0</v>
@@ -2154,28 +2154,28 @@
         <v>0</v>
       </c>
       <c r="DV3" t="n">
-        <v>62.52</v>
+        <v>62.88</v>
       </c>
       <c r="DW3" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DX3" t="n">
-        <v>16.08</v>
+        <v>16.33</v>
       </c>
       <c r="DY3" t="n">
-        <v>10.87</v>
+        <v>10.88</v>
       </c>
       <c r="DZ3" t="n">
-        <v>5.22</v>
+        <v>5.46</v>
       </c>
       <c r="EA3" t="n">
-        <v>20.65</v>
+        <v>20.66</v>
       </c>
       <c r="EB3" t="n">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="EC3" t="n">
-        <v>1.39</v>
+        <v>1.33</v>
       </c>
     </row>
     <row r="4">
@@ -2660,10 +2660,10 @@
         <v>0.08</v>
       </c>
       <c r="Z5" t="n">
-        <v>16.17</v>
+        <v>16.25</v>
       </c>
       <c r="AA5" t="n">
-        <v>11.92</v>
+        <v>12</v>
       </c>
       <c r="AB5" t="n">
         <v>4.25</v>
@@ -2672,7 +2672,7 @@
         <v>19.67</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="AE5" t="n">
         <v>1.58</v>
@@ -2966,10 +2966,10 @@
         <v>0.12</v>
       </c>
       <c r="DX5" t="n">
-        <v>13.75</v>
+        <v>13.79</v>
       </c>
       <c r="DY5" t="n">
-        <v>9.25</v>
+        <v>9.289999999999999</v>
       </c>
       <c r="DZ5" t="n">
         <v>4.5</v>
@@ -2978,7 +2978,7 @@
         <v>18.71</v>
       </c>
       <c r="EB5" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="EC5" t="n">
         <v>1.58</v>
@@ -2991,10 +2991,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C6" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D6" t="n">
         <v>12</v>
@@ -3003,49 +3003,49 @@
         <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>0.55</v>
+        <v>0.58</v>
       </c>
       <c r="G6" t="n">
-        <v>4.27</v>
+        <v>4.08</v>
       </c>
       <c r="H6" t="n">
-        <v>130.18</v>
+        <v>129.25</v>
       </c>
       <c r="I6" t="n">
-        <v>0</v>
+        <v>0.08</v>
       </c>
       <c r="J6" t="n">
-        <v>1.18</v>
+        <v>1.25</v>
       </c>
       <c r="K6" t="n">
-        <v>6.91</v>
+        <v>6.75</v>
       </c>
       <c r="L6" t="n">
-        <v>0.55</v>
+        <v>0.5</v>
       </c>
       <c r="M6" t="n">
-        <v>62.45</v>
+        <v>62.92</v>
       </c>
       <c r="N6" t="n">
-        <v>0.55</v>
+        <v>0.58</v>
       </c>
       <c r="O6" t="n">
-        <v>2.55</v>
+        <v>2.58</v>
       </c>
       <c r="P6" t="n">
-        <v>10.82</v>
+        <v>10.67</v>
       </c>
       <c r="Q6" t="n">
-        <v>13.55</v>
+        <v>14.08</v>
       </c>
       <c r="R6" t="n">
-        <v>5.64</v>
+        <v>5.75</v>
       </c>
       <c r="S6" t="n">
-        <v>1.55</v>
+        <v>1.42</v>
       </c>
       <c r="T6" t="n">
-        <v>1.36</v>
+        <v>1.42</v>
       </c>
       <c r="U6" t="n">
         <v>0</v>
@@ -3057,28 +3057,28 @@
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>64.45</v>
+        <v>63.5</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="Z6" t="n">
-        <v>18.18</v>
+        <v>18.17</v>
       </c>
       <c r="AA6" t="n">
-        <v>12.27</v>
+        <v>12.08</v>
       </c>
       <c r="AB6" t="n">
-        <v>5.91</v>
+        <v>6.08</v>
       </c>
       <c r="AC6" t="n">
-        <v>21.45</v>
+        <v>21.75</v>
       </c>
       <c r="AD6" t="n">
-        <v>2.02</v>
+        <v>2.03</v>
       </c>
       <c r="AE6" t="n">
-        <v>1</v>
+        <v>1.08</v>
       </c>
       <c r="AF6" t="n">
         <v>0.25</v>
@@ -3162,70 +3162,70 @@
         <v>1.67</v>
       </c>
       <c r="BG6" t="n">
-        <v>2.87</v>
+        <v>2.83</v>
       </c>
       <c r="BH6" t="n">
-        <v>9.779999999999999</v>
+        <v>9.880000000000001</v>
       </c>
       <c r="BI6" t="n">
-        <v>2.87</v>
+        <v>2.83</v>
       </c>
       <c r="BJ6" t="n">
-        <v>0.61</v>
+        <v>0.58</v>
       </c>
       <c r="BK6" t="n">
-        <v>0.91</v>
+        <v>0.88</v>
       </c>
       <c r="BL6" t="n">
-        <v>0.83</v>
+        <v>0.88</v>
       </c>
       <c r="BM6" t="n">
-        <v>0.52</v>
+        <v>0.5</v>
       </c>
       <c r="BN6" t="n">
-        <v>1.35</v>
+        <v>1.38</v>
       </c>
       <c r="BO6" t="n">
-        <v>1.52</v>
+        <v>1.46</v>
       </c>
       <c r="BP6" t="n">
-        <v>4.39</v>
+        <v>4.46</v>
       </c>
       <c r="BQ6" t="n">
-        <v>5.35</v>
+        <v>5.38</v>
       </c>
       <c r="BR6" t="n">
         <v>100</v>
       </c>
       <c r="BS6" t="n">
-        <v>86.95999999999999</v>
+        <v>87.5</v>
       </c>
       <c r="BT6" t="n">
-        <v>60.87</v>
+        <v>58.33</v>
       </c>
       <c r="BU6" t="n">
-        <v>17.39</v>
+        <v>16.67</v>
       </c>
       <c r="BV6" t="n">
-        <v>8.699999999999999</v>
+        <v>8.33</v>
       </c>
       <c r="BW6" t="n">
-        <v>4.35</v>
+        <v>4.17</v>
       </c>
       <c r="BX6" t="n">
-        <v>82.61</v>
+        <v>79.17</v>
       </c>
       <c r="BY6" t="n">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="BZ6" t="n">
         <v>1.91</v>
       </c>
       <c r="CA6" t="n">
-        <v>3.82</v>
+        <v>3.8</v>
       </c>
       <c r="CB6" t="n">
-        <v>3.94</v>
+        <v>3.92</v>
       </c>
       <c r="CC6" t="n">
         <v>2.38</v>
@@ -3240,7 +3240,7 @@
         <v>2.43</v>
       </c>
       <c r="CG6" t="n">
-        <v>3.26</v>
+        <v>3.25</v>
       </c>
       <c r="CH6" t="n">
         <v>1.52</v>
@@ -3249,7 +3249,7 @@
         <v>2.24</v>
       </c>
       <c r="CJ6" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="CK6" t="n">
         <v>1.51</v>
@@ -3258,19 +3258,19 @@
         <v>1.97</v>
       </c>
       <c r="CM6" t="n">
-        <v>2.43</v>
+        <v>2.42</v>
       </c>
       <c r="CN6" t="n">
         <v>1.88</v>
       </c>
       <c r="CO6" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="CP6" t="n">
         <v>1.7</v>
       </c>
       <c r="CQ6" t="n">
-        <v>2.7</v>
+        <v>2.71</v>
       </c>
       <c r="CR6" t="n">
         <v>1.37</v>
@@ -3285,10 +3285,10 @@
         <v>1.53</v>
       </c>
       <c r="CV6" t="n">
-        <v>2.29</v>
+        <v>2.28</v>
       </c>
       <c r="CW6" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="CX6" t="n">
         <v>1.58</v>
@@ -3297,7 +3297,7 @@
         <v>1.92</v>
       </c>
       <c r="CZ6" t="n">
-        <v>2.35</v>
+        <v>2.36</v>
       </c>
       <c r="DA6" t="n">
         <v>1.9</v>
@@ -3312,46 +3312,46 @@
         <v>2.83</v>
       </c>
       <c r="DE6" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="DF6" t="n">
         <v>0.92</v>
       </c>
       <c r="DG6" t="n">
-        <v>3.35</v>
+        <v>3.29</v>
       </c>
       <c r="DH6" t="n">
-        <v>113</v>
+        <v>113.25</v>
       </c>
       <c r="DI6" t="n">
-        <v>0.04</v>
+        <v>0.08</v>
       </c>
       <c r="DJ6" t="n">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="DK6" t="n">
-        <v>5.65</v>
+        <v>5.62</v>
       </c>
       <c r="DL6" t="n">
-        <v>0.65</v>
+        <v>0.62</v>
       </c>
       <c r="DM6" t="n">
-        <v>54</v>
+        <v>54.58</v>
       </c>
       <c r="DN6" t="n">
-        <v>0.48</v>
+        <v>0.5</v>
       </c>
       <c r="DO6" t="n">
-        <v>2.26</v>
+        <v>2.29</v>
       </c>
       <c r="DP6" t="n">
-        <v>10.26</v>
+        <v>10.21</v>
       </c>
       <c r="DQ6" t="n">
-        <v>12.7</v>
+        <v>13</v>
       </c>
       <c r="DR6" t="n">
-        <v>6.91</v>
+        <v>6.92</v>
       </c>
       <c r="DS6" t="n">
         <v>0</v>
@@ -3363,28 +3363,28 @@
         <v>0</v>
       </c>
       <c r="DV6" t="n">
-        <v>62.22</v>
+        <v>61.84</v>
       </c>
       <c r="DW6" t="n">
         <v>0.04</v>
       </c>
       <c r="DX6" t="n">
-        <v>15.83</v>
+        <v>15.92</v>
       </c>
       <c r="DY6" t="n">
         <v>10.17</v>
       </c>
       <c r="DZ6" t="n">
-        <v>5.65</v>
+        <v>5.75</v>
       </c>
       <c r="EA6" t="n">
-        <v>20.04</v>
+        <v>20.25</v>
       </c>
       <c r="EB6" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="EC6" t="n">
-        <v>1.35</v>
+        <v>1.38</v>
       </c>
     </row>
     <row r="7">
@@ -3394,94 +3394,94 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C7" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D7" t="n">
         <v>12</v>
       </c>
       <c r="E7" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="F7" t="n">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="G7" t="n">
-        <v>2.73</v>
+        <v>2.67</v>
       </c>
       <c r="H7" t="n">
-        <v>92.45</v>
+        <v>89.83</v>
       </c>
       <c r="I7" t="n">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="J7" t="n">
-        <v>2.45</v>
+        <v>2.33</v>
       </c>
       <c r="K7" t="n">
-        <v>5</v>
+        <v>4.83</v>
       </c>
       <c r="L7" t="n">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="M7" t="n">
-        <v>52.82</v>
+        <v>50.67</v>
       </c>
       <c r="N7" t="n">
-        <v>0.73</v>
+        <v>0.67</v>
       </c>
       <c r="O7" t="n">
-        <v>2.27</v>
+        <v>2.17</v>
       </c>
       <c r="P7" t="n">
-        <v>10.55</v>
+        <v>10.42</v>
       </c>
       <c r="Q7" t="n">
-        <v>11.18</v>
+        <v>11.5</v>
       </c>
       <c r="R7" t="n">
-        <v>9.449999999999999</v>
+        <v>9.33</v>
       </c>
       <c r="S7" t="n">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="T7" t="n">
-        <v>1.09</v>
+        <v>1.17</v>
       </c>
       <c r="U7" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="V7" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>51.45</v>
+        <v>49.92</v>
       </c>
       <c r="Y7" t="n">
         <v>0</v>
       </c>
       <c r="Z7" t="n">
-        <v>10.91</v>
+        <v>10.67</v>
       </c>
       <c r="AA7" t="n">
-        <v>7.27</v>
+        <v>7.17</v>
       </c>
       <c r="AB7" t="n">
-        <v>3.64</v>
+        <v>3.5</v>
       </c>
       <c r="AC7" t="n">
-        <v>21.55</v>
+        <v>21.33</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="AE7" t="n">
-        <v>2.45</v>
+        <v>2.33</v>
       </c>
       <c r="AF7" t="n">
         <v>0.08</v>
@@ -3565,70 +3565,70 @@
         <v>2.58</v>
       </c>
       <c r="BG7" t="n">
-        <v>2.35</v>
+        <v>2.33</v>
       </c>
       <c r="BH7" t="n">
-        <v>11.43</v>
+        <v>11.33</v>
       </c>
       <c r="BI7" t="n">
-        <v>2.35</v>
+        <v>2.33</v>
       </c>
       <c r="BJ7" t="n">
-        <v>0.52</v>
+        <v>0.54</v>
       </c>
       <c r="BK7" t="n">
-        <v>0.43</v>
+        <v>0.42</v>
       </c>
       <c r="BL7" t="n">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="BM7" t="n">
-        <v>0.78</v>
+        <v>0.75</v>
       </c>
       <c r="BN7" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="BO7" t="n">
         <v>0.96</v>
       </c>
       <c r="BP7" t="n">
-        <v>5.17</v>
+        <v>5.08</v>
       </c>
       <c r="BQ7" t="n">
-        <v>6.26</v>
+        <v>6.25</v>
       </c>
       <c r="BR7" t="n">
-        <v>95.65000000000001</v>
+        <v>95.83</v>
       </c>
       <c r="BS7" t="n">
-        <v>69.56999999999999</v>
+        <v>70.83</v>
       </c>
       <c r="BT7" t="n">
-        <v>34.78</v>
+        <v>33.33</v>
       </c>
       <c r="BU7" t="n">
-        <v>26.09</v>
+        <v>25</v>
       </c>
       <c r="BV7" t="n">
-        <v>8.699999999999999</v>
+        <v>8.33</v>
       </c>
       <c r="BW7" t="n">
         <v>0</v>
       </c>
       <c r="BX7" t="n">
-        <v>65.22</v>
+        <v>62.5</v>
       </c>
       <c r="BY7" t="n">
-        <v>2.81</v>
+        <v>2.78</v>
       </c>
       <c r="BZ7" t="n">
-        <v>2.99</v>
+        <v>2.94</v>
       </c>
       <c r="CA7" t="n">
-        <v>3.69</v>
+        <v>3.67</v>
       </c>
       <c r="CB7" t="n">
-        <v>3.82</v>
+        <v>3.8</v>
       </c>
       <c r="CC7" t="n">
         <v>3.93</v>
@@ -3640,154 +3640,154 @@
         <v>1.31</v>
       </c>
       <c r="CF7" t="n">
-        <v>2.45</v>
+        <v>2.46</v>
       </c>
       <c r="CG7" t="n">
-        <v>3.23</v>
+        <v>3.21</v>
       </c>
       <c r="CH7" t="n">
         <v>1.51</v>
       </c>
       <c r="CI7" t="n">
-        <v>2.21</v>
+        <v>2.2</v>
       </c>
       <c r="CJ7" t="n">
         <v>1.64</v>
       </c>
       <c r="CK7" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="CL7" t="n">
-        <v>1.77</v>
+        <v>1.79</v>
       </c>
       <c r="CM7" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="CN7" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="CO7" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="CP7" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="CQ7" t="n">
         <v>2.76</v>
-      </c>
-      <c r="CN7" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="CO7" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="CP7" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="CQ7" t="n">
-        <v>2.72</v>
       </c>
       <c r="CR7" t="n">
         <v>1.36</v>
       </c>
       <c r="CS7" t="n">
-        <v>2.57</v>
+        <v>2.59</v>
       </c>
       <c r="CT7" t="n">
-        <v>3.2</v>
+        <v>3.18</v>
       </c>
       <c r="CU7" t="n">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="CV7" t="n">
-        <v>2.34</v>
+        <v>2.32</v>
       </c>
       <c r="CW7" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="CX7" t="n">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="CY7" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="CZ7" t="n">
-        <v>2.58</v>
+        <v>2.56</v>
       </c>
       <c r="DA7" t="n">
-        <v>2.13</v>
+        <v>2.12</v>
       </c>
       <c r="DB7" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="DC7" t="n">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="DD7" t="n">
-        <v>2.85</v>
+        <v>2.87</v>
       </c>
       <c r="DE7" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="DF7" t="n">
-        <v>1.74</v>
+        <v>1.71</v>
       </c>
       <c r="DG7" t="n">
-        <v>2.87</v>
+        <v>2.83</v>
       </c>
       <c r="DH7" t="n">
-        <v>89.22</v>
+        <v>88.04000000000001</v>
       </c>
       <c r="DI7" t="n">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
       <c r="DJ7" t="n">
-        <v>2.52</v>
+        <v>2.46</v>
       </c>
       <c r="DK7" t="n">
-        <v>5.04</v>
+        <v>4.96</v>
       </c>
       <c r="DL7" t="n">
-        <v>0.3</v>
+        <v>0.29</v>
       </c>
       <c r="DM7" t="n">
-        <v>47.44</v>
+        <v>46.58</v>
       </c>
       <c r="DN7" t="n">
-        <v>0.78</v>
+        <v>0.75</v>
       </c>
       <c r="DO7" t="n">
-        <v>2.17</v>
+        <v>2.12</v>
       </c>
       <c r="DP7" t="n">
-        <v>10.44</v>
+        <v>10.38</v>
       </c>
       <c r="DQ7" t="n">
-        <v>11.44</v>
+        <v>11.58</v>
       </c>
       <c r="DR7" t="n">
-        <v>9.130000000000001</v>
+        <v>9.08</v>
       </c>
       <c r="DS7" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DT7" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DU7" t="n">
         <v>0</v>
       </c>
       <c r="DV7" t="n">
-        <v>50.3</v>
+        <v>49.58</v>
       </c>
       <c r="DW7" t="n">
         <v>0</v>
       </c>
       <c r="DX7" t="n">
-        <v>10.61</v>
+        <v>10.5</v>
       </c>
       <c r="DY7" t="n">
-        <v>6.65</v>
+        <v>6.62</v>
       </c>
       <c r="DZ7" t="n">
-        <v>3.96</v>
+        <v>3.88</v>
       </c>
       <c r="EA7" t="n">
-        <v>21.61</v>
+        <v>21.5</v>
       </c>
       <c r="EB7" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="EC7" t="n">
-        <v>2.52</v>
+        <v>2.46</v>
       </c>
     </row>
     <row r="8">
@@ -4603,13 +4603,13 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C10" t="n">
         <v>12</v>
       </c>
       <c r="D10" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
@@ -4693,52 +4693,52 @@
         <v>1.5</v>
       </c>
       <c r="AF10" t="n">
-        <v>0.09</v>
+        <v>0.17</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.18</v>
+        <v>1.42</v>
       </c>
       <c r="AH10" t="n">
-        <v>2.64</v>
+        <v>2.42</v>
       </c>
       <c r="AI10" t="n">
-        <v>82.09</v>
+        <v>80.92</v>
       </c>
       <c r="AJ10" t="n">
         <v>0</v>
       </c>
       <c r="AK10" t="n">
-        <v>2.09</v>
+        <v>2.25</v>
       </c>
       <c r="AL10" t="n">
-        <v>3.82</v>
+        <v>3.58</v>
       </c>
       <c r="AM10" t="n">
-        <v>0.18</v>
+        <v>0.25</v>
       </c>
       <c r="AN10" t="n">
-        <v>37.36</v>
+        <v>36.75</v>
       </c>
       <c r="AO10" t="n">
-        <v>0.82</v>
+        <v>0.75</v>
       </c>
       <c r="AP10" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AQ10" t="n">
-        <v>12.18</v>
+        <v>12</v>
       </c>
       <c r="AR10" t="n">
-        <v>12.55</v>
+        <v>12.58</v>
       </c>
       <c r="AS10" t="n">
-        <v>8.449999999999999</v>
+        <v>8.58</v>
       </c>
       <c r="AT10" t="n">
-        <v>1.55</v>
+        <v>1.58</v>
       </c>
       <c r="AU10" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AV10" t="n">
         <v>0</v>
@@ -4750,82 +4750,82 @@
         <v>0</v>
       </c>
       <c r="AY10" t="n">
-        <v>33.27</v>
+        <v>33.58</v>
       </c>
       <c r="AZ10" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="BA10" t="n">
-        <v>9.09</v>
+        <v>8.83</v>
       </c>
       <c r="BB10" t="n">
-        <v>6.45</v>
+        <v>6.33</v>
       </c>
       <c r="BC10" t="n">
-        <v>2.64</v>
+        <v>2.5</v>
       </c>
       <c r="BD10" t="n">
-        <v>20.45</v>
+        <v>20.75</v>
       </c>
       <c r="BE10" t="n">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="BF10" t="n">
-        <v>1.91</v>
+        <v>2.08</v>
       </c>
       <c r="BG10" t="n">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="BH10" t="n">
-        <v>8.960000000000001</v>
+        <v>9</v>
       </c>
       <c r="BI10" t="n">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="BJ10" t="n">
-        <v>0.52</v>
+        <v>0.54</v>
       </c>
       <c r="BK10" t="n">
-        <v>0.3</v>
+        <v>0.33</v>
       </c>
       <c r="BL10" t="n">
-        <v>0.52</v>
+        <v>0.54</v>
       </c>
       <c r="BM10" t="n">
-        <v>0.65</v>
+        <v>0.62</v>
       </c>
       <c r="BN10" t="n">
         <v>1.17</v>
       </c>
       <c r="BO10" t="n">
-        <v>0.83</v>
+        <v>0.88</v>
       </c>
       <c r="BP10" t="n">
-        <v>3.61</v>
+        <v>3.62</v>
       </c>
       <c r="BQ10" t="n">
-        <v>5.35</v>
+        <v>5.38</v>
       </c>
       <c r="BR10" t="n">
-        <v>73.91</v>
+        <v>75</v>
       </c>
       <c r="BS10" t="n">
-        <v>56.52</v>
+        <v>58.33</v>
       </c>
       <c r="BT10" t="n">
-        <v>43.48</v>
+        <v>45.83</v>
       </c>
       <c r="BU10" t="n">
-        <v>17.39</v>
+        <v>16.67</v>
       </c>
       <c r="BV10" t="n">
-        <v>8.699999999999999</v>
+        <v>8.33</v>
       </c>
       <c r="BW10" t="n">
         <v>0</v>
       </c>
       <c r="BX10" t="n">
-        <v>52.17</v>
+        <v>54.17</v>
       </c>
       <c r="BY10" t="n">
         <v>3.41</v>
@@ -4834,16 +4834,16 @@
         <v>3.51</v>
       </c>
       <c r="CA10" t="n">
-        <v>3.52</v>
+        <v>3.56</v>
       </c>
       <c r="CB10" t="n">
-        <v>3.61</v>
+        <v>3.66</v>
       </c>
       <c r="CC10" t="n">
-        <v>4.49</v>
+        <v>4.79</v>
       </c>
       <c r="CD10" t="n">
-        <v>4.83</v>
+        <v>5.13</v>
       </c>
       <c r="CE10" t="n">
         <v>1.39</v>
@@ -4858,10 +4858,10 @@
         <v>1.4</v>
       </c>
       <c r="CI10" t="n">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="CJ10" t="n">
-        <v>1.84</v>
+        <v>1.86</v>
       </c>
       <c r="CK10" t="n">
         <v>1.57</v>
@@ -4876,7 +4876,7 @@
         <v>1.82</v>
       </c>
       <c r="CO10" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="CP10" t="n">
         <v>1.98</v>
@@ -4888,7 +4888,7 @@
         <v>1.4</v>
       </c>
       <c r="CS10" t="n">
-        <v>2.91</v>
+        <v>2.92</v>
       </c>
       <c r="CT10" t="n">
         <v>3.02</v>
@@ -4897,10 +4897,10 @@
         <v>1.43</v>
       </c>
       <c r="CV10" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="CW10" t="n">
-        <v>1.86</v>
+        <v>1.88</v>
       </c>
       <c r="CX10" t="n">
         <v>1.61</v>
@@ -4912,7 +4912,7 @@
         <v>2.31</v>
       </c>
       <c r="DA10" t="n">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="DB10" t="n">
         <v>1.33</v>
@@ -4924,46 +4924,46 @@
         <v>3.56</v>
       </c>
       <c r="DE10" t="n">
-        <v>0.04</v>
+        <v>0.08</v>
       </c>
       <c r="DF10" t="n">
-        <v>0.96</v>
+        <v>1.08</v>
       </c>
       <c r="DG10" t="n">
-        <v>3</v>
+        <v>2.88</v>
       </c>
       <c r="DH10" t="n">
-        <v>83.48</v>
+        <v>82.84</v>
       </c>
       <c r="DI10" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DJ10" t="n">
-        <v>1.78</v>
+        <v>1.88</v>
       </c>
       <c r="DK10" t="n">
-        <v>4.87</v>
+        <v>4.71</v>
       </c>
       <c r="DL10" t="n">
-        <v>0.17</v>
+        <v>0.21</v>
       </c>
       <c r="DM10" t="n">
-        <v>41.87</v>
+        <v>41.38</v>
       </c>
       <c r="DN10" t="n">
-        <v>0.78</v>
+        <v>0.75</v>
       </c>
       <c r="DO10" t="n">
-        <v>1.87</v>
+        <v>1.84</v>
       </c>
       <c r="DP10" t="n">
-        <v>11.61</v>
+        <v>11.54</v>
       </c>
       <c r="DQ10" t="n">
-        <v>12.09</v>
+        <v>12.12</v>
       </c>
       <c r="DR10" t="n">
-        <v>8.52</v>
+        <v>8.58</v>
       </c>
       <c r="DS10" t="n">
         <v>0</v>
@@ -4975,28 +4975,28 @@
         <v>0</v>
       </c>
       <c r="DV10" t="n">
-        <v>36.17</v>
+        <v>36.2</v>
       </c>
       <c r="DW10" t="n">
         <v>0.04</v>
       </c>
       <c r="DX10" t="n">
-        <v>9.65</v>
+        <v>9.5</v>
       </c>
       <c r="DY10" t="n">
-        <v>6.87</v>
+        <v>6.79</v>
       </c>
       <c r="DZ10" t="n">
-        <v>2.79</v>
+        <v>2.71</v>
       </c>
       <c r="EA10" t="n">
-        <v>20.96</v>
+        <v>21.08</v>
       </c>
       <c r="EB10" t="n">
-        <v>1.09</v>
+        <v>1.07</v>
       </c>
       <c r="EC10" t="n">
-        <v>1.7</v>
+        <v>1.79</v>
       </c>
     </row>
     <row r="11">
@@ -5006,13 +5006,13 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C11" t="n">
         <v>12</v>
       </c>
       <c r="D11" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E11" t="n">
         <v>0.08</v>
@@ -5096,139 +5096,139 @@
         <v>2.5</v>
       </c>
       <c r="AF11" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.55</v>
+        <v>1.42</v>
       </c>
       <c r="AH11" t="n">
-        <v>3.09</v>
+        <v>3.17</v>
       </c>
       <c r="AI11" t="n">
-        <v>98.91</v>
+        <v>97.08</v>
       </c>
       <c r="AJ11" t="n">
         <v>0</v>
       </c>
       <c r="AK11" t="n">
-        <v>2.82</v>
+        <v>2.67</v>
       </c>
       <c r="AL11" t="n">
-        <v>6.18</v>
+        <v>6.25</v>
       </c>
       <c r="AM11" t="n">
-        <v>0.36</v>
+        <v>0.33</v>
       </c>
       <c r="AN11" t="n">
-        <v>55</v>
+        <v>54.42</v>
       </c>
       <c r="AO11" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AP11" t="n">
-        <v>3.09</v>
+        <v>3.08</v>
       </c>
       <c r="AQ11" t="n">
-        <v>14.55</v>
+        <v>15</v>
       </c>
       <c r="AR11" t="n">
-        <v>9.82</v>
+        <v>9.83</v>
       </c>
       <c r="AS11" t="n">
-        <v>8.18</v>
+        <v>8.08</v>
       </c>
       <c r="AT11" t="n">
-        <v>1.64</v>
+        <v>1.67</v>
       </c>
       <c r="AU11" t="n">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="AV11" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="AW11" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="AX11" t="n">
         <v>0</v>
       </c>
       <c r="AY11" t="n">
-        <v>55.91</v>
+        <v>55.17</v>
       </c>
       <c r="AZ11" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="BA11" t="n">
-        <v>12.82</v>
+        <v>12.67</v>
       </c>
       <c r="BB11" t="n">
-        <v>8.82</v>
+        <v>8.75</v>
       </c>
       <c r="BC11" t="n">
-        <v>4</v>
+        <v>3.92</v>
       </c>
       <c r="BD11" t="n">
-        <v>23.27</v>
+        <v>22</v>
       </c>
       <c r="BE11" t="n">
-        <v>1.49</v>
+        <v>1.47</v>
       </c>
       <c r="BF11" t="n">
-        <v>2.64</v>
+        <v>2.5</v>
       </c>
       <c r="BG11" t="n">
-        <v>2.52</v>
+        <v>2.5</v>
       </c>
       <c r="BH11" t="n">
-        <v>10.74</v>
+        <v>10.79</v>
       </c>
       <c r="BI11" t="n">
-        <v>2.52</v>
+        <v>2.5</v>
       </c>
       <c r="BJ11" t="n">
-        <v>0.7</v>
+        <v>0.67</v>
       </c>
       <c r="BK11" t="n">
-        <v>0.39</v>
+        <v>0.38</v>
       </c>
       <c r="BL11" t="n">
-        <v>0.87</v>
+        <v>0.92</v>
       </c>
       <c r="BM11" t="n">
-        <v>0.57</v>
+        <v>0.54</v>
       </c>
       <c r="BN11" t="n">
-        <v>1.43</v>
+        <v>1.46</v>
       </c>
       <c r="BO11" t="n">
-        <v>1.09</v>
+        <v>1.04</v>
       </c>
       <c r="BP11" t="n">
-        <v>5.17</v>
+        <v>5.21</v>
       </c>
       <c r="BQ11" t="n">
-        <v>5.57</v>
+        <v>5.58</v>
       </c>
       <c r="BR11" t="n">
-        <v>91.3</v>
+        <v>91.67</v>
       </c>
       <c r="BS11" t="n">
-        <v>65.22</v>
+        <v>66.67</v>
       </c>
       <c r="BT11" t="n">
-        <v>39.13</v>
+        <v>37.5</v>
       </c>
       <c r="BU11" t="n">
-        <v>30.43</v>
+        <v>29.17</v>
       </c>
       <c r="BV11" t="n">
-        <v>13.04</v>
+        <v>12.5</v>
       </c>
       <c r="BW11" t="n">
-        <v>8.699999999999999</v>
+        <v>8.33</v>
       </c>
       <c r="BX11" t="n">
-        <v>43.48</v>
+        <v>41.67</v>
       </c>
       <c r="BY11" t="n">
         <v>1.93</v>
@@ -5243,16 +5243,16 @@
         <v>3.7</v>
       </c>
       <c r="CC11" t="n">
-        <v>2.41</v>
+        <v>2.48</v>
       </c>
       <c r="CD11" t="n">
-        <v>2.56</v>
+        <v>2.7</v>
       </c>
       <c r="CE11" t="n">
         <v>1.33</v>
       </c>
       <c r="CF11" t="n">
-        <v>2.57</v>
+        <v>2.56</v>
       </c>
       <c r="CG11" t="n">
         <v>3.06</v>
@@ -5261,7 +5261,7 @@
         <v>1.47</v>
       </c>
       <c r="CI11" t="n">
-        <v>2.12</v>
+        <v>2.13</v>
       </c>
       <c r="CJ11" t="n">
         <v>1.69</v>
@@ -5273,7 +5273,7 @@
         <v>1.91</v>
       </c>
       <c r="CM11" t="n">
-        <v>2.53</v>
+        <v>2.52</v>
       </c>
       <c r="CN11" t="n">
         <v>1.94</v>
@@ -5300,7 +5300,7 @@
         <v>1.49</v>
       </c>
       <c r="CV11" t="n">
-        <v>2.2</v>
+        <v>2.19</v>
       </c>
       <c r="CW11" t="n">
         <v>1.73</v>
@@ -5312,10 +5312,10 @@
         <v>1.83</v>
       </c>
       <c r="CZ11" t="n">
-        <v>2.5</v>
+        <v>2.49</v>
       </c>
       <c r="DA11" t="n">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="DB11" t="n">
         <v>1.27</v>
@@ -5327,46 +5327,46 @@
         <v>3.1</v>
       </c>
       <c r="DE11" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="DF11" t="n">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="DG11" t="n">
-        <v>3.3</v>
+        <v>3.33</v>
       </c>
       <c r="DH11" t="n">
-        <v>103.87</v>
+        <v>102.75</v>
       </c>
       <c r="DI11" t="n">
         <v>0</v>
       </c>
       <c r="DJ11" t="n">
-        <v>2.74</v>
+        <v>2.67</v>
       </c>
       <c r="DK11" t="n">
-        <v>6.35</v>
+        <v>6.38</v>
       </c>
       <c r="DL11" t="n">
-        <v>0.52</v>
+        <v>0.5</v>
       </c>
       <c r="DM11" t="n">
-        <v>57.57</v>
+        <v>57.17</v>
       </c>
       <c r="DN11" t="n">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="DO11" t="n">
         <v>3.04</v>
       </c>
       <c r="DP11" t="n">
-        <v>13.65</v>
+        <v>13.92</v>
       </c>
       <c r="DQ11" t="n">
-        <v>10.96</v>
+        <v>10.92</v>
       </c>
       <c r="DR11" t="n">
-        <v>7.74</v>
+        <v>7.71</v>
       </c>
       <c r="DS11" t="n">
         <v>0.17</v>
@@ -5378,28 +5378,28 @@
         <v>0</v>
       </c>
       <c r="DV11" t="n">
-        <v>53.91</v>
+        <v>53.62</v>
       </c>
       <c r="DW11" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="DX11" t="n">
-        <v>15.04</v>
+        <v>14.88</v>
       </c>
       <c r="DY11" t="n">
-        <v>10.31</v>
+        <v>10.21</v>
       </c>
       <c r="DZ11" t="n">
-        <v>4.74</v>
+        <v>4.67</v>
       </c>
       <c r="EA11" t="n">
-        <v>21.69</v>
+        <v>21.12</v>
       </c>
       <c r="EB11" t="n">
-        <v>1.7</v>
+        <v>1.68</v>
       </c>
       <c r="EC11" t="n">
-        <v>2.57</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="12">
@@ -5409,13 +5409,13 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C12" t="n">
         <v>12</v>
       </c>
       <c r="D12" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E12" t="n">
         <v>0.08</v>
@@ -5502,127 +5502,127 @@
         <v>0</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="AH12" t="n">
-        <v>2.27</v>
+        <v>2.42</v>
       </c>
       <c r="AI12" t="n">
-        <v>91.36</v>
+        <v>95.67</v>
       </c>
       <c r="AJ12" t="n">
         <v>0</v>
       </c>
       <c r="AK12" t="n">
-        <v>2</v>
+        <v>1.92</v>
       </c>
       <c r="AL12" t="n">
-        <v>3.36</v>
+        <v>3.58</v>
       </c>
       <c r="AM12" t="n">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="AN12" t="n">
-        <v>35.82</v>
+        <v>38.67</v>
       </c>
       <c r="AO12" t="n">
-        <v>0.45</v>
+        <v>0.42</v>
       </c>
       <c r="AP12" t="n">
-        <v>1.09</v>
+        <v>1.17</v>
       </c>
       <c r="AQ12" t="n">
-        <v>13.09</v>
+        <v>13.25</v>
       </c>
       <c r="AR12" t="n">
-        <v>12.09</v>
+        <v>11.83</v>
       </c>
       <c r="AS12" t="n">
-        <v>7.82</v>
+        <v>7.5</v>
       </c>
       <c r="AT12" t="n">
-        <v>0.82</v>
+        <v>0.92</v>
       </c>
       <c r="AU12" t="n">
-        <v>0.82</v>
+        <v>0.75</v>
       </c>
       <c r="AV12" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="AW12" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="AX12" t="n">
         <v>0</v>
       </c>
       <c r="AY12" t="n">
-        <v>46</v>
+        <v>47.75</v>
       </c>
       <c r="AZ12" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="BA12" t="n">
-        <v>10.18</v>
+        <v>10.67</v>
       </c>
       <c r="BB12" t="n">
-        <v>6.73</v>
+        <v>7.08</v>
       </c>
       <c r="BC12" t="n">
-        <v>3.45</v>
+        <v>3.58</v>
       </c>
       <c r="BD12" t="n">
-        <v>21.27</v>
+        <v>22.25</v>
       </c>
       <c r="BE12" t="n">
-        <v>1.15</v>
+        <v>1.21</v>
       </c>
       <c r="BF12" t="n">
-        <v>1.82</v>
+        <v>1.75</v>
       </c>
       <c r="BG12" t="n">
-        <v>2.26</v>
+        <v>2.25</v>
       </c>
       <c r="BH12" t="n">
-        <v>9.220000000000001</v>
+        <v>9.210000000000001</v>
       </c>
       <c r="BI12" t="n">
-        <v>2.26</v>
+        <v>2.25</v>
       </c>
       <c r="BJ12" t="n">
-        <v>0.7</v>
+        <v>0.71</v>
       </c>
       <c r="BK12" t="n">
-        <v>0.48</v>
+        <v>0.46</v>
       </c>
       <c r="BL12" t="n">
-        <v>0.52</v>
+        <v>0.54</v>
       </c>
       <c r="BM12" t="n">
-        <v>0.57</v>
+        <v>0.54</v>
       </c>
       <c r="BN12" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="BO12" t="n">
         <v>1.17</v>
       </c>
       <c r="BP12" t="n">
-        <v>4.04</v>
+        <v>4</v>
       </c>
       <c r="BQ12" t="n">
-        <v>5.13</v>
+        <v>5.17</v>
       </c>
       <c r="BR12" t="n">
-        <v>95.65000000000001</v>
+        <v>95.83</v>
       </c>
       <c r="BS12" t="n">
-        <v>73.91</v>
+        <v>75</v>
       </c>
       <c r="BT12" t="n">
-        <v>39.13</v>
+        <v>37.5</v>
       </c>
       <c r="BU12" t="n">
-        <v>17.39</v>
+        <v>16.67</v>
       </c>
       <c r="BV12" t="n">
         <v>0</v>
@@ -5631,7 +5631,7 @@
         <v>0</v>
       </c>
       <c r="BX12" t="n">
-        <v>47.83</v>
+        <v>45.83</v>
       </c>
       <c r="BY12" t="n">
         <v>2.72</v>
@@ -5640,43 +5640,43 @@
         <v>2.93</v>
       </c>
       <c r="CA12" t="n">
-        <v>3.51</v>
+        <v>3.5</v>
       </c>
       <c r="CB12" t="n">
-        <v>3.64</v>
+        <v>3.62</v>
       </c>
       <c r="CC12" t="n">
-        <v>3.92</v>
+        <v>3.85</v>
       </c>
       <c r="CD12" t="n">
-        <v>4.35</v>
+        <v>4.25</v>
       </c>
       <c r="CE12" t="n">
         <v>1.34</v>
       </c>
       <c r="CF12" t="n">
-        <v>2.61</v>
+        <v>2.62</v>
       </c>
       <c r="CG12" t="n">
-        <v>3.01</v>
+        <v>3</v>
       </c>
       <c r="CH12" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="CI12" t="n">
-        <v>2.09</v>
+        <v>2.08</v>
       </c>
       <c r="CJ12" t="n">
         <v>1.7</v>
       </c>
       <c r="CK12" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="CL12" t="n">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="CM12" t="n">
-        <v>2.44</v>
+        <v>2.43</v>
       </c>
       <c r="CN12" t="n">
         <v>1.89</v>
@@ -5688,16 +5688,16 @@
         <v>1.85</v>
       </c>
       <c r="CQ12" t="n">
-        <v>3.06</v>
+        <v>3.08</v>
       </c>
       <c r="CR12" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="CS12" t="n">
-        <v>2.74</v>
+        <v>2.76</v>
       </c>
       <c r="CT12" t="n">
-        <v>3.14</v>
+        <v>3.13</v>
       </c>
       <c r="CU12" t="n">
         <v>1.47</v>
@@ -5709,7 +5709,7 @@
         <v>1.76</v>
       </c>
       <c r="CX12" t="n">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="CY12" t="n">
         <v>1.93</v>
@@ -5727,82 +5727,82 @@
         <v>1.92</v>
       </c>
       <c r="DD12" t="n">
-        <v>3.2</v>
+        <v>3.21</v>
       </c>
       <c r="DE12" t="n">
         <v>0.04</v>
       </c>
       <c r="DF12" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="DG12" t="n">
-        <v>2.3</v>
+        <v>2.38</v>
       </c>
       <c r="DH12" t="n">
-        <v>94.43000000000001</v>
+        <v>96.45999999999999</v>
       </c>
       <c r="DI12" t="n">
         <v>0.04</v>
       </c>
       <c r="DJ12" t="n">
-        <v>2.09</v>
+        <v>2.04</v>
       </c>
       <c r="DK12" t="n">
-        <v>4.09</v>
+        <v>4.16</v>
       </c>
       <c r="DL12" t="n">
-        <v>0.43</v>
+        <v>0.42</v>
       </c>
       <c r="DM12" t="n">
-        <v>40.52</v>
+        <v>41.75</v>
       </c>
       <c r="DN12" t="n">
-        <v>0.65</v>
+        <v>0.62</v>
       </c>
       <c r="DO12" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="DP12" t="n">
-        <v>12.56</v>
+        <v>12.66</v>
       </c>
       <c r="DQ12" t="n">
-        <v>12.17</v>
+        <v>12.04</v>
       </c>
       <c r="DR12" t="n">
-        <v>7.43</v>
+        <v>7.29</v>
       </c>
       <c r="DS12" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="DT12" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="DU12" t="n">
         <v>0</v>
       </c>
       <c r="DV12" t="n">
-        <v>48.18</v>
+        <v>48.96</v>
       </c>
       <c r="DW12" t="n">
         <v>0.08</v>
       </c>
       <c r="DX12" t="n">
-        <v>11.74</v>
+        <v>11.92</v>
       </c>
       <c r="DY12" t="n">
-        <v>7.35</v>
+        <v>7.5</v>
       </c>
       <c r="DZ12" t="n">
-        <v>4.39</v>
+        <v>4.42</v>
       </c>
       <c r="EA12" t="n">
-        <v>21.04</v>
+        <v>21.54</v>
       </c>
       <c r="EB12" t="n">
-        <v>1.35</v>
+        <v>1.37</v>
       </c>
       <c r="EC12" t="n">
-        <v>1.91</v>
+        <v>1.88</v>
       </c>
     </row>
     <row r="13">
@@ -6618,13 +6618,13 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C15" t="n">
         <v>12</v>
       </c>
       <c r="D15" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E15" t="n">
         <v>0.17</v>
@@ -6708,16 +6708,16 @@
         <v>2.33</v>
       </c>
       <c r="AF15" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.36</v>
+        <v>1.42</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.73</v>
+        <v>1.58</v>
       </c>
       <c r="AI15" t="n">
-        <v>85.36</v>
+        <v>84.08</v>
       </c>
       <c r="AJ15" t="n">
         <v>0</v>
@@ -6726,112 +6726,112 @@
         <v>2</v>
       </c>
       <c r="AL15" t="n">
-        <v>3.45</v>
+        <v>3.17</v>
       </c>
       <c r="AM15" t="n">
-        <v>0.36</v>
+        <v>0.33</v>
       </c>
       <c r="AN15" t="n">
-        <v>36</v>
+        <v>38.75</v>
       </c>
       <c r="AO15" t="n">
-        <v>0.64</v>
+        <v>0.58</v>
       </c>
       <c r="AP15" t="n">
-        <v>1.73</v>
+        <v>1.58</v>
       </c>
       <c r="AQ15" t="n">
-        <v>11.18</v>
+        <v>11.08</v>
       </c>
       <c r="AR15" t="n">
-        <v>12</v>
+        <v>11.67</v>
       </c>
       <c r="AS15" t="n">
-        <v>10.09</v>
+        <v>9.92</v>
       </c>
       <c r="AT15" t="n">
-        <v>1.18</v>
+        <v>1.33</v>
       </c>
       <c r="AU15" t="n">
-        <v>0.73</v>
+        <v>0.67</v>
       </c>
       <c r="AV15" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="AW15" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="AX15" t="n">
         <v>0</v>
       </c>
       <c r="AY15" t="n">
-        <v>45.18</v>
+        <v>43.83</v>
       </c>
       <c r="AZ15" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="BA15" t="n">
-        <v>8.09</v>
+        <v>7.83</v>
       </c>
       <c r="BB15" t="n">
-        <v>5.64</v>
+        <v>5.58</v>
       </c>
       <c r="BC15" t="n">
-        <v>2.45</v>
+        <v>2.25</v>
       </c>
       <c r="BD15" t="n">
-        <v>18.09</v>
+        <v>17.5</v>
       </c>
       <c r="BE15" t="n">
-        <v>0.95</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="BF15" t="n">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="BG15" t="n">
-        <v>2.13</v>
+        <v>2.17</v>
       </c>
       <c r="BH15" t="n">
-        <v>10</v>
+        <v>9.880000000000001</v>
       </c>
       <c r="BI15" t="n">
-        <v>2.13</v>
+        <v>2.17</v>
       </c>
       <c r="BJ15" t="n">
-        <v>0.52</v>
+        <v>0.62</v>
       </c>
       <c r="BK15" t="n">
-        <v>0.65</v>
+        <v>0.62</v>
       </c>
       <c r="BL15" t="n">
-        <v>0.57</v>
+        <v>0.54</v>
       </c>
       <c r="BM15" t="n">
-        <v>0.39</v>
+        <v>0.38</v>
       </c>
       <c r="BN15" t="n">
-        <v>0.96</v>
+        <v>0.92</v>
       </c>
       <c r="BO15" t="n">
-        <v>1.17</v>
+        <v>1.25</v>
       </c>
       <c r="BP15" t="n">
-        <v>4.61</v>
+        <v>4.58</v>
       </c>
       <c r="BQ15" t="n">
-        <v>5.39</v>
+        <v>5.29</v>
       </c>
       <c r="BR15" t="n">
-        <v>95.65000000000001</v>
+        <v>95.83</v>
       </c>
       <c r="BS15" t="n">
-        <v>65.22</v>
+        <v>66.67</v>
       </c>
       <c r="BT15" t="n">
-        <v>39.13</v>
+        <v>41.67</v>
       </c>
       <c r="BU15" t="n">
-        <v>13.04</v>
+        <v>12.5</v>
       </c>
       <c r="BV15" t="n">
         <v>0</v>
@@ -6840,7 +6840,7 @@
         <v>0</v>
       </c>
       <c r="BX15" t="n">
-        <v>30.43</v>
+        <v>29.17</v>
       </c>
       <c r="BY15" t="n">
         <v>2.88</v>
@@ -6849,31 +6849,31 @@
         <v>3.12</v>
       </c>
       <c r="CA15" t="n">
-        <v>3.42</v>
+        <v>3.51</v>
       </c>
       <c r="CB15" t="n">
-        <v>3.47</v>
+        <v>3.58</v>
       </c>
       <c r="CC15" t="n">
-        <v>4.01</v>
+        <v>4.23</v>
       </c>
       <c r="CD15" t="n">
-        <v>4.54</v>
+        <v>5.07</v>
       </c>
       <c r="CE15" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="CF15" t="n">
-        <v>2.84</v>
+        <v>2.82</v>
       </c>
       <c r="CG15" t="n">
-        <v>2.85</v>
+        <v>2.87</v>
       </c>
       <c r="CH15" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="CI15" t="n">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="CJ15" t="n">
         <v>1.82</v>
@@ -6882,7 +6882,7 @@
         <v>1.5</v>
       </c>
       <c r="CL15" t="n">
-        <v>1.87</v>
+        <v>1.89</v>
       </c>
       <c r="CM15" t="n">
         <v>2.51</v>
@@ -6894,124 +6894,124 @@
         <v>1.31</v>
       </c>
       <c r="CP15" t="n">
-        <v>1.99</v>
+        <v>1.97</v>
       </c>
       <c r="CQ15" t="n">
-        <v>3.47</v>
+        <v>3.43</v>
       </c>
       <c r="CR15" t="n">
         <v>1.41</v>
       </c>
       <c r="CS15" t="n">
-        <v>2.97</v>
+        <v>2.94</v>
       </c>
       <c r="CT15" t="n">
         <v>2.99</v>
       </c>
       <c r="CU15" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="CV15" t="n">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="CW15" t="n">
         <v>1.85</v>
       </c>
       <c r="CX15" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="CY15" t="n">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="CZ15" t="n">
-        <v>2.4</v>
+        <v>2.39</v>
       </c>
       <c r="DA15" t="n">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="DB15" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="DC15" t="n">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="DD15" t="n">
-        <v>3.58</v>
+        <v>3.53</v>
       </c>
       <c r="DE15" t="n">
         <v>0.17</v>
       </c>
       <c r="DF15" t="n">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="DG15" t="n">
-        <v>2.04</v>
+        <v>1.96</v>
       </c>
       <c r="DH15" t="n">
-        <v>86.87</v>
+        <v>86.16</v>
       </c>
       <c r="DI15" t="n">
         <v>0</v>
       </c>
       <c r="DJ15" t="n">
-        <v>2.52</v>
+        <v>2.5</v>
       </c>
       <c r="DK15" t="n">
-        <v>4.52</v>
+        <v>4.34</v>
       </c>
       <c r="DL15" t="n">
-        <v>0.61</v>
+        <v>0.58</v>
       </c>
       <c r="DM15" t="n">
-        <v>44.26</v>
+        <v>45.29</v>
       </c>
       <c r="DN15" t="n">
-        <v>0.87</v>
+        <v>0.83</v>
       </c>
       <c r="DO15" t="n">
-        <v>2.48</v>
+        <v>2.38</v>
       </c>
       <c r="DP15" t="n">
-        <v>11.17</v>
+        <v>11.12</v>
       </c>
       <c r="DQ15" t="n">
-        <v>12.43</v>
+        <v>12.25</v>
       </c>
       <c r="DR15" t="n">
-        <v>9.300000000000001</v>
+        <v>9.25</v>
       </c>
       <c r="DS15" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="DT15" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="DU15" t="n">
         <v>0</v>
       </c>
       <c r="DV15" t="n">
-        <v>44.87</v>
+        <v>44.21</v>
       </c>
       <c r="DW15" t="n">
-        <v>0.26</v>
+        <v>0.25</v>
       </c>
       <c r="DX15" t="n">
-        <v>9.779999999999999</v>
+        <v>9.58</v>
       </c>
       <c r="DY15" t="n">
-        <v>6.52</v>
+        <v>6.46</v>
       </c>
       <c r="DZ15" t="n">
-        <v>3.26</v>
+        <v>3.12</v>
       </c>
       <c r="EA15" t="n">
-        <v>19.39</v>
+        <v>19.04</v>
       </c>
       <c r="EB15" t="n">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="EC15" t="n">
-        <v>2.09</v>
+        <v>2.08</v>
       </c>
     </row>
     <row r="16">
@@ -7021,94 +7021,94 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C16" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D16" t="n">
         <v>12</v>
       </c>
       <c r="E16" t="n">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="F16" t="n">
-        <v>1.36</v>
+        <v>1.58</v>
       </c>
       <c r="G16" t="n">
-        <v>3.18</v>
+        <v>3.42</v>
       </c>
       <c r="H16" t="n">
-        <v>98.45</v>
+        <v>100.25</v>
       </c>
       <c r="I16" t="n">
         <v>0</v>
       </c>
       <c r="J16" t="n">
-        <v>1.64</v>
+        <v>1.83</v>
       </c>
       <c r="K16" t="n">
-        <v>6.18</v>
+        <v>6.42</v>
       </c>
       <c r="L16" t="n">
-        <v>0.45</v>
+        <v>0.42</v>
       </c>
       <c r="M16" t="n">
-        <v>54.91</v>
+        <v>55.75</v>
       </c>
       <c r="N16" t="n">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="O16" t="n">
         <v>3</v>
       </c>
       <c r="P16" t="n">
-        <v>12.27</v>
+        <v>12.25</v>
       </c>
       <c r="Q16" t="n">
-        <v>9.91</v>
+        <v>10</v>
       </c>
       <c r="R16" t="n">
-        <v>5.36</v>
+        <v>5.42</v>
       </c>
       <c r="S16" t="n">
-        <v>0.18</v>
+        <v>0.25</v>
       </c>
       <c r="T16" t="n">
-        <v>2.18</v>
+        <v>2.17</v>
       </c>
       <c r="U16" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="V16" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="W16" t="n">
         <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>50.18</v>
+        <v>51.25</v>
       </c>
       <c r="Y16" t="n">
         <v>0</v>
       </c>
       <c r="Z16" t="n">
-        <v>16.55</v>
+        <v>16.5</v>
       </c>
       <c r="AA16" t="n">
-        <v>10</v>
+        <v>9.83</v>
       </c>
       <c r="AB16" t="n">
-        <v>6.55</v>
+        <v>6.67</v>
       </c>
       <c r="AC16" t="n">
-        <v>20</v>
+        <v>20.92</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.64</v>
+        <v>1.83</v>
       </c>
       <c r="AF16" t="n">
         <v>0.08</v>
@@ -7192,70 +7192,70 @@
         <v>2.83</v>
       </c>
       <c r="BG16" t="n">
-        <v>2.17</v>
+        <v>2.21</v>
       </c>
       <c r="BH16" t="n">
-        <v>9.52</v>
+        <v>9.539999999999999</v>
       </c>
       <c r="BI16" t="n">
-        <v>2.17</v>
+        <v>2.21</v>
       </c>
       <c r="BJ16" t="n">
-        <v>0.52</v>
+        <v>0.54</v>
       </c>
       <c r="BK16" t="n">
-        <v>0.35</v>
+        <v>0.38</v>
       </c>
       <c r="BL16" t="n">
         <v>0.96</v>
       </c>
       <c r="BM16" t="n">
-        <v>0.35</v>
+        <v>0.33</v>
       </c>
       <c r="BN16" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="BO16" t="n">
-        <v>0.87</v>
+        <v>0.92</v>
       </c>
       <c r="BP16" t="n">
-        <v>4.83</v>
+        <v>4.79</v>
       </c>
       <c r="BQ16" t="n">
-        <v>4.7</v>
+        <v>4.75</v>
       </c>
       <c r="BR16" t="n">
-        <v>91.3</v>
+        <v>91.67</v>
       </c>
       <c r="BS16" t="n">
-        <v>69.56999999999999</v>
+        <v>70.83</v>
       </c>
       <c r="BT16" t="n">
-        <v>26.09</v>
+        <v>29.17</v>
       </c>
       <c r="BU16" t="n">
-        <v>17.39</v>
+        <v>16.67</v>
       </c>
       <c r="BV16" t="n">
-        <v>13.04</v>
+        <v>12.5</v>
       </c>
       <c r="BW16" t="n">
         <v>0</v>
       </c>
       <c r="BX16" t="n">
-        <v>39.13</v>
+        <v>41.67</v>
       </c>
       <c r="BY16" t="n">
         <v>1.42</v>
       </c>
       <c r="BZ16" t="n">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="CA16" t="n">
-        <v>4.16</v>
+        <v>4.17</v>
       </c>
       <c r="CB16" t="n">
-        <v>4.35</v>
+        <v>4.37</v>
       </c>
       <c r="CC16" t="n">
         <v>1.89</v>
@@ -7264,61 +7264,61 @@
         <v>1.94</v>
       </c>
       <c r="CE16" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="CF16" t="n">
-        <v>2.53</v>
+        <v>2.54</v>
       </c>
       <c r="CG16" t="n">
-        <v>3.17</v>
+        <v>3.16</v>
       </c>
       <c r="CH16" t="n">
         <v>1.49</v>
       </c>
       <c r="CI16" t="n">
-        <v>1.94</v>
+        <v>1.92</v>
       </c>
       <c r="CJ16" t="n">
-        <v>1.82</v>
+        <v>1.84</v>
       </c>
       <c r="CK16" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="CL16" t="n">
         <v>1.96</v>
       </c>
       <c r="CM16" t="n">
-        <v>2.48</v>
+        <v>2.47</v>
       </c>
       <c r="CN16" t="n">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="CO16" t="n">
         <v>1.23</v>
       </c>
       <c r="CP16" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="CQ16" t="n">
-        <v>2.82</v>
+        <v>2.85</v>
       </c>
       <c r="CR16" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="CS16" t="n">
-        <v>2.65</v>
+        <v>2.66</v>
       </c>
       <c r="CT16" t="n">
-        <v>3.17</v>
+        <v>3.16</v>
       </c>
       <c r="CU16" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="CV16" t="n">
-        <v>2.03</v>
+        <v>2.01</v>
       </c>
       <c r="CW16" t="n">
-        <v>1.87</v>
+        <v>1.89</v>
       </c>
       <c r="CX16" t="n">
         <v>1.57</v>
@@ -7330,91 +7330,91 @@
         <v>2.37</v>
       </c>
       <c r="DA16" t="n">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="DB16" t="n">
         <v>1.26</v>
       </c>
       <c r="DC16" t="n">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="DD16" t="n">
-        <v>2.99</v>
+        <v>3.01</v>
       </c>
       <c r="DE16" t="n">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
       <c r="DF16" t="n">
-        <v>1.61</v>
+        <v>1.7</v>
       </c>
       <c r="DG16" t="n">
-        <v>3</v>
+        <v>3.12</v>
       </c>
       <c r="DH16" t="n">
-        <v>104.74</v>
+        <v>105.38</v>
       </c>
       <c r="DI16" t="n">
         <v>0.04</v>
       </c>
       <c r="DJ16" t="n">
-        <v>2.31</v>
+        <v>2.38</v>
       </c>
       <c r="DK16" t="n">
-        <v>5.83</v>
+        <v>5.96</v>
       </c>
       <c r="DL16" t="n">
-        <v>0.48</v>
+        <v>0.46</v>
       </c>
       <c r="DM16" t="n">
-        <v>53.22</v>
+        <v>53.71</v>
       </c>
       <c r="DN16" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.66</v>
       </c>
       <c r="DO16" t="n">
         <v>2.83</v>
       </c>
       <c r="DP16" t="n">
-        <v>12.91</v>
+        <v>12.88</v>
       </c>
       <c r="DQ16" t="n">
-        <v>9.65</v>
+        <v>9.710000000000001</v>
       </c>
       <c r="DR16" t="n">
-        <v>5.87</v>
+        <v>5.88</v>
       </c>
       <c r="DS16" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DT16" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DU16" t="n">
         <v>0</v>
       </c>
       <c r="DV16" t="n">
-        <v>52.69</v>
+        <v>53.12</v>
       </c>
       <c r="DW16" t="n">
         <v>0.04</v>
       </c>
       <c r="DX16" t="n">
-        <v>15.31</v>
+        <v>15.34</v>
       </c>
       <c r="DY16" t="n">
-        <v>9.699999999999999</v>
+        <v>9.619999999999999</v>
       </c>
       <c r="DZ16" t="n">
-        <v>5.61</v>
+        <v>5.71</v>
       </c>
       <c r="EA16" t="n">
-        <v>19.78</v>
+        <v>20.25</v>
       </c>
       <c r="EB16" t="n">
-        <v>1.74</v>
+        <v>1.76</v>
       </c>
       <c r="EC16" t="n">
-        <v>2.26</v>
+        <v>2.33</v>
       </c>
     </row>
     <row r="17">

--- a/data/teams/leagues/Averages_Belgium_Pro_League_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Belgium_Pro_League_2025-2026.xlsx
@@ -2185,13 +2185,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C4" t="n">
         <v>12</v>
       </c>
       <c r="D4" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
@@ -2275,31 +2275,31 @@
         <v>1.83</v>
       </c>
       <c r="AF4" t="n">
-        <v>0.17</v>
+        <v>0.23</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.75</v>
+        <v>1.62</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.42</v>
+        <v>1.69</v>
       </c>
       <c r="AI4" t="n">
-        <v>88.92</v>
+        <v>88.45999999999999</v>
       </c>
       <c r="AJ4" t="n">
-        <v>0.17</v>
+        <v>0.15</v>
       </c>
       <c r="AK4" t="n">
-        <v>2.83</v>
+        <v>2.69</v>
       </c>
       <c r="AL4" t="n">
-        <v>3.33</v>
+        <v>3.62</v>
       </c>
       <c r="AM4" t="n">
         <v>0.08</v>
       </c>
       <c r="AN4" t="n">
-        <v>38.92</v>
+        <v>40.08</v>
       </c>
       <c r="AO4" t="n">
         <v>0.92</v>
@@ -2308,106 +2308,106 @@
         <v>1.92</v>
       </c>
       <c r="AQ4" t="n">
-        <v>11.83</v>
+        <v>11.54</v>
       </c>
       <c r="AR4" t="n">
-        <v>11.83</v>
+        <v>11.54</v>
       </c>
       <c r="AS4" t="n">
-        <v>10.83</v>
+        <v>10.38</v>
       </c>
       <c r="AT4" t="n">
-        <v>1.5</v>
+        <v>1.62</v>
       </c>
       <c r="AU4" t="n">
-        <v>0.83</v>
+        <v>0.92</v>
       </c>
       <c r="AV4" t="n">
-        <v>0.08</v>
+        <v>0.15</v>
       </c>
       <c r="AW4" t="n">
-        <v>0.08</v>
+        <v>0.15</v>
       </c>
       <c r="AX4" t="n">
         <v>0</v>
       </c>
       <c r="AY4" t="n">
-        <v>43.67</v>
+        <v>44.77</v>
       </c>
       <c r="AZ4" t="n">
-        <v>0.33</v>
+        <v>0.31</v>
       </c>
       <c r="BA4" t="n">
-        <v>10.83</v>
+        <v>11</v>
       </c>
       <c r="BB4" t="n">
-        <v>6.5</v>
+        <v>6.69</v>
       </c>
       <c r="BC4" t="n">
-        <v>4.33</v>
+        <v>4.31</v>
       </c>
       <c r="BD4" t="n">
-        <v>20.17</v>
+        <v>21.08</v>
       </c>
       <c r="BE4" t="n">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="BF4" t="n">
-        <v>2.33</v>
+        <v>2.23</v>
       </c>
       <c r="BG4" t="n">
-        <v>2.29</v>
+        <v>2.4</v>
       </c>
       <c r="BH4" t="n">
-        <v>8.380000000000001</v>
+        <v>8.720000000000001</v>
       </c>
       <c r="BI4" t="n">
-        <v>2.29</v>
+        <v>2.4</v>
       </c>
       <c r="BJ4" t="n">
-        <v>0.5</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="BK4" t="n">
-        <v>0.33</v>
+        <v>0.36</v>
       </c>
       <c r="BL4" t="n">
-        <v>0.58</v>
+        <v>0.6</v>
       </c>
       <c r="BM4" t="n">
         <v>0.88</v>
       </c>
       <c r="BN4" t="n">
-        <v>1.46</v>
+        <v>1.48</v>
       </c>
       <c r="BO4" t="n">
-        <v>0.83</v>
+        <v>0.92</v>
       </c>
       <c r="BP4" t="n">
-        <v>3.71</v>
+        <v>3.92</v>
       </c>
       <c r="BQ4" t="n">
-        <v>4.12</v>
+        <v>4.28</v>
       </c>
       <c r="BR4" t="n">
-        <v>87.5</v>
+        <v>88</v>
       </c>
       <c r="BS4" t="n">
-        <v>66.67</v>
+        <v>68</v>
       </c>
       <c r="BT4" t="n">
-        <v>45.83</v>
+        <v>48</v>
       </c>
       <c r="BU4" t="n">
-        <v>20.83</v>
+        <v>24</v>
       </c>
       <c r="BV4" t="n">
-        <v>4.17</v>
+        <v>8</v>
       </c>
       <c r="BW4" t="n">
-        <v>4.17</v>
+        <v>4</v>
       </c>
       <c r="BX4" t="n">
-        <v>54.17</v>
+        <v>56</v>
       </c>
       <c r="BY4" t="n">
         <v>3.41</v>
@@ -2416,31 +2416,31 @@
         <v>3.57</v>
       </c>
       <c r="CA4" t="n">
-        <v>3.66</v>
+        <v>3.65</v>
       </c>
       <c r="CB4" t="n">
-        <v>3.81</v>
+        <v>3.79</v>
       </c>
       <c r="CC4" t="n">
-        <v>4.65</v>
+        <v>4.56</v>
       </c>
       <c r="CD4" t="n">
-        <v>4.93</v>
+        <v>4.83</v>
       </c>
       <c r="CE4" t="n">
         <v>1.35</v>
       </c>
       <c r="CF4" t="n">
-        <v>2.61</v>
+        <v>2.62</v>
       </c>
       <c r="CG4" t="n">
-        <v>3.07</v>
+        <v>3.05</v>
       </c>
       <c r="CH4" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="CI4" t="n">
-        <v>2.03</v>
+        <v>2.02</v>
       </c>
       <c r="CJ4" t="n">
         <v>1.74</v>
@@ -2449,22 +2449,22 @@
         <v>1.55</v>
       </c>
       <c r="CL4" t="n">
-        <v>2.02</v>
+        <v>2.01</v>
       </c>
       <c r="CM4" t="n">
-        <v>2.35</v>
+        <v>2.34</v>
       </c>
       <c r="CN4" t="n">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="CO4" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="CP4" t="n">
-        <v>1.84</v>
+        <v>1.86</v>
       </c>
       <c r="CQ4" t="n">
-        <v>3.07</v>
+        <v>3.11</v>
       </c>
       <c r="CR4" t="n">
         <v>1.39</v>
@@ -2485,13 +2485,13 @@
         <v>1.77</v>
       </c>
       <c r="CX4" t="n">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="CY4" t="n">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="CZ4" t="n">
-        <v>2.36</v>
+        <v>2.37</v>
       </c>
       <c r="DA4" t="n">
         <v>1.87</v>
@@ -2503,82 +2503,82 @@
         <v>1.91</v>
       </c>
       <c r="DD4" t="n">
-        <v>3.17</v>
+        <v>3.19</v>
       </c>
       <c r="DE4" t="n">
-        <v>0.08</v>
+        <v>0.12</v>
       </c>
       <c r="DF4" t="n">
-        <v>1.54</v>
+        <v>1.48</v>
       </c>
       <c r="DG4" t="n">
-        <v>1.42</v>
+        <v>1.56</v>
       </c>
       <c r="DH4" t="n">
-        <v>89.12</v>
+        <v>88.88</v>
       </c>
       <c r="DI4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DJ4" t="n">
-        <v>2.33</v>
+        <v>2.28</v>
       </c>
       <c r="DK4" t="n">
-        <v>3.38</v>
+        <v>3.52</v>
       </c>
       <c r="DL4" t="n">
         <v>0.08</v>
       </c>
       <c r="DM4" t="n">
-        <v>43.38</v>
+        <v>43.8</v>
       </c>
       <c r="DN4" t="n">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="DO4" t="n">
-        <v>1.62</v>
+        <v>1.64</v>
       </c>
       <c r="DP4" t="n">
-        <v>11.2</v>
+        <v>11.08</v>
       </c>
       <c r="DQ4" t="n">
-        <v>11.5</v>
+        <v>11.36</v>
       </c>
       <c r="DR4" t="n">
-        <v>10.58</v>
+        <v>10.36</v>
       </c>
       <c r="DS4" t="n">
-        <v>0.08</v>
+        <v>0.12</v>
       </c>
       <c r="DT4" t="n">
-        <v>0.08</v>
+        <v>0.12</v>
       </c>
       <c r="DU4" t="n">
         <v>0</v>
       </c>
       <c r="DV4" t="n">
-        <v>46.84</v>
+        <v>47.28</v>
       </c>
       <c r="DW4" t="n">
         <v>0.16</v>
       </c>
       <c r="DX4" t="n">
-        <v>10.7</v>
+        <v>10.8</v>
       </c>
       <c r="DY4" t="n">
-        <v>6.88</v>
+        <v>6.96</v>
       </c>
       <c r="DZ4" t="n">
-        <v>3.83</v>
+        <v>3.84</v>
       </c>
       <c r="EA4" t="n">
-        <v>21.5</v>
+        <v>21.92</v>
       </c>
       <c r="EB4" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="EC4" t="n">
-        <v>2.08</v>
+        <v>2.04</v>
       </c>
     </row>
     <row r="5">
@@ -2588,13 +2588,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C5" t="n">
         <v>12</v>
       </c>
       <c r="D5" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E5" t="n">
         <v>0.25</v>
@@ -2681,136 +2681,136 @@
         <v>0.08</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.08</v>
+        <v>1.15</v>
       </c>
       <c r="AH5" t="n">
-        <v>2.83</v>
+        <v>2.69</v>
       </c>
       <c r="AI5" t="n">
-        <v>88.08</v>
+        <v>87.45999999999999</v>
       </c>
       <c r="AJ5" t="n">
         <v>-0.08</v>
       </c>
       <c r="AK5" t="n">
+        <v>2</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>4.62</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>39.15</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="AP5" t="n">
         <v>1.92</v>
       </c>
-      <c r="AL5" t="n">
-        <v>4.67</v>
-      </c>
-      <c r="AM5" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="AN5" t="n">
+      <c r="AQ5" t="n">
+        <v>10.69</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>10.92</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>11.08</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AV5" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="AW5" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="AX5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY5" t="n">
+        <v>47.77</v>
+      </c>
+      <c r="AZ5" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="BA5" t="n">
+        <v>11.31</v>
+      </c>
+      <c r="BB5" t="n">
+        <v>6.38</v>
+      </c>
+      <c r="BC5" t="n">
+        <v>4.92</v>
+      </c>
+      <c r="BD5" t="n">
+        <v>17.31</v>
+      </c>
+      <c r="BE5" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="BF5" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="BG5" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="BH5" t="n">
+        <v>10.44</v>
+      </c>
+      <c r="BI5" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="BJ5" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="BK5" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="BL5" t="n">
+        <v>1</v>
+      </c>
+      <c r="BM5" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="BN5" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="BO5" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="BP5" t="n">
+        <v>4.24</v>
+      </c>
+      <c r="BQ5" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BR5" t="n">
+        <v>96</v>
+      </c>
+      <c r="BS5" t="n">
+        <v>88</v>
+      </c>
+      <c r="BT5" t="n">
+        <v>60</v>
+      </c>
+      <c r="BU5" t="n">
         <v>40</v>
       </c>
-      <c r="AO5" t="n">
-        <v>0.67</v>
-      </c>
-      <c r="AP5" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AQ5" t="n">
-        <v>11</v>
-      </c>
-      <c r="AR5" t="n">
-        <v>11.25</v>
-      </c>
-      <c r="AS5" t="n">
-        <v>10.92</v>
-      </c>
-      <c r="AT5" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AU5" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AV5" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="AW5" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="AX5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY5" t="n">
-        <v>48.67</v>
-      </c>
-      <c r="AZ5" t="n">
-        <v>0.17</v>
-      </c>
-      <c r="BA5" t="n">
-        <v>11.33</v>
-      </c>
-      <c r="BB5" t="n">
-        <v>6.58</v>
-      </c>
-      <c r="BC5" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="BD5" t="n">
-        <v>17.75</v>
-      </c>
-      <c r="BE5" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="BF5" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="BG5" t="n">
-        <v>3.04</v>
-      </c>
-      <c r="BH5" t="n">
-        <v>10.21</v>
-      </c>
-      <c r="BI5" t="n">
-        <v>3.04</v>
-      </c>
-      <c r="BJ5" t="n">
-        <v>0.79</v>
-      </c>
-      <c r="BK5" t="n">
-        <v>0.58</v>
-      </c>
-      <c r="BL5" t="n">
-        <v>0.96</v>
-      </c>
-      <c r="BM5" t="n">
-        <v>0.71</v>
-      </c>
-      <c r="BN5" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="BO5" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="BP5" t="n">
-        <v>4.12</v>
-      </c>
-      <c r="BQ5" t="n">
-        <v>6.08</v>
-      </c>
-      <c r="BR5" t="n">
-        <v>95.83</v>
-      </c>
-      <c r="BS5" t="n">
-        <v>87.5</v>
-      </c>
-      <c r="BT5" t="n">
-        <v>58.33</v>
-      </c>
-      <c r="BU5" t="n">
-        <v>37.5</v>
-      </c>
       <c r="BV5" t="n">
-        <v>16.67</v>
+        <v>20</v>
       </c>
       <c r="BW5" t="n">
-        <v>8.33</v>
+        <v>8</v>
       </c>
       <c r="BX5" t="n">
-        <v>62.5</v>
+        <v>64</v>
       </c>
       <c r="BY5" t="n">
         <v>2.65</v>
@@ -2819,22 +2819,22 @@
         <v>2.76</v>
       </c>
       <c r="CA5" t="n">
-        <v>3.59</v>
+        <v>3.58</v>
       </c>
       <c r="CB5" t="n">
-        <v>3.76</v>
+        <v>3.75</v>
       </c>
       <c r="CC5" t="n">
-        <v>3.58</v>
+        <v>3.6</v>
       </c>
       <c r="CD5" t="n">
-        <v>3.9</v>
+        <v>3.93</v>
       </c>
       <c r="CE5" t="n">
         <v>1.31</v>
       </c>
       <c r="CF5" t="n">
-        <v>2.48</v>
+        <v>2.49</v>
       </c>
       <c r="CG5" t="n">
         <v>3.21</v>
@@ -2843,7 +2843,7 @@
         <v>1.5</v>
       </c>
       <c r="CI5" t="n">
-        <v>2.21</v>
+        <v>2.2</v>
       </c>
       <c r="CJ5" t="n">
         <v>1.63</v>
@@ -2852,37 +2852,37 @@
         <v>1.47</v>
       </c>
       <c r="CL5" t="n">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="CM5" t="n">
-        <v>2.53</v>
+        <v>2.52</v>
       </c>
       <c r="CN5" t="n">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="CO5" t="n">
         <v>1.22</v>
       </c>
       <c r="CP5" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="CQ5" t="n">
-        <v>2.78</v>
+        <v>2.79</v>
       </c>
       <c r="CR5" t="n">
         <v>1.36</v>
       </c>
       <c r="CS5" t="n">
-        <v>2.54</v>
+        <v>2.56</v>
       </c>
       <c r="CT5" t="n">
-        <v>3.22</v>
+        <v>3.21</v>
       </c>
       <c r="CU5" t="n">
         <v>1.54</v>
       </c>
       <c r="CV5" t="n">
-        <v>2.31</v>
+        <v>2.3</v>
       </c>
       <c r="CW5" t="n">
         <v>1.67</v>
@@ -2903,85 +2903,85 @@
         <v>1.24</v>
       </c>
       <c r="DC5" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="DD5" t="n">
-        <v>2.89</v>
+        <v>2.9</v>
       </c>
       <c r="DE5" t="n">
         <v>0.16</v>
       </c>
       <c r="DF5" t="n">
-        <v>1.12</v>
+        <v>1.16</v>
       </c>
       <c r="DG5" t="n">
-        <v>2.79</v>
+        <v>2.72</v>
       </c>
       <c r="DH5" t="n">
-        <v>97.12</v>
+        <v>96.44</v>
       </c>
       <c r="DI5" t="n">
         <v>-0.04</v>
       </c>
       <c r="DJ5" t="n">
-        <v>1.84</v>
+        <v>1.88</v>
       </c>
       <c r="DK5" t="n">
-        <v>4.88</v>
+        <v>4.84</v>
       </c>
       <c r="DL5" t="n">
-        <v>0.58</v>
+        <v>0.6</v>
       </c>
       <c r="DM5" t="n">
-        <v>47</v>
+        <v>46.28</v>
       </c>
       <c r="DN5" t="n">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="DO5" t="n">
-        <v>2.08</v>
+        <v>2.12</v>
       </c>
       <c r="DP5" t="n">
-        <v>11.04</v>
+        <v>10.88</v>
       </c>
       <c r="DQ5" t="n">
-        <v>11.08</v>
+        <v>10.92</v>
       </c>
       <c r="DR5" t="n">
-        <v>9.5</v>
+        <v>9.640000000000001</v>
       </c>
       <c r="DS5" t="n">
-        <v>0.08</v>
+        <v>0.12</v>
       </c>
       <c r="DT5" t="n">
-        <v>0.08</v>
+        <v>0.12</v>
       </c>
       <c r="DU5" t="n">
         <v>0</v>
       </c>
       <c r="DV5" t="n">
-        <v>52</v>
+        <v>51.4</v>
       </c>
       <c r="DW5" t="n">
         <v>0.12</v>
       </c>
       <c r="DX5" t="n">
-        <v>13.79</v>
+        <v>13.68</v>
       </c>
       <c r="DY5" t="n">
-        <v>9.289999999999999</v>
+        <v>9.08</v>
       </c>
       <c r="DZ5" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="EA5" t="n">
-        <v>18.71</v>
+        <v>18.44</v>
       </c>
       <c r="EB5" t="n">
         <v>1.53</v>
       </c>
       <c r="EC5" t="n">
-        <v>1.58</v>
+        <v>1.64</v>
       </c>
     </row>
     <row r="6">
@@ -2991,13 +2991,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C6" t="n">
         <v>12</v>
       </c>
       <c r="D6" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
@@ -3081,97 +3081,97 @@
         <v>1.08</v>
       </c>
       <c r="AF6" t="n">
-        <v>0.25</v>
+        <v>0.23</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.25</v>
+        <v>1.31</v>
       </c>
       <c r="AH6" t="n">
-        <v>2.5</v>
+        <v>2.54</v>
       </c>
       <c r="AI6" t="n">
-        <v>97.25</v>
+        <v>98.08</v>
       </c>
       <c r="AJ6" t="n">
         <v>0.08</v>
       </c>
       <c r="AK6" t="n">
-        <v>1.67</v>
+        <v>1.77</v>
       </c>
       <c r="AL6" t="n">
-        <v>4.5</v>
+        <v>4.46</v>
       </c>
       <c r="AM6" t="n">
-        <v>0.75</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AN6" t="n">
-        <v>46.25</v>
+        <v>47.85</v>
       </c>
       <c r="AO6" t="n">
-        <v>0.42</v>
+        <v>0.46</v>
       </c>
       <c r="AP6" t="n">
-        <v>2</v>
+        <v>1.92</v>
       </c>
       <c r="AQ6" t="n">
-        <v>9.75</v>
+        <v>10</v>
       </c>
       <c r="AR6" t="n">
-        <v>11.92</v>
+        <v>11.77</v>
       </c>
       <c r="AS6" t="n">
         <v>8.08</v>
       </c>
       <c r="AT6" t="n">
-        <v>1.5</v>
+        <v>1.54</v>
       </c>
       <c r="AU6" t="n">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="AV6" t="n">
-        <v>0</v>
+        <v>0.08</v>
       </c>
       <c r="AW6" t="n">
-        <v>0</v>
+        <v>0.08</v>
       </c>
       <c r="AX6" t="n">
         <v>0</v>
       </c>
       <c r="AY6" t="n">
-        <v>60.17</v>
+        <v>59.92</v>
       </c>
       <c r="AZ6" t="n">
         <v>0</v>
       </c>
       <c r="BA6" t="n">
-        <v>13.67</v>
+        <v>13.54</v>
       </c>
       <c r="BB6" t="n">
-        <v>8.25</v>
+        <v>8</v>
       </c>
       <c r="BC6" t="n">
-        <v>5.42</v>
+        <v>5.54</v>
       </c>
       <c r="BD6" t="n">
-        <v>18.75</v>
+        <v>18.69</v>
       </c>
       <c r="BE6" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="BF6" t="n">
-        <v>1.67</v>
+        <v>1.77</v>
       </c>
       <c r="BG6" t="n">
-        <v>2.83</v>
+        <v>2.92</v>
       </c>
       <c r="BH6" t="n">
-        <v>9.880000000000001</v>
+        <v>9.720000000000001</v>
       </c>
       <c r="BI6" t="n">
-        <v>2.83</v>
+        <v>2.92</v>
       </c>
       <c r="BJ6" t="n">
-        <v>0.58</v>
+        <v>0.6</v>
       </c>
       <c r="BK6" t="n">
         <v>0.88</v>
@@ -3180,40 +3180,40 @@
         <v>0.88</v>
       </c>
       <c r="BM6" t="n">
-        <v>0.5</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="BN6" t="n">
-        <v>1.38</v>
+        <v>1.44</v>
       </c>
       <c r="BO6" t="n">
-        <v>1.46</v>
+        <v>1.48</v>
       </c>
       <c r="BP6" t="n">
-        <v>4.46</v>
+        <v>4.36</v>
       </c>
       <c r="BQ6" t="n">
-        <v>5.38</v>
+        <v>5.32</v>
       </c>
       <c r="BR6" t="n">
         <v>100</v>
       </c>
       <c r="BS6" t="n">
-        <v>87.5</v>
+        <v>88</v>
       </c>
       <c r="BT6" t="n">
-        <v>58.33</v>
+        <v>60</v>
       </c>
       <c r="BU6" t="n">
-        <v>16.67</v>
+        <v>20</v>
       </c>
       <c r="BV6" t="n">
-        <v>8.33</v>
+        <v>12</v>
       </c>
       <c r="BW6" t="n">
-        <v>4.17</v>
+        <v>4</v>
       </c>
       <c r="BX6" t="n">
-        <v>79.17</v>
+        <v>80</v>
       </c>
       <c r="BY6" t="n">
         <v>1.83</v>
@@ -3222,25 +3222,25 @@
         <v>1.91</v>
       </c>
       <c r="CA6" t="n">
-        <v>3.8</v>
+        <v>3.79</v>
       </c>
       <c r="CB6" t="n">
-        <v>3.92</v>
+        <v>3.9</v>
       </c>
       <c r="CC6" t="n">
-        <v>2.38</v>
+        <v>2.37</v>
       </c>
       <c r="CD6" t="n">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="CE6" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="CF6" t="n">
-        <v>2.43</v>
+        <v>2.44</v>
       </c>
       <c r="CG6" t="n">
-        <v>3.25</v>
+        <v>3.24</v>
       </c>
       <c r="CH6" t="n">
         <v>1.52</v>
@@ -3249,19 +3249,19 @@
         <v>2.24</v>
       </c>
       <c r="CJ6" t="n">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="CK6" t="n">
         <v>1.51</v>
       </c>
       <c r="CL6" t="n">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="CM6" t="n">
-        <v>2.42</v>
+        <v>2.43</v>
       </c>
       <c r="CN6" t="n">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="CO6" t="n">
         <v>1.2</v>
@@ -3270,7 +3270,7 @@
         <v>1.7</v>
       </c>
       <c r="CQ6" t="n">
-        <v>2.71</v>
+        <v>2.72</v>
       </c>
       <c r="CR6" t="n">
         <v>1.37</v>
@@ -3279,7 +3279,7 @@
         <v>2.59</v>
       </c>
       <c r="CT6" t="n">
-        <v>3.14</v>
+        <v>3.16</v>
       </c>
       <c r="CU6" t="n">
         <v>1.53</v>
@@ -3288,25 +3288,25 @@
         <v>2.28</v>
       </c>
       <c r="CW6" t="n">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="CX6" t="n">
         <v>1.58</v>
       </c>
       <c r="CY6" t="n">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="CZ6" t="n">
-        <v>2.36</v>
+        <v>2.37</v>
       </c>
       <c r="DA6" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="DB6" t="n">
         <v>1.23</v>
       </c>
       <c r="DC6" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="DD6" t="n">
         <v>2.83</v>
@@ -3315,76 +3315,76 @@
         <v>0.12</v>
       </c>
       <c r="DF6" t="n">
-        <v>0.92</v>
+        <v>0.96</v>
       </c>
       <c r="DG6" t="n">
-        <v>3.29</v>
+        <v>3.28</v>
       </c>
       <c r="DH6" t="n">
-        <v>113.25</v>
+        <v>113.04</v>
       </c>
       <c r="DI6" t="n">
         <v>0.08</v>
       </c>
       <c r="DJ6" t="n">
-        <v>1.46</v>
+        <v>1.52</v>
       </c>
       <c r="DK6" t="n">
-        <v>5.62</v>
+        <v>5.56</v>
       </c>
       <c r="DL6" t="n">
-        <v>0.62</v>
+        <v>0.6</v>
       </c>
       <c r="DM6" t="n">
-        <v>54.58</v>
+        <v>55.08</v>
       </c>
       <c r="DN6" t="n">
-        <v>0.5</v>
+        <v>0.52</v>
       </c>
       <c r="DO6" t="n">
-        <v>2.29</v>
+        <v>2.24</v>
       </c>
       <c r="DP6" t="n">
-        <v>10.21</v>
+        <v>10.32</v>
       </c>
       <c r="DQ6" t="n">
-        <v>13</v>
+        <v>12.88</v>
       </c>
       <c r="DR6" t="n">
-        <v>6.92</v>
+        <v>6.96</v>
       </c>
       <c r="DS6" t="n">
-        <v>0</v>
+        <v>0.04</v>
       </c>
       <c r="DT6" t="n">
-        <v>0</v>
+        <v>0.04</v>
       </c>
       <c r="DU6" t="n">
         <v>0</v>
       </c>
       <c r="DV6" t="n">
-        <v>61.84</v>
+        <v>61.64</v>
       </c>
       <c r="DW6" t="n">
         <v>0.04</v>
       </c>
       <c r="DX6" t="n">
-        <v>15.92</v>
+        <v>15.76</v>
       </c>
       <c r="DY6" t="n">
-        <v>10.17</v>
+        <v>9.960000000000001</v>
       </c>
       <c r="DZ6" t="n">
-        <v>5.75</v>
+        <v>5.8</v>
       </c>
       <c r="EA6" t="n">
-        <v>20.25</v>
+        <v>20.16</v>
       </c>
       <c r="EB6" t="n">
         <v>1.8</v>
       </c>
       <c r="EC6" t="n">
-        <v>1.38</v>
+        <v>1.44</v>
       </c>
     </row>
     <row r="7">
@@ -3394,94 +3394,94 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C7" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D7" t="n">
         <v>12</v>
       </c>
       <c r="E7" t="n">
-        <v>0.17</v>
+        <v>0.15</v>
       </c>
       <c r="F7" t="n">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="G7" t="n">
-        <v>2.67</v>
+        <v>2.54</v>
       </c>
       <c r="H7" t="n">
-        <v>89.83</v>
+        <v>89.54000000000001</v>
       </c>
       <c r="I7" t="n">
-        <v>0.25</v>
+        <v>0.23</v>
       </c>
       <c r="J7" t="n">
-        <v>2.33</v>
+        <v>2.31</v>
       </c>
       <c r="K7" t="n">
-        <v>4.83</v>
+        <v>4.62</v>
       </c>
       <c r="L7" t="n">
-        <v>0.25</v>
+        <v>0.23</v>
       </c>
       <c r="M7" t="n">
-        <v>50.67</v>
+        <v>50</v>
       </c>
       <c r="N7" t="n">
-        <v>0.67</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="O7" t="n">
-        <v>2.17</v>
+        <v>2.08</v>
       </c>
       <c r="P7" t="n">
-        <v>10.42</v>
+        <v>10.46</v>
       </c>
       <c r="Q7" t="n">
-        <v>11.5</v>
+        <v>11.62</v>
       </c>
       <c r="R7" t="n">
-        <v>9.33</v>
+        <v>9.15</v>
       </c>
       <c r="S7" t="n">
-        <v>1</v>
+        <v>1.15</v>
       </c>
       <c r="T7" t="n">
-        <v>1.17</v>
+        <v>1.23</v>
       </c>
       <c r="U7" t="n">
-        <v>0.17</v>
+        <v>0.15</v>
       </c>
       <c r="V7" t="n">
-        <v>0.17</v>
+        <v>0.15</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>49.92</v>
+        <v>49.38</v>
       </c>
       <c r="Y7" t="n">
         <v>0</v>
       </c>
       <c r="Z7" t="n">
-        <v>10.67</v>
+        <v>10.85</v>
       </c>
       <c r="AA7" t="n">
-        <v>7.17</v>
+        <v>7.15</v>
       </c>
       <c r="AB7" t="n">
-        <v>3.5</v>
+        <v>3.69</v>
       </c>
       <c r="AC7" t="n">
-        <v>21.33</v>
+        <v>21.08</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="AE7" t="n">
-        <v>2.33</v>
+        <v>2.31</v>
       </c>
       <c r="AF7" t="n">
         <v>0.08</v>
@@ -3565,70 +3565,70 @@
         <v>2.58</v>
       </c>
       <c r="BG7" t="n">
-        <v>2.33</v>
+        <v>2.44</v>
       </c>
       <c r="BH7" t="n">
-        <v>11.33</v>
+        <v>11.12</v>
       </c>
       <c r="BI7" t="n">
-        <v>2.33</v>
+        <v>2.44</v>
       </c>
       <c r="BJ7" t="n">
-        <v>0.54</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="BK7" t="n">
-        <v>0.42</v>
+        <v>0.44</v>
       </c>
       <c r="BL7" t="n">
-        <v>0.62</v>
+        <v>0.64</v>
       </c>
       <c r="BM7" t="n">
-        <v>0.75</v>
+        <v>0.8</v>
       </c>
       <c r="BN7" t="n">
-        <v>1.38</v>
+        <v>1.44</v>
       </c>
       <c r="BO7" t="n">
-        <v>0.96</v>
+        <v>1</v>
       </c>
       <c r="BP7" t="n">
-        <v>5.08</v>
+        <v>4.96</v>
       </c>
       <c r="BQ7" t="n">
-        <v>6.25</v>
+        <v>6.16</v>
       </c>
       <c r="BR7" t="n">
-        <v>95.83</v>
+        <v>96</v>
       </c>
       <c r="BS7" t="n">
-        <v>70.83</v>
+        <v>72</v>
       </c>
       <c r="BT7" t="n">
-        <v>33.33</v>
+        <v>36</v>
       </c>
       <c r="BU7" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="BV7" t="n">
-        <v>8.33</v>
+        <v>12</v>
       </c>
       <c r="BW7" t="n">
         <v>0</v>
       </c>
       <c r="BX7" t="n">
-        <v>62.5</v>
+        <v>64</v>
       </c>
       <c r="BY7" t="n">
-        <v>2.78</v>
+        <v>2.82</v>
       </c>
       <c r="BZ7" t="n">
-        <v>2.94</v>
+        <v>2.97</v>
       </c>
       <c r="CA7" t="n">
-        <v>3.67</v>
+        <v>3.66</v>
       </c>
       <c r="CB7" t="n">
-        <v>3.8</v>
+        <v>3.79</v>
       </c>
       <c r="CC7" t="n">
         <v>3.93</v>
@@ -3640,10 +3640,10 @@
         <v>1.31</v>
       </c>
       <c r="CF7" t="n">
-        <v>2.46</v>
+        <v>2.47</v>
       </c>
       <c r="CG7" t="n">
-        <v>3.21</v>
+        <v>3.2</v>
       </c>
       <c r="CH7" t="n">
         <v>1.51</v>
@@ -3658,10 +3658,10 @@
         <v>1.4</v>
       </c>
       <c r="CL7" t="n">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="CM7" t="n">
-        <v>2.74</v>
+        <v>2.73</v>
       </c>
       <c r="CN7" t="n">
         <v>2.09</v>
@@ -3670,7 +3670,7 @@
         <v>1.22</v>
       </c>
       <c r="CP7" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="CQ7" t="n">
         <v>2.76</v>
@@ -3682,7 +3682,7 @@
         <v>2.59</v>
       </c>
       <c r="CT7" t="n">
-        <v>3.18</v>
+        <v>3.19</v>
       </c>
       <c r="CU7" t="n">
         <v>1.53</v>
@@ -3691,7 +3691,7 @@
         <v>2.32</v>
       </c>
       <c r="CW7" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="CX7" t="n">
         <v>1.49</v>
@@ -3712,49 +3712,49 @@
         <v>1.78</v>
       </c>
       <c r="DD7" t="n">
-        <v>2.87</v>
+        <v>2.88</v>
       </c>
       <c r="DE7" t="n">
         <v>0.12</v>
       </c>
       <c r="DF7" t="n">
-        <v>1.71</v>
+        <v>1.68</v>
       </c>
       <c r="DG7" t="n">
-        <v>2.83</v>
+        <v>2.76</v>
       </c>
       <c r="DH7" t="n">
-        <v>88.04000000000001</v>
+        <v>87.95999999999999</v>
       </c>
       <c r="DI7" t="n">
         <v>0.16</v>
       </c>
       <c r="DJ7" t="n">
-        <v>2.46</v>
+        <v>2.44</v>
       </c>
       <c r="DK7" t="n">
-        <v>4.96</v>
+        <v>4.84</v>
       </c>
       <c r="DL7" t="n">
-        <v>0.29</v>
+        <v>0.28</v>
       </c>
       <c r="DM7" t="n">
-        <v>46.58</v>
+        <v>46.4</v>
       </c>
       <c r="DN7" t="n">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="DO7" t="n">
-        <v>2.12</v>
+        <v>2.08</v>
       </c>
       <c r="DP7" t="n">
-        <v>10.38</v>
+        <v>10.4</v>
       </c>
       <c r="DQ7" t="n">
-        <v>11.58</v>
+        <v>11.64</v>
       </c>
       <c r="DR7" t="n">
-        <v>9.08</v>
+        <v>9</v>
       </c>
       <c r="DS7" t="n">
         <v>0.08</v>
@@ -3766,28 +3766,28 @@
         <v>0</v>
       </c>
       <c r="DV7" t="n">
-        <v>49.58</v>
+        <v>49.32</v>
       </c>
       <c r="DW7" t="n">
         <v>0</v>
       </c>
       <c r="DX7" t="n">
-        <v>10.5</v>
+        <v>10.6</v>
       </c>
       <c r="DY7" t="n">
-        <v>6.62</v>
+        <v>6.64</v>
       </c>
       <c r="DZ7" t="n">
-        <v>3.88</v>
+        <v>3.96</v>
       </c>
       <c r="EA7" t="n">
-        <v>21.5</v>
+        <v>21.36</v>
       </c>
       <c r="EB7" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="EC7" t="n">
-        <v>2.46</v>
+        <v>2.44</v>
       </c>
     </row>
     <row r="8">
@@ -4200,94 +4200,94 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C9" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D9" t="n">
         <v>12</v>
       </c>
       <c r="E9" t="n">
-        <v>0.25</v>
+        <v>0.23</v>
       </c>
       <c r="F9" t="n">
-        <v>2.25</v>
+        <v>2.23</v>
       </c>
       <c r="G9" t="n">
-        <v>2.33</v>
+        <v>2.38</v>
       </c>
       <c r="H9" t="n">
-        <v>81.58</v>
+        <v>81.15000000000001</v>
       </c>
       <c r="I9" t="n">
         <v>0.08</v>
       </c>
       <c r="J9" t="n">
-        <v>3.08</v>
+        <v>3</v>
       </c>
       <c r="K9" t="n">
-        <v>4.58</v>
+        <v>5</v>
       </c>
       <c r="L9" t="n">
-        <v>0.42</v>
+        <v>0.54</v>
       </c>
       <c r="M9" t="n">
-        <v>40.58</v>
+        <v>40.85</v>
       </c>
       <c r="N9" t="n">
-        <v>0.83</v>
+        <v>0.77</v>
       </c>
       <c r="O9" t="n">
-        <v>2.17</v>
+        <v>2.54</v>
       </c>
       <c r="P9" t="n">
-        <v>16.75</v>
+        <v>16.08</v>
       </c>
       <c r="Q9" t="n">
-        <v>12.58</v>
+        <v>12.31</v>
       </c>
       <c r="R9" t="n">
-        <v>8.25</v>
+        <v>7.85</v>
       </c>
       <c r="S9" t="n">
-        <v>1.25</v>
+        <v>1.31</v>
       </c>
       <c r="T9" t="n">
-        <v>1.17</v>
+        <v>1.31</v>
       </c>
       <c r="U9" t="n">
-        <v>0.08</v>
+        <v>0.15</v>
       </c>
       <c r="V9" t="n">
-        <v>0.08</v>
+        <v>0.15</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>45.75</v>
+        <v>45.46</v>
       </c>
       <c r="Y9" t="n">
         <v>0</v>
       </c>
       <c r="Z9" t="n">
-        <v>14.67</v>
+        <v>15.08</v>
       </c>
       <c r="AA9" t="n">
-        <v>10</v>
+        <v>10.15</v>
       </c>
       <c r="AB9" t="n">
-        <v>4.67</v>
+        <v>4.92</v>
       </c>
       <c r="AC9" t="n">
-        <v>19.58</v>
+        <v>20</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.54</v>
+        <v>1.59</v>
       </c>
       <c r="AE9" t="n">
-        <v>3.08</v>
+        <v>3</v>
       </c>
       <c r="AF9" t="n">
         <v>0</v>
@@ -4371,70 +4371,70 @@
         <v>3.42</v>
       </c>
       <c r="BG9" t="n">
-        <v>2.38</v>
+        <v>2.48</v>
       </c>
       <c r="BH9" t="n">
-        <v>10.29</v>
+        <v>10.56</v>
       </c>
       <c r="BI9" t="n">
-        <v>2.38</v>
+        <v>2.48</v>
       </c>
       <c r="BJ9" t="n">
-        <v>0.67</v>
+        <v>0.72</v>
       </c>
       <c r="BK9" t="n">
-        <v>0.46</v>
+        <v>0.48</v>
       </c>
       <c r="BL9" t="n">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="BM9" t="n">
-        <v>0.58</v>
+        <v>0.6</v>
       </c>
       <c r="BN9" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="BO9" t="n">
-        <v>1.12</v>
+        <v>1.2</v>
       </c>
       <c r="BP9" t="n">
-        <v>5.04</v>
+        <v>5.2</v>
       </c>
       <c r="BQ9" t="n">
-        <v>5.21</v>
+        <v>5.32</v>
       </c>
       <c r="BR9" t="n">
-        <v>91.67</v>
+        <v>92</v>
       </c>
       <c r="BS9" t="n">
-        <v>70.83</v>
+        <v>72</v>
       </c>
       <c r="BT9" t="n">
-        <v>45.83</v>
+        <v>48</v>
       </c>
       <c r="BU9" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="BV9" t="n">
-        <v>4.17</v>
+        <v>8</v>
       </c>
       <c r="BW9" t="n">
         <v>0</v>
       </c>
       <c r="BX9" t="n">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="BY9" t="n">
-        <v>2.98</v>
+        <v>2.91</v>
       </c>
       <c r="BZ9" t="n">
-        <v>3.01</v>
+        <v>2.95</v>
       </c>
       <c r="CA9" t="n">
-        <v>3.49</v>
+        <v>3.48</v>
       </c>
       <c r="CB9" t="n">
-        <v>3.52</v>
+        <v>3.51</v>
       </c>
       <c r="CC9" t="n">
         <v>4.14</v>
@@ -4446,40 +4446,40 @@
         <v>1.37</v>
       </c>
       <c r="CF9" t="n">
-        <v>2.73</v>
+        <v>2.74</v>
       </c>
       <c r="CG9" t="n">
-        <v>2.97</v>
+        <v>2.95</v>
       </c>
       <c r="CH9" t="n">
         <v>1.42</v>
       </c>
       <c r="CI9" t="n">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="CJ9" t="n">
         <v>1.77</v>
       </c>
       <c r="CK9" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="CL9" t="n">
         <v>1.86</v>
       </c>
       <c r="CM9" t="n">
-        <v>2.53</v>
+        <v>2.52</v>
       </c>
       <c r="CN9" t="n">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="CO9" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="CP9" t="n">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="CQ9" t="n">
-        <v>3.28</v>
+        <v>3.31</v>
       </c>
       <c r="CR9" t="n">
         <v>1.38</v>
@@ -4497,103 +4497,103 @@
         <v>2.09</v>
       </c>
       <c r="CW9" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="CX9" t="n">
         <v>1.55</v>
       </c>
       <c r="CY9" t="n">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="CZ9" t="n">
         <v>2.44</v>
       </c>
       <c r="DA9" t="n">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="DB9" t="n">
         <v>1.31</v>
       </c>
       <c r="DC9" t="n">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="DD9" t="n">
-        <v>3.38</v>
+        <v>3.39</v>
       </c>
       <c r="DE9" t="n">
         <v>0.12</v>
       </c>
       <c r="DF9" t="n">
-        <v>2.29</v>
+        <v>2.28</v>
       </c>
       <c r="DG9" t="n">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="DH9" t="n">
-        <v>79.95999999999999</v>
+        <v>79.8</v>
       </c>
       <c r="DI9" t="n">
         <v>0.04</v>
       </c>
       <c r="DJ9" t="n">
-        <v>3.29</v>
+        <v>3.24</v>
       </c>
       <c r="DK9" t="n">
-        <v>4.46</v>
+        <v>4.68</v>
       </c>
       <c r="DL9" t="n">
-        <v>0.46</v>
+        <v>0.52</v>
       </c>
       <c r="DM9" t="n">
-        <v>43.16</v>
+        <v>43.2</v>
       </c>
       <c r="DN9" t="n">
-        <v>1</v>
+        <v>0.96</v>
       </c>
       <c r="DO9" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="DP9" t="n">
-        <v>16.46</v>
+        <v>16.12</v>
       </c>
       <c r="DQ9" t="n">
-        <v>11.62</v>
+        <v>11.52</v>
       </c>
       <c r="DR9" t="n">
-        <v>8.619999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="DS9" t="n">
-        <v>0.08</v>
+        <v>0.12</v>
       </c>
       <c r="DT9" t="n">
-        <v>0.08</v>
+        <v>0.12</v>
       </c>
       <c r="DU9" t="n">
         <v>0</v>
       </c>
       <c r="DV9" t="n">
-        <v>45.29</v>
+        <v>45.16</v>
       </c>
       <c r="DW9" t="n">
         <v>0.04</v>
       </c>
       <c r="DX9" t="n">
-        <v>13.58</v>
+        <v>13.84</v>
       </c>
       <c r="DY9" t="n">
-        <v>9.25</v>
+        <v>9.359999999999999</v>
       </c>
       <c r="DZ9" t="n">
-        <v>4.34</v>
+        <v>4.48</v>
       </c>
       <c r="EA9" t="n">
-        <v>19.45</v>
+        <v>19.68</v>
       </c>
       <c r="EB9" t="n">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="EC9" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
     </row>
     <row r="10">
@@ -6215,94 +6215,94 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C14" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D14" t="n">
         <v>12</v>
       </c>
       <c r="E14" t="n">
-        <v>0.17</v>
+        <v>0.15</v>
       </c>
       <c r="F14" t="n">
-        <v>1.83</v>
+        <v>1.69</v>
       </c>
       <c r="G14" t="n">
-        <v>2.75</v>
+        <v>3.15</v>
       </c>
       <c r="H14" t="n">
-        <v>94.75</v>
+        <v>96.23</v>
       </c>
       <c r="I14" t="n">
         <v>0</v>
       </c>
       <c r="J14" t="n">
-        <v>2.33</v>
+        <v>2.15</v>
       </c>
       <c r="K14" t="n">
-        <v>5.33</v>
+        <v>5.85</v>
       </c>
       <c r="L14" t="n">
-        <v>0.08</v>
+        <v>0.15</v>
       </c>
       <c r="M14" t="n">
-        <v>50.67</v>
+        <v>54</v>
       </c>
       <c r="N14" t="n">
-        <v>0.33</v>
+        <v>0.31</v>
       </c>
       <c r="O14" t="n">
-        <v>2.58</v>
+        <v>2.69</v>
       </c>
       <c r="P14" t="n">
-        <v>11.75</v>
+        <v>11.46</v>
       </c>
       <c r="Q14" t="n">
-        <v>12.5</v>
+        <v>12.15</v>
       </c>
       <c r="R14" t="n">
-        <v>7.33</v>
+        <v>7.38</v>
       </c>
       <c r="S14" t="n">
-        <v>1.17</v>
+        <v>1.31</v>
       </c>
       <c r="T14" t="n">
-        <v>1.42</v>
+        <v>1.46</v>
       </c>
       <c r="U14" t="n">
-        <v>0.17</v>
+        <v>0.15</v>
       </c>
       <c r="V14" t="n">
-        <v>0.17</v>
+        <v>0.15</v>
       </c>
       <c r="W14" t="n">
         <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>48.75</v>
+        <v>49.85</v>
       </c>
       <c r="Y14" t="n">
-        <v>0.25</v>
+        <v>0.23</v>
       </c>
       <c r="Z14" t="n">
-        <v>13.08</v>
+        <v>14</v>
       </c>
       <c r="AA14" t="n">
-        <v>8.17</v>
+        <v>8.92</v>
       </c>
       <c r="AB14" t="n">
-        <v>4.92</v>
+        <v>5.08</v>
       </c>
       <c r="AC14" t="n">
-        <v>17.92</v>
+        <v>18.23</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.54</v>
+        <v>1.63</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.92</v>
+        <v>1.77</v>
       </c>
       <c r="AF14" t="n">
         <v>0.17</v>
@@ -6386,67 +6386,67 @@
         <v>2.33</v>
       </c>
       <c r="BG14" t="n">
-        <v>2.58</v>
+        <v>2.68</v>
       </c>
       <c r="BH14" t="n">
-        <v>9.92</v>
+        <v>10.16</v>
       </c>
       <c r="BI14" t="n">
-        <v>2.58</v>
+        <v>2.68</v>
       </c>
       <c r="BJ14" t="n">
-        <v>0.67</v>
+        <v>0.64</v>
       </c>
       <c r="BK14" t="n">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="BL14" t="n">
-        <v>0.71</v>
+        <v>0.76</v>
       </c>
       <c r="BM14" t="n">
-        <v>0.46</v>
+        <v>0.52</v>
       </c>
       <c r="BN14" t="n">
-        <v>1.17</v>
+        <v>1.28</v>
       </c>
       <c r="BO14" t="n">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="BP14" t="n">
-        <v>4.96</v>
+        <v>5.04</v>
       </c>
       <c r="BQ14" t="n">
-        <v>4.96</v>
+        <v>5.12</v>
       </c>
       <c r="BR14" t="n">
-        <v>95.83</v>
+        <v>96</v>
       </c>
       <c r="BS14" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="BT14" t="n">
-        <v>41.67</v>
+        <v>44</v>
       </c>
       <c r="BU14" t="n">
-        <v>29.17</v>
+        <v>32</v>
       </c>
       <c r="BV14" t="n">
-        <v>8.33</v>
+        <v>12</v>
       </c>
       <c r="BW14" t="n">
-        <v>4.17</v>
+        <v>4</v>
       </c>
       <c r="BX14" t="n">
-        <v>54.17</v>
+        <v>56</v>
       </c>
       <c r="BY14" t="n">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="BZ14" t="n">
-        <v>2.4</v>
+        <v>2.36</v>
       </c>
       <c r="CA14" t="n">
-        <v>3.49</v>
+        <v>3.48</v>
       </c>
       <c r="CB14" t="n">
         <v>3.51</v>
@@ -6476,13 +6476,13 @@
         <v>1.75</v>
       </c>
       <c r="CK14" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="CL14" t="n">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="CM14" t="n">
-        <v>2.51</v>
+        <v>2.5</v>
       </c>
       <c r="CN14" t="n">
         <v>1.92</v>
@@ -6494,7 +6494,7 @@
         <v>1.89</v>
       </c>
       <c r="CQ14" t="n">
-        <v>3.19</v>
+        <v>3.18</v>
       </c>
       <c r="CR14" t="n">
         <v>1.39</v>
@@ -6533,49 +6533,49 @@
         <v>1.99</v>
       </c>
       <c r="DD14" t="n">
-        <v>3.38</v>
+        <v>3.37</v>
       </c>
       <c r="DE14" t="n">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
       <c r="DF14" t="n">
-        <v>1.75</v>
+        <v>1.68</v>
       </c>
       <c r="DG14" t="n">
-        <v>2.46</v>
+        <v>2.68</v>
       </c>
       <c r="DH14" t="n">
-        <v>93.54000000000001</v>
+        <v>94.36</v>
       </c>
       <c r="DI14" t="n">
         <v>0</v>
       </c>
       <c r="DJ14" t="n">
-        <v>2.33</v>
+        <v>2.24</v>
       </c>
       <c r="DK14" t="n">
-        <v>4.96</v>
+        <v>5.24</v>
       </c>
       <c r="DL14" t="n">
-        <v>0.38</v>
+        <v>0.4</v>
       </c>
       <c r="DM14" t="n">
-        <v>47.67</v>
+        <v>49.52</v>
       </c>
       <c r="DN14" t="n">
-        <v>0.5</v>
+        <v>0.48</v>
       </c>
       <c r="DO14" t="n">
-        <v>2.5</v>
+        <v>2.56</v>
       </c>
       <c r="DP14" t="n">
-        <v>11.88</v>
+        <v>11.72</v>
       </c>
       <c r="DQ14" t="n">
-        <v>11.04</v>
+        <v>10.92</v>
       </c>
       <c r="DR14" t="n">
-        <v>7.5</v>
+        <v>7.52</v>
       </c>
       <c r="DS14" t="n">
         <v>0.12</v>
@@ -6587,28 +6587,28 @@
         <v>0</v>
       </c>
       <c r="DV14" t="n">
-        <v>48</v>
+        <v>48.6</v>
       </c>
       <c r="DW14" t="n">
         <v>0.12</v>
       </c>
       <c r="DX14" t="n">
-        <v>12.2</v>
+        <v>12.72</v>
       </c>
       <c r="DY14" t="n">
-        <v>7.84</v>
+        <v>8.24</v>
       </c>
       <c r="DZ14" t="n">
-        <v>4.38</v>
+        <v>4.48</v>
       </c>
       <c r="EA14" t="n">
-        <v>19.5</v>
+        <v>19.6</v>
       </c>
       <c r="EB14" t="n">
-        <v>1.42</v>
+        <v>1.48</v>
       </c>
       <c r="EC14" t="n">
-        <v>2.12</v>
+        <v>2.04</v>
       </c>
     </row>
     <row r="15">
@@ -6618,94 +6618,94 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C15" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D15" t="n">
         <v>12</v>
       </c>
       <c r="E15" t="n">
-        <v>0.17</v>
+        <v>0.15</v>
       </c>
       <c r="F15" t="n">
-        <v>1.58</v>
+        <v>1.62</v>
       </c>
       <c r="G15" t="n">
-        <v>2.33</v>
+        <v>2.31</v>
       </c>
       <c r="H15" t="n">
-        <v>88.25</v>
+        <v>88.45999999999999</v>
       </c>
       <c r="I15" t="n">
         <v>0</v>
       </c>
       <c r="J15" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="K15" t="n">
+        <v>5.31</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="M15" t="n">
+        <v>50</v>
+      </c>
+      <c r="N15" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="O15" t="n">
         <v>3</v>
       </c>
-      <c r="K15" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="L15" t="n">
-        <v>0.83</v>
-      </c>
-      <c r="M15" t="n">
-        <v>51.83</v>
-      </c>
-      <c r="N15" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="O15" t="n">
-        <v>3.17</v>
-      </c>
       <c r="P15" t="n">
-        <v>11.17</v>
+        <v>10.92</v>
       </c>
       <c r="Q15" t="n">
-        <v>12.83</v>
+        <v>13.08</v>
       </c>
       <c r="R15" t="n">
-        <v>8.58</v>
+        <v>8.77</v>
       </c>
       <c r="S15" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="T15" t="n">
         <v>1</v>
       </c>
       <c r="U15" t="n">
-        <v>0.17</v>
+        <v>0.15</v>
       </c>
       <c r="V15" t="n">
-        <v>0.17</v>
+        <v>0.15</v>
       </c>
       <c r="W15" t="n">
         <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>44.58</v>
+        <v>43.69</v>
       </c>
       <c r="Y15" t="n">
-        <v>0.33</v>
+        <v>0.31</v>
       </c>
       <c r="Z15" t="n">
-        <v>11.33</v>
+        <v>11</v>
       </c>
       <c r="AA15" t="n">
-        <v>7.33</v>
+        <v>7.15</v>
       </c>
       <c r="AB15" t="n">
-        <v>4</v>
+        <v>3.85</v>
       </c>
       <c r="AC15" t="n">
-        <v>20.58</v>
+        <v>20.46</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.37</v>
+        <v>1.33</v>
       </c>
       <c r="AE15" t="n">
-        <v>2.33</v>
+        <v>2.46</v>
       </c>
       <c r="AF15" t="n">
         <v>0.17</v>
@@ -6789,49 +6789,49 @@
         <v>1.83</v>
       </c>
       <c r="BG15" t="n">
-        <v>2.17</v>
+        <v>2.16</v>
       </c>
       <c r="BH15" t="n">
-        <v>9.880000000000001</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BI15" t="n">
-        <v>2.17</v>
+        <v>2.16</v>
       </c>
       <c r="BJ15" t="n">
-        <v>0.62</v>
+        <v>0.64</v>
       </c>
       <c r="BK15" t="n">
-        <v>0.62</v>
+        <v>0.6</v>
       </c>
       <c r="BL15" t="n">
-        <v>0.54</v>
+        <v>0.52</v>
       </c>
       <c r="BM15" t="n">
-        <v>0.38</v>
+        <v>0.4</v>
       </c>
       <c r="BN15" t="n">
         <v>0.92</v>
       </c>
       <c r="BO15" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="BP15" t="n">
-        <v>4.58</v>
+        <v>4.56</v>
       </c>
       <c r="BQ15" t="n">
-        <v>5.29</v>
+        <v>5.24</v>
       </c>
       <c r="BR15" t="n">
-        <v>95.83</v>
+        <v>96</v>
       </c>
       <c r="BS15" t="n">
-        <v>66.67</v>
+        <v>68</v>
       </c>
       <c r="BT15" t="n">
-        <v>41.67</v>
+        <v>40</v>
       </c>
       <c r="BU15" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="BV15" t="n">
         <v>0</v>
@@ -6840,19 +6840,19 @@
         <v>0</v>
       </c>
       <c r="BX15" t="n">
-        <v>29.17</v>
+        <v>32</v>
       </c>
       <c r="BY15" t="n">
-        <v>2.88</v>
+        <v>3.1</v>
       </c>
       <c r="BZ15" t="n">
-        <v>3.12</v>
+        <v>3.5</v>
       </c>
       <c r="CA15" t="n">
-        <v>3.51</v>
+        <v>3.53</v>
       </c>
       <c r="CB15" t="n">
-        <v>3.58</v>
+        <v>3.6</v>
       </c>
       <c r="CC15" t="n">
         <v>4.23</v>
@@ -6876,19 +6876,19 @@
         <v>1.93</v>
       </c>
       <c r="CJ15" t="n">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="CK15" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="CL15" t="n">
         <v>1.89</v>
       </c>
       <c r="CM15" t="n">
-        <v>2.51</v>
+        <v>2.5</v>
       </c>
       <c r="CN15" t="n">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="CO15" t="n">
         <v>1.31</v>
@@ -6897,25 +6897,25 @@
         <v>1.97</v>
       </c>
       <c r="CQ15" t="n">
-        <v>3.43</v>
+        <v>3.42</v>
       </c>
       <c r="CR15" t="n">
         <v>1.41</v>
       </c>
       <c r="CS15" t="n">
-        <v>2.94</v>
+        <v>2.95</v>
       </c>
       <c r="CT15" t="n">
-        <v>2.99</v>
+        <v>2.98</v>
       </c>
       <c r="CU15" t="n">
         <v>1.43</v>
       </c>
       <c r="CV15" t="n">
-        <v>2.04</v>
+        <v>2.03</v>
       </c>
       <c r="CW15" t="n">
-        <v>1.85</v>
+        <v>1.88</v>
       </c>
       <c r="CX15" t="n">
         <v>1.57</v>
@@ -6924,7 +6924,7 @@
         <v>1.92</v>
       </c>
       <c r="CZ15" t="n">
-        <v>2.39</v>
+        <v>2.38</v>
       </c>
       <c r="DA15" t="n">
         <v>1.9</v>
@@ -6933,52 +6933,52 @@
         <v>1.33</v>
       </c>
       <c r="DC15" t="n">
-        <v>2.04</v>
+        <v>2.05</v>
       </c>
       <c r="DD15" t="n">
-        <v>3.53</v>
+        <v>3.55</v>
       </c>
       <c r="DE15" t="n">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
       <c r="DF15" t="n">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="DG15" t="n">
         <v>1.96</v>
       </c>
       <c r="DH15" t="n">
-        <v>86.16</v>
+        <v>86.36</v>
       </c>
       <c r="DI15" t="n">
         <v>0</v>
       </c>
       <c r="DJ15" t="n">
-        <v>2.5</v>
+        <v>2.56</v>
       </c>
       <c r="DK15" t="n">
-        <v>4.34</v>
+        <v>4.28</v>
       </c>
       <c r="DL15" t="n">
-        <v>0.58</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="DM15" t="n">
-        <v>45.29</v>
+        <v>44.6</v>
       </c>
       <c r="DN15" t="n">
-        <v>0.83</v>
+        <v>0.88</v>
       </c>
       <c r="DO15" t="n">
-        <v>2.38</v>
+        <v>2.32</v>
       </c>
       <c r="DP15" t="n">
-        <v>11.12</v>
+        <v>11</v>
       </c>
       <c r="DQ15" t="n">
-        <v>12.25</v>
+        <v>12.4</v>
       </c>
       <c r="DR15" t="n">
-        <v>9.25</v>
+        <v>9.32</v>
       </c>
       <c r="DS15" t="n">
         <v>0.12</v>
@@ -6990,28 +6990,28 @@
         <v>0</v>
       </c>
       <c r="DV15" t="n">
-        <v>44.21</v>
+        <v>43.76</v>
       </c>
       <c r="DW15" t="n">
-        <v>0.25</v>
+        <v>0.24</v>
       </c>
       <c r="DX15" t="n">
-        <v>9.58</v>
+        <v>9.48</v>
       </c>
       <c r="DY15" t="n">
-        <v>6.46</v>
+        <v>6.4</v>
       </c>
       <c r="DZ15" t="n">
-        <v>3.12</v>
+        <v>3.08</v>
       </c>
       <c r="EA15" t="n">
         <v>19.04</v>
       </c>
       <c r="EB15" t="n">
-        <v>1.16</v>
+        <v>1.14</v>
       </c>
       <c r="EC15" t="n">
-        <v>2.08</v>
+        <v>2.16</v>
       </c>
     </row>
     <row r="16">
@@ -7021,13 +7021,13 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C16" t="n">
         <v>12</v>
       </c>
       <c r="D16" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E16" t="n">
         <v>0.25</v>
@@ -7114,49 +7114,49 @@
         <v>0.08</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.83</v>
+        <v>2</v>
       </c>
       <c r="AH16" t="n">
-        <v>2.83</v>
+        <v>2.77</v>
       </c>
       <c r="AI16" t="n">
-        <v>110.5</v>
+        <v>111.46</v>
       </c>
       <c r="AJ16" t="n">
         <v>0.08</v>
       </c>
       <c r="AK16" t="n">
-        <v>2.92</v>
+        <v>3</v>
       </c>
       <c r="AL16" t="n">
-        <v>5.5</v>
+        <v>5.46</v>
       </c>
       <c r="AM16" t="n">
-        <v>0.5</v>
+        <v>0.54</v>
       </c>
       <c r="AN16" t="n">
-        <v>51.67</v>
+        <v>52.85</v>
       </c>
       <c r="AO16" t="n">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AP16" t="n">
-        <v>2.67</v>
+        <v>2.69</v>
       </c>
       <c r="AQ16" t="n">
-        <v>13.5</v>
+        <v>13.62</v>
       </c>
       <c r="AR16" t="n">
-        <v>9.42</v>
+        <v>9.31</v>
       </c>
       <c r="AS16" t="n">
-        <v>6.33</v>
+        <v>6.15</v>
       </c>
       <c r="AT16" t="n">
-        <v>0.83</v>
+        <v>0.85</v>
       </c>
       <c r="AU16" t="n">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="AV16" t="n">
         <v>0</v>
@@ -7168,82 +7168,82 @@
         <v>0</v>
       </c>
       <c r="AY16" t="n">
-        <v>55</v>
+        <v>55.92</v>
       </c>
       <c r="AZ16" t="n">
         <v>0.08</v>
       </c>
       <c r="BA16" t="n">
-        <v>14.17</v>
+        <v>14.31</v>
       </c>
       <c r="BB16" t="n">
-        <v>9.42</v>
+        <v>9.69</v>
       </c>
       <c r="BC16" t="n">
-        <v>4.75</v>
+        <v>4.62</v>
       </c>
       <c r="BD16" t="n">
-        <v>19.58</v>
+        <v>19.69</v>
       </c>
       <c r="BE16" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="BF16" t="n">
-        <v>2.83</v>
+        <v>2.92</v>
       </c>
       <c r="BG16" t="n">
-        <v>2.21</v>
+        <v>2.2</v>
       </c>
       <c r="BH16" t="n">
-        <v>9.539999999999999</v>
+        <v>9.48</v>
       </c>
       <c r="BI16" t="n">
-        <v>2.21</v>
+        <v>2.2</v>
       </c>
       <c r="BJ16" t="n">
-        <v>0.54</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="BK16" t="n">
-        <v>0.38</v>
+        <v>0.36</v>
       </c>
       <c r="BL16" t="n">
-        <v>0.96</v>
+        <v>0.92</v>
       </c>
       <c r="BM16" t="n">
-        <v>0.33</v>
+        <v>0.36</v>
       </c>
       <c r="BN16" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="BO16" t="n">
         <v>0.92</v>
       </c>
       <c r="BP16" t="n">
-        <v>4.79</v>
+        <v>4.76</v>
       </c>
       <c r="BQ16" t="n">
-        <v>4.75</v>
+        <v>4.72</v>
       </c>
       <c r="BR16" t="n">
-        <v>91.67</v>
+        <v>92</v>
       </c>
       <c r="BS16" t="n">
-        <v>70.83</v>
+        <v>72</v>
       </c>
       <c r="BT16" t="n">
-        <v>29.17</v>
+        <v>28</v>
       </c>
       <c r="BU16" t="n">
-        <v>16.67</v>
+        <v>16</v>
       </c>
       <c r="BV16" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="BW16" t="n">
         <v>0</v>
       </c>
       <c r="BX16" t="n">
-        <v>41.67</v>
+        <v>44</v>
       </c>
       <c r="BY16" t="n">
         <v>1.42</v>
@@ -7252,34 +7252,34 @@
         <v>1.49</v>
       </c>
       <c r="CA16" t="n">
-        <v>4.17</v>
+        <v>4.16</v>
       </c>
       <c r="CB16" t="n">
-        <v>4.37</v>
+        <v>4.36</v>
       </c>
       <c r="CC16" t="n">
-        <v>1.89</v>
+        <v>1.87</v>
       </c>
       <c r="CD16" t="n">
-        <v>1.94</v>
+        <v>1.9</v>
       </c>
       <c r="CE16" t="n">
         <v>1.32</v>
       </c>
       <c r="CF16" t="n">
-        <v>2.54</v>
+        <v>2.55</v>
       </c>
       <c r="CG16" t="n">
-        <v>3.16</v>
+        <v>3.14</v>
       </c>
       <c r="CH16" t="n">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="CI16" t="n">
         <v>1.92</v>
       </c>
       <c r="CJ16" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="CK16" t="n">
         <v>1.48</v>
@@ -7288,7 +7288,7 @@
         <v>1.96</v>
       </c>
       <c r="CM16" t="n">
-        <v>2.47</v>
+        <v>2.46</v>
       </c>
       <c r="CN16" t="n">
         <v>1.93</v>
@@ -7297,91 +7297,91 @@
         <v>1.23</v>
       </c>
       <c r="CP16" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="CQ16" t="n">
-        <v>2.85</v>
+        <v>2.87</v>
       </c>
       <c r="CR16" t="n">
         <v>1.37</v>
       </c>
       <c r="CS16" t="n">
-        <v>2.66</v>
+        <v>2.69</v>
       </c>
       <c r="CT16" t="n">
-        <v>3.16</v>
+        <v>3.13</v>
       </c>
       <c r="CU16" t="n">
         <v>1.5</v>
       </c>
       <c r="CV16" t="n">
-        <v>2.01</v>
+        <v>2</v>
       </c>
       <c r="CW16" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="CX16" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="CY16" t="n">
         <v>1.89</v>
       </c>
-      <c r="CX16" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="CY16" t="n">
-        <v>1.88</v>
-      </c>
       <c r="CZ16" t="n">
-        <v>2.37</v>
+        <v>2.36</v>
       </c>
       <c r="DA16" t="n">
         <v>1.93</v>
       </c>
       <c r="DB16" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="DC16" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="DD16" t="n">
-        <v>3.01</v>
+        <v>3.06</v>
       </c>
       <c r="DE16" t="n">
         <v>0.16</v>
       </c>
       <c r="DF16" t="n">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="DG16" t="n">
-        <v>3.12</v>
+        <v>3.08</v>
       </c>
       <c r="DH16" t="n">
-        <v>105.38</v>
+        <v>106.08</v>
       </c>
       <c r="DI16" t="n">
         <v>0.04</v>
       </c>
       <c r="DJ16" t="n">
-        <v>2.38</v>
+        <v>2.44</v>
       </c>
       <c r="DK16" t="n">
-        <v>5.96</v>
+        <v>5.92</v>
       </c>
       <c r="DL16" t="n">
-        <v>0.46</v>
+        <v>0.48</v>
       </c>
       <c r="DM16" t="n">
-        <v>53.71</v>
+        <v>54.24</v>
       </c>
       <c r="DN16" t="n">
-        <v>0.66</v>
+        <v>0.64</v>
       </c>
       <c r="DO16" t="n">
-        <v>2.83</v>
+        <v>2.84</v>
       </c>
       <c r="DP16" t="n">
-        <v>12.88</v>
+        <v>12.96</v>
       </c>
       <c r="DQ16" t="n">
-        <v>9.710000000000001</v>
+        <v>9.640000000000001</v>
       </c>
       <c r="DR16" t="n">
-        <v>5.88</v>
+        <v>5.8</v>
       </c>
       <c r="DS16" t="n">
         <v>0.08</v>
@@ -7393,28 +7393,28 @@
         <v>0</v>
       </c>
       <c r="DV16" t="n">
-        <v>53.12</v>
+        <v>53.68</v>
       </c>
       <c r="DW16" t="n">
         <v>0.04</v>
       </c>
       <c r="DX16" t="n">
-        <v>15.34</v>
+        <v>15.36</v>
       </c>
       <c r="DY16" t="n">
-        <v>9.619999999999999</v>
+        <v>9.76</v>
       </c>
       <c r="DZ16" t="n">
-        <v>5.71</v>
+        <v>5.6</v>
       </c>
       <c r="EA16" t="n">
-        <v>20.25</v>
+        <v>20.28</v>
       </c>
       <c r="EB16" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="EC16" t="n">
-        <v>2.33</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="17">

--- a/data/teams/leagues/Averages_Belgium_Pro_League_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Belgium_Pro_League_2025-2026.xlsx
@@ -645,7 +645,7 @@
     <col width="9.6" customWidth="1" min="73" max="73"/>
     <col width="9.6" customWidth="1" min="74" max="74"/>
     <col width="9.6" customWidth="1" min="75" max="75"/>
-    <col width="8.4" customWidth="1" min="76" max="76"/>
+    <col width="7.199999999999999" customWidth="1" min="76" max="76"/>
     <col width="18" customWidth="1" min="77" max="77"/>
     <col width="27.6" customWidth="1" min="78" max="78"/>
     <col width="18" customWidth="1" min="79" max="79"/>
@@ -1379,10 +1379,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D2" t="n">
         <v>12</v>
@@ -1394,79 +1394,79 @@
         <v>0.92</v>
       </c>
       <c r="G2" t="n">
-        <v>2.67</v>
+        <v>2.54</v>
       </c>
       <c r="H2" t="n">
-        <v>107.33</v>
+        <v>107.62</v>
       </c>
       <c r="I2" t="n">
         <v>0.08</v>
       </c>
       <c r="J2" t="n">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="K2" t="n">
-        <v>4.67</v>
+        <v>4.46</v>
       </c>
       <c r="L2" t="n">
-        <v>0.42</v>
+        <v>0.38</v>
       </c>
       <c r="M2" t="n">
-        <v>47.92</v>
+        <v>49</v>
       </c>
       <c r="N2" t="n">
-        <v>0.5</v>
+        <v>0.46</v>
       </c>
       <c r="O2" t="n">
-        <v>2</v>
+        <v>1.92</v>
       </c>
       <c r="P2" t="n">
         <v>9.08</v>
       </c>
       <c r="Q2" t="n">
-        <v>13.58</v>
+        <v>13.62</v>
       </c>
       <c r="R2" t="n">
-        <v>6.92</v>
+        <v>6.62</v>
       </c>
       <c r="S2" t="n">
-        <v>2.17</v>
+        <v>2.15</v>
       </c>
       <c r="T2" t="n">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="U2" t="n">
-        <v>0.5</v>
+        <v>0.46</v>
       </c>
       <c r="V2" t="n">
-        <v>0.5</v>
+        <v>0.46</v>
       </c>
       <c r="W2" t="n">
         <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>49.58</v>
+        <v>48.62</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.17</v>
+        <v>0.15</v>
       </c>
       <c r="Z2" t="n">
-        <v>13.75</v>
+        <v>14.08</v>
       </c>
       <c r="AA2" t="n">
-        <v>9.08</v>
+        <v>9.380000000000001</v>
       </c>
       <c r="AB2" t="n">
-        <v>4.67</v>
+        <v>4.69</v>
       </c>
       <c r="AC2" t="n">
-        <v>23.42</v>
+        <v>23.31</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.55</v>
+        <v>1.58</v>
       </c>
       <c r="AE2" t="n">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="AF2" t="n">
         <v>0.17</v>
@@ -1559,61 +1559,61 @@
         <v>2.92</v>
       </c>
       <c r="BJ2" t="n">
-        <v>0.62</v>
+        <v>0.6</v>
       </c>
       <c r="BK2" t="n">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="BL2" t="n">
-        <v>0.58</v>
+        <v>0.6</v>
       </c>
       <c r="BM2" t="n">
-        <v>0.62</v>
+        <v>0.68</v>
       </c>
       <c r="BN2" t="n">
-        <v>1.21</v>
+        <v>1.28</v>
       </c>
       <c r="BO2" t="n">
-        <v>1.71</v>
+        <v>1.64</v>
       </c>
       <c r="BP2" t="n">
-        <v>4.42</v>
+        <v>4.4</v>
       </c>
       <c r="BQ2" t="n">
-        <v>5.5</v>
+        <v>5.52</v>
       </c>
       <c r="BR2" t="n">
-        <v>91.67</v>
+        <v>92</v>
       </c>
       <c r="BS2" t="n">
-        <v>91.67</v>
+        <v>92</v>
       </c>
       <c r="BT2" t="n">
-        <v>45.83</v>
+        <v>48</v>
       </c>
       <c r="BU2" t="n">
-        <v>29.17</v>
+        <v>28</v>
       </c>
       <c r="BV2" t="n">
-        <v>20.83</v>
+        <v>20</v>
       </c>
       <c r="BW2" t="n">
-        <v>8.33</v>
+        <v>8</v>
       </c>
       <c r="BX2" t="n">
-        <v>62.5</v>
+        <v>64</v>
       </c>
       <c r="BY2" t="n">
-        <v>2.33</v>
+        <v>2.51</v>
       </c>
       <c r="BZ2" t="n">
-        <v>2.42</v>
+        <v>2.65</v>
       </c>
       <c r="CA2" t="n">
-        <v>3.54</v>
+        <v>3.55</v>
       </c>
       <c r="CB2" t="n">
-        <v>3.65</v>
+        <v>3.68</v>
       </c>
       <c r="CC2" t="n">
         <v>3.44</v>
@@ -1625,10 +1625,10 @@
         <v>1.32</v>
       </c>
       <c r="CF2" t="n">
-        <v>2.53</v>
+        <v>2.52</v>
       </c>
       <c r="CG2" t="n">
-        <v>3.14</v>
+        <v>3.15</v>
       </c>
       <c r="CH2" t="n">
         <v>1.48</v>
@@ -1637,7 +1637,7 @@
         <v>2.17</v>
       </c>
       <c r="CJ2" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="CK2" t="n">
         <v>1.44</v>
@@ -1658,19 +1658,19 @@
         <v>1.76</v>
       </c>
       <c r="CQ2" t="n">
-        <v>2.9</v>
+        <v>2.88</v>
       </c>
       <c r="CR2" t="n">
         <v>1.36</v>
       </c>
       <c r="CS2" t="n">
-        <v>2.65</v>
+        <v>2.63</v>
       </c>
       <c r="CT2" t="n">
         <v>3.19</v>
       </c>
       <c r="CU2" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="CV2" t="n">
         <v>2.29</v>
@@ -1691,88 +1691,88 @@
         <v>2.08</v>
       </c>
       <c r="DB2" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="DC2" t="n">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="DD2" t="n">
-        <v>2.94</v>
+        <v>2.92</v>
       </c>
       <c r="DE2" t="n">
         <v>0.08</v>
       </c>
       <c r="DF2" t="n">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="DG2" t="n">
-        <v>2.42</v>
+        <v>2.36</v>
       </c>
       <c r="DH2" t="n">
-        <v>103.79</v>
+        <v>104.08</v>
       </c>
       <c r="DI2" t="n">
         <v>0.12</v>
       </c>
       <c r="DJ2" t="n">
-        <v>2.21</v>
+        <v>2.16</v>
       </c>
       <c r="DK2" t="n">
-        <v>4.54</v>
+        <v>4.44</v>
       </c>
       <c r="DL2" t="n">
-        <v>0.5</v>
+        <v>0.48</v>
       </c>
       <c r="DM2" t="n">
-        <v>48</v>
+        <v>48.56</v>
       </c>
       <c r="DN2" t="n">
-        <v>0.92</v>
+        <v>0.88</v>
       </c>
       <c r="DO2" t="n">
-        <v>2.12</v>
+        <v>2.08</v>
       </c>
       <c r="DP2" t="n">
-        <v>10.75</v>
+        <v>10.68</v>
       </c>
       <c r="DQ2" t="n">
-        <v>12.7</v>
+        <v>12.76</v>
       </c>
       <c r="DR2" t="n">
-        <v>7.38</v>
+        <v>7.2</v>
       </c>
       <c r="DS2" t="n">
-        <v>0.34</v>
+        <v>0.32</v>
       </c>
       <c r="DT2" t="n">
-        <v>0.34</v>
+        <v>0.32</v>
       </c>
       <c r="DU2" t="n">
         <v>0</v>
       </c>
       <c r="DV2" t="n">
-        <v>47.42</v>
+        <v>47</v>
       </c>
       <c r="DW2" t="n">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
       <c r="DX2" t="n">
-        <v>12.79</v>
+        <v>13</v>
       </c>
       <c r="DY2" t="n">
-        <v>8.67</v>
+        <v>8.84</v>
       </c>
       <c r="DZ2" t="n">
-        <v>4.12</v>
+        <v>4.16</v>
       </c>
       <c r="EA2" t="n">
-        <v>22.33</v>
+        <v>22.32</v>
       </c>
       <c r="EB2" t="n">
-        <v>1.45</v>
+        <v>1.47</v>
       </c>
       <c r="EC2" t="n">
-        <v>1.92</v>
+        <v>1.88</v>
       </c>
     </row>
     <row r="3">
@@ -1782,13 +1782,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C3" t="n">
         <v>12</v>
       </c>
       <c r="D3" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E3" t="n">
         <v>0.08</v>
@@ -1875,49 +1875,49 @@
         <v>0.08</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.08</v>
+        <v>1.23</v>
       </c>
       <c r="AH3" t="n">
-        <v>3.5</v>
+        <v>3.62</v>
       </c>
       <c r="AI3" t="n">
-        <v>107.08</v>
+        <v>104.31</v>
       </c>
       <c r="AJ3" t="n">
         <v>0</v>
       </c>
       <c r="AK3" t="n">
-        <v>1.58</v>
+        <v>1.69</v>
       </c>
       <c r="AL3" t="n">
-        <v>5.83</v>
+        <v>6</v>
       </c>
       <c r="AM3" t="n">
-        <v>0.33</v>
+        <v>0.31</v>
       </c>
       <c r="AN3" t="n">
-        <v>56.67</v>
+        <v>55.31</v>
       </c>
       <c r="AO3" t="n">
-        <v>0.5</v>
+        <v>0.46</v>
       </c>
       <c r="AP3" t="n">
-        <v>2.33</v>
+        <v>2.38</v>
       </c>
       <c r="AQ3" t="n">
-        <v>9.5</v>
+        <v>9.77</v>
       </c>
       <c r="AR3" t="n">
-        <v>11.5</v>
+        <v>11.31</v>
       </c>
       <c r="AS3" t="n">
-        <v>7.92</v>
+        <v>8.31</v>
       </c>
       <c r="AT3" t="n">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="AU3" t="n">
-        <v>1.58</v>
+        <v>1.62</v>
       </c>
       <c r="AV3" t="n">
         <v>0</v>
@@ -1929,58 +1929,58 @@
         <v>0</v>
       </c>
       <c r="AY3" t="n">
-        <v>60.08</v>
+        <v>60.31</v>
       </c>
       <c r="AZ3" t="n">
         <v>0</v>
       </c>
       <c r="BA3" t="n">
-        <v>14.83</v>
+        <v>14.46</v>
       </c>
       <c r="BB3" t="n">
-        <v>9.58</v>
+        <v>9.380000000000001</v>
       </c>
       <c r="BC3" t="n">
-        <v>5.25</v>
+        <v>5.08</v>
       </c>
       <c r="BD3" t="n">
-        <v>18.5</v>
+        <v>18.77</v>
       </c>
       <c r="BE3" t="n">
-        <v>1.72</v>
+        <v>1.67</v>
       </c>
       <c r="BF3" t="n">
-        <v>1.58</v>
+        <v>1.69</v>
       </c>
       <c r="BG3" t="n">
         <v>3.08</v>
       </c>
       <c r="BH3" t="n">
-        <v>10.58</v>
+        <v>10.56</v>
       </c>
       <c r="BI3" t="n">
         <v>3.08</v>
       </c>
       <c r="BJ3" t="n">
-        <v>0.83</v>
+        <v>0.8</v>
       </c>
       <c r="BK3" t="n">
-        <v>0.5</v>
+        <v>0.48</v>
       </c>
       <c r="BL3" t="n">
-        <v>0.83</v>
+        <v>0.84</v>
       </c>
       <c r="BM3" t="n">
-        <v>0.92</v>
+        <v>0.96</v>
       </c>
       <c r="BN3" t="n">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="BO3" t="n">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="BP3" t="n">
-        <v>4.71</v>
+        <v>4.68</v>
       </c>
       <c r="BQ3" t="n">
         <v>5.88</v>
@@ -1989,22 +1989,22 @@
         <v>100</v>
       </c>
       <c r="BS3" t="n">
-        <v>62.5</v>
+        <v>64</v>
       </c>
       <c r="BT3" t="n">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="BU3" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="BV3" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="BW3" t="n">
-        <v>16.67</v>
+        <v>16</v>
       </c>
       <c r="BX3" t="n">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="BY3" t="n">
         <v>1.45</v>
@@ -2013,16 +2013,16 @@
         <v>1.47</v>
       </c>
       <c r="CA3" t="n">
-        <v>4.47</v>
+        <v>4.45</v>
       </c>
       <c r="CB3" t="n">
-        <v>4.75</v>
+        <v>4.74</v>
       </c>
       <c r="CC3" t="n">
         <v>1.87</v>
       </c>
       <c r="CD3" t="n">
-        <v>1.92</v>
+        <v>1.9</v>
       </c>
       <c r="CE3" t="n">
         <v>1.26</v>
@@ -2031,7 +2031,7 @@
         <v>2.25</v>
       </c>
       <c r="CG3" t="n">
-        <v>3.52</v>
+        <v>3.51</v>
       </c>
       <c r="CH3" t="n">
         <v>1.61</v>
@@ -2067,7 +2067,7 @@
         <v>1.34</v>
       </c>
       <c r="CS3" t="n">
-        <v>2.33</v>
+        <v>2.34</v>
       </c>
       <c r="CT3" t="n">
         <v>3.24</v>
@@ -2085,13 +2085,13 @@
         <v>1.53</v>
       </c>
       <c r="CY3" t="n">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="CZ3" t="n">
         <v>2.47</v>
       </c>
       <c r="DA3" t="n">
-        <v>2.01</v>
+        <v>2.02</v>
       </c>
       <c r="DB3" t="n">
         <v>1.19</v>
@@ -2106,43 +2106,43 @@
         <v>0.08</v>
       </c>
       <c r="DF3" t="n">
-        <v>1.04</v>
+        <v>1.12</v>
       </c>
       <c r="DG3" t="n">
-        <v>3.62</v>
+        <v>3.68</v>
       </c>
       <c r="DH3" t="n">
-        <v>111.33</v>
+        <v>109.72</v>
       </c>
       <c r="DI3" t="n">
         <v>0</v>
       </c>
       <c r="DJ3" t="n">
-        <v>1.5</v>
+        <v>1.56</v>
       </c>
       <c r="DK3" t="n">
-        <v>6.33</v>
+        <v>6.4</v>
       </c>
       <c r="DL3" t="n">
-        <v>0.58</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="DM3" t="n">
-        <v>60.92</v>
+        <v>60.04</v>
       </c>
       <c r="DN3" t="n">
-        <v>0.38</v>
+        <v>0.36</v>
       </c>
       <c r="DO3" t="n">
-        <v>2.7</v>
+        <v>2.72</v>
       </c>
       <c r="DP3" t="n">
-        <v>9.5</v>
+        <v>9.640000000000001</v>
       </c>
       <c r="DQ3" t="n">
-        <v>11.71</v>
+        <v>11.6</v>
       </c>
       <c r="DR3" t="n">
-        <v>7.12</v>
+        <v>7.36</v>
       </c>
       <c r="DS3" t="n">
         <v>0</v>
@@ -2160,22 +2160,22 @@
         <v>0.08</v>
       </c>
       <c r="DX3" t="n">
-        <v>16.33</v>
+        <v>16.08</v>
       </c>
       <c r="DY3" t="n">
-        <v>10.88</v>
+        <v>10.72</v>
       </c>
       <c r="DZ3" t="n">
-        <v>5.46</v>
+        <v>5.36</v>
       </c>
       <c r="EA3" t="n">
-        <v>20.66</v>
+        <v>20.72</v>
       </c>
       <c r="EB3" t="n">
-        <v>1.85</v>
+        <v>1.82</v>
       </c>
       <c r="EC3" t="n">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
     </row>
     <row r="4">
@@ -2332,7 +2332,7 @@
         <v>0</v>
       </c>
       <c r="AY4" t="n">
-        <v>44.77</v>
+        <v>44.85</v>
       </c>
       <c r="AZ4" t="n">
         <v>0.31</v>
@@ -2557,7 +2557,7 @@
         <v>0</v>
       </c>
       <c r="DV4" t="n">
-        <v>47.28</v>
+        <v>47.32</v>
       </c>
       <c r="DW4" t="n">
         <v>0.16</v>
@@ -3797,13 +3797,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C8" t="n">
         <v>12</v>
       </c>
       <c r="D8" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E8" t="n">
         <v>0.25</v>
@@ -3890,136 +3890,136 @@
         <v>0.08</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.58</v>
+        <v>1.69</v>
       </c>
       <c r="AH8" t="n">
-        <v>2.08</v>
+        <v>2</v>
       </c>
       <c r="AI8" t="n">
-        <v>87.25</v>
+        <v>88.69</v>
       </c>
       <c r="AJ8" t="n">
         <v>0</v>
       </c>
       <c r="AK8" t="n">
-        <v>1.75</v>
+        <v>1.92</v>
       </c>
       <c r="AL8" t="n">
-        <v>4.33</v>
+        <v>4.15</v>
       </c>
       <c r="AM8" t="n">
-        <v>0.25</v>
+        <v>0.23</v>
       </c>
       <c r="AN8" t="n">
-        <v>42.67</v>
+        <v>42.92</v>
       </c>
       <c r="AO8" t="n">
-        <v>0.08</v>
+        <v>0.15</v>
       </c>
       <c r="AP8" t="n">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="AQ8" t="n">
-        <v>13.08</v>
+        <v>13.15</v>
       </c>
       <c r="AR8" t="n">
-        <v>11.58</v>
+        <v>11.92</v>
       </c>
       <c r="AS8" t="n">
-        <v>9</v>
+        <v>8.85</v>
       </c>
       <c r="AT8" t="n">
-        <v>2</v>
+        <v>1.85</v>
       </c>
       <c r="AU8" t="n">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
       <c r="AV8" t="n">
-        <v>0.17</v>
+        <v>0.15</v>
       </c>
       <c r="AW8" t="n">
-        <v>0.17</v>
+        <v>0.15</v>
       </c>
       <c r="AX8" t="n">
         <v>0</v>
       </c>
       <c r="AY8" t="n">
-        <v>46.92</v>
+        <v>47</v>
       </c>
       <c r="AZ8" t="n">
         <v>0.08</v>
       </c>
       <c r="BA8" t="n">
-        <v>13.17</v>
+        <v>13.08</v>
       </c>
       <c r="BB8" t="n">
-        <v>8.83</v>
+        <v>8.460000000000001</v>
       </c>
       <c r="BC8" t="n">
-        <v>4.33</v>
+        <v>4.62</v>
       </c>
       <c r="BD8" t="n">
-        <v>22.08</v>
+        <v>23.54</v>
       </c>
       <c r="BE8" t="n">
-        <v>1.41</v>
+        <v>1.43</v>
       </c>
       <c r="BF8" t="n">
-        <v>1.58</v>
+        <v>1.77</v>
       </c>
       <c r="BG8" t="n">
-        <v>2.79</v>
+        <v>2.76</v>
       </c>
       <c r="BH8" t="n">
-        <v>10.46</v>
+        <v>10.28</v>
       </c>
       <c r="BI8" t="n">
-        <v>2.79</v>
+        <v>2.76</v>
       </c>
       <c r="BJ8" t="n">
-        <v>0.75</v>
+        <v>0.72</v>
       </c>
       <c r="BK8" t="n">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="BL8" t="n">
-        <v>0.83</v>
+        <v>0.8</v>
       </c>
       <c r="BM8" t="n">
-        <v>0.54</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="BN8" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="BO8" t="n">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="BP8" t="n">
-        <v>4.92</v>
+        <v>4.84</v>
       </c>
       <c r="BQ8" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="BR8" t="n">
-        <v>91.67</v>
+        <v>92</v>
       </c>
       <c r="BS8" t="n">
-        <v>79.17</v>
+        <v>80</v>
       </c>
       <c r="BT8" t="n">
-        <v>37.5</v>
+        <v>36</v>
       </c>
       <c r="BU8" t="n">
-        <v>29.17</v>
+        <v>28</v>
       </c>
       <c r="BV8" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="BW8" t="n">
-        <v>8.33</v>
+        <v>8</v>
       </c>
       <c r="BX8" t="n">
-        <v>37.5</v>
+        <v>36</v>
       </c>
       <c r="BY8" t="n">
         <v>2.2</v>
@@ -4028,31 +4028,31 @@
         <v>2.32</v>
       </c>
       <c r="CA8" t="n">
-        <v>3.79</v>
+        <v>3.77</v>
       </c>
       <c r="CB8" t="n">
-        <v>3.87</v>
+        <v>3.86</v>
       </c>
       <c r="CC8" t="n">
-        <v>3.99</v>
+        <v>3.93</v>
       </c>
       <c r="CD8" t="n">
-        <v>3.93</v>
+        <v>3.89</v>
       </c>
       <c r="CE8" t="n">
         <v>1.27</v>
       </c>
       <c r="CF8" t="n">
-        <v>2.28</v>
+        <v>2.29</v>
       </c>
       <c r="CG8" t="n">
-        <v>3.47</v>
+        <v>3.45</v>
       </c>
       <c r="CH8" t="n">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="CI8" t="n">
-        <v>2.4</v>
+        <v>2.39</v>
       </c>
       <c r="CJ8" t="n">
         <v>1.55</v>
@@ -4064,10 +4064,10 @@
         <v>1.69</v>
       </c>
       <c r="CM8" t="n">
-        <v>2.88</v>
+        <v>2.87</v>
       </c>
       <c r="CN8" t="n">
-        <v>2.21</v>
+        <v>2.2</v>
       </c>
       <c r="CO8" t="n">
         <v>1.16</v>
@@ -4076,22 +4076,22 @@
         <v>1.61</v>
       </c>
       <c r="CQ8" t="n">
-        <v>2.46</v>
+        <v>2.48</v>
       </c>
       <c r="CR8" t="n">
         <v>1.34</v>
       </c>
       <c r="CS8" t="n">
-        <v>2.35</v>
+        <v>2.37</v>
       </c>
       <c r="CT8" t="n">
         <v>3.31</v>
       </c>
       <c r="CU8" t="n">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="CV8" t="n">
-        <v>2.57</v>
+        <v>2.56</v>
       </c>
       <c r="CW8" t="n">
         <v>1.55</v>
@@ -4112,52 +4112,52 @@
         <v>1.19</v>
       </c>
       <c r="DC8" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="DD8" t="n">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="DE8" t="n">
         <v>0.16</v>
       </c>
       <c r="DF8" t="n">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="DG8" t="n">
-        <v>2.54</v>
+        <v>2.48</v>
       </c>
       <c r="DH8" t="n">
-        <v>93.29000000000001</v>
+        <v>93.8</v>
       </c>
       <c r="DI8" t="n">
         <v>0</v>
       </c>
       <c r="DJ8" t="n">
-        <v>1.58</v>
+        <v>1.68</v>
       </c>
       <c r="DK8" t="n">
-        <v>5.29</v>
+        <v>5.16</v>
       </c>
       <c r="DL8" t="n">
-        <v>0.29</v>
+        <v>0.28</v>
       </c>
       <c r="DM8" t="n">
-        <v>50.12</v>
+        <v>49.96</v>
       </c>
       <c r="DN8" t="n">
-        <v>0.2</v>
+        <v>0.24</v>
       </c>
       <c r="DO8" t="n">
-        <v>2.75</v>
+        <v>2.68</v>
       </c>
       <c r="DP8" t="n">
-        <v>11.92</v>
+        <v>12</v>
       </c>
       <c r="DQ8" t="n">
-        <v>11.79</v>
+        <v>11.96</v>
       </c>
       <c r="DR8" t="n">
-        <v>8.380000000000001</v>
+        <v>8.32</v>
       </c>
       <c r="DS8" t="n">
         <v>0.12</v>
@@ -4169,28 +4169,28 @@
         <v>0</v>
       </c>
       <c r="DV8" t="n">
-        <v>49.42</v>
+        <v>49.36</v>
       </c>
       <c r="DW8" t="n">
         <v>0.08</v>
       </c>
       <c r="DX8" t="n">
-        <v>14.8</v>
+        <v>14.68</v>
       </c>
       <c r="DY8" t="n">
-        <v>10.2</v>
+        <v>9.960000000000001</v>
       </c>
       <c r="DZ8" t="n">
-        <v>4.58</v>
+        <v>4.72</v>
       </c>
       <c r="EA8" t="n">
-        <v>21.16</v>
+        <v>21.96</v>
       </c>
       <c r="EB8" t="n">
         <v>1.6</v>
       </c>
       <c r="EC8" t="n">
-        <v>1.46</v>
+        <v>1.56</v>
       </c>
     </row>
     <row r="9">
@@ -4266,7 +4266,7 @@
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>45.46</v>
+        <v>45.38</v>
       </c>
       <c r="Y9" t="n">
         <v>0</v>
@@ -4572,7 +4572,7 @@
         <v>0</v>
       </c>
       <c r="DV9" t="n">
-        <v>45.16</v>
+        <v>45.12</v>
       </c>
       <c r="DW9" t="n">
         <v>0.04</v>
@@ -4603,13 +4603,13 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C10" t="n">
         <v>12</v>
       </c>
       <c r="D10" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
@@ -4693,52 +4693,52 @@
         <v>1.5</v>
       </c>
       <c r="AF10" t="n">
-        <v>0.17</v>
+        <v>0.15</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.42</v>
+        <v>1.62</v>
       </c>
       <c r="AH10" t="n">
-        <v>2.42</v>
+        <v>2.38</v>
       </c>
       <c r="AI10" t="n">
-        <v>80.92</v>
+        <v>80.62</v>
       </c>
       <c r="AJ10" t="n">
-        <v>0</v>
+        <v>0.08</v>
       </c>
       <c r="AK10" t="n">
-        <v>2.25</v>
+        <v>2.46</v>
       </c>
       <c r="AL10" t="n">
-        <v>3.58</v>
+        <v>3.62</v>
       </c>
       <c r="AM10" t="n">
-        <v>0.25</v>
+        <v>0.23</v>
       </c>
       <c r="AN10" t="n">
-        <v>36.75</v>
+        <v>36.54</v>
       </c>
       <c r="AO10" t="n">
-        <v>0.75</v>
+        <v>0.77</v>
       </c>
       <c r="AP10" t="n">
-        <v>1.17</v>
+        <v>1.23</v>
       </c>
       <c r="AQ10" t="n">
-        <v>12</v>
+        <v>11.85</v>
       </c>
       <c r="AR10" t="n">
-        <v>12.58</v>
+        <v>12.77</v>
       </c>
       <c r="AS10" t="n">
-        <v>8.58</v>
+        <v>8.619999999999999</v>
       </c>
       <c r="AT10" t="n">
-        <v>1.58</v>
+        <v>1.46</v>
       </c>
       <c r="AU10" t="n">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="AV10" t="n">
         <v>0</v>
@@ -4750,82 +4750,82 @@
         <v>0</v>
       </c>
       <c r="AY10" t="n">
-        <v>33.58</v>
+        <v>33.54</v>
       </c>
       <c r="AZ10" t="n">
         <v>0.08</v>
       </c>
       <c r="BA10" t="n">
-        <v>8.83</v>
+        <v>8.69</v>
       </c>
       <c r="BB10" t="n">
-        <v>6.33</v>
+        <v>6.38</v>
       </c>
       <c r="BC10" t="n">
-        <v>2.5</v>
+        <v>2.31</v>
       </c>
       <c r="BD10" t="n">
-        <v>20.75</v>
+        <v>20.77</v>
       </c>
       <c r="BE10" t="n">
-        <v>1</v>
+        <v>0.98</v>
       </c>
       <c r="BF10" t="n">
-        <v>2.08</v>
+        <v>2.31</v>
       </c>
       <c r="BG10" t="n">
-        <v>2.04</v>
+        <v>1.96</v>
       </c>
       <c r="BH10" t="n">
-        <v>9</v>
+        <v>9.119999999999999</v>
       </c>
       <c r="BI10" t="n">
-        <v>2.04</v>
+        <v>1.96</v>
       </c>
       <c r="BJ10" t="n">
-        <v>0.54</v>
+        <v>0.52</v>
       </c>
       <c r="BK10" t="n">
-        <v>0.33</v>
+        <v>0.32</v>
       </c>
       <c r="BL10" t="n">
-        <v>0.54</v>
+        <v>0.52</v>
       </c>
       <c r="BM10" t="n">
-        <v>0.62</v>
+        <v>0.6</v>
       </c>
       <c r="BN10" t="n">
-        <v>1.17</v>
+        <v>1.12</v>
       </c>
       <c r="BO10" t="n">
-        <v>0.88</v>
+        <v>0.84</v>
       </c>
       <c r="BP10" t="n">
-        <v>3.62</v>
+        <v>3.8</v>
       </c>
       <c r="BQ10" t="n">
-        <v>5.38</v>
+        <v>5.32</v>
       </c>
       <c r="BR10" t="n">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="BS10" t="n">
-        <v>58.33</v>
+        <v>56</v>
       </c>
       <c r="BT10" t="n">
-        <v>45.83</v>
+        <v>44</v>
       </c>
       <c r="BU10" t="n">
-        <v>16.67</v>
+        <v>16</v>
       </c>
       <c r="BV10" t="n">
-        <v>8.33</v>
+        <v>8</v>
       </c>
       <c r="BW10" t="n">
         <v>0</v>
       </c>
       <c r="BX10" t="n">
-        <v>54.17</v>
+        <v>52</v>
       </c>
       <c r="BY10" t="n">
         <v>3.41</v>
@@ -4840,10 +4840,10 @@
         <v>3.66</v>
       </c>
       <c r="CC10" t="n">
-        <v>4.79</v>
+        <v>4.8</v>
       </c>
       <c r="CD10" t="n">
-        <v>5.13</v>
+        <v>5.11</v>
       </c>
       <c r="CE10" t="n">
         <v>1.39</v>
@@ -4852,7 +4852,7 @@
         <v>2.79</v>
       </c>
       <c r="CG10" t="n">
-        <v>2.88</v>
+        <v>2.87</v>
       </c>
       <c r="CH10" t="n">
         <v>1.4</v>
@@ -4861,7 +4861,7 @@
         <v>1.89</v>
       </c>
       <c r="CJ10" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="CK10" t="n">
         <v>1.57</v>
@@ -4876,7 +4876,7 @@
         <v>1.82</v>
       </c>
       <c r="CO10" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="CP10" t="n">
         <v>1.98</v>
@@ -4891,7 +4891,7 @@
         <v>2.92</v>
       </c>
       <c r="CT10" t="n">
-        <v>3.02</v>
+        <v>3.01</v>
       </c>
       <c r="CU10" t="n">
         <v>1.43</v>
@@ -4903,16 +4903,16 @@
         <v>1.88</v>
       </c>
       <c r="CX10" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="CY10" t="n">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="CZ10" t="n">
-        <v>2.31</v>
+        <v>2.32</v>
       </c>
       <c r="DA10" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="DB10" t="n">
         <v>1.33</v>
@@ -4921,49 +4921,49 @@
         <v>2.06</v>
       </c>
       <c r="DD10" t="n">
-        <v>3.56</v>
+        <v>3.57</v>
       </c>
       <c r="DE10" t="n">
         <v>0.08</v>
       </c>
       <c r="DF10" t="n">
-        <v>1.08</v>
+        <v>1.2</v>
       </c>
       <c r="DG10" t="n">
-        <v>2.88</v>
+        <v>2.84</v>
       </c>
       <c r="DH10" t="n">
-        <v>82.84</v>
+        <v>82.59999999999999</v>
       </c>
       <c r="DI10" t="n">
-        <v>0.08</v>
+        <v>0.12</v>
       </c>
       <c r="DJ10" t="n">
-        <v>1.88</v>
+        <v>2</v>
       </c>
       <c r="DK10" t="n">
-        <v>4.71</v>
+        <v>4.68</v>
       </c>
       <c r="DL10" t="n">
-        <v>0.21</v>
+        <v>0.2</v>
       </c>
       <c r="DM10" t="n">
-        <v>41.38</v>
+        <v>41.08</v>
       </c>
       <c r="DN10" t="n">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="DO10" t="n">
         <v>1.84</v>
       </c>
       <c r="DP10" t="n">
-        <v>11.54</v>
+        <v>11.48</v>
       </c>
       <c r="DQ10" t="n">
-        <v>12.12</v>
+        <v>12.24</v>
       </c>
       <c r="DR10" t="n">
-        <v>8.58</v>
+        <v>8.6</v>
       </c>
       <c r="DS10" t="n">
         <v>0</v>
@@ -4975,28 +4975,28 @@
         <v>0</v>
       </c>
       <c r="DV10" t="n">
-        <v>36.2</v>
+        <v>36.08</v>
       </c>
       <c r="DW10" t="n">
         <v>0.04</v>
       </c>
       <c r="DX10" t="n">
-        <v>9.5</v>
+        <v>9.4</v>
       </c>
       <c r="DY10" t="n">
-        <v>6.79</v>
+        <v>6.8</v>
       </c>
       <c r="DZ10" t="n">
-        <v>2.71</v>
+        <v>2.6</v>
       </c>
       <c r="EA10" t="n">
         <v>21.08</v>
       </c>
       <c r="EB10" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="EC10" t="n">
-        <v>1.79</v>
+        <v>1.92</v>
       </c>
     </row>
     <row r="11">
@@ -5006,10 +5006,10 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C11" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D11" t="n">
         <v>12</v>
@@ -5018,82 +5018,82 @@
         <v>0.08</v>
       </c>
       <c r="F11" t="n">
-        <v>1.58</v>
+        <v>1.54</v>
       </c>
       <c r="G11" t="n">
-        <v>3.5</v>
+        <v>3.38</v>
       </c>
       <c r="H11" t="n">
-        <v>108.42</v>
+        <v>109.69</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
       </c>
       <c r="J11" t="n">
-        <v>2.67</v>
+        <v>2.54</v>
       </c>
       <c r="K11" t="n">
-        <v>6.5</v>
+        <v>6.62</v>
       </c>
       <c r="L11" t="n">
-        <v>0.67</v>
+        <v>0.77</v>
       </c>
       <c r="M11" t="n">
-        <v>59.92</v>
+        <v>59.15</v>
       </c>
       <c r="N11" t="n">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="O11" t="n">
-        <v>3</v>
+        <v>3.23</v>
       </c>
       <c r="P11" t="n">
-        <v>12.83</v>
+        <v>13</v>
       </c>
       <c r="Q11" t="n">
-        <v>12</v>
+        <v>11.77</v>
       </c>
       <c r="R11" t="n">
-        <v>7.33</v>
+        <v>7.46</v>
       </c>
       <c r="S11" t="n">
-        <v>0.83</v>
+        <v>0.77</v>
       </c>
       <c r="T11" t="n">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="U11" t="n">
-        <v>0.17</v>
+        <v>0.15</v>
       </c>
       <c r="V11" t="n">
-        <v>0.17</v>
+        <v>0.15</v>
       </c>
       <c r="W11" t="n">
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>52.08</v>
+        <v>53.23</v>
       </c>
       <c r="Y11" t="n">
         <v>0.08</v>
       </c>
       <c r="Z11" t="n">
-        <v>17.08</v>
+        <v>17.23</v>
       </c>
       <c r="AA11" t="n">
-        <v>11.67</v>
+        <v>11.85</v>
       </c>
       <c r="AB11" t="n">
-        <v>5.42</v>
+        <v>5.38</v>
       </c>
       <c r="AC11" t="n">
-        <v>20.25</v>
+        <v>21.15</v>
       </c>
       <c r="AD11" t="n">
         <v>1.89</v>
       </c>
       <c r="AE11" t="n">
-        <v>2.5</v>
+        <v>2.38</v>
       </c>
       <c r="AF11" t="n">
         <v>0.17</v>
@@ -5177,70 +5177,70 @@
         <v>2.5</v>
       </c>
       <c r="BG11" t="n">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="BH11" t="n">
-        <v>10.79</v>
+        <v>10.84</v>
       </c>
       <c r="BI11" t="n">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="BJ11" t="n">
-        <v>0.67</v>
+        <v>0.64</v>
       </c>
       <c r="BK11" t="n">
-        <v>0.38</v>
+        <v>0.36</v>
       </c>
       <c r="BL11" t="n">
-        <v>0.92</v>
+        <v>0.88</v>
       </c>
       <c r="BM11" t="n">
-        <v>0.54</v>
+        <v>0.52</v>
       </c>
       <c r="BN11" t="n">
-        <v>1.46</v>
+        <v>1.4</v>
       </c>
       <c r="BO11" t="n">
-        <v>1.04</v>
+        <v>1</v>
       </c>
       <c r="BP11" t="n">
-        <v>5.21</v>
+        <v>5.32</v>
       </c>
       <c r="BQ11" t="n">
-        <v>5.58</v>
+        <v>5.52</v>
       </c>
       <c r="BR11" t="n">
-        <v>91.67</v>
+        <v>88</v>
       </c>
       <c r="BS11" t="n">
-        <v>66.67</v>
+        <v>64</v>
       </c>
       <c r="BT11" t="n">
-        <v>37.5</v>
+        <v>36</v>
       </c>
       <c r="BU11" t="n">
-        <v>29.17</v>
+        <v>28</v>
       </c>
       <c r="BV11" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="BW11" t="n">
-        <v>8.33</v>
+        <v>8</v>
       </c>
       <c r="BX11" t="n">
-        <v>41.67</v>
+        <v>40</v>
       </c>
       <c r="BY11" t="n">
-        <v>1.93</v>
+        <v>1.91</v>
       </c>
       <c r="BZ11" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="CA11" t="n">
-        <v>3.62</v>
+        <v>3.61</v>
       </c>
       <c r="CB11" t="n">
-        <v>3.7</v>
+        <v>3.69</v>
       </c>
       <c r="CC11" t="n">
         <v>2.48</v>
@@ -5252,58 +5252,58 @@
         <v>1.33</v>
       </c>
       <c r="CF11" t="n">
-        <v>2.56</v>
+        <v>2.57</v>
       </c>
       <c r="CG11" t="n">
-        <v>3.06</v>
+        <v>3.04</v>
       </c>
       <c r="CH11" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="CI11" t="n">
-        <v>2.13</v>
+        <v>2.11</v>
       </c>
       <c r="CJ11" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="CK11" t="n">
         <v>1.48</v>
       </c>
       <c r="CL11" t="n">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="CM11" t="n">
         <v>2.52</v>
       </c>
       <c r="CN11" t="n">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="CO11" t="n">
         <v>1.24</v>
       </c>
       <c r="CP11" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="CQ11" t="n">
-        <v>2.94</v>
+        <v>2.96</v>
       </c>
       <c r="CR11" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="CS11" t="n">
-        <v>2.7</v>
+        <v>2.72</v>
       </c>
       <c r="CT11" t="n">
-        <v>3.19</v>
+        <v>3.17</v>
       </c>
       <c r="CU11" t="n">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="CV11" t="n">
-        <v>2.19</v>
+        <v>2.18</v>
       </c>
       <c r="CW11" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="CX11" t="n">
         <v>1.52</v>
@@ -5321,85 +5321,85 @@
         <v>1.27</v>
       </c>
       <c r="DC11" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="DD11" t="n">
-        <v>3.1</v>
+        <v>3.13</v>
       </c>
       <c r="DE11" t="n">
         <v>0.12</v>
       </c>
       <c r="DF11" t="n">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="DG11" t="n">
-        <v>3.33</v>
+        <v>3.28</v>
       </c>
       <c r="DH11" t="n">
-        <v>102.75</v>
+        <v>103.64</v>
       </c>
       <c r="DI11" t="n">
         <v>0</v>
       </c>
       <c r="DJ11" t="n">
-        <v>2.67</v>
+        <v>2.6</v>
       </c>
       <c r="DK11" t="n">
-        <v>6.38</v>
+        <v>6.44</v>
       </c>
       <c r="DL11" t="n">
-        <v>0.5</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="DM11" t="n">
-        <v>57.17</v>
+        <v>56.88</v>
       </c>
       <c r="DN11" t="n">
-        <v>1.12</v>
+        <v>1.08</v>
       </c>
       <c r="DO11" t="n">
-        <v>3.04</v>
+        <v>3.16</v>
       </c>
       <c r="DP11" t="n">
-        <v>13.92</v>
+        <v>13.96</v>
       </c>
       <c r="DQ11" t="n">
-        <v>10.92</v>
+        <v>10.84</v>
       </c>
       <c r="DR11" t="n">
-        <v>7.71</v>
+        <v>7.76</v>
       </c>
       <c r="DS11" t="n">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
       <c r="DT11" t="n">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
       <c r="DU11" t="n">
         <v>0</v>
       </c>
       <c r="DV11" t="n">
-        <v>53.62</v>
+        <v>54.16</v>
       </c>
       <c r="DW11" t="n">
         <v>0.12</v>
       </c>
       <c r="DX11" t="n">
-        <v>14.88</v>
+        <v>15.04</v>
       </c>
       <c r="DY11" t="n">
-        <v>10.21</v>
+        <v>10.36</v>
       </c>
       <c r="DZ11" t="n">
-        <v>4.67</v>
+        <v>4.68</v>
       </c>
       <c r="EA11" t="n">
-        <v>21.12</v>
+        <v>21.56</v>
       </c>
       <c r="EB11" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="EC11" t="n">
-        <v>2.5</v>
+        <v>2.44</v>
       </c>
     </row>
     <row r="12">
@@ -5409,10 +5409,10 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C12" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D12" t="n">
         <v>12</v>
@@ -5421,79 +5421,79 @@
         <v>0.08</v>
       </c>
       <c r="F12" t="n">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="G12" t="n">
-        <v>2.33</v>
+        <v>2.31</v>
       </c>
       <c r="H12" t="n">
-        <v>97.25</v>
+        <v>96.84999999999999</v>
       </c>
       <c r="I12" t="n">
         <v>0.08</v>
       </c>
       <c r="J12" t="n">
-        <v>2.17</v>
+        <v>2.15</v>
       </c>
       <c r="K12" t="n">
-        <v>4.75</v>
+        <v>4.69</v>
       </c>
       <c r="L12" t="n">
-        <v>0.58</v>
+        <v>0.54</v>
       </c>
       <c r="M12" t="n">
-        <v>44.83</v>
+        <v>44</v>
       </c>
       <c r="N12" t="n">
-        <v>0.83</v>
+        <v>0.85</v>
       </c>
       <c r="O12" t="n">
-        <v>2.33</v>
+        <v>2.31</v>
       </c>
       <c r="P12" t="n">
-        <v>12.08</v>
+        <v>12.38</v>
       </c>
       <c r="Q12" t="n">
-        <v>12.25</v>
+        <v>12.46</v>
       </c>
       <c r="R12" t="n">
-        <v>7.08</v>
+        <v>7</v>
       </c>
       <c r="S12" t="n">
-        <v>1.25</v>
+        <v>1.31</v>
       </c>
       <c r="T12" t="n">
-        <v>1.58</v>
+        <v>1.46</v>
       </c>
       <c r="U12" t="n">
-        <v>0.33</v>
+        <v>0.31</v>
       </c>
       <c r="V12" t="n">
-        <v>0.33</v>
+        <v>0.31</v>
       </c>
       <c r="W12" t="n">
         <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>50.17</v>
+        <v>50.31</v>
       </c>
       <c r="Y12" t="n">
         <v>0.08</v>
       </c>
       <c r="Z12" t="n">
-        <v>13.17</v>
+        <v>12.54</v>
       </c>
       <c r="AA12" t="n">
-        <v>7.92</v>
+        <v>7.62</v>
       </c>
       <c r="AB12" t="n">
-        <v>5.25</v>
+        <v>4.92</v>
       </c>
       <c r="AC12" t="n">
-        <v>20.83</v>
+        <v>21.31</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.53</v>
+        <v>1.46</v>
       </c>
       <c r="AE12" t="n">
         <v>2</v>
@@ -5580,49 +5580,49 @@
         <v>1.75</v>
       </c>
       <c r="BG12" t="n">
-        <v>2.25</v>
+        <v>2.24</v>
       </c>
       <c r="BH12" t="n">
-        <v>9.210000000000001</v>
+        <v>9.08</v>
       </c>
       <c r="BI12" t="n">
-        <v>2.25</v>
+        <v>2.24</v>
       </c>
       <c r="BJ12" t="n">
-        <v>0.71</v>
+        <v>0.68</v>
       </c>
       <c r="BK12" t="n">
-        <v>0.46</v>
+        <v>0.48</v>
       </c>
       <c r="BL12" t="n">
-        <v>0.54</v>
+        <v>0.52</v>
       </c>
       <c r="BM12" t="n">
-        <v>0.54</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="BN12" t="n">
         <v>1.08</v>
       </c>
       <c r="BO12" t="n">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="BP12" t="n">
-        <v>4</v>
+        <v>3.96</v>
       </c>
       <c r="BQ12" t="n">
-        <v>5.17</v>
+        <v>5.08</v>
       </c>
       <c r="BR12" t="n">
-        <v>95.83</v>
+        <v>96</v>
       </c>
       <c r="BS12" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="BT12" t="n">
-        <v>37.5</v>
+        <v>36</v>
       </c>
       <c r="BU12" t="n">
-        <v>16.67</v>
+        <v>16</v>
       </c>
       <c r="BV12" t="n">
         <v>0</v>
@@ -5631,13 +5631,13 @@
         <v>0</v>
       </c>
       <c r="BX12" t="n">
-        <v>45.83</v>
+        <v>44</v>
       </c>
       <c r="BY12" t="n">
-        <v>2.72</v>
+        <v>2.67</v>
       </c>
       <c r="BZ12" t="n">
-        <v>2.93</v>
+        <v>2.87</v>
       </c>
       <c r="CA12" t="n">
         <v>3.5</v>
@@ -5664,19 +5664,19 @@
         <v>1.44</v>
       </c>
       <c r="CI12" t="n">
-        <v>2.08</v>
+        <v>2.09</v>
       </c>
       <c r="CJ12" t="n">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="CK12" t="n">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="CL12" t="n">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="CM12" t="n">
-        <v>2.43</v>
+        <v>2.44</v>
       </c>
       <c r="CN12" t="n">
         <v>1.89</v>
@@ -5691,19 +5691,19 @@
         <v>3.08</v>
       </c>
       <c r="CR12" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="CS12" t="n">
-        <v>2.76</v>
+        <v>2.75</v>
       </c>
       <c r="CT12" t="n">
-        <v>3.13</v>
+        <v>3.14</v>
       </c>
       <c r="CU12" t="n">
         <v>1.47</v>
       </c>
       <c r="CV12" t="n">
-        <v>2.14</v>
+        <v>2.15</v>
       </c>
       <c r="CW12" t="n">
         <v>1.76</v>
@@ -5712,13 +5712,13 @@
         <v>1.58</v>
       </c>
       <c r="CY12" t="n">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="CZ12" t="n">
         <v>2.36</v>
       </c>
       <c r="DA12" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="DB12" t="n">
         <v>1.28</v>
@@ -5727,19 +5727,19 @@
         <v>1.92</v>
       </c>
       <c r="DD12" t="n">
-        <v>3.21</v>
+        <v>3.2</v>
       </c>
       <c r="DE12" t="n">
         <v>0.04</v>
       </c>
       <c r="DF12" t="n">
-        <v>1.34</v>
+        <v>1.32</v>
       </c>
       <c r="DG12" t="n">
-        <v>2.38</v>
+        <v>2.36</v>
       </c>
       <c r="DH12" t="n">
-        <v>96.45999999999999</v>
+        <v>96.28</v>
       </c>
       <c r="DI12" t="n">
         <v>0.04</v>
@@ -5751,25 +5751,25 @@
         <v>4.16</v>
       </c>
       <c r="DL12" t="n">
-        <v>0.42</v>
+        <v>0.4</v>
       </c>
       <c r="DM12" t="n">
-        <v>41.75</v>
+        <v>41.44</v>
       </c>
       <c r="DN12" t="n">
-        <v>0.62</v>
+        <v>0.64</v>
       </c>
       <c r="DO12" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="DP12" t="n">
-        <v>12.66</v>
+        <v>12.8</v>
       </c>
       <c r="DQ12" t="n">
-        <v>12.04</v>
+        <v>12.16</v>
       </c>
       <c r="DR12" t="n">
-        <v>7.29</v>
+        <v>7.24</v>
       </c>
       <c r="DS12" t="n">
         <v>0.2</v>
@@ -5781,25 +5781,25 @@
         <v>0</v>
       </c>
       <c r="DV12" t="n">
-        <v>48.96</v>
+        <v>49.08</v>
       </c>
       <c r="DW12" t="n">
         <v>0.08</v>
       </c>
       <c r="DX12" t="n">
-        <v>11.92</v>
+        <v>11.64</v>
       </c>
       <c r="DY12" t="n">
-        <v>7.5</v>
+        <v>7.36</v>
       </c>
       <c r="DZ12" t="n">
-        <v>4.42</v>
+        <v>4.28</v>
       </c>
       <c r="EA12" t="n">
-        <v>21.54</v>
+        <v>21.76</v>
       </c>
       <c r="EB12" t="n">
-        <v>1.37</v>
+        <v>1.34</v>
       </c>
       <c r="EC12" t="n">
         <v>1.88</v>
@@ -5812,94 +5812,94 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C13" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D13" t="n">
         <v>12</v>
       </c>
       <c r="E13" t="n">
-        <v>0.25</v>
+        <v>0.23</v>
       </c>
       <c r="F13" t="n">
-        <v>1.58</v>
+        <v>1.62</v>
       </c>
       <c r="G13" t="n">
-        <v>3.33</v>
+        <v>3.38</v>
       </c>
       <c r="H13" t="n">
-        <v>101.67</v>
+        <v>102.31</v>
       </c>
       <c r="I13" t="n">
         <v>0</v>
       </c>
       <c r="J13" t="n">
-        <v>2.25</v>
+        <v>2.31</v>
       </c>
       <c r="K13" t="n">
-        <v>5.08</v>
+        <v>5.23</v>
       </c>
       <c r="L13" t="n">
-        <v>0.25</v>
+        <v>0.31</v>
       </c>
       <c r="M13" t="n">
-        <v>53.08</v>
+        <v>55.15</v>
       </c>
       <c r="N13" t="n">
-        <v>0.5</v>
+        <v>0.54</v>
       </c>
       <c r="O13" t="n">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="P13" t="n">
-        <v>10.67</v>
+        <v>10.69</v>
       </c>
       <c r="Q13" t="n">
-        <v>11.83</v>
+        <v>11.77</v>
       </c>
       <c r="R13" t="n">
-        <v>6.75</v>
+        <v>6.46</v>
       </c>
       <c r="S13" t="n">
-        <v>1.08</v>
+        <v>1.15</v>
       </c>
       <c r="T13" t="n">
-        <v>1.42</v>
+        <v>1.54</v>
       </c>
       <c r="U13" t="n">
-        <v>0.17</v>
+        <v>0.23</v>
       </c>
       <c r="V13" t="n">
-        <v>0.17</v>
+        <v>0.23</v>
       </c>
       <c r="W13" t="n">
         <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>53</v>
+        <v>53.46</v>
       </c>
       <c r="Y13" t="n">
-        <v>0.17</v>
+        <v>0.15</v>
       </c>
       <c r="Z13" t="n">
-        <v>15.33</v>
+        <v>15.46</v>
       </c>
       <c r="AA13" t="n">
-        <v>10.67</v>
+        <v>10.62</v>
       </c>
       <c r="AB13" t="n">
-        <v>4.67</v>
+        <v>4.85</v>
       </c>
       <c r="AC13" t="n">
-        <v>21.67</v>
+        <v>22.77</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.68</v>
+        <v>1.71</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AF13" t="n">
         <v>0.08</v>
@@ -5983,70 +5983,70 @@
         <v>1.83</v>
       </c>
       <c r="BG13" t="n">
-        <v>2.62</v>
+        <v>2.72</v>
       </c>
       <c r="BH13" t="n">
-        <v>9.789999999999999</v>
+        <v>9.92</v>
       </c>
       <c r="BI13" t="n">
-        <v>2.62</v>
+        <v>2.72</v>
       </c>
       <c r="BJ13" t="n">
-        <v>0.67</v>
+        <v>0.72</v>
       </c>
       <c r="BK13" t="n">
-        <v>0.5</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="BL13" t="n">
-        <v>0.58</v>
+        <v>0.6</v>
       </c>
       <c r="BM13" t="n">
-        <v>0.88</v>
+        <v>0.84</v>
       </c>
       <c r="BN13" t="n">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="BO13" t="n">
-        <v>1.17</v>
+        <v>1.28</v>
       </c>
       <c r="BP13" t="n">
-        <v>4.04</v>
+        <v>4.08</v>
       </c>
       <c r="BQ13" t="n">
-        <v>5.75</v>
+        <v>5.84</v>
       </c>
       <c r="BR13" t="n">
         <v>100</v>
       </c>
       <c r="BS13" t="n">
-        <v>83.33</v>
+        <v>84</v>
       </c>
       <c r="BT13" t="n">
-        <v>54.17</v>
+        <v>56</v>
       </c>
       <c r="BU13" t="n">
-        <v>20.83</v>
+        <v>24</v>
       </c>
       <c r="BV13" t="n">
-        <v>4.17</v>
+        <v>8</v>
       </c>
       <c r="BW13" t="n">
         <v>0</v>
       </c>
       <c r="BX13" t="n">
-        <v>54.17</v>
+        <v>56</v>
       </c>
       <c r="BY13" t="n">
-        <v>2.27</v>
+        <v>2.23</v>
       </c>
       <c r="BZ13" t="n">
-        <v>2.35</v>
+        <v>2.31</v>
       </c>
       <c r="CA13" t="n">
-        <v>3.65</v>
+        <v>3.66</v>
       </c>
       <c r="CB13" t="n">
-        <v>3.77</v>
+        <v>3.78</v>
       </c>
       <c r="CC13" t="n">
         <v>3.71</v>
@@ -6070,19 +6070,19 @@
         <v>2.18</v>
       </c>
       <c r="CJ13" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="CK13" t="n">
         <v>1.46</v>
       </c>
       <c r="CL13" t="n">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="CM13" t="n">
-        <v>2.53</v>
+        <v>2.52</v>
       </c>
       <c r="CN13" t="n">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="CO13" t="n">
         <v>1.22</v>
@@ -6115,13 +6115,13 @@
         <v>1.54</v>
       </c>
       <c r="CY13" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="CZ13" t="n">
-        <v>2.44</v>
+        <v>2.43</v>
       </c>
       <c r="DA13" t="n">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="DB13" t="n">
         <v>1.24</v>
@@ -6130,82 +6130,82 @@
         <v>1.78</v>
       </c>
       <c r="DD13" t="n">
-        <v>2.87</v>
+        <v>2.88</v>
       </c>
       <c r="DE13" t="n">
         <v>0.16</v>
       </c>
       <c r="DF13" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="DG13" t="n">
-        <v>3.29</v>
+        <v>3.32</v>
       </c>
       <c r="DH13" t="n">
-        <v>98.92</v>
+        <v>99.36</v>
       </c>
       <c r="DI13" t="n">
         <v>0.08</v>
       </c>
       <c r="DJ13" t="n">
-        <v>2.04</v>
+        <v>2.08</v>
       </c>
       <c r="DK13" t="n">
-        <v>5.25</v>
+        <v>5.32</v>
       </c>
       <c r="DL13" t="n">
-        <v>0.34</v>
+        <v>0.36</v>
       </c>
       <c r="DM13" t="n">
-        <v>51.71</v>
+        <v>52.84</v>
       </c>
       <c r="DN13" t="n">
-        <v>0.62</v>
+        <v>0.64</v>
       </c>
       <c r="DO13" t="n">
-        <v>1.96</v>
+        <v>2</v>
       </c>
       <c r="DP13" t="n">
-        <v>11.54</v>
+        <v>11.52</v>
       </c>
       <c r="DQ13" t="n">
-        <v>11.38</v>
+        <v>11.36</v>
       </c>
       <c r="DR13" t="n">
-        <v>7.71</v>
+        <v>7.52</v>
       </c>
       <c r="DS13" t="n">
-        <v>0.25</v>
+        <v>0.28</v>
       </c>
       <c r="DT13" t="n">
-        <v>0.25</v>
+        <v>0.28</v>
       </c>
       <c r="DU13" t="n">
         <v>0</v>
       </c>
       <c r="DV13" t="n">
-        <v>53.25</v>
+        <v>53.48</v>
       </c>
       <c r="DW13" t="n">
         <v>0.08</v>
       </c>
       <c r="DX13" t="n">
-        <v>14.5</v>
+        <v>14.6</v>
       </c>
       <c r="DY13" t="n">
         <v>10</v>
       </c>
       <c r="DZ13" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="EA13" t="n">
-        <v>21.62</v>
+        <v>22.2</v>
       </c>
       <c r="EB13" t="n">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="EC13" t="n">
-        <v>1.88</v>
+        <v>1.92</v>
       </c>
     </row>
     <row r="14">
@@ -7424,13 +7424,13 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C17" t="n">
         <v>12</v>
       </c>
       <c r="D17" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
@@ -7517,49 +7517,49 @@
         <v>0.08</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.25</v>
+        <v>1.38</v>
       </c>
       <c r="AH17" t="n">
-        <v>2.17</v>
+        <v>2.31</v>
       </c>
       <c r="AI17" t="n">
-        <v>93.5</v>
+        <v>94.54000000000001</v>
       </c>
       <c r="AJ17" t="n">
         <v>0.08</v>
       </c>
       <c r="AK17" t="n">
-        <v>1.92</v>
+        <v>2.15</v>
       </c>
       <c r="AL17" t="n">
-        <v>4.17</v>
+        <v>4.31</v>
       </c>
       <c r="AM17" t="n">
-        <v>0.17</v>
+        <v>0.23</v>
       </c>
       <c r="AN17" t="n">
-        <v>47</v>
+        <v>46.69</v>
       </c>
       <c r="AO17" t="n">
-        <v>0.58</v>
+        <v>0.62</v>
       </c>
       <c r="AP17" t="n">
-        <v>1.42</v>
+        <v>1.46</v>
       </c>
       <c r="AQ17" t="n">
-        <v>12.17</v>
+        <v>12.15</v>
       </c>
       <c r="AR17" t="n">
         <v>10.92</v>
       </c>
       <c r="AS17" t="n">
-        <v>8.83</v>
+        <v>9.31</v>
       </c>
       <c r="AT17" t="n">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AU17" t="n">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
       <c r="AV17" t="n">
         <v>0.08</v>
@@ -7571,82 +7571,82 @@
         <v>0</v>
       </c>
       <c r="AY17" t="n">
-        <v>48</v>
+        <v>47.46</v>
       </c>
       <c r="AZ17" t="n">
-        <v>0.08</v>
+        <v>0.15</v>
       </c>
       <c r="BA17" t="n">
-        <v>10.5</v>
+        <v>10.62</v>
       </c>
       <c r="BB17" t="n">
-        <v>6.92</v>
+        <v>7.08</v>
       </c>
       <c r="BC17" t="n">
-        <v>3.58</v>
+        <v>3.54</v>
       </c>
       <c r="BD17" t="n">
-        <v>19.17</v>
+        <v>19.08</v>
       </c>
       <c r="BE17" t="n">
         <v>1.26</v>
       </c>
       <c r="BF17" t="n">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="BG17" t="n">
-        <v>2.79</v>
+        <v>2.88</v>
       </c>
       <c r="BH17" t="n">
-        <v>9.619999999999999</v>
+        <v>9.76</v>
       </c>
       <c r="BI17" t="n">
-        <v>2.79</v>
+        <v>2.88</v>
       </c>
       <c r="BJ17" t="n">
-        <v>0.71</v>
+        <v>0.76</v>
       </c>
       <c r="BK17" t="n">
-        <v>0.58</v>
+        <v>0.64</v>
       </c>
       <c r="BL17" t="n">
-        <v>0.83</v>
+        <v>0.84</v>
       </c>
       <c r="BM17" t="n">
-        <v>0.67</v>
+        <v>0.64</v>
       </c>
       <c r="BN17" t="n">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="BO17" t="n">
-        <v>1.29</v>
+        <v>1.4</v>
       </c>
       <c r="BP17" t="n">
-        <v>3.58</v>
+        <v>3.64</v>
       </c>
       <c r="BQ17" t="n">
-        <v>5.46</v>
+        <v>5.56</v>
       </c>
       <c r="BR17" t="n">
-        <v>91.67</v>
+        <v>92</v>
       </c>
       <c r="BS17" t="n">
-        <v>79.17</v>
+        <v>80</v>
       </c>
       <c r="BT17" t="n">
-        <v>45.83</v>
+        <v>48</v>
       </c>
       <c r="BU17" t="n">
-        <v>33.33</v>
+        <v>36</v>
       </c>
       <c r="BV17" t="n">
-        <v>20.83</v>
+        <v>24</v>
       </c>
       <c r="BW17" t="n">
-        <v>4.17</v>
+        <v>4</v>
       </c>
       <c r="BX17" t="n">
-        <v>62.5</v>
+        <v>64</v>
       </c>
       <c r="BY17" t="n">
         <v>2.94</v>
@@ -7655,16 +7655,16 @@
         <v>3.15</v>
       </c>
       <c r="CA17" t="n">
-        <v>3.75</v>
+        <v>3.76</v>
       </c>
       <c r="CB17" t="n">
         <v>3.83</v>
       </c>
       <c r="CC17" t="n">
-        <v>4.42</v>
+        <v>4.44</v>
       </c>
       <c r="CD17" t="n">
-        <v>4.93</v>
+        <v>4.9</v>
       </c>
       <c r="CE17" t="n">
         <v>1.3</v>
@@ -7673,7 +7673,7 @@
         <v>2.47</v>
       </c>
       <c r="CG17" t="n">
-        <v>3.3</v>
+        <v>3.29</v>
       </c>
       <c r="CH17" t="n">
         <v>1.52</v>
@@ -7685,16 +7685,16 @@
         <v>1.64</v>
       </c>
       <c r="CK17" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="CL17" t="n">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="CM17" t="n">
-        <v>2.66</v>
+        <v>2.64</v>
       </c>
       <c r="CN17" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="CO17" t="n">
         <v>1.21</v>
@@ -7703,7 +7703,7 @@
         <v>1.71</v>
       </c>
       <c r="CQ17" t="n">
-        <v>2.71</v>
+        <v>2.72</v>
       </c>
       <c r="CR17" t="n">
         <v>1.35</v>
@@ -7718,7 +7718,7 @@
         <v>1.53</v>
       </c>
       <c r="CV17" t="n">
-        <v>2.3</v>
+        <v>2.29</v>
       </c>
       <c r="CW17" t="n">
         <v>1.68</v>
@@ -7727,13 +7727,13 @@
         <v>1.53</v>
       </c>
       <c r="CY17" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="CZ17" t="n">
-        <v>2.47</v>
+        <v>2.45</v>
       </c>
       <c r="DA17" t="n">
-        <v>2.05</v>
+        <v>2.03</v>
       </c>
       <c r="DB17" t="n">
         <v>1.24</v>
@@ -7742,49 +7742,49 @@
         <v>1.77</v>
       </c>
       <c r="DD17" t="n">
-        <v>2.86</v>
+        <v>2.87</v>
       </c>
       <c r="DE17" t="n">
         <v>0.04</v>
       </c>
       <c r="DF17" t="n">
-        <v>1.08</v>
+        <v>1.16</v>
       </c>
       <c r="DG17" t="n">
-        <v>2.34</v>
+        <v>2.4</v>
       </c>
       <c r="DH17" t="n">
-        <v>93.84</v>
+        <v>94.36</v>
       </c>
       <c r="DI17" t="n">
         <v>0.08</v>
       </c>
       <c r="DJ17" t="n">
-        <v>1.71</v>
+        <v>1.84</v>
       </c>
       <c r="DK17" t="n">
-        <v>4.21</v>
+        <v>4.28</v>
       </c>
       <c r="DL17" t="n">
-        <v>0.17</v>
+        <v>0.2</v>
       </c>
       <c r="DM17" t="n">
-        <v>45.79</v>
+        <v>45.68</v>
       </c>
       <c r="DN17" t="n">
-        <v>0.54</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="DO17" t="n">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
       <c r="DP17" t="n">
-        <v>11.04</v>
+        <v>11.08</v>
       </c>
       <c r="DQ17" t="n">
-        <v>11.88</v>
+        <v>11.84</v>
       </c>
       <c r="DR17" t="n">
-        <v>9.199999999999999</v>
+        <v>9.44</v>
       </c>
       <c r="DS17" t="n">
         <v>0.2</v>
@@ -7796,28 +7796,28 @@
         <v>0</v>
       </c>
       <c r="DV17" t="n">
-        <v>47.38</v>
+        <v>47.12</v>
       </c>
       <c r="DW17" t="n">
-        <v>0.08</v>
+        <v>0.12</v>
       </c>
       <c r="DX17" t="n">
-        <v>11.71</v>
+        <v>11.72</v>
       </c>
       <c r="DY17" t="n">
-        <v>7.58</v>
+        <v>7.64</v>
       </c>
       <c r="DZ17" t="n">
-        <v>4.12</v>
+        <v>4.08</v>
       </c>
       <c r="EA17" t="n">
-        <v>20</v>
+        <v>19.92</v>
       </c>
       <c r="EB17" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="EC17" t="n">
-        <v>1.54</v>
+        <v>1.6</v>
       </c>
     </row>
   </sheetData>

--- a/data/teams/leagues/Averages_Belgium_Pro_League_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Belgium_Pro_League_2025-2026.xlsx
@@ -3944,7 +3944,7 @@
         <v>0</v>
       </c>
       <c r="AY8" t="n">
-        <v>47</v>
+        <v>47.08</v>
       </c>
       <c r="AZ8" t="n">
         <v>0.08</v>
@@ -4169,7 +4169,7 @@
         <v>0</v>
       </c>
       <c r="DV8" t="n">
-        <v>49.36</v>
+        <v>49.4</v>
       </c>
       <c r="DW8" t="n">
         <v>0.08</v>
@@ -5475,7 +5475,7 @@
         <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>50.31</v>
+        <v>50.23</v>
       </c>
       <c r="Y12" t="n">
         <v>0.08</v>
@@ -5781,7 +5781,7 @@
         <v>0</v>
       </c>
       <c r="DV12" t="n">
-        <v>49.08</v>
+        <v>49.04</v>
       </c>
       <c r="DW12" t="n">
         <v>0.08</v>

--- a/data/teams/leagues/Averages_Belgium_Pro_League_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Belgium_Pro_League_2025-2026.xlsx
@@ -645,7 +645,7 @@
     <col width="9.6" customWidth="1" min="73" max="73"/>
     <col width="9.6" customWidth="1" min="74" max="74"/>
     <col width="9.6" customWidth="1" min="75" max="75"/>
-    <col width="7.199999999999999" customWidth="1" min="76" max="76"/>
+    <col width="8.4" customWidth="1" min="76" max="76"/>
     <col width="18" customWidth="1" min="77" max="77"/>
     <col width="27.6" customWidth="1" min="78" max="78"/>
     <col width="18" customWidth="1" min="79" max="79"/>
@@ -1379,13 +1379,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C2" t="n">
         <v>13</v>
       </c>
       <c r="D2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
@@ -1469,139 +1469,139 @@
         <v>1.23</v>
       </c>
       <c r="AF2" t="n">
-        <v>0.17</v>
+        <v>0.15</v>
       </c>
       <c r="AG2" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>102.69</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>3</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>4.85</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>49.46</v>
+      </c>
+      <c r="AO2" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AP2" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AQ2" t="n">
+        <v>12.23</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>11.38</v>
+      </c>
+      <c r="AS2" t="n">
+        <v>7.54</v>
+      </c>
+      <c r="AT2" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="AU2" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AV2" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="AW2" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="AX2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY2" t="n">
+        <v>46</v>
+      </c>
+      <c r="AZ2" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="BA2" t="n">
+        <v>12.69</v>
+      </c>
+      <c r="BB2" t="n">
+        <v>9.08</v>
+      </c>
+      <c r="BC2" t="n">
+        <v>3.62</v>
+      </c>
+      <c r="BD2" t="n">
+        <v>21.85</v>
+      </c>
+      <c r="BE2" t="n">
         <v>1.42</v>
       </c>
-      <c r="AH2" t="n">
-        <v>2.17</v>
-      </c>
-      <c r="AI2" t="n">
-        <v>100.25</v>
-      </c>
-      <c r="AJ2" t="n">
-        <v>0.17</v>
-      </c>
-      <c r="AK2" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="AL2" t="n">
-        <v>4.42</v>
-      </c>
-      <c r="AM2" t="n">
+      <c r="BF2" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="BG2" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="BH2" t="n">
+        <v>10.12</v>
+      </c>
+      <c r="BI2" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="BJ2" t="n">
         <v>0.58</v>
-      </c>
-      <c r="AN2" t="n">
-        <v>48.08</v>
-      </c>
-      <c r="AO2" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AP2" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AQ2" t="n">
-        <v>12.42</v>
-      </c>
-      <c r="AR2" t="n">
-        <v>11.83</v>
-      </c>
-      <c r="AS2" t="n">
-        <v>7.83</v>
-      </c>
-      <c r="AT2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AU2" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AV2" t="n">
-        <v>0.17</v>
-      </c>
-      <c r="AW2" t="n">
-        <v>0.17</v>
-      </c>
-      <c r="AX2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY2" t="n">
-        <v>45.25</v>
-      </c>
-      <c r="AZ2" t="n">
-        <v>0.17</v>
-      </c>
-      <c r="BA2" t="n">
-        <v>11.83</v>
-      </c>
-      <c r="BB2" t="n">
-        <v>8.25</v>
-      </c>
-      <c r="BC2" t="n">
-        <v>3.58</v>
-      </c>
-      <c r="BD2" t="n">
-        <v>21.25</v>
-      </c>
-      <c r="BE2" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="BF2" t="n">
-        <v>2.58</v>
-      </c>
-      <c r="BG2" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="BH2" t="n">
-        <v>9.960000000000001</v>
-      </c>
-      <c r="BI2" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="BJ2" t="n">
-        <v>0.6</v>
       </c>
       <c r="BK2" t="n">
         <v>1.04</v>
       </c>
       <c r="BL2" t="n">
-        <v>0.6</v>
+        <v>0.58</v>
       </c>
       <c r="BM2" t="n">
-        <v>0.68</v>
+        <v>0.65</v>
       </c>
       <c r="BN2" t="n">
-        <v>1.28</v>
+        <v>1.23</v>
       </c>
       <c r="BO2" t="n">
-        <v>1.64</v>
+        <v>1.62</v>
       </c>
       <c r="BP2" t="n">
-        <v>4.4</v>
+        <v>4.38</v>
       </c>
       <c r="BQ2" t="n">
-        <v>5.52</v>
+        <v>5.69</v>
       </c>
       <c r="BR2" t="n">
-        <v>92</v>
+        <v>92.31</v>
       </c>
       <c r="BS2" t="n">
-        <v>92</v>
+        <v>88.45999999999999</v>
       </c>
       <c r="BT2" t="n">
-        <v>48</v>
+        <v>46.15</v>
       </c>
       <c r="BU2" t="n">
-        <v>28</v>
+        <v>26.92</v>
       </c>
       <c r="BV2" t="n">
-        <v>20</v>
+        <v>19.23</v>
       </c>
       <c r="BW2" t="n">
-        <v>8</v>
+        <v>7.69</v>
       </c>
       <c r="BX2" t="n">
-        <v>64</v>
+        <v>61.54</v>
       </c>
       <c r="BY2" t="n">
         <v>2.51</v>
@@ -1610,16 +1610,16 @@
         <v>2.65</v>
       </c>
       <c r="CA2" t="n">
-        <v>3.55</v>
+        <v>3.54</v>
       </c>
       <c r="CB2" t="n">
         <v>3.68</v>
       </c>
       <c r="CC2" t="n">
-        <v>3.44</v>
+        <v>3.38</v>
       </c>
       <c r="CD2" t="n">
-        <v>3.54</v>
+        <v>3.52</v>
       </c>
       <c r="CE2" t="n">
         <v>1.32</v>
@@ -1634,7 +1634,7 @@
         <v>1.48</v>
       </c>
       <c r="CI2" t="n">
-        <v>2.17</v>
+        <v>2.18</v>
       </c>
       <c r="CJ2" t="n">
         <v>1.65</v>
@@ -1646,7 +1646,7 @@
         <v>1.81</v>
       </c>
       <c r="CM2" t="n">
-        <v>2.6</v>
+        <v>2.59</v>
       </c>
       <c r="CN2" t="n">
         <v>2.03</v>
@@ -1655,16 +1655,16 @@
         <v>1.22</v>
       </c>
       <c r="CP2" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="CQ2" t="n">
-        <v>2.88</v>
+        <v>2.86</v>
       </c>
       <c r="CR2" t="n">
         <v>1.36</v>
       </c>
       <c r="CS2" t="n">
-        <v>2.63</v>
+        <v>2.62</v>
       </c>
       <c r="CT2" t="n">
         <v>3.19</v>
@@ -1673,10 +1673,10 @@
         <v>1.51</v>
       </c>
       <c r="CV2" t="n">
-        <v>2.29</v>
+        <v>2.3</v>
       </c>
       <c r="CW2" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="CX2" t="n">
         <v>1.5</v>
@@ -1703,76 +1703,76 @@
         <v>0.08</v>
       </c>
       <c r="DF2" t="n">
-        <v>1.16</v>
+        <v>1.23</v>
       </c>
       <c r="DG2" t="n">
-        <v>2.36</v>
+        <v>2.5</v>
       </c>
       <c r="DH2" t="n">
-        <v>104.08</v>
+        <v>105.15</v>
       </c>
       <c r="DI2" t="n">
         <v>0.12</v>
       </c>
       <c r="DJ2" t="n">
-        <v>2.16</v>
+        <v>2.23</v>
       </c>
       <c r="DK2" t="n">
-        <v>4.44</v>
+        <v>4.66</v>
       </c>
       <c r="DL2" t="n">
-        <v>0.48</v>
+        <v>0.5</v>
       </c>
       <c r="DM2" t="n">
-        <v>48.56</v>
+        <v>49.23</v>
       </c>
       <c r="DN2" t="n">
         <v>0.88</v>
       </c>
       <c r="DO2" t="n">
-        <v>2.08</v>
+        <v>2.15</v>
       </c>
       <c r="DP2" t="n">
-        <v>10.68</v>
+        <v>10.66</v>
       </c>
       <c r="DQ2" t="n">
-        <v>12.76</v>
+        <v>12.5</v>
       </c>
       <c r="DR2" t="n">
-        <v>7.2</v>
+        <v>7.08</v>
       </c>
       <c r="DS2" t="n">
-        <v>0.32</v>
+        <v>0.31</v>
       </c>
       <c r="DT2" t="n">
-        <v>0.32</v>
+        <v>0.31</v>
       </c>
       <c r="DU2" t="n">
         <v>0</v>
       </c>
       <c r="DV2" t="n">
-        <v>47</v>
+        <v>47.31</v>
       </c>
       <c r="DW2" t="n">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
       <c r="DX2" t="n">
-        <v>13</v>
+        <v>13.38</v>
       </c>
       <c r="DY2" t="n">
-        <v>8.84</v>
+        <v>9.23</v>
       </c>
       <c r="DZ2" t="n">
         <v>4.16</v>
       </c>
       <c r="EA2" t="n">
-        <v>22.32</v>
+        <v>22.58</v>
       </c>
       <c r="EB2" t="n">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="EC2" t="n">
-        <v>1.88</v>
+        <v>1.96</v>
       </c>
     </row>
     <row r="3">
@@ -1782,10 +1782,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C3" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D3" t="n">
         <v>13</v>
@@ -1794,82 +1794,82 @@
         <v>0.08</v>
       </c>
       <c r="F3" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="G3" t="n">
+        <v>3.92</v>
+      </c>
+      <c r="H3" t="n">
+        <v>114.23</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J3" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="K3" t="n">
+        <v>7.23</v>
+      </c>
+      <c r="L3" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="M3" t="n">
+        <v>66</v>
+      </c>
+      <c r="N3" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="O3" t="n">
+        <v>3.31</v>
+      </c>
+      <c r="P3" t="n">
+        <v>9.380000000000001</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>12.08</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6.38</v>
+      </c>
+      <c r="S3" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="T3" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="U3" t="n">
+        <v>0</v>
+      </c>
+      <c r="V3" t="n">
+        <v>0</v>
+      </c>
+      <c r="W3" t="n">
+        <v>0</v>
+      </c>
+      <c r="X3" t="n">
+        <v>65.54000000000001</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>18.08</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>12.08</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>6</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>22.92</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="AE3" t="n">
         <v>1</v>
-      </c>
-      <c r="G3" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="H3" t="n">
-        <v>115.58</v>
-      </c>
-      <c r="I3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J3" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="K3" t="n">
-        <v>6.83</v>
-      </c>
-      <c r="L3" t="n">
-        <v>0.83</v>
-      </c>
-      <c r="M3" t="n">
-        <v>65.17</v>
-      </c>
-      <c r="N3" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="O3" t="n">
-        <v>3.08</v>
-      </c>
-      <c r="P3" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>11.92</v>
-      </c>
-      <c r="R3" t="n">
-        <v>6.33</v>
-      </c>
-      <c r="S3" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="T3" t="n">
-        <v>2.17</v>
-      </c>
-      <c r="U3" t="n">
-        <v>0</v>
-      </c>
-      <c r="V3" t="n">
-        <v>0</v>
-      </c>
-      <c r="W3" t="n">
-        <v>0</v>
-      </c>
-      <c r="X3" t="n">
-        <v>65.67</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>0.17</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>17.83</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>12.17</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>5.67</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>22.83</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>1.99</v>
-      </c>
-      <c r="AE3" t="n">
-        <v>1.08</v>
       </c>
       <c r="AF3" t="n">
         <v>0.08</v>
@@ -1956,67 +1956,67 @@
         <v>3.08</v>
       </c>
       <c r="BH3" t="n">
-        <v>10.56</v>
+        <v>10.77</v>
       </c>
       <c r="BI3" t="n">
         <v>3.08</v>
       </c>
       <c r="BJ3" t="n">
-        <v>0.8</v>
+        <v>0.77</v>
       </c>
       <c r="BK3" t="n">
-        <v>0.48</v>
+        <v>0.46</v>
       </c>
       <c r="BL3" t="n">
-        <v>0.84</v>
+        <v>0.88</v>
       </c>
       <c r="BM3" t="n">
         <v>0.96</v>
       </c>
       <c r="BN3" t="n">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="BO3" t="n">
-        <v>1.28</v>
+        <v>1.23</v>
       </c>
       <c r="BP3" t="n">
-        <v>4.68</v>
+        <v>4.77</v>
       </c>
       <c r="BQ3" t="n">
-        <v>5.88</v>
+        <v>6</v>
       </c>
       <c r="BR3" t="n">
         <v>100</v>
       </c>
       <c r="BS3" t="n">
-        <v>64</v>
+        <v>65.38</v>
       </c>
       <c r="BT3" t="n">
-        <v>52</v>
+        <v>53.85</v>
       </c>
       <c r="BU3" t="n">
-        <v>24</v>
+        <v>23.08</v>
       </c>
       <c r="BV3" t="n">
-        <v>24</v>
+        <v>23.08</v>
       </c>
       <c r="BW3" t="n">
-        <v>16</v>
+        <v>15.38</v>
       </c>
       <c r="BX3" t="n">
-        <v>52</v>
+        <v>53.85</v>
       </c>
       <c r="BY3" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="BZ3" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="CA3" t="n">
-        <v>4.45</v>
+        <v>4.46</v>
       </c>
       <c r="CB3" t="n">
-        <v>4.74</v>
+        <v>4.77</v>
       </c>
       <c r="CC3" t="n">
         <v>1.87</v>
@@ -2046,7 +2046,7 @@
         <v>1.48</v>
       </c>
       <c r="CL3" t="n">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="CM3" t="n">
         <v>2.51</v>
@@ -2067,7 +2067,7 @@
         <v>1.34</v>
       </c>
       <c r="CS3" t="n">
-        <v>2.34</v>
+        <v>2.33</v>
       </c>
       <c r="CT3" t="n">
         <v>3.24</v>
@@ -2106,43 +2106,43 @@
         <v>0.08</v>
       </c>
       <c r="DF3" t="n">
-        <v>1.12</v>
+        <v>1.08</v>
       </c>
       <c r="DG3" t="n">
-        <v>3.68</v>
+        <v>3.77</v>
       </c>
       <c r="DH3" t="n">
-        <v>109.72</v>
+        <v>109.27</v>
       </c>
       <c r="DI3" t="n">
         <v>0</v>
       </c>
       <c r="DJ3" t="n">
-        <v>1.56</v>
+        <v>1.5</v>
       </c>
       <c r="DK3" t="n">
-        <v>6.4</v>
+        <v>6.62</v>
       </c>
       <c r="DL3" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.62</v>
       </c>
       <c r="DM3" t="n">
-        <v>60.04</v>
+        <v>60.66</v>
       </c>
       <c r="DN3" t="n">
-        <v>0.36</v>
+        <v>0.34</v>
       </c>
       <c r="DO3" t="n">
-        <v>2.72</v>
+        <v>2.84</v>
       </c>
       <c r="DP3" t="n">
-        <v>9.640000000000001</v>
+        <v>9.57</v>
       </c>
       <c r="DQ3" t="n">
-        <v>11.6</v>
+        <v>11.7</v>
       </c>
       <c r="DR3" t="n">
-        <v>7.36</v>
+        <v>7.34</v>
       </c>
       <c r="DS3" t="n">
         <v>0</v>
@@ -2154,28 +2154,28 @@
         <v>0</v>
       </c>
       <c r="DV3" t="n">
-        <v>62.88</v>
+        <v>62.92</v>
       </c>
       <c r="DW3" t="n">
         <v>0.08</v>
       </c>
       <c r="DX3" t="n">
-        <v>16.08</v>
+        <v>16.27</v>
       </c>
       <c r="DY3" t="n">
-        <v>10.72</v>
+        <v>10.73</v>
       </c>
       <c r="DZ3" t="n">
-        <v>5.36</v>
+        <v>5.54</v>
       </c>
       <c r="EA3" t="n">
-        <v>20.72</v>
+        <v>20.85</v>
       </c>
       <c r="EB3" t="n">
-        <v>1.82</v>
+        <v>1.86</v>
       </c>
       <c r="EC3" t="n">
-        <v>1.4</v>
+        <v>1.34</v>
       </c>
     </row>
     <row r="4">
@@ -2185,61 +2185,61 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C4" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D4" t="n">
         <v>13</v>
       </c>
       <c r="E4" t="n">
-        <v>0</v>
+        <v>0.08</v>
       </c>
       <c r="F4" t="n">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="G4" t="n">
-        <v>1.42</v>
+        <v>1.62</v>
       </c>
       <c r="H4" t="n">
-        <v>89.33</v>
+        <v>88.23</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.17</v>
+        <v>-0.15</v>
       </c>
       <c r="J4" t="n">
-        <v>1.83</v>
+        <v>1.92</v>
       </c>
       <c r="K4" t="n">
-        <v>3.42</v>
+        <v>3.46</v>
       </c>
       <c r="L4" t="n">
         <v>0.08</v>
       </c>
       <c r="M4" t="n">
-        <v>47.83</v>
+        <v>47.23</v>
       </c>
       <c r="N4" t="n">
-        <v>0.5</v>
+        <v>0.46</v>
       </c>
       <c r="O4" t="n">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="P4" t="n">
-        <v>10.58</v>
+        <v>10.85</v>
       </c>
       <c r="Q4" t="n">
-        <v>11.17</v>
+        <v>11</v>
       </c>
       <c r="R4" t="n">
-        <v>10.33</v>
+        <v>10.15</v>
       </c>
       <c r="S4" t="n">
-        <v>1.58</v>
+        <v>1.77</v>
       </c>
       <c r="T4" t="n">
-        <v>0.67</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="U4" t="n">
         <v>0.08</v>
@@ -2251,28 +2251,28 @@
         <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>50</v>
+        <v>49.15</v>
       </c>
       <c r="Y4" t="n">
         <v>0</v>
       </c>
       <c r="Z4" t="n">
-        <v>10.58</v>
+        <v>10.62</v>
       </c>
       <c r="AA4" t="n">
-        <v>7.25</v>
+        <v>7.23</v>
       </c>
       <c r="AB4" t="n">
-        <v>3.33</v>
+        <v>3.38</v>
       </c>
       <c r="AC4" t="n">
-        <v>22.83</v>
+        <v>22.46</v>
       </c>
       <c r="AD4" t="n">
         <v>1.25</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.83</v>
+        <v>1.92</v>
       </c>
       <c r="AF4" t="n">
         <v>0.23</v>
@@ -2356,70 +2356,70 @@
         <v>2.23</v>
       </c>
       <c r="BG4" t="n">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="BH4" t="n">
-        <v>8.720000000000001</v>
+        <v>8.880000000000001</v>
       </c>
       <c r="BI4" t="n">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="BJ4" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.58</v>
       </c>
       <c r="BK4" t="n">
-        <v>0.36</v>
+        <v>0.42</v>
       </c>
       <c r="BL4" t="n">
-        <v>0.6</v>
+        <v>0.58</v>
       </c>
       <c r="BM4" t="n">
-        <v>0.88</v>
+        <v>0.92</v>
       </c>
       <c r="BN4" t="n">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="BO4" t="n">
-        <v>0.92</v>
+        <v>1</v>
       </c>
       <c r="BP4" t="n">
         <v>3.92</v>
       </c>
       <c r="BQ4" t="n">
-        <v>4.28</v>
+        <v>4.46</v>
       </c>
       <c r="BR4" t="n">
-        <v>88</v>
+        <v>88.45999999999999</v>
       </c>
       <c r="BS4" t="n">
-        <v>68</v>
+        <v>69.23</v>
       </c>
       <c r="BT4" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="BU4" t="n">
-        <v>24</v>
+        <v>26.92</v>
       </c>
       <c r="BV4" t="n">
-        <v>8</v>
+        <v>11.54</v>
       </c>
       <c r="BW4" t="n">
-        <v>4</v>
+        <v>3.85</v>
       </c>
       <c r="BX4" t="n">
-        <v>56</v>
+        <v>57.69</v>
       </c>
       <c r="BY4" t="n">
-        <v>3.41</v>
+        <v>3.42</v>
       </c>
       <c r="BZ4" t="n">
-        <v>3.57</v>
+        <v>3.55</v>
       </c>
       <c r="CA4" t="n">
         <v>3.65</v>
       </c>
       <c r="CB4" t="n">
-        <v>3.79</v>
+        <v>3.78</v>
       </c>
       <c r="CC4" t="n">
         <v>4.56</v>
@@ -2434,13 +2434,13 @@
         <v>2.62</v>
       </c>
       <c r="CG4" t="n">
-        <v>3.05</v>
+        <v>3.06</v>
       </c>
       <c r="CH4" t="n">
         <v>1.45</v>
       </c>
       <c r="CI4" t="n">
-        <v>2.02</v>
+        <v>2.03</v>
       </c>
       <c r="CJ4" t="n">
         <v>1.74</v>
@@ -2464,10 +2464,10 @@
         <v>1.86</v>
       </c>
       <c r="CQ4" t="n">
-        <v>3.11</v>
+        <v>3.1</v>
       </c>
       <c r="CR4" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="CS4" t="n">
         <v>2.76</v>
@@ -2485,16 +2485,16 @@
         <v>1.77</v>
       </c>
       <c r="CX4" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="CY4" t="n">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="CZ4" t="n">
-        <v>2.37</v>
+        <v>2.36</v>
       </c>
       <c r="DA4" t="n">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="DB4" t="n">
         <v>1.28</v>
@@ -2506,46 +2506,46 @@
         <v>3.19</v>
       </c>
       <c r="DE4" t="n">
-        <v>0.12</v>
+        <v>0.16</v>
       </c>
       <c r="DF4" t="n">
-        <v>1.48</v>
+        <v>1.54</v>
       </c>
       <c r="DG4" t="n">
-        <v>1.56</v>
+        <v>1.66</v>
       </c>
       <c r="DH4" t="n">
-        <v>88.88</v>
+        <v>88.34999999999999</v>
       </c>
       <c r="DI4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DJ4" t="n">
-        <v>2.28</v>
+        <v>2.31</v>
       </c>
       <c r="DK4" t="n">
-        <v>3.52</v>
+        <v>3.54</v>
       </c>
       <c r="DL4" t="n">
         <v>0.08</v>
       </c>
       <c r="DM4" t="n">
-        <v>43.8</v>
+        <v>43.66</v>
       </c>
       <c r="DN4" t="n">
-        <v>0.72</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="DO4" t="n">
-        <v>1.64</v>
+        <v>1.58</v>
       </c>
       <c r="DP4" t="n">
-        <v>11.08</v>
+        <v>11.19</v>
       </c>
       <c r="DQ4" t="n">
-        <v>11.36</v>
+        <v>11.27</v>
       </c>
       <c r="DR4" t="n">
-        <v>10.36</v>
+        <v>10.26</v>
       </c>
       <c r="DS4" t="n">
         <v>0.12</v>
@@ -2557,13 +2557,13 @@
         <v>0</v>
       </c>
       <c r="DV4" t="n">
-        <v>47.32</v>
+        <v>47</v>
       </c>
       <c r="DW4" t="n">
         <v>0.16</v>
       </c>
       <c r="DX4" t="n">
-        <v>10.8</v>
+        <v>10.81</v>
       </c>
       <c r="DY4" t="n">
         <v>6.96</v>
@@ -2572,13 +2572,13 @@
         <v>3.84</v>
       </c>
       <c r="EA4" t="n">
-        <v>21.92</v>
+        <v>21.77</v>
       </c>
       <c r="EB4" t="n">
         <v>1.27</v>
       </c>
       <c r="EC4" t="n">
-        <v>2.04</v>
+        <v>2.08</v>
       </c>
     </row>
     <row r="5">
@@ -2588,61 +2588,61 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C5" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D5" t="n">
         <v>13</v>
       </c>
       <c r="E5" t="n">
-        <v>0.25</v>
+        <v>0.23</v>
       </c>
       <c r="F5" t="n">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="G5" t="n">
-        <v>2.75</v>
+        <v>2.85</v>
       </c>
       <c r="H5" t="n">
-        <v>106.17</v>
+        <v>103.54</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="K5" t="n">
-        <v>5.08</v>
+        <v>5</v>
       </c>
       <c r="L5" t="n">
-        <v>0.42</v>
+        <v>0.38</v>
       </c>
       <c r="M5" t="n">
-        <v>54</v>
+        <v>52.77</v>
       </c>
       <c r="N5" t="n">
-        <v>0.5</v>
+        <v>0.46</v>
       </c>
       <c r="O5" t="n">
-        <v>2.33</v>
+        <v>2.15</v>
       </c>
       <c r="P5" t="n">
-        <v>11.08</v>
+        <v>10.77</v>
       </c>
       <c r="Q5" t="n">
-        <v>10.92</v>
+        <v>10.85</v>
       </c>
       <c r="R5" t="n">
-        <v>8.08</v>
+        <v>8.380000000000001</v>
       </c>
       <c r="S5" t="n">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="T5" t="n">
-        <v>1.83</v>
+        <v>1.69</v>
       </c>
       <c r="U5" t="n">
         <v>0.08</v>
@@ -2654,28 +2654,28 @@
         <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>55.33</v>
+        <v>54.54</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.08</v>
+        <v>0.15</v>
       </c>
       <c r="Z5" t="n">
-        <v>16.25</v>
+        <v>15.38</v>
       </c>
       <c r="AA5" t="n">
-        <v>12</v>
+        <v>11.38</v>
       </c>
       <c r="AB5" t="n">
-        <v>4.25</v>
+        <v>4</v>
       </c>
       <c r="AC5" t="n">
-        <v>19.67</v>
+        <v>20.08</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.72</v>
+        <v>1.63</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.58</v>
+        <v>1.46</v>
       </c>
       <c r="AF5" t="n">
         <v>0.08</v>
@@ -2759,70 +2759,70 @@
         <v>1.69</v>
       </c>
       <c r="BG5" t="n">
-        <v>3.12</v>
+        <v>3.04</v>
       </c>
       <c r="BH5" t="n">
-        <v>10.44</v>
+        <v>10.58</v>
       </c>
       <c r="BI5" t="n">
-        <v>3.12</v>
+        <v>3.04</v>
       </c>
       <c r="BJ5" t="n">
-        <v>0.76</v>
+        <v>0.73</v>
       </c>
       <c r="BK5" t="n">
-        <v>0.6</v>
+        <v>0.62</v>
       </c>
       <c r="BL5" t="n">
-        <v>1</v>
+        <v>0.96</v>
       </c>
       <c r="BM5" t="n">
-        <v>0.76</v>
+        <v>0.73</v>
       </c>
       <c r="BN5" t="n">
-        <v>1.76</v>
+        <v>1.69</v>
       </c>
       <c r="BO5" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="BP5" t="n">
-        <v>4.24</v>
+        <v>4.23</v>
       </c>
       <c r="BQ5" t="n">
-        <v>6.2</v>
+        <v>6.35</v>
       </c>
       <c r="BR5" t="n">
-        <v>96</v>
+        <v>96.15000000000001</v>
       </c>
       <c r="BS5" t="n">
-        <v>88</v>
+        <v>84.62</v>
       </c>
       <c r="BT5" t="n">
-        <v>60</v>
+        <v>57.69</v>
       </c>
       <c r="BU5" t="n">
-        <v>40</v>
+        <v>38.46</v>
       </c>
       <c r="BV5" t="n">
-        <v>20</v>
+        <v>19.23</v>
       </c>
       <c r="BW5" t="n">
-        <v>8</v>
+        <v>7.69</v>
       </c>
       <c r="BX5" t="n">
-        <v>64</v>
+        <v>61.54</v>
       </c>
       <c r="BY5" t="n">
-        <v>2.65</v>
+        <v>2.61</v>
       </c>
       <c r="BZ5" t="n">
-        <v>2.76</v>
+        <v>2.72</v>
       </c>
       <c r="CA5" t="n">
-        <v>3.58</v>
+        <v>3.57</v>
       </c>
       <c r="CB5" t="n">
-        <v>3.75</v>
+        <v>3.74</v>
       </c>
       <c r="CC5" t="n">
         <v>3.6</v>
@@ -2843,37 +2843,37 @@
         <v>1.5</v>
       </c>
       <c r="CI5" t="n">
-        <v>2.2</v>
+        <v>2.21</v>
       </c>
       <c r="CJ5" t="n">
         <v>1.63</v>
       </c>
       <c r="CK5" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="CL5" t="n">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="CM5" t="n">
         <v>2.52</v>
       </c>
       <c r="CN5" t="n">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="CO5" t="n">
         <v>1.22</v>
       </c>
       <c r="CP5" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="CQ5" t="n">
-        <v>2.79</v>
+        <v>2.78</v>
       </c>
       <c r="CR5" t="n">
         <v>1.36</v>
       </c>
       <c r="CS5" t="n">
-        <v>2.56</v>
+        <v>2.55</v>
       </c>
       <c r="CT5" t="n">
         <v>3.21</v>
@@ -2882,7 +2882,7 @@
         <v>1.54</v>
       </c>
       <c r="CV5" t="n">
-        <v>2.3</v>
+        <v>2.31</v>
       </c>
       <c r="CW5" t="n">
         <v>1.67</v>
@@ -2912,43 +2912,43 @@
         <v>0.16</v>
       </c>
       <c r="DF5" t="n">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="DG5" t="n">
-        <v>2.72</v>
+        <v>2.77</v>
       </c>
       <c r="DH5" t="n">
-        <v>96.44</v>
+        <v>95.5</v>
       </c>
       <c r="DI5" t="n">
         <v>-0.04</v>
       </c>
       <c r="DJ5" t="n">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="DK5" t="n">
-        <v>4.84</v>
+        <v>4.81</v>
       </c>
       <c r="DL5" t="n">
-        <v>0.6</v>
+        <v>0.57</v>
       </c>
       <c r="DM5" t="n">
-        <v>46.28</v>
+        <v>45.96</v>
       </c>
       <c r="DN5" t="n">
-        <v>0.6</v>
+        <v>0.57</v>
       </c>
       <c r="DO5" t="n">
-        <v>2.12</v>
+        <v>2.03</v>
       </c>
       <c r="DP5" t="n">
+        <v>10.73</v>
+      </c>
+      <c r="DQ5" t="n">
         <v>10.88</v>
       </c>
-      <c r="DQ5" t="n">
-        <v>10.92</v>
-      </c>
       <c r="DR5" t="n">
-        <v>9.640000000000001</v>
+        <v>9.73</v>
       </c>
       <c r="DS5" t="n">
         <v>0.12</v>
@@ -2960,28 +2960,28 @@
         <v>0</v>
       </c>
       <c r="DV5" t="n">
-        <v>51.4</v>
+        <v>51.16</v>
       </c>
       <c r="DW5" t="n">
-        <v>0.12</v>
+        <v>0.15</v>
       </c>
       <c r="DX5" t="n">
-        <v>13.68</v>
+        <v>13.34</v>
       </c>
       <c r="DY5" t="n">
-        <v>9.08</v>
+        <v>8.880000000000001</v>
       </c>
       <c r="DZ5" t="n">
-        <v>4.6</v>
+        <v>4.46</v>
       </c>
       <c r="EA5" t="n">
-        <v>18.44</v>
+        <v>18.69</v>
       </c>
       <c r="EB5" t="n">
-        <v>1.53</v>
+        <v>1.49</v>
       </c>
       <c r="EC5" t="n">
-        <v>1.64</v>
+        <v>1.58</v>
       </c>
     </row>
     <row r="6">
@@ -2991,10 +2991,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C6" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D6" t="n">
         <v>13</v>
@@ -3003,49 +3003,49 @@
         <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>0.58</v>
+        <v>0.54</v>
       </c>
       <c r="G6" t="n">
-        <v>4.08</v>
+        <v>4.15</v>
       </c>
       <c r="H6" t="n">
-        <v>129.25</v>
+        <v>129.77</v>
       </c>
       <c r="I6" t="n">
-        <v>0.08</v>
+        <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="K6" t="n">
-        <v>6.75</v>
+        <v>6.92</v>
       </c>
       <c r="L6" t="n">
-        <v>0.5</v>
+        <v>0.46</v>
       </c>
       <c r="M6" t="n">
-        <v>62.92</v>
+        <v>63.08</v>
       </c>
       <c r="N6" t="n">
-        <v>0.58</v>
+        <v>0.54</v>
       </c>
       <c r="O6" t="n">
-        <v>2.58</v>
+        <v>2.69</v>
       </c>
       <c r="P6" t="n">
-        <v>10.67</v>
+        <v>10.15</v>
       </c>
       <c r="Q6" t="n">
-        <v>14.08</v>
+        <v>13.54</v>
       </c>
       <c r="R6" t="n">
-        <v>5.75</v>
+        <v>5.69</v>
       </c>
       <c r="S6" t="n">
-        <v>1.42</v>
+        <v>1.54</v>
       </c>
       <c r="T6" t="n">
-        <v>1.42</v>
+        <v>1.31</v>
       </c>
       <c r="U6" t="n">
         <v>0</v>
@@ -3057,28 +3057,28 @@
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>63.5</v>
+        <v>64.08</v>
       </c>
       <c r="Y6" t="n">
         <v>0.08</v>
       </c>
       <c r="Z6" t="n">
-        <v>18.17</v>
+        <v>18.31</v>
       </c>
       <c r="AA6" t="n">
-        <v>12.08</v>
+        <v>12.15</v>
       </c>
       <c r="AB6" t="n">
-        <v>6.08</v>
+        <v>6.15</v>
       </c>
       <c r="AC6" t="n">
-        <v>21.75</v>
+        <v>21.92</v>
       </c>
       <c r="AD6" t="n">
-        <v>2.03</v>
+        <v>2.05</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AF6" t="n">
         <v>0.23</v>
@@ -3165,67 +3165,67 @@
         <v>2.92</v>
       </c>
       <c r="BH6" t="n">
-        <v>9.720000000000001</v>
+        <v>9.880000000000001</v>
       </c>
       <c r="BI6" t="n">
         <v>2.92</v>
       </c>
       <c r="BJ6" t="n">
-        <v>0.6</v>
+        <v>0.58</v>
       </c>
       <c r="BK6" t="n">
-        <v>0.88</v>
+        <v>0.92</v>
       </c>
       <c r="BL6" t="n">
-        <v>0.88</v>
+        <v>0.85</v>
       </c>
       <c r="BM6" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.58</v>
       </c>
       <c r="BN6" t="n">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="BO6" t="n">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="BP6" t="n">
-        <v>4.36</v>
+        <v>4.54</v>
       </c>
       <c r="BQ6" t="n">
-        <v>5.32</v>
+        <v>5.31</v>
       </c>
       <c r="BR6" t="n">
         <v>100</v>
       </c>
       <c r="BS6" t="n">
-        <v>88</v>
+        <v>88.45999999999999</v>
       </c>
       <c r="BT6" t="n">
-        <v>60</v>
+        <v>61.54</v>
       </c>
       <c r="BU6" t="n">
-        <v>20</v>
+        <v>19.23</v>
       </c>
       <c r="BV6" t="n">
-        <v>12</v>
+        <v>11.54</v>
       </c>
       <c r="BW6" t="n">
-        <v>4</v>
+        <v>3.85</v>
       </c>
       <c r="BX6" t="n">
-        <v>80</v>
+        <v>76.92</v>
       </c>
       <c r="BY6" t="n">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="BZ6" t="n">
-        <v>1.91</v>
+        <v>1.87</v>
       </c>
       <c r="CA6" t="n">
-        <v>3.79</v>
+        <v>3.81</v>
       </c>
       <c r="CB6" t="n">
-        <v>3.9</v>
+        <v>3.93</v>
       </c>
       <c r="CC6" t="n">
         <v>2.37</v>
@@ -3237,22 +3237,22 @@
         <v>1.3</v>
       </c>
       <c r="CF6" t="n">
-        <v>2.44</v>
+        <v>2.45</v>
       </c>
       <c r="CG6" t="n">
-        <v>3.24</v>
+        <v>3.23</v>
       </c>
       <c r="CH6" t="n">
         <v>1.52</v>
       </c>
       <c r="CI6" t="n">
-        <v>2.24</v>
+        <v>2.22</v>
       </c>
       <c r="CJ6" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="CK6" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="CL6" t="n">
         <v>1.96</v>
@@ -3267,28 +3267,28 @@
         <v>1.2</v>
       </c>
       <c r="CP6" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="CQ6" t="n">
         <v>2.72</v>
       </c>
       <c r="CR6" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="CS6" t="n">
-        <v>2.59</v>
+        <v>2.6</v>
       </c>
       <c r="CT6" t="n">
         <v>3.16</v>
       </c>
       <c r="CU6" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="CV6" t="n">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="CW6" t="n">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="CX6" t="n">
         <v>1.58</v>
@@ -3303,55 +3303,55 @@
         <v>1.91</v>
       </c>
       <c r="DB6" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="DC6" t="n">
         <v>1.76</v>
       </c>
       <c r="DD6" t="n">
-        <v>2.83</v>
+        <v>2.85</v>
       </c>
       <c r="DE6" t="n">
         <v>0.12</v>
       </c>
       <c r="DF6" t="n">
-        <v>0.96</v>
+        <v>0.92</v>
       </c>
       <c r="DG6" t="n">
-        <v>3.28</v>
+        <v>3.34</v>
       </c>
       <c r="DH6" t="n">
-        <v>113.04</v>
+        <v>113.93</v>
       </c>
       <c r="DI6" t="n">
-        <v>0.08</v>
+        <v>0.04</v>
       </c>
       <c r="DJ6" t="n">
-        <v>1.52</v>
+        <v>1.46</v>
       </c>
       <c r="DK6" t="n">
-        <v>5.56</v>
+        <v>5.69</v>
       </c>
       <c r="DL6" t="n">
-        <v>0.6</v>
+        <v>0.57</v>
       </c>
       <c r="DM6" t="n">
-        <v>55.08</v>
+        <v>55.46</v>
       </c>
       <c r="DN6" t="n">
-        <v>0.52</v>
+        <v>0.5</v>
       </c>
       <c r="DO6" t="n">
-        <v>2.24</v>
+        <v>2.31</v>
       </c>
       <c r="DP6" t="n">
-        <v>10.32</v>
+        <v>10.08</v>
       </c>
       <c r="DQ6" t="n">
-        <v>12.88</v>
+        <v>12.66</v>
       </c>
       <c r="DR6" t="n">
-        <v>6.96</v>
+        <v>6.88</v>
       </c>
       <c r="DS6" t="n">
         <v>0.04</v>
@@ -3363,28 +3363,28 @@
         <v>0</v>
       </c>
       <c r="DV6" t="n">
-        <v>61.64</v>
+        <v>62</v>
       </c>
       <c r="DW6" t="n">
         <v>0.04</v>
       </c>
       <c r="DX6" t="n">
-        <v>15.76</v>
+        <v>15.92</v>
       </c>
       <c r="DY6" t="n">
-        <v>9.960000000000001</v>
+        <v>10.08</v>
       </c>
       <c r="DZ6" t="n">
-        <v>5.8</v>
+        <v>5.84</v>
       </c>
       <c r="EA6" t="n">
-        <v>20.16</v>
+        <v>20.31</v>
       </c>
       <c r="EB6" t="n">
-        <v>1.8</v>
+        <v>1.82</v>
       </c>
       <c r="EC6" t="n">
-        <v>1.44</v>
+        <v>1.39</v>
       </c>
     </row>
     <row r="7">
@@ -3394,13 +3394,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C7" t="n">
         <v>13</v>
       </c>
       <c r="D7" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E7" t="n">
         <v>0.15</v>
@@ -3487,49 +3487,49 @@
         <v>0.08</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.75</v>
+        <v>1.62</v>
       </c>
       <c r="AH7" t="n">
-        <v>3</v>
+        <v>2.92</v>
       </c>
       <c r="AI7" t="n">
-        <v>86.25</v>
+        <v>88.92</v>
       </c>
       <c r="AJ7" t="n">
         <v>0.08</v>
       </c>
       <c r="AK7" t="n">
-        <v>2.58</v>
+        <v>2.38</v>
       </c>
       <c r="AL7" t="n">
-        <v>5.08</v>
+        <v>5</v>
       </c>
       <c r="AM7" t="n">
-        <v>0.33</v>
+        <v>0.31</v>
       </c>
       <c r="AN7" t="n">
-        <v>42.5</v>
+        <v>43.46</v>
       </c>
       <c r="AO7" t="n">
-        <v>0.83</v>
+        <v>0.77</v>
       </c>
       <c r="AP7" t="n">
         <v>2.08</v>
       </c>
       <c r="AQ7" t="n">
-        <v>10.33</v>
+        <v>10.69</v>
       </c>
       <c r="AR7" t="n">
-        <v>11.67</v>
+        <v>11.77</v>
       </c>
       <c r="AS7" t="n">
-        <v>8.83</v>
+        <v>8.85</v>
       </c>
       <c r="AT7" t="n">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="AU7" t="n">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
       <c r="AV7" t="n">
         <v>0</v>
@@ -3541,82 +3541,82 @@
         <v>0</v>
       </c>
       <c r="AY7" t="n">
-        <v>49.25</v>
+        <v>51.15</v>
       </c>
       <c r="AZ7" t="n">
         <v>0</v>
       </c>
       <c r="BA7" t="n">
-        <v>10.33</v>
+        <v>10</v>
       </c>
       <c r="BB7" t="n">
-        <v>6.08</v>
+        <v>5.92</v>
       </c>
       <c r="BC7" t="n">
-        <v>4.25</v>
+        <v>4.08</v>
       </c>
       <c r="BD7" t="n">
-        <v>21.67</v>
+        <v>21.31</v>
       </c>
       <c r="BE7" t="n">
-        <v>1.26</v>
+        <v>1.24</v>
       </c>
       <c r="BF7" t="n">
-        <v>2.58</v>
+        <v>2.38</v>
       </c>
       <c r="BG7" t="n">
-        <v>2.44</v>
+        <v>2.42</v>
       </c>
       <c r="BH7" t="n">
-        <v>11.12</v>
+        <v>11</v>
       </c>
       <c r="BI7" t="n">
-        <v>2.44</v>
+        <v>2.42</v>
       </c>
       <c r="BJ7" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.54</v>
       </c>
       <c r="BK7" t="n">
-        <v>0.44</v>
+        <v>0.46</v>
       </c>
       <c r="BL7" t="n">
-        <v>0.64</v>
+        <v>0.62</v>
       </c>
       <c r="BM7" t="n">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="BN7" t="n">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="BO7" t="n">
         <v>1</v>
       </c>
       <c r="BP7" t="n">
-        <v>4.96</v>
+        <v>4.92</v>
       </c>
       <c r="BQ7" t="n">
-        <v>6.16</v>
+        <v>6.08</v>
       </c>
       <c r="BR7" t="n">
-        <v>96</v>
+        <v>96.15000000000001</v>
       </c>
       <c r="BS7" t="n">
-        <v>72</v>
+        <v>73.08</v>
       </c>
       <c r="BT7" t="n">
-        <v>36</v>
+        <v>34.62</v>
       </c>
       <c r="BU7" t="n">
-        <v>28</v>
+        <v>26.92</v>
       </c>
       <c r="BV7" t="n">
-        <v>12</v>
+        <v>11.54</v>
       </c>
       <c r="BW7" t="n">
         <v>0</v>
       </c>
       <c r="BX7" t="n">
-        <v>64</v>
+        <v>61.54</v>
       </c>
       <c r="BY7" t="n">
         <v>2.82</v>
@@ -3625,31 +3625,31 @@
         <v>2.97</v>
       </c>
       <c r="CA7" t="n">
-        <v>3.66</v>
+        <v>3.65</v>
       </c>
       <c r="CB7" t="n">
-        <v>3.79</v>
+        <v>3.78</v>
       </c>
       <c r="CC7" t="n">
-        <v>3.93</v>
+        <v>3.86</v>
       </c>
       <c r="CD7" t="n">
-        <v>4.43</v>
+        <v>4.33</v>
       </c>
       <c r="CE7" t="n">
         <v>1.31</v>
       </c>
       <c r="CF7" t="n">
-        <v>2.47</v>
+        <v>2.48</v>
       </c>
       <c r="CG7" t="n">
-        <v>3.2</v>
+        <v>3.18</v>
       </c>
       <c r="CH7" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="CI7" t="n">
-        <v>2.2</v>
+        <v>2.19</v>
       </c>
       <c r="CJ7" t="n">
         <v>1.64</v>
@@ -3658,13 +3658,13 @@
         <v>1.4</v>
       </c>
       <c r="CL7" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="CM7" t="n">
-        <v>2.73</v>
+        <v>2.72</v>
       </c>
       <c r="CN7" t="n">
-        <v>2.09</v>
+        <v>2.08</v>
       </c>
       <c r="CO7" t="n">
         <v>1.22</v>
@@ -3673,85 +3673,85 @@
         <v>1.72</v>
       </c>
       <c r="CQ7" t="n">
-        <v>2.76</v>
+        <v>2.78</v>
       </c>
       <c r="CR7" t="n">
         <v>1.36</v>
       </c>
       <c r="CS7" t="n">
-        <v>2.59</v>
+        <v>2.6</v>
       </c>
       <c r="CT7" t="n">
-        <v>3.19</v>
+        <v>3.18</v>
       </c>
       <c r="CU7" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="CV7" t="n">
-        <v>2.32</v>
+        <v>2.31</v>
       </c>
       <c r="CW7" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="CX7" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="CY7" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="CZ7" t="n">
-        <v>2.56</v>
+        <v>2.55</v>
       </c>
       <c r="DA7" t="n">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="DB7" t="n">
         <v>1.24</v>
       </c>
       <c r="DC7" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="DD7" t="n">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="DE7" t="n">
         <v>0.12</v>
       </c>
       <c r="DF7" t="n">
-        <v>1.68</v>
+        <v>1.62</v>
       </c>
       <c r="DG7" t="n">
-        <v>2.76</v>
+        <v>2.73</v>
       </c>
       <c r="DH7" t="n">
-        <v>87.95999999999999</v>
+        <v>89.23</v>
       </c>
       <c r="DI7" t="n">
         <v>0.16</v>
       </c>
       <c r="DJ7" t="n">
-        <v>2.44</v>
+        <v>2.34</v>
       </c>
       <c r="DK7" t="n">
-        <v>4.84</v>
+        <v>4.81</v>
       </c>
       <c r="DL7" t="n">
-        <v>0.28</v>
+        <v>0.27</v>
       </c>
       <c r="DM7" t="n">
-        <v>46.4</v>
+        <v>46.73</v>
       </c>
       <c r="DN7" t="n">
-        <v>0.76</v>
+        <v>0.73</v>
       </c>
       <c r="DO7" t="n">
         <v>2.08</v>
       </c>
       <c r="DP7" t="n">
-        <v>10.4</v>
+        <v>10.58</v>
       </c>
       <c r="DQ7" t="n">
-        <v>11.64</v>
+        <v>11.7</v>
       </c>
       <c r="DR7" t="n">
         <v>9</v>
@@ -3766,28 +3766,28 @@
         <v>0</v>
       </c>
       <c r="DV7" t="n">
-        <v>49.32</v>
+        <v>50.26</v>
       </c>
       <c r="DW7" t="n">
         <v>0</v>
       </c>
       <c r="DX7" t="n">
-        <v>10.6</v>
+        <v>10.42</v>
       </c>
       <c r="DY7" t="n">
-        <v>6.64</v>
+        <v>6.54</v>
       </c>
       <c r="DZ7" t="n">
-        <v>3.96</v>
+        <v>3.88</v>
       </c>
       <c r="EA7" t="n">
-        <v>21.36</v>
+        <v>21.19</v>
       </c>
       <c r="EB7" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="EC7" t="n">
-        <v>2.44</v>
+        <v>2.34</v>
       </c>
     </row>
     <row r="8">
@@ -3797,94 +3797,94 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C8" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D8" t="n">
         <v>13</v>
       </c>
       <c r="E8" t="n">
-        <v>0.25</v>
+        <v>0.23</v>
       </c>
       <c r="F8" t="n">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="G8" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="H8" t="n">
+        <v>97.69</v>
+      </c>
+      <c r="I8" t="n">
+        <v>-0.08</v>
+      </c>
+      <c r="J8" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="K8" t="n">
+        <v>5.77</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="M8" t="n">
+        <v>55.85</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="O8" t="n">
         <v>3</v>
       </c>
-      <c r="H8" t="n">
-        <v>99.33</v>
-      </c>
-      <c r="I8" t="n">
-        <v>0</v>
-      </c>
-      <c r="J8" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="K8" t="n">
-        <v>6.25</v>
-      </c>
-      <c r="L8" t="n">
-        <v>0.33</v>
-      </c>
-      <c r="M8" t="n">
-        <v>57.58</v>
-      </c>
-      <c r="N8" t="n">
-        <v>0.33</v>
-      </c>
-      <c r="O8" t="n">
-        <v>3.25</v>
-      </c>
       <c r="P8" t="n">
-        <v>10.75</v>
+        <v>10.69</v>
       </c>
       <c r="Q8" t="n">
         <v>12</v>
       </c>
       <c r="R8" t="n">
-        <v>7.75</v>
+        <v>8.15</v>
       </c>
       <c r="S8" t="n">
         <v>1.08</v>
       </c>
       <c r="T8" t="n">
-        <v>1.17</v>
+        <v>1.23</v>
       </c>
       <c r="U8" t="n">
-        <v>0.08</v>
+        <v>0.15</v>
       </c>
       <c r="V8" t="n">
-        <v>0.08</v>
+        <v>0.15</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>51.92</v>
+        <v>51.46</v>
       </c>
       <c r="Y8" t="n">
         <v>0.08</v>
       </c>
       <c r="Z8" t="n">
-        <v>16.42</v>
+        <v>16.08</v>
       </c>
       <c r="AA8" t="n">
-        <v>11.58</v>
+        <v>11.23</v>
       </c>
       <c r="AB8" t="n">
-        <v>4.83</v>
+        <v>4.85</v>
       </c>
       <c r="AC8" t="n">
-        <v>20.25</v>
+        <v>19.77</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.79</v>
+        <v>1.76</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="AF8" t="n">
         <v>0.08</v>
@@ -3968,70 +3968,70 @@
         <v>1.77</v>
       </c>
       <c r="BG8" t="n">
-        <v>2.76</v>
+        <v>2.77</v>
       </c>
       <c r="BH8" t="n">
-        <v>10.28</v>
+        <v>10.12</v>
       </c>
       <c r="BI8" t="n">
-        <v>2.76</v>
+        <v>2.77</v>
       </c>
       <c r="BJ8" t="n">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="BK8" t="n">
-        <v>0.68</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="BL8" t="n">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="BM8" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.54</v>
       </c>
       <c r="BN8" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="BO8" t="n">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="BP8" t="n">
-        <v>4.84</v>
+        <v>4.73</v>
       </c>
       <c r="BQ8" t="n">
-        <v>5.4</v>
+        <v>5.35</v>
       </c>
       <c r="BR8" t="n">
-        <v>92</v>
+        <v>92.31</v>
       </c>
       <c r="BS8" t="n">
-        <v>80</v>
+        <v>80.77</v>
       </c>
       <c r="BT8" t="n">
-        <v>36</v>
+        <v>38.46</v>
       </c>
       <c r="BU8" t="n">
-        <v>28</v>
+        <v>26.92</v>
       </c>
       <c r="BV8" t="n">
-        <v>12</v>
+        <v>11.54</v>
       </c>
       <c r="BW8" t="n">
-        <v>8</v>
+        <v>7.69</v>
       </c>
       <c r="BX8" t="n">
-        <v>36</v>
+        <v>38.46</v>
       </c>
       <c r="BY8" t="n">
-        <v>2.2</v>
+        <v>2.21</v>
       </c>
       <c r="BZ8" t="n">
-        <v>2.32</v>
+        <v>2.35</v>
       </c>
       <c r="CA8" t="n">
-        <v>3.77</v>
+        <v>3.76</v>
       </c>
       <c r="CB8" t="n">
-        <v>3.86</v>
+        <v>3.84</v>
       </c>
       <c r="CC8" t="n">
         <v>3.93</v>
@@ -4043,10 +4043,10 @@
         <v>1.27</v>
       </c>
       <c r="CF8" t="n">
-        <v>2.29</v>
+        <v>2.3</v>
       </c>
       <c r="CG8" t="n">
-        <v>3.45</v>
+        <v>3.43</v>
       </c>
       <c r="CH8" t="n">
         <v>1.58</v>
@@ -4058,139 +4058,139 @@
         <v>1.55</v>
       </c>
       <c r="CK8" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="CL8" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="CM8" t="n">
-        <v>2.87</v>
+        <v>2.86</v>
       </c>
       <c r="CN8" t="n">
-        <v>2.2</v>
+        <v>2.19</v>
       </c>
       <c r="CO8" t="n">
         <v>1.16</v>
       </c>
       <c r="CP8" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="CQ8" t="n">
-        <v>2.48</v>
+        <v>2.49</v>
       </c>
       <c r="CR8" t="n">
         <v>1.34</v>
       </c>
       <c r="CS8" t="n">
-        <v>2.37</v>
+        <v>2.38</v>
       </c>
       <c r="CT8" t="n">
-        <v>3.31</v>
+        <v>3.32</v>
       </c>
       <c r="CU8" t="n">
         <v>1.62</v>
       </c>
       <c r="CV8" t="n">
-        <v>2.56</v>
+        <v>2.55</v>
       </c>
       <c r="CW8" t="n">
         <v>1.55</v>
       </c>
       <c r="CX8" t="n">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="CY8" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="CZ8" t="n">
-        <v>2.54</v>
+        <v>2.57</v>
       </c>
       <c r="DA8" t="n">
-        <v>2.24</v>
+        <v>2.22</v>
       </c>
       <c r="DB8" t="n">
         <v>1.19</v>
       </c>
       <c r="DC8" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="DD8" t="n">
-        <v>2.52</v>
+        <v>2.53</v>
       </c>
       <c r="DE8" t="n">
         <v>0.16</v>
       </c>
       <c r="DF8" t="n">
-        <v>1.4</v>
+        <v>1.34</v>
       </c>
       <c r="DG8" t="n">
-        <v>2.48</v>
+        <v>2.38</v>
       </c>
       <c r="DH8" t="n">
-        <v>93.8</v>
+        <v>93.19</v>
       </c>
       <c r="DI8" t="n">
-        <v>0</v>
+        <v>-0.04</v>
       </c>
       <c r="DJ8" t="n">
-        <v>1.68</v>
+        <v>1.62</v>
       </c>
       <c r="DK8" t="n">
-        <v>5.16</v>
+        <v>4.96</v>
       </c>
       <c r="DL8" t="n">
-        <v>0.28</v>
+        <v>0.27</v>
       </c>
       <c r="DM8" t="n">
-        <v>49.96</v>
+        <v>49.39</v>
       </c>
       <c r="DN8" t="n">
-        <v>0.24</v>
+        <v>0.23</v>
       </c>
       <c r="DO8" t="n">
-        <v>2.68</v>
+        <v>2.58</v>
       </c>
       <c r="DP8" t="n">
-        <v>12</v>
+        <v>11.92</v>
       </c>
       <c r="DQ8" t="n">
         <v>11.96</v>
       </c>
       <c r="DR8" t="n">
-        <v>8.32</v>
+        <v>8.5</v>
       </c>
       <c r="DS8" t="n">
-        <v>0.12</v>
+        <v>0.15</v>
       </c>
       <c r="DT8" t="n">
-        <v>0.12</v>
+        <v>0.15</v>
       </c>
       <c r="DU8" t="n">
         <v>0</v>
       </c>
       <c r="DV8" t="n">
-        <v>49.4</v>
+        <v>49.27</v>
       </c>
       <c r="DW8" t="n">
         <v>0.08</v>
       </c>
       <c r="DX8" t="n">
-        <v>14.68</v>
+        <v>14.58</v>
       </c>
       <c r="DY8" t="n">
-        <v>9.960000000000001</v>
+        <v>9.85</v>
       </c>
       <c r="DZ8" t="n">
-        <v>4.72</v>
+        <v>4.74</v>
       </c>
       <c r="EA8" t="n">
-        <v>21.96</v>
+        <v>21.65</v>
       </c>
       <c r="EB8" t="n">
         <v>1.6</v>
       </c>
       <c r="EC8" t="n">
-        <v>1.56</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="9">
@@ -4200,13 +4200,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C9" t="n">
         <v>13</v>
       </c>
       <c r="D9" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E9" t="n">
         <v>0.23</v>
@@ -4293,49 +4293,49 @@
         <v>0</v>
       </c>
       <c r="AG9" t="n">
-        <v>2.33</v>
+        <v>2.23</v>
       </c>
       <c r="AH9" t="n">
-        <v>2.5</v>
+        <v>2.54</v>
       </c>
       <c r="AI9" t="n">
-        <v>78.33</v>
+        <v>76.69</v>
       </c>
       <c r="AJ9" t="n">
         <v>0</v>
       </c>
       <c r="AK9" t="n">
-        <v>3.5</v>
+        <v>3.31</v>
       </c>
       <c r="AL9" t="n">
-        <v>4.33</v>
+        <v>4.31</v>
       </c>
       <c r="AM9" t="n">
-        <v>0.5</v>
+        <v>0.46</v>
       </c>
       <c r="AN9" t="n">
-        <v>45.75</v>
+        <v>44.31</v>
       </c>
       <c r="AO9" t="n">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="AP9" t="n">
-        <v>1.83</v>
+        <v>1.77</v>
       </c>
       <c r="AQ9" t="n">
-        <v>16.17</v>
+        <v>16</v>
       </c>
       <c r="AR9" t="n">
-        <v>10.67</v>
+        <v>10.38</v>
       </c>
       <c r="AS9" t="n">
-        <v>9</v>
+        <v>9.08</v>
       </c>
       <c r="AT9" t="n">
-        <v>1.5</v>
+        <v>1.54</v>
       </c>
       <c r="AU9" t="n">
-        <v>0.83</v>
+        <v>0.85</v>
       </c>
       <c r="AV9" t="n">
         <v>0.08</v>
@@ -4347,82 +4347,82 @@
         <v>0</v>
       </c>
       <c r="AY9" t="n">
-        <v>44.83</v>
+        <v>44.15</v>
       </c>
       <c r="AZ9" t="n">
         <v>0.08</v>
       </c>
       <c r="BA9" t="n">
-        <v>12.5</v>
+        <v>12.46</v>
       </c>
       <c r="BB9" t="n">
-        <v>8.5</v>
+        <v>8.539999999999999</v>
       </c>
       <c r="BC9" t="n">
-        <v>4</v>
+        <v>3.92</v>
       </c>
       <c r="BD9" t="n">
-        <v>19.33</v>
+        <v>19.15</v>
       </c>
       <c r="BE9" t="n">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="BF9" t="n">
-        <v>3.42</v>
+        <v>3.23</v>
       </c>
       <c r="BG9" t="n">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="BH9" t="n">
-        <v>10.56</v>
+        <v>10.77</v>
       </c>
       <c r="BI9" t="n">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="BJ9" t="n">
-        <v>0.72</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="BK9" t="n">
-        <v>0.48</v>
+        <v>0.46</v>
       </c>
       <c r="BL9" t="n">
-        <v>0.68</v>
+        <v>0.73</v>
       </c>
       <c r="BM9" t="n">
-        <v>0.6</v>
+        <v>0.62</v>
       </c>
       <c r="BN9" t="n">
-        <v>1.28</v>
+        <v>1.35</v>
       </c>
       <c r="BO9" t="n">
-        <v>1.2</v>
+        <v>1.15</v>
       </c>
       <c r="BP9" t="n">
-        <v>5.2</v>
+        <v>5.27</v>
       </c>
       <c r="BQ9" t="n">
-        <v>5.32</v>
+        <v>5.46</v>
       </c>
       <c r="BR9" t="n">
-        <v>92</v>
+        <v>92.31</v>
       </c>
       <c r="BS9" t="n">
-        <v>72</v>
+        <v>73.08</v>
       </c>
       <c r="BT9" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="BU9" t="n">
-        <v>28</v>
+        <v>26.92</v>
       </c>
       <c r="BV9" t="n">
-        <v>8</v>
+        <v>7.69</v>
       </c>
       <c r="BW9" t="n">
         <v>0</v>
       </c>
       <c r="BX9" t="n">
-        <v>52</v>
+        <v>53.85</v>
       </c>
       <c r="BY9" t="n">
         <v>2.91</v>
@@ -4431,25 +4431,25 @@
         <v>2.95</v>
       </c>
       <c r="CA9" t="n">
-        <v>3.48</v>
+        <v>3.54</v>
       </c>
       <c r="CB9" t="n">
-        <v>3.51</v>
+        <v>3.6</v>
       </c>
       <c r="CC9" t="n">
-        <v>4.14</v>
+        <v>4.42</v>
       </c>
       <c r="CD9" t="n">
-        <v>4.39</v>
+        <v>4.72</v>
       </c>
       <c r="CE9" t="n">
         <v>1.37</v>
       </c>
       <c r="CF9" t="n">
-        <v>2.74</v>
+        <v>2.72</v>
       </c>
       <c r="CG9" t="n">
-        <v>2.95</v>
+        <v>2.97</v>
       </c>
       <c r="CH9" t="n">
         <v>1.42</v>
@@ -4473,31 +4473,31 @@
         <v>1.96</v>
       </c>
       <c r="CO9" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="CP9" t="n">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="CQ9" t="n">
-        <v>3.31</v>
+        <v>3.27</v>
       </c>
       <c r="CR9" t="n">
         <v>1.38</v>
       </c>
       <c r="CS9" t="n">
-        <v>2.84</v>
+        <v>2.81</v>
       </c>
       <c r="CT9" t="n">
         <v>3.08</v>
       </c>
       <c r="CU9" t="n">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="CV9" t="n">
         <v>2.09</v>
       </c>
       <c r="CW9" t="n">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="CX9" t="n">
         <v>1.55</v>
@@ -4512,55 +4512,55 @@
         <v>1.99</v>
       </c>
       <c r="DB9" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="DC9" t="n">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="DD9" t="n">
-        <v>3.39</v>
+        <v>3.35</v>
       </c>
       <c r="DE9" t="n">
         <v>0.12</v>
       </c>
       <c r="DF9" t="n">
-        <v>2.28</v>
+        <v>2.23</v>
       </c>
       <c r="DG9" t="n">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="DH9" t="n">
-        <v>79.8</v>
+        <v>78.92</v>
       </c>
       <c r="DI9" t="n">
         <v>0.04</v>
       </c>
       <c r="DJ9" t="n">
-        <v>3.24</v>
+        <v>3.16</v>
       </c>
       <c r="DK9" t="n">
-        <v>4.68</v>
+        <v>4.66</v>
       </c>
       <c r="DL9" t="n">
-        <v>0.52</v>
+        <v>0.5</v>
       </c>
       <c r="DM9" t="n">
-        <v>43.2</v>
+        <v>42.58</v>
       </c>
       <c r="DN9" t="n">
-        <v>0.96</v>
+        <v>0.92</v>
       </c>
       <c r="DO9" t="n">
-        <v>2.2</v>
+        <v>2.16</v>
       </c>
       <c r="DP9" t="n">
-        <v>16.12</v>
+        <v>16.04</v>
       </c>
       <c r="DQ9" t="n">
-        <v>11.52</v>
+        <v>11.34</v>
       </c>
       <c r="DR9" t="n">
-        <v>8.4</v>
+        <v>8.460000000000001</v>
       </c>
       <c r="DS9" t="n">
         <v>0.12</v>
@@ -4572,28 +4572,28 @@
         <v>0</v>
       </c>
       <c r="DV9" t="n">
-        <v>45.12</v>
+        <v>44.76</v>
       </c>
       <c r="DW9" t="n">
         <v>0.04</v>
       </c>
       <c r="DX9" t="n">
-        <v>13.84</v>
+        <v>13.77</v>
       </c>
       <c r="DY9" t="n">
-        <v>9.359999999999999</v>
+        <v>9.35</v>
       </c>
       <c r="DZ9" t="n">
-        <v>4.48</v>
+        <v>4.42</v>
       </c>
       <c r="EA9" t="n">
-        <v>19.68</v>
+        <v>19.58</v>
       </c>
       <c r="EB9" t="n">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="EC9" t="n">
-        <v>3.2</v>
+        <v>3.12</v>
       </c>
     </row>
     <row r="10">
@@ -4603,10 +4603,10 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C10" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D10" t="n">
         <v>13</v>
@@ -4615,49 +4615,49 @@
         <v>0</v>
       </c>
       <c r="F10" t="n">
-        <v>0.75</v>
+        <v>0.77</v>
       </c>
       <c r="G10" t="n">
-        <v>3.33</v>
+        <v>3.23</v>
       </c>
       <c r="H10" t="n">
-        <v>84.75</v>
+        <v>82.69</v>
       </c>
       <c r="I10" t="n">
-        <v>0.17</v>
+        <v>0.15</v>
       </c>
       <c r="J10" t="n">
-        <v>1.5</v>
+        <v>1.62</v>
       </c>
       <c r="K10" t="n">
-        <v>5.83</v>
+        <v>5.69</v>
       </c>
       <c r="L10" t="n">
-        <v>0.17</v>
+        <v>0.15</v>
       </c>
       <c r="M10" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="N10" t="n">
-        <v>0.75</v>
+        <v>0.77</v>
       </c>
       <c r="O10" t="n">
-        <v>2.5</v>
+        <v>2.46</v>
       </c>
       <c r="P10" t="n">
-        <v>11.08</v>
+        <v>11.23</v>
       </c>
       <c r="Q10" t="n">
-        <v>11.67</v>
+        <v>11.92</v>
       </c>
       <c r="R10" t="n">
-        <v>8.58</v>
+        <v>8.31</v>
       </c>
       <c r="S10" t="n">
-        <v>0.75</v>
+        <v>0.85</v>
       </c>
       <c r="T10" t="n">
-        <v>0.58</v>
+        <v>0.54</v>
       </c>
       <c r="U10" t="n">
         <v>0</v>
@@ -4669,28 +4669,28 @@
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>38.83</v>
+        <v>37.85</v>
       </c>
       <c r="Y10" t="n">
-        <v>0</v>
+        <v>0.08</v>
       </c>
       <c r="Z10" t="n">
-        <v>10.17</v>
+        <v>9.92</v>
       </c>
       <c r="AA10" t="n">
-        <v>7.25</v>
+        <v>7.08</v>
       </c>
       <c r="AB10" t="n">
-        <v>2.92</v>
+        <v>2.85</v>
       </c>
       <c r="AC10" t="n">
-        <v>21.42</v>
+        <v>22</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.14</v>
+        <v>1.11</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="AF10" t="n">
         <v>0.15</v>
@@ -4777,67 +4777,67 @@
         <v>1.96</v>
       </c>
       <c r="BH10" t="n">
-        <v>9.119999999999999</v>
+        <v>9.08</v>
       </c>
       <c r="BI10" t="n">
         <v>1.96</v>
       </c>
       <c r="BJ10" t="n">
-        <v>0.52</v>
+        <v>0.5</v>
       </c>
       <c r="BK10" t="n">
-        <v>0.32</v>
+        <v>0.35</v>
       </c>
       <c r="BL10" t="n">
-        <v>0.52</v>
+        <v>0.5</v>
       </c>
       <c r="BM10" t="n">
-        <v>0.6</v>
+        <v>0.62</v>
       </c>
       <c r="BN10" t="n">
         <v>1.12</v>
       </c>
       <c r="BO10" t="n">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="BP10" t="n">
-        <v>3.8</v>
+        <v>3.81</v>
       </c>
       <c r="BQ10" t="n">
-        <v>5.32</v>
+        <v>5.27</v>
       </c>
       <c r="BR10" t="n">
-        <v>72</v>
+        <v>73.08</v>
       </c>
       <c r="BS10" t="n">
-        <v>56</v>
+        <v>57.69</v>
       </c>
       <c r="BT10" t="n">
-        <v>44</v>
+        <v>42.31</v>
       </c>
       <c r="BU10" t="n">
-        <v>16</v>
+        <v>15.38</v>
       </c>
       <c r="BV10" t="n">
-        <v>8</v>
+        <v>7.69</v>
       </c>
       <c r="BW10" t="n">
         <v>0</v>
       </c>
       <c r="BX10" t="n">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="BY10" t="n">
+        <v>3.33</v>
+      </c>
+      <c r="BZ10" t="n">
         <v>3.41</v>
       </c>
-      <c r="BZ10" t="n">
-        <v>3.51</v>
-      </c>
       <c r="CA10" t="n">
-        <v>3.56</v>
+        <v>3.55</v>
       </c>
       <c r="CB10" t="n">
-        <v>3.66</v>
+        <v>3.65</v>
       </c>
       <c r="CC10" t="n">
         <v>4.8</v>
@@ -4861,7 +4861,7 @@
         <v>1.89</v>
       </c>
       <c r="CJ10" t="n">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="CK10" t="n">
         <v>1.57</v>
@@ -4870,13 +4870,13 @@
         <v>2.01</v>
       </c>
       <c r="CM10" t="n">
-        <v>2.31</v>
+        <v>2.32</v>
       </c>
       <c r="CN10" t="n">
         <v>1.82</v>
       </c>
       <c r="CO10" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="CP10" t="n">
         <v>1.98</v>
@@ -4921,7 +4921,7 @@
         <v>2.06</v>
       </c>
       <c r="DD10" t="n">
-        <v>3.57</v>
+        <v>3.56</v>
       </c>
       <c r="DE10" t="n">
         <v>0.08</v>
@@ -4930,40 +4930,40 @@
         <v>1.2</v>
       </c>
       <c r="DG10" t="n">
-        <v>2.84</v>
+        <v>2.8</v>
       </c>
       <c r="DH10" t="n">
-        <v>82.59999999999999</v>
+        <v>81.65000000000001</v>
       </c>
       <c r="DI10" t="n">
         <v>0.12</v>
       </c>
       <c r="DJ10" t="n">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="DK10" t="n">
-        <v>4.68</v>
+        <v>4.66</v>
       </c>
       <c r="DL10" t="n">
-        <v>0.2</v>
+        <v>0.19</v>
       </c>
       <c r="DM10" t="n">
-        <v>41.08</v>
+        <v>40.77</v>
       </c>
       <c r="DN10" t="n">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="DO10" t="n">
         <v>1.84</v>
       </c>
       <c r="DP10" t="n">
-        <v>11.48</v>
+        <v>11.54</v>
       </c>
       <c r="DQ10" t="n">
-        <v>12.24</v>
+        <v>12.34</v>
       </c>
       <c r="DR10" t="n">
-        <v>8.6</v>
+        <v>8.460000000000001</v>
       </c>
       <c r="DS10" t="n">
         <v>0</v>
@@ -4975,28 +4975,28 @@
         <v>0</v>
       </c>
       <c r="DV10" t="n">
-        <v>36.08</v>
+        <v>35.7</v>
       </c>
       <c r="DW10" t="n">
-        <v>0.04</v>
+        <v>0.08</v>
       </c>
       <c r="DX10" t="n">
-        <v>9.4</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="DY10" t="n">
-        <v>6.8</v>
+        <v>6.73</v>
       </c>
       <c r="DZ10" t="n">
-        <v>2.6</v>
+        <v>2.58</v>
       </c>
       <c r="EA10" t="n">
-        <v>21.08</v>
+        <v>21.38</v>
       </c>
       <c r="EB10" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="EC10" t="n">
-        <v>1.92</v>
+        <v>1.89</v>
       </c>
     </row>
     <row r="11">
@@ -5006,13 +5006,13 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C11" t="n">
         <v>13</v>
       </c>
       <c r="D11" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E11" t="n">
         <v>0.08</v>
@@ -5096,139 +5096,139 @@
         <v>2.38</v>
       </c>
       <c r="AF11" t="n">
-        <v>0.17</v>
+        <v>0.15</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="AH11" t="n">
-        <v>3.17</v>
+        <v>3</v>
       </c>
       <c r="AI11" t="n">
-        <v>97.08</v>
+        <v>95.62</v>
       </c>
       <c r="AJ11" t="n">
         <v>0</v>
       </c>
       <c r="AK11" t="n">
-        <v>2.67</v>
+        <v>2.54</v>
       </c>
       <c r="AL11" t="n">
-        <v>6.25</v>
+        <v>6.08</v>
       </c>
       <c r="AM11" t="n">
-        <v>0.33</v>
+        <v>0.31</v>
       </c>
       <c r="AN11" t="n">
-        <v>54.42</v>
+        <v>52.85</v>
       </c>
       <c r="AO11" t="n">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="AP11" t="n">
         <v>3.08</v>
       </c>
       <c r="AQ11" t="n">
-        <v>15</v>
+        <v>14.77</v>
       </c>
       <c r="AR11" t="n">
-        <v>9.83</v>
+        <v>9.69</v>
       </c>
       <c r="AS11" t="n">
-        <v>8.08</v>
+        <v>8.460000000000001</v>
       </c>
       <c r="AT11" t="n">
-        <v>1.67</v>
+        <v>1.69</v>
       </c>
       <c r="AU11" t="n">
-        <v>1</v>
+        <v>1.23</v>
       </c>
       <c r="AV11" t="n">
-        <v>0.17</v>
+        <v>0.23</v>
       </c>
       <c r="AW11" t="n">
-        <v>0.17</v>
+        <v>0.23</v>
       </c>
       <c r="AX11" t="n">
         <v>0</v>
       </c>
       <c r="AY11" t="n">
-        <v>55.17</v>
+        <v>54.38</v>
       </c>
       <c r="AZ11" t="n">
-        <v>0.17</v>
+        <v>0.15</v>
       </c>
       <c r="BA11" t="n">
-        <v>12.67</v>
+        <v>12.62</v>
       </c>
       <c r="BB11" t="n">
-        <v>8.75</v>
+        <v>8.619999999999999</v>
       </c>
       <c r="BC11" t="n">
-        <v>3.92</v>
+        <v>4</v>
       </c>
       <c r="BD11" t="n">
-        <v>22</v>
+        <v>21.23</v>
       </c>
       <c r="BE11" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="BF11" t="n">
-        <v>2.5</v>
+        <v>2.38</v>
       </c>
       <c r="BG11" t="n">
-        <v>2.4</v>
+        <v>2.54</v>
       </c>
       <c r="BH11" t="n">
-        <v>10.84</v>
+        <v>10.81</v>
       </c>
       <c r="BI11" t="n">
-        <v>2.4</v>
+        <v>2.54</v>
       </c>
       <c r="BJ11" t="n">
-        <v>0.64</v>
+        <v>0.62</v>
       </c>
       <c r="BK11" t="n">
-        <v>0.36</v>
+        <v>0.46</v>
       </c>
       <c r="BL11" t="n">
-        <v>0.88</v>
+        <v>0.92</v>
       </c>
       <c r="BM11" t="n">
-        <v>0.52</v>
+        <v>0.54</v>
       </c>
       <c r="BN11" t="n">
-        <v>1.4</v>
+        <v>1.46</v>
       </c>
       <c r="BO11" t="n">
-        <v>1</v>
+        <v>1.08</v>
       </c>
       <c r="BP11" t="n">
-        <v>5.32</v>
+        <v>5.27</v>
       </c>
       <c r="BQ11" t="n">
-        <v>5.52</v>
+        <v>5.54</v>
       </c>
       <c r="BR11" t="n">
-        <v>88</v>
+        <v>88.45999999999999</v>
       </c>
       <c r="BS11" t="n">
-        <v>64</v>
+        <v>65.38</v>
       </c>
       <c r="BT11" t="n">
-        <v>36</v>
+        <v>38.46</v>
       </c>
       <c r="BU11" t="n">
-        <v>28</v>
+        <v>30.77</v>
       </c>
       <c r="BV11" t="n">
-        <v>12</v>
+        <v>15.38</v>
       </c>
       <c r="BW11" t="n">
-        <v>8</v>
+        <v>11.54</v>
       </c>
       <c r="BX11" t="n">
-        <v>40</v>
+        <v>42.31</v>
       </c>
       <c r="BY11" t="n">
         <v>1.91</v>
@@ -5243,10 +5243,10 @@
         <v>3.69</v>
       </c>
       <c r="CC11" t="n">
-        <v>2.48</v>
+        <v>2.47</v>
       </c>
       <c r="CD11" t="n">
-        <v>2.7</v>
+        <v>2.67</v>
       </c>
       <c r="CE11" t="n">
         <v>1.33</v>
@@ -5276,16 +5276,16 @@
         <v>2.52</v>
       </c>
       <c r="CN11" t="n">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="CO11" t="n">
         <v>1.24</v>
       </c>
       <c r="CP11" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="CQ11" t="n">
-        <v>2.96</v>
+        <v>2.97</v>
       </c>
       <c r="CR11" t="n">
         <v>1.37</v>
@@ -5300,10 +5300,10 @@
         <v>1.48</v>
       </c>
       <c r="CV11" t="n">
-        <v>2.18</v>
+        <v>2.19</v>
       </c>
       <c r="CW11" t="n">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="CX11" t="n">
         <v>1.52</v>
@@ -5315,7 +5315,7 @@
         <v>2.49</v>
       </c>
       <c r="DA11" t="n">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="DB11" t="n">
         <v>1.27</v>
@@ -5330,76 +5330,76 @@
         <v>0.12</v>
       </c>
       <c r="DF11" t="n">
-        <v>1.48</v>
+        <v>1.46</v>
       </c>
       <c r="DG11" t="n">
-        <v>3.28</v>
+        <v>3.19</v>
       </c>
       <c r="DH11" t="n">
-        <v>103.64</v>
+        <v>102.65</v>
       </c>
       <c r="DI11" t="n">
         <v>0</v>
       </c>
       <c r="DJ11" t="n">
-        <v>2.6</v>
+        <v>2.54</v>
       </c>
       <c r="DK11" t="n">
-        <v>6.44</v>
+        <v>6.35</v>
       </c>
       <c r="DL11" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.54</v>
       </c>
       <c r="DM11" t="n">
-        <v>56.88</v>
+        <v>56</v>
       </c>
       <c r="DN11" t="n">
-        <v>1.08</v>
+        <v>1.03</v>
       </c>
       <c r="DO11" t="n">
         <v>3.16</v>
       </c>
       <c r="DP11" t="n">
-        <v>13.96</v>
+        <v>13.88</v>
       </c>
       <c r="DQ11" t="n">
-        <v>10.84</v>
+        <v>10.73</v>
       </c>
       <c r="DR11" t="n">
-        <v>7.76</v>
+        <v>7.96</v>
       </c>
       <c r="DS11" t="n">
-        <v>0.16</v>
+        <v>0.19</v>
       </c>
       <c r="DT11" t="n">
-        <v>0.16</v>
+        <v>0.19</v>
       </c>
       <c r="DU11" t="n">
         <v>0</v>
       </c>
       <c r="DV11" t="n">
-        <v>54.16</v>
+        <v>53.8</v>
       </c>
       <c r="DW11" t="n">
         <v>0.12</v>
       </c>
       <c r="DX11" t="n">
-        <v>15.04</v>
+        <v>14.92</v>
       </c>
       <c r="DY11" t="n">
-        <v>10.36</v>
+        <v>10.23</v>
       </c>
       <c r="DZ11" t="n">
-        <v>4.68</v>
+        <v>4.69</v>
       </c>
       <c r="EA11" t="n">
-        <v>21.56</v>
+        <v>21.19</v>
       </c>
       <c r="EB11" t="n">
-        <v>1.69</v>
+        <v>1.67</v>
       </c>
       <c r="EC11" t="n">
-        <v>2.44</v>
+        <v>2.38</v>
       </c>
     </row>
     <row r="12">
@@ -5409,13 +5409,13 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C12" t="n">
         <v>13</v>
       </c>
       <c r="D12" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E12" t="n">
         <v>0.08</v>
@@ -5502,49 +5502,49 @@
         <v>0</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.42</v>
+        <v>1.31</v>
       </c>
       <c r="AH12" t="n">
-        <v>2.42</v>
+        <v>2.31</v>
       </c>
       <c r="AI12" t="n">
-        <v>95.67</v>
+        <v>94.54000000000001</v>
       </c>
       <c r="AJ12" t="n">
-        <v>0</v>
+        <v>0.08</v>
       </c>
       <c r="AK12" t="n">
-        <v>1.92</v>
+        <v>1.85</v>
       </c>
       <c r="AL12" t="n">
-        <v>3.58</v>
+        <v>3.38</v>
       </c>
       <c r="AM12" t="n">
-        <v>0.25</v>
+        <v>0.23</v>
       </c>
       <c r="AN12" t="n">
-        <v>38.67</v>
+        <v>37</v>
       </c>
       <c r="AO12" t="n">
-        <v>0.42</v>
+        <v>0.46</v>
       </c>
       <c r="AP12" t="n">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="AQ12" t="n">
-        <v>13.25</v>
+        <v>13.08</v>
       </c>
       <c r="AR12" t="n">
-        <v>11.83</v>
+        <v>11.92</v>
       </c>
       <c r="AS12" t="n">
-        <v>7.5</v>
+        <v>7.77</v>
       </c>
       <c r="AT12" t="n">
-        <v>0.92</v>
+        <v>1</v>
       </c>
       <c r="AU12" t="n">
-        <v>0.75</v>
+        <v>0.77</v>
       </c>
       <c r="AV12" t="n">
         <v>0.08</v>
@@ -5556,73 +5556,73 @@
         <v>0</v>
       </c>
       <c r="AY12" t="n">
-        <v>47.75</v>
+        <v>47</v>
       </c>
       <c r="AZ12" t="n">
         <v>0.08</v>
       </c>
       <c r="BA12" t="n">
-        <v>10.67</v>
+        <v>10.15</v>
       </c>
       <c r="BB12" t="n">
-        <v>7.08</v>
+        <v>6.69</v>
       </c>
       <c r="BC12" t="n">
-        <v>3.58</v>
+        <v>3.46</v>
       </c>
       <c r="BD12" t="n">
-        <v>22.25</v>
+        <v>21.38</v>
       </c>
       <c r="BE12" t="n">
-        <v>1.21</v>
+        <v>1.16</v>
       </c>
       <c r="BF12" t="n">
-        <v>1.75</v>
+        <v>1.69</v>
       </c>
       <c r="BG12" t="n">
-        <v>2.24</v>
+        <v>2.27</v>
       </c>
       <c r="BH12" t="n">
-        <v>9.08</v>
+        <v>9.15</v>
       </c>
       <c r="BI12" t="n">
-        <v>2.24</v>
+        <v>2.27</v>
       </c>
       <c r="BJ12" t="n">
-        <v>0.68</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="BK12" t="n">
-        <v>0.48</v>
+        <v>0.46</v>
       </c>
       <c r="BL12" t="n">
-        <v>0.52</v>
+        <v>0.54</v>
       </c>
       <c r="BM12" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.58</v>
       </c>
       <c r="BN12" t="n">
-        <v>1.08</v>
+        <v>1.12</v>
       </c>
       <c r="BO12" t="n">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="BP12" t="n">
         <v>3.96</v>
       </c>
       <c r="BQ12" t="n">
-        <v>5.08</v>
+        <v>5.15</v>
       </c>
       <c r="BR12" t="n">
-        <v>96</v>
+        <v>96.15000000000001</v>
       </c>
       <c r="BS12" t="n">
-        <v>76</v>
+        <v>76.92</v>
       </c>
       <c r="BT12" t="n">
-        <v>36</v>
+        <v>38.46</v>
       </c>
       <c r="BU12" t="n">
-        <v>16</v>
+        <v>15.38</v>
       </c>
       <c r="BV12" t="n">
         <v>0</v>
@@ -5631,7 +5631,7 @@
         <v>0</v>
       </c>
       <c r="BX12" t="n">
-        <v>44</v>
+        <v>46.15</v>
       </c>
       <c r="BY12" t="n">
         <v>2.67</v>
@@ -5640,37 +5640,37 @@
         <v>2.87</v>
       </c>
       <c r="CA12" t="n">
-        <v>3.5</v>
+        <v>3.54</v>
       </c>
       <c r="CB12" t="n">
-        <v>3.62</v>
+        <v>3.67</v>
       </c>
       <c r="CC12" t="n">
-        <v>3.85</v>
+        <v>4.13</v>
       </c>
       <c r="CD12" t="n">
-        <v>4.25</v>
+        <v>4.67</v>
       </c>
       <c r="CE12" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="CF12" t="n">
         <v>2.62</v>
       </c>
       <c r="CG12" t="n">
-        <v>3</v>
+        <v>3.01</v>
       </c>
       <c r="CH12" t="n">
         <v>1.44</v>
       </c>
       <c r="CI12" t="n">
-        <v>2.09</v>
+        <v>2.07</v>
       </c>
       <c r="CJ12" t="n">
-        <v>1.69</v>
+        <v>1.71</v>
       </c>
       <c r="CK12" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="CL12" t="n">
         <v>1.97</v>
@@ -5703,10 +5703,10 @@
         <v>1.47</v>
       </c>
       <c r="CV12" t="n">
-        <v>2.15</v>
+        <v>2.13</v>
       </c>
       <c r="CW12" t="n">
-        <v>1.76</v>
+        <v>1.78</v>
       </c>
       <c r="CX12" t="n">
         <v>1.58</v>
@@ -5733,43 +5733,43 @@
         <v>0.04</v>
       </c>
       <c r="DF12" t="n">
-        <v>1.32</v>
+        <v>1.27</v>
       </c>
       <c r="DG12" t="n">
-        <v>2.36</v>
+        <v>2.31</v>
       </c>
       <c r="DH12" t="n">
-        <v>96.28</v>
+        <v>95.7</v>
       </c>
       <c r="DI12" t="n">
-        <v>0.04</v>
+        <v>0.08</v>
       </c>
       <c r="DJ12" t="n">
-        <v>2.04</v>
+        <v>2</v>
       </c>
       <c r="DK12" t="n">
-        <v>4.16</v>
+        <v>4.04</v>
       </c>
       <c r="DL12" t="n">
-        <v>0.4</v>
+        <v>0.39</v>
       </c>
       <c r="DM12" t="n">
-        <v>41.44</v>
+        <v>40.5</v>
       </c>
       <c r="DN12" t="n">
-        <v>0.64</v>
+        <v>0.66</v>
       </c>
       <c r="DO12" t="n">
-        <v>1.76</v>
+        <v>1.7</v>
       </c>
       <c r="DP12" t="n">
-        <v>12.8</v>
+        <v>12.73</v>
       </c>
       <c r="DQ12" t="n">
-        <v>12.16</v>
+        <v>12.19</v>
       </c>
       <c r="DR12" t="n">
-        <v>7.24</v>
+        <v>7.38</v>
       </c>
       <c r="DS12" t="n">
         <v>0.2</v>
@@ -5781,28 +5781,28 @@
         <v>0</v>
       </c>
       <c r="DV12" t="n">
-        <v>49.04</v>
+        <v>48.62</v>
       </c>
       <c r="DW12" t="n">
         <v>0.08</v>
       </c>
       <c r="DX12" t="n">
-        <v>11.64</v>
+        <v>11.34</v>
       </c>
       <c r="DY12" t="n">
-        <v>7.36</v>
+        <v>7.16</v>
       </c>
       <c r="DZ12" t="n">
-        <v>4.28</v>
+        <v>4.19</v>
       </c>
       <c r="EA12" t="n">
-        <v>21.76</v>
+        <v>21.35</v>
       </c>
       <c r="EB12" t="n">
-        <v>1.34</v>
+        <v>1.31</v>
       </c>
       <c r="EC12" t="n">
-        <v>1.88</v>
+        <v>1.84</v>
       </c>
     </row>
     <row r="13">
@@ -5812,13 +5812,13 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C13" t="n">
         <v>13</v>
       </c>
       <c r="D13" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E13" t="n">
         <v>0.23</v>
@@ -5905,136 +5905,136 @@
         <v>0.08</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AH13" t="n">
-        <v>3.25</v>
+        <v>3.38</v>
       </c>
       <c r="AI13" t="n">
-        <v>96.17</v>
+        <v>97.69</v>
       </c>
       <c r="AJ13" t="n">
-        <v>0.17</v>
+        <v>0.15</v>
       </c>
       <c r="AK13" t="n">
-        <v>1.83</v>
+        <v>1.69</v>
       </c>
       <c r="AL13" t="n">
-        <v>5.42</v>
+        <v>5.69</v>
       </c>
       <c r="AM13" t="n">
-        <v>0.42</v>
+        <v>0.62</v>
       </c>
       <c r="AN13" t="n">
-        <v>50.33</v>
+        <v>51</v>
       </c>
       <c r="AO13" t="n">
-        <v>0.75</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AP13" t="n">
-        <v>2.17</v>
+        <v>2.31</v>
       </c>
       <c r="AQ13" t="n">
-        <v>12.42</v>
+        <v>12.08</v>
       </c>
       <c r="AR13" t="n">
-        <v>10.92</v>
+        <v>11.15</v>
       </c>
       <c r="AS13" t="n">
-        <v>8.67</v>
+        <v>8.539999999999999</v>
       </c>
       <c r="AT13" t="n">
         <v>1.08</v>
       </c>
       <c r="AU13" t="n">
-        <v>1.67</v>
+        <v>1.85</v>
       </c>
       <c r="AV13" t="n">
-        <v>0.33</v>
+        <v>0.31</v>
       </c>
       <c r="AW13" t="n">
-        <v>0.33</v>
+        <v>0.31</v>
       </c>
       <c r="AX13" t="n">
         <v>0</v>
       </c>
       <c r="AY13" t="n">
-        <v>53.5</v>
+        <v>54.08</v>
       </c>
       <c r="AZ13" t="n">
         <v>0</v>
       </c>
       <c r="BA13" t="n">
-        <v>13.67</v>
+        <v>13.69</v>
       </c>
       <c r="BB13" t="n">
-        <v>9.33</v>
+        <v>9.380000000000001</v>
       </c>
       <c r="BC13" t="n">
-        <v>4.33</v>
+        <v>4.31</v>
       </c>
       <c r="BD13" t="n">
-        <v>21.58</v>
+        <v>21.38</v>
       </c>
       <c r="BE13" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="BF13" t="n">
-        <v>1.83</v>
+        <v>1.69</v>
       </c>
       <c r="BG13" t="n">
-        <v>2.72</v>
+        <v>2.81</v>
       </c>
       <c r="BH13" t="n">
-        <v>9.92</v>
+        <v>10.04</v>
       </c>
       <c r="BI13" t="n">
-        <v>2.72</v>
+        <v>2.81</v>
       </c>
       <c r="BJ13" t="n">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="BK13" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.62</v>
       </c>
       <c r="BL13" t="n">
-        <v>0.6</v>
+        <v>0.58</v>
       </c>
       <c r="BM13" t="n">
-        <v>0.84</v>
+        <v>0.88</v>
       </c>
       <c r="BN13" t="n">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="BO13" t="n">
-        <v>1.28</v>
+        <v>1.35</v>
       </c>
       <c r="BP13" t="n">
         <v>4.08</v>
       </c>
       <c r="BQ13" t="n">
-        <v>5.84</v>
+        <v>5.96</v>
       </c>
       <c r="BR13" t="n">
         <v>100</v>
       </c>
       <c r="BS13" t="n">
-        <v>84</v>
+        <v>84.62</v>
       </c>
       <c r="BT13" t="n">
-        <v>56</v>
+        <v>57.69</v>
       </c>
       <c r="BU13" t="n">
-        <v>24</v>
+        <v>26.92</v>
       </c>
       <c r="BV13" t="n">
-        <v>8</v>
+        <v>11.54</v>
       </c>
       <c r="BW13" t="n">
         <v>0</v>
       </c>
       <c r="BX13" t="n">
-        <v>56</v>
+        <v>57.69</v>
       </c>
       <c r="BY13" t="n">
         <v>2.23</v>
@@ -6046,40 +6046,40 @@
         <v>3.66</v>
       </c>
       <c r="CB13" t="n">
-        <v>3.78</v>
+        <v>3.77</v>
       </c>
       <c r="CC13" t="n">
-        <v>3.71</v>
+        <v>3.59</v>
       </c>
       <c r="CD13" t="n">
-        <v>3.96</v>
+        <v>3.82</v>
       </c>
       <c r="CE13" t="n">
         <v>1.31</v>
       </c>
       <c r="CF13" t="n">
-        <v>2.48</v>
+        <v>2.49</v>
       </c>
       <c r="CG13" t="n">
-        <v>3.15</v>
+        <v>3.16</v>
       </c>
       <c r="CH13" t="n">
         <v>1.5</v>
       </c>
       <c r="CI13" t="n">
-        <v>2.18</v>
+        <v>2.17</v>
       </c>
       <c r="CJ13" t="n">
         <v>1.64</v>
       </c>
       <c r="CK13" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="CL13" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="CM13" t="n">
-        <v>2.52</v>
+        <v>2.51</v>
       </c>
       <c r="CN13" t="n">
         <v>1.94</v>
@@ -6091,13 +6091,13 @@
         <v>1.75</v>
       </c>
       <c r="CQ13" t="n">
-        <v>2.81</v>
+        <v>2.82</v>
       </c>
       <c r="CR13" t="n">
         <v>1.35</v>
       </c>
       <c r="CS13" t="n">
-        <v>2.63</v>
+        <v>2.64</v>
       </c>
       <c r="CT13" t="n">
         <v>3.24</v>
@@ -6112,100 +6112,100 @@
         <v>1.66</v>
       </c>
       <c r="CX13" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="CY13" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="CZ13" t="n">
-        <v>2.43</v>
+        <v>2.42</v>
       </c>
       <c r="DA13" t="n">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="DB13" t="n">
         <v>1.24</v>
       </c>
       <c r="DC13" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="DD13" t="n">
-        <v>2.88</v>
+        <v>2.89</v>
       </c>
       <c r="DE13" t="n">
         <v>0.16</v>
       </c>
       <c r="DF13" t="n">
-        <v>1.36</v>
+        <v>1.31</v>
       </c>
       <c r="DG13" t="n">
-        <v>3.32</v>
+        <v>3.38</v>
       </c>
       <c r="DH13" t="n">
-        <v>99.36</v>
+        <v>100</v>
       </c>
       <c r="DI13" t="n">
         <v>0.08</v>
       </c>
       <c r="DJ13" t="n">
+        <v>2</v>
+      </c>
+      <c r="DK13" t="n">
+        <v>5.46</v>
+      </c>
+      <c r="DL13" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="DM13" t="n">
+        <v>53.08</v>
+      </c>
+      <c r="DN13" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="DO13" t="n">
         <v>2.08</v>
       </c>
-      <c r="DK13" t="n">
-        <v>5.32</v>
-      </c>
-      <c r="DL13" t="n">
-        <v>0.36</v>
-      </c>
-      <c r="DM13" t="n">
-        <v>52.84</v>
-      </c>
-      <c r="DN13" t="n">
-        <v>0.64</v>
-      </c>
-      <c r="DO13" t="n">
-        <v>2</v>
-      </c>
       <c r="DP13" t="n">
-        <v>11.52</v>
+        <v>11.38</v>
       </c>
       <c r="DQ13" t="n">
-        <v>11.36</v>
+        <v>11.46</v>
       </c>
       <c r="DR13" t="n">
-        <v>7.52</v>
+        <v>7.5</v>
       </c>
       <c r="DS13" t="n">
-        <v>0.28</v>
+        <v>0.27</v>
       </c>
       <c r="DT13" t="n">
-        <v>0.28</v>
+        <v>0.27</v>
       </c>
       <c r="DU13" t="n">
         <v>0</v>
       </c>
       <c r="DV13" t="n">
-        <v>53.48</v>
+        <v>53.77</v>
       </c>
       <c r="DW13" t="n">
         <v>0.08</v>
       </c>
       <c r="DX13" t="n">
-        <v>14.6</v>
+        <v>14.58</v>
       </c>
       <c r="DY13" t="n">
         <v>10</v>
       </c>
       <c r="DZ13" t="n">
-        <v>4.6</v>
+        <v>4.58</v>
       </c>
       <c r="EA13" t="n">
-        <v>22.2</v>
+        <v>22.08</v>
       </c>
       <c r="EB13" t="n">
         <v>1.62</v>
       </c>
       <c r="EC13" t="n">
-        <v>1.92</v>
+        <v>1.84</v>
       </c>
     </row>
     <row r="14">
@@ -6215,13 +6215,13 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C14" t="n">
         <v>13</v>
       </c>
       <c r="D14" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E14" t="n">
         <v>0.15</v>
@@ -6305,52 +6305,52 @@
         <v>1.77</v>
       </c>
       <c r="AF14" t="n">
-        <v>0.17</v>
+        <v>0.15</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.67</v>
+        <v>1.54</v>
       </c>
       <c r="AH14" t="n">
-        <v>2.17</v>
+        <v>2.31</v>
       </c>
       <c r="AI14" t="n">
-        <v>92.33</v>
+        <v>92.45999999999999</v>
       </c>
       <c r="AJ14" t="n">
-        <v>0</v>
+        <v>-0.08</v>
       </c>
       <c r="AK14" t="n">
-        <v>2.33</v>
+        <v>2.15</v>
       </c>
       <c r="AL14" t="n">
-        <v>4.58</v>
+        <v>4.69</v>
       </c>
       <c r="AM14" t="n">
-        <v>0.67</v>
+        <v>0.62</v>
       </c>
       <c r="AN14" t="n">
-        <v>44.67</v>
+        <v>45.38</v>
       </c>
       <c r="AO14" t="n">
-        <v>0.67</v>
+        <v>0.62</v>
       </c>
       <c r="AP14" t="n">
-        <v>2.42</v>
+        <v>2.38</v>
       </c>
       <c r="AQ14" t="n">
-        <v>12</v>
+        <v>12.08</v>
       </c>
       <c r="AR14" t="n">
-        <v>9.58</v>
+        <v>9.619999999999999</v>
       </c>
       <c r="AS14" t="n">
-        <v>7.67</v>
+        <v>7.85</v>
       </c>
       <c r="AT14" t="n">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
       <c r="AU14" t="n">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="AV14" t="n">
         <v>0.08</v>
@@ -6362,82 +6362,82 @@
         <v>0</v>
       </c>
       <c r="AY14" t="n">
-        <v>47.25</v>
+        <v>47.77</v>
       </c>
       <c r="AZ14" t="n">
         <v>0</v>
       </c>
       <c r="BA14" t="n">
-        <v>11.33</v>
+        <v>11.69</v>
       </c>
       <c r="BB14" t="n">
-        <v>7.5</v>
+        <v>8</v>
       </c>
       <c r="BC14" t="n">
-        <v>3.83</v>
+        <v>3.69</v>
       </c>
       <c r="BD14" t="n">
-        <v>21.08</v>
+        <v>20.15</v>
       </c>
       <c r="BE14" t="n">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="BF14" t="n">
-        <v>2.33</v>
+        <v>2.15</v>
       </c>
       <c r="BG14" t="n">
-        <v>2.68</v>
+        <v>2.69</v>
       </c>
       <c r="BH14" t="n">
-        <v>10.16</v>
+        <v>10</v>
       </c>
       <c r="BI14" t="n">
-        <v>2.68</v>
+        <v>2.69</v>
       </c>
       <c r="BJ14" t="n">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="BK14" t="n">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="BL14" t="n">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="BM14" t="n">
-        <v>0.52</v>
+        <v>0.5</v>
       </c>
       <c r="BN14" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="BO14" t="n">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="BP14" t="n">
-        <v>5.04</v>
+        <v>4.92</v>
       </c>
       <c r="BQ14" t="n">
-        <v>5.12</v>
+        <v>5.08</v>
       </c>
       <c r="BR14" t="n">
-        <v>96</v>
+        <v>96.15000000000001</v>
       </c>
       <c r="BS14" t="n">
-        <v>76</v>
+        <v>76.92</v>
       </c>
       <c r="BT14" t="n">
-        <v>44</v>
+        <v>46.15</v>
       </c>
       <c r="BU14" t="n">
-        <v>32</v>
+        <v>30.77</v>
       </c>
       <c r="BV14" t="n">
-        <v>12</v>
+        <v>11.54</v>
       </c>
       <c r="BW14" t="n">
-        <v>4</v>
+        <v>3.85</v>
       </c>
       <c r="BX14" t="n">
-        <v>56</v>
+        <v>57.69</v>
       </c>
       <c r="BY14" t="n">
         <v>2.26</v>
@@ -6452,16 +6452,16 @@
         <v>3.51</v>
       </c>
       <c r="CC14" t="n">
-        <v>3.71</v>
+        <v>3.64</v>
       </c>
       <c r="CD14" t="n">
-        <v>3.85</v>
+        <v>3.76</v>
       </c>
       <c r="CE14" t="n">
         <v>1.36</v>
       </c>
       <c r="CF14" t="n">
-        <v>2.7</v>
+        <v>2.69</v>
       </c>
       <c r="CG14" t="n">
         <v>2.98</v>
@@ -6470,10 +6470,10 @@
         <v>1.43</v>
       </c>
       <c r="CI14" t="n">
-        <v>2.03</v>
+        <v>2.04</v>
       </c>
       <c r="CJ14" t="n">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="CK14" t="n">
         <v>1.47</v>
@@ -6482,7 +6482,7 @@
         <v>1.92</v>
       </c>
       <c r="CM14" t="n">
-        <v>2.5</v>
+        <v>2.51</v>
       </c>
       <c r="CN14" t="n">
         <v>1.92</v>
@@ -6494,34 +6494,34 @@
         <v>1.89</v>
       </c>
       <c r="CQ14" t="n">
-        <v>3.18</v>
+        <v>3.16</v>
       </c>
       <c r="CR14" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="CS14" t="n">
-        <v>2.86</v>
+        <v>2.85</v>
       </c>
       <c r="CT14" t="n">
-        <v>3.08</v>
+        <v>3.09</v>
       </c>
       <c r="CU14" t="n">
         <v>1.44</v>
       </c>
       <c r="CV14" t="n">
-        <v>2.12</v>
+        <v>2.13</v>
       </c>
       <c r="CW14" t="n">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="CX14" t="n">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="CY14" t="n">
         <v>1.88</v>
       </c>
       <c r="CZ14" t="n">
-        <v>2.45</v>
+        <v>2.46</v>
       </c>
       <c r="DA14" t="n">
         <v>1.93</v>
@@ -6530,52 +6530,52 @@
         <v>1.3</v>
       </c>
       <c r="DC14" t="n">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="DD14" t="n">
-        <v>3.37</v>
+        <v>3.35</v>
       </c>
       <c r="DE14" t="n">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
       <c r="DF14" t="n">
-        <v>1.68</v>
+        <v>1.61</v>
       </c>
       <c r="DG14" t="n">
-        <v>2.68</v>
+        <v>2.73</v>
       </c>
       <c r="DH14" t="n">
-        <v>94.36</v>
+        <v>94.34999999999999</v>
       </c>
       <c r="DI14" t="n">
-        <v>0</v>
+        <v>-0.04</v>
       </c>
       <c r="DJ14" t="n">
-        <v>2.24</v>
+        <v>2.15</v>
       </c>
       <c r="DK14" t="n">
-        <v>5.24</v>
+        <v>5.27</v>
       </c>
       <c r="DL14" t="n">
-        <v>0.4</v>
+        <v>0.38</v>
       </c>
       <c r="DM14" t="n">
-        <v>49.52</v>
+        <v>49.69</v>
       </c>
       <c r="DN14" t="n">
-        <v>0.48</v>
+        <v>0.46</v>
       </c>
       <c r="DO14" t="n">
-        <v>2.56</v>
+        <v>2.53</v>
       </c>
       <c r="DP14" t="n">
-        <v>11.72</v>
+        <v>11.77</v>
       </c>
       <c r="DQ14" t="n">
-        <v>10.92</v>
+        <v>10.88</v>
       </c>
       <c r="DR14" t="n">
-        <v>7.52</v>
+        <v>7.62</v>
       </c>
       <c r="DS14" t="n">
         <v>0.12</v>
@@ -6587,28 +6587,28 @@
         <v>0</v>
       </c>
       <c r="DV14" t="n">
-        <v>48.6</v>
+        <v>48.81</v>
       </c>
       <c r="DW14" t="n">
         <v>0.12</v>
       </c>
       <c r="DX14" t="n">
-        <v>12.72</v>
+        <v>12.84</v>
       </c>
       <c r="DY14" t="n">
-        <v>8.24</v>
+        <v>8.460000000000001</v>
       </c>
       <c r="DZ14" t="n">
-        <v>4.48</v>
+        <v>4.38</v>
       </c>
       <c r="EA14" t="n">
-        <v>19.6</v>
+        <v>19.19</v>
       </c>
       <c r="EB14" t="n">
         <v>1.48</v>
       </c>
       <c r="EC14" t="n">
-        <v>2.04</v>
+        <v>1.96</v>
       </c>
     </row>
     <row r="15">
@@ -6618,13 +6618,13 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C15" t="n">
         <v>13</v>
       </c>
       <c r="D15" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E15" t="n">
         <v>0.15</v>
@@ -6708,52 +6708,52 @@
         <v>2.46</v>
       </c>
       <c r="AF15" t="n">
-        <v>0.17</v>
+        <v>0.15</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.42</v>
+        <v>1.31</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.58</v>
+        <v>1.46</v>
       </c>
       <c r="AI15" t="n">
-        <v>84.08</v>
+        <v>83.54000000000001</v>
       </c>
       <c r="AJ15" t="n">
-        <v>0</v>
+        <v>-0.08</v>
       </c>
       <c r="AK15" t="n">
-        <v>2</v>
+        <v>1.85</v>
       </c>
       <c r="AL15" t="n">
-        <v>3.17</v>
+        <v>3.31</v>
       </c>
       <c r="AM15" t="n">
-        <v>0.33</v>
+        <v>0.31</v>
       </c>
       <c r="AN15" t="n">
-        <v>38.75</v>
+        <v>37.31</v>
       </c>
       <c r="AO15" t="n">
-        <v>0.58</v>
+        <v>0.54</v>
       </c>
       <c r="AP15" t="n">
-        <v>1.58</v>
+        <v>1.85</v>
       </c>
       <c r="AQ15" t="n">
-        <v>11.08</v>
+        <v>10.77</v>
       </c>
       <c r="AR15" t="n">
-        <v>11.67</v>
+        <v>11.15</v>
       </c>
       <c r="AS15" t="n">
-        <v>9.92</v>
+        <v>10.08</v>
       </c>
       <c r="AT15" t="n">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="AU15" t="n">
-        <v>0.67</v>
+        <v>0.85</v>
       </c>
       <c r="AV15" t="n">
         <v>0.08</v>
@@ -6765,73 +6765,73 @@
         <v>0</v>
       </c>
       <c r="AY15" t="n">
-        <v>43.83</v>
+        <v>42.69</v>
       </c>
       <c r="AZ15" t="n">
-        <v>0.17</v>
+        <v>0.15</v>
       </c>
       <c r="BA15" t="n">
-        <v>7.83</v>
+        <v>8.15</v>
       </c>
       <c r="BB15" t="n">
-        <v>5.58</v>
+        <v>5.85</v>
       </c>
       <c r="BC15" t="n">
-        <v>2.25</v>
+        <v>2.31</v>
       </c>
       <c r="BD15" t="n">
-        <v>17.5</v>
+        <v>16.92</v>
       </c>
       <c r="BE15" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.95</v>
       </c>
       <c r="BF15" t="n">
-        <v>1.83</v>
+        <v>1.69</v>
       </c>
       <c r="BG15" t="n">
-        <v>2.16</v>
+        <v>2.19</v>
       </c>
       <c r="BH15" t="n">
-        <v>9.800000000000001</v>
+        <v>9.960000000000001</v>
       </c>
       <c r="BI15" t="n">
-        <v>2.16</v>
+        <v>2.19</v>
       </c>
       <c r="BJ15" t="n">
-        <v>0.64</v>
+        <v>0.62</v>
       </c>
       <c r="BK15" t="n">
-        <v>0.6</v>
+        <v>0.65</v>
       </c>
       <c r="BL15" t="n">
-        <v>0.52</v>
+        <v>0.5</v>
       </c>
       <c r="BM15" t="n">
-        <v>0.4</v>
+        <v>0.42</v>
       </c>
       <c r="BN15" t="n">
         <v>0.92</v>
       </c>
       <c r="BO15" t="n">
-        <v>1.24</v>
+        <v>1.27</v>
       </c>
       <c r="BP15" t="n">
-        <v>4.56</v>
+        <v>4.73</v>
       </c>
       <c r="BQ15" t="n">
-        <v>5.24</v>
+        <v>5.23</v>
       </c>
       <c r="BR15" t="n">
-        <v>96</v>
+        <v>96.15000000000001</v>
       </c>
       <c r="BS15" t="n">
-        <v>68</v>
+        <v>69.23</v>
       </c>
       <c r="BT15" t="n">
-        <v>40</v>
+        <v>42.31</v>
       </c>
       <c r="BU15" t="n">
-        <v>12</v>
+        <v>11.54</v>
       </c>
       <c r="BV15" t="n">
         <v>0</v>
@@ -6840,7 +6840,7 @@
         <v>0</v>
       </c>
       <c r="BX15" t="n">
-        <v>32</v>
+        <v>30.77</v>
       </c>
       <c r="BY15" t="n">
         <v>3.1</v>
@@ -6849,22 +6849,22 @@
         <v>3.5</v>
       </c>
       <c r="CA15" t="n">
-        <v>3.53</v>
+        <v>3.56</v>
       </c>
       <c r="CB15" t="n">
-        <v>3.6</v>
+        <v>3.64</v>
       </c>
       <c r="CC15" t="n">
-        <v>4.23</v>
+        <v>4.37</v>
       </c>
       <c r="CD15" t="n">
-        <v>5.07</v>
+        <v>5.27</v>
       </c>
       <c r="CE15" t="n">
         <v>1.38</v>
       </c>
       <c r="CF15" t="n">
-        <v>2.82</v>
+        <v>2.81</v>
       </c>
       <c r="CG15" t="n">
         <v>2.87</v>
@@ -6873,7 +6873,7 @@
         <v>1.4</v>
       </c>
       <c r="CI15" t="n">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="CJ15" t="n">
         <v>1.83</v>
@@ -6882,7 +6882,7 @@
         <v>1.51</v>
       </c>
       <c r="CL15" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="CM15" t="n">
         <v>2.5</v>
@@ -6894,10 +6894,10 @@
         <v>1.31</v>
       </c>
       <c r="CP15" t="n">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="CQ15" t="n">
-        <v>3.42</v>
+        <v>3.4</v>
       </c>
       <c r="CR15" t="n">
         <v>1.41</v>
@@ -6906,13 +6906,13 @@
         <v>2.95</v>
       </c>
       <c r="CT15" t="n">
-        <v>2.98</v>
+        <v>2.99</v>
       </c>
       <c r="CU15" t="n">
         <v>1.43</v>
       </c>
       <c r="CV15" t="n">
-        <v>2.03</v>
+        <v>2.02</v>
       </c>
       <c r="CW15" t="n">
         <v>1.88</v>
@@ -6936,49 +6936,49 @@
         <v>2.05</v>
       </c>
       <c r="DD15" t="n">
-        <v>3.55</v>
+        <v>3.54</v>
       </c>
       <c r="DE15" t="n">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
       <c r="DF15" t="n">
-        <v>1.52</v>
+        <v>1.46</v>
       </c>
       <c r="DG15" t="n">
-        <v>1.96</v>
+        <v>1.89</v>
       </c>
       <c r="DH15" t="n">
-        <v>86.36</v>
+        <v>86</v>
       </c>
       <c r="DI15" t="n">
-        <v>0</v>
+        <v>-0.04</v>
       </c>
       <c r="DJ15" t="n">
-        <v>2.56</v>
+        <v>2.47</v>
       </c>
       <c r="DK15" t="n">
-        <v>4.28</v>
+        <v>4.31</v>
       </c>
       <c r="DL15" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.54</v>
       </c>
       <c r="DM15" t="n">
-        <v>44.6</v>
+        <v>43.66</v>
       </c>
       <c r="DN15" t="n">
-        <v>0.88</v>
+        <v>0.84</v>
       </c>
       <c r="DO15" t="n">
-        <v>2.32</v>
+        <v>2.42</v>
       </c>
       <c r="DP15" t="n">
-        <v>11</v>
+        <v>10.84</v>
       </c>
       <c r="DQ15" t="n">
-        <v>12.4</v>
+        <v>12.12</v>
       </c>
       <c r="DR15" t="n">
-        <v>9.32</v>
+        <v>9.42</v>
       </c>
       <c r="DS15" t="n">
         <v>0.12</v>
@@ -6990,28 +6990,28 @@
         <v>0</v>
       </c>
       <c r="DV15" t="n">
-        <v>43.76</v>
+        <v>43.19</v>
       </c>
       <c r="DW15" t="n">
-        <v>0.24</v>
+        <v>0.23</v>
       </c>
       <c r="DX15" t="n">
-        <v>9.48</v>
+        <v>9.57</v>
       </c>
       <c r="DY15" t="n">
-        <v>6.4</v>
+        <v>6.5</v>
       </c>
       <c r="DZ15" t="n">
         <v>3.08</v>
       </c>
       <c r="EA15" t="n">
-        <v>19.04</v>
+        <v>18.69</v>
       </c>
       <c r="EB15" t="n">
         <v>1.14</v>
       </c>
       <c r="EC15" t="n">
-        <v>2.16</v>
+        <v>2.08</v>
       </c>
     </row>
     <row r="16">
@@ -7021,94 +7021,94 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C16" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D16" t="n">
         <v>13</v>
       </c>
       <c r="E16" t="n">
-        <v>0.25</v>
+        <v>0.23</v>
       </c>
       <c r="F16" t="n">
-        <v>1.58</v>
+        <v>1.62</v>
       </c>
       <c r="G16" t="n">
-        <v>3.42</v>
+        <v>3.62</v>
       </c>
       <c r="H16" t="n">
-        <v>100.25</v>
+        <v>103.38</v>
       </c>
       <c r="I16" t="n">
         <v>0</v>
       </c>
       <c r="J16" t="n">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="K16" t="n">
-        <v>6.42</v>
+        <v>6.69</v>
       </c>
       <c r="L16" t="n">
-        <v>0.42</v>
+        <v>0.38</v>
       </c>
       <c r="M16" t="n">
-        <v>55.75</v>
+        <v>56.23</v>
       </c>
       <c r="N16" t="n">
-        <v>0.25</v>
+        <v>0.23</v>
       </c>
       <c r="O16" t="n">
-        <v>3</v>
+        <v>3.08</v>
       </c>
       <c r="P16" t="n">
-        <v>12.25</v>
+        <v>12.15</v>
       </c>
       <c r="Q16" t="n">
-        <v>10</v>
+        <v>10.15</v>
       </c>
       <c r="R16" t="n">
-        <v>5.42</v>
+        <v>5.23</v>
       </c>
       <c r="S16" t="n">
-        <v>0.25</v>
+        <v>0.31</v>
       </c>
       <c r="T16" t="n">
-        <v>2.17</v>
+        <v>2.15</v>
       </c>
       <c r="U16" t="n">
-        <v>0.17</v>
+        <v>0.15</v>
       </c>
       <c r="V16" t="n">
-        <v>0.17</v>
+        <v>0.15</v>
       </c>
       <c r="W16" t="n">
         <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>51.25</v>
+        <v>52.08</v>
       </c>
       <c r="Y16" t="n">
         <v>0</v>
       </c>
       <c r="Z16" t="n">
-        <v>16.5</v>
+        <v>16.77</v>
       </c>
       <c r="AA16" t="n">
-        <v>9.83</v>
+        <v>10.15</v>
       </c>
       <c r="AB16" t="n">
-        <v>6.67</v>
+        <v>6.62</v>
       </c>
       <c r="AC16" t="n">
-        <v>20.92</v>
+        <v>20.85</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.91</v>
+        <v>1.93</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="AF16" t="n">
         <v>0.08</v>
@@ -7192,70 +7192,70 @@
         <v>2.92</v>
       </c>
       <c r="BG16" t="n">
-        <v>2.2</v>
+        <v>2.23</v>
       </c>
       <c r="BH16" t="n">
-        <v>9.48</v>
+        <v>9.539999999999999</v>
       </c>
       <c r="BI16" t="n">
-        <v>2.2</v>
+        <v>2.23</v>
       </c>
       <c r="BJ16" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.58</v>
       </c>
       <c r="BK16" t="n">
-        <v>0.36</v>
+        <v>0.35</v>
       </c>
       <c r="BL16" t="n">
         <v>0.92</v>
       </c>
       <c r="BM16" t="n">
-        <v>0.36</v>
+        <v>0.38</v>
       </c>
       <c r="BN16" t="n">
-        <v>1.28</v>
+        <v>1.31</v>
       </c>
       <c r="BO16" t="n">
         <v>0.92</v>
       </c>
       <c r="BP16" t="n">
-        <v>4.76</v>
+        <v>4.73</v>
       </c>
       <c r="BQ16" t="n">
-        <v>4.72</v>
+        <v>4.81</v>
       </c>
       <c r="BR16" t="n">
-        <v>92</v>
+        <v>92.31</v>
       </c>
       <c r="BS16" t="n">
-        <v>72</v>
+        <v>73.08</v>
       </c>
       <c r="BT16" t="n">
-        <v>28</v>
+        <v>30.77</v>
       </c>
       <c r="BU16" t="n">
-        <v>16</v>
+        <v>15.38</v>
       </c>
       <c r="BV16" t="n">
-        <v>12</v>
+        <v>11.54</v>
       </c>
       <c r="BW16" t="n">
         <v>0</v>
       </c>
       <c r="BX16" t="n">
-        <v>44</v>
+        <v>46.15</v>
       </c>
       <c r="BY16" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="BZ16" t="n">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="CA16" t="n">
-        <v>4.16</v>
+        <v>4.17</v>
       </c>
       <c r="CB16" t="n">
-        <v>4.36</v>
+        <v>4.38</v>
       </c>
       <c r="CC16" t="n">
         <v>1.87</v>
@@ -7270,28 +7270,28 @@
         <v>2.55</v>
       </c>
       <c r="CG16" t="n">
-        <v>3.14</v>
+        <v>3.15</v>
       </c>
       <c r="CH16" t="n">
         <v>1.48</v>
       </c>
       <c r="CI16" t="n">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="CJ16" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="CK16" t="n">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="CL16" t="n">
         <v>1.96</v>
       </c>
       <c r="CM16" t="n">
-        <v>2.46</v>
+        <v>2.45</v>
       </c>
       <c r="CN16" t="n">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="CO16" t="n">
         <v>1.23</v>
@@ -7300,7 +7300,7 @@
         <v>1.8</v>
       </c>
       <c r="CQ16" t="n">
-        <v>2.87</v>
+        <v>2.88</v>
       </c>
       <c r="CR16" t="n">
         <v>1.37</v>
@@ -7309,16 +7309,16 @@
         <v>2.69</v>
       </c>
       <c r="CT16" t="n">
-        <v>3.13</v>
+        <v>3.14</v>
       </c>
       <c r="CU16" t="n">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="CV16" t="n">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="CW16" t="n">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="CX16" t="n">
         <v>1.58</v>
@@ -7330,7 +7330,7 @@
         <v>2.36</v>
       </c>
       <c r="DA16" t="n">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="DB16" t="n">
         <v>1.27</v>
@@ -7345,43 +7345,43 @@
         <v>0.16</v>
       </c>
       <c r="DF16" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="DG16" t="n">
-        <v>3.08</v>
+        <v>3.2</v>
       </c>
       <c r="DH16" t="n">
-        <v>106.08</v>
+        <v>107.42</v>
       </c>
       <c r="DI16" t="n">
         <v>0.04</v>
       </c>
       <c r="DJ16" t="n">
-        <v>2.44</v>
+        <v>2.42</v>
       </c>
       <c r="DK16" t="n">
-        <v>5.92</v>
+        <v>6.07</v>
       </c>
       <c r="DL16" t="n">
-        <v>0.48</v>
+        <v>0.46</v>
       </c>
       <c r="DM16" t="n">
-        <v>54.24</v>
+        <v>54.54</v>
       </c>
       <c r="DN16" t="n">
-        <v>0.64</v>
+        <v>0.62</v>
       </c>
       <c r="DO16" t="n">
-        <v>2.84</v>
+        <v>2.88</v>
       </c>
       <c r="DP16" t="n">
-        <v>12.96</v>
+        <v>12.88</v>
       </c>
       <c r="DQ16" t="n">
-        <v>9.640000000000001</v>
+        <v>9.73</v>
       </c>
       <c r="DR16" t="n">
-        <v>5.8</v>
+        <v>5.69</v>
       </c>
       <c r="DS16" t="n">
         <v>0.08</v>
@@ -7393,28 +7393,28 @@
         <v>0</v>
       </c>
       <c r="DV16" t="n">
-        <v>53.68</v>
+        <v>54</v>
       </c>
       <c r="DW16" t="n">
         <v>0.04</v>
       </c>
       <c r="DX16" t="n">
-        <v>15.36</v>
+        <v>15.54</v>
       </c>
       <c r="DY16" t="n">
-        <v>9.76</v>
+        <v>9.92</v>
       </c>
       <c r="DZ16" t="n">
-        <v>5.6</v>
+        <v>5.62</v>
       </c>
       <c r="EA16" t="n">
-        <v>20.28</v>
+        <v>20.27</v>
       </c>
       <c r="EB16" t="n">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="EC16" t="n">
-        <v>2.4</v>
+        <v>2.39</v>
       </c>
     </row>
     <row r="17">
@@ -7424,10 +7424,10 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C17" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D17" t="n">
         <v>13</v>
@@ -7439,79 +7439,79 @@
         <v>0.92</v>
       </c>
       <c r="G17" t="n">
-        <v>2.5</v>
+        <v>2.69</v>
       </c>
       <c r="H17" t="n">
-        <v>94.17</v>
+        <v>96.31</v>
       </c>
       <c r="I17" t="n">
         <v>0.08</v>
       </c>
       <c r="J17" t="n">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="K17" t="n">
-        <v>4.25</v>
+        <v>4.38</v>
       </c>
       <c r="L17" t="n">
-        <v>0.17</v>
+        <v>0.15</v>
       </c>
       <c r="M17" t="n">
-        <v>44.58</v>
+        <v>48.92</v>
       </c>
       <c r="N17" t="n">
-        <v>0.5</v>
+        <v>0.46</v>
       </c>
       <c r="O17" t="n">
-        <v>1.75</v>
+        <v>1.69</v>
       </c>
       <c r="P17" t="n">
-        <v>9.92</v>
+        <v>9.85</v>
       </c>
       <c r="Q17" t="n">
-        <v>12.83</v>
+        <v>12.77</v>
       </c>
       <c r="R17" t="n">
-        <v>9.58</v>
+        <v>9.15</v>
       </c>
       <c r="S17" t="n">
-        <v>1.17</v>
+        <v>1.38</v>
       </c>
       <c r="T17" t="n">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
       <c r="U17" t="n">
-        <v>0.33</v>
+        <v>0.31</v>
       </c>
       <c r="V17" t="n">
-        <v>0.33</v>
+        <v>0.31</v>
       </c>
       <c r="W17" t="n">
         <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>46.75</v>
+        <v>47.38</v>
       </c>
       <c r="Y17" t="n">
         <v>0.08</v>
       </c>
       <c r="Z17" t="n">
-        <v>12.92</v>
+        <v>14.23</v>
       </c>
       <c r="AA17" t="n">
-        <v>8.25</v>
+        <v>9.460000000000001</v>
       </c>
       <c r="AB17" t="n">
-        <v>4.67</v>
+        <v>4.77</v>
       </c>
       <c r="AC17" t="n">
-        <v>20.83</v>
+        <v>21</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.47</v>
+        <v>1.59</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AF17" t="n">
         <v>0.08</v>
@@ -7595,70 +7595,70 @@
         <v>1.85</v>
       </c>
       <c r="BG17" t="n">
-        <v>2.88</v>
+        <v>3</v>
       </c>
       <c r="BH17" t="n">
-        <v>9.76</v>
+        <v>9.77</v>
       </c>
       <c r="BI17" t="n">
-        <v>2.88</v>
+        <v>3</v>
       </c>
       <c r="BJ17" t="n">
-        <v>0.76</v>
+        <v>0.73</v>
       </c>
       <c r="BK17" t="n">
-        <v>0.64</v>
+        <v>0.73</v>
       </c>
       <c r="BL17" t="n">
-        <v>0.84</v>
+        <v>0.88</v>
       </c>
       <c r="BM17" t="n">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="BN17" t="n">
-        <v>1.48</v>
+        <v>1.54</v>
       </c>
       <c r="BO17" t="n">
-        <v>1.4</v>
+        <v>1.46</v>
       </c>
       <c r="BP17" t="n">
-        <v>3.64</v>
+        <v>3.65</v>
       </c>
       <c r="BQ17" t="n">
-        <v>5.56</v>
+        <v>5.58</v>
       </c>
       <c r="BR17" t="n">
-        <v>92</v>
+        <v>92.31</v>
       </c>
       <c r="BS17" t="n">
-        <v>80</v>
+        <v>80.77</v>
       </c>
       <c r="BT17" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="BU17" t="n">
-        <v>36</v>
+        <v>38.46</v>
       </c>
       <c r="BV17" t="n">
-        <v>24</v>
+        <v>26.92</v>
       </c>
       <c r="BW17" t="n">
-        <v>4</v>
+        <v>7.69</v>
       </c>
       <c r="BX17" t="n">
-        <v>64</v>
+        <v>65.38</v>
       </c>
       <c r="BY17" t="n">
-        <v>2.94</v>
+        <v>2.95</v>
       </c>
       <c r="BZ17" t="n">
-        <v>3.15</v>
+        <v>3.16</v>
       </c>
       <c r="CA17" t="n">
-        <v>3.76</v>
+        <v>3.74</v>
       </c>
       <c r="CB17" t="n">
-        <v>3.83</v>
+        <v>3.82</v>
       </c>
       <c r="CC17" t="n">
         <v>4.44</v>
@@ -7667,58 +7667,58 @@
         <v>4.9</v>
       </c>
       <c r="CE17" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="CF17" t="n">
-        <v>2.47</v>
+        <v>2.48</v>
       </c>
       <c r="CG17" t="n">
-        <v>3.29</v>
+        <v>3.28</v>
       </c>
       <c r="CH17" t="n">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="CI17" t="n">
-        <v>2.18</v>
+        <v>2.17</v>
       </c>
       <c r="CJ17" t="n">
         <v>1.64</v>
       </c>
       <c r="CK17" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="CL17" t="n">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="CM17" t="n">
-        <v>2.64</v>
+        <v>2.65</v>
       </c>
       <c r="CN17" t="n">
-        <v>2.05</v>
+        <v>2.04</v>
       </c>
       <c r="CO17" t="n">
         <v>1.21</v>
       </c>
       <c r="CP17" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="CQ17" t="n">
-        <v>2.72</v>
+        <v>2.74</v>
       </c>
       <c r="CR17" t="n">
         <v>1.35</v>
       </c>
       <c r="CS17" t="n">
-        <v>2.56</v>
+        <v>2.57</v>
       </c>
       <c r="CT17" t="n">
-        <v>3.24</v>
+        <v>3.23</v>
       </c>
       <c r="CU17" t="n">
         <v>1.53</v>
       </c>
       <c r="CV17" t="n">
-        <v>2.29</v>
+        <v>2.3</v>
       </c>
       <c r="CW17" t="n">
         <v>1.68</v>
@@ -7733,58 +7733,58 @@
         <v>2.45</v>
       </c>
       <c r="DA17" t="n">
-        <v>2.03</v>
+        <v>2.04</v>
       </c>
       <c r="DB17" t="n">
         <v>1.24</v>
       </c>
       <c r="DC17" t="n">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="DD17" t="n">
-        <v>2.87</v>
+        <v>2.88</v>
       </c>
       <c r="DE17" t="n">
         <v>0.04</v>
       </c>
       <c r="DF17" t="n">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="DG17" t="n">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="DH17" t="n">
-        <v>94.36</v>
+        <v>95.43000000000001</v>
       </c>
       <c r="DI17" t="n">
         <v>0.08</v>
       </c>
       <c r="DJ17" t="n">
-        <v>1.84</v>
+        <v>1.8</v>
       </c>
       <c r="DK17" t="n">
-        <v>4.28</v>
+        <v>4.34</v>
       </c>
       <c r="DL17" t="n">
-        <v>0.2</v>
+        <v>0.19</v>
       </c>
       <c r="DM17" t="n">
-        <v>45.68</v>
+        <v>47.8</v>
       </c>
       <c r="DN17" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.54</v>
       </c>
       <c r="DO17" t="n">
-        <v>1.6</v>
+        <v>1.58</v>
       </c>
       <c r="DP17" t="n">
-        <v>11.08</v>
+        <v>11</v>
       </c>
       <c r="DQ17" t="n">
         <v>11.84</v>
       </c>
       <c r="DR17" t="n">
-        <v>9.44</v>
+        <v>9.23</v>
       </c>
       <c r="DS17" t="n">
         <v>0.2</v>
@@ -7796,28 +7796,28 @@
         <v>0</v>
       </c>
       <c r="DV17" t="n">
-        <v>47.12</v>
+        <v>47.42</v>
       </c>
       <c r="DW17" t="n">
         <v>0.12</v>
       </c>
       <c r="DX17" t="n">
-        <v>11.72</v>
+        <v>12.42</v>
       </c>
       <c r="DY17" t="n">
-        <v>7.64</v>
+        <v>8.27</v>
       </c>
       <c r="DZ17" t="n">
-        <v>4.08</v>
+        <v>4.16</v>
       </c>
       <c r="EA17" t="n">
-        <v>19.92</v>
+        <v>20.04</v>
       </c>
       <c r="EB17" t="n">
-        <v>1.36</v>
+        <v>1.42</v>
       </c>
       <c r="EC17" t="n">
-        <v>1.6</v>
+        <v>1.58</v>
       </c>
     </row>
   </sheetData>

--- a/data/teams/leagues/Averages_Belgium_Pro_League_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Belgium_Pro_League_2025-2026.xlsx
@@ -7496,10 +7496,10 @@
         <v>0.08</v>
       </c>
       <c r="Z17" t="n">
-        <v>14.23</v>
+        <v>14.31</v>
       </c>
       <c r="AA17" t="n">
-        <v>9.460000000000001</v>
+        <v>9.539999999999999</v>
       </c>
       <c r="AB17" t="n">
         <v>4.77</v>
@@ -7802,10 +7802,10 @@
         <v>0.12</v>
       </c>
       <c r="DX17" t="n">
-        <v>12.42</v>
+        <v>12.47</v>
       </c>
       <c r="DY17" t="n">
-        <v>8.27</v>
+        <v>8.31</v>
       </c>
       <c r="DZ17" t="n">
         <v>4.16</v>

--- a/data/teams/leagues/Averages_Belgium_Pro_League_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Belgium_Pro_League_2025-2026.xlsx
@@ -3394,94 +3394,94 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C7" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D7" t="n">
         <v>13</v>
       </c>
       <c r="E7" t="n">
-        <v>0.15</v>
+        <v>0.21</v>
       </c>
       <c r="F7" t="n">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="G7" t="n">
-        <v>2.54</v>
+        <v>2.43</v>
       </c>
       <c r="H7" t="n">
-        <v>89.54000000000001</v>
+        <v>89.20999999999999</v>
       </c>
       <c r="I7" t="n">
-        <v>0.23</v>
+        <v>0.21</v>
       </c>
       <c r="J7" t="n">
-        <v>2.31</v>
+        <v>2.21</v>
       </c>
       <c r="K7" t="n">
-        <v>4.62</v>
+        <v>4.36</v>
       </c>
       <c r="L7" t="n">
-        <v>0.23</v>
+        <v>0.21</v>
       </c>
       <c r="M7" t="n">
-        <v>50</v>
+        <v>49.07</v>
       </c>
       <c r="N7" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.64</v>
       </c>
       <c r="O7" t="n">
-        <v>2.08</v>
+        <v>1.93</v>
       </c>
       <c r="P7" t="n">
-        <v>10.46</v>
+        <v>10.5</v>
       </c>
       <c r="Q7" t="n">
-        <v>11.62</v>
+        <v>11.57</v>
       </c>
       <c r="R7" t="n">
-        <v>9.15</v>
+        <v>9.5</v>
       </c>
       <c r="S7" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="T7" t="n">
-        <v>1.23</v>
+        <v>1.29</v>
       </c>
       <c r="U7" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="V7" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>49.38</v>
+        <v>48.71</v>
       </c>
       <c r="Y7" t="n">
         <v>0</v>
       </c>
       <c r="Z7" t="n">
-        <v>10.85</v>
+        <v>10.43</v>
       </c>
       <c r="AA7" t="n">
-        <v>7.15</v>
+        <v>6.79</v>
       </c>
       <c r="AB7" t="n">
-        <v>3.69</v>
+        <v>3.64</v>
       </c>
       <c r="AC7" t="n">
-        <v>21.08</v>
+        <v>21.36</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.31</v>
+        <v>1.27</v>
       </c>
       <c r="AE7" t="n">
-        <v>2.31</v>
+        <v>2.21</v>
       </c>
       <c r="AF7" t="n">
         <v>0.08</v>
@@ -3565,70 +3565,70 @@
         <v>2.38</v>
       </c>
       <c r="BG7" t="n">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="BH7" t="n">
-        <v>11</v>
+        <v>10.93</v>
       </c>
       <c r="BI7" t="n">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="BJ7" t="n">
-        <v>0.54</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="BK7" t="n">
-        <v>0.46</v>
+        <v>0.44</v>
       </c>
       <c r="BL7" t="n">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="BM7" t="n">
         <v>0.8100000000000001</v>
       </c>
       <c r="BN7" t="n">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="BO7" t="n">
         <v>1</v>
       </c>
       <c r="BP7" t="n">
-        <v>4.92</v>
+        <v>4.89</v>
       </c>
       <c r="BQ7" t="n">
-        <v>6.08</v>
+        <v>6.04</v>
       </c>
       <c r="BR7" t="n">
-        <v>96.15000000000001</v>
+        <v>96.3</v>
       </c>
       <c r="BS7" t="n">
-        <v>73.08</v>
+        <v>74.06999999999999</v>
       </c>
       <c r="BT7" t="n">
-        <v>34.62</v>
+        <v>37.04</v>
       </c>
       <c r="BU7" t="n">
-        <v>26.92</v>
+        <v>25.93</v>
       </c>
       <c r="BV7" t="n">
-        <v>11.54</v>
+        <v>11.11</v>
       </c>
       <c r="BW7" t="n">
         <v>0</v>
       </c>
       <c r="BX7" t="n">
-        <v>61.54</v>
+        <v>62.96</v>
       </c>
       <c r="BY7" t="n">
-        <v>2.82</v>
+        <v>2.77</v>
       </c>
       <c r="BZ7" t="n">
-        <v>2.97</v>
+        <v>2.93</v>
       </c>
       <c r="CA7" t="n">
         <v>3.65</v>
       </c>
       <c r="CB7" t="n">
-        <v>3.78</v>
+        <v>3.77</v>
       </c>
       <c r="CC7" t="n">
         <v>3.86</v>
@@ -3640,16 +3640,16 @@
         <v>1.31</v>
       </c>
       <c r="CF7" t="n">
-        <v>2.48</v>
+        <v>2.47</v>
       </c>
       <c r="CG7" t="n">
-        <v>3.18</v>
+        <v>3.19</v>
       </c>
       <c r="CH7" t="n">
         <v>1.5</v>
       </c>
       <c r="CI7" t="n">
-        <v>2.19</v>
+        <v>2.2</v>
       </c>
       <c r="CJ7" t="n">
         <v>1.64</v>
@@ -3664,7 +3664,7 @@
         <v>2.72</v>
       </c>
       <c r="CN7" t="n">
-        <v>2.08</v>
+        <v>2.07</v>
       </c>
       <c r="CO7" t="n">
         <v>1.22</v>
@@ -3688,13 +3688,13 @@
         <v>1.52</v>
       </c>
       <c r="CV7" t="n">
-        <v>2.31</v>
+        <v>2.32</v>
       </c>
       <c r="CW7" t="n">
         <v>1.67</v>
       </c>
       <c r="CX7" t="n">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="CY7" t="n">
         <v>1.74</v>
@@ -3712,82 +3712,82 @@
         <v>1.79</v>
       </c>
       <c r="DD7" t="n">
-        <v>2.9</v>
+        <v>2.89</v>
       </c>
       <c r="DE7" t="n">
-        <v>0.12</v>
+        <v>0.15</v>
       </c>
       <c r="DF7" t="n">
-        <v>1.62</v>
+        <v>1.59</v>
       </c>
       <c r="DG7" t="n">
-        <v>2.73</v>
+        <v>2.67</v>
       </c>
       <c r="DH7" t="n">
-        <v>89.23</v>
+        <v>89.06999999999999</v>
       </c>
       <c r="DI7" t="n">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
       <c r="DJ7" t="n">
-        <v>2.34</v>
+        <v>2.29</v>
       </c>
       <c r="DK7" t="n">
-        <v>4.81</v>
+        <v>4.67</v>
       </c>
       <c r="DL7" t="n">
-        <v>0.27</v>
+        <v>0.26</v>
       </c>
       <c r="DM7" t="n">
-        <v>46.73</v>
+        <v>46.37</v>
       </c>
       <c r="DN7" t="n">
-        <v>0.73</v>
+        <v>0.7</v>
       </c>
       <c r="DO7" t="n">
-        <v>2.08</v>
+        <v>2</v>
       </c>
       <c r="DP7" t="n">
-        <v>10.58</v>
+        <v>10.59</v>
       </c>
       <c r="DQ7" t="n">
-        <v>11.7</v>
+        <v>11.67</v>
       </c>
       <c r="DR7" t="n">
-        <v>9</v>
+        <v>9.19</v>
       </c>
       <c r="DS7" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="DT7" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="DU7" t="n">
         <v>0</v>
       </c>
       <c r="DV7" t="n">
-        <v>50.26</v>
+        <v>49.88</v>
       </c>
       <c r="DW7" t="n">
         <v>0</v>
       </c>
       <c r="DX7" t="n">
-        <v>10.42</v>
+        <v>10.22</v>
       </c>
       <c r="DY7" t="n">
-        <v>6.54</v>
+        <v>6.37</v>
       </c>
       <c r="DZ7" t="n">
-        <v>3.88</v>
+        <v>3.85</v>
       </c>
       <c r="EA7" t="n">
-        <v>21.19</v>
+        <v>21.34</v>
       </c>
       <c r="EB7" t="n">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="EC7" t="n">
-        <v>2.34</v>
+        <v>2.29</v>
       </c>
     </row>
     <row r="8">
@@ -4200,13 +4200,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C9" t="n">
         <v>13</v>
       </c>
       <c r="D9" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E9" t="n">
         <v>0.23</v>
@@ -4290,139 +4290,139 @@
         <v>3</v>
       </c>
       <c r="AF9" t="n">
-        <v>0</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="AG9" t="n">
-        <v>2.23</v>
+        <v>2.29</v>
       </c>
       <c r="AH9" t="n">
-        <v>2.54</v>
+        <v>2.29</v>
       </c>
       <c r="AI9" t="n">
-        <v>76.69</v>
+        <v>76.5</v>
       </c>
       <c r="AJ9" t="n">
         <v>0</v>
       </c>
       <c r="AK9" t="n">
-        <v>3.31</v>
+        <v>3.36</v>
       </c>
       <c r="AL9" t="n">
-        <v>4.31</v>
+        <v>4.5</v>
       </c>
       <c r="AM9" t="n">
-        <v>0.46</v>
+        <v>0.36</v>
       </c>
       <c r="AN9" t="n">
-        <v>44.31</v>
+        <v>43.21</v>
       </c>
       <c r="AO9" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="AP9" t="n">
-        <v>1.77</v>
+        <v>1.57</v>
       </c>
       <c r="AQ9" t="n">
-        <v>16</v>
+        <v>15.71</v>
       </c>
       <c r="AR9" t="n">
-        <v>10.38</v>
+        <v>10.86</v>
       </c>
       <c r="AS9" t="n">
-        <v>9.08</v>
+        <v>8.859999999999999</v>
       </c>
       <c r="AT9" t="n">
-        <v>1.54</v>
+        <v>1.79</v>
       </c>
       <c r="AU9" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="AV9" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="AW9" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="AX9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY9" t="n">
+        <v>44.07</v>
+      </c>
+      <c r="AZ9" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="BA9" t="n">
+        <v>12.07</v>
+      </c>
+      <c r="BB9" t="n">
+        <v>8.289999999999999</v>
+      </c>
+      <c r="BC9" t="n">
+        <v>3.79</v>
+      </c>
+      <c r="BD9" t="n">
+        <v>19</v>
+      </c>
+      <c r="BE9" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="BF9" t="n">
+        <v>3.29</v>
+      </c>
+      <c r="BG9" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="BH9" t="n">
+        <v>10.96</v>
+      </c>
+      <c r="BI9" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="BJ9" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="BK9" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="BL9" t="n">
         <v>0.85</v>
       </c>
-      <c r="AV9" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="AW9" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="AX9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY9" t="n">
-        <v>44.15</v>
-      </c>
-      <c r="AZ9" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="BA9" t="n">
-        <v>12.46</v>
-      </c>
-      <c r="BB9" t="n">
-        <v>8.539999999999999</v>
-      </c>
-      <c r="BC9" t="n">
-        <v>3.92</v>
-      </c>
-      <c r="BD9" t="n">
-        <v>19.15</v>
-      </c>
-      <c r="BE9" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="BF9" t="n">
-        <v>3.23</v>
-      </c>
-      <c r="BG9" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="BH9" t="n">
-        <v>10.77</v>
-      </c>
-      <c r="BI9" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="BJ9" t="n">
-        <v>0.6899999999999999</v>
-      </c>
-      <c r="BK9" t="n">
-        <v>0.46</v>
-      </c>
-      <c r="BL9" t="n">
-        <v>0.73</v>
-      </c>
       <c r="BM9" t="n">
-        <v>0.62</v>
+        <v>0.59</v>
       </c>
       <c r="BN9" t="n">
-        <v>1.35</v>
+        <v>1.44</v>
       </c>
       <c r="BO9" t="n">
-        <v>1.15</v>
+        <v>1.19</v>
       </c>
       <c r="BP9" t="n">
-        <v>5.27</v>
+        <v>5.04</v>
       </c>
       <c r="BQ9" t="n">
-        <v>5.46</v>
+        <v>5.22</v>
       </c>
       <c r="BR9" t="n">
-        <v>92.31</v>
+        <v>92.59</v>
       </c>
       <c r="BS9" t="n">
-        <v>73.08</v>
+        <v>74.06999999999999</v>
       </c>
       <c r="BT9" t="n">
-        <v>50</v>
+        <v>51.85</v>
       </c>
       <c r="BU9" t="n">
-        <v>26.92</v>
+        <v>29.63</v>
       </c>
       <c r="BV9" t="n">
-        <v>7.69</v>
+        <v>11.11</v>
       </c>
       <c r="BW9" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="BX9" t="n">
-        <v>53.85</v>
+        <v>55.56</v>
       </c>
       <c r="BY9" t="n">
         <v>2.91</v>
@@ -4431,22 +4431,22 @@
         <v>2.95</v>
       </c>
       <c r="CA9" t="n">
-        <v>3.54</v>
+        <v>3.53</v>
       </c>
       <c r="CB9" t="n">
-        <v>3.6</v>
+        <v>3.61</v>
       </c>
       <c r="CC9" t="n">
-        <v>4.42</v>
+        <v>4.43</v>
       </c>
       <c r="CD9" t="n">
-        <v>4.72</v>
+        <v>4.74</v>
       </c>
       <c r="CE9" t="n">
         <v>1.37</v>
       </c>
       <c r="CF9" t="n">
-        <v>2.72</v>
+        <v>2.71</v>
       </c>
       <c r="CG9" t="n">
         <v>2.97</v>
@@ -4464,19 +4464,19 @@
         <v>1.47</v>
       </c>
       <c r="CL9" t="n">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="CM9" t="n">
-        <v>2.52</v>
+        <v>2.54</v>
       </c>
       <c r="CN9" t="n">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="CO9" t="n">
         <v>1.28</v>
       </c>
       <c r="CP9" t="n">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="CQ9" t="n">
         <v>3.27</v>
@@ -4488,7 +4488,7 @@
         <v>2.81</v>
       </c>
       <c r="CT9" t="n">
-        <v>3.08</v>
+        <v>3.1</v>
       </c>
       <c r="CU9" t="n">
         <v>1.46</v>
@@ -4500,100 +4500,100 @@
         <v>1.8</v>
       </c>
       <c r="CX9" t="n">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="CY9" t="n">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="CZ9" t="n">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="DA9" t="n">
-        <v>1.99</v>
+        <v>2.01</v>
       </c>
       <c r="DB9" t="n">
         <v>1.3</v>
       </c>
       <c r="DC9" t="n">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="DD9" t="n">
-        <v>3.35</v>
+        <v>3.34</v>
       </c>
       <c r="DE9" t="n">
-        <v>0.12</v>
+        <v>0.15</v>
       </c>
       <c r="DF9" t="n">
-        <v>2.23</v>
+        <v>2.26</v>
       </c>
       <c r="DG9" t="n">
-        <v>2.46</v>
+        <v>2.33</v>
       </c>
       <c r="DH9" t="n">
-        <v>78.92</v>
+        <v>78.73999999999999</v>
       </c>
       <c r="DI9" t="n">
         <v>0.04</v>
       </c>
       <c r="DJ9" t="n">
-        <v>3.16</v>
+        <v>3.19</v>
       </c>
       <c r="DK9" t="n">
-        <v>4.66</v>
+        <v>4.74</v>
       </c>
       <c r="DL9" t="n">
-        <v>0.5</v>
+        <v>0.45</v>
       </c>
       <c r="DM9" t="n">
-        <v>42.58</v>
+        <v>42.07</v>
       </c>
       <c r="DN9" t="n">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="DO9" t="n">
-        <v>2.16</v>
+        <v>2.04</v>
       </c>
       <c r="DP9" t="n">
-        <v>16.04</v>
+        <v>15.89</v>
       </c>
       <c r="DQ9" t="n">
-        <v>11.34</v>
+        <v>11.56</v>
       </c>
       <c r="DR9" t="n">
-        <v>8.460000000000001</v>
+        <v>8.369999999999999</v>
       </c>
       <c r="DS9" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DT9" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DU9" t="n">
         <v>0</v>
       </c>
       <c r="DV9" t="n">
-        <v>44.76</v>
+        <v>44.7</v>
       </c>
       <c r="DW9" t="n">
         <v>0.04</v>
       </c>
       <c r="DX9" t="n">
-        <v>13.77</v>
+        <v>13.52</v>
       </c>
       <c r="DY9" t="n">
-        <v>9.35</v>
+        <v>9.19</v>
       </c>
       <c r="DZ9" t="n">
-        <v>4.42</v>
+        <v>4.33</v>
       </c>
       <c r="EA9" t="n">
-        <v>19.58</v>
+        <v>19.48</v>
       </c>
       <c r="EB9" t="n">
-        <v>1.48</v>
+        <v>1.46</v>
       </c>
       <c r="EC9" t="n">
-        <v>3.12</v>
+        <v>3.15</v>
       </c>
     </row>
     <row r="10">
@@ -4603,13 +4603,13 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C10" t="n">
         <v>13</v>
       </c>
       <c r="D10" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
@@ -4693,52 +4693,52 @@
         <v>1.46</v>
       </c>
       <c r="AF10" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.62</v>
+        <v>1.71</v>
       </c>
       <c r="AH10" t="n">
-        <v>2.38</v>
+        <v>2.29</v>
       </c>
       <c r="AI10" t="n">
-        <v>80.62</v>
+        <v>81.43000000000001</v>
       </c>
       <c r="AJ10" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="AK10" t="n">
-        <v>2.46</v>
+        <v>2.5</v>
       </c>
       <c r="AL10" t="n">
-        <v>3.62</v>
+        <v>3.57</v>
       </c>
       <c r="AM10" t="n">
-        <v>0.23</v>
+        <v>0.21</v>
       </c>
       <c r="AN10" t="n">
-        <v>36.54</v>
+        <v>36.21</v>
       </c>
       <c r="AO10" t="n">
-        <v>0.77</v>
+        <v>0.71</v>
       </c>
       <c r="AP10" t="n">
-        <v>1.23</v>
+        <v>1.29</v>
       </c>
       <c r="AQ10" t="n">
-        <v>11.85</v>
+        <v>12</v>
       </c>
       <c r="AR10" t="n">
-        <v>12.77</v>
+        <v>12.71</v>
       </c>
       <c r="AS10" t="n">
-        <v>8.619999999999999</v>
+        <v>8.43</v>
       </c>
       <c r="AT10" t="n">
-        <v>1.46</v>
+        <v>1.43</v>
       </c>
       <c r="AU10" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="AV10" t="n">
         <v>0</v>
@@ -4750,82 +4750,82 @@
         <v>0</v>
       </c>
       <c r="AY10" t="n">
-        <v>33.54</v>
+        <v>34.5</v>
       </c>
       <c r="AZ10" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="BA10" t="n">
-        <v>8.69</v>
+        <v>8.93</v>
       </c>
       <c r="BB10" t="n">
-        <v>6.38</v>
+        <v>6.57</v>
       </c>
       <c r="BC10" t="n">
-        <v>2.31</v>
+        <v>2.36</v>
       </c>
       <c r="BD10" t="n">
-        <v>20.77</v>
+        <v>20.86</v>
       </c>
       <c r="BE10" t="n">
-        <v>0.98</v>
+        <v>1</v>
       </c>
       <c r="BF10" t="n">
-        <v>2.31</v>
+        <v>2.36</v>
       </c>
       <c r="BG10" t="n">
         <v>1.96</v>
       </c>
       <c r="BH10" t="n">
-        <v>9.08</v>
+        <v>9</v>
       </c>
       <c r="BI10" t="n">
         <v>1.96</v>
       </c>
       <c r="BJ10" t="n">
-        <v>0.5</v>
+        <v>0.52</v>
       </c>
       <c r="BK10" t="n">
-        <v>0.35</v>
+        <v>0.37</v>
       </c>
       <c r="BL10" t="n">
-        <v>0.5</v>
+        <v>0.48</v>
       </c>
       <c r="BM10" t="n">
-        <v>0.62</v>
+        <v>0.59</v>
       </c>
       <c r="BN10" t="n">
-        <v>1.12</v>
+        <v>1.07</v>
       </c>
       <c r="BO10" t="n">
-        <v>0.85</v>
+        <v>0.89</v>
       </c>
       <c r="BP10" t="n">
-        <v>3.81</v>
+        <v>3.89</v>
       </c>
       <c r="BQ10" t="n">
-        <v>5.27</v>
+        <v>5.11</v>
       </c>
       <c r="BR10" t="n">
-        <v>73.08</v>
+        <v>74.06999999999999</v>
       </c>
       <c r="BS10" t="n">
-        <v>57.69</v>
+        <v>59.26</v>
       </c>
       <c r="BT10" t="n">
-        <v>42.31</v>
+        <v>40.74</v>
       </c>
       <c r="BU10" t="n">
-        <v>15.38</v>
+        <v>14.81</v>
       </c>
       <c r="BV10" t="n">
-        <v>7.69</v>
+        <v>7.41</v>
       </c>
       <c r="BW10" t="n">
         <v>0</v>
       </c>
       <c r="BX10" t="n">
-        <v>50</v>
+        <v>51.85</v>
       </c>
       <c r="BY10" t="n">
         <v>3.33</v>
@@ -4834,28 +4834,28 @@
         <v>3.41</v>
       </c>
       <c r="CA10" t="n">
-        <v>3.55</v>
+        <v>3.54</v>
       </c>
       <c r="CB10" t="n">
-        <v>3.65</v>
+        <v>3.63</v>
       </c>
       <c r="CC10" t="n">
-        <v>4.8</v>
+        <v>4.69</v>
       </c>
       <c r="CD10" t="n">
-        <v>5.11</v>
+        <v>4.98</v>
       </c>
       <c r="CE10" t="n">
         <v>1.39</v>
       </c>
       <c r="CF10" t="n">
-        <v>2.79</v>
+        <v>2.81</v>
       </c>
       <c r="CG10" t="n">
-        <v>2.87</v>
+        <v>2.85</v>
       </c>
       <c r="CH10" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="CI10" t="n">
         <v>1.89</v>
@@ -4867,7 +4867,7 @@
         <v>1.57</v>
       </c>
       <c r="CL10" t="n">
-        <v>2.01</v>
+        <v>2</v>
       </c>
       <c r="CM10" t="n">
         <v>2.32</v>
@@ -4876,13 +4876,13 @@
         <v>1.82</v>
       </c>
       <c r="CO10" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="CP10" t="n">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="CQ10" t="n">
-        <v>3.49</v>
+        <v>3.52</v>
       </c>
       <c r="CR10" t="n">
         <v>1.4</v>
@@ -4918,52 +4918,52 @@
         <v>1.33</v>
       </c>
       <c r="DC10" t="n">
-        <v>2.06</v>
+        <v>2.07</v>
       </c>
       <c r="DD10" t="n">
-        <v>3.56</v>
+        <v>3.61</v>
       </c>
       <c r="DE10" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="DF10" t="n">
-        <v>1.2</v>
+        <v>1.26</v>
       </c>
       <c r="DG10" t="n">
-        <v>2.8</v>
+        <v>2.74</v>
       </c>
       <c r="DH10" t="n">
-        <v>81.65000000000001</v>
+        <v>82.04000000000001</v>
       </c>
       <c r="DI10" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DJ10" t="n">
-        <v>2.04</v>
+        <v>2.08</v>
       </c>
       <c r="DK10" t="n">
-        <v>4.66</v>
+        <v>4.59</v>
       </c>
       <c r="DL10" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
       <c r="DM10" t="n">
-        <v>40.77</v>
+        <v>40.44</v>
       </c>
       <c r="DN10" t="n">
-        <v>0.77</v>
+        <v>0.74</v>
       </c>
       <c r="DO10" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="DP10" t="n">
-        <v>11.54</v>
+        <v>11.63</v>
       </c>
       <c r="DQ10" t="n">
-        <v>12.34</v>
+        <v>12.33</v>
       </c>
       <c r="DR10" t="n">
-        <v>8.460000000000001</v>
+        <v>8.369999999999999</v>
       </c>
       <c r="DS10" t="n">
         <v>0</v>
@@ -4975,28 +4975,28 @@
         <v>0</v>
       </c>
       <c r="DV10" t="n">
-        <v>35.7</v>
+        <v>36.11</v>
       </c>
       <c r="DW10" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="DX10" t="n">
-        <v>9.300000000000001</v>
+        <v>9.41</v>
       </c>
       <c r="DY10" t="n">
-        <v>6.73</v>
+        <v>6.82</v>
       </c>
       <c r="DZ10" t="n">
-        <v>2.58</v>
+        <v>2.6</v>
       </c>
       <c r="EA10" t="n">
-        <v>21.38</v>
+        <v>21.41</v>
       </c>
       <c r="EB10" t="n">
         <v>1.05</v>
       </c>
       <c r="EC10" t="n">
-        <v>1.89</v>
+        <v>1.93</v>
       </c>
     </row>
     <row r="11">
@@ -5006,94 +5006,94 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C11" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D11" t="n">
         <v>13</v>
       </c>
       <c r="E11" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="F11" t="n">
-        <v>1.54</v>
+        <v>1.71</v>
       </c>
       <c r="G11" t="n">
-        <v>3.38</v>
+        <v>3.07</v>
       </c>
       <c r="H11" t="n">
-        <v>109.69</v>
+        <v>109.57</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
       </c>
       <c r="J11" t="n">
-        <v>2.54</v>
+        <v>2.64</v>
       </c>
       <c r="K11" t="n">
-        <v>6.62</v>
+        <v>6.79</v>
       </c>
       <c r="L11" t="n">
-        <v>0.77</v>
+        <v>0.64</v>
       </c>
       <c r="M11" t="n">
-        <v>59.15</v>
+        <v>58.71</v>
       </c>
       <c r="N11" t="n">
-        <v>0.92</v>
+        <v>0.86</v>
       </c>
       <c r="O11" t="n">
-        <v>3.23</v>
+        <v>2.93</v>
       </c>
       <c r="P11" t="n">
-        <v>13</v>
+        <v>13.21</v>
       </c>
       <c r="Q11" t="n">
-        <v>11.77</v>
+        <v>11.79</v>
       </c>
       <c r="R11" t="n">
-        <v>7.46</v>
+        <v>7.29</v>
       </c>
       <c r="S11" t="n">
-        <v>0.77</v>
+        <v>0.79</v>
       </c>
       <c r="T11" t="n">
-        <v>1.38</v>
+        <v>1.64</v>
       </c>
       <c r="U11" t="n">
-        <v>0.15</v>
+        <v>0.21</v>
       </c>
       <c r="V11" t="n">
-        <v>0.15</v>
+        <v>0.21</v>
       </c>
       <c r="W11" t="n">
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>53.23</v>
+        <v>53.5</v>
       </c>
       <c r="Y11" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="Z11" t="n">
-        <v>17.23</v>
+        <v>17</v>
       </c>
       <c r="AA11" t="n">
-        <v>11.85</v>
+        <v>11.57</v>
       </c>
       <c r="AB11" t="n">
-        <v>5.38</v>
+        <v>5.43</v>
       </c>
       <c r="AC11" t="n">
-        <v>21.15</v>
+        <v>20.86</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="AE11" t="n">
-        <v>2.38</v>
+        <v>2.5</v>
       </c>
       <c r="AF11" t="n">
         <v>0.15</v>
@@ -5177,67 +5177,67 @@
         <v>2.38</v>
       </c>
       <c r="BG11" t="n">
-        <v>2.54</v>
+        <v>2.67</v>
       </c>
       <c r="BH11" t="n">
-        <v>10.81</v>
+        <v>11</v>
       </c>
       <c r="BI11" t="n">
-        <v>2.54</v>
+        <v>2.67</v>
       </c>
       <c r="BJ11" t="n">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="BK11" t="n">
-        <v>0.46</v>
+        <v>0.48</v>
       </c>
       <c r="BL11" t="n">
-        <v>0.92</v>
+        <v>1.04</v>
       </c>
       <c r="BM11" t="n">
-        <v>0.54</v>
+        <v>0.52</v>
       </c>
       <c r="BN11" t="n">
-        <v>1.46</v>
+        <v>1.56</v>
       </c>
       <c r="BO11" t="n">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="BP11" t="n">
-        <v>5.27</v>
+        <v>5.04</v>
       </c>
       <c r="BQ11" t="n">
-        <v>5.54</v>
+        <v>5.3</v>
       </c>
       <c r="BR11" t="n">
-        <v>88.45999999999999</v>
+        <v>88.89</v>
       </c>
       <c r="BS11" t="n">
-        <v>65.38</v>
+        <v>66.67</v>
       </c>
       <c r="BT11" t="n">
-        <v>38.46</v>
+        <v>40.74</v>
       </c>
       <c r="BU11" t="n">
-        <v>30.77</v>
+        <v>33.33</v>
       </c>
       <c r="BV11" t="n">
-        <v>15.38</v>
+        <v>18.52</v>
       </c>
       <c r="BW11" t="n">
-        <v>11.54</v>
+        <v>14.81</v>
       </c>
       <c r="BX11" t="n">
-        <v>42.31</v>
+        <v>44.44</v>
       </c>
       <c r="BY11" t="n">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="BZ11" t="n">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="CA11" t="n">
-        <v>3.61</v>
+        <v>3.6</v>
       </c>
       <c r="CB11" t="n">
         <v>3.69</v>
@@ -5252,16 +5252,16 @@
         <v>1.33</v>
       </c>
       <c r="CF11" t="n">
-        <v>2.57</v>
+        <v>2.58</v>
       </c>
       <c r="CG11" t="n">
-        <v>3.04</v>
+        <v>3.03</v>
       </c>
       <c r="CH11" t="n">
         <v>1.46</v>
       </c>
       <c r="CI11" t="n">
-        <v>2.11</v>
+        <v>2.1</v>
       </c>
       <c r="CJ11" t="n">
         <v>1.7</v>
@@ -5270,13 +5270,13 @@
         <v>1.48</v>
       </c>
       <c r="CL11" t="n">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="CM11" t="n">
-        <v>2.52</v>
+        <v>2.54</v>
       </c>
       <c r="CN11" t="n">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="CO11" t="n">
         <v>1.24</v>
@@ -5285,16 +5285,16 @@
         <v>1.81</v>
       </c>
       <c r="CQ11" t="n">
-        <v>2.97</v>
+        <v>2.98</v>
       </c>
       <c r="CR11" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="CS11" t="n">
         <v>2.72</v>
       </c>
       <c r="CT11" t="n">
-        <v>3.17</v>
+        <v>3.18</v>
       </c>
       <c r="CU11" t="n">
         <v>1.48</v>
@@ -5306,16 +5306,16 @@
         <v>1.73</v>
       </c>
       <c r="CX11" t="n">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="CY11" t="n">
-        <v>1.83</v>
+        <v>1.81</v>
       </c>
       <c r="CZ11" t="n">
-        <v>2.49</v>
+        <v>2.5</v>
       </c>
       <c r="DA11" t="n">
-        <v>1.99</v>
+        <v>2.01</v>
       </c>
       <c r="DB11" t="n">
         <v>1.27</v>
@@ -5327,79 +5327,79 @@
         <v>3.13</v>
       </c>
       <c r="DE11" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DF11" t="n">
-        <v>1.46</v>
+        <v>1.55</v>
       </c>
       <c r="DG11" t="n">
-        <v>3.19</v>
+        <v>3.04</v>
       </c>
       <c r="DH11" t="n">
-        <v>102.65</v>
+        <v>102.85</v>
       </c>
       <c r="DI11" t="n">
         <v>0</v>
       </c>
       <c r="DJ11" t="n">
-        <v>2.54</v>
+        <v>2.59</v>
       </c>
       <c r="DK11" t="n">
-        <v>6.35</v>
+        <v>6.45</v>
       </c>
       <c r="DL11" t="n">
-        <v>0.54</v>
+        <v>0.48</v>
       </c>
       <c r="DM11" t="n">
-        <v>56</v>
+        <v>55.89</v>
       </c>
       <c r="DN11" t="n">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="DO11" t="n">
-        <v>3.16</v>
+        <v>3</v>
       </c>
       <c r="DP11" t="n">
-        <v>13.88</v>
+        <v>13.96</v>
       </c>
       <c r="DQ11" t="n">
-        <v>10.73</v>
+        <v>10.78</v>
       </c>
       <c r="DR11" t="n">
-        <v>7.96</v>
+        <v>7.85</v>
       </c>
       <c r="DS11" t="n">
-        <v>0.19</v>
+        <v>0.22</v>
       </c>
       <c r="DT11" t="n">
-        <v>0.19</v>
+        <v>0.22</v>
       </c>
       <c r="DU11" t="n">
         <v>0</v>
       </c>
       <c r="DV11" t="n">
-        <v>53.8</v>
+        <v>53.92</v>
       </c>
       <c r="DW11" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DX11" t="n">
-        <v>14.92</v>
+        <v>14.89</v>
       </c>
       <c r="DY11" t="n">
-        <v>10.23</v>
+        <v>10.15</v>
       </c>
       <c r="DZ11" t="n">
-        <v>4.69</v>
+        <v>4.74</v>
       </c>
       <c r="EA11" t="n">
-        <v>21.19</v>
+        <v>21.04</v>
       </c>
       <c r="EB11" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="EC11" t="n">
-        <v>2.38</v>
+        <v>2.44</v>
       </c>
     </row>
     <row r="12">
@@ -5409,91 +5409,91 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C12" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D12" t="n">
         <v>13</v>
       </c>
       <c r="E12" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="F12" t="n">
-        <v>1.23</v>
+        <v>1.14</v>
       </c>
       <c r="G12" t="n">
-        <v>2.31</v>
+        <v>2.29</v>
       </c>
       <c r="H12" t="n">
-        <v>96.84999999999999</v>
+        <v>96.20999999999999</v>
       </c>
       <c r="I12" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="J12" t="n">
-        <v>2.15</v>
+        <v>2.14</v>
       </c>
       <c r="K12" t="n">
-        <v>4.69</v>
+        <v>4.57</v>
       </c>
       <c r="L12" t="n">
-        <v>0.54</v>
+        <v>0.57</v>
       </c>
       <c r="M12" t="n">
-        <v>44</v>
+        <v>42.79</v>
       </c>
       <c r="N12" t="n">
-        <v>0.85</v>
+        <v>0.93</v>
       </c>
       <c r="O12" t="n">
-        <v>2.31</v>
+        <v>2.21</v>
       </c>
       <c r="P12" t="n">
-        <v>12.38</v>
+        <v>12.29</v>
       </c>
       <c r="Q12" t="n">
-        <v>12.46</v>
+        <v>12.07</v>
       </c>
       <c r="R12" t="n">
-        <v>7</v>
+        <v>7.5</v>
       </c>
       <c r="S12" t="n">
-        <v>1.31</v>
+        <v>1.21</v>
       </c>
       <c r="T12" t="n">
-        <v>1.46</v>
+        <v>1.43</v>
       </c>
       <c r="U12" t="n">
-        <v>0.31</v>
+        <v>0.29</v>
       </c>
       <c r="V12" t="n">
-        <v>0.31</v>
+        <v>0.29</v>
       </c>
       <c r="W12" t="n">
         <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>50.23</v>
+        <v>48.79</v>
       </c>
       <c r="Y12" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="Z12" t="n">
-        <v>12.54</v>
+        <v>12.5</v>
       </c>
       <c r="AA12" t="n">
-        <v>7.62</v>
+        <v>7.5</v>
       </c>
       <c r="AB12" t="n">
-        <v>4.92</v>
+        <v>5</v>
       </c>
       <c r="AC12" t="n">
-        <v>21.31</v>
+        <v>20.79</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="AE12" t="n">
         <v>2</v>
@@ -5580,49 +5580,49 @@
         <v>1.69</v>
       </c>
       <c r="BG12" t="n">
-        <v>2.27</v>
+        <v>2.22</v>
       </c>
       <c r="BH12" t="n">
-        <v>9.15</v>
+        <v>9.07</v>
       </c>
       <c r="BI12" t="n">
-        <v>2.27</v>
+        <v>2.22</v>
       </c>
       <c r="BJ12" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.67</v>
       </c>
       <c r="BK12" t="n">
-        <v>0.46</v>
+        <v>0.44</v>
       </c>
       <c r="BL12" t="n">
-        <v>0.54</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="BM12" t="n">
-        <v>0.58</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="BN12" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="BO12" t="n">
-        <v>1.15</v>
+        <v>1.11</v>
       </c>
       <c r="BP12" t="n">
-        <v>3.96</v>
+        <v>3.93</v>
       </c>
       <c r="BQ12" t="n">
-        <v>5.15</v>
+        <v>5.11</v>
       </c>
       <c r="BR12" t="n">
-        <v>96.15000000000001</v>
+        <v>96.3</v>
       </c>
       <c r="BS12" t="n">
-        <v>76.92</v>
+        <v>74.06999999999999</v>
       </c>
       <c r="BT12" t="n">
-        <v>38.46</v>
+        <v>37.04</v>
       </c>
       <c r="BU12" t="n">
-        <v>15.38</v>
+        <v>14.81</v>
       </c>
       <c r="BV12" t="n">
         <v>0</v>
@@ -5631,19 +5631,19 @@
         <v>0</v>
       </c>
       <c r="BX12" t="n">
-        <v>46.15</v>
+        <v>44.44</v>
       </c>
       <c r="BY12" t="n">
-        <v>2.67</v>
+        <v>2.72</v>
       </c>
       <c r="BZ12" t="n">
-        <v>2.87</v>
+        <v>2.9</v>
       </c>
       <c r="CA12" t="n">
         <v>3.54</v>
       </c>
       <c r="CB12" t="n">
-        <v>3.67</v>
+        <v>3.66</v>
       </c>
       <c r="CC12" t="n">
         <v>4.13</v>
@@ -5652,7 +5652,7 @@
         <v>4.67</v>
       </c>
       <c r="CE12" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="CF12" t="n">
         <v>2.62</v>
@@ -5685,7 +5685,7 @@
         <v>1.26</v>
       </c>
       <c r="CP12" t="n">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="CQ12" t="n">
         <v>3.08</v>
@@ -5703,10 +5703,10 @@
         <v>1.47</v>
       </c>
       <c r="CV12" t="n">
-        <v>2.13</v>
+        <v>2.14</v>
       </c>
       <c r="CW12" t="n">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="CX12" t="n">
         <v>1.58</v>
@@ -5724,85 +5724,85 @@
         <v>1.28</v>
       </c>
       <c r="DC12" t="n">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="DD12" t="n">
-        <v>3.2</v>
+        <v>3.18</v>
       </c>
       <c r="DE12" t="n">
         <v>0.04</v>
       </c>
       <c r="DF12" t="n">
-        <v>1.27</v>
+        <v>1.22</v>
       </c>
       <c r="DG12" t="n">
-        <v>2.31</v>
+        <v>2.3</v>
       </c>
       <c r="DH12" t="n">
-        <v>95.7</v>
+        <v>95.41</v>
       </c>
       <c r="DI12" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="DJ12" t="n">
         <v>2</v>
       </c>
       <c r="DK12" t="n">
-        <v>4.04</v>
+        <v>4</v>
       </c>
       <c r="DL12" t="n">
-        <v>0.39</v>
+        <v>0.41</v>
       </c>
       <c r="DM12" t="n">
-        <v>40.5</v>
+        <v>40</v>
       </c>
       <c r="DN12" t="n">
-        <v>0.66</v>
+        <v>0.7</v>
       </c>
       <c r="DO12" t="n">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="DP12" t="n">
-        <v>12.73</v>
+        <v>12.67</v>
       </c>
       <c r="DQ12" t="n">
-        <v>12.19</v>
+        <v>12</v>
       </c>
       <c r="DR12" t="n">
-        <v>7.38</v>
+        <v>7.63</v>
       </c>
       <c r="DS12" t="n">
-        <v>0.2</v>
+        <v>0.19</v>
       </c>
       <c r="DT12" t="n">
-        <v>0.2</v>
+        <v>0.19</v>
       </c>
       <c r="DU12" t="n">
         <v>0</v>
       </c>
       <c r="DV12" t="n">
-        <v>48.62</v>
+        <v>47.93</v>
       </c>
       <c r="DW12" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="DX12" t="n">
-        <v>11.34</v>
+        <v>11.37</v>
       </c>
       <c r="DY12" t="n">
-        <v>7.16</v>
+        <v>7.11</v>
       </c>
       <c r="DZ12" t="n">
-        <v>4.19</v>
+        <v>4.26</v>
       </c>
       <c r="EA12" t="n">
-        <v>21.35</v>
+        <v>21.07</v>
       </c>
       <c r="EB12" t="n">
         <v>1.31</v>
       </c>
       <c r="EC12" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
     </row>
     <row r="13">
@@ -5812,13 +5812,13 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C13" t="n">
         <v>13</v>
       </c>
       <c r="D13" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E13" t="n">
         <v>0.23</v>
@@ -5902,139 +5902,139 @@
         <v>2</v>
       </c>
       <c r="AF13" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="AG13" t="n">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AH13" t="n">
-        <v>3.38</v>
+        <v>3.29</v>
       </c>
       <c r="AI13" t="n">
-        <v>97.69</v>
+        <v>99.36</v>
       </c>
       <c r="AJ13" t="n">
-        <v>0.15</v>
+        <v>0.21</v>
       </c>
       <c r="AK13" t="n">
-        <v>1.69</v>
+        <v>1.64</v>
       </c>
       <c r="AL13" t="n">
-        <v>5.69</v>
+        <v>5.57</v>
       </c>
       <c r="AM13" t="n">
-        <v>0.62</v>
+        <v>0.57</v>
       </c>
       <c r="AN13" t="n">
-        <v>51</v>
+        <v>52.71</v>
       </c>
       <c r="AO13" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.71</v>
       </c>
       <c r="AP13" t="n">
-        <v>2.31</v>
+        <v>2.29</v>
       </c>
       <c r="AQ13" t="n">
-        <v>12.08</v>
+        <v>11.71</v>
       </c>
       <c r="AR13" t="n">
-        <v>11.15</v>
+        <v>11.14</v>
       </c>
       <c r="AS13" t="n">
-        <v>8.539999999999999</v>
+        <v>8.640000000000001</v>
       </c>
       <c r="AT13" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="AU13" t="n">
-        <v>1.85</v>
+        <v>1.71</v>
       </c>
       <c r="AV13" t="n">
-        <v>0.31</v>
+        <v>0.29</v>
       </c>
       <c r="AW13" t="n">
-        <v>0.31</v>
+        <v>0.29</v>
       </c>
       <c r="AX13" t="n">
         <v>0</v>
       </c>
       <c r="AY13" t="n">
-        <v>54.08</v>
+        <v>55.21</v>
       </c>
       <c r="AZ13" t="n">
         <v>0</v>
       </c>
       <c r="BA13" t="n">
-        <v>13.69</v>
+        <v>13.43</v>
       </c>
       <c r="BB13" t="n">
-        <v>9.380000000000001</v>
+        <v>9.210000000000001</v>
       </c>
       <c r="BC13" t="n">
-        <v>4.31</v>
+        <v>4.21</v>
       </c>
       <c r="BD13" t="n">
-        <v>21.38</v>
+        <v>21.71</v>
       </c>
       <c r="BE13" t="n">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="BF13" t="n">
-        <v>1.69</v>
+        <v>1.64</v>
       </c>
       <c r="BG13" t="n">
-        <v>2.81</v>
+        <v>2.74</v>
       </c>
       <c r="BH13" t="n">
-        <v>10.04</v>
+        <v>9.93</v>
       </c>
       <c r="BI13" t="n">
-        <v>2.81</v>
+        <v>2.74</v>
       </c>
       <c r="BJ13" t="n">
-        <v>0.73</v>
+        <v>0.7</v>
       </c>
       <c r="BK13" t="n">
-        <v>0.62</v>
+        <v>0.59</v>
       </c>
       <c r="BL13" t="n">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="BM13" t="n">
-        <v>0.88</v>
+        <v>0.85</v>
       </c>
       <c r="BN13" t="n">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="BO13" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="BP13" t="n">
-        <v>4.08</v>
+        <v>4.04</v>
       </c>
       <c r="BQ13" t="n">
-        <v>5.96</v>
+        <v>5.89</v>
       </c>
       <c r="BR13" t="n">
         <v>100</v>
       </c>
       <c r="BS13" t="n">
-        <v>84.62</v>
+        <v>81.48</v>
       </c>
       <c r="BT13" t="n">
-        <v>57.69</v>
+        <v>55.56</v>
       </c>
       <c r="BU13" t="n">
-        <v>26.92</v>
+        <v>25.93</v>
       </c>
       <c r="BV13" t="n">
-        <v>11.54</v>
+        <v>11.11</v>
       </c>
       <c r="BW13" t="n">
         <v>0</v>
       </c>
       <c r="BX13" t="n">
-        <v>57.69</v>
+        <v>55.56</v>
       </c>
       <c r="BY13" t="n">
         <v>2.23</v>
@@ -6043,16 +6043,16 @@
         <v>2.31</v>
       </c>
       <c r="CA13" t="n">
-        <v>3.66</v>
+        <v>3.65</v>
       </c>
       <c r="CB13" t="n">
-        <v>3.77</v>
+        <v>3.76</v>
       </c>
       <c r="CC13" t="n">
-        <v>3.59</v>
+        <v>3.49</v>
       </c>
       <c r="CD13" t="n">
-        <v>3.82</v>
+        <v>3.71</v>
       </c>
       <c r="CE13" t="n">
         <v>1.31</v>
@@ -6076,13 +6076,13 @@
         <v>1.47</v>
       </c>
       <c r="CL13" t="n">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="CM13" t="n">
-        <v>2.51</v>
+        <v>2.5</v>
       </c>
       <c r="CN13" t="n">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="CO13" t="n">
         <v>1.22</v>
@@ -6091,7 +6091,7 @@
         <v>1.75</v>
       </c>
       <c r="CQ13" t="n">
-        <v>2.82</v>
+        <v>2.83</v>
       </c>
       <c r="CR13" t="n">
         <v>1.35</v>
@@ -6127,85 +6127,85 @@
         <v>1.24</v>
       </c>
       <c r="DC13" t="n">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="DD13" t="n">
         <v>2.89</v>
       </c>
       <c r="DE13" t="n">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
       <c r="DF13" t="n">
-        <v>1.31</v>
+        <v>1.26</v>
       </c>
       <c r="DG13" t="n">
-        <v>3.38</v>
+        <v>3.33</v>
       </c>
       <c r="DH13" t="n">
-        <v>100</v>
+        <v>100.78</v>
       </c>
       <c r="DI13" t="n">
-        <v>0.08</v>
+        <v>0.11</v>
       </c>
       <c r="DJ13" t="n">
-        <v>2</v>
+        <v>1.96</v>
       </c>
       <c r="DK13" t="n">
-        <v>5.46</v>
+        <v>5.41</v>
       </c>
       <c r="DL13" t="n">
-        <v>0.46</v>
+        <v>0.44</v>
       </c>
       <c r="DM13" t="n">
-        <v>53.08</v>
+        <v>53.88</v>
       </c>
       <c r="DN13" t="n">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="DO13" t="n">
         <v>2.08</v>
       </c>
       <c r="DP13" t="n">
-        <v>11.38</v>
+        <v>11.22</v>
       </c>
       <c r="DQ13" t="n">
-        <v>11.46</v>
+        <v>11.44</v>
       </c>
       <c r="DR13" t="n">
-        <v>7.5</v>
+        <v>7.59</v>
       </c>
       <c r="DS13" t="n">
-        <v>0.27</v>
+        <v>0.26</v>
       </c>
       <c r="DT13" t="n">
-        <v>0.27</v>
+        <v>0.26</v>
       </c>
       <c r="DU13" t="n">
         <v>0</v>
       </c>
       <c r="DV13" t="n">
-        <v>53.77</v>
+        <v>54.37</v>
       </c>
       <c r="DW13" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="DX13" t="n">
-        <v>14.58</v>
+        <v>14.41</v>
       </c>
       <c r="DY13" t="n">
-        <v>10</v>
+        <v>9.890000000000001</v>
       </c>
       <c r="DZ13" t="n">
-        <v>4.58</v>
+        <v>4.52</v>
       </c>
       <c r="EA13" t="n">
-        <v>22.08</v>
+        <v>22.22</v>
       </c>
       <c r="EB13" t="n">
         <v>1.62</v>
       </c>
       <c r="EC13" t="n">
-        <v>1.84</v>
+        <v>1.81</v>
       </c>
     </row>
     <row r="14">
@@ -6618,94 +6618,94 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C15" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D15" t="n">
         <v>13</v>
       </c>
       <c r="E15" t="n">
-        <v>0.15</v>
+        <v>0.21</v>
       </c>
       <c r="F15" t="n">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="G15" t="n">
-        <v>2.31</v>
+        <v>2.14</v>
       </c>
       <c r="H15" t="n">
-        <v>88.45999999999999</v>
+        <v>89.93000000000001</v>
       </c>
       <c r="I15" t="n">
         <v>0</v>
       </c>
       <c r="J15" t="n">
-        <v>3.08</v>
+        <v>2.93</v>
       </c>
       <c r="K15" t="n">
-        <v>5.31</v>
+        <v>5.21</v>
       </c>
       <c r="L15" t="n">
-        <v>0.77</v>
+        <v>0.79</v>
       </c>
       <c r="M15" t="n">
-        <v>50</v>
+        <v>49.21</v>
       </c>
       <c r="N15" t="n">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="O15" t="n">
-        <v>3</v>
+        <v>3.07</v>
       </c>
       <c r="P15" t="n">
-        <v>10.92</v>
+        <v>11</v>
       </c>
       <c r="Q15" t="n">
-        <v>13.08</v>
+        <v>13.07</v>
       </c>
       <c r="R15" t="n">
-        <v>8.77</v>
+        <v>9</v>
       </c>
       <c r="S15" t="n">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="T15" t="n">
         <v>1</v>
       </c>
       <c r="U15" t="n">
-        <v>0.15</v>
+        <v>0.21</v>
       </c>
       <c r="V15" t="n">
-        <v>0.15</v>
+        <v>0.21</v>
       </c>
       <c r="W15" t="n">
         <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>43.69</v>
+        <v>44.36</v>
       </c>
       <c r="Y15" t="n">
-        <v>0.31</v>
+        <v>0.29</v>
       </c>
       <c r="Z15" t="n">
-        <v>11</v>
+        <v>10.86</v>
       </c>
       <c r="AA15" t="n">
-        <v>7.15</v>
+        <v>7.14</v>
       </c>
       <c r="AB15" t="n">
-        <v>3.85</v>
+        <v>3.71</v>
       </c>
       <c r="AC15" t="n">
-        <v>20.46</v>
+        <v>20.86</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AE15" t="n">
-        <v>2.46</v>
+        <v>2.36</v>
       </c>
       <c r="AF15" t="n">
         <v>0.15</v>
@@ -6792,46 +6792,46 @@
         <v>2.19</v>
       </c>
       <c r="BH15" t="n">
-        <v>9.960000000000001</v>
+        <v>9.85</v>
       </c>
       <c r="BI15" t="n">
         <v>2.19</v>
       </c>
       <c r="BJ15" t="n">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="BK15" t="n">
-        <v>0.65</v>
+        <v>0.67</v>
       </c>
       <c r="BL15" t="n">
-        <v>0.5</v>
+        <v>0.48</v>
       </c>
       <c r="BM15" t="n">
-        <v>0.42</v>
+        <v>0.41</v>
       </c>
       <c r="BN15" t="n">
-        <v>0.92</v>
+        <v>0.89</v>
       </c>
       <c r="BO15" t="n">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="BP15" t="n">
-        <v>4.73</v>
+        <v>4.78</v>
       </c>
       <c r="BQ15" t="n">
-        <v>5.23</v>
+        <v>5.07</v>
       </c>
       <c r="BR15" t="n">
-        <v>96.15000000000001</v>
+        <v>96.3</v>
       </c>
       <c r="BS15" t="n">
-        <v>69.23</v>
+        <v>70.37</v>
       </c>
       <c r="BT15" t="n">
-        <v>42.31</v>
+        <v>40.74</v>
       </c>
       <c r="BU15" t="n">
-        <v>11.54</v>
+        <v>11.11</v>
       </c>
       <c r="BV15" t="n">
         <v>0</v>
@@ -6840,19 +6840,19 @@
         <v>0</v>
       </c>
       <c r="BX15" t="n">
-        <v>30.77</v>
+        <v>33.33</v>
       </c>
       <c r="BY15" t="n">
-        <v>3.1</v>
+        <v>3.04</v>
       </c>
       <c r="BZ15" t="n">
-        <v>3.5</v>
+        <v>3.43</v>
       </c>
       <c r="CA15" t="n">
-        <v>3.56</v>
+        <v>3.55</v>
       </c>
       <c r="CB15" t="n">
-        <v>3.64</v>
+        <v>3.62</v>
       </c>
       <c r="CC15" t="n">
         <v>4.37</v>
@@ -6861,13 +6861,13 @@
         <v>5.27</v>
       </c>
       <c r="CE15" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="CF15" t="n">
-        <v>2.81</v>
+        <v>2.83</v>
       </c>
       <c r="CG15" t="n">
-        <v>2.87</v>
+        <v>2.86</v>
       </c>
       <c r="CH15" t="n">
         <v>1.4</v>
@@ -6876,7 +6876,7 @@
         <v>1.92</v>
       </c>
       <c r="CJ15" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="CK15" t="n">
         <v>1.51</v>
@@ -6885,7 +6885,7 @@
         <v>1.9</v>
       </c>
       <c r="CM15" t="n">
-        <v>2.5</v>
+        <v>2.49</v>
       </c>
       <c r="CN15" t="n">
         <v>1.91</v>
@@ -6894,10 +6894,10 @@
         <v>1.31</v>
       </c>
       <c r="CP15" t="n">
-        <v>1.96</v>
+        <v>1.98</v>
       </c>
       <c r="CQ15" t="n">
-        <v>3.4</v>
+        <v>3.44</v>
       </c>
       <c r="CR15" t="n">
         <v>1.41</v>
@@ -6912,10 +6912,10 @@
         <v>1.43</v>
       </c>
       <c r="CV15" t="n">
-        <v>2.02</v>
+        <v>2.01</v>
       </c>
       <c r="CW15" t="n">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="CX15" t="n">
         <v>1.57</v>
@@ -6927,91 +6927,91 @@
         <v>2.38</v>
       </c>
       <c r="DA15" t="n">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="DB15" t="n">
         <v>1.33</v>
       </c>
       <c r="DC15" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="DD15" t="n">
-        <v>3.54</v>
+        <v>3.59</v>
       </c>
       <c r="DE15" t="n">
-        <v>0.15</v>
+        <v>0.18</v>
       </c>
       <c r="DF15" t="n">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="DG15" t="n">
-        <v>1.89</v>
+        <v>1.81</v>
       </c>
       <c r="DH15" t="n">
-        <v>86</v>
+        <v>86.84999999999999</v>
       </c>
       <c r="DI15" t="n">
         <v>-0.04</v>
       </c>
       <c r="DJ15" t="n">
-        <v>2.47</v>
+        <v>2.41</v>
       </c>
       <c r="DK15" t="n">
-        <v>4.31</v>
+        <v>4.3</v>
       </c>
       <c r="DL15" t="n">
-        <v>0.54</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="DM15" t="n">
-        <v>43.66</v>
+        <v>43.48</v>
       </c>
       <c r="DN15" t="n">
-        <v>0.84</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="DO15" t="n">
-        <v>2.42</v>
+        <v>2.48</v>
       </c>
       <c r="DP15" t="n">
-        <v>10.84</v>
+        <v>10.89</v>
       </c>
       <c r="DQ15" t="n">
-        <v>12.12</v>
+        <v>12.15</v>
       </c>
       <c r="DR15" t="n">
-        <v>9.42</v>
+        <v>9.52</v>
       </c>
       <c r="DS15" t="n">
-        <v>0.12</v>
+        <v>0.15</v>
       </c>
       <c r="DT15" t="n">
-        <v>0.12</v>
+        <v>0.15</v>
       </c>
       <c r="DU15" t="n">
         <v>0</v>
       </c>
       <c r="DV15" t="n">
-        <v>43.19</v>
+        <v>43.56</v>
       </c>
       <c r="DW15" t="n">
-        <v>0.23</v>
+        <v>0.22</v>
       </c>
       <c r="DX15" t="n">
-        <v>9.57</v>
+        <v>9.56</v>
       </c>
       <c r="DY15" t="n">
-        <v>6.5</v>
+        <v>6.52</v>
       </c>
       <c r="DZ15" t="n">
-        <v>3.08</v>
+        <v>3.04</v>
       </c>
       <c r="EA15" t="n">
-        <v>18.69</v>
+        <v>18.96</v>
       </c>
       <c r="EB15" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="EC15" t="n">
-        <v>2.08</v>
+        <v>2.04</v>
       </c>
     </row>
     <row r="16">
@@ -7424,13 +7424,13 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C17" t="n">
         <v>13</v>
       </c>
       <c r="D17" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
@@ -7514,139 +7514,139 @@
         <v>1.31</v>
       </c>
       <c r="AF17" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.38</v>
+        <v>1.43</v>
       </c>
       <c r="AH17" t="n">
-        <v>2.31</v>
+        <v>2.43</v>
       </c>
       <c r="AI17" t="n">
-        <v>94.54000000000001</v>
+        <v>96.20999999999999</v>
       </c>
       <c r="AJ17" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="AK17" t="n">
-        <v>2.15</v>
+        <v>2.14</v>
       </c>
       <c r="AL17" t="n">
-        <v>4.31</v>
+        <v>4.57</v>
       </c>
       <c r="AM17" t="n">
-        <v>0.23</v>
+        <v>0.29</v>
       </c>
       <c r="AN17" t="n">
-        <v>46.69</v>
+        <v>47.36</v>
       </c>
       <c r="AO17" t="n">
-        <v>0.62</v>
+        <v>0.57</v>
       </c>
       <c r="AP17" t="n">
-        <v>1.46</v>
+        <v>1.64</v>
       </c>
       <c r="AQ17" t="n">
-        <v>12.15</v>
+        <v>11.93</v>
       </c>
       <c r="AR17" t="n">
-        <v>10.92</v>
+        <v>11.07</v>
       </c>
       <c r="AS17" t="n">
-        <v>9.31</v>
+        <v>9.140000000000001</v>
       </c>
       <c r="AT17" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="AU17" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="AV17" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="AW17" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="AX17" t="n">
         <v>0</v>
       </c>
       <c r="AY17" t="n">
-        <v>47.46</v>
+        <v>48.36</v>
       </c>
       <c r="AZ17" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="BA17" t="n">
-        <v>10.62</v>
+        <v>11</v>
       </c>
       <c r="BB17" t="n">
-        <v>7.08</v>
+        <v>7.36</v>
       </c>
       <c r="BC17" t="n">
-        <v>3.54</v>
+        <v>3.64</v>
       </c>
       <c r="BD17" t="n">
-        <v>19.08</v>
+        <v>19.43</v>
       </c>
       <c r="BE17" t="n">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="BF17" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="BG17" t="n">
         <v>3</v>
       </c>
       <c r="BH17" t="n">
-        <v>9.77</v>
+        <v>9.74</v>
       </c>
       <c r="BI17" t="n">
         <v>3</v>
       </c>
       <c r="BJ17" t="n">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="BK17" t="n">
-        <v>0.73</v>
+        <v>0.7</v>
       </c>
       <c r="BL17" t="n">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="BM17" t="n">
-        <v>0.65</v>
+        <v>0.67</v>
       </c>
       <c r="BN17" t="n">
-        <v>1.54</v>
+        <v>1.56</v>
       </c>
       <c r="BO17" t="n">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="BP17" t="n">
-        <v>3.65</v>
+        <v>3.67</v>
       </c>
       <c r="BQ17" t="n">
-        <v>5.58</v>
+        <v>5.56</v>
       </c>
       <c r="BR17" t="n">
-        <v>92.31</v>
+        <v>92.59</v>
       </c>
       <c r="BS17" t="n">
-        <v>80.77</v>
+        <v>81.48</v>
       </c>
       <c r="BT17" t="n">
-        <v>50</v>
+        <v>51.85</v>
       </c>
       <c r="BU17" t="n">
-        <v>38.46</v>
+        <v>37.04</v>
       </c>
       <c r="BV17" t="n">
-        <v>26.92</v>
+        <v>25.93</v>
       </c>
       <c r="BW17" t="n">
-        <v>7.69</v>
+        <v>7.41</v>
       </c>
       <c r="BX17" t="n">
-        <v>65.38</v>
+        <v>66.67</v>
       </c>
       <c r="BY17" t="n">
         <v>2.95</v>
@@ -7658,13 +7658,13 @@
         <v>3.74</v>
       </c>
       <c r="CB17" t="n">
-        <v>3.82</v>
+        <v>3.81</v>
       </c>
       <c r="CC17" t="n">
-        <v>4.44</v>
+        <v>4.34</v>
       </c>
       <c r="CD17" t="n">
-        <v>4.9</v>
+        <v>4.77</v>
       </c>
       <c r="CE17" t="n">
         <v>1.31</v>
@@ -7679,10 +7679,10 @@
         <v>1.51</v>
       </c>
       <c r="CI17" t="n">
-        <v>2.17</v>
+        <v>2.18</v>
       </c>
       <c r="CJ17" t="n">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="CK17" t="n">
         <v>1.43</v>
@@ -7691,7 +7691,7 @@
         <v>1.83</v>
       </c>
       <c r="CM17" t="n">
-        <v>2.65</v>
+        <v>2.64</v>
       </c>
       <c r="CN17" t="n">
         <v>2.04</v>
@@ -7700,10 +7700,10 @@
         <v>1.21</v>
       </c>
       <c r="CP17" t="n">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="CQ17" t="n">
-        <v>2.74</v>
+        <v>2.73</v>
       </c>
       <c r="CR17" t="n">
         <v>1.35</v>
@@ -7730,10 +7730,10 @@
         <v>1.79</v>
       </c>
       <c r="CZ17" t="n">
-        <v>2.45</v>
+        <v>2.46</v>
       </c>
       <c r="DA17" t="n">
-        <v>2.04</v>
+        <v>2.03</v>
       </c>
       <c r="DB17" t="n">
         <v>1.24</v>
@@ -7742,82 +7742,82 @@
         <v>1.78</v>
       </c>
       <c r="DD17" t="n">
-        <v>2.88</v>
+        <v>2.87</v>
       </c>
       <c r="DE17" t="n">
         <v>0.04</v>
       </c>
       <c r="DF17" t="n">
-        <v>1.15</v>
+        <v>1.18</v>
       </c>
       <c r="DG17" t="n">
-        <v>2.5</v>
+        <v>2.56</v>
       </c>
       <c r="DH17" t="n">
-        <v>95.43000000000001</v>
+        <v>96.26000000000001</v>
       </c>
       <c r="DI17" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="DJ17" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="DK17" t="n">
-        <v>4.34</v>
+        <v>4.48</v>
       </c>
       <c r="DL17" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="DM17" t="n">
+        <v>48.11</v>
+      </c>
+      <c r="DN17" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="DO17" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="DP17" t="n">
+        <v>10.93</v>
+      </c>
+      <c r="DQ17" t="n">
+        <v>11.89</v>
+      </c>
+      <c r="DR17" t="n">
+        <v>9.140000000000001</v>
+      </c>
+      <c r="DS17" t="n">
         <v>0.19</v>
       </c>
-      <c r="DM17" t="n">
-        <v>47.8</v>
-      </c>
-      <c r="DN17" t="n">
-        <v>0.54</v>
-      </c>
-      <c r="DO17" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="DP17" t="n">
-        <v>11</v>
-      </c>
-      <c r="DQ17" t="n">
-        <v>11.84</v>
-      </c>
-      <c r="DR17" t="n">
-        <v>9.23</v>
-      </c>
-      <c r="DS17" t="n">
-        <v>0.2</v>
-      </c>
       <c r="DT17" t="n">
-        <v>0.2</v>
+        <v>0.19</v>
       </c>
       <c r="DU17" t="n">
         <v>0</v>
       </c>
       <c r="DV17" t="n">
-        <v>47.42</v>
+        <v>47.89</v>
       </c>
       <c r="DW17" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DX17" t="n">
-        <v>12.47</v>
+        <v>12.59</v>
       </c>
       <c r="DY17" t="n">
-        <v>8.31</v>
+        <v>8.41</v>
       </c>
       <c r="DZ17" t="n">
-        <v>4.16</v>
+        <v>4.18</v>
       </c>
       <c r="EA17" t="n">
-        <v>20.04</v>
+        <v>20.19</v>
       </c>
       <c r="EB17" t="n">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="EC17" t="n">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
     </row>
   </sheetData>

--- a/data/teams/leagues/Averages_Belgium_Pro_League_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Belgium_Pro_League_2025-2026.xlsx
@@ -1379,10 +1379,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D2" t="n">
         <v>13</v>
@@ -1391,82 +1391,82 @@
         <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>0.92</v>
+        <v>0.86</v>
       </c>
       <c r="G2" t="n">
-        <v>2.54</v>
+        <v>2.29</v>
       </c>
       <c r="H2" t="n">
-        <v>107.62</v>
+        <v>108.07</v>
       </c>
       <c r="I2" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="J2" t="n">
-        <v>1.46</v>
+        <v>1.43</v>
       </c>
       <c r="K2" t="n">
-        <v>4.46</v>
+        <v>4.79</v>
       </c>
       <c r="L2" t="n">
-        <v>0.38</v>
+        <v>0.29</v>
       </c>
       <c r="M2" t="n">
-        <v>49</v>
+        <v>50.07</v>
       </c>
       <c r="N2" t="n">
-        <v>0.46</v>
+        <v>0.5</v>
       </c>
       <c r="O2" t="n">
-        <v>1.92</v>
+        <v>1.71</v>
       </c>
       <c r="P2" t="n">
-        <v>9.08</v>
+        <v>9.140000000000001</v>
       </c>
       <c r="Q2" t="n">
-        <v>13.62</v>
+        <v>13.36</v>
       </c>
       <c r="R2" t="n">
-        <v>6.62</v>
+        <v>6.43</v>
       </c>
       <c r="S2" t="n">
-        <v>2.15</v>
+        <v>2</v>
       </c>
       <c r="T2" t="n">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="U2" t="n">
-        <v>0.46</v>
+        <v>0.43</v>
       </c>
       <c r="V2" t="n">
-        <v>0.46</v>
+        <v>0.43</v>
       </c>
       <c r="W2" t="n">
         <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>48.62</v>
+        <v>48.57</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="Z2" t="n">
-        <v>14.08</v>
+        <v>14.57</v>
       </c>
       <c r="AA2" t="n">
-        <v>9.380000000000001</v>
+        <v>9.640000000000001</v>
       </c>
       <c r="AB2" t="n">
-        <v>4.69</v>
+        <v>4.93</v>
       </c>
       <c r="AC2" t="n">
-        <v>23.31</v>
+        <v>23.36</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.58</v>
+        <v>1.63</v>
       </c>
       <c r="AE2" t="n">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="AF2" t="n">
         <v>0.15</v>
@@ -1550,67 +1550,67 @@
         <v>2.69</v>
       </c>
       <c r="BG2" t="n">
-        <v>2.85</v>
+        <v>2.74</v>
       </c>
       <c r="BH2" t="n">
-        <v>10.12</v>
+        <v>10.22</v>
       </c>
       <c r="BI2" t="n">
-        <v>2.85</v>
+        <v>2.74</v>
       </c>
       <c r="BJ2" t="n">
-        <v>0.58</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="BK2" t="n">
-        <v>1.04</v>
+        <v>1</v>
       </c>
       <c r="BL2" t="n">
-        <v>0.58</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="BM2" t="n">
-        <v>0.65</v>
+        <v>0.63</v>
       </c>
       <c r="BN2" t="n">
-        <v>1.23</v>
+        <v>1.19</v>
       </c>
       <c r="BO2" t="n">
-        <v>1.62</v>
+        <v>1.56</v>
       </c>
       <c r="BP2" t="n">
-        <v>4.38</v>
+        <v>4.19</v>
       </c>
       <c r="BQ2" t="n">
-        <v>5.69</v>
+        <v>5.44</v>
       </c>
       <c r="BR2" t="n">
-        <v>92.31</v>
+        <v>88.89</v>
       </c>
       <c r="BS2" t="n">
-        <v>88.45999999999999</v>
+        <v>85.19</v>
       </c>
       <c r="BT2" t="n">
-        <v>46.15</v>
+        <v>44.44</v>
       </c>
       <c r="BU2" t="n">
-        <v>26.92</v>
+        <v>25.93</v>
       </c>
       <c r="BV2" t="n">
-        <v>19.23</v>
+        <v>18.52</v>
       </c>
       <c r="BW2" t="n">
-        <v>7.69</v>
+        <v>7.41</v>
       </c>
       <c r="BX2" t="n">
-        <v>61.54</v>
+        <v>59.26</v>
       </c>
       <c r="BY2" t="n">
-        <v>2.51</v>
+        <v>2.45</v>
       </c>
       <c r="BZ2" t="n">
-        <v>2.65</v>
+        <v>2.59</v>
       </c>
       <c r="CA2" t="n">
-        <v>3.54</v>
+        <v>3.56</v>
       </c>
       <c r="CB2" t="n">
         <v>3.68</v>
@@ -1628,13 +1628,13 @@
         <v>2.52</v>
       </c>
       <c r="CG2" t="n">
-        <v>3.15</v>
+        <v>3.14</v>
       </c>
       <c r="CH2" t="n">
         <v>1.48</v>
       </c>
       <c r="CI2" t="n">
-        <v>2.18</v>
+        <v>2.17</v>
       </c>
       <c r="CJ2" t="n">
         <v>1.65</v>
@@ -1649,7 +1649,7 @@
         <v>2.59</v>
       </c>
       <c r="CN2" t="n">
-        <v>2.03</v>
+        <v>2.02</v>
       </c>
       <c r="CO2" t="n">
         <v>1.22</v>
@@ -1658,7 +1658,7 @@
         <v>1.75</v>
       </c>
       <c r="CQ2" t="n">
-        <v>2.86</v>
+        <v>2.87</v>
       </c>
       <c r="CR2" t="n">
         <v>1.36</v>
@@ -1673,7 +1673,7 @@
         <v>1.51</v>
       </c>
       <c r="CV2" t="n">
-        <v>2.3</v>
+        <v>2.29</v>
       </c>
       <c r="CW2" t="n">
         <v>1.67</v>
@@ -1691,88 +1691,88 @@
         <v>2.08</v>
       </c>
       <c r="DB2" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="DC2" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="DD2" t="n">
-        <v>2.92</v>
+        <v>2.93</v>
       </c>
       <c r="DE2" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="DF2" t="n">
-        <v>1.23</v>
+        <v>1.19</v>
       </c>
       <c r="DG2" t="n">
-        <v>2.5</v>
+        <v>2.37</v>
       </c>
       <c r="DH2" t="n">
-        <v>105.15</v>
+        <v>105.48</v>
       </c>
       <c r="DI2" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DJ2" t="n">
-        <v>2.23</v>
+        <v>2.19</v>
       </c>
       <c r="DK2" t="n">
-        <v>4.66</v>
+        <v>4.82</v>
       </c>
       <c r="DL2" t="n">
-        <v>0.5</v>
+        <v>0.45</v>
       </c>
       <c r="DM2" t="n">
-        <v>49.23</v>
+        <v>49.78</v>
       </c>
       <c r="DN2" t="n">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="DO2" t="n">
-        <v>2.15</v>
+        <v>2.03</v>
       </c>
       <c r="DP2" t="n">
-        <v>10.66</v>
+        <v>10.63</v>
       </c>
       <c r="DQ2" t="n">
-        <v>12.5</v>
+        <v>12.41</v>
       </c>
       <c r="DR2" t="n">
-        <v>7.08</v>
+        <v>6.96</v>
       </c>
       <c r="DS2" t="n">
-        <v>0.31</v>
+        <v>0.3</v>
       </c>
       <c r="DT2" t="n">
-        <v>0.31</v>
+        <v>0.3</v>
       </c>
       <c r="DU2" t="n">
         <v>0</v>
       </c>
       <c r="DV2" t="n">
-        <v>47.31</v>
+        <v>47.33</v>
       </c>
       <c r="DW2" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="DX2" t="n">
-        <v>13.38</v>
+        <v>13.66</v>
       </c>
       <c r="DY2" t="n">
-        <v>9.23</v>
+        <v>9.369999999999999</v>
       </c>
       <c r="DZ2" t="n">
-        <v>4.16</v>
+        <v>4.3</v>
       </c>
       <c r="EA2" t="n">
-        <v>22.58</v>
+        <v>22.63</v>
       </c>
       <c r="EB2" t="n">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="EC2" t="n">
-        <v>1.96</v>
+        <v>1.92</v>
       </c>
     </row>
     <row r="3">
@@ -1782,13 +1782,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C3" t="n">
         <v>13</v>
       </c>
       <c r="D3" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E3" t="n">
         <v>0.08</v>
@@ -1872,139 +1872,139 @@
         <v>1</v>
       </c>
       <c r="AF3" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="AH3" t="n">
-        <v>3.62</v>
+        <v>3.43</v>
       </c>
       <c r="AI3" t="n">
-        <v>104.31</v>
+        <v>104.93</v>
       </c>
       <c r="AJ3" t="n">
         <v>0</v>
       </c>
       <c r="AK3" t="n">
-        <v>1.69</v>
+        <v>1.64</v>
       </c>
       <c r="AL3" t="n">
-        <v>6</v>
+        <v>5.86</v>
       </c>
       <c r="AM3" t="n">
-        <v>0.31</v>
+        <v>0.29</v>
       </c>
       <c r="AN3" t="n">
-        <v>55.31</v>
+        <v>57.14</v>
       </c>
       <c r="AO3" t="n">
-        <v>0.46</v>
+        <v>0.43</v>
       </c>
       <c r="AP3" t="n">
-        <v>2.38</v>
+        <v>2.43</v>
       </c>
       <c r="AQ3" t="n">
-        <v>9.77</v>
+        <v>9.710000000000001</v>
       </c>
       <c r="AR3" t="n">
-        <v>11.31</v>
+        <v>11</v>
       </c>
       <c r="AS3" t="n">
-        <v>8.31</v>
+        <v>8</v>
       </c>
       <c r="AT3" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="AU3" t="n">
-        <v>1.62</v>
+        <v>1.64</v>
       </c>
       <c r="AV3" t="n">
-        <v>0</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="AW3" t="n">
-        <v>0</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="AX3" t="n">
         <v>0</v>
       </c>
       <c r="AY3" t="n">
-        <v>60.31</v>
+        <v>60.36</v>
       </c>
       <c r="AZ3" t="n">
         <v>0</v>
       </c>
       <c r="BA3" t="n">
-        <v>14.46</v>
+        <v>14.5</v>
       </c>
       <c r="BB3" t="n">
-        <v>9.380000000000001</v>
+        <v>9.43</v>
       </c>
       <c r="BC3" t="n">
-        <v>5.08</v>
+        <v>5.07</v>
       </c>
       <c r="BD3" t="n">
-        <v>18.77</v>
+        <v>18.71</v>
       </c>
       <c r="BE3" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="BF3" t="n">
-        <v>1.69</v>
+        <v>1.64</v>
       </c>
       <c r="BG3" t="n">
-        <v>3.08</v>
+        <v>3.07</v>
       </c>
       <c r="BH3" t="n">
-        <v>10.77</v>
+        <v>10.59</v>
       </c>
       <c r="BI3" t="n">
-        <v>3.08</v>
+        <v>3.07</v>
       </c>
       <c r="BJ3" t="n">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="BK3" t="n">
-        <v>0.46</v>
+        <v>0.44</v>
       </c>
       <c r="BL3" t="n">
-        <v>0.88</v>
+        <v>0.85</v>
       </c>
       <c r="BM3" t="n">
-        <v>0.96</v>
+        <v>1</v>
       </c>
       <c r="BN3" t="n">
         <v>1.85</v>
       </c>
       <c r="BO3" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="BP3" t="n">
-        <v>4.77</v>
+        <v>4.78</v>
       </c>
       <c r="BQ3" t="n">
-        <v>6</v>
+        <v>5.81</v>
       </c>
       <c r="BR3" t="n">
         <v>100</v>
       </c>
       <c r="BS3" t="n">
-        <v>65.38</v>
+        <v>66.67</v>
       </c>
       <c r="BT3" t="n">
-        <v>53.85</v>
+        <v>55.56</v>
       </c>
       <c r="BU3" t="n">
-        <v>23.08</v>
+        <v>22.22</v>
       </c>
       <c r="BV3" t="n">
-        <v>23.08</v>
+        <v>22.22</v>
       </c>
       <c r="BW3" t="n">
-        <v>15.38</v>
+        <v>14.81</v>
       </c>
       <c r="BX3" t="n">
-        <v>53.85</v>
+        <v>55.56</v>
       </c>
       <c r="BY3" t="n">
         <v>1.44</v>
@@ -2013,13 +2013,13 @@
         <v>1.46</v>
       </c>
       <c r="CA3" t="n">
-        <v>4.46</v>
+        <v>4.44</v>
       </c>
       <c r="CB3" t="n">
-        <v>4.77</v>
+        <v>4.74</v>
       </c>
       <c r="CC3" t="n">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="CD3" t="n">
         <v>1.9</v>
@@ -2028,13 +2028,13 @@
         <v>1.26</v>
       </c>
       <c r="CF3" t="n">
-        <v>2.25</v>
+        <v>2.26</v>
       </c>
       <c r="CG3" t="n">
-        <v>3.51</v>
+        <v>3.5</v>
       </c>
       <c r="CH3" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="CI3" t="n">
         <v>2.11</v>
@@ -2046,7 +2046,7 @@
         <v>1.48</v>
       </c>
       <c r="CL3" t="n">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="CM3" t="n">
         <v>2.51</v>
@@ -2055,22 +2055,22 @@
         <v>1.95</v>
       </c>
       <c r="CO3" t="n">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="CP3" t="n">
         <v>1.57</v>
       </c>
       <c r="CQ3" t="n">
-        <v>2.41</v>
+        <v>2.42</v>
       </c>
       <c r="CR3" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="CS3" t="n">
-        <v>2.33</v>
+        <v>2.34</v>
       </c>
       <c r="CT3" t="n">
-        <v>3.24</v>
+        <v>3.26</v>
       </c>
       <c r="CU3" t="n">
         <v>1.63</v>
@@ -2085,13 +2085,13 @@
         <v>1.53</v>
       </c>
       <c r="CY3" t="n">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="CZ3" t="n">
-        <v>2.47</v>
+        <v>2.48</v>
       </c>
       <c r="DA3" t="n">
-        <v>2.02</v>
+        <v>2.03</v>
       </c>
       <c r="DB3" t="n">
         <v>1.19</v>
@@ -2100,82 +2100,82 @@
         <v>1.6</v>
       </c>
       <c r="DD3" t="n">
-        <v>2.48</v>
+        <v>2.49</v>
       </c>
       <c r="DE3" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="DF3" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="DG3" t="n">
-        <v>3.77</v>
+        <v>3.67</v>
       </c>
       <c r="DH3" t="n">
-        <v>109.27</v>
+        <v>109.41</v>
       </c>
       <c r="DI3" t="n">
         <v>0</v>
       </c>
       <c r="DJ3" t="n">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="DK3" t="n">
-        <v>6.62</v>
+        <v>6.52</v>
       </c>
       <c r="DL3" t="n">
-        <v>0.62</v>
+        <v>0.59</v>
       </c>
       <c r="DM3" t="n">
-        <v>60.66</v>
+        <v>61.41</v>
       </c>
       <c r="DN3" t="n">
-        <v>0.34</v>
+        <v>0.33</v>
       </c>
       <c r="DO3" t="n">
-        <v>2.84</v>
+        <v>2.85</v>
       </c>
       <c r="DP3" t="n">
-        <v>9.57</v>
+        <v>9.550000000000001</v>
       </c>
       <c r="DQ3" t="n">
-        <v>11.7</v>
+        <v>11.52</v>
       </c>
       <c r="DR3" t="n">
-        <v>7.34</v>
+        <v>7.22</v>
       </c>
       <c r="DS3" t="n">
-        <v>0</v>
+        <v>0.04</v>
       </c>
       <c r="DT3" t="n">
-        <v>0</v>
+        <v>0.04</v>
       </c>
       <c r="DU3" t="n">
         <v>0</v>
       </c>
       <c r="DV3" t="n">
-        <v>62.92</v>
+        <v>62.85</v>
       </c>
       <c r="DW3" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="DX3" t="n">
-        <v>16.27</v>
+        <v>16.22</v>
       </c>
       <c r="DY3" t="n">
-        <v>10.73</v>
+        <v>10.71</v>
       </c>
       <c r="DZ3" t="n">
-        <v>5.54</v>
+        <v>5.52</v>
       </c>
       <c r="EA3" t="n">
-        <v>20.85</v>
+        <v>20.74</v>
       </c>
       <c r="EB3" t="n">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="EC3" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
     </row>
     <row r="4">
@@ -2185,13 +2185,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C4" t="n">
         <v>13</v>
       </c>
       <c r="D4" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E4" t="n">
         <v>0.08</v>
@@ -2275,139 +2275,139 @@
         <v>1.92</v>
       </c>
       <c r="AF4" t="n">
-        <v>0.23</v>
+        <v>0.21</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.62</v>
+        <v>1.5</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.69</v>
+        <v>1.5</v>
       </c>
       <c r="AI4" t="n">
-        <v>88.45999999999999</v>
+        <v>88</v>
       </c>
       <c r="AJ4" t="n">
-        <v>0.15</v>
+        <v>0.21</v>
       </c>
       <c r="AK4" t="n">
-        <v>2.69</v>
+        <v>2.64</v>
       </c>
       <c r="AL4" t="n">
-        <v>3.62</v>
+        <v>3.64</v>
       </c>
       <c r="AM4" t="n">
-        <v>0.08</v>
+        <v>0</v>
       </c>
       <c r="AN4" t="n">
-        <v>40.08</v>
+        <v>39.93</v>
       </c>
       <c r="AO4" t="n">
-        <v>0.92</v>
+        <v>1</v>
       </c>
       <c r="AP4" t="n">
-        <v>1.92</v>
+        <v>1.71</v>
       </c>
       <c r="AQ4" t="n">
-        <v>11.54</v>
+        <v>11.43</v>
       </c>
       <c r="AR4" t="n">
-        <v>11.54</v>
+        <v>11.43</v>
       </c>
       <c r="AS4" t="n">
-        <v>10.38</v>
+        <v>10.36</v>
       </c>
       <c r="AT4" t="n">
-        <v>1.62</v>
+        <v>1.5</v>
       </c>
       <c r="AU4" t="n">
-        <v>0.92</v>
+        <v>0.86</v>
       </c>
       <c r="AV4" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="AW4" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="AX4" t="n">
         <v>0</v>
       </c>
       <c r="AY4" t="n">
-        <v>44.85</v>
+        <v>45.36</v>
       </c>
       <c r="AZ4" t="n">
-        <v>0.31</v>
+        <v>0.29</v>
       </c>
       <c r="BA4" t="n">
         <v>11</v>
       </c>
       <c r="BB4" t="n">
-        <v>6.69</v>
+        <v>6.57</v>
       </c>
       <c r="BC4" t="n">
-        <v>4.31</v>
+        <v>4.43</v>
       </c>
       <c r="BD4" t="n">
-        <v>21.08</v>
+        <v>21.93</v>
       </c>
       <c r="BE4" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="BF4" t="n">
-        <v>2.23</v>
+        <v>2.21</v>
       </c>
       <c r="BG4" t="n">
-        <v>2.5</v>
+        <v>2.41</v>
       </c>
       <c r="BH4" t="n">
-        <v>8.880000000000001</v>
+        <v>9.039999999999999</v>
       </c>
       <c r="BI4" t="n">
-        <v>2.5</v>
+        <v>2.41</v>
       </c>
       <c r="BJ4" t="n">
-        <v>0.58</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="BK4" t="n">
-        <v>0.42</v>
+        <v>0.41</v>
       </c>
       <c r="BL4" t="n">
-        <v>0.58</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="BM4" t="n">
-        <v>0.92</v>
+        <v>0.89</v>
       </c>
       <c r="BN4" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="BO4" t="n">
-        <v>1</v>
+        <v>0.96</v>
       </c>
       <c r="BP4" t="n">
-        <v>3.92</v>
+        <v>3.74</v>
       </c>
       <c r="BQ4" t="n">
-        <v>4.46</v>
+        <v>4.26</v>
       </c>
       <c r="BR4" t="n">
-        <v>88.45999999999999</v>
+        <v>85.19</v>
       </c>
       <c r="BS4" t="n">
-        <v>69.23</v>
+        <v>66.67</v>
       </c>
       <c r="BT4" t="n">
-        <v>50</v>
+        <v>48.15</v>
       </c>
       <c r="BU4" t="n">
-        <v>26.92</v>
+        <v>25.93</v>
       </c>
       <c r="BV4" t="n">
-        <v>11.54</v>
+        <v>11.11</v>
       </c>
       <c r="BW4" t="n">
-        <v>3.85</v>
+        <v>3.7</v>
       </c>
       <c r="BX4" t="n">
-        <v>57.69</v>
+        <v>55.56</v>
       </c>
       <c r="BY4" t="n">
         <v>3.42</v>
@@ -2416,16 +2416,16 @@
         <v>3.55</v>
       </c>
       <c r="CA4" t="n">
-        <v>3.65</v>
+        <v>3.66</v>
       </c>
       <c r="CB4" t="n">
         <v>3.78</v>
       </c>
       <c r="CC4" t="n">
-        <v>4.56</v>
+        <v>4.57</v>
       </c>
       <c r="CD4" t="n">
-        <v>4.83</v>
+        <v>4.79</v>
       </c>
       <c r="CE4" t="n">
         <v>1.35</v>
@@ -2440,7 +2440,7 @@
         <v>1.45</v>
       </c>
       <c r="CI4" t="n">
-        <v>2.03</v>
+        <v>2.02</v>
       </c>
       <c r="CJ4" t="n">
         <v>1.74</v>
@@ -2461,7 +2461,7 @@
         <v>1.26</v>
       </c>
       <c r="CP4" t="n">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="CQ4" t="n">
         <v>3.1</v>
@@ -2479,7 +2479,7 @@
         <v>1.48</v>
       </c>
       <c r="CV4" t="n">
-        <v>2.13</v>
+        <v>2.12</v>
       </c>
       <c r="CW4" t="n">
         <v>1.77</v>
@@ -2503,82 +2503,82 @@
         <v>1.91</v>
       </c>
       <c r="DD4" t="n">
-        <v>3.19</v>
+        <v>3.2</v>
       </c>
       <c r="DE4" t="n">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
       <c r="DF4" t="n">
-        <v>1.54</v>
+        <v>1.48</v>
       </c>
       <c r="DG4" t="n">
-        <v>1.66</v>
+        <v>1.56</v>
       </c>
       <c r="DH4" t="n">
-        <v>88.34999999999999</v>
+        <v>88.11</v>
       </c>
       <c r="DI4" t="n">
-        <v>0</v>
+        <v>0.04</v>
       </c>
       <c r="DJ4" t="n">
-        <v>2.31</v>
+        <v>2.29</v>
       </c>
       <c r="DK4" t="n">
-        <v>3.54</v>
+        <v>3.55</v>
       </c>
       <c r="DL4" t="n">
-        <v>0.08</v>
+        <v>0.04</v>
       </c>
       <c r="DM4" t="n">
-        <v>43.66</v>
+        <v>43.44</v>
       </c>
       <c r="DN4" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.74</v>
       </c>
       <c r="DO4" t="n">
-        <v>1.58</v>
+        <v>1.48</v>
       </c>
       <c r="DP4" t="n">
-        <v>11.19</v>
+        <v>11.15</v>
       </c>
       <c r="DQ4" t="n">
-        <v>11.27</v>
+        <v>11.22</v>
       </c>
       <c r="DR4" t="n">
         <v>10.26</v>
       </c>
       <c r="DS4" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DT4" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DU4" t="n">
         <v>0</v>
       </c>
       <c r="DV4" t="n">
-        <v>47</v>
+        <v>47.18</v>
       </c>
       <c r="DW4" t="n">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
       <c r="DX4" t="n">
-        <v>10.81</v>
+        <v>10.82</v>
       </c>
       <c r="DY4" t="n">
-        <v>6.96</v>
+        <v>6.89</v>
       </c>
       <c r="DZ4" t="n">
-        <v>3.84</v>
+        <v>3.92</v>
       </c>
       <c r="EA4" t="n">
-        <v>21.77</v>
+        <v>22.19</v>
       </c>
       <c r="EB4" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="EC4" t="n">
-        <v>2.08</v>
+        <v>2.07</v>
       </c>
     </row>
     <row r="5">
@@ -2588,13 +2588,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C5" t="n">
         <v>13</v>
       </c>
       <c r="D5" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E5" t="n">
         <v>0.23</v>
@@ -2678,139 +2678,139 @@
         <v>1.46</v>
       </c>
       <c r="AF5" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="AH5" t="n">
-        <v>2.69</v>
+        <v>2.79</v>
       </c>
       <c r="AI5" t="n">
-        <v>87.45999999999999</v>
+        <v>88.36</v>
       </c>
       <c r="AJ5" t="n">
-        <v>-0.08</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="AK5" t="n">
-        <v>2</v>
+        <v>1.86</v>
       </c>
       <c r="AL5" t="n">
-        <v>4.62</v>
+        <v>4.86</v>
       </c>
       <c r="AM5" t="n">
-        <v>0.77</v>
+        <v>0.86</v>
       </c>
       <c r="AN5" t="n">
-        <v>39.15</v>
+        <v>42</v>
       </c>
       <c r="AO5" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.64</v>
       </c>
       <c r="AP5" t="n">
-        <v>1.92</v>
+        <v>2.07</v>
       </c>
       <c r="AQ5" t="n">
-        <v>10.69</v>
+        <v>10.57</v>
       </c>
       <c r="AR5" t="n">
-        <v>10.92</v>
+        <v>10.79</v>
       </c>
       <c r="AS5" t="n">
-        <v>11.08</v>
+        <v>10.86</v>
       </c>
       <c r="AT5" t="n">
-        <v>1.69</v>
+        <v>1.79</v>
       </c>
       <c r="AU5" t="n">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="AV5" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="AW5" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="AX5" t="n">
         <v>0</v>
       </c>
       <c r="AY5" t="n">
-        <v>47.77</v>
+        <v>48.14</v>
       </c>
       <c r="AZ5" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="BA5" t="n">
-        <v>11.31</v>
+        <v>11.5</v>
       </c>
       <c r="BB5" t="n">
-        <v>6.38</v>
+        <v>6.79</v>
       </c>
       <c r="BC5" t="n">
-        <v>4.92</v>
+        <v>4.71</v>
       </c>
       <c r="BD5" t="n">
-        <v>17.31</v>
+        <v>18.29</v>
       </c>
       <c r="BE5" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="BF5" t="n">
-        <v>1.69</v>
+        <v>1.57</v>
       </c>
       <c r="BG5" t="n">
         <v>3.04</v>
       </c>
       <c r="BH5" t="n">
-        <v>10.58</v>
+        <v>10.74</v>
       </c>
       <c r="BI5" t="n">
         <v>3.04</v>
       </c>
       <c r="BJ5" t="n">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="BK5" t="n">
-        <v>0.62</v>
+        <v>0.59</v>
       </c>
       <c r="BL5" t="n">
-        <v>0.96</v>
+        <v>1</v>
       </c>
       <c r="BM5" t="n">
-        <v>0.73</v>
+        <v>0.7</v>
       </c>
       <c r="BN5" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="BO5" t="n">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="BP5" t="n">
-        <v>4.23</v>
+        <v>4.37</v>
       </c>
       <c r="BQ5" t="n">
-        <v>6.35</v>
+        <v>6.37</v>
       </c>
       <c r="BR5" t="n">
-        <v>96.15000000000001</v>
+        <v>96.3</v>
       </c>
       <c r="BS5" t="n">
-        <v>84.62</v>
+        <v>85.19</v>
       </c>
       <c r="BT5" t="n">
-        <v>57.69</v>
+        <v>59.26</v>
       </c>
       <c r="BU5" t="n">
-        <v>38.46</v>
+        <v>37.04</v>
       </c>
       <c r="BV5" t="n">
-        <v>19.23</v>
+        <v>18.52</v>
       </c>
       <c r="BW5" t="n">
-        <v>7.69</v>
+        <v>7.41</v>
       </c>
       <c r="BX5" t="n">
-        <v>61.54</v>
+        <v>59.26</v>
       </c>
       <c r="BY5" t="n">
         <v>2.61</v>
@@ -2819,22 +2819,22 @@
         <v>2.72</v>
       </c>
       <c r="CA5" t="n">
-        <v>3.57</v>
+        <v>3.59</v>
       </c>
       <c r="CB5" t="n">
-        <v>3.74</v>
+        <v>3.75</v>
       </c>
       <c r="CC5" t="n">
-        <v>3.6</v>
+        <v>3.66</v>
       </c>
       <c r="CD5" t="n">
-        <v>3.93</v>
+        <v>3.94</v>
       </c>
       <c r="CE5" t="n">
         <v>1.31</v>
       </c>
       <c r="CF5" t="n">
-        <v>2.49</v>
+        <v>2.48</v>
       </c>
       <c r="CG5" t="n">
         <v>3.21</v>
@@ -2867,7 +2867,7 @@
         <v>1.75</v>
       </c>
       <c r="CQ5" t="n">
-        <v>2.78</v>
+        <v>2.77</v>
       </c>
       <c r="CR5" t="n">
         <v>1.36</v>
@@ -2891,97 +2891,97 @@
         <v>1.55</v>
       </c>
       <c r="CY5" t="n">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="CZ5" t="n">
         <v>2.44</v>
       </c>
       <c r="DA5" t="n">
-        <v>2.02</v>
+        <v>2.03</v>
       </c>
       <c r="DB5" t="n">
         <v>1.24</v>
       </c>
       <c r="DC5" t="n">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="DD5" t="n">
         <v>2.9</v>
       </c>
       <c r="DE5" t="n">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
       <c r="DF5" t="n">
-        <v>1.15</v>
+        <v>1.11</v>
       </c>
       <c r="DG5" t="n">
-        <v>2.77</v>
+        <v>2.82</v>
       </c>
       <c r="DH5" t="n">
-        <v>95.5</v>
+        <v>95.67</v>
       </c>
       <c r="DI5" t="n">
         <v>-0.04</v>
       </c>
       <c r="DJ5" t="n">
-        <v>1.89</v>
+        <v>1.82</v>
       </c>
       <c r="DK5" t="n">
-        <v>4.81</v>
+        <v>4.93</v>
       </c>
       <c r="DL5" t="n">
-        <v>0.57</v>
+        <v>0.63</v>
       </c>
       <c r="DM5" t="n">
-        <v>45.96</v>
+        <v>47.19</v>
       </c>
       <c r="DN5" t="n">
-        <v>0.57</v>
+        <v>0.55</v>
       </c>
       <c r="DO5" t="n">
-        <v>2.03</v>
+        <v>2.11</v>
       </c>
       <c r="DP5" t="n">
-        <v>10.73</v>
+        <v>10.67</v>
       </c>
       <c r="DQ5" t="n">
-        <v>10.88</v>
+        <v>10.82</v>
       </c>
       <c r="DR5" t="n">
-        <v>9.73</v>
+        <v>9.67</v>
       </c>
       <c r="DS5" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DT5" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DU5" t="n">
         <v>0</v>
       </c>
       <c r="DV5" t="n">
-        <v>51.16</v>
+        <v>51.22</v>
       </c>
       <c r="DW5" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="DX5" t="n">
-        <v>13.34</v>
+        <v>13.37</v>
       </c>
       <c r="DY5" t="n">
-        <v>8.880000000000001</v>
+        <v>9</v>
       </c>
       <c r="DZ5" t="n">
-        <v>4.46</v>
+        <v>4.37</v>
       </c>
       <c r="EA5" t="n">
-        <v>18.69</v>
+        <v>19.15</v>
       </c>
       <c r="EB5" t="n">
         <v>1.49</v>
       </c>
       <c r="EC5" t="n">
-        <v>1.58</v>
+        <v>1.52</v>
       </c>
     </row>
     <row r="6">
@@ -2991,61 +2991,61 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C6" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D6" t="n">
         <v>13</v>
       </c>
       <c r="E6" t="n">
-        <v>0</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="F6" t="n">
-        <v>0.54</v>
+        <v>0.64</v>
       </c>
       <c r="G6" t="n">
-        <v>4.15</v>
+        <v>4.07</v>
       </c>
       <c r="H6" t="n">
-        <v>129.77</v>
+        <v>126.43</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>1.15</v>
+        <v>1.21</v>
       </c>
       <c r="K6" t="n">
-        <v>6.92</v>
+        <v>6.93</v>
       </c>
       <c r="L6" t="n">
-        <v>0.46</v>
+        <v>0.5</v>
       </c>
       <c r="M6" t="n">
-        <v>63.08</v>
+        <v>61.57</v>
       </c>
       <c r="N6" t="n">
-        <v>0.54</v>
+        <v>0.5</v>
       </c>
       <c r="O6" t="n">
-        <v>2.69</v>
+        <v>2.79</v>
       </c>
       <c r="P6" t="n">
-        <v>10.15</v>
+        <v>10.07</v>
       </c>
       <c r="Q6" t="n">
-        <v>13.54</v>
+        <v>13.21</v>
       </c>
       <c r="R6" t="n">
-        <v>5.69</v>
+        <v>6</v>
       </c>
       <c r="S6" t="n">
-        <v>1.54</v>
+        <v>1.43</v>
       </c>
       <c r="T6" t="n">
-        <v>1.31</v>
+        <v>1.43</v>
       </c>
       <c r="U6" t="n">
         <v>0</v>
@@ -3057,28 +3057,28 @@
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>64.08</v>
+        <v>62.86</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="Z6" t="n">
-        <v>18.31</v>
+        <v>18.14</v>
       </c>
       <c r="AA6" t="n">
-        <v>12.15</v>
+        <v>12</v>
       </c>
       <c r="AB6" t="n">
-        <v>6.15</v>
+        <v>6.14</v>
       </c>
       <c r="AC6" t="n">
-        <v>21.92</v>
+        <v>21.57</v>
       </c>
       <c r="AD6" t="n">
-        <v>2.05</v>
+        <v>2.02</v>
       </c>
       <c r="AE6" t="n">
-        <v>1</v>
+        <v>1.07</v>
       </c>
       <c r="AF6" t="n">
         <v>0.23</v>
@@ -3162,58 +3162,58 @@
         <v>1.77</v>
       </c>
       <c r="BG6" t="n">
-        <v>2.92</v>
+        <v>2.93</v>
       </c>
       <c r="BH6" t="n">
-        <v>9.880000000000001</v>
+        <v>10.07</v>
       </c>
       <c r="BI6" t="n">
-        <v>2.92</v>
+        <v>2.93</v>
       </c>
       <c r="BJ6" t="n">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="BK6" t="n">
-        <v>0.92</v>
+        <v>0.89</v>
       </c>
       <c r="BL6" t="n">
-        <v>0.85</v>
+        <v>0.89</v>
       </c>
       <c r="BM6" t="n">
-        <v>0.58</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="BN6" t="n">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="BO6" t="n">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="BP6" t="n">
-        <v>4.54</v>
+        <v>4.67</v>
       </c>
       <c r="BQ6" t="n">
-        <v>5.31</v>
+        <v>5.37</v>
       </c>
       <c r="BR6" t="n">
         <v>100</v>
       </c>
       <c r="BS6" t="n">
-        <v>88.45999999999999</v>
+        <v>88.89</v>
       </c>
       <c r="BT6" t="n">
-        <v>61.54</v>
+        <v>62.96</v>
       </c>
       <c r="BU6" t="n">
-        <v>19.23</v>
+        <v>18.52</v>
       </c>
       <c r="BV6" t="n">
-        <v>11.54</v>
+        <v>11.11</v>
       </c>
       <c r="BW6" t="n">
-        <v>3.85</v>
+        <v>3.7</v>
       </c>
       <c r="BX6" t="n">
-        <v>76.92</v>
+        <v>74.06999999999999</v>
       </c>
       <c r="BY6" t="n">
         <v>1.8</v>
@@ -3222,7 +3222,7 @@
         <v>1.87</v>
       </c>
       <c r="CA6" t="n">
-        <v>3.81</v>
+        <v>3.82</v>
       </c>
       <c r="CB6" t="n">
         <v>3.93</v>
@@ -3237,10 +3237,10 @@
         <v>1.3</v>
       </c>
       <c r="CF6" t="n">
-        <v>2.45</v>
+        <v>2.44</v>
       </c>
       <c r="CG6" t="n">
-        <v>3.23</v>
+        <v>3.24</v>
       </c>
       <c r="CH6" t="n">
         <v>1.52</v>
@@ -3255,10 +3255,10 @@
         <v>1.5</v>
       </c>
       <c r="CL6" t="n">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="CM6" t="n">
-        <v>2.43</v>
+        <v>2.44</v>
       </c>
       <c r="CN6" t="n">
         <v>1.89</v>
@@ -3267,7 +3267,7 @@
         <v>1.2</v>
       </c>
       <c r="CP6" t="n">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="CQ6" t="n">
         <v>2.72</v>
@@ -3276,16 +3276,16 @@
         <v>1.36</v>
       </c>
       <c r="CS6" t="n">
-        <v>2.6</v>
+        <v>2.59</v>
       </c>
       <c r="CT6" t="n">
         <v>3.16</v>
       </c>
       <c r="CU6" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="CV6" t="n">
-        <v>2.26</v>
+        <v>2.27</v>
       </c>
       <c r="CW6" t="n">
         <v>1.7</v>
@@ -3294,64 +3294,64 @@
         <v>1.58</v>
       </c>
       <c r="CY6" t="n">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="CZ6" t="n">
         <v>2.37</v>
       </c>
       <c r="DA6" t="n">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="DB6" t="n">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="DC6" t="n">
         <v>1.76</v>
       </c>
       <c r="DD6" t="n">
-        <v>2.85</v>
+        <v>2.84</v>
       </c>
       <c r="DE6" t="n">
-        <v>0.12</v>
+        <v>0.15</v>
       </c>
       <c r="DF6" t="n">
-        <v>0.92</v>
+        <v>0.96</v>
       </c>
       <c r="DG6" t="n">
-        <v>3.34</v>
+        <v>3.33</v>
       </c>
       <c r="DH6" t="n">
-        <v>113.93</v>
+        <v>112.78</v>
       </c>
       <c r="DI6" t="n">
         <v>0.04</v>
       </c>
       <c r="DJ6" t="n">
-        <v>1.46</v>
+        <v>1.48</v>
       </c>
       <c r="DK6" t="n">
-        <v>5.69</v>
+        <v>5.74</v>
       </c>
       <c r="DL6" t="n">
-        <v>0.57</v>
+        <v>0.59</v>
       </c>
       <c r="DM6" t="n">
-        <v>55.46</v>
+        <v>54.96</v>
       </c>
       <c r="DN6" t="n">
-        <v>0.5</v>
+        <v>0.48</v>
       </c>
       <c r="DO6" t="n">
-        <v>2.31</v>
+        <v>2.37</v>
       </c>
       <c r="DP6" t="n">
-        <v>10.08</v>
+        <v>10.04</v>
       </c>
       <c r="DQ6" t="n">
-        <v>12.66</v>
+        <v>12.52</v>
       </c>
       <c r="DR6" t="n">
-        <v>6.88</v>
+        <v>7</v>
       </c>
       <c r="DS6" t="n">
         <v>0.04</v>
@@ -3363,28 +3363,28 @@
         <v>0</v>
       </c>
       <c r="DV6" t="n">
-        <v>62</v>
+        <v>61.44</v>
       </c>
       <c r="DW6" t="n">
         <v>0.04</v>
       </c>
       <c r="DX6" t="n">
-        <v>15.92</v>
+        <v>15.93</v>
       </c>
       <c r="DY6" t="n">
-        <v>10.08</v>
+        <v>10.07</v>
       </c>
       <c r="DZ6" t="n">
-        <v>5.84</v>
+        <v>5.85</v>
       </c>
       <c r="EA6" t="n">
-        <v>20.31</v>
+        <v>20.18</v>
       </c>
       <c r="EB6" t="n">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="EC6" t="n">
-        <v>1.39</v>
+        <v>1.41</v>
       </c>
     </row>
     <row r="7">
@@ -3460,7 +3460,7 @@
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>48.71</v>
+        <v>48.79</v>
       </c>
       <c r="Y7" t="n">
         <v>0</v>
@@ -3766,7 +3766,7 @@
         <v>0</v>
       </c>
       <c r="DV7" t="n">
-        <v>49.88</v>
+        <v>49.93</v>
       </c>
       <c r="DW7" t="n">
         <v>0</v>
@@ -3797,94 +3797,94 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C8" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D8" t="n">
         <v>13</v>
       </c>
       <c r="E8" t="n">
-        <v>0.23</v>
+        <v>0.21</v>
       </c>
       <c r="F8" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="G8" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="H8" t="n">
+        <v>97.86</v>
+      </c>
+      <c r="I8" t="n">
+        <v>-0.07000000000000001</v>
+      </c>
+      <c r="J8" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="K8" t="n">
+        <v>5.71</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="M8" t="n">
+        <v>54.64</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="O8" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="P8" t="n">
+        <v>10.29</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>12.36</v>
+      </c>
+      <c r="R8" t="n">
+        <v>8.140000000000001</v>
+      </c>
+      <c r="S8" t="n">
         <v>1</v>
       </c>
-      <c r="G8" t="n">
-        <v>2.77</v>
-      </c>
-      <c r="H8" t="n">
-        <v>97.69</v>
-      </c>
-      <c r="I8" t="n">
-        <v>-0.08</v>
-      </c>
-      <c r="J8" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="K8" t="n">
-        <v>5.77</v>
-      </c>
-      <c r="L8" t="n">
-        <v>0.31</v>
-      </c>
-      <c r="M8" t="n">
-        <v>55.85</v>
-      </c>
-      <c r="N8" t="n">
-        <v>0.31</v>
-      </c>
-      <c r="O8" t="n">
-        <v>3</v>
-      </c>
-      <c r="P8" t="n">
-        <v>10.69</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>12</v>
-      </c>
-      <c r="R8" t="n">
-        <v>8.15</v>
-      </c>
-      <c r="S8" t="n">
-        <v>1.08</v>
-      </c>
       <c r="T8" t="n">
-        <v>1.23</v>
+        <v>1.14</v>
       </c>
       <c r="U8" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="V8" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>51.46</v>
+        <v>50.57</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.08</v>
+        <v>0.14</v>
       </c>
       <c r="Z8" t="n">
-        <v>16.08</v>
+        <v>15.5</v>
       </c>
       <c r="AA8" t="n">
-        <v>11.23</v>
+        <v>10.71</v>
       </c>
       <c r="AB8" t="n">
-        <v>4.85</v>
+        <v>4.79</v>
       </c>
       <c r="AC8" t="n">
-        <v>19.77</v>
+        <v>19.79</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.76</v>
+        <v>1.71</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.23</v>
+        <v>1.14</v>
       </c>
       <c r="AF8" t="n">
         <v>0.08</v>
@@ -3968,67 +3968,67 @@
         <v>1.77</v>
       </c>
       <c r="BG8" t="n">
-        <v>2.77</v>
+        <v>2.67</v>
       </c>
       <c r="BH8" t="n">
-        <v>10.12</v>
+        <v>10.04</v>
       </c>
       <c r="BI8" t="n">
-        <v>2.77</v>
+        <v>2.67</v>
       </c>
       <c r="BJ8" t="n">
-        <v>0.73</v>
+        <v>0.7</v>
       </c>
       <c r="BK8" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.67</v>
       </c>
       <c r="BL8" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.78</v>
       </c>
       <c r="BM8" t="n">
-        <v>0.54</v>
+        <v>0.52</v>
       </c>
       <c r="BN8" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="BO8" t="n">
-        <v>1.42</v>
+        <v>1.37</v>
       </c>
       <c r="BP8" t="n">
-        <v>4.73</v>
+        <v>4.67</v>
       </c>
       <c r="BQ8" t="n">
-        <v>5.35</v>
+        <v>5.33</v>
       </c>
       <c r="BR8" t="n">
-        <v>92.31</v>
+        <v>88.89</v>
       </c>
       <c r="BS8" t="n">
-        <v>80.77</v>
+        <v>77.78</v>
       </c>
       <c r="BT8" t="n">
-        <v>38.46</v>
+        <v>37.04</v>
       </c>
       <c r="BU8" t="n">
-        <v>26.92</v>
+        <v>25.93</v>
       </c>
       <c r="BV8" t="n">
-        <v>11.54</v>
+        <v>11.11</v>
       </c>
       <c r="BW8" t="n">
-        <v>7.69</v>
+        <v>7.41</v>
       </c>
       <c r="BX8" t="n">
-        <v>38.46</v>
+        <v>37.04</v>
       </c>
       <c r="BY8" t="n">
-        <v>2.21</v>
+        <v>2.4</v>
       </c>
       <c r="BZ8" t="n">
-        <v>2.35</v>
+        <v>2.49</v>
       </c>
       <c r="CA8" t="n">
-        <v>3.76</v>
+        <v>3.77</v>
       </c>
       <c r="CB8" t="n">
         <v>3.84</v>
@@ -4040,22 +4040,22 @@
         <v>3.89</v>
       </c>
       <c r="CE8" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="CF8" t="n">
         <v>2.3</v>
       </c>
       <c r="CG8" t="n">
-        <v>3.43</v>
+        <v>3.42</v>
       </c>
       <c r="CH8" t="n">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="CI8" t="n">
-        <v>2.39</v>
+        <v>2.38</v>
       </c>
       <c r="CJ8" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="CK8" t="n">
         <v>1.36</v>
@@ -4076,37 +4076,37 @@
         <v>1.62</v>
       </c>
       <c r="CQ8" t="n">
-        <v>2.49</v>
+        <v>2.5</v>
       </c>
       <c r="CR8" t="n">
         <v>1.34</v>
       </c>
       <c r="CS8" t="n">
-        <v>2.38</v>
+        <v>2.39</v>
       </c>
       <c r="CT8" t="n">
-        <v>3.32</v>
+        <v>3.31</v>
       </c>
       <c r="CU8" t="n">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="CV8" t="n">
-        <v>2.55</v>
+        <v>2.54</v>
       </c>
       <c r="CW8" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="CX8" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="CY8" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="CZ8" t="n">
-        <v>2.57</v>
+        <v>2.53</v>
       </c>
       <c r="DA8" t="n">
-        <v>2.22</v>
+        <v>2.21</v>
       </c>
       <c r="DB8" t="n">
         <v>1.19</v>
@@ -4115,82 +4115,82 @@
         <v>1.64</v>
       </c>
       <c r="DD8" t="n">
-        <v>2.53</v>
+        <v>2.55</v>
       </c>
       <c r="DE8" t="n">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
       <c r="DF8" t="n">
-        <v>1.34</v>
+        <v>1.3</v>
       </c>
       <c r="DG8" t="n">
-        <v>2.38</v>
+        <v>2.45</v>
       </c>
       <c r="DH8" t="n">
-        <v>93.19</v>
+        <v>93.44</v>
       </c>
       <c r="DI8" t="n">
         <v>-0.04</v>
       </c>
       <c r="DJ8" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="DK8" t="n">
         <v>4.96</v>
       </c>
       <c r="DL8" t="n">
-        <v>0.27</v>
+        <v>0.26</v>
       </c>
       <c r="DM8" t="n">
-        <v>49.39</v>
+        <v>49</v>
       </c>
       <c r="DN8" t="n">
-        <v>0.23</v>
+        <v>0.26</v>
       </c>
       <c r="DO8" t="n">
-        <v>2.58</v>
+        <v>2.52</v>
       </c>
       <c r="DP8" t="n">
-        <v>11.92</v>
+        <v>11.67</v>
       </c>
       <c r="DQ8" t="n">
-        <v>11.96</v>
+        <v>12.15</v>
       </c>
       <c r="DR8" t="n">
-        <v>8.5</v>
+        <v>8.48</v>
       </c>
       <c r="DS8" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="DT8" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="DU8" t="n">
         <v>0</v>
       </c>
       <c r="DV8" t="n">
-        <v>49.27</v>
+        <v>48.89</v>
       </c>
       <c r="DW8" t="n">
-        <v>0.08</v>
+        <v>0.11</v>
       </c>
       <c r="DX8" t="n">
-        <v>14.58</v>
+        <v>14.33</v>
       </c>
       <c r="DY8" t="n">
-        <v>9.85</v>
+        <v>9.630000000000001</v>
       </c>
       <c r="DZ8" t="n">
-        <v>4.74</v>
+        <v>4.71</v>
       </c>
       <c r="EA8" t="n">
-        <v>21.65</v>
+        <v>21.6</v>
       </c>
       <c r="EB8" t="n">
-        <v>1.6</v>
+        <v>1.58</v>
       </c>
       <c r="EC8" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
     </row>
     <row r="9">
@@ -4296,7 +4296,7 @@
         <v>2.29</v>
       </c>
       <c r="AH9" t="n">
-        <v>2.29</v>
+        <v>2.64</v>
       </c>
       <c r="AI9" t="n">
         <v>76.5</v>
@@ -4308,10 +4308,10 @@
         <v>3.36</v>
       </c>
       <c r="AL9" t="n">
-        <v>4.5</v>
+        <v>4.57</v>
       </c>
       <c r="AM9" t="n">
-        <v>0.36</v>
+        <v>0.5</v>
       </c>
       <c r="AN9" t="n">
         <v>43.21</v>
@@ -4320,7 +4320,7 @@
         <v>1.07</v>
       </c>
       <c r="AP9" t="n">
-        <v>1.57</v>
+        <v>1.93</v>
       </c>
       <c r="AQ9" t="n">
         <v>15.71</v>
@@ -4374,7 +4374,7 @@
         <v>2.63</v>
       </c>
       <c r="BH9" t="n">
-        <v>10.96</v>
+        <v>11</v>
       </c>
       <c r="BI9" t="n">
         <v>2.63</v>
@@ -4398,10 +4398,10 @@
         <v>1.19</v>
       </c>
       <c r="BP9" t="n">
-        <v>5.04</v>
+        <v>5.48</v>
       </c>
       <c r="BQ9" t="n">
-        <v>5.22</v>
+        <v>5.48</v>
       </c>
       <c r="BR9" t="n">
         <v>92.59</v>
@@ -4527,7 +4527,7 @@
         <v>2.26</v>
       </c>
       <c r="DG9" t="n">
-        <v>2.33</v>
+        <v>2.51</v>
       </c>
       <c r="DH9" t="n">
         <v>78.73999999999999</v>
@@ -4539,10 +4539,10 @@
         <v>3.19</v>
       </c>
       <c r="DK9" t="n">
-        <v>4.74</v>
+        <v>4.78</v>
       </c>
       <c r="DL9" t="n">
-        <v>0.45</v>
+        <v>0.52</v>
       </c>
       <c r="DM9" t="n">
         <v>42.07</v>
@@ -4551,7 +4551,7 @@
         <v>0.93</v>
       </c>
       <c r="DO9" t="n">
-        <v>2.04</v>
+        <v>2.22</v>
       </c>
       <c r="DP9" t="n">
         <v>15.89</v>
@@ -5021,7 +5021,7 @@
         <v>1.71</v>
       </c>
       <c r="G11" t="n">
-        <v>3.07</v>
+        <v>3.29</v>
       </c>
       <c r="H11" t="n">
         <v>109.57</v>
@@ -5036,7 +5036,7 @@
         <v>6.79</v>
       </c>
       <c r="L11" t="n">
-        <v>0.64</v>
+        <v>0.71</v>
       </c>
       <c r="M11" t="n">
         <v>58.71</v>
@@ -5045,7 +5045,7 @@
         <v>0.86</v>
       </c>
       <c r="O11" t="n">
-        <v>2.93</v>
+        <v>3.5</v>
       </c>
       <c r="P11" t="n">
         <v>13.21</v>
@@ -5180,7 +5180,7 @@
         <v>2.67</v>
       </c>
       <c r="BH11" t="n">
-        <v>11</v>
+        <v>11.04</v>
       </c>
       <c r="BI11" t="n">
         <v>2.67</v>
@@ -5204,10 +5204,10 @@
         <v>1.11</v>
       </c>
       <c r="BP11" t="n">
-        <v>5.04</v>
+        <v>5.48</v>
       </c>
       <c r="BQ11" t="n">
-        <v>5.3</v>
+        <v>5.56</v>
       </c>
       <c r="BR11" t="n">
         <v>88.89</v>
@@ -5333,7 +5333,7 @@
         <v>1.55</v>
       </c>
       <c r="DG11" t="n">
-        <v>3.04</v>
+        <v>3.15</v>
       </c>
       <c r="DH11" t="n">
         <v>102.85</v>
@@ -5348,7 +5348,7 @@
         <v>6.45</v>
       </c>
       <c r="DL11" t="n">
-        <v>0.48</v>
+        <v>0.52</v>
       </c>
       <c r="DM11" t="n">
         <v>55.89</v>
@@ -5357,7 +5357,7 @@
         <v>1</v>
       </c>
       <c r="DO11" t="n">
-        <v>3</v>
+        <v>3.3</v>
       </c>
       <c r="DP11" t="n">
         <v>13.96</v>
@@ -6215,94 +6215,94 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C14" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D14" t="n">
         <v>13</v>
       </c>
       <c r="E14" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="F14" t="n">
-        <v>1.69</v>
+        <v>1.86</v>
       </c>
       <c r="G14" t="n">
-        <v>3.15</v>
+        <v>2.93</v>
       </c>
       <c r="H14" t="n">
-        <v>96.23</v>
+        <v>95.43000000000001</v>
       </c>
       <c r="I14" t="n">
         <v>0</v>
       </c>
       <c r="J14" t="n">
-        <v>2.15</v>
+        <v>2.43</v>
       </c>
       <c r="K14" t="n">
-        <v>5.85</v>
+        <v>5.57</v>
       </c>
       <c r="L14" t="n">
-        <v>0.15</v>
+        <v>0.29</v>
       </c>
       <c r="M14" t="n">
-        <v>54</v>
+        <v>52.07</v>
       </c>
       <c r="N14" t="n">
-        <v>0.31</v>
+        <v>0.36</v>
       </c>
       <c r="O14" t="n">
-        <v>2.69</v>
+        <v>2.64</v>
       </c>
       <c r="P14" t="n">
-        <v>11.46</v>
+        <v>11.21</v>
       </c>
       <c r="Q14" t="n">
-        <v>12.15</v>
+        <v>11.93</v>
       </c>
       <c r="R14" t="n">
-        <v>7.38</v>
+        <v>7.86</v>
       </c>
       <c r="S14" t="n">
-        <v>1.31</v>
+        <v>1.36</v>
       </c>
       <c r="T14" t="n">
-        <v>1.46</v>
+        <v>1.43</v>
       </c>
       <c r="U14" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="V14" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="W14" t="n">
         <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>49.85</v>
+        <v>49.07</v>
       </c>
       <c r="Y14" t="n">
-        <v>0.23</v>
+        <v>0.29</v>
       </c>
       <c r="Z14" t="n">
-        <v>14</v>
+        <v>13.64</v>
       </c>
       <c r="AA14" t="n">
-        <v>8.92</v>
+        <v>8.710000000000001</v>
       </c>
       <c r="AB14" t="n">
-        <v>5.08</v>
+        <v>4.93</v>
       </c>
       <c r="AC14" t="n">
-        <v>18.23</v>
+        <v>17.5</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.63</v>
+        <v>1.58</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.77</v>
+        <v>1.93</v>
       </c>
       <c r="AF14" t="n">
         <v>0.15</v>
@@ -6386,70 +6386,70 @@
         <v>2.15</v>
       </c>
       <c r="BG14" t="n">
-        <v>2.69</v>
+        <v>2.7</v>
       </c>
       <c r="BH14" t="n">
-        <v>10</v>
+        <v>9.85</v>
       </c>
       <c r="BI14" t="n">
-        <v>2.69</v>
+        <v>2.7</v>
       </c>
       <c r="BJ14" t="n">
-        <v>0.65</v>
+        <v>0.67</v>
       </c>
       <c r="BK14" t="n">
-        <v>0.77</v>
+        <v>0.74</v>
       </c>
       <c r="BL14" t="n">
-        <v>0.77</v>
+        <v>0.74</v>
       </c>
       <c r="BM14" t="n">
-        <v>0.5</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="BN14" t="n">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="BO14" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="BP14" t="n">
-        <v>4.92</v>
+        <v>4.93</v>
       </c>
       <c r="BQ14" t="n">
-        <v>5.08</v>
+        <v>4.93</v>
       </c>
       <c r="BR14" t="n">
-        <v>96.15000000000001</v>
+        <v>96.3</v>
       </c>
       <c r="BS14" t="n">
-        <v>76.92</v>
+        <v>77.78</v>
       </c>
       <c r="BT14" t="n">
-        <v>46.15</v>
+        <v>48.15</v>
       </c>
       <c r="BU14" t="n">
-        <v>30.77</v>
+        <v>29.63</v>
       </c>
       <c r="BV14" t="n">
-        <v>11.54</v>
+        <v>11.11</v>
       </c>
       <c r="BW14" t="n">
-        <v>3.85</v>
+        <v>3.7</v>
       </c>
       <c r="BX14" t="n">
-        <v>57.69</v>
+        <v>59.26</v>
       </c>
       <c r="BY14" t="n">
-        <v>2.26</v>
+        <v>2.38</v>
       </c>
       <c r="BZ14" t="n">
-        <v>2.36</v>
+        <v>2.47</v>
       </c>
       <c r="CA14" t="n">
-        <v>3.48</v>
+        <v>3.49</v>
       </c>
       <c r="CB14" t="n">
-        <v>3.51</v>
+        <v>3.52</v>
       </c>
       <c r="CC14" t="n">
         <v>3.64</v>
@@ -6461,16 +6461,16 @@
         <v>1.36</v>
       </c>
       <c r="CF14" t="n">
-        <v>2.69</v>
+        <v>2.68</v>
       </c>
       <c r="CG14" t="n">
-        <v>2.98</v>
+        <v>2.99</v>
       </c>
       <c r="CH14" t="n">
         <v>1.43</v>
       </c>
       <c r="CI14" t="n">
-        <v>2.04</v>
+        <v>2.05</v>
       </c>
       <c r="CJ14" t="n">
         <v>1.74</v>
@@ -6479,10 +6479,10 @@
         <v>1.47</v>
       </c>
       <c r="CL14" t="n">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="CM14" t="n">
-        <v>2.51</v>
+        <v>2.5</v>
       </c>
       <c r="CN14" t="n">
         <v>1.92</v>
@@ -6491,124 +6491,124 @@
         <v>1.27</v>
       </c>
       <c r="CP14" t="n">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="CQ14" t="n">
-        <v>3.16</v>
+        <v>3.14</v>
       </c>
       <c r="CR14" t="n">
         <v>1.38</v>
       </c>
       <c r="CS14" t="n">
-        <v>2.85</v>
+        <v>2.83</v>
       </c>
       <c r="CT14" t="n">
-        <v>3.09</v>
+        <v>3.1</v>
       </c>
       <c r="CU14" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="CV14" t="n">
-        <v>2.13</v>
+        <v>2.14</v>
       </c>
       <c r="CW14" t="n">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="CX14" t="n">
         <v>1.53</v>
       </c>
       <c r="CY14" t="n">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="CZ14" t="n">
-        <v>2.46</v>
+        <v>2.47</v>
       </c>
       <c r="DA14" t="n">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="DB14" t="n">
         <v>1.3</v>
       </c>
       <c r="DC14" t="n">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="DD14" t="n">
-        <v>3.35</v>
+        <v>3.33</v>
       </c>
       <c r="DE14" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="DF14" t="n">
-        <v>1.61</v>
+        <v>1.71</v>
       </c>
       <c r="DG14" t="n">
-        <v>2.73</v>
+        <v>2.63</v>
       </c>
       <c r="DH14" t="n">
-        <v>94.34999999999999</v>
+        <v>94</v>
       </c>
       <c r="DI14" t="n">
         <v>-0.04</v>
       </c>
       <c r="DJ14" t="n">
-        <v>2.15</v>
+        <v>2.3</v>
       </c>
       <c r="DK14" t="n">
-        <v>5.27</v>
+        <v>5.15</v>
       </c>
       <c r="DL14" t="n">
-        <v>0.38</v>
+        <v>0.45</v>
       </c>
       <c r="DM14" t="n">
-        <v>49.69</v>
+        <v>48.85</v>
       </c>
       <c r="DN14" t="n">
-        <v>0.46</v>
+        <v>0.49</v>
       </c>
       <c r="DO14" t="n">
-        <v>2.53</v>
+        <v>2.51</v>
       </c>
       <c r="DP14" t="n">
-        <v>11.77</v>
+        <v>11.63</v>
       </c>
       <c r="DQ14" t="n">
-        <v>10.88</v>
+        <v>10.82</v>
       </c>
       <c r="DR14" t="n">
-        <v>7.62</v>
+        <v>7.86</v>
       </c>
       <c r="DS14" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DT14" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DU14" t="n">
         <v>0</v>
       </c>
       <c r="DV14" t="n">
-        <v>48.81</v>
+        <v>48.44</v>
       </c>
       <c r="DW14" t="n">
-        <v>0.12</v>
+        <v>0.15</v>
       </c>
       <c r="DX14" t="n">
-        <v>12.84</v>
+        <v>12.7</v>
       </c>
       <c r="DY14" t="n">
-        <v>8.460000000000001</v>
+        <v>8.369999999999999</v>
       </c>
       <c r="DZ14" t="n">
-        <v>4.38</v>
+        <v>4.33</v>
       </c>
       <c r="EA14" t="n">
-        <v>19.19</v>
+        <v>18.78</v>
       </c>
       <c r="EB14" t="n">
-        <v>1.48</v>
+        <v>1.46</v>
       </c>
       <c r="EC14" t="n">
-        <v>1.96</v>
+        <v>2.04</v>
       </c>
     </row>
     <row r="15">
@@ -7021,13 +7021,13 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C16" t="n">
         <v>13</v>
       </c>
       <c r="D16" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E16" t="n">
         <v>0.23</v>
@@ -7111,52 +7111,52 @@
         <v>1.85</v>
       </c>
       <c r="AF16" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="AG16" t="n">
-        <v>2</v>
+        <v>1.93</v>
       </c>
       <c r="AH16" t="n">
-        <v>2.77</v>
+        <v>2.64</v>
       </c>
       <c r="AI16" t="n">
-        <v>111.46</v>
+        <v>110.29</v>
       </c>
       <c r="AJ16" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="AK16" t="n">
-        <v>3</v>
+        <v>2.93</v>
       </c>
       <c r="AL16" t="n">
-        <v>5.46</v>
+        <v>5.29</v>
       </c>
       <c r="AM16" t="n">
-        <v>0.54</v>
+        <v>0.5</v>
       </c>
       <c r="AN16" t="n">
-        <v>52.85</v>
+        <v>51.57</v>
       </c>
       <c r="AO16" t="n">
         <v>1</v>
       </c>
       <c r="AP16" t="n">
-        <v>2.69</v>
+        <v>2.64</v>
       </c>
       <c r="AQ16" t="n">
-        <v>13.62</v>
+        <v>13.86</v>
       </c>
       <c r="AR16" t="n">
-        <v>9.31</v>
+        <v>9.07</v>
       </c>
       <c r="AS16" t="n">
-        <v>6.15</v>
+        <v>6.07</v>
       </c>
       <c r="AT16" t="n">
-        <v>0.85</v>
+        <v>0.79</v>
       </c>
       <c r="AU16" t="n">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="AV16" t="n">
         <v>0</v>
@@ -7168,82 +7168,82 @@
         <v>0</v>
       </c>
       <c r="AY16" t="n">
-        <v>55.92</v>
+        <v>56.29</v>
       </c>
       <c r="AZ16" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="BA16" t="n">
-        <v>14.31</v>
+        <v>13.79</v>
       </c>
       <c r="BB16" t="n">
-        <v>9.69</v>
+        <v>9.43</v>
       </c>
       <c r="BC16" t="n">
-        <v>4.62</v>
+        <v>4.36</v>
       </c>
       <c r="BD16" t="n">
-        <v>19.69</v>
+        <v>20.14</v>
       </c>
       <c r="BE16" t="n">
-        <v>1.61</v>
+        <v>1.55</v>
       </c>
       <c r="BF16" t="n">
-        <v>2.92</v>
+        <v>2.86</v>
       </c>
       <c r="BG16" t="n">
-        <v>2.23</v>
+        <v>2.15</v>
       </c>
       <c r="BH16" t="n">
-        <v>9.539999999999999</v>
+        <v>9.48</v>
       </c>
       <c r="BI16" t="n">
-        <v>2.23</v>
+        <v>2.15</v>
       </c>
       <c r="BJ16" t="n">
-        <v>0.58</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="BK16" t="n">
-        <v>0.35</v>
+        <v>0.33</v>
       </c>
       <c r="BL16" t="n">
-        <v>0.92</v>
+        <v>0.89</v>
       </c>
       <c r="BM16" t="n">
-        <v>0.38</v>
+        <v>0.37</v>
       </c>
       <c r="BN16" t="n">
-        <v>1.31</v>
+        <v>1.26</v>
       </c>
       <c r="BO16" t="n">
-        <v>0.92</v>
+        <v>0.89</v>
       </c>
       <c r="BP16" t="n">
-        <v>4.73</v>
+        <v>4.67</v>
       </c>
       <c r="BQ16" t="n">
         <v>4.81</v>
       </c>
       <c r="BR16" t="n">
-        <v>92.31</v>
+        <v>88.89</v>
       </c>
       <c r="BS16" t="n">
-        <v>73.08</v>
+        <v>70.37</v>
       </c>
       <c r="BT16" t="n">
-        <v>30.77</v>
+        <v>29.63</v>
       </c>
       <c r="BU16" t="n">
-        <v>15.38</v>
+        <v>14.81</v>
       </c>
       <c r="BV16" t="n">
-        <v>11.54</v>
+        <v>11.11</v>
       </c>
       <c r="BW16" t="n">
         <v>0</v>
       </c>
       <c r="BX16" t="n">
-        <v>46.15</v>
+        <v>44.44</v>
       </c>
       <c r="BY16" t="n">
         <v>1.41</v>
@@ -7255,10 +7255,10 @@
         <v>4.17</v>
       </c>
       <c r="CB16" t="n">
-        <v>4.38</v>
+        <v>4.36</v>
       </c>
       <c r="CC16" t="n">
-        <v>1.87</v>
+        <v>1.85</v>
       </c>
       <c r="CD16" t="n">
         <v>1.9</v>
@@ -7279,28 +7279,28 @@
         <v>1.91</v>
       </c>
       <c r="CJ16" t="n">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="CK16" t="n">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="CL16" t="n">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="CM16" t="n">
-        <v>2.45</v>
+        <v>2.47</v>
       </c>
       <c r="CN16" t="n">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="CO16" t="n">
         <v>1.23</v>
       </c>
       <c r="CP16" t="n">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="CQ16" t="n">
-        <v>2.88</v>
+        <v>2.87</v>
       </c>
       <c r="CR16" t="n">
         <v>1.37</v>
@@ -7309,7 +7309,7 @@
         <v>2.69</v>
       </c>
       <c r="CT16" t="n">
-        <v>3.14</v>
+        <v>3.15</v>
       </c>
       <c r="CU16" t="n">
         <v>1.49</v>
@@ -7318,13 +7318,13 @@
         <v>1.99</v>
       </c>
       <c r="CW16" t="n">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="CX16" t="n">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="CY16" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="CZ16" t="n">
         <v>2.36</v>
@@ -7342,79 +7342,79 @@
         <v>3.06</v>
       </c>
       <c r="DE16" t="n">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
       <c r="DF16" t="n">
-        <v>1.81</v>
+        <v>1.78</v>
       </c>
       <c r="DG16" t="n">
-        <v>3.2</v>
+        <v>3.11</v>
       </c>
       <c r="DH16" t="n">
-        <v>107.42</v>
+        <v>106.96</v>
       </c>
       <c r="DI16" t="n">
         <v>0.04</v>
       </c>
       <c r="DJ16" t="n">
-        <v>2.42</v>
+        <v>2.41</v>
       </c>
       <c r="DK16" t="n">
-        <v>6.07</v>
+        <v>5.96</v>
       </c>
       <c r="DL16" t="n">
-        <v>0.46</v>
+        <v>0.44</v>
       </c>
       <c r="DM16" t="n">
-        <v>54.54</v>
+        <v>53.81</v>
       </c>
       <c r="DN16" t="n">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="DO16" t="n">
-        <v>2.88</v>
+        <v>2.85</v>
       </c>
       <c r="DP16" t="n">
-        <v>12.88</v>
+        <v>13.04</v>
       </c>
       <c r="DQ16" t="n">
-        <v>9.73</v>
+        <v>9.59</v>
       </c>
       <c r="DR16" t="n">
-        <v>5.69</v>
+        <v>5.67</v>
       </c>
       <c r="DS16" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="DT16" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="DU16" t="n">
         <v>0</v>
       </c>
       <c r="DV16" t="n">
-        <v>54</v>
+        <v>54.26</v>
       </c>
       <c r="DW16" t="n">
         <v>0.04</v>
       </c>
       <c r="DX16" t="n">
-        <v>15.54</v>
+        <v>15.22</v>
       </c>
       <c r="DY16" t="n">
-        <v>9.92</v>
+        <v>9.779999999999999</v>
       </c>
       <c r="DZ16" t="n">
-        <v>5.62</v>
+        <v>5.45</v>
       </c>
       <c r="EA16" t="n">
-        <v>20.27</v>
+        <v>20.48</v>
       </c>
       <c r="EB16" t="n">
-        <v>1.77</v>
+        <v>1.73</v>
       </c>
       <c r="EC16" t="n">
-        <v>2.39</v>
+        <v>2.37</v>
       </c>
     </row>
     <row r="17">
@@ -7571,7 +7571,7 @@
         <v>0</v>
       </c>
       <c r="AY17" t="n">
-        <v>48.36</v>
+        <v>48.29</v>
       </c>
       <c r="AZ17" t="n">
         <v>0.14</v>
@@ -7796,7 +7796,7 @@
         <v>0</v>
       </c>
       <c r="DV17" t="n">
-        <v>47.89</v>
+        <v>47.85</v>
       </c>
       <c r="DW17" t="n">
         <v>0.11</v>

--- a/data/teams/leagues/Averages_Belgium_Pro_League_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Belgium_Pro_League_2025-2026.xlsx
@@ -1451,10 +1451,10 @@
         <v>0.14</v>
       </c>
       <c r="Z2" t="n">
-        <v>14.57</v>
+        <v>14.64</v>
       </c>
       <c r="AA2" t="n">
-        <v>9.640000000000001</v>
+        <v>9.710000000000001</v>
       </c>
       <c r="AB2" t="n">
         <v>4.93</v>
@@ -1463,7 +1463,7 @@
         <v>23.36</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="AE2" t="n">
         <v>1.21</v>
@@ -1757,10 +1757,10 @@
         <v>0.14</v>
       </c>
       <c r="DX2" t="n">
-        <v>13.66</v>
+        <v>13.7</v>
       </c>
       <c r="DY2" t="n">
-        <v>9.369999999999999</v>
+        <v>9.41</v>
       </c>
       <c r="DZ2" t="n">
         <v>4.3</v>
@@ -1935,10 +1935,10 @@
         <v>0</v>
       </c>
       <c r="BA3" t="n">
-        <v>14.5</v>
+        <v>14.57</v>
       </c>
       <c r="BB3" t="n">
-        <v>9.43</v>
+        <v>9.5</v>
       </c>
       <c r="BC3" t="n">
         <v>5.07</v>
@@ -1947,7 +1947,7 @@
         <v>18.71</v>
       </c>
       <c r="BE3" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="BF3" t="n">
         <v>1.64</v>
@@ -2160,10 +2160,10 @@
         <v>0.07000000000000001</v>
       </c>
       <c r="DX3" t="n">
-        <v>16.22</v>
+        <v>16.26</v>
       </c>
       <c r="DY3" t="n">
-        <v>10.71</v>
+        <v>10.74</v>
       </c>
       <c r="DZ3" t="n">
         <v>5.52</v>
@@ -2172,7 +2172,7 @@
         <v>20.74</v>
       </c>
       <c r="EB3" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="EC3" t="n">
         <v>1.33</v>
@@ -3842,7 +3842,7 @@
         <v>10.29</v>
       </c>
       <c r="Q8" t="n">
-        <v>12.36</v>
+        <v>12.29</v>
       </c>
       <c r="R8" t="n">
         <v>8.140000000000001</v>
@@ -4154,7 +4154,7 @@
         <v>11.67</v>
       </c>
       <c r="DQ8" t="n">
-        <v>12.15</v>
+        <v>12.11</v>
       </c>
       <c r="DR8" t="n">
         <v>8.48</v>
@@ -7174,10 +7174,10 @@
         <v>0.07000000000000001</v>
       </c>
       <c r="BA16" t="n">
-        <v>13.79</v>
+        <v>13.71</v>
       </c>
       <c r="BB16" t="n">
-        <v>9.43</v>
+        <v>9.359999999999999</v>
       </c>
       <c r="BC16" t="n">
         <v>4.36</v>
@@ -7399,10 +7399,10 @@
         <v>0.04</v>
       </c>
       <c r="DX16" t="n">
-        <v>15.22</v>
+        <v>15.18</v>
       </c>
       <c r="DY16" t="n">
-        <v>9.779999999999999</v>
+        <v>9.74</v>
       </c>
       <c r="DZ16" t="n">
         <v>5.45</v>

--- a/data/teams/leagues/Averages_Belgium_Pro_League_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Belgium_Pro_League_2025-2026.xlsx
@@ -3797,13 +3797,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C8" t="n">
         <v>14</v>
       </c>
       <c r="D8" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E8" t="n">
         <v>0.21</v>
@@ -3887,139 +3887,139 @@
         <v>1.14</v>
       </c>
       <c r="AF8" t="n">
-        <v>0.08</v>
+        <v>0.14</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.69</v>
+        <v>1.57</v>
       </c>
       <c r="AH8" t="n">
-        <v>2</v>
+        <v>1.79</v>
       </c>
       <c r="AI8" t="n">
-        <v>88.69</v>
+        <v>86.36</v>
       </c>
       <c r="AJ8" t="n">
         <v>0</v>
       </c>
       <c r="AK8" t="n">
-        <v>1.92</v>
+        <v>1.86</v>
       </c>
       <c r="AL8" t="n">
-        <v>4.15</v>
+        <v>4.36</v>
       </c>
       <c r="AM8" t="n">
-        <v>0.23</v>
+        <v>0.14</v>
       </c>
       <c r="AN8" t="n">
-        <v>42.92</v>
+        <v>42.29</v>
       </c>
       <c r="AO8" t="n">
-        <v>0.15</v>
+        <v>0.21</v>
       </c>
       <c r="AP8" t="n">
-        <v>2.15</v>
+        <v>1.93</v>
       </c>
       <c r="AQ8" t="n">
-        <v>13.15</v>
+        <v>13.14</v>
       </c>
       <c r="AR8" t="n">
-        <v>11.92</v>
+        <v>12</v>
       </c>
       <c r="AS8" t="n">
-        <v>8.85</v>
+        <v>9.789999999999999</v>
       </c>
       <c r="AT8" t="n">
-        <v>1.85</v>
+        <v>1.71</v>
       </c>
       <c r="AU8" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="AV8" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="AW8" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="AX8" t="n">
         <v>0</v>
       </c>
       <c r="AY8" t="n">
-        <v>47.08</v>
+        <v>46.5</v>
       </c>
       <c r="AZ8" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="BA8" t="n">
-        <v>13.08</v>
+        <v>12.79</v>
       </c>
       <c r="BB8" t="n">
-        <v>8.460000000000001</v>
+        <v>8.43</v>
       </c>
       <c r="BC8" t="n">
-        <v>4.62</v>
+        <v>4.36</v>
       </c>
       <c r="BD8" t="n">
-        <v>23.54</v>
+        <v>23.21</v>
       </c>
       <c r="BE8" t="n">
-        <v>1.43</v>
+        <v>1.39</v>
       </c>
       <c r="BF8" t="n">
-        <v>1.77</v>
+        <v>1.71</v>
       </c>
       <c r="BG8" t="n">
-        <v>2.67</v>
+        <v>2.61</v>
       </c>
       <c r="BH8" t="n">
-        <v>10.04</v>
+        <v>10.25</v>
       </c>
       <c r="BI8" t="n">
-        <v>2.67</v>
+        <v>2.61</v>
       </c>
       <c r="BJ8" t="n">
-        <v>0.7</v>
+        <v>0.68</v>
       </c>
       <c r="BK8" t="n">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="BL8" t="n">
-        <v>0.78</v>
+        <v>0.75</v>
       </c>
       <c r="BM8" t="n">
-        <v>0.52</v>
+        <v>0.5</v>
       </c>
       <c r="BN8" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="BO8" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="BP8" t="n">
-        <v>4.67</v>
+        <v>4.46</v>
       </c>
       <c r="BQ8" t="n">
-        <v>5.33</v>
+        <v>5.11</v>
       </c>
       <c r="BR8" t="n">
-        <v>88.89</v>
+        <v>89.29000000000001</v>
       </c>
       <c r="BS8" t="n">
-        <v>77.78</v>
+        <v>75</v>
       </c>
       <c r="BT8" t="n">
-        <v>37.04</v>
+        <v>35.71</v>
       </c>
       <c r="BU8" t="n">
-        <v>25.93</v>
+        <v>25</v>
       </c>
       <c r="BV8" t="n">
-        <v>11.11</v>
+        <v>10.71</v>
       </c>
       <c r="BW8" t="n">
-        <v>7.41</v>
+        <v>7.14</v>
       </c>
       <c r="BX8" t="n">
-        <v>37.04</v>
+        <v>35.71</v>
       </c>
       <c r="BY8" t="n">
         <v>2.4</v>
@@ -4028,31 +4028,31 @@
         <v>2.49</v>
       </c>
       <c r="CA8" t="n">
-        <v>3.77</v>
+        <v>3.76</v>
       </c>
       <c r="CB8" t="n">
-        <v>3.84</v>
+        <v>3.83</v>
       </c>
       <c r="CC8" t="n">
-        <v>3.93</v>
+        <v>3.85</v>
       </c>
       <c r="CD8" t="n">
-        <v>3.89</v>
+        <v>3.82</v>
       </c>
       <c r="CE8" t="n">
         <v>1.28</v>
       </c>
       <c r="CF8" t="n">
-        <v>2.3</v>
+        <v>2.31</v>
       </c>
       <c r="CG8" t="n">
-        <v>3.42</v>
+        <v>3.41</v>
       </c>
       <c r="CH8" t="n">
         <v>1.57</v>
       </c>
       <c r="CI8" t="n">
-        <v>2.38</v>
+        <v>2.37</v>
       </c>
       <c r="CJ8" t="n">
         <v>1.56</v>
@@ -4061,7 +4061,7 @@
         <v>1.36</v>
       </c>
       <c r="CL8" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="CM8" t="n">
         <v>2.86</v>
@@ -4076,7 +4076,7 @@
         <v>1.62</v>
       </c>
       <c r="CQ8" t="n">
-        <v>2.5</v>
+        <v>2.51</v>
       </c>
       <c r="CR8" t="n">
         <v>1.34</v>
@@ -4100,13 +4100,13 @@
         <v>1.5</v>
       </c>
       <c r="CY8" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="CZ8" t="n">
         <v>2.53</v>
       </c>
       <c r="DA8" t="n">
-        <v>2.21</v>
+        <v>2.2</v>
       </c>
       <c r="DB8" t="n">
         <v>1.19</v>
@@ -4118,46 +4118,46 @@
         <v>2.55</v>
       </c>
       <c r="DE8" t="n">
-        <v>0.15</v>
+        <v>0.18</v>
       </c>
       <c r="DF8" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="DG8" t="n">
-        <v>2.45</v>
+        <v>2.32</v>
       </c>
       <c r="DH8" t="n">
-        <v>93.44</v>
+        <v>92.11</v>
       </c>
       <c r="DI8" t="n">
         <v>-0.04</v>
       </c>
       <c r="DJ8" t="n">
-        <v>1.63</v>
+        <v>1.61</v>
       </c>
       <c r="DK8" t="n">
-        <v>4.96</v>
+        <v>5.04</v>
       </c>
       <c r="DL8" t="n">
-        <v>0.26</v>
+        <v>0.22</v>
       </c>
       <c r="DM8" t="n">
-        <v>49</v>
+        <v>48.46</v>
       </c>
       <c r="DN8" t="n">
-        <v>0.26</v>
+        <v>0.29</v>
       </c>
       <c r="DO8" t="n">
-        <v>2.52</v>
+        <v>2.4</v>
       </c>
       <c r="DP8" t="n">
-        <v>11.67</v>
+        <v>11.72</v>
       </c>
       <c r="DQ8" t="n">
-        <v>12.11</v>
+        <v>12.14</v>
       </c>
       <c r="DR8" t="n">
-        <v>8.48</v>
+        <v>8.960000000000001</v>
       </c>
       <c r="DS8" t="n">
         <v>0.14</v>
@@ -4169,28 +4169,28 @@
         <v>0</v>
       </c>
       <c r="DV8" t="n">
-        <v>48.89</v>
+        <v>48.54</v>
       </c>
       <c r="DW8" t="n">
         <v>0.11</v>
       </c>
       <c r="DX8" t="n">
-        <v>14.33</v>
+        <v>14.14</v>
       </c>
       <c r="DY8" t="n">
-        <v>9.630000000000001</v>
+        <v>9.57</v>
       </c>
       <c r="DZ8" t="n">
-        <v>4.71</v>
+        <v>4.58</v>
       </c>
       <c r="EA8" t="n">
-        <v>21.6</v>
+        <v>21.5</v>
       </c>
       <c r="EB8" t="n">
-        <v>1.58</v>
+        <v>1.55</v>
       </c>
       <c r="EC8" t="n">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
     </row>
     <row r="9">
@@ -4200,94 +4200,94 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C9" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D9" t="n">
         <v>14</v>
       </c>
       <c r="E9" t="n">
-        <v>0.23</v>
+        <v>0.21</v>
       </c>
       <c r="F9" t="n">
-        <v>2.23</v>
+        <v>2.07</v>
       </c>
       <c r="G9" t="n">
-        <v>2.38</v>
+        <v>2.14</v>
       </c>
       <c r="H9" t="n">
-        <v>81.15000000000001</v>
+        <v>83.56999999999999</v>
       </c>
       <c r="I9" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="J9" t="n">
-        <v>3</v>
+        <v>2.79</v>
       </c>
       <c r="K9" t="n">
-        <v>5</v>
+        <v>5.29</v>
       </c>
       <c r="L9" t="n">
-        <v>0.54</v>
+        <v>0.43</v>
       </c>
       <c r="M9" t="n">
-        <v>40.85</v>
+        <v>42.21</v>
       </c>
       <c r="N9" t="n">
-        <v>0.77</v>
+        <v>0.71</v>
       </c>
       <c r="O9" t="n">
-        <v>2.54</v>
+        <v>2.29</v>
       </c>
       <c r="P9" t="n">
-        <v>16.08</v>
+        <v>15.86</v>
       </c>
       <c r="Q9" t="n">
-        <v>12.31</v>
+        <v>12.5</v>
       </c>
       <c r="R9" t="n">
-        <v>7.85</v>
+        <v>7.86</v>
       </c>
       <c r="S9" t="n">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="T9" t="n">
-        <v>1.31</v>
+        <v>1.21</v>
       </c>
       <c r="U9" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="V9" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>45.38</v>
+        <v>46.5</v>
       </c>
       <c r="Y9" t="n">
         <v>0</v>
       </c>
       <c r="Z9" t="n">
-        <v>15.08</v>
+        <v>15.5</v>
       </c>
       <c r="AA9" t="n">
-        <v>10.15</v>
+        <v>10.64</v>
       </c>
       <c r="AB9" t="n">
-        <v>4.92</v>
+        <v>4.86</v>
       </c>
       <c r="AC9" t="n">
-        <v>20</v>
+        <v>20.14</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.59</v>
+        <v>1.62</v>
       </c>
       <c r="AE9" t="n">
-        <v>3</v>
+        <v>2.79</v>
       </c>
       <c r="AF9" t="n">
         <v>0.07000000000000001</v>
@@ -4371,70 +4371,70 @@
         <v>3.29</v>
       </c>
       <c r="BG9" t="n">
-        <v>2.63</v>
+        <v>2.57</v>
       </c>
       <c r="BH9" t="n">
-        <v>11</v>
+        <v>11.18</v>
       </c>
       <c r="BI9" t="n">
-        <v>2.63</v>
+        <v>2.57</v>
       </c>
       <c r="BJ9" t="n">
-        <v>0.7</v>
+        <v>0.68</v>
       </c>
       <c r="BK9" t="n">
-        <v>0.48</v>
+        <v>0.5</v>
       </c>
       <c r="BL9" t="n">
-        <v>0.85</v>
+        <v>0.82</v>
       </c>
       <c r="BM9" t="n">
-        <v>0.59</v>
+        <v>0.57</v>
       </c>
       <c r="BN9" t="n">
-        <v>1.44</v>
+        <v>1.39</v>
       </c>
       <c r="BO9" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="BP9" t="n">
-        <v>5.48</v>
+        <v>5.25</v>
       </c>
       <c r="BQ9" t="n">
-        <v>5.48</v>
+        <v>5.25</v>
       </c>
       <c r="BR9" t="n">
-        <v>92.59</v>
+        <v>92.86</v>
       </c>
       <c r="BS9" t="n">
-        <v>74.06999999999999</v>
+        <v>71.43000000000001</v>
       </c>
       <c r="BT9" t="n">
-        <v>51.85</v>
+        <v>50</v>
       </c>
       <c r="BU9" t="n">
-        <v>29.63</v>
+        <v>28.57</v>
       </c>
       <c r="BV9" t="n">
-        <v>11.11</v>
+        <v>10.71</v>
       </c>
       <c r="BW9" t="n">
-        <v>3.7</v>
+        <v>3.57</v>
       </c>
       <c r="BX9" t="n">
-        <v>55.56</v>
+        <v>53.57</v>
       </c>
       <c r="BY9" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="BZ9" t="n">
         <v>2.91</v>
-      </c>
-      <c r="BZ9" t="n">
-        <v>2.95</v>
       </c>
       <c r="CA9" t="n">
         <v>3.53</v>
       </c>
       <c r="CB9" t="n">
-        <v>3.61</v>
+        <v>3.6</v>
       </c>
       <c r="CC9" t="n">
         <v>4.43</v>
@@ -4443,49 +4443,49 @@
         <v>4.74</v>
       </c>
       <c r="CE9" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="CF9" t="n">
-        <v>2.71</v>
+        <v>2.7</v>
       </c>
       <c r="CG9" t="n">
         <v>2.97</v>
       </c>
       <c r="CH9" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="CI9" t="n">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="CJ9" t="n">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="CK9" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="CL9" t="n">
         <v>1.85</v>
       </c>
       <c r="CM9" t="n">
-        <v>2.54</v>
+        <v>2.55</v>
       </c>
       <c r="CN9" t="n">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="CO9" t="n">
         <v>1.28</v>
       </c>
       <c r="CP9" t="n">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="CQ9" t="n">
-        <v>3.27</v>
+        <v>3.25</v>
       </c>
       <c r="CR9" t="n">
         <v>1.38</v>
       </c>
       <c r="CS9" t="n">
-        <v>2.81</v>
+        <v>2.79</v>
       </c>
       <c r="CT9" t="n">
         <v>3.1</v>
@@ -4494,7 +4494,7 @@
         <v>1.46</v>
       </c>
       <c r="CV9" t="n">
-        <v>2.09</v>
+        <v>2.1</v>
       </c>
       <c r="CW9" t="n">
         <v>1.8</v>
@@ -4503,7 +4503,7 @@
         <v>1.54</v>
       </c>
       <c r="CY9" t="n">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="CZ9" t="n">
         <v>2.46</v>
@@ -4515,52 +4515,52 @@
         <v>1.3</v>
       </c>
       <c r="DC9" t="n">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="DD9" t="n">
-        <v>3.34</v>
+        <v>3.31</v>
       </c>
       <c r="DE9" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="DF9" t="n">
-        <v>2.26</v>
+        <v>2.18</v>
       </c>
       <c r="DG9" t="n">
-        <v>2.51</v>
+        <v>2.39</v>
       </c>
       <c r="DH9" t="n">
-        <v>78.73999999999999</v>
+        <v>80.04000000000001</v>
       </c>
       <c r="DI9" t="n">
         <v>0.04</v>
       </c>
       <c r="DJ9" t="n">
-        <v>3.19</v>
+        <v>3.08</v>
       </c>
       <c r="DK9" t="n">
-        <v>4.78</v>
+        <v>4.93</v>
       </c>
       <c r="DL9" t="n">
-        <v>0.52</v>
+        <v>0.46</v>
       </c>
       <c r="DM9" t="n">
-        <v>42.07</v>
+        <v>42.71</v>
       </c>
       <c r="DN9" t="n">
-        <v>0.93</v>
+        <v>0.89</v>
       </c>
       <c r="DO9" t="n">
-        <v>2.22</v>
+        <v>2.11</v>
       </c>
       <c r="DP9" t="n">
-        <v>15.89</v>
+        <v>15.78</v>
       </c>
       <c r="DQ9" t="n">
-        <v>11.56</v>
+        <v>11.68</v>
       </c>
       <c r="DR9" t="n">
-        <v>8.369999999999999</v>
+        <v>8.359999999999999</v>
       </c>
       <c r="DS9" t="n">
         <v>0.11</v>
@@ -4572,28 +4572,28 @@
         <v>0</v>
       </c>
       <c r="DV9" t="n">
-        <v>44.7</v>
+        <v>45.28</v>
       </c>
       <c r="DW9" t="n">
         <v>0.04</v>
       </c>
       <c r="DX9" t="n">
-        <v>13.52</v>
+        <v>13.78</v>
       </c>
       <c r="DY9" t="n">
-        <v>9.19</v>
+        <v>9.460000000000001</v>
       </c>
       <c r="DZ9" t="n">
-        <v>4.33</v>
+        <v>4.32</v>
       </c>
       <c r="EA9" t="n">
-        <v>19.48</v>
+        <v>19.57</v>
       </c>
       <c r="EB9" t="n">
-        <v>1.46</v>
+        <v>1.48</v>
       </c>
       <c r="EC9" t="n">
-        <v>3.15</v>
+        <v>3.04</v>
       </c>
     </row>
     <row r="10">
@@ -4603,10 +4603,10 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C10" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D10" t="n">
         <v>14</v>
@@ -4615,49 +4615,49 @@
         <v>0</v>
       </c>
       <c r="F10" t="n">
-        <v>0.77</v>
+        <v>0.79</v>
       </c>
       <c r="G10" t="n">
-        <v>3.23</v>
+        <v>3.29</v>
       </c>
       <c r="H10" t="n">
-        <v>82.69</v>
+        <v>85.29000000000001</v>
       </c>
       <c r="I10" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="J10" t="n">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="K10" t="n">
-        <v>5.69</v>
+        <v>5.79</v>
       </c>
       <c r="L10" t="n">
-        <v>0.15</v>
+        <v>0.29</v>
       </c>
       <c r="M10" t="n">
-        <v>45</v>
+        <v>45.93</v>
       </c>
       <c r="N10" t="n">
-        <v>0.77</v>
+        <v>0.71</v>
       </c>
       <c r="O10" t="n">
-        <v>2.46</v>
+        <v>2.5</v>
       </c>
       <c r="P10" t="n">
-        <v>11.23</v>
+        <v>11.07</v>
       </c>
       <c r="Q10" t="n">
-        <v>11.92</v>
+        <v>12.57</v>
       </c>
       <c r="R10" t="n">
-        <v>8.31</v>
+        <v>7.86</v>
       </c>
       <c r="S10" t="n">
-        <v>0.85</v>
+        <v>0.79</v>
       </c>
       <c r="T10" t="n">
-        <v>0.54</v>
+        <v>0.5</v>
       </c>
       <c r="U10" t="n">
         <v>0</v>
@@ -4669,28 +4669,28 @@
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>37.85</v>
+        <v>39.43</v>
       </c>
       <c r="Y10" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="Z10" t="n">
-        <v>9.92</v>
+        <v>10.71</v>
       </c>
       <c r="AA10" t="n">
-        <v>7.08</v>
+        <v>7.36</v>
       </c>
       <c r="AB10" t="n">
-        <v>2.85</v>
+        <v>3.36</v>
       </c>
       <c r="AC10" t="n">
-        <v>22</v>
+        <v>22.36</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.11</v>
+        <v>1.21</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.46</v>
+        <v>1.43</v>
       </c>
       <c r="AF10" t="n">
         <v>0.14</v>
@@ -4774,70 +4774,70 @@
         <v>2.36</v>
       </c>
       <c r="BG10" t="n">
-        <v>1.96</v>
+        <v>1.89</v>
       </c>
       <c r="BH10" t="n">
-        <v>9</v>
+        <v>9.039999999999999</v>
       </c>
       <c r="BI10" t="n">
-        <v>1.96</v>
+        <v>1.89</v>
       </c>
       <c r="BJ10" t="n">
-        <v>0.52</v>
+        <v>0.5</v>
       </c>
       <c r="BK10" t="n">
-        <v>0.37</v>
+        <v>0.36</v>
       </c>
       <c r="BL10" t="n">
-        <v>0.48</v>
+        <v>0.46</v>
       </c>
       <c r="BM10" t="n">
-        <v>0.59</v>
+        <v>0.57</v>
       </c>
       <c r="BN10" t="n">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="BO10" t="n">
-        <v>0.89</v>
+        <v>0.86</v>
       </c>
       <c r="BP10" t="n">
-        <v>3.89</v>
+        <v>3.93</v>
       </c>
       <c r="BQ10" t="n">
         <v>5.11</v>
       </c>
       <c r="BR10" t="n">
-        <v>74.06999999999999</v>
+        <v>71.43000000000001</v>
       </c>
       <c r="BS10" t="n">
-        <v>59.26</v>
+        <v>57.14</v>
       </c>
       <c r="BT10" t="n">
-        <v>40.74</v>
+        <v>39.29</v>
       </c>
       <c r="BU10" t="n">
-        <v>14.81</v>
+        <v>14.29</v>
       </c>
       <c r="BV10" t="n">
-        <v>7.41</v>
+        <v>7.14</v>
       </c>
       <c r="BW10" t="n">
         <v>0</v>
       </c>
       <c r="BX10" t="n">
-        <v>51.85</v>
+        <v>50</v>
       </c>
       <c r="BY10" t="n">
-        <v>3.33</v>
+        <v>3.24</v>
       </c>
       <c r="BZ10" t="n">
-        <v>3.41</v>
+        <v>3.32</v>
       </c>
       <c r="CA10" t="n">
-        <v>3.54</v>
+        <v>3.53</v>
       </c>
       <c r="CB10" t="n">
-        <v>3.63</v>
+        <v>3.61</v>
       </c>
       <c r="CC10" t="n">
         <v>4.69</v>
@@ -4849,16 +4849,16 @@
         <v>1.39</v>
       </c>
       <c r="CF10" t="n">
-        <v>2.81</v>
+        <v>2.82</v>
       </c>
       <c r="CG10" t="n">
-        <v>2.85</v>
+        <v>2.84</v>
       </c>
       <c r="CH10" t="n">
         <v>1.39</v>
       </c>
       <c r="CI10" t="n">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="CJ10" t="n">
         <v>1.86</v>
@@ -4867,22 +4867,22 @@
         <v>1.57</v>
       </c>
       <c r="CL10" t="n">
-        <v>2</v>
+        <v>2.01</v>
       </c>
       <c r="CM10" t="n">
-        <v>2.32</v>
+        <v>2.31</v>
       </c>
       <c r="CN10" t="n">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="CO10" t="n">
         <v>1.31</v>
       </c>
       <c r="CP10" t="n">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="CQ10" t="n">
-        <v>3.52</v>
+        <v>3.53</v>
       </c>
       <c r="CR10" t="n">
         <v>1.4</v>
@@ -4897,10 +4897,10 @@
         <v>1.43</v>
       </c>
       <c r="CV10" t="n">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="CW10" t="n">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="CX10" t="n">
         <v>1.6</v>
@@ -4915,55 +4915,55 @@
         <v>1.85</v>
       </c>
       <c r="DB10" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="DC10" t="n">
-        <v>2.07</v>
+        <v>2.08</v>
       </c>
       <c r="DD10" t="n">
-        <v>3.61</v>
+        <v>3.64</v>
       </c>
       <c r="DE10" t="n">
         <v>0.07000000000000001</v>
       </c>
       <c r="DF10" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="DG10" t="n">
-        <v>2.74</v>
+        <v>2.79</v>
       </c>
       <c r="DH10" t="n">
-        <v>82.04000000000001</v>
+        <v>83.36</v>
       </c>
       <c r="DI10" t="n">
         <v>0.11</v>
       </c>
       <c r="DJ10" t="n">
-        <v>2.08</v>
+        <v>2.04</v>
       </c>
       <c r="DK10" t="n">
-        <v>4.59</v>
+        <v>4.68</v>
       </c>
       <c r="DL10" t="n">
-        <v>0.18</v>
+        <v>0.25</v>
       </c>
       <c r="DM10" t="n">
-        <v>40.44</v>
+        <v>41.07</v>
       </c>
       <c r="DN10" t="n">
-        <v>0.74</v>
+        <v>0.71</v>
       </c>
       <c r="DO10" t="n">
-        <v>1.85</v>
+        <v>1.9</v>
       </c>
       <c r="DP10" t="n">
-        <v>11.63</v>
+        <v>11.54</v>
       </c>
       <c r="DQ10" t="n">
-        <v>12.33</v>
+        <v>12.64</v>
       </c>
       <c r="DR10" t="n">
-        <v>8.369999999999999</v>
+        <v>8.140000000000001</v>
       </c>
       <c r="DS10" t="n">
         <v>0</v>
@@ -4975,28 +4975,28 @@
         <v>0</v>
       </c>
       <c r="DV10" t="n">
-        <v>36.11</v>
+        <v>36.96</v>
       </c>
       <c r="DW10" t="n">
         <v>0.07000000000000001</v>
       </c>
       <c r="DX10" t="n">
-        <v>9.41</v>
+        <v>9.82</v>
       </c>
       <c r="DY10" t="n">
-        <v>6.82</v>
+        <v>6.97</v>
       </c>
       <c r="DZ10" t="n">
-        <v>2.6</v>
+        <v>2.86</v>
       </c>
       <c r="EA10" t="n">
-        <v>21.41</v>
+        <v>21.61</v>
       </c>
       <c r="EB10" t="n">
-        <v>1.05</v>
+        <v>1.1</v>
       </c>
       <c r="EC10" t="n">
-        <v>1.93</v>
+        <v>1.9</v>
       </c>
     </row>
     <row r="11">
@@ -5409,13 +5409,13 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C12" t="n">
         <v>14</v>
       </c>
       <c r="D12" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E12" t="n">
         <v>0.07000000000000001</v>
@@ -5502,127 +5502,127 @@
         <v>0</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.31</v>
+        <v>1.43</v>
       </c>
       <c r="AH12" t="n">
-        <v>2.31</v>
+        <v>2.21</v>
       </c>
       <c r="AI12" t="n">
-        <v>94.54000000000001</v>
+        <v>94.93000000000001</v>
       </c>
       <c r="AJ12" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="AK12" t="n">
-        <v>1.85</v>
+        <v>1.93</v>
       </c>
       <c r="AL12" t="n">
-        <v>3.38</v>
+        <v>3.36</v>
       </c>
       <c r="AM12" t="n">
-        <v>0.23</v>
+        <v>0.29</v>
       </c>
       <c r="AN12" t="n">
-        <v>37</v>
+        <v>36.79</v>
       </c>
       <c r="AO12" t="n">
-        <v>0.46</v>
+        <v>0.43</v>
       </c>
       <c r="AP12" t="n">
-        <v>1.08</v>
+        <v>1.14</v>
       </c>
       <c r="AQ12" t="n">
-        <v>13.08</v>
+        <v>13.64</v>
       </c>
       <c r="AR12" t="n">
-        <v>11.92</v>
+        <v>11.71</v>
       </c>
       <c r="AS12" t="n">
-        <v>7.77</v>
+        <v>8.07</v>
       </c>
       <c r="AT12" t="n">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AU12" t="n">
-        <v>0.77</v>
+        <v>0.71</v>
       </c>
       <c r="AV12" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="AW12" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="AX12" t="n">
         <v>0</v>
       </c>
       <c r="AY12" t="n">
-        <v>47</v>
+        <v>46.5</v>
       </c>
       <c r="AZ12" t="n">
-        <v>0.08</v>
+        <v>0.14</v>
       </c>
       <c r="BA12" t="n">
-        <v>10.15</v>
+        <v>9.789999999999999</v>
       </c>
       <c r="BB12" t="n">
-        <v>6.69</v>
+        <v>6.21</v>
       </c>
       <c r="BC12" t="n">
-        <v>3.46</v>
+        <v>3.57</v>
       </c>
       <c r="BD12" t="n">
-        <v>21.38</v>
+        <v>20.57</v>
       </c>
       <c r="BE12" t="n">
-        <v>1.16</v>
+        <v>1.14</v>
       </c>
       <c r="BF12" t="n">
-        <v>1.69</v>
+        <v>1.71</v>
       </c>
       <c r="BG12" t="n">
-        <v>2.22</v>
+        <v>2.14</v>
       </c>
       <c r="BH12" t="n">
-        <v>9.07</v>
+        <v>9.109999999999999</v>
       </c>
       <c r="BI12" t="n">
-        <v>2.22</v>
+        <v>2.14</v>
       </c>
       <c r="BJ12" t="n">
-        <v>0.67</v>
+        <v>0.64</v>
       </c>
       <c r="BK12" t="n">
-        <v>0.44</v>
+        <v>0.43</v>
       </c>
       <c r="BL12" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.54</v>
       </c>
       <c r="BM12" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.54</v>
       </c>
       <c r="BN12" t="n">
-        <v>1.11</v>
+        <v>1.07</v>
       </c>
       <c r="BO12" t="n">
-        <v>1.11</v>
+        <v>1.07</v>
       </c>
       <c r="BP12" t="n">
-        <v>3.93</v>
+        <v>3.96</v>
       </c>
       <c r="BQ12" t="n">
         <v>5.11</v>
       </c>
       <c r="BR12" t="n">
-        <v>96.3</v>
+        <v>92.86</v>
       </c>
       <c r="BS12" t="n">
-        <v>74.06999999999999</v>
+        <v>71.43000000000001</v>
       </c>
       <c r="BT12" t="n">
-        <v>37.04</v>
+        <v>35.71</v>
       </c>
       <c r="BU12" t="n">
-        <v>14.81</v>
+        <v>14.29</v>
       </c>
       <c r="BV12" t="n">
         <v>0</v>
@@ -5631,7 +5631,7 @@
         <v>0</v>
       </c>
       <c r="BX12" t="n">
-        <v>44.44</v>
+        <v>42.86</v>
       </c>
       <c r="BY12" t="n">
         <v>2.72</v>
@@ -5640,34 +5640,34 @@
         <v>2.9</v>
       </c>
       <c r="CA12" t="n">
-        <v>3.54</v>
+        <v>3.53</v>
       </c>
       <c r="CB12" t="n">
-        <v>3.66</v>
+        <v>3.65</v>
       </c>
       <c r="CC12" t="n">
-        <v>4.13</v>
+        <v>4.1</v>
       </c>
       <c r="CD12" t="n">
-        <v>4.67</v>
+        <v>4.62</v>
       </c>
       <c r="CE12" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="CF12" t="n">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="CG12" t="n">
-        <v>3.01</v>
+        <v>3</v>
       </c>
       <c r="CH12" t="n">
         <v>1.44</v>
       </c>
       <c r="CI12" t="n">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="CJ12" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="CK12" t="n">
         <v>1.5</v>
@@ -5676,19 +5676,19 @@
         <v>1.97</v>
       </c>
       <c r="CM12" t="n">
-        <v>2.44</v>
+        <v>2.43</v>
       </c>
       <c r="CN12" t="n">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="CO12" t="n">
         <v>1.26</v>
       </c>
       <c r="CP12" t="n">
-        <v>1.84</v>
+        <v>1.86</v>
       </c>
       <c r="CQ12" t="n">
-        <v>3.08</v>
+        <v>3.11</v>
       </c>
       <c r="CR12" t="n">
         <v>1.37</v>
@@ -5703,10 +5703,10 @@
         <v>1.47</v>
       </c>
       <c r="CV12" t="n">
-        <v>2.14</v>
+        <v>2.13</v>
       </c>
       <c r="CW12" t="n">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="CX12" t="n">
         <v>1.58</v>
@@ -5721,88 +5721,88 @@
         <v>1.9</v>
       </c>
       <c r="DB12" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="DC12" t="n">
-        <v>1.91</v>
+        <v>1.93</v>
       </c>
       <c r="DD12" t="n">
-        <v>3.18</v>
+        <v>3.23</v>
       </c>
       <c r="DE12" t="n">
         <v>0.04</v>
       </c>
       <c r="DF12" t="n">
-        <v>1.22</v>
+        <v>1.28</v>
       </c>
       <c r="DG12" t="n">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="DH12" t="n">
-        <v>95.41</v>
+        <v>95.56999999999999</v>
       </c>
       <c r="DI12" t="n">
         <v>0.07000000000000001</v>
       </c>
       <c r="DJ12" t="n">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="DK12" t="n">
-        <v>4</v>
+        <v>3.97</v>
       </c>
       <c r="DL12" t="n">
-        <v>0.41</v>
+        <v>0.43</v>
       </c>
       <c r="DM12" t="n">
-        <v>40</v>
+        <v>39.79</v>
       </c>
       <c r="DN12" t="n">
-        <v>0.7</v>
+        <v>0.68</v>
       </c>
       <c r="DO12" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="DP12" t="n">
-        <v>12.67</v>
+        <v>12.96</v>
       </c>
       <c r="DQ12" t="n">
-        <v>12</v>
+        <v>11.89</v>
       </c>
       <c r="DR12" t="n">
-        <v>7.63</v>
+        <v>7.79</v>
       </c>
       <c r="DS12" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
       <c r="DT12" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
       <c r="DU12" t="n">
         <v>0</v>
       </c>
       <c r="DV12" t="n">
-        <v>47.93</v>
+        <v>47.64</v>
       </c>
       <c r="DW12" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.11</v>
       </c>
       <c r="DX12" t="n">
-        <v>11.37</v>
+        <v>11.14</v>
       </c>
       <c r="DY12" t="n">
-        <v>7.11</v>
+        <v>6.86</v>
       </c>
       <c r="DZ12" t="n">
-        <v>4.26</v>
+        <v>4.28</v>
       </c>
       <c r="EA12" t="n">
-        <v>21.07</v>
+        <v>20.68</v>
       </c>
       <c r="EB12" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="EC12" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
     </row>
     <row r="13">

--- a/data/teams/leagues/Averages_Belgium_Pro_League_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Belgium_Pro_League_2025-2026.xlsx
@@ -1379,13 +1379,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C2" t="n">
         <v>14</v>
       </c>
       <c r="D2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
@@ -1469,139 +1469,139 @@
         <v>1.21</v>
       </c>
       <c r="AF2" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="AG2" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>103.07</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>3.07</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>4.86</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>50.43</v>
+      </c>
+      <c r="AO2" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AP2" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="AQ2" t="n">
+        <v>11.93</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>11.14</v>
+      </c>
+      <c r="AS2" t="n">
+        <v>7.21</v>
+      </c>
+      <c r="AT2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU2" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AV2" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="AW2" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="AX2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY2" t="n">
+        <v>45.5</v>
+      </c>
+      <c r="AZ2" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="BA2" t="n">
+        <v>13.07</v>
+      </c>
+      <c r="BB2" t="n">
+        <v>9.289999999999999</v>
+      </c>
+      <c r="BC2" t="n">
+        <v>3.79</v>
+      </c>
+      <c r="BD2" t="n">
+        <v>22</v>
+      </c>
+      <c r="BE2" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="BF2" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="BG2" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="BH2" t="n">
+        <v>10.29</v>
+      </c>
+      <c r="BI2" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="BJ2" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="BK2" t="n">
+        <v>0.96</v>
+      </c>
+      <c r="BL2" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="BM2" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="BN2" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="BO2" t="n">
         <v>1.54</v>
       </c>
-      <c r="AH2" t="n">
-        <v>2.46</v>
-      </c>
-      <c r="AI2" t="n">
-        <v>102.69</v>
-      </c>
-      <c r="AJ2" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="AK2" t="n">
-        <v>3</v>
-      </c>
-      <c r="AL2" t="n">
-        <v>4.85</v>
-      </c>
-      <c r="AM2" t="n">
-        <v>0.62</v>
-      </c>
-      <c r="AN2" t="n">
-        <v>49.46</v>
-      </c>
-      <c r="AO2" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="AP2" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AQ2" t="n">
-        <v>12.23</v>
-      </c>
-      <c r="AR2" t="n">
-        <v>11.38</v>
-      </c>
-      <c r="AS2" t="n">
-        <v>7.54</v>
-      </c>
-      <c r="AT2" t="n">
-        <v>0.92</v>
-      </c>
-      <c r="AU2" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="AV2" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="AW2" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="AX2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY2" t="n">
-        <v>46</v>
-      </c>
-      <c r="AZ2" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="BA2" t="n">
-        <v>12.69</v>
-      </c>
-      <c r="BB2" t="n">
-        <v>9.08</v>
-      </c>
-      <c r="BC2" t="n">
-        <v>3.62</v>
-      </c>
-      <c r="BD2" t="n">
-        <v>21.85</v>
-      </c>
-      <c r="BE2" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="BF2" t="n">
-        <v>2.69</v>
-      </c>
-      <c r="BG2" t="n">
-        <v>2.74</v>
-      </c>
-      <c r="BH2" t="n">
-        <v>10.22</v>
-      </c>
-      <c r="BI2" t="n">
-        <v>2.74</v>
-      </c>
-      <c r="BJ2" t="n">
-        <v>0.5600000000000001</v>
-      </c>
-      <c r="BK2" t="n">
-        <v>1</v>
-      </c>
-      <c r="BL2" t="n">
-        <v>0.5600000000000001</v>
-      </c>
-      <c r="BM2" t="n">
-        <v>0.63</v>
-      </c>
-      <c r="BN2" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="BO2" t="n">
-        <v>1.56</v>
-      </c>
       <c r="BP2" t="n">
-        <v>4.19</v>
+        <v>4.21</v>
       </c>
       <c r="BQ2" t="n">
-        <v>5.44</v>
+        <v>5.5</v>
       </c>
       <c r="BR2" t="n">
-        <v>88.89</v>
+        <v>89.29000000000001</v>
       </c>
       <c r="BS2" t="n">
-        <v>85.19</v>
+        <v>85.70999999999999</v>
       </c>
       <c r="BT2" t="n">
-        <v>44.44</v>
+        <v>46.43</v>
       </c>
       <c r="BU2" t="n">
-        <v>25.93</v>
+        <v>25</v>
       </c>
       <c r="BV2" t="n">
-        <v>18.52</v>
+        <v>17.86</v>
       </c>
       <c r="BW2" t="n">
-        <v>7.41</v>
+        <v>7.14</v>
       </c>
       <c r="BX2" t="n">
-        <v>59.26</v>
+        <v>60.71</v>
       </c>
       <c r="BY2" t="n">
         <v>2.45</v>
@@ -1610,31 +1610,31 @@
         <v>2.59</v>
       </c>
       <c r="CA2" t="n">
-        <v>3.56</v>
+        <v>3.57</v>
       </c>
       <c r="CB2" t="n">
-        <v>3.68</v>
+        <v>3.7</v>
       </c>
       <c r="CC2" t="n">
-        <v>3.38</v>
+        <v>3.39</v>
       </c>
       <c r="CD2" t="n">
-        <v>3.52</v>
+        <v>3.61</v>
       </c>
       <c r="CE2" t="n">
         <v>1.32</v>
       </c>
       <c r="CF2" t="n">
-        <v>2.52</v>
+        <v>2.51</v>
       </c>
       <c r="CG2" t="n">
-        <v>3.14</v>
+        <v>3.15</v>
       </c>
       <c r="CH2" t="n">
         <v>1.48</v>
       </c>
       <c r="CI2" t="n">
-        <v>2.17</v>
+        <v>2.18</v>
       </c>
       <c r="CJ2" t="n">
         <v>1.65</v>
@@ -1643,7 +1643,7 @@
         <v>1.44</v>
       </c>
       <c r="CL2" t="n">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="CM2" t="n">
         <v>2.59</v>
@@ -1655,10 +1655,10 @@
         <v>1.22</v>
       </c>
       <c r="CP2" t="n">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="CQ2" t="n">
-        <v>2.87</v>
+        <v>2.85</v>
       </c>
       <c r="CR2" t="n">
         <v>1.36</v>
@@ -1673,7 +1673,7 @@
         <v>1.51</v>
       </c>
       <c r="CV2" t="n">
-        <v>2.29</v>
+        <v>2.3</v>
       </c>
       <c r="CW2" t="n">
         <v>1.67</v>
@@ -1682,97 +1682,97 @@
         <v>1.5</v>
       </c>
       <c r="CY2" t="n">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="CZ2" t="n">
-        <v>2.54</v>
+        <v>2.53</v>
       </c>
       <c r="DA2" t="n">
-        <v>2.08</v>
+        <v>2.09</v>
       </c>
       <c r="DB2" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="DC2" t="n">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="DD2" t="n">
-        <v>2.93</v>
+        <v>2.91</v>
       </c>
       <c r="DE2" t="n">
         <v>0.07000000000000001</v>
       </c>
       <c r="DF2" t="n">
-        <v>1.19</v>
+        <v>1.25</v>
       </c>
       <c r="DG2" t="n">
-        <v>2.37</v>
+        <v>2.36</v>
       </c>
       <c r="DH2" t="n">
-        <v>105.48</v>
+        <v>105.57</v>
       </c>
       <c r="DI2" t="n">
         <v>0.11</v>
       </c>
       <c r="DJ2" t="n">
-        <v>2.19</v>
+        <v>2.25</v>
       </c>
       <c r="DK2" t="n">
-        <v>4.82</v>
+        <v>4.83</v>
       </c>
       <c r="DL2" t="n">
-        <v>0.45</v>
+        <v>0.43</v>
       </c>
       <c r="DM2" t="n">
-        <v>49.78</v>
+        <v>50.25</v>
       </c>
       <c r="DN2" t="n">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="DO2" t="n">
-        <v>2.03</v>
+        <v>2.07</v>
       </c>
       <c r="DP2" t="n">
-        <v>10.63</v>
+        <v>10.54</v>
       </c>
       <c r="DQ2" t="n">
-        <v>12.41</v>
+        <v>12.25</v>
       </c>
       <c r="DR2" t="n">
-        <v>6.96</v>
+        <v>6.82</v>
       </c>
       <c r="DS2" t="n">
-        <v>0.3</v>
+        <v>0.28</v>
       </c>
       <c r="DT2" t="n">
-        <v>0.3</v>
+        <v>0.28</v>
       </c>
       <c r="DU2" t="n">
         <v>0</v>
       </c>
       <c r="DV2" t="n">
-        <v>47.33</v>
+        <v>47.04</v>
       </c>
       <c r="DW2" t="n">
         <v>0.14</v>
       </c>
       <c r="DX2" t="n">
-        <v>13.7</v>
+        <v>13.86</v>
       </c>
       <c r="DY2" t="n">
-        <v>9.41</v>
+        <v>9.5</v>
       </c>
       <c r="DZ2" t="n">
-        <v>4.3</v>
+        <v>4.36</v>
       </c>
       <c r="EA2" t="n">
-        <v>22.63</v>
+        <v>22.68</v>
       </c>
       <c r="EB2" t="n">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="EC2" t="n">
-        <v>1.92</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3">
@@ -1782,61 +1782,61 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C3" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D3" t="n">
         <v>14</v>
       </c>
       <c r="E3" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="F3" t="n">
-        <v>0.92</v>
+        <v>0.86</v>
       </c>
       <c r="G3" t="n">
-        <v>3.92</v>
+        <v>4.14</v>
       </c>
       <c r="H3" t="n">
-        <v>114.23</v>
+        <v>115.57</v>
       </c>
       <c r="I3" t="n">
         <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="K3" t="n">
-        <v>7.23</v>
+        <v>7.5</v>
       </c>
       <c r="L3" t="n">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="M3" t="n">
-        <v>66</v>
+        <v>66.70999999999999</v>
       </c>
       <c r="N3" t="n">
-        <v>0.23</v>
+        <v>0.29</v>
       </c>
       <c r="O3" t="n">
-        <v>3.31</v>
+        <v>3.36</v>
       </c>
       <c r="P3" t="n">
-        <v>9.380000000000001</v>
+        <v>9.210000000000001</v>
       </c>
       <c r="Q3" t="n">
-        <v>12.08</v>
+        <v>12.21</v>
       </c>
       <c r="R3" t="n">
-        <v>6.38</v>
+        <v>6.36</v>
       </c>
       <c r="S3" t="n">
-        <v>1.23</v>
+        <v>1.29</v>
       </c>
       <c r="T3" t="n">
-        <v>2.15</v>
+        <v>2.14</v>
       </c>
       <c r="U3" t="n">
         <v>0</v>
@@ -1848,25 +1848,25 @@
         <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>65.54000000000001</v>
+        <v>65.79000000000001</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="Z3" t="n">
-        <v>18.08</v>
+        <v>18.5</v>
       </c>
       <c r="AA3" t="n">
-        <v>12.08</v>
+        <v>12.29</v>
       </c>
       <c r="AB3" t="n">
-        <v>6</v>
+        <v>6.21</v>
       </c>
       <c r="AC3" t="n">
-        <v>22.92</v>
+        <v>23</v>
       </c>
       <c r="AD3" t="n">
-        <v>2.04</v>
+        <v>2.08</v>
       </c>
       <c r="AE3" t="n">
         <v>1</v>
@@ -1953,58 +1953,58 @@
         <v>1.64</v>
       </c>
       <c r="BG3" t="n">
-        <v>3.07</v>
+        <v>3.11</v>
       </c>
       <c r="BH3" t="n">
-        <v>10.59</v>
+        <v>10.68</v>
       </c>
       <c r="BI3" t="n">
-        <v>3.07</v>
+        <v>3.11</v>
       </c>
       <c r="BJ3" t="n">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="BK3" t="n">
-        <v>0.44</v>
+        <v>0.46</v>
       </c>
       <c r="BL3" t="n">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="BM3" t="n">
         <v>1</v>
       </c>
       <c r="BN3" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="BO3" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="BP3" t="n">
-        <v>4.78</v>
+        <v>4.79</v>
       </c>
       <c r="BQ3" t="n">
-        <v>5.81</v>
+        <v>5.89</v>
       </c>
       <c r="BR3" t="n">
         <v>100</v>
       </c>
       <c r="BS3" t="n">
-        <v>66.67</v>
+        <v>67.86</v>
       </c>
       <c r="BT3" t="n">
-        <v>55.56</v>
+        <v>57.14</v>
       </c>
       <c r="BU3" t="n">
-        <v>22.22</v>
+        <v>25</v>
       </c>
       <c r="BV3" t="n">
-        <v>22.22</v>
+        <v>21.43</v>
       </c>
       <c r="BW3" t="n">
-        <v>14.81</v>
+        <v>14.29</v>
       </c>
       <c r="BX3" t="n">
-        <v>55.56</v>
+        <v>57.14</v>
       </c>
       <c r="BY3" t="n">
         <v>1.44</v>
@@ -2013,10 +2013,10 @@
         <v>1.46</v>
       </c>
       <c r="CA3" t="n">
-        <v>4.44</v>
+        <v>4.43</v>
       </c>
       <c r="CB3" t="n">
-        <v>4.74</v>
+        <v>4.75</v>
       </c>
       <c r="CC3" t="n">
         <v>1.86</v>
@@ -2031,28 +2031,28 @@
         <v>2.26</v>
       </c>
       <c r="CG3" t="n">
-        <v>3.5</v>
+        <v>3.51</v>
       </c>
       <c r="CH3" t="n">
         <v>1.6</v>
       </c>
       <c r="CI3" t="n">
-        <v>2.11</v>
+        <v>2.12</v>
       </c>
       <c r="CJ3" t="n">
         <v>1.68</v>
       </c>
       <c r="CK3" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="CL3" t="n">
         <v>1.93</v>
       </c>
       <c r="CM3" t="n">
-        <v>2.51</v>
+        <v>2.52</v>
       </c>
       <c r="CN3" t="n">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="CO3" t="n">
         <v>1.17</v>
@@ -2061,7 +2061,7 @@
         <v>1.57</v>
       </c>
       <c r="CQ3" t="n">
-        <v>2.42</v>
+        <v>2.41</v>
       </c>
       <c r="CR3" t="n">
         <v>1.33</v>
@@ -2082,13 +2082,13 @@
         <v>1.7</v>
       </c>
       <c r="CX3" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="CY3" t="n">
         <v>1.8</v>
       </c>
       <c r="CZ3" t="n">
-        <v>2.48</v>
+        <v>2.49</v>
       </c>
       <c r="DA3" t="n">
         <v>2.03</v>
@@ -2100,49 +2100,49 @@
         <v>1.6</v>
       </c>
       <c r="DD3" t="n">
-        <v>2.49</v>
+        <v>2.48</v>
       </c>
       <c r="DE3" t="n">
         <v>0.07000000000000001</v>
       </c>
       <c r="DF3" t="n">
-        <v>1.07</v>
+        <v>1.03</v>
       </c>
       <c r="DG3" t="n">
-        <v>3.67</v>
+        <v>3.78</v>
       </c>
       <c r="DH3" t="n">
-        <v>109.41</v>
+        <v>110.25</v>
       </c>
       <c r="DI3" t="n">
         <v>0</v>
       </c>
       <c r="DJ3" t="n">
-        <v>1.48</v>
+        <v>1.46</v>
       </c>
       <c r="DK3" t="n">
-        <v>6.52</v>
+        <v>6.68</v>
       </c>
       <c r="DL3" t="n">
-        <v>0.59</v>
+        <v>0.61</v>
       </c>
       <c r="DM3" t="n">
-        <v>61.41</v>
+        <v>61.92</v>
       </c>
       <c r="DN3" t="n">
-        <v>0.33</v>
+        <v>0.36</v>
       </c>
       <c r="DO3" t="n">
-        <v>2.85</v>
+        <v>2.9</v>
       </c>
       <c r="DP3" t="n">
-        <v>9.550000000000001</v>
+        <v>9.460000000000001</v>
       </c>
       <c r="DQ3" t="n">
-        <v>11.52</v>
+        <v>11.6</v>
       </c>
       <c r="DR3" t="n">
-        <v>7.22</v>
+        <v>7.18</v>
       </c>
       <c r="DS3" t="n">
         <v>0.04</v>
@@ -2154,28 +2154,28 @@
         <v>0</v>
       </c>
       <c r="DV3" t="n">
-        <v>62.85</v>
+        <v>63.08</v>
       </c>
       <c r="DW3" t="n">
         <v>0.07000000000000001</v>
       </c>
       <c r="DX3" t="n">
-        <v>16.26</v>
+        <v>16.54</v>
       </c>
       <c r="DY3" t="n">
-        <v>10.74</v>
+        <v>10.9</v>
       </c>
       <c r="DZ3" t="n">
-        <v>5.52</v>
+        <v>5.64</v>
       </c>
       <c r="EA3" t="n">
-        <v>20.74</v>
+        <v>20.86</v>
       </c>
       <c r="EB3" t="n">
-        <v>1.86</v>
+        <v>1.88</v>
       </c>
       <c r="EC3" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
     </row>
     <row r="4">
@@ -2185,94 +2185,94 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C4" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D4" t="n">
         <v>14</v>
       </c>
       <c r="E4" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="F4" t="n">
-        <v>1.46</v>
+        <v>1.43</v>
       </c>
       <c r="G4" t="n">
-        <v>1.62</v>
+        <v>1.71</v>
       </c>
       <c r="H4" t="n">
-        <v>88.23</v>
+        <v>87.14</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.15</v>
+        <v>-0.14</v>
       </c>
       <c r="J4" t="n">
-        <v>1.92</v>
+        <v>1.86</v>
       </c>
       <c r="K4" t="n">
-        <v>3.46</v>
+        <v>3.57</v>
       </c>
       <c r="L4" t="n">
-        <v>0.08</v>
+        <v>0.14</v>
       </c>
       <c r="M4" t="n">
-        <v>47.23</v>
+        <v>46.36</v>
       </c>
       <c r="N4" t="n">
-        <v>0.46</v>
+        <v>0.43</v>
       </c>
       <c r="O4" t="n">
-        <v>1.23</v>
+        <v>1.29</v>
       </c>
       <c r="P4" t="n">
-        <v>10.85</v>
+        <v>10.71</v>
       </c>
       <c r="Q4" t="n">
         <v>11</v>
       </c>
       <c r="R4" t="n">
-        <v>10.15</v>
+        <v>10.43</v>
       </c>
       <c r="S4" t="n">
-        <v>1.77</v>
+        <v>1.79</v>
       </c>
       <c r="T4" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.79</v>
       </c>
       <c r="U4" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="V4" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="W4" t="n">
         <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>49.15</v>
+        <v>48.71</v>
       </c>
       <c r="Y4" t="n">
         <v>0</v>
       </c>
       <c r="Z4" t="n">
-        <v>10.62</v>
+        <v>10.93</v>
       </c>
       <c r="AA4" t="n">
-        <v>7.23</v>
+        <v>7.43</v>
       </c>
       <c r="AB4" t="n">
-        <v>3.38</v>
+        <v>3.5</v>
       </c>
       <c r="AC4" t="n">
-        <v>22.46</v>
+        <v>22.07</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.92</v>
+        <v>1.86</v>
       </c>
       <c r="AF4" t="n">
         <v>0.21</v>
@@ -2356,70 +2356,70 @@
         <v>2.21</v>
       </c>
       <c r="BG4" t="n">
-        <v>2.41</v>
+        <v>2.46</v>
       </c>
       <c r="BH4" t="n">
-        <v>9.039999999999999</v>
+        <v>9.359999999999999</v>
       </c>
       <c r="BI4" t="n">
-        <v>2.41</v>
+        <v>2.46</v>
       </c>
       <c r="BJ4" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.61</v>
       </c>
       <c r="BK4" t="n">
-        <v>0.41</v>
+        <v>0.43</v>
       </c>
       <c r="BL4" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.54</v>
       </c>
       <c r="BM4" t="n">
         <v>0.89</v>
       </c>
       <c r="BN4" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="BO4" t="n">
-        <v>0.96</v>
+        <v>1.04</v>
       </c>
       <c r="BP4" t="n">
-        <v>3.74</v>
+        <v>3.79</v>
       </c>
       <c r="BQ4" t="n">
-        <v>4.26</v>
+        <v>4.54</v>
       </c>
       <c r="BR4" t="n">
-        <v>85.19</v>
+        <v>85.70999999999999</v>
       </c>
       <c r="BS4" t="n">
-        <v>66.67</v>
+        <v>67.86</v>
       </c>
       <c r="BT4" t="n">
-        <v>48.15</v>
+        <v>50</v>
       </c>
       <c r="BU4" t="n">
-        <v>25.93</v>
+        <v>28.57</v>
       </c>
       <c r="BV4" t="n">
-        <v>11.11</v>
+        <v>10.71</v>
       </c>
       <c r="BW4" t="n">
-        <v>3.7</v>
+        <v>3.57</v>
       </c>
       <c r="BX4" t="n">
-        <v>55.56</v>
+        <v>57.14</v>
       </c>
       <c r="BY4" t="n">
-        <v>3.42</v>
+        <v>3.4</v>
       </c>
       <c r="BZ4" t="n">
-        <v>3.55</v>
+        <v>3.59</v>
       </c>
       <c r="CA4" t="n">
-        <v>3.66</v>
+        <v>3.65</v>
       </c>
       <c r="CB4" t="n">
-        <v>3.78</v>
+        <v>3.77</v>
       </c>
       <c r="CC4" t="n">
         <v>4.57</v>
@@ -2434,7 +2434,7 @@
         <v>2.62</v>
       </c>
       <c r="CG4" t="n">
-        <v>3.06</v>
+        <v>3.05</v>
       </c>
       <c r="CH4" t="n">
         <v>1.45</v>
@@ -2449,7 +2449,7 @@
         <v>1.55</v>
       </c>
       <c r="CL4" t="n">
-        <v>2.01</v>
+        <v>2</v>
       </c>
       <c r="CM4" t="n">
         <v>2.34</v>
@@ -2467,22 +2467,22 @@
         <v>3.1</v>
       </c>
       <c r="CR4" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="CS4" t="n">
-        <v>2.76</v>
+        <v>2.77</v>
       </c>
       <c r="CT4" t="n">
         <v>3.08</v>
       </c>
       <c r="CU4" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="CV4" t="n">
         <v>2.12</v>
       </c>
       <c r="CW4" t="n">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="CX4" t="n">
         <v>1.59</v>
@@ -2500,52 +2500,52 @@
         <v>1.28</v>
       </c>
       <c r="DC4" t="n">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="DD4" t="n">
-        <v>3.2</v>
+        <v>3.21</v>
       </c>
       <c r="DE4" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="DF4" t="n">
-        <v>1.48</v>
+        <v>1.46</v>
       </c>
       <c r="DG4" t="n">
-        <v>1.56</v>
+        <v>1.6</v>
       </c>
       <c r="DH4" t="n">
-        <v>88.11</v>
+        <v>87.56999999999999</v>
       </c>
       <c r="DI4" t="n">
-        <v>0.04</v>
+        <v>0.03</v>
       </c>
       <c r="DJ4" t="n">
-        <v>2.29</v>
+        <v>2.25</v>
       </c>
       <c r="DK4" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="DL4" t="n">
-        <v>0.04</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="DM4" t="n">
-        <v>43.44</v>
+        <v>43.14</v>
       </c>
       <c r="DN4" t="n">
-        <v>0.74</v>
+        <v>0.72</v>
       </c>
       <c r="DO4" t="n">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="DP4" t="n">
-        <v>11.15</v>
+        <v>11.07</v>
       </c>
       <c r="DQ4" t="n">
         <v>11.22</v>
       </c>
       <c r="DR4" t="n">
-        <v>10.26</v>
+        <v>10.39</v>
       </c>
       <c r="DS4" t="n">
         <v>0.11</v>
@@ -2557,28 +2557,28 @@
         <v>0</v>
       </c>
       <c r="DV4" t="n">
-        <v>47.18</v>
+        <v>47.04</v>
       </c>
       <c r="DW4" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="DX4" t="n">
-        <v>10.82</v>
+        <v>10.96</v>
       </c>
       <c r="DY4" t="n">
-        <v>6.89</v>
+        <v>7</v>
       </c>
       <c r="DZ4" t="n">
-        <v>3.92</v>
+        <v>3.96</v>
       </c>
       <c r="EA4" t="n">
-        <v>22.19</v>
+        <v>22</v>
       </c>
       <c r="EB4" t="n">
         <v>1.28</v>
       </c>
       <c r="EC4" t="n">
-        <v>2.07</v>
+        <v>2.04</v>
       </c>
     </row>
     <row r="5">
@@ -2588,94 +2588,94 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C5" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D5" t="n">
         <v>14</v>
       </c>
       <c r="E5" t="n">
-        <v>0.23</v>
+        <v>0.21</v>
       </c>
       <c r="F5" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="G5" t="n">
-        <v>2.85</v>
+        <v>2.64</v>
       </c>
       <c r="H5" t="n">
-        <v>103.54</v>
+        <v>103.14</v>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="J5" t="n">
-        <v>1.77</v>
+        <v>1.79</v>
       </c>
       <c r="K5" t="n">
-        <v>5</v>
+        <v>4.86</v>
       </c>
       <c r="L5" t="n">
-        <v>0.38</v>
+        <v>0.43</v>
       </c>
       <c r="M5" t="n">
-        <v>52.77</v>
+        <v>52.14</v>
       </c>
       <c r="N5" t="n">
-        <v>0.46</v>
+        <v>0.5</v>
       </c>
       <c r="O5" t="n">
-        <v>2.15</v>
+        <v>2.21</v>
       </c>
       <c r="P5" t="n">
-        <v>10.77</v>
+        <v>10.64</v>
       </c>
       <c r="Q5" t="n">
-        <v>10.85</v>
+        <v>11.36</v>
       </c>
       <c r="R5" t="n">
-        <v>8.380000000000001</v>
+        <v>8.140000000000001</v>
       </c>
       <c r="S5" t="n">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="T5" t="n">
-        <v>1.69</v>
+        <v>1.79</v>
       </c>
       <c r="U5" t="n">
-        <v>0.08</v>
+        <v>0.14</v>
       </c>
       <c r="V5" t="n">
-        <v>0.08</v>
+        <v>0.14</v>
       </c>
       <c r="W5" t="n">
         <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>54.54</v>
+        <v>53.93</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="Z5" t="n">
-        <v>15.38</v>
+        <v>15.21</v>
       </c>
       <c r="AA5" t="n">
-        <v>11.38</v>
+        <v>11.14</v>
       </c>
       <c r="AB5" t="n">
-        <v>4</v>
+        <v>4.07</v>
       </c>
       <c r="AC5" t="n">
-        <v>20.08</v>
+        <v>19.79</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.46</v>
+        <v>1.5</v>
       </c>
       <c r="AF5" t="n">
         <v>0.07000000000000001</v>
@@ -2759,64 +2759,64 @@
         <v>1.57</v>
       </c>
       <c r="BG5" t="n">
-        <v>3.04</v>
+        <v>3.07</v>
       </c>
       <c r="BH5" t="n">
-        <v>10.74</v>
+        <v>10.64</v>
       </c>
       <c r="BI5" t="n">
-        <v>3.04</v>
+        <v>3.07</v>
       </c>
       <c r="BJ5" t="n">
-        <v>0.74</v>
+        <v>0.79</v>
       </c>
       <c r="BK5" t="n">
-        <v>0.59</v>
+        <v>0.57</v>
       </c>
       <c r="BL5" t="n">
         <v>1</v>
       </c>
       <c r="BM5" t="n">
-        <v>0.7</v>
+        <v>0.71</v>
       </c>
       <c r="BN5" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="BO5" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="BP5" t="n">
-        <v>4.37</v>
+        <v>4.39</v>
       </c>
       <c r="BQ5" t="n">
-        <v>6.37</v>
+        <v>6.25</v>
       </c>
       <c r="BR5" t="n">
-        <v>96.3</v>
+        <v>96.43000000000001</v>
       </c>
       <c r="BS5" t="n">
-        <v>85.19</v>
+        <v>85.70999999999999</v>
       </c>
       <c r="BT5" t="n">
-        <v>59.26</v>
+        <v>60.71</v>
       </c>
       <c r="BU5" t="n">
-        <v>37.04</v>
+        <v>39.29</v>
       </c>
       <c r="BV5" t="n">
-        <v>18.52</v>
+        <v>17.86</v>
       </c>
       <c r="BW5" t="n">
-        <v>7.41</v>
+        <v>7.14</v>
       </c>
       <c r="BX5" t="n">
-        <v>59.26</v>
+        <v>60.71</v>
       </c>
       <c r="BY5" t="n">
-        <v>2.61</v>
+        <v>2.57</v>
       </c>
       <c r="BZ5" t="n">
-        <v>2.72</v>
+        <v>2.68</v>
       </c>
       <c r="CA5" t="n">
         <v>3.59</v>
@@ -2852,10 +2852,10 @@
         <v>1.46</v>
       </c>
       <c r="CL5" t="n">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="CM5" t="n">
-        <v>2.52</v>
+        <v>2.53</v>
       </c>
       <c r="CN5" t="n">
         <v>1.98</v>
@@ -2864,7 +2864,7 @@
         <v>1.22</v>
       </c>
       <c r="CP5" t="n">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="CQ5" t="n">
         <v>2.77</v>
@@ -2882,7 +2882,7 @@
         <v>1.54</v>
       </c>
       <c r="CV5" t="n">
-        <v>2.31</v>
+        <v>2.32</v>
       </c>
       <c r="CW5" t="n">
         <v>1.67</v>
@@ -2906,82 +2906,82 @@
         <v>1.78</v>
       </c>
       <c r="DD5" t="n">
-        <v>2.9</v>
+        <v>2.89</v>
       </c>
       <c r="DE5" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="DF5" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="DG5" t="n">
-        <v>2.82</v>
+        <v>2.72</v>
       </c>
       <c r="DH5" t="n">
-        <v>95.67</v>
+        <v>95.75</v>
       </c>
       <c r="DI5" t="n">
-        <v>-0.04</v>
+        <v>0</v>
       </c>
       <c r="DJ5" t="n">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="DK5" t="n">
-        <v>4.93</v>
+        <v>4.86</v>
       </c>
       <c r="DL5" t="n">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="DM5" t="n">
-        <v>47.19</v>
+        <v>47.07</v>
       </c>
       <c r="DN5" t="n">
-        <v>0.55</v>
+        <v>0.57</v>
       </c>
       <c r="DO5" t="n">
-        <v>2.11</v>
+        <v>2.14</v>
       </c>
       <c r="DP5" t="n">
-        <v>10.67</v>
+        <v>10.61</v>
       </c>
       <c r="DQ5" t="n">
-        <v>10.82</v>
+        <v>11.08</v>
       </c>
       <c r="DR5" t="n">
-        <v>9.67</v>
+        <v>9.5</v>
       </c>
       <c r="DS5" t="n">
-        <v>0.11</v>
+        <v>0.14</v>
       </c>
       <c r="DT5" t="n">
-        <v>0.11</v>
+        <v>0.14</v>
       </c>
       <c r="DU5" t="n">
         <v>0</v>
       </c>
       <c r="DV5" t="n">
-        <v>51.22</v>
+        <v>51.04</v>
       </c>
       <c r="DW5" t="n">
         <v>0.14</v>
       </c>
       <c r="DX5" t="n">
-        <v>13.37</v>
+        <v>13.36</v>
       </c>
       <c r="DY5" t="n">
-        <v>9</v>
+        <v>8.960000000000001</v>
       </c>
       <c r="DZ5" t="n">
-        <v>4.37</v>
+        <v>4.39</v>
       </c>
       <c r="EA5" t="n">
-        <v>19.15</v>
+        <v>19.04</v>
       </c>
       <c r="EB5" t="n">
         <v>1.49</v>
       </c>
       <c r="EC5" t="n">
-        <v>1.52</v>
+        <v>1.54</v>
       </c>
     </row>
     <row r="6">
@@ -2991,13 +2991,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C6" t="n">
         <v>14</v>
       </c>
       <c r="D6" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E6" t="n">
         <v>0.07000000000000001</v>
@@ -3081,139 +3081,139 @@
         <v>1.07</v>
       </c>
       <c r="AF6" t="n">
-        <v>0.23</v>
+        <v>0.21</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="AH6" t="n">
-        <v>2.54</v>
+        <v>2.36</v>
       </c>
       <c r="AI6" t="n">
-        <v>98.08</v>
+        <v>99.20999999999999</v>
       </c>
       <c r="AJ6" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="AK6" t="n">
-        <v>1.77</v>
+        <v>1.79</v>
       </c>
       <c r="AL6" t="n">
-        <v>4.46</v>
+        <v>4.21</v>
       </c>
       <c r="AM6" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.64</v>
       </c>
       <c r="AN6" t="n">
-        <v>47.85</v>
+        <v>46.43</v>
       </c>
       <c r="AO6" t="n">
-        <v>0.46</v>
+        <v>0.5</v>
       </c>
       <c r="AP6" t="n">
-        <v>1.92</v>
+        <v>1.86</v>
       </c>
       <c r="AQ6" t="n">
-        <v>10</v>
+        <v>9.93</v>
       </c>
       <c r="AR6" t="n">
-        <v>11.77</v>
+        <v>11.5</v>
       </c>
       <c r="AS6" t="n">
-        <v>8.08</v>
+        <v>8.289999999999999</v>
       </c>
       <c r="AT6" t="n">
-        <v>1.54</v>
+        <v>1.57</v>
       </c>
       <c r="AU6" t="n">
-        <v>1.46</v>
+        <v>1.43</v>
       </c>
       <c r="AV6" t="n">
-        <v>0.08</v>
+        <v>0.14</v>
       </c>
       <c r="AW6" t="n">
-        <v>0.08</v>
+        <v>0.14</v>
       </c>
       <c r="AX6" t="n">
         <v>0</v>
       </c>
       <c r="AY6" t="n">
-        <v>59.92</v>
+        <v>59.71</v>
       </c>
       <c r="AZ6" t="n">
         <v>0</v>
       </c>
       <c r="BA6" t="n">
-        <v>13.54</v>
+        <v>12.93</v>
       </c>
       <c r="BB6" t="n">
-        <v>8</v>
+        <v>7.57</v>
       </c>
       <c r="BC6" t="n">
-        <v>5.54</v>
+        <v>5.36</v>
       </c>
       <c r="BD6" t="n">
-        <v>18.69</v>
+        <v>18.79</v>
       </c>
       <c r="BE6" t="n">
-        <v>1.59</v>
+        <v>1.53</v>
       </c>
       <c r="BF6" t="n">
-        <v>1.77</v>
+        <v>1.79</v>
       </c>
       <c r="BG6" t="n">
         <v>2.93</v>
       </c>
       <c r="BH6" t="n">
-        <v>10.07</v>
+        <v>9.93</v>
       </c>
       <c r="BI6" t="n">
         <v>2.93</v>
       </c>
       <c r="BJ6" t="n">
-        <v>0.59</v>
+        <v>0.61</v>
       </c>
       <c r="BK6" t="n">
-        <v>0.89</v>
+        <v>0.86</v>
       </c>
       <c r="BL6" t="n">
         <v>0.89</v>
       </c>
       <c r="BM6" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.57</v>
       </c>
       <c r="BN6" t="n">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="BO6" t="n">
-        <v>1.48</v>
+        <v>1.46</v>
       </c>
       <c r="BP6" t="n">
-        <v>4.67</v>
+        <v>4.64</v>
       </c>
       <c r="BQ6" t="n">
-        <v>5.37</v>
+        <v>5.25</v>
       </c>
       <c r="BR6" t="n">
         <v>100</v>
       </c>
       <c r="BS6" t="n">
-        <v>88.89</v>
+        <v>89.29000000000001</v>
       </c>
       <c r="BT6" t="n">
-        <v>62.96</v>
+        <v>64.29000000000001</v>
       </c>
       <c r="BU6" t="n">
-        <v>18.52</v>
+        <v>17.86</v>
       </c>
       <c r="BV6" t="n">
-        <v>11.11</v>
+        <v>10.71</v>
       </c>
       <c r="BW6" t="n">
-        <v>3.7</v>
+        <v>3.57</v>
       </c>
       <c r="BX6" t="n">
-        <v>74.06999999999999</v>
+        <v>75</v>
       </c>
       <c r="BY6" t="n">
         <v>1.8</v>
@@ -3222,40 +3222,40 @@
         <v>1.87</v>
       </c>
       <c r="CA6" t="n">
-        <v>3.82</v>
+        <v>3.83</v>
       </c>
       <c r="CB6" t="n">
-        <v>3.93</v>
+        <v>3.92</v>
       </c>
       <c r="CC6" t="n">
-        <v>2.37</v>
+        <v>2.54</v>
       </c>
       <c r="CD6" t="n">
-        <v>2.4</v>
+        <v>2.64</v>
       </c>
       <c r="CE6" t="n">
         <v>1.3</v>
       </c>
       <c r="CF6" t="n">
-        <v>2.44</v>
+        <v>2.45</v>
       </c>
       <c r="CG6" t="n">
-        <v>3.24</v>
+        <v>3.23</v>
       </c>
       <c r="CH6" t="n">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="CI6" t="n">
-        <v>2.22</v>
+        <v>2.21</v>
       </c>
       <c r="CJ6" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="CK6" t="n">
         <v>1.5</v>
       </c>
       <c r="CL6" t="n">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="CM6" t="n">
         <v>2.44</v>
@@ -3267,124 +3267,124 @@
         <v>1.2</v>
       </c>
       <c r="CP6" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="CQ6" t="n">
-        <v>2.72</v>
+        <v>2.73</v>
       </c>
       <c r="CR6" t="n">
         <v>1.36</v>
       </c>
       <c r="CS6" t="n">
-        <v>2.59</v>
+        <v>2.6</v>
       </c>
       <c r="CT6" t="n">
-        <v>3.16</v>
+        <v>3.17</v>
       </c>
       <c r="CU6" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="CV6" t="n">
-        <v>2.27</v>
+        <v>2.26</v>
       </c>
       <c r="CW6" t="n">
         <v>1.7</v>
       </c>
       <c r="CX6" t="n">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="CY6" t="n">
         <v>1.9</v>
       </c>
       <c r="CZ6" t="n">
-        <v>2.37</v>
+        <v>2.38</v>
       </c>
       <c r="DA6" t="n">
         <v>1.92</v>
       </c>
       <c r="DB6" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="DC6" t="n">
         <v>1.76</v>
       </c>
       <c r="DD6" t="n">
-        <v>2.84</v>
+        <v>2.85</v>
       </c>
       <c r="DE6" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="DF6" t="n">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="DG6" t="n">
-        <v>3.33</v>
+        <v>3.22</v>
       </c>
       <c r="DH6" t="n">
-        <v>112.78</v>
+        <v>112.82</v>
       </c>
       <c r="DI6" t="n">
         <v>0.04</v>
       </c>
       <c r="DJ6" t="n">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="DK6" t="n">
-        <v>5.74</v>
+        <v>5.57</v>
       </c>
       <c r="DL6" t="n">
-        <v>0.59</v>
+        <v>0.57</v>
       </c>
       <c r="DM6" t="n">
-        <v>54.96</v>
+        <v>54</v>
       </c>
       <c r="DN6" t="n">
-        <v>0.48</v>
+        <v>0.5</v>
       </c>
       <c r="DO6" t="n">
-        <v>2.37</v>
+        <v>2.33</v>
       </c>
       <c r="DP6" t="n">
-        <v>10.04</v>
+        <v>10</v>
       </c>
       <c r="DQ6" t="n">
-        <v>12.52</v>
+        <v>12.36</v>
       </c>
       <c r="DR6" t="n">
-        <v>7</v>
+        <v>7.14</v>
       </c>
       <c r="DS6" t="n">
-        <v>0.04</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="DT6" t="n">
-        <v>0.04</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="DU6" t="n">
         <v>0</v>
       </c>
       <c r="DV6" t="n">
-        <v>61.44</v>
+        <v>61.28</v>
       </c>
       <c r="DW6" t="n">
         <v>0.04</v>
       </c>
       <c r="DX6" t="n">
-        <v>15.93</v>
+        <v>15.54</v>
       </c>
       <c r="DY6" t="n">
-        <v>10.07</v>
+        <v>9.779999999999999</v>
       </c>
       <c r="DZ6" t="n">
-        <v>5.85</v>
+        <v>5.75</v>
       </c>
       <c r="EA6" t="n">
         <v>20.18</v>
       </c>
       <c r="EB6" t="n">
-        <v>1.81</v>
+        <v>1.78</v>
       </c>
       <c r="EC6" t="n">
-        <v>1.41</v>
+        <v>1.43</v>
       </c>
     </row>
     <row r="7">
@@ -3394,13 +3394,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C7" t="n">
         <v>14</v>
       </c>
       <c r="D7" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E7" t="n">
         <v>0.21</v>
@@ -3484,52 +3484,52 @@
         <v>2.21</v>
       </c>
       <c r="AF7" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="AH7" t="n">
-        <v>2.92</v>
+        <v>2.93</v>
       </c>
       <c r="AI7" t="n">
-        <v>88.92</v>
+        <v>90</v>
       </c>
       <c r="AJ7" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="AK7" t="n">
-        <v>2.38</v>
+        <v>2.36</v>
       </c>
       <c r="AL7" t="n">
         <v>5</v>
       </c>
       <c r="AM7" t="n">
-        <v>0.31</v>
+        <v>0.29</v>
       </c>
       <c r="AN7" t="n">
-        <v>43.46</v>
+        <v>45.07</v>
       </c>
       <c r="AO7" t="n">
-        <v>0.77</v>
+        <v>0.79</v>
       </c>
       <c r="AP7" t="n">
-        <v>2.08</v>
+        <v>2.07</v>
       </c>
       <c r="AQ7" t="n">
-        <v>10.69</v>
+        <v>11.21</v>
       </c>
       <c r="AR7" t="n">
-        <v>11.77</v>
+        <v>11.57</v>
       </c>
       <c r="AS7" t="n">
-        <v>8.85</v>
+        <v>8.640000000000001</v>
       </c>
       <c r="AT7" t="n">
-        <v>1.08</v>
+        <v>1.21</v>
       </c>
       <c r="AU7" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="AV7" t="n">
         <v>0</v>
@@ -3541,82 +3541,82 @@
         <v>0</v>
       </c>
       <c r="AY7" t="n">
-        <v>51.15</v>
+        <v>51.36</v>
       </c>
       <c r="AZ7" t="n">
         <v>0</v>
       </c>
       <c r="BA7" t="n">
-        <v>10</v>
+        <v>9.859999999999999</v>
       </c>
       <c r="BB7" t="n">
-        <v>5.92</v>
+        <v>5.86</v>
       </c>
       <c r="BC7" t="n">
-        <v>4.08</v>
+        <v>4</v>
       </c>
       <c r="BD7" t="n">
-        <v>21.31</v>
+        <v>21.71</v>
       </c>
       <c r="BE7" t="n">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="BF7" t="n">
-        <v>2.38</v>
+        <v>2.36</v>
       </c>
       <c r="BG7" t="n">
-        <v>2.44</v>
+        <v>2.5</v>
       </c>
       <c r="BH7" t="n">
-        <v>10.93</v>
+        <v>10.82</v>
       </c>
       <c r="BI7" t="n">
-        <v>2.44</v>
+        <v>2.5</v>
       </c>
       <c r="BJ7" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.61</v>
       </c>
       <c r="BK7" t="n">
-        <v>0.44</v>
+        <v>0.43</v>
       </c>
       <c r="BL7" t="n">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="BM7" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.82</v>
       </c>
       <c r="BN7" t="n">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="BO7" t="n">
-        <v>1</v>
+        <v>1.04</v>
       </c>
       <c r="BP7" t="n">
         <v>4.89</v>
       </c>
       <c r="BQ7" t="n">
-        <v>6.04</v>
+        <v>5.93</v>
       </c>
       <c r="BR7" t="n">
-        <v>96.3</v>
+        <v>96.43000000000001</v>
       </c>
       <c r="BS7" t="n">
-        <v>74.06999999999999</v>
+        <v>75</v>
       </c>
       <c r="BT7" t="n">
-        <v>37.04</v>
+        <v>39.29</v>
       </c>
       <c r="BU7" t="n">
-        <v>25.93</v>
+        <v>28.57</v>
       </c>
       <c r="BV7" t="n">
-        <v>11.11</v>
+        <v>10.71</v>
       </c>
       <c r="BW7" t="n">
         <v>0</v>
       </c>
       <c r="BX7" t="n">
-        <v>62.96</v>
+        <v>64.29000000000001</v>
       </c>
       <c r="BY7" t="n">
         <v>2.77</v>
@@ -3628,16 +3628,16 @@
         <v>3.65</v>
       </c>
       <c r="CB7" t="n">
-        <v>3.77</v>
+        <v>3.76</v>
       </c>
       <c r="CC7" t="n">
-        <v>3.86</v>
+        <v>3.81</v>
       </c>
       <c r="CD7" t="n">
-        <v>4.33</v>
+        <v>4.28</v>
       </c>
       <c r="CE7" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="CF7" t="n">
         <v>2.47</v>
@@ -3652,13 +3652,13 @@
         <v>2.2</v>
       </c>
       <c r="CJ7" t="n">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="CK7" t="n">
         <v>1.4</v>
       </c>
       <c r="CL7" t="n">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="CM7" t="n">
         <v>2.72</v>
@@ -3673,7 +3673,7 @@
         <v>1.72</v>
       </c>
       <c r="CQ7" t="n">
-        <v>2.78</v>
+        <v>2.77</v>
       </c>
       <c r="CR7" t="n">
         <v>1.36</v>
@@ -3691,7 +3691,7 @@
         <v>2.32</v>
       </c>
       <c r="CW7" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="CX7" t="n">
         <v>1.49</v>
@@ -3712,49 +3712,49 @@
         <v>1.79</v>
       </c>
       <c r="DD7" t="n">
-        <v>2.89</v>
+        <v>2.88</v>
       </c>
       <c r="DE7" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="DF7" t="n">
-        <v>1.59</v>
+        <v>1.57</v>
       </c>
       <c r="DG7" t="n">
-        <v>2.67</v>
+        <v>2.68</v>
       </c>
       <c r="DH7" t="n">
-        <v>89.06999999999999</v>
+        <v>89.59999999999999</v>
       </c>
       <c r="DI7" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="DJ7" t="n">
-        <v>2.29</v>
+        <v>2.28</v>
       </c>
       <c r="DK7" t="n">
-        <v>4.67</v>
+        <v>4.68</v>
       </c>
       <c r="DL7" t="n">
-        <v>0.26</v>
+        <v>0.25</v>
       </c>
       <c r="DM7" t="n">
-        <v>46.37</v>
+        <v>47.07</v>
       </c>
       <c r="DN7" t="n">
-        <v>0.7</v>
+        <v>0.72</v>
       </c>
       <c r="DO7" t="n">
         <v>2</v>
       </c>
       <c r="DP7" t="n">
-        <v>10.59</v>
+        <v>10.86</v>
       </c>
       <c r="DQ7" t="n">
-        <v>11.67</v>
+        <v>11.57</v>
       </c>
       <c r="DR7" t="n">
-        <v>9.19</v>
+        <v>9.07</v>
       </c>
       <c r="DS7" t="n">
         <v>0.07000000000000001</v>
@@ -3766,28 +3766,28 @@
         <v>0</v>
       </c>
       <c r="DV7" t="n">
-        <v>49.93</v>
+        <v>50.08</v>
       </c>
       <c r="DW7" t="n">
         <v>0</v>
       </c>
       <c r="DX7" t="n">
-        <v>10.22</v>
+        <v>10.14</v>
       </c>
       <c r="DY7" t="n">
-        <v>6.37</v>
+        <v>6.33</v>
       </c>
       <c r="DZ7" t="n">
-        <v>3.85</v>
+        <v>3.82</v>
       </c>
       <c r="EA7" t="n">
-        <v>21.34</v>
+        <v>21.54</v>
       </c>
       <c r="EB7" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="EC7" t="n">
-        <v>2.29</v>
+        <v>2.28</v>
       </c>
     </row>
     <row r="8">
@@ -3893,7 +3893,7 @@
         <v>1.57</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.79</v>
+        <v>2</v>
       </c>
       <c r="AI8" t="n">
         <v>86.36</v>
@@ -3905,10 +3905,10 @@
         <v>1.86</v>
       </c>
       <c r="AL8" t="n">
-        <v>4.36</v>
+        <v>4.21</v>
       </c>
       <c r="AM8" t="n">
-        <v>0.14</v>
+        <v>0.36</v>
       </c>
       <c r="AN8" t="n">
         <v>42.29</v>
@@ -3917,7 +3917,7 @@
         <v>0.21</v>
       </c>
       <c r="AP8" t="n">
-        <v>1.93</v>
+        <v>2.21</v>
       </c>
       <c r="AQ8" t="n">
         <v>13.14</v>
@@ -3953,10 +3953,10 @@
         <v>12.79</v>
       </c>
       <c r="BB8" t="n">
-        <v>8.43</v>
+        <v>8.359999999999999</v>
       </c>
       <c r="BC8" t="n">
-        <v>4.36</v>
+        <v>4.43</v>
       </c>
       <c r="BD8" t="n">
         <v>23.21</v>
@@ -3971,7 +3971,7 @@
         <v>2.61</v>
       </c>
       <c r="BH8" t="n">
-        <v>10.25</v>
+        <v>10.18</v>
       </c>
       <c r="BI8" t="n">
         <v>2.61</v>
@@ -3995,10 +3995,10 @@
         <v>1.36</v>
       </c>
       <c r="BP8" t="n">
-        <v>4.46</v>
+        <v>4.82</v>
       </c>
       <c r="BQ8" t="n">
-        <v>5.11</v>
+        <v>5.32</v>
       </c>
       <c r="BR8" t="n">
         <v>89.29000000000001</v>
@@ -4037,7 +4037,7 @@
         <v>3.85</v>
       </c>
       <c r="CD8" t="n">
-        <v>3.82</v>
+        <v>3.83</v>
       </c>
       <c r="CE8" t="n">
         <v>1.28</v>
@@ -4091,7 +4091,7 @@
         <v>1.61</v>
       </c>
       <c r="CV8" t="n">
-        <v>2.54</v>
+        <v>2.53</v>
       </c>
       <c r="CW8" t="n">
         <v>1.56</v>
@@ -4100,22 +4100,22 @@
         <v>1.5</v>
       </c>
       <c r="CY8" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="CZ8" t="n">
         <v>2.53</v>
       </c>
       <c r="DA8" t="n">
-        <v>2.2</v>
+        <v>2.21</v>
       </c>
       <c r="DB8" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="DC8" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="DD8" t="n">
-        <v>2.55</v>
+        <v>2.56</v>
       </c>
       <c r="DE8" t="n">
         <v>0.18</v>
@@ -4124,7 +4124,7 @@
         <v>1.25</v>
       </c>
       <c r="DG8" t="n">
-        <v>2.32</v>
+        <v>2.43</v>
       </c>
       <c r="DH8" t="n">
         <v>92.11</v>
@@ -4136,10 +4136,10 @@
         <v>1.61</v>
       </c>
       <c r="DK8" t="n">
-        <v>5.04</v>
+        <v>4.96</v>
       </c>
       <c r="DL8" t="n">
-        <v>0.22</v>
+        <v>0.32</v>
       </c>
       <c r="DM8" t="n">
         <v>48.46</v>
@@ -4148,7 +4148,7 @@
         <v>0.29</v>
       </c>
       <c r="DO8" t="n">
-        <v>2.4</v>
+        <v>2.53</v>
       </c>
       <c r="DP8" t="n">
         <v>11.72</v>
@@ -4178,10 +4178,10 @@
         <v>14.14</v>
       </c>
       <c r="DY8" t="n">
-        <v>9.57</v>
+        <v>9.539999999999999</v>
       </c>
       <c r="DZ8" t="n">
-        <v>4.58</v>
+        <v>4.61</v>
       </c>
       <c r="EA8" t="n">
         <v>21.5</v>
@@ -4215,7 +4215,7 @@
         <v>2.07</v>
       </c>
       <c r="G9" t="n">
-        <v>2.14</v>
+        <v>2.43</v>
       </c>
       <c r="H9" t="n">
         <v>83.56999999999999</v>
@@ -4230,7 +4230,7 @@
         <v>5.29</v>
       </c>
       <c r="L9" t="n">
-        <v>0.43</v>
+        <v>0.57</v>
       </c>
       <c r="M9" t="n">
         <v>42.21</v>
@@ -4239,7 +4239,7 @@
         <v>0.71</v>
       </c>
       <c r="O9" t="n">
-        <v>2.29</v>
+        <v>2.79</v>
       </c>
       <c r="P9" t="n">
         <v>15.86</v>
@@ -4281,7 +4281,7 @@
         <v>4.86</v>
       </c>
       <c r="AC9" t="n">
-        <v>20.14</v>
+        <v>20.21</v>
       </c>
       <c r="AD9" t="n">
         <v>1.62</v>
@@ -4374,7 +4374,7 @@
         <v>2.57</v>
       </c>
       <c r="BH9" t="n">
-        <v>11.18</v>
+        <v>11.11</v>
       </c>
       <c r="BI9" t="n">
         <v>2.57</v>
@@ -4398,10 +4398,10 @@
         <v>1.18</v>
       </c>
       <c r="BP9" t="n">
-        <v>5.25</v>
+        <v>5.61</v>
       </c>
       <c r="BQ9" t="n">
-        <v>5.25</v>
+        <v>5.46</v>
       </c>
       <c r="BR9" t="n">
         <v>92.86</v>
@@ -4485,7 +4485,7 @@
         <v>1.38</v>
       </c>
       <c r="CS9" t="n">
-        <v>2.79</v>
+        <v>2.81</v>
       </c>
       <c r="CT9" t="n">
         <v>3.1</v>
@@ -4509,7 +4509,7 @@
         <v>2.46</v>
       </c>
       <c r="DA9" t="n">
-        <v>2.01</v>
+        <v>2.02</v>
       </c>
       <c r="DB9" t="n">
         <v>1.3</v>
@@ -4518,7 +4518,7 @@
         <v>1.96</v>
       </c>
       <c r="DD9" t="n">
-        <v>3.31</v>
+        <v>3.32</v>
       </c>
       <c r="DE9" t="n">
         <v>0.14</v>
@@ -4527,7 +4527,7 @@
         <v>2.18</v>
       </c>
       <c r="DG9" t="n">
-        <v>2.39</v>
+        <v>2.54</v>
       </c>
       <c r="DH9" t="n">
         <v>80.04000000000001</v>
@@ -4542,7 +4542,7 @@
         <v>4.93</v>
       </c>
       <c r="DL9" t="n">
-        <v>0.46</v>
+        <v>0.54</v>
       </c>
       <c r="DM9" t="n">
         <v>42.71</v>
@@ -4551,7 +4551,7 @@
         <v>0.89</v>
       </c>
       <c r="DO9" t="n">
-        <v>2.11</v>
+        <v>2.36</v>
       </c>
       <c r="DP9" t="n">
         <v>15.78</v>
@@ -4587,7 +4587,7 @@
         <v>4.32</v>
       </c>
       <c r="EA9" t="n">
-        <v>19.57</v>
+        <v>19.6</v>
       </c>
       <c r="EB9" t="n">
         <v>1.48</v>
@@ -5006,13 +5006,13 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C11" t="n">
         <v>14</v>
       </c>
       <c r="D11" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E11" t="n">
         <v>0.07000000000000001</v>
@@ -5096,139 +5096,139 @@
         <v>2.5</v>
       </c>
       <c r="AF11" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.38</v>
+        <v>1.43</v>
       </c>
       <c r="AH11" t="n">
-        <v>3</v>
+        <v>2.86</v>
       </c>
       <c r="AI11" t="n">
-        <v>95.62</v>
+        <v>92.93000000000001</v>
       </c>
       <c r="AJ11" t="n">
         <v>0</v>
       </c>
       <c r="AK11" t="n">
-        <v>2.54</v>
+        <v>2.57</v>
       </c>
       <c r="AL11" t="n">
-        <v>6.08</v>
+        <v>5.79</v>
       </c>
       <c r="AM11" t="n">
-        <v>0.31</v>
+        <v>0.29</v>
       </c>
       <c r="AN11" t="n">
-        <v>52.85</v>
+        <v>51.79</v>
       </c>
       <c r="AO11" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="AP11" t="n">
-        <v>3.08</v>
+        <v>2.93</v>
       </c>
       <c r="AQ11" t="n">
-        <v>14.77</v>
+        <v>14.64</v>
       </c>
       <c r="AR11" t="n">
-        <v>9.69</v>
+        <v>9.5</v>
       </c>
       <c r="AS11" t="n">
-        <v>8.460000000000001</v>
+        <v>8.859999999999999</v>
       </c>
       <c r="AT11" t="n">
-        <v>1.69</v>
+        <v>1.71</v>
       </c>
       <c r="AU11" t="n">
-        <v>1.23</v>
+        <v>1.29</v>
       </c>
       <c r="AV11" t="n">
-        <v>0.23</v>
+        <v>0.21</v>
       </c>
       <c r="AW11" t="n">
-        <v>0.23</v>
+        <v>0.21</v>
       </c>
       <c r="AX11" t="n">
         <v>0</v>
       </c>
       <c r="AY11" t="n">
-        <v>54.38</v>
+        <v>52.71</v>
       </c>
       <c r="AZ11" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="BA11" t="n">
-        <v>12.62</v>
+        <v>12.64</v>
       </c>
       <c r="BB11" t="n">
-        <v>8.619999999999999</v>
+        <v>8.57</v>
       </c>
       <c r="BC11" t="n">
-        <v>4</v>
+        <v>4.07</v>
       </c>
       <c r="BD11" t="n">
-        <v>21.23</v>
+        <v>20.79</v>
       </c>
       <c r="BE11" t="n">
         <v>1.46</v>
       </c>
       <c r="BF11" t="n">
-        <v>2.38</v>
+        <v>2.43</v>
       </c>
       <c r="BG11" t="n">
-        <v>2.67</v>
+        <v>2.71</v>
       </c>
       <c r="BH11" t="n">
-        <v>11.04</v>
+        <v>11.11</v>
       </c>
       <c r="BI11" t="n">
-        <v>2.67</v>
+        <v>2.71</v>
       </c>
       <c r="BJ11" t="n">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="BK11" t="n">
-        <v>0.48</v>
+        <v>0.5</v>
       </c>
       <c r="BL11" t="n">
         <v>1.04</v>
       </c>
       <c r="BM11" t="n">
-        <v>0.52</v>
+        <v>0.54</v>
       </c>
       <c r="BN11" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="BO11" t="n">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="BP11" t="n">
-        <v>5.48</v>
+        <v>5.46</v>
       </c>
       <c r="BQ11" t="n">
-        <v>5.56</v>
+        <v>5.64</v>
       </c>
       <c r="BR11" t="n">
-        <v>88.89</v>
+        <v>89.29000000000001</v>
       </c>
       <c r="BS11" t="n">
-        <v>66.67</v>
+        <v>67.86</v>
       </c>
       <c r="BT11" t="n">
-        <v>40.74</v>
+        <v>42.86</v>
       </c>
       <c r="BU11" t="n">
-        <v>33.33</v>
+        <v>35.71</v>
       </c>
       <c r="BV11" t="n">
-        <v>18.52</v>
+        <v>17.86</v>
       </c>
       <c r="BW11" t="n">
-        <v>14.81</v>
+        <v>14.29</v>
       </c>
       <c r="BX11" t="n">
-        <v>44.44</v>
+        <v>46.43</v>
       </c>
       <c r="BY11" t="n">
         <v>1.9</v>
@@ -5237,43 +5237,43 @@
         <v>1.98</v>
       </c>
       <c r="CA11" t="n">
-        <v>3.6</v>
+        <v>3.62</v>
       </c>
       <c r="CB11" t="n">
-        <v>3.69</v>
+        <v>3.74</v>
       </c>
       <c r="CC11" t="n">
-        <v>2.47</v>
+        <v>2.63</v>
       </c>
       <c r="CD11" t="n">
-        <v>2.67</v>
+        <v>2.96</v>
       </c>
       <c r="CE11" t="n">
         <v>1.33</v>
       </c>
       <c r="CF11" t="n">
-        <v>2.58</v>
+        <v>2.56</v>
       </c>
       <c r="CG11" t="n">
-        <v>3.03</v>
+        <v>3.06</v>
       </c>
       <c r="CH11" t="n">
         <v>1.46</v>
       </c>
       <c r="CI11" t="n">
-        <v>2.1</v>
+        <v>2.11</v>
       </c>
       <c r="CJ11" t="n">
         <v>1.7</v>
       </c>
       <c r="CK11" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="CL11" t="n">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="CM11" t="n">
-        <v>2.54</v>
+        <v>2.55</v>
       </c>
       <c r="CN11" t="n">
         <v>1.95</v>
@@ -5282,22 +5282,22 @@
         <v>1.24</v>
       </c>
       <c r="CP11" t="n">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="CQ11" t="n">
-        <v>2.98</v>
+        <v>2.95</v>
       </c>
       <c r="CR11" t="n">
         <v>1.36</v>
       </c>
       <c r="CS11" t="n">
-        <v>2.72</v>
+        <v>2.7</v>
       </c>
       <c r="CT11" t="n">
         <v>3.18</v>
       </c>
       <c r="CU11" t="n">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="CV11" t="n">
         <v>2.19</v>
@@ -5312,94 +5312,94 @@
         <v>1.81</v>
       </c>
       <c r="CZ11" t="n">
-        <v>2.5</v>
+        <v>2.51</v>
       </c>
       <c r="DA11" t="n">
-        <v>2.01</v>
+        <v>2.02</v>
       </c>
       <c r="DB11" t="n">
         <v>1.27</v>
       </c>
       <c r="DC11" t="n">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="DD11" t="n">
-        <v>3.13</v>
+        <v>3.1</v>
       </c>
       <c r="DE11" t="n">
         <v>0.11</v>
       </c>
       <c r="DF11" t="n">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="DG11" t="n">
-        <v>3.15</v>
+        <v>3.08</v>
       </c>
       <c r="DH11" t="n">
-        <v>102.85</v>
+        <v>101.25</v>
       </c>
       <c r="DI11" t="n">
         <v>0</v>
       </c>
       <c r="DJ11" t="n">
-        <v>2.59</v>
+        <v>2.6</v>
       </c>
       <c r="DK11" t="n">
-        <v>6.45</v>
+        <v>6.29</v>
       </c>
       <c r="DL11" t="n">
-        <v>0.52</v>
+        <v>0.5</v>
       </c>
       <c r="DM11" t="n">
-        <v>55.89</v>
+        <v>55.25</v>
       </c>
       <c r="DN11" t="n">
         <v>1</v>
       </c>
       <c r="DO11" t="n">
-        <v>3.3</v>
+        <v>3.22</v>
       </c>
       <c r="DP11" t="n">
-        <v>13.96</v>
+        <v>13.92</v>
       </c>
       <c r="DQ11" t="n">
-        <v>10.78</v>
+        <v>10.64</v>
       </c>
       <c r="DR11" t="n">
-        <v>7.85</v>
+        <v>8.07</v>
       </c>
       <c r="DS11" t="n">
-        <v>0.22</v>
+        <v>0.21</v>
       </c>
       <c r="DT11" t="n">
-        <v>0.22</v>
+        <v>0.21</v>
       </c>
       <c r="DU11" t="n">
         <v>0</v>
       </c>
       <c r="DV11" t="n">
-        <v>53.92</v>
+        <v>53.1</v>
       </c>
       <c r="DW11" t="n">
         <v>0.11</v>
       </c>
       <c r="DX11" t="n">
-        <v>14.89</v>
+        <v>14.82</v>
       </c>
       <c r="DY11" t="n">
-        <v>10.15</v>
+        <v>10.07</v>
       </c>
       <c r="DZ11" t="n">
-        <v>4.74</v>
+        <v>4.75</v>
       </c>
       <c r="EA11" t="n">
-        <v>21.04</v>
+        <v>20.82</v>
       </c>
       <c r="EB11" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="EC11" t="n">
-        <v>2.44</v>
+        <v>2.47</v>
       </c>
     </row>
     <row r="12">
@@ -5812,94 +5812,94 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C13" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D13" t="n">
         <v>14</v>
       </c>
       <c r="E13" t="n">
-        <v>0.23</v>
+        <v>0.21</v>
       </c>
       <c r="F13" t="n">
-        <v>1.62</v>
+        <v>1.5</v>
       </c>
       <c r="G13" t="n">
-        <v>3.38</v>
+        <v>3.5</v>
       </c>
       <c r="H13" t="n">
-        <v>102.31</v>
+        <v>102.5</v>
       </c>
       <c r="I13" t="n">
         <v>0</v>
       </c>
       <c r="J13" t="n">
-        <v>2.31</v>
+        <v>2.14</v>
       </c>
       <c r="K13" t="n">
-        <v>5.23</v>
+        <v>5.36</v>
       </c>
       <c r="L13" t="n">
-        <v>0.31</v>
+        <v>0.29</v>
       </c>
       <c r="M13" t="n">
-        <v>55.15</v>
+        <v>55.93</v>
       </c>
       <c r="N13" t="n">
-        <v>0.54</v>
+        <v>0.5</v>
       </c>
       <c r="O13" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="P13" t="n">
-        <v>10.69</v>
+        <v>10.43</v>
       </c>
       <c r="Q13" t="n">
-        <v>11.77</v>
+        <v>11.79</v>
       </c>
       <c r="R13" t="n">
-        <v>6.46</v>
+        <v>6.43</v>
       </c>
       <c r="S13" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="T13" t="n">
-        <v>1.54</v>
+        <v>1.57</v>
       </c>
       <c r="U13" t="n">
-        <v>0.23</v>
+        <v>0.21</v>
       </c>
       <c r="V13" t="n">
-        <v>0.23</v>
+        <v>0.21</v>
       </c>
       <c r="W13" t="n">
         <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>53.46</v>
+        <v>54</v>
       </c>
       <c r="Y13" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="Z13" t="n">
-        <v>15.46</v>
+        <v>15.43</v>
       </c>
       <c r="AA13" t="n">
-        <v>10.62</v>
+        <v>10.43</v>
       </c>
       <c r="AB13" t="n">
-        <v>4.85</v>
+        <v>5</v>
       </c>
       <c r="AC13" t="n">
-        <v>22.77</v>
+        <v>23</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.71</v>
+        <v>1.73</v>
       </c>
       <c r="AE13" t="n">
-        <v>2</v>
+        <v>1.86</v>
       </c>
       <c r="AF13" t="n">
         <v>0.07000000000000001</v>
@@ -5983,70 +5983,70 @@
         <v>1.64</v>
       </c>
       <c r="BG13" t="n">
-        <v>2.74</v>
+        <v>2.75</v>
       </c>
       <c r="BH13" t="n">
-        <v>9.93</v>
+        <v>10</v>
       </c>
       <c r="BI13" t="n">
-        <v>2.74</v>
+        <v>2.75</v>
       </c>
       <c r="BJ13" t="n">
-        <v>0.7</v>
+        <v>0.71</v>
       </c>
       <c r="BK13" t="n">
-        <v>0.59</v>
+        <v>0.57</v>
       </c>
       <c r="BL13" t="n">
-        <v>0.59</v>
+        <v>0.61</v>
       </c>
       <c r="BM13" t="n">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="BN13" t="n">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="BO13" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="BP13" t="n">
-        <v>4.04</v>
+        <v>4.07</v>
       </c>
       <c r="BQ13" t="n">
-        <v>5.89</v>
+        <v>5.93</v>
       </c>
       <c r="BR13" t="n">
         <v>100</v>
       </c>
       <c r="BS13" t="n">
-        <v>81.48</v>
+        <v>82.14</v>
       </c>
       <c r="BT13" t="n">
-        <v>55.56</v>
+        <v>57.14</v>
       </c>
       <c r="BU13" t="n">
-        <v>25.93</v>
+        <v>25</v>
       </c>
       <c r="BV13" t="n">
-        <v>11.11</v>
+        <v>10.71</v>
       </c>
       <c r="BW13" t="n">
         <v>0</v>
       </c>
       <c r="BX13" t="n">
-        <v>55.56</v>
+        <v>57.14</v>
       </c>
       <c r="BY13" t="n">
-        <v>2.23</v>
+        <v>2.2</v>
       </c>
       <c r="BZ13" t="n">
-        <v>2.31</v>
+        <v>2.27</v>
       </c>
       <c r="CA13" t="n">
-        <v>3.65</v>
+        <v>3.66</v>
       </c>
       <c r="CB13" t="n">
-        <v>3.76</v>
+        <v>3.78</v>
       </c>
       <c r="CC13" t="n">
         <v>3.49</v>
@@ -6058,16 +6058,16 @@
         <v>1.31</v>
       </c>
       <c r="CF13" t="n">
-        <v>2.49</v>
+        <v>2.48</v>
       </c>
       <c r="CG13" t="n">
-        <v>3.16</v>
+        <v>3.17</v>
       </c>
       <c r="CH13" t="n">
         <v>1.5</v>
       </c>
       <c r="CI13" t="n">
-        <v>2.17</v>
+        <v>2.18</v>
       </c>
       <c r="CJ13" t="n">
         <v>1.64</v>
@@ -6076,13 +6076,13 @@
         <v>1.47</v>
       </c>
       <c r="CL13" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="CM13" t="n">
-        <v>2.5</v>
+        <v>2.51</v>
       </c>
       <c r="CN13" t="n">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="CO13" t="n">
         <v>1.22</v>
@@ -6091,7 +6091,7 @@
         <v>1.75</v>
       </c>
       <c r="CQ13" t="n">
-        <v>2.83</v>
+        <v>2.81</v>
       </c>
       <c r="CR13" t="n">
         <v>1.35</v>
@@ -6106,7 +6106,7 @@
         <v>1.51</v>
       </c>
       <c r="CV13" t="n">
-        <v>2.31</v>
+        <v>2.32</v>
       </c>
       <c r="CW13" t="n">
         <v>1.66</v>
@@ -6115,13 +6115,13 @@
         <v>1.55</v>
       </c>
       <c r="CY13" t="n">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="CZ13" t="n">
-        <v>2.42</v>
+        <v>2.43</v>
       </c>
       <c r="DA13" t="n">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="DB13" t="n">
         <v>1.24</v>
@@ -6130,82 +6130,82 @@
         <v>1.78</v>
       </c>
       <c r="DD13" t="n">
-        <v>2.89</v>
+        <v>2.87</v>
       </c>
       <c r="DE13" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="DF13" t="n">
-        <v>1.26</v>
+        <v>1.22</v>
       </c>
       <c r="DG13" t="n">
-        <v>3.33</v>
+        <v>3.4</v>
       </c>
       <c r="DH13" t="n">
-        <v>100.78</v>
+        <v>100.93</v>
       </c>
       <c r="DI13" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DJ13" t="n">
-        <v>1.96</v>
+        <v>1.89</v>
       </c>
       <c r="DK13" t="n">
-        <v>5.41</v>
+        <v>5.47</v>
       </c>
       <c r="DL13" t="n">
-        <v>0.44</v>
+        <v>0.43</v>
       </c>
       <c r="DM13" t="n">
-        <v>53.88</v>
+        <v>54.32</v>
       </c>
       <c r="DN13" t="n">
-        <v>0.63</v>
+        <v>0.6</v>
       </c>
       <c r="DO13" t="n">
         <v>2.08</v>
       </c>
       <c r="DP13" t="n">
-        <v>11.22</v>
+        <v>11.07</v>
       </c>
       <c r="DQ13" t="n">
-        <v>11.44</v>
+        <v>11.46</v>
       </c>
       <c r="DR13" t="n">
-        <v>7.59</v>
+        <v>7.54</v>
       </c>
       <c r="DS13" t="n">
-        <v>0.26</v>
+        <v>0.25</v>
       </c>
       <c r="DT13" t="n">
-        <v>0.26</v>
+        <v>0.25</v>
       </c>
       <c r="DU13" t="n">
         <v>0</v>
       </c>
       <c r="DV13" t="n">
-        <v>54.37</v>
+        <v>54.6</v>
       </c>
       <c r="DW13" t="n">
         <v>0.07000000000000001</v>
       </c>
       <c r="DX13" t="n">
-        <v>14.41</v>
+        <v>14.43</v>
       </c>
       <c r="DY13" t="n">
-        <v>9.890000000000001</v>
+        <v>9.82</v>
       </c>
       <c r="DZ13" t="n">
-        <v>4.52</v>
+        <v>4.6</v>
       </c>
       <c r="EA13" t="n">
-        <v>22.22</v>
+        <v>22.36</v>
       </c>
       <c r="EB13" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="EC13" t="n">
-        <v>1.81</v>
+        <v>1.75</v>
       </c>
     </row>
     <row r="14">
@@ -6215,13 +6215,13 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C14" t="n">
         <v>14</v>
       </c>
       <c r="D14" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E14" t="n">
         <v>0.14</v>
@@ -6305,139 +6305,139 @@
         <v>1.93</v>
       </c>
       <c r="AF14" t="n">
-        <v>0.15</v>
+        <v>0.21</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.54</v>
+        <v>1.5</v>
       </c>
       <c r="AH14" t="n">
-        <v>2.31</v>
+        <v>2.79</v>
       </c>
       <c r="AI14" t="n">
-        <v>92.45999999999999</v>
+        <v>93.29000000000001</v>
       </c>
       <c r="AJ14" t="n">
-        <v>-0.08</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="AK14" t="n">
-        <v>2.15</v>
+        <v>2.07</v>
       </c>
       <c r="AL14" t="n">
-        <v>4.69</v>
+        <v>5.29</v>
       </c>
       <c r="AM14" t="n">
-        <v>0.62</v>
+        <v>0.71</v>
       </c>
       <c r="AN14" t="n">
-        <v>45.38</v>
+        <v>48.07</v>
       </c>
       <c r="AO14" t="n">
-        <v>0.62</v>
+        <v>0.57</v>
       </c>
       <c r="AP14" t="n">
-        <v>2.38</v>
+        <v>2.43</v>
       </c>
       <c r="AQ14" t="n">
-        <v>12.08</v>
+        <v>12</v>
       </c>
       <c r="AR14" t="n">
-        <v>9.619999999999999</v>
+        <v>9.5</v>
       </c>
       <c r="AS14" t="n">
-        <v>7.85</v>
+        <v>7.64</v>
       </c>
       <c r="AT14" t="n">
-        <v>1.38</v>
+        <v>1.43</v>
       </c>
       <c r="AU14" t="n">
-        <v>1.23</v>
+        <v>1.29</v>
       </c>
       <c r="AV14" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="AW14" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="AX14" t="n">
         <v>0</v>
       </c>
       <c r="AY14" t="n">
-        <v>47.77</v>
+        <v>48.43</v>
       </c>
       <c r="AZ14" t="n">
         <v>0</v>
       </c>
       <c r="BA14" t="n">
-        <v>11.69</v>
+        <v>12.43</v>
       </c>
       <c r="BB14" t="n">
-        <v>8</v>
+        <v>8.5</v>
       </c>
       <c r="BC14" t="n">
-        <v>3.69</v>
+        <v>3.93</v>
       </c>
       <c r="BD14" t="n">
-        <v>20.15</v>
+        <v>20.71</v>
       </c>
       <c r="BE14" t="n">
-        <v>1.33</v>
+        <v>1.41</v>
       </c>
       <c r="BF14" t="n">
-        <v>2.15</v>
+        <v>2.07</v>
       </c>
       <c r="BG14" t="n">
-        <v>2.7</v>
+        <v>2.75</v>
       </c>
       <c r="BH14" t="n">
-        <v>9.85</v>
+        <v>10.14</v>
       </c>
       <c r="BI14" t="n">
-        <v>2.7</v>
+        <v>2.75</v>
       </c>
       <c r="BJ14" t="n">
-        <v>0.67</v>
+        <v>0.71</v>
       </c>
       <c r="BK14" t="n">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="BL14" t="n">
-        <v>0.74</v>
+        <v>0.71</v>
       </c>
       <c r="BM14" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.57</v>
       </c>
       <c r="BN14" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="BO14" t="n">
-        <v>1.41</v>
+        <v>1.46</v>
       </c>
       <c r="BP14" t="n">
         <v>4.93</v>
       </c>
       <c r="BQ14" t="n">
-        <v>4.93</v>
+        <v>5.18</v>
       </c>
       <c r="BR14" t="n">
-        <v>96.3</v>
+        <v>96.43000000000001</v>
       </c>
       <c r="BS14" t="n">
-        <v>77.78</v>
+        <v>78.56999999999999</v>
       </c>
       <c r="BT14" t="n">
-        <v>48.15</v>
+        <v>50</v>
       </c>
       <c r="BU14" t="n">
-        <v>29.63</v>
+        <v>32.14</v>
       </c>
       <c r="BV14" t="n">
-        <v>11.11</v>
+        <v>10.71</v>
       </c>
       <c r="BW14" t="n">
-        <v>3.7</v>
+        <v>3.57</v>
       </c>
       <c r="BX14" t="n">
-        <v>59.26</v>
+        <v>60.71</v>
       </c>
       <c r="BY14" t="n">
         <v>2.38</v>
@@ -6452,10 +6452,10 @@
         <v>3.52</v>
       </c>
       <c r="CC14" t="n">
-        <v>3.64</v>
+        <v>3.52</v>
       </c>
       <c r="CD14" t="n">
-        <v>3.76</v>
+        <v>3.63</v>
       </c>
       <c r="CE14" t="n">
         <v>1.36</v>
@@ -6470,13 +6470,13 @@
         <v>1.43</v>
       </c>
       <c r="CI14" t="n">
-        <v>2.05</v>
+        <v>2.04</v>
       </c>
       <c r="CJ14" t="n">
         <v>1.74</v>
       </c>
       <c r="CK14" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="CL14" t="n">
         <v>1.91</v>
@@ -6485,7 +6485,7 @@
         <v>2.5</v>
       </c>
       <c r="CN14" t="n">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="CO14" t="n">
         <v>1.27</v>
@@ -6494,13 +6494,13 @@
         <v>1.88</v>
       </c>
       <c r="CQ14" t="n">
-        <v>3.14</v>
+        <v>3.15</v>
       </c>
       <c r="CR14" t="n">
         <v>1.38</v>
       </c>
       <c r="CS14" t="n">
-        <v>2.83</v>
+        <v>2.84</v>
       </c>
       <c r="CT14" t="n">
         <v>3.1</v>
@@ -6512,7 +6512,7 @@
         <v>2.14</v>
       </c>
       <c r="CW14" t="n">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="CX14" t="n">
         <v>1.53</v>
@@ -6533,49 +6533,49 @@
         <v>1.97</v>
       </c>
       <c r="DD14" t="n">
-        <v>3.33</v>
+        <v>3.34</v>
       </c>
       <c r="DE14" t="n">
-        <v>0.14</v>
+        <v>0.18</v>
       </c>
       <c r="DF14" t="n">
-        <v>1.71</v>
+        <v>1.68</v>
       </c>
       <c r="DG14" t="n">
-        <v>2.63</v>
+        <v>2.86</v>
       </c>
       <c r="DH14" t="n">
-        <v>94</v>
+        <v>94.36</v>
       </c>
       <c r="DI14" t="n">
         <v>-0.04</v>
       </c>
       <c r="DJ14" t="n">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="DK14" t="n">
-        <v>5.15</v>
+        <v>5.43</v>
       </c>
       <c r="DL14" t="n">
-        <v>0.45</v>
+        <v>0.5</v>
       </c>
       <c r="DM14" t="n">
-        <v>48.85</v>
+        <v>50.07</v>
       </c>
       <c r="DN14" t="n">
-        <v>0.49</v>
+        <v>0.46</v>
       </c>
       <c r="DO14" t="n">
-        <v>2.51</v>
+        <v>2.54</v>
       </c>
       <c r="DP14" t="n">
-        <v>11.63</v>
+        <v>11.6</v>
       </c>
       <c r="DQ14" t="n">
-        <v>10.82</v>
+        <v>10.72</v>
       </c>
       <c r="DR14" t="n">
-        <v>7.86</v>
+        <v>7.75</v>
       </c>
       <c r="DS14" t="n">
         <v>0.11</v>
@@ -6587,28 +6587,28 @@
         <v>0</v>
       </c>
       <c r="DV14" t="n">
-        <v>48.44</v>
+        <v>48.75</v>
       </c>
       <c r="DW14" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="DX14" t="n">
-        <v>12.7</v>
+        <v>13.04</v>
       </c>
       <c r="DY14" t="n">
-        <v>8.369999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="DZ14" t="n">
-        <v>4.33</v>
+        <v>4.43</v>
       </c>
       <c r="EA14" t="n">
-        <v>18.78</v>
+        <v>19.1</v>
       </c>
       <c r="EB14" t="n">
-        <v>1.46</v>
+        <v>1.5</v>
       </c>
       <c r="EC14" t="n">
-        <v>2.04</v>
+        <v>2</v>
       </c>
     </row>
     <row r="15">
@@ -6618,13 +6618,13 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C15" t="n">
         <v>14</v>
       </c>
       <c r="D15" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E15" t="n">
         <v>0.21</v>
@@ -6708,130 +6708,130 @@
         <v>2.36</v>
       </c>
       <c r="AF15" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.46</v>
+        <v>1.5</v>
       </c>
       <c r="AI15" t="n">
-        <v>83.54000000000001</v>
+        <v>83.64</v>
       </c>
       <c r="AJ15" t="n">
-        <v>-0.08</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="AK15" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="AL15" t="n">
-        <v>3.31</v>
+        <v>3.21</v>
       </c>
       <c r="AM15" t="n">
-        <v>0.31</v>
+        <v>0.29</v>
       </c>
       <c r="AN15" t="n">
-        <v>37.31</v>
+        <v>37.21</v>
       </c>
       <c r="AO15" t="n">
-        <v>0.54</v>
+        <v>0.57</v>
       </c>
       <c r="AP15" t="n">
-        <v>1.85</v>
+        <v>1.71</v>
       </c>
       <c r="AQ15" t="n">
-        <v>10.77</v>
+        <v>10.64</v>
       </c>
       <c r="AR15" t="n">
-        <v>11.15</v>
+        <v>11.07</v>
       </c>
       <c r="AS15" t="n">
-        <v>10.08</v>
+        <v>10.07</v>
       </c>
       <c r="AT15" t="n">
-        <v>1.23</v>
+        <v>1.14</v>
       </c>
       <c r="AU15" t="n">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="AV15" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="AW15" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="AX15" t="n">
         <v>0</v>
       </c>
       <c r="AY15" t="n">
-        <v>42.69</v>
+        <v>43.29</v>
       </c>
       <c r="AZ15" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="BA15" t="n">
-        <v>8.15</v>
+        <v>8.210000000000001</v>
       </c>
       <c r="BB15" t="n">
-        <v>5.85</v>
+        <v>5.79</v>
       </c>
       <c r="BC15" t="n">
-        <v>2.31</v>
+        <v>2.43</v>
       </c>
       <c r="BD15" t="n">
-        <v>16.92</v>
+        <v>16.86</v>
       </c>
       <c r="BE15" t="n">
-        <v>0.95</v>
+        <v>0.97</v>
       </c>
       <c r="BF15" t="n">
-        <v>1.69</v>
+        <v>1.71</v>
       </c>
       <c r="BG15" t="n">
-        <v>2.19</v>
+        <v>2.14</v>
       </c>
       <c r="BH15" t="n">
-        <v>9.85</v>
+        <v>9.68</v>
       </c>
       <c r="BI15" t="n">
-        <v>2.19</v>
+        <v>2.14</v>
       </c>
       <c r="BJ15" t="n">
-        <v>0.63</v>
+        <v>0.61</v>
       </c>
       <c r="BK15" t="n">
-        <v>0.67</v>
+        <v>0.64</v>
       </c>
       <c r="BL15" t="n">
-        <v>0.48</v>
+        <v>0.46</v>
       </c>
       <c r="BM15" t="n">
-        <v>0.41</v>
+        <v>0.43</v>
       </c>
       <c r="BN15" t="n">
         <v>0.89</v>
       </c>
       <c r="BO15" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="BP15" t="n">
-        <v>4.78</v>
+        <v>4.68</v>
       </c>
       <c r="BQ15" t="n">
-        <v>5.07</v>
+        <v>5</v>
       </c>
       <c r="BR15" t="n">
-        <v>96.3</v>
+        <v>96.43000000000001</v>
       </c>
       <c r="BS15" t="n">
-        <v>70.37</v>
+        <v>67.86</v>
       </c>
       <c r="BT15" t="n">
-        <v>40.74</v>
+        <v>39.29</v>
       </c>
       <c r="BU15" t="n">
-        <v>11.11</v>
+        <v>10.71</v>
       </c>
       <c r="BV15" t="n">
         <v>0</v>
@@ -6840,7 +6840,7 @@
         <v>0</v>
       </c>
       <c r="BX15" t="n">
-        <v>33.33</v>
+        <v>32.14</v>
       </c>
       <c r="BY15" t="n">
         <v>3.04</v>
@@ -6855,10 +6855,10 @@
         <v>3.62</v>
       </c>
       <c r="CC15" t="n">
-        <v>4.37</v>
+        <v>4.39</v>
       </c>
       <c r="CD15" t="n">
-        <v>5.27</v>
+        <v>5.2</v>
       </c>
       <c r="CE15" t="n">
         <v>1.39</v>
@@ -6876,16 +6876,16 @@
         <v>1.92</v>
       </c>
       <c r="CJ15" t="n">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="CK15" t="n">
         <v>1.51</v>
       </c>
       <c r="CL15" t="n">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="CM15" t="n">
-        <v>2.49</v>
+        <v>2.5</v>
       </c>
       <c r="CN15" t="n">
         <v>1.91</v>
@@ -6894,10 +6894,10 @@
         <v>1.31</v>
       </c>
       <c r="CP15" t="n">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="CQ15" t="n">
-        <v>3.44</v>
+        <v>3.43</v>
       </c>
       <c r="CR15" t="n">
         <v>1.41</v>
@@ -6924,10 +6924,10 @@
         <v>1.92</v>
       </c>
       <c r="CZ15" t="n">
-        <v>2.38</v>
+        <v>2.39</v>
       </c>
       <c r="DA15" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="DB15" t="n">
         <v>1.33</v>
@@ -6936,82 +6936,82 @@
         <v>2.06</v>
       </c>
       <c r="DD15" t="n">
-        <v>3.59</v>
+        <v>3.58</v>
       </c>
       <c r="DE15" t="n">
         <v>0.18</v>
       </c>
       <c r="DF15" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="DG15" t="n">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="DH15" t="n">
-        <v>86.84999999999999</v>
+        <v>86.78</v>
       </c>
       <c r="DI15" t="n">
         <v>-0.04</v>
       </c>
       <c r="DJ15" t="n">
-        <v>2.41</v>
+        <v>2.4</v>
       </c>
       <c r="DK15" t="n">
-        <v>4.3</v>
+        <v>4.21</v>
       </c>
       <c r="DL15" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.54</v>
       </c>
       <c r="DM15" t="n">
-        <v>43.48</v>
+        <v>43.21</v>
       </c>
       <c r="DN15" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.82</v>
       </c>
       <c r="DO15" t="n">
-        <v>2.48</v>
+        <v>2.39</v>
       </c>
       <c r="DP15" t="n">
-        <v>10.89</v>
+        <v>10.82</v>
       </c>
       <c r="DQ15" t="n">
-        <v>12.15</v>
+        <v>12.07</v>
       </c>
       <c r="DR15" t="n">
-        <v>9.52</v>
+        <v>9.539999999999999</v>
       </c>
       <c r="DS15" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="DT15" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="DU15" t="n">
         <v>0</v>
       </c>
       <c r="DV15" t="n">
-        <v>43.56</v>
+        <v>43.82</v>
       </c>
       <c r="DW15" t="n">
         <v>0.22</v>
       </c>
       <c r="DX15" t="n">
-        <v>9.56</v>
+        <v>9.539999999999999</v>
       </c>
       <c r="DY15" t="n">
-        <v>6.52</v>
+        <v>6.46</v>
       </c>
       <c r="DZ15" t="n">
-        <v>3.04</v>
+        <v>3.07</v>
       </c>
       <c r="EA15" t="n">
-        <v>18.96</v>
+        <v>18.86</v>
       </c>
       <c r="EB15" t="n">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="EC15" t="n">
-        <v>2.04</v>
+        <v>2.03</v>
       </c>
     </row>
     <row r="16">
@@ -7021,94 +7021,94 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C16" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D16" t="n">
         <v>14</v>
       </c>
       <c r="E16" t="n">
-        <v>0.23</v>
+        <v>0.21</v>
       </c>
       <c r="F16" t="n">
-        <v>1.62</v>
+        <v>1.71</v>
       </c>
       <c r="G16" t="n">
-        <v>3.62</v>
+        <v>3.5</v>
       </c>
       <c r="H16" t="n">
-        <v>103.38</v>
+        <v>103.86</v>
       </c>
       <c r="I16" t="n">
         <v>0</v>
       </c>
       <c r="J16" t="n">
-        <v>1.85</v>
+        <v>1.93</v>
       </c>
       <c r="K16" t="n">
-        <v>6.69</v>
+        <v>6.57</v>
       </c>
       <c r="L16" t="n">
-        <v>0.38</v>
+        <v>0.36</v>
       </c>
       <c r="M16" t="n">
-        <v>56.23</v>
+        <v>55.79</v>
       </c>
       <c r="N16" t="n">
-        <v>0.23</v>
+        <v>0.21</v>
       </c>
       <c r="O16" t="n">
-        <v>3.08</v>
+        <v>3.07</v>
       </c>
       <c r="P16" t="n">
-        <v>12.15</v>
+        <v>11.93</v>
       </c>
       <c r="Q16" t="n">
-        <v>10.15</v>
+        <v>10.07</v>
       </c>
       <c r="R16" t="n">
-        <v>5.23</v>
+        <v>5.21</v>
       </c>
       <c r="S16" t="n">
-        <v>0.31</v>
+        <v>0.36</v>
       </c>
       <c r="T16" t="n">
-        <v>2.15</v>
+        <v>2.14</v>
       </c>
       <c r="U16" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="V16" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="W16" t="n">
         <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>52.08</v>
+        <v>51.43</v>
       </c>
       <c r="Y16" t="n">
         <v>0</v>
       </c>
       <c r="Z16" t="n">
-        <v>16.77</v>
+        <v>16.43</v>
       </c>
       <c r="AA16" t="n">
-        <v>10.15</v>
+        <v>10</v>
       </c>
       <c r="AB16" t="n">
-        <v>6.62</v>
+        <v>6.43</v>
       </c>
       <c r="AC16" t="n">
-        <v>20.85</v>
+        <v>21.36</v>
       </c>
       <c r="AD16" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="AE16" t="n">
         <v>1.93</v>
-      </c>
-      <c r="AE16" t="n">
-        <v>1.85</v>
       </c>
       <c r="AF16" t="n">
         <v>0.07000000000000001</v>
@@ -7192,70 +7192,70 @@
         <v>2.86</v>
       </c>
       <c r="BG16" t="n">
-        <v>2.15</v>
+        <v>2.18</v>
       </c>
       <c r="BH16" t="n">
-        <v>9.48</v>
+        <v>9.359999999999999</v>
       </c>
       <c r="BI16" t="n">
-        <v>2.15</v>
+        <v>2.18</v>
       </c>
       <c r="BJ16" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.57</v>
       </c>
       <c r="BK16" t="n">
-        <v>0.33</v>
+        <v>0.32</v>
       </c>
       <c r="BL16" t="n">
         <v>0.89</v>
       </c>
       <c r="BM16" t="n">
-        <v>0.37</v>
+        <v>0.39</v>
       </c>
       <c r="BN16" t="n">
-        <v>1.26</v>
+        <v>1.29</v>
       </c>
       <c r="BO16" t="n">
         <v>0.89</v>
       </c>
       <c r="BP16" t="n">
-        <v>4.67</v>
+        <v>4.64</v>
       </c>
       <c r="BQ16" t="n">
-        <v>4.81</v>
+        <v>4.71</v>
       </c>
       <c r="BR16" t="n">
-        <v>88.89</v>
+        <v>89.29000000000001</v>
       </c>
       <c r="BS16" t="n">
-        <v>70.37</v>
+        <v>71.43000000000001</v>
       </c>
       <c r="BT16" t="n">
-        <v>29.63</v>
+        <v>32.14</v>
       </c>
       <c r="BU16" t="n">
-        <v>14.81</v>
+        <v>14.29</v>
       </c>
       <c r="BV16" t="n">
-        <v>11.11</v>
+        <v>10.71</v>
       </c>
       <c r="BW16" t="n">
         <v>0</v>
       </c>
       <c r="BX16" t="n">
-        <v>44.44</v>
+        <v>46.43</v>
       </c>
       <c r="BY16" t="n">
-        <v>1.41</v>
+        <v>1.43</v>
       </c>
       <c r="BZ16" t="n">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="CA16" t="n">
         <v>4.17</v>
       </c>
       <c r="CB16" t="n">
-        <v>4.36</v>
+        <v>4.34</v>
       </c>
       <c r="CC16" t="n">
         <v>1.85</v>
@@ -7270,13 +7270,13 @@
         <v>2.55</v>
       </c>
       <c r="CG16" t="n">
-        <v>3.15</v>
+        <v>3.14</v>
       </c>
       <c r="CH16" t="n">
         <v>1.48</v>
       </c>
       <c r="CI16" t="n">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="CJ16" t="n">
         <v>1.85</v>
@@ -7297,16 +7297,16 @@
         <v>1.23</v>
       </c>
       <c r="CP16" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="CQ16" t="n">
-        <v>2.87</v>
+        <v>2.88</v>
       </c>
       <c r="CR16" t="n">
         <v>1.37</v>
       </c>
       <c r="CS16" t="n">
-        <v>2.69</v>
+        <v>2.7</v>
       </c>
       <c r="CT16" t="n">
         <v>3.15</v>
@@ -7327,7 +7327,7 @@
         <v>1.9</v>
       </c>
       <c r="CZ16" t="n">
-        <v>2.36</v>
+        <v>2.37</v>
       </c>
       <c r="DA16" t="n">
         <v>1.92</v>
@@ -7342,46 +7342,46 @@
         <v>3.06</v>
       </c>
       <c r="DE16" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="DF16" t="n">
-        <v>1.78</v>
+        <v>1.82</v>
       </c>
       <c r="DG16" t="n">
-        <v>3.11</v>
+        <v>3.07</v>
       </c>
       <c r="DH16" t="n">
-        <v>106.96</v>
+        <v>107.08</v>
       </c>
       <c r="DI16" t="n">
         <v>0.04</v>
       </c>
       <c r="DJ16" t="n">
-        <v>2.41</v>
+        <v>2.43</v>
       </c>
       <c r="DK16" t="n">
-        <v>5.96</v>
+        <v>5.93</v>
       </c>
       <c r="DL16" t="n">
-        <v>0.44</v>
+        <v>0.43</v>
       </c>
       <c r="DM16" t="n">
-        <v>53.81</v>
+        <v>53.68</v>
       </c>
       <c r="DN16" t="n">
-        <v>0.63</v>
+        <v>0.61</v>
       </c>
       <c r="DO16" t="n">
-        <v>2.85</v>
+        <v>2.86</v>
       </c>
       <c r="DP16" t="n">
-        <v>13.04</v>
+        <v>12.89</v>
       </c>
       <c r="DQ16" t="n">
-        <v>9.59</v>
+        <v>9.57</v>
       </c>
       <c r="DR16" t="n">
-        <v>5.67</v>
+        <v>5.64</v>
       </c>
       <c r="DS16" t="n">
         <v>0.07000000000000001</v>
@@ -7393,28 +7393,28 @@
         <v>0</v>
       </c>
       <c r="DV16" t="n">
-        <v>54.26</v>
+        <v>53.86</v>
       </c>
       <c r="DW16" t="n">
         <v>0.04</v>
       </c>
       <c r="DX16" t="n">
-        <v>15.18</v>
+        <v>15.07</v>
       </c>
       <c r="DY16" t="n">
-        <v>9.74</v>
+        <v>9.68</v>
       </c>
       <c r="DZ16" t="n">
-        <v>5.45</v>
+        <v>5.4</v>
       </c>
       <c r="EA16" t="n">
-        <v>20.48</v>
+        <v>20.75</v>
       </c>
       <c r="EB16" t="n">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="EC16" t="n">
-        <v>2.37</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="17">
@@ -7424,10 +7424,10 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C17" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D17" t="n">
         <v>14</v>
@@ -7436,82 +7436,82 @@
         <v>0</v>
       </c>
       <c r="F17" t="n">
-        <v>0.92</v>
+        <v>0.86</v>
       </c>
       <c r="G17" t="n">
-        <v>2.69</v>
+        <v>2.57</v>
       </c>
       <c r="H17" t="n">
-        <v>96.31</v>
+        <v>97.86</v>
       </c>
       <c r="I17" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="J17" t="n">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="K17" t="n">
-        <v>4.38</v>
+        <v>4.29</v>
       </c>
       <c r="L17" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="M17" t="n">
-        <v>48.92</v>
+        <v>48.93</v>
       </c>
       <c r="N17" t="n">
-        <v>0.46</v>
+        <v>0.43</v>
       </c>
       <c r="O17" t="n">
-        <v>1.69</v>
+        <v>1.71</v>
       </c>
       <c r="P17" t="n">
-        <v>9.85</v>
+        <v>9.859999999999999</v>
       </c>
       <c r="Q17" t="n">
-        <v>12.77</v>
+        <v>12.5</v>
       </c>
       <c r="R17" t="n">
-        <v>9.15</v>
+        <v>9.07</v>
       </c>
       <c r="S17" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="T17" t="n">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="U17" t="n">
-        <v>0.31</v>
+        <v>0.29</v>
       </c>
       <c r="V17" t="n">
-        <v>0.31</v>
+        <v>0.29</v>
       </c>
       <c r="W17" t="n">
         <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>47.38</v>
+        <v>47.5</v>
       </c>
       <c r="Y17" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="Z17" t="n">
-        <v>14.31</v>
+        <v>14.64</v>
       </c>
       <c r="AA17" t="n">
-        <v>9.539999999999999</v>
+        <v>9.859999999999999</v>
       </c>
       <c r="AB17" t="n">
-        <v>4.77</v>
+        <v>4.79</v>
       </c>
       <c r="AC17" t="n">
-        <v>21</v>
+        <v>21.36</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.59</v>
+        <v>1.62</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.31</v>
+        <v>1.21</v>
       </c>
       <c r="AF17" t="n">
         <v>0.07000000000000001</v>
@@ -7595,70 +7595,70 @@
         <v>1.86</v>
       </c>
       <c r="BG17" t="n">
-        <v>3</v>
+        <v>2.93</v>
       </c>
       <c r="BH17" t="n">
-        <v>9.74</v>
+        <v>9.57</v>
       </c>
       <c r="BI17" t="n">
-        <v>3</v>
+        <v>2.93</v>
       </c>
       <c r="BJ17" t="n">
-        <v>0.74</v>
+        <v>0.71</v>
       </c>
       <c r="BK17" t="n">
-        <v>0.7</v>
+        <v>0.68</v>
       </c>
       <c r="BL17" t="n">
-        <v>0.89</v>
+        <v>0.86</v>
       </c>
       <c r="BM17" t="n">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="BN17" t="n">
-        <v>1.56</v>
+        <v>1.54</v>
       </c>
       <c r="BO17" t="n">
-        <v>1.44</v>
+        <v>1.39</v>
       </c>
       <c r="BP17" t="n">
-        <v>3.67</v>
+        <v>3.61</v>
       </c>
       <c r="BQ17" t="n">
-        <v>5.56</v>
+        <v>5.46</v>
       </c>
       <c r="BR17" t="n">
-        <v>92.59</v>
+        <v>92.86</v>
       </c>
       <c r="BS17" t="n">
-        <v>81.48</v>
+        <v>78.56999999999999</v>
       </c>
       <c r="BT17" t="n">
-        <v>51.85</v>
+        <v>50</v>
       </c>
       <c r="BU17" t="n">
-        <v>37.04</v>
+        <v>35.71</v>
       </c>
       <c r="BV17" t="n">
-        <v>25.93</v>
+        <v>25</v>
       </c>
       <c r="BW17" t="n">
-        <v>7.41</v>
+        <v>7.14</v>
       </c>
       <c r="BX17" t="n">
-        <v>66.67</v>
+        <v>64.29000000000001</v>
       </c>
       <c r="BY17" t="n">
-        <v>2.95</v>
+        <v>2.87</v>
       </c>
       <c r="BZ17" t="n">
-        <v>3.16</v>
+        <v>3.07</v>
       </c>
       <c r="CA17" t="n">
-        <v>3.74</v>
+        <v>3.73</v>
       </c>
       <c r="CB17" t="n">
-        <v>3.81</v>
+        <v>3.8</v>
       </c>
       <c r="CC17" t="n">
         <v>4.34</v>
@@ -7670,25 +7670,25 @@
         <v>1.31</v>
       </c>
       <c r="CF17" t="n">
-        <v>2.48</v>
+        <v>2.49</v>
       </c>
       <c r="CG17" t="n">
-        <v>3.28</v>
+        <v>3.27</v>
       </c>
       <c r="CH17" t="n">
         <v>1.51</v>
       </c>
       <c r="CI17" t="n">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="CJ17" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="CK17" t="n">
         <v>1.43</v>
       </c>
       <c r="CL17" t="n">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="CM17" t="n">
         <v>2.64</v>
@@ -7700,10 +7700,10 @@
         <v>1.21</v>
       </c>
       <c r="CP17" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="CQ17" t="n">
-        <v>2.73</v>
+        <v>2.75</v>
       </c>
       <c r="CR17" t="n">
         <v>1.35</v>
@@ -7718,19 +7718,19 @@
         <v>1.53</v>
       </c>
       <c r="CV17" t="n">
-        <v>2.3</v>
+        <v>2.29</v>
       </c>
       <c r="CW17" t="n">
         <v>1.68</v>
       </c>
       <c r="CX17" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="CY17" t="n">
         <v>1.79</v>
       </c>
       <c r="CZ17" t="n">
-        <v>2.46</v>
+        <v>2.47</v>
       </c>
       <c r="DA17" t="n">
         <v>2.03</v>
@@ -7739,85 +7739,85 @@
         <v>1.24</v>
       </c>
       <c r="DC17" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="DD17" t="n">
-        <v>2.87</v>
+        <v>2.9</v>
       </c>
       <c r="DE17" t="n">
         <v>0.04</v>
       </c>
       <c r="DF17" t="n">
-        <v>1.18</v>
+        <v>1.14</v>
       </c>
       <c r="DG17" t="n">
-        <v>2.56</v>
+        <v>2.5</v>
       </c>
       <c r="DH17" t="n">
-        <v>96.26000000000001</v>
+        <v>97.03</v>
       </c>
       <c r="DI17" t="n">
         <v>0.07000000000000001</v>
       </c>
       <c r="DJ17" t="n">
-        <v>1.81</v>
+        <v>1.75</v>
       </c>
       <c r="DK17" t="n">
-        <v>4.48</v>
+        <v>4.43</v>
       </c>
       <c r="DL17" t="n">
         <v>0.22</v>
       </c>
       <c r="DM17" t="n">
-        <v>48.11</v>
+        <v>48.14</v>
       </c>
       <c r="DN17" t="n">
-        <v>0.52</v>
+        <v>0.5</v>
       </c>
       <c r="DO17" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="DP17" t="n">
-        <v>10.93</v>
+        <v>10.89</v>
       </c>
       <c r="DQ17" t="n">
-        <v>11.89</v>
+        <v>11.78</v>
       </c>
       <c r="DR17" t="n">
-        <v>9.140000000000001</v>
+        <v>9.1</v>
       </c>
       <c r="DS17" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
       <c r="DT17" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
       <c r="DU17" t="n">
         <v>0</v>
       </c>
       <c r="DV17" t="n">
-        <v>47.85</v>
+        <v>47.9</v>
       </c>
       <c r="DW17" t="n">
         <v>0.11</v>
       </c>
       <c r="DX17" t="n">
-        <v>12.59</v>
+        <v>12.82</v>
       </c>
       <c r="DY17" t="n">
-        <v>8.41</v>
+        <v>8.609999999999999</v>
       </c>
       <c r="DZ17" t="n">
-        <v>4.18</v>
+        <v>4.22</v>
       </c>
       <c r="EA17" t="n">
-        <v>20.19</v>
+        <v>20.4</v>
       </c>
       <c r="EB17" t="n">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="EC17" t="n">
-        <v>1.6</v>
+        <v>1.54</v>
       </c>
     </row>
   </sheetData>

--- a/data/teams/leagues/Averages_Belgium_Pro_League_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Belgium_Pro_League_2025-2026.xlsx
@@ -3138,7 +3138,7 @@
         <v>0</v>
       </c>
       <c r="AY6" t="n">
-        <v>59.71</v>
+        <v>59.79</v>
       </c>
       <c r="AZ6" t="n">
         <v>0</v>
@@ -3363,7 +3363,7 @@
         <v>0</v>
       </c>
       <c r="DV6" t="n">
-        <v>61.28</v>
+        <v>61.32</v>
       </c>
       <c r="DW6" t="n">
         <v>0.04</v>
@@ -7087,7 +7087,7 @@
         <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>51.43</v>
+        <v>51.36</v>
       </c>
       <c r="Y16" t="n">
         <v>0</v>
@@ -7393,7 +7393,7 @@
         <v>0</v>
       </c>
       <c r="DV16" t="n">
-        <v>53.86</v>
+        <v>53.82</v>
       </c>
       <c r="DW16" t="n">
         <v>0.04</v>
@@ -7472,7 +7472,7 @@
         <v>12.5</v>
       </c>
       <c r="R17" t="n">
-        <v>9.07</v>
+        <v>9</v>
       </c>
       <c r="S17" t="n">
         <v>1.36</v>
@@ -7784,7 +7784,7 @@
         <v>11.78</v>
       </c>
       <c r="DR17" t="n">
-        <v>9.1</v>
+        <v>9.07</v>
       </c>
       <c r="DS17" t="n">
         <v>0.18</v>

--- a/data/teams/leagues/Averages_Belgium_Pro_League_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Belgium_Pro_League_2025-2026.xlsx
@@ -2588,94 +2588,94 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C5" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D5" t="n">
         <v>14</v>
       </c>
       <c r="E5" t="n">
-        <v>0.21</v>
+        <v>0.2</v>
       </c>
       <c r="F5" t="n">
-        <v>1.14</v>
+        <v>1.2</v>
       </c>
       <c r="G5" t="n">
-        <v>2.64</v>
+        <v>2.47</v>
       </c>
       <c r="H5" t="n">
-        <v>103.14</v>
+        <v>104.33</v>
       </c>
       <c r="I5" t="n">
         <v>0.07000000000000001</v>
       </c>
       <c r="J5" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="K5" t="n">
-        <v>4.86</v>
+        <v>4.67</v>
       </c>
       <c r="L5" t="n">
-        <v>0.43</v>
+        <v>0.4</v>
       </c>
       <c r="M5" t="n">
-        <v>52.14</v>
+        <v>51.73</v>
       </c>
       <c r="N5" t="n">
-        <v>0.5</v>
+        <v>0.47</v>
       </c>
       <c r="O5" t="n">
-        <v>2.21</v>
+        <v>2.2</v>
       </c>
       <c r="P5" t="n">
-        <v>10.64</v>
+        <v>10.8</v>
       </c>
       <c r="Q5" t="n">
-        <v>11.36</v>
+        <v>11.4</v>
       </c>
       <c r="R5" t="n">
-        <v>8.140000000000001</v>
+        <v>7.93</v>
       </c>
       <c r="S5" t="n">
-        <v>1.21</v>
+        <v>1.13</v>
       </c>
       <c r="T5" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="U5" t="n">
-        <v>0.14</v>
+        <v>0.2</v>
       </c>
       <c r="V5" t="n">
-        <v>0.14</v>
+        <v>0.2</v>
       </c>
       <c r="W5" t="n">
         <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>53.93</v>
+        <v>53.73</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="Z5" t="n">
-        <v>15.21</v>
+        <v>14.93</v>
       </c>
       <c r="AA5" t="n">
-        <v>11.14</v>
+        <v>10.8</v>
       </c>
       <c r="AB5" t="n">
-        <v>4.07</v>
+        <v>4.13</v>
       </c>
       <c r="AC5" t="n">
-        <v>19.79</v>
+        <v>19.93</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="AF5" t="n">
         <v>0.07000000000000001</v>
@@ -2759,70 +2759,70 @@
         <v>1.57</v>
       </c>
       <c r="BG5" t="n">
-        <v>3.07</v>
+        <v>3.03</v>
       </c>
       <c r="BH5" t="n">
-        <v>10.64</v>
+        <v>10.55</v>
       </c>
       <c r="BI5" t="n">
-        <v>3.07</v>
+        <v>3.03</v>
       </c>
       <c r="BJ5" t="n">
         <v>0.79</v>
       </c>
       <c r="BK5" t="n">
-        <v>0.57</v>
+        <v>0.55</v>
       </c>
       <c r="BL5" t="n">
         <v>1</v>
       </c>
       <c r="BM5" t="n">
-        <v>0.71</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="BN5" t="n">
-        <v>1.71</v>
+        <v>1.69</v>
       </c>
       <c r="BO5" t="n">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="BP5" t="n">
-        <v>4.39</v>
+        <v>4.38</v>
       </c>
       <c r="BQ5" t="n">
-        <v>6.25</v>
+        <v>6.17</v>
       </c>
       <c r="BR5" t="n">
-        <v>96.43000000000001</v>
+        <v>96.55</v>
       </c>
       <c r="BS5" t="n">
-        <v>85.70999999999999</v>
+        <v>86.20999999999999</v>
       </c>
       <c r="BT5" t="n">
-        <v>60.71</v>
+        <v>58.62</v>
       </c>
       <c r="BU5" t="n">
-        <v>39.29</v>
+        <v>37.93</v>
       </c>
       <c r="BV5" t="n">
-        <v>17.86</v>
+        <v>17.24</v>
       </c>
       <c r="BW5" t="n">
-        <v>7.14</v>
+        <v>6.9</v>
       </c>
       <c r="BX5" t="n">
-        <v>60.71</v>
+        <v>58.62</v>
       </c>
       <c r="BY5" t="n">
-        <v>2.57</v>
+        <v>2.56</v>
       </c>
       <c r="BZ5" t="n">
-        <v>2.68</v>
+        <v>2.66</v>
       </c>
       <c r="CA5" t="n">
         <v>3.59</v>
       </c>
       <c r="CB5" t="n">
-        <v>3.75</v>
+        <v>3.74</v>
       </c>
       <c r="CC5" t="n">
         <v>3.66</v>
@@ -2834,7 +2834,7 @@
         <v>1.31</v>
       </c>
       <c r="CF5" t="n">
-        <v>2.48</v>
+        <v>2.47</v>
       </c>
       <c r="CG5" t="n">
         <v>3.21</v>
@@ -2846,13 +2846,13 @@
         <v>2.21</v>
       </c>
       <c r="CJ5" t="n">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="CK5" t="n">
         <v>1.46</v>
       </c>
       <c r="CL5" t="n">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="CM5" t="n">
         <v>2.53</v>
@@ -2867,7 +2867,7 @@
         <v>1.74</v>
       </c>
       <c r="CQ5" t="n">
-        <v>2.77</v>
+        <v>2.76</v>
       </c>
       <c r="CR5" t="n">
         <v>1.36</v>
@@ -2882,10 +2882,10 @@
         <v>1.54</v>
       </c>
       <c r="CV5" t="n">
-        <v>2.32</v>
+        <v>2.33</v>
       </c>
       <c r="CW5" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="CX5" t="n">
         <v>1.55</v>
@@ -2912,13 +2912,13 @@
         <v>0.14</v>
       </c>
       <c r="DF5" t="n">
-        <v>1.1</v>
+        <v>1.14</v>
       </c>
       <c r="DG5" t="n">
-        <v>2.72</v>
+        <v>2.62</v>
       </c>
       <c r="DH5" t="n">
-        <v>95.75</v>
+        <v>96.62</v>
       </c>
       <c r="DI5" t="n">
         <v>0</v>
@@ -2927,61 +2927,61 @@
         <v>1.83</v>
       </c>
       <c r="DK5" t="n">
-        <v>4.86</v>
+        <v>4.76</v>
       </c>
       <c r="DL5" t="n">
-        <v>0.64</v>
+        <v>0.62</v>
       </c>
       <c r="DM5" t="n">
-        <v>47.07</v>
+        <v>47.03</v>
       </c>
       <c r="DN5" t="n">
-        <v>0.57</v>
+        <v>0.55</v>
       </c>
       <c r="DO5" t="n">
         <v>2.14</v>
       </c>
       <c r="DP5" t="n">
-        <v>10.61</v>
+        <v>10.69</v>
       </c>
       <c r="DQ5" t="n">
-        <v>11.08</v>
+        <v>11.11</v>
       </c>
       <c r="DR5" t="n">
-        <v>9.5</v>
+        <v>9.34</v>
       </c>
       <c r="DS5" t="n">
-        <v>0.14</v>
+        <v>0.17</v>
       </c>
       <c r="DT5" t="n">
-        <v>0.14</v>
+        <v>0.17</v>
       </c>
       <c r="DU5" t="n">
         <v>0</v>
       </c>
       <c r="DV5" t="n">
-        <v>51.04</v>
+        <v>51.03</v>
       </c>
       <c r="DW5" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DX5" t="n">
-        <v>13.36</v>
+        <v>13.27</v>
       </c>
       <c r="DY5" t="n">
-        <v>8.960000000000001</v>
+        <v>8.859999999999999</v>
       </c>
       <c r="DZ5" t="n">
-        <v>4.39</v>
+        <v>4.41</v>
       </c>
       <c r="EA5" t="n">
-        <v>19.04</v>
+        <v>19.14</v>
       </c>
       <c r="EB5" t="n">
         <v>1.49</v>
       </c>
       <c r="EC5" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
     </row>
     <row r="6">
@@ -7424,13 +7424,13 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C17" t="n">
         <v>14</v>
       </c>
       <c r="D17" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
@@ -7517,49 +7517,49 @@
         <v>0.07000000000000001</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="AH17" t="n">
-        <v>2.43</v>
+        <v>2.53</v>
       </c>
       <c r="AI17" t="n">
-        <v>96.20999999999999</v>
+        <v>96</v>
       </c>
       <c r="AJ17" t="n">
         <v>0.07000000000000001</v>
       </c>
       <c r="AK17" t="n">
-        <v>2.14</v>
+        <v>2.07</v>
       </c>
       <c r="AL17" t="n">
-        <v>4.57</v>
+        <v>4.67</v>
       </c>
       <c r="AM17" t="n">
-        <v>0.29</v>
+        <v>0.4</v>
       </c>
       <c r="AN17" t="n">
-        <v>47.36</v>
+        <v>47.27</v>
       </c>
       <c r="AO17" t="n">
-        <v>0.57</v>
+        <v>0.53</v>
       </c>
       <c r="AP17" t="n">
-        <v>1.64</v>
+        <v>1.67</v>
       </c>
       <c r="AQ17" t="n">
-        <v>11.93</v>
+        <v>12</v>
       </c>
       <c r="AR17" t="n">
-        <v>11.07</v>
+        <v>11.13</v>
       </c>
       <c r="AS17" t="n">
-        <v>9.140000000000001</v>
+        <v>8.93</v>
       </c>
       <c r="AT17" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="AU17" t="n">
-        <v>1.36</v>
+        <v>1.27</v>
       </c>
       <c r="AV17" t="n">
         <v>0.07000000000000001</v>
@@ -7571,82 +7571,82 @@
         <v>0</v>
       </c>
       <c r="AY17" t="n">
-        <v>48.29</v>
+        <v>48.33</v>
       </c>
       <c r="AZ17" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="BA17" t="n">
-        <v>11</v>
+        <v>10.6</v>
       </c>
       <c r="BB17" t="n">
-        <v>7.36</v>
+        <v>7.13</v>
       </c>
       <c r="BC17" t="n">
-        <v>3.64</v>
+        <v>3.47</v>
       </c>
       <c r="BD17" t="n">
-        <v>19.43</v>
+        <v>19.6</v>
       </c>
       <c r="BE17" t="n">
-        <v>1.3</v>
+        <v>1.26</v>
       </c>
       <c r="BF17" t="n">
-        <v>1.86</v>
+        <v>1.8</v>
       </c>
       <c r="BG17" t="n">
-        <v>2.93</v>
+        <v>2.9</v>
       </c>
       <c r="BH17" t="n">
-        <v>9.57</v>
+        <v>9.52</v>
       </c>
       <c r="BI17" t="n">
-        <v>2.93</v>
+        <v>2.9</v>
       </c>
       <c r="BJ17" t="n">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="BK17" t="n">
-        <v>0.68</v>
+        <v>0.66</v>
       </c>
       <c r="BL17" t="n">
         <v>0.86</v>
       </c>
       <c r="BM17" t="n">
-        <v>0.68</v>
+        <v>0.66</v>
       </c>
       <c r="BN17" t="n">
-        <v>1.54</v>
+        <v>1.52</v>
       </c>
       <c r="BO17" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="BP17" t="n">
-        <v>3.61</v>
+        <v>3.62</v>
       </c>
       <c r="BQ17" t="n">
-        <v>5.46</v>
+        <v>5.41</v>
       </c>
       <c r="BR17" t="n">
-        <v>92.86</v>
+        <v>93.09999999999999</v>
       </c>
       <c r="BS17" t="n">
-        <v>78.56999999999999</v>
+        <v>79.31</v>
       </c>
       <c r="BT17" t="n">
-        <v>50</v>
+        <v>48.28</v>
       </c>
       <c r="BU17" t="n">
-        <v>35.71</v>
+        <v>34.48</v>
       </c>
       <c r="BV17" t="n">
-        <v>25</v>
+        <v>24.14</v>
       </c>
       <c r="BW17" t="n">
-        <v>7.14</v>
+        <v>6.9</v>
       </c>
       <c r="BX17" t="n">
-        <v>64.29000000000001</v>
+        <v>62.07</v>
       </c>
       <c r="BY17" t="n">
         <v>2.87</v>
@@ -7655,16 +7655,16 @@
         <v>3.07</v>
       </c>
       <c r="CA17" t="n">
-        <v>3.73</v>
+        <v>3.72</v>
       </c>
       <c r="CB17" t="n">
-        <v>3.8</v>
+        <v>3.79</v>
       </c>
       <c r="CC17" t="n">
-        <v>4.34</v>
+        <v>4.26</v>
       </c>
       <c r="CD17" t="n">
-        <v>4.77</v>
+        <v>4.66</v>
       </c>
       <c r="CE17" t="n">
         <v>1.31</v>
@@ -7679,7 +7679,7 @@
         <v>1.51</v>
       </c>
       <c r="CI17" t="n">
-        <v>2.16</v>
+        <v>2.17</v>
       </c>
       <c r="CJ17" t="n">
         <v>1.64</v>
@@ -7709,7 +7709,7 @@
         <v>1.35</v>
       </c>
       <c r="CS17" t="n">
-        <v>2.57</v>
+        <v>2.56</v>
       </c>
       <c r="CT17" t="n">
         <v>3.23</v>
@@ -7718,7 +7718,7 @@
         <v>1.53</v>
       </c>
       <c r="CV17" t="n">
-        <v>2.29</v>
+        <v>2.3</v>
       </c>
       <c r="CW17" t="n">
         <v>1.68</v>
@@ -7751,40 +7751,40 @@
         <v>1.14</v>
       </c>
       <c r="DG17" t="n">
-        <v>2.5</v>
+        <v>2.55</v>
       </c>
       <c r="DH17" t="n">
-        <v>97.03</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="DI17" t="n">
         <v>0.07000000000000001</v>
       </c>
       <c r="DJ17" t="n">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="DK17" t="n">
-        <v>4.43</v>
+        <v>4.49</v>
       </c>
       <c r="DL17" t="n">
-        <v>0.22</v>
+        <v>0.27</v>
       </c>
       <c r="DM17" t="n">
-        <v>48.14</v>
+        <v>48.07</v>
       </c>
       <c r="DN17" t="n">
-        <v>0.5</v>
+        <v>0.48</v>
       </c>
       <c r="DO17" t="n">
-        <v>1.67</v>
+        <v>1.69</v>
       </c>
       <c r="DP17" t="n">
-        <v>10.89</v>
+        <v>10.97</v>
       </c>
       <c r="DQ17" t="n">
-        <v>11.78</v>
+        <v>11.79</v>
       </c>
       <c r="DR17" t="n">
-        <v>9.07</v>
+        <v>8.960000000000001</v>
       </c>
       <c r="DS17" t="n">
         <v>0.18</v>
@@ -7796,28 +7796,28 @@
         <v>0</v>
       </c>
       <c r="DV17" t="n">
-        <v>47.9</v>
+        <v>47.93</v>
       </c>
       <c r="DW17" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DX17" t="n">
-        <v>12.82</v>
+        <v>12.55</v>
       </c>
       <c r="DY17" t="n">
-        <v>8.609999999999999</v>
+        <v>8.449999999999999</v>
       </c>
       <c r="DZ17" t="n">
-        <v>4.22</v>
+        <v>4.11</v>
       </c>
       <c r="EA17" t="n">
-        <v>20.4</v>
+        <v>20.45</v>
       </c>
       <c r="EB17" t="n">
-        <v>1.46</v>
+        <v>1.43</v>
       </c>
       <c r="EC17" t="n">
-        <v>1.54</v>
+        <v>1.52</v>
       </c>
     </row>
   </sheetData>

--- a/data/teams/leagues/Averages_Belgium_Pro_League_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Belgium_Pro_League_2025-2026.xlsx
@@ -1379,10 +1379,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D2" t="n">
         <v>14</v>
@@ -1391,82 +1391,82 @@
         <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="G2" t="n">
-        <v>2.29</v>
+        <v>2.2</v>
       </c>
       <c r="H2" t="n">
-        <v>108.07</v>
+        <v>109.27</v>
       </c>
       <c r="I2" t="n">
         <v>0.07000000000000001</v>
       </c>
       <c r="J2" t="n">
-        <v>1.43</v>
+        <v>1.47</v>
       </c>
       <c r="K2" t="n">
-        <v>4.79</v>
+        <v>4.8</v>
       </c>
       <c r="L2" t="n">
-        <v>0.29</v>
+        <v>0.4</v>
       </c>
       <c r="M2" t="n">
-        <v>50.07</v>
+        <v>51.53</v>
       </c>
       <c r="N2" t="n">
-        <v>0.5</v>
+        <v>0.53</v>
       </c>
       <c r="O2" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="P2" t="n">
+        <v>9.07</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>13.2</v>
+      </c>
+      <c r="R2" t="n">
+        <v>6.33</v>
+      </c>
+      <c r="S2" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="T2" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="U2" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="V2" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="W2" t="n">
+        <v>0</v>
+      </c>
+      <c r="X2" t="n">
+        <v>49.53</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>15.33</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>10.07</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>5.27</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>23.47</v>
+      </c>
+      <c r="AD2" t="n">
         <v>1.71</v>
       </c>
-      <c r="P2" t="n">
-        <v>9.140000000000001</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>13.36</v>
-      </c>
-      <c r="R2" t="n">
-        <v>6.43</v>
-      </c>
-      <c r="S2" t="n">
-        <v>2</v>
-      </c>
-      <c r="T2" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="U2" t="n">
-        <v>0.43</v>
-      </c>
-      <c r="V2" t="n">
-        <v>0.43</v>
-      </c>
-      <c r="W2" t="n">
-        <v>0</v>
-      </c>
-      <c r="X2" t="n">
-        <v>48.57</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>0.14</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>14.64</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>9.710000000000001</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>4.93</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>23.36</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>1.64</v>
-      </c>
       <c r="AE2" t="n">
-        <v>1.21</v>
+        <v>1.27</v>
       </c>
       <c r="AF2" t="n">
         <v>0.14</v>
@@ -1550,67 +1550,67 @@
         <v>2.79</v>
       </c>
       <c r="BG2" t="n">
-        <v>2.75</v>
+        <v>2.79</v>
       </c>
       <c r="BH2" t="n">
-        <v>10.29</v>
+        <v>10.34</v>
       </c>
       <c r="BI2" t="n">
-        <v>2.75</v>
+        <v>2.79</v>
       </c>
       <c r="BJ2" t="n">
-        <v>0.57</v>
+        <v>0.55</v>
       </c>
       <c r="BK2" t="n">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="BL2" t="n">
-        <v>0.57</v>
+        <v>0.59</v>
       </c>
       <c r="BM2" t="n">
-        <v>0.64</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="BN2" t="n">
-        <v>1.21</v>
+        <v>1.28</v>
       </c>
       <c r="BO2" t="n">
-        <v>1.54</v>
+        <v>1.52</v>
       </c>
       <c r="BP2" t="n">
-        <v>4.21</v>
+        <v>4.34</v>
       </c>
       <c r="BQ2" t="n">
-        <v>5.5</v>
+        <v>5.45</v>
       </c>
       <c r="BR2" t="n">
-        <v>89.29000000000001</v>
+        <v>89.66</v>
       </c>
       <c r="BS2" t="n">
-        <v>85.70999999999999</v>
+        <v>86.20999999999999</v>
       </c>
       <c r="BT2" t="n">
-        <v>46.43</v>
+        <v>48.28</v>
       </c>
       <c r="BU2" t="n">
-        <v>25</v>
+        <v>27.59</v>
       </c>
       <c r="BV2" t="n">
-        <v>17.86</v>
+        <v>17.24</v>
       </c>
       <c r="BW2" t="n">
-        <v>7.14</v>
+        <v>6.9</v>
       </c>
       <c r="BX2" t="n">
-        <v>60.71</v>
+        <v>62.07</v>
       </c>
       <c r="BY2" t="n">
-        <v>2.45</v>
+        <v>2.42</v>
       </c>
       <c r="BZ2" t="n">
-        <v>2.59</v>
+        <v>2.56</v>
       </c>
       <c r="CA2" t="n">
-        <v>3.57</v>
+        <v>3.56</v>
       </c>
       <c r="CB2" t="n">
         <v>3.7</v>
@@ -1625,7 +1625,7 @@
         <v>1.32</v>
       </c>
       <c r="CF2" t="n">
-        <v>2.51</v>
+        <v>2.52</v>
       </c>
       <c r="CG2" t="n">
         <v>3.15</v>
@@ -1634,7 +1634,7 @@
         <v>1.48</v>
       </c>
       <c r="CI2" t="n">
-        <v>2.18</v>
+        <v>2.17</v>
       </c>
       <c r="CJ2" t="n">
         <v>1.65</v>
@@ -1658,34 +1658,34 @@
         <v>1.74</v>
       </c>
       <c r="CQ2" t="n">
-        <v>2.85</v>
+        <v>2.86</v>
       </c>
       <c r="CR2" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="CS2" t="n">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="CT2" t="n">
-        <v>3.19</v>
+        <v>3.18</v>
       </c>
       <c r="CU2" t="n">
         <v>1.51</v>
       </c>
       <c r="CV2" t="n">
-        <v>2.3</v>
+        <v>2.29</v>
       </c>
       <c r="CW2" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="CX2" t="n">
         <v>1.5</v>
       </c>
       <c r="CY2" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="CZ2" t="n">
-        <v>2.53</v>
+        <v>2.54</v>
       </c>
       <c r="DA2" t="n">
         <v>2.09</v>
@@ -1697,79 +1697,79 @@
         <v>1.79</v>
       </c>
       <c r="DD2" t="n">
-        <v>2.91</v>
+        <v>2.92</v>
       </c>
       <c r="DE2" t="n">
         <v>0.07000000000000001</v>
       </c>
       <c r="DF2" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="DG2" t="n">
-        <v>2.36</v>
+        <v>2.31</v>
       </c>
       <c r="DH2" t="n">
-        <v>105.57</v>
+        <v>106.28</v>
       </c>
       <c r="DI2" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DJ2" t="n">
-        <v>2.25</v>
+        <v>2.24</v>
       </c>
       <c r="DK2" t="n">
         <v>4.83</v>
       </c>
       <c r="DL2" t="n">
-        <v>0.43</v>
+        <v>0.48</v>
       </c>
       <c r="DM2" t="n">
-        <v>50.25</v>
+        <v>51</v>
       </c>
       <c r="DN2" t="n">
         <v>0.9</v>
       </c>
       <c r="DO2" t="n">
-        <v>2.07</v>
+        <v>2.14</v>
       </c>
       <c r="DP2" t="n">
-        <v>10.54</v>
+        <v>10.45</v>
       </c>
       <c r="DQ2" t="n">
-        <v>12.25</v>
+        <v>12.21</v>
       </c>
       <c r="DR2" t="n">
-        <v>6.82</v>
+        <v>6.75</v>
       </c>
       <c r="DS2" t="n">
-        <v>0.28</v>
+        <v>0.27</v>
       </c>
       <c r="DT2" t="n">
-        <v>0.28</v>
+        <v>0.27</v>
       </c>
       <c r="DU2" t="n">
         <v>0</v>
       </c>
       <c r="DV2" t="n">
-        <v>47.04</v>
+        <v>47.58</v>
       </c>
       <c r="DW2" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DX2" t="n">
-        <v>13.86</v>
+        <v>14.24</v>
       </c>
       <c r="DY2" t="n">
-        <v>9.5</v>
+        <v>9.69</v>
       </c>
       <c r="DZ2" t="n">
-        <v>4.36</v>
+        <v>4.56</v>
       </c>
       <c r="EA2" t="n">
-        <v>22.68</v>
+        <v>22.76</v>
       </c>
       <c r="EB2" t="n">
-        <v>1.55</v>
+        <v>1.59</v>
       </c>
       <c r="EC2" t="n">
         <v>2</v>
@@ -1782,13 +1782,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C3" t="n">
         <v>14</v>
       </c>
       <c r="D3" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E3" t="n">
         <v>0.07000000000000001</v>
@@ -1872,52 +1872,52 @@
         <v>1</v>
       </c>
       <c r="AF3" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.13</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.21</v>
+        <v>1.27</v>
       </c>
       <c r="AH3" t="n">
-        <v>3.43</v>
+        <v>3.2</v>
       </c>
       <c r="AI3" t="n">
-        <v>104.93</v>
+        <v>102.47</v>
       </c>
       <c r="AJ3" t="n">
         <v>0</v>
       </c>
       <c r="AK3" t="n">
-        <v>1.64</v>
+        <v>1.67</v>
       </c>
       <c r="AL3" t="n">
-        <v>5.86</v>
+        <v>5.6</v>
       </c>
       <c r="AM3" t="n">
-        <v>0.29</v>
+        <v>0.27</v>
       </c>
       <c r="AN3" t="n">
-        <v>57.14</v>
+        <v>55.2</v>
       </c>
       <c r="AO3" t="n">
-        <v>0.43</v>
+        <v>0.4</v>
       </c>
       <c r="AP3" t="n">
-        <v>2.43</v>
+        <v>2.4</v>
       </c>
       <c r="AQ3" t="n">
-        <v>9.710000000000001</v>
+        <v>10.2</v>
       </c>
       <c r="AR3" t="n">
-        <v>11</v>
+        <v>10.93</v>
       </c>
       <c r="AS3" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AT3" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AU3" t="n">
-        <v>1.64</v>
+        <v>1.67</v>
       </c>
       <c r="AV3" t="n">
         <v>0.07000000000000001</v>
@@ -1929,82 +1929,82 @@
         <v>0</v>
       </c>
       <c r="AY3" t="n">
-        <v>60.36</v>
+        <v>59.53</v>
       </c>
       <c r="AZ3" t="n">
         <v>0</v>
       </c>
       <c r="BA3" t="n">
-        <v>14.57</v>
+        <v>14</v>
       </c>
       <c r="BB3" t="n">
-        <v>9.5</v>
+        <v>9.07</v>
       </c>
       <c r="BC3" t="n">
-        <v>5.07</v>
+        <v>4.93</v>
       </c>
       <c r="BD3" t="n">
-        <v>18.71</v>
+        <v>18.4</v>
       </c>
       <c r="BE3" t="n">
-        <v>1.69</v>
+        <v>1.63</v>
       </c>
       <c r="BF3" t="n">
-        <v>1.64</v>
+        <v>1.67</v>
       </c>
       <c r="BG3" t="n">
-        <v>3.11</v>
+        <v>3.1</v>
       </c>
       <c r="BH3" t="n">
-        <v>10.68</v>
+        <v>10.76</v>
       </c>
       <c r="BI3" t="n">
-        <v>3.11</v>
+        <v>3.1</v>
       </c>
       <c r="BJ3" t="n">
-        <v>0.79</v>
+        <v>0.76</v>
       </c>
       <c r="BK3" t="n">
-        <v>0.46</v>
+        <v>0.52</v>
       </c>
       <c r="BL3" t="n">
         <v>0.86</v>
       </c>
       <c r="BM3" t="n">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="BN3" t="n">
-        <v>1.86</v>
+        <v>1.83</v>
       </c>
       <c r="BO3" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="BP3" t="n">
-        <v>4.79</v>
+        <v>4.9</v>
       </c>
       <c r="BQ3" t="n">
-        <v>5.89</v>
+        <v>5.86</v>
       </c>
       <c r="BR3" t="n">
         <v>100</v>
       </c>
       <c r="BS3" t="n">
-        <v>67.86</v>
+        <v>68.97</v>
       </c>
       <c r="BT3" t="n">
-        <v>57.14</v>
+        <v>58.62</v>
       </c>
       <c r="BU3" t="n">
-        <v>25</v>
+        <v>24.14</v>
       </c>
       <c r="BV3" t="n">
-        <v>21.43</v>
+        <v>20.69</v>
       </c>
       <c r="BW3" t="n">
-        <v>14.29</v>
+        <v>13.79</v>
       </c>
       <c r="BX3" t="n">
-        <v>57.14</v>
+        <v>58.62</v>
       </c>
       <c r="BY3" t="n">
         <v>1.44</v>
@@ -2019,55 +2019,55 @@
         <v>4.75</v>
       </c>
       <c r="CC3" t="n">
-        <v>1.86</v>
+        <v>1.84</v>
       </c>
       <c r="CD3" t="n">
-        <v>1.9</v>
+        <v>1.88</v>
       </c>
       <c r="CE3" t="n">
         <v>1.26</v>
       </c>
       <c r="CF3" t="n">
-        <v>2.26</v>
+        <v>2.25</v>
       </c>
       <c r="CG3" t="n">
-        <v>3.51</v>
+        <v>3.52</v>
       </c>
       <c r="CH3" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="CI3" t="n">
-        <v>2.12</v>
+        <v>2.13</v>
       </c>
       <c r="CJ3" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="CK3" t="n">
         <v>1.47</v>
       </c>
       <c r="CL3" t="n">
-        <v>1.93</v>
+        <v>1.91</v>
       </c>
       <c r="CM3" t="n">
-        <v>2.52</v>
+        <v>2.54</v>
       </c>
       <c r="CN3" t="n">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="CO3" t="n">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="CP3" t="n">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="CQ3" t="n">
-        <v>2.41</v>
+        <v>2.4</v>
       </c>
       <c r="CR3" t="n">
         <v>1.33</v>
       </c>
       <c r="CS3" t="n">
-        <v>2.34</v>
+        <v>2.33</v>
       </c>
       <c r="CT3" t="n">
         <v>3.26</v>
@@ -2076,73 +2076,73 @@
         <v>1.63</v>
       </c>
       <c r="CV3" t="n">
-        <v>2.26</v>
+        <v>2.27</v>
       </c>
       <c r="CW3" t="n">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="CX3" t="n">
         <v>1.52</v>
       </c>
       <c r="CY3" t="n">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="CZ3" t="n">
         <v>2.49</v>
       </c>
       <c r="DA3" t="n">
-        <v>2.03</v>
+        <v>2.04</v>
       </c>
       <c r="DB3" t="n">
         <v>1.19</v>
       </c>
       <c r="DC3" t="n">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="DD3" t="n">
-        <v>2.48</v>
+        <v>2.47</v>
       </c>
       <c r="DE3" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.1</v>
       </c>
       <c r="DF3" t="n">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="DG3" t="n">
-        <v>3.78</v>
+        <v>3.65</v>
       </c>
       <c r="DH3" t="n">
-        <v>110.25</v>
+        <v>108.79</v>
       </c>
       <c r="DI3" t="n">
         <v>0</v>
       </c>
       <c r="DJ3" t="n">
-        <v>1.46</v>
+        <v>1.49</v>
       </c>
       <c r="DK3" t="n">
-        <v>6.68</v>
+        <v>6.52</v>
       </c>
       <c r="DL3" t="n">
-        <v>0.61</v>
+        <v>0.59</v>
       </c>
       <c r="DM3" t="n">
-        <v>61.92</v>
+        <v>60.76</v>
       </c>
       <c r="DN3" t="n">
-        <v>0.36</v>
+        <v>0.35</v>
       </c>
       <c r="DO3" t="n">
-        <v>2.9</v>
+        <v>2.86</v>
       </c>
       <c r="DP3" t="n">
-        <v>9.460000000000001</v>
+        <v>9.720000000000001</v>
       </c>
       <c r="DQ3" t="n">
-        <v>11.6</v>
+        <v>11.55</v>
       </c>
       <c r="DR3" t="n">
-        <v>7.18</v>
+        <v>7.31</v>
       </c>
       <c r="DS3" t="n">
         <v>0.04</v>
@@ -2154,28 +2154,28 @@
         <v>0</v>
       </c>
       <c r="DV3" t="n">
-        <v>63.08</v>
+        <v>62.55</v>
       </c>
       <c r="DW3" t="n">
         <v>0.07000000000000001</v>
       </c>
       <c r="DX3" t="n">
-        <v>16.54</v>
+        <v>16.17</v>
       </c>
       <c r="DY3" t="n">
-        <v>10.9</v>
+        <v>10.62</v>
       </c>
       <c r="DZ3" t="n">
-        <v>5.64</v>
+        <v>5.55</v>
       </c>
       <c r="EA3" t="n">
-        <v>20.86</v>
+        <v>20.62</v>
       </c>
       <c r="EB3" t="n">
-        <v>1.88</v>
+        <v>1.85</v>
       </c>
       <c r="EC3" t="n">
-        <v>1.32</v>
+        <v>1.35</v>
       </c>
     </row>
     <row r="4">
@@ -2185,13 +2185,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C4" t="n">
         <v>14</v>
       </c>
       <c r="D4" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E4" t="n">
         <v>0.07000000000000001</v>
@@ -2275,139 +2275,139 @@
         <v>1.86</v>
       </c>
       <c r="AF4" t="n">
-        <v>0.21</v>
+        <v>0.2</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="AI4" t="n">
-        <v>88</v>
+        <v>87.87</v>
       </c>
       <c r="AJ4" t="n">
-        <v>0.21</v>
+        <v>0.2</v>
       </c>
       <c r="AK4" t="n">
-        <v>2.64</v>
+        <v>2.53</v>
       </c>
       <c r="AL4" t="n">
-        <v>3.64</v>
+        <v>3.73</v>
       </c>
       <c r="AM4" t="n">
         <v>0</v>
       </c>
       <c r="AN4" t="n">
-        <v>39.93</v>
+        <v>40.2</v>
       </c>
       <c r="AO4" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="AP4" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AQ4" t="n">
+        <v>11.2</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>11.33</v>
+      </c>
+      <c r="AS4" t="n">
+        <v>10</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AU4" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="AV4" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="AW4" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="AX4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY4" t="n">
+        <v>45.73</v>
+      </c>
+      <c r="AZ4" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="BA4" t="n">
+        <v>10.6</v>
+      </c>
+      <c r="BB4" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BC4" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BD4" t="n">
+        <v>22.2</v>
+      </c>
+      <c r="BE4" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="BF4" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="BG4" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="BH4" t="n">
+        <v>9.380000000000001</v>
+      </c>
+      <c r="BI4" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="BJ4" t="n">
+        <v>0.59</v>
+      </c>
+      <c r="BK4" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="BL4" t="n">
+        <v>0.59</v>
+      </c>
+      <c r="BM4" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="BN4" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="BO4" t="n">
         <v>1</v>
       </c>
-      <c r="AP4" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="AQ4" t="n">
-        <v>11.43</v>
-      </c>
-      <c r="AR4" t="n">
-        <v>11.43</v>
-      </c>
-      <c r="AS4" t="n">
-        <v>10.36</v>
-      </c>
-      <c r="AT4" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AU4" t="n">
-        <v>0.86</v>
-      </c>
-      <c r="AV4" t="n">
-        <v>0.14</v>
-      </c>
-      <c r="AW4" t="n">
-        <v>0.14</v>
-      </c>
-      <c r="AX4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY4" t="n">
-        <v>45.36</v>
-      </c>
-      <c r="AZ4" t="n">
-        <v>0.29</v>
-      </c>
-      <c r="BA4" t="n">
-        <v>11</v>
-      </c>
-      <c r="BB4" t="n">
-        <v>6.57</v>
-      </c>
-      <c r="BC4" t="n">
-        <v>4.43</v>
-      </c>
-      <c r="BD4" t="n">
-        <v>21.93</v>
-      </c>
-      <c r="BE4" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="BF4" t="n">
-        <v>2.21</v>
-      </c>
-      <c r="BG4" t="n">
-        <v>2.46</v>
-      </c>
-      <c r="BH4" t="n">
-        <v>9.359999999999999</v>
-      </c>
-      <c r="BI4" t="n">
-        <v>2.46</v>
-      </c>
-      <c r="BJ4" t="n">
-        <v>0.61</v>
-      </c>
-      <c r="BK4" t="n">
-        <v>0.43</v>
-      </c>
-      <c r="BL4" t="n">
-        <v>0.54</v>
-      </c>
-      <c r="BM4" t="n">
-        <v>0.89</v>
-      </c>
-      <c r="BN4" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="BO4" t="n">
-        <v>1.04</v>
-      </c>
       <c r="BP4" t="n">
-        <v>3.79</v>
+        <v>3.86</v>
       </c>
       <c r="BQ4" t="n">
-        <v>4.54</v>
+        <v>4.52</v>
       </c>
       <c r="BR4" t="n">
-        <v>85.70999999999999</v>
+        <v>86.20999999999999</v>
       </c>
       <c r="BS4" t="n">
-        <v>67.86</v>
+        <v>68.97</v>
       </c>
       <c r="BT4" t="n">
-        <v>50</v>
+        <v>48.28</v>
       </c>
       <c r="BU4" t="n">
-        <v>28.57</v>
+        <v>27.59</v>
       </c>
       <c r="BV4" t="n">
-        <v>10.71</v>
+        <v>10.34</v>
       </c>
       <c r="BW4" t="n">
-        <v>3.57</v>
+        <v>3.45</v>
       </c>
       <c r="BX4" t="n">
-        <v>57.14</v>
+        <v>55.17</v>
       </c>
       <c r="BY4" t="n">
         <v>3.4</v>
@@ -2416,46 +2416,46 @@
         <v>3.59</v>
       </c>
       <c r="CA4" t="n">
-        <v>3.65</v>
+        <v>3.71</v>
       </c>
       <c r="CB4" t="n">
-        <v>3.77</v>
+        <v>3.83</v>
       </c>
       <c r="CC4" t="n">
-        <v>4.57</v>
+        <v>5.03</v>
       </c>
       <c r="CD4" t="n">
-        <v>4.79</v>
+        <v>5.29</v>
       </c>
       <c r="CE4" t="n">
         <v>1.35</v>
       </c>
       <c r="CF4" t="n">
-        <v>2.62</v>
+        <v>2.61</v>
       </c>
       <c r="CG4" t="n">
-        <v>3.05</v>
+        <v>3.07</v>
       </c>
       <c r="CH4" t="n">
         <v>1.45</v>
       </c>
       <c r="CI4" t="n">
-        <v>2.02</v>
+        <v>2.01</v>
       </c>
       <c r="CJ4" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="CK4" t="n">
         <v>1.55</v>
       </c>
       <c r="CL4" t="n">
-        <v>2</v>
+        <v>2.01</v>
       </c>
       <c r="CM4" t="n">
-        <v>2.34</v>
+        <v>2.35</v>
       </c>
       <c r="CN4" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="CO4" t="n">
         <v>1.26</v>
@@ -2464,37 +2464,37 @@
         <v>1.85</v>
       </c>
       <c r="CQ4" t="n">
-        <v>3.1</v>
+        <v>3.08</v>
       </c>
       <c r="CR4" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="CS4" t="n">
         <v>2.77</v>
       </c>
       <c r="CT4" t="n">
-        <v>3.08</v>
+        <v>3.09</v>
       </c>
       <c r="CU4" t="n">
         <v>1.47</v>
       </c>
       <c r="CV4" t="n">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="CW4" t="n">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="CX4" t="n">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="CY4" t="n">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="CZ4" t="n">
-        <v>2.36</v>
+        <v>2.37</v>
       </c>
       <c r="DA4" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="DB4" t="n">
         <v>1.28</v>
@@ -2503,82 +2503,82 @@
         <v>1.92</v>
       </c>
       <c r="DD4" t="n">
-        <v>3.21</v>
+        <v>3.2</v>
       </c>
       <c r="DE4" t="n">
         <v>0.14</v>
       </c>
       <c r="DF4" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="DG4" t="n">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="DH4" t="n">
-        <v>87.56999999999999</v>
+        <v>87.52</v>
       </c>
       <c r="DI4" t="n">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="DJ4" t="n">
-        <v>2.25</v>
+        <v>2.21</v>
       </c>
       <c r="DK4" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="DL4" t="n">
         <v>0.07000000000000001</v>
       </c>
       <c r="DM4" t="n">
-        <v>43.14</v>
+        <v>43.17</v>
       </c>
       <c r="DN4" t="n">
-        <v>0.72</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="DO4" t="n">
-        <v>1.5</v>
+        <v>1.59</v>
       </c>
       <c r="DP4" t="n">
-        <v>11.07</v>
+        <v>10.96</v>
       </c>
       <c r="DQ4" t="n">
-        <v>11.22</v>
+        <v>11.17</v>
       </c>
       <c r="DR4" t="n">
-        <v>10.39</v>
+        <v>10.21</v>
       </c>
       <c r="DS4" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DT4" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DU4" t="n">
         <v>0</v>
       </c>
       <c r="DV4" t="n">
-        <v>47.04</v>
+        <v>47.17</v>
       </c>
       <c r="DW4" t="n">
         <v>0.14</v>
       </c>
       <c r="DX4" t="n">
-        <v>10.96</v>
+        <v>10.76</v>
       </c>
       <c r="DY4" t="n">
-        <v>7</v>
+        <v>6.9</v>
       </c>
       <c r="DZ4" t="n">
-        <v>3.96</v>
+        <v>3.86</v>
       </c>
       <c r="EA4" t="n">
-        <v>22</v>
+        <v>22.14</v>
       </c>
       <c r="EB4" t="n">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="EC4" t="n">
-        <v>2.04</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5">
@@ -2991,10 +2991,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C6" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D6" t="n">
         <v>14</v>
@@ -3003,49 +3003,49 @@
         <v>0.07000000000000001</v>
       </c>
       <c r="F6" t="n">
-        <v>0.64</v>
+        <v>0.73</v>
       </c>
       <c r="G6" t="n">
-        <v>4.07</v>
+        <v>4</v>
       </c>
       <c r="H6" t="n">
-        <v>126.43</v>
+        <v>124.93</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>1.21</v>
+        <v>1.27</v>
       </c>
       <c r="K6" t="n">
-        <v>6.93</v>
+        <v>6.8</v>
       </c>
       <c r="L6" t="n">
-        <v>0.5</v>
+        <v>0.47</v>
       </c>
       <c r="M6" t="n">
-        <v>61.57</v>
+        <v>60.2</v>
       </c>
       <c r="N6" t="n">
-        <v>0.5</v>
+        <v>0.47</v>
       </c>
       <c r="O6" t="n">
-        <v>2.79</v>
+        <v>2.73</v>
       </c>
       <c r="P6" t="n">
-        <v>10.07</v>
+        <v>10</v>
       </c>
       <c r="Q6" t="n">
-        <v>13.21</v>
+        <v>12.87</v>
       </c>
       <c r="R6" t="n">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="S6" t="n">
-        <v>1.43</v>
+        <v>1.33</v>
       </c>
       <c r="T6" t="n">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="U6" t="n">
         <v>0</v>
@@ -3057,28 +3057,28 @@
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>62.86</v>
+        <v>61.07</v>
       </c>
       <c r="Y6" t="n">
         <v>0.07000000000000001</v>
       </c>
       <c r="Z6" t="n">
-        <v>18.14</v>
+        <v>17.8</v>
       </c>
       <c r="AA6" t="n">
-        <v>12</v>
+        <v>11.8</v>
       </c>
       <c r="AB6" t="n">
-        <v>6.14</v>
+        <v>6</v>
       </c>
       <c r="AC6" t="n">
-        <v>21.57</v>
+        <v>21.13</v>
       </c>
       <c r="AD6" t="n">
-        <v>2.02</v>
+        <v>1.98</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.07</v>
+        <v>1.13</v>
       </c>
       <c r="AF6" t="n">
         <v>0.21</v>
@@ -3162,67 +3162,67 @@
         <v>1.79</v>
       </c>
       <c r="BG6" t="n">
-        <v>2.93</v>
+        <v>2.86</v>
       </c>
       <c r="BH6" t="n">
-        <v>9.93</v>
+        <v>10.03</v>
       </c>
       <c r="BI6" t="n">
-        <v>2.93</v>
+        <v>2.86</v>
       </c>
       <c r="BJ6" t="n">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="BK6" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="BL6" t="n">
         <v>0.86</v>
       </c>
-      <c r="BL6" t="n">
-        <v>0.89</v>
-      </c>
       <c r="BM6" t="n">
-        <v>0.57</v>
+        <v>0.55</v>
       </c>
       <c r="BN6" t="n">
-        <v>1.46</v>
+        <v>1.41</v>
       </c>
       <c r="BO6" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="BP6" t="n">
-        <v>4.64</v>
+        <v>4.66</v>
       </c>
       <c r="BQ6" t="n">
-        <v>5.25</v>
+        <v>5.34</v>
       </c>
       <c r="BR6" t="n">
         <v>100</v>
       </c>
       <c r="BS6" t="n">
-        <v>89.29000000000001</v>
+        <v>86.20999999999999</v>
       </c>
       <c r="BT6" t="n">
-        <v>64.29000000000001</v>
+        <v>62.07</v>
       </c>
       <c r="BU6" t="n">
-        <v>17.86</v>
+        <v>17.24</v>
       </c>
       <c r="BV6" t="n">
-        <v>10.71</v>
+        <v>10.34</v>
       </c>
       <c r="BW6" t="n">
-        <v>3.57</v>
+        <v>3.45</v>
       </c>
       <c r="BX6" t="n">
-        <v>75</v>
+        <v>72.41</v>
       </c>
       <c r="BY6" t="n">
-        <v>1.8</v>
+        <v>1.82</v>
       </c>
       <c r="BZ6" t="n">
-        <v>1.87</v>
+        <v>1.89</v>
       </c>
       <c r="CA6" t="n">
-        <v>3.83</v>
+        <v>3.82</v>
       </c>
       <c r="CB6" t="n">
         <v>3.92</v>
@@ -3246,16 +3246,16 @@
         <v>1.51</v>
       </c>
       <c r="CI6" t="n">
-        <v>2.21</v>
+        <v>2.22</v>
       </c>
       <c r="CJ6" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="CK6" t="n">
         <v>1.5</v>
       </c>
       <c r="CL6" t="n">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="CM6" t="n">
         <v>2.44</v>
@@ -3270,7 +3270,7 @@
         <v>1.71</v>
       </c>
       <c r="CQ6" t="n">
-        <v>2.73</v>
+        <v>2.72</v>
       </c>
       <c r="CR6" t="n">
         <v>1.36</v>
@@ -3315,43 +3315,43 @@
         <v>0.14</v>
       </c>
       <c r="DF6" t="n">
-        <v>0.97</v>
+        <v>1</v>
       </c>
       <c r="DG6" t="n">
-        <v>3.22</v>
+        <v>3.21</v>
       </c>
       <c r="DH6" t="n">
-        <v>112.82</v>
+        <v>112.51</v>
       </c>
       <c r="DI6" t="n">
-        <v>0.04</v>
+        <v>0.03</v>
       </c>
       <c r="DJ6" t="n">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="DK6" t="n">
-        <v>5.57</v>
+        <v>5.55</v>
       </c>
       <c r="DL6" t="n">
-        <v>0.57</v>
+        <v>0.55</v>
       </c>
       <c r="DM6" t="n">
-        <v>54</v>
+        <v>53.55</v>
       </c>
       <c r="DN6" t="n">
-        <v>0.5</v>
+        <v>0.48</v>
       </c>
       <c r="DO6" t="n">
-        <v>2.33</v>
+        <v>2.31</v>
       </c>
       <c r="DP6" t="n">
-        <v>10</v>
+        <v>9.970000000000001</v>
       </c>
       <c r="DQ6" t="n">
-        <v>12.36</v>
+        <v>12.21</v>
       </c>
       <c r="DR6" t="n">
-        <v>7.14</v>
+        <v>7.31</v>
       </c>
       <c r="DS6" t="n">
         <v>0.07000000000000001</v>
@@ -3363,28 +3363,28 @@
         <v>0</v>
       </c>
       <c r="DV6" t="n">
-        <v>61.32</v>
+        <v>60.45</v>
       </c>
       <c r="DW6" t="n">
         <v>0.04</v>
       </c>
       <c r="DX6" t="n">
-        <v>15.54</v>
+        <v>15.45</v>
       </c>
       <c r="DY6" t="n">
-        <v>9.779999999999999</v>
+        <v>9.76</v>
       </c>
       <c r="DZ6" t="n">
-        <v>5.75</v>
+        <v>5.69</v>
       </c>
       <c r="EA6" t="n">
-        <v>20.18</v>
+        <v>20</v>
       </c>
       <c r="EB6" t="n">
-        <v>1.78</v>
+        <v>1.76</v>
       </c>
       <c r="EC6" t="n">
-        <v>1.43</v>
+        <v>1.45</v>
       </c>
     </row>
     <row r="7">
@@ -3394,94 +3394,94 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C7" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D7" t="n">
         <v>14</v>
       </c>
       <c r="E7" t="n">
-        <v>0.21</v>
+        <v>0.2</v>
       </c>
       <c r="F7" t="n">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="G7" t="n">
-        <v>2.43</v>
+        <v>2.4</v>
       </c>
       <c r="H7" t="n">
-        <v>89.20999999999999</v>
+        <v>87.67</v>
       </c>
       <c r="I7" t="n">
-        <v>0.21</v>
+        <v>0.2</v>
       </c>
       <c r="J7" t="n">
-        <v>2.21</v>
+        <v>2.2</v>
       </c>
       <c r="K7" t="n">
-        <v>4.36</v>
+        <v>4.4</v>
       </c>
       <c r="L7" t="n">
-        <v>0.21</v>
+        <v>0.27</v>
       </c>
       <c r="M7" t="n">
-        <v>49.07</v>
+        <v>48.73</v>
       </c>
       <c r="N7" t="n">
-        <v>0.64</v>
+        <v>0.6</v>
       </c>
       <c r="O7" t="n">
-        <v>1.93</v>
+        <v>2</v>
       </c>
       <c r="P7" t="n">
-        <v>10.5</v>
+        <v>10.33</v>
       </c>
       <c r="Q7" t="n">
-        <v>11.57</v>
+        <v>12.07</v>
       </c>
       <c r="R7" t="n">
-        <v>9.5</v>
+        <v>9.27</v>
       </c>
       <c r="S7" t="n">
-        <v>1.14</v>
+        <v>1.07</v>
       </c>
       <c r="T7" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="U7" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="V7" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="W7" t="n">
+        <v>0</v>
+      </c>
+      <c r="X7" t="n">
+        <v>48.2</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>10.6</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>6.87</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>3.73</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>21.4</v>
+      </c>
+      <c r="AD7" t="n">
         <v>1.29</v>
       </c>
-      <c r="U7" t="n">
-        <v>0.14</v>
-      </c>
-      <c r="V7" t="n">
-        <v>0.14</v>
-      </c>
-      <c r="W7" t="n">
-        <v>0</v>
-      </c>
-      <c r="X7" t="n">
-        <v>48.79</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>10.43</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>6.79</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>3.64</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>21.36</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>1.27</v>
-      </c>
       <c r="AE7" t="n">
-        <v>2.21</v>
+        <v>2.2</v>
       </c>
       <c r="AF7" t="n">
         <v>0.07000000000000001</v>
@@ -3565,70 +3565,70 @@
         <v>2.36</v>
       </c>
       <c r="BG7" t="n">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="BH7" t="n">
-        <v>10.82</v>
+        <v>10.76</v>
       </c>
       <c r="BI7" t="n">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="BJ7" t="n">
-        <v>0.61</v>
+        <v>0.59</v>
       </c>
       <c r="BK7" t="n">
-        <v>0.43</v>
+        <v>0.41</v>
       </c>
       <c r="BL7" t="n">
-        <v>0.64</v>
+        <v>0.66</v>
       </c>
       <c r="BM7" t="n">
-        <v>0.82</v>
+        <v>0.79</v>
       </c>
       <c r="BN7" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="BO7" t="n">
-        <v>1.04</v>
+        <v>1</v>
       </c>
       <c r="BP7" t="n">
-        <v>4.89</v>
+        <v>4.93</v>
       </c>
       <c r="BQ7" t="n">
-        <v>5.93</v>
+        <v>5.83</v>
       </c>
       <c r="BR7" t="n">
-        <v>96.43000000000001</v>
+        <v>96.55</v>
       </c>
       <c r="BS7" t="n">
-        <v>75</v>
+        <v>72.41</v>
       </c>
       <c r="BT7" t="n">
-        <v>39.29</v>
+        <v>37.93</v>
       </c>
       <c r="BU7" t="n">
-        <v>28.57</v>
+        <v>27.59</v>
       </c>
       <c r="BV7" t="n">
-        <v>10.71</v>
+        <v>10.34</v>
       </c>
       <c r="BW7" t="n">
         <v>0</v>
       </c>
       <c r="BX7" t="n">
-        <v>64.29000000000001</v>
+        <v>62.07</v>
       </c>
       <c r="BY7" t="n">
-        <v>2.77</v>
+        <v>2.79</v>
       </c>
       <c r="BZ7" t="n">
-        <v>2.93</v>
+        <v>2.94</v>
       </c>
       <c r="CA7" t="n">
-        <v>3.65</v>
+        <v>3.64</v>
       </c>
       <c r="CB7" t="n">
-        <v>3.76</v>
+        <v>3.75</v>
       </c>
       <c r="CC7" t="n">
         <v>3.81</v>
@@ -3661,7 +3661,7 @@
         <v>1.78</v>
       </c>
       <c r="CM7" t="n">
-        <v>2.72</v>
+        <v>2.71</v>
       </c>
       <c r="CN7" t="n">
         <v>2.07</v>
@@ -3679,7 +3679,7 @@
         <v>1.36</v>
       </c>
       <c r="CS7" t="n">
-        <v>2.6</v>
+        <v>2.61</v>
       </c>
       <c r="CT7" t="n">
         <v>3.18</v>
@@ -3700,10 +3700,10 @@
         <v>1.74</v>
       </c>
       <c r="CZ7" t="n">
-        <v>2.55</v>
+        <v>2.56</v>
       </c>
       <c r="DA7" t="n">
-        <v>2.1</v>
+        <v>2.09</v>
       </c>
       <c r="DB7" t="n">
         <v>1.24</v>
@@ -3712,19 +3712,19 @@
         <v>1.79</v>
       </c>
       <c r="DD7" t="n">
-        <v>2.88</v>
+        <v>2.89</v>
       </c>
       <c r="DE7" t="n">
         <v>0.14</v>
       </c>
       <c r="DF7" t="n">
-        <v>1.57</v>
+        <v>1.59</v>
       </c>
       <c r="DG7" t="n">
-        <v>2.68</v>
+        <v>2.66</v>
       </c>
       <c r="DH7" t="n">
-        <v>89.59999999999999</v>
+        <v>88.79000000000001</v>
       </c>
       <c r="DI7" t="n">
         <v>0.14</v>
@@ -3733,28 +3733,28 @@
         <v>2.28</v>
       </c>
       <c r="DK7" t="n">
-        <v>4.68</v>
+        <v>4.69</v>
       </c>
       <c r="DL7" t="n">
-        <v>0.25</v>
+        <v>0.28</v>
       </c>
       <c r="DM7" t="n">
-        <v>47.07</v>
+        <v>46.96</v>
       </c>
       <c r="DN7" t="n">
-        <v>0.72</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="DO7" t="n">
-        <v>2</v>
+        <v>2.03</v>
       </c>
       <c r="DP7" t="n">
-        <v>10.86</v>
+        <v>10.75</v>
       </c>
       <c r="DQ7" t="n">
-        <v>11.57</v>
+        <v>11.83</v>
       </c>
       <c r="DR7" t="n">
-        <v>9.07</v>
+        <v>8.970000000000001</v>
       </c>
       <c r="DS7" t="n">
         <v>0.07000000000000001</v>
@@ -3766,25 +3766,25 @@
         <v>0</v>
       </c>
       <c r="DV7" t="n">
-        <v>50.08</v>
+        <v>49.73</v>
       </c>
       <c r="DW7" t="n">
         <v>0</v>
       </c>
       <c r="DX7" t="n">
-        <v>10.14</v>
+        <v>10.24</v>
       </c>
       <c r="DY7" t="n">
-        <v>6.33</v>
+        <v>6.38</v>
       </c>
       <c r="DZ7" t="n">
-        <v>3.82</v>
+        <v>3.86</v>
       </c>
       <c r="EA7" t="n">
-        <v>21.54</v>
+        <v>21.55</v>
       </c>
       <c r="EB7" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="EC7" t="n">
         <v>2.28</v>
@@ -3797,94 +3797,94 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C8" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D8" t="n">
         <v>14</v>
       </c>
       <c r="E8" t="n">
-        <v>0.21</v>
+        <v>0.2</v>
       </c>
       <c r="F8" t="n">
         <v>0.93</v>
       </c>
       <c r="G8" t="n">
-        <v>2.86</v>
+        <v>3</v>
       </c>
       <c r="H8" t="n">
-        <v>97.86</v>
+        <v>97.13</v>
       </c>
       <c r="I8" t="n">
         <v>-0.07000000000000001</v>
       </c>
       <c r="J8" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="K8" t="n">
-        <v>5.71</v>
+        <v>6.07</v>
       </c>
       <c r="L8" t="n">
-        <v>0.29</v>
+        <v>0.33</v>
       </c>
       <c r="M8" t="n">
-        <v>54.64</v>
+        <v>55.4</v>
       </c>
       <c r="N8" t="n">
-        <v>0.36</v>
+        <v>0.33</v>
       </c>
       <c r="O8" t="n">
-        <v>2.86</v>
+        <v>3.07</v>
       </c>
       <c r="P8" t="n">
-        <v>10.29</v>
+        <v>10.27</v>
       </c>
       <c r="Q8" t="n">
-        <v>12.29</v>
+        <v>12.67</v>
       </c>
       <c r="R8" t="n">
-        <v>8.140000000000001</v>
+        <v>7.8</v>
       </c>
       <c r="S8" t="n">
-        <v>1</v>
+        <v>1.07</v>
       </c>
       <c r="T8" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="U8" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="V8" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>50.57</v>
+        <v>50.67</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="Z8" t="n">
-        <v>15.5</v>
+        <v>15.4</v>
       </c>
       <c r="AA8" t="n">
-        <v>10.71</v>
+        <v>10.73</v>
       </c>
       <c r="AB8" t="n">
-        <v>4.79</v>
+        <v>4.67</v>
       </c>
       <c r="AC8" t="n">
-        <v>19.79</v>
+        <v>19.47</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AF8" t="n">
         <v>0.14</v>
@@ -3968,70 +3968,70 @@
         <v>1.71</v>
       </c>
       <c r="BG8" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="BH8" t="n">
+        <v>10.28</v>
+      </c>
+      <c r="BI8" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="BJ8" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="BK8" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="BL8" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="BM8" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="BN8" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="BO8" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="BP8" t="n">
+        <v>4.93</v>
+      </c>
+      <c r="BQ8" t="n">
+        <v>5.31</v>
+      </c>
+      <c r="BR8" t="n">
+        <v>89.66</v>
+      </c>
+      <c r="BS8" t="n">
+        <v>75.86</v>
+      </c>
+      <c r="BT8" t="n">
+        <v>37.93</v>
+      </c>
+      <c r="BU8" t="n">
+        <v>24.14</v>
+      </c>
+      <c r="BV8" t="n">
+        <v>10.34</v>
+      </c>
+      <c r="BW8" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="BX8" t="n">
+        <v>37.93</v>
+      </c>
+      <c r="BY8" t="n">
         <v>2.61</v>
       </c>
-      <c r="BH8" t="n">
-        <v>10.18</v>
-      </c>
-      <c r="BI8" t="n">
-        <v>2.61</v>
-      </c>
-      <c r="BJ8" t="n">
-        <v>0.68</v>
-      </c>
-      <c r="BK8" t="n">
-        <v>0.68</v>
-      </c>
-      <c r="BL8" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="BM8" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="BN8" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="BO8" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="BP8" t="n">
-        <v>4.82</v>
-      </c>
-      <c r="BQ8" t="n">
-        <v>5.32</v>
-      </c>
-      <c r="BR8" t="n">
-        <v>89.29000000000001</v>
-      </c>
-      <c r="BS8" t="n">
-        <v>75</v>
-      </c>
-      <c r="BT8" t="n">
-        <v>35.71</v>
-      </c>
-      <c r="BU8" t="n">
-        <v>25</v>
-      </c>
-      <c r="BV8" t="n">
-        <v>10.71</v>
-      </c>
-      <c r="BW8" t="n">
-        <v>7.14</v>
-      </c>
-      <c r="BX8" t="n">
-        <v>35.71</v>
-      </c>
-      <c r="BY8" t="n">
-        <v>2.4</v>
-      </c>
       <c r="BZ8" t="n">
-        <v>2.49</v>
+        <v>2.69</v>
       </c>
       <c r="CA8" t="n">
-        <v>3.76</v>
+        <v>3.78</v>
       </c>
       <c r="CB8" t="n">
-        <v>3.83</v>
+        <v>3.86</v>
       </c>
       <c r="CC8" t="n">
         <v>3.85</v>
@@ -4040,19 +4040,19 @@
         <v>3.83</v>
       </c>
       <c r="CE8" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="CF8" t="n">
-        <v>2.31</v>
+        <v>2.3</v>
       </c>
       <c r="CG8" t="n">
-        <v>3.41</v>
+        <v>3.43</v>
       </c>
       <c r="CH8" t="n">
         <v>1.57</v>
       </c>
       <c r="CI8" t="n">
-        <v>2.37</v>
+        <v>2.38</v>
       </c>
       <c r="CJ8" t="n">
         <v>1.56</v>
@@ -4061,10 +4061,10 @@
         <v>1.36</v>
       </c>
       <c r="CL8" t="n">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="CM8" t="n">
-        <v>2.86</v>
+        <v>2.87</v>
       </c>
       <c r="CN8" t="n">
         <v>2.19</v>
@@ -4076,19 +4076,19 @@
         <v>1.62</v>
       </c>
       <c r="CQ8" t="n">
-        <v>2.51</v>
+        <v>2.49</v>
       </c>
       <c r="CR8" t="n">
         <v>1.34</v>
       </c>
       <c r="CS8" t="n">
-        <v>2.39</v>
+        <v>2.38</v>
       </c>
       <c r="CT8" t="n">
         <v>3.31</v>
       </c>
       <c r="CU8" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="CV8" t="n">
         <v>2.53</v>
@@ -4109,88 +4109,88 @@
         <v>2.21</v>
       </c>
       <c r="DB8" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="DC8" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="DD8" t="n">
-        <v>2.56</v>
+        <v>2.55</v>
       </c>
       <c r="DE8" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="DF8" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="DG8" t="n">
-        <v>2.43</v>
+        <v>2.52</v>
       </c>
       <c r="DH8" t="n">
-        <v>92.11</v>
+        <v>91.93000000000001</v>
       </c>
       <c r="DI8" t="n">
         <v>-0.04</v>
       </c>
       <c r="DJ8" t="n">
-        <v>1.61</v>
+        <v>1.59</v>
       </c>
       <c r="DK8" t="n">
-        <v>4.96</v>
+        <v>5.17</v>
       </c>
       <c r="DL8" t="n">
-        <v>0.32</v>
+        <v>0.34</v>
       </c>
       <c r="DM8" t="n">
-        <v>48.46</v>
+        <v>49.07</v>
       </c>
       <c r="DN8" t="n">
-        <v>0.29</v>
+        <v>0.27</v>
       </c>
       <c r="DO8" t="n">
-        <v>2.53</v>
+        <v>2.65</v>
       </c>
       <c r="DP8" t="n">
-        <v>11.72</v>
+        <v>11.66</v>
       </c>
       <c r="DQ8" t="n">
-        <v>12.14</v>
+        <v>12.35</v>
       </c>
       <c r="DR8" t="n">
-        <v>8.960000000000001</v>
+        <v>8.76</v>
       </c>
       <c r="DS8" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DT8" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DU8" t="n">
         <v>0</v>
       </c>
       <c r="DV8" t="n">
-        <v>48.54</v>
+        <v>48.66</v>
       </c>
       <c r="DW8" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DX8" t="n">
         <v>14.14</v>
       </c>
       <c r="DY8" t="n">
-        <v>9.539999999999999</v>
+        <v>9.59</v>
       </c>
       <c r="DZ8" t="n">
-        <v>4.61</v>
+        <v>4.55</v>
       </c>
       <c r="EA8" t="n">
-        <v>21.5</v>
+        <v>21.28</v>
       </c>
       <c r="EB8" t="n">
         <v>1.55</v>
       </c>
       <c r="EC8" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
     </row>
     <row r="9">
@@ -4200,13 +4200,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C9" t="n">
         <v>14</v>
       </c>
       <c r="D9" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E9" t="n">
         <v>0.21</v>
@@ -4293,49 +4293,49 @@
         <v>0.07000000000000001</v>
       </c>
       <c r="AG9" t="n">
-        <v>2.29</v>
+        <v>2.13</v>
       </c>
       <c r="AH9" t="n">
-        <v>2.64</v>
+        <v>2.4</v>
       </c>
       <c r="AI9" t="n">
-        <v>76.5</v>
+        <v>76.59999999999999</v>
       </c>
       <c r="AJ9" t="n">
         <v>0</v>
       </c>
       <c r="AK9" t="n">
-        <v>3.36</v>
+        <v>3.2</v>
       </c>
       <c r="AL9" t="n">
-        <v>4.57</v>
+        <v>4.47</v>
       </c>
       <c r="AM9" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="AN9" t="n">
-        <v>43.21</v>
+        <v>42</v>
       </c>
       <c r="AO9" t="n">
         <v>1.07</v>
       </c>
       <c r="AP9" t="n">
-        <v>1.93</v>
+        <v>1.73</v>
       </c>
       <c r="AQ9" t="n">
-        <v>15.71</v>
+        <v>15.4</v>
       </c>
       <c r="AR9" t="n">
-        <v>10.86</v>
+        <v>10.47</v>
       </c>
       <c r="AS9" t="n">
-        <v>8.859999999999999</v>
+        <v>9</v>
       </c>
       <c r="AT9" t="n">
-        <v>1.79</v>
+        <v>1.67</v>
       </c>
       <c r="AU9" t="n">
-        <v>0.86</v>
+        <v>0.93</v>
       </c>
       <c r="AV9" t="n">
         <v>0.07000000000000001</v>
@@ -4347,82 +4347,82 @@
         <v>0</v>
       </c>
       <c r="AY9" t="n">
-        <v>44.07</v>
+        <v>43.53</v>
       </c>
       <c r="AZ9" t="n">
         <v>0.07000000000000001</v>
       </c>
       <c r="BA9" t="n">
-        <v>12.07</v>
+        <v>11.93</v>
       </c>
       <c r="BB9" t="n">
-        <v>8.289999999999999</v>
+        <v>8.07</v>
       </c>
       <c r="BC9" t="n">
-        <v>3.79</v>
+        <v>3.87</v>
       </c>
       <c r="BD9" t="n">
-        <v>19</v>
+        <v>19.47</v>
       </c>
       <c r="BE9" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="BF9" t="n">
-        <v>3.29</v>
+        <v>3.13</v>
       </c>
       <c r="BG9" t="n">
-        <v>2.57</v>
+        <v>2.55</v>
       </c>
       <c r="BH9" t="n">
-        <v>11.11</v>
+        <v>11.17</v>
       </c>
       <c r="BI9" t="n">
-        <v>2.57</v>
+        <v>2.55</v>
       </c>
       <c r="BJ9" t="n">
-        <v>0.68</v>
+        <v>0.66</v>
       </c>
       <c r="BK9" t="n">
-        <v>0.5</v>
+        <v>0.48</v>
       </c>
       <c r="BL9" t="n">
-        <v>0.82</v>
+        <v>0.79</v>
       </c>
       <c r="BM9" t="n">
-        <v>0.57</v>
+        <v>0.62</v>
       </c>
       <c r="BN9" t="n">
-        <v>1.39</v>
+        <v>1.41</v>
       </c>
       <c r="BO9" t="n">
-        <v>1.18</v>
+        <v>1.14</v>
       </c>
       <c r="BP9" t="n">
-        <v>5.61</v>
+        <v>5.38</v>
       </c>
       <c r="BQ9" t="n">
-        <v>5.46</v>
+        <v>5.24</v>
       </c>
       <c r="BR9" t="n">
-        <v>92.86</v>
+        <v>93.09999999999999</v>
       </c>
       <c r="BS9" t="n">
-        <v>71.43000000000001</v>
+        <v>72.41</v>
       </c>
       <c r="BT9" t="n">
-        <v>50</v>
+        <v>48.28</v>
       </c>
       <c r="BU9" t="n">
-        <v>28.57</v>
+        <v>27.59</v>
       </c>
       <c r="BV9" t="n">
-        <v>10.71</v>
+        <v>10.34</v>
       </c>
       <c r="BW9" t="n">
-        <v>3.57</v>
+        <v>3.45</v>
       </c>
       <c r="BX9" t="n">
-        <v>53.57</v>
+        <v>51.72</v>
       </c>
       <c r="BY9" t="n">
         <v>2.85</v>
@@ -4434,13 +4434,13 @@
         <v>3.53</v>
       </c>
       <c r="CB9" t="n">
-        <v>3.6</v>
+        <v>3.61</v>
       </c>
       <c r="CC9" t="n">
         <v>4.43</v>
       </c>
       <c r="CD9" t="n">
-        <v>4.74</v>
+        <v>4.73</v>
       </c>
       <c r="CE9" t="n">
         <v>1.36</v>
@@ -4449,7 +4449,7 @@
         <v>2.7</v>
       </c>
       <c r="CG9" t="n">
-        <v>2.97</v>
+        <v>2.98</v>
       </c>
       <c r="CH9" t="n">
         <v>1.43</v>
@@ -4479,16 +4479,16 @@
         <v>1.91</v>
       </c>
       <c r="CQ9" t="n">
-        <v>3.25</v>
+        <v>3.23</v>
       </c>
       <c r="CR9" t="n">
         <v>1.38</v>
       </c>
       <c r="CS9" t="n">
-        <v>2.81</v>
+        <v>2.8</v>
       </c>
       <c r="CT9" t="n">
-        <v>3.1</v>
+        <v>3.11</v>
       </c>
       <c r="CU9" t="n">
         <v>1.46</v>
@@ -4497,19 +4497,19 @@
         <v>2.1</v>
       </c>
       <c r="CW9" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="CX9" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="CY9" t="n">
         <v>1.8</v>
       </c>
-      <c r="CX9" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="CY9" t="n">
-        <v>1.81</v>
-      </c>
       <c r="CZ9" t="n">
-        <v>2.46</v>
+        <v>2.47</v>
       </c>
       <c r="DA9" t="n">
-        <v>2.02</v>
+        <v>2.03</v>
       </c>
       <c r="DB9" t="n">
         <v>1.3</v>
@@ -4518,82 +4518,82 @@
         <v>1.96</v>
       </c>
       <c r="DD9" t="n">
-        <v>3.32</v>
+        <v>3.31</v>
       </c>
       <c r="DE9" t="n">
         <v>0.14</v>
       </c>
       <c r="DF9" t="n">
-        <v>2.18</v>
+        <v>2.1</v>
       </c>
       <c r="DG9" t="n">
-        <v>2.54</v>
+        <v>2.41</v>
       </c>
       <c r="DH9" t="n">
-        <v>80.04000000000001</v>
+        <v>79.95999999999999</v>
       </c>
       <c r="DI9" t="n">
-        <v>0.04</v>
+        <v>0.03</v>
       </c>
       <c r="DJ9" t="n">
-        <v>3.08</v>
+        <v>3</v>
       </c>
       <c r="DK9" t="n">
-        <v>4.93</v>
+        <v>4.87</v>
       </c>
       <c r="DL9" t="n">
-        <v>0.54</v>
+        <v>0.48</v>
       </c>
       <c r="DM9" t="n">
-        <v>42.71</v>
+        <v>42.1</v>
       </c>
       <c r="DN9" t="n">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="DO9" t="n">
-        <v>2.36</v>
+        <v>2.24</v>
       </c>
       <c r="DP9" t="n">
-        <v>15.78</v>
+        <v>15.62</v>
       </c>
       <c r="DQ9" t="n">
-        <v>11.68</v>
+        <v>11.45</v>
       </c>
       <c r="DR9" t="n">
-        <v>8.359999999999999</v>
+        <v>8.449999999999999</v>
       </c>
       <c r="DS9" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DT9" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DU9" t="n">
         <v>0</v>
       </c>
       <c r="DV9" t="n">
-        <v>45.28</v>
+        <v>44.96</v>
       </c>
       <c r="DW9" t="n">
         <v>0.04</v>
       </c>
       <c r="DX9" t="n">
-        <v>13.78</v>
+        <v>13.65</v>
       </c>
       <c r="DY9" t="n">
-        <v>9.460000000000001</v>
+        <v>9.31</v>
       </c>
       <c r="DZ9" t="n">
-        <v>4.32</v>
+        <v>4.35</v>
       </c>
       <c r="EA9" t="n">
-        <v>19.6</v>
+        <v>19.83</v>
       </c>
       <c r="EB9" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="EC9" t="n">
-        <v>3.04</v>
+        <v>2.97</v>
       </c>
     </row>
     <row r="10">
@@ -4603,13 +4603,13 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C10" t="n">
         <v>14</v>
       </c>
       <c r="D10" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
@@ -4693,139 +4693,139 @@
         <v>1.43</v>
       </c>
       <c r="AF10" t="n">
-        <v>0.14</v>
+        <v>0.2</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.71</v>
+        <v>1.6</v>
       </c>
       <c r="AH10" t="n">
-        <v>2.29</v>
+        <v>2.33</v>
       </c>
       <c r="AI10" t="n">
-        <v>81.43000000000001</v>
+        <v>83.2</v>
       </c>
       <c r="AJ10" t="n">
         <v>0.07000000000000001</v>
       </c>
       <c r="AK10" t="n">
-        <v>2.5</v>
+        <v>2.47</v>
       </c>
       <c r="AL10" t="n">
-        <v>3.57</v>
+        <v>3.8</v>
       </c>
       <c r="AM10" t="n">
-        <v>0.21</v>
+        <v>0.2</v>
       </c>
       <c r="AN10" t="n">
-        <v>36.21</v>
+        <v>36.13</v>
       </c>
       <c r="AO10" t="n">
-        <v>0.71</v>
+        <v>0.8</v>
       </c>
       <c r="AP10" t="n">
-        <v>1.29</v>
+        <v>1.47</v>
       </c>
       <c r="AQ10" t="n">
-        <v>12</v>
+        <v>11.93</v>
       </c>
       <c r="AR10" t="n">
-        <v>12.71</v>
+        <v>12.33</v>
       </c>
       <c r="AS10" t="n">
-        <v>8.43</v>
+        <v>8.869999999999999</v>
       </c>
       <c r="AT10" t="n">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="AU10" t="n">
-        <v>1.07</v>
+        <v>1.2</v>
       </c>
       <c r="AV10" t="n">
-        <v>0</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="AW10" t="n">
-        <v>0</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="AX10" t="n">
         <v>0</v>
       </c>
       <c r="AY10" t="n">
-        <v>34.5</v>
+        <v>34.67</v>
       </c>
       <c r="AZ10" t="n">
         <v>0.07000000000000001</v>
       </c>
       <c r="BA10" t="n">
-        <v>8.93</v>
+        <v>9.33</v>
       </c>
       <c r="BB10" t="n">
-        <v>6.57</v>
+        <v>6.8</v>
       </c>
       <c r="BC10" t="n">
-        <v>2.36</v>
+        <v>2.53</v>
       </c>
       <c r="BD10" t="n">
-        <v>20.86</v>
+        <v>21.13</v>
       </c>
       <c r="BE10" t="n">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="BF10" t="n">
-        <v>2.36</v>
+        <v>2.33</v>
       </c>
       <c r="BG10" t="n">
-        <v>1.89</v>
+        <v>1.97</v>
       </c>
       <c r="BH10" t="n">
-        <v>9.039999999999999</v>
+        <v>9.140000000000001</v>
       </c>
       <c r="BI10" t="n">
-        <v>1.89</v>
+        <v>1.97</v>
       </c>
       <c r="BJ10" t="n">
-        <v>0.5</v>
+        <v>0.48</v>
       </c>
       <c r="BK10" t="n">
-        <v>0.36</v>
+        <v>0.38</v>
       </c>
       <c r="BL10" t="n">
-        <v>0.46</v>
+        <v>0.48</v>
       </c>
       <c r="BM10" t="n">
-        <v>0.57</v>
+        <v>0.62</v>
       </c>
       <c r="BN10" t="n">
-        <v>1.04</v>
+        <v>1.1</v>
       </c>
       <c r="BO10" t="n">
         <v>0.86</v>
       </c>
       <c r="BP10" t="n">
-        <v>3.93</v>
+        <v>4.07</v>
       </c>
       <c r="BQ10" t="n">
-        <v>5.11</v>
+        <v>5.07</v>
       </c>
       <c r="BR10" t="n">
-        <v>71.43000000000001</v>
+        <v>72.41</v>
       </c>
       <c r="BS10" t="n">
-        <v>57.14</v>
+        <v>58.62</v>
       </c>
       <c r="BT10" t="n">
-        <v>39.29</v>
+        <v>41.38</v>
       </c>
       <c r="BU10" t="n">
-        <v>14.29</v>
+        <v>17.24</v>
       </c>
       <c r="BV10" t="n">
-        <v>7.14</v>
+        <v>6.9</v>
       </c>
       <c r="BW10" t="n">
         <v>0</v>
       </c>
       <c r="BX10" t="n">
-        <v>50</v>
+        <v>51.72</v>
       </c>
       <c r="BY10" t="n">
         <v>3.24</v>
@@ -4834,16 +4834,16 @@
         <v>3.32</v>
       </c>
       <c r="CA10" t="n">
-        <v>3.53</v>
+        <v>3.52</v>
       </c>
       <c r="CB10" t="n">
         <v>3.61</v>
       </c>
       <c r="CC10" t="n">
-        <v>4.69</v>
+        <v>4.62</v>
       </c>
       <c r="CD10" t="n">
-        <v>4.98</v>
+        <v>4.91</v>
       </c>
       <c r="CE10" t="n">
         <v>1.39</v>
@@ -4858,31 +4858,31 @@
         <v>1.39</v>
       </c>
       <c r="CI10" t="n">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="CJ10" t="n">
         <v>1.86</v>
       </c>
       <c r="CK10" t="n">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="CL10" t="n">
-        <v>2.01</v>
+        <v>2</v>
       </c>
       <c r="CM10" t="n">
-        <v>2.31</v>
+        <v>2.32</v>
       </c>
       <c r="CN10" t="n">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="CO10" t="n">
         <v>1.31</v>
       </c>
       <c r="CP10" t="n">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="CQ10" t="n">
-        <v>3.53</v>
+        <v>3.52</v>
       </c>
       <c r="CR10" t="n">
         <v>1.4</v>
@@ -4891,7 +4891,7 @@
         <v>2.92</v>
       </c>
       <c r="CT10" t="n">
-        <v>3.01</v>
+        <v>3.02</v>
       </c>
       <c r="CU10" t="n">
         <v>1.43</v>
@@ -4900,19 +4900,19 @@
         <v>1.99</v>
       </c>
       <c r="CW10" t="n">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="CX10" t="n">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="CY10" t="n">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="CZ10" t="n">
-        <v>2.32</v>
+        <v>2.33</v>
       </c>
       <c r="DA10" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="DB10" t="n">
         <v>1.34</v>
@@ -4921,79 +4921,79 @@
         <v>2.08</v>
       </c>
       <c r="DD10" t="n">
-        <v>3.64</v>
+        <v>3.62</v>
       </c>
       <c r="DE10" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.1</v>
       </c>
       <c r="DF10" t="n">
-        <v>1.25</v>
+        <v>1.21</v>
       </c>
       <c r="DG10" t="n">
         <v>2.79</v>
       </c>
       <c r="DH10" t="n">
-        <v>83.36</v>
+        <v>84.20999999999999</v>
       </c>
       <c r="DI10" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DJ10" t="n">
         <v>2.04</v>
       </c>
       <c r="DK10" t="n">
-        <v>4.68</v>
+        <v>4.76</v>
       </c>
       <c r="DL10" t="n">
-        <v>0.25</v>
+        <v>0.24</v>
       </c>
       <c r="DM10" t="n">
-        <v>41.07</v>
+        <v>40.86</v>
       </c>
       <c r="DN10" t="n">
-        <v>0.71</v>
+        <v>0.76</v>
       </c>
       <c r="DO10" t="n">
-        <v>1.9</v>
+        <v>1.97</v>
       </c>
       <c r="DP10" t="n">
-        <v>11.54</v>
+        <v>11.51</v>
       </c>
       <c r="DQ10" t="n">
-        <v>12.64</v>
+        <v>12.45</v>
       </c>
       <c r="DR10" t="n">
-        <v>8.140000000000001</v>
+        <v>8.380000000000001</v>
       </c>
       <c r="DS10" t="n">
-        <v>0</v>
+        <v>0.04</v>
       </c>
       <c r="DT10" t="n">
-        <v>0</v>
+        <v>0.04</v>
       </c>
       <c r="DU10" t="n">
         <v>0</v>
       </c>
       <c r="DV10" t="n">
-        <v>36.96</v>
+        <v>36.97</v>
       </c>
       <c r="DW10" t="n">
         <v>0.07000000000000001</v>
       </c>
       <c r="DX10" t="n">
-        <v>9.82</v>
+        <v>10</v>
       </c>
       <c r="DY10" t="n">
-        <v>6.97</v>
+        <v>7.07</v>
       </c>
       <c r="DZ10" t="n">
-        <v>2.86</v>
+        <v>2.93</v>
       </c>
       <c r="EA10" t="n">
-        <v>21.61</v>
+        <v>21.72</v>
       </c>
       <c r="EB10" t="n">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="EC10" t="n">
         <v>1.9</v>
@@ -5006,13 +5006,13 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C11" t="n">
         <v>14</v>
       </c>
       <c r="D11" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E11" t="n">
         <v>0.07000000000000001</v>
@@ -5096,139 +5096,139 @@
         <v>2.5</v>
       </c>
       <c r="AF11" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.43</v>
+        <v>1.8</v>
       </c>
       <c r="AH11" t="n">
-        <v>2.86</v>
+        <v>2.73</v>
       </c>
       <c r="AI11" t="n">
-        <v>92.93000000000001</v>
+        <v>95.06999999999999</v>
       </c>
       <c r="AJ11" t="n">
         <v>0</v>
       </c>
       <c r="AK11" t="n">
-        <v>2.57</v>
+        <v>2.93</v>
       </c>
       <c r="AL11" t="n">
-        <v>5.79</v>
+        <v>5.67</v>
       </c>
       <c r="AM11" t="n">
-        <v>0.29</v>
+        <v>0.27</v>
       </c>
       <c r="AN11" t="n">
-        <v>51.79</v>
+        <v>52.33</v>
       </c>
       <c r="AO11" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AP11" t="n">
         <v>2.93</v>
       </c>
       <c r="AQ11" t="n">
-        <v>14.64</v>
+        <v>14.87</v>
       </c>
       <c r="AR11" t="n">
-        <v>9.5</v>
+        <v>9.470000000000001</v>
       </c>
       <c r="AS11" t="n">
-        <v>8.859999999999999</v>
+        <v>8.67</v>
       </c>
       <c r="AT11" t="n">
-        <v>1.71</v>
+        <v>1.67</v>
       </c>
       <c r="AU11" t="n">
-        <v>1.29</v>
+        <v>1.2</v>
       </c>
       <c r="AV11" t="n">
-        <v>0.21</v>
+        <v>0.2</v>
       </c>
       <c r="AW11" t="n">
-        <v>0.21</v>
+        <v>0.2</v>
       </c>
       <c r="AX11" t="n">
         <v>0</v>
       </c>
       <c r="AY11" t="n">
-        <v>52.71</v>
+        <v>53.2</v>
       </c>
       <c r="AZ11" t="n">
-        <v>0.14</v>
+        <v>0.2</v>
       </c>
       <c r="BA11" t="n">
-        <v>12.64</v>
+        <v>12.93</v>
       </c>
       <c r="BB11" t="n">
-        <v>8.57</v>
+        <v>8.869999999999999</v>
       </c>
       <c r="BC11" t="n">
         <v>4.07</v>
       </c>
       <c r="BD11" t="n">
-        <v>20.79</v>
+        <v>21</v>
       </c>
       <c r="BE11" t="n">
-        <v>1.46</v>
+        <v>1.48</v>
       </c>
       <c r="BF11" t="n">
-        <v>2.43</v>
+        <v>2.73</v>
       </c>
       <c r="BG11" t="n">
-        <v>2.71</v>
+        <v>2.66</v>
       </c>
       <c r="BH11" t="n">
-        <v>11.11</v>
+        <v>11.03</v>
       </c>
       <c r="BI11" t="n">
-        <v>2.71</v>
+        <v>2.66</v>
       </c>
       <c r="BJ11" t="n">
-        <v>0.64</v>
+        <v>0.62</v>
       </c>
       <c r="BK11" t="n">
-        <v>0.5</v>
+        <v>0.48</v>
       </c>
       <c r="BL11" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="BM11" t="n">
-        <v>0.54</v>
+        <v>0.52</v>
       </c>
       <c r="BN11" t="n">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="BO11" t="n">
-        <v>1.14</v>
+        <v>1.1</v>
       </c>
       <c r="BP11" t="n">
-        <v>5.46</v>
+        <v>5.48</v>
       </c>
       <c r="BQ11" t="n">
-        <v>5.64</v>
+        <v>5.55</v>
       </c>
       <c r="BR11" t="n">
-        <v>89.29000000000001</v>
+        <v>89.66</v>
       </c>
       <c r="BS11" t="n">
-        <v>67.86</v>
+        <v>65.52</v>
       </c>
       <c r="BT11" t="n">
-        <v>42.86</v>
+        <v>41.38</v>
       </c>
       <c r="BU11" t="n">
-        <v>35.71</v>
+        <v>34.48</v>
       </c>
       <c r="BV11" t="n">
-        <v>17.86</v>
+        <v>17.24</v>
       </c>
       <c r="BW11" t="n">
-        <v>14.29</v>
+        <v>13.79</v>
       </c>
       <c r="BX11" t="n">
-        <v>46.43</v>
+        <v>44.83</v>
       </c>
       <c r="BY11" t="n">
         <v>1.9</v>
@@ -5237,16 +5237,16 @@
         <v>1.98</v>
       </c>
       <c r="CA11" t="n">
-        <v>3.62</v>
+        <v>3.61</v>
       </c>
       <c r="CB11" t="n">
         <v>3.74</v>
       </c>
       <c r="CC11" t="n">
-        <v>2.63</v>
+        <v>2.61</v>
       </c>
       <c r="CD11" t="n">
-        <v>2.96</v>
+        <v>2.92</v>
       </c>
       <c r="CE11" t="n">
         <v>1.33</v>
@@ -5255,25 +5255,25 @@
         <v>2.56</v>
       </c>
       <c r="CG11" t="n">
-        <v>3.06</v>
+        <v>3.07</v>
       </c>
       <c r="CH11" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="CI11" t="n">
         <v>2.11</v>
       </c>
       <c r="CJ11" t="n">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="CK11" t="n">
         <v>1.47</v>
       </c>
       <c r="CL11" t="n">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="CM11" t="n">
-        <v>2.55</v>
+        <v>2.54</v>
       </c>
       <c r="CN11" t="n">
         <v>1.95</v>
@@ -5282,10 +5282,10 @@
         <v>1.24</v>
       </c>
       <c r="CP11" t="n">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="CQ11" t="n">
-        <v>2.95</v>
+        <v>2.94</v>
       </c>
       <c r="CR11" t="n">
         <v>1.36</v>
@@ -5312,94 +5312,94 @@
         <v>1.81</v>
       </c>
       <c r="CZ11" t="n">
-        <v>2.51</v>
+        <v>2.52</v>
       </c>
       <c r="DA11" t="n">
-        <v>2.02</v>
+        <v>2.01</v>
       </c>
       <c r="DB11" t="n">
         <v>1.27</v>
       </c>
       <c r="DC11" t="n">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="DD11" t="n">
-        <v>3.1</v>
+        <v>3.09</v>
       </c>
       <c r="DE11" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DF11" t="n">
-        <v>1.57</v>
+        <v>1.76</v>
       </c>
       <c r="DG11" t="n">
-        <v>3.08</v>
+        <v>3</v>
       </c>
       <c r="DH11" t="n">
-        <v>101.25</v>
+        <v>102.07</v>
       </c>
       <c r="DI11" t="n">
         <v>0</v>
       </c>
       <c r="DJ11" t="n">
-        <v>2.6</v>
+        <v>2.79</v>
       </c>
       <c r="DK11" t="n">
-        <v>6.29</v>
+        <v>6.21</v>
       </c>
       <c r="DL11" t="n">
-        <v>0.5</v>
+        <v>0.48</v>
       </c>
       <c r="DM11" t="n">
-        <v>55.25</v>
+        <v>55.41</v>
       </c>
       <c r="DN11" t="n">
         <v>1</v>
       </c>
       <c r="DO11" t="n">
-        <v>3.22</v>
+        <v>3.21</v>
       </c>
       <c r="DP11" t="n">
-        <v>13.92</v>
+        <v>14.07</v>
       </c>
       <c r="DQ11" t="n">
-        <v>10.64</v>
+        <v>10.59</v>
       </c>
       <c r="DR11" t="n">
-        <v>8.07</v>
+        <v>8</v>
       </c>
       <c r="DS11" t="n">
-        <v>0.21</v>
+        <v>0.2</v>
       </c>
       <c r="DT11" t="n">
-        <v>0.21</v>
+        <v>0.2</v>
       </c>
       <c r="DU11" t="n">
         <v>0</v>
       </c>
       <c r="DV11" t="n">
-        <v>53.1</v>
+        <v>53.34</v>
       </c>
       <c r="DW11" t="n">
-        <v>0.11</v>
+        <v>0.14</v>
       </c>
       <c r="DX11" t="n">
-        <v>14.82</v>
+        <v>14.89</v>
       </c>
       <c r="DY11" t="n">
-        <v>10.07</v>
+        <v>10.17</v>
       </c>
       <c r="DZ11" t="n">
-        <v>4.75</v>
+        <v>4.73</v>
       </c>
       <c r="EA11" t="n">
-        <v>20.82</v>
+        <v>20.93</v>
       </c>
       <c r="EB11" t="n">
         <v>1.67</v>
       </c>
       <c r="EC11" t="n">
-        <v>2.47</v>
+        <v>2.62</v>
       </c>
     </row>
     <row r="12">
@@ -5409,10 +5409,10 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C12" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D12" t="n">
         <v>14</v>
@@ -5421,82 +5421,82 @@
         <v>0.07000000000000001</v>
       </c>
       <c r="F12" t="n">
-        <v>1.14</v>
+        <v>1.2</v>
       </c>
       <c r="G12" t="n">
-        <v>2.29</v>
+        <v>2.27</v>
       </c>
       <c r="H12" t="n">
-        <v>96.20999999999999</v>
+        <v>95.47</v>
       </c>
       <c r="I12" t="n">
         <v>0.07000000000000001</v>
       </c>
       <c r="J12" t="n">
-        <v>2.14</v>
+        <v>2.13</v>
       </c>
       <c r="K12" t="n">
-        <v>4.57</v>
+        <v>4.6</v>
       </c>
       <c r="L12" t="n">
-        <v>0.57</v>
+        <v>0.53</v>
       </c>
       <c r="M12" t="n">
-        <v>42.79</v>
+        <v>42.33</v>
       </c>
       <c r="N12" t="n">
-        <v>0.93</v>
+        <v>0.87</v>
       </c>
       <c r="O12" t="n">
-        <v>2.21</v>
+        <v>2.27</v>
       </c>
       <c r="P12" t="n">
-        <v>12.29</v>
+        <v>12.2</v>
       </c>
       <c r="Q12" t="n">
-        <v>12.07</v>
+        <v>11.93</v>
       </c>
       <c r="R12" t="n">
-        <v>7.5</v>
+        <v>7.53</v>
       </c>
       <c r="S12" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="T12" t="n">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="U12" t="n">
-        <v>0.29</v>
+        <v>0.27</v>
       </c>
       <c r="V12" t="n">
-        <v>0.29</v>
+        <v>0.27</v>
       </c>
       <c r="W12" t="n">
         <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>48.79</v>
+        <v>48.27</v>
       </c>
       <c r="Y12" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.13</v>
       </c>
       <c r="Z12" t="n">
-        <v>12.5</v>
+        <v>12.27</v>
       </c>
       <c r="AA12" t="n">
-        <v>7.5</v>
+        <v>7.47</v>
       </c>
       <c r="AB12" t="n">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="AC12" t="n">
-        <v>20.79</v>
+        <v>20.47</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="AE12" t="n">
-        <v>2</v>
+        <v>1.93</v>
       </c>
       <c r="AF12" t="n">
         <v>0</v>
@@ -5583,46 +5583,46 @@
         <v>2.14</v>
       </c>
       <c r="BH12" t="n">
-        <v>9.109999999999999</v>
+        <v>9.07</v>
       </c>
       <c r="BI12" t="n">
         <v>2.14</v>
       </c>
       <c r="BJ12" t="n">
-        <v>0.64</v>
+        <v>0.62</v>
       </c>
       <c r="BK12" t="n">
-        <v>0.43</v>
+        <v>0.41</v>
       </c>
       <c r="BL12" t="n">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="BM12" t="n">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="BN12" t="n">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="BO12" t="n">
-        <v>1.07</v>
+        <v>1.03</v>
       </c>
       <c r="BP12" t="n">
-        <v>3.96</v>
+        <v>3.93</v>
       </c>
       <c r="BQ12" t="n">
-        <v>5.11</v>
+        <v>5.1</v>
       </c>
       <c r="BR12" t="n">
-        <v>92.86</v>
+        <v>93.09999999999999</v>
       </c>
       <c r="BS12" t="n">
-        <v>71.43000000000001</v>
+        <v>72.41</v>
       </c>
       <c r="BT12" t="n">
-        <v>35.71</v>
+        <v>34.48</v>
       </c>
       <c r="BU12" t="n">
-        <v>14.29</v>
+        <v>13.79</v>
       </c>
       <c r="BV12" t="n">
         <v>0</v>
@@ -5631,19 +5631,19 @@
         <v>0</v>
       </c>
       <c r="BX12" t="n">
-        <v>42.86</v>
+        <v>44.83</v>
       </c>
       <c r="BY12" t="n">
-        <v>2.72</v>
+        <v>2.68</v>
       </c>
       <c r="BZ12" t="n">
-        <v>2.9</v>
+        <v>2.87</v>
       </c>
       <c r="CA12" t="n">
-        <v>3.53</v>
+        <v>3.51</v>
       </c>
       <c r="CB12" t="n">
-        <v>3.65</v>
+        <v>3.63</v>
       </c>
       <c r="CC12" t="n">
         <v>4.1</v>
@@ -5655,10 +5655,10 @@
         <v>1.35</v>
       </c>
       <c r="CF12" t="n">
-        <v>2.64</v>
+        <v>2.65</v>
       </c>
       <c r="CG12" t="n">
-        <v>3</v>
+        <v>2.99</v>
       </c>
       <c r="CH12" t="n">
         <v>1.44</v>
@@ -5676,34 +5676,34 @@
         <v>1.97</v>
       </c>
       <c r="CM12" t="n">
-        <v>2.43</v>
+        <v>2.42</v>
       </c>
       <c r="CN12" t="n">
         <v>1.88</v>
       </c>
       <c r="CO12" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="CP12" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="CQ12" t="n">
-        <v>3.11</v>
+        <v>3.13</v>
       </c>
       <c r="CR12" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="CS12" t="n">
-        <v>2.75</v>
+        <v>2.78</v>
       </c>
       <c r="CT12" t="n">
-        <v>3.14</v>
+        <v>3.12</v>
       </c>
       <c r="CU12" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="CV12" t="n">
-        <v>2.13</v>
+        <v>2.12</v>
       </c>
       <c r="CW12" t="n">
         <v>1.78</v>
@@ -5712,97 +5712,97 @@
         <v>1.58</v>
       </c>
       <c r="CY12" t="n">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="CZ12" t="n">
         <v>2.36</v>
       </c>
       <c r="DA12" t="n">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="DB12" t="n">
         <v>1.29</v>
       </c>
       <c r="DC12" t="n">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="DD12" t="n">
-        <v>3.23</v>
+        <v>3.27</v>
       </c>
       <c r="DE12" t="n">
         <v>0.04</v>
       </c>
       <c r="DF12" t="n">
-        <v>1.28</v>
+        <v>1.31</v>
       </c>
       <c r="DG12" t="n">
-        <v>2.25</v>
+        <v>2.24</v>
       </c>
       <c r="DH12" t="n">
-        <v>95.56999999999999</v>
+        <v>95.20999999999999</v>
       </c>
       <c r="DI12" t="n">
         <v>0.07000000000000001</v>
       </c>
       <c r="DJ12" t="n">
-        <v>2.04</v>
+        <v>2.03</v>
       </c>
       <c r="DK12" t="n">
-        <v>3.97</v>
+        <v>4</v>
       </c>
       <c r="DL12" t="n">
-        <v>0.43</v>
+        <v>0.41</v>
       </c>
       <c r="DM12" t="n">
-        <v>39.79</v>
+        <v>39.66</v>
       </c>
       <c r="DN12" t="n">
-        <v>0.68</v>
+        <v>0.66</v>
       </c>
       <c r="DO12" t="n">
-        <v>1.68</v>
+        <v>1.72</v>
       </c>
       <c r="DP12" t="n">
-        <v>12.96</v>
+        <v>12.9</v>
       </c>
       <c r="DQ12" t="n">
-        <v>11.89</v>
+        <v>11.82</v>
       </c>
       <c r="DR12" t="n">
         <v>7.79</v>
       </c>
       <c r="DS12" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="DT12" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="DU12" t="n">
         <v>0</v>
       </c>
       <c r="DV12" t="n">
-        <v>47.64</v>
+        <v>47.42</v>
       </c>
       <c r="DW12" t="n">
-        <v>0.11</v>
+        <v>0.13</v>
       </c>
       <c r="DX12" t="n">
-        <v>11.14</v>
+        <v>11.07</v>
       </c>
       <c r="DY12" t="n">
         <v>6.86</v>
       </c>
       <c r="DZ12" t="n">
-        <v>4.28</v>
+        <v>4.21</v>
       </c>
       <c r="EA12" t="n">
-        <v>20.68</v>
+        <v>20.52</v>
       </c>
       <c r="EB12" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="EC12" t="n">
-        <v>1.86</v>
+        <v>1.82</v>
       </c>
     </row>
     <row r="13">
@@ -5812,13 +5812,13 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C13" t="n">
         <v>14</v>
       </c>
       <c r="D13" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E13" t="n">
         <v>0.21</v>
@@ -5905,136 +5905,136 @@
         <v>0.07000000000000001</v>
       </c>
       <c r="AG13" t="n">
-        <v>0.93</v>
+        <v>0.87</v>
       </c>
       <c r="AH13" t="n">
-        <v>3.29</v>
+        <v>3.4</v>
       </c>
       <c r="AI13" t="n">
-        <v>99.36</v>
+        <v>100.73</v>
       </c>
       <c r="AJ13" t="n">
-        <v>0.21</v>
+        <v>0.2</v>
       </c>
       <c r="AK13" t="n">
-        <v>1.64</v>
+        <v>1.53</v>
       </c>
       <c r="AL13" t="n">
-        <v>5.57</v>
+        <v>5.73</v>
       </c>
       <c r="AM13" t="n">
-        <v>0.57</v>
+        <v>0.53</v>
       </c>
       <c r="AN13" t="n">
-        <v>52.71</v>
+        <v>55</v>
       </c>
       <c r="AO13" t="n">
-        <v>0.71</v>
+        <v>0.67</v>
       </c>
       <c r="AP13" t="n">
-        <v>2.29</v>
+        <v>2.33</v>
       </c>
       <c r="AQ13" t="n">
-        <v>11.71</v>
+        <v>11.47</v>
       </c>
       <c r="AR13" t="n">
-        <v>11.14</v>
+        <v>11.07</v>
       </c>
       <c r="AS13" t="n">
-        <v>8.640000000000001</v>
+        <v>8.529999999999999</v>
       </c>
       <c r="AT13" t="n">
         <v>1.07</v>
       </c>
       <c r="AU13" t="n">
-        <v>1.71</v>
+        <v>1.6</v>
       </c>
       <c r="AV13" t="n">
-        <v>0.29</v>
+        <v>0.27</v>
       </c>
       <c r="AW13" t="n">
-        <v>0.29</v>
+        <v>0.27</v>
       </c>
       <c r="AX13" t="n">
         <v>0</v>
       </c>
       <c r="AY13" t="n">
-        <v>55.21</v>
+        <v>55.8</v>
       </c>
       <c r="AZ13" t="n">
         <v>0</v>
       </c>
       <c r="BA13" t="n">
-        <v>13.43</v>
+        <v>13.07</v>
       </c>
       <c r="BB13" t="n">
-        <v>9.210000000000001</v>
+        <v>9.07</v>
       </c>
       <c r="BC13" t="n">
-        <v>4.21</v>
+        <v>4</v>
       </c>
       <c r="BD13" t="n">
-        <v>21.71</v>
+        <v>21.47</v>
       </c>
       <c r="BE13" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="BF13" t="n">
         <v>1.53</v>
       </c>
-      <c r="BF13" t="n">
-        <v>1.64</v>
-      </c>
       <c r="BG13" t="n">
-        <v>2.75</v>
+        <v>2.69</v>
       </c>
       <c r="BH13" t="n">
-        <v>10</v>
+        <v>10.1</v>
       </c>
       <c r="BI13" t="n">
-        <v>2.75</v>
+        <v>2.69</v>
       </c>
       <c r="BJ13" t="n">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="BK13" t="n">
-        <v>0.57</v>
+        <v>0.55</v>
       </c>
       <c r="BL13" t="n">
-        <v>0.61</v>
+        <v>0.59</v>
       </c>
       <c r="BM13" t="n">
-        <v>0.86</v>
+        <v>0.83</v>
       </c>
       <c r="BN13" t="n">
-        <v>1.46</v>
+        <v>1.41</v>
       </c>
       <c r="BO13" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="BP13" t="n">
-        <v>4.07</v>
+        <v>4.1</v>
       </c>
       <c r="BQ13" t="n">
-        <v>5.93</v>
+        <v>6</v>
       </c>
       <c r="BR13" t="n">
         <v>100</v>
       </c>
       <c r="BS13" t="n">
-        <v>82.14</v>
+        <v>79.31</v>
       </c>
       <c r="BT13" t="n">
-        <v>57.14</v>
+        <v>55.17</v>
       </c>
       <c r="BU13" t="n">
-        <v>25</v>
+        <v>24.14</v>
       </c>
       <c r="BV13" t="n">
-        <v>10.71</v>
+        <v>10.34</v>
       </c>
       <c r="BW13" t="n">
         <v>0</v>
       </c>
       <c r="BX13" t="n">
-        <v>57.14</v>
+        <v>55.17</v>
       </c>
       <c r="BY13" t="n">
         <v>2.2</v>
@@ -6043,16 +6043,16 @@
         <v>2.27</v>
       </c>
       <c r="CA13" t="n">
-        <v>3.66</v>
+        <v>3.65</v>
       </c>
       <c r="CB13" t="n">
         <v>3.78</v>
       </c>
       <c r="CC13" t="n">
-        <v>3.49</v>
+        <v>3.45</v>
       </c>
       <c r="CD13" t="n">
-        <v>3.71</v>
+        <v>3.68</v>
       </c>
       <c r="CE13" t="n">
         <v>1.31</v>
@@ -6070,34 +6070,34 @@
         <v>2.18</v>
       </c>
       <c r="CJ13" t="n">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="CK13" t="n">
         <v>1.47</v>
       </c>
       <c r="CL13" t="n">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="CM13" t="n">
-        <v>2.51</v>
+        <v>2.5</v>
       </c>
       <c r="CN13" t="n">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="CO13" t="n">
         <v>1.22</v>
       </c>
       <c r="CP13" t="n">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="CQ13" t="n">
-        <v>2.81</v>
+        <v>2.8</v>
       </c>
       <c r="CR13" t="n">
         <v>1.35</v>
       </c>
       <c r="CS13" t="n">
-        <v>2.64</v>
+        <v>2.63</v>
       </c>
       <c r="CT13" t="n">
         <v>3.24</v>
@@ -6109,13 +6109,13 @@
         <v>2.32</v>
       </c>
       <c r="CW13" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="CX13" t="n">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="CY13" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="CZ13" t="n">
         <v>2.43</v>
@@ -6127,7 +6127,7 @@
         <v>1.24</v>
       </c>
       <c r="DC13" t="n">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="DD13" t="n">
         <v>2.87</v>
@@ -6136,76 +6136,76 @@
         <v>0.14</v>
       </c>
       <c r="DF13" t="n">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="DG13" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="DH13" t="n">
-        <v>100.93</v>
+        <v>101.58</v>
       </c>
       <c r="DI13" t="n">
         <v>0.1</v>
       </c>
       <c r="DJ13" t="n">
-        <v>1.89</v>
+        <v>1.82</v>
       </c>
       <c r="DK13" t="n">
-        <v>5.47</v>
+        <v>5.55</v>
       </c>
       <c r="DL13" t="n">
-        <v>0.43</v>
+        <v>0.41</v>
       </c>
       <c r="DM13" t="n">
-        <v>54.32</v>
+        <v>55.45</v>
       </c>
       <c r="DN13" t="n">
-        <v>0.6</v>
+        <v>0.59</v>
       </c>
       <c r="DO13" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="DP13" t="n">
-        <v>11.07</v>
+        <v>10.97</v>
       </c>
       <c r="DQ13" t="n">
-        <v>11.46</v>
+        <v>11.42</v>
       </c>
       <c r="DR13" t="n">
-        <v>7.54</v>
+        <v>7.52</v>
       </c>
       <c r="DS13" t="n">
-        <v>0.25</v>
+        <v>0.24</v>
       </c>
       <c r="DT13" t="n">
-        <v>0.25</v>
+        <v>0.24</v>
       </c>
       <c r="DU13" t="n">
         <v>0</v>
       </c>
       <c r="DV13" t="n">
-        <v>54.6</v>
+        <v>54.93</v>
       </c>
       <c r="DW13" t="n">
         <v>0.07000000000000001</v>
       </c>
       <c r="DX13" t="n">
-        <v>14.43</v>
+        <v>14.21</v>
       </c>
       <c r="DY13" t="n">
-        <v>9.82</v>
+        <v>9.73</v>
       </c>
       <c r="DZ13" t="n">
-        <v>4.6</v>
+        <v>4.48</v>
       </c>
       <c r="EA13" t="n">
-        <v>22.36</v>
+        <v>22.21</v>
       </c>
       <c r="EB13" t="n">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="EC13" t="n">
-        <v>1.75</v>
+        <v>1.69</v>
       </c>
     </row>
     <row r="14">
@@ -6215,94 +6215,94 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C14" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D14" t="n">
         <v>14</v>
       </c>
       <c r="E14" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="F14" t="n">
-        <v>1.86</v>
+        <v>1.8</v>
       </c>
       <c r="G14" t="n">
-        <v>2.93</v>
+        <v>2.67</v>
       </c>
       <c r="H14" t="n">
-        <v>95.43000000000001</v>
+        <v>95.59999999999999</v>
       </c>
       <c r="I14" t="n">
         <v>0</v>
       </c>
       <c r="J14" t="n">
-        <v>2.43</v>
+        <v>2.33</v>
       </c>
       <c r="K14" t="n">
-        <v>5.57</v>
+        <v>5.87</v>
       </c>
       <c r="L14" t="n">
-        <v>0.29</v>
+        <v>0.2</v>
       </c>
       <c r="M14" t="n">
-        <v>52.07</v>
+        <v>52.53</v>
       </c>
       <c r="N14" t="n">
-        <v>0.36</v>
+        <v>0.33</v>
       </c>
       <c r="O14" t="n">
-        <v>2.64</v>
+        <v>2.4</v>
       </c>
       <c r="P14" t="n">
-        <v>11.21</v>
+        <v>10.87</v>
       </c>
       <c r="Q14" t="n">
-        <v>11.93</v>
+        <v>12.13</v>
       </c>
       <c r="R14" t="n">
-        <v>7.86</v>
+        <v>7.53</v>
       </c>
       <c r="S14" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="T14" t="n">
-        <v>1.43</v>
+        <v>1.33</v>
       </c>
       <c r="U14" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="V14" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="W14" t="n">
         <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>49.07</v>
+        <v>50.07</v>
       </c>
       <c r="Y14" t="n">
-        <v>0.29</v>
+        <v>0.27</v>
       </c>
       <c r="Z14" t="n">
-        <v>13.64</v>
+        <v>14</v>
       </c>
       <c r="AA14" t="n">
-        <v>8.710000000000001</v>
+        <v>9.07</v>
       </c>
       <c r="AB14" t="n">
         <v>4.93</v>
       </c>
       <c r="AC14" t="n">
-        <v>17.5</v>
+        <v>17.53</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.58</v>
+        <v>1.61</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.93</v>
+        <v>1.87</v>
       </c>
       <c r="AF14" t="n">
         <v>0.21</v>
@@ -6386,70 +6386,70 @@
         <v>2.07</v>
       </c>
       <c r="BG14" t="n">
-        <v>2.75</v>
+        <v>2.72</v>
       </c>
       <c r="BH14" t="n">
-        <v>10.14</v>
+        <v>10.24</v>
       </c>
       <c r="BI14" t="n">
-        <v>2.75</v>
+        <v>2.72</v>
       </c>
       <c r="BJ14" t="n">
-        <v>0.71</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="BK14" t="n">
-        <v>0.75</v>
+        <v>0.72</v>
       </c>
       <c r="BL14" t="n">
-        <v>0.71</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="BM14" t="n">
-        <v>0.57</v>
+        <v>0.62</v>
       </c>
       <c r="BN14" t="n">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="BO14" t="n">
-        <v>1.46</v>
+        <v>1.41</v>
       </c>
       <c r="BP14" t="n">
-        <v>4.93</v>
+        <v>4.72</v>
       </c>
       <c r="BQ14" t="n">
-        <v>5.18</v>
+        <v>4.97</v>
       </c>
       <c r="BR14" t="n">
-        <v>96.43000000000001</v>
+        <v>96.55</v>
       </c>
       <c r="BS14" t="n">
-        <v>78.56999999999999</v>
+        <v>79.31</v>
       </c>
       <c r="BT14" t="n">
-        <v>50</v>
+        <v>48.28</v>
       </c>
       <c r="BU14" t="n">
-        <v>32.14</v>
+        <v>31.03</v>
       </c>
       <c r="BV14" t="n">
-        <v>10.71</v>
+        <v>10.34</v>
       </c>
       <c r="BW14" t="n">
-        <v>3.57</v>
+        <v>3.45</v>
       </c>
       <c r="BX14" t="n">
-        <v>60.71</v>
+        <v>58.62</v>
       </c>
       <c r="BY14" t="n">
-        <v>2.38</v>
+        <v>2.34</v>
       </c>
       <c r="BZ14" t="n">
-        <v>2.47</v>
+        <v>2.42</v>
       </c>
       <c r="CA14" t="n">
         <v>3.49</v>
       </c>
       <c r="CB14" t="n">
-        <v>3.52</v>
+        <v>3.53</v>
       </c>
       <c r="CC14" t="n">
         <v>3.52</v>
@@ -6476,7 +6476,7 @@
         <v>1.74</v>
       </c>
       <c r="CK14" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="CL14" t="n">
         <v>1.91</v>
@@ -6485,7 +6485,7 @@
         <v>2.5</v>
       </c>
       <c r="CN14" t="n">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="CO14" t="n">
         <v>1.27</v>
@@ -6494,16 +6494,16 @@
         <v>1.88</v>
       </c>
       <c r="CQ14" t="n">
-        <v>3.15</v>
+        <v>3.13</v>
       </c>
       <c r="CR14" t="n">
         <v>1.38</v>
       </c>
       <c r="CS14" t="n">
-        <v>2.84</v>
+        <v>2.83</v>
       </c>
       <c r="CT14" t="n">
-        <v>3.1</v>
+        <v>3.11</v>
       </c>
       <c r="CU14" t="n">
         <v>1.45</v>
@@ -6512,103 +6512,103 @@
         <v>2.14</v>
       </c>
       <c r="CW14" t="n">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="CX14" t="n">
         <v>1.53</v>
       </c>
       <c r="CY14" t="n">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="CZ14" t="n">
-        <v>2.47</v>
+        <v>2.48</v>
       </c>
       <c r="DA14" t="n">
-        <v>1.94</v>
+        <v>1.96</v>
       </c>
       <c r="DB14" t="n">
         <v>1.3</v>
       </c>
       <c r="DC14" t="n">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="DD14" t="n">
-        <v>3.34</v>
+        <v>3.32</v>
       </c>
       <c r="DE14" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="DF14" t="n">
-        <v>1.68</v>
+        <v>1.66</v>
       </c>
       <c r="DG14" t="n">
-        <v>2.86</v>
+        <v>2.73</v>
       </c>
       <c r="DH14" t="n">
-        <v>94.36</v>
+        <v>94.48</v>
       </c>
       <c r="DI14" t="n">
-        <v>-0.04</v>
+        <v>-0.03</v>
       </c>
       <c r="DJ14" t="n">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="DK14" t="n">
-        <v>5.43</v>
+        <v>5.59</v>
       </c>
       <c r="DL14" t="n">
-        <v>0.5</v>
+        <v>0.45</v>
       </c>
       <c r="DM14" t="n">
-        <v>50.07</v>
+        <v>50.38</v>
       </c>
       <c r="DN14" t="n">
-        <v>0.46</v>
+        <v>0.45</v>
       </c>
       <c r="DO14" t="n">
-        <v>2.54</v>
+        <v>2.41</v>
       </c>
       <c r="DP14" t="n">
-        <v>11.6</v>
+        <v>11.42</v>
       </c>
       <c r="DQ14" t="n">
-        <v>10.72</v>
+        <v>10.86</v>
       </c>
       <c r="DR14" t="n">
-        <v>7.75</v>
+        <v>7.58</v>
       </c>
       <c r="DS14" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DT14" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DU14" t="n">
         <v>0</v>
       </c>
       <c r="DV14" t="n">
-        <v>48.75</v>
+        <v>49.28</v>
       </c>
       <c r="DW14" t="n">
         <v>0.14</v>
       </c>
       <c r="DX14" t="n">
-        <v>13.04</v>
+        <v>13.24</v>
       </c>
       <c r="DY14" t="n">
-        <v>8.6</v>
+        <v>8.789999999999999</v>
       </c>
       <c r="DZ14" t="n">
-        <v>4.43</v>
+        <v>4.45</v>
       </c>
       <c r="EA14" t="n">
-        <v>19.1</v>
+        <v>19.07</v>
       </c>
       <c r="EB14" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="EC14" t="n">
-        <v>2</v>
+        <v>1.97</v>
       </c>
     </row>
     <row r="15">
@@ -6618,13 +6618,13 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C15" t="n">
         <v>14</v>
       </c>
       <c r="D15" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E15" t="n">
         <v>0.21</v>
@@ -6708,52 +6708,52 @@
         <v>2.36</v>
       </c>
       <c r="AF15" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="AI15" t="n">
-        <v>83.64</v>
+        <v>83.2</v>
       </c>
       <c r="AJ15" t="n">
         <v>-0.07000000000000001</v>
       </c>
       <c r="AK15" t="n">
-        <v>1.86</v>
+        <v>1.93</v>
       </c>
       <c r="AL15" t="n">
-        <v>3.21</v>
+        <v>3.2</v>
       </c>
       <c r="AM15" t="n">
-        <v>0.29</v>
+        <v>0.27</v>
       </c>
       <c r="AN15" t="n">
-        <v>37.21</v>
+        <v>37.07</v>
       </c>
       <c r="AO15" t="n">
-        <v>0.57</v>
+        <v>0.6</v>
       </c>
       <c r="AP15" t="n">
-        <v>1.71</v>
+        <v>1.6</v>
       </c>
       <c r="AQ15" t="n">
-        <v>10.64</v>
+        <v>10.53</v>
       </c>
       <c r="AR15" t="n">
-        <v>11.07</v>
+        <v>11</v>
       </c>
       <c r="AS15" t="n">
-        <v>10.07</v>
+        <v>10</v>
       </c>
       <c r="AT15" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AU15" t="n">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="AV15" t="n">
         <v>0.07000000000000001</v>
@@ -6765,73 +6765,73 @@
         <v>0</v>
       </c>
       <c r="AY15" t="n">
-        <v>43.29</v>
+        <v>44.33</v>
       </c>
       <c r="AZ15" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="BA15" t="n">
-        <v>8.210000000000001</v>
+        <v>8.470000000000001</v>
       </c>
       <c r="BB15" t="n">
-        <v>5.79</v>
+        <v>5.8</v>
       </c>
       <c r="BC15" t="n">
-        <v>2.43</v>
+        <v>2.67</v>
       </c>
       <c r="BD15" t="n">
-        <v>16.86</v>
+        <v>18.07</v>
       </c>
       <c r="BE15" t="n">
-        <v>0.97</v>
+        <v>1</v>
       </c>
       <c r="BF15" t="n">
-        <v>1.71</v>
+        <v>1.8</v>
       </c>
       <c r="BG15" t="n">
         <v>2.14</v>
       </c>
       <c r="BH15" t="n">
-        <v>9.68</v>
+        <v>9.619999999999999</v>
       </c>
       <c r="BI15" t="n">
         <v>2.14</v>
       </c>
       <c r="BJ15" t="n">
-        <v>0.61</v>
+        <v>0.59</v>
       </c>
       <c r="BK15" t="n">
-        <v>0.64</v>
+        <v>0.62</v>
       </c>
       <c r="BL15" t="n">
-        <v>0.46</v>
+        <v>0.48</v>
       </c>
       <c r="BM15" t="n">
-        <v>0.43</v>
+        <v>0.45</v>
       </c>
       <c r="BN15" t="n">
-        <v>0.89</v>
+        <v>0.93</v>
       </c>
       <c r="BO15" t="n">
-        <v>1.25</v>
+        <v>1.21</v>
       </c>
       <c r="BP15" t="n">
-        <v>4.68</v>
+        <v>4.62</v>
       </c>
       <c r="BQ15" t="n">
         <v>5</v>
       </c>
       <c r="BR15" t="n">
-        <v>96.43000000000001</v>
+        <v>96.55</v>
       </c>
       <c r="BS15" t="n">
-        <v>67.86</v>
+        <v>68.97</v>
       </c>
       <c r="BT15" t="n">
-        <v>39.29</v>
+        <v>37.93</v>
       </c>
       <c r="BU15" t="n">
-        <v>10.71</v>
+        <v>10.34</v>
       </c>
       <c r="BV15" t="n">
         <v>0</v>
@@ -6840,7 +6840,7 @@
         <v>0</v>
       </c>
       <c r="BX15" t="n">
-        <v>32.14</v>
+        <v>34.48</v>
       </c>
       <c r="BY15" t="n">
         <v>3.04</v>
@@ -6849,34 +6849,34 @@
         <v>3.43</v>
       </c>
       <c r="CA15" t="n">
-        <v>3.55</v>
+        <v>3.54</v>
       </c>
       <c r="CB15" t="n">
-        <v>3.62</v>
+        <v>3.59</v>
       </c>
       <c r="CC15" t="n">
-        <v>4.39</v>
+        <v>4.35</v>
       </c>
       <c r="CD15" t="n">
-        <v>5.2</v>
+        <v>5.09</v>
       </c>
       <c r="CE15" t="n">
         <v>1.39</v>
       </c>
       <c r="CF15" t="n">
-        <v>2.83</v>
+        <v>2.84</v>
       </c>
       <c r="CG15" t="n">
-        <v>2.86</v>
+        <v>2.85</v>
       </c>
       <c r="CH15" t="n">
         <v>1.4</v>
       </c>
       <c r="CI15" t="n">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="CJ15" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="CK15" t="n">
         <v>1.51</v>
@@ -6885,7 +6885,7 @@
         <v>1.89</v>
       </c>
       <c r="CM15" t="n">
-        <v>2.5</v>
+        <v>2.49</v>
       </c>
       <c r="CN15" t="n">
         <v>1.91</v>
@@ -6894,22 +6894,22 @@
         <v>1.31</v>
       </c>
       <c r="CP15" t="n">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="CQ15" t="n">
-        <v>3.43</v>
+        <v>3.45</v>
       </c>
       <c r="CR15" t="n">
         <v>1.41</v>
       </c>
       <c r="CS15" t="n">
-        <v>2.95</v>
+        <v>2.96</v>
       </c>
       <c r="CT15" t="n">
-        <v>2.99</v>
+        <v>2.97</v>
       </c>
       <c r="CU15" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="CV15" t="n">
         <v>2.01</v>
@@ -6921,64 +6921,64 @@
         <v>1.57</v>
       </c>
       <c r="CY15" t="n">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="CZ15" t="n">
-        <v>2.39</v>
+        <v>2.38</v>
       </c>
       <c r="DA15" t="n">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="DB15" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="DC15" t="n">
-        <v>2.06</v>
+        <v>2.07</v>
       </c>
       <c r="DD15" t="n">
-        <v>3.58</v>
+        <v>3.61</v>
       </c>
       <c r="DE15" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="DF15" t="n">
-        <v>1.43</v>
+        <v>1.45</v>
       </c>
       <c r="DG15" t="n">
-        <v>1.82</v>
+        <v>1.86</v>
       </c>
       <c r="DH15" t="n">
-        <v>86.78</v>
+        <v>86.45</v>
       </c>
       <c r="DI15" t="n">
         <v>-0.04</v>
       </c>
       <c r="DJ15" t="n">
-        <v>2.4</v>
+        <v>2.41</v>
       </c>
       <c r="DK15" t="n">
-        <v>4.21</v>
+        <v>4.17</v>
       </c>
       <c r="DL15" t="n">
-        <v>0.54</v>
+        <v>0.52</v>
       </c>
       <c r="DM15" t="n">
-        <v>43.21</v>
+        <v>42.93</v>
       </c>
       <c r="DN15" t="n">
-        <v>0.82</v>
+        <v>0.83</v>
       </c>
       <c r="DO15" t="n">
-        <v>2.39</v>
+        <v>2.31</v>
       </c>
       <c r="DP15" t="n">
-        <v>10.82</v>
+        <v>10.76</v>
       </c>
       <c r="DQ15" t="n">
-        <v>12.07</v>
+        <v>12</v>
       </c>
       <c r="DR15" t="n">
-        <v>9.539999999999999</v>
+        <v>9.52</v>
       </c>
       <c r="DS15" t="n">
         <v>0.14</v>
@@ -6990,28 +6990,28 @@
         <v>0</v>
       </c>
       <c r="DV15" t="n">
-        <v>43.82</v>
+        <v>44.34</v>
       </c>
       <c r="DW15" t="n">
-        <v>0.22</v>
+        <v>0.21</v>
       </c>
       <c r="DX15" t="n">
-        <v>9.539999999999999</v>
+        <v>9.619999999999999</v>
       </c>
       <c r="DY15" t="n">
-        <v>6.46</v>
+        <v>6.45</v>
       </c>
       <c r="DZ15" t="n">
-        <v>3.07</v>
+        <v>3.17</v>
       </c>
       <c r="EA15" t="n">
-        <v>18.86</v>
+        <v>19.42</v>
       </c>
       <c r="EB15" t="n">
         <v>1.14</v>
       </c>
       <c r="EC15" t="n">
-        <v>2.03</v>
+        <v>2.07</v>
       </c>
     </row>
     <row r="16">
@@ -7021,94 +7021,94 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C16" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D16" t="n">
         <v>14</v>
       </c>
       <c r="E16" t="n">
-        <v>0.21</v>
+        <v>0.2</v>
       </c>
       <c r="F16" t="n">
-        <v>1.71</v>
+        <v>1.6</v>
       </c>
       <c r="G16" t="n">
-        <v>3.5</v>
+        <v>3.47</v>
       </c>
       <c r="H16" t="n">
-        <v>103.86</v>
+        <v>104.27</v>
       </c>
       <c r="I16" t="n">
         <v>0</v>
       </c>
       <c r="J16" t="n">
-        <v>1.93</v>
+        <v>1.8</v>
       </c>
       <c r="K16" t="n">
-        <v>6.57</v>
+        <v>6.47</v>
       </c>
       <c r="L16" t="n">
-        <v>0.36</v>
+        <v>0.47</v>
       </c>
       <c r="M16" t="n">
-        <v>55.79</v>
+        <v>55.13</v>
       </c>
       <c r="N16" t="n">
-        <v>0.21</v>
+        <v>0.2</v>
       </c>
       <c r="O16" t="n">
-        <v>3.07</v>
+        <v>3</v>
       </c>
       <c r="P16" t="n">
-        <v>11.93</v>
+        <v>11.73</v>
       </c>
       <c r="Q16" t="n">
-        <v>10.07</v>
+        <v>9.93</v>
       </c>
       <c r="R16" t="n">
-        <v>5.21</v>
+        <v>5.13</v>
       </c>
       <c r="S16" t="n">
-        <v>0.36</v>
+        <v>0.33</v>
       </c>
       <c r="T16" t="n">
-        <v>2.14</v>
+        <v>2.13</v>
       </c>
       <c r="U16" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="V16" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="W16" t="n">
         <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>51.36</v>
+        <v>51.2</v>
       </c>
       <c r="Y16" t="n">
         <v>0</v>
       </c>
       <c r="Z16" t="n">
-        <v>16.43</v>
+        <v>15.93</v>
       </c>
       <c r="AA16" t="n">
-        <v>10</v>
+        <v>9.73</v>
       </c>
       <c r="AB16" t="n">
-        <v>6.43</v>
+        <v>6.2</v>
       </c>
       <c r="AC16" t="n">
-        <v>21.36</v>
+        <v>21.13</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.89</v>
+        <v>1.84</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.93</v>
+        <v>1.8</v>
       </c>
       <c r="AF16" t="n">
         <v>0.07000000000000001</v>
@@ -7192,70 +7192,70 @@
         <v>2.86</v>
       </c>
       <c r="BG16" t="n">
-        <v>2.18</v>
+        <v>2.17</v>
       </c>
       <c r="BH16" t="n">
-        <v>9.359999999999999</v>
+        <v>9.380000000000001</v>
       </c>
       <c r="BI16" t="n">
-        <v>2.18</v>
+        <v>2.17</v>
       </c>
       <c r="BJ16" t="n">
-        <v>0.57</v>
+        <v>0.55</v>
       </c>
       <c r="BK16" t="n">
-        <v>0.32</v>
+        <v>0.31</v>
       </c>
       <c r="BL16" t="n">
-        <v>0.89</v>
+        <v>0.93</v>
       </c>
       <c r="BM16" t="n">
-        <v>0.39</v>
+        <v>0.38</v>
       </c>
       <c r="BN16" t="n">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="BO16" t="n">
-        <v>0.89</v>
+        <v>0.86</v>
       </c>
       <c r="BP16" t="n">
-        <v>4.64</v>
+        <v>4.69</v>
       </c>
       <c r="BQ16" t="n">
-        <v>4.71</v>
+        <v>4.69</v>
       </c>
       <c r="BR16" t="n">
-        <v>89.29000000000001</v>
+        <v>89.66</v>
       </c>
       <c r="BS16" t="n">
-        <v>71.43000000000001</v>
+        <v>72.41</v>
       </c>
       <c r="BT16" t="n">
-        <v>32.14</v>
+        <v>31.03</v>
       </c>
       <c r="BU16" t="n">
-        <v>14.29</v>
+        <v>13.79</v>
       </c>
       <c r="BV16" t="n">
-        <v>10.71</v>
+        <v>10.34</v>
       </c>
       <c r="BW16" t="n">
         <v>0</v>
       </c>
       <c r="BX16" t="n">
-        <v>46.43</v>
+        <v>44.83</v>
       </c>
       <c r="BY16" t="n">
-        <v>1.43</v>
+        <v>1.41</v>
       </c>
       <c r="BZ16" t="n">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="CA16" t="n">
-        <v>4.17</v>
+        <v>4.21</v>
       </c>
       <c r="CB16" t="n">
-        <v>4.34</v>
+        <v>4.38</v>
       </c>
       <c r="CC16" t="n">
         <v>1.85</v>
@@ -7267,28 +7267,28 @@
         <v>1.32</v>
       </c>
       <c r="CF16" t="n">
-        <v>2.55</v>
+        <v>2.54</v>
       </c>
       <c r="CG16" t="n">
-        <v>3.14</v>
+        <v>3.15</v>
       </c>
       <c r="CH16" t="n">
         <v>1.48</v>
       </c>
       <c r="CI16" t="n">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="CJ16" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="CK16" t="n">
         <v>1.48</v>
       </c>
       <c r="CL16" t="n">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="CM16" t="n">
-        <v>2.47</v>
+        <v>2.48</v>
       </c>
       <c r="CN16" t="n">
         <v>1.93</v>
@@ -7300,7 +7300,7 @@
         <v>1.8</v>
       </c>
       <c r="CQ16" t="n">
-        <v>2.88</v>
+        <v>2.87</v>
       </c>
       <c r="CR16" t="n">
         <v>1.37</v>
@@ -7309,25 +7309,25 @@
         <v>2.7</v>
       </c>
       <c r="CT16" t="n">
-        <v>3.15</v>
+        <v>3.16</v>
       </c>
       <c r="CU16" t="n">
         <v>1.49</v>
       </c>
       <c r="CV16" t="n">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="CW16" t="n">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="CX16" t="n">
         <v>1.57</v>
       </c>
       <c r="CY16" t="n">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="CZ16" t="n">
-        <v>2.37</v>
+        <v>2.38</v>
       </c>
       <c r="DA16" t="n">
         <v>1.92</v>
@@ -7345,43 +7345,43 @@
         <v>0.14</v>
       </c>
       <c r="DF16" t="n">
-        <v>1.82</v>
+        <v>1.76</v>
       </c>
       <c r="DG16" t="n">
         <v>3.07</v>
       </c>
       <c r="DH16" t="n">
-        <v>107.08</v>
+        <v>107.18</v>
       </c>
       <c r="DI16" t="n">
-        <v>0.04</v>
+        <v>0.03</v>
       </c>
       <c r="DJ16" t="n">
-        <v>2.43</v>
+        <v>2.35</v>
       </c>
       <c r="DK16" t="n">
-        <v>5.93</v>
+        <v>5.9</v>
       </c>
       <c r="DL16" t="n">
-        <v>0.43</v>
+        <v>0.48</v>
       </c>
       <c r="DM16" t="n">
-        <v>53.68</v>
+        <v>53.41</v>
       </c>
       <c r="DN16" t="n">
-        <v>0.61</v>
+        <v>0.59</v>
       </c>
       <c r="DO16" t="n">
-        <v>2.86</v>
+        <v>2.83</v>
       </c>
       <c r="DP16" t="n">
-        <v>12.89</v>
+        <v>12.76</v>
       </c>
       <c r="DQ16" t="n">
-        <v>9.57</v>
+        <v>9.51</v>
       </c>
       <c r="DR16" t="n">
-        <v>5.64</v>
+        <v>5.58</v>
       </c>
       <c r="DS16" t="n">
         <v>0.07000000000000001</v>
@@ -7393,28 +7393,28 @@
         <v>0</v>
       </c>
       <c r="DV16" t="n">
-        <v>53.82</v>
+        <v>53.66</v>
       </c>
       <c r="DW16" t="n">
-        <v>0.04</v>
+        <v>0.03</v>
       </c>
       <c r="DX16" t="n">
-        <v>15.07</v>
+        <v>14.86</v>
       </c>
       <c r="DY16" t="n">
-        <v>9.68</v>
+        <v>9.550000000000001</v>
       </c>
       <c r="DZ16" t="n">
-        <v>5.4</v>
+        <v>5.31</v>
       </c>
       <c r="EA16" t="n">
-        <v>20.75</v>
+        <v>20.65</v>
       </c>
       <c r="EB16" t="n">
-        <v>1.72</v>
+        <v>1.7</v>
       </c>
       <c r="EC16" t="n">
-        <v>2.4</v>
+        <v>2.31</v>
       </c>
     </row>
     <row r="17">

--- a/data/teams/leagues/Averages_Belgium_Pro_League_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Belgium_Pro_League_2025-2026.xlsx
@@ -1379,13 +1379,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C2" t="n">
         <v>15</v>
       </c>
       <c r="D2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
@@ -1469,139 +1469,139 @@
         <v>1.27</v>
       </c>
       <c r="AF2" t="n">
-        <v>0.14</v>
+        <v>0.2</v>
       </c>
       <c r="AG2" t="n">
-        <v>1.64</v>
+        <v>1.67</v>
       </c>
       <c r="AH2" t="n">
-        <v>2.43</v>
+        <v>2.4</v>
       </c>
       <c r="AI2" t="n">
-        <v>103.07</v>
+        <v>100.6</v>
       </c>
       <c r="AJ2" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="AK2" t="n">
-        <v>3.07</v>
+        <v>3</v>
       </c>
       <c r="AL2" t="n">
-        <v>4.86</v>
+        <v>5</v>
       </c>
       <c r="AM2" t="n">
-        <v>0.57</v>
+        <v>0.67</v>
       </c>
       <c r="AN2" t="n">
-        <v>50.43</v>
+        <v>49.33</v>
       </c>
       <c r="AO2" t="n">
-        <v>1.29</v>
+        <v>1.2</v>
       </c>
       <c r="AP2" t="n">
-        <v>2.43</v>
+        <v>2.6</v>
       </c>
       <c r="AQ2" t="n">
-        <v>11.93</v>
+        <v>11.87</v>
       </c>
       <c r="AR2" t="n">
-        <v>11.14</v>
+        <v>11.33</v>
       </c>
       <c r="AS2" t="n">
-        <v>7.21</v>
+        <v>7.2</v>
       </c>
       <c r="AT2" t="n">
-        <v>1</v>
+        <v>1.07</v>
       </c>
       <c r="AU2" t="n">
-        <v>1.21</v>
+        <v>1.33</v>
       </c>
       <c r="AV2" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="AW2" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="AX2" t="n">
         <v>0</v>
       </c>
       <c r="AY2" t="n">
-        <v>45.5</v>
+        <v>44.4</v>
       </c>
       <c r="AZ2" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="BA2" t="n">
-        <v>13.07</v>
+        <v>13.13</v>
       </c>
       <c r="BB2" t="n">
-        <v>9.289999999999999</v>
+        <v>9.27</v>
       </c>
       <c r="BC2" t="n">
-        <v>3.79</v>
+        <v>3.87</v>
       </c>
       <c r="BD2" t="n">
-        <v>22</v>
+        <v>21.53</v>
       </c>
       <c r="BE2" t="n">
         <v>1.46</v>
       </c>
       <c r="BF2" t="n">
-        <v>2.79</v>
+        <v>2.73</v>
       </c>
       <c r="BG2" t="n">
-        <v>2.79</v>
+        <v>2.87</v>
       </c>
       <c r="BH2" t="n">
-        <v>10.34</v>
+        <v>10.5</v>
       </c>
       <c r="BI2" t="n">
-        <v>2.79</v>
+        <v>2.87</v>
       </c>
       <c r="BJ2" t="n">
-        <v>0.55</v>
+        <v>0.57</v>
       </c>
       <c r="BK2" t="n">
-        <v>0.97</v>
+        <v>1.03</v>
       </c>
       <c r="BL2" t="n">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="BM2" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.67</v>
       </c>
       <c r="BN2" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="BO2" t="n">
-        <v>1.52</v>
+        <v>1.6</v>
       </c>
       <c r="BP2" t="n">
-        <v>4.34</v>
+        <v>4.43</v>
       </c>
       <c r="BQ2" t="n">
-        <v>5.45</v>
+        <v>5.53</v>
       </c>
       <c r="BR2" t="n">
-        <v>89.66</v>
+        <v>90</v>
       </c>
       <c r="BS2" t="n">
-        <v>86.20999999999999</v>
+        <v>86.67</v>
       </c>
       <c r="BT2" t="n">
-        <v>48.28</v>
+        <v>50</v>
       </c>
       <c r="BU2" t="n">
-        <v>27.59</v>
+        <v>30</v>
       </c>
       <c r="BV2" t="n">
-        <v>17.24</v>
+        <v>20</v>
       </c>
       <c r="BW2" t="n">
-        <v>6.9</v>
+        <v>6.67</v>
       </c>
       <c r="BX2" t="n">
-        <v>62.07</v>
+        <v>63.33</v>
       </c>
       <c r="BY2" t="n">
         <v>2.42</v>
@@ -1619,7 +1619,7 @@
         <v>3.39</v>
       </c>
       <c r="CD2" t="n">
-        <v>3.61</v>
+        <v>3.6</v>
       </c>
       <c r="CE2" t="n">
         <v>1.32</v>
@@ -1634,22 +1634,22 @@
         <v>1.48</v>
       </c>
       <c r="CI2" t="n">
-        <v>2.17</v>
+        <v>2.18</v>
       </c>
       <c r="CJ2" t="n">
         <v>1.65</v>
       </c>
       <c r="CK2" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="CL2" t="n">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="CM2" t="n">
-        <v>2.59</v>
+        <v>2.6</v>
       </c>
       <c r="CN2" t="n">
-        <v>2.02</v>
+        <v>2.03</v>
       </c>
       <c r="CO2" t="n">
         <v>1.22</v>
@@ -1658,7 +1658,7 @@
         <v>1.74</v>
       </c>
       <c r="CQ2" t="n">
-        <v>2.86</v>
+        <v>2.85</v>
       </c>
       <c r="CR2" t="n">
         <v>1.37</v>
@@ -1673,16 +1673,16 @@
         <v>1.51</v>
       </c>
       <c r="CV2" t="n">
-        <v>2.29</v>
+        <v>2.3</v>
       </c>
       <c r="CW2" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="CX2" t="n">
         <v>1.5</v>
       </c>
       <c r="CY2" t="n">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="CZ2" t="n">
         <v>2.54</v>
@@ -1697,19 +1697,19 @@
         <v>1.79</v>
       </c>
       <c r="DD2" t="n">
-        <v>2.92</v>
+        <v>2.91</v>
       </c>
       <c r="DE2" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.1</v>
       </c>
       <c r="DF2" t="n">
-        <v>1.24</v>
+        <v>1.27</v>
       </c>
       <c r="DG2" t="n">
-        <v>2.31</v>
+        <v>2.3</v>
       </c>
       <c r="DH2" t="n">
-        <v>106.28</v>
+        <v>104.94</v>
       </c>
       <c r="DI2" t="n">
         <v>0.1</v>
@@ -1718,58 +1718,58 @@
         <v>2.24</v>
       </c>
       <c r="DK2" t="n">
-        <v>4.83</v>
+        <v>4.9</v>
       </c>
       <c r="DL2" t="n">
-        <v>0.48</v>
+        <v>0.54</v>
       </c>
       <c r="DM2" t="n">
-        <v>51</v>
+        <v>50.43</v>
       </c>
       <c r="DN2" t="n">
-        <v>0.9</v>
+        <v>0.86</v>
       </c>
       <c r="DO2" t="n">
-        <v>2.14</v>
+        <v>2.24</v>
       </c>
       <c r="DP2" t="n">
-        <v>10.45</v>
+        <v>10.47</v>
       </c>
       <c r="DQ2" t="n">
-        <v>12.21</v>
+        <v>12.26</v>
       </c>
       <c r="DR2" t="n">
-        <v>6.75</v>
+        <v>6.76</v>
       </c>
       <c r="DS2" t="n">
-        <v>0.27</v>
+        <v>0.26</v>
       </c>
       <c r="DT2" t="n">
-        <v>0.27</v>
+        <v>0.26</v>
       </c>
       <c r="DU2" t="n">
         <v>0</v>
       </c>
       <c r="DV2" t="n">
-        <v>47.58</v>
+        <v>46.96</v>
       </c>
       <c r="DW2" t="n">
         <v>0.13</v>
       </c>
       <c r="DX2" t="n">
-        <v>14.24</v>
+        <v>14.23</v>
       </c>
       <c r="DY2" t="n">
-        <v>9.69</v>
+        <v>9.67</v>
       </c>
       <c r="DZ2" t="n">
-        <v>4.56</v>
+        <v>4.57</v>
       </c>
       <c r="EA2" t="n">
-        <v>22.76</v>
+        <v>22.5</v>
       </c>
       <c r="EB2" t="n">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="EC2" t="n">
         <v>2</v>
@@ -1782,61 +1782,61 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C3" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D3" t="n">
         <v>15</v>
       </c>
       <c r="E3" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.13</v>
       </c>
       <c r="F3" t="n">
-        <v>0.86</v>
+        <v>0.8</v>
       </c>
       <c r="G3" t="n">
-        <v>4.14</v>
+        <v>4.33</v>
       </c>
       <c r="H3" t="n">
-        <v>115.57</v>
+        <v>115.33</v>
       </c>
       <c r="I3" t="n">
         <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>1.29</v>
+        <v>1.2</v>
       </c>
       <c r="K3" t="n">
-        <v>7.5</v>
+        <v>8</v>
       </c>
       <c r="L3" t="n">
         <v>0.93</v>
       </c>
       <c r="M3" t="n">
-        <v>66.70999999999999</v>
+        <v>65.87</v>
       </c>
       <c r="N3" t="n">
-        <v>0.29</v>
+        <v>0.27</v>
       </c>
       <c r="O3" t="n">
-        <v>3.36</v>
+        <v>3.67</v>
       </c>
       <c r="P3" t="n">
-        <v>9.210000000000001</v>
+        <v>9.130000000000001</v>
       </c>
       <c r="Q3" t="n">
-        <v>12.21</v>
+        <v>11.8</v>
       </c>
       <c r="R3" t="n">
-        <v>6.36</v>
+        <v>6.07</v>
       </c>
       <c r="S3" t="n">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="T3" t="n">
-        <v>2.14</v>
+        <v>2.27</v>
       </c>
       <c r="U3" t="n">
         <v>0</v>
@@ -1848,28 +1848,28 @@
         <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>65.79000000000001</v>
+        <v>65.33</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="Z3" t="n">
-        <v>18.5</v>
+        <v>18.87</v>
       </c>
       <c r="AA3" t="n">
-        <v>12.29</v>
+        <v>12.47</v>
       </c>
       <c r="AB3" t="n">
-        <v>6.21</v>
+        <v>6.4</v>
       </c>
       <c r="AC3" t="n">
-        <v>23</v>
+        <v>22.87</v>
       </c>
       <c r="AD3" t="n">
-        <v>2.08</v>
+        <v>2.11</v>
       </c>
       <c r="AE3" t="n">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AF3" t="n">
         <v>0.13</v>
@@ -1953,22 +1953,22 @@
         <v>1.67</v>
       </c>
       <c r="BG3" t="n">
-        <v>3.1</v>
+        <v>3.17</v>
       </c>
       <c r="BH3" t="n">
-        <v>10.76</v>
+        <v>10.97</v>
       </c>
       <c r="BI3" t="n">
-        <v>3.1</v>
+        <v>3.17</v>
       </c>
       <c r="BJ3" t="n">
-        <v>0.76</v>
+        <v>0.83</v>
       </c>
       <c r="BK3" t="n">
-        <v>0.52</v>
+        <v>0.5</v>
       </c>
       <c r="BL3" t="n">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="BM3" t="n">
         <v>0.97</v>
@@ -1977,46 +1977,46 @@
         <v>1.83</v>
       </c>
       <c r="BO3" t="n">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="BP3" t="n">
-        <v>4.9</v>
+        <v>5.03</v>
       </c>
       <c r="BQ3" t="n">
-        <v>5.86</v>
+        <v>5.93</v>
       </c>
       <c r="BR3" t="n">
         <v>100</v>
       </c>
       <c r="BS3" t="n">
-        <v>68.97</v>
+        <v>70</v>
       </c>
       <c r="BT3" t="n">
-        <v>58.62</v>
+        <v>60</v>
       </c>
       <c r="BU3" t="n">
-        <v>24.14</v>
+        <v>26.67</v>
       </c>
       <c r="BV3" t="n">
-        <v>20.69</v>
+        <v>23.33</v>
       </c>
       <c r="BW3" t="n">
-        <v>13.79</v>
+        <v>13.33</v>
       </c>
       <c r="BX3" t="n">
-        <v>58.62</v>
+        <v>60</v>
       </c>
       <c r="BY3" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="BZ3" t="n">
         <v>1.44</v>
       </c>
-      <c r="BZ3" t="n">
-        <v>1.46</v>
-      </c>
       <c r="CA3" t="n">
-        <v>4.43</v>
+        <v>4.51</v>
       </c>
       <c r="CB3" t="n">
-        <v>4.75</v>
+        <v>4.82</v>
       </c>
       <c r="CC3" t="n">
         <v>1.84</v>
@@ -2025,34 +2025,34 @@
         <v>1.88</v>
       </c>
       <c r="CE3" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="CF3" t="n">
-        <v>2.25</v>
+        <v>2.24</v>
       </c>
       <c r="CG3" t="n">
-        <v>3.52</v>
+        <v>3.54</v>
       </c>
       <c r="CH3" t="n">
         <v>1.61</v>
       </c>
       <c r="CI3" t="n">
-        <v>2.13</v>
+        <v>2.12</v>
       </c>
       <c r="CJ3" t="n">
         <v>1.67</v>
       </c>
       <c r="CK3" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="CL3" t="n">
         <v>1.91</v>
       </c>
       <c r="CM3" t="n">
-        <v>2.54</v>
+        <v>2.56</v>
       </c>
       <c r="CN3" t="n">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="CO3" t="n">
         <v>1.16</v>
@@ -2061,25 +2061,25 @@
         <v>1.56</v>
       </c>
       <c r="CQ3" t="n">
-        <v>2.4</v>
+        <v>2.39</v>
       </c>
       <c r="CR3" t="n">
         <v>1.33</v>
       </c>
       <c r="CS3" t="n">
-        <v>2.33</v>
+        <v>2.32</v>
       </c>
       <c r="CT3" t="n">
         <v>3.26</v>
       </c>
       <c r="CU3" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="CV3" t="n">
-        <v>2.27</v>
+        <v>2.26</v>
       </c>
       <c r="CW3" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="CX3" t="n">
         <v>1.52</v>
@@ -2094,55 +2094,55 @@
         <v>2.04</v>
       </c>
       <c r="DB3" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="DC3" t="n">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="DD3" t="n">
-        <v>2.47</v>
+        <v>2.45</v>
       </c>
       <c r="DE3" t="n">
-        <v>0.1</v>
+        <v>0.13</v>
       </c>
       <c r="DF3" t="n">
-        <v>1.07</v>
+        <v>1.03</v>
       </c>
       <c r="DG3" t="n">
-        <v>3.65</v>
+        <v>3.76</v>
       </c>
       <c r="DH3" t="n">
-        <v>108.79</v>
+        <v>108.9</v>
       </c>
       <c r="DI3" t="n">
         <v>0</v>
       </c>
       <c r="DJ3" t="n">
-        <v>1.49</v>
+        <v>1.43</v>
       </c>
       <c r="DK3" t="n">
-        <v>6.52</v>
+        <v>6.8</v>
       </c>
       <c r="DL3" t="n">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="DM3" t="n">
-        <v>60.76</v>
+        <v>60.54</v>
       </c>
       <c r="DN3" t="n">
-        <v>0.35</v>
+        <v>0.34</v>
       </c>
       <c r="DO3" t="n">
-        <v>2.86</v>
+        <v>3.03</v>
       </c>
       <c r="DP3" t="n">
-        <v>9.720000000000001</v>
+        <v>9.67</v>
       </c>
       <c r="DQ3" t="n">
-        <v>11.55</v>
+        <v>11.36</v>
       </c>
       <c r="DR3" t="n">
-        <v>7.31</v>
+        <v>7.14</v>
       </c>
       <c r="DS3" t="n">
         <v>0.04</v>
@@ -2154,28 +2154,28 @@
         <v>0</v>
       </c>
       <c r="DV3" t="n">
-        <v>62.55</v>
+        <v>62.43</v>
       </c>
       <c r="DW3" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="DX3" t="n">
-        <v>16.17</v>
+        <v>16.43</v>
       </c>
       <c r="DY3" t="n">
-        <v>10.62</v>
+        <v>10.77</v>
       </c>
       <c r="DZ3" t="n">
-        <v>5.55</v>
+        <v>5.66</v>
       </c>
       <c r="EA3" t="n">
-        <v>20.62</v>
+        <v>20.64</v>
       </c>
       <c r="EB3" t="n">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="EC3" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
     </row>
     <row r="4">
@@ -2185,10 +2185,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C4" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D4" t="n">
         <v>15</v>
@@ -2197,49 +2197,49 @@
         <v>0.07000000000000001</v>
       </c>
       <c r="F4" t="n">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="G4" t="n">
-        <v>1.71</v>
+        <v>1.8</v>
       </c>
       <c r="H4" t="n">
-        <v>87.14</v>
+        <v>87.47</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.14</v>
+        <v>-0.13</v>
       </c>
       <c r="J4" t="n">
-        <v>1.86</v>
+        <v>1.8</v>
       </c>
       <c r="K4" t="n">
-        <v>3.57</v>
+        <v>3.73</v>
       </c>
       <c r="L4" t="n">
-        <v>0.14</v>
+        <v>0.2</v>
       </c>
       <c r="M4" t="n">
-        <v>46.36</v>
+        <v>46.47</v>
       </c>
       <c r="N4" t="n">
-        <v>0.43</v>
+        <v>0.4</v>
       </c>
       <c r="O4" t="n">
-        <v>1.29</v>
+        <v>1.4</v>
       </c>
       <c r="P4" t="n">
-        <v>10.71</v>
+        <v>10.8</v>
       </c>
       <c r="Q4" t="n">
-        <v>11</v>
+        <v>10.6</v>
       </c>
       <c r="R4" t="n">
-        <v>10.43</v>
+        <v>10.27</v>
       </c>
       <c r="S4" t="n">
-        <v>1.79</v>
+        <v>1.87</v>
       </c>
       <c r="T4" t="n">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="U4" t="n">
         <v>0.07000000000000001</v>
@@ -2251,28 +2251,28 @@
         <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>48.71</v>
+        <v>49.07</v>
       </c>
       <c r="Y4" t="n">
         <v>0</v>
       </c>
       <c r="Z4" t="n">
-        <v>10.93</v>
+        <v>11.2</v>
       </c>
       <c r="AA4" t="n">
-        <v>7.43</v>
+        <v>7.67</v>
       </c>
       <c r="AB4" t="n">
-        <v>3.5</v>
+        <v>3.53</v>
       </c>
       <c r="AC4" t="n">
-        <v>22.07</v>
+        <v>22.27</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.86</v>
+        <v>1.8</v>
       </c>
       <c r="AF4" t="n">
         <v>0.2</v>
@@ -2356,67 +2356,67 @@
         <v>2.13</v>
       </c>
       <c r="BG4" t="n">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="BH4" t="n">
-        <v>9.380000000000001</v>
+        <v>9.369999999999999</v>
       </c>
       <c r="BI4" t="n">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="BJ4" t="n">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="BK4" t="n">
-        <v>0.41</v>
+        <v>0.43</v>
       </c>
       <c r="BL4" t="n">
-        <v>0.59</v>
+        <v>0.57</v>
       </c>
       <c r="BM4" t="n">
-        <v>0.86</v>
+        <v>0.9</v>
       </c>
       <c r="BN4" t="n">
-        <v>1.45</v>
+        <v>1.47</v>
       </c>
       <c r="BO4" t="n">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="BP4" t="n">
-        <v>3.86</v>
+        <v>3.9</v>
       </c>
       <c r="BQ4" t="n">
-        <v>4.52</v>
+        <v>4.5</v>
       </c>
       <c r="BR4" t="n">
-        <v>86.20999999999999</v>
+        <v>86.67</v>
       </c>
       <c r="BS4" t="n">
-        <v>68.97</v>
+        <v>70</v>
       </c>
       <c r="BT4" t="n">
-        <v>48.28</v>
+        <v>50</v>
       </c>
       <c r="BU4" t="n">
-        <v>27.59</v>
+        <v>30</v>
       </c>
       <c r="BV4" t="n">
-        <v>10.34</v>
+        <v>10</v>
       </c>
       <c r="BW4" t="n">
-        <v>3.45</v>
+        <v>3.33</v>
       </c>
       <c r="BX4" t="n">
-        <v>55.17</v>
+        <v>56.67</v>
       </c>
       <c r="BY4" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="BZ4" t="n">
-        <v>3.59</v>
+        <v>3.55</v>
       </c>
       <c r="CA4" t="n">
-        <v>3.71</v>
+        <v>3.7</v>
       </c>
       <c r="CB4" t="n">
         <v>3.83</v>
@@ -2434,7 +2434,7 @@
         <v>2.61</v>
       </c>
       <c r="CG4" t="n">
-        <v>3.07</v>
+        <v>3.06</v>
       </c>
       <c r="CH4" t="n">
         <v>1.45</v>
@@ -2446,13 +2446,13 @@
         <v>1.75</v>
       </c>
       <c r="CK4" t="n">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="CL4" t="n">
-        <v>2.01</v>
+        <v>2</v>
       </c>
       <c r="CM4" t="n">
-        <v>2.35</v>
+        <v>2.37</v>
       </c>
       <c r="CN4" t="n">
         <v>1.84</v>
@@ -2473,16 +2473,16 @@
         <v>2.77</v>
       </c>
       <c r="CT4" t="n">
-        <v>3.09</v>
+        <v>3.1</v>
       </c>
       <c r="CU4" t="n">
         <v>1.47</v>
       </c>
       <c r="CV4" t="n">
-        <v>2.1</v>
+        <v>2.11</v>
       </c>
       <c r="CW4" t="n">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="CX4" t="n">
         <v>1.58</v>
@@ -2494,7 +2494,7 @@
         <v>2.37</v>
       </c>
       <c r="DA4" t="n">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="DB4" t="n">
         <v>1.28</v>
@@ -2506,46 +2506,46 @@
         <v>3.2</v>
       </c>
       <c r="DE4" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DF4" t="n">
-        <v>1.45</v>
+        <v>1.43</v>
       </c>
       <c r="DG4" t="n">
-        <v>1.59</v>
+        <v>1.64</v>
       </c>
       <c r="DH4" t="n">
-        <v>87.52</v>
+        <v>87.67</v>
       </c>
       <c r="DI4" t="n">
-        <v>0.04</v>
+        <v>0.03</v>
       </c>
       <c r="DJ4" t="n">
-        <v>2.21</v>
+        <v>2.16</v>
       </c>
       <c r="DK4" t="n">
-        <v>3.65</v>
+        <v>3.73</v>
       </c>
       <c r="DL4" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.1</v>
       </c>
       <c r="DM4" t="n">
-        <v>43.17</v>
+        <v>43.34</v>
       </c>
       <c r="DN4" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.67</v>
       </c>
       <c r="DO4" t="n">
-        <v>1.59</v>
+        <v>1.64</v>
       </c>
       <c r="DP4" t="n">
+        <v>11</v>
+      </c>
+      <c r="DQ4" t="n">
         <v>10.96</v>
       </c>
-      <c r="DQ4" t="n">
-        <v>11.17</v>
-      </c>
       <c r="DR4" t="n">
-        <v>10.21</v>
+        <v>10.13</v>
       </c>
       <c r="DS4" t="n">
         <v>0.1</v>
@@ -2557,28 +2557,28 @@
         <v>0</v>
       </c>
       <c r="DV4" t="n">
-        <v>47.17</v>
+        <v>47.4</v>
       </c>
       <c r="DW4" t="n">
         <v>0.14</v>
       </c>
       <c r="DX4" t="n">
-        <v>10.76</v>
+        <v>10.9</v>
       </c>
       <c r="DY4" t="n">
-        <v>6.9</v>
+        <v>7.04</v>
       </c>
       <c r="DZ4" t="n">
         <v>3.86</v>
       </c>
       <c r="EA4" t="n">
-        <v>22.14</v>
+        <v>22.24</v>
       </c>
       <c r="EB4" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="EC4" t="n">
-        <v>2</v>
+        <v>1.96</v>
       </c>
     </row>
     <row r="5">
@@ -2588,13 +2588,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C5" t="n">
         <v>15</v>
       </c>
       <c r="D5" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E5" t="n">
         <v>0.2</v>
@@ -2681,136 +2681,136 @@
         <v>0.07000000000000001</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.07</v>
+        <v>1.13</v>
       </c>
       <c r="AH5" t="n">
-        <v>2.79</v>
+        <v>2.67</v>
       </c>
       <c r="AI5" t="n">
-        <v>88.36</v>
+        <v>88.33</v>
       </c>
       <c r="AJ5" t="n">
         <v>-0.07000000000000001</v>
       </c>
       <c r="AK5" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="AL5" t="n">
-        <v>4.86</v>
+        <v>4.73</v>
       </c>
       <c r="AM5" t="n">
-        <v>0.86</v>
+        <v>0.8</v>
       </c>
       <c r="AN5" t="n">
-        <v>42</v>
+        <v>43.53</v>
       </c>
       <c r="AO5" t="n">
-        <v>0.64</v>
+        <v>0.6</v>
       </c>
       <c r="AP5" t="n">
         <v>2.07</v>
       </c>
       <c r="AQ5" t="n">
-        <v>10.57</v>
+        <v>10.13</v>
       </c>
       <c r="AR5" t="n">
-        <v>10.79</v>
+        <v>10.87</v>
       </c>
       <c r="AS5" t="n">
-        <v>10.86</v>
+        <v>10.67</v>
       </c>
       <c r="AT5" t="n">
-        <v>1.79</v>
+        <v>1.73</v>
       </c>
       <c r="AU5" t="n">
-        <v>1.36</v>
+        <v>1.47</v>
       </c>
       <c r="AV5" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="AW5" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="AX5" t="n">
         <v>0</v>
       </c>
       <c r="AY5" t="n">
-        <v>48.14</v>
+        <v>48</v>
       </c>
       <c r="AZ5" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="BA5" t="n">
-        <v>11.5</v>
+        <v>11.53</v>
       </c>
       <c r="BB5" t="n">
-        <v>6.79</v>
+        <v>6.6</v>
       </c>
       <c r="BC5" t="n">
-        <v>4.71</v>
+        <v>4.93</v>
       </c>
       <c r="BD5" t="n">
-        <v>18.29</v>
+        <v>18.93</v>
       </c>
       <c r="BE5" t="n">
-        <v>1.36</v>
+        <v>1.39</v>
       </c>
       <c r="BF5" t="n">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="BG5" t="n">
-        <v>3.03</v>
+        <v>3.07</v>
       </c>
       <c r="BH5" t="n">
-        <v>10.55</v>
+        <v>10.5</v>
       </c>
       <c r="BI5" t="n">
-        <v>3.03</v>
+        <v>3.07</v>
       </c>
       <c r="BJ5" t="n">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="BK5" t="n">
-        <v>0.55</v>
+        <v>0.57</v>
       </c>
       <c r="BL5" t="n">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="BM5" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.73</v>
       </c>
       <c r="BN5" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="BO5" t="n">
-        <v>1.34</v>
+        <v>1.37</v>
       </c>
       <c r="BP5" t="n">
-        <v>4.38</v>
+        <v>4.4</v>
       </c>
       <c r="BQ5" t="n">
-        <v>6.17</v>
+        <v>6.1</v>
       </c>
       <c r="BR5" t="n">
-        <v>96.55</v>
+        <v>96.67</v>
       </c>
       <c r="BS5" t="n">
-        <v>86.20999999999999</v>
+        <v>86.67</v>
       </c>
       <c r="BT5" t="n">
-        <v>58.62</v>
+        <v>60</v>
       </c>
       <c r="BU5" t="n">
-        <v>37.93</v>
+        <v>40</v>
       </c>
       <c r="BV5" t="n">
-        <v>17.24</v>
+        <v>16.67</v>
       </c>
       <c r="BW5" t="n">
-        <v>6.9</v>
+        <v>6.67</v>
       </c>
       <c r="BX5" t="n">
-        <v>58.62</v>
+        <v>60</v>
       </c>
       <c r="BY5" t="n">
         <v>2.56</v>
@@ -2819,25 +2819,25 @@
         <v>2.66</v>
       </c>
       <c r="CA5" t="n">
-        <v>3.59</v>
+        <v>3.58</v>
       </c>
       <c r="CB5" t="n">
-        <v>3.74</v>
+        <v>3.73</v>
       </c>
       <c r="CC5" t="n">
-        <v>3.66</v>
+        <v>3.55</v>
       </c>
       <c r="CD5" t="n">
-        <v>3.94</v>
+        <v>3.83</v>
       </c>
       <c r="CE5" t="n">
         <v>1.31</v>
       </c>
       <c r="CF5" t="n">
-        <v>2.47</v>
+        <v>2.48</v>
       </c>
       <c r="CG5" t="n">
-        <v>3.21</v>
+        <v>3.2</v>
       </c>
       <c r="CH5" t="n">
         <v>1.5</v>
@@ -2846,7 +2846,7 @@
         <v>2.21</v>
       </c>
       <c r="CJ5" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="CK5" t="n">
         <v>1.46</v>
@@ -2855,7 +2855,7 @@
         <v>1.86</v>
       </c>
       <c r="CM5" t="n">
-        <v>2.53</v>
+        <v>2.54</v>
       </c>
       <c r="CN5" t="n">
         <v>1.98</v>
@@ -2867,7 +2867,7 @@
         <v>1.74</v>
       </c>
       <c r="CQ5" t="n">
-        <v>2.76</v>
+        <v>2.77</v>
       </c>
       <c r="CR5" t="n">
         <v>1.36</v>
@@ -2879,10 +2879,10 @@
         <v>3.21</v>
       </c>
       <c r="CU5" t="n">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="CV5" t="n">
-        <v>2.33</v>
+        <v>2.32</v>
       </c>
       <c r="CW5" t="n">
         <v>1.66</v>
@@ -2891,7 +2891,7 @@
         <v>1.55</v>
       </c>
       <c r="CY5" t="n">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="CZ5" t="n">
         <v>2.44</v>
@@ -2903,85 +2903,85 @@
         <v>1.24</v>
       </c>
       <c r="DC5" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="DD5" t="n">
-        <v>2.89</v>
+        <v>2.9</v>
       </c>
       <c r="DE5" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DF5" t="n">
-        <v>1.14</v>
+        <v>1.16</v>
       </c>
       <c r="DG5" t="n">
-        <v>2.62</v>
+        <v>2.57</v>
       </c>
       <c r="DH5" t="n">
-        <v>96.62</v>
+        <v>96.33</v>
       </c>
       <c r="DI5" t="n">
         <v>0</v>
       </c>
       <c r="DJ5" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="DK5" t="n">
-        <v>4.76</v>
+        <v>4.7</v>
       </c>
       <c r="DL5" t="n">
-        <v>0.62</v>
+        <v>0.6</v>
       </c>
       <c r="DM5" t="n">
-        <v>47.03</v>
+        <v>47.63</v>
       </c>
       <c r="DN5" t="n">
-        <v>0.55</v>
+        <v>0.54</v>
       </c>
       <c r="DO5" t="n">
-        <v>2.14</v>
+        <v>2.13</v>
       </c>
       <c r="DP5" t="n">
-        <v>10.69</v>
+        <v>10.47</v>
       </c>
       <c r="DQ5" t="n">
-        <v>11.11</v>
+        <v>11.13</v>
       </c>
       <c r="DR5" t="n">
-        <v>9.34</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="DS5" t="n">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
       <c r="DT5" t="n">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
       <c r="DU5" t="n">
         <v>0</v>
       </c>
       <c r="DV5" t="n">
-        <v>51.03</v>
+        <v>50.86</v>
       </c>
       <c r="DW5" t="n">
         <v>0.13</v>
       </c>
       <c r="DX5" t="n">
-        <v>13.27</v>
+        <v>13.23</v>
       </c>
       <c r="DY5" t="n">
-        <v>8.859999999999999</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="DZ5" t="n">
-        <v>4.41</v>
+        <v>4.53</v>
       </c>
       <c r="EA5" t="n">
-        <v>19.14</v>
+        <v>19.43</v>
       </c>
       <c r="EB5" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="EC5" t="n">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
     </row>
     <row r="6">
@@ -2991,13 +2991,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C6" t="n">
         <v>15</v>
       </c>
       <c r="D6" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E6" t="n">
         <v>0.07000000000000001</v>
@@ -3081,139 +3081,139 @@
         <v>1.13</v>
       </c>
       <c r="AF6" t="n">
-        <v>0.21</v>
+        <v>0.27</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.29</v>
+        <v>1.2</v>
       </c>
       <c r="AH6" t="n">
-        <v>2.36</v>
+        <v>2.33</v>
       </c>
       <c r="AI6" t="n">
-        <v>99.20999999999999</v>
+        <v>98.73</v>
       </c>
       <c r="AJ6" t="n">
         <v>0.07000000000000001</v>
       </c>
       <c r="AK6" t="n">
-        <v>1.79</v>
+        <v>1.73</v>
       </c>
       <c r="AL6" t="n">
-        <v>4.21</v>
+        <v>4.13</v>
       </c>
       <c r="AM6" t="n">
-        <v>0.64</v>
+        <v>0.67</v>
       </c>
       <c r="AN6" t="n">
-        <v>46.43</v>
+        <v>45.87</v>
       </c>
       <c r="AO6" t="n">
-        <v>0.5</v>
+        <v>0.53</v>
       </c>
       <c r="AP6" t="n">
-        <v>1.86</v>
+        <v>1.8</v>
       </c>
       <c r="AQ6" t="n">
-        <v>9.93</v>
+        <v>9.67</v>
       </c>
       <c r="AR6" t="n">
-        <v>11.5</v>
+        <v>11.4</v>
       </c>
       <c r="AS6" t="n">
-        <v>8.289999999999999</v>
+        <v>8.27</v>
       </c>
       <c r="AT6" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="AX6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY6" t="n">
+        <v>59.47</v>
+      </c>
+      <c r="AZ6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA6" t="n">
+        <v>13</v>
+      </c>
+      <c r="BB6" t="n">
+        <v>7.53</v>
+      </c>
+      <c r="BC6" t="n">
+        <v>5.47</v>
+      </c>
+      <c r="BD6" t="n">
+        <v>18.67</v>
+      </c>
+      <c r="BE6" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="BF6" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="BG6" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="BH6" t="n">
+        <v>10.13</v>
+      </c>
+      <c r="BI6" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="BJ6" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="BK6" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="BL6" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="BM6" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="BN6" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="BO6" t="n">
         <v>1.57</v>
       </c>
-      <c r="AU6" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="AV6" t="n">
-        <v>0.14</v>
-      </c>
-      <c r="AW6" t="n">
-        <v>0.14</v>
-      </c>
-      <c r="AX6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY6" t="n">
-        <v>59.79</v>
-      </c>
-      <c r="AZ6" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA6" t="n">
-        <v>12.93</v>
-      </c>
-      <c r="BB6" t="n">
-        <v>7.57</v>
-      </c>
-      <c r="BC6" t="n">
-        <v>5.36</v>
-      </c>
-      <c r="BD6" t="n">
-        <v>18.79</v>
-      </c>
-      <c r="BE6" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="BF6" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="BG6" t="n">
-        <v>2.86</v>
-      </c>
-      <c r="BH6" t="n">
-        <v>10.03</v>
-      </c>
-      <c r="BI6" t="n">
-        <v>2.86</v>
-      </c>
-      <c r="BJ6" t="n">
-        <v>0.62</v>
-      </c>
-      <c r="BK6" t="n">
-        <v>0.83</v>
-      </c>
-      <c r="BL6" t="n">
-        <v>0.86</v>
-      </c>
-      <c r="BM6" t="n">
-        <v>0.55</v>
-      </c>
-      <c r="BN6" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="BO6" t="n">
-        <v>1.45</v>
-      </c>
       <c r="BP6" t="n">
-        <v>4.66</v>
+        <v>4.7</v>
       </c>
       <c r="BQ6" t="n">
-        <v>5.34</v>
+        <v>5.4</v>
       </c>
       <c r="BR6" t="n">
         <v>100</v>
       </c>
       <c r="BS6" t="n">
-        <v>86.20999999999999</v>
+        <v>86.67</v>
       </c>
       <c r="BT6" t="n">
-        <v>62.07</v>
+        <v>63.33</v>
       </c>
       <c r="BU6" t="n">
-        <v>17.24</v>
+        <v>20</v>
       </c>
       <c r="BV6" t="n">
-        <v>10.34</v>
+        <v>13.33</v>
       </c>
       <c r="BW6" t="n">
-        <v>3.45</v>
+        <v>6.67</v>
       </c>
       <c r="BX6" t="n">
-        <v>72.41</v>
+        <v>73.33</v>
       </c>
       <c r="BY6" t="n">
         <v>1.82</v>
@@ -3225,13 +3225,13 @@
         <v>3.82</v>
       </c>
       <c r="CB6" t="n">
-        <v>3.92</v>
+        <v>3.91</v>
       </c>
       <c r="CC6" t="n">
-        <v>2.54</v>
+        <v>2.5</v>
       </c>
       <c r="CD6" t="n">
-        <v>2.64</v>
+        <v>2.62</v>
       </c>
       <c r="CE6" t="n">
         <v>1.3</v>
@@ -3246,7 +3246,7 @@
         <v>1.51</v>
       </c>
       <c r="CI6" t="n">
-        <v>2.22</v>
+        <v>2.21</v>
       </c>
       <c r="CJ6" t="n">
         <v>1.64</v>
@@ -3255,7 +3255,7 @@
         <v>1.5</v>
       </c>
       <c r="CL6" t="n">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="CM6" t="n">
         <v>2.44</v>
@@ -3279,13 +3279,13 @@
         <v>2.6</v>
       </c>
       <c r="CT6" t="n">
-        <v>3.17</v>
+        <v>3.18</v>
       </c>
       <c r="CU6" t="n">
         <v>1.52</v>
       </c>
       <c r="CV6" t="n">
-        <v>2.26</v>
+        <v>2.27</v>
       </c>
       <c r="CW6" t="n">
         <v>1.7</v>
@@ -3297,7 +3297,7 @@
         <v>1.9</v>
       </c>
       <c r="CZ6" t="n">
-        <v>2.38</v>
+        <v>2.39</v>
       </c>
       <c r="DA6" t="n">
         <v>1.92</v>
@@ -3312,79 +3312,79 @@
         <v>2.85</v>
       </c>
       <c r="DE6" t="n">
-        <v>0.14</v>
+        <v>0.17</v>
       </c>
       <c r="DF6" t="n">
-        <v>1</v>
+        <v>0.96</v>
       </c>
       <c r="DG6" t="n">
-        <v>3.21</v>
+        <v>3.16</v>
       </c>
       <c r="DH6" t="n">
-        <v>112.51</v>
+        <v>111.83</v>
       </c>
       <c r="DI6" t="n">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="DJ6" t="n">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="DK6" t="n">
-        <v>5.55</v>
+        <v>5.46</v>
       </c>
       <c r="DL6" t="n">
-        <v>0.55</v>
+        <v>0.57</v>
       </c>
       <c r="DM6" t="n">
-        <v>53.55</v>
+        <v>53.04</v>
       </c>
       <c r="DN6" t="n">
-        <v>0.48</v>
+        <v>0.5</v>
       </c>
       <c r="DO6" t="n">
-        <v>2.31</v>
+        <v>2.26</v>
       </c>
       <c r="DP6" t="n">
-        <v>9.970000000000001</v>
+        <v>9.84</v>
       </c>
       <c r="DQ6" t="n">
-        <v>12.21</v>
+        <v>12.13</v>
       </c>
       <c r="DR6" t="n">
-        <v>7.31</v>
+        <v>7.34</v>
       </c>
       <c r="DS6" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="DT6" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="DU6" t="n">
         <v>0</v>
       </c>
       <c r="DV6" t="n">
-        <v>60.45</v>
+        <v>60.27</v>
       </c>
       <c r="DW6" t="n">
         <v>0.04</v>
       </c>
       <c r="DX6" t="n">
-        <v>15.45</v>
+        <v>15.4</v>
       </c>
       <c r="DY6" t="n">
-        <v>9.76</v>
+        <v>9.66</v>
       </c>
       <c r="DZ6" t="n">
-        <v>5.69</v>
+        <v>5.74</v>
       </c>
       <c r="EA6" t="n">
-        <v>20</v>
+        <v>19.9</v>
       </c>
       <c r="EB6" t="n">
         <v>1.76</v>
       </c>
       <c r="EC6" t="n">
-        <v>1.45</v>
+        <v>1.43</v>
       </c>
     </row>
     <row r="7">
@@ -3394,13 +3394,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C7" t="n">
         <v>15</v>
       </c>
       <c r="D7" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E7" t="n">
         <v>0.2</v>
@@ -3487,49 +3487,49 @@
         <v>0.07000000000000001</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.57</v>
+        <v>1.47</v>
       </c>
       <c r="AH7" t="n">
-        <v>2.93</v>
+        <v>2.8</v>
       </c>
       <c r="AI7" t="n">
-        <v>90</v>
+        <v>88.33</v>
       </c>
       <c r="AJ7" t="n">
         <v>0.07000000000000001</v>
       </c>
       <c r="AK7" t="n">
-        <v>2.36</v>
+        <v>2.27</v>
       </c>
       <c r="AL7" t="n">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="AM7" t="n">
-        <v>0.29</v>
+        <v>0.33</v>
       </c>
       <c r="AN7" t="n">
-        <v>45.07</v>
+        <v>44.2</v>
       </c>
       <c r="AO7" t="n">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="AP7" t="n">
-        <v>2.07</v>
+        <v>2</v>
       </c>
       <c r="AQ7" t="n">
-        <v>11.21</v>
+        <v>10.87</v>
       </c>
       <c r="AR7" t="n">
-        <v>11.57</v>
+        <v>11.47</v>
       </c>
       <c r="AS7" t="n">
-        <v>8.640000000000001</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AT7" t="n">
-        <v>1.21</v>
+        <v>1.4</v>
       </c>
       <c r="AU7" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AV7" t="n">
         <v>0</v>
@@ -3541,82 +3541,82 @@
         <v>0</v>
       </c>
       <c r="AY7" t="n">
-        <v>51.36</v>
+        <v>50.67</v>
       </c>
       <c r="AZ7" t="n">
         <v>0</v>
       </c>
       <c r="BA7" t="n">
-        <v>9.859999999999999</v>
+        <v>9.529999999999999</v>
       </c>
       <c r="BB7" t="n">
-        <v>5.86</v>
+        <v>5.73</v>
       </c>
       <c r="BC7" t="n">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="BD7" t="n">
-        <v>21.71</v>
+        <v>21.53</v>
       </c>
       <c r="BE7" t="n">
-        <v>1.23</v>
+        <v>1.19</v>
       </c>
       <c r="BF7" t="n">
-        <v>2.36</v>
+        <v>2.27</v>
       </c>
       <c r="BG7" t="n">
-        <v>2.45</v>
+        <v>2.53</v>
       </c>
       <c r="BH7" t="n">
-        <v>10.76</v>
+        <v>10.97</v>
       </c>
       <c r="BI7" t="n">
-        <v>2.45</v>
+        <v>2.53</v>
       </c>
       <c r="BJ7" t="n">
-        <v>0.59</v>
+        <v>0.67</v>
       </c>
       <c r="BK7" t="n">
-        <v>0.41</v>
+        <v>0.4</v>
       </c>
       <c r="BL7" t="n">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="BM7" t="n">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="BN7" t="n">
-        <v>1.45</v>
+        <v>1.47</v>
       </c>
       <c r="BO7" t="n">
-        <v>1</v>
+        <v>1.07</v>
       </c>
       <c r="BP7" t="n">
-        <v>4.93</v>
+        <v>5.07</v>
       </c>
       <c r="BQ7" t="n">
-        <v>5.83</v>
+        <v>5.9</v>
       </c>
       <c r="BR7" t="n">
-        <v>96.55</v>
+        <v>96.67</v>
       </c>
       <c r="BS7" t="n">
-        <v>72.41</v>
+        <v>73.33</v>
       </c>
       <c r="BT7" t="n">
-        <v>37.93</v>
+        <v>40</v>
       </c>
       <c r="BU7" t="n">
-        <v>27.59</v>
+        <v>30</v>
       </c>
       <c r="BV7" t="n">
-        <v>10.34</v>
+        <v>13.33</v>
       </c>
       <c r="BW7" t="n">
         <v>0</v>
       </c>
       <c r="BX7" t="n">
-        <v>62.07</v>
+        <v>63.33</v>
       </c>
       <c r="BY7" t="n">
         <v>2.79</v>
@@ -3625,34 +3625,34 @@
         <v>2.94</v>
       </c>
       <c r="CA7" t="n">
-        <v>3.64</v>
+        <v>3.74</v>
       </c>
       <c r="CB7" t="n">
-        <v>3.75</v>
+        <v>3.86</v>
       </c>
       <c r="CC7" t="n">
-        <v>3.81</v>
+        <v>4.19</v>
       </c>
       <c r="CD7" t="n">
-        <v>4.28</v>
+        <v>4.69</v>
       </c>
       <c r="CE7" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="CF7" t="n">
-        <v>2.47</v>
+        <v>2.46</v>
       </c>
       <c r="CG7" t="n">
-        <v>3.19</v>
+        <v>3.22</v>
       </c>
       <c r="CH7" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="CI7" t="n">
-        <v>2.2</v>
+        <v>2.19</v>
       </c>
       <c r="CJ7" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="CK7" t="n">
         <v>1.4</v>
@@ -3661,37 +3661,37 @@
         <v>1.78</v>
       </c>
       <c r="CM7" t="n">
-        <v>2.71</v>
+        <v>2.72</v>
       </c>
       <c r="CN7" t="n">
-        <v>2.07</v>
+        <v>2.08</v>
       </c>
       <c r="CO7" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="CP7" t="n">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="CQ7" t="n">
-        <v>2.77</v>
+        <v>2.75</v>
       </c>
       <c r="CR7" t="n">
         <v>1.36</v>
       </c>
       <c r="CS7" t="n">
-        <v>2.61</v>
+        <v>2.59</v>
       </c>
       <c r="CT7" t="n">
         <v>3.18</v>
       </c>
       <c r="CU7" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="CV7" t="n">
-        <v>2.32</v>
+        <v>2.31</v>
       </c>
       <c r="CW7" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="CX7" t="n">
         <v>1.49</v>
@@ -3709,85 +3709,85 @@
         <v>1.24</v>
       </c>
       <c r="DC7" t="n">
-        <v>1.79</v>
+        <v>1.77</v>
       </c>
       <c r="DD7" t="n">
-        <v>2.89</v>
+        <v>2.86</v>
       </c>
       <c r="DE7" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DF7" t="n">
-        <v>1.59</v>
+        <v>1.54</v>
       </c>
       <c r="DG7" t="n">
-        <v>2.66</v>
+        <v>2.6</v>
       </c>
       <c r="DH7" t="n">
-        <v>88.79000000000001</v>
+        <v>88</v>
       </c>
       <c r="DI7" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DJ7" t="n">
-        <v>2.28</v>
+        <v>2.24</v>
       </c>
       <c r="DK7" t="n">
-        <v>4.69</v>
+        <v>4.6</v>
       </c>
       <c r="DL7" t="n">
-        <v>0.28</v>
+        <v>0.3</v>
       </c>
       <c r="DM7" t="n">
-        <v>46.96</v>
+        <v>46.46</v>
       </c>
       <c r="DN7" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.7</v>
       </c>
       <c r="DO7" t="n">
-        <v>2.03</v>
+        <v>2</v>
       </c>
       <c r="DP7" t="n">
-        <v>10.75</v>
+        <v>10.6</v>
       </c>
       <c r="DQ7" t="n">
-        <v>11.83</v>
+        <v>11.77</v>
       </c>
       <c r="DR7" t="n">
-        <v>8.970000000000001</v>
+        <v>9.029999999999999</v>
       </c>
       <c r="DS7" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="DT7" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="DU7" t="n">
         <v>0</v>
       </c>
       <c r="DV7" t="n">
-        <v>49.73</v>
+        <v>49.44</v>
       </c>
       <c r="DW7" t="n">
         <v>0</v>
       </c>
       <c r="DX7" t="n">
-        <v>10.24</v>
+        <v>10.06</v>
       </c>
       <c r="DY7" t="n">
-        <v>6.38</v>
+        <v>6.3</v>
       </c>
       <c r="DZ7" t="n">
-        <v>3.86</v>
+        <v>3.76</v>
       </c>
       <c r="EA7" t="n">
-        <v>21.55</v>
+        <v>21.46</v>
       </c>
       <c r="EB7" t="n">
-        <v>1.26</v>
+        <v>1.24</v>
       </c>
       <c r="EC7" t="n">
-        <v>2.28</v>
+        <v>2.24</v>
       </c>
     </row>
     <row r="8">
@@ -3797,13 +3797,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C8" t="n">
         <v>15</v>
       </c>
       <c r="D8" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E8" t="n">
         <v>0.2</v>
@@ -3887,139 +3887,139 @@
         <v>1.13</v>
       </c>
       <c r="AF8" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.57</v>
+        <v>1.47</v>
       </c>
       <c r="AH8" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>87.27</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>4.53</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>42.27</v>
+      </c>
+      <c r="AO8" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="AP8" t="n">
         <v>2</v>
       </c>
-      <c r="AI8" t="n">
-        <v>86.36</v>
-      </c>
-      <c r="AJ8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK8" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="AL8" t="n">
-        <v>4.21</v>
-      </c>
-      <c r="AM8" t="n">
-        <v>0.36</v>
-      </c>
-      <c r="AN8" t="n">
-        <v>42.29</v>
-      </c>
-      <c r="AO8" t="n">
-        <v>0.21</v>
-      </c>
-      <c r="AP8" t="n">
-        <v>2.21</v>
-      </c>
       <c r="AQ8" t="n">
-        <v>13.14</v>
+        <v>12.67</v>
       </c>
       <c r="AR8" t="n">
-        <v>12</v>
+        <v>12.07</v>
       </c>
       <c r="AS8" t="n">
-        <v>9.789999999999999</v>
+        <v>9.529999999999999</v>
       </c>
       <c r="AT8" t="n">
-        <v>1.71</v>
+        <v>1.6</v>
       </c>
       <c r="AU8" t="n">
-        <v>1.36</v>
+        <v>1.27</v>
       </c>
       <c r="AV8" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="AW8" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="AX8" t="n">
         <v>0</v>
       </c>
       <c r="AY8" t="n">
-        <v>46.5</v>
+        <v>46.93</v>
       </c>
       <c r="AZ8" t="n">
         <v>0.07000000000000001</v>
       </c>
       <c r="BA8" t="n">
-        <v>12.79</v>
+        <v>13.33</v>
       </c>
       <c r="BB8" t="n">
-        <v>8.359999999999999</v>
+        <v>9</v>
       </c>
       <c r="BC8" t="n">
-        <v>4.43</v>
+        <v>4.33</v>
       </c>
       <c r="BD8" t="n">
-        <v>23.21</v>
+        <v>22.87</v>
       </c>
       <c r="BE8" t="n">
-        <v>1.39</v>
+        <v>1.42</v>
       </c>
       <c r="BF8" t="n">
-        <v>1.71</v>
+        <v>1.67</v>
       </c>
       <c r="BG8" t="n">
-        <v>2.62</v>
+        <v>2.53</v>
       </c>
       <c r="BH8" t="n">
-        <v>10.28</v>
+        <v>10.43</v>
       </c>
       <c r="BI8" t="n">
-        <v>2.62</v>
+        <v>2.53</v>
       </c>
       <c r="BJ8" t="n">
-        <v>0.66</v>
+        <v>0.63</v>
       </c>
       <c r="BK8" t="n">
-        <v>0.72</v>
+        <v>0.7</v>
       </c>
       <c r="BL8" t="n">
-        <v>0.76</v>
+        <v>0.73</v>
       </c>
       <c r="BM8" t="n">
-        <v>0.48</v>
+        <v>0.47</v>
       </c>
       <c r="BN8" t="n">
-        <v>1.24</v>
+        <v>1.2</v>
       </c>
       <c r="BO8" t="n">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="BP8" t="n">
-        <v>4.93</v>
+        <v>4.73</v>
       </c>
       <c r="BQ8" t="n">
-        <v>5.31</v>
+        <v>5.1</v>
       </c>
       <c r="BR8" t="n">
-        <v>89.66</v>
+        <v>86.67</v>
       </c>
       <c r="BS8" t="n">
-        <v>75.86</v>
+        <v>73.33</v>
       </c>
       <c r="BT8" t="n">
-        <v>37.93</v>
+        <v>36.67</v>
       </c>
       <c r="BU8" t="n">
-        <v>24.14</v>
+        <v>23.33</v>
       </c>
       <c r="BV8" t="n">
-        <v>10.34</v>
+        <v>10</v>
       </c>
       <c r="BW8" t="n">
-        <v>6.9</v>
+        <v>6.67</v>
       </c>
       <c r="BX8" t="n">
-        <v>37.93</v>
+        <v>36.67</v>
       </c>
       <c r="BY8" t="n">
         <v>2.61</v>
@@ -4028,31 +4028,31 @@
         <v>2.69</v>
       </c>
       <c r="CA8" t="n">
+        <v>3.76</v>
+      </c>
+      <c r="CB8" t="n">
+        <v>3.84</v>
+      </c>
+      <c r="CC8" t="n">
         <v>3.78</v>
       </c>
-      <c r="CB8" t="n">
-        <v>3.86</v>
-      </c>
-      <c r="CC8" t="n">
-        <v>3.85</v>
-      </c>
       <c r="CD8" t="n">
-        <v>3.83</v>
+        <v>3.78</v>
       </c>
       <c r="CE8" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="CF8" t="n">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="CG8" t="n">
-        <v>3.43</v>
+        <v>3.4</v>
       </c>
       <c r="CH8" t="n">
         <v>1.57</v>
       </c>
       <c r="CI8" t="n">
-        <v>2.38</v>
+        <v>2.36</v>
       </c>
       <c r="CJ8" t="n">
         <v>1.56</v>
@@ -4061,103 +4061,103 @@
         <v>1.36</v>
       </c>
       <c r="CL8" t="n">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="CM8" t="n">
-        <v>2.87</v>
+        <v>2.85</v>
       </c>
       <c r="CN8" t="n">
-        <v>2.19</v>
+        <v>2.18</v>
       </c>
       <c r="CO8" t="n">
         <v>1.16</v>
       </c>
       <c r="CP8" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="CQ8" t="n">
-        <v>2.49</v>
+        <v>2.52</v>
       </c>
       <c r="CR8" t="n">
         <v>1.34</v>
       </c>
       <c r="CS8" t="n">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="CT8" t="n">
-        <v>3.31</v>
+        <v>3.28</v>
       </c>
       <c r="CU8" t="n">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="CV8" t="n">
-        <v>2.53</v>
+        <v>2.52</v>
       </c>
       <c r="CW8" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="CX8" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="CY8" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="CZ8" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="DA8" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="DB8" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="DC8" t="n">
         <v>1.66</v>
       </c>
-      <c r="CZ8" t="n">
-        <v>2.53</v>
-      </c>
-      <c r="DA8" t="n">
-        <v>2.21</v>
-      </c>
-      <c r="DB8" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="DC8" t="n">
-        <v>1.64</v>
-      </c>
       <c r="DD8" t="n">
-        <v>2.55</v>
+        <v>2.58</v>
       </c>
       <c r="DE8" t="n">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
       <c r="DF8" t="n">
-        <v>1.24</v>
+        <v>1.2</v>
       </c>
       <c r="DG8" t="n">
-        <v>2.52</v>
+        <v>2.4</v>
       </c>
       <c r="DH8" t="n">
-        <v>91.93000000000001</v>
+        <v>92.2</v>
       </c>
       <c r="DI8" t="n">
         <v>-0.04</v>
       </c>
       <c r="DJ8" t="n">
-        <v>1.59</v>
+        <v>1.57</v>
       </c>
       <c r="DK8" t="n">
-        <v>5.17</v>
+        <v>5.3</v>
       </c>
       <c r="DL8" t="n">
-        <v>0.34</v>
+        <v>0.3</v>
       </c>
       <c r="DM8" t="n">
-        <v>49.07</v>
+        <v>48.84</v>
       </c>
       <c r="DN8" t="n">
-        <v>0.27</v>
+        <v>0.3</v>
       </c>
       <c r="DO8" t="n">
-        <v>2.65</v>
+        <v>2.53</v>
       </c>
       <c r="DP8" t="n">
-        <v>11.66</v>
+        <v>11.47</v>
       </c>
       <c r="DQ8" t="n">
-        <v>12.35</v>
+        <v>12.37</v>
       </c>
       <c r="DR8" t="n">
-        <v>8.76</v>
+        <v>8.66</v>
       </c>
       <c r="DS8" t="n">
         <v>0.13</v>
@@ -4169,28 +4169,28 @@
         <v>0</v>
       </c>
       <c r="DV8" t="n">
-        <v>48.66</v>
+        <v>48.8</v>
       </c>
       <c r="DW8" t="n">
         <v>0.1</v>
       </c>
       <c r="DX8" t="n">
-        <v>14.14</v>
+        <v>14.36</v>
       </c>
       <c r="DY8" t="n">
-        <v>9.59</v>
+        <v>9.869999999999999</v>
       </c>
       <c r="DZ8" t="n">
-        <v>4.55</v>
+        <v>4.5</v>
       </c>
       <c r="EA8" t="n">
-        <v>21.28</v>
+        <v>21.17</v>
       </c>
       <c r="EB8" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="EC8" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
     </row>
     <row r="9">
@@ -4200,94 +4200,94 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C9" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D9" t="n">
         <v>15</v>
       </c>
       <c r="E9" t="n">
-        <v>0.21</v>
+        <v>0.2</v>
       </c>
       <c r="F9" t="n">
         <v>2.07</v>
       </c>
       <c r="G9" t="n">
-        <v>2.43</v>
+        <v>2.53</v>
       </c>
       <c r="H9" t="n">
-        <v>83.56999999999999</v>
+        <v>85.40000000000001</v>
       </c>
       <c r="I9" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.13</v>
       </c>
       <c r="J9" t="n">
-        <v>2.79</v>
+        <v>2.8</v>
       </c>
       <c r="K9" t="n">
-        <v>5.29</v>
+        <v>5.27</v>
       </c>
       <c r="L9" t="n">
-        <v>0.57</v>
+        <v>0.53</v>
       </c>
       <c r="M9" t="n">
-        <v>42.21</v>
+        <v>44</v>
       </c>
       <c r="N9" t="n">
-        <v>0.71</v>
+        <v>0.73</v>
       </c>
       <c r="O9" t="n">
-        <v>2.79</v>
+        <v>2.67</v>
       </c>
       <c r="P9" t="n">
-        <v>15.86</v>
+        <v>15.53</v>
       </c>
       <c r="Q9" t="n">
-        <v>12.5</v>
+        <v>12.4</v>
       </c>
       <c r="R9" t="n">
-        <v>7.86</v>
+        <v>7.8</v>
       </c>
       <c r="S9" t="n">
-        <v>1.29</v>
+        <v>1.2</v>
       </c>
       <c r="T9" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="U9" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="V9" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>46.5</v>
+        <v>46.93</v>
       </c>
       <c r="Y9" t="n">
         <v>0</v>
       </c>
       <c r="Z9" t="n">
-        <v>15.5</v>
+        <v>15.6</v>
       </c>
       <c r="AA9" t="n">
-        <v>10.64</v>
+        <v>10.8</v>
       </c>
       <c r="AB9" t="n">
-        <v>4.86</v>
+        <v>4.8</v>
       </c>
       <c r="AC9" t="n">
-        <v>20.21</v>
+        <v>20.27</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.62</v>
+        <v>1.64</v>
       </c>
       <c r="AE9" t="n">
-        <v>2.79</v>
+        <v>2.8</v>
       </c>
       <c r="AF9" t="n">
         <v>0.07000000000000001</v>
@@ -4371,70 +4371,70 @@
         <v>3.13</v>
       </c>
       <c r="BG9" t="n">
-        <v>2.55</v>
+        <v>2.5</v>
       </c>
       <c r="BH9" t="n">
-        <v>11.17</v>
+        <v>11.13</v>
       </c>
       <c r="BI9" t="n">
-        <v>2.55</v>
+        <v>2.5</v>
       </c>
       <c r="BJ9" t="n">
-        <v>0.66</v>
+        <v>0.63</v>
       </c>
       <c r="BK9" t="n">
-        <v>0.48</v>
+        <v>0.47</v>
       </c>
       <c r="BL9" t="n">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="BM9" t="n">
-        <v>0.62</v>
+        <v>0.6</v>
       </c>
       <c r="BN9" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="BO9" t="n">
-        <v>1.14</v>
+        <v>1.1</v>
       </c>
       <c r="BP9" t="n">
-        <v>5.38</v>
+        <v>5.37</v>
       </c>
       <c r="BQ9" t="n">
-        <v>5.24</v>
+        <v>5.23</v>
       </c>
       <c r="BR9" t="n">
-        <v>93.09999999999999</v>
+        <v>93.33</v>
       </c>
       <c r="BS9" t="n">
-        <v>72.41</v>
+        <v>70</v>
       </c>
       <c r="BT9" t="n">
-        <v>48.28</v>
+        <v>46.67</v>
       </c>
       <c r="BU9" t="n">
-        <v>27.59</v>
+        <v>26.67</v>
       </c>
       <c r="BV9" t="n">
-        <v>10.34</v>
+        <v>10</v>
       </c>
       <c r="BW9" t="n">
-        <v>3.45</v>
+        <v>3.33</v>
       </c>
       <c r="BX9" t="n">
-        <v>51.72</v>
+        <v>50</v>
       </c>
       <c r="BY9" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="BZ9" t="n">
         <v>2.85</v>
       </c>
-      <c r="BZ9" t="n">
-        <v>2.91</v>
-      </c>
       <c r="CA9" t="n">
-        <v>3.53</v>
+        <v>3.52</v>
       </c>
       <c r="CB9" t="n">
-        <v>3.61</v>
+        <v>3.6</v>
       </c>
       <c r="CC9" t="n">
         <v>4.43</v>
@@ -4464,7 +4464,7 @@
         <v>1.46</v>
       </c>
       <c r="CL9" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="CM9" t="n">
         <v>2.55</v>
@@ -4479,7 +4479,7 @@
         <v>1.91</v>
       </c>
       <c r="CQ9" t="n">
-        <v>3.23</v>
+        <v>3.22</v>
       </c>
       <c r="CR9" t="n">
         <v>1.38</v>
@@ -4488,13 +4488,13 @@
         <v>2.8</v>
       </c>
       <c r="CT9" t="n">
-        <v>3.11</v>
+        <v>3.12</v>
       </c>
       <c r="CU9" t="n">
         <v>1.46</v>
       </c>
       <c r="CV9" t="n">
-        <v>2.1</v>
+        <v>2.11</v>
       </c>
       <c r="CW9" t="n">
         <v>1.79</v>
@@ -4521,19 +4521,19 @@
         <v>3.31</v>
       </c>
       <c r="DE9" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DF9" t="n">
         <v>2.1</v>
       </c>
       <c r="DG9" t="n">
-        <v>2.41</v>
+        <v>2.46</v>
       </c>
       <c r="DH9" t="n">
-        <v>79.95999999999999</v>
+        <v>81</v>
       </c>
       <c r="DI9" t="n">
-        <v>0.03</v>
+        <v>0.06</v>
       </c>
       <c r="DJ9" t="n">
         <v>3</v>
@@ -4542,25 +4542,25 @@
         <v>4.87</v>
       </c>
       <c r="DL9" t="n">
-        <v>0.48</v>
+        <v>0.46</v>
       </c>
       <c r="DM9" t="n">
-        <v>42.1</v>
+        <v>43</v>
       </c>
       <c r="DN9" t="n">
         <v>0.9</v>
       </c>
       <c r="DO9" t="n">
-        <v>2.24</v>
+        <v>2.2</v>
       </c>
       <c r="DP9" t="n">
-        <v>15.62</v>
+        <v>15.46</v>
       </c>
       <c r="DQ9" t="n">
-        <v>11.45</v>
+        <v>11.44</v>
       </c>
       <c r="DR9" t="n">
-        <v>8.449999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="DS9" t="n">
         <v>0.1</v>
@@ -4572,28 +4572,28 @@
         <v>0</v>
       </c>
       <c r="DV9" t="n">
-        <v>44.96</v>
+        <v>45.23</v>
       </c>
       <c r="DW9" t="n">
         <v>0.04</v>
       </c>
       <c r="DX9" t="n">
-        <v>13.65</v>
+        <v>13.76</v>
       </c>
       <c r="DY9" t="n">
-        <v>9.31</v>
+        <v>9.44</v>
       </c>
       <c r="DZ9" t="n">
-        <v>4.35</v>
+        <v>4.34</v>
       </c>
       <c r="EA9" t="n">
-        <v>19.83</v>
+        <v>19.87</v>
       </c>
       <c r="EB9" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="EC9" t="n">
-        <v>2.97</v>
+        <v>2.96</v>
       </c>
     </row>
     <row r="10">
@@ -4603,10 +4603,10 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C10" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D10" t="n">
         <v>15</v>
@@ -4615,49 +4615,49 @@
         <v>0</v>
       </c>
       <c r="F10" t="n">
-        <v>0.79</v>
+        <v>0.87</v>
       </c>
       <c r="G10" t="n">
-        <v>3.29</v>
+        <v>3.4</v>
       </c>
       <c r="H10" t="n">
-        <v>85.29000000000001</v>
+        <v>87.06999999999999</v>
       </c>
       <c r="I10" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="J10" t="n">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="K10" t="n">
-        <v>5.79</v>
+        <v>6.07</v>
       </c>
       <c r="L10" t="n">
-        <v>0.29</v>
+        <v>0.33</v>
       </c>
       <c r="M10" t="n">
-        <v>45.93</v>
+        <v>46.2</v>
       </c>
       <c r="N10" t="n">
-        <v>0.71</v>
+        <v>0.67</v>
       </c>
       <c r="O10" t="n">
-        <v>2.5</v>
+        <v>2.67</v>
       </c>
       <c r="P10" t="n">
-        <v>11.07</v>
+        <v>10.93</v>
       </c>
       <c r="Q10" t="n">
-        <v>12.57</v>
+        <v>12.33</v>
       </c>
       <c r="R10" t="n">
-        <v>7.86</v>
+        <v>7.6</v>
       </c>
       <c r="S10" t="n">
-        <v>0.79</v>
+        <v>1.07</v>
       </c>
       <c r="T10" t="n">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="U10" t="n">
         <v>0</v>
@@ -4669,28 +4669,28 @@
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>39.43</v>
+        <v>39.8</v>
       </c>
       <c r="Y10" t="n">
         <v>0.07000000000000001</v>
       </c>
       <c r="Z10" t="n">
-        <v>10.71</v>
+        <v>11.2</v>
       </c>
       <c r="AA10" t="n">
-        <v>7.36</v>
+        <v>7.53</v>
       </c>
       <c r="AB10" t="n">
-        <v>3.36</v>
+        <v>3.67</v>
       </c>
       <c r="AC10" t="n">
-        <v>22.36</v>
+        <v>22.8</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.21</v>
+        <v>1.26</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.43</v>
+        <v>1.47</v>
       </c>
       <c r="AF10" t="n">
         <v>0.2</v>
@@ -4774,67 +4774,67 @@
         <v>2.33</v>
       </c>
       <c r="BG10" t="n">
-        <v>1.97</v>
+        <v>2.23</v>
       </c>
       <c r="BH10" t="n">
-        <v>9.140000000000001</v>
+        <v>9.27</v>
       </c>
       <c r="BI10" t="n">
-        <v>1.97</v>
+        <v>2.23</v>
       </c>
       <c r="BJ10" t="n">
-        <v>0.48</v>
+        <v>0.53</v>
       </c>
       <c r="BK10" t="n">
-        <v>0.38</v>
+        <v>0.47</v>
       </c>
       <c r="BL10" t="n">
-        <v>0.48</v>
+        <v>0.57</v>
       </c>
       <c r="BM10" t="n">
-        <v>0.62</v>
+        <v>0.67</v>
       </c>
       <c r="BN10" t="n">
-        <v>1.1</v>
+        <v>1.23</v>
       </c>
       <c r="BO10" t="n">
-        <v>0.86</v>
+        <v>1</v>
       </c>
       <c r="BP10" t="n">
-        <v>4.07</v>
+        <v>4.13</v>
       </c>
       <c r="BQ10" t="n">
-        <v>5.07</v>
+        <v>5.13</v>
       </c>
       <c r="BR10" t="n">
-        <v>72.41</v>
+        <v>73.33</v>
       </c>
       <c r="BS10" t="n">
-        <v>58.62</v>
+        <v>60</v>
       </c>
       <c r="BT10" t="n">
-        <v>41.38</v>
+        <v>43.33</v>
       </c>
       <c r="BU10" t="n">
-        <v>17.24</v>
+        <v>20</v>
       </c>
       <c r="BV10" t="n">
-        <v>6.9</v>
+        <v>10</v>
       </c>
       <c r="BW10" t="n">
-        <v>0</v>
+        <v>3.33</v>
       </c>
       <c r="BX10" t="n">
-        <v>51.72</v>
+        <v>53.33</v>
       </c>
       <c r="BY10" t="n">
-        <v>3.24</v>
+        <v>3.25</v>
       </c>
       <c r="BZ10" t="n">
-        <v>3.32</v>
+        <v>3.3</v>
       </c>
       <c r="CA10" t="n">
-        <v>3.52</v>
+        <v>3.53</v>
       </c>
       <c r="CB10" t="n">
         <v>3.61</v>
@@ -4849,19 +4849,19 @@
         <v>1.39</v>
       </c>
       <c r="CF10" t="n">
-        <v>2.82</v>
+        <v>2.81</v>
       </c>
       <c r="CG10" t="n">
-        <v>2.84</v>
+        <v>2.85</v>
       </c>
       <c r="CH10" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="CI10" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="CJ10" t="n">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="CK10" t="n">
         <v>1.56</v>
@@ -4879,25 +4879,25 @@
         <v>1.31</v>
       </c>
       <c r="CP10" t="n">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="CQ10" t="n">
-        <v>3.52</v>
+        <v>3.49</v>
       </c>
       <c r="CR10" t="n">
         <v>1.4</v>
       </c>
       <c r="CS10" t="n">
-        <v>2.92</v>
+        <v>2.91</v>
       </c>
       <c r="CT10" t="n">
-        <v>3.02</v>
+        <v>3.03</v>
       </c>
       <c r="CU10" t="n">
         <v>1.43</v>
       </c>
       <c r="CV10" t="n">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="CW10" t="n">
         <v>1.88</v>
@@ -4909,31 +4909,31 @@
         <v>1.96</v>
       </c>
       <c r="CZ10" t="n">
-        <v>2.33</v>
+        <v>2.34</v>
       </c>
       <c r="DA10" t="n">
         <v>1.86</v>
       </c>
       <c r="DB10" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="DC10" t="n">
-        <v>2.08</v>
+        <v>2.07</v>
       </c>
       <c r="DD10" t="n">
-        <v>3.62</v>
+        <v>3.6</v>
       </c>
       <c r="DE10" t="n">
         <v>0.1</v>
       </c>
       <c r="DF10" t="n">
-        <v>1.21</v>
+        <v>1.23</v>
       </c>
       <c r="DG10" t="n">
-        <v>2.79</v>
+        <v>2.86</v>
       </c>
       <c r="DH10" t="n">
-        <v>84.20999999999999</v>
+        <v>85.14</v>
       </c>
       <c r="DI10" t="n">
         <v>0.1</v>
@@ -4942,28 +4942,28 @@
         <v>2.04</v>
       </c>
       <c r="DK10" t="n">
-        <v>4.76</v>
+        <v>4.94</v>
       </c>
       <c r="DL10" t="n">
-        <v>0.24</v>
+        <v>0.26</v>
       </c>
       <c r="DM10" t="n">
-        <v>40.86</v>
+        <v>41.16</v>
       </c>
       <c r="DN10" t="n">
-        <v>0.76</v>
+        <v>0.74</v>
       </c>
       <c r="DO10" t="n">
-        <v>1.97</v>
+        <v>2.07</v>
       </c>
       <c r="DP10" t="n">
-        <v>11.51</v>
+        <v>11.43</v>
       </c>
       <c r="DQ10" t="n">
-        <v>12.45</v>
+        <v>12.33</v>
       </c>
       <c r="DR10" t="n">
-        <v>8.380000000000001</v>
+        <v>8.24</v>
       </c>
       <c r="DS10" t="n">
         <v>0.04</v>
@@ -4975,25 +4975,25 @@
         <v>0</v>
       </c>
       <c r="DV10" t="n">
-        <v>36.97</v>
+        <v>37.24</v>
       </c>
       <c r="DW10" t="n">
         <v>0.07000000000000001</v>
       </c>
       <c r="DX10" t="n">
-        <v>10</v>
+        <v>10.26</v>
       </c>
       <c r="DY10" t="n">
-        <v>7.07</v>
+        <v>7.16</v>
       </c>
       <c r="DZ10" t="n">
-        <v>2.93</v>
+        <v>3.1</v>
       </c>
       <c r="EA10" t="n">
-        <v>21.72</v>
+        <v>21.96</v>
       </c>
       <c r="EB10" t="n">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="EC10" t="n">
         <v>1.9</v>
@@ -5006,10 +5006,10 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C11" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D11" t="n">
         <v>15</v>
@@ -5018,82 +5018,82 @@
         <v>0.07000000000000001</v>
       </c>
       <c r="F11" t="n">
-        <v>1.71</v>
+        <v>1.67</v>
       </c>
       <c r="G11" t="n">
-        <v>3.29</v>
+        <v>3.47</v>
       </c>
       <c r="H11" t="n">
-        <v>109.57</v>
+        <v>112.27</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
       </c>
       <c r="J11" t="n">
-        <v>2.64</v>
+        <v>2.53</v>
       </c>
       <c r="K11" t="n">
-        <v>6.79</v>
+        <v>6.87</v>
       </c>
       <c r="L11" t="n">
-        <v>0.71</v>
+        <v>0.67</v>
       </c>
       <c r="M11" t="n">
-        <v>58.71</v>
+        <v>60</v>
       </c>
       <c r="N11" t="n">
-        <v>0.86</v>
+        <v>0.8</v>
       </c>
       <c r="O11" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="P11" t="n">
-        <v>13.21</v>
+        <v>13.2</v>
       </c>
       <c r="Q11" t="n">
-        <v>11.79</v>
+        <v>11.73</v>
       </c>
       <c r="R11" t="n">
-        <v>7.29</v>
+        <v>7.27</v>
       </c>
       <c r="S11" t="n">
-        <v>0.79</v>
+        <v>0.93</v>
       </c>
       <c r="T11" t="n">
-        <v>1.64</v>
+        <v>1.67</v>
       </c>
       <c r="U11" t="n">
-        <v>0.21</v>
+        <v>0.2</v>
       </c>
       <c r="V11" t="n">
-        <v>0.21</v>
+        <v>0.2</v>
       </c>
       <c r="W11" t="n">
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>53.5</v>
+        <v>54.67</v>
       </c>
       <c r="Y11" t="n">
         <v>0.07000000000000001</v>
       </c>
       <c r="Z11" t="n">
-        <v>17</v>
+        <v>16.93</v>
       </c>
       <c r="AA11" t="n">
-        <v>11.57</v>
+        <v>11.33</v>
       </c>
       <c r="AB11" t="n">
-        <v>5.43</v>
+        <v>5.6</v>
       </c>
       <c r="AC11" t="n">
-        <v>20.86</v>
+        <v>21.2</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.88</v>
+        <v>1.9</v>
       </c>
       <c r="AE11" t="n">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="AF11" t="n">
         <v>0.13</v>
@@ -5177,64 +5177,64 @@
         <v>2.73</v>
       </c>
       <c r="BG11" t="n">
-        <v>2.66</v>
+        <v>2.73</v>
       </c>
       <c r="BH11" t="n">
-        <v>11.03</v>
+        <v>11.17</v>
       </c>
       <c r="BI11" t="n">
-        <v>2.66</v>
+        <v>2.73</v>
       </c>
       <c r="BJ11" t="n">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="BK11" t="n">
-        <v>0.48</v>
+        <v>0.57</v>
       </c>
       <c r="BL11" t="n">
         <v>1.03</v>
       </c>
       <c r="BM11" t="n">
-        <v>0.52</v>
+        <v>0.5</v>
       </c>
       <c r="BN11" t="n">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="BO11" t="n">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="BP11" t="n">
-        <v>5.48</v>
+        <v>5.53</v>
       </c>
       <c r="BQ11" t="n">
-        <v>5.55</v>
+        <v>5.63</v>
       </c>
       <c r="BR11" t="n">
-        <v>89.66</v>
+        <v>90</v>
       </c>
       <c r="BS11" t="n">
-        <v>65.52</v>
+        <v>66.67</v>
       </c>
       <c r="BT11" t="n">
-        <v>41.38</v>
+        <v>43.33</v>
       </c>
       <c r="BU11" t="n">
-        <v>34.48</v>
+        <v>36.67</v>
       </c>
       <c r="BV11" t="n">
-        <v>17.24</v>
+        <v>20</v>
       </c>
       <c r="BW11" t="n">
-        <v>13.79</v>
+        <v>13.33</v>
       </c>
       <c r="BX11" t="n">
-        <v>44.83</v>
+        <v>46.67</v>
       </c>
       <c r="BY11" t="n">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="BZ11" t="n">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="CA11" t="n">
         <v>3.61</v>
@@ -5252,7 +5252,7 @@
         <v>1.33</v>
       </c>
       <c r="CF11" t="n">
-        <v>2.56</v>
+        <v>2.55</v>
       </c>
       <c r="CG11" t="n">
         <v>3.07</v>
@@ -5261,7 +5261,7 @@
         <v>1.47</v>
       </c>
       <c r="CI11" t="n">
-        <v>2.11</v>
+        <v>2.12</v>
       </c>
       <c r="CJ11" t="n">
         <v>1.69</v>
@@ -5273,10 +5273,10 @@
         <v>1.89</v>
       </c>
       <c r="CM11" t="n">
-        <v>2.54</v>
+        <v>2.56</v>
       </c>
       <c r="CN11" t="n">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="CO11" t="n">
         <v>1.24</v>
@@ -5285,7 +5285,7 @@
         <v>1.79</v>
       </c>
       <c r="CQ11" t="n">
-        <v>2.94</v>
+        <v>2.93</v>
       </c>
       <c r="CR11" t="n">
         <v>1.36</v>
@@ -5300,73 +5300,73 @@
         <v>1.49</v>
       </c>
       <c r="CV11" t="n">
-        <v>2.19</v>
+        <v>2.2</v>
       </c>
       <c r="CW11" t="n">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="CX11" t="n">
         <v>1.51</v>
       </c>
       <c r="CY11" t="n">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="CZ11" t="n">
         <v>2.52</v>
       </c>
       <c r="DA11" t="n">
-        <v>2.01</v>
+        <v>2.03</v>
       </c>
       <c r="DB11" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="DC11" t="n">
         <v>1.85</v>
       </c>
       <c r="DD11" t="n">
-        <v>3.09</v>
+        <v>3.08</v>
       </c>
       <c r="DE11" t="n">
         <v>0.1</v>
       </c>
       <c r="DF11" t="n">
-        <v>1.76</v>
+        <v>1.74</v>
       </c>
       <c r="DG11" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="DH11" t="n">
-        <v>102.07</v>
+        <v>103.67</v>
       </c>
       <c r="DI11" t="n">
         <v>0</v>
       </c>
       <c r="DJ11" t="n">
-        <v>2.79</v>
+        <v>2.73</v>
       </c>
       <c r="DK11" t="n">
-        <v>6.21</v>
+        <v>6.27</v>
       </c>
       <c r="DL11" t="n">
-        <v>0.48</v>
+        <v>0.47</v>
       </c>
       <c r="DM11" t="n">
-        <v>55.41</v>
+        <v>56.16</v>
       </c>
       <c r="DN11" t="n">
-        <v>1</v>
+        <v>0.96</v>
       </c>
       <c r="DO11" t="n">
-        <v>3.21</v>
+        <v>3.16</v>
       </c>
       <c r="DP11" t="n">
-        <v>14.07</v>
+        <v>14.03</v>
       </c>
       <c r="DQ11" t="n">
-        <v>10.59</v>
+        <v>10.6</v>
       </c>
       <c r="DR11" t="n">
-        <v>8</v>
+        <v>7.97</v>
       </c>
       <c r="DS11" t="n">
         <v>0.2</v>
@@ -5378,28 +5378,28 @@
         <v>0</v>
       </c>
       <c r="DV11" t="n">
-        <v>53.34</v>
+        <v>53.94</v>
       </c>
       <c r="DW11" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DX11" t="n">
-        <v>14.89</v>
+        <v>14.93</v>
       </c>
       <c r="DY11" t="n">
-        <v>10.17</v>
+        <v>10.1</v>
       </c>
       <c r="DZ11" t="n">
-        <v>4.73</v>
+        <v>4.84</v>
       </c>
       <c r="EA11" t="n">
-        <v>20.93</v>
+        <v>21.1</v>
       </c>
       <c r="EB11" t="n">
-        <v>1.67</v>
+        <v>1.69</v>
       </c>
       <c r="EC11" t="n">
-        <v>2.62</v>
+        <v>2.56</v>
       </c>
     </row>
     <row r="12">
@@ -5409,13 +5409,13 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C12" t="n">
         <v>15</v>
       </c>
       <c r="D12" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E12" t="n">
         <v>0.07000000000000001</v>
@@ -5502,49 +5502,49 @@
         <v>0</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.43</v>
+        <v>1.53</v>
       </c>
       <c r="AH12" t="n">
-        <v>2.21</v>
+        <v>2.13</v>
       </c>
       <c r="AI12" t="n">
-        <v>94.93000000000001</v>
+        <v>93.59999999999999</v>
       </c>
       <c r="AJ12" t="n">
         <v>0.07000000000000001</v>
       </c>
       <c r="AK12" t="n">
-        <v>1.93</v>
+        <v>2.13</v>
       </c>
       <c r="AL12" t="n">
-        <v>3.36</v>
+        <v>3.47</v>
       </c>
       <c r="AM12" t="n">
-        <v>0.29</v>
+        <v>0.27</v>
       </c>
       <c r="AN12" t="n">
-        <v>36.79</v>
+        <v>36.2</v>
       </c>
       <c r="AO12" t="n">
-        <v>0.43</v>
+        <v>0.53</v>
       </c>
       <c r="AP12" t="n">
-        <v>1.14</v>
+        <v>1.33</v>
       </c>
       <c r="AQ12" t="n">
-        <v>13.64</v>
+        <v>13.47</v>
       </c>
       <c r="AR12" t="n">
-        <v>11.71</v>
+        <v>11.67</v>
       </c>
       <c r="AS12" t="n">
-        <v>8.07</v>
+        <v>8.4</v>
       </c>
       <c r="AT12" t="n">
         <v>0.93</v>
       </c>
       <c r="AU12" t="n">
-        <v>0.71</v>
+        <v>0.67</v>
       </c>
       <c r="AV12" t="n">
         <v>0.07000000000000001</v>
@@ -5556,73 +5556,73 @@
         <v>0</v>
       </c>
       <c r="AY12" t="n">
-        <v>46.5</v>
+        <v>46.53</v>
       </c>
       <c r="AZ12" t="n">
-        <v>0.14</v>
+        <v>0.2</v>
       </c>
       <c r="BA12" t="n">
-        <v>9.789999999999999</v>
+        <v>9.470000000000001</v>
       </c>
       <c r="BB12" t="n">
-        <v>6.21</v>
+        <v>6.13</v>
       </c>
       <c r="BC12" t="n">
-        <v>3.57</v>
+        <v>3.33</v>
       </c>
       <c r="BD12" t="n">
-        <v>20.57</v>
+        <v>20.73</v>
       </c>
       <c r="BE12" t="n">
-        <v>1.14</v>
+        <v>1.1</v>
       </c>
       <c r="BF12" t="n">
-        <v>1.71</v>
+        <v>1.87</v>
       </c>
       <c r="BG12" t="n">
-        <v>2.14</v>
+        <v>2.1</v>
       </c>
       <c r="BH12" t="n">
-        <v>9.07</v>
+        <v>9.1</v>
       </c>
       <c r="BI12" t="n">
-        <v>2.14</v>
+        <v>2.1</v>
       </c>
       <c r="BJ12" t="n">
-        <v>0.62</v>
+        <v>0.6</v>
       </c>
       <c r="BK12" t="n">
-        <v>0.41</v>
+        <v>0.4</v>
       </c>
       <c r="BL12" t="n">
-        <v>0.55</v>
+        <v>0.57</v>
       </c>
       <c r="BM12" t="n">
-        <v>0.55</v>
+        <v>0.53</v>
       </c>
       <c r="BN12" t="n">
         <v>1.1</v>
       </c>
       <c r="BO12" t="n">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="BP12" t="n">
-        <v>3.93</v>
+        <v>3.97</v>
       </c>
       <c r="BQ12" t="n">
         <v>5.1</v>
       </c>
       <c r="BR12" t="n">
-        <v>93.09999999999999</v>
+        <v>93.33</v>
       </c>
       <c r="BS12" t="n">
-        <v>72.41</v>
+        <v>70</v>
       </c>
       <c r="BT12" t="n">
-        <v>34.48</v>
+        <v>33.33</v>
       </c>
       <c r="BU12" t="n">
-        <v>13.79</v>
+        <v>13.33</v>
       </c>
       <c r="BV12" t="n">
         <v>0</v>
@@ -5631,7 +5631,7 @@
         <v>0</v>
       </c>
       <c r="BX12" t="n">
-        <v>44.83</v>
+        <v>43.33</v>
       </c>
       <c r="BY12" t="n">
         <v>2.68</v>
@@ -5643,13 +5643,13 @@
         <v>3.51</v>
       </c>
       <c r="CB12" t="n">
-        <v>3.63</v>
+        <v>3.62</v>
       </c>
       <c r="CC12" t="n">
-        <v>4.1</v>
+        <v>4.06</v>
       </c>
       <c r="CD12" t="n">
-        <v>4.62</v>
+        <v>4.57</v>
       </c>
       <c r="CE12" t="n">
         <v>1.35</v>
@@ -5658,13 +5658,13 @@
         <v>2.65</v>
       </c>
       <c r="CG12" t="n">
-        <v>2.99</v>
+        <v>2.98</v>
       </c>
       <c r="CH12" t="n">
         <v>1.44</v>
       </c>
       <c r="CI12" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="CJ12" t="n">
         <v>1.72</v>
@@ -5673,7 +5673,7 @@
         <v>1.5</v>
       </c>
       <c r="CL12" t="n">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="CM12" t="n">
         <v>2.42</v>
@@ -5733,43 +5733,43 @@
         <v>0.04</v>
       </c>
       <c r="DF12" t="n">
-        <v>1.31</v>
+        <v>1.36</v>
       </c>
       <c r="DG12" t="n">
-        <v>2.24</v>
+        <v>2.2</v>
       </c>
       <c r="DH12" t="n">
-        <v>95.20999999999999</v>
+        <v>94.54000000000001</v>
       </c>
       <c r="DI12" t="n">
         <v>0.07000000000000001</v>
       </c>
       <c r="DJ12" t="n">
-        <v>2.03</v>
+        <v>2.13</v>
       </c>
       <c r="DK12" t="n">
-        <v>4</v>
+        <v>4.04</v>
       </c>
       <c r="DL12" t="n">
-        <v>0.41</v>
+        <v>0.4</v>
       </c>
       <c r="DM12" t="n">
-        <v>39.66</v>
+        <v>39.26</v>
       </c>
       <c r="DN12" t="n">
-        <v>0.66</v>
+        <v>0.7</v>
       </c>
       <c r="DO12" t="n">
-        <v>1.72</v>
+        <v>1.8</v>
       </c>
       <c r="DP12" t="n">
-        <v>12.9</v>
+        <v>12.84</v>
       </c>
       <c r="DQ12" t="n">
-        <v>11.82</v>
+        <v>11.8</v>
       </c>
       <c r="DR12" t="n">
-        <v>7.79</v>
+        <v>7.96</v>
       </c>
       <c r="DS12" t="n">
         <v>0.17</v>
@@ -5781,28 +5781,28 @@
         <v>0</v>
       </c>
       <c r="DV12" t="n">
-        <v>47.42</v>
+        <v>47.4</v>
       </c>
       <c r="DW12" t="n">
-        <v>0.13</v>
+        <v>0.16</v>
       </c>
       <c r="DX12" t="n">
-        <v>11.07</v>
+        <v>10.87</v>
       </c>
       <c r="DY12" t="n">
-        <v>6.86</v>
+        <v>6.8</v>
       </c>
       <c r="DZ12" t="n">
-        <v>4.21</v>
+        <v>4.07</v>
       </c>
       <c r="EA12" t="n">
-        <v>20.52</v>
+        <v>20.6</v>
       </c>
       <c r="EB12" t="n">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="EC12" t="n">
-        <v>1.82</v>
+        <v>1.9</v>
       </c>
     </row>
     <row r="13">
@@ -5812,94 +5812,94 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C13" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D13" t="n">
         <v>15</v>
       </c>
       <c r="E13" t="n">
-        <v>0.21</v>
+        <v>0.2</v>
       </c>
       <c r="F13" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="G13" t="n">
-        <v>3.5</v>
+        <v>3.47</v>
       </c>
       <c r="H13" t="n">
-        <v>102.5</v>
+        <v>102.53</v>
       </c>
       <c r="I13" t="n">
-        <v>0</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="J13" t="n">
-        <v>2.14</v>
+        <v>2</v>
       </c>
       <c r="K13" t="n">
-        <v>5.36</v>
+        <v>5.33</v>
       </c>
       <c r="L13" t="n">
-        <v>0.29</v>
+        <v>0.27</v>
       </c>
       <c r="M13" t="n">
-        <v>55.93</v>
+        <v>56.6</v>
       </c>
       <c r="N13" t="n">
-        <v>0.5</v>
+        <v>0.47</v>
       </c>
       <c r="O13" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="P13" t="n">
-        <v>10.43</v>
+        <v>9.869999999999999</v>
       </c>
       <c r="Q13" t="n">
-        <v>11.79</v>
+        <v>11.27</v>
       </c>
       <c r="R13" t="n">
-        <v>6.43</v>
+        <v>6.4</v>
       </c>
       <c r="S13" t="n">
-        <v>1.14</v>
+        <v>1.27</v>
       </c>
       <c r="T13" t="n">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="U13" t="n">
-        <v>0.21</v>
+        <v>0.2</v>
       </c>
       <c r="V13" t="n">
-        <v>0.21</v>
+        <v>0.2</v>
       </c>
       <c r="W13" t="n">
         <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>54</v>
+        <v>54.33</v>
       </c>
       <c r="Y13" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="Z13" t="n">
-        <v>15.43</v>
+        <v>15</v>
       </c>
       <c r="AA13" t="n">
-        <v>10.43</v>
+        <v>10.2</v>
       </c>
       <c r="AB13" t="n">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="AC13" t="n">
-        <v>23</v>
+        <v>22.93</v>
       </c>
       <c r="AD13" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="AE13" t="n">
         <v>1.73</v>
-      </c>
-      <c r="AE13" t="n">
-        <v>1.86</v>
       </c>
       <c r="AF13" t="n">
         <v>0.07000000000000001</v>
@@ -5983,70 +5983,70 @@
         <v>1.53</v>
       </c>
       <c r="BG13" t="n">
-        <v>2.69</v>
+        <v>2.73</v>
       </c>
       <c r="BH13" t="n">
         <v>10.1</v>
       </c>
       <c r="BI13" t="n">
-        <v>2.69</v>
+        <v>2.73</v>
       </c>
       <c r="BJ13" t="n">
-        <v>0.72</v>
+        <v>0.7</v>
       </c>
       <c r="BK13" t="n">
-        <v>0.55</v>
+        <v>0.6</v>
       </c>
       <c r="BL13" t="n">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="BM13" t="n">
         <v>0.83</v>
       </c>
       <c r="BN13" t="n">
-        <v>1.41</v>
+        <v>1.43</v>
       </c>
       <c r="BO13" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="BP13" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="BQ13" t="n">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="BR13" t="n">
         <v>100</v>
       </c>
       <c r="BS13" t="n">
-        <v>79.31</v>
+        <v>80</v>
       </c>
       <c r="BT13" t="n">
-        <v>55.17</v>
+        <v>56.67</v>
       </c>
       <c r="BU13" t="n">
-        <v>24.14</v>
+        <v>26.67</v>
       </c>
       <c r="BV13" t="n">
-        <v>10.34</v>
+        <v>10</v>
       </c>
       <c r="BW13" t="n">
         <v>0</v>
       </c>
       <c r="BX13" t="n">
-        <v>55.17</v>
+        <v>56.67</v>
       </c>
       <c r="BY13" t="n">
-        <v>2.2</v>
+        <v>2.28</v>
       </c>
       <c r="BZ13" t="n">
-        <v>2.27</v>
+        <v>2.33</v>
       </c>
       <c r="CA13" t="n">
-        <v>3.65</v>
+        <v>3.63</v>
       </c>
       <c r="CB13" t="n">
-        <v>3.78</v>
+        <v>3.76</v>
       </c>
       <c r="CC13" t="n">
         <v>3.45</v>
@@ -6055,28 +6055,28 @@
         <v>3.68</v>
       </c>
       <c r="CE13" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="CF13" t="n">
-        <v>2.48</v>
+        <v>2.49</v>
       </c>
       <c r="CG13" t="n">
-        <v>3.17</v>
+        <v>3.15</v>
       </c>
       <c r="CH13" t="n">
         <v>1.5</v>
       </c>
       <c r="CI13" t="n">
-        <v>2.18</v>
+        <v>2.17</v>
       </c>
       <c r="CJ13" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="CK13" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="CL13" t="n">
-        <v>1.89</v>
+        <v>1.91</v>
       </c>
       <c r="CM13" t="n">
         <v>2.5</v>
@@ -6088,31 +6088,31 @@
         <v>1.22</v>
       </c>
       <c r="CP13" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="CQ13" t="n">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="CR13" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="CS13" t="n">
-        <v>2.63</v>
+        <v>2.65</v>
       </c>
       <c r="CT13" t="n">
-        <v>3.24</v>
+        <v>3.22</v>
       </c>
       <c r="CU13" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="CV13" t="n">
-        <v>2.32</v>
+        <v>2.31</v>
       </c>
       <c r="CW13" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="CX13" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="CY13" t="n">
         <v>1.85</v>
@@ -6121,58 +6121,58 @@
         <v>2.43</v>
       </c>
       <c r="DA13" t="n">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="DB13" t="n">
         <v>1.24</v>
       </c>
       <c r="DC13" t="n">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="DD13" t="n">
-        <v>2.87</v>
+        <v>2.89</v>
       </c>
       <c r="DE13" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DF13" t="n">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="DG13" t="n">
-        <v>3.45</v>
+        <v>3.44</v>
       </c>
       <c r="DH13" t="n">
-        <v>101.58</v>
+        <v>101.63</v>
       </c>
       <c r="DI13" t="n">
-        <v>0.1</v>
+        <v>0.06</v>
       </c>
       <c r="DJ13" t="n">
-        <v>1.82</v>
+        <v>1.76</v>
       </c>
       <c r="DK13" t="n">
-        <v>5.55</v>
+        <v>5.53</v>
       </c>
       <c r="DL13" t="n">
-        <v>0.41</v>
+        <v>0.4</v>
       </c>
       <c r="DM13" t="n">
-        <v>55.45</v>
+        <v>55.8</v>
       </c>
       <c r="DN13" t="n">
-        <v>0.59</v>
+        <v>0.57</v>
       </c>
       <c r="DO13" t="n">
         <v>2.1</v>
       </c>
       <c r="DP13" t="n">
-        <v>10.97</v>
+        <v>10.67</v>
       </c>
       <c r="DQ13" t="n">
-        <v>11.42</v>
+        <v>11.17</v>
       </c>
       <c r="DR13" t="n">
-        <v>7.52</v>
+        <v>7.46</v>
       </c>
       <c r="DS13" t="n">
         <v>0.24</v>
@@ -6184,28 +6184,28 @@
         <v>0</v>
       </c>
       <c r="DV13" t="n">
-        <v>54.93</v>
+        <v>55.06</v>
       </c>
       <c r="DW13" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="DX13" t="n">
-        <v>14.21</v>
+        <v>14.04</v>
       </c>
       <c r="DY13" t="n">
-        <v>9.73</v>
+        <v>9.640000000000001</v>
       </c>
       <c r="DZ13" t="n">
-        <v>4.48</v>
+        <v>4.4</v>
       </c>
       <c r="EA13" t="n">
-        <v>22.21</v>
+        <v>22.2</v>
       </c>
       <c r="EB13" t="n">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="EC13" t="n">
-        <v>1.69</v>
+        <v>1.63</v>
       </c>
     </row>
     <row r="14">
@@ -6215,13 +6215,13 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C14" t="n">
         <v>15</v>
       </c>
       <c r="D14" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E14" t="n">
         <v>0.13</v>
@@ -6305,16 +6305,16 @@
         <v>1.87</v>
       </c>
       <c r="AF14" t="n">
-        <v>0.21</v>
+        <v>0.2</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="AH14" t="n">
-        <v>2.79</v>
+        <v>3.13</v>
       </c>
       <c r="AI14" t="n">
-        <v>93.29000000000001</v>
+        <v>94.06999999999999</v>
       </c>
       <c r="AJ14" t="n">
         <v>-0.07000000000000001</v>
@@ -6323,34 +6323,34 @@
         <v>2.07</v>
       </c>
       <c r="AL14" t="n">
-        <v>5.29</v>
+        <v>5.6</v>
       </c>
       <c r="AM14" t="n">
-        <v>0.71</v>
+        <v>0.67</v>
       </c>
       <c r="AN14" t="n">
-        <v>48.07</v>
+        <v>48.67</v>
       </c>
       <c r="AO14" t="n">
-        <v>0.57</v>
+        <v>0.6</v>
       </c>
       <c r="AP14" t="n">
-        <v>2.43</v>
+        <v>2.4</v>
       </c>
       <c r="AQ14" t="n">
-        <v>12</v>
+        <v>11.73</v>
       </c>
       <c r="AR14" t="n">
-        <v>9.5</v>
+        <v>9.33</v>
       </c>
       <c r="AS14" t="n">
-        <v>7.64</v>
+        <v>7.4</v>
       </c>
       <c r="AT14" t="n">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="AU14" t="n">
-        <v>1.29</v>
+        <v>1.2</v>
       </c>
       <c r="AV14" t="n">
         <v>0.07000000000000001</v>
@@ -6362,22 +6362,22 @@
         <v>0</v>
       </c>
       <c r="AY14" t="n">
-        <v>48.43</v>
+        <v>49.4</v>
       </c>
       <c r="AZ14" t="n">
         <v>0</v>
       </c>
       <c r="BA14" t="n">
-        <v>12.43</v>
+        <v>12.4</v>
       </c>
       <c r="BB14" t="n">
-        <v>8.5</v>
+        <v>8.470000000000001</v>
       </c>
       <c r="BC14" t="n">
         <v>3.93</v>
       </c>
       <c r="BD14" t="n">
-        <v>20.71</v>
+        <v>20.67</v>
       </c>
       <c r="BE14" t="n">
         <v>1.41</v>
@@ -6386,58 +6386,58 @@
         <v>2.07</v>
       </c>
       <c r="BG14" t="n">
-        <v>2.72</v>
+        <v>2.67</v>
       </c>
       <c r="BH14" t="n">
-        <v>10.24</v>
+        <v>10.37</v>
       </c>
       <c r="BI14" t="n">
-        <v>2.72</v>
+        <v>2.67</v>
       </c>
       <c r="BJ14" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.7</v>
       </c>
       <c r="BK14" t="n">
-        <v>0.72</v>
+        <v>0.7</v>
       </c>
       <c r="BL14" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.67</v>
       </c>
       <c r="BM14" t="n">
-        <v>0.62</v>
+        <v>0.6</v>
       </c>
       <c r="BN14" t="n">
-        <v>1.31</v>
+        <v>1.27</v>
       </c>
       <c r="BO14" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="BP14" t="n">
-        <v>4.72</v>
+        <v>4.73</v>
       </c>
       <c r="BQ14" t="n">
-        <v>4.97</v>
+        <v>5.1</v>
       </c>
       <c r="BR14" t="n">
-        <v>96.55</v>
+        <v>96.67</v>
       </c>
       <c r="BS14" t="n">
-        <v>79.31</v>
+        <v>76.67</v>
       </c>
       <c r="BT14" t="n">
-        <v>48.28</v>
+        <v>46.67</v>
       </c>
       <c r="BU14" t="n">
-        <v>31.03</v>
+        <v>30</v>
       </c>
       <c r="BV14" t="n">
-        <v>10.34</v>
+        <v>10</v>
       </c>
       <c r="BW14" t="n">
-        <v>3.45</v>
+        <v>3.33</v>
       </c>
       <c r="BX14" t="n">
-        <v>58.62</v>
+        <v>56.67</v>
       </c>
       <c r="BY14" t="n">
         <v>2.34</v>
@@ -6446,22 +6446,22 @@
         <v>2.42</v>
       </c>
       <c r="CA14" t="n">
-        <v>3.49</v>
+        <v>3.48</v>
       </c>
       <c r="CB14" t="n">
         <v>3.53</v>
       </c>
       <c r="CC14" t="n">
-        <v>3.52</v>
+        <v>3.48</v>
       </c>
       <c r="CD14" t="n">
-        <v>3.63</v>
+        <v>3.59</v>
       </c>
       <c r="CE14" t="n">
         <v>1.36</v>
       </c>
       <c r="CF14" t="n">
-        <v>2.68</v>
+        <v>2.67</v>
       </c>
       <c r="CG14" t="n">
         <v>2.99</v>
@@ -6470,10 +6470,10 @@
         <v>1.43</v>
       </c>
       <c r="CI14" t="n">
-        <v>2.04</v>
+        <v>2.05</v>
       </c>
       <c r="CJ14" t="n">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="CK14" t="n">
         <v>1.47</v>
@@ -6482,25 +6482,25 @@
         <v>1.91</v>
       </c>
       <c r="CM14" t="n">
-        <v>2.5</v>
+        <v>2.51</v>
       </c>
       <c r="CN14" t="n">
         <v>1.92</v>
       </c>
       <c r="CO14" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="CP14" t="n">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="CQ14" t="n">
-        <v>3.13</v>
+        <v>3.12</v>
       </c>
       <c r="CR14" t="n">
         <v>1.38</v>
       </c>
       <c r="CS14" t="n">
-        <v>2.83</v>
+        <v>2.82</v>
       </c>
       <c r="CT14" t="n">
         <v>3.11</v>
@@ -6509,7 +6509,7 @@
         <v>1.45</v>
       </c>
       <c r="CV14" t="n">
-        <v>2.14</v>
+        <v>2.15</v>
       </c>
       <c r="CW14" t="n">
         <v>1.76</v>
@@ -6518,7 +6518,7 @@
         <v>1.53</v>
       </c>
       <c r="CY14" t="n">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="CZ14" t="n">
         <v>2.48</v>
@@ -6536,46 +6536,46 @@
         <v>3.32</v>
       </c>
       <c r="DE14" t="n">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
       <c r="DF14" t="n">
-        <v>1.66</v>
+        <v>1.64</v>
       </c>
       <c r="DG14" t="n">
-        <v>2.73</v>
+        <v>2.9</v>
       </c>
       <c r="DH14" t="n">
-        <v>94.48</v>
+        <v>94.84</v>
       </c>
       <c r="DI14" t="n">
-        <v>-0.03</v>
+        <v>-0.04</v>
       </c>
       <c r="DJ14" t="n">
         <v>2.2</v>
       </c>
       <c r="DK14" t="n">
-        <v>5.59</v>
+        <v>5.74</v>
       </c>
       <c r="DL14" t="n">
-        <v>0.45</v>
+        <v>0.44</v>
       </c>
       <c r="DM14" t="n">
-        <v>50.38</v>
+        <v>50.6</v>
       </c>
       <c r="DN14" t="n">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="DO14" t="n">
-        <v>2.41</v>
+        <v>2.4</v>
       </c>
       <c r="DP14" t="n">
-        <v>11.42</v>
+        <v>11.3</v>
       </c>
       <c r="DQ14" t="n">
-        <v>10.86</v>
+        <v>10.73</v>
       </c>
       <c r="DR14" t="n">
-        <v>7.58</v>
+        <v>7.46</v>
       </c>
       <c r="DS14" t="n">
         <v>0.1</v>
@@ -6587,22 +6587,22 @@
         <v>0</v>
       </c>
       <c r="DV14" t="n">
-        <v>49.28</v>
+        <v>49.74</v>
       </c>
       <c r="DW14" t="n">
         <v>0.14</v>
       </c>
       <c r="DX14" t="n">
-        <v>13.24</v>
+        <v>13.2</v>
       </c>
       <c r="DY14" t="n">
-        <v>8.789999999999999</v>
+        <v>8.77</v>
       </c>
       <c r="DZ14" t="n">
-        <v>4.45</v>
+        <v>4.43</v>
       </c>
       <c r="EA14" t="n">
-        <v>19.07</v>
+        <v>19.1</v>
       </c>
       <c r="EB14" t="n">
         <v>1.51</v>
@@ -6618,25 +6618,25 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C15" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D15" t="n">
         <v>15</v>
       </c>
       <c r="E15" t="n">
-        <v>0.21</v>
+        <v>0.2</v>
       </c>
       <c r="F15" t="n">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="G15" t="n">
-        <v>2.14</v>
+        <v>1.93</v>
       </c>
       <c r="H15" t="n">
-        <v>89.93000000000001</v>
+        <v>88.87</v>
       </c>
       <c r="I15" t="n">
         <v>0</v>
@@ -6645,67 +6645,67 @@
         <v>2.93</v>
       </c>
       <c r="K15" t="n">
-        <v>5.21</v>
+        <v>5.27</v>
       </c>
       <c r="L15" t="n">
-        <v>0.79</v>
+        <v>0.67</v>
       </c>
       <c r="M15" t="n">
-        <v>49.21</v>
+        <v>48.73</v>
       </c>
       <c r="N15" t="n">
-        <v>1.07</v>
+        <v>1</v>
       </c>
       <c r="O15" t="n">
-        <v>3.07</v>
+        <v>2.8</v>
       </c>
       <c r="P15" t="n">
-        <v>11</v>
+        <v>11.2</v>
       </c>
       <c r="Q15" t="n">
-        <v>13.07</v>
+        <v>12.6</v>
       </c>
       <c r="R15" t="n">
-        <v>9</v>
+        <v>9.27</v>
       </c>
       <c r="S15" t="n">
-        <v>1.29</v>
+        <v>1.2</v>
       </c>
       <c r="T15" t="n">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="U15" t="n">
-        <v>0.21</v>
+        <v>0.2</v>
       </c>
       <c r="V15" t="n">
-        <v>0.21</v>
+        <v>0.2</v>
       </c>
       <c r="W15" t="n">
         <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>44.36</v>
+        <v>44.53</v>
       </c>
       <c r="Y15" t="n">
-        <v>0.29</v>
+        <v>0.27</v>
       </c>
       <c r="Z15" t="n">
-        <v>10.86</v>
+        <v>10.6</v>
       </c>
       <c r="AA15" t="n">
-        <v>7.14</v>
+        <v>7.07</v>
       </c>
       <c r="AB15" t="n">
-        <v>3.71</v>
+        <v>3.53</v>
       </c>
       <c r="AC15" t="n">
-        <v>20.86</v>
+        <v>21.2</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AE15" t="n">
-        <v>2.36</v>
+        <v>2.4</v>
       </c>
       <c r="AF15" t="n">
         <v>0.13</v>
@@ -6789,49 +6789,49 @@
         <v>1.8</v>
       </c>
       <c r="BG15" t="n">
-        <v>2.14</v>
+        <v>2.07</v>
      